--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1452"/>
+  <dimension ref="A1:F1453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29452,19 +29452,39 @@
         <v>46276</v>
       </c>
       <c r="B1452" t="n">
-        <v>18.29</v>
+        <v>18.29000091552734</v>
       </c>
       <c r="C1452" t="n">
-        <v>18.64</v>
+        <v>18.63999938964844</v>
       </c>
       <c r="D1452" t="n">
-        <v>18.29</v>
+        <v>18.29000091552734</v>
       </c>
       <c r="E1452" t="n">
         <v>18.5</v>
       </c>
       <c r="F1452" t="n">
         <v>2814000</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B1453" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="C1453" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="D1453" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="E1453" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="F1453" t="n">
+        <v>4184800</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1453"/>
+  <dimension ref="A1:F1454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,16 +512,16 @@
         <v>44152</v>
       </c>
       <c r="B5" t="n">
-        <v>20.17695426940918</v>
+        <v>20.17695617675781</v>
       </c>
       <c r="C5" t="n">
-        <v>20.17695426940918</v>
+        <v>20.17695617675781</v>
       </c>
       <c r="D5" t="n">
-        <v>19.85012445790661</v>
+        <v>19.85012633435968</v>
       </c>
       <c r="E5" t="n">
-        <v>20.12888973916155</v>
+        <v>20.12889164196659</v>
       </c>
       <c r="F5" t="n">
         <v>262242</v>
@@ -572,16 +572,16 @@
         <v>44158</v>
       </c>
       <c r="B8" t="n">
-        <v>20.20579147338867</v>
+        <v>20.2057933807373</v>
       </c>
       <c r="C8" t="n">
-        <v>20.52300874747816</v>
+        <v>20.52301068477087</v>
       </c>
       <c r="D8" t="n">
-        <v>20.14811628674976</v>
+        <v>20.14811818865408</v>
       </c>
       <c r="E8" t="n">
-        <v>20.14811628674976</v>
+        <v>20.14811818865408</v>
       </c>
       <c r="F8" t="n">
         <v>79408</v>
@@ -632,16 +632,16 @@
         <v>44161</v>
       </c>
       <c r="B11" t="n">
-        <v>22.87810897827148</v>
+        <v>22.87811088562012</v>
       </c>
       <c r="C11" t="n">
-        <v>22.87810897827148</v>
+        <v>22.87811088562012</v>
       </c>
       <c r="D11" t="n">
-        <v>22.31096214463751</v>
+        <v>22.3109640047031</v>
       </c>
       <c r="E11" t="n">
-        <v>22.31096214463751</v>
+        <v>22.3109640047031</v>
       </c>
       <c r="F11" t="n">
         <v>72970</v>
@@ -652,16 +652,16 @@
         <v>44162</v>
       </c>
       <c r="B12" t="n">
-        <v>23.07036399841309</v>
+        <v>23.07036209106445</v>
       </c>
       <c r="C12" t="n">
-        <v>23.55099623037812</v>
+        <v>23.55099428329309</v>
       </c>
       <c r="D12" t="n">
-        <v>22.10909953448302</v>
+        <v>22.10909770660719</v>
       </c>
       <c r="E12" t="n">
-        <v>23.07036399841309</v>
+        <v>23.07036209106445</v>
       </c>
       <c r="F12" t="n">
         <v>72050</v>
@@ -692,16 +692,16 @@
         <v>44166</v>
       </c>
       <c r="B14" t="n">
-        <v>23.07036399841309</v>
+        <v>23.07036209106445</v>
       </c>
       <c r="C14" t="n">
-        <v>23.16649119432127</v>
+        <v>23.1664892790253</v>
       </c>
       <c r="D14" t="n">
-        <v>23.03191386956499</v>
+        <v>23.03191196539523</v>
       </c>
       <c r="E14" t="n">
-        <v>23.12803919168523</v>
+        <v>23.12803727956828</v>
       </c>
       <c r="F14" t="n">
         <v>93512</v>
@@ -792,16 +792,16 @@
         <v>44173</v>
       </c>
       <c r="B19" t="n">
-        <v>26.33866310119629</v>
+        <v>26.33866500854492</v>
       </c>
       <c r="C19" t="n">
-        <v>26.57898012603766</v>
+        <v>26.57898205078916</v>
       </c>
       <c r="D19" t="n">
-        <v>25.56965124500673</v>
+        <v>25.56965309666637</v>
       </c>
       <c r="E19" t="n">
-        <v>25.56965124500673</v>
+        <v>25.56965309666637</v>
       </c>
       <c r="F19" t="n">
         <v>126420</v>
@@ -812,16 +812,16 @@
         <v>44174</v>
       </c>
       <c r="B20" t="n">
-        <v>26.83852195739746</v>
+        <v>26.83852005004883</v>
       </c>
       <c r="C20" t="n">
-        <v>27.77095064592048</v>
+        <v>27.77094867230641</v>
       </c>
       <c r="D20" t="n">
-        <v>26.27137696749292</v>
+        <v>26.27137510044991</v>
       </c>
       <c r="E20" t="n">
-        <v>26.49246706969505</v>
+        <v>26.4924651869397</v>
       </c>
       <c r="F20" t="n">
         <v>212880</v>
@@ -892,16 +892,16 @@
         <v>44180</v>
       </c>
       <c r="B24" t="n">
-        <v>33.00984573364258</v>
+        <v>33.00984191894531</v>
       </c>
       <c r="C24" t="n">
-        <v>33.98072266755544</v>
+        <v>33.9807187406613</v>
       </c>
       <c r="D24" t="n">
-        <v>30.76048335959674</v>
+        <v>30.7604798048412</v>
       </c>
       <c r="E24" t="n">
-        <v>30.76048335959674</v>
+        <v>30.7604798048412</v>
       </c>
       <c r="F24" t="n">
         <v>887803</v>
@@ -912,16 +912,16 @@
         <v>44181</v>
       </c>
       <c r="B25" t="n">
-        <v>32.68301391601562</v>
+        <v>32.68301773071289</v>
       </c>
       <c r="C25" t="n">
-        <v>34.45173835953219</v>
+        <v>34.4517423806715</v>
       </c>
       <c r="D25" t="n">
-        <v>32.10625456033017</v>
+        <v>32.10625830770921</v>
       </c>
       <c r="E25" t="n">
-        <v>33.62505319761509</v>
+        <v>33.62505712226533</v>
       </c>
       <c r="F25" t="n">
         <v>376808</v>
@@ -932,16 +932,16 @@
         <v>44182</v>
       </c>
       <c r="B26" t="n">
-        <v>32.10625839233398</v>
+        <v>32.10625457763672</v>
       </c>
       <c r="C26" t="n">
-        <v>33.64428227520571</v>
+        <v>33.64427827776851</v>
       </c>
       <c r="D26" t="n">
-        <v>31.64484935368452</v>
+        <v>31.64484559380946</v>
       </c>
       <c r="E26" t="n">
-        <v>33.6250572108933</v>
+        <v>33.62505321574033</v>
       </c>
       <c r="F26" t="n">
         <v>258257</v>
@@ -972,16 +972,16 @@
         <v>44186</v>
       </c>
       <c r="B28" t="n">
-        <v>32.18315887451172</v>
+        <v>32.18315505981445</v>
       </c>
       <c r="C28" t="n">
-        <v>33.33667773162143</v>
+        <v>33.33667378019659</v>
       </c>
       <c r="D28" t="n">
-        <v>29.12633427792858</v>
+        <v>29.12633082555934</v>
       </c>
       <c r="E28" t="n">
-        <v>31.86594156356414</v>
+        <v>31.86593778646691</v>
       </c>
       <c r="F28" t="n">
         <v>236079</v>
@@ -992,16 +992,16 @@
         <v>44187</v>
       </c>
       <c r="B29" t="n">
-        <v>33.16364288330078</v>
+        <v>33.16364669799805</v>
       </c>
       <c r="C29" t="n">
-        <v>33.47124761081827</v>
+        <v>33.47125146089823</v>
       </c>
       <c r="D29" t="n">
-        <v>32.59649608138177</v>
+        <v>32.59649983084212</v>
       </c>
       <c r="E29" t="n">
-        <v>33.21170553641675</v>
+        <v>33.21170935664249</v>
       </c>
       <c r="F29" t="n">
         <v>167504</v>
@@ -1032,16 +1032,16 @@
         <v>44193</v>
       </c>
       <c r="B31" t="n">
-        <v>36.21085739135742</v>
+        <v>36.21085357666016</v>
       </c>
       <c r="C31" t="n">
-        <v>36.66265388599569</v>
+        <v>36.66265002370312</v>
       </c>
       <c r="D31" t="n">
-        <v>35.56681025863972</v>
+        <v>35.56680651179074</v>
       </c>
       <c r="E31" t="n">
-        <v>35.56681025863972</v>
+        <v>35.56680651179074</v>
       </c>
       <c r="F31" t="n">
         <v>451822</v>
@@ -1052,16 +1052,16 @@
         <v>44194</v>
       </c>
       <c r="B32" t="n">
-        <v>36.09550476074219</v>
+        <v>36.09550857543945</v>
       </c>
       <c r="C32" t="n">
-        <v>37.06638166531152</v>
+        <v>37.06638558261441</v>
       </c>
       <c r="D32" t="n">
-        <v>35.95131304358604</v>
+        <v>35.95131684304462</v>
       </c>
       <c r="E32" t="n">
-        <v>36.52807241705953</v>
+        <v>36.52807627747203</v>
       </c>
       <c r="F32" t="n">
         <v>337154</v>
@@ -1092,16 +1092,16 @@
         <v>44200</v>
       </c>
       <c r="B34" t="n">
-        <v>34.99966049194336</v>
+        <v>34.99966430664062</v>
       </c>
       <c r="C34" t="n">
-        <v>36.62420073506411</v>
+        <v>36.62420472682393</v>
       </c>
       <c r="D34" t="n">
-        <v>34.98043542972244</v>
+        <v>34.98043924232432</v>
       </c>
       <c r="E34" t="n">
-        <v>36.52807167638402</v>
+        <v>36.52807565766651</v>
       </c>
       <c r="F34" t="n">
         <v>331840</v>
@@ -1112,16 +1112,16 @@
         <v>44201</v>
       </c>
       <c r="B35" t="n">
-        <v>36.13395690917969</v>
+        <v>36.13395309448242</v>
       </c>
       <c r="C35" t="n">
-        <v>36.32621129362743</v>
+        <v>36.32620745863368</v>
       </c>
       <c r="D35" t="n">
-        <v>34.60554560816865</v>
+        <v>34.60554195482727</v>
       </c>
       <c r="E35" t="n">
-        <v>35.45145965313264</v>
+        <v>35.45145591048728</v>
       </c>
       <c r="F35" t="n">
         <v>328059</v>
@@ -1172,16 +1172,16 @@
         <v>44204</v>
       </c>
       <c r="B38" t="n">
-        <v>34.13452529907227</v>
+        <v>34.134521484375</v>
       </c>
       <c r="C38" t="n">
-        <v>35.75906572541368</v>
+        <v>35.75906172916622</v>
       </c>
       <c r="D38" t="n">
-        <v>34.13452529907227</v>
+        <v>34.134521484375</v>
       </c>
       <c r="E38" t="n">
-        <v>35.16308123419719</v>
+        <v>35.16307730455386</v>
       </c>
       <c r="F38" t="n">
         <v>367201</v>
@@ -1272,16 +1272,16 @@
         <v>44211</v>
       </c>
       <c r="B43" t="n">
-        <v>33.94226837158203</v>
+        <v>33.9422721862793</v>
       </c>
       <c r="C43" t="n">
-        <v>35.04772061203977</v>
+        <v>35.0477245509764</v>
       </c>
       <c r="D43" t="n">
-        <v>33.16364216523639</v>
+        <v>33.16364589242556</v>
       </c>
       <c r="E43" t="n">
-        <v>34.60554046537172</v>
+        <v>34.60554435461268</v>
       </c>
       <c r="F43" t="n">
         <v>319883</v>
@@ -1292,16 +1292,16 @@
         <v>44214</v>
       </c>
       <c r="B44" t="n">
-        <v>34.04801177978516</v>
+        <v>34.04800796508789</v>
       </c>
       <c r="C44" t="n">
-        <v>34.5094208103909</v>
+        <v>34.50941694399793</v>
       </c>
       <c r="D44" t="n">
-        <v>33.27900172554335</v>
+        <v>33.27899799700501</v>
       </c>
       <c r="E44" t="n">
-        <v>34.11529950370554</v>
+        <v>34.11529568146945</v>
       </c>
       <c r="F44" t="n">
         <v>117631</v>
@@ -1332,16 +1332,16 @@
         <v>44216</v>
       </c>
       <c r="B46" t="n">
-        <v>34.12490844726562</v>
+        <v>34.12491226196289</v>
       </c>
       <c r="C46" t="n">
-        <v>35.28803968588292</v>
+        <v>35.28804363060232</v>
       </c>
       <c r="D46" t="n">
-        <v>33.66350321275509</v>
+        <v>33.66350697587357</v>
       </c>
       <c r="E46" t="n">
-        <v>34.60554249130722</v>
+        <v>34.60554635973278</v>
       </c>
       <c r="F46" t="n">
         <v>359332</v>
@@ -1372,16 +1372,16 @@
         <v>44218</v>
       </c>
       <c r="B48" t="n">
-        <v>32.95216369628906</v>
+        <v>32.95216751098633</v>
       </c>
       <c r="C48" t="n">
-        <v>33.45202278739948</v>
+        <v>33.45202665996278</v>
       </c>
       <c r="D48" t="n">
-        <v>32.53882112897777</v>
+        <v>32.53882489582456</v>
       </c>
       <c r="E48" t="n">
-        <v>33.19248071115274</v>
+        <v>33.19248455367023</v>
       </c>
       <c r="F48" t="n">
         <v>220341</v>
@@ -1472,16 +1472,16 @@
         <v>44228</v>
       </c>
       <c r="B53" t="n">
-        <v>31.7794246673584</v>
+        <v>31.77942657470703</v>
       </c>
       <c r="C53" t="n">
-        <v>33.1155814640686</v>
+        <v>33.11558345161116</v>
       </c>
       <c r="D53" t="n">
-        <v>31.66407054800669</v>
+        <v>31.66407244843196</v>
       </c>
       <c r="E53" t="n">
-        <v>32.68301382233215</v>
+        <v>32.68301578391271</v>
       </c>
       <c r="F53" t="n">
         <v>610435</v>
@@ -1492,16 +1492,16 @@
         <v>44229</v>
       </c>
       <c r="B54" t="n">
-        <v>32.63494873046875</v>
+        <v>32.63495254516602</v>
       </c>
       <c r="C54" t="n">
-        <v>33.65389204571495</v>
+        <v>33.65389597951643</v>
       </c>
       <c r="D54" t="n">
-        <v>31.97167657096734</v>
+        <v>31.97168030813476</v>
       </c>
       <c r="E54" t="n">
-        <v>33.64427951434755</v>
+        <v>33.64428344702543</v>
       </c>
       <c r="F54" t="n">
         <v>582228</v>
@@ -1532,16 +1532,16 @@
         <v>44231</v>
       </c>
       <c r="B56" t="n">
-        <v>32.68301391601562</v>
+        <v>32.68301773071289</v>
       </c>
       <c r="C56" t="n">
-        <v>34.11529602664492</v>
+        <v>34.11530000851534</v>
       </c>
       <c r="D56" t="n">
-        <v>32.44269689321744</v>
+        <v>32.44270067986538</v>
       </c>
       <c r="E56" t="n">
-        <v>33.06751890394745</v>
+        <v>33.06752276352339</v>
       </c>
       <c r="F56" t="n">
         <v>466743</v>
@@ -1612,16 +1612,16 @@
         <v>44237</v>
       </c>
       <c r="B60" t="n">
-        <v>34.83624649047852</v>
+        <v>34.83625030517578</v>
       </c>
       <c r="C60" t="n">
-        <v>35.33610184184258</v>
+        <v>35.33610571127585</v>
       </c>
       <c r="D60" t="n">
-        <v>34.23064955227608</v>
+        <v>34.23065330065825</v>
       </c>
       <c r="E60" t="n">
-        <v>34.43251269995998</v>
+        <v>34.43251647044691</v>
       </c>
       <c r="F60" t="n">
         <v>186206</v>
@@ -1652,16 +1652,16 @@
         <v>44239</v>
       </c>
       <c r="B62" t="n">
-        <v>34.40367889404297</v>
+        <v>34.4036750793457</v>
       </c>
       <c r="C62" t="n">
-        <v>34.52864555631986</v>
+        <v>34.52864172776623</v>
       </c>
       <c r="D62" t="n">
-        <v>32.673400666573</v>
+        <v>32.67339704372985</v>
       </c>
       <c r="E62" t="n">
-        <v>33.67311897448496</v>
+        <v>33.67311524079254</v>
       </c>
       <c r="F62" t="n">
         <v>218195</v>
@@ -1692,16 +1692,16 @@
         <v>44245</v>
       </c>
       <c r="B64" t="n">
-        <v>37.00870895385742</v>
+        <v>37.00870513916016</v>
       </c>
       <c r="C64" t="n">
-        <v>37.38360144742785</v>
+        <v>37.38359759408829</v>
       </c>
       <c r="D64" t="n">
-        <v>35.71100215049589</v>
+        <v>35.71099846956061</v>
       </c>
       <c r="E64" t="n">
-        <v>36.37427435009953</v>
+        <v>36.37427060079703</v>
       </c>
       <c r="F64" t="n">
         <v>661534</v>
@@ -1812,16 +1812,16 @@
         <v>44253</v>
       </c>
       <c r="B70" t="n">
-        <v>34.57670593261719</v>
+        <v>34.57670974731445</v>
       </c>
       <c r="C70" t="n">
-        <v>37.21057322750037</v>
+        <v>37.21057733278074</v>
       </c>
       <c r="D70" t="n">
-        <v>33.75001700107128</v>
+        <v>33.75002072456356</v>
       </c>
       <c r="E70" t="n">
-        <v>36.5376847961999</v>
+        <v>36.53768882724342</v>
       </c>
       <c r="F70" t="n">
         <v>410022</v>
@@ -1932,16 +1932,16 @@
         <v>44263</v>
       </c>
       <c r="B76" t="n">
-        <v>41.91115951538086</v>
+        <v>41.91115570068359</v>
       </c>
       <c r="C76" t="n">
-        <v>44.60270214463106</v>
+        <v>44.60269808495321</v>
       </c>
       <c r="D76" t="n">
-        <v>40.70957805138659</v>
+        <v>40.70957434605565</v>
       </c>
       <c r="E76" t="n">
-        <v>43.55492493684502</v>
+        <v>43.55492097253444</v>
       </c>
       <c r="F76" t="n">
         <v>1012691</v>
@@ -1952,16 +1952,16 @@
         <v>44264</v>
       </c>
       <c r="B77" t="n">
-        <v>43.50686264038086</v>
+        <v>43.50685882568359</v>
       </c>
       <c r="C77" t="n">
-        <v>43.50686264038086</v>
+        <v>43.50685882568359</v>
       </c>
       <c r="D77" t="n">
-        <v>39.89250193891922</v>
+        <v>39.89249844113039</v>
       </c>
       <c r="E77" t="n">
-        <v>42.29566488693005</v>
+        <v>42.29566117843103</v>
       </c>
       <c r="F77" t="n">
         <v>563525</v>
@@ -1972,16 +1972,16 @@
         <v>44265</v>
       </c>
       <c r="B78" t="n">
-        <v>44.69882583618164</v>
+        <v>44.69882965087891</v>
       </c>
       <c r="C78" t="n">
-        <v>44.89108021255291</v>
+        <v>44.89108404365759</v>
       </c>
       <c r="D78" t="n">
-        <v>43.38189403862891</v>
+        <v>43.38189774093629</v>
       </c>
       <c r="E78" t="n">
-        <v>43.83369051144994</v>
+        <v>43.83369425231464</v>
       </c>
       <c r="F78" t="n">
         <v>425454</v>
@@ -2012,16 +2012,16 @@
         <v>44267</v>
       </c>
       <c r="B80" t="n">
-        <v>45.66009521484375</v>
+        <v>45.66009140014648</v>
       </c>
       <c r="C80" t="n">
-        <v>49.01491000208902</v>
+        <v>49.01490590711195</v>
       </c>
       <c r="D80" t="n">
-        <v>45.18907366630634</v>
+        <v>45.18906989096082</v>
       </c>
       <c r="E80" t="n">
-        <v>47.15005636649431</v>
+        <v>47.15005242731743</v>
       </c>
       <c r="F80" t="n">
         <v>954539</v>
@@ -2052,16 +2052,16 @@
         <v>44271</v>
       </c>
       <c r="B82" t="n">
-        <v>42.75707244873047</v>
+        <v>42.7570686340332</v>
       </c>
       <c r="C82" t="n">
-        <v>45.18907290913018</v>
+        <v>45.18906887745489</v>
       </c>
       <c r="D82" t="n">
-        <v>42.75707244873047</v>
+        <v>42.7570686340332</v>
       </c>
       <c r="E82" t="n">
-        <v>44.50657567458991</v>
+        <v>44.5065717038056</v>
       </c>
       <c r="F82" t="n">
         <v>561175</v>
@@ -2092,16 +2092,16 @@
         <v>44273</v>
       </c>
       <c r="B84" t="n">
-        <v>40.89221954345703</v>
+        <v>40.89221572875977</v>
       </c>
       <c r="C84" t="n">
-        <v>45.0256568951004</v>
+        <v>45.02565269480871</v>
       </c>
       <c r="D84" t="n">
-        <v>40.57500224961562</v>
+        <v>40.57499846451049</v>
       </c>
       <c r="E84" t="n">
-        <v>44.01632982334604</v>
+        <v>44.01632571721106</v>
       </c>
       <c r="F84" t="n">
         <v>572621</v>
@@ -2112,16 +2112,16 @@
         <v>44274</v>
       </c>
       <c r="B85" t="n">
-        <v>42.29566192626953</v>
+        <v>42.2956657409668</v>
       </c>
       <c r="C85" t="n">
-        <v>44.17013174266427</v>
+        <v>44.17013572642225</v>
       </c>
       <c r="D85" t="n">
-        <v>41.4593642170013</v>
+        <v>41.45936795627186</v>
       </c>
       <c r="E85" t="n">
-        <v>41.4593642170013</v>
+        <v>41.45936795627186</v>
       </c>
       <c r="F85" t="n">
         <v>639255</v>
@@ -2212,16 +2212,16 @@
         <v>44281</v>
       </c>
       <c r="B90" t="n">
-        <v>37.87384414672852</v>
+        <v>37.87384796142578</v>
       </c>
       <c r="C90" t="n">
-        <v>40.949891527232</v>
+        <v>40.94989565175231</v>
       </c>
       <c r="D90" t="n">
-        <v>37.56623940867817</v>
+        <v>37.56624319239313</v>
       </c>
       <c r="E90" t="n">
-        <v>39.95978959641457</v>
+        <v>39.95979362121066</v>
       </c>
       <c r="F90" t="n">
         <v>840076</v>
@@ -2312,16 +2312,16 @@
         <v>44291</v>
       </c>
       <c r="B95" t="n">
-        <v>35.68215942382812</v>
+        <v>35.68216323852539</v>
       </c>
       <c r="C95" t="n">
-        <v>37.01831616285484</v>
+        <v>37.01832012039754</v>
       </c>
       <c r="D95" t="n">
-        <v>35.09578756412892</v>
+        <v>35.09579131613852</v>
       </c>
       <c r="E95" t="n">
-        <v>37.01831616285484</v>
+        <v>37.01832012039754</v>
       </c>
       <c r="F95" t="n">
         <v>1091895</v>
@@ -2512,16 +2512,16 @@
         <v>44305</v>
       </c>
       <c r="B105" t="n">
-        <v>41.33439636230469</v>
+        <v>41.33440017700195</v>
       </c>
       <c r="C105" t="n">
-        <v>42.23798551125894</v>
+        <v>42.23798940934727</v>
       </c>
       <c r="D105" t="n">
-        <v>40.20971525467667</v>
+        <v>40.2097189655786</v>
       </c>
       <c r="E105" t="n">
-        <v>40.38274455876383</v>
+        <v>40.38274828563441</v>
       </c>
       <c r="F105" t="n">
         <v>1793083</v>
@@ -2552,16 +2552,16 @@
         <v>44308</v>
       </c>
       <c r="B107" t="n">
-        <v>42.3725700378418</v>
+        <v>42.37256622314453</v>
       </c>
       <c r="C107" t="n">
-        <v>42.77630013488342</v>
+        <v>42.77629628383934</v>
       </c>
       <c r="D107" t="n">
-        <v>41.04602186600353</v>
+        <v>41.0460181707321</v>
       </c>
       <c r="E107" t="n">
-        <v>42.58404574470481</v>
+        <v>42.58404191096891</v>
       </c>
       <c r="F107" t="n">
         <v>1175903</v>
@@ -2572,16 +2572,16 @@
         <v>44309</v>
       </c>
       <c r="B108" t="n">
-        <v>44.09323501586914</v>
+        <v>44.09323120117188</v>
       </c>
       <c r="C108" t="n">
-        <v>44.31432325105797</v>
+        <v>44.3143194172334</v>
       </c>
       <c r="D108" t="n">
-        <v>42.38218184069201</v>
+        <v>42.38217817402538</v>
       </c>
       <c r="E108" t="n">
-        <v>42.82436205864548</v>
+        <v>42.82435835372392</v>
       </c>
       <c r="F108" t="n">
         <v>1899574</v>
@@ -2612,16 +2612,16 @@
         <v>44313</v>
       </c>
       <c r="B110" t="n">
-        <v>43.7375602722168</v>
+        <v>43.73756408691406</v>
       </c>
       <c r="C110" t="n">
-        <v>44.31431963823069</v>
+        <v>44.31432350323168</v>
       </c>
       <c r="D110" t="n">
-        <v>43.04545053203033</v>
+        <v>43.04545428636325</v>
       </c>
       <c r="E110" t="n">
-        <v>43.40111793330461</v>
+        <v>43.40112171865809</v>
       </c>
       <c r="F110" t="n">
         <v>1146163</v>
@@ -2732,16 +2732,16 @@
         <v>44321</v>
       </c>
       <c r="B116" t="n">
-        <v>39.74831390380859</v>
+        <v>39.74831008911133</v>
       </c>
       <c r="C116" t="n">
-        <v>40.64229060912697</v>
+        <v>40.6422867086336</v>
       </c>
       <c r="D116" t="n">
-        <v>39.0754291787498</v>
+        <v>39.07542542863015</v>
       </c>
       <c r="E116" t="n">
-        <v>39.89250188164586</v>
+        <v>39.89249805311069</v>
       </c>
       <c r="F116" t="n">
         <v>3650961</v>
@@ -2772,16 +2772,16 @@
         <v>44323</v>
       </c>
       <c r="B118" t="n">
-        <v>38.83510971069336</v>
+        <v>38.83511352539062</v>
       </c>
       <c r="C118" t="n">
-        <v>39.99824098294782</v>
+        <v>39.99824491189721</v>
       </c>
       <c r="D118" t="n">
-        <v>37.51817793834604</v>
+        <v>37.51818162368365</v>
       </c>
       <c r="E118" t="n">
-        <v>39.66179864141913</v>
+        <v>39.66180253732045</v>
       </c>
       <c r="F118" t="n">
         <v>2227429</v>
@@ -2832,16 +2832,16 @@
         <v>44328</v>
       </c>
       <c r="B121" t="n">
-        <v>37.05677032470703</v>
+        <v>37.05676651000977</v>
       </c>
       <c r="C121" t="n">
-        <v>38.70053196862062</v>
+        <v>38.70052798471127</v>
       </c>
       <c r="D121" t="n">
-        <v>37.05677032470703</v>
+        <v>37.05676651000977</v>
       </c>
       <c r="E121" t="n">
-        <v>37.8161715649591</v>
+        <v>37.81616767208757</v>
       </c>
       <c r="F121" t="n">
         <v>783049</v>
@@ -2892,16 +2892,16 @@
         <v>44333</v>
       </c>
       <c r="B124" t="n">
-        <v>36.43194580078125</v>
+        <v>36.43194961547852</v>
       </c>
       <c r="C124" t="n">
-        <v>37.13366805612294</v>
+        <v>37.13367194429578</v>
       </c>
       <c r="D124" t="n">
-        <v>35.93208669563144</v>
+        <v>35.93209045798972</v>
       </c>
       <c r="E124" t="n">
-        <v>36.52807111039643</v>
+        <v>36.52807493515874</v>
       </c>
       <c r="F124" t="n">
         <v>946466</v>
@@ -2912,16 +2912,16 @@
         <v>44334</v>
       </c>
       <c r="B125" t="n">
-        <v>35.14385604858398</v>
+        <v>35.14385223388672</v>
       </c>
       <c r="C125" t="n">
-        <v>36.91258445174329</v>
+        <v>36.91258044505902</v>
       </c>
       <c r="D125" t="n">
-        <v>34.59593422023043</v>
+        <v>34.59593046500746</v>
       </c>
       <c r="E125" t="n">
-        <v>36.52807567013412</v>
+        <v>36.52807170518645</v>
       </c>
       <c r="F125" t="n">
         <v>2070451</v>
@@ -2952,16 +2952,16 @@
         <v>44336</v>
       </c>
       <c r="B127" t="n">
-        <v>34.63438415527344</v>
+        <v>34.63438034057617</v>
       </c>
       <c r="C127" t="n">
-        <v>35.26881876953347</v>
+        <v>35.26881488495837</v>
       </c>
       <c r="D127" t="n">
-        <v>34.51903376998102</v>
+        <v>34.51902996798866</v>
       </c>
       <c r="E127" t="n">
-        <v>34.51903376998102</v>
+        <v>34.51902996798866</v>
       </c>
       <c r="F127" t="n">
         <v>943604</v>
@@ -3012,16 +3012,16 @@
         <v>44341</v>
       </c>
       <c r="B130" t="n">
-        <v>37.29708862304688</v>
+        <v>37.29708480834961</v>
       </c>
       <c r="C130" t="n">
-        <v>38.78704981148397</v>
+        <v>38.78704584439543</v>
       </c>
       <c r="D130" t="n">
-        <v>37.22980089947328</v>
+        <v>37.22979709165812</v>
       </c>
       <c r="E130" t="n">
-        <v>37.52779313716071</v>
+        <v>37.52778929886728</v>
       </c>
       <c r="F130" t="n">
         <v>1731150</v>
@@ -3092,16 +3092,16 @@
         <v>44347</v>
       </c>
       <c r="B134" t="n">
-        <v>39.38303375244141</v>
+        <v>39.38302993774414</v>
       </c>
       <c r="C134" t="n">
-        <v>40.11359366504992</v>
+        <v>40.11358977958957</v>
       </c>
       <c r="D134" t="n">
-        <v>39.02736632794579</v>
+        <v>39.02736254769899</v>
       </c>
       <c r="E134" t="n">
-        <v>39.39264628425005</v>
+        <v>39.3926424686217</v>
       </c>
       <c r="F134" t="n">
         <v>715598</v>
@@ -3192,16 +3192,16 @@
         <v>44355</v>
       </c>
       <c r="B139" t="n">
-        <v>38.4602165222168</v>
+        <v>38.46022033691406</v>
       </c>
       <c r="C139" t="n">
-        <v>38.85433404388245</v>
+        <v>38.85433789767048</v>
       </c>
       <c r="D139" t="n">
-        <v>37.72004038668688</v>
+        <v>37.72004412796937</v>
       </c>
       <c r="E139" t="n">
-        <v>38.43137892899068</v>
+        <v>38.43138274082768</v>
       </c>
       <c r="F139" t="n">
         <v>978352</v>
@@ -3212,16 +3212,16 @@
         <v>44356</v>
       </c>
       <c r="B140" t="n">
-        <v>38.01803588867188</v>
+        <v>38.01803207397461</v>
       </c>
       <c r="C140" t="n">
-        <v>38.66208302162527</v>
+        <v>38.66207914230487</v>
       </c>
       <c r="D140" t="n">
-        <v>37.29708850045856</v>
+        <v>37.29708475810054</v>
       </c>
       <c r="E140" t="n">
-        <v>38.48905744729046</v>
+        <v>38.48905358533129</v>
       </c>
       <c r="F140" t="n">
         <v>837521</v>
@@ -3332,16 +3332,16 @@
         <v>44364</v>
       </c>
       <c r="B146" t="n">
-        <v>42.4879150390625</v>
+        <v>42.48791885375977</v>
       </c>
       <c r="C146" t="n">
-        <v>44.0067136610316</v>
+        <v>44.00671761209134</v>
       </c>
       <c r="D146" t="n">
-        <v>41.62277601425852</v>
+        <v>41.62277975128091</v>
       </c>
       <c r="E146" t="n">
-        <v>42.95893654890009</v>
+        <v>42.95894040588714</v>
       </c>
       <c r="F146" t="n">
         <v>1582144</v>
@@ -3372,16 +3372,16 @@
         <v>44368</v>
       </c>
       <c r="B148" t="n">
-        <v>46.96741485595703</v>
+        <v>46.96741104125977</v>
       </c>
       <c r="C148" t="n">
-        <v>47.24618202489792</v>
+        <v>47.24617818755916</v>
       </c>
       <c r="D148" t="n">
-        <v>43.53569979030122</v>
+        <v>43.53569625432814</v>
       </c>
       <c r="E148" t="n">
-        <v>43.73756295749668</v>
+        <v>43.73755940512824</v>
       </c>
       <c r="F148" t="n">
         <v>2655439</v>
@@ -3452,16 +3452,16 @@
         <v>44372</v>
       </c>
       <c r="B152" t="n">
-        <v>44.45851135253906</v>
+        <v>44.45851516723633</v>
       </c>
       <c r="C152" t="n">
-        <v>44.98720431506052</v>
+        <v>44.9872081751215</v>
       </c>
       <c r="D152" t="n">
-        <v>43.97787729834627</v>
+        <v>43.97788107180344</v>
       </c>
       <c r="E152" t="n">
-        <v>44.98720431506052</v>
+        <v>44.9872081751215</v>
       </c>
       <c r="F152" t="n">
         <v>1347904</v>
@@ -3472,16 +3472,16 @@
         <v>44375</v>
       </c>
       <c r="B153" t="n">
-        <v>44.5354118347168</v>
+        <v>44.53541564941406</v>
       </c>
       <c r="C153" t="n">
-        <v>44.64114967825854</v>
+        <v>44.64115350201283</v>
       </c>
       <c r="D153" t="n">
-        <v>43.20886378695175</v>
+        <v>43.20886748802305</v>
       </c>
       <c r="E153" t="n">
-        <v>44.13168177543641</v>
+        <v>44.13168555555202</v>
       </c>
       <c r="F153" t="n">
         <v>1110393</v>
@@ -3512,16 +3512,16 @@
         <v>44377</v>
       </c>
       <c r="B155" t="n">
-        <v>43.58376312255859</v>
+        <v>43.58375930786133</v>
       </c>
       <c r="C155" t="n">
-        <v>44.45851476998166</v>
+        <v>44.45851087872119</v>
       </c>
       <c r="D155" t="n">
-        <v>43.50686286720073</v>
+        <v>43.50685905923421</v>
       </c>
       <c r="E155" t="n">
-        <v>44.21819772441255</v>
+        <v>44.21819385418598</v>
       </c>
       <c r="F155" t="n">
         <v>1274116</v>
@@ -3572,16 +3572,16 @@
         <v>44382</v>
       </c>
       <c r="B158" t="n">
-        <v>45.04488372802734</v>
+        <v>45.04488754272461</v>
       </c>
       <c r="C158" t="n">
-        <v>46.21762753484401</v>
+        <v>46.21763144885693</v>
       </c>
       <c r="D158" t="n">
-        <v>44.42967048319475</v>
+        <v>44.42967424579171</v>
       </c>
       <c r="E158" t="n">
-        <v>44.98720479275436</v>
+        <v>44.98720860256699</v>
       </c>
       <c r="F158" t="n">
         <v>3391068</v>
@@ -3592,16 +3592,16 @@
         <v>44383</v>
       </c>
       <c r="B159" t="n">
-        <v>44.37199401855469</v>
+        <v>44.37199783325195</v>
       </c>
       <c r="C159" t="n">
-        <v>45.94847158903642</v>
+        <v>45.94847553926477</v>
       </c>
       <c r="D159" t="n">
-        <v>43.75678453900221</v>
+        <v>43.75678830080941</v>
       </c>
       <c r="E159" t="n">
-        <v>45.7850548143543</v>
+        <v>45.78505875053358</v>
       </c>
       <c r="F159" t="n">
         <v>1563442</v>
@@ -3652,16 +3652,16 @@
         <v>44389</v>
       </c>
       <c r="B162" t="n">
-        <v>44.72766876220703</v>
+        <v>44.72766494750977</v>
       </c>
       <c r="C162" t="n">
-        <v>45.75622090541913</v>
+        <v>45.75621700299953</v>
       </c>
       <c r="D162" t="n">
-        <v>44.08361789020423</v>
+        <v>44.08361413043626</v>
       </c>
       <c r="E162" t="n">
-        <v>45.75622090541913</v>
+        <v>45.75621700299953</v>
       </c>
       <c r="F162" t="n">
         <v>1597780</v>
@@ -3732,16 +3732,16 @@
         <v>44393</v>
       </c>
       <c r="B166" t="n">
-        <v>41.70928955078125</v>
+        <v>41.70929336547852</v>
       </c>
       <c r="C166" t="n">
-        <v>41.91115645117827</v>
+        <v>41.91116028433812</v>
       </c>
       <c r="D166" t="n">
-        <v>40.45003298811638</v>
+        <v>40.45003668764308</v>
       </c>
       <c r="E166" t="n">
-        <v>41.62277677100059</v>
+        <v>41.62278057778546</v>
       </c>
       <c r="F166" t="n">
         <v>1471156</v>
@@ -3752,16 +3752,16 @@
         <v>44396</v>
       </c>
       <c r="B167" t="n">
-        <v>40.22894287109375</v>
+        <v>40.22894668579102</v>
       </c>
       <c r="C167" t="n">
-        <v>41.05562800061862</v>
+        <v>41.05563189370605</v>
       </c>
       <c r="D167" t="n">
-        <v>39.50799183094843</v>
+        <v>39.50799557728174</v>
       </c>
       <c r="E167" t="n">
-        <v>40.46925613690023</v>
+        <v>40.46925997438512</v>
       </c>
       <c r="F167" t="n">
         <v>1632835</v>
@@ -3792,16 +3792,16 @@
         <v>44398</v>
       </c>
       <c r="B169" t="n">
-        <v>40.45964431762695</v>
+        <v>40.45964813232422</v>
       </c>
       <c r="C169" t="n">
-        <v>41.40168732645247</v>
+        <v>41.40169122996932</v>
       </c>
       <c r="D169" t="n">
-        <v>40.22894357839657</v>
+        <v>40.22894737134245</v>
       </c>
       <c r="E169" t="n">
-        <v>40.37313154041556</v>
+        <v>40.37313534695605</v>
       </c>
       <c r="F169" t="n">
         <v>985812</v>
@@ -3812,16 +3812,16 @@
         <v>44399</v>
       </c>
       <c r="B170" t="n">
-        <v>40.89221954345703</v>
+        <v>40.89221572875977</v>
       </c>
       <c r="C170" t="n">
-        <v>41.15176164706832</v>
+        <v>41.15175780815924</v>
       </c>
       <c r="D170" t="n">
-        <v>40.3923603996445</v>
+        <v>40.39235663157741</v>
       </c>
       <c r="E170" t="n">
-        <v>41.08447017755746</v>
+        <v>41.08446634492577</v>
       </c>
       <c r="F170" t="n">
         <v>757704</v>
@@ -3832,16 +3832,16 @@
         <v>44400</v>
       </c>
       <c r="B171" t="n">
-        <v>40.56538772583008</v>
+        <v>40.56539154052734</v>
       </c>
       <c r="C171" t="n">
-        <v>40.86337994162768</v>
+        <v>40.8633837843476</v>
       </c>
       <c r="D171" t="n">
-        <v>40.20010404382616</v>
+        <v>40.20010782417279</v>
       </c>
       <c r="E171" t="n">
-        <v>40.6230629132279</v>
+        <v>40.62306673334884</v>
       </c>
       <c r="F171" t="n">
         <v>715496</v>
@@ -3872,16 +3872,16 @@
         <v>44404</v>
       </c>
       <c r="B173" t="n">
-        <v>38.54673004150391</v>
+        <v>38.54673385620117</v>
       </c>
       <c r="C173" t="n">
-        <v>40.84415499320262</v>
+        <v>40.84415903525979</v>
       </c>
       <c r="D173" t="n">
-        <v>38.32563807495276</v>
+        <v>38.32564186777011</v>
       </c>
       <c r="E173" t="n">
-        <v>40.62306302665147</v>
+        <v>40.62306704682872</v>
       </c>
       <c r="F173" t="n">
         <v>1543819</v>
@@ -3932,16 +3932,16 @@
         <v>44407</v>
       </c>
       <c r="B176" t="n">
-        <v>37.2105712890625</v>
+        <v>37.21057510375977</v>
       </c>
       <c r="C176" t="n">
-        <v>38.26796091589321</v>
+        <v>38.26796483899034</v>
       </c>
       <c r="D176" t="n">
-        <v>36.33581974675896</v>
+        <v>36.33582347177977</v>
       </c>
       <c r="E176" t="n">
-        <v>37.5662386749276</v>
+        <v>37.56624252608663</v>
       </c>
       <c r="F176" t="n">
         <v>1168442</v>
@@ -3952,16 +3952,16 @@
         <v>44410</v>
       </c>
       <c r="B177" t="n">
-        <v>39.04658889770508</v>
+        <v>39.04659271240234</v>
       </c>
       <c r="C177" t="n">
-        <v>40.3442955992922</v>
+        <v>40.34429954077027</v>
       </c>
       <c r="D177" t="n">
-        <v>38.19106237864987</v>
+        <v>38.19106610976557</v>
       </c>
       <c r="E177" t="n">
-        <v>39.17155180323623</v>
+        <v>39.17155563014188</v>
       </c>
       <c r="F177" t="n">
         <v>3352028</v>
@@ -4052,16 +4052,16 @@
         <v>44417</v>
       </c>
       <c r="B182" t="n">
-        <v>37.10483169555664</v>
+        <v>37.10483551025391</v>
       </c>
       <c r="C182" t="n">
-        <v>37.44127403795907</v>
+        <v>37.44127788724551</v>
       </c>
       <c r="D182" t="n">
-        <v>35.94170042028153</v>
+        <v>35.94170411539885</v>
       </c>
       <c r="E182" t="n">
-        <v>36.1147297309109</v>
+        <v>36.11473344381713</v>
       </c>
       <c r="F182" t="n">
         <v>1206460</v>
@@ -4092,16 +4092,16 @@
         <v>44419</v>
       </c>
       <c r="B184" t="n">
-        <v>36.43194580078125</v>
+        <v>36.43194961547852</v>
       </c>
       <c r="C184" t="n">
-        <v>36.74916307008678</v>
+        <v>36.74916691799907</v>
       </c>
       <c r="D184" t="n">
-        <v>36.09550346955268</v>
+        <v>36.09550724902192</v>
       </c>
       <c r="E184" t="n">
-        <v>36.47039592462733</v>
+        <v>36.4703997433506</v>
       </c>
       <c r="F184" t="n">
         <v>786524</v>
@@ -4112,16 +4112,16 @@
         <v>44420</v>
       </c>
       <c r="B185" t="n">
-        <v>36.12434387207031</v>
+        <v>36.12434005737305</v>
       </c>
       <c r="C185" t="n">
-        <v>36.95103284178433</v>
+        <v>36.95102893978947</v>
       </c>
       <c r="D185" t="n">
-        <v>35.4706842206967</v>
+        <v>35.47068047502529</v>
       </c>
       <c r="E185" t="n">
-        <v>36.19163159403436</v>
+        <v>36.19162777223157</v>
       </c>
       <c r="F185" t="n">
         <v>689639</v>
@@ -4132,16 +4132,16 @@
         <v>44421</v>
       </c>
       <c r="B186" t="n">
-        <v>34.75934219360352</v>
+        <v>34.75934600830078</v>
       </c>
       <c r="C186" t="n">
-        <v>35.97053605946554</v>
+        <v>35.97054000708643</v>
       </c>
       <c r="D186" t="n">
-        <v>34.59592917071041</v>
+        <v>34.59593296747376</v>
       </c>
       <c r="E186" t="n">
-        <v>35.69177266747142</v>
+        <v>35.69177658449917</v>
       </c>
       <c r="F186" t="n">
         <v>915908</v>
@@ -4252,16 +4252,16 @@
         <v>44431</v>
       </c>
       <c r="B192" t="n">
-        <v>33.16364288330078</v>
+        <v>33.16364669799805</v>
       </c>
       <c r="C192" t="n">
-        <v>34.42289938524034</v>
+        <v>34.42290334478545</v>
       </c>
       <c r="D192" t="n">
-        <v>32.77913791079774</v>
+        <v>32.77914168126674</v>
       </c>
       <c r="E192" t="n">
-        <v>33.740402215843</v>
+        <v>33.74040609688286</v>
       </c>
       <c r="F192" t="n">
         <v>2084044</v>
@@ -4272,16 +4272,16 @@
         <v>44432</v>
       </c>
       <c r="B193" t="n">
-        <v>35.43223571777344</v>
+        <v>35.43223190307617</v>
       </c>
       <c r="C193" t="n">
-        <v>35.43223571777344</v>
+        <v>35.43223190307617</v>
       </c>
       <c r="D193" t="n">
-        <v>33.47125292620207</v>
+        <v>33.47124932262768</v>
       </c>
       <c r="E193" t="n">
-        <v>33.93266196453976</v>
+        <v>33.93265831128927</v>
       </c>
       <c r="F193" t="n">
         <v>1429663</v>
@@ -4332,16 +4332,16 @@
         <v>44435</v>
       </c>
       <c r="B196" t="n">
-        <v>36.43194580078125</v>
+        <v>36.43194961547852</v>
       </c>
       <c r="C196" t="n">
-        <v>36.66265029143312</v>
+        <v>36.66265413028687</v>
       </c>
       <c r="D196" t="n">
-        <v>35.02849754252244</v>
+        <v>35.02850121026817</v>
       </c>
       <c r="E196" t="n">
-        <v>35.75906113832411</v>
+        <v>35.75906488256532</v>
       </c>
       <c r="F196" t="n">
         <v>2701327</v>
@@ -4392,16 +4392,16 @@
         <v>44440</v>
       </c>
       <c r="B199" t="n">
-        <v>36.00899124145508</v>
+        <v>36.00899505615234</v>
       </c>
       <c r="C199" t="n">
-        <v>37.22979768253502</v>
+        <v>37.2298016265613</v>
       </c>
       <c r="D199" t="n">
-        <v>35.47068200422877</v>
+        <v>35.47068576189898</v>
       </c>
       <c r="E199" t="n">
-        <v>37.10483103054919</v>
+        <v>37.10483496133683</v>
       </c>
       <c r="F199" t="n">
         <v>1150659</v>
@@ -4712,16 +4712,16 @@
         <v>44463</v>
       </c>
       <c r="B215" t="n">
-        <v>34.54786682128906</v>
+        <v>34.54787063598633</v>
       </c>
       <c r="C215" t="n">
-        <v>35.65331911097231</v>
+        <v>35.65332304773112</v>
       </c>
       <c r="D215" t="n">
-        <v>33.88459095038866</v>
+        <v>33.88459469184851</v>
       </c>
       <c r="E215" t="n">
-        <v>34.46135404370111</v>
+        <v>34.46135784884584</v>
       </c>
       <c r="F215" t="n">
         <v>2639905</v>
@@ -4852,16 +4852,16 @@
         <v>44474</v>
       </c>
       <c r="B222" t="n">
-        <v>41.23827362060547</v>
+        <v>41.2382698059082</v>
       </c>
       <c r="C222" t="n">
-        <v>43.07428962557536</v>
+        <v>43.07428564103963</v>
       </c>
       <c r="D222" t="n">
-        <v>40.9498939275561</v>
+        <v>40.94989013953506</v>
       </c>
       <c r="E222" t="n">
-        <v>41.82464553821999</v>
+        <v>41.82464166928109</v>
       </c>
       <c r="F222" t="n">
         <v>3033780</v>
@@ -4952,16 +4952,16 @@
         <v>44482</v>
       </c>
       <c r="B227" t="n">
-        <v>39.66179656982422</v>
+        <v>39.66180038452148</v>
       </c>
       <c r="C227" t="n">
-        <v>40.05591407830239</v>
+        <v>40.05591793090613</v>
       </c>
       <c r="D227" t="n">
-        <v>38.88317033604628</v>
+        <v>38.88317407585477</v>
       </c>
       <c r="E227" t="n">
-        <v>39.43109208415942</v>
+        <v>39.43109587666738</v>
       </c>
       <c r="F227" t="n">
         <v>1130628</v>
@@ -5012,16 +5012,16 @@
         <v>44487</v>
       </c>
       <c r="B230" t="n">
-        <v>39.87327194213867</v>
+        <v>39.87327575683594</v>
       </c>
       <c r="C230" t="n">
-        <v>41.44974945917212</v>
+        <v>41.44975342469183</v>
       </c>
       <c r="D230" t="n">
-        <v>39.18116223800101</v>
+        <v>39.18116598648377</v>
       </c>
       <c r="E230" t="n">
-        <v>39.72908398193304</v>
+        <v>39.72908778283576</v>
       </c>
       <c r="F230" t="n">
         <v>2573169</v>
@@ -5032,16 +5032,16 @@
         <v>44488</v>
       </c>
       <c r="B231" t="n">
-        <v>37.58546447753906</v>
+        <v>37.58546829223633</v>
       </c>
       <c r="C231" t="n">
-        <v>40.08475250621378</v>
+        <v>40.08475657457366</v>
       </c>
       <c r="D231" t="n">
-        <v>36.86451716082918</v>
+        <v>36.86452090235465</v>
       </c>
       <c r="E231" t="n">
-        <v>39.57528087049455</v>
+        <v>39.57528488714614</v>
       </c>
       <c r="F231" t="n">
         <v>2915331</v>
@@ -5072,16 +5072,16 @@
         <v>44490</v>
       </c>
       <c r="B233" t="n">
-        <v>34.41328811645508</v>
+        <v>34.41329193115234</v>
       </c>
       <c r="C233" t="n">
-        <v>36.09550352264783</v>
+        <v>36.09550752381791</v>
       </c>
       <c r="D233" t="n">
-        <v>33.48086136908995</v>
+        <v>33.48086508042814</v>
       </c>
       <c r="E233" t="n">
-        <v>35.62448200968972</v>
+        <v>35.62448595864728</v>
       </c>
       <c r="F233" t="n">
         <v>3113087</v>
@@ -5092,16 +5092,16 @@
         <v>44491</v>
       </c>
       <c r="B234" t="n">
-        <v>32.63494873046875</v>
+        <v>32.63495254516602</v>
       </c>
       <c r="C234" t="n">
-        <v>34.06723464208851</v>
+        <v>34.06723862420559</v>
       </c>
       <c r="D234" t="n">
-        <v>31.04886231697067</v>
+        <v>31.04886594627039</v>
       </c>
       <c r="E234" t="n">
-        <v>33.63466698298016</v>
+        <v>33.63467091453443</v>
       </c>
       <c r="F234" t="n">
         <v>4894520</v>
@@ -5112,16 +5112,16 @@
         <v>44494</v>
       </c>
       <c r="B235" t="n">
-        <v>36.8470573425293</v>
+        <v>36.84706115722656</v>
       </c>
       <c r="C235" t="n">
-        <v>37.3112732591762</v>
+        <v>37.31127712193275</v>
       </c>
       <c r="D235" t="n">
-        <v>32.95925887799699</v>
+        <v>32.95926229019877</v>
       </c>
       <c r="E235" t="n">
-        <v>32.95925887799699</v>
+        <v>32.95926229019877</v>
       </c>
       <c r="F235" t="n">
         <v>3449995</v>
@@ -5152,16 +5152,16 @@
         <v>44496</v>
       </c>
       <c r="B237" t="n">
-        <v>35.29000854492188</v>
+        <v>35.29000473022461</v>
       </c>
       <c r="C237" t="n">
-        <v>36.07337184605893</v>
+        <v>36.07336794668348</v>
       </c>
       <c r="D237" t="n">
-        <v>34.47763151058894</v>
+        <v>34.47762778370612</v>
       </c>
       <c r="E237" t="n">
-        <v>36.07337184605893</v>
+        <v>36.07336794668348</v>
       </c>
       <c r="F237" t="n">
         <v>2270538</v>
@@ -5272,16 +5272,16 @@
         <v>44505</v>
       </c>
       <c r="B243" t="n">
-        <v>34.33255767822266</v>
+        <v>34.33256149291992</v>
       </c>
       <c r="C243" t="n">
-        <v>35.80257411368536</v>
+        <v>35.80257809171644</v>
       </c>
       <c r="D243" t="n">
-        <v>31.73102080869616</v>
+        <v>31.73102433433615</v>
       </c>
       <c r="E243" t="n">
-        <v>33.17202351532898</v>
+        <v>33.17202720107906</v>
       </c>
       <c r="F243" t="n">
         <v>9166770</v>
@@ -5312,16 +5312,16 @@
         <v>44509</v>
       </c>
       <c r="B245" t="n">
-        <v>34.50664138793945</v>
+        <v>34.50664520263672</v>
       </c>
       <c r="C245" t="n">
-        <v>35.1062534768846</v>
+        <v>35.10625735786877</v>
       </c>
       <c r="D245" t="n">
-        <v>32.63044017132788</v>
+        <v>32.63044377861175</v>
       </c>
       <c r="E245" t="n">
-        <v>33.89736055406007</v>
+        <v>33.89736430140155</v>
       </c>
       <c r="F245" t="n">
         <v>7032350</v>
@@ -5372,16 +5372,16 @@
         <v>44512</v>
       </c>
       <c r="B248" t="n">
-        <v>30.94766044616699</v>
+        <v>30.94766235351562</v>
       </c>
       <c r="C248" t="n">
-        <v>33.11399707089411</v>
+        <v>33.11399911175717</v>
       </c>
       <c r="D248" t="n">
-        <v>30.69620937113922</v>
+        <v>30.69621126299056</v>
       </c>
       <c r="E248" t="n">
-        <v>32.10819651835855</v>
+        <v>32.10819849723269</v>
       </c>
       <c r="F248" t="n">
         <v>3403064</v>
@@ -5552,16 +5552,16 @@
         <v>44526</v>
       </c>
       <c r="B257" t="n">
-        <v>26.69235801696777</v>
+        <v>26.69235992431641</v>
       </c>
       <c r="C257" t="n">
-        <v>27.61111551515892</v>
+        <v>27.61111748815896</v>
       </c>
       <c r="D257" t="n">
-        <v>25.85096734243463</v>
+        <v>25.85096918966023</v>
       </c>
       <c r="E257" t="n">
-        <v>26.59564620826666</v>
+        <v>26.59564810870458</v>
       </c>
       <c r="F257" t="n">
         <v>3664026</v>
@@ -5592,16 +5592,16 @@
         <v>44530</v>
       </c>
       <c r="B259" t="n">
-        <v>26.71169853210449</v>
+        <v>26.71170043945312</v>
       </c>
       <c r="C259" t="n">
-        <v>26.71169853210449</v>
+        <v>26.71170043945312</v>
       </c>
       <c r="D259" t="n">
-        <v>25.48346440355603</v>
+        <v>25.48346622320262</v>
       </c>
       <c r="E259" t="n">
-        <v>26.53761803066504</v>
+        <v>26.53761992558345</v>
       </c>
       <c r="F259" t="n">
         <v>4757647</v>
@@ -5612,16 +5612,16 @@
         <v>44531</v>
       </c>
       <c r="B260" t="n">
-        <v>26.69235801696777</v>
+        <v>26.69235992431641</v>
       </c>
       <c r="C260" t="n">
-        <v>28.01730398743094</v>
+        <v>28.01730598945588</v>
       </c>
       <c r="D260" t="n">
-        <v>26.32485389341864</v>
+        <v>26.32485577450663</v>
       </c>
       <c r="E260" t="n">
-        <v>27.17591518668557</v>
+        <v>27.17591712858762</v>
       </c>
       <c r="F260" t="n">
         <v>3467467</v>
@@ -5752,16 +5752,16 @@
         <v>44540</v>
       </c>
       <c r="B267" t="n">
-        <v>29.43896293640137</v>
+        <v>29.43896102905273</v>
       </c>
       <c r="C267" t="n">
-        <v>29.76778272429381</v>
+        <v>29.76778079564096</v>
       </c>
       <c r="D267" t="n">
-        <v>28.76198212238038</v>
+        <v>28.76198025889329</v>
       </c>
       <c r="E267" t="n">
-        <v>29.57435909920557</v>
+        <v>29.57435718308462</v>
       </c>
       <c r="F267" t="n">
         <v>1281952</v>
@@ -5832,16 +5832,16 @@
         <v>44546</v>
       </c>
       <c r="B271" t="n">
-        <v>30.62851333618164</v>
+        <v>30.62851524353027</v>
       </c>
       <c r="C271" t="n">
-        <v>30.86062130141829</v>
+        <v>30.86062322322113</v>
       </c>
       <c r="D271" t="n">
-        <v>29.25521052973079</v>
+        <v>29.25521235155887</v>
       </c>
       <c r="E271" t="n">
-        <v>29.4969891136642</v>
+        <v>29.49699095054871</v>
       </c>
       <c r="F271" t="n">
         <v>3477726</v>
@@ -5952,16 +5952,16 @@
         <v>44557</v>
       </c>
       <c r="B277" t="n">
-        <v>30.72522354125977</v>
+        <v>30.7252254486084</v>
       </c>
       <c r="C277" t="n">
-        <v>31.01535896880716</v>
+        <v>31.01536089416671</v>
       </c>
       <c r="D277" t="n">
-        <v>29.98054654550914</v>
+        <v>29.98054840663</v>
       </c>
       <c r="E277" t="n">
-        <v>29.98054654550914</v>
+        <v>29.98054840663</v>
       </c>
       <c r="F277" t="n">
         <v>1273927</v>
@@ -6132,16 +6132,16 @@
         <v>44571</v>
       </c>
       <c r="B286" t="n">
-        <v>33.37511444091797</v>
+        <v>33.37511825561523</v>
       </c>
       <c r="C286" t="n">
-        <v>33.89735778992546</v>
+        <v>33.89736166431392</v>
       </c>
       <c r="D286" t="n">
-        <v>32.24359030771443</v>
+        <v>32.24359399308115</v>
       </c>
       <c r="E286" t="n">
-        <v>32.37898645393302</v>
+        <v>32.3789901547752</v>
       </c>
       <c r="F286" t="n">
         <v>2829132</v>
@@ -6152,16 +6152,16 @@
         <v>44572</v>
       </c>
       <c r="B287" t="n">
-        <v>35.10625457763672</v>
+        <v>35.10625076293945</v>
       </c>
       <c r="C287" t="n">
-        <v>35.63816673084244</v>
+        <v>35.63816285834681</v>
       </c>
       <c r="D287" t="n">
-        <v>33.18169458570739</v>
+        <v>33.18169098013564</v>
       </c>
       <c r="E287" t="n">
-        <v>33.55886933935793</v>
+        <v>33.55886569280182</v>
       </c>
       <c r="F287" t="n">
         <v>3953735</v>
@@ -6172,16 +6172,16 @@
         <v>44573</v>
       </c>
       <c r="B288" t="n">
-        <v>34.89348983764648</v>
+        <v>34.89348602294922</v>
       </c>
       <c r="C288" t="n">
-        <v>35.98632787872025</v>
+        <v>35.98632394454952</v>
       </c>
       <c r="D288" t="n">
-        <v>34.13914032772324</v>
+        <v>34.13913659549451</v>
       </c>
       <c r="E288" t="n">
-        <v>35.34803329265463</v>
+        <v>35.34802942826484</v>
       </c>
       <c r="F288" t="n">
         <v>3302601</v>
@@ -6292,16 +6292,16 @@
         <v>44581</v>
       </c>
       <c r="B294" t="n">
-        <v>35.29967498779297</v>
+        <v>35.2996711730957</v>
       </c>
       <c r="C294" t="n">
-        <v>36.17007943172774</v>
+        <v>36.17007552296929</v>
       </c>
       <c r="D294" t="n">
-        <v>34.98052769103708</v>
+        <v>34.98052391082881</v>
       </c>
       <c r="E294" t="n">
-        <v>35.87027337331519</v>
+        <v>35.8702694969556</v>
       </c>
       <c r="F294" t="n">
         <v>3650414</v>
@@ -6332,16 +6332,16 @@
         <v>44585</v>
       </c>
       <c r="B296" t="n">
-        <v>34.35190200805664</v>
+        <v>34.35190582275391</v>
       </c>
       <c r="C296" t="n">
-        <v>35.3190162904272</v>
+        <v>35.31902021252021</v>
       </c>
       <c r="D296" t="n">
-        <v>34.05209598090971</v>
+        <v>34.05209976231423</v>
       </c>
       <c r="E296" t="n">
-        <v>34.23584709494806</v>
+        <v>34.2358508967577</v>
       </c>
       <c r="F296" t="n">
         <v>2113697</v>
@@ -6392,16 +6392,16 @@
         <v>44588</v>
       </c>
       <c r="B299" t="n">
-        <v>36.09271240234375</v>
+        <v>36.09270858764648</v>
       </c>
       <c r="C299" t="n">
-        <v>37.1081818022467</v>
+        <v>37.10817788022283</v>
       </c>
       <c r="D299" t="n">
-        <v>35.68652389286739</v>
+        <v>35.68652012110085</v>
       </c>
       <c r="E299" t="n">
-        <v>35.87994752798603</v>
+        <v>35.87994373577622</v>
       </c>
       <c r="F299" t="n">
         <v>3171460</v>
@@ -6492,16 +6492,16 @@
         <v>44595</v>
       </c>
       <c r="B304" t="n">
-        <v>35.29967498779297</v>
+        <v>35.2996711730957</v>
       </c>
       <c r="C304" t="n">
-        <v>35.58981230082171</v>
+        <v>35.58980845477045</v>
       </c>
       <c r="D304" t="n">
-        <v>33.84900341295216</v>
+        <v>33.84899975502328</v>
       </c>
       <c r="E304" t="n">
-        <v>34.98052769103708</v>
+        <v>34.98052391082881</v>
       </c>
       <c r="F304" t="n">
         <v>4177823</v>
@@ -6592,16 +6592,16 @@
         <v>44602</v>
       </c>
       <c r="B309" t="n">
-        <v>37.28226470947266</v>
+        <v>37.28226089477539</v>
       </c>
       <c r="C309" t="n">
-        <v>38.3847753224369</v>
+        <v>38.38477139493146</v>
       </c>
       <c r="D309" t="n">
-        <v>36.33449150769526</v>
+        <v>36.33448778997354</v>
       </c>
       <c r="E309" t="n">
-        <v>36.36350524073979</v>
+        <v>36.3635015200494</v>
       </c>
       <c r="F309" t="n">
         <v>7025951</v>
@@ -6612,16 +6612,16 @@
         <v>44603</v>
       </c>
       <c r="B310" t="n">
-        <v>38.07529067993164</v>
+        <v>38.07529449462891</v>
       </c>
       <c r="C310" t="n">
-        <v>38.49115162219439</v>
+        <v>38.49115547855604</v>
       </c>
       <c r="D310" t="n">
-        <v>37.37896869306991</v>
+        <v>37.37897243800389</v>
       </c>
       <c r="E310" t="n">
-        <v>37.78515714333515</v>
+        <v>37.78516092896444</v>
       </c>
       <c r="F310" t="n">
         <v>5486491</v>
@@ -6632,16 +6632,16 @@
         <v>44606</v>
       </c>
       <c r="B311" t="n">
-        <v>37.57239151000977</v>
+        <v>37.57239532470703</v>
       </c>
       <c r="C311" t="n">
-        <v>38.84898429079868</v>
+        <v>38.84898823510746</v>
       </c>
       <c r="D311" t="n">
-        <v>36.95343822941596</v>
+        <v>36.95344198127135</v>
       </c>
       <c r="E311" t="n">
-        <v>38.29772721003804</v>
+        <v>38.2977310983781</v>
       </c>
       <c r="F311" t="n">
         <v>3902640</v>
@@ -6652,16 +6652,16 @@
         <v>44607</v>
       </c>
       <c r="B312" t="n">
-        <v>35.79290008544922</v>
+        <v>35.79290390014648</v>
       </c>
       <c r="C312" t="n">
-        <v>36.65363192612031</v>
+        <v>36.65363583255173</v>
       </c>
       <c r="D312" t="n">
-        <v>35.63816270338088</v>
+        <v>35.63816650158672</v>
       </c>
       <c r="E312" t="n">
-        <v>36.55692199922141</v>
+        <v>36.55692589534578</v>
       </c>
       <c r="F312" t="n">
         <v>3810709</v>
@@ -6672,16 +6672,16 @@
         <v>44608</v>
       </c>
       <c r="B313" t="n">
-        <v>35.92830276489258</v>
+        <v>35.92829895019531</v>
       </c>
       <c r="C313" t="n">
-        <v>36.80837600146183</v>
+        <v>36.80837209332255</v>
       </c>
       <c r="D313" t="n">
-        <v>35.69619664958365</v>
+        <v>35.69619285953032</v>
       </c>
       <c r="E313" t="n">
-        <v>36.44087371532872</v>
+        <v>36.4408698462091</v>
       </c>
       <c r="F313" t="n">
         <v>4244663</v>
@@ -6692,16 +6692,16 @@
         <v>44609</v>
       </c>
       <c r="B314" t="n">
-        <v>35.29967498779297</v>
+        <v>35.2996711730957</v>
       </c>
       <c r="C314" t="n">
-        <v>35.89928710461807</v>
+        <v>35.89928322512308</v>
       </c>
       <c r="D314" t="n">
-        <v>34.41960179847439</v>
+        <v>34.41959807888318</v>
       </c>
       <c r="E314" t="n">
-        <v>35.68652224011414</v>
+        <v>35.68651838361181</v>
       </c>
       <c r="F314" t="n">
         <v>4430658</v>
@@ -6712,16 +6712,16 @@
         <v>44610</v>
       </c>
       <c r="B315" t="n">
-        <v>34.48730087280273</v>
+        <v>34.48729705810547</v>
       </c>
       <c r="C315" t="n">
-        <v>35.41572900804387</v>
+        <v>35.41572509065163</v>
       </c>
       <c r="D315" t="n">
-        <v>33.80064757961473</v>
+        <v>33.80064384086931</v>
       </c>
       <c r="E315" t="n">
-        <v>34.83546189196511</v>
+        <v>34.83545803875718</v>
       </c>
       <c r="F315" t="n">
         <v>4069741</v>
@@ -6852,16 +6852,16 @@
         <v>44623</v>
       </c>
       <c r="B322" t="n">
-        <v>37.34028625488281</v>
+        <v>37.34028244018555</v>
       </c>
       <c r="C322" t="n">
-        <v>37.88187465766974</v>
+        <v>37.88187078764361</v>
       </c>
       <c r="D322" t="n">
-        <v>36.31514815474819</v>
+        <v>36.31514444477941</v>
       </c>
       <c r="E322" t="n">
-        <v>37.12752138998924</v>
+        <v>37.12751759702811</v>
       </c>
       <c r="F322" t="n">
         <v>9786414</v>
@@ -6892,16 +6892,16 @@
         <v>44627</v>
       </c>
       <c r="B324" t="n">
-        <v>37.04048156738281</v>
+        <v>37.04048538208008</v>
       </c>
       <c r="C324" t="n">
-        <v>39.28418499781101</v>
+        <v>39.28418904358112</v>
       </c>
       <c r="D324" t="n">
-        <v>36.65363433916909</v>
+        <v>36.65363811402602</v>
       </c>
       <c r="E324" t="n">
-        <v>38.17200577495368</v>
+        <v>38.17200970618351</v>
       </c>
       <c r="F324" t="n">
         <v>5025922</v>
@@ -6952,16 +6952,16 @@
         <v>44630</v>
       </c>
       <c r="B327" t="n">
-        <v>35.7252082824707</v>
+        <v>35.72520446777344</v>
       </c>
       <c r="C327" t="n">
-        <v>37.22423481932497</v>
+        <v>37.22423084456335</v>
       </c>
       <c r="D327" t="n">
-        <v>35.51244341905014</v>
+        <v>35.51243962707166</v>
       </c>
       <c r="E327" t="n">
-        <v>36.75034637550812</v>
+        <v>36.75034245134777</v>
       </c>
       <c r="F327" t="n">
         <v>4502679</v>
@@ -7032,16 +7032,16 @@
         <v>44636</v>
       </c>
       <c r="B331" t="n">
-        <v>32.84320449829102</v>
+        <v>32.84320831298828</v>
       </c>
       <c r="C331" t="n">
-        <v>34.44861337459189</v>
+        <v>34.44861737575539</v>
       </c>
       <c r="D331" t="n">
-        <v>32.34030609979657</v>
+        <v>32.34030985608281</v>
       </c>
       <c r="E331" t="n">
-        <v>34.10045236831488</v>
+        <v>34.10045632903992</v>
       </c>
       <c r="F331" t="n">
         <v>3899288</v>
@@ -7092,16 +7092,16 @@
         <v>44641</v>
       </c>
       <c r="B334" t="n">
-        <v>36.61494827270508</v>
+        <v>36.61495208740234</v>
       </c>
       <c r="C334" t="n">
-        <v>36.86639934686866</v>
+        <v>36.86640318776314</v>
       </c>
       <c r="D334" t="n">
-        <v>35.88961252740777</v>
+        <v>35.88961626653654</v>
       </c>
       <c r="E334" t="n">
-        <v>35.97665371626157</v>
+        <v>35.97665746445866</v>
       </c>
       <c r="F334" t="n">
         <v>3600944</v>
@@ -7212,16 +7212,16 @@
         <v>44649</v>
       </c>
       <c r="B340" t="n">
-        <v>40.11590194702148</v>
+        <v>40.11590576171875</v>
       </c>
       <c r="C340" t="n">
-        <v>40.60913158587444</v>
+        <v>40.60913544747385</v>
       </c>
       <c r="D340" t="n">
-        <v>37.81417112752509</v>
+        <v>37.8141747233464</v>
       </c>
       <c r="E340" t="n">
-        <v>38.00759473575618</v>
+        <v>38.00759834997051</v>
       </c>
       <c r="F340" t="n">
         <v>6952609</v>
@@ -7252,16 +7252,16 @@
         <v>44651</v>
       </c>
       <c r="B342" t="n">
-        <v>40.47373962402344</v>
+        <v>40.47373580932617</v>
       </c>
       <c r="C342" t="n">
-        <v>41.13137921056172</v>
+        <v>41.13137533388116</v>
       </c>
       <c r="D342" t="n">
-        <v>39.67103512697872</v>
+        <v>39.6710313879373</v>
       </c>
       <c r="E342" t="n">
-        <v>40.135251085266</v>
+        <v>40.13524730247168</v>
       </c>
       <c r="F342" t="n">
         <v>3810811</v>
@@ -7312,16 +7312,16 @@
         <v>44656</v>
       </c>
       <c r="B345" t="n">
-        <v>41.97276306152344</v>
+        <v>41.9727668762207</v>
       </c>
       <c r="C345" t="n">
-        <v>43.03659106395681</v>
+        <v>43.03659497534015</v>
       </c>
       <c r="D345" t="n">
-        <v>41.57624708903781</v>
+        <v>41.5762508676977</v>
       </c>
       <c r="E345" t="n">
-        <v>42.30158283032514</v>
+        <v>42.30158667490721</v>
       </c>
       <c r="F345" t="n">
         <v>5903074</v>
@@ -7432,16 +7432,16 @@
         <v>44664</v>
       </c>
       <c r="B351" t="n">
-        <v>43.62652969360352</v>
+        <v>43.62653350830078</v>
       </c>
       <c r="C351" t="n">
-        <v>43.71356713249195</v>
+        <v>43.71357095479976</v>
       </c>
       <c r="D351" t="n">
-        <v>42.8431665105797</v>
+        <v>42.8431702567798</v>
       </c>
       <c r="E351" t="n">
-        <v>43.30738242414481</v>
+        <v>43.30738621093589</v>
       </c>
       <c r="F351" t="n">
         <v>3238402</v>
@@ -7452,16 +7452,16 @@
         <v>44665</v>
       </c>
       <c r="B352" t="n">
-        <v>42.93988037109375</v>
+        <v>42.93987655639648</v>
       </c>
       <c r="C352" t="n">
-        <v>43.62653368593358</v>
+        <v>43.62652981023535</v>
       </c>
       <c r="D352" t="n">
-        <v>42.2242170723533</v>
+        <v>42.2242133212342</v>
       </c>
       <c r="E352" t="n">
-        <v>43.62653368593358</v>
+        <v>43.62652981023535</v>
       </c>
       <c r="F352" t="n">
         <v>2345809</v>
@@ -7552,16 +7552,16 @@
         <v>44676</v>
       </c>
       <c r="B357" t="n">
-        <v>41.94375228881836</v>
+        <v>41.94374847412109</v>
       </c>
       <c r="C357" t="n">
-        <v>42.40796824528748</v>
+        <v>42.40796438837074</v>
       </c>
       <c r="D357" t="n">
-        <v>40.64782185452133</v>
+        <v>40.64781815768625</v>
       </c>
       <c r="E357" t="n">
-        <v>40.75420428750637</v>
+        <v>40.75420058099602</v>
       </c>
       <c r="F357" t="n">
         <v>3287465</v>
@@ -7592,16 +7592,16 @@
         <v>44678</v>
       </c>
       <c r="B359" t="n">
-        <v>42.16618728637695</v>
+        <v>42.16619110107422</v>
       </c>
       <c r="C359" t="n">
-        <v>43.58784506009413</v>
+        <v>43.58784900340616</v>
       </c>
       <c r="D359" t="n">
-        <v>41.46986526445734</v>
+        <v>41.46986901615963</v>
       </c>
       <c r="E359" t="n">
-        <v>43.52014885542929</v>
+        <v>43.52015279261696</v>
       </c>
       <c r="F359" t="n">
         <v>3779727</v>
@@ -7672,16 +7672,16 @@
         <v>44684</v>
       </c>
       <c r="B363" t="n">
-        <v>42.12750244140625</v>
+        <v>42.12749862670898</v>
       </c>
       <c r="C363" t="n">
-        <v>42.54336341820335</v>
+        <v>42.54335956584936</v>
       </c>
       <c r="D363" t="n">
-        <v>41.25710175933607</v>
+        <v>41.25709802345466</v>
       </c>
       <c r="E363" t="n">
-        <v>42.54336341820335</v>
+        <v>42.54335956584936</v>
       </c>
       <c r="F363" t="n">
         <v>4458389</v>
@@ -7692,16 +7692,16 @@
         <v>44685</v>
       </c>
       <c r="B364" t="n">
-        <v>44.10041427612305</v>
+        <v>44.10041809082031</v>
       </c>
       <c r="C364" t="n">
-        <v>44.32285161417975</v>
+        <v>44.32285544811791</v>
       </c>
       <c r="D364" t="n">
-        <v>42.16618567842227</v>
+        <v>42.16618932580826</v>
       </c>
       <c r="E364" t="n">
-        <v>43.04625879095802</v>
+        <v>43.04626251447057</v>
       </c>
       <c r="F364" t="n">
         <v>5759540</v>
@@ -7712,16 +7712,16 @@
         <v>44686</v>
       </c>
       <c r="B365" t="n">
-        <v>42.92053985595703</v>
+        <v>42.92053604125977</v>
       </c>
       <c r="C365" t="n">
-        <v>44.57430384010176</v>
+        <v>44.57429987842104</v>
       </c>
       <c r="D365" t="n">
-        <v>42.01145291457887</v>
+        <v>42.01144918067956</v>
       </c>
       <c r="E365" t="n">
-        <v>44.09074663744735</v>
+        <v>44.09074271874429</v>
       </c>
       <c r="F365" t="n">
         <v>4814532</v>
@@ -7732,16 +7732,16 @@
         <v>44687</v>
       </c>
       <c r="B366" t="n">
-        <v>42.55303573608398</v>
+        <v>42.55303192138672</v>
       </c>
       <c r="C366" t="n">
-        <v>43.90699359626386</v>
+        <v>43.90698966019007</v>
       </c>
       <c r="D366" t="n">
-        <v>41.82769996355259</v>
+        <v>41.82769621387857</v>
       </c>
       <c r="E366" t="n">
-        <v>43.33639522245434</v>
+        <v>43.33639133753226</v>
       </c>
       <c r="F366" t="n">
         <v>4093307</v>
@@ -7892,16 +7892,16 @@
         <v>44699</v>
       </c>
       <c r="B374" t="n">
-        <v>39.99985504150391</v>
+        <v>39.99985122680664</v>
       </c>
       <c r="C374" t="n">
-        <v>42.22421740419406</v>
+        <v>42.2242133773643</v>
       </c>
       <c r="D374" t="n">
-        <v>39.72906271064676</v>
+        <v>39.72905892177436</v>
       </c>
       <c r="E374" t="n">
-        <v>42.13717620908088</v>
+        <v>42.13717219055205</v>
       </c>
       <c r="F374" t="n">
         <v>1865839</v>
@@ -7952,16 +7952,16 @@
         <v>44704</v>
       </c>
       <c r="B377" t="n">
-        <v>42.28224563598633</v>
+        <v>42.28224182128906</v>
       </c>
       <c r="C377" t="n">
-        <v>42.79481657531103</v>
+        <v>42.7948127143697</v>
       </c>
       <c r="D377" t="n">
-        <v>41.35381369972519</v>
+        <v>41.3538099687909</v>
       </c>
       <c r="E377" t="n">
-        <v>41.42151365745766</v>
+        <v>41.42150992041549</v>
       </c>
       <c r="F377" t="n">
         <v>3400119</v>
@@ -8012,16 +8012,16 @@
         <v>44707</v>
       </c>
       <c r="B380" t="n">
-        <v>46.5955696105957</v>
+        <v>46.59557342529297</v>
       </c>
       <c r="C380" t="n">
-        <v>47.1661679572728</v>
+        <v>47.16617181868395</v>
       </c>
       <c r="D380" t="n">
-        <v>45.10621566046026</v>
+        <v>45.10621935322675</v>
       </c>
       <c r="E380" t="n">
-        <v>45.2512805595232</v>
+        <v>45.25128426416589</v>
       </c>
       <c r="F380" t="n">
         <v>4582217</v>
@@ -8072,16 +8072,16 @@
         <v>44712</v>
       </c>
       <c r="B383" t="n">
-        <v>47.14682769775391</v>
+        <v>47.14683151245117</v>
       </c>
       <c r="C383" t="n">
-        <v>49.5452685563496</v>
+        <v>49.54527256510714</v>
       </c>
       <c r="D383" t="n">
-        <v>47.11781396782467</v>
+        <v>47.11781778017441</v>
       </c>
       <c r="E383" t="n">
-        <v>48.22032446240879</v>
+        <v>48.22032836396376</v>
       </c>
       <c r="F383" t="n">
         <v>6322705</v>
@@ -8152,16 +8152,16 @@
         <v>44718</v>
       </c>
       <c r="B387" t="n">
-        <v>45.3189811706543</v>
+        <v>45.31898498535156</v>
       </c>
       <c r="C387" t="n">
-        <v>47.4563021942838</v>
+        <v>47.45630618888874</v>
       </c>
       <c r="D387" t="n">
-        <v>45.13522629971035</v>
+        <v>45.13523009894016</v>
       </c>
       <c r="E387" t="n">
-        <v>47.15649615191405</v>
+        <v>47.156500121283</v>
       </c>
       <c r="F387" t="n">
         <v>1711233</v>
@@ -8172,16 +8172,16 @@
         <v>44719</v>
       </c>
       <c r="B388" t="n">
-        <v>45.3189811706543</v>
+        <v>45.31898498535156</v>
       </c>
       <c r="C388" t="n">
-        <v>45.84122081100923</v>
+        <v>45.84122466966569</v>
       </c>
       <c r="D388" t="n">
-        <v>44.73871032322317</v>
+        <v>44.73871408907649</v>
       </c>
       <c r="E388" t="n">
-        <v>44.98048890609225</v>
+        <v>44.98049269229714</v>
       </c>
       <c r="F388" t="n">
         <v>1887578</v>
@@ -8192,16 +8192,16 @@
         <v>44720</v>
       </c>
       <c r="B389" t="n">
-        <v>45.25128555297852</v>
+        <v>45.25128173828125</v>
       </c>
       <c r="C389" t="n">
-        <v>46.00563510358936</v>
+        <v>46.00563122530019</v>
       </c>
       <c r="D389" t="n">
-        <v>44.92246574936335</v>
+        <v>44.9224619623857</v>
       </c>
       <c r="E389" t="n">
-        <v>45.31898551140559</v>
+        <v>45.31898169100119</v>
       </c>
       <c r="F389" t="n">
         <v>1920490</v>
@@ -8212,16 +8212,16 @@
         <v>44721</v>
       </c>
       <c r="B390" t="n">
-        <v>44.5066032409668</v>
+        <v>44.50660705566406</v>
       </c>
       <c r="C390" t="n">
-        <v>45.59944121195702</v>
+        <v>45.59944512032232</v>
       </c>
       <c r="D390" t="n">
-        <v>44.32285212169327</v>
+        <v>44.32285592064108</v>
       </c>
       <c r="E390" t="n">
-        <v>45.22226648118356</v>
+        <v>45.2222703572209</v>
       </c>
       <c r="F390" t="n">
         <v>1644697</v>
@@ -8472,16 +8472,16 @@
         <v>44741</v>
       </c>
       <c r="B403" t="n">
-        <v>34.71940612792969</v>
+        <v>34.71940994262695</v>
       </c>
       <c r="C403" t="n">
-        <v>35.41572814937177</v>
+        <v>35.41573204057546</v>
       </c>
       <c r="D403" t="n">
-        <v>34.09078031110602</v>
+        <v>34.0907840567348</v>
       </c>
       <c r="E403" t="n">
-        <v>35.29967322993957</v>
+        <v>35.29967710839206</v>
       </c>
       <c r="F403" t="n">
         <v>2690880</v>
@@ -8532,16 +8532,16 @@
         <v>44746</v>
       </c>
       <c r="B406" t="n">
-        <v>35.08691024780273</v>
+        <v>35.08690643310547</v>
       </c>
       <c r="C406" t="n">
-        <v>35.60915366553204</v>
+        <v>35.60914979405575</v>
       </c>
       <c r="D406" t="n">
-        <v>34.1971683099429</v>
+        <v>34.19716459197961</v>
       </c>
       <c r="E406" t="n">
-        <v>34.57433932306729</v>
+        <v>34.57433556409744</v>
       </c>
       <c r="F406" t="n">
         <v>2359523</v>
@@ -8612,16 +8612,16 @@
         <v>44750</v>
       </c>
       <c r="B410" t="n">
-        <v>31.81806373596191</v>
+        <v>31.81806564331055</v>
       </c>
       <c r="C410" t="n">
-        <v>32.48537204040704</v>
+        <v>32.48537398775778</v>
       </c>
       <c r="D410" t="n">
-        <v>31.19911039968697</v>
+        <v>31.19911226993215</v>
       </c>
       <c r="E410" t="n">
-        <v>31.3151653213559</v>
+        <v>31.31516719855805</v>
       </c>
       <c r="F410" t="n">
         <v>4375906</v>
@@ -8712,16 +8712,16 @@
         <v>44757</v>
       </c>
       <c r="B415" t="n">
-        <v>27.79486846923828</v>
+        <v>27.79486656188965</v>
       </c>
       <c r="C415" t="n">
-        <v>29.07146143004599</v>
+        <v>29.07145943509457</v>
       </c>
       <c r="D415" t="n">
-        <v>27.79486846923828</v>
+        <v>27.79486656188965</v>
       </c>
       <c r="E415" t="n">
-        <v>29.06178893688788</v>
+        <v>29.06178694260021</v>
       </c>
       <c r="F415" t="n">
         <v>4618481</v>
@@ -8752,16 +8752,16 @@
         <v>44761</v>
       </c>
       <c r="B417" t="n">
-        <v>29.43896293640137</v>
+        <v>29.43896102905273</v>
       </c>
       <c r="C417" t="n">
-        <v>29.53567474894549</v>
+        <v>29.5356728353309</v>
       </c>
       <c r="D417" t="n">
-        <v>28.11401691328927</v>
+        <v>28.11401509178381</v>
       </c>
       <c r="E417" t="n">
-        <v>28.14303064443129</v>
+        <v>28.14302882104603</v>
       </c>
       <c r="F417" t="n">
         <v>4570230</v>
@@ -8772,16 +8772,16 @@
         <v>44762</v>
       </c>
       <c r="B418" t="n">
-        <v>30.59950065612793</v>
+        <v>30.5994987487793</v>
       </c>
       <c r="C418" t="n">
-        <v>30.97667540990739</v>
+        <v>30.97667347904845</v>
       </c>
       <c r="D418" t="n">
-        <v>29.21652718353251</v>
+        <v>29.21652536238831</v>
       </c>
       <c r="E418" t="n">
-        <v>29.21652718353251</v>
+        <v>29.21652536238831</v>
       </c>
       <c r="F418" t="n">
         <v>5027446</v>
@@ -8792,16 +8792,16 @@
         <v>44763</v>
       </c>
       <c r="B419" t="n">
-        <v>29.44863510131836</v>
+        <v>29.44863319396973</v>
       </c>
       <c r="C419" t="n">
-        <v>29.86449233042948</v>
+        <v>29.86449039614633</v>
       </c>
       <c r="D419" t="n">
-        <v>28.83935237548546</v>
+        <v>28.83935050759925</v>
       </c>
       <c r="E419" t="n">
-        <v>29.86449233042948</v>
+        <v>29.86449039614633</v>
       </c>
       <c r="F419" t="n">
         <v>5437325</v>
@@ -8832,16 +8832,16 @@
         <v>44767</v>
       </c>
       <c r="B421" t="n">
-        <v>29.2648811340332</v>
+        <v>29.26488304138184</v>
       </c>
       <c r="C421" t="n">
-        <v>29.7194245717984</v>
+        <v>29.71942650877206</v>
       </c>
       <c r="D421" t="n">
-        <v>28.43316295561438</v>
+        <v>28.43316480875549</v>
       </c>
       <c r="E421" t="n">
-        <v>28.87803577468757</v>
+        <v>28.87803765682343</v>
       </c>
       <c r="F421" t="n">
         <v>3521914</v>
@@ -8852,16 +8852,16 @@
         <v>44768</v>
       </c>
       <c r="B422" t="n">
-        <v>28.95540428161621</v>
+        <v>28.95540618896484</v>
       </c>
       <c r="C422" t="n">
-        <v>30.15462657412001</v>
+        <v>30.15462856046375</v>
       </c>
       <c r="D422" t="n">
-        <v>28.81033750703789</v>
+        <v>28.81033940483069</v>
       </c>
       <c r="E422" t="n">
-        <v>29.88383426222034</v>
+        <v>29.88383623072646</v>
       </c>
       <c r="F422" t="n">
         <v>2984449</v>
@@ -8872,16 +8872,16 @@
         <v>44769</v>
       </c>
       <c r="B423" t="n">
-        <v>29.66139984130859</v>
+        <v>29.66139793395996</v>
       </c>
       <c r="C423" t="n">
-        <v>29.76778227135207</v>
+        <v>29.76778035716261</v>
       </c>
       <c r="D423" t="n">
-        <v>28.61691490502781</v>
+        <v>28.6169130648438</v>
       </c>
       <c r="E423" t="n">
-        <v>28.95540530688788</v>
+        <v>28.95540344493757</v>
       </c>
       <c r="F423" t="n">
         <v>2554762</v>
@@ -8892,16 +8892,16 @@
         <v>44770</v>
       </c>
       <c r="B424" t="n">
-        <v>30.78325271606445</v>
+        <v>30.78325080871582</v>
       </c>
       <c r="C424" t="n">
-        <v>30.88963514995402</v>
+        <v>30.88963323601387</v>
       </c>
       <c r="D424" t="n">
-        <v>29.53567536735125</v>
+        <v>29.53567353730325</v>
       </c>
       <c r="E424" t="n">
-        <v>29.96120510290952</v>
+        <v>29.96120324649545</v>
       </c>
       <c r="F424" t="n">
         <v>4208906</v>
@@ -8952,16 +8952,16 @@
         <v>44775</v>
       </c>
       <c r="B427" t="n">
-        <v>31.85674858093262</v>
+        <v>31.85675048828125</v>
       </c>
       <c r="C427" t="n">
-        <v>32.0791821744082</v>
+        <v>32.07918409507452</v>
       </c>
       <c r="D427" t="n">
-        <v>30.94765985359998</v>
+        <v>30.94766170651904</v>
       </c>
       <c r="E427" t="n">
-        <v>31.32483458513196</v>
+        <v>31.32483646063348</v>
       </c>
       <c r="F427" t="n">
         <v>3020206</v>
@@ -9072,16 +9072,16 @@
         <v>44783</v>
       </c>
       <c r="B433" t="n">
-        <v>33.26873397827148</v>
+        <v>33.26873779296875</v>
       </c>
       <c r="C433" t="n">
-        <v>33.97472847846024</v>
+        <v>33.97473237410905</v>
       </c>
       <c r="D433" t="n">
-        <v>32.87221800802422</v>
+        <v>32.87222177725572</v>
       </c>
       <c r="E433" t="n">
-        <v>33.62656747451073</v>
+        <v>33.62657133023831</v>
       </c>
       <c r="F433" t="n">
         <v>3325457</v>
@@ -9152,16 +9152,16 @@
         <v>44789</v>
       </c>
       <c r="B437" t="n">
-        <v>32.27260589599609</v>
+        <v>32.27260971069336</v>
       </c>
       <c r="C437" t="n">
-        <v>32.61109815484615</v>
+        <v>32.61110200955398</v>
       </c>
       <c r="D437" t="n">
-        <v>31.73102127989639</v>
+        <v>31.73102503057709</v>
       </c>
       <c r="E437" t="n">
-        <v>32.39832955774229</v>
+        <v>32.39833338730038</v>
       </c>
       <c r="F437" t="n">
         <v>2684074</v>
@@ -9172,16 +9172,16 @@
         <v>44790</v>
       </c>
       <c r="B438" t="n">
-        <v>32.53372955322266</v>
+        <v>32.53372573852539</v>
       </c>
       <c r="C438" t="n">
-        <v>32.93024931741367</v>
+        <v>32.93024545622303</v>
       </c>
       <c r="D438" t="n">
-        <v>31.80839373121048</v>
+        <v>31.80839000156146</v>
       </c>
       <c r="E438" t="n">
-        <v>31.8180662246313</v>
+        <v>31.81806249384815</v>
       </c>
       <c r="F438" t="n">
         <v>3057587</v>
@@ -9252,16 +9252,16 @@
         <v>44796</v>
       </c>
       <c r="B442" t="n">
-        <v>35.11592102050781</v>
+        <v>35.11592483520508</v>
       </c>
       <c r="C442" t="n">
-        <v>35.54145071517264</v>
+        <v>35.54145457609587</v>
       </c>
       <c r="D442" t="n">
-        <v>33.43314347863087</v>
+        <v>33.43314711052539</v>
       </c>
       <c r="E442" t="n">
-        <v>33.46215720759215</v>
+        <v>33.46216084263848</v>
       </c>
       <c r="F442" t="n">
         <v>5706007</v>
@@ -9292,16 +9292,16 @@
         <v>44798</v>
       </c>
       <c r="B444" t="n">
-        <v>35.7348747253418</v>
+        <v>35.73487854003906</v>
       </c>
       <c r="C444" t="n">
-        <v>36.56659288719009</v>
+        <v>36.56659679067325</v>
       </c>
       <c r="D444" t="n">
-        <v>35.39638621377552</v>
+        <v>35.39638999233915</v>
       </c>
       <c r="E444" t="n">
-        <v>35.8606021347718</v>
+        <v>35.86060596289047</v>
       </c>
       <c r="F444" t="n">
         <v>2850362</v>
@@ -9372,16 +9372,16 @@
         <v>44804</v>
       </c>
       <c r="B448" t="n">
-        <v>36.16040420532227</v>
+        <v>36.16040802001953</v>
       </c>
       <c r="C448" t="n">
-        <v>36.46021024107181</v>
+        <v>36.46021408739674</v>
       </c>
       <c r="D448" t="n">
-        <v>35.22230362431106</v>
+        <v>35.22230734004456</v>
       </c>
       <c r="E448" t="n">
-        <v>35.91862562779205</v>
+        <v>35.91862941698318</v>
       </c>
       <c r="F448" t="n">
         <v>3394125</v>
@@ -9392,16 +9392,16 @@
         <v>44805</v>
       </c>
       <c r="B449" t="n">
-        <v>35.58013534545898</v>
+        <v>35.58013916015625</v>
       </c>
       <c r="C449" t="n">
-        <v>36.22810235066332</v>
+        <v>36.22810623483188</v>
       </c>
       <c r="D449" t="n">
-        <v>35.00953703150028</v>
+        <v>35.00954078502128</v>
       </c>
       <c r="E449" t="n">
-        <v>35.8412551468599</v>
+        <v>35.84125898955293</v>
       </c>
       <c r="F449" t="n">
         <v>3340084</v>
@@ -9492,16 +9492,16 @@
         <v>44813</v>
       </c>
       <c r="B454" t="n">
-        <v>35.92830276489258</v>
+        <v>35.92829895019531</v>
       </c>
       <c r="C454" t="n">
-        <v>36.37317375612866</v>
+        <v>36.3731698941971</v>
       </c>
       <c r="D454" t="n">
-        <v>35.60915545100184</v>
+        <v>35.60915167019012</v>
       </c>
       <c r="E454" t="n">
-        <v>35.79290659406839</v>
+        <v>35.79290279374685</v>
       </c>
       <c r="F454" t="n">
         <v>3544465</v>
@@ -9552,16 +9552,16 @@
         <v>44818</v>
       </c>
       <c r="B457" t="n">
-        <v>37.25324630737305</v>
+        <v>37.25325012207031</v>
       </c>
       <c r="C457" t="n">
-        <v>37.57239358328728</v>
+        <v>37.57239743066493</v>
       </c>
       <c r="D457" t="n">
-        <v>35.96698471138824</v>
+        <v>35.96698839437353</v>
       </c>
       <c r="E457" t="n">
-        <v>36.05402215203722</v>
+        <v>36.05402584393507</v>
       </c>
       <c r="F457" t="n">
         <v>4057043</v>
@@ -9592,16 +9592,16 @@
         <v>44820</v>
       </c>
       <c r="B459" t="n">
-        <v>36.79870223999023</v>
+        <v>36.7987060546875</v>
       </c>
       <c r="C459" t="n">
-        <v>36.79870223999023</v>
+        <v>36.7987060546875</v>
       </c>
       <c r="D459" t="n">
-        <v>35.78322922342723</v>
+        <v>35.7832329328566</v>
       </c>
       <c r="E459" t="n">
-        <v>36.14106271488564</v>
+        <v>36.14106646140942</v>
       </c>
       <c r="F459" t="n">
         <v>2974596</v>
@@ -9612,16 +9612,16 @@
         <v>44823</v>
       </c>
       <c r="B460" t="n">
-        <v>36.8470573425293</v>
+        <v>36.84706115722656</v>
       </c>
       <c r="C460" t="n">
-        <v>37.3983144462179</v>
+        <v>37.39831831798563</v>
       </c>
       <c r="D460" t="n">
-        <v>35.7929018485589</v>
+        <v>35.79290555412169</v>
       </c>
       <c r="E460" t="n">
-        <v>35.7929018485589</v>
+        <v>35.79290555412169</v>
       </c>
       <c r="F460" t="n">
         <v>3461677</v>
@@ -9652,16 +9652,16 @@
         <v>44825</v>
       </c>
       <c r="B462" t="n">
-        <v>38.0366096496582</v>
+        <v>38.03661346435547</v>
       </c>
       <c r="C462" t="n">
-        <v>38.79095912196355</v>
+        <v>38.79096301231463</v>
       </c>
       <c r="D462" t="n">
-        <v>37.62074869162363</v>
+        <v>37.62075246461414</v>
       </c>
       <c r="E462" t="n">
-        <v>37.9398959687412</v>
+        <v>37.93989977373904</v>
       </c>
       <c r="F462" t="n">
         <v>4689181</v>
@@ -9732,16 +9732,16 @@
         <v>44831</v>
       </c>
       <c r="B466" t="n">
-        <v>33.61689758300781</v>
+        <v>33.61689376831055</v>
       </c>
       <c r="C466" t="n">
-        <v>34.44861580943209</v>
+        <v>34.44861190035511</v>
       </c>
       <c r="D466" t="n">
-        <v>33.32676401519949</v>
+        <v>33.3267602334253</v>
       </c>
       <c r="E466" t="n">
-        <v>34.44861580943209</v>
+        <v>34.44861190035511</v>
       </c>
       <c r="F466" t="n">
         <v>5480701</v>
@@ -9752,16 +9752,16 @@
         <v>44832</v>
       </c>
       <c r="B467" t="n">
-        <v>34.5743408203125</v>
+        <v>34.57433700561523</v>
       </c>
       <c r="C467" t="n">
-        <v>34.99987431683395</v>
+        <v>34.99987045518622</v>
       </c>
       <c r="D467" t="n">
-        <v>33.19136913623947</v>
+        <v>33.19136547412988</v>
       </c>
       <c r="E467" t="n">
-        <v>33.66525385709685</v>
+        <v>33.66525014270204</v>
       </c>
       <c r="F467" t="n">
         <v>4399676</v>
@@ -9772,16 +9772,16 @@
         <v>44833</v>
       </c>
       <c r="B468" t="n">
-        <v>33.90702819824219</v>
+        <v>33.90703201293945</v>
       </c>
       <c r="C468" t="n">
-        <v>34.69039138641359</v>
+        <v>34.69039528924284</v>
       </c>
       <c r="D468" t="n">
-        <v>33.09465502863428</v>
+        <v>33.09465875193581</v>
       </c>
       <c r="E468" t="n">
-        <v>34.61302269157358</v>
+        <v>34.61302658569848</v>
       </c>
       <c r="F468" t="n">
         <v>4499631</v>
@@ -9812,16 +9812,16 @@
         <v>44837</v>
       </c>
       <c r="B470" t="n">
-        <v>36.79870223999023</v>
+        <v>36.7987060546875</v>
       </c>
       <c r="C470" t="n">
-        <v>36.91475715561467</v>
+        <v>36.91476098234264</v>
       </c>
       <c r="D470" t="n">
-        <v>35.52210941084767</v>
+        <v>35.52211309320833</v>
       </c>
       <c r="E470" t="n">
-        <v>36.26678637509517</v>
+        <v>36.26679013465196</v>
       </c>
       <c r="F470" t="n">
         <v>4419789</v>
@@ -9852,16 +9852,16 @@
         <v>44839</v>
       </c>
       <c r="B472" t="n">
-        <v>41.63427352905273</v>
+        <v>41.63427734375</v>
       </c>
       <c r="C472" t="n">
-        <v>42.48533291211138</v>
+        <v>42.48533680478608</v>
       </c>
       <c r="D472" t="n">
-        <v>40.55110431601417</v>
+        <v>40.55110803146717</v>
       </c>
       <c r="E472" t="n">
-        <v>40.61880426561678</v>
+        <v>40.61880798727272</v>
       </c>
       <c r="F472" t="n">
         <v>6927519</v>
@@ -9892,16 +9892,16 @@
         <v>44841</v>
       </c>
       <c r="B474" t="n">
-        <v>41.47954177856445</v>
+        <v>41.47953796386719</v>
       </c>
       <c r="C474" t="n">
-        <v>42.45632495390688</v>
+        <v>42.45632104937901</v>
       </c>
       <c r="D474" t="n">
-        <v>41.22809067776815</v>
+        <v>41.22808688619578</v>
       </c>
       <c r="E474" t="n">
-        <v>41.59559296175236</v>
+        <v>41.59558913638236</v>
       </c>
       <c r="F474" t="n">
         <v>3503020</v>
@@ -10072,16 +10072,16 @@
         <v>44855</v>
       </c>
       <c r="B483" t="n">
-        <v>44.22613906860352</v>
+        <v>44.22614288330078</v>
       </c>
       <c r="C483" t="n">
-        <v>44.68068250090031</v>
+        <v>44.68068635480393</v>
       </c>
       <c r="D483" t="n">
-        <v>42.41763783177974</v>
+        <v>42.41764149048589</v>
       </c>
       <c r="E483" t="n">
-        <v>42.96889119740864</v>
+        <v>42.9688949036628</v>
       </c>
       <c r="F483" t="n">
         <v>5360835</v>
@@ -10112,16 +10112,16 @@
         <v>44859</v>
       </c>
       <c r="B485" t="n">
-        <v>42.69809722900391</v>
+        <v>42.69810104370117</v>
       </c>
       <c r="C485" t="n">
-        <v>44.7193669863075</v>
+        <v>44.71937098158734</v>
       </c>
       <c r="D485" t="n">
-        <v>42.52401860625056</v>
+        <v>42.52402240539543</v>
       </c>
       <c r="E485" t="n">
-        <v>43.43310543554394</v>
+        <v>43.43310931590769</v>
       </c>
       <c r="F485" t="n">
         <v>3364870</v>
@@ -10232,16 +10232,16 @@
         <v>44868</v>
       </c>
       <c r="B491" t="n">
-        <v>46.30543518066406</v>
+        <v>46.30543899536133</v>
       </c>
       <c r="C491" t="n">
-        <v>46.4311588402996</v>
+        <v>46.43116266535413</v>
       </c>
       <c r="D491" t="n">
-        <v>44.51627522669133</v>
+        <v>44.51627889399545</v>
       </c>
       <c r="E491" t="n">
-        <v>44.98048739191887</v>
+        <v>44.98049109746535</v>
       </c>
       <c r="F491" t="n">
         <v>3262984</v>
@@ -10312,16 +10312,16 @@
         <v>44874</v>
       </c>
       <c r="B495" t="n">
-        <v>44.69035339355469</v>
+        <v>44.69035720825195</v>
       </c>
       <c r="C495" t="n">
-        <v>46.49885831321781</v>
+        <v>46.49886228228617</v>
       </c>
       <c r="D495" t="n">
-        <v>44.23580997752845</v>
+        <v>44.23581375342662</v>
       </c>
       <c r="E495" t="n">
-        <v>45.35766165335595</v>
+        <v>45.35766552501359</v>
       </c>
       <c r="F495" t="n">
         <v>4884014</v>
@@ -10332,16 +10332,16 @@
         <v>44875</v>
       </c>
       <c r="B496" t="n">
-        <v>42.0598030090332</v>
+        <v>42.05980682373047</v>
       </c>
       <c r="C496" t="n">
-        <v>44.68068109462947</v>
+        <v>44.68068514703247</v>
       </c>
       <c r="D496" t="n">
-        <v>41.64394206412777</v>
+        <v>41.6439458411077</v>
       </c>
       <c r="E496" t="n">
-        <v>43.65554309181744</v>
+        <v>43.65554705124352</v>
       </c>
       <c r="F496" t="n">
         <v>5453172</v>
@@ -10472,16 +10472,16 @@
         <v>44887</v>
       </c>
       <c r="B503" t="n">
-        <v>35.7252082824707</v>
+        <v>35.72520446777344</v>
       </c>
       <c r="C503" t="n">
-        <v>38.01726681069696</v>
+        <v>38.01726275125628</v>
       </c>
       <c r="D503" t="n">
-        <v>35.41572973267442</v>
+        <v>35.41572595102293</v>
       </c>
       <c r="E503" t="n">
-        <v>37.37897222043525</v>
+        <v>37.37896822915095</v>
       </c>
       <c r="F503" t="n">
         <v>4879239</v>
@@ -10492,16 +10492,16 @@
         <v>44888</v>
       </c>
       <c r="B504" t="n">
-        <v>34.29387664794922</v>
+        <v>34.29388046264648</v>
       </c>
       <c r="C504" t="n">
-        <v>35.59947950993321</v>
+        <v>35.59948346985989</v>
       </c>
       <c r="D504" t="n">
-        <v>33.84900195222058</v>
+        <v>33.84900571743197</v>
       </c>
       <c r="E504" t="n">
-        <v>35.37704590964446</v>
+        <v>35.37704984482862</v>
       </c>
       <c r="F504" t="n">
         <v>5644348</v>
@@ -10532,16 +10532,16 @@
         <v>44890</v>
       </c>
       <c r="B506" t="n">
-        <v>34.2358512878418</v>
+        <v>34.23584747314453</v>
       </c>
       <c r="C506" t="n">
-        <v>36.49889988516448</v>
+        <v>36.49889581830917</v>
       </c>
       <c r="D506" t="n">
-        <v>34.11012761496025</v>
+        <v>34.11012381427162</v>
       </c>
       <c r="E506" t="n">
-        <v>36.17008008946956</v>
+        <v>36.17007605925269</v>
       </c>
       <c r="F506" t="n">
         <v>4398253</v>
@@ -10552,16 +10552,16 @@
         <v>44893</v>
       </c>
       <c r="B507" t="n">
-        <v>33.64591217041016</v>
+        <v>33.64590835571289</v>
       </c>
       <c r="C507" t="n">
-        <v>34.11012813925738</v>
+        <v>34.11012427192836</v>
       </c>
       <c r="D507" t="n">
-        <v>32.92057635865081</v>
+        <v>32.92057262619048</v>
       </c>
       <c r="E507" t="n">
-        <v>33.36544734092983</v>
+        <v>33.36544355803103</v>
       </c>
       <c r="F507" t="n">
         <v>4077054</v>
@@ -10652,16 +10652,16 @@
         <v>44900</v>
       </c>
       <c r="B512" t="n">
-        <v>34.04242706298828</v>
+        <v>34.04242324829102</v>
       </c>
       <c r="C512" t="n">
-        <v>35.879945891439</v>
+        <v>35.87994187083461</v>
       </c>
       <c r="D512" t="n">
-        <v>33.77163473568869</v>
+        <v>33.77163095133564</v>
       </c>
       <c r="E512" t="n">
-        <v>35.57046733984986</v>
+        <v>35.57046335392476</v>
       </c>
       <c r="F512" t="n">
         <v>5158181</v>
@@ -10732,16 +10732,16 @@
         <v>44904</v>
       </c>
       <c r="B516" t="n">
-        <v>31.69233894348145</v>
+        <v>31.69234085083008</v>
       </c>
       <c r="C516" t="n">
-        <v>32.74649445099531</v>
+        <v>32.74649642178647</v>
       </c>
       <c r="D516" t="n">
-        <v>31.48924283777486</v>
+        <v>31.4892447329005</v>
       </c>
       <c r="E516" t="n">
-        <v>32.22425106961099</v>
+        <v>32.22425300897184</v>
       </c>
       <c r="F516" t="n">
         <v>2885712</v>
@@ -10752,16 +10752,16 @@
         <v>44907</v>
       </c>
       <c r="B517" t="n">
-        <v>32.23392105102539</v>
+        <v>32.23392486572266</v>
       </c>
       <c r="C517" t="n">
-        <v>32.41767215777701</v>
+        <v>32.41767599422015</v>
       </c>
       <c r="D517" t="n">
-        <v>31.06371071712008</v>
+        <v>31.06371439332975</v>
       </c>
       <c r="E517" t="n">
-        <v>31.59562280181559</v>
+        <v>31.59562654097396</v>
       </c>
       <c r="F517" t="n">
         <v>3445728</v>
@@ -10772,16 +10772,16 @@
         <v>44908</v>
       </c>
       <c r="B518" t="n">
-        <v>32.52405548095703</v>
+        <v>32.5240592956543</v>
       </c>
       <c r="C518" t="n">
-        <v>33.41380105995531</v>
+        <v>33.41380497900949</v>
       </c>
       <c r="D518" t="n">
-        <v>31.9824708896037</v>
+        <v>31.98247464077933</v>
       </c>
       <c r="E518" t="n">
-        <v>32.39832807738018</v>
+        <v>32.39833187733107</v>
       </c>
       <c r="F518" t="n">
         <v>3369136</v>
@@ -10872,16 +10872,16 @@
         <v>44915</v>
       </c>
       <c r="B523" t="n">
-        <v>31.63431358337402</v>
+        <v>31.63431167602539</v>
       </c>
       <c r="C523" t="n">
-        <v>31.83740595497857</v>
+        <v>31.83740403538475</v>
       </c>
       <c r="D523" t="n">
-        <v>30.62851484937437</v>
+        <v>30.62851300266902</v>
       </c>
       <c r="E523" t="n">
-        <v>30.76391101296931</v>
+        <v>30.76390915810044</v>
       </c>
       <c r="F523" t="n">
         <v>3472546</v>
@@ -10892,16 +10892,16 @@
         <v>44916</v>
       </c>
       <c r="B524" t="n">
-        <v>32.19524002075195</v>
+        <v>32.19523620605469</v>
       </c>
       <c r="C524" t="n">
-        <v>32.50471857745117</v>
+        <v>32.50471472608491</v>
       </c>
       <c r="D524" t="n">
-        <v>31.22812562087756</v>
+        <v>31.22812192077017</v>
       </c>
       <c r="E524" t="n">
-        <v>32.34997742531367</v>
+        <v>32.34997359228213</v>
       </c>
       <c r="F524" t="n">
         <v>3938295</v>
@@ -10912,16 +10912,16 @@
         <v>44917</v>
       </c>
       <c r="B525" t="n">
-        <v>32.0114860534668</v>
+        <v>32.01148986816406</v>
       </c>
       <c r="C525" t="n">
-        <v>32.78517675543017</v>
+        <v>32.78518066232546</v>
       </c>
       <c r="D525" t="n">
-        <v>31.5376013885634</v>
+        <v>31.53760514678948</v>
       </c>
       <c r="E525" t="n">
-        <v>32.41767451520204</v>
+        <v>32.41767837830338</v>
       </c>
       <c r="F525" t="n">
         <v>3822391</v>
@@ -10932,16 +10932,16 @@
         <v>44918</v>
       </c>
       <c r="B526" t="n">
-        <v>34.68072509765625</v>
+        <v>34.68072128295898</v>
       </c>
       <c r="C526" t="n">
-        <v>34.88381746754605</v>
+        <v>34.88381363050969</v>
       </c>
       <c r="D526" t="n">
-        <v>32.68846888482701</v>
+        <v>32.68846528926745</v>
       </c>
       <c r="E526" t="n">
-        <v>33.17202607250107</v>
+        <v>33.17202242375276</v>
       </c>
       <c r="F526" t="n">
         <v>6955860</v>
@@ -11012,16 +11012,16 @@
         <v>44924</v>
       </c>
       <c r="B530" t="n">
-        <v>36.50856399536133</v>
+        <v>36.50856781005859</v>
       </c>
       <c r="C530" t="n">
-        <v>37.23389970387844</v>
+        <v>37.23390359436439</v>
       </c>
       <c r="D530" t="n">
-        <v>35.61882215744662</v>
+        <v>35.61882587917678</v>
       </c>
       <c r="E530" t="n">
-        <v>35.87994196319169</v>
+        <v>35.87994571220566</v>
       </c>
       <c r="F530" t="n">
         <v>4887264</v>
@@ -11032,16 +11032,16 @@
         <v>44928</v>
       </c>
       <c r="B531" t="n">
-        <v>35.21263885498047</v>
+        <v>35.2126350402832</v>
       </c>
       <c r="C531" t="n">
-        <v>36.68265172299981</v>
+        <v>36.68264774905137</v>
       </c>
       <c r="D531" t="n">
-        <v>34.78710911009928</v>
+        <v>34.78710534150101</v>
       </c>
       <c r="E531" t="n">
-        <v>36.01534337329287</v>
+        <v>36.01533947163607</v>
       </c>
       <c r="F531" t="n">
         <v>2924313</v>
@@ -11152,16 +11152,16 @@
         <v>44936</v>
       </c>
       <c r="B537" t="n">
-        <v>37.79483413696289</v>
+        <v>37.79483032226562</v>
       </c>
       <c r="C537" t="n">
-        <v>38.07529521496675</v>
+        <v>38.07529137196207</v>
       </c>
       <c r="D537" t="n">
-        <v>36.49889993855829</v>
+        <v>36.49889625466188</v>
       </c>
       <c r="E537" t="n">
-        <v>37.09850831958851</v>
+        <v>37.0985045751726</v>
       </c>
       <c r="F537" t="n">
         <v>3183751</v>
@@ -11192,16 +11192,16 @@
         <v>44938</v>
       </c>
       <c r="B539" t="n">
-        <v>43.42343521118164</v>
+        <v>43.42343902587891</v>
       </c>
       <c r="C539" t="n">
-        <v>44.72904181410123</v>
+        <v>44.7290457434945</v>
       </c>
       <c r="D539" t="n">
-        <v>43.19132911953119</v>
+        <v>43.19133291383822</v>
       </c>
       <c r="E539" t="n">
-        <v>43.40409397377132</v>
+        <v>43.40409778676949</v>
       </c>
       <c r="F539" t="n">
         <v>7341055</v>
@@ -11212,16 +11212,16 @@
         <v>44939</v>
       </c>
       <c r="B540" t="n">
-        <v>42.75613021850586</v>
+        <v>42.75612640380859</v>
       </c>
       <c r="C540" t="n">
-        <v>43.50080726582102</v>
+        <v>43.50080338468374</v>
       </c>
       <c r="D540" t="n">
-        <v>42.35961420932546</v>
+        <v>42.35961043000531</v>
       </c>
       <c r="E540" t="n">
-        <v>43.42343856263282</v>
+        <v>43.42343468839838</v>
       </c>
       <c r="F540" t="n">
         <v>4249336</v>
@@ -11272,16 +11272,16 @@
         <v>44944</v>
       </c>
       <c r="B543" t="n">
-        <v>44.53562164306641</v>
+        <v>44.53561782836914</v>
       </c>
       <c r="C543" t="n">
-        <v>45.24161621271021</v>
+        <v>45.241612337541</v>
       </c>
       <c r="D543" t="n">
-        <v>43.22034619346439</v>
+        <v>43.220342491427</v>
       </c>
       <c r="E543" t="n">
-        <v>43.42343857092518</v>
+        <v>43.42343485149192</v>
       </c>
       <c r="F543" t="n">
         <v>6730959</v>
@@ -11332,16 +11332,16 @@
         <v>44949</v>
       </c>
       <c r="B546" t="n">
-        <v>46.45050811767578</v>
+        <v>46.45050430297852</v>
       </c>
       <c r="C546" t="n">
-        <v>48.53947429699662</v>
+        <v>48.53947031074529</v>
       </c>
       <c r="D546" t="n">
-        <v>45.88958222216792</v>
+        <v>45.88957845353607</v>
       </c>
       <c r="E546" t="n">
-        <v>47.67874234150205</v>
+        <v>47.67873842593739</v>
       </c>
       <c r="F546" t="n">
         <v>5971946</v>
@@ -11392,16 +11392,16 @@
         <v>44952</v>
       </c>
       <c r="B549" t="n">
-        <v>45.26095581054688</v>
+        <v>45.26095199584961</v>
       </c>
       <c r="C549" t="n">
-        <v>46.77932358255676</v>
+        <v>46.77931963988798</v>
       </c>
       <c r="D549" t="n">
-        <v>45.24161457234137</v>
+        <v>45.24161075927422</v>
       </c>
       <c r="E549" t="n">
-        <v>45.92826413060603</v>
+        <v>45.92826025966649</v>
       </c>
       <c r="F549" t="n">
         <v>3327082</v>
@@ -11412,16 +11412,16 @@
         <v>44953</v>
       </c>
       <c r="B550" t="n">
-        <v>44.5066032409668</v>
+        <v>44.50660705566406</v>
       </c>
       <c r="C550" t="n">
-        <v>46.34412192885299</v>
+        <v>46.34412590104548</v>
       </c>
       <c r="D550" t="n">
-        <v>44.16811098394805</v>
+        <v>44.16811476963287</v>
       </c>
       <c r="E550" t="n">
-        <v>46.20872577556058</v>
+        <v>46.20872973614816</v>
       </c>
       <c r="F550" t="n">
         <v>4035914</v>
@@ -11432,16 +11432,16 @@
         <v>44956</v>
       </c>
       <c r="B551" t="n">
-        <v>43.79094314575195</v>
+        <v>43.79093933105469</v>
       </c>
       <c r="C551" t="n">
-        <v>44.43890648207057</v>
+        <v>44.43890261092821</v>
       </c>
       <c r="D551" t="n">
-        <v>43.13330356893655</v>
+        <v>43.13329981152729</v>
       </c>
       <c r="E551" t="n">
-        <v>44.31318281197527</v>
+        <v>44.3131789517849</v>
       </c>
       <c r="F551" t="n">
         <v>3870439</v>
@@ -11572,16 +11572,16 @@
         <v>44965</v>
       </c>
       <c r="B558" t="n">
-        <v>43.12362670898438</v>
+        <v>43.12363052368164</v>
       </c>
       <c r="C558" t="n">
-        <v>43.13329920092593</v>
+        <v>43.13330301647882</v>
       </c>
       <c r="D558" t="n">
-        <v>42.08881622667597</v>
+        <v>42.08881994983436</v>
       </c>
       <c r="E558" t="n">
-        <v>42.57237336739773</v>
+        <v>42.57237713333137</v>
       </c>
       <c r="F558" t="n">
         <v>2757212</v>
@@ -11672,16 +11672,16 @@
         <v>44972</v>
       </c>
       <c r="B563" t="n">
-        <v>40.04821014404297</v>
+        <v>40.0482063293457</v>
       </c>
       <c r="C563" t="n">
-        <v>40.52209485081966</v>
+        <v>40.52209099098364</v>
       </c>
       <c r="D563" t="n">
-        <v>38.90701335343782</v>
+        <v>38.90700964744255</v>
       </c>
       <c r="E563" t="n">
-        <v>38.92635833968847</v>
+        <v>38.92635463185054</v>
       </c>
       <c r="F563" t="n">
         <v>3495706</v>
@@ -11752,16 +11752,16 @@
         <v>44980</v>
       </c>
       <c r="B567" t="n">
-        <v>38.00759887695312</v>
+        <v>38.00759506225586</v>
       </c>
       <c r="C567" t="n">
-        <v>39.07142321677222</v>
+        <v>39.07141929530241</v>
       </c>
       <c r="D567" t="n">
-        <v>37.73680654543994</v>
+        <v>37.7368027579212</v>
       </c>
       <c r="E567" t="n">
-        <v>37.95924390652058</v>
+        <v>37.95924009667655</v>
       </c>
       <c r="F567" t="n">
         <v>3548732</v>
@@ -11812,16 +11812,16 @@
         <v>44985</v>
       </c>
       <c r="B570" t="n">
-        <v>35.21263885498047</v>
+        <v>35.2126350402832</v>
       </c>
       <c r="C570" t="n">
-        <v>38.49115688632073</v>
+        <v>38.49115271645117</v>
       </c>
       <c r="D570" t="n">
-        <v>35.21263885498047</v>
+        <v>35.2126350402832</v>
       </c>
       <c r="E570" t="n">
-        <v>37.13719520026616</v>
+        <v>37.13719117707558</v>
       </c>
       <c r="F570" t="n">
         <v>11036876</v>
@@ -11832,16 +11832,16 @@
         <v>44986</v>
       </c>
       <c r="B571" t="n">
-        <v>31.52793121337891</v>
+        <v>31.52792930603027</v>
       </c>
       <c r="C571" t="n">
-        <v>35.21263762145776</v>
+        <v>35.21263549119504</v>
       </c>
       <c r="D571" t="n">
-        <v>29.89350662783602</v>
+        <v>29.89350481936535</v>
       </c>
       <c r="E571" t="n">
-        <v>35.10625518896411</v>
+        <v>35.10625306513723</v>
       </c>
       <c r="F571" t="n">
         <v>24633899</v>
@@ -11872,16 +11872,16 @@
         <v>44988</v>
       </c>
       <c r="B573" t="n">
-        <v>31.74069595336914</v>
+        <v>31.74069404602051</v>
       </c>
       <c r="C573" t="n">
-        <v>31.93411957920744</v>
+        <v>31.93411766023568</v>
       </c>
       <c r="D573" t="n">
-        <v>30.40607743217574</v>
+        <v>30.40607560502645</v>
       </c>
       <c r="E573" t="n">
-        <v>30.47377551384036</v>
+        <v>30.47377368262298</v>
       </c>
       <c r="F573" t="n">
         <v>7573675</v>
@@ -11892,16 +11892,16 @@
         <v>44991</v>
       </c>
       <c r="B574" t="n">
-        <v>31.86642074584961</v>
+        <v>31.86641883850098</v>
       </c>
       <c r="C574" t="n">
-        <v>32.34997795368473</v>
+        <v>32.34997601739302</v>
       </c>
       <c r="D574" t="n">
-        <v>30.94766317523564</v>
+        <v>30.94766132287878</v>
       </c>
       <c r="E574" t="n">
-        <v>31.74069707103675</v>
+        <v>31.74069517121325</v>
       </c>
       <c r="F574" t="n">
         <v>5963007</v>
@@ -11992,16 +11992,16 @@
         <v>44998</v>
       </c>
       <c r="B579" t="n">
-        <v>26.45058059692383</v>
+        <v>26.4505786895752</v>
       </c>
       <c r="C579" t="n">
-        <v>27.32098316598858</v>
+        <v>27.32098119587531</v>
       </c>
       <c r="D579" t="n">
-        <v>25.76392728704381</v>
+        <v>25.76392542920967</v>
       </c>
       <c r="E579" t="n">
-        <v>26.59564737946998</v>
+        <v>26.59564546166059</v>
       </c>
       <c r="F579" t="n">
         <v>13860726</v>
@@ -12032,16 +12032,16 @@
         <v>45000</v>
       </c>
       <c r="B581" t="n">
-        <v>26.28616905212402</v>
+        <v>26.28617095947266</v>
       </c>
       <c r="C581" t="n">
-        <v>26.82775179788365</v>
+        <v>26.82775374453002</v>
       </c>
       <c r="D581" t="n">
-        <v>25.62853138858268</v>
+        <v>25.62853324821252</v>
       </c>
       <c r="E581" t="n">
-        <v>26.58597321755539</v>
+        <v>26.58597514665809</v>
       </c>
       <c r="F581" t="n">
         <v>12174787</v>
@@ -12072,16 +12072,16 @@
         <v>45002</v>
       </c>
       <c r="B583" t="n">
-        <v>30.70588302612305</v>
+        <v>30.70588111877441</v>
       </c>
       <c r="C583" t="n">
-        <v>30.88963415624145</v>
+        <v>30.8896322374788</v>
       </c>
       <c r="D583" t="n">
-        <v>27.73684184447329</v>
+        <v>27.73684012155175</v>
       </c>
       <c r="E583" t="n">
-        <v>30.45443194157511</v>
+        <v>30.45443004984579</v>
       </c>
       <c r="F583" t="n">
         <v>23193684</v>
@@ -12092,16 +12092,16 @@
         <v>45005</v>
       </c>
       <c r="B584" t="n">
-        <v>29.79679489135742</v>
+        <v>29.79679679870605</v>
       </c>
       <c r="C584" t="n">
-        <v>31.20878203377826</v>
+        <v>31.20878403151084</v>
       </c>
       <c r="D584" t="n">
-        <v>29.32290834641774</v>
+        <v>29.32291022343201</v>
       </c>
       <c r="E584" t="n">
-        <v>30.70588175921954</v>
+        <v>30.70588372476053</v>
       </c>
       <c r="F584" t="n">
         <v>7729094</v>
@@ -12252,16 +12252,16 @@
         <v>45015</v>
       </c>
       <c r="B592" t="n">
-        <v>29.38093376159668</v>
+        <v>29.38093566894531</v>
       </c>
       <c r="C592" t="n">
-        <v>30.51245796745546</v>
+        <v>30.51245994826028</v>
       </c>
       <c r="D592" t="n">
-        <v>29.2745513361352</v>
+        <v>29.27455323657771</v>
       </c>
       <c r="E592" t="n">
-        <v>29.95153211069714</v>
+        <v>29.95153405508782</v>
       </c>
       <c r="F592" t="n">
         <v>5560645</v>
@@ -12312,16 +12312,16 @@
         <v>45020</v>
       </c>
       <c r="B595" t="n">
-        <v>27.92059135437012</v>
+        <v>27.92059326171875</v>
       </c>
       <c r="C595" t="n">
-        <v>29.70975320425825</v>
+        <v>29.70975523383049</v>
       </c>
       <c r="D595" t="n">
-        <v>27.91092073592187</v>
+        <v>27.91092264260987</v>
       </c>
       <c r="E595" t="n">
-        <v>29.57435705083184</v>
+        <v>29.57435907115471</v>
       </c>
       <c r="F595" t="n">
         <v>7552242</v>
@@ -12332,16 +12332,16 @@
         <v>45021</v>
       </c>
       <c r="B596" t="n">
-        <v>26.76972770690918</v>
+        <v>26.76972579956055</v>
       </c>
       <c r="C596" t="n">
-        <v>27.8528951326722</v>
+        <v>27.85289314814766</v>
       </c>
       <c r="D596" t="n">
-        <v>26.23781367622606</v>
+        <v>26.23781180677641</v>
       </c>
       <c r="E596" t="n">
-        <v>27.65947338188658</v>
+        <v>27.65947141114338</v>
       </c>
       <c r="F596" t="n">
         <v>12382825</v>
@@ -12372,16 +12372,16 @@
         <v>45026</v>
       </c>
       <c r="B598" t="n">
-        <v>29.6517276763916</v>
+        <v>29.65172576904297</v>
       </c>
       <c r="C598" t="n">
-        <v>29.83547880780963</v>
+        <v>29.8354768886412</v>
       </c>
       <c r="D598" t="n">
-        <v>28.19138549654949</v>
+        <v>28.19138368313743</v>
       </c>
       <c r="E598" t="n">
-        <v>28.33645227786835</v>
+        <v>28.33645045512486</v>
       </c>
       <c r="F598" t="n">
         <v>8774363</v>
@@ -12552,16 +12552,16 @@
         <v>45040</v>
       </c>
       <c r="B607" t="n">
-        <v>26.96700477600098</v>
+        <v>26.96700286865234</v>
       </c>
       <c r="C607" t="n">
-        <v>27.07506799883479</v>
+        <v>27.07506608384296</v>
       </c>
       <c r="D607" t="n">
-        <v>26.23020138729918</v>
+        <v>26.23019953206389</v>
       </c>
       <c r="E607" t="n">
-        <v>26.86876394941649</v>
+        <v>26.86876204901633</v>
       </c>
       <c r="F607" t="n">
         <v>6680100</v>
@@ -12572,16 +12572,16 @@
         <v>45041</v>
       </c>
       <c r="B608" t="n">
-        <v>27.21260261535645</v>
+        <v>27.21260452270508</v>
       </c>
       <c r="C608" t="n">
-        <v>27.45820371522866</v>
+        <v>27.45820563979163</v>
       </c>
       <c r="D608" t="n">
-        <v>26.42667797149275</v>
+        <v>26.42667982375542</v>
       </c>
       <c r="E608" t="n">
-        <v>26.79999269261962</v>
+        <v>26.79999457104816</v>
       </c>
       <c r="F608" t="n">
         <v>5323000</v>
@@ -12612,16 +12612,16 @@
         <v>45043</v>
       </c>
       <c r="B610" t="n">
-        <v>29.90439414978027</v>
+        <v>29.90439224243164</v>
       </c>
       <c r="C610" t="n">
-        <v>30.26788277330051</v>
+        <v>30.267880842768</v>
       </c>
       <c r="D610" t="n">
-        <v>26.73122612224756</v>
+        <v>26.73122441728851</v>
       </c>
       <c r="E610" t="n">
-        <v>26.73122612224756</v>
+        <v>26.73122441728851</v>
       </c>
       <c r="F610" t="n">
         <v>20933600</v>
@@ -12672,16 +12672,16 @@
         <v>45049</v>
       </c>
       <c r="B613" t="n">
-        <v>29.14794158935547</v>
+        <v>29.14793968200684</v>
       </c>
       <c r="C613" t="n">
-        <v>29.61949529963673</v>
+        <v>29.61949336143113</v>
       </c>
       <c r="D613" t="n">
-        <v>28.33254592932366</v>
+        <v>28.33254407533193</v>
       </c>
       <c r="E613" t="n">
-        <v>29.26583095381972</v>
+        <v>29.26582903875679</v>
       </c>
       <c r="F613" t="n">
         <v>9250000</v>
@@ -12692,16 +12692,16 @@
         <v>45050</v>
       </c>
       <c r="B614" t="n">
-        <v>29.27565383911133</v>
+        <v>29.2756519317627</v>
       </c>
       <c r="C614" t="n">
-        <v>29.95351348008578</v>
+        <v>29.95351152857367</v>
       </c>
       <c r="D614" t="n">
-        <v>29.17741488650197</v>
+        <v>29.17741298555374</v>
       </c>
       <c r="E614" t="n">
-        <v>29.47213549190587</v>
+        <v>29.47213357175619</v>
       </c>
       <c r="F614" t="n">
         <v>6670900</v>
@@ -12792,16 +12792,16 @@
         <v>45057</v>
       </c>
       <c r="B619" t="n">
-        <v>31.66289710998535</v>
+        <v>31.66289520263672</v>
       </c>
       <c r="C619" t="n">
-        <v>31.81025928645763</v>
+        <v>31.81025737023202</v>
       </c>
       <c r="D619" t="n">
-        <v>31.10292683551199</v>
+        <v>31.10292496189554</v>
       </c>
       <c r="E619" t="n">
-        <v>31.71201658628417</v>
+        <v>31.71201467597662</v>
       </c>
       <c r="F619" t="n">
         <v>4858000</v>
@@ -12812,16 +12812,16 @@
         <v>45058</v>
       </c>
       <c r="B620" t="n">
-        <v>32.49794387817383</v>
+        <v>32.49794006347656</v>
       </c>
       <c r="C620" t="n">
-        <v>32.64530231015733</v>
+        <v>32.64529847816273</v>
       </c>
       <c r="D620" t="n">
-        <v>31.46641611640984</v>
+        <v>31.46641242279611</v>
       </c>
       <c r="E620" t="n">
-        <v>31.55483267463029</v>
+        <v>31.554828970638</v>
       </c>
       <c r="F620" t="n">
         <v>5317000</v>
@@ -12852,16 +12852,16 @@
         <v>45062</v>
       </c>
       <c r="B622" t="n">
-        <v>29.90439414978027</v>
+        <v>29.90439224243164</v>
       </c>
       <c r="C622" t="n">
-        <v>32.08533151226543</v>
+        <v>32.08532946581322</v>
       </c>
       <c r="D622" t="n">
-        <v>29.70791249602647</v>
+        <v>29.70791060120974</v>
       </c>
       <c r="E622" t="n">
-        <v>31.86920131837866</v>
+        <v>31.86919928571158</v>
       </c>
       <c r="F622" t="n">
         <v>13269700</v>
@@ -12912,16 +12912,16 @@
         <v>45065</v>
       </c>
       <c r="B625" t="n">
-        <v>32.49794387817383</v>
+        <v>32.49794006347656</v>
       </c>
       <c r="C625" t="n">
-        <v>34.87536105853923</v>
+        <v>34.87535696477425</v>
       </c>
       <c r="D625" t="n">
-        <v>31.0439837395418</v>
+        <v>31.04398009551434</v>
       </c>
       <c r="E625" t="n">
-        <v>31.86920182661951</v>
+        <v>31.8691980857257</v>
       </c>
       <c r="F625" t="n">
         <v>19443700</v>
@@ -12972,16 +12972,16 @@
         <v>45070</v>
       </c>
       <c r="B628" t="n">
-        <v>31.48606109619141</v>
+        <v>31.48606300354004</v>
       </c>
       <c r="C628" t="n">
-        <v>31.86919822262693</v>
+        <v>31.86920015318507</v>
       </c>
       <c r="D628" t="n">
-        <v>30.46436146776744</v>
+        <v>30.464363313224</v>
       </c>
       <c r="E628" t="n">
-        <v>31.04398022887067</v>
+        <v>31.04398210943912</v>
       </c>
       <c r="F628" t="n">
         <v>7685200</v>
@@ -13212,16 +13212,16 @@
         <v>45089</v>
       </c>
       <c r="B640" t="n">
-        <v>31.26011085510254</v>
+        <v>31.26010894775391</v>
       </c>
       <c r="C640" t="n">
-        <v>31.86920059509758</v>
+        <v>31.86919865058509</v>
       </c>
       <c r="D640" t="n">
-        <v>30.47418800549994</v>
+        <v>30.47418614610471</v>
       </c>
       <c r="E640" t="n">
-        <v>31.61377707431765</v>
+        <v>31.61377514538992</v>
       </c>
       <c r="F640" t="n">
         <v>7223600</v>
@@ -13252,16 +13252,16 @@
         <v>45091</v>
       </c>
       <c r="B642" t="n">
-        <v>31.14222145080566</v>
+        <v>31.1422233581543</v>
       </c>
       <c r="C642" t="n">
-        <v>31.71201407641177</v>
+        <v>31.71201601865814</v>
       </c>
       <c r="D642" t="n">
-        <v>30.5724269514118</v>
+        <v>30.57242882386257</v>
       </c>
       <c r="E642" t="n">
-        <v>31.33870121423831</v>
+        <v>31.33870313362062</v>
       </c>
       <c r="F642" t="n">
         <v>8288400</v>
@@ -13292,16 +13292,16 @@
         <v>45093</v>
       </c>
       <c r="B644" t="n">
-        <v>31.9183235168457</v>
+        <v>31.91832160949707</v>
       </c>
       <c r="C644" t="n">
-        <v>31.9183235168457</v>
+        <v>31.91832160949707</v>
       </c>
       <c r="D644" t="n">
-        <v>31.19134254558997</v>
+        <v>31.19134068168367</v>
       </c>
       <c r="E644" t="n">
-        <v>31.4271193982454</v>
+        <v>31.42711752024974</v>
       </c>
       <c r="F644" t="n">
         <v>5722800</v>
@@ -13332,16 +13332,16 @@
         <v>45097</v>
       </c>
       <c r="B646" t="n">
-        <v>32.16392517089844</v>
+        <v>32.16392135620117</v>
       </c>
       <c r="C646" t="n">
-        <v>32.2916350584061</v>
+        <v>32.29163122856222</v>
       </c>
       <c r="D646" t="n">
-        <v>31.48606366340425</v>
+        <v>31.48605992910253</v>
       </c>
       <c r="E646" t="n">
-        <v>32.12462809124572</v>
+        <v>32.12462428120915</v>
       </c>
       <c r="F646" t="n">
         <v>4954700</v>
@@ -13352,16 +13352,16 @@
         <v>45098</v>
       </c>
       <c r="B647" t="n">
-        <v>32.06567764282227</v>
+        <v>32.06568145751953</v>
       </c>
       <c r="C647" t="n">
-        <v>32.36039820068254</v>
+        <v>32.36040205044127</v>
       </c>
       <c r="D647" t="n">
-        <v>31.4860589217478</v>
+        <v>31.48606266749066</v>
       </c>
       <c r="E647" t="n">
-        <v>32.1246232534244</v>
+        <v>32.12462707513414</v>
       </c>
       <c r="F647" t="n">
         <v>4670300</v>
@@ -13412,16 +13412,16 @@
         <v>45103</v>
       </c>
       <c r="B650" t="n">
-        <v>30.53312873840332</v>
+        <v>30.53313064575195</v>
       </c>
       <c r="C650" t="n">
-        <v>30.83767357835474</v>
+        <v>30.83767550472773</v>
       </c>
       <c r="D650" t="n">
-        <v>30.30717617565832</v>
+        <v>30.30717806889212</v>
       </c>
       <c r="E650" t="n">
-        <v>30.58224820898695</v>
+        <v>30.58225011940398</v>
       </c>
       <c r="F650" t="n">
         <v>2874500</v>
@@ -13452,16 +13452,16 @@
         <v>45105</v>
       </c>
       <c r="B652" t="n">
-        <v>29.37389373779297</v>
+        <v>29.37389183044434</v>
       </c>
       <c r="C652" t="n">
-        <v>30.06157762706682</v>
+        <v>30.06157567506449</v>
       </c>
       <c r="D652" t="n">
-        <v>29.30512572362315</v>
+        <v>29.30512382073987</v>
       </c>
       <c r="E652" t="n">
-        <v>29.75703276126285</v>
+        <v>29.75703082903567</v>
       </c>
       <c r="F652" t="n">
         <v>4532500</v>
@@ -13532,16 +13532,16 @@
         <v>45111</v>
       </c>
       <c r="B656" t="n">
-        <v>29.80615043640137</v>
+        <v>29.80615234375</v>
       </c>
       <c r="C656" t="n">
-        <v>30.15981662939312</v>
+        <v>30.15981855937348</v>
       </c>
       <c r="D656" t="n">
-        <v>29.57037359900278</v>
+        <v>29.57037549126363</v>
       </c>
       <c r="E656" t="n">
-        <v>29.80615043640137</v>
+        <v>29.80615234375</v>
       </c>
       <c r="F656" t="n">
         <v>2514900</v>
@@ -13552,16 +13552,16 @@
         <v>45112</v>
       </c>
       <c r="B657" t="n">
-        <v>30.40541839599609</v>
+        <v>30.40542030334473</v>
       </c>
       <c r="C657" t="n">
-        <v>30.70996325002402</v>
+        <v>30.70996517647691</v>
       </c>
       <c r="D657" t="n">
-        <v>29.34442166777476</v>
+        <v>29.34442350856649</v>
       </c>
       <c r="E657" t="n">
-        <v>29.60966944448926</v>
+        <v>29.60967130192012</v>
       </c>
       <c r="F657" t="n">
         <v>5394800</v>
@@ -13612,16 +13612,16 @@
         <v>45117</v>
       </c>
       <c r="B660" t="n">
-        <v>31.07345199584961</v>
+        <v>31.07345390319824</v>
       </c>
       <c r="C660" t="n">
-        <v>31.93796708924193</v>
+        <v>31.93796904965617</v>
       </c>
       <c r="D660" t="n">
-        <v>30.84749942157282</v>
+        <v>30.84750131505205</v>
       </c>
       <c r="E660" t="n">
-        <v>31.56465609569361</v>
+        <v>31.56465803319331</v>
       </c>
       <c r="F660" t="n">
         <v>7339200</v>
@@ -13652,16 +13652,16 @@
         <v>45119</v>
       </c>
       <c r="B662" t="n">
-        <v>31.07345199584961</v>
+        <v>31.07345390319824</v>
       </c>
       <c r="C662" t="n">
-        <v>32.08532925608902</v>
+        <v>32.08533122554864</v>
       </c>
       <c r="D662" t="n">
-        <v>31.04398106151042</v>
+        <v>31.04398296705007</v>
       </c>
       <c r="E662" t="n">
-        <v>31.77096013121909</v>
+        <v>31.77096208138212</v>
       </c>
       <c r="F662" t="n">
         <v>4503800</v>
@@ -13732,16 +13732,16 @@
         <v>45125</v>
       </c>
       <c r="B666" t="n">
-        <v>32.91055297851562</v>
+        <v>32.91054916381836</v>
       </c>
       <c r="C666" t="n">
-        <v>33.03826662148488</v>
+        <v>33.03826279198419</v>
       </c>
       <c r="D666" t="n">
-        <v>32.03621351392245</v>
+        <v>32.0362098005708</v>
       </c>
       <c r="E666" t="n">
-        <v>32.18357195035527</v>
+        <v>32.18356821992315</v>
       </c>
       <c r="F666" t="n">
         <v>4775600</v>
@@ -13752,16 +13752,16 @@
         <v>45126</v>
       </c>
       <c r="B667" t="n">
-        <v>33.6473503112793</v>
+        <v>33.64735412597656</v>
       </c>
       <c r="C667" t="n">
-        <v>34.04031356576963</v>
+        <v>34.04031742501827</v>
       </c>
       <c r="D667" t="n">
-        <v>33.04808303459044</v>
+        <v>33.04808678134705</v>
       </c>
       <c r="E667" t="n">
-        <v>33.04808303459044</v>
+        <v>33.04808678134705</v>
       </c>
       <c r="F667" t="n">
         <v>7484200</v>
@@ -13772,16 +13772,16 @@
         <v>45127</v>
       </c>
       <c r="B668" t="n">
-        <v>33.92242813110352</v>
+        <v>33.92242431640625</v>
       </c>
       <c r="C668" t="n">
-        <v>34.11890979188617</v>
+        <v>34.11890595509385</v>
       </c>
       <c r="D668" t="n">
-        <v>33.64735605455338</v>
+        <v>33.64735227078894</v>
       </c>
       <c r="E668" t="n">
-        <v>33.91260573447357</v>
+        <v>33.91260192088087</v>
       </c>
       <c r="F668" t="n">
         <v>3587900</v>
@@ -13952,16 +13952,16 @@
         <v>45140</v>
       </c>
       <c r="B677" t="n">
-        <v>34.4431037902832</v>
+        <v>34.44309997558594</v>
       </c>
       <c r="C677" t="n">
-        <v>34.5806398233511</v>
+        <v>34.58063599342123</v>
       </c>
       <c r="D677" t="n">
-        <v>33.71612279718397</v>
+        <v>33.71611906300245</v>
       </c>
       <c r="E677" t="n">
-        <v>34.38415817000732</v>
+        <v>34.38415436183849</v>
       </c>
       <c r="F677" t="n">
         <v>3408800</v>
@@ -14012,16 +14012,16 @@
         <v>45145</v>
       </c>
       <c r="B680" t="n">
-        <v>35.68092727661133</v>
+        <v>35.68093109130859</v>
       </c>
       <c r="C680" t="n">
-        <v>36.15248093584172</v>
+        <v>36.15248480095344</v>
       </c>
       <c r="D680" t="n">
-        <v>35.09148613946717</v>
+        <v>35.09148989114647</v>
       </c>
       <c r="E680" t="n">
-        <v>36.05424199550948</v>
+        <v>36.05424585011833</v>
       </c>
       <c r="F680" t="n">
         <v>3820600</v>
@@ -14032,16 +14032,16 @@
         <v>45146</v>
       </c>
       <c r="B681" t="n">
-        <v>36.34896469116211</v>
+        <v>36.34896850585938</v>
       </c>
       <c r="C681" t="n">
-        <v>36.51597164901496</v>
+        <v>36.51597548123902</v>
       </c>
       <c r="D681" t="n">
-        <v>34.30556163401185</v>
+        <v>34.30556523426109</v>
       </c>
       <c r="E681" t="n">
-        <v>34.76729292525891</v>
+        <v>34.76729657396523</v>
       </c>
       <c r="F681" t="n">
         <v>5274900</v>
@@ -14172,16 +14172,16 @@
         <v>45155</v>
       </c>
       <c r="B688" t="n">
-        <v>31.26993370056152</v>
+        <v>31.26993560791016</v>
       </c>
       <c r="C688" t="n">
-        <v>31.74148926263102</v>
+        <v>31.74149119874277</v>
       </c>
       <c r="D688" t="n">
-        <v>30.9653888444364</v>
+        <v>30.96539073320894</v>
       </c>
       <c r="E688" t="n">
-        <v>31.46641346711834</v>
+        <v>31.4664153864515</v>
       </c>
       <c r="F688" t="n">
         <v>4529600</v>
@@ -14252,16 +14252,16 @@
         <v>45161</v>
       </c>
       <c r="B692" t="n">
-        <v>31.05380630493164</v>
+        <v>31.05380439758301</v>
       </c>
       <c r="C692" t="n">
-        <v>31.2404618075605</v>
+        <v>31.24045988874735</v>
       </c>
       <c r="D692" t="n">
-        <v>30.68049155209822</v>
+        <v>30.68048966767887</v>
       </c>
       <c r="E692" t="n">
-        <v>31.09310150987904</v>
+        <v>31.09309960011686</v>
       </c>
       <c r="F692" t="n">
         <v>4847400</v>
@@ -14272,16 +14272,16 @@
         <v>45162</v>
       </c>
       <c r="B693" t="n">
-        <v>30.91626930236816</v>
+        <v>30.91626739501953</v>
       </c>
       <c r="C693" t="n">
-        <v>31.30923260599883</v>
+        <v>31.30923067440671</v>
       </c>
       <c r="D693" t="n">
-        <v>30.56260495240363</v>
+        <v>30.56260306687397</v>
       </c>
       <c r="E693" t="n">
-        <v>31.05380720815405</v>
+        <v>31.05380529232016</v>
       </c>
       <c r="F693" t="n">
         <v>3471700</v>
@@ -14332,16 +14332,16 @@
         <v>45167</v>
       </c>
       <c r="B696" t="n">
-        <v>31.29940795898438</v>
+        <v>31.29940605163574</v>
       </c>
       <c r="C696" t="n">
-        <v>31.55483147996431</v>
+        <v>31.55482955705047</v>
       </c>
       <c r="D696" t="n">
-        <v>30.63137259940515</v>
+        <v>30.63137073276579</v>
       </c>
       <c r="E696" t="n">
-        <v>31.06363110391898</v>
+        <v>31.06362921093831</v>
       </c>
       <c r="F696" t="n">
         <v>3743200</v>
@@ -14352,16 +14352,16 @@
         <v>45168</v>
       </c>
       <c r="B697" t="n">
-        <v>31.6334228515625</v>
+        <v>31.63342475891113</v>
       </c>
       <c r="C697" t="n">
-        <v>31.70219086067396</v>
+        <v>31.70219277216898</v>
       </c>
       <c r="D697" t="n">
-        <v>30.96538755084366</v>
+        <v>30.96538941791287</v>
       </c>
       <c r="E697" t="n">
-        <v>31.49588683333958</v>
+        <v>31.49588873239543</v>
       </c>
       <c r="F697" t="n">
         <v>3276100</v>
@@ -14412,16 +14412,16 @@
         <v>45173</v>
       </c>
       <c r="B700" t="n">
-        <v>32.2719841003418</v>
+        <v>32.27198791503906</v>
       </c>
       <c r="C700" t="n">
-        <v>32.55688228511206</v>
+        <v>32.55688613348561</v>
       </c>
       <c r="D700" t="n">
-        <v>32.06568006898767</v>
+        <v>32.06568385929886</v>
       </c>
       <c r="E700" t="n">
-        <v>32.22286462824446</v>
+        <v>32.22286843713558</v>
       </c>
       <c r="F700" t="n">
         <v>2652900</v>
@@ -14432,16 +14432,16 @@
         <v>45174</v>
       </c>
       <c r="B701" t="n">
-        <v>32.63547515869141</v>
+        <v>32.63547897338867</v>
       </c>
       <c r="C701" t="n">
-        <v>32.93019572729314</v>
+        <v>32.93019957643972</v>
       </c>
       <c r="D701" t="n">
-        <v>32.07550495407551</v>
+        <v>32.07550870331895</v>
       </c>
       <c r="E701" t="n">
-        <v>32.27198283475976</v>
+        <v>32.27198660696912</v>
       </c>
       <c r="F701" t="n">
         <v>6036900</v>
@@ -14452,16 +14452,16 @@
         <v>45175</v>
       </c>
       <c r="B702" t="n">
-        <v>32.00674057006836</v>
+        <v>32.00673675537109</v>
       </c>
       <c r="C702" t="n">
-        <v>32.71406926527997</v>
+        <v>32.71406536628031</v>
       </c>
       <c r="D702" t="n">
-        <v>31.92814641083608</v>
+        <v>31.928142605506</v>
       </c>
       <c r="E702" t="n">
-        <v>32.65512739343153</v>
+        <v>32.65512350145682</v>
       </c>
       <c r="F702" t="n">
         <v>4505300</v>
@@ -14512,16 +14512,16 @@
         <v>45181</v>
       </c>
       <c r="B705" t="n">
-        <v>32.3309326171875</v>
+        <v>32.33092880249023</v>
       </c>
       <c r="C705" t="n">
-        <v>32.6453017639165</v>
+        <v>32.64529791212711</v>
       </c>
       <c r="D705" t="n">
-        <v>31.76113994408213</v>
+        <v>31.76113619661418</v>
       </c>
       <c r="E705" t="n">
-        <v>31.97726639022342</v>
+        <v>31.97726261725491</v>
       </c>
       <c r="F705" t="n">
         <v>3620500</v>
@@ -14532,16 +14532,16 @@
         <v>45182</v>
       </c>
       <c r="B706" t="n">
-        <v>31.6334228515625</v>
+        <v>31.63342475891113</v>
       </c>
       <c r="C706" t="n">
-        <v>32.11479891534272</v>
+        <v>32.1148008517161</v>
       </c>
       <c r="D706" t="n">
-        <v>31.44676361462388</v>
+        <v>31.44676551071783</v>
       </c>
       <c r="E706" t="n">
-        <v>31.60394817081799</v>
+        <v>31.60395007638945</v>
       </c>
       <c r="F706" t="n">
         <v>7302700</v>
@@ -14552,16 +14552,16 @@
         <v>45183</v>
       </c>
       <c r="B707" t="n">
-        <v>32.311279296875</v>
+        <v>32.31128311157227</v>
       </c>
       <c r="C707" t="n">
-        <v>32.311279296875</v>
+        <v>32.31128311157227</v>
       </c>
       <c r="D707" t="n">
-        <v>31.74148670806588</v>
+        <v>31.74149045549294</v>
       </c>
       <c r="E707" t="n">
-        <v>31.83972564654409</v>
+        <v>31.83972940556933</v>
       </c>
       <c r="F707" t="n">
         <v>4362300</v>
@@ -14592,16 +14592,16 @@
         <v>45187</v>
       </c>
       <c r="B709" t="n">
-        <v>31.98709297180176</v>
+        <v>31.98709106445312</v>
       </c>
       <c r="C709" t="n">
-        <v>32.71407022822005</v>
+        <v>32.7140682775227</v>
       </c>
       <c r="D709" t="n">
-        <v>31.75131423474054</v>
+        <v>31.75131234145109</v>
       </c>
       <c r="E709" t="n">
-        <v>32.55688565270453</v>
+        <v>32.5568837113799</v>
       </c>
       <c r="F709" t="n">
         <v>5099000</v>
@@ -14692,16 +14692,16 @@
         <v>45194</v>
       </c>
       <c r="B714" t="n">
-        <v>30.95556640625</v>
+        <v>30.95556449890137</v>
       </c>
       <c r="C714" t="n">
-        <v>31.20116753431566</v>
+        <v>31.20116561183414</v>
       </c>
       <c r="D714" t="n">
-        <v>29.99281043394172</v>
+        <v>29.99280858591396</v>
       </c>
       <c r="E714" t="n">
-        <v>30.45453988014151</v>
+        <v>30.45453800366397</v>
       </c>
       <c r="F714" t="n">
         <v>6350700</v>
@@ -14712,16 +14712,16 @@
         <v>45195</v>
       </c>
       <c r="B715" t="n">
-        <v>30.32682800292969</v>
+        <v>30.32682609558105</v>
       </c>
       <c r="C715" t="n">
-        <v>30.83767692328888</v>
+        <v>30.83767498381136</v>
       </c>
       <c r="D715" t="n">
-        <v>30.19911436749897</v>
+        <v>30.19911246818264</v>
       </c>
       <c r="E715" t="n">
-        <v>30.75908463755763</v>
+        <v>30.75908270302303</v>
       </c>
       <c r="F715" t="n">
         <v>3433500</v>
@@ -14732,16 +14732,16 @@
         <v>45196</v>
       </c>
       <c r="B716" t="n">
-        <v>30.86714744567871</v>
+        <v>30.86714935302734</v>
       </c>
       <c r="C716" t="n">
-        <v>31.07345147776449</v>
+        <v>31.0734533978611</v>
       </c>
       <c r="D716" t="n">
-        <v>30.42506470008381</v>
+        <v>30.42506658011519</v>
       </c>
       <c r="E716" t="n">
-        <v>30.65101914438107</v>
+        <v>30.65102103837466</v>
       </c>
       <c r="F716" t="n">
         <v>4307600</v>
@@ -14752,16 +14752,16 @@
         <v>45197</v>
       </c>
       <c r="B717" t="n">
-        <v>30.58225059509277</v>
+        <v>30.58224868774414</v>
       </c>
       <c r="C717" t="n">
-        <v>31.21099073558775</v>
+        <v>31.21098878902595</v>
       </c>
       <c r="D717" t="n">
-        <v>30.41524175877521</v>
+        <v>30.41523986184255</v>
       </c>
       <c r="E717" t="n">
-        <v>30.82785171474873</v>
+        <v>30.82784979208249</v>
       </c>
       <c r="F717" t="n">
         <v>4298000</v>
@@ -14772,16 +14772,16 @@
         <v>45198</v>
       </c>
       <c r="B718" t="n">
-        <v>31.02433204650879</v>
+        <v>31.02433395385742</v>
       </c>
       <c r="C718" t="n">
-        <v>31.60394894047274</v>
+        <v>31.60395088345571</v>
       </c>
       <c r="D718" t="n">
-        <v>30.47418608643163</v>
+        <v>30.47418795995777</v>
       </c>
       <c r="E718" t="n">
-        <v>30.86714748648674</v>
+        <v>30.86714938417181</v>
       </c>
       <c r="F718" t="n">
         <v>5846000</v>
@@ -14852,16 +14852,16 @@
         <v>45204</v>
       </c>
       <c r="B722" t="n">
-        <v>28.0378246307373</v>
+        <v>28.03782272338867</v>
       </c>
       <c r="C722" t="n">
-        <v>28.78445038319864</v>
+        <v>28.78444842505877</v>
       </c>
       <c r="D722" t="n">
-        <v>27.72345362458937</v>
+        <v>27.72345173862667</v>
       </c>
       <c r="E722" t="n">
-        <v>28.62726581701858</v>
+        <v>28.62726386957162</v>
       </c>
       <c r="F722" t="n">
         <v>8409300</v>
@@ -14912,16 +14912,16 @@
         <v>45209</v>
       </c>
       <c r="B725" t="n">
-        <v>30.2777042388916</v>
+        <v>30.27770614624023</v>
       </c>
       <c r="C725" t="n">
-        <v>30.40541786413846</v>
+        <v>30.40541977953243</v>
       </c>
       <c r="D725" t="n">
-        <v>29.43283582930937</v>
+        <v>29.43283768343539</v>
       </c>
       <c r="E725" t="n">
-        <v>29.7570310901109</v>
+        <v>29.75703296465965</v>
       </c>
       <c r="F725" t="n">
         <v>7018100</v>
@@ -14972,16 +14972,16 @@
         <v>45215</v>
       </c>
       <c r="B728" t="n">
-        <v>31.67272186279297</v>
+        <v>31.67271995544434</v>
       </c>
       <c r="C728" t="n">
-        <v>32.01656192935982</v>
+        <v>32.01656000130495</v>
       </c>
       <c r="D728" t="n">
-        <v>31.32887804865046</v>
+        <v>31.32887616200829</v>
       </c>
       <c r="E728" t="n">
-        <v>31.91832298107662</v>
+        <v>31.91832105893775</v>
       </c>
       <c r="F728" t="n">
         <v>3741500</v>
@@ -15012,16 +15012,16 @@
         <v>45217</v>
       </c>
       <c r="B730" t="n">
-        <v>32.06567764282227</v>
+        <v>32.06568145751953</v>
       </c>
       <c r="C730" t="n">
-        <v>33.06773053760736</v>
+        <v>33.06773447151397</v>
       </c>
       <c r="D730" t="n">
-        <v>31.63342107446555</v>
+        <v>31.63342483773936</v>
       </c>
       <c r="E730" t="n">
-        <v>32.52740889026767</v>
+        <v>32.52741275989484</v>
       </c>
       <c r="F730" t="n">
         <v>7439800</v>
@@ -15132,16 +15132,16 @@
         <v>45225</v>
       </c>
       <c r="B736" t="n">
-        <v>31.98709297180176</v>
+        <v>31.98709106445312</v>
       </c>
       <c r="C736" t="n">
-        <v>32.12462900693085</v>
+        <v>32.12462709138111</v>
       </c>
       <c r="D736" t="n">
-        <v>31.19134395024304</v>
+        <v>31.19134209034388</v>
       </c>
       <c r="E736" t="n">
-        <v>31.57448111883861</v>
+        <v>31.57447923609348</v>
       </c>
       <c r="F736" t="n">
         <v>2923500</v>
@@ -15152,16 +15152,16 @@
         <v>45226</v>
       </c>
       <c r="B737" t="n">
-        <v>31.52536010742188</v>
+        <v>31.52535820007324</v>
       </c>
       <c r="C737" t="n">
-        <v>32.55688406826494</v>
+        <v>32.556882098507</v>
       </c>
       <c r="D737" t="n">
-        <v>31.24046190704763</v>
+        <v>31.24046001693592</v>
       </c>
       <c r="E737" t="n">
-        <v>32.32110909025403</v>
+        <v>32.32110713476096</v>
       </c>
       <c r="F737" t="n">
         <v>3378100</v>
@@ -15172,16 +15172,16 @@
         <v>45229</v>
       </c>
       <c r="B738" t="n">
-        <v>31.07345199584961</v>
+        <v>31.07345390319824</v>
       </c>
       <c r="C738" t="n">
-        <v>32.11480019042821</v>
+        <v>32.11480216169681</v>
       </c>
       <c r="D738" t="n">
-        <v>30.98503731904426</v>
+        <v>30.98503922096583</v>
       </c>
       <c r="E738" t="n">
-        <v>31.5450075569423</v>
+        <v>31.54500949323592</v>
       </c>
       <c r="F738" t="n">
         <v>3227500</v>
@@ -15192,16 +15192,16 @@
         <v>45230</v>
       </c>
       <c r="B739" t="n">
-        <v>31.86919975280762</v>
+        <v>31.86919784545898</v>
       </c>
       <c r="C739" t="n">
-        <v>32.10497847524474</v>
+        <v>32.10497655378492</v>
       </c>
       <c r="D739" t="n">
-        <v>31.2011662851952</v>
+        <v>31.20116441782789</v>
       </c>
       <c r="E739" t="n">
-        <v>31.2011662851952</v>
+        <v>31.20116441782789</v>
       </c>
       <c r="F739" t="n">
         <v>3372100</v>
@@ -15212,16 +15212,16 @@
         <v>45231</v>
       </c>
       <c r="B740" t="n">
-        <v>32.06567764282227</v>
+        <v>32.06568145751953</v>
       </c>
       <c r="C740" t="n">
-        <v>32.74353904823363</v>
+        <v>32.74354294357276</v>
       </c>
       <c r="D740" t="n">
-        <v>31.9477901691932</v>
+        <v>31.94779396986597</v>
       </c>
       <c r="E740" t="n">
-        <v>32.07550378504357</v>
+        <v>32.0755076009098</v>
       </c>
       <c r="F740" t="n">
         <v>4282500</v>
@@ -15232,16 +15232,16 @@
         <v>45233</v>
       </c>
       <c r="B741" t="n">
-        <v>32.69441986083984</v>
+        <v>32.69441604614258</v>
       </c>
       <c r="C741" t="n">
-        <v>32.94984712401398</v>
+        <v>32.94984327951414</v>
       </c>
       <c r="D741" t="n">
-        <v>32.46846728038622</v>
+        <v>32.4684634920525</v>
       </c>
       <c r="E741" t="n">
-        <v>32.73371693941674</v>
+        <v>32.7337131201344</v>
       </c>
       <c r="F741" t="n">
         <v>3190300</v>
@@ -15272,16 +15272,16 @@
         <v>45237</v>
       </c>
       <c r="B743" t="n">
-        <v>32.48811721801758</v>
+        <v>32.48811340332031</v>
       </c>
       <c r="C743" t="n">
-        <v>32.63547939523581</v>
+        <v>32.63547556323554</v>
       </c>
       <c r="D743" t="n">
-        <v>31.81025944748058</v>
+        <v>31.81025571237618</v>
       </c>
       <c r="E743" t="n">
-        <v>31.8790274641622</v>
+        <v>31.87902372098318</v>
       </c>
       <c r="F743" t="n">
         <v>3324000</v>
@@ -15312,16 +15312,16 @@
         <v>45239</v>
       </c>
       <c r="B745" t="n">
-        <v>30.81802749633789</v>
+        <v>30.81802940368652</v>
       </c>
       <c r="C745" t="n">
-        <v>33.77506502697286</v>
+        <v>33.77506711733456</v>
       </c>
       <c r="D745" t="n">
-        <v>30.67066533422895</v>
+        <v>30.67066723245724</v>
       </c>
       <c r="E745" t="n">
-        <v>33.41157269312426</v>
+        <v>33.41157476098916</v>
       </c>
       <c r="F745" t="n">
         <v>15431300</v>
@@ -15332,16 +15332,16 @@
         <v>45240</v>
       </c>
       <c r="B746" t="n">
-        <v>31.25028610229492</v>
+        <v>31.25028419494629</v>
       </c>
       <c r="C746" t="n">
-        <v>32.06568174882637</v>
+        <v>32.06567979171039</v>
       </c>
       <c r="D746" t="n">
-        <v>31.04398206013306</v>
+        <v>31.04398016537612</v>
       </c>
       <c r="E746" t="n">
-        <v>31.05380632982475</v>
+        <v>31.05380443446818</v>
       </c>
       <c r="F746" t="n">
         <v>4738300</v>
@@ -15352,16 +15352,16 @@
         <v>45243</v>
       </c>
       <c r="B747" t="n">
-        <v>30.94573974609375</v>
+        <v>30.94574165344238</v>
       </c>
       <c r="C747" t="n">
-        <v>31.41729342584897</v>
+        <v>31.41729536226194</v>
       </c>
       <c r="D747" t="n">
-        <v>30.67066582934266</v>
+        <v>30.67066771973704</v>
       </c>
       <c r="E747" t="n">
-        <v>31.21098939362647</v>
+        <v>31.21099131732383</v>
       </c>
       <c r="F747" t="n">
         <v>3172300</v>
@@ -15392,16 +15392,16 @@
         <v>45246</v>
       </c>
       <c r="B749" t="n">
-        <v>31.13239860534668</v>
+        <v>31.13239669799805</v>
       </c>
       <c r="C749" t="n">
-        <v>32.13444975439192</v>
+        <v>32.13444778565191</v>
       </c>
       <c r="D749" t="n">
-        <v>30.68049156858774</v>
+        <v>30.68048968892551</v>
       </c>
       <c r="E749" t="n">
-        <v>31.78078354073604</v>
+        <v>31.78078159366364</v>
       </c>
       <c r="F749" t="n">
         <v>5148500</v>
@@ -15492,16 +15492,16 @@
         <v>45253</v>
       </c>
       <c r="B754" t="n">
-        <v>31.81025505065918</v>
+        <v>31.81025886535645</v>
       </c>
       <c r="C754" t="n">
-        <v>32.00673667726713</v>
+        <v>32.00674051552654</v>
       </c>
       <c r="D754" t="n">
-        <v>31.5843024917114</v>
+        <v>31.58430627931235</v>
       </c>
       <c r="E754" t="n">
-        <v>31.82990358807751</v>
+        <v>31.82990740513103</v>
       </c>
       <c r="F754" t="n">
         <v>2086300</v>
@@ -15552,16 +15552,16 @@
         <v>45258</v>
       </c>
       <c r="B757" t="n">
-        <v>29.80615043640137</v>
+        <v>29.80615234375</v>
       </c>
       <c r="C757" t="n">
-        <v>30.21876037029583</v>
+        <v>30.21876230404811</v>
       </c>
       <c r="D757" t="n">
-        <v>29.63914160902057</v>
+        <v>29.63914350568201</v>
       </c>
       <c r="E757" t="n">
-        <v>30.17946329383553</v>
+        <v>30.17946522507312</v>
       </c>
       <c r="F757" t="n">
         <v>5777500</v>
@@ -15592,16 +15592,16 @@
         <v>45260</v>
       </c>
       <c r="B759" t="n">
-        <v>29.45248603820801</v>
+        <v>29.45248413085938</v>
       </c>
       <c r="C759" t="n">
-        <v>29.83562506189301</v>
+        <v>29.83562312973222</v>
       </c>
       <c r="D759" t="n">
-        <v>29.1774139813743</v>
+        <v>29.17741209183939</v>
       </c>
       <c r="E759" t="n">
-        <v>29.66861622433489</v>
+        <v>29.66861430298963</v>
       </c>
       <c r="F759" t="n">
         <v>4483800</v>
@@ -15732,16 +15732,16 @@
         <v>45271</v>
       </c>
       <c r="B766" t="n">
-        <v>26.91788101196289</v>
+        <v>26.91788291931152</v>
       </c>
       <c r="C766" t="n">
-        <v>27.08488984004369</v>
+        <v>27.08489175922624</v>
       </c>
       <c r="D766" t="n">
-        <v>26.48562253802652</v>
+        <v>26.48562441474616</v>
       </c>
       <c r="E766" t="n">
-        <v>26.96700235774415</v>
+        <v>26.96700426857343</v>
       </c>
       <c r="F766" t="n">
         <v>6627000</v>
@@ -15792,16 +15792,16 @@
         <v>45274</v>
       </c>
       <c r="B769" t="n">
-        <v>27.00629997253418</v>
+        <v>27.00629806518555</v>
       </c>
       <c r="C769" t="n">
-        <v>27.20278162563166</v>
+        <v>27.2027797044063</v>
       </c>
       <c r="D769" t="n">
-        <v>26.49544917351107</v>
+        <v>26.49544730224182</v>
       </c>
       <c r="E769" t="n">
-        <v>26.82946685950403</v>
+        <v>26.82946496464443</v>
       </c>
       <c r="F769" t="n">
         <v>14011300</v>
@@ -15812,16 +15812,16 @@
         <v>45275</v>
       </c>
       <c r="B770" t="n">
-        <v>25.8863582611084</v>
+        <v>25.88635635375977</v>
       </c>
       <c r="C770" t="n">
-        <v>27.21260467558413</v>
+        <v>27.21260267051552</v>
       </c>
       <c r="D770" t="n">
-        <v>25.8863582611084</v>
+        <v>25.88635635375977</v>
       </c>
       <c r="E770" t="n">
-        <v>27.16348332761816</v>
+        <v>27.1634813261689</v>
       </c>
       <c r="F770" t="n">
         <v>11924000</v>
@@ -15832,16 +15832,16 @@
         <v>45278</v>
       </c>
       <c r="B771" t="n">
-        <v>26.21055221557617</v>
+        <v>26.21055030822754</v>
       </c>
       <c r="C771" t="n">
-        <v>26.76069820788825</v>
+        <v>26.76069626050536</v>
       </c>
       <c r="D771" t="n">
-        <v>25.94530255232668</v>
+        <v>25.94530066428034</v>
       </c>
       <c r="E771" t="n">
-        <v>26.12213566115967</v>
+        <v>26.12213376024514</v>
       </c>
       <c r="F771" t="n">
         <v>4958200</v>
@@ -15852,16 +15852,16 @@
         <v>45279</v>
       </c>
       <c r="B772" t="n">
-        <v>26.32843780517578</v>
+        <v>26.32843971252441</v>
       </c>
       <c r="C772" t="n">
-        <v>26.52491943942738</v>
+        <v>26.52492136101001</v>
       </c>
       <c r="D772" t="n">
-        <v>26.13195804471192</v>
+        <v>26.13195993782669</v>
       </c>
       <c r="E772" t="n">
-        <v>26.30879114078081</v>
+        <v>26.30879304670615</v>
       </c>
       <c r="F772" t="n">
         <v>3900900</v>
@@ -15872,16 +15872,16 @@
         <v>45280</v>
       </c>
       <c r="B773" t="n">
-        <v>25.85688400268555</v>
+        <v>25.85688591003418</v>
       </c>
       <c r="C773" t="n">
-        <v>26.54456784535201</v>
+        <v>26.54456980342805</v>
       </c>
       <c r="D773" t="n">
-        <v>25.68987517654013</v>
+        <v>25.68987707156926</v>
       </c>
       <c r="E773" t="n">
-        <v>26.54456784535201</v>
+        <v>26.54456980342805</v>
       </c>
       <c r="F773" t="n">
         <v>6168300</v>
@@ -15912,16 +15912,16 @@
         <v>45282</v>
       </c>
       <c r="B775" t="n">
-        <v>25.95512771606445</v>
+        <v>25.95512580871582</v>
       </c>
       <c r="C775" t="n">
-        <v>26.22037738844958</v>
+        <v>26.2203754616087</v>
       </c>
       <c r="D775" t="n">
-        <v>25.79794314141873</v>
+        <v>25.79794124562103</v>
       </c>
       <c r="E775" t="n">
-        <v>26.03372000338731</v>
+        <v>26.03371809026321</v>
       </c>
       <c r="F775" t="n">
         <v>3644200</v>
@@ -16012,16 +16012,16 @@
         <v>45294</v>
       </c>
       <c r="B780" t="n">
-        <v>25.8863582611084</v>
+        <v>25.88635635375977</v>
       </c>
       <c r="C780" t="n">
-        <v>26.28914394549015</v>
+        <v>26.28914200846361</v>
       </c>
       <c r="D780" t="n">
-        <v>25.35585894580298</v>
+        <v>25.35585707754239</v>
       </c>
       <c r="E780" t="n">
-        <v>25.64075714264207</v>
+        <v>25.64075525338972</v>
       </c>
       <c r="F780" t="n">
         <v>5734800</v>
@@ -16052,16 +16052,16 @@
         <v>45296</v>
       </c>
       <c r="B782" t="n">
-        <v>25.68987655639648</v>
+        <v>25.68987464904785</v>
       </c>
       <c r="C782" t="n">
-        <v>25.97477475256549</v>
+        <v>25.97477282406455</v>
       </c>
       <c r="D782" t="n">
-        <v>25.21832285975933</v>
+        <v>25.21832098742127</v>
       </c>
       <c r="E782" t="n">
-        <v>25.36568315573496</v>
+        <v>25.36568127245611</v>
       </c>
       <c r="F782" t="n">
         <v>3417300</v>
@@ -16092,16 +16092,16 @@
         <v>45300</v>
       </c>
       <c r="B784" t="n">
-        <v>28.0181770324707</v>
+        <v>28.01817512512207</v>
       </c>
       <c r="C784" t="n">
-        <v>28.24412961971936</v>
+        <v>28.24412769698892</v>
       </c>
       <c r="D784" t="n">
-        <v>26.7999956667704</v>
+        <v>26.79999384234995</v>
       </c>
       <c r="E784" t="n">
-        <v>27.01612398407939</v>
+        <v>27.01612214494592</v>
       </c>
       <c r="F784" t="n">
         <v>10290300</v>
@@ -16152,16 +16152,16 @@
         <v>45303</v>
       </c>
       <c r="B787" t="n">
-        <v>28.20483016967773</v>
+        <v>28.20483207702637</v>
       </c>
       <c r="C787" t="n">
-        <v>28.86304121001741</v>
+        <v>28.86304316187749</v>
       </c>
       <c r="D787" t="n">
-        <v>27.82169304316834</v>
+        <v>27.82169492460737</v>
       </c>
       <c r="E787" t="n">
-        <v>28.63708864175739</v>
+        <v>28.63709057833746</v>
       </c>
       <c r="F787" t="n">
         <v>5067700</v>
@@ -16172,16 +16172,16 @@
         <v>45306</v>
       </c>
       <c r="B788" t="n">
-        <v>28.52902603149414</v>
+        <v>28.52902793884277</v>
       </c>
       <c r="C788" t="n">
-        <v>28.68621059306261</v>
+        <v>28.68621251092004</v>
       </c>
       <c r="D788" t="n">
-        <v>27.90028591143248</v>
+        <v>27.9002877767458</v>
       </c>
       <c r="E788" t="n">
-        <v>28.06729474232245</v>
+        <v>28.06729661880138</v>
       </c>
       <c r="F788" t="n">
         <v>3859400</v>
@@ -16252,16 +16252,16 @@
         <v>45310</v>
       </c>
       <c r="B792" t="n">
-        <v>29.03005218505859</v>
+        <v>29.03005027770996</v>
       </c>
       <c r="C792" t="n">
-        <v>29.19706102477754</v>
+        <v>29.197059106456</v>
       </c>
       <c r="D792" t="n">
-        <v>28.05747195626752</v>
+        <v>28.0574701128199</v>
       </c>
       <c r="E792" t="n">
-        <v>28.73533158498416</v>
+        <v>28.73532969699943</v>
       </c>
       <c r="F792" t="n">
         <v>7851200</v>
@@ -16312,16 +16312,16 @@
         <v>45315</v>
       </c>
       <c r="B795" t="n">
-        <v>27.86099052429199</v>
+        <v>27.86099243164062</v>
       </c>
       <c r="C795" t="n">
-        <v>28.52902584344861</v>
+        <v>28.52902779653059</v>
       </c>
       <c r="D795" t="n">
-        <v>27.63503607896236</v>
+        <v>27.63503797084227</v>
       </c>
       <c r="E795" t="n">
-        <v>28.04764601880687</v>
+        <v>28.04764793893384</v>
       </c>
       <c r="F795" t="n">
         <v>4070600</v>
@@ -16352,16 +16352,16 @@
         <v>45317</v>
       </c>
       <c r="B797" t="n">
-        <v>28.2441291809082</v>
+        <v>28.24412727355957</v>
       </c>
       <c r="C797" t="n">
-        <v>28.2441291809082</v>
+        <v>28.24412727355957</v>
       </c>
       <c r="D797" t="n">
-        <v>27.50732581097147</v>
+        <v>27.50732395337975</v>
       </c>
       <c r="E797" t="n">
-        <v>27.65468611020124</v>
+        <v>27.65468424265817</v>
       </c>
       <c r="F797" t="n">
         <v>2761100</v>
@@ -16392,16 +16392,16 @@
         <v>45321</v>
       </c>
       <c r="B799" t="n">
-        <v>27.24207496643066</v>
+        <v>27.2420768737793</v>
       </c>
       <c r="C799" t="n">
-        <v>27.54662169525507</v>
+        <v>27.54662362392648</v>
       </c>
       <c r="D799" t="n">
-        <v>26.97682531504984</v>
+        <v>26.97682720382707</v>
       </c>
       <c r="E799" t="n">
-        <v>27.36978859433452</v>
+        <v>27.369790510625</v>
       </c>
       <c r="F799" t="n">
         <v>2184900</v>
@@ -16432,16 +16432,16 @@
         <v>45323</v>
       </c>
       <c r="B801" t="n">
-        <v>26.24002075195312</v>
+        <v>26.24002265930176</v>
       </c>
       <c r="C801" t="n">
-        <v>27.4090825182884</v>
+        <v>27.40908451061442</v>
       </c>
       <c r="D801" t="n">
-        <v>26.10248473489757</v>
+        <v>26.10248663224892</v>
       </c>
       <c r="E801" t="n">
-        <v>27.31084170305399</v>
+        <v>27.31084368823903</v>
       </c>
       <c r="F801" t="n">
         <v>7611700</v>
@@ -16532,16 +16532,16 @@
         <v>45330</v>
       </c>
       <c r="B806" t="n">
-        <v>28.79427337646484</v>
+        <v>28.79427528381348</v>
       </c>
       <c r="C806" t="n">
-        <v>28.81392191481336</v>
+        <v>28.81392382346353</v>
       </c>
       <c r="D806" t="n">
-        <v>27.39925900811183</v>
+        <v>27.39926082305394</v>
       </c>
       <c r="E806" t="n">
-        <v>28.71568109685852</v>
+        <v>28.71568299900116</v>
       </c>
       <c r="F806" t="n">
         <v>6908300</v>
@@ -16552,16 +16552,16 @@
         <v>45331</v>
       </c>
       <c r="B807" t="n">
-        <v>27.69398307800293</v>
+        <v>27.6939811706543</v>
       </c>
       <c r="C807" t="n">
-        <v>28.9121644198793</v>
+        <v>28.9121624286317</v>
       </c>
       <c r="D807" t="n">
-        <v>27.52697423987057</v>
+        <v>27.52697234402422</v>
       </c>
       <c r="E807" t="n">
-        <v>28.83357213568689</v>
+        <v>28.83357014985212</v>
       </c>
       <c r="F807" t="n">
         <v>5513900</v>
@@ -16592,16 +16592,16 @@
         <v>45337</v>
       </c>
       <c r="B809" t="n">
-        <v>28.00835037231445</v>
+        <v>28.00835227966309</v>
       </c>
       <c r="C809" t="n">
-        <v>28.26377574758426</v>
+        <v>28.26377767232718</v>
       </c>
       <c r="D809" t="n">
-        <v>27.28137132291011</v>
+        <v>27.28137318075199</v>
       </c>
       <c r="E809" t="n">
-        <v>27.40908307365115</v>
+        <v>27.40908494019011</v>
       </c>
       <c r="F809" t="n">
         <v>2788300</v>
@@ -16632,16 +16632,16 @@
         <v>45341</v>
       </c>
       <c r="B811" t="n">
-        <v>28.6763858795166</v>
+        <v>28.67638778686523</v>
       </c>
       <c r="C811" t="n">
-        <v>28.76480242825268</v>
+        <v>28.76480434148215</v>
       </c>
       <c r="D811" t="n">
-        <v>28.2343031358362</v>
+        <v>28.23430501378064</v>
       </c>
       <c r="E811" t="n">
-        <v>28.74515388991405</v>
+        <v>28.74515580183664</v>
       </c>
       <c r="F811" t="n">
         <v>1698200</v>
@@ -16672,16 +16672,16 @@
         <v>45343</v>
       </c>
       <c r="B813" t="n">
-        <v>28.92198753356934</v>
+        <v>28.92198944091797</v>
       </c>
       <c r="C813" t="n">
-        <v>28.98093127591061</v>
+        <v>28.98093318714647</v>
       </c>
       <c r="D813" t="n">
-        <v>28.36201729685779</v>
+        <v>28.36201916727748</v>
       </c>
       <c r="E813" t="n">
-        <v>28.63708934364225</v>
+        <v>28.6370912322024</v>
       </c>
       <c r="F813" t="n">
         <v>2751400</v>
@@ -16792,16 +16792,16 @@
         <v>45351</v>
       </c>
       <c r="B819" t="n">
-        <v>27.45820426940918</v>
+        <v>27.45820617675781</v>
       </c>
       <c r="C819" t="n">
-        <v>28.14588623865804</v>
+        <v>28.14588819377561</v>
       </c>
       <c r="D819" t="n">
-        <v>27.45820426940918</v>
+        <v>27.45820617675781</v>
       </c>
       <c r="E819" t="n">
-        <v>27.98870168147043</v>
+        <v>27.98870362566938</v>
       </c>
       <c r="F819" t="n">
         <v>2784300</v>
@@ -16972,16 +16972,16 @@
         <v>45364</v>
       </c>
       <c r="B828" t="n">
-        <v>29.13811492919922</v>
+        <v>29.13811683654785</v>
       </c>
       <c r="C828" t="n">
-        <v>29.36406749594983</v>
+        <v>29.36406941808906</v>
       </c>
       <c r="D828" t="n">
-        <v>28.98093037199986</v>
+        <v>28.98093226905937</v>
       </c>
       <c r="E828" t="n">
-        <v>28.98093037199986</v>
+        <v>28.98093226905937</v>
       </c>
       <c r="F828" t="n">
         <v>2596400</v>
@@ -17032,16 +17032,16 @@
         <v>45369</v>
       </c>
       <c r="B831" t="n">
-        <v>28.98093223571777</v>
+        <v>28.98093032836914</v>
       </c>
       <c r="C831" t="n">
-        <v>29.28547710065286</v>
+        <v>29.28547517326093</v>
       </c>
       <c r="D831" t="n">
-        <v>28.61744175270144</v>
+        <v>28.61743986927554</v>
       </c>
       <c r="E831" t="n">
-        <v>28.77462819379693</v>
+        <v>28.77462630002598</v>
       </c>
       <c r="F831" t="n">
         <v>4710300</v>
@@ -17112,16 +17112,16 @@
         <v>45373</v>
       </c>
       <c r="B835" t="n">
-        <v>29.71773529052734</v>
+        <v>29.71773338317871</v>
       </c>
       <c r="C835" t="n">
-        <v>30.0026334869456</v>
+        <v>30.00263156131158</v>
       </c>
       <c r="D835" t="n">
-        <v>29.28547679800454</v>
+        <v>29.28547491839919</v>
       </c>
       <c r="E835" t="n">
-        <v>29.88474412578926</v>
+        <v>29.88474220772164</v>
       </c>
       <c r="F835" t="n">
         <v>3854000</v>
@@ -17152,16 +17152,16 @@
         <v>45377</v>
       </c>
       <c r="B837" t="n">
-        <v>30.81802749633789</v>
+        <v>30.81802940368652</v>
       </c>
       <c r="C837" t="n">
-        <v>31.22081315885015</v>
+        <v>31.22081509112746</v>
       </c>
       <c r="D837" t="n">
-        <v>30.51348077684796</v>
+        <v>30.51348266534799</v>
       </c>
       <c r="E837" t="n">
-        <v>30.61172159365801</v>
+        <v>30.61172348823823</v>
       </c>
       <c r="F837" t="n">
         <v>3327200</v>
@@ -17172,16 +17172,16 @@
         <v>45378</v>
       </c>
       <c r="B838" t="n">
-        <v>31.48606109619141</v>
+        <v>31.48606300354004</v>
       </c>
       <c r="C838" t="n">
-        <v>31.91832144197546</v>
+        <v>31.91832337550937</v>
       </c>
       <c r="D838" t="n">
-        <v>30.3857691886579</v>
+        <v>30.38577102935353</v>
       </c>
       <c r="E838" t="n">
-        <v>30.65101883332299</v>
+        <v>30.6510206900868</v>
       </c>
       <c r="F838" t="n">
         <v>9071000</v>
@@ -17372,16 +17372,16 @@
         <v>45393</v>
       </c>
       <c r="B848" t="n">
-        <v>35.62198638916016</v>
+        <v>35.62198257446289</v>
       </c>
       <c r="C848" t="n">
-        <v>35.91671074440308</v>
+        <v>35.91670689814429</v>
       </c>
       <c r="D848" t="n">
-        <v>34.59046238853748</v>
+        <v>34.59045868430435</v>
       </c>
       <c r="E848" t="n">
-        <v>34.74764696246498</v>
+        <v>34.74764324139922</v>
       </c>
       <c r="F848" t="n">
         <v>5960900</v>
@@ -17412,16 +17412,16 @@
         <v>45397</v>
       </c>
       <c r="B850" t="n">
-        <v>34.06978607177734</v>
+        <v>34.06978988647461</v>
       </c>
       <c r="C850" t="n">
-        <v>34.52169121201051</v>
+        <v>34.52169507730631</v>
       </c>
       <c r="D850" t="n">
-        <v>33.83400735867823</v>
+        <v>33.83401114697602</v>
       </c>
       <c r="E850" t="n">
-        <v>34.43327466304528</v>
+        <v>34.43327851844133</v>
       </c>
       <c r="F850" t="n">
         <v>4151100</v>
@@ -17472,16 +17472,16 @@
         <v>45400</v>
       </c>
       <c r="B853" t="n">
-        <v>32.3309326171875</v>
+        <v>32.33092880249023</v>
       </c>
       <c r="C853" t="n">
-        <v>33.28386620122118</v>
+        <v>33.28386227408815</v>
       </c>
       <c r="D853" t="n">
-        <v>31.93796930998834</v>
+        <v>31.93796554165645</v>
       </c>
       <c r="E853" t="n">
-        <v>33.00879038715143</v>
+        <v>33.00878649247434</v>
       </c>
       <c r="F853" t="n">
         <v>4478700</v>
@@ -17632,16 +17632,16 @@
         <v>45412</v>
       </c>
       <c r="B861" t="n">
-        <v>32.58635711669922</v>
+        <v>32.58635330200195</v>
       </c>
       <c r="C861" t="n">
-        <v>33.66700436998067</v>
+        <v>33.66700042877825</v>
       </c>
       <c r="D861" t="n">
-        <v>32.43899868278081</v>
+        <v>32.43899488533395</v>
       </c>
       <c r="E861" t="n">
-        <v>33.60805874786774</v>
+        <v>33.60805481356574</v>
       </c>
       <c r="F861" t="n">
         <v>6661700</v>
@@ -29475,16 +29475,36 @@
         <v>17.75</v>
       </c>
       <c r="C1453" t="n">
-        <v>18.6</v>
+        <v>18.60000038146973</v>
       </c>
       <c r="D1453" t="n">
-        <v>17.72</v>
+        <v>17.71999931335449</v>
       </c>
       <c r="E1453" t="n">
-        <v>18.45</v>
+        <v>18.45000076293945</v>
       </c>
       <c r="F1453" t="n">
         <v>4184800</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1454" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="C1454" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="D1454" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="E1454" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="F1454" t="n">
+        <v>2729900</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1454"/>
+  <dimension ref="A1:F1455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29492,19 +29492,39 @@
         <v>46280</v>
       </c>
       <c r="B1454" t="n">
-        <v>17.91</v>
+        <v>17.90999984741211</v>
       </c>
       <c r="C1454" t="n">
-        <v>18.1</v>
+        <v>18.10000038146973</v>
       </c>
       <c r="D1454" t="n">
-        <v>17.57</v>
+        <v>17.56999969482422</v>
       </c>
       <c r="E1454" t="n">
-        <v>17.71</v>
+        <v>17.70999908447266</v>
       </c>
       <c r="F1454" t="n">
         <v>2729900</v>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1455" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="C1455" t="n">
+        <v>17.81</v>
+      </c>
+      <c r="D1455" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="E1455" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F1455" t="n">
+        <v>3314100</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1455"/>
+  <dimension ref="A1:F1456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,16 +512,16 @@
         <v>44152</v>
       </c>
       <c r="B5" t="n">
-        <v>20.17695617675781</v>
+        <v>20.17695426940918</v>
       </c>
       <c r="C5" t="n">
-        <v>20.17695617675781</v>
+        <v>20.17695426940918</v>
       </c>
       <c r="D5" t="n">
-        <v>19.85012633435968</v>
+        <v>19.85012445790661</v>
       </c>
       <c r="E5" t="n">
-        <v>20.12889164196659</v>
+        <v>20.12888973916155</v>
       </c>
       <c r="F5" t="n">
         <v>262242</v>
@@ -572,16 +572,16 @@
         <v>44158</v>
       </c>
       <c r="B8" t="n">
-        <v>20.2057933807373</v>
+        <v>20.20579147338867</v>
       </c>
       <c r="C8" t="n">
-        <v>20.52301068477087</v>
+        <v>20.52300874747816</v>
       </c>
       <c r="D8" t="n">
-        <v>20.14811818865408</v>
+        <v>20.14811628674976</v>
       </c>
       <c r="E8" t="n">
-        <v>20.14811818865408</v>
+        <v>20.14811628674976</v>
       </c>
       <c r="F8" t="n">
         <v>79408</v>
@@ -632,16 +632,16 @@
         <v>44161</v>
       </c>
       <c r="B11" t="n">
-        <v>22.87811088562012</v>
+        <v>22.87810897827148</v>
       </c>
       <c r="C11" t="n">
-        <v>22.87811088562012</v>
+        <v>22.87810897827148</v>
       </c>
       <c r="D11" t="n">
-        <v>22.3109640047031</v>
+        <v>22.31096214463751</v>
       </c>
       <c r="E11" t="n">
-        <v>22.3109640047031</v>
+        <v>22.31096214463751</v>
       </c>
       <c r="F11" t="n">
         <v>72970</v>
@@ -652,16 +652,16 @@
         <v>44162</v>
       </c>
       <c r="B12" t="n">
-        <v>23.07036209106445</v>
+        <v>23.07036399841309</v>
       </c>
       <c r="C12" t="n">
-        <v>23.55099428329309</v>
+        <v>23.55099623037812</v>
       </c>
       <c r="D12" t="n">
-        <v>22.10909770660719</v>
+        <v>22.10909953448302</v>
       </c>
       <c r="E12" t="n">
-        <v>23.07036209106445</v>
+        <v>23.07036399841309</v>
       </c>
       <c r="F12" t="n">
         <v>72050</v>
@@ -692,16 +692,16 @@
         <v>44166</v>
       </c>
       <c r="B14" t="n">
-        <v>23.07036209106445</v>
+        <v>23.07036399841309</v>
       </c>
       <c r="C14" t="n">
-        <v>23.1664892790253</v>
+        <v>23.16649119432127</v>
       </c>
       <c r="D14" t="n">
-        <v>23.03191196539523</v>
+        <v>23.03191386956499</v>
       </c>
       <c r="E14" t="n">
-        <v>23.12803727956828</v>
+        <v>23.12803919168523</v>
       </c>
       <c r="F14" t="n">
         <v>93512</v>
@@ -792,16 +792,16 @@
         <v>44173</v>
       </c>
       <c r="B19" t="n">
-        <v>26.33866500854492</v>
+        <v>26.33866310119629</v>
       </c>
       <c r="C19" t="n">
-        <v>26.57898205078916</v>
+        <v>26.57898012603766</v>
       </c>
       <c r="D19" t="n">
-        <v>25.56965309666637</v>
+        <v>25.56965124500673</v>
       </c>
       <c r="E19" t="n">
-        <v>25.56965309666637</v>
+        <v>25.56965124500673</v>
       </c>
       <c r="F19" t="n">
         <v>126420</v>
@@ -812,16 +812,16 @@
         <v>44174</v>
       </c>
       <c r="B20" t="n">
-        <v>26.83852005004883</v>
+        <v>26.83852195739746</v>
       </c>
       <c r="C20" t="n">
-        <v>27.77094867230641</v>
+        <v>27.77095064592048</v>
       </c>
       <c r="D20" t="n">
-        <v>26.27137510044991</v>
+        <v>26.27137696749292</v>
       </c>
       <c r="E20" t="n">
-        <v>26.4924651869397</v>
+        <v>26.49246706969505</v>
       </c>
       <c r="F20" t="n">
         <v>212880</v>
@@ -892,16 +892,16 @@
         <v>44180</v>
       </c>
       <c r="B24" t="n">
-        <v>33.00984191894531</v>
+        <v>33.00984573364258</v>
       </c>
       <c r="C24" t="n">
-        <v>33.9807187406613</v>
+        <v>33.98072266755544</v>
       </c>
       <c r="D24" t="n">
-        <v>30.7604798048412</v>
+        <v>30.76048335959674</v>
       </c>
       <c r="E24" t="n">
-        <v>30.7604798048412</v>
+        <v>30.76048335959674</v>
       </c>
       <c r="F24" t="n">
         <v>887803</v>
@@ -912,16 +912,16 @@
         <v>44181</v>
       </c>
       <c r="B25" t="n">
-        <v>32.68301773071289</v>
+        <v>32.68301391601562</v>
       </c>
       <c r="C25" t="n">
-        <v>34.4517423806715</v>
+        <v>34.45173835953219</v>
       </c>
       <c r="D25" t="n">
-        <v>32.10625830770921</v>
+        <v>32.10625456033017</v>
       </c>
       <c r="E25" t="n">
-        <v>33.62505712226533</v>
+        <v>33.62505319761509</v>
       </c>
       <c r="F25" t="n">
         <v>376808</v>
@@ -932,16 +932,16 @@
         <v>44182</v>
       </c>
       <c r="B26" t="n">
-        <v>32.10625457763672</v>
+        <v>32.10625839233398</v>
       </c>
       <c r="C26" t="n">
-        <v>33.64427827776851</v>
+        <v>33.64428227520571</v>
       </c>
       <c r="D26" t="n">
-        <v>31.64484559380946</v>
+        <v>31.64484935368452</v>
       </c>
       <c r="E26" t="n">
-        <v>33.62505321574033</v>
+        <v>33.6250572108933</v>
       </c>
       <c r="F26" t="n">
         <v>258257</v>
@@ -972,16 +972,16 @@
         <v>44186</v>
       </c>
       <c r="B28" t="n">
-        <v>32.18315505981445</v>
+        <v>32.18315887451172</v>
       </c>
       <c r="C28" t="n">
-        <v>33.33667378019659</v>
+        <v>33.33667773162143</v>
       </c>
       <c r="D28" t="n">
-        <v>29.12633082555934</v>
+        <v>29.12633427792858</v>
       </c>
       <c r="E28" t="n">
-        <v>31.86593778646691</v>
+        <v>31.86594156356414</v>
       </c>
       <c r="F28" t="n">
         <v>236079</v>
@@ -992,16 +992,16 @@
         <v>44187</v>
       </c>
       <c r="B29" t="n">
-        <v>33.16364669799805</v>
+        <v>33.16364288330078</v>
       </c>
       <c r="C29" t="n">
-        <v>33.47125146089823</v>
+        <v>33.47124761081827</v>
       </c>
       <c r="D29" t="n">
-        <v>32.59649983084212</v>
+        <v>32.59649608138177</v>
       </c>
       <c r="E29" t="n">
-        <v>33.21170935664249</v>
+        <v>33.21170553641675</v>
       </c>
       <c r="F29" t="n">
         <v>167504</v>
@@ -1032,16 +1032,16 @@
         <v>44193</v>
       </c>
       <c r="B31" t="n">
-        <v>36.21085357666016</v>
+        <v>36.21085739135742</v>
       </c>
       <c r="C31" t="n">
-        <v>36.66265002370312</v>
+        <v>36.66265388599569</v>
       </c>
       <c r="D31" t="n">
-        <v>35.56680651179074</v>
+        <v>35.56681025863972</v>
       </c>
       <c r="E31" t="n">
-        <v>35.56680651179074</v>
+        <v>35.56681025863972</v>
       </c>
       <c r="F31" t="n">
         <v>451822</v>
@@ -1052,16 +1052,16 @@
         <v>44194</v>
       </c>
       <c r="B32" t="n">
-        <v>36.09550857543945</v>
+        <v>36.09550476074219</v>
       </c>
       <c r="C32" t="n">
-        <v>37.06638558261441</v>
+        <v>37.06638166531152</v>
       </c>
       <c r="D32" t="n">
-        <v>35.95131684304462</v>
+        <v>35.95131304358604</v>
       </c>
       <c r="E32" t="n">
-        <v>36.52807627747203</v>
+        <v>36.52807241705953</v>
       </c>
       <c r="F32" t="n">
         <v>337154</v>
@@ -1092,16 +1092,16 @@
         <v>44200</v>
       </c>
       <c r="B34" t="n">
-        <v>34.99966430664062</v>
+        <v>34.99966049194336</v>
       </c>
       <c r="C34" t="n">
-        <v>36.62420472682393</v>
+        <v>36.62420073506411</v>
       </c>
       <c r="D34" t="n">
-        <v>34.98043924232432</v>
+        <v>34.98043542972244</v>
       </c>
       <c r="E34" t="n">
-        <v>36.52807565766651</v>
+        <v>36.52807167638402</v>
       </c>
       <c r="F34" t="n">
         <v>331840</v>
@@ -1112,16 +1112,16 @@
         <v>44201</v>
       </c>
       <c r="B35" t="n">
-        <v>36.13395309448242</v>
+        <v>36.13395690917969</v>
       </c>
       <c r="C35" t="n">
-        <v>36.32620745863368</v>
+        <v>36.32621129362743</v>
       </c>
       <c r="D35" t="n">
-        <v>34.60554195482727</v>
+        <v>34.60554560816865</v>
       </c>
       <c r="E35" t="n">
-        <v>35.45145591048728</v>
+        <v>35.45145965313264</v>
       </c>
       <c r="F35" t="n">
         <v>328059</v>
@@ -1172,16 +1172,16 @@
         <v>44204</v>
       </c>
       <c r="B38" t="n">
-        <v>34.134521484375</v>
+        <v>34.13452529907227</v>
       </c>
       <c r="C38" t="n">
-        <v>35.75906172916622</v>
+        <v>35.75906572541368</v>
       </c>
       <c r="D38" t="n">
-        <v>34.134521484375</v>
+        <v>34.13452529907227</v>
       </c>
       <c r="E38" t="n">
-        <v>35.16307730455386</v>
+        <v>35.16308123419719</v>
       </c>
       <c r="F38" t="n">
         <v>367201</v>
@@ -1272,16 +1272,16 @@
         <v>44211</v>
       </c>
       <c r="B43" t="n">
-        <v>33.9422721862793</v>
+        <v>33.94226837158203</v>
       </c>
       <c r="C43" t="n">
-        <v>35.0477245509764</v>
+        <v>35.04772061203977</v>
       </c>
       <c r="D43" t="n">
-        <v>33.16364589242556</v>
+        <v>33.16364216523639</v>
       </c>
       <c r="E43" t="n">
-        <v>34.60554435461268</v>
+        <v>34.60554046537172</v>
       </c>
       <c r="F43" t="n">
         <v>319883</v>
@@ -1292,16 +1292,16 @@
         <v>44214</v>
       </c>
       <c r="B44" t="n">
-        <v>34.04800796508789</v>
+        <v>34.04801177978516</v>
       </c>
       <c r="C44" t="n">
-        <v>34.50941694399793</v>
+        <v>34.5094208103909</v>
       </c>
       <c r="D44" t="n">
-        <v>33.27899799700501</v>
+        <v>33.27900172554335</v>
       </c>
       <c r="E44" t="n">
-        <v>34.11529568146945</v>
+        <v>34.11529950370554</v>
       </c>
       <c r="F44" t="n">
         <v>117631</v>
@@ -1332,16 +1332,16 @@
         <v>44216</v>
       </c>
       <c r="B46" t="n">
-        <v>34.12491226196289</v>
+        <v>34.12490844726562</v>
       </c>
       <c r="C46" t="n">
-        <v>35.28804363060232</v>
+        <v>35.28803968588292</v>
       </c>
       <c r="D46" t="n">
-        <v>33.66350697587357</v>
+        <v>33.66350321275509</v>
       </c>
       <c r="E46" t="n">
-        <v>34.60554635973278</v>
+        <v>34.60554249130722</v>
       </c>
       <c r="F46" t="n">
         <v>359332</v>
@@ -1372,16 +1372,16 @@
         <v>44218</v>
       </c>
       <c r="B48" t="n">
-        <v>32.95216751098633</v>
+        <v>32.95216369628906</v>
       </c>
       <c r="C48" t="n">
-        <v>33.45202665996278</v>
+        <v>33.45202278739948</v>
       </c>
       <c r="D48" t="n">
-        <v>32.53882489582456</v>
+        <v>32.53882112897777</v>
       </c>
       <c r="E48" t="n">
-        <v>33.19248455367023</v>
+        <v>33.19248071115274</v>
       </c>
       <c r="F48" t="n">
         <v>220341</v>
@@ -1472,16 +1472,16 @@
         <v>44228</v>
       </c>
       <c r="B53" t="n">
-        <v>31.77942657470703</v>
+        <v>31.7794246673584</v>
       </c>
       <c r="C53" t="n">
-        <v>33.11558345161116</v>
+        <v>33.1155814640686</v>
       </c>
       <c r="D53" t="n">
-        <v>31.66407244843196</v>
+        <v>31.66407054800669</v>
       </c>
       <c r="E53" t="n">
-        <v>32.68301578391271</v>
+        <v>32.68301382233215</v>
       </c>
       <c r="F53" t="n">
         <v>610435</v>
@@ -1492,16 +1492,16 @@
         <v>44229</v>
       </c>
       <c r="B54" t="n">
-        <v>32.63495254516602</v>
+        <v>32.63494873046875</v>
       </c>
       <c r="C54" t="n">
-        <v>33.65389597951643</v>
+        <v>33.65389204571495</v>
       </c>
       <c r="D54" t="n">
-        <v>31.97168030813476</v>
+        <v>31.97167657096734</v>
       </c>
       <c r="E54" t="n">
-        <v>33.64428344702543</v>
+        <v>33.64427951434755</v>
       </c>
       <c r="F54" t="n">
         <v>582228</v>
@@ -1532,16 +1532,16 @@
         <v>44231</v>
       </c>
       <c r="B56" t="n">
-        <v>32.68301773071289</v>
+        <v>32.68301391601562</v>
       </c>
       <c r="C56" t="n">
-        <v>34.11530000851534</v>
+        <v>34.11529602664492</v>
       </c>
       <c r="D56" t="n">
-        <v>32.44270067986538</v>
+        <v>32.44269689321744</v>
       </c>
       <c r="E56" t="n">
-        <v>33.06752276352339</v>
+        <v>33.06751890394745</v>
       </c>
       <c r="F56" t="n">
         <v>466743</v>
@@ -1612,16 +1612,16 @@
         <v>44237</v>
       </c>
       <c r="B60" t="n">
-        <v>34.83625030517578</v>
+        <v>34.83624649047852</v>
       </c>
       <c r="C60" t="n">
-        <v>35.33610571127585</v>
+        <v>35.33610184184258</v>
       </c>
       <c r="D60" t="n">
-        <v>34.23065330065825</v>
+        <v>34.23064955227608</v>
       </c>
       <c r="E60" t="n">
-        <v>34.43251647044691</v>
+        <v>34.43251269995998</v>
       </c>
       <c r="F60" t="n">
         <v>186206</v>
@@ -1652,16 +1652,16 @@
         <v>44239</v>
       </c>
       <c r="B62" t="n">
-        <v>34.4036750793457</v>
+        <v>34.40367889404297</v>
       </c>
       <c r="C62" t="n">
-        <v>34.52864172776623</v>
+        <v>34.52864555631986</v>
       </c>
       <c r="D62" t="n">
-        <v>32.67339704372985</v>
+        <v>32.673400666573</v>
       </c>
       <c r="E62" t="n">
-        <v>33.67311524079254</v>
+        <v>33.67311897448496</v>
       </c>
       <c r="F62" t="n">
         <v>218195</v>
@@ -1692,16 +1692,16 @@
         <v>44245</v>
       </c>
       <c r="B64" t="n">
-        <v>37.00870513916016</v>
+        <v>37.00870895385742</v>
       </c>
       <c r="C64" t="n">
-        <v>37.38359759408829</v>
+        <v>37.38360144742785</v>
       </c>
       <c r="D64" t="n">
-        <v>35.71099846956061</v>
+        <v>35.71100215049589</v>
       </c>
       <c r="E64" t="n">
-        <v>36.37427060079703</v>
+        <v>36.37427435009953</v>
       </c>
       <c r="F64" t="n">
         <v>661534</v>
@@ -1812,16 +1812,16 @@
         <v>44253</v>
       </c>
       <c r="B70" t="n">
-        <v>34.57670974731445</v>
+        <v>34.57670593261719</v>
       </c>
       <c r="C70" t="n">
-        <v>37.21057733278074</v>
+        <v>37.21057322750037</v>
       </c>
       <c r="D70" t="n">
-        <v>33.75002072456356</v>
+        <v>33.75001700107128</v>
       </c>
       <c r="E70" t="n">
-        <v>36.53768882724342</v>
+        <v>36.5376847961999</v>
       </c>
       <c r="F70" t="n">
         <v>410022</v>
@@ -1932,16 +1932,16 @@
         <v>44263</v>
       </c>
       <c r="B76" t="n">
-        <v>41.91115570068359</v>
+        <v>41.91115951538086</v>
       </c>
       <c r="C76" t="n">
-        <v>44.60269808495321</v>
+        <v>44.60270214463106</v>
       </c>
       <c r="D76" t="n">
-        <v>40.70957434605565</v>
+        <v>40.70957805138659</v>
       </c>
       <c r="E76" t="n">
-        <v>43.55492097253444</v>
+        <v>43.55492493684502</v>
       </c>
       <c r="F76" t="n">
         <v>1012691</v>
@@ -1952,16 +1952,16 @@
         <v>44264</v>
       </c>
       <c r="B77" t="n">
-        <v>43.50685882568359</v>
+        <v>43.50686264038086</v>
       </c>
       <c r="C77" t="n">
-        <v>43.50685882568359</v>
+        <v>43.50686264038086</v>
       </c>
       <c r="D77" t="n">
-        <v>39.89249844113039</v>
+        <v>39.89250193891922</v>
       </c>
       <c r="E77" t="n">
-        <v>42.29566117843103</v>
+        <v>42.29566488693005</v>
       </c>
       <c r="F77" t="n">
         <v>563525</v>
@@ -1972,16 +1972,16 @@
         <v>44265</v>
       </c>
       <c r="B78" t="n">
-        <v>44.69882965087891</v>
+        <v>44.69882583618164</v>
       </c>
       <c r="C78" t="n">
-        <v>44.89108404365759</v>
+        <v>44.89108021255291</v>
       </c>
       <c r="D78" t="n">
-        <v>43.38189774093629</v>
+        <v>43.38189403862891</v>
       </c>
       <c r="E78" t="n">
-        <v>43.83369425231464</v>
+        <v>43.83369051144994</v>
       </c>
       <c r="F78" t="n">
         <v>425454</v>
@@ -2012,16 +2012,16 @@
         <v>44267</v>
       </c>
       <c r="B80" t="n">
-        <v>45.66009140014648</v>
+        <v>45.66009521484375</v>
       </c>
       <c r="C80" t="n">
-        <v>49.01490590711195</v>
+        <v>49.01491000208902</v>
       </c>
       <c r="D80" t="n">
-        <v>45.18906989096082</v>
+        <v>45.18907366630634</v>
       </c>
       <c r="E80" t="n">
-        <v>47.15005242731743</v>
+        <v>47.15005636649431</v>
       </c>
       <c r="F80" t="n">
         <v>954539</v>
@@ -2052,16 +2052,16 @@
         <v>44271</v>
       </c>
       <c r="B82" t="n">
-        <v>42.7570686340332</v>
+        <v>42.75707244873047</v>
       </c>
       <c r="C82" t="n">
-        <v>45.18906887745489</v>
+        <v>45.18907290913018</v>
       </c>
       <c r="D82" t="n">
-        <v>42.7570686340332</v>
+        <v>42.75707244873047</v>
       </c>
       <c r="E82" t="n">
-        <v>44.5065717038056</v>
+        <v>44.50657567458991</v>
       </c>
       <c r="F82" t="n">
         <v>561175</v>
@@ -2092,16 +2092,16 @@
         <v>44273</v>
       </c>
       <c r="B84" t="n">
-        <v>40.89221572875977</v>
+        <v>40.89221954345703</v>
       </c>
       <c r="C84" t="n">
-        <v>45.02565269480871</v>
+        <v>45.0256568951004</v>
       </c>
       <c r="D84" t="n">
-        <v>40.57499846451049</v>
+        <v>40.57500224961562</v>
       </c>
       <c r="E84" t="n">
-        <v>44.01632571721106</v>
+        <v>44.01632982334604</v>
       </c>
       <c r="F84" t="n">
         <v>572621</v>
@@ -2112,16 +2112,16 @@
         <v>44274</v>
       </c>
       <c r="B85" t="n">
-        <v>42.2956657409668</v>
+        <v>42.29566192626953</v>
       </c>
       <c r="C85" t="n">
-        <v>44.17013572642225</v>
+        <v>44.17013174266427</v>
       </c>
       <c r="D85" t="n">
-        <v>41.45936795627186</v>
+        <v>41.4593642170013</v>
       </c>
       <c r="E85" t="n">
-        <v>41.45936795627186</v>
+        <v>41.4593642170013</v>
       </c>
       <c r="F85" t="n">
         <v>639255</v>
@@ -2212,16 +2212,16 @@
         <v>44281</v>
       </c>
       <c r="B90" t="n">
-        <v>37.87384796142578</v>
+        <v>37.87384414672852</v>
       </c>
       <c r="C90" t="n">
-        <v>40.94989565175231</v>
+        <v>40.949891527232</v>
       </c>
       <c r="D90" t="n">
-        <v>37.56624319239313</v>
+        <v>37.56623940867817</v>
       </c>
       <c r="E90" t="n">
-        <v>39.95979362121066</v>
+        <v>39.95978959641457</v>
       </c>
       <c r="F90" t="n">
         <v>840076</v>
@@ -2312,16 +2312,16 @@
         <v>44291</v>
       </c>
       <c r="B95" t="n">
-        <v>35.68216323852539</v>
+        <v>35.68215942382812</v>
       </c>
       <c r="C95" t="n">
-        <v>37.01832012039754</v>
+        <v>37.01831616285484</v>
       </c>
       <c r="D95" t="n">
-        <v>35.09579131613852</v>
+        <v>35.09578756412892</v>
       </c>
       <c r="E95" t="n">
-        <v>37.01832012039754</v>
+        <v>37.01831616285484</v>
       </c>
       <c r="F95" t="n">
         <v>1091895</v>
@@ -2512,16 +2512,16 @@
         <v>44305</v>
       </c>
       <c r="B105" t="n">
-        <v>41.33440017700195</v>
+        <v>41.33439636230469</v>
       </c>
       <c r="C105" t="n">
-        <v>42.23798940934727</v>
+        <v>42.23798551125894</v>
       </c>
       <c r="D105" t="n">
-        <v>40.2097189655786</v>
+        <v>40.20971525467667</v>
       </c>
       <c r="E105" t="n">
-        <v>40.38274828563441</v>
+        <v>40.38274455876383</v>
       </c>
       <c r="F105" t="n">
         <v>1793083</v>
@@ -2552,16 +2552,16 @@
         <v>44308</v>
       </c>
       <c r="B107" t="n">
-        <v>42.37256622314453</v>
+        <v>42.3725700378418</v>
       </c>
       <c r="C107" t="n">
-        <v>42.77629628383934</v>
+        <v>42.77630013488342</v>
       </c>
       <c r="D107" t="n">
-        <v>41.0460181707321</v>
+        <v>41.04602186600353</v>
       </c>
       <c r="E107" t="n">
-        <v>42.58404191096891</v>
+        <v>42.58404574470481</v>
       </c>
       <c r="F107" t="n">
         <v>1175903</v>
@@ -2572,16 +2572,16 @@
         <v>44309</v>
       </c>
       <c r="B108" t="n">
-        <v>44.09323120117188</v>
+        <v>44.09323501586914</v>
       </c>
       <c r="C108" t="n">
-        <v>44.3143194172334</v>
+        <v>44.31432325105797</v>
       </c>
       <c r="D108" t="n">
-        <v>42.38217817402538</v>
+        <v>42.38218184069201</v>
       </c>
       <c r="E108" t="n">
-        <v>42.82435835372392</v>
+        <v>42.82436205864548</v>
       </c>
       <c r="F108" t="n">
         <v>1899574</v>
@@ -2612,16 +2612,16 @@
         <v>44313</v>
       </c>
       <c r="B110" t="n">
-        <v>43.73756408691406</v>
+        <v>43.7375602722168</v>
       </c>
       <c r="C110" t="n">
-        <v>44.31432350323168</v>
+        <v>44.31431963823069</v>
       </c>
       <c r="D110" t="n">
-        <v>43.04545428636325</v>
+        <v>43.04545053203033</v>
       </c>
       <c r="E110" t="n">
-        <v>43.40112171865809</v>
+        <v>43.40111793330461</v>
       </c>
       <c r="F110" t="n">
         <v>1146163</v>
@@ -2732,16 +2732,16 @@
         <v>44321</v>
       </c>
       <c r="B116" t="n">
-        <v>39.74831008911133</v>
+        <v>39.74831390380859</v>
       </c>
       <c r="C116" t="n">
-        <v>40.6422867086336</v>
+        <v>40.64229060912697</v>
       </c>
       <c r="D116" t="n">
-        <v>39.07542542863015</v>
+        <v>39.0754291787498</v>
       </c>
       <c r="E116" t="n">
-        <v>39.89249805311069</v>
+        <v>39.89250188164586</v>
       </c>
       <c r="F116" t="n">
         <v>3650961</v>
@@ -2772,16 +2772,16 @@
         <v>44323</v>
       </c>
       <c r="B118" t="n">
-        <v>38.83511352539062</v>
+        <v>38.83510971069336</v>
       </c>
       <c r="C118" t="n">
-        <v>39.99824491189721</v>
+        <v>39.99824098294782</v>
       </c>
       <c r="D118" t="n">
-        <v>37.51818162368365</v>
+        <v>37.51817793834604</v>
       </c>
       <c r="E118" t="n">
-        <v>39.66180253732045</v>
+        <v>39.66179864141913</v>
       </c>
       <c r="F118" t="n">
         <v>2227429</v>
@@ -2832,16 +2832,16 @@
         <v>44328</v>
       </c>
       <c r="B121" t="n">
-        <v>37.05676651000977</v>
+        <v>37.05677032470703</v>
       </c>
       <c r="C121" t="n">
-        <v>38.70052798471127</v>
+        <v>38.70053196862062</v>
       </c>
       <c r="D121" t="n">
-        <v>37.05676651000977</v>
+        <v>37.05677032470703</v>
       </c>
       <c r="E121" t="n">
-        <v>37.81616767208757</v>
+        <v>37.8161715649591</v>
       </c>
       <c r="F121" t="n">
         <v>783049</v>
@@ -2892,16 +2892,16 @@
         <v>44333</v>
       </c>
       <c r="B124" t="n">
-        <v>36.43194961547852</v>
+        <v>36.43194580078125</v>
       </c>
       <c r="C124" t="n">
-        <v>37.13367194429578</v>
+        <v>37.13366805612294</v>
       </c>
       <c r="D124" t="n">
-        <v>35.93209045798972</v>
+        <v>35.93208669563144</v>
       </c>
       <c r="E124" t="n">
-        <v>36.52807493515874</v>
+        <v>36.52807111039643</v>
       </c>
       <c r="F124" t="n">
         <v>946466</v>
@@ -2912,16 +2912,16 @@
         <v>44334</v>
       </c>
       <c r="B125" t="n">
-        <v>35.14385223388672</v>
+        <v>35.14385604858398</v>
       </c>
       <c r="C125" t="n">
-        <v>36.91258044505902</v>
+        <v>36.91258445174329</v>
       </c>
       <c r="D125" t="n">
-        <v>34.59593046500746</v>
+        <v>34.59593422023043</v>
       </c>
       <c r="E125" t="n">
-        <v>36.52807170518645</v>
+        <v>36.52807567013412</v>
       </c>
       <c r="F125" t="n">
         <v>2070451</v>
@@ -2952,16 +2952,16 @@
         <v>44336</v>
       </c>
       <c r="B127" t="n">
-        <v>34.63438034057617</v>
+        <v>34.63438415527344</v>
       </c>
       <c r="C127" t="n">
-        <v>35.26881488495837</v>
+        <v>35.26881876953347</v>
       </c>
       <c r="D127" t="n">
-        <v>34.51902996798866</v>
+        <v>34.51903376998102</v>
       </c>
       <c r="E127" t="n">
-        <v>34.51902996798866</v>
+        <v>34.51903376998102</v>
       </c>
       <c r="F127" t="n">
         <v>943604</v>
@@ -3012,16 +3012,16 @@
         <v>44341</v>
       </c>
       <c r="B130" t="n">
-        <v>37.29708480834961</v>
+        <v>37.29708862304688</v>
       </c>
       <c r="C130" t="n">
-        <v>38.78704584439543</v>
+        <v>38.78704981148397</v>
       </c>
       <c r="D130" t="n">
-        <v>37.22979709165812</v>
+        <v>37.22980089947328</v>
       </c>
       <c r="E130" t="n">
-        <v>37.52778929886728</v>
+        <v>37.52779313716071</v>
       </c>
       <c r="F130" t="n">
         <v>1731150</v>
@@ -3092,16 +3092,16 @@
         <v>44347</v>
       </c>
       <c r="B134" t="n">
-        <v>39.38302993774414</v>
+        <v>39.38303375244141</v>
       </c>
       <c r="C134" t="n">
-        <v>40.11358977958957</v>
+        <v>40.11359366504992</v>
       </c>
       <c r="D134" t="n">
-        <v>39.02736254769899</v>
+        <v>39.02736632794579</v>
       </c>
       <c r="E134" t="n">
-        <v>39.3926424686217</v>
+        <v>39.39264628425005</v>
       </c>
       <c r="F134" t="n">
         <v>715598</v>
@@ -3192,16 +3192,16 @@
         <v>44355</v>
       </c>
       <c r="B139" t="n">
-        <v>38.46022033691406</v>
+        <v>38.4602165222168</v>
       </c>
       <c r="C139" t="n">
-        <v>38.85433789767048</v>
+        <v>38.85433404388245</v>
       </c>
       <c r="D139" t="n">
-        <v>37.72004412796937</v>
+        <v>37.72004038668688</v>
       </c>
       <c r="E139" t="n">
-        <v>38.43138274082768</v>
+        <v>38.43137892899068</v>
       </c>
       <c r="F139" t="n">
         <v>978352</v>
@@ -3212,16 +3212,16 @@
         <v>44356</v>
       </c>
       <c r="B140" t="n">
-        <v>38.01803207397461</v>
+        <v>38.01803588867188</v>
       </c>
       <c r="C140" t="n">
-        <v>38.66207914230487</v>
+        <v>38.66208302162527</v>
       </c>
       <c r="D140" t="n">
-        <v>37.29708475810054</v>
+        <v>37.29708850045856</v>
       </c>
       <c r="E140" t="n">
-        <v>38.48905358533129</v>
+        <v>38.48905744729046</v>
       </c>
       <c r="F140" t="n">
         <v>837521</v>
@@ -3332,16 +3332,16 @@
         <v>44364</v>
       </c>
       <c r="B146" t="n">
-        <v>42.48791885375977</v>
+        <v>42.4879150390625</v>
       </c>
       <c r="C146" t="n">
-        <v>44.00671761209134</v>
+        <v>44.0067136610316</v>
       </c>
       <c r="D146" t="n">
-        <v>41.62277975128091</v>
+        <v>41.62277601425852</v>
       </c>
       <c r="E146" t="n">
-        <v>42.95894040588714</v>
+        <v>42.95893654890009</v>
       </c>
       <c r="F146" t="n">
         <v>1582144</v>
@@ -3372,16 +3372,16 @@
         <v>44368</v>
       </c>
       <c r="B148" t="n">
-        <v>46.96741104125977</v>
+        <v>46.96741485595703</v>
       </c>
       <c r="C148" t="n">
-        <v>47.24617818755916</v>
+        <v>47.24618202489792</v>
       </c>
       <c r="D148" t="n">
-        <v>43.53569625432814</v>
+        <v>43.53569979030122</v>
       </c>
       <c r="E148" t="n">
-        <v>43.73755940512824</v>
+        <v>43.73756295749668</v>
       </c>
       <c r="F148" t="n">
         <v>2655439</v>
@@ -3452,16 +3452,16 @@
         <v>44372</v>
       </c>
       <c r="B152" t="n">
-        <v>44.45851516723633</v>
+        <v>44.45851135253906</v>
       </c>
       <c r="C152" t="n">
-        <v>44.9872081751215</v>
+        <v>44.98720431506052</v>
       </c>
       <c r="D152" t="n">
-        <v>43.97788107180344</v>
+        <v>43.97787729834627</v>
       </c>
       <c r="E152" t="n">
-        <v>44.9872081751215</v>
+        <v>44.98720431506052</v>
       </c>
       <c r="F152" t="n">
         <v>1347904</v>
@@ -3472,16 +3472,16 @@
         <v>44375</v>
       </c>
       <c r="B153" t="n">
-        <v>44.53541564941406</v>
+        <v>44.5354118347168</v>
       </c>
       <c r="C153" t="n">
-        <v>44.64115350201283</v>
+        <v>44.64114967825854</v>
       </c>
       <c r="D153" t="n">
-        <v>43.20886748802305</v>
+        <v>43.20886378695175</v>
       </c>
       <c r="E153" t="n">
-        <v>44.13168555555202</v>
+        <v>44.13168177543641</v>
       </c>
       <c r="F153" t="n">
         <v>1110393</v>
@@ -3512,16 +3512,16 @@
         <v>44377</v>
       </c>
       <c r="B155" t="n">
-        <v>43.58375930786133</v>
+        <v>43.58376312255859</v>
       </c>
       <c r="C155" t="n">
-        <v>44.45851087872119</v>
+        <v>44.45851476998166</v>
       </c>
       <c r="D155" t="n">
-        <v>43.50685905923421</v>
+        <v>43.50686286720073</v>
       </c>
       <c r="E155" t="n">
-        <v>44.21819385418598</v>
+        <v>44.21819772441255</v>
       </c>
       <c r="F155" t="n">
         <v>1274116</v>
@@ -3572,16 +3572,16 @@
         <v>44382</v>
       </c>
       <c r="B158" t="n">
-        <v>45.04488754272461</v>
+        <v>45.04488372802734</v>
       </c>
       <c r="C158" t="n">
-        <v>46.21763144885693</v>
+        <v>46.21762753484401</v>
       </c>
       <c r="D158" t="n">
-        <v>44.42967424579171</v>
+        <v>44.42967048319475</v>
       </c>
       <c r="E158" t="n">
-        <v>44.98720860256699</v>
+        <v>44.98720479275436</v>
       </c>
       <c r="F158" t="n">
         <v>3391068</v>
@@ -3592,16 +3592,16 @@
         <v>44383</v>
       </c>
       <c r="B159" t="n">
-        <v>44.37199783325195</v>
+        <v>44.37199401855469</v>
       </c>
       <c r="C159" t="n">
-        <v>45.94847553926477</v>
+        <v>45.94847158903642</v>
       </c>
       <c r="D159" t="n">
-        <v>43.75678830080941</v>
+        <v>43.75678453900221</v>
       </c>
       <c r="E159" t="n">
-        <v>45.78505875053358</v>
+        <v>45.7850548143543</v>
       </c>
       <c r="F159" t="n">
         <v>1563442</v>
@@ -3652,16 +3652,16 @@
         <v>44389</v>
       </c>
       <c r="B162" t="n">
-        <v>44.72766494750977</v>
+        <v>44.72766876220703</v>
       </c>
       <c r="C162" t="n">
-        <v>45.75621700299953</v>
+        <v>45.75622090541913</v>
       </c>
       <c r="D162" t="n">
-        <v>44.08361413043626</v>
+        <v>44.08361789020423</v>
       </c>
       <c r="E162" t="n">
-        <v>45.75621700299953</v>
+        <v>45.75622090541913</v>
       </c>
       <c r="F162" t="n">
         <v>1597780</v>
@@ -3732,16 +3732,16 @@
         <v>44393</v>
       </c>
       <c r="B166" t="n">
-        <v>41.70929336547852</v>
+        <v>41.70928955078125</v>
       </c>
       <c r="C166" t="n">
-        <v>41.91116028433812</v>
+        <v>41.91115645117827</v>
       </c>
       <c r="D166" t="n">
-        <v>40.45003668764308</v>
+        <v>40.45003298811638</v>
       </c>
       <c r="E166" t="n">
-        <v>41.62278057778546</v>
+        <v>41.62277677100059</v>
       </c>
       <c r="F166" t="n">
         <v>1471156</v>
@@ -3752,16 +3752,16 @@
         <v>44396</v>
       </c>
       <c r="B167" t="n">
-        <v>40.22894668579102</v>
+        <v>40.22894287109375</v>
       </c>
       <c r="C167" t="n">
-        <v>41.05563189370605</v>
+        <v>41.05562800061862</v>
       </c>
       <c r="D167" t="n">
-        <v>39.50799557728174</v>
+        <v>39.50799183094843</v>
       </c>
       <c r="E167" t="n">
-        <v>40.46925997438512</v>
+        <v>40.46925613690023</v>
       </c>
       <c r="F167" t="n">
         <v>1632835</v>
@@ -3792,16 +3792,16 @@
         <v>44398</v>
       </c>
       <c r="B169" t="n">
-        <v>40.45964813232422</v>
+        <v>40.45964431762695</v>
       </c>
       <c r="C169" t="n">
-        <v>41.40169122996932</v>
+        <v>41.40168732645247</v>
       </c>
       <c r="D169" t="n">
-        <v>40.22894737134245</v>
+        <v>40.22894357839657</v>
       </c>
       <c r="E169" t="n">
-        <v>40.37313534695605</v>
+        <v>40.37313154041556</v>
       </c>
       <c r="F169" t="n">
         <v>985812</v>
@@ -3812,16 +3812,16 @@
         <v>44399</v>
       </c>
       <c r="B170" t="n">
-        <v>40.89221572875977</v>
+        <v>40.89221954345703</v>
       </c>
       <c r="C170" t="n">
-        <v>41.15175780815924</v>
+        <v>41.15176164706832</v>
       </c>
       <c r="D170" t="n">
-        <v>40.39235663157741</v>
+        <v>40.3923603996445</v>
       </c>
       <c r="E170" t="n">
-        <v>41.08446634492577</v>
+        <v>41.08447017755746</v>
       </c>
       <c r="F170" t="n">
         <v>757704</v>
@@ -3832,16 +3832,16 @@
         <v>44400</v>
       </c>
       <c r="B171" t="n">
-        <v>40.56539154052734</v>
+        <v>40.56538772583008</v>
       </c>
       <c r="C171" t="n">
-        <v>40.8633837843476</v>
+        <v>40.86337994162768</v>
       </c>
       <c r="D171" t="n">
-        <v>40.20010782417279</v>
+        <v>40.20010404382616</v>
       </c>
       <c r="E171" t="n">
-        <v>40.62306673334884</v>
+        <v>40.6230629132279</v>
       </c>
       <c r="F171" t="n">
         <v>715496</v>
@@ -3872,16 +3872,16 @@
         <v>44404</v>
       </c>
       <c r="B173" t="n">
-        <v>38.54673385620117</v>
+        <v>38.54673004150391</v>
       </c>
       <c r="C173" t="n">
-        <v>40.84415903525979</v>
+        <v>40.84415499320262</v>
       </c>
       <c r="D173" t="n">
-        <v>38.32564186777011</v>
+        <v>38.32563807495276</v>
       </c>
       <c r="E173" t="n">
-        <v>40.62306704682872</v>
+        <v>40.62306302665147</v>
       </c>
       <c r="F173" t="n">
         <v>1543819</v>
@@ -3932,16 +3932,16 @@
         <v>44407</v>
       </c>
       <c r="B176" t="n">
-        <v>37.21057510375977</v>
+        <v>37.2105712890625</v>
       </c>
       <c r="C176" t="n">
-        <v>38.26796483899034</v>
+        <v>38.26796091589321</v>
       </c>
       <c r="D176" t="n">
-        <v>36.33582347177977</v>
+        <v>36.33581974675896</v>
       </c>
       <c r="E176" t="n">
-        <v>37.56624252608663</v>
+        <v>37.5662386749276</v>
       </c>
       <c r="F176" t="n">
         <v>1168442</v>
@@ -3952,16 +3952,16 @@
         <v>44410</v>
       </c>
       <c r="B177" t="n">
-        <v>39.04659271240234</v>
+        <v>39.04658889770508</v>
       </c>
       <c r="C177" t="n">
-        <v>40.34429954077027</v>
+        <v>40.3442955992922</v>
       </c>
       <c r="D177" t="n">
-        <v>38.19106610976557</v>
+        <v>38.19106237864987</v>
       </c>
       <c r="E177" t="n">
-        <v>39.17155563014188</v>
+        <v>39.17155180323623</v>
       </c>
       <c r="F177" t="n">
         <v>3352028</v>
@@ -4052,16 +4052,16 @@
         <v>44417</v>
       </c>
       <c r="B182" t="n">
-        <v>37.10483551025391</v>
+        <v>37.10483169555664</v>
       </c>
       <c r="C182" t="n">
-        <v>37.44127788724551</v>
+        <v>37.44127403795907</v>
       </c>
       <c r="D182" t="n">
-        <v>35.94170411539885</v>
+        <v>35.94170042028153</v>
       </c>
       <c r="E182" t="n">
-        <v>36.11473344381713</v>
+        <v>36.1147297309109</v>
       </c>
       <c r="F182" t="n">
         <v>1206460</v>
@@ -4092,16 +4092,16 @@
         <v>44419</v>
       </c>
       <c r="B184" t="n">
-        <v>36.43194961547852</v>
+        <v>36.43194580078125</v>
       </c>
       <c r="C184" t="n">
-        <v>36.74916691799907</v>
+        <v>36.74916307008678</v>
       </c>
       <c r="D184" t="n">
-        <v>36.09550724902192</v>
+        <v>36.09550346955268</v>
       </c>
       <c r="E184" t="n">
-        <v>36.4703997433506</v>
+        <v>36.47039592462733</v>
       </c>
       <c r="F184" t="n">
         <v>786524</v>
@@ -4112,16 +4112,16 @@
         <v>44420</v>
       </c>
       <c r="B185" t="n">
-        <v>36.12434005737305</v>
+        <v>36.12434387207031</v>
       </c>
       <c r="C185" t="n">
-        <v>36.95102893978947</v>
+        <v>36.95103284178433</v>
       </c>
       <c r="D185" t="n">
-        <v>35.47068047502529</v>
+        <v>35.4706842206967</v>
       </c>
       <c r="E185" t="n">
-        <v>36.19162777223157</v>
+        <v>36.19163159403436</v>
       </c>
       <c r="F185" t="n">
         <v>689639</v>
@@ -4132,16 +4132,16 @@
         <v>44421</v>
       </c>
       <c r="B186" t="n">
-        <v>34.75934600830078</v>
+        <v>34.75934219360352</v>
       </c>
       <c r="C186" t="n">
-        <v>35.97054000708643</v>
+        <v>35.97053605946554</v>
       </c>
       <c r="D186" t="n">
-        <v>34.59593296747376</v>
+        <v>34.59592917071041</v>
       </c>
       <c r="E186" t="n">
-        <v>35.69177658449917</v>
+        <v>35.69177266747142</v>
       </c>
       <c r="F186" t="n">
         <v>915908</v>
@@ -4252,16 +4252,16 @@
         <v>44431</v>
       </c>
       <c r="B192" t="n">
-        <v>33.16364669799805</v>
+        <v>33.16364288330078</v>
       </c>
       <c r="C192" t="n">
-        <v>34.42290334478545</v>
+        <v>34.42289938524034</v>
       </c>
       <c r="D192" t="n">
-        <v>32.77914168126674</v>
+        <v>32.77913791079774</v>
       </c>
       <c r="E192" t="n">
-        <v>33.74040609688286</v>
+        <v>33.740402215843</v>
       </c>
       <c r="F192" t="n">
         <v>2084044</v>
@@ -4272,16 +4272,16 @@
         <v>44432</v>
       </c>
       <c r="B193" t="n">
-        <v>35.43223190307617</v>
+        <v>35.43223571777344</v>
       </c>
       <c r="C193" t="n">
-        <v>35.43223190307617</v>
+        <v>35.43223571777344</v>
       </c>
       <c r="D193" t="n">
-        <v>33.47124932262768</v>
+        <v>33.47125292620207</v>
       </c>
       <c r="E193" t="n">
-        <v>33.93265831128927</v>
+        <v>33.93266196453976</v>
       </c>
       <c r="F193" t="n">
         <v>1429663</v>
@@ -4332,16 +4332,16 @@
         <v>44435</v>
       </c>
       <c r="B196" t="n">
-        <v>36.43194961547852</v>
+        <v>36.43194580078125</v>
       </c>
       <c r="C196" t="n">
-        <v>36.66265413028687</v>
+        <v>36.66265029143312</v>
       </c>
       <c r="D196" t="n">
-        <v>35.02850121026817</v>
+        <v>35.02849754252244</v>
       </c>
       <c r="E196" t="n">
-        <v>35.75906488256532</v>
+        <v>35.75906113832411</v>
       </c>
       <c r="F196" t="n">
         <v>2701327</v>
@@ -4392,16 +4392,16 @@
         <v>44440</v>
       </c>
       <c r="B199" t="n">
-        <v>36.00899505615234</v>
+        <v>36.00899124145508</v>
       </c>
       <c r="C199" t="n">
-        <v>37.2298016265613</v>
+        <v>37.22979768253502</v>
       </c>
       <c r="D199" t="n">
-        <v>35.47068576189898</v>
+        <v>35.47068200422877</v>
       </c>
       <c r="E199" t="n">
-        <v>37.10483496133683</v>
+        <v>37.10483103054919</v>
       </c>
       <c r="F199" t="n">
         <v>1150659</v>
@@ -4712,16 +4712,16 @@
         <v>44463</v>
       </c>
       <c r="B215" t="n">
-        <v>34.54787063598633</v>
+        <v>34.54786682128906</v>
       </c>
       <c r="C215" t="n">
-        <v>35.65332304773112</v>
+        <v>35.65331911097231</v>
       </c>
       <c r="D215" t="n">
-        <v>33.88459469184851</v>
+        <v>33.88459095038866</v>
       </c>
       <c r="E215" t="n">
-        <v>34.46135784884584</v>
+        <v>34.46135404370111</v>
       </c>
       <c r="F215" t="n">
         <v>2639905</v>
@@ -4852,16 +4852,16 @@
         <v>44474</v>
       </c>
       <c r="B222" t="n">
-        <v>41.2382698059082</v>
+        <v>41.23827362060547</v>
       </c>
       <c r="C222" t="n">
-        <v>43.07428564103963</v>
+        <v>43.07428962557536</v>
       </c>
       <c r="D222" t="n">
-        <v>40.94989013953506</v>
+        <v>40.9498939275561</v>
       </c>
       <c r="E222" t="n">
-        <v>41.82464166928109</v>
+        <v>41.82464553821999</v>
       </c>
       <c r="F222" t="n">
         <v>3033780</v>
@@ -4952,16 +4952,16 @@
         <v>44482</v>
       </c>
       <c r="B227" t="n">
-        <v>39.66180038452148</v>
+        <v>39.66179656982422</v>
       </c>
       <c r="C227" t="n">
-        <v>40.05591793090613</v>
+        <v>40.05591407830239</v>
       </c>
       <c r="D227" t="n">
-        <v>38.88317407585477</v>
+        <v>38.88317033604628</v>
       </c>
       <c r="E227" t="n">
-        <v>39.43109587666738</v>
+        <v>39.43109208415942</v>
       </c>
       <c r="F227" t="n">
         <v>1130628</v>
@@ -5012,16 +5012,16 @@
         <v>44487</v>
       </c>
       <c r="B230" t="n">
-        <v>39.87327575683594</v>
+        <v>39.87327194213867</v>
       </c>
       <c r="C230" t="n">
-        <v>41.44975342469183</v>
+        <v>41.44974945917212</v>
       </c>
       <c r="D230" t="n">
-        <v>39.18116598648377</v>
+        <v>39.18116223800101</v>
       </c>
       <c r="E230" t="n">
-        <v>39.72908778283576</v>
+        <v>39.72908398193304</v>
       </c>
       <c r="F230" t="n">
         <v>2573169</v>
@@ -5032,16 +5032,16 @@
         <v>44488</v>
       </c>
       <c r="B231" t="n">
-        <v>37.58546829223633</v>
+        <v>37.58546447753906</v>
       </c>
       <c r="C231" t="n">
-        <v>40.08475657457366</v>
+        <v>40.08475250621378</v>
       </c>
       <c r="D231" t="n">
-        <v>36.86452090235465</v>
+        <v>36.86451716082918</v>
       </c>
       <c r="E231" t="n">
-        <v>39.57528488714614</v>
+        <v>39.57528087049455</v>
       </c>
       <c r="F231" t="n">
         <v>2915331</v>
@@ -5072,16 +5072,16 @@
         <v>44490</v>
       </c>
       <c r="B233" t="n">
-        <v>34.41329193115234</v>
+        <v>34.41328811645508</v>
       </c>
       <c r="C233" t="n">
-        <v>36.09550752381791</v>
+        <v>36.09550352264783</v>
       </c>
       <c r="D233" t="n">
-        <v>33.48086508042814</v>
+        <v>33.48086136908995</v>
       </c>
       <c r="E233" t="n">
-        <v>35.62448595864728</v>
+        <v>35.62448200968972</v>
       </c>
       <c r="F233" t="n">
         <v>3113087</v>
@@ -5092,16 +5092,16 @@
         <v>44491</v>
       </c>
       <c r="B234" t="n">
-        <v>32.63495254516602</v>
+        <v>32.63494873046875</v>
       </c>
       <c r="C234" t="n">
-        <v>34.06723862420559</v>
+        <v>34.06723464208851</v>
       </c>
       <c r="D234" t="n">
-        <v>31.04886594627039</v>
+        <v>31.04886231697067</v>
       </c>
       <c r="E234" t="n">
-        <v>33.63467091453443</v>
+        <v>33.63466698298016</v>
       </c>
       <c r="F234" t="n">
         <v>4894520</v>
@@ -5112,16 +5112,16 @@
         <v>44494</v>
       </c>
       <c r="B235" t="n">
-        <v>36.84706115722656</v>
+        <v>36.8470573425293</v>
       </c>
       <c r="C235" t="n">
-        <v>37.31127712193275</v>
+        <v>37.3112732591762</v>
       </c>
       <c r="D235" t="n">
-        <v>32.95926229019877</v>
+        <v>32.95925887799699</v>
       </c>
       <c r="E235" t="n">
-        <v>32.95926229019877</v>
+        <v>32.95925887799699</v>
       </c>
       <c r="F235" t="n">
         <v>3449995</v>
@@ -5152,16 +5152,16 @@
         <v>44496</v>
       </c>
       <c r="B237" t="n">
-        <v>35.29000473022461</v>
+        <v>35.29000854492188</v>
       </c>
       <c r="C237" t="n">
-        <v>36.07336794668348</v>
+        <v>36.07337184605893</v>
       </c>
       <c r="D237" t="n">
-        <v>34.47762778370612</v>
+        <v>34.47763151058894</v>
       </c>
       <c r="E237" t="n">
-        <v>36.07336794668348</v>
+        <v>36.07337184605893</v>
       </c>
       <c r="F237" t="n">
         <v>2270538</v>
@@ -5272,16 +5272,16 @@
         <v>44505</v>
       </c>
       <c r="B243" t="n">
-        <v>34.33256149291992</v>
+        <v>34.33255767822266</v>
       </c>
       <c r="C243" t="n">
-        <v>35.80257809171644</v>
+        <v>35.80257411368536</v>
       </c>
       <c r="D243" t="n">
-        <v>31.73102433433615</v>
+        <v>31.73102080869616</v>
       </c>
       <c r="E243" t="n">
-        <v>33.17202720107906</v>
+        <v>33.17202351532898</v>
       </c>
       <c r="F243" t="n">
         <v>9166770</v>
@@ -5312,16 +5312,16 @@
         <v>44509</v>
       </c>
       <c r="B245" t="n">
-        <v>34.50664520263672</v>
+        <v>34.50664138793945</v>
       </c>
       <c r="C245" t="n">
-        <v>35.10625735786877</v>
+        <v>35.1062534768846</v>
       </c>
       <c r="D245" t="n">
-        <v>32.63044377861175</v>
+        <v>32.63044017132788</v>
       </c>
       <c r="E245" t="n">
-        <v>33.89736430140155</v>
+        <v>33.89736055406007</v>
       </c>
       <c r="F245" t="n">
         <v>7032350</v>
@@ -5372,16 +5372,16 @@
         <v>44512</v>
       </c>
       <c r="B248" t="n">
-        <v>30.94766235351562</v>
+        <v>30.94766044616699</v>
       </c>
       <c r="C248" t="n">
-        <v>33.11399911175717</v>
+        <v>33.11399707089411</v>
       </c>
       <c r="D248" t="n">
-        <v>30.69621126299056</v>
+        <v>30.69620937113922</v>
       </c>
       <c r="E248" t="n">
-        <v>32.10819849723269</v>
+        <v>32.10819651835855</v>
       </c>
       <c r="F248" t="n">
         <v>3403064</v>
@@ -5552,16 +5552,16 @@
         <v>44526</v>
       </c>
       <c r="B257" t="n">
-        <v>26.69235992431641</v>
+        <v>26.69235801696777</v>
       </c>
       <c r="C257" t="n">
-        <v>27.61111748815896</v>
+        <v>27.61111551515892</v>
       </c>
       <c r="D257" t="n">
-        <v>25.85096918966023</v>
+        <v>25.85096734243463</v>
       </c>
       <c r="E257" t="n">
-        <v>26.59564810870458</v>
+        <v>26.59564620826666</v>
       </c>
       <c r="F257" t="n">
         <v>3664026</v>
@@ -5592,16 +5592,16 @@
         <v>44530</v>
       </c>
       <c r="B259" t="n">
-        <v>26.71170043945312</v>
+        <v>26.71169853210449</v>
       </c>
       <c r="C259" t="n">
-        <v>26.71170043945312</v>
+        <v>26.71169853210449</v>
       </c>
       <c r="D259" t="n">
-        <v>25.48346622320262</v>
+        <v>25.48346440355603</v>
       </c>
       <c r="E259" t="n">
-        <v>26.53761992558345</v>
+        <v>26.53761803066504</v>
       </c>
       <c r="F259" t="n">
         <v>4757647</v>
@@ -5612,16 +5612,16 @@
         <v>44531</v>
       </c>
       <c r="B260" t="n">
-        <v>26.69235992431641</v>
+        <v>26.69235801696777</v>
       </c>
       <c r="C260" t="n">
-        <v>28.01730598945588</v>
+        <v>28.01730398743094</v>
       </c>
       <c r="D260" t="n">
-        <v>26.32485577450663</v>
+        <v>26.32485389341864</v>
       </c>
       <c r="E260" t="n">
-        <v>27.17591712858762</v>
+        <v>27.17591518668557</v>
       </c>
       <c r="F260" t="n">
         <v>3467467</v>
@@ -5752,16 +5752,16 @@
         <v>44540</v>
       </c>
       <c r="B267" t="n">
-        <v>29.43896102905273</v>
+        <v>29.43896293640137</v>
       </c>
       <c r="C267" t="n">
-        <v>29.76778079564096</v>
+        <v>29.76778272429381</v>
       </c>
       <c r="D267" t="n">
-        <v>28.76198025889329</v>
+        <v>28.76198212238038</v>
       </c>
       <c r="E267" t="n">
-        <v>29.57435718308462</v>
+        <v>29.57435909920557</v>
       </c>
       <c r="F267" t="n">
         <v>1281952</v>
@@ -5832,16 +5832,16 @@
         <v>44546</v>
       </c>
       <c r="B271" t="n">
-        <v>30.62851524353027</v>
+        <v>30.62851333618164</v>
       </c>
       <c r="C271" t="n">
-        <v>30.86062322322113</v>
+        <v>30.86062130141829</v>
       </c>
       <c r="D271" t="n">
-        <v>29.25521235155887</v>
+        <v>29.25521052973079</v>
       </c>
       <c r="E271" t="n">
-        <v>29.49699095054871</v>
+        <v>29.4969891136642</v>
       </c>
       <c r="F271" t="n">
         <v>3477726</v>
@@ -5952,16 +5952,16 @@
         <v>44557</v>
       </c>
       <c r="B277" t="n">
-        <v>30.7252254486084</v>
+        <v>30.72522354125977</v>
       </c>
       <c r="C277" t="n">
-        <v>31.01536089416671</v>
+        <v>31.01535896880716</v>
       </c>
       <c r="D277" t="n">
-        <v>29.98054840663</v>
+        <v>29.98054654550914</v>
       </c>
       <c r="E277" t="n">
-        <v>29.98054840663</v>
+        <v>29.98054654550914</v>
       </c>
       <c r="F277" t="n">
         <v>1273927</v>
@@ -6132,16 +6132,16 @@
         <v>44571</v>
       </c>
       <c r="B286" t="n">
-        <v>33.37511825561523</v>
+        <v>33.37511444091797</v>
       </c>
       <c r="C286" t="n">
-        <v>33.89736166431392</v>
+        <v>33.89735778992546</v>
       </c>
       <c r="D286" t="n">
-        <v>32.24359399308115</v>
+        <v>32.24359030771443</v>
       </c>
       <c r="E286" t="n">
-        <v>32.3789901547752</v>
+        <v>32.37898645393302</v>
       </c>
       <c r="F286" t="n">
         <v>2829132</v>
@@ -6152,16 +6152,16 @@
         <v>44572</v>
       </c>
       <c r="B287" t="n">
-        <v>35.10625076293945</v>
+        <v>35.10625457763672</v>
       </c>
       <c r="C287" t="n">
-        <v>35.63816285834681</v>
+        <v>35.63816673084244</v>
       </c>
       <c r="D287" t="n">
-        <v>33.18169098013564</v>
+        <v>33.18169458570739</v>
       </c>
       <c r="E287" t="n">
-        <v>33.55886569280182</v>
+        <v>33.55886933935793</v>
       </c>
       <c r="F287" t="n">
         <v>3953735</v>
@@ -6172,16 +6172,16 @@
         <v>44573</v>
       </c>
       <c r="B288" t="n">
-        <v>34.89348602294922</v>
+        <v>34.89348983764648</v>
       </c>
       <c r="C288" t="n">
-        <v>35.98632394454952</v>
+        <v>35.98632787872025</v>
       </c>
       <c r="D288" t="n">
-        <v>34.13913659549451</v>
+        <v>34.13914032772324</v>
       </c>
       <c r="E288" t="n">
-        <v>35.34802942826484</v>
+        <v>35.34803329265463</v>
       </c>
       <c r="F288" t="n">
         <v>3302601</v>
@@ -6292,16 +6292,16 @@
         <v>44581</v>
       </c>
       <c r="B294" t="n">
-        <v>35.2996711730957</v>
+        <v>35.29967498779297</v>
       </c>
       <c r="C294" t="n">
-        <v>36.17007552296929</v>
+        <v>36.17007943172774</v>
       </c>
       <c r="D294" t="n">
-        <v>34.98052391082881</v>
+        <v>34.98052769103708</v>
       </c>
       <c r="E294" t="n">
-        <v>35.8702694969556</v>
+        <v>35.87027337331519</v>
       </c>
       <c r="F294" t="n">
         <v>3650414</v>
@@ -6332,16 +6332,16 @@
         <v>44585</v>
       </c>
       <c r="B296" t="n">
-        <v>34.35190582275391</v>
+        <v>34.35190200805664</v>
       </c>
       <c r="C296" t="n">
-        <v>35.31902021252021</v>
+        <v>35.3190162904272</v>
       </c>
       <c r="D296" t="n">
-        <v>34.05209976231423</v>
+        <v>34.05209598090971</v>
       </c>
       <c r="E296" t="n">
-        <v>34.2358508967577</v>
+        <v>34.23584709494806</v>
       </c>
       <c r="F296" t="n">
         <v>2113697</v>
@@ -6392,16 +6392,16 @@
         <v>44588</v>
       </c>
       <c r="B299" t="n">
-        <v>36.09270858764648</v>
+        <v>36.09271240234375</v>
       </c>
       <c r="C299" t="n">
-        <v>37.10817788022283</v>
+        <v>37.1081818022467</v>
       </c>
       <c r="D299" t="n">
-        <v>35.68652012110085</v>
+        <v>35.68652389286739</v>
       </c>
       <c r="E299" t="n">
-        <v>35.87994373577622</v>
+        <v>35.87994752798603</v>
       </c>
       <c r="F299" t="n">
         <v>3171460</v>
@@ -6492,16 +6492,16 @@
         <v>44595</v>
       </c>
       <c r="B304" t="n">
-        <v>35.2996711730957</v>
+        <v>35.29967498779297</v>
       </c>
       <c r="C304" t="n">
-        <v>35.58980845477045</v>
+        <v>35.58981230082171</v>
       </c>
       <c r="D304" t="n">
-        <v>33.84899975502328</v>
+        <v>33.84900341295216</v>
       </c>
       <c r="E304" t="n">
-        <v>34.98052391082881</v>
+        <v>34.98052769103708</v>
       </c>
       <c r="F304" t="n">
         <v>4177823</v>
@@ -6592,16 +6592,16 @@
         <v>44602</v>
       </c>
       <c r="B309" t="n">
-        <v>37.28226089477539</v>
+        <v>37.28226470947266</v>
       </c>
       <c r="C309" t="n">
-        <v>38.38477139493146</v>
+        <v>38.3847753224369</v>
       </c>
       <c r="D309" t="n">
-        <v>36.33448778997354</v>
+        <v>36.33449150769526</v>
       </c>
       <c r="E309" t="n">
-        <v>36.3635015200494</v>
+        <v>36.36350524073979</v>
       </c>
       <c r="F309" t="n">
         <v>7025951</v>
@@ -6612,16 +6612,16 @@
         <v>44603</v>
       </c>
       <c r="B310" t="n">
-        <v>38.07529449462891</v>
+        <v>38.07529067993164</v>
       </c>
       <c r="C310" t="n">
-        <v>38.49115547855604</v>
+        <v>38.49115162219439</v>
       </c>
       <c r="D310" t="n">
-        <v>37.37897243800389</v>
+        <v>37.37896869306991</v>
       </c>
       <c r="E310" t="n">
-        <v>37.78516092896444</v>
+        <v>37.78515714333515</v>
       </c>
       <c r="F310" t="n">
         <v>5486491</v>
@@ -6632,16 +6632,16 @@
         <v>44606</v>
       </c>
       <c r="B311" t="n">
-        <v>37.57239532470703</v>
+        <v>37.57239151000977</v>
       </c>
       <c r="C311" t="n">
-        <v>38.84898823510746</v>
+        <v>38.84898429079868</v>
       </c>
       <c r="D311" t="n">
-        <v>36.95344198127135</v>
+        <v>36.95343822941596</v>
       </c>
       <c r="E311" t="n">
-        <v>38.2977310983781</v>
+        <v>38.29772721003804</v>
       </c>
       <c r="F311" t="n">
         <v>3902640</v>
@@ -6652,16 +6652,16 @@
         <v>44607</v>
       </c>
       <c r="B312" t="n">
-        <v>35.79290390014648</v>
+        <v>35.79290008544922</v>
       </c>
       <c r="C312" t="n">
-        <v>36.65363583255173</v>
+        <v>36.65363192612031</v>
       </c>
       <c r="D312" t="n">
-        <v>35.63816650158672</v>
+        <v>35.63816270338088</v>
       </c>
       <c r="E312" t="n">
-        <v>36.55692589534578</v>
+        <v>36.55692199922141</v>
       </c>
       <c r="F312" t="n">
         <v>3810709</v>
@@ -6672,16 +6672,16 @@
         <v>44608</v>
       </c>
       <c r="B313" t="n">
-        <v>35.92829895019531</v>
+        <v>35.92830276489258</v>
       </c>
       <c r="C313" t="n">
-        <v>36.80837209332255</v>
+        <v>36.80837600146183</v>
       </c>
       <c r="D313" t="n">
-        <v>35.69619285953032</v>
+        <v>35.69619664958365</v>
       </c>
       <c r="E313" t="n">
-        <v>36.4408698462091</v>
+        <v>36.44087371532872</v>
       </c>
       <c r="F313" t="n">
         <v>4244663</v>
@@ -6692,16 +6692,16 @@
         <v>44609</v>
       </c>
       <c r="B314" t="n">
-        <v>35.2996711730957</v>
+        <v>35.29967498779297</v>
       </c>
       <c r="C314" t="n">
-        <v>35.89928322512308</v>
+        <v>35.89928710461807</v>
       </c>
       <c r="D314" t="n">
-        <v>34.41959807888318</v>
+        <v>34.41960179847439</v>
       </c>
       <c r="E314" t="n">
-        <v>35.68651838361181</v>
+        <v>35.68652224011414</v>
       </c>
       <c r="F314" t="n">
         <v>4430658</v>
@@ -6712,16 +6712,16 @@
         <v>44610</v>
       </c>
       <c r="B315" t="n">
-        <v>34.48729705810547</v>
+        <v>34.48730087280273</v>
       </c>
       <c r="C315" t="n">
-        <v>35.41572509065163</v>
+        <v>35.41572900804387</v>
       </c>
       <c r="D315" t="n">
-        <v>33.80064384086931</v>
+        <v>33.80064757961473</v>
       </c>
       <c r="E315" t="n">
-        <v>34.83545803875718</v>
+        <v>34.83546189196511</v>
       </c>
       <c r="F315" t="n">
         <v>4069741</v>
@@ -6852,16 +6852,16 @@
         <v>44623</v>
       </c>
       <c r="B322" t="n">
-        <v>37.34028244018555</v>
+        <v>37.34028625488281</v>
       </c>
       <c r="C322" t="n">
-        <v>37.88187078764361</v>
+        <v>37.88187465766974</v>
       </c>
       <c r="D322" t="n">
-        <v>36.31514444477941</v>
+        <v>36.31514815474819</v>
       </c>
       <c r="E322" t="n">
-        <v>37.12751759702811</v>
+        <v>37.12752138998924</v>
       </c>
       <c r="F322" t="n">
         <v>9786414</v>
@@ -6892,16 +6892,16 @@
         <v>44627</v>
       </c>
       <c r="B324" t="n">
-        <v>37.04048538208008</v>
+        <v>37.04048156738281</v>
       </c>
       <c r="C324" t="n">
-        <v>39.28418904358112</v>
+        <v>39.28418499781101</v>
       </c>
       <c r="D324" t="n">
-        <v>36.65363811402602</v>
+        <v>36.65363433916909</v>
       </c>
       <c r="E324" t="n">
-        <v>38.17200970618351</v>
+        <v>38.17200577495368</v>
       </c>
       <c r="F324" t="n">
         <v>5025922</v>
@@ -6952,16 +6952,16 @@
         <v>44630</v>
       </c>
       <c r="B327" t="n">
-        <v>35.72520446777344</v>
+        <v>35.7252082824707</v>
       </c>
       <c r="C327" t="n">
-        <v>37.22423084456335</v>
+        <v>37.22423481932497</v>
       </c>
       <c r="D327" t="n">
-        <v>35.51243962707166</v>
+        <v>35.51244341905014</v>
       </c>
       <c r="E327" t="n">
-        <v>36.75034245134777</v>
+        <v>36.75034637550812</v>
       </c>
       <c r="F327" t="n">
         <v>4502679</v>
@@ -7032,16 +7032,16 @@
         <v>44636</v>
       </c>
       <c r="B331" t="n">
-        <v>32.84320831298828</v>
+        <v>32.84320449829102</v>
       </c>
       <c r="C331" t="n">
-        <v>34.44861737575539</v>
+        <v>34.44861337459189</v>
       </c>
       <c r="D331" t="n">
-        <v>32.34030985608281</v>
+        <v>32.34030609979657</v>
       </c>
       <c r="E331" t="n">
-        <v>34.10045632903992</v>
+        <v>34.10045236831488</v>
       </c>
       <c r="F331" t="n">
         <v>3899288</v>
@@ -7092,16 +7092,16 @@
         <v>44641</v>
       </c>
       <c r="B334" t="n">
-        <v>36.61495208740234</v>
+        <v>36.61494827270508</v>
       </c>
       <c r="C334" t="n">
-        <v>36.86640318776314</v>
+        <v>36.86639934686866</v>
       </c>
       <c r="D334" t="n">
-        <v>35.88961626653654</v>
+        <v>35.88961252740777</v>
       </c>
       <c r="E334" t="n">
-        <v>35.97665746445866</v>
+        <v>35.97665371626157</v>
       </c>
       <c r="F334" t="n">
         <v>3600944</v>
@@ -7212,16 +7212,16 @@
         <v>44649</v>
       </c>
       <c r="B340" t="n">
-        <v>40.11590576171875</v>
+        <v>40.11590194702148</v>
       </c>
       <c r="C340" t="n">
-        <v>40.60913544747385</v>
+        <v>40.60913158587444</v>
       </c>
       <c r="D340" t="n">
-        <v>37.8141747233464</v>
+        <v>37.81417112752509</v>
       </c>
       <c r="E340" t="n">
-        <v>38.00759834997051</v>
+        <v>38.00759473575618</v>
       </c>
       <c r="F340" t="n">
         <v>6952609</v>
@@ -7252,16 +7252,16 @@
         <v>44651</v>
       </c>
       <c r="B342" t="n">
-        <v>40.47373580932617</v>
+        <v>40.47373962402344</v>
       </c>
       <c r="C342" t="n">
-        <v>41.13137533388116</v>
+        <v>41.13137921056172</v>
       </c>
       <c r="D342" t="n">
-        <v>39.6710313879373</v>
+        <v>39.67103512697872</v>
       </c>
       <c r="E342" t="n">
-        <v>40.13524730247168</v>
+        <v>40.135251085266</v>
       </c>
       <c r="F342" t="n">
         <v>3810811</v>
@@ -7312,16 +7312,16 @@
         <v>44656</v>
       </c>
       <c r="B345" t="n">
-        <v>41.9727668762207</v>
+        <v>41.97276306152344</v>
       </c>
       <c r="C345" t="n">
-        <v>43.03659497534015</v>
+        <v>43.03659106395681</v>
       </c>
       <c r="D345" t="n">
-        <v>41.5762508676977</v>
+        <v>41.57624708903781</v>
       </c>
       <c r="E345" t="n">
-        <v>42.30158667490721</v>
+        <v>42.30158283032514</v>
       </c>
       <c r="F345" t="n">
         <v>5903074</v>
@@ -7432,16 +7432,16 @@
         <v>44664</v>
       </c>
       <c r="B351" t="n">
-        <v>43.62653350830078</v>
+        <v>43.62652969360352</v>
       </c>
       <c r="C351" t="n">
-        <v>43.71357095479976</v>
+        <v>43.71356713249195</v>
       </c>
       <c r="D351" t="n">
-        <v>42.8431702567798</v>
+        <v>42.8431665105797</v>
       </c>
       <c r="E351" t="n">
-        <v>43.30738621093589</v>
+        <v>43.30738242414481</v>
       </c>
       <c r="F351" t="n">
         <v>3238402</v>
@@ -7452,16 +7452,16 @@
         <v>44665</v>
       </c>
       <c r="B352" t="n">
-        <v>42.93987655639648</v>
+        <v>42.93988037109375</v>
       </c>
       <c r="C352" t="n">
-        <v>43.62652981023535</v>
+        <v>43.62653368593358</v>
       </c>
       <c r="D352" t="n">
-        <v>42.2242133212342</v>
+        <v>42.2242170723533</v>
       </c>
       <c r="E352" t="n">
-        <v>43.62652981023535</v>
+        <v>43.62653368593358</v>
       </c>
       <c r="F352" t="n">
         <v>2345809</v>
@@ -7552,16 +7552,16 @@
         <v>44676</v>
       </c>
       <c r="B357" t="n">
-        <v>41.94374847412109</v>
+        <v>41.94375228881836</v>
       </c>
       <c r="C357" t="n">
-        <v>42.40796438837074</v>
+        <v>42.40796824528748</v>
       </c>
       <c r="D357" t="n">
-        <v>40.64781815768625</v>
+        <v>40.64782185452133</v>
       </c>
       <c r="E357" t="n">
-        <v>40.75420058099602</v>
+        <v>40.75420428750637</v>
       </c>
       <c r="F357" t="n">
         <v>3287465</v>
@@ -7592,16 +7592,16 @@
         <v>44678</v>
       </c>
       <c r="B359" t="n">
-        <v>42.16619110107422</v>
+        <v>42.16618728637695</v>
       </c>
       <c r="C359" t="n">
-        <v>43.58784900340616</v>
+        <v>43.58784506009413</v>
       </c>
       <c r="D359" t="n">
-        <v>41.46986901615963</v>
+        <v>41.46986526445734</v>
       </c>
       <c r="E359" t="n">
-        <v>43.52015279261696</v>
+        <v>43.52014885542929</v>
       </c>
       <c r="F359" t="n">
         <v>3779727</v>
@@ -7672,16 +7672,16 @@
         <v>44684</v>
       </c>
       <c r="B363" t="n">
-        <v>42.12749862670898</v>
+        <v>42.12750244140625</v>
       </c>
       <c r="C363" t="n">
-        <v>42.54335956584936</v>
+        <v>42.54336341820335</v>
       </c>
       <c r="D363" t="n">
-        <v>41.25709802345466</v>
+        <v>41.25710175933607</v>
       </c>
       <c r="E363" t="n">
-        <v>42.54335956584936</v>
+        <v>42.54336341820335</v>
       </c>
       <c r="F363" t="n">
         <v>4458389</v>
@@ -7692,16 +7692,16 @@
         <v>44685</v>
       </c>
       <c r="B364" t="n">
-        <v>44.10041809082031</v>
+        <v>44.10041427612305</v>
       </c>
       <c r="C364" t="n">
-        <v>44.32285544811791</v>
+        <v>44.32285161417975</v>
       </c>
       <c r="D364" t="n">
-        <v>42.16618932580826</v>
+        <v>42.16618567842227</v>
       </c>
       <c r="E364" t="n">
-        <v>43.04626251447057</v>
+        <v>43.04625879095802</v>
       </c>
       <c r="F364" t="n">
         <v>5759540</v>
@@ -7712,16 +7712,16 @@
         <v>44686</v>
       </c>
       <c r="B365" t="n">
-        <v>42.92053604125977</v>
+        <v>42.92053985595703</v>
       </c>
       <c r="C365" t="n">
-        <v>44.57429987842104</v>
+        <v>44.57430384010176</v>
       </c>
       <c r="D365" t="n">
-        <v>42.01144918067956</v>
+        <v>42.01145291457887</v>
       </c>
       <c r="E365" t="n">
-        <v>44.09074271874429</v>
+        <v>44.09074663744735</v>
       </c>
       <c r="F365" t="n">
         <v>4814532</v>
@@ -7732,16 +7732,16 @@
         <v>44687</v>
       </c>
       <c r="B366" t="n">
-        <v>42.55303192138672</v>
+        <v>42.55303573608398</v>
       </c>
       <c r="C366" t="n">
-        <v>43.90698966019007</v>
+        <v>43.90699359626386</v>
       </c>
       <c r="D366" t="n">
-        <v>41.82769621387857</v>
+        <v>41.82769996355259</v>
       </c>
       <c r="E366" t="n">
-        <v>43.33639133753226</v>
+        <v>43.33639522245434</v>
       </c>
       <c r="F366" t="n">
         <v>4093307</v>
@@ -7892,16 +7892,16 @@
         <v>44699</v>
       </c>
       <c r="B374" t="n">
-        <v>39.99985122680664</v>
+        <v>39.99985504150391</v>
       </c>
       <c r="C374" t="n">
-        <v>42.2242133773643</v>
+        <v>42.22421740419406</v>
       </c>
       <c r="D374" t="n">
-        <v>39.72905892177436</v>
+        <v>39.72906271064676</v>
       </c>
       <c r="E374" t="n">
-        <v>42.13717219055205</v>
+        <v>42.13717620908088</v>
       </c>
       <c r="F374" t="n">
         <v>1865839</v>
@@ -7952,16 +7952,16 @@
         <v>44704</v>
       </c>
       <c r="B377" t="n">
-        <v>42.28224182128906</v>
+        <v>42.28224563598633</v>
       </c>
       <c r="C377" t="n">
-        <v>42.7948127143697</v>
+        <v>42.79481657531103</v>
       </c>
       <c r="D377" t="n">
-        <v>41.3538099687909</v>
+        <v>41.35381369972519</v>
       </c>
       <c r="E377" t="n">
-        <v>41.42150992041549</v>
+        <v>41.42151365745766</v>
       </c>
       <c r="F377" t="n">
         <v>3400119</v>
@@ -8012,16 +8012,16 @@
         <v>44707</v>
       </c>
       <c r="B380" t="n">
-        <v>46.59557342529297</v>
+        <v>46.5955696105957</v>
       </c>
       <c r="C380" t="n">
-        <v>47.16617181868395</v>
+        <v>47.1661679572728</v>
       </c>
       <c r="D380" t="n">
-        <v>45.10621935322675</v>
+        <v>45.10621566046026</v>
       </c>
       <c r="E380" t="n">
-        <v>45.25128426416589</v>
+        <v>45.2512805595232</v>
       </c>
       <c r="F380" t="n">
         <v>4582217</v>
@@ -8072,16 +8072,16 @@
         <v>44712</v>
       </c>
       <c r="B383" t="n">
-        <v>47.14683151245117</v>
+        <v>47.14682769775391</v>
       </c>
       <c r="C383" t="n">
-        <v>49.54527256510714</v>
+        <v>49.5452685563496</v>
       </c>
       <c r="D383" t="n">
-        <v>47.11781778017441</v>
+        <v>47.11781396782467</v>
       </c>
       <c r="E383" t="n">
-        <v>48.22032836396376</v>
+        <v>48.22032446240879</v>
       </c>
       <c r="F383" t="n">
         <v>6322705</v>
@@ -8152,16 +8152,16 @@
         <v>44718</v>
       </c>
       <c r="B387" t="n">
-        <v>45.31898498535156</v>
+        <v>45.3189811706543</v>
       </c>
       <c r="C387" t="n">
-        <v>47.45630618888874</v>
+        <v>47.4563021942838</v>
       </c>
       <c r="D387" t="n">
-        <v>45.13523009894016</v>
+        <v>45.13522629971035</v>
       </c>
       <c r="E387" t="n">
-        <v>47.156500121283</v>
+        <v>47.15649615191405</v>
       </c>
       <c r="F387" t="n">
         <v>1711233</v>
@@ -8172,16 +8172,16 @@
         <v>44719</v>
       </c>
       <c r="B388" t="n">
-        <v>45.31898498535156</v>
+        <v>45.3189811706543</v>
       </c>
       <c r="C388" t="n">
-        <v>45.84122466966569</v>
+        <v>45.84122081100923</v>
       </c>
       <c r="D388" t="n">
-        <v>44.73871408907649</v>
+        <v>44.73871032322317</v>
       </c>
       <c r="E388" t="n">
-        <v>44.98049269229714</v>
+        <v>44.98048890609225</v>
       </c>
       <c r="F388" t="n">
         <v>1887578</v>
@@ -8192,16 +8192,16 @@
         <v>44720</v>
       </c>
       <c r="B389" t="n">
-        <v>45.25128173828125</v>
+        <v>45.25128555297852</v>
       </c>
       <c r="C389" t="n">
-        <v>46.00563122530019</v>
+        <v>46.00563510358936</v>
       </c>
       <c r="D389" t="n">
-        <v>44.9224619623857</v>
+        <v>44.92246574936335</v>
       </c>
       <c r="E389" t="n">
-        <v>45.31898169100119</v>
+        <v>45.31898551140559</v>
       </c>
       <c r="F389" t="n">
         <v>1920490</v>
@@ -8212,16 +8212,16 @@
         <v>44721</v>
       </c>
       <c r="B390" t="n">
-        <v>44.50660705566406</v>
+        <v>44.5066032409668</v>
       </c>
       <c r="C390" t="n">
-        <v>45.59944512032232</v>
+        <v>45.59944121195702</v>
       </c>
       <c r="D390" t="n">
-        <v>44.32285592064108</v>
+        <v>44.32285212169327</v>
       </c>
       <c r="E390" t="n">
-        <v>45.2222703572209</v>
+        <v>45.22226648118356</v>
       </c>
       <c r="F390" t="n">
         <v>1644697</v>
@@ -8472,16 +8472,16 @@
         <v>44741</v>
       </c>
       <c r="B403" t="n">
-        <v>34.71940994262695</v>
+        <v>34.71940612792969</v>
       </c>
       <c r="C403" t="n">
-        <v>35.41573204057546</v>
+        <v>35.41572814937177</v>
       </c>
       <c r="D403" t="n">
-        <v>34.0907840567348</v>
+        <v>34.09078031110602</v>
       </c>
       <c r="E403" t="n">
-        <v>35.29967710839206</v>
+        <v>35.29967322993957</v>
       </c>
       <c r="F403" t="n">
         <v>2690880</v>
@@ -8532,16 +8532,16 @@
         <v>44746</v>
       </c>
       <c r="B406" t="n">
-        <v>35.08690643310547</v>
+        <v>35.08691024780273</v>
       </c>
       <c r="C406" t="n">
-        <v>35.60914979405575</v>
+        <v>35.60915366553204</v>
       </c>
       <c r="D406" t="n">
-        <v>34.19716459197961</v>
+        <v>34.1971683099429</v>
       </c>
       <c r="E406" t="n">
-        <v>34.57433556409744</v>
+        <v>34.57433932306729</v>
       </c>
       <c r="F406" t="n">
         <v>2359523</v>
@@ -8612,16 +8612,16 @@
         <v>44750</v>
       </c>
       <c r="B410" t="n">
-        <v>31.81806564331055</v>
+        <v>31.81806373596191</v>
       </c>
       <c r="C410" t="n">
-        <v>32.48537398775778</v>
+        <v>32.48537204040704</v>
       </c>
       <c r="D410" t="n">
-        <v>31.19911226993215</v>
+        <v>31.19911039968697</v>
       </c>
       <c r="E410" t="n">
-        <v>31.31516719855805</v>
+        <v>31.3151653213559</v>
       </c>
       <c r="F410" t="n">
         <v>4375906</v>
@@ -8712,16 +8712,16 @@
         <v>44757</v>
       </c>
       <c r="B415" t="n">
-        <v>27.79486656188965</v>
+        <v>27.79486846923828</v>
       </c>
       <c r="C415" t="n">
-        <v>29.07145943509457</v>
+        <v>29.07146143004599</v>
       </c>
       <c r="D415" t="n">
-        <v>27.79486656188965</v>
+        <v>27.79486846923828</v>
       </c>
       <c r="E415" t="n">
-        <v>29.06178694260021</v>
+        <v>29.06178893688788</v>
       </c>
       <c r="F415" t="n">
         <v>4618481</v>
@@ -8752,16 +8752,16 @@
         <v>44761</v>
       </c>
       <c r="B417" t="n">
-        <v>29.43896102905273</v>
+        <v>29.43896293640137</v>
       </c>
       <c r="C417" t="n">
-        <v>29.5356728353309</v>
+        <v>29.53567474894549</v>
       </c>
       <c r="D417" t="n">
-        <v>28.11401509178381</v>
+        <v>28.11401691328927</v>
       </c>
       <c r="E417" t="n">
-        <v>28.14302882104603</v>
+        <v>28.14303064443129</v>
       </c>
       <c r="F417" t="n">
         <v>4570230</v>
@@ -8772,16 +8772,16 @@
         <v>44762</v>
       </c>
       <c r="B418" t="n">
-        <v>30.5994987487793</v>
+        <v>30.59950065612793</v>
       </c>
       <c r="C418" t="n">
-        <v>30.97667347904845</v>
+        <v>30.97667540990739</v>
       </c>
       <c r="D418" t="n">
-        <v>29.21652536238831</v>
+        <v>29.21652718353251</v>
       </c>
       <c r="E418" t="n">
-        <v>29.21652536238831</v>
+        <v>29.21652718353251</v>
       </c>
       <c r="F418" t="n">
         <v>5027446</v>
@@ -8792,16 +8792,16 @@
         <v>44763</v>
       </c>
       <c r="B419" t="n">
-        <v>29.44863319396973</v>
+        <v>29.44863510131836</v>
       </c>
       <c r="C419" t="n">
-        <v>29.86449039614633</v>
+        <v>29.86449233042948</v>
       </c>
       <c r="D419" t="n">
-        <v>28.83935050759925</v>
+        <v>28.83935237548546</v>
       </c>
       <c r="E419" t="n">
-        <v>29.86449039614633</v>
+        <v>29.86449233042948</v>
       </c>
       <c r="F419" t="n">
         <v>5437325</v>
@@ -8832,16 +8832,16 @@
         <v>44767</v>
       </c>
       <c r="B421" t="n">
-        <v>29.26488304138184</v>
+        <v>29.2648811340332</v>
       </c>
       <c r="C421" t="n">
-        <v>29.71942650877206</v>
+        <v>29.7194245717984</v>
       </c>
       <c r="D421" t="n">
-        <v>28.43316480875549</v>
+        <v>28.43316295561438</v>
       </c>
       <c r="E421" t="n">
-        <v>28.87803765682343</v>
+        <v>28.87803577468757</v>
       </c>
       <c r="F421" t="n">
         <v>3521914</v>
@@ -8852,16 +8852,16 @@
         <v>44768</v>
       </c>
       <c r="B422" t="n">
-        <v>28.95540618896484</v>
+        <v>28.95540428161621</v>
       </c>
       <c r="C422" t="n">
-        <v>30.15462856046375</v>
+        <v>30.15462657412001</v>
       </c>
       <c r="D422" t="n">
-        <v>28.81033940483069</v>
+        <v>28.81033750703789</v>
       </c>
       <c r="E422" t="n">
-        <v>29.88383623072646</v>
+        <v>29.88383426222034</v>
       </c>
       <c r="F422" t="n">
         <v>2984449</v>
@@ -8872,16 +8872,16 @@
         <v>44769</v>
       </c>
       <c r="B423" t="n">
-        <v>29.66139793395996</v>
+        <v>29.66139984130859</v>
       </c>
       <c r="C423" t="n">
-        <v>29.76778035716261</v>
+        <v>29.76778227135207</v>
       </c>
       <c r="D423" t="n">
-        <v>28.6169130648438</v>
+        <v>28.61691490502781</v>
       </c>
       <c r="E423" t="n">
-        <v>28.95540344493757</v>
+        <v>28.95540530688788</v>
       </c>
       <c r="F423" t="n">
         <v>2554762</v>
@@ -8892,16 +8892,16 @@
         <v>44770</v>
       </c>
       <c r="B424" t="n">
-        <v>30.78325080871582</v>
+        <v>30.78325271606445</v>
       </c>
       <c r="C424" t="n">
-        <v>30.88963323601387</v>
+        <v>30.88963514995402</v>
       </c>
       <c r="D424" t="n">
-        <v>29.53567353730325</v>
+        <v>29.53567536735125</v>
       </c>
       <c r="E424" t="n">
-        <v>29.96120324649545</v>
+        <v>29.96120510290952</v>
       </c>
       <c r="F424" t="n">
         <v>4208906</v>
@@ -8952,16 +8952,16 @@
         <v>44775</v>
       </c>
       <c r="B427" t="n">
-        <v>31.85675048828125</v>
+        <v>31.85674858093262</v>
       </c>
       <c r="C427" t="n">
-        <v>32.07918409507452</v>
+        <v>32.0791821744082</v>
       </c>
       <c r="D427" t="n">
-        <v>30.94766170651904</v>
+        <v>30.94765985359998</v>
       </c>
       <c r="E427" t="n">
-        <v>31.32483646063348</v>
+        <v>31.32483458513196</v>
       </c>
       <c r="F427" t="n">
         <v>3020206</v>
@@ -9072,16 +9072,16 @@
         <v>44783</v>
       </c>
       <c r="B433" t="n">
-        <v>33.26873779296875</v>
+        <v>33.26873397827148</v>
       </c>
       <c r="C433" t="n">
-        <v>33.97473237410905</v>
+        <v>33.97472847846024</v>
       </c>
       <c r="D433" t="n">
-        <v>32.87222177725572</v>
+        <v>32.87221800802422</v>
       </c>
       <c r="E433" t="n">
-        <v>33.62657133023831</v>
+        <v>33.62656747451073</v>
       </c>
       <c r="F433" t="n">
         <v>3325457</v>
@@ -9152,16 +9152,16 @@
         <v>44789</v>
       </c>
       <c r="B437" t="n">
-        <v>32.27260971069336</v>
+        <v>32.27260589599609</v>
       </c>
       <c r="C437" t="n">
-        <v>32.61110200955398</v>
+        <v>32.61109815484615</v>
       </c>
       <c r="D437" t="n">
-        <v>31.73102503057709</v>
+        <v>31.73102127989639</v>
       </c>
       <c r="E437" t="n">
-        <v>32.39833338730038</v>
+        <v>32.39832955774229</v>
       </c>
       <c r="F437" t="n">
         <v>2684074</v>
@@ -9172,16 +9172,16 @@
         <v>44790</v>
       </c>
       <c r="B438" t="n">
-        <v>32.53372573852539</v>
+        <v>32.53372955322266</v>
       </c>
       <c r="C438" t="n">
-        <v>32.93024545622303</v>
+        <v>32.93024931741367</v>
       </c>
       <c r="D438" t="n">
-        <v>31.80839000156146</v>
+        <v>31.80839373121048</v>
       </c>
       <c r="E438" t="n">
-        <v>31.81806249384815</v>
+        <v>31.8180662246313</v>
       </c>
       <c r="F438" t="n">
         <v>3057587</v>
@@ -9252,16 +9252,16 @@
         <v>44796</v>
       </c>
       <c r="B442" t="n">
-        <v>35.11592483520508</v>
+        <v>35.11592102050781</v>
       </c>
       <c r="C442" t="n">
-        <v>35.54145457609587</v>
+        <v>35.54145071517264</v>
       </c>
       <c r="D442" t="n">
-        <v>33.43314711052539</v>
+        <v>33.43314347863087</v>
       </c>
       <c r="E442" t="n">
-        <v>33.46216084263848</v>
+        <v>33.46215720759215</v>
       </c>
       <c r="F442" t="n">
         <v>5706007</v>
@@ -9292,16 +9292,16 @@
         <v>44798</v>
       </c>
       <c r="B444" t="n">
-        <v>35.73487854003906</v>
+        <v>35.7348747253418</v>
       </c>
       <c r="C444" t="n">
-        <v>36.56659679067325</v>
+        <v>36.56659288719009</v>
       </c>
       <c r="D444" t="n">
-        <v>35.39638999233915</v>
+        <v>35.39638621377552</v>
       </c>
       <c r="E444" t="n">
-        <v>35.86060596289047</v>
+        <v>35.8606021347718</v>
       </c>
       <c r="F444" t="n">
         <v>2850362</v>
@@ -9372,16 +9372,16 @@
         <v>44804</v>
       </c>
       <c r="B448" t="n">
-        <v>36.16040802001953</v>
+        <v>36.16040420532227</v>
       </c>
       <c r="C448" t="n">
-        <v>36.46021408739674</v>
+        <v>36.46021024107181</v>
       </c>
       <c r="D448" t="n">
-        <v>35.22230734004456</v>
+        <v>35.22230362431106</v>
       </c>
       <c r="E448" t="n">
-        <v>35.91862941698318</v>
+        <v>35.91862562779205</v>
       </c>
       <c r="F448" t="n">
         <v>3394125</v>
@@ -9392,16 +9392,16 @@
         <v>44805</v>
       </c>
       <c r="B449" t="n">
-        <v>35.58013916015625</v>
+        <v>35.58013534545898</v>
       </c>
       <c r="C449" t="n">
-        <v>36.22810623483188</v>
+        <v>36.22810235066332</v>
       </c>
       <c r="D449" t="n">
-        <v>35.00954078502128</v>
+        <v>35.00953703150028</v>
       </c>
       <c r="E449" t="n">
-        <v>35.84125898955293</v>
+        <v>35.8412551468599</v>
       </c>
       <c r="F449" t="n">
         <v>3340084</v>
@@ -9492,16 +9492,16 @@
         <v>44813</v>
       </c>
       <c r="B454" t="n">
-        <v>35.92829895019531</v>
+        <v>35.92830276489258</v>
       </c>
       <c r="C454" t="n">
-        <v>36.3731698941971</v>
+        <v>36.37317375612866</v>
       </c>
       <c r="D454" t="n">
-        <v>35.60915167019012</v>
+        <v>35.60915545100184</v>
       </c>
       <c r="E454" t="n">
-        <v>35.79290279374685</v>
+        <v>35.79290659406839</v>
       </c>
       <c r="F454" t="n">
         <v>3544465</v>
@@ -9552,16 +9552,16 @@
         <v>44818</v>
       </c>
       <c r="B457" t="n">
-        <v>37.25325012207031</v>
+        <v>37.25324630737305</v>
       </c>
       <c r="C457" t="n">
-        <v>37.57239743066493</v>
+        <v>37.57239358328728</v>
       </c>
       <c r="D457" t="n">
-        <v>35.96698839437353</v>
+        <v>35.96698471138824</v>
       </c>
       <c r="E457" t="n">
-        <v>36.05402584393507</v>
+        <v>36.05402215203722</v>
       </c>
       <c r="F457" t="n">
         <v>4057043</v>
@@ -9592,16 +9592,16 @@
         <v>44820</v>
       </c>
       <c r="B459" t="n">
-        <v>36.7987060546875</v>
+        <v>36.79870223999023</v>
       </c>
       <c r="C459" t="n">
-        <v>36.7987060546875</v>
+        <v>36.79870223999023</v>
       </c>
       <c r="D459" t="n">
-        <v>35.7832329328566</v>
+        <v>35.78322922342723</v>
       </c>
       <c r="E459" t="n">
-        <v>36.14106646140942</v>
+        <v>36.14106271488564</v>
       </c>
       <c r="F459" t="n">
         <v>2974596</v>
@@ -9612,16 +9612,16 @@
         <v>44823</v>
       </c>
       <c r="B460" t="n">
-        <v>36.84706115722656</v>
+        <v>36.8470573425293</v>
       </c>
       <c r="C460" t="n">
-        <v>37.39831831798563</v>
+        <v>37.3983144462179</v>
       </c>
       <c r="D460" t="n">
-        <v>35.79290555412169</v>
+        <v>35.7929018485589</v>
       </c>
       <c r="E460" t="n">
-        <v>35.79290555412169</v>
+        <v>35.7929018485589</v>
       </c>
       <c r="F460" t="n">
         <v>3461677</v>
@@ -9652,16 +9652,16 @@
         <v>44825</v>
       </c>
       <c r="B462" t="n">
-        <v>38.03661346435547</v>
+        <v>38.0366096496582</v>
       </c>
       <c r="C462" t="n">
-        <v>38.79096301231463</v>
+        <v>38.79095912196355</v>
       </c>
       <c r="D462" t="n">
-        <v>37.62075246461414</v>
+        <v>37.62074869162363</v>
       </c>
       <c r="E462" t="n">
-        <v>37.93989977373904</v>
+        <v>37.9398959687412</v>
       </c>
       <c r="F462" t="n">
         <v>4689181</v>
@@ -9732,16 +9732,16 @@
         <v>44831</v>
       </c>
       <c r="B466" t="n">
-        <v>33.61689376831055</v>
+        <v>33.61689758300781</v>
       </c>
       <c r="C466" t="n">
-        <v>34.44861190035511</v>
+        <v>34.44861580943209</v>
       </c>
       <c r="D466" t="n">
-        <v>33.3267602334253</v>
+        <v>33.32676401519949</v>
       </c>
       <c r="E466" t="n">
-        <v>34.44861190035511</v>
+        <v>34.44861580943209</v>
       </c>
       <c r="F466" t="n">
         <v>5480701</v>
@@ -9752,16 +9752,16 @@
         <v>44832</v>
       </c>
       <c r="B467" t="n">
-        <v>34.57433700561523</v>
+        <v>34.5743408203125</v>
       </c>
       <c r="C467" t="n">
-        <v>34.99987045518622</v>
+        <v>34.99987431683395</v>
       </c>
       <c r="D467" t="n">
-        <v>33.19136547412988</v>
+        <v>33.19136913623947</v>
       </c>
       <c r="E467" t="n">
-        <v>33.66525014270204</v>
+        <v>33.66525385709685</v>
       </c>
       <c r="F467" t="n">
         <v>4399676</v>
@@ -9772,16 +9772,16 @@
         <v>44833</v>
       </c>
       <c r="B468" t="n">
-        <v>33.90703201293945</v>
+        <v>33.90702819824219</v>
       </c>
       <c r="C468" t="n">
-        <v>34.69039528924284</v>
+        <v>34.69039138641359</v>
       </c>
       <c r="D468" t="n">
-        <v>33.09465875193581</v>
+        <v>33.09465502863428</v>
       </c>
       <c r="E468" t="n">
-        <v>34.61302658569848</v>
+        <v>34.61302269157358</v>
       </c>
       <c r="F468" t="n">
         <v>4499631</v>
@@ -9812,16 +9812,16 @@
         <v>44837</v>
       </c>
       <c r="B470" t="n">
-        <v>36.7987060546875</v>
+        <v>36.79870223999023</v>
       </c>
       <c r="C470" t="n">
-        <v>36.91476098234264</v>
+        <v>36.91475715561467</v>
       </c>
       <c r="D470" t="n">
-        <v>35.52211309320833</v>
+        <v>35.52210941084767</v>
       </c>
       <c r="E470" t="n">
-        <v>36.26679013465196</v>
+        <v>36.26678637509517</v>
       </c>
       <c r="F470" t="n">
         <v>4419789</v>
@@ -9852,16 +9852,16 @@
         <v>44839</v>
       </c>
       <c r="B472" t="n">
-        <v>41.63427734375</v>
+        <v>41.63427352905273</v>
       </c>
       <c r="C472" t="n">
-        <v>42.48533680478608</v>
+        <v>42.48533291211138</v>
       </c>
       <c r="D472" t="n">
-        <v>40.55110803146717</v>
+        <v>40.55110431601417</v>
       </c>
       <c r="E472" t="n">
-        <v>40.61880798727272</v>
+        <v>40.61880426561678</v>
       </c>
       <c r="F472" t="n">
         <v>6927519</v>
@@ -9892,16 +9892,16 @@
         <v>44841</v>
       </c>
       <c r="B474" t="n">
-        <v>41.47953796386719</v>
+        <v>41.47954177856445</v>
       </c>
       <c r="C474" t="n">
-        <v>42.45632104937901</v>
+        <v>42.45632495390688</v>
       </c>
       <c r="D474" t="n">
-        <v>41.22808688619578</v>
+        <v>41.22809067776815</v>
       </c>
       <c r="E474" t="n">
-        <v>41.59558913638236</v>
+        <v>41.59559296175236</v>
       </c>
       <c r="F474" t="n">
         <v>3503020</v>
@@ -10072,16 +10072,16 @@
         <v>44855</v>
       </c>
       <c r="B483" t="n">
-        <v>44.22614288330078</v>
+        <v>44.22613906860352</v>
       </c>
       <c r="C483" t="n">
-        <v>44.68068635480393</v>
+        <v>44.68068250090031</v>
       </c>
       <c r="D483" t="n">
-        <v>42.41764149048589</v>
+        <v>42.41763783177974</v>
       </c>
       <c r="E483" t="n">
-        <v>42.9688949036628</v>
+        <v>42.96889119740864</v>
       </c>
       <c r="F483" t="n">
         <v>5360835</v>
@@ -10112,16 +10112,16 @@
         <v>44859</v>
       </c>
       <c r="B485" t="n">
-        <v>42.69810104370117</v>
+        <v>42.69809722900391</v>
       </c>
       <c r="C485" t="n">
-        <v>44.71937098158734</v>
+        <v>44.7193669863075</v>
       </c>
       <c r="D485" t="n">
-        <v>42.52402240539543</v>
+        <v>42.52401860625056</v>
       </c>
       <c r="E485" t="n">
-        <v>43.43310931590769</v>
+        <v>43.43310543554394</v>
       </c>
       <c r="F485" t="n">
         <v>3364870</v>
@@ -10232,16 +10232,16 @@
         <v>44868</v>
       </c>
       <c r="B491" t="n">
-        <v>46.30543899536133</v>
+        <v>46.30543518066406</v>
       </c>
       <c r="C491" t="n">
-        <v>46.43116266535413</v>
+        <v>46.4311588402996</v>
       </c>
       <c r="D491" t="n">
-        <v>44.51627889399545</v>
+        <v>44.51627522669133</v>
       </c>
       <c r="E491" t="n">
-        <v>44.98049109746535</v>
+        <v>44.98048739191887</v>
       </c>
       <c r="F491" t="n">
         <v>3262984</v>
@@ -10312,16 +10312,16 @@
         <v>44874</v>
       </c>
       <c r="B495" t="n">
-        <v>44.69035720825195</v>
+        <v>44.69035339355469</v>
       </c>
       <c r="C495" t="n">
-        <v>46.49886228228617</v>
+        <v>46.49885831321781</v>
       </c>
       <c r="D495" t="n">
-        <v>44.23581375342662</v>
+        <v>44.23580997752845</v>
       </c>
       <c r="E495" t="n">
-        <v>45.35766552501359</v>
+        <v>45.35766165335595</v>
       </c>
       <c r="F495" t="n">
         <v>4884014</v>
@@ -10332,16 +10332,16 @@
         <v>44875</v>
       </c>
       <c r="B496" t="n">
-        <v>42.05980682373047</v>
+        <v>42.0598030090332</v>
       </c>
       <c r="C496" t="n">
-        <v>44.68068514703247</v>
+        <v>44.68068109462947</v>
       </c>
       <c r="D496" t="n">
-        <v>41.6439458411077</v>
+        <v>41.64394206412777</v>
       </c>
       <c r="E496" t="n">
-        <v>43.65554705124352</v>
+        <v>43.65554309181744</v>
       </c>
       <c r="F496" t="n">
         <v>5453172</v>
@@ -10472,16 +10472,16 @@
         <v>44887</v>
       </c>
       <c r="B503" t="n">
-        <v>35.72520446777344</v>
+        <v>35.7252082824707</v>
       </c>
       <c r="C503" t="n">
-        <v>38.01726275125628</v>
+        <v>38.01726681069696</v>
       </c>
       <c r="D503" t="n">
-        <v>35.41572595102293</v>
+        <v>35.41572973267442</v>
       </c>
       <c r="E503" t="n">
-        <v>37.37896822915095</v>
+        <v>37.37897222043525</v>
       </c>
       <c r="F503" t="n">
         <v>4879239</v>
@@ -10492,16 +10492,16 @@
         <v>44888</v>
       </c>
       <c r="B504" t="n">
-        <v>34.29388046264648</v>
+        <v>34.29387664794922</v>
       </c>
       <c r="C504" t="n">
-        <v>35.59948346985989</v>
+        <v>35.59947950993321</v>
       </c>
       <c r="D504" t="n">
-        <v>33.84900571743197</v>
+        <v>33.84900195222058</v>
       </c>
       <c r="E504" t="n">
-        <v>35.37704984482862</v>
+        <v>35.37704590964446</v>
       </c>
       <c r="F504" t="n">
         <v>5644348</v>
@@ -10532,16 +10532,16 @@
         <v>44890</v>
       </c>
       <c r="B506" t="n">
-        <v>34.23584747314453</v>
+        <v>34.2358512878418</v>
       </c>
       <c r="C506" t="n">
-        <v>36.49889581830917</v>
+        <v>36.49889988516448</v>
       </c>
       <c r="D506" t="n">
-        <v>34.11012381427162</v>
+        <v>34.11012761496025</v>
       </c>
       <c r="E506" t="n">
-        <v>36.17007605925269</v>
+        <v>36.17008008946956</v>
       </c>
       <c r="F506" t="n">
         <v>4398253</v>
@@ -10552,16 +10552,16 @@
         <v>44893</v>
       </c>
       <c r="B507" t="n">
-        <v>33.64590835571289</v>
+        <v>33.64591217041016</v>
       </c>
       <c r="C507" t="n">
-        <v>34.11012427192836</v>
+        <v>34.11012813925738</v>
       </c>
       <c r="D507" t="n">
-        <v>32.92057262619048</v>
+        <v>32.92057635865081</v>
       </c>
       <c r="E507" t="n">
-        <v>33.36544355803103</v>
+        <v>33.36544734092983</v>
       </c>
       <c r="F507" t="n">
         <v>4077054</v>
@@ -10652,16 +10652,16 @@
         <v>44900</v>
       </c>
       <c r="B512" t="n">
-        <v>34.04242324829102</v>
+        <v>34.04242706298828</v>
       </c>
       <c r="C512" t="n">
-        <v>35.87994187083461</v>
+        <v>35.879945891439</v>
       </c>
       <c r="D512" t="n">
-        <v>33.77163095133564</v>
+        <v>33.77163473568869</v>
       </c>
       <c r="E512" t="n">
-        <v>35.57046335392476</v>
+        <v>35.57046733984986</v>
       </c>
       <c r="F512" t="n">
         <v>5158181</v>
@@ -10732,16 +10732,16 @@
         <v>44904</v>
       </c>
       <c r="B516" t="n">
-        <v>31.69234085083008</v>
+        <v>31.69233894348145</v>
       </c>
       <c r="C516" t="n">
-        <v>32.74649642178647</v>
+        <v>32.74649445099531</v>
       </c>
       <c r="D516" t="n">
-        <v>31.4892447329005</v>
+        <v>31.48924283777486</v>
       </c>
       <c r="E516" t="n">
-        <v>32.22425300897184</v>
+        <v>32.22425106961099</v>
       </c>
       <c r="F516" t="n">
         <v>2885712</v>
@@ -10752,16 +10752,16 @@
         <v>44907</v>
       </c>
       <c r="B517" t="n">
-        <v>32.23392486572266</v>
+        <v>32.23392105102539</v>
       </c>
       <c r="C517" t="n">
-        <v>32.41767599422015</v>
+        <v>32.41767215777701</v>
       </c>
       <c r="D517" t="n">
-        <v>31.06371439332975</v>
+        <v>31.06371071712008</v>
       </c>
       <c r="E517" t="n">
-        <v>31.59562654097396</v>
+        <v>31.59562280181559</v>
       </c>
       <c r="F517" t="n">
         <v>3445728</v>
@@ -10772,16 +10772,16 @@
         <v>44908</v>
       </c>
       <c r="B518" t="n">
-        <v>32.5240592956543</v>
+        <v>32.52405548095703</v>
       </c>
       <c r="C518" t="n">
-        <v>33.41380497900949</v>
+        <v>33.41380105995531</v>
       </c>
       <c r="D518" t="n">
-        <v>31.98247464077933</v>
+        <v>31.9824708896037</v>
       </c>
       <c r="E518" t="n">
-        <v>32.39833187733107</v>
+        <v>32.39832807738018</v>
       </c>
       <c r="F518" t="n">
         <v>3369136</v>
@@ -10872,16 +10872,16 @@
         <v>44915</v>
       </c>
       <c r="B523" t="n">
-        <v>31.63431167602539</v>
+        <v>31.63431358337402</v>
       </c>
       <c r="C523" t="n">
-        <v>31.83740403538475</v>
+        <v>31.83740595497857</v>
       </c>
       <c r="D523" t="n">
-        <v>30.62851300266902</v>
+        <v>30.62851484937437</v>
       </c>
       <c r="E523" t="n">
-        <v>30.76390915810044</v>
+        <v>30.76391101296931</v>
       </c>
       <c r="F523" t="n">
         <v>3472546</v>
@@ -10892,16 +10892,16 @@
         <v>44916</v>
       </c>
       <c r="B524" t="n">
-        <v>32.19523620605469</v>
+        <v>32.19524002075195</v>
       </c>
       <c r="C524" t="n">
-        <v>32.50471472608491</v>
+        <v>32.50471857745117</v>
       </c>
       <c r="D524" t="n">
-        <v>31.22812192077017</v>
+        <v>31.22812562087756</v>
       </c>
       <c r="E524" t="n">
-        <v>32.34997359228213</v>
+        <v>32.34997742531367</v>
       </c>
       <c r="F524" t="n">
         <v>3938295</v>
@@ -10912,16 +10912,16 @@
         <v>44917</v>
       </c>
       <c r="B525" t="n">
-        <v>32.01148986816406</v>
+        <v>32.0114860534668</v>
       </c>
       <c r="C525" t="n">
-        <v>32.78518066232546</v>
+        <v>32.78517675543017</v>
       </c>
       <c r="D525" t="n">
-        <v>31.53760514678948</v>
+        <v>31.5376013885634</v>
       </c>
       <c r="E525" t="n">
-        <v>32.41767837830338</v>
+        <v>32.41767451520204</v>
       </c>
       <c r="F525" t="n">
         <v>3822391</v>
@@ -10932,16 +10932,16 @@
         <v>44918</v>
       </c>
       <c r="B526" t="n">
-        <v>34.68072128295898</v>
+        <v>34.68072509765625</v>
       </c>
       <c r="C526" t="n">
-        <v>34.88381363050969</v>
+        <v>34.88381746754605</v>
       </c>
       <c r="D526" t="n">
-        <v>32.68846528926745</v>
+        <v>32.68846888482701</v>
       </c>
       <c r="E526" t="n">
-        <v>33.17202242375276</v>
+        <v>33.17202607250107</v>
       </c>
       <c r="F526" t="n">
         <v>6955860</v>
@@ -11012,16 +11012,16 @@
         <v>44924</v>
       </c>
       <c r="B530" t="n">
-        <v>36.50856781005859</v>
+        <v>36.50856399536133</v>
       </c>
       <c r="C530" t="n">
-        <v>37.23390359436439</v>
+        <v>37.23389970387844</v>
       </c>
       <c r="D530" t="n">
-        <v>35.61882587917678</v>
+        <v>35.61882215744662</v>
       </c>
       <c r="E530" t="n">
-        <v>35.87994571220566</v>
+        <v>35.87994196319169</v>
       </c>
       <c r="F530" t="n">
         <v>4887264</v>
@@ -11032,16 +11032,16 @@
         <v>44928</v>
       </c>
       <c r="B531" t="n">
-        <v>35.2126350402832</v>
+        <v>35.21263885498047</v>
       </c>
       <c r="C531" t="n">
-        <v>36.68264774905137</v>
+        <v>36.68265172299981</v>
       </c>
       <c r="D531" t="n">
-        <v>34.78710534150101</v>
+        <v>34.78710911009928</v>
       </c>
       <c r="E531" t="n">
-        <v>36.01533947163607</v>
+        <v>36.01534337329287</v>
       </c>
       <c r="F531" t="n">
         <v>2924313</v>
@@ -11152,16 +11152,16 @@
         <v>44936</v>
       </c>
       <c r="B537" t="n">
-        <v>37.79483032226562</v>
+        <v>37.79483413696289</v>
       </c>
       <c r="C537" t="n">
-        <v>38.07529137196207</v>
+        <v>38.07529521496675</v>
       </c>
       <c r="D537" t="n">
-        <v>36.49889625466188</v>
+        <v>36.49889993855829</v>
       </c>
       <c r="E537" t="n">
-        <v>37.0985045751726</v>
+        <v>37.09850831958851</v>
       </c>
       <c r="F537" t="n">
         <v>3183751</v>
@@ -11192,16 +11192,16 @@
         <v>44938</v>
       </c>
       <c r="B539" t="n">
-        <v>43.42343902587891</v>
+        <v>43.42343521118164</v>
       </c>
       <c r="C539" t="n">
-        <v>44.7290457434945</v>
+        <v>44.72904181410123</v>
       </c>
       <c r="D539" t="n">
-        <v>43.19133291383822</v>
+        <v>43.19132911953119</v>
       </c>
       <c r="E539" t="n">
-        <v>43.40409778676949</v>
+        <v>43.40409397377132</v>
       </c>
       <c r="F539" t="n">
         <v>7341055</v>
@@ -11212,16 +11212,16 @@
         <v>44939</v>
       </c>
       <c r="B540" t="n">
-        <v>42.75612640380859</v>
+        <v>42.75613021850586</v>
       </c>
       <c r="C540" t="n">
-        <v>43.50080338468374</v>
+        <v>43.50080726582102</v>
       </c>
       <c r="D540" t="n">
-        <v>42.35961043000531</v>
+        <v>42.35961420932546</v>
       </c>
       <c r="E540" t="n">
-        <v>43.42343468839838</v>
+        <v>43.42343856263282</v>
       </c>
       <c r="F540" t="n">
         <v>4249336</v>
@@ -11272,16 +11272,16 @@
         <v>44944</v>
       </c>
       <c r="B543" t="n">
-        <v>44.53561782836914</v>
+        <v>44.53562164306641</v>
       </c>
       <c r="C543" t="n">
-        <v>45.241612337541</v>
+        <v>45.24161621271021</v>
       </c>
       <c r="D543" t="n">
-        <v>43.220342491427</v>
+        <v>43.22034619346439</v>
       </c>
       <c r="E543" t="n">
-        <v>43.42343485149192</v>
+        <v>43.42343857092518</v>
       </c>
       <c r="F543" t="n">
         <v>6730959</v>
@@ -11332,16 +11332,16 @@
         <v>44949</v>
       </c>
       <c r="B546" t="n">
-        <v>46.45050430297852</v>
+        <v>46.45050811767578</v>
       </c>
       <c r="C546" t="n">
-        <v>48.53947031074529</v>
+        <v>48.53947429699662</v>
       </c>
       <c r="D546" t="n">
-        <v>45.88957845353607</v>
+        <v>45.88958222216792</v>
       </c>
       <c r="E546" t="n">
-        <v>47.67873842593739</v>
+        <v>47.67874234150205</v>
       </c>
       <c r="F546" t="n">
         <v>5971946</v>
@@ -11392,16 +11392,16 @@
         <v>44952</v>
       </c>
       <c r="B549" t="n">
-        <v>45.26095199584961</v>
+        <v>45.26095581054688</v>
       </c>
       <c r="C549" t="n">
-        <v>46.77931963988798</v>
+        <v>46.77932358255676</v>
       </c>
       <c r="D549" t="n">
-        <v>45.24161075927422</v>
+        <v>45.24161457234137</v>
       </c>
       <c r="E549" t="n">
-        <v>45.92826025966649</v>
+        <v>45.92826413060603</v>
       </c>
       <c r="F549" t="n">
         <v>3327082</v>
@@ -11412,16 +11412,16 @@
         <v>44953</v>
       </c>
       <c r="B550" t="n">
-        <v>44.50660705566406</v>
+        <v>44.5066032409668</v>
       </c>
       <c r="C550" t="n">
-        <v>46.34412590104548</v>
+        <v>46.34412192885299</v>
       </c>
       <c r="D550" t="n">
-        <v>44.16811476963287</v>
+        <v>44.16811098394805</v>
       </c>
       <c r="E550" t="n">
-        <v>46.20872973614816</v>
+        <v>46.20872577556058</v>
       </c>
       <c r="F550" t="n">
         <v>4035914</v>
@@ -11432,16 +11432,16 @@
         <v>44956</v>
       </c>
       <c r="B551" t="n">
-        <v>43.79093933105469</v>
+        <v>43.79094314575195</v>
       </c>
       <c r="C551" t="n">
-        <v>44.43890261092821</v>
+        <v>44.43890648207057</v>
       </c>
       <c r="D551" t="n">
-        <v>43.13329981152729</v>
+        <v>43.13330356893655</v>
       </c>
       <c r="E551" t="n">
-        <v>44.3131789517849</v>
+        <v>44.31318281197527</v>
       </c>
       <c r="F551" t="n">
         <v>3870439</v>
@@ -11572,16 +11572,16 @@
         <v>44965</v>
       </c>
       <c r="B558" t="n">
-        <v>43.12363052368164</v>
+        <v>43.12362670898438</v>
       </c>
       <c r="C558" t="n">
-        <v>43.13330301647882</v>
+        <v>43.13329920092593</v>
       </c>
       <c r="D558" t="n">
-        <v>42.08881994983436</v>
+        <v>42.08881622667597</v>
       </c>
       <c r="E558" t="n">
-        <v>42.57237713333137</v>
+        <v>42.57237336739773</v>
       </c>
       <c r="F558" t="n">
         <v>2757212</v>
@@ -11672,16 +11672,16 @@
         <v>44972</v>
       </c>
       <c r="B563" t="n">
-        <v>40.0482063293457</v>
+        <v>40.04821014404297</v>
       </c>
       <c r="C563" t="n">
-        <v>40.52209099098364</v>
+        <v>40.52209485081966</v>
       </c>
       <c r="D563" t="n">
-        <v>38.90700964744255</v>
+        <v>38.90701335343782</v>
       </c>
       <c r="E563" t="n">
-        <v>38.92635463185054</v>
+        <v>38.92635833968847</v>
       </c>
       <c r="F563" t="n">
         <v>3495706</v>
@@ -11752,16 +11752,16 @@
         <v>44980</v>
       </c>
       <c r="B567" t="n">
-        <v>38.00759506225586</v>
+        <v>38.00759887695312</v>
       </c>
       <c r="C567" t="n">
-        <v>39.07141929530241</v>
+        <v>39.07142321677222</v>
       </c>
       <c r="D567" t="n">
-        <v>37.7368027579212</v>
+        <v>37.73680654543994</v>
       </c>
       <c r="E567" t="n">
-        <v>37.95924009667655</v>
+        <v>37.95924390652058</v>
       </c>
       <c r="F567" t="n">
         <v>3548732</v>
@@ -11812,16 +11812,16 @@
         <v>44985</v>
       </c>
       <c r="B570" t="n">
-        <v>35.2126350402832</v>
+        <v>35.21263885498047</v>
       </c>
       <c r="C570" t="n">
-        <v>38.49115271645117</v>
+        <v>38.49115688632073</v>
       </c>
       <c r="D570" t="n">
-        <v>35.2126350402832</v>
+        <v>35.21263885498047</v>
       </c>
       <c r="E570" t="n">
-        <v>37.13719117707558</v>
+        <v>37.13719520026616</v>
       </c>
       <c r="F570" t="n">
         <v>11036876</v>
@@ -11832,16 +11832,16 @@
         <v>44986</v>
       </c>
       <c r="B571" t="n">
-        <v>31.52792930603027</v>
+        <v>31.52793121337891</v>
       </c>
       <c r="C571" t="n">
-        <v>35.21263549119504</v>
+        <v>35.21263762145776</v>
       </c>
       <c r="D571" t="n">
-        <v>29.89350481936535</v>
+        <v>29.89350662783602</v>
       </c>
       <c r="E571" t="n">
-        <v>35.10625306513723</v>
+        <v>35.10625518896411</v>
       </c>
       <c r="F571" t="n">
         <v>24633899</v>
@@ -11872,16 +11872,16 @@
         <v>44988</v>
       </c>
       <c r="B573" t="n">
-        <v>31.74069404602051</v>
+        <v>31.74069595336914</v>
       </c>
       <c r="C573" t="n">
-        <v>31.93411766023568</v>
+        <v>31.93411957920744</v>
       </c>
       <c r="D573" t="n">
-        <v>30.40607560502645</v>
+        <v>30.40607743217574</v>
       </c>
       <c r="E573" t="n">
-        <v>30.47377368262298</v>
+        <v>30.47377551384036</v>
       </c>
       <c r="F573" t="n">
         <v>7573675</v>
@@ -11892,16 +11892,16 @@
         <v>44991</v>
       </c>
       <c r="B574" t="n">
-        <v>31.86641883850098</v>
+        <v>31.86642074584961</v>
       </c>
       <c r="C574" t="n">
-        <v>32.34997601739302</v>
+        <v>32.34997795368473</v>
       </c>
       <c r="D574" t="n">
-        <v>30.94766132287878</v>
+        <v>30.94766317523564</v>
       </c>
       <c r="E574" t="n">
-        <v>31.74069517121325</v>
+        <v>31.74069707103675</v>
       </c>
       <c r="F574" t="n">
         <v>5963007</v>
@@ -11992,16 +11992,16 @@
         <v>44998</v>
       </c>
       <c r="B579" t="n">
-        <v>26.4505786895752</v>
+        <v>26.45058059692383</v>
       </c>
       <c r="C579" t="n">
-        <v>27.32098119587531</v>
+        <v>27.32098316598858</v>
       </c>
       <c r="D579" t="n">
-        <v>25.76392542920967</v>
+        <v>25.76392728704381</v>
       </c>
       <c r="E579" t="n">
-        <v>26.59564546166059</v>
+        <v>26.59564737946998</v>
       </c>
       <c r="F579" t="n">
         <v>13860726</v>
@@ -12032,16 +12032,16 @@
         <v>45000</v>
       </c>
       <c r="B581" t="n">
-        <v>26.28617095947266</v>
+        <v>26.28616905212402</v>
       </c>
       <c r="C581" t="n">
-        <v>26.82775374453002</v>
+        <v>26.82775179788365</v>
       </c>
       <c r="D581" t="n">
-        <v>25.62853324821252</v>
+        <v>25.62853138858268</v>
       </c>
       <c r="E581" t="n">
-        <v>26.58597514665809</v>
+        <v>26.58597321755539</v>
       </c>
       <c r="F581" t="n">
         <v>12174787</v>
@@ -12072,16 +12072,16 @@
         <v>45002</v>
       </c>
       <c r="B583" t="n">
-        <v>30.70588111877441</v>
+        <v>30.70588302612305</v>
       </c>
       <c r="C583" t="n">
-        <v>30.8896322374788</v>
+        <v>30.88963415624145</v>
       </c>
       <c r="D583" t="n">
-        <v>27.73684012155175</v>
+        <v>27.73684184447329</v>
       </c>
       <c r="E583" t="n">
-        <v>30.45443004984579</v>
+        <v>30.45443194157511</v>
       </c>
       <c r="F583" t="n">
         <v>23193684</v>
@@ -12092,16 +12092,16 @@
         <v>45005</v>
       </c>
       <c r="B584" t="n">
-        <v>29.79679679870605</v>
+        <v>29.79679489135742</v>
       </c>
       <c r="C584" t="n">
-        <v>31.20878403151084</v>
+        <v>31.20878203377826</v>
       </c>
       <c r="D584" t="n">
-        <v>29.32291022343201</v>
+        <v>29.32290834641774</v>
       </c>
       <c r="E584" t="n">
-        <v>30.70588372476053</v>
+        <v>30.70588175921954</v>
       </c>
       <c r="F584" t="n">
         <v>7729094</v>
@@ -12252,16 +12252,16 @@
         <v>45015</v>
       </c>
       <c r="B592" t="n">
-        <v>29.38093566894531</v>
+        <v>29.38093376159668</v>
       </c>
       <c r="C592" t="n">
-        <v>30.51245994826028</v>
+        <v>30.51245796745546</v>
       </c>
       <c r="D592" t="n">
-        <v>29.27455323657771</v>
+        <v>29.2745513361352</v>
       </c>
       <c r="E592" t="n">
-        <v>29.95153405508782</v>
+        <v>29.95153211069714</v>
       </c>
       <c r="F592" t="n">
         <v>5560645</v>
@@ -12312,16 +12312,16 @@
         <v>45020</v>
       </c>
       <c r="B595" t="n">
-        <v>27.92059326171875</v>
+        <v>27.92059135437012</v>
       </c>
       <c r="C595" t="n">
-        <v>29.70975523383049</v>
+        <v>29.70975320425825</v>
       </c>
       <c r="D595" t="n">
-        <v>27.91092264260987</v>
+        <v>27.91092073592187</v>
       </c>
       <c r="E595" t="n">
-        <v>29.57435907115471</v>
+        <v>29.57435705083184</v>
       </c>
       <c r="F595" t="n">
         <v>7552242</v>
@@ -12332,16 +12332,16 @@
         <v>45021</v>
       </c>
       <c r="B596" t="n">
-        <v>26.76972579956055</v>
+        <v>26.76972770690918</v>
       </c>
       <c r="C596" t="n">
-        <v>27.85289314814766</v>
+        <v>27.8528951326722</v>
       </c>
       <c r="D596" t="n">
-        <v>26.23781180677641</v>
+        <v>26.23781367622606</v>
       </c>
       <c r="E596" t="n">
-        <v>27.65947141114338</v>
+        <v>27.65947338188658</v>
       </c>
       <c r="F596" t="n">
         <v>12382825</v>
@@ -12372,16 +12372,16 @@
         <v>45026</v>
       </c>
       <c r="B598" t="n">
-        <v>29.65172576904297</v>
+        <v>29.6517276763916</v>
       </c>
       <c r="C598" t="n">
-        <v>29.8354768886412</v>
+        <v>29.83547880780963</v>
       </c>
       <c r="D598" t="n">
-        <v>28.19138368313743</v>
+        <v>28.19138549654949</v>
       </c>
       <c r="E598" t="n">
-        <v>28.33645045512486</v>
+        <v>28.33645227786835</v>
       </c>
       <c r="F598" t="n">
         <v>8774363</v>
@@ -12552,16 +12552,16 @@
         <v>45040</v>
       </c>
       <c r="B607" t="n">
-        <v>26.96700286865234</v>
+        <v>26.96700477600098</v>
       </c>
       <c r="C607" t="n">
-        <v>27.07506608384296</v>
+        <v>27.07506799883479</v>
       </c>
       <c r="D607" t="n">
-        <v>26.23019953206389</v>
+        <v>26.23020138729918</v>
       </c>
       <c r="E607" t="n">
-        <v>26.86876204901633</v>
+        <v>26.86876394941649</v>
       </c>
       <c r="F607" t="n">
         <v>6680100</v>
@@ -12572,16 +12572,16 @@
         <v>45041</v>
       </c>
       <c r="B608" t="n">
-        <v>27.21260452270508</v>
+        <v>27.21260261535645</v>
       </c>
       <c r="C608" t="n">
-        <v>27.45820563979163</v>
+        <v>27.45820371522866</v>
       </c>
       <c r="D608" t="n">
-        <v>26.42667982375542</v>
+        <v>26.42667797149275</v>
       </c>
       <c r="E608" t="n">
-        <v>26.79999457104816</v>
+        <v>26.79999269261962</v>
       </c>
       <c r="F608" t="n">
         <v>5323000</v>
@@ -12612,16 +12612,16 @@
         <v>45043</v>
       </c>
       <c r="B610" t="n">
-        <v>29.90439224243164</v>
+        <v>29.90439414978027</v>
       </c>
       <c r="C610" t="n">
-        <v>30.267880842768</v>
+        <v>30.26788277330051</v>
       </c>
       <c r="D610" t="n">
-        <v>26.73122441728851</v>
+        <v>26.73122612224756</v>
       </c>
       <c r="E610" t="n">
-        <v>26.73122441728851</v>
+        <v>26.73122612224756</v>
       </c>
       <c r="F610" t="n">
         <v>20933600</v>
@@ -12672,16 +12672,16 @@
         <v>45049</v>
       </c>
       <c r="B613" t="n">
-        <v>29.14793968200684</v>
+        <v>29.14794158935547</v>
       </c>
       <c r="C613" t="n">
-        <v>29.61949336143113</v>
+        <v>29.61949529963673</v>
       </c>
       <c r="D613" t="n">
-        <v>28.33254407533193</v>
+        <v>28.33254592932366</v>
       </c>
       <c r="E613" t="n">
-        <v>29.26582903875679</v>
+        <v>29.26583095381972</v>
       </c>
       <c r="F613" t="n">
         <v>9250000</v>
@@ -12692,16 +12692,16 @@
         <v>45050</v>
       </c>
       <c r="B614" t="n">
-        <v>29.2756519317627</v>
+        <v>29.27565383911133</v>
       </c>
       <c r="C614" t="n">
-        <v>29.95351152857367</v>
+        <v>29.95351348008578</v>
       </c>
       <c r="D614" t="n">
-        <v>29.17741298555374</v>
+        <v>29.17741488650197</v>
       </c>
       <c r="E614" t="n">
-        <v>29.47213357175619</v>
+        <v>29.47213549190587</v>
       </c>
       <c r="F614" t="n">
         <v>6670900</v>
@@ -12792,16 +12792,16 @@
         <v>45057</v>
       </c>
       <c r="B619" t="n">
-        <v>31.66289520263672</v>
+        <v>31.66289710998535</v>
       </c>
       <c r="C619" t="n">
-        <v>31.81025737023202</v>
+        <v>31.81025928645763</v>
       </c>
       <c r="D619" t="n">
-        <v>31.10292496189554</v>
+        <v>31.10292683551199</v>
       </c>
       <c r="E619" t="n">
-        <v>31.71201467597662</v>
+        <v>31.71201658628417</v>
       </c>
       <c r="F619" t="n">
         <v>4858000</v>
@@ -12812,16 +12812,16 @@
         <v>45058</v>
       </c>
       <c r="B620" t="n">
-        <v>32.49794006347656</v>
+        <v>32.49794387817383</v>
       </c>
       <c r="C620" t="n">
-        <v>32.64529847816273</v>
+        <v>32.64530231015733</v>
       </c>
       <c r="D620" t="n">
-        <v>31.46641242279611</v>
+        <v>31.46641611640984</v>
       </c>
       <c r="E620" t="n">
-        <v>31.554828970638</v>
+        <v>31.55483267463029</v>
       </c>
       <c r="F620" t="n">
         <v>5317000</v>
@@ -12852,16 +12852,16 @@
         <v>45062</v>
       </c>
       <c r="B622" t="n">
-        <v>29.90439224243164</v>
+        <v>29.90439414978027</v>
       </c>
       <c r="C622" t="n">
-        <v>32.08532946581322</v>
+        <v>32.08533151226543</v>
       </c>
       <c r="D622" t="n">
-        <v>29.70791060120974</v>
+        <v>29.70791249602647</v>
       </c>
       <c r="E622" t="n">
-        <v>31.86919928571158</v>
+        <v>31.86920131837866</v>
       </c>
       <c r="F622" t="n">
         <v>13269700</v>
@@ -12912,16 +12912,16 @@
         <v>45065</v>
       </c>
       <c r="B625" t="n">
-        <v>32.49794006347656</v>
+        <v>32.49794387817383</v>
       </c>
       <c r="C625" t="n">
-        <v>34.87535696477425</v>
+        <v>34.87536105853923</v>
       </c>
       <c r="D625" t="n">
-        <v>31.04398009551434</v>
+        <v>31.0439837395418</v>
       </c>
       <c r="E625" t="n">
-        <v>31.8691980857257</v>
+        <v>31.86920182661951</v>
       </c>
       <c r="F625" t="n">
         <v>19443700</v>
@@ -12972,16 +12972,16 @@
         <v>45070</v>
       </c>
       <c r="B628" t="n">
-        <v>31.48606300354004</v>
+        <v>31.48606109619141</v>
       </c>
       <c r="C628" t="n">
-        <v>31.86920015318507</v>
+        <v>31.86919822262693</v>
       </c>
       <c r="D628" t="n">
-        <v>30.464363313224</v>
+        <v>30.46436146776744</v>
       </c>
       <c r="E628" t="n">
-        <v>31.04398210943912</v>
+        <v>31.04398022887067</v>
       </c>
       <c r="F628" t="n">
         <v>7685200</v>
@@ -13212,16 +13212,16 @@
         <v>45089</v>
       </c>
       <c r="B640" t="n">
-        <v>31.26010894775391</v>
+        <v>31.26011085510254</v>
       </c>
       <c r="C640" t="n">
-        <v>31.86919865058509</v>
+        <v>31.86920059509758</v>
       </c>
       <c r="D640" t="n">
-        <v>30.47418614610471</v>
+        <v>30.47418800549994</v>
       </c>
       <c r="E640" t="n">
-        <v>31.61377514538992</v>
+        <v>31.61377707431765</v>
       </c>
       <c r="F640" t="n">
         <v>7223600</v>
@@ -13252,16 +13252,16 @@
         <v>45091</v>
       </c>
       <c r="B642" t="n">
-        <v>31.1422233581543</v>
+        <v>31.14222145080566</v>
       </c>
       <c r="C642" t="n">
-        <v>31.71201601865814</v>
+        <v>31.71201407641177</v>
       </c>
       <c r="D642" t="n">
-        <v>30.57242882386257</v>
+        <v>30.5724269514118</v>
       </c>
       <c r="E642" t="n">
-        <v>31.33870313362062</v>
+        <v>31.33870121423831</v>
       </c>
       <c r="F642" t="n">
         <v>8288400</v>
@@ -13292,16 +13292,16 @@
         <v>45093</v>
       </c>
       <c r="B644" t="n">
-        <v>31.91832160949707</v>
+        <v>31.9183235168457</v>
       </c>
       <c r="C644" t="n">
-        <v>31.91832160949707</v>
+        <v>31.9183235168457</v>
       </c>
       <c r="D644" t="n">
-        <v>31.19134068168367</v>
+        <v>31.19134254558997</v>
       </c>
       <c r="E644" t="n">
-        <v>31.42711752024974</v>
+        <v>31.4271193982454</v>
       </c>
       <c r="F644" t="n">
         <v>5722800</v>
@@ -13332,16 +13332,16 @@
         <v>45097</v>
       </c>
       <c r="B646" t="n">
-        <v>32.16392135620117</v>
+        <v>32.16392517089844</v>
       </c>
       <c r="C646" t="n">
-        <v>32.29163122856222</v>
+        <v>32.2916350584061</v>
       </c>
       <c r="D646" t="n">
-        <v>31.48605992910253</v>
+        <v>31.48606366340425</v>
       </c>
       <c r="E646" t="n">
-        <v>32.12462428120915</v>
+        <v>32.12462809124572</v>
       </c>
       <c r="F646" t="n">
         <v>4954700</v>
@@ -13352,16 +13352,16 @@
         <v>45098</v>
       </c>
       <c r="B647" t="n">
-        <v>32.06568145751953</v>
+        <v>32.06567764282227</v>
       </c>
       <c r="C647" t="n">
-        <v>32.36040205044127</v>
+        <v>32.36039820068254</v>
       </c>
       <c r="D647" t="n">
-        <v>31.48606266749066</v>
+        <v>31.4860589217478</v>
       </c>
       <c r="E647" t="n">
-        <v>32.12462707513414</v>
+        <v>32.1246232534244</v>
       </c>
       <c r="F647" t="n">
         <v>4670300</v>
@@ -13412,16 +13412,16 @@
         <v>45103</v>
       </c>
       <c r="B650" t="n">
-        <v>30.53313064575195</v>
+        <v>30.53312873840332</v>
       </c>
       <c r="C650" t="n">
-        <v>30.83767550472773</v>
+        <v>30.83767357835474</v>
       </c>
       <c r="D650" t="n">
-        <v>30.30717806889212</v>
+        <v>30.30717617565832</v>
       </c>
       <c r="E650" t="n">
-        <v>30.58225011940398</v>
+        <v>30.58224820898695</v>
       </c>
       <c r="F650" t="n">
         <v>2874500</v>
@@ -13452,16 +13452,16 @@
         <v>45105</v>
       </c>
       <c r="B652" t="n">
-        <v>29.37389183044434</v>
+        <v>29.37389373779297</v>
       </c>
       <c r="C652" t="n">
-        <v>30.06157567506449</v>
+        <v>30.06157762706682</v>
       </c>
       <c r="D652" t="n">
-        <v>29.30512382073987</v>
+        <v>29.30512572362315</v>
       </c>
       <c r="E652" t="n">
-        <v>29.75703082903567</v>
+        <v>29.75703276126285</v>
       </c>
       <c r="F652" t="n">
         <v>4532500</v>
@@ -13532,16 +13532,16 @@
         <v>45111</v>
       </c>
       <c r="B656" t="n">
-        <v>29.80615234375</v>
+        <v>29.80615043640137</v>
       </c>
       <c r="C656" t="n">
-        <v>30.15981855937348</v>
+        <v>30.15981662939312</v>
       </c>
       <c r="D656" t="n">
-        <v>29.57037549126363</v>
+        <v>29.57037359900278</v>
       </c>
       <c r="E656" t="n">
-        <v>29.80615234375</v>
+        <v>29.80615043640137</v>
       </c>
       <c r="F656" t="n">
         <v>2514900</v>
@@ -13552,16 +13552,16 @@
         <v>45112</v>
       </c>
       <c r="B657" t="n">
-        <v>30.40542030334473</v>
+        <v>30.40541839599609</v>
       </c>
       <c r="C657" t="n">
-        <v>30.70996517647691</v>
+        <v>30.70996325002402</v>
       </c>
       <c r="D657" t="n">
-        <v>29.34442350856649</v>
+        <v>29.34442166777476</v>
       </c>
       <c r="E657" t="n">
-        <v>29.60967130192012</v>
+        <v>29.60966944448926</v>
       </c>
       <c r="F657" t="n">
         <v>5394800</v>
@@ -13612,16 +13612,16 @@
         <v>45117</v>
       </c>
       <c r="B660" t="n">
-        <v>31.07345390319824</v>
+        <v>31.07345199584961</v>
       </c>
       <c r="C660" t="n">
-        <v>31.93796904965617</v>
+        <v>31.93796708924193</v>
       </c>
       <c r="D660" t="n">
-        <v>30.84750131505205</v>
+        <v>30.84749942157282</v>
       </c>
       <c r="E660" t="n">
-        <v>31.56465803319331</v>
+        <v>31.56465609569361</v>
       </c>
       <c r="F660" t="n">
         <v>7339200</v>
@@ -13652,16 +13652,16 @@
         <v>45119</v>
       </c>
       <c r="B662" t="n">
-        <v>31.07345390319824</v>
+        <v>31.07345199584961</v>
       </c>
       <c r="C662" t="n">
-        <v>32.08533122554864</v>
+        <v>32.08532925608902</v>
       </c>
       <c r="D662" t="n">
-        <v>31.04398296705007</v>
+        <v>31.04398106151042</v>
       </c>
       <c r="E662" t="n">
-        <v>31.77096208138212</v>
+        <v>31.77096013121909</v>
       </c>
       <c r="F662" t="n">
         <v>4503800</v>
@@ -13732,16 +13732,16 @@
         <v>45125</v>
       </c>
       <c r="B666" t="n">
-        <v>32.91054916381836</v>
+        <v>32.91055297851562</v>
       </c>
       <c r="C666" t="n">
-        <v>33.03826279198419</v>
+        <v>33.03826662148488</v>
       </c>
       <c r="D666" t="n">
-        <v>32.0362098005708</v>
+        <v>32.03621351392245</v>
       </c>
       <c r="E666" t="n">
-        <v>32.18356821992315</v>
+        <v>32.18357195035527</v>
       </c>
       <c r="F666" t="n">
         <v>4775600</v>
@@ -13752,16 +13752,16 @@
         <v>45126</v>
       </c>
       <c r="B667" t="n">
-        <v>33.64735412597656</v>
+        <v>33.6473503112793</v>
       </c>
       <c r="C667" t="n">
-        <v>34.04031742501827</v>
+        <v>34.04031356576963</v>
       </c>
       <c r="D667" t="n">
-        <v>33.04808678134705</v>
+        <v>33.04808303459044</v>
       </c>
       <c r="E667" t="n">
-        <v>33.04808678134705</v>
+        <v>33.04808303459044</v>
       </c>
       <c r="F667" t="n">
         <v>7484200</v>
@@ -13772,16 +13772,16 @@
         <v>45127</v>
       </c>
       <c r="B668" t="n">
-        <v>33.92242431640625</v>
+        <v>33.92242813110352</v>
       </c>
       <c r="C668" t="n">
-        <v>34.11890595509385</v>
+        <v>34.11890979188617</v>
       </c>
       <c r="D668" t="n">
-        <v>33.64735227078894</v>
+        <v>33.64735605455338</v>
       </c>
       <c r="E668" t="n">
-        <v>33.91260192088087</v>
+        <v>33.91260573447357</v>
       </c>
       <c r="F668" t="n">
         <v>3587900</v>
@@ -13952,16 +13952,16 @@
         <v>45140</v>
       </c>
       <c r="B677" t="n">
-        <v>34.44309997558594</v>
+        <v>34.4431037902832</v>
       </c>
       <c r="C677" t="n">
-        <v>34.58063599342123</v>
+        <v>34.5806398233511</v>
       </c>
       <c r="D677" t="n">
-        <v>33.71611906300245</v>
+        <v>33.71612279718397</v>
       </c>
       <c r="E677" t="n">
-        <v>34.38415436183849</v>
+        <v>34.38415817000732</v>
       </c>
       <c r="F677" t="n">
         <v>3408800</v>
@@ -14012,16 +14012,16 @@
         <v>45145</v>
       </c>
       <c r="B680" t="n">
-        <v>35.68093109130859</v>
+        <v>35.68092727661133</v>
       </c>
       <c r="C680" t="n">
-        <v>36.15248480095344</v>
+        <v>36.15248093584172</v>
       </c>
       <c r="D680" t="n">
-        <v>35.09148989114647</v>
+        <v>35.09148613946717</v>
       </c>
       <c r="E680" t="n">
-        <v>36.05424585011833</v>
+        <v>36.05424199550948</v>
       </c>
       <c r="F680" t="n">
         <v>3820600</v>
@@ -14032,16 +14032,16 @@
         <v>45146</v>
       </c>
       <c r="B681" t="n">
-        <v>36.34896850585938</v>
+        <v>36.34896469116211</v>
       </c>
       <c r="C681" t="n">
-        <v>36.51597548123902</v>
+        <v>36.51597164901496</v>
       </c>
       <c r="D681" t="n">
-        <v>34.30556523426109</v>
+        <v>34.30556163401185</v>
       </c>
       <c r="E681" t="n">
-        <v>34.76729657396523</v>
+        <v>34.76729292525891</v>
       </c>
       <c r="F681" t="n">
         <v>5274900</v>
@@ -14172,16 +14172,16 @@
         <v>45155</v>
       </c>
       <c r="B688" t="n">
-        <v>31.26993560791016</v>
+        <v>31.26993370056152</v>
       </c>
       <c r="C688" t="n">
-        <v>31.74149119874277</v>
+        <v>31.74148926263102</v>
       </c>
       <c r="D688" t="n">
-        <v>30.96539073320894</v>
+        <v>30.9653888444364</v>
       </c>
       <c r="E688" t="n">
-        <v>31.4664153864515</v>
+        <v>31.46641346711834</v>
       </c>
       <c r="F688" t="n">
         <v>4529600</v>
@@ -14252,16 +14252,16 @@
         <v>45161</v>
       </c>
       <c r="B692" t="n">
-        <v>31.05380439758301</v>
+        <v>31.05380630493164</v>
       </c>
       <c r="C692" t="n">
-        <v>31.24045988874735</v>
+        <v>31.2404618075605</v>
       </c>
       <c r="D692" t="n">
-        <v>30.68048966767887</v>
+        <v>30.68049155209822</v>
       </c>
       <c r="E692" t="n">
-        <v>31.09309960011686</v>
+        <v>31.09310150987904</v>
       </c>
       <c r="F692" t="n">
         <v>4847400</v>
@@ -14272,16 +14272,16 @@
         <v>45162</v>
       </c>
       <c r="B693" t="n">
-        <v>30.91626739501953</v>
+        <v>30.91626930236816</v>
       </c>
       <c r="C693" t="n">
-        <v>31.30923067440671</v>
+        <v>31.30923260599883</v>
       </c>
       <c r="D693" t="n">
-        <v>30.56260306687397</v>
+        <v>30.56260495240363</v>
       </c>
       <c r="E693" t="n">
-        <v>31.05380529232016</v>
+        <v>31.05380720815405</v>
       </c>
       <c r="F693" t="n">
         <v>3471700</v>
@@ -14332,16 +14332,16 @@
         <v>45167</v>
       </c>
       <c r="B696" t="n">
-        <v>31.29940605163574</v>
+        <v>31.29940795898438</v>
       </c>
       <c r="C696" t="n">
-        <v>31.55482955705047</v>
+        <v>31.55483147996431</v>
       </c>
       <c r="D696" t="n">
-        <v>30.63137073276579</v>
+        <v>30.63137259940515</v>
       </c>
       <c r="E696" t="n">
-        <v>31.06362921093831</v>
+        <v>31.06363110391898</v>
       </c>
       <c r="F696" t="n">
         <v>3743200</v>
@@ -14352,16 +14352,16 @@
         <v>45168</v>
       </c>
       <c r="B697" t="n">
-        <v>31.63342475891113</v>
+        <v>31.6334228515625</v>
       </c>
       <c r="C697" t="n">
-        <v>31.70219277216898</v>
+        <v>31.70219086067396</v>
       </c>
       <c r="D697" t="n">
-        <v>30.96538941791287</v>
+        <v>30.96538755084366</v>
       </c>
       <c r="E697" t="n">
-        <v>31.49588873239543</v>
+        <v>31.49588683333958</v>
       </c>
       <c r="F697" t="n">
         <v>3276100</v>
@@ -14412,16 +14412,16 @@
         <v>45173</v>
       </c>
       <c r="B700" t="n">
-        <v>32.27198791503906</v>
+        <v>32.2719841003418</v>
       </c>
       <c r="C700" t="n">
-        <v>32.55688613348561</v>
+        <v>32.55688228511206</v>
       </c>
       <c r="D700" t="n">
-        <v>32.06568385929886</v>
+        <v>32.06568006898767</v>
       </c>
       <c r="E700" t="n">
-        <v>32.22286843713558</v>
+        <v>32.22286462824446</v>
       </c>
       <c r="F700" t="n">
         <v>2652900</v>
@@ -14432,16 +14432,16 @@
         <v>45174</v>
       </c>
       <c r="B701" t="n">
-        <v>32.63547897338867</v>
+        <v>32.63547515869141</v>
       </c>
       <c r="C701" t="n">
-        <v>32.93019957643972</v>
+        <v>32.93019572729314</v>
       </c>
       <c r="D701" t="n">
-        <v>32.07550870331895</v>
+        <v>32.07550495407551</v>
       </c>
       <c r="E701" t="n">
-        <v>32.27198660696912</v>
+        <v>32.27198283475976</v>
       </c>
       <c r="F701" t="n">
         <v>6036900</v>
@@ -14452,16 +14452,16 @@
         <v>45175</v>
       </c>
       <c r="B702" t="n">
-        <v>32.00673675537109</v>
+        <v>32.00674057006836</v>
       </c>
       <c r="C702" t="n">
-        <v>32.71406536628031</v>
+        <v>32.71406926527997</v>
       </c>
       <c r="D702" t="n">
-        <v>31.928142605506</v>
+        <v>31.92814641083608</v>
       </c>
       <c r="E702" t="n">
-        <v>32.65512350145682</v>
+        <v>32.65512739343153</v>
       </c>
       <c r="F702" t="n">
         <v>4505300</v>
@@ -14512,16 +14512,16 @@
         <v>45181</v>
       </c>
       <c r="B705" t="n">
-        <v>32.33092880249023</v>
+        <v>32.3309326171875</v>
       </c>
       <c r="C705" t="n">
-        <v>32.64529791212711</v>
+        <v>32.6453017639165</v>
       </c>
       <c r="D705" t="n">
-        <v>31.76113619661418</v>
+        <v>31.76113994408213</v>
       </c>
       <c r="E705" t="n">
-        <v>31.97726261725491</v>
+        <v>31.97726639022342</v>
       </c>
       <c r="F705" t="n">
         <v>3620500</v>
@@ -14532,16 +14532,16 @@
         <v>45182</v>
       </c>
       <c r="B706" t="n">
-        <v>31.63342475891113</v>
+        <v>31.6334228515625</v>
       </c>
       <c r="C706" t="n">
-        <v>32.1148008517161</v>
+        <v>32.11479891534272</v>
       </c>
       <c r="D706" t="n">
-        <v>31.44676551071783</v>
+        <v>31.44676361462388</v>
       </c>
       <c r="E706" t="n">
-        <v>31.60395007638945</v>
+        <v>31.60394817081799</v>
       </c>
       <c r="F706" t="n">
         <v>7302700</v>
@@ -14552,16 +14552,16 @@
         <v>45183</v>
       </c>
       <c r="B707" t="n">
-        <v>32.31128311157227</v>
+        <v>32.311279296875</v>
       </c>
       <c r="C707" t="n">
-        <v>32.31128311157227</v>
+        <v>32.311279296875</v>
       </c>
       <c r="D707" t="n">
-        <v>31.74149045549294</v>
+        <v>31.74148670806588</v>
       </c>
       <c r="E707" t="n">
-        <v>31.83972940556933</v>
+        <v>31.83972564654409</v>
       </c>
       <c r="F707" t="n">
         <v>4362300</v>
@@ -14592,16 +14592,16 @@
         <v>45187</v>
       </c>
       <c r="B709" t="n">
-        <v>31.98709106445312</v>
+        <v>31.98709297180176</v>
       </c>
       <c r="C709" t="n">
-        <v>32.7140682775227</v>
+        <v>32.71407022822005</v>
       </c>
       <c r="D709" t="n">
-        <v>31.75131234145109</v>
+        <v>31.75131423474054</v>
       </c>
       <c r="E709" t="n">
-        <v>32.5568837113799</v>
+        <v>32.55688565270453</v>
       </c>
       <c r="F709" t="n">
         <v>5099000</v>
@@ -14692,16 +14692,16 @@
         <v>45194</v>
       </c>
       <c r="B714" t="n">
-        <v>30.95556449890137</v>
+        <v>30.95556640625</v>
       </c>
       <c r="C714" t="n">
-        <v>31.20116561183414</v>
+        <v>31.20116753431566</v>
       </c>
       <c r="D714" t="n">
-        <v>29.99280858591396</v>
+        <v>29.99281043394172</v>
       </c>
       <c r="E714" t="n">
-        <v>30.45453800366397</v>
+        <v>30.45453988014151</v>
       </c>
       <c r="F714" t="n">
         <v>6350700</v>
@@ -14712,16 +14712,16 @@
         <v>45195</v>
       </c>
       <c r="B715" t="n">
-        <v>30.32682609558105</v>
+        <v>30.32682800292969</v>
       </c>
       <c r="C715" t="n">
-        <v>30.83767498381136</v>
+        <v>30.83767692328888</v>
       </c>
       <c r="D715" t="n">
-        <v>30.19911246818264</v>
+        <v>30.19911436749897</v>
       </c>
       <c r="E715" t="n">
-        <v>30.75908270302303</v>
+        <v>30.75908463755763</v>
       </c>
       <c r="F715" t="n">
         <v>3433500</v>
@@ -14732,16 +14732,16 @@
         <v>45196</v>
       </c>
       <c r="B716" t="n">
-        <v>30.86714935302734</v>
+        <v>30.86714744567871</v>
       </c>
       <c r="C716" t="n">
-        <v>31.0734533978611</v>
+        <v>31.07345147776449</v>
       </c>
       <c r="D716" t="n">
-        <v>30.42506658011519</v>
+        <v>30.42506470008381</v>
       </c>
       <c r="E716" t="n">
-        <v>30.65102103837466</v>
+        <v>30.65101914438107</v>
       </c>
       <c r="F716" t="n">
         <v>4307600</v>
@@ -14752,16 +14752,16 @@
         <v>45197</v>
       </c>
       <c r="B717" t="n">
-        <v>30.58224868774414</v>
+        <v>30.58225059509277</v>
       </c>
       <c r="C717" t="n">
-        <v>31.21098878902595</v>
+        <v>31.21099073558775</v>
       </c>
       <c r="D717" t="n">
-        <v>30.41523986184255</v>
+        <v>30.41524175877521</v>
       </c>
       <c r="E717" t="n">
-        <v>30.82784979208249</v>
+        <v>30.82785171474873</v>
       </c>
       <c r="F717" t="n">
         <v>4298000</v>
@@ -14772,16 +14772,16 @@
         <v>45198</v>
       </c>
       <c r="B718" t="n">
-        <v>31.02433395385742</v>
+        <v>31.02433204650879</v>
       </c>
       <c r="C718" t="n">
-        <v>31.60395088345571</v>
+        <v>31.60394894047274</v>
       </c>
       <c r="D718" t="n">
-        <v>30.47418795995777</v>
+        <v>30.47418608643163</v>
       </c>
       <c r="E718" t="n">
-        <v>30.86714938417181</v>
+        <v>30.86714748648674</v>
       </c>
       <c r="F718" t="n">
         <v>5846000</v>
@@ -14852,16 +14852,16 @@
         <v>45204</v>
       </c>
       <c r="B722" t="n">
-        <v>28.03782272338867</v>
+        <v>28.0378246307373</v>
       </c>
       <c r="C722" t="n">
-        <v>28.78444842505877</v>
+        <v>28.78445038319864</v>
       </c>
       <c r="D722" t="n">
-        <v>27.72345173862667</v>
+        <v>27.72345362458937</v>
       </c>
       <c r="E722" t="n">
-        <v>28.62726386957162</v>
+        <v>28.62726581701858</v>
       </c>
       <c r="F722" t="n">
         <v>8409300</v>
@@ -14912,16 +14912,16 @@
         <v>45209</v>
       </c>
       <c r="B725" t="n">
-        <v>30.27770614624023</v>
+        <v>30.2777042388916</v>
       </c>
       <c r="C725" t="n">
-        <v>30.40541977953243</v>
+        <v>30.40541786413846</v>
       </c>
       <c r="D725" t="n">
-        <v>29.43283768343539</v>
+        <v>29.43283582930937</v>
       </c>
       <c r="E725" t="n">
-        <v>29.75703296465965</v>
+        <v>29.7570310901109</v>
       </c>
       <c r="F725" t="n">
         <v>7018100</v>
@@ -14972,16 +14972,16 @@
         <v>45215</v>
       </c>
       <c r="B728" t="n">
-        <v>31.67271995544434</v>
+        <v>31.67272186279297</v>
       </c>
       <c r="C728" t="n">
-        <v>32.01656000130495</v>
+        <v>32.01656192935982</v>
       </c>
       <c r="D728" t="n">
-        <v>31.32887616200829</v>
+        <v>31.32887804865046</v>
       </c>
       <c r="E728" t="n">
-        <v>31.91832105893775</v>
+        <v>31.91832298107662</v>
       </c>
       <c r="F728" t="n">
         <v>3741500</v>
@@ -15012,16 +15012,16 @@
         <v>45217</v>
       </c>
       <c r="B730" t="n">
-        <v>32.06568145751953</v>
+        <v>32.06567764282227</v>
       </c>
       <c r="C730" t="n">
-        <v>33.06773447151397</v>
+        <v>33.06773053760736</v>
       </c>
       <c r="D730" t="n">
-        <v>31.63342483773936</v>
+        <v>31.63342107446555</v>
       </c>
       <c r="E730" t="n">
-        <v>32.52741275989484</v>
+        <v>32.52740889026767</v>
       </c>
       <c r="F730" t="n">
         <v>7439800</v>
@@ -15132,16 +15132,16 @@
         <v>45225</v>
       </c>
       <c r="B736" t="n">
-        <v>31.98709106445312</v>
+        <v>31.98709297180176</v>
       </c>
       <c r="C736" t="n">
-        <v>32.12462709138111</v>
+        <v>32.12462900693085</v>
       </c>
       <c r="D736" t="n">
-        <v>31.19134209034388</v>
+        <v>31.19134395024304</v>
       </c>
       <c r="E736" t="n">
-        <v>31.57447923609348</v>
+        <v>31.57448111883861</v>
       </c>
       <c r="F736" t="n">
         <v>2923500</v>
@@ -15152,16 +15152,16 @@
         <v>45226</v>
       </c>
       <c r="B737" t="n">
-        <v>31.52535820007324</v>
+        <v>31.52536010742188</v>
       </c>
       <c r="C737" t="n">
-        <v>32.556882098507</v>
+        <v>32.55688406826494</v>
       </c>
       <c r="D737" t="n">
-        <v>31.24046001693592</v>
+        <v>31.24046190704763</v>
       </c>
       <c r="E737" t="n">
-        <v>32.32110713476096</v>
+        <v>32.32110909025403</v>
       </c>
       <c r="F737" t="n">
         <v>3378100</v>
@@ -15172,16 +15172,16 @@
         <v>45229</v>
       </c>
       <c r="B738" t="n">
-        <v>31.07345390319824</v>
+        <v>31.07345199584961</v>
       </c>
       <c r="C738" t="n">
-        <v>32.11480216169681</v>
+        <v>32.11480019042821</v>
       </c>
       <c r="D738" t="n">
-        <v>30.98503922096583</v>
+        <v>30.98503731904426</v>
       </c>
       <c r="E738" t="n">
-        <v>31.54500949323592</v>
+        <v>31.5450075569423</v>
       </c>
       <c r="F738" t="n">
         <v>3227500</v>
@@ -15192,16 +15192,16 @@
         <v>45230</v>
       </c>
       <c r="B739" t="n">
-        <v>31.86919784545898</v>
+        <v>31.86919975280762</v>
       </c>
       <c r="C739" t="n">
-        <v>32.10497655378492</v>
+        <v>32.10497847524474</v>
       </c>
       <c r="D739" t="n">
-        <v>31.20116441782789</v>
+        <v>31.2011662851952</v>
       </c>
       <c r="E739" t="n">
-        <v>31.20116441782789</v>
+        <v>31.2011662851952</v>
       </c>
       <c r="F739" t="n">
         <v>3372100</v>
@@ -15212,16 +15212,16 @@
         <v>45231</v>
       </c>
       <c r="B740" t="n">
-        <v>32.06568145751953</v>
+        <v>32.06567764282227</v>
       </c>
       <c r="C740" t="n">
-        <v>32.74354294357276</v>
+        <v>32.74353904823363</v>
       </c>
       <c r="D740" t="n">
-        <v>31.94779396986597</v>
+        <v>31.9477901691932</v>
       </c>
       <c r="E740" t="n">
-        <v>32.0755076009098</v>
+        <v>32.07550378504357</v>
       </c>
       <c r="F740" t="n">
         <v>4282500</v>
@@ -15232,16 +15232,16 @@
         <v>45233</v>
       </c>
       <c r="B741" t="n">
-        <v>32.69441604614258</v>
+        <v>32.69441986083984</v>
       </c>
       <c r="C741" t="n">
-        <v>32.94984327951414</v>
+        <v>32.94984712401398</v>
       </c>
       <c r="D741" t="n">
-        <v>32.4684634920525</v>
+        <v>32.46846728038622</v>
       </c>
       <c r="E741" t="n">
-        <v>32.7337131201344</v>
+        <v>32.73371693941674</v>
       </c>
       <c r="F741" t="n">
         <v>3190300</v>
@@ -15272,16 +15272,16 @@
         <v>45237</v>
       </c>
       <c r="B743" t="n">
-        <v>32.48811340332031</v>
+        <v>32.48811721801758</v>
       </c>
       <c r="C743" t="n">
-        <v>32.63547556323554</v>
+        <v>32.63547939523581</v>
       </c>
       <c r="D743" t="n">
-        <v>31.81025571237618</v>
+        <v>31.81025944748058</v>
       </c>
       <c r="E743" t="n">
-        <v>31.87902372098318</v>
+        <v>31.8790274641622</v>
       </c>
       <c r="F743" t="n">
         <v>3324000</v>
@@ -15312,16 +15312,16 @@
         <v>45239</v>
       </c>
       <c r="B745" t="n">
-        <v>30.81802940368652</v>
+        <v>30.81802749633789</v>
       </c>
       <c r="C745" t="n">
-        <v>33.77506711733456</v>
+        <v>33.77506502697286</v>
       </c>
       <c r="D745" t="n">
-        <v>30.67066723245724</v>
+        <v>30.67066533422895</v>
       </c>
       <c r="E745" t="n">
-        <v>33.41157476098916</v>
+        <v>33.41157269312426</v>
       </c>
       <c r="F745" t="n">
         <v>15431300</v>
@@ -15332,16 +15332,16 @@
         <v>45240</v>
       </c>
       <c r="B746" t="n">
-        <v>31.25028419494629</v>
+        <v>31.25028610229492</v>
       </c>
       <c r="C746" t="n">
-        <v>32.06567979171039</v>
+        <v>32.06568174882637</v>
       </c>
       <c r="D746" t="n">
-        <v>31.04398016537612</v>
+        <v>31.04398206013306</v>
       </c>
       <c r="E746" t="n">
-        <v>31.05380443446818</v>
+        <v>31.05380632982475</v>
       </c>
       <c r="F746" t="n">
         <v>4738300</v>
@@ -15352,16 +15352,16 @@
         <v>45243</v>
       </c>
       <c r="B747" t="n">
-        <v>30.94574165344238</v>
+        <v>30.94573974609375</v>
       </c>
       <c r="C747" t="n">
-        <v>31.41729536226194</v>
+        <v>31.41729342584897</v>
       </c>
       <c r="D747" t="n">
-        <v>30.67066771973704</v>
+        <v>30.67066582934266</v>
       </c>
       <c r="E747" t="n">
-        <v>31.21099131732383</v>
+        <v>31.21098939362647</v>
       </c>
       <c r="F747" t="n">
         <v>3172300</v>
@@ -15392,16 +15392,16 @@
         <v>45246</v>
       </c>
       <c r="B749" t="n">
-        <v>31.13239669799805</v>
+        <v>31.13239860534668</v>
       </c>
       <c r="C749" t="n">
-        <v>32.13444778565191</v>
+        <v>32.13444975439192</v>
       </c>
       <c r="D749" t="n">
-        <v>30.68048968892551</v>
+        <v>30.68049156858774</v>
       </c>
       <c r="E749" t="n">
-        <v>31.78078159366364</v>
+        <v>31.78078354073604</v>
       </c>
       <c r="F749" t="n">
         <v>5148500</v>
@@ -15492,16 +15492,16 @@
         <v>45253</v>
       </c>
       <c r="B754" t="n">
-        <v>31.81025886535645</v>
+        <v>31.81025505065918</v>
       </c>
       <c r="C754" t="n">
-        <v>32.00674051552654</v>
+        <v>32.00673667726713</v>
       </c>
       <c r="D754" t="n">
-        <v>31.58430627931235</v>
+        <v>31.5843024917114</v>
       </c>
       <c r="E754" t="n">
-        <v>31.82990740513103</v>
+        <v>31.82990358807751</v>
       </c>
       <c r="F754" t="n">
         <v>2086300</v>
@@ -15552,16 +15552,16 @@
         <v>45258</v>
       </c>
       <c r="B757" t="n">
-        <v>29.80615234375</v>
+        <v>29.80615043640137</v>
       </c>
       <c r="C757" t="n">
-        <v>30.21876230404811</v>
+        <v>30.21876037029583</v>
       </c>
       <c r="D757" t="n">
-        <v>29.63914350568201</v>
+        <v>29.63914160902057</v>
       </c>
       <c r="E757" t="n">
-        <v>30.17946522507312</v>
+        <v>30.17946329383553</v>
       </c>
       <c r="F757" t="n">
         <v>5777500</v>
@@ -15592,16 +15592,16 @@
         <v>45260</v>
       </c>
       <c r="B759" t="n">
-        <v>29.45248413085938</v>
+        <v>29.45248603820801</v>
       </c>
       <c r="C759" t="n">
-        <v>29.83562312973222</v>
+        <v>29.83562506189301</v>
       </c>
       <c r="D759" t="n">
-        <v>29.17741209183939</v>
+        <v>29.1774139813743</v>
       </c>
       <c r="E759" t="n">
-        <v>29.66861430298963</v>
+        <v>29.66861622433489</v>
       </c>
       <c r="F759" t="n">
         <v>4483800</v>
@@ -15732,16 +15732,16 @@
         <v>45271</v>
       </c>
       <c r="B766" t="n">
-        <v>26.91788291931152</v>
+        <v>26.91788101196289</v>
       </c>
       <c r="C766" t="n">
-        <v>27.08489175922624</v>
+        <v>27.08488984004369</v>
       </c>
       <c r="D766" t="n">
-        <v>26.48562441474616</v>
+        <v>26.48562253802652</v>
       </c>
       <c r="E766" t="n">
-        <v>26.96700426857343</v>
+        <v>26.96700235774415</v>
       </c>
       <c r="F766" t="n">
         <v>6627000</v>
@@ -15792,16 +15792,16 @@
         <v>45274</v>
       </c>
       <c r="B769" t="n">
-        <v>27.00629806518555</v>
+        <v>27.00629997253418</v>
       </c>
       <c r="C769" t="n">
-        <v>27.2027797044063</v>
+        <v>27.20278162563166</v>
       </c>
       <c r="D769" t="n">
-        <v>26.49544730224182</v>
+        <v>26.49544917351107</v>
       </c>
       <c r="E769" t="n">
-        <v>26.82946496464443</v>
+        <v>26.82946685950403</v>
       </c>
       <c r="F769" t="n">
         <v>14011300</v>
@@ -15812,16 +15812,16 @@
         <v>45275</v>
       </c>
       <c r="B770" t="n">
-        <v>25.88635635375977</v>
+        <v>25.8863582611084</v>
       </c>
       <c r="C770" t="n">
-        <v>27.21260267051552</v>
+        <v>27.21260467558413</v>
       </c>
       <c r="D770" t="n">
-        <v>25.88635635375977</v>
+        <v>25.8863582611084</v>
       </c>
       <c r="E770" t="n">
-        <v>27.1634813261689</v>
+        <v>27.16348332761816</v>
       </c>
       <c r="F770" t="n">
         <v>11924000</v>
@@ -15832,16 +15832,16 @@
         <v>45278</v>
       </c>
       <c r="B771" t="n">
-        <v>26.21055030822754</v>
+        <v>26.21055221557617</v>
       </c>
       <c r="C771" t="n">
-        <v>26.76069626050536</v>
+        <v>26.76069820788825</v>
       </c>
       <c r="D771" t="n">
-        <v>25.94530066428034</v>
+        <v>25.94530255232668</v>
       </c>
       <c r="E771" t="n">
-        <v>26.12213376024514</v>
+        <v>26.12213566115967</v>
       </c>
       <c r="F771" t="n">
         <v>4958200</v>
@@ -15852,16 +15852,16 @@
         <v>45279</v>
       </c>
       <c r="B772" t="n">
-        <v>26.32843971252441</v>
+        <v>26.32843780517578</v>
       </c>
       <c r="C772" t="n">
-        <v>26.52492136101001</v>
+        <v>26.52491943942738</v>
       </c>
       <c r="D772" t="n">
-        <v>26.13195993782669</v>
+        <v>26.13195804471192</v>
       </c>
       <c r="E772" t="n">
-        <v>26.30879304670615</v>
+        <v>26.30879114078081</v>
       </c>
       <c r="F772" t="n">
         <v>3900900</v>
@@ -15872,16 +15872,16 @@
         <v>45280</v>
       </c>
       <c r="B773" t="n">
-        <v>25.85688591003418</v>
+        <v>25.85688400268555</v>
       </c>
       <c r="C773" t="n">
-        <v>26.54456980342805</v>
+        <v>26.54456784535201</v>
       </c>
       <c r="D773" t="n">
-        <v>25.68987707156926</v>
+        <v>25.68987517654013</v>
       </c>
       <c r="E773" t="n">
-        <v>26.54456980342805</v>
+        <v>26.54456784535201</v>
       </c>
       <c r="F773" t="n">
         <v>6168300</v>
@@ -15912,16 +15912,16 @@
         <v>45282</v>
       </c>
       <c r="B775" t="n">
-        <v>25.95512580871582</v>
+        <v>25.95512771606445</v>
       </c>
       <c r="C775" t="n">
-        <v>26.2203754616087</v>
+        <v>26.22037738844958</v>
       </c>
       <c r="D775" t="n">
-        <v>25.79794124562103</v>
+        <v>25.79794314141873</v>
       </c>
       <c r="E775" t="n">
-        <v>26.03371809026321</v>
+        <v>26.03372000338731</v>
       </c>
       <c r="F775" t="n">
         <v>3644200</v>
@@ -16012,16 +16012,16 @@
         <v>45294</v>
       </c>
       <c r="B780" t="n">
-        <v>25.88635635375977</v>
+        <v>25.8863582611084</v>
       </c>
       <c r="C780" t="n">
-        <v>26.28914200846361</v>
+        <v>26.28914394549015</v>
       </c>
       <c r="D780" t="n">
-        <v>25.35585707754239</v>
+        <v>25.35585894580298</v>
       </c>
       <c r="E780" t="n">
-        <v>25.64075525338972</v>
+        <v>25.64075714264207</v>
       </c>
       <c r="F780" t="n">
         <v>5734800</v>
@@ -16052,16 +16052,16 @@
         <v>45296</v>
       </c>
       <c r="B782" t="n">
-        <v>25.68987464904785</v>
+        <v>25.68987655639648</v>
       </c>
       <c r="C782" t="n">
-        <v>25.97477282406455</v>
+        <v>25.97477475256549</v>
       </c>
       <c r="D782" t="n">
-        <v>25.21832098742127</v>
+        <v>25.21832285975933</v>
       </c>
       <c r="E782" t="n">
-        <v>25.36568127245611</v>
+        <v>25.36568315573496</v>
       </c>
       <c r="F782" t="n">
         <v>3417300</v>
@@ -16092,16 +16092,16 @@
         <v>45300</v>
       </c>
       <c r="B784" t="n">
-        <v>28.01817512512207</v>
+        <v>28.0181770324707</v>
       </c>
       <c r="C784" t="n">
-        <v>28.24412769698892</v>
+        <v>28.24412961971936</v>
       </c>
       <c r="D784" t="n">
-        <v>26.79999384234995</v>
+        <v>26.7999956667704</v>
       </c>
       <c r="E784" t="n">
-        <v>27.01612214494592</v>
+        <v>27.01612398407939</v>
       </c>
       <c r="F784" t="n">
         <v>10290300</v>
@@ -16152,16 +16152,16 @@
         <v>45303</v>
       </c>
       <c r="B787" t="n">
-        <v>28.20483207702637</v>
+        <v>28.20483016967773</v>
       </c>
       <c r="C787" t="n">
-        <v>28.86304316187749</v>
+        <v>28.86304121001741</v>
       </c>
       <c r="D787" t="n">
-        <v>27.82169492460737</v>
+        <v>27.82169304316834</v>
       </c>
       <c r="E787" t="n">
-        <v>28.63709057833746</v>
+        <v>28.63708864175739</v>
       </c>
       <c r="F787" t="n">
         <v>5067700</v>
@@ -16172,16 +16172,16 @@
         <v>45306</v>
       </c>
       <c r="B788" t="n">
-        <v>28.52902793884277</v>
+        <v>28.52902603149414</v>
       </c>
       <c r="C788" t="n">
-        <v>28.68621251092004</v>
+        <v>28.68621059306261</v>
       </c>
       <c r="D788" t="n">
-        <v>27.9002877767458</v>
+        <v>27.90028591143248</v>
       </c>
       <c r="E788" t="n">
-        <v>28.06729661880138</v>
+        <v>28.06729474232245</v>
       </c>
       <c r="F788" t="n">
         <v>3859400</v>
@@ -16252,16 +16252,16 @@
         <v>45310</v>
       </c>
       <c r="B792" t="n">
-        <v>29.03005027770996</v>
+        <v>29.03005218505859</v>
       </c>
       <c r="C792" t="n">
-        <v>29.197059106456</v>
+        <v>29.19706102477754</v>
       </c>
       <c r="D792" t="n">
-        <v>28.0574701128199</v>
+        <v>28.05747195626752</v>
       </c>
       <c r="E792" t="n">
-        <v>28.73532969699943</v>
+        <v>28.73533158498416</v>
       </c>
       <c r="F792" t="n">
         <v>7851200</v>
@@ -16312,16 +16312,16 @@
         <v>45315</v>
       </c>
       <c r="B795" t="n">
-        <v>27.86099243164062</v>
+        <v>27.86099052429199</v>
       </c>
       <c r="C795" t="n">
-        <v>28.52902779653059</v>
+        <v>28.52902584344861</v>
       </c>
       <c r="D795" t="n">
-        <v>27.63503797084227</v>
+        <v>27.63503607896236</v>
       </c>
       <c r="E795" t="n">
-        <v>28.04764793893384</v>
+        <v>28.04764601880687</v>
       </c>
       <c r="F795" t="n">
         <v>4070600</v>
@@ -16352,16 +16352,16 @@
         <v>45317</v>
       </c>
       <c r="B797" t="n">
-        <v>28.24412727355957</v>
+        <v>28.2441291809082</v>
       </c>
       <c r="C797" t="n">
-        <v>28.24412727355957</v>
+        <v>28.2441291809082</v>
       </c>
       <c r="D797" t="n">
-        <v>27.50732395337975</v>
+        <v>27.50732581097147</v>
       </c>
       <c r="E797" t="n">
-        <v>27.65468424265817</v>
+        <v>27.65468611020124</v>
       </c>
       <c r="F797" t="n">
         <v>2761100</v>
@@ -16392,16 +16392,16 @@
         <v>45321</v>
       </c>
       <c r="B799" t="n">
-        <v>27.2420768737793</v>
+        <v>27.24207496643066</v>
       </c>
       <c r="C799" t="n">
-        <v>27.54662362392648</v>
+        <v>27.54662169525507</v>
       </c>
       <c r="D799" t="n">
-        <v>26.97682720382707</v>
+        <v>26.97682531504984</v>
       </c>
       <c r="E799" t="n">
-        <v>27.369790510625</v>
+        <v>27.36978859433452</v>
       </c>
       <c r="F799" t="n">
         <v>2184900</v>
@@ -16432,16 +16432,16 @@
         <v>45323</v>
       </c>
       <c r="B801" t="n">
-        <v>26.24002265930176</v>
+        <v>26.24002075195312</v>
       </c>
       <c r="C801" t="n">
-        <v>27.40908451061442</v>
+        <v>27.4090825182884</v>
       </c>
       <c r="D801" t="n">
-        <v>26.10248663224892</v>
+        <v>26.10248473489757</v>
       </c>
       <c r="E801" t="n">
-        <v>27.31084368823903</v>
+        <v>27.31084170305399</v>
       </c>
       <c r="F801" t="n">
         <v>7611700</v>
@@ -16532,16 +16532,16 @@
         <v>45330</v>
       </c>
       <c r="B806" t="n">
-        <v>28.79427528381348</v>
+        <v>28.79427337646484</v>
       </c>
       <c r="C806" t="n">
-        <v>28.81392382346353</v>
+        <v>28.81392191481336</v>
       </c>
       <c r="D806" t="n">
-        <v>27.39926082305394</v>
+        <v>27.39925900811183</v>
       </c>
       <c r="E806" t="n">
-        <v>28.71568299900116</v>
+        <v>28.71568109685852</v>
       </c>
       <c r="F806" t="n">
         <v>6908300</v>
@@ -16552,16 +16552,16 @@
         <v>45331</v>
       </c>
       <c r="B807" t="n">
-        <v>27.6939811706543</v>
+        <v>27.69398307800293</v>
       </c>
       <c r="C807" t="n">
-        <v>28.9121624286317</v>
+        <v>28.9121644198793</v>
       </c>
       <c r="D807" t="n">
-        <v>27.52697234402422</v>
+        <v>27.52697423987057</v>
       </c>
       <c r="E807" t="n">
-        <v>28.83357014985212</v>
+        <v>28.83357213568689</v>
       </c>
       <c r="F807" t="n">
         <v>5513900</v>
@@ -16592,16 +16592,16 @@
         <v>45337</v>
       </c>
       <c r="B809" t="n">
-        <v>28.00835227966309</v>
+        <v>28.00835037231445</v>
       </c>
       <c r="C809" t="n">
-        <v>28.26377767232718</v>
+        <v>28.26377574758426</v>
       </c>
       <c r="D809" t="n">
-        <v>27.28137318075199</v>
+        <v>27.28137132291011</v>
       </c>
       <c r="E809" t="n">
-        <v>27.40908494019011</v>
+        <v>27.40908307365115</v>
       </c>
       <c r="F809" t="n">
         <v>2788300</v>
@@ -16632,16 +16632,16 @@
         <v>45341</v>
       </c>
       <c r="B811" t="n">
-        <v>28.67638778686523</v>
+        <v>28.6763858795166</v>
       </c>
       <c r="C811" t="n">
-        <v>28.76480434148215</v>
+        <v>28.76480242825268</v>
       </c>
       <c r="D811" t="n">
-        <v>28.23430501378064</v>
+        <v>28.2343031358362</v>
       </c>
       <c r="E811" t="n">
-        <v>28.74515580183664</v>
+        <v>28.74515388991405</v>
       </c>
       <c r="F811" t="n">
         <v>1698200</v>
@@ -16672,16 +16672,16 @@
         <v>45343</v>
       </c>
       <c r="B813" t="n">
-        <v>28.92198944091797</v>
+        <v>28.92198753356934</v>
       </c>
       <c r="C813" t="n">
-        <v>28.98093318714647</v>
+        <v>28.98093127591061</v>
       </c>
       <c r="D813" t="n">
-        <v>28.36201916727748</v>
+        <v>28.36201729685779</v>
       </c>
       <c r="E813" t="n">
-        <v>28.6370912322024</v>
+        <v>28.63708934364225</v>
       </c>
       <c r="F813" t="n">
         <v>2751400</v>
@@ -16792,16 +16792,16 @@
         <v>45351</v>
       </c>
       <c r="B819" t="n">
-        <v>27.45820617675781</v>
+        <v>27.45820426940918</v>
       </c>
       <c r="C819" t="n">
-        <v>28.14588819377561</v>
+        <v>28.14588623865804</v>
       </c>
       <c r="D819" t="n">
-        <v>27.45820617675781</v>
+        <v>27.45820426940918</v>
       </c>
       <c r="E819" t="n">
-        <v>27.98870362566938</v>
+        <v>27.98870168147043</v>
       </c>
       <c r="F819" t="n">
         <v>2784300</v>
@@ -16972,16 +16972,16 @@
         <v>45364</v>
       </c>
       <c r="B828" t="n">
-        <v>29.13811683654785</v>
+        <v>29.13811492919922</v>
       </c>
       <c r="C828" t="n">
-        <v>29.36406941808906</v>
+        <v>29.36406749594983</v>
       </c>
       <c r="D828" t="n">
-        <v>28.98093226905937</v>
+        <v>28.98093037199986</v>
       </c>
       <c r="E828" t="n">
-        <v>28.98093226905937</v>
+        <v>28.98093037199986</v>
       </c>
       <c r="F828" t="n">
         <v>2596400</v>
@@ -17032,16 +17032,16 @@
         <v>45369</v>
       </c>
       <c r="B831" t="n">
-        <v>28.98093032836914</v>
+        <v>28.98093223571777</v>
       </c>
       <c r="C831" t="n">
-        <v>29.28547517326093</v>
+        <v>29.28547710065286</v>
       </c>
       <c r="D831" t="n">
-        <v>28.61743986927554</v>
+        <v>28.61744175270144</v>
       </c>
       <c r="E831" t="n">
-        <v>28.77462630002598</v>
+        <v>28.77462819379693</v>
       </c>
       <c r="F831" t="n">
         <v>4710300</v>
@@ -17112,16 +17112,16 @@
         <v>45373</v>
       </c>
       <c r="B835" t="n">
-        <v>29.71773338317871</v>
+        <v>29.71773529052734</v>
       </c>
       <c r="C835" t="n">
-        <v>30.00263156131158</v>
+        <v>30.0026334869456</v>
       </c>
       <c r="D835" t="n">
-        <v>29.28547491839919</v>
+        <v>29.28547679800454</v>
       </c>
       <c r="E835" t="n">
-        <v>29.88474220772164</v>
+        <v>29.88474412578926</v>
       </c>
       <c r="F835" t="n">
         <v>3854000</v>
@@ -17152,16 +17152,16 @@
         <v>45377</v>
       </c>
       <c r="B837" t="n">
-        <v>30.81802940368652</v>
+        <v>30.81802749633789</v>
       </c>
       <c r="C837" t="n">
-        <v>31.22081509112746</v>
+        <v>31.22081315885015</v>
       </c>
       <c r="D837" t="n">
-        <v>30.51348266534799</v>
+        <v>30.51348077684796</v>
       </c>
       <c r="E837" t="n">
-        <v>30.61172348823823</v>
+        <v>30.61172159365801</v>
       </c>
       <c r="F837" t="n">
         <v>3327200</v>
@@ -17172,16 +17172,16 @@
         <v>45378</v>
       </c>
       <c r="B838" t="n">
-        <v>31.48606300354004</v>
+        <v>31.48606109619141</v>
       </c>
       <c r="C838" t="n">
-        <v>31.91832337550937</v>
+        <v>31.91832144197546</v>
       </c>
       <c r="D838" t="n">
-        <v>30.38577102935353</v>
+        <v>30.3857691886579</v>
       </c>
       <c r="E838" t="n">
-        <v>30.6510206900868</v>
+        <v>30.65101883332299</v>
       </c>
       <c r="F838" t="n">
         <v>9071000</v>
@@ -17372,16 +17372,16 @@
         <v>45393</v>
       </c>
       <c r="B848" t="n">
-        <v>35.62198257446289</v>
+        <v>35.62198638916016</v>
       </c>
       <c r="C848" t="n">
-        <v>35.91670689814429</v>
+        <v>35.91671074440308</v>
       </c>
       <c r="D848" t="n">
-        <v>34.59045868430435</v>
+        <v>34.59046238853748</v>
       </c>
       <c r="E848" t="n">
-        <v>34.74764324139922</v>
+        <v>34.74764696246498</v>
       </c>
       <c r="F848" t="n">
         <v>5960900</v>
@@ -17412,16 +17412,16 @@
         <v>45397</v>
       </c>
       <c r="B850" t="n">
-        <v>34.06978988647461</v>
+        <v>34.06978607177734</v>
       </c>
       <c r="C850" t="n">
-        <v>34.52169507730631</v>
+        <v>34.52169121201051</v>
       </c>
       <c r="D850" t="n">
-        <v>33.83401114697602</v>
+        <v>33.83400735867823</v>
       </c>
       <c r="E850" t="n">
-        <v>34.43327851844133</v>
+        <v>34.43327466304528</v>
       </c>
       <c r="F850" t="n">
         <v>4151100</v>
@@ -17472,16 +17472,16 @@
         <v>45400</v>
       </c>
       <c r="B853" t="n">
-        <v>32.33092880249023</v>
+        <v>32.3309326171875</v>
       </c>
       <c r="C853" t="n">
-        <v>33.28386227408815</v>
+        <v>33.28386620122118</v>
       </c>
       <c r="D853" t="n">
-        <v>31.93796554165645</v>
+        <v>31.93796930998834</v>
       </c>
       <c r="E853" t="n">
-        <v>33.00878649247434</v>
+        <v>33.00879038715143</v>
       </c>
       <c r="F853" t="n">
         <v>4478700</v>
@@ -17632,16 +17632,16 @@
         <v>45412</v>
       </c>
       <c r="B861" t="n">
-        <v>32.58635330200195</v>
+        <v>32.58635711669922</v>
       </c>
       <c r="C861" t="n">
-        <v>33.66700042877825</v>
+        <v>33.66700436998067</v>
       </c>
       <c r="D861" t="n">
-        <v>32.43899488533395</v>
+        <v>32.43899868278081</v>
       </c>
       <c r="E861" t="n">
-        <v>33.60805481356574</v>
+        <v>33.60805874786774</v>
       </c>
       <c r="F861" t="n">
         <v>6661700</v>
@@ -29512,19 +29512,39 @@
         <v>46281</v>
       </c>
       <c r="B1455" t="n">
-        <v>17.73</v>
+        <v>17.72999954223633</v>
       </c>
       <c r="C1455" t="n">
-        <v>17.81</v>
+        <v>17.80999946594238</v>
       </c>
       <c r="D1455" t="n">
-        <v>17.55</v>
+        <v>17.54999923706055</v>
       </c>
       <c r="E1455" t="n">
-        <v>17.8</v>
+        <v>17.79999923706055</v>
       </c>
       <c r="F1455" t="n">
         <v>3314100</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B1456" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="C1456" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="D1456" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="E1456" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="F1456" t="n">
+        <v>2811000</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1456"/>
+  <dimension ref="A1:F1457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,16 +512,16 @@
         <v>44152</v>
       </c>
       <c r="B5" t="n">
-        <v>20.17695426940918</v>
+        <v>20.17695617675781</v>
       </c>
       <c r="C5" t="n">
-        <v>20.17695426940918</v>
+        <v>20.17695617675781</v>
       </c>
       <c r="D5" t="n">
-        <v>19.85012445790661</v>
+        <v>19.85012633435968</v>
       </c>
       <c r="E5" t="n">
-        <v>20.12888973916155</v>
+        <v>20.12889164196659</v>
       </c>
       <c r="F5" t="n">
         <v>262242</v>
@@ -572,16 +572,16 @@
         <v>44158</v>
       </c>
       <c r="B8" t="n">
-        <v>20.20579147338867</v>
+        <v>20.2057933807373</v>
       </c>
       <c r="C8" t="n">
-        <v>20.52300874747816</v>
+        <v>20.52301068477087</v>
       </c>
       <c r="D8" t="n">
-        <v>20.14811628674976</v>
+        <v>20.14811818865408</v>
       </c>
       <c r="E8" t="n">
-        <v>20.14811628674976</v>
+        <v>20.14811818865408</v>
       </c>
       <c r="F8" t="n">
         <v>79408</v>
@@ -632,16 +632,16 @@
         <v>44161</v>
       </c>
       <c r="B11" t="n">
-        <v>22.87810897827148</v>
+        <v>22.87811088562012</v>
       </c>
       <c r="C11" t="n">
-        <v>22.87810897827148</v>
+        <v>22.87811088562012</v>
       </c>
       <c r="D11" t="n">
-        <v>22.31096214463751</v>
+        <v>22.3109640047031</v>
       </c>
       <c r="E11" t="n">
-        <v>22.31096214463751</v>
+        <v>22.3109640047031</v>
       </c>
       <c r="F11" t="n">
         <v>72970</v>
@@ -652,16 +652,16 @@
         <v>44162</v>
       </c>
       <c r="B12" t="n">
-        <v>23.07036399841309</v>
+        <v>23.07036209106445</v>
       </c>
       <c r="C12" t="n">
-        <v>23.55099623037812</v>
+        <v>23.55099428329309</v>
       </c>
       <c r="D12" t="n">
-        <v>22.10909953448302</v>
+        <v>22.10909770660719</v>
       </c>
       <c r="E12" t="n">
-        <v>23.07036399841309</v>
+        <v>23.07036209106445</v>
       </c>
       <c r="F12" t="n">
         <v>72050</v>
@@ -692,16 +692,16 @@
         <v>44166</v>
       </c>
       <c r="B14" t="n">
-        <v>23.07036399841309</v>
+        <v>23.07036209106445</v>
       </c>
       <c r="C14" t="n">
-        <v>23.16649119432127</v>
+        <v>23.1664892790253</v>
       </c>
       <c r="D14" t="n">
-        <v>23.03191386956499</v>
+        <v>23.03191196539523</v>
       </c>
       <c r="E14" t="n">
-        <v>23.12803919168523</v>
+        <v>23.12803727956828</v>
       </c>
       <c r="F14" t="n">
         <v>93512</v>
@@ -792,16 +792,16 @@
         <v>44173</v>
       </c>
       <c r="B19" t="n">
-        <v>26.33866310119629</v>
+        <v>26.33866500854492</v>
       </c>
       <c r="C19" t="n">
-        <v>26.57898012603766</v>
+        <v>26.57898205078916</v>
       </c>
       <c r="D19" t="n">
-        <v>25.56965124500673</v>
+        <v>25.56965309666637</v>
       </c>
       <c r="E19" t="n">
-        <v>25.56965124500673</v>
+        <v>25.56965309666637</v>
       </c>
       <c r="F19" t="n">
         <v>126420</v>
@@ -812,16 +812,16 @@
         <v>44174</v>
       </c>
       <c r="B20" t="n">
-        <v>26.83852195739746</v>
+        <v>26.83852005004883</v>
       </c>
       <c r="C20" t="n">
-        <v>27.77095064592048</v>
+        <v>27.77094867230641</v>
       </c>
       <c r="D20" t="n">
-        <v>26.27137696749292</v>
+        <v>26.27137510044991</v>
       </c>
       <c r="E20" t="n">
-        <v>26.49246706969505</v>
+        <v>26.4924651869397</v>
       </c>
       <c r="F20" t="n">
         <v>212880</v>
@@ -892,16 +892,16 @@
         <v>44180</v>
       </c>
       <c r="B24" t="n">
-        <v>33.00984573364258</v>
+        <v>33.00984191894531</v>
       </c>
       <c r="C24" t="n">
-        <v>33.98072266755544</v>
+        <v>33.9807187406613</v>
       </c>
       <c r="D24" t="n">
-        <v>30.76048335959674</v>
+        <v>30.7604798048412</v>
       </c>
       <c r="E24" t="n">
-        <v>30.76048335959674</v>
+        <v>30.7604798048412</v>
       </c>
       <c r="F24" t="n">
         <v>887803</v>
@@ -912,16 +912,16 @@
         <v>44181</v>
       </c>
       <c r="B25" t="n">
-        <v>32.68301391601562</v>
+        <v>32.68301773071289</v>
       </c>
       <c r="C25" t="n">
-        <v>34.45173835953219</v>
+        <v>34.4517423806715</v>
       </c>
       <c r="D25" t="n">
-        <v>32.10625456033017</v>
+        <v>32.10625830770921</v>
       </c>
       <c r="E25" t="n">
-        <v>33.62505319761509</v>
+        <v>33.62505712226533</v>
       </c>
       <c r="F25" t="n">
         <v>376808</v>
@@ -932,16 +932,16 @@
         <v>44182</v>
       </c>
       <c r="B26" t="n">
-        <v>32.10625839233398</v>
+        <v>32.10625457763672</v>
       </c>
       <c r="C26" t="n">
-        <v>33.64428227520571</v>
+        <v>33.64427827776851</v>
       </c>
       <c r="D26" t="n">
-        <v>31.64484935368452</v>
+        <v>31.64484559380946</v>
       </c>
       <c r="E26" t="n">
-        <v>33.6250572108933</v>
+        <v>33.62505321574033</v>
       </c>
       <c r="F26" t="n">
         <v>258257</v>
@@ -972,16 +972,16 @@
         <v>44186</v>
       </c>
       <c r="B28" t="n">
-        <v>32.18315887451172</v>
+        <v>32.18315505981445</v>
       </c>
       <c r="C28" t="n">
-        <v>33.33667773162143</v>
+        <v>33.33667378019659</v>
       </c>
       <c r="D28" t="n">
-        <v>29.12633427792858</v>
+        <v>29.12633082555934</v>
       </c>
       <c r="E28" t="n">
-        <v>31.86594156356414</v>
+        <v>31.86593778646691</v>
       </c>
       <c r="F28" t="n">
         <v>236079</v>
@@ -992,16 +992,16 @@
         <v>44187</v>
       </c>
       <c r="B29" t="n">
-        <v>33.16364288330078</v>
+        <v>33.16364669799805</v>
       </c>
       <c r="C29" t="n">
-        <v>33.47124761081827</v>
+        <v>33.47125146089823</v>
       </c>
       <c r="D29" t="n">
-        <v>32.59649608138177</v>
+        <v>32.59649983084212</v>
       </c>
       <c r="E29" t="n">
-        <v>33.21170553641675</v>
+        <v>33.21170935664249</v>
       </c>
       <c r="F29" t="n">
         <v>167504</v>
@@ -1032,16 +1032,16 @@
         <v>44193</v>
       </c>
       <c r="B31" t="n">
-        <v>36.21085739135742</v>
+        <v>36.21085357666016</v>
       </c>
       <c r="C31" t="n">
-        <v>36.66265388599569</v>
+        <v>36.66265002370312</v>
       </c>
       <c r="D31" t="n">
-        <v>35.56681025863972</v>
+        <v>35.56680651179074</v>
       </c>
       <c r="E31" t="n">
-        <v>35.56681025863972</v>
+        <v>35.56680651179074</v>
       </c>
       <c r="F31" t="n">
         <v>451822</v>
@@ -1052,16 +1052,16 @@
         <v>44194</v>
       </c>
       <c r="B32" t="n">
-        <v>36.09550476074219</v>
+        <v>36.09550857543945</v>
       </c>
       <c r="C32" t="n">
-        <v>37.06638166531152</v>
+        <v>37.06638558261441</v>
       </c>
       <c r="D32" t="n">
-        <v>35.95131304358604</v>
+        <v>35.95131684304462</v>
       </c>
       <c r="E32" t="n">
-        <v>36.52807241705953</v>
+        <v>36.52807627747203</v>
       </c>
       <c r="F32" t="n">
         <v>337154</v>
@@ -1092,16 +1092,16 @@
         <v>44200</v>
       </c>
       <c r="B34" t="n">
-        <v>34.99966049194336</v>
+        <v>34.99966430664062</v>
       </c>
       <c r="C34" t="n">
-        <v>36.62420073506411</v>
+        <v>36.62420472682393</v>
       </c>
       <c r="D34" t="n">
-        <v>34.98043542972244</v>
+        <v>34.98043924232432</v>
       </c>
       <c r="E34" t="n">
-        <v>36.52807167638402</v>
+        <v>36.52807565766651</v>
       </c>
       <c r="F34" t="n">
         <v>331840</v>
@@ -1112,16 +1112,16 @@
         <v>44201</v>
       </c>
       <c r="B35" t="n">
-        <v>36.13395690917969</v>
+        <v>36.13395309448242</v>
       </c>
       <c r="C35" t="n">
-        <v>36.32621129362743</v>
+        <v>36.32620745863368</v>
       </c>
       <c r="D35" t="n">
-        <v>34.60554560816865</v>
+        <v>34.60554195482727</v>
       </c>
       <c r="E35" t="n">
-        <v>35.45145965313264</v>
+        <v>35.45145591048728</v>
       </c>
       <c r="F35" t="n">
         <v>328059</v>
@@ -1172,16 +1172,16 @@
         <v>44204</v>
       </c>
       <c r="B38" t="n">
-        <v>34.13452529907227</v>
+        <v>34.134521484375</v>
       </c>
       <c r="C38" t="n">
-        <v>35.75906572541368</v>
+        <v>35.75906172916622</v>
       </c>
       <c r="D38" t="n">
-        <v>34.13452529907227</v>
+        <v>34.134521484375</v>
       </c>
       <c r="E38" t="n">
-        <v>35.16308123419719</v>
+        <v>35.16307730455386</v>
       </c>
       <c r="F38" t="n">
         <v>367201</v>
@@ -1272,16 +1272,16 @@
         <v>44211</v>
       </c>
       <c r="B43" t="n">
-        <v>33.94226837158203</v>
+        <v>33.9422721862793</v>
       </c>
       <c r="C43" t="n">
-        <v>35.04772061203977</v>
+        <v>35.0477245509764</v>
       </c>
       <c r="D43" t="n">
-        <v>33.16364216523639</v>
+        <v>33.16364589242556</v>
       </c>
       <c r="E43" t="n">
-        <v>34.60554046537172</v>
+        <v>34.60554435461268</v>
       </c>
       <c r="F43" t="n">
         <v>319883</v>
@@ -1292,16 +1292,16 @@
         <v>44214</v>
       </c>
       <c r="B44" t="n">
-        <v>34.04801177978516</v>
+        <v>34.04800796508789</v>
       </c>
       <c r="C44" t="n">
-        <v>34.5094208103909</v>
+        <v>34.50941694399793</v>
       </c>
       <c r="D44" t="n">
-        <v>33.27900172554335</v>
+        <v>33.27899799700501</v>
       </c>
       <c r="E44" t="n">
-        <v>34.11529950370554</v>
+        <v>34.11529568146945</v>
       </c>
       <c r="F44" t="n">
         <v>117631</v>
@@ -1332,16 +1332,16 @@
         <v>44216</v>
       </c>
       <c r="B46" t="n">
-        <v>34.12490844726562</v>
+        <v>34.12491226196289</v>
       </c>
       <c r="C46" t="n">
-        <v>35.28803968588292</v>
+        <v>35.28804363060232</v>
       </c>
       <c r="D46" t="n">
-        <v>33.66350321275509</v>
+        <v>33.66350697587357</v>
       </c>
       <c r="E46" t="n">
-        <v>34.60554249130722</v>
+        <v>34.60554635973278</v>
       </c>
       <c r="F46" t="n">
         <v>359332</v>
@@ -1372,16 +1372,16 @@
         <v>44218</v>
       </c>
       <c r="B48" t="n">
-        <v>32.95216369628906</v>
+        <v>32.95216751098633</v>
       </c>
       <c r="C48" t="n">
-        <v>33.45202278739948</v>
+        <v>33.45202665996278</v>
       </c>
       <c r="D48" t="n">
-        <v>32.53882112897777</v>
+        <v>32.53882489582456</v>
       </c>
       <c r="E48" t="n">
-        <v>33.19248071115274</v>
+        <v>33.19248455367023</v>
       </c>
       <c r="F48" t="n">
         <v>220341</v>
@@ -1472,16 +1472,16 @@
         <v>44228</v>
       </c>
       <c r="B53" t="n">
-        <v>31.7794246673584</v>
+        <v>31.77942657470703</v>
       </c>
       <c r="C53" t="n">
-        <v>33.1155814640686</v>
+        <v>33.11558345161116</v>
       </c>
       <c r="D53" t="n">
-        <v>31.66407054800669</v>
+        <v>31.66407244843196</v>
       </c>
       <c r="E53" t="n">
-        <v>32.68301382233215</v>
+        <v>32.68301578391271</v>
       </c>
       <c r="F53" t="n">
         <v>610435</v>
@@ -1492,16 +1492,16 @@
         <v>44229</v>
       </c>
       <c r="B54" t="n">
-        <v>32.63494873046875</v>
+        <v>32.63495254516602</v>
       </c>
       <c r="C54" t="n">
-        <v>33.65389204571495</v>
+        <v>33.65389597951643</v>
       </c>
       <c r="D54" t="n">
-        <v>31.97167657096734</v>
+        <v>31.97168030813476</v>
       </c>
       <c r="E54" t="n">
-        <v>33.64427951434755</v>
+        <v>33.64428344702543</v>
       </c>
       <c r="F54" t="n">
         <v>582228</v>
@@ -1532,16 +1532,16 @@
         <v>44231</v>
       </c>
       <c r="B56" t="n">
-        <v>32.68301391601562</v>
+        <v>32.68301773071289</v>
       </c>
       <c r="C56" t="n">
-        <v>34.11529602664492</v>
+        <v>34.11530000851534</v>
       </c>
       <c r="D56" t="n">
-        <v>32.44269689321744</v>
+        <v>32.44270067986538</v>
       </c>
       <c r="E56" t="n">
-        <v>33.06751890394745</v>
+        <v>33.06752276352339</v>
       </c>
       <c r="F56" t="n">
         <v>466743</v>
@@ -1612,16 +1612,16 @@
         <v>44237</v>
       </c>
       <c r="B60" t="n">
-        <v>34.83624649047852</v>
+        <v>34.83625030517578</v>
       </c>
       <c r="C60" t="n">
-        <v>35.33610184184258</v>
+        <v>35.33610571127585</v>
       </c>
       <c r="D60" t="n">
-        <v>34.23064955227608</v>
+        <v>34.23065330065825</v>
       </c>
       <c r="E60" t="n">
-        <v>34.43251269995998</v>
+        <v>34.43251647044691</v>
       </c>
       <c r="F60" t="n">
         <v>186206</v>
@@ -1652,16 +1652,16 @@
         <v>44239</v>
       </c>
       <c r="B62" t="n">
-        <v>34.40367889404297</v>
+        <v>34.4036750793457</v>
       </c>
       <c r="C62" t="n">
-        <v>34.52864555631986</v>
+        <v>34.52864172776623</v>
       </c>
       <c r="D62" t="n">
-        <v>32.673400666573</v>
+        <v>32.67339704372985</v>
       </c>
       <c r="E62" t="n">
-        <v>33.67311897448496</v>
+        <v>33.67311524079254</v>
       </c>
       <c r="F62" t="n">
         <v>218195</v>
@@ -1692,16 +1692,16 @@
         <v>44245</v>
       </c>
       <c r="B64" t="n">
-        <v>37.00870895385742</v>
+        <v>37.00870513916016</v>
       </c>
       <c r="C64" t="n">
-        <v>37.38360144742785</v>
+        <v>37.38359759408829</v>
       </c>
       <c r="D64" t="n">
-        <v>35.71100215049589</v>
+        <v>35.71099846956061</v>
       </c>
       <c r="E64" t="n">
-        <v>36.37427435009953</v>
+        <v>36.37427060079703</v>
       </c>
       <c r="F64" t="n">
         <v>661534</v>
@@ -1812,16 +1812,16 @@
         <v>44253</v>
       </c>
       <c r="B70" t="n">
-        <v>34.57670593261719</v>
+        <v>34.57670974731445</v>
       </c>
       <c r="C70" t="n">
-        <v>37.21057322750037</v>
+        <v>37.21057733278074</v>
       </c>
       <c r="D70" t="n">
-        <v>33.75001700107128</v>
+        <v>33.75002072456356</v>
       </c>
       <c r="E70" t="n">
-        <v>36.5376847961999</v>
+        <v>36.53768882724342</v>
       </c>
       <c r="F70" t="n">
         <v>410022</v>
@@ -1932,16 +1932,16 @@
         <v>44263</v>
       </c>
       <c r="B76" t="n">
-        <v>41.91115951538086</v>
+        <v>41.91115570068359</v>
       </c>
       <c r="C76" t="n">
-        <v>44.60270214463106</v>
+        <v>44.60269808495321</v>
       </c>
       <c r="D76" t="n">
-        <v>40.70957805138659</v>
+        <v>40.70957434605565</v>
       </c>
       <c r="E76" t="n">
-        <v>43.55492493684502</v>
+        <v>43.55492097253444</v>
       </c>
       <c r="F76" t="n">
         <v>1012691</v>
@@ -1952,16 +1952,16 @@
         <v>44264</v>
       </c>
       <c r="B77" t="n">
-        <v>43.50686264038086</v>
+        <v>43.50685882568359</v>
       </c>
       <c r="C77" t="n">
-        <v>43.50686264038086</v>
+        <v>43.50685882568359</v>
       </c>
       <c r="D77" t="n">
-        <v>39.89250193891922</v>
+        <v>39.89249844113039</v>
       </c>
       <c r="E77" t="n">
-        <v>42.29566488693005</v>
+        <v>42.29566117843103</v>
       </c>
       <c r="F77" t="n">
         <v>563525</v>
@@ -1972,16 +1972,16 @@
         <v>44265</v>
       </c>
       <c r="B78" t="n">
-        <v>44.69882583618164</v>
+        <v>44.69882965087891</v>
       </c>
       <c r="C78" t="n">
-        <v>44.89108021255291</v>
+        <v>44.89108404365759</v>
       </c>
       <c r="D78" t="n">
-        <v>43.38189403862891</v>
+        <v>43.38189774093629</v>
       </c>
       <c r="E78" t="n">
-        <v>43.83369051144994</v>
+        <v>43.83369425231464</v>
       </c>
       <c r="F78" t="n">
         <v>425454</v>
@@ -2012,16 +2012,16 @@
         <v>44267</v>
       </c>
       <c r="B80" t="n">
-        <v>45.66009521484375</v>
+        <v>45.66009140014648</v>
       </c>
       <c r="C80" t="n">
-        <v>49.01491000208902</v>
+        <v>49.01490590711195</v>
       </c>
       <c r="D80" t="n">
-        <v>45.18907366630634</v>
+        <v>45.18906989096082</v>
       </c>
       <c r="E80" t="n">
-        <v>47.15005636649431</v>
+        <v>47.15005242731743</v>
       </c>
       <c r="F80" t="n">
         <v>954539</v>
@@ -2052,16 +2052,16 @@
         <v>44271</v>
       </c>
       <c r="B82" t="n">
-        <v>42.75707244873047</v>
+        <v>42.7570686340332</v>
       </c>
       <c r="C82" t="n">
-        <v>45.18907290913018</v>
+        <v>45.18906887745489</v>
       </c>
       <c r="D82" t="n">
-        <v>42.75707244873047</v>
+        <v>42.7570686340332</v>
       </c>
       <c r="E82" t="n">
-        <v>44.50657567458991</v>
+        <v>44.5065717038056</v>
       </c>
       <c r="F82" t="n">
         <v>561175</v>
@@ -2092,16 +2092,16 @@
         <v>44273</v>
       </c>
       <c r="B84" t="n">
-        <v>40.89221954345703</v>
+        <v>40.89221572875977</v>
       </c>
       <c r="C84" t="n">
-        <v>45.0256568951004</v>
+        <v>45.02565269480871</v>
       </c>
       <c r="D84" t="n">
-        <v>40.57500224961562</v>
+        <v>40.57499846451049</v>
       </c>
       <c r="E84" t="n">
-        <v>44.01632982334604</v>
+        <v>44.01632571721106</v>
       </c>
       <c r="F84" t="n">
         <v>572621</v>
@@ -2112,16 +2112,16 @@
         <v>44274</v>
       </c>
       <c r="B85" t="n">
-        <v>42.29566192626953</v>
+        <v>42.2956657409668</v>
       </c>
       <c r="C85" t="n">
-        <v>44.17013174266427</v>
+        <v>44.17013572642225</v>
       </c>
       <c r="D85" t="n">
-        <v>41.4593642170013</v>
+        <v>41.45936795627186</v>
       </c>
       <c r="E85" t="n">
-        <v>41.4593642170013</v>
+        <v>41.45936795627186</v>
       </c>
       <c r="F85" t="n">
         <v>639255</v>
@@ -2212,16 +2212,16 @@
         <v>44281</v>
       </c>
       <c r="B90" t="n">
-        <v>37.87384414672852</v>
+        <v>37.87384796142578</v>
       </c>
       <c r="C90" t="n">
-        <v>40.949891527232</v>
+        <v>40.94989565175231</v>
       </c>
       <c r="D90" t="n">
-        <v>37.56623940867817</v>
+        <v>37.56624319239313</v>
       </c>
       <c r="E90" t="n">
-        <v>39.95978959641457</v>
+        <v>39.95979362121066</v>
       </c>
       <c r="F90" t="n">
         <v>840076</v>
@@ -2312,16 +2312,16 @@
         <v>44291</v>
       </c>
       <c r="B95" t="n">
-        <v>35.68215942382812</v>
+        <v>35.68216323852539</v>
       </c>
       <c r="C95" t="n">
-        <v>37.01831616285484</v>
+        <v>37.01832012039754</v>
       </c>
       <c r="D95" t="n">
-        <v>35.09578756412892</v>
+        <v>35.09579131613852</v>
       </c>
       <c r="E95" t="n">
-        <v>37.01831616285484</v>
+        <v>37.01832012039754</v>
       </c>
       <c r="F95" t="n">
         <v>1091895</v>
@@ -2512,16 +2512,16 @@
         <v>44305</v>
       </c>
       <c r="B105" t="n">
-        <v>41.33439636230469</v>
+        <v>41.33440017700195</v>
       </c>
       <c r="C105" t="n">
-        <v>42.23798551125894</v>
+        <v>42.23798940934727</v>
       </c>
       <c r="D105" t="n">
-        <v>40.20971525467667</v>
+        <v>40.2097189655786</v>
       </c>
       <c r="E105" t="n">
-        <v>40.38274455876383</v>
+        <v>40.38274828563441</v>
       </c>
       <c r="F105" t="n">
         <v>1793083</v>
@@ -2552,16 +2552,16 @@
         <v>44308</v>
       </c>
       <c r="B107" t="n">
-        <v>42.3725700378418</v>
+        <v>42.37256622314453</v>
       </c>
       <c r="C107" t="n">
-        <v>42.77630013488342</v>
+        <v>42.77629628383934</v>
       </c>
       <c r="D107" t="n">
-        <v>41.04602186600353</v>
+        <v>41.0460181707321</v>
       </c>
       <c r="E107" t="n">
-        <v>42.58404574470481</v>
+        <v>42.58404191096891</v>
       </c>
       <c r="F107" t="n">
         <v>1175903</v>
@@ -2572,16 +2572,16 @@
         <v>44309</v>
       </c>
       <c r="B108" t="n">
-        <v>44.09323501586914</v>
+        <v>44.09323120117188</v>
       </c>
       <c r="C108" t="n">
-        <v>44.31432325105797</v>
+        <v>44.3143194172334</v>
       </c>
       <c r="D108" t="n">
-        <v>42.38218184069201</v>
+        <v>42.38217817402538</v>
       </c>
       <c r="E108" t="n">
-        <v>42.82436205864548</v>
+        <v>42.82435835372392</v>
       </c>
       <c r="F108" t="n">
         <v>1899574</v>
@@ -2612,16 +2612,16 @@
         <v>44313</v>
       </c>
       <c r="B110" t="n">
-        <v>43.7375602722168</v>
+        <v>43.73756408691406</v>
       </c>
       <c r="C110" t="n">
-        <v>44.31431963823069</v>
+        <v>44.31432350323168</v>
       </c>
       <c r="D110" t="n">
-        <v>43.04545053203033</v>
+        <v>43.04545428636325</v>
       </c>
       <c r="E110" t="n">
-        <v>43.40111793330461</v>
+        <v>43.40112171865809</v>
       </c>
       <c r="F110" t="n">
         <v>1146163</v>
@@ -2732,16 +2732,16 @@
         <v>44321</v>
       </c>
       <c r="B116" t="n">
-        <v>39.74831390380859</v>
+        <v>39.74831008911133</v>
       </c>
       <c r="C116" t="n">
-        <v>40.64229060912697</v>
+        <v>40.6422867086336</v>
       </c>
       <c r="D116" t="n">
-        <v>39.0754291787498</v>
+        <v>39.07542542863015</v>
       </c>
       <c r="E116" t="n">
-        <v>39.89250188164586</v>
+        <v>39.89249805311069</v>
       </c>
       <c r="F116" t="n">
         <v>3650961</v>
@@ -2772,16 +2772,16 @@
         <v>44323</v>
       </c>
       <c r="B118" t="n">
-        <v>38.83510971069336</v>
+        <v>38.83511352539062</v>
       </c>
       <c r="C118" t="n">
-        <v>39.99824098294782</v>
+        <v>39.99824491189721</v>
       </c>
       <c r="D118" t="n">
-        <v>37.51817793834604</v>
+        <v>37.51818162368365</v>
       </c>
       <c r="E118" t="n">
-        <v>39.66179864141913</v>
+        <v>39.66180253732045</v>
       </c>
       <c r="F118" t="n">
         <v>2227429</v>
@@ -2832,16 +2832,16 @@
         <v>44328</v>
       </c>
       <c r="B121" t="n">
-        <v>37.05677032470703</v>
+        <v>37.05676651000977</v>
       </c>
       <c r="C121" t="n">
-        <v>38.70053196862062</v>
+        <v>38.70052798471127</v>
       </c>
       <c r="D121" t="n">
-        <v>37.05677032470703</v>
+        <v>37.05676651000977</v>
       </c>
       <c r="E121" t="n">
-        <v>37.8161715649591</v>
+        <v>37.81616767208757</v>
       </c>
       <c r="F121" t="n">
         <v>783049</v>
@@ -2892,16 +2892,16 @@
         <v>44333</v>
       </c>
       <c r="B124" t="n">
-        <v>36.43194580078125</v>
+        <v>36.43194961547852</v>
       </c>
       <c r="C124" t="n">
-        <v>37.13366805612294</v>
+        <v>37.13367194429578</v>
       </c>
       <c r="D124" t="n">
-        <v>35.93208669563144</v>
+        <v>35.93209045798972</v>
       </c>
       <c r="E124" t="n">
-        <v>36.52807111039643</v>
+        <v>36.52807493515874</v>
       </c>
       <c r="F124" t="n">
         <v>946466</v>
@@ -2912,16 +2912,16 @@
         <v>44334</v>
       </c>
       <c r="B125" t="n">
-        <v>35.14385604858398</v>
+        <v>35.14385223388672</v>
       </c>
       <c r="C125" t="n">
-        <v>36.91258445174329</v>
+        <v>36.91258044505902</v>
       </c>
       <c r="D125" t="n">
-        <v>34.59593422023043</v>
+        <v>34.59593046500746</v>
       </c>
       <c r="E125" t="n">
-        <v>36.52807567013412</v>
+        <v>36.52807170518645</v>
       </c>
       <c r="F125" t="n">
         <v>2070451</v>
@@ -2952,16 +2952,16 @@
         <v>44336</v>
       </c>
       <c r="B127" t="n">
-        <v>34.63438415527344</v>
+        <v>34.63438034057617</v>
       </c>
       <c r="C127" t="n">
-        <v>35.26881876953347</v>
+        <v>35.26881488495837</v>
       </c>
       <c r="D127" t="n">
-        <v>34.51903376998102</v>
+        <v>34.51902996798866</v>
       </c>
       <c r="E127" t="n">
-        <v>34.51903376998102</v>
+        <v>34.51902996798866</v>
       </c>
       <c r="F127" t="n">
         <v>943604</v>
@@ -3012,16 +3012,16 @@
         <v>44341</v>
       </c>
       <c r="B130" t="n">
-        <v>37.29708862304688</v>
+        <v>37.29708480834961</v>
       </c>
       <c r="C130" t="n">
-        <v>38.78704981148397</v>
+        <v>38.78704584439543</v>
       </c>
       <c r="D130" t="n">
-        <v>37.22980089947328</v>
+        <v>37.22979709165812</v>
       </c>
       <c r="E130" t="n">
-        <v>37.52779313716071</v>
+        <v>37.52778929886728</v>
       </c>
       <c r="F130" t="n">
         <v>1731150</v>
@@ -3092,16 +3092,16 @@
         <v>44347</v>
       </c>
       <c r="B134" t="n">
-        <v>39.38303375244141</v>
+        <v>39.38302993774414</v>
       </c>
       <c r="C134" t="n">
-        <v>40.11359366504992</v>
+        <v>40.11358977958957</v>
       </c>
       <c r="D134" t="n">
-        <v>39.02736632794579</v>
+        <v>39.02736254769899</v>
       </c>
       <c r="E134" t="n">
-        <v>39.39264628425005</v>
+        <v>39.3926424686217</v>
       </c>
       <c r="F134" t="n">
         <v>715598</v>
@@ -3192,16 +3192,16 @@
         <v>44355</v>
       </c>
       <c r="B139" t="n">
-        <v>38.4602165222168</v>
+        <v>38.46022033691406</v>
       </c>
       <c r="C139" t="n">
-        <v>38.85433404388245</v>
+        <v>38.85433789767048</v>
       </c>
       <c r="D139" t="n">
-        <v>37.72004038668688</v>
+        <v>37.72004412796937</v>
       </c>
       <c r="E139" t="n">
-        <v>38.43137892899068</v>
+        <v>38.43138274082768</v>
       </c>
       <c r="F139" t="n">
         <v>978352</v>
@@ -3212,16 +3212,16 @@
         <v>44356</v>
       </c>
       <c r="B140" t="n">
-        <v>38.01803588867188</v>
+        <v>38.01803207397461</v>
       </c>
       <c r="C140" t="n">
-        <v>38.66208302162527</v>
+        <v>38.66207914230487</v>
       </c>
       <c r="D140" t="n">
-        <v>37.29708850045856</v>
+        <v>37.29708475810054</v>
       </c>
       <c r="E140" t="n">
-        <v>38.48905744729046</v>
+        <v>38.48905358533129</v>
       </c>
       <c r="F140" t="n">
         <v>837521</v>
@@ -3332,16 +3332,16 @@
         <v>44364</v>
       </c>
       <c r="B146" t="n">
-        <v>42.4879150390625</v>
+        <v>42.48791885375977</v>
       </c>
       <c r="C146" t="n">
-        <v>44.0067136610316</v>
+        <v>44.00671761209134</v>
       </c>
       <c r="D146" t="n">
-        <v>41.62277601425852</v>
+        <v>41.62277975128091</v>
       </c>
       <c r="E146" t="n">
-        <v>42.95893654890009</v>
+        <v>42.95894040588714</v>
       </c>
       <c r="F146" t="n">
         <v>1582144</v>
@@ -3372,16 +3372,16 @@
         <v>44368</v>
       </c>
       <c r="B148" t="n">
-        <v>46.96741485595703</v>
+        <v>46.96741104125977</v>
       </c>
       <c r="C148" t="n">
-        <v>47.24618202489792</v>
+        <v>47.24617818755916</v>
       </c>
       <c r="D148" t="n">
-        <v>43.53569979030122</v>
+        <v>43.53569625432814</v>
       </c>
       <c r="E148" t="n">
-        <v>43.73756295749668</v>
+        <v>43.73755940512824</v>
       </c>
       <c r="F148" t="n">
         <v>2655439</v>
@@ -3452,16 +3452,16 @@
         <v>44372</v>
       </c>
       <c r="B152" t="n">
-        <v>44.45851135253906</v>
+        <v>44.45851516723633</v>
       </c>
       <c r="C152" t="n">
-        <v>44.98720431506052</v>
+        <v>44.9872081751215</v>
       </c>
       <c r="D152" t="n">
-        <v>43.97787729834627</v>
+        <v>43.97788107180344</v>
       </c>
       <c r="E152" t="n">
-        <v>44.98720431506052</v>
+        <v>44.9872081751215</v>
       </c>
       <c r="F152" t="n">
         <v>1347904</v>
@@ -3472,16 +3472,16 @@
         <v>44375</v>
       </c>
       <c r="B153" t="n">
-        <v>44.5354118347168</v>
+        <v>44.53541564941406</v>
       </c>
       <c r="C153" t="n">
-        <v>44.64114967825854</v>
+        <v>44.64115350201283</v>
       </c>
       <c r="D153" t="n">
-        <v>43.20886378695175</v>
+        <v>43.20886748802305</v>
       </c>
       <c r="E153" t="n">
-        <v>44.13168177543641</v>
+        <v>44.13168555555202</v>
       </c>
       <c r="F153" t="n">
         <v>1110393</v>
@@ -3512,16 +3512,16 @@
         <v>44377</v>
       </c>
       <c r="B155" t="n">
-        <v>43.58376312255859</v>
+        <v>43.58375930786133</v>
       </c>
       <c r="C155" t="n">
-        <v>44.45851476998166</v>
+        <v>44.45851087872119</v>
       </c>
       <c r="D155" t="n">
-        <v>43.50686286720073</v>
+        <v>43.50685905923421</v>
       </c>
       <c r="E155" t="n">
-        <v>44.21819772441255</v>
+        <v>44.21819385418598</v>
       </c>
       <c r="F155" t="n">
         <v>1274116</v>
@@ -3572,16 +3572,16 @@
         <v>44382</v>
       </c>
       <c r="B158" t="n">
-        <v>45.04488372802734</v>
+        <v>45.04488754272461</v>
       </c>
       <c r="C158" t="n">
-        <v>46.21762753484401</v>
+        <v>46.21763144885693</v>
       </c>
       <c r="D158" t="n">
-        <v>44.42967048319475</v>
+        <v>44.42967424579171</v>
       </c>
       <c r="E158" t="n">
-        <v>44.98720479275436</v>
+        <v>44.98720860256699</v>
       </c>
       <c r="F158" t="n">
         <v>3391068</v>
@@ -3592,16 +3592,16 @@
         <v>44383</v>
       </c>
       <c r="B159" t="n">
-        <v>44.37199401855469</v>
+        <v>44.37199783325195</v>
       </c>
       <c r="C159" t="n">
-        <v>45.94847158903642</v>
+        <v>45.94847553926477</v>
       </c>
       <c r="D159" t="n">
-        <v>43.75678453900221</v>
+        <v>43.75678830080941</v>
       </c>
       <c r="E159" t="n">
-        <v>45.7850548143543</v>
+        <v>45.78505875053358</v>
       </c>
       <c r="F159" t="n">
         <v>1563442</v>
@@ -3652,16 +3652,16 @@
         <v>44389</v>
       </c>
       <c r="B162" t="n">
-        <v>44.72766876220703</v>
+        <v>44.72766494750977</v>
       </c>
       <c r="C162" t="n">
-        <v>45.75622090541913</v>
+        <v>45.75621700299953</v>
       </c>
       <c r="D162" t="n">
-        <v>44.08361789020423</v>
+        <v>44.08361413043626</v>
       </c>
       <c r="E162" t="n">
-        <v>45.75622090541913</v>
+        <v>45.75621700299953</v>
       </c>
       <c r="F162" t="n">
         <v>1597780</v>
@@ -3732,16 +3732,16 @@
         <v>44393</v>
       </c>
       <c r="B166" t="n">
-        <v>41.70928955078125</v>
+        <v>41.70929336547852</v>
       </c>
       <c r="C166" t="n">
-        <v>41.91115645117827</v>
+        <v>41.91116028433812</v>
       </c>
       <c r="D166" t="n">
-        <v>40.45003298811638</v>
+        <v>40.45003668764308</v>
       </c>
       <c r="E166" t="n">
-        <v>41.62277677100059</v>
+        <v>41.62278057778546</v>
       </c>
       <c r="F166" t="n">
         <v>1471156</v>
@@ -3752,16 +3752,16 @@
         <v>44396</v>
       </c>
       <c r="B167" t="n">
-        <v>40.22894287109375</v>
+        <v>40.22894668579102</v>
       </c>
       <c r="C167" t="n">
-        <v>41.05562800061862</v>
+        <v>41.05563189370605</v>
       </c>
       <c r="D167" t="n">
-        <v>39.50799183094843</v>
+        <v>39.50799557728174</v>
       </c>
       <c r="E167" t="n">
-        <v>40.46925613690023</v>
+        <v>40.46925997438512</v>
       </c>
       <c r="F167" t="n">
         <v>1632835</v>
@@ -3792,16 +3792,16 @@
         <v>44398</v>
       </c>
       <c r="B169" t="n">
-        <v>40.45964431762695</v>
+        <v>40.45964813232422</v>
       </c>
       <c r="C169" t="n">
-        <v>41.40168732645247</v>
+        <v>41.40169122996932</v>
       </c>
       <c r="D169" t="n">
-        <v>40.22894357839657</v>
+        <v>40.22894737134245</v>
       </c>
       <c r="E169" t="n">
-        <v>40.37313154041556</v>
+        <v>40.37313534695605</v>
       </c>
       <c r="F169" t="n">
         <v>985812</v>
@@ -3812,16 +3812,16 @@
         <v>44399</v>
       </c>
       <c r="B170" t="n">
-        <v>40.89221954345703</v>
+        <v>40.89221572875977</v>
       </c>
       <c r="C170" t="n">
-        <v>41.15176164706832</v>
+        <v>41.15175780815924</v>
       </c>
       <c r="D170" t="n">
-        <v>40.3923603996445</v>
+        <v>40.39235663157741</v>
       </c>
       <c r="E170" t="n">
-        <v>41.08447017755746</v>
+        <v>41.08446634492577</v>
       </c>
       <c r="F170" t="n">
         <v>757704</v>
@@ -3832,16 +3832,16 @@
         <v>44400</v>
       </c>
       <c r="B171" t="n">
-        <v>40.56538772583008</v>
+        <v>40.56539154052734</v>
       </c>
       <c r="C171" t="n">
-        <v>40.86337994162768</v>
+        <v>40.8633837843476</v>
       </c>
       <c r="D171" t="n">
-        <v>40.20010404382616</v>
+        <v>40.20010782417279</v>
       </c>
       <c r="E171" t="n">
-        <v>40.6230629132279</v>
+        <v>40.62306673334884</v>
       </c>
       <c r="F171" t="n">
         <v>715496</v>
@@ -3872,16 +3872,16 @@
         <v>44404</v>
       </c>
       <c r="B173" t="n">
-        <v>38.54673004150391</v>
+        <v>38.54673385620117</v>
       </c>
       <c r="C173" t="n">
-        <v>40.84415499320262</v>
+        <v>40.84415903525979</v>
       </c>
       <c r="D173" t="n">
-        <v>38.32563807495276</v>
+        <v>38.32564186777011</v>
       </c>
       <c r="E173" t="n">
-        <v>40.62306302665147</v>
+        <v>40.62306704682872</v>
       </c>
       <c r="F173" t="n">
         <v>1543819</v>
@@ -3932,16 +3932,16 @@
         <v>44407</v>
       </c>
       <c r="B176" t="n">
-        <v>37.2105712890625</v>
+        <v>37.21057510375977</v>
       </c>
       <c r="C176" t="n">
-        <v>38.26796091589321</v>
+        <v>38.26796483899034</v>
       </c>
       <c r="D176" t="n">
-        <v>36.33581974675896</v>
+        <v>36.33582347177977</v>
       </c>
       <c r="E176" t="n">
-        <v>37.5662386749276</v>
+        <v>37.56624252608663</v>
       </c>
       <c r="F176" t="n">
         <v>1168442</v>
@@ -3952,16 +3952,16 @@
         <v>44410</v>
       </c>
       <c r="B177" t="n">
-        <v>39.04658889770508</v>
+        <v>39.04659271240234</v>
       </c>
       <c r="C177" t="n">
-        <v>40.3442955992922</v>
+        <v>40.34429954077027</v>
       </c>
       <c r="D177" t="n">
-        <v>38.19106237864987</v>
+        <v>38.19106610976557</v>
       </c>
       <c r="E177" t="n">
-        <v>39.17155180323623</v>
+        <v>39.17155563014188</v>
       </c>
       <c r="F177" t="n">
         <v>3352028</v>
@@ -4052,16 +4052,16 @@
         <v>44417</v>
       </c>
       <c r="B182" t="n">
-        <v>37.10483169555664</v>
+        <v>37.10483551025391</v>
       </c>
       <c r="C182" t="n">
-        <v>37.44127403795907</v>
+        <v>37.44127788724551</v>
       </c>
       <c r="D182" t="n">
-        <v>35.94170042028153</v>
+        <v>35.94170411539885</v>
       </c>
       <c r="E182" t="n">
-        <v>36.1147297309109</v>
+        <v>36.11473344381713</v>
       </c>
       <c r="F182" t="n">
         <v>1206460</v>
@@ -4092,16 +4092,16 @@
         <v>44419</v>
       </c>
       <c r="B184" t="n">
-        <v>36.43194580078125</v>
+        <v>36.43194961547852</v>
       </c>
       <c r="C184" t="n">
-        <v>36.74916307008678</v>
+        <v>36.74916691799907</v>
       </c>
       <c r="D184" t="n">
-        <v>36.09550346955268</v>
+        <v>36.09550724902192</v>
       </c>
       <c r="E184" t="n">
-        <v>36.47039592462733</v>
+        <v>36.4703997433506</v>
       </c>
       <c r="F184" t="n">
         <v>786524</v>
@@ -4112,16 +4112,16 @@
         <v>44420</v>
       </c>
       <c r="B185" t="n">
-        <v>36.12434387207031</v>
+        <v>36.12434005737305</v>
       </c>
       <c r="C185" t="n">
-        <v>36.95103284178433</v>
+        <v>36.95102893978947</v>
       </c>
       <c r="D185" t="n">
-        <v>35.4706842206967</v>
+        <v>35.47068047502529</v>
       </c>
       <c r="E185" t="n">
-        <v>36.19163159403436</v>
+        <v>36.19162777223157</v>
       </c>
       <c r="F185" t="n">
         <v>689639</v>
@@ -4132,16 +4132,16 @@
         <v>44421</v>
       </c>
       <c r="B186" t="n">
-        <v>34.75934219360352</v>
+        <v>34.75934600830078</v>
       </c>
       <c r="C186" t="n">
-        <v>35.97053605946554</v>
+        <v>35.97054000708643</v>
       </c>
       <c r="D186" t="n">
-        <v>34.59592917071041</v>
+        <v>34.59593296747376</v>
       </c>
       <c r="E186" t="n">
-        <v>35.69177266747142</v>
+        <v>35.69177658449917</v>
       </c>
       <c r="F186" t="n">
         <v>915908</v>
@@ -4252,16 +4252,16 @@
         <v>44431</v>
       </c>
       <c r="B192" t="n">
-        <v>33.16364288330078</v>
+        <v>33.16364669799805</v>
       </c>
       <c r="C192" t="n">
-        <v>34.42289938524034</v>
+        <v>34.42290334478545</v>
       </c>
       <c r="D192" t="n">
-        <v>32.77913791079774</v>
+        <v>32.77914168126674</v>
       </c>
       <c r="E192" t="n">
-        <v>33.740402215843</v>
+        <v>33.74040609688286</v>
       </c>
       <c r="F192" t="n">
         <v>2084044</v>
@@ -4272,16 +4272,16 @@
         <v>44432</v>
       </c>
       <c r="B193" t="n">
-        <v>35.43223571777344</v>
+        <v>35.43223190307617</v>
       </c>
       <c r="C193" t="n">
-        <v>35.43223571777344</v>
+        <v>35.43223190307617</v>
       </c>
       <c r="D193" t="n">
-        <v>33.47125292620207</v>
+        <v>33.47124932262768</v>
       </c>
       <c r="E193" t="n">
-        <v>33.93266196453976</v>
+        <v>33.93265831128927</v>
       </c>
       <c r="F193" t="n">
         <v>1429663</v>
@@ -4332,16 +4332,16 @@
         <v>44435</v>
       </c>
       <c r="B196" t="n">
-        <v>36.43194580078125</v>
+        <v>36.43194961547852</v>
       </c>
       <c r="C196" t="n">
-        <v>36.66265029143312</v>
+        <v>36.66265413028687</v>
       </c>
       <c r="D196" t="n">
-        <v>35.02849754252244</v>
+        <v>35.02850121026817</v>
       </c>
       <c r="E196" t="n">
-        <v>35.75906113832411</v>
+        <v>35.75906488256532</v>
       </c>
       <c r="F196" t="n">
         <v>2701327</v>
@@ -4392,16 +4392,16 @@
         <v>44440</v>
       </c>
       <c r="B199" t="n">
-        <v>36.00899124145508</v>
+        <v>36.00899505615234</v>
       </c>
       <c r="C199" t="n">
-        <v>37.22979768253502</v>
+        <v>37.2298016265613</v>
       </c>
       <c r="D199" t="n">
-        <v>35.47068200422877</v>
+        <v>35.47068576189898</v>
       </c>
       <c r="E199" t="n">
-        <v>37.10483103054919</v>
+        <v>37.10483496133683</v>
       </c>
       <c r="F199" t="n">
         <v>1150659</v>
@@ -4712,16 +4712,16 @@
         <v>44463</v>
       </c>
       <c r="B215" t="n">
-        <v>34.54786682128906</v>
+        <v>34.54787063598633</v>
       </c>
       <c r="C215" t="n">
-        <v>35.65331911097231</v>
+        <v>35.65332304773112</v>
       </c>
       <c r="D215" t="n">
-        <v>33.88459095038866</v>
+        <v>33.88459469184851</v>
       </c>
       <c r="E215" t="n">
-        <v>34.46135404370111</v>
+        <v>34.46135784884584</v>
       </c>
       <c r="F215" t="n">
         <v>2639905</v>
@@ -4852,16 +4852,16 @@
         <v>44474</v>
       </c>
       <c r="B222" t="n">
-        <v>41.23827362060547</v>
+        <v>41.2382698059082</v>
       </c>
       <c r="C222" t="n">
-        <v>43.07428962557536</v>
+        <v>43.07428564103963</v>
       </c>
       <c r="D222" t="n">
-        <v>40.9498939275561</v>
+        <v>40.94989013953506</v>
       </c>
       <c r="E222" t="n">
-        <v>41.82464553821999</v>
+        <v>41.82464166928109</v>
       </c>
       <c r="F222" t="n">
         <v>3033780</v>
@@ -4952,16 +4952,16 @@
         <v>44482</v>
       </c>
       <c r="B227" t="n">
-        <v>39.66179656982422</v>
+        <v>39.66180038452148</v>
       </c>
       <c r="C227" t="n">
-        <v>40.05591407830239</v>
+        <v>40.05591793090613</v>
       </c>
       <c r="D227" t="n">
-        <v>38.88317033604628</v>
+        <v>38.88317407585477</v>
       </c>
       <c r="E227" t="n">
-        <v>39.43109208415942</v>
+        <v>39.43109587666738</v>
       </c>
       <c r="F227" t="n">
         <v>1130628</v>
@@ -5012,16 +5012,16 @@
         <v>44487</v>
       </c>
       <c r="B230" t="n">
-        <v>39.87327194213867</v>
+        <v>39.87327575683594</v>
       </c>
       <c r="C230" t="n">
-        <v>41.44974945917212</v>
+        <v>41.44975342469183</v>
       </c>
       <c r="D230" t="n">
-        <v>39.18116223800101</v>
+        <v>39.18116598648377</v>
       </c>
       <c r="E230" t="n">
-        <v>39.72908398193304</v>
+        <v>39.72908778283576</v>
       </c>
       <c r="F230" t="n">
         <v>2573169</v>
@@ -5032,16 +5032,16 @@
         <v>44488</v>
       </c>
       <c r="B231" t="n">
-        <v>37.58546447753906</v>
+        <v>37.58546829223633</v>
       </c>
       <c r="C231" t="n">
-        <v>40.08475250621378</v>
+        <v>40.08475657457366</v>
       </c>
       <c r="D231" t="n">
-        <v>36.86451716082918</v>
+        <v>36.86452090235465</v>
       </c>
       <c r="E231" t="n">
-        <v>39.57528087049455</v>
+        <v>39.57528488714614</v>
       </c>
       <c r="F231" t="n">
         <v>2915331</v>
@@ -5072,16 +5072,16 @@
         <v>44490</v>
       </c>
       <c r="B233" t="n">
-        <v>34.41328811645508</v>
+        <v>34.41329193115234</v>
       </c>
       <c r="C233" t="n">
-        <v>36.09550352264783</v>
+        <v>36.09550752381791</v>
       </c>
       <c r="D233" t="n">
-        <v>33.48086136908995</v>
+        <v>33.48086508042814</v>
       </c>
       <c r="E233" t="n">
-        <v>35.62448200968972</v>
+        <v>35.62448595864728</v>
       </c>
       <c r="F233" t="n">
         <v>3113087</v>
@@ -5092,16 +5092,16 @@
         <v>44491</v>
       </c>
       <c r="B234" t="n">
-        <v>32.63494873046875</v>
+        <v>32.63495254516602</v>
       </c>
       <c r="C234" t="n">
-        <v>34.06723464208851</v>
+        <v>34.06723862420559</v>
       </c>
       <c r="D234" t="n">
-        <v>31.04886231697067</v>
+        <v>31.04886594627039</v>
       </c>
       <c r="E234" t="n">
-        <v>33.63466698298016</v>
+        <v>33.63467091453443</v>
       </c>
       <c r="F234" t="n">
         <v>4894520</v>
@@ -5112,16 +5112,16 @@
         <v>44494</v>
       </c>
       <c r="B235" t="n">
-        <v>36.8470573425293</v>
+        <v>36.84706115722656</v>
       </c>
       <c r="C235" t="n">
-        <v>37.3112732591762</v>
+        <v>37.31127712193275</v>
       </c>
       <c r="D235" t="n">
-        <v>32.95925887799699</v>
+        <v>32.95926229019877</v>
       </c>
       <c r="E235" t="n">
-        <v>32.95925887799699</v>
+        <v>32.95926229019877</v>
       </c>
       <c r="F235" t="n">
         <v>3449995</v>
@@ -5152,16 +5152,16 @@
         <v>44496</v>
       </c>
       <c r="B237" t="n">
-        <v>35.29000854492188</v>
+        <v>35.29000473022461</v>
       </c>
       <c r="C237" t="n">
-        <v>36.07337184605893</v>
+        <v>36.07336794668348</v>
       </c>
       <c r="D237" t="n">
-        <v>34.47763151058894</v>
+        <v>34.47762778370612</v>
       </c>
       <c r="E237" t="n">
-        <v>36.07337184605893</v>
+        <v>36.07336794668348</v>
       </c>
       <c r="F237" t="n">
         <v>2270538</v>
@@ -5272,16 +5272,16 @@
         <v>44505</v>
       </c>
       <c r="B243" t="n">
-        <v>34.33255767822266</v>
+        <v>34.33256149291992</v>
       </c>
       <c r="C243" t="n">
-        <v>35.80257411368536</v>
+        <v>35.80257809171644</v>
       </c>
       <c r="D243" t="n">
-        <v>31.73102080869616</v>
+        <v>31.73102433433615</v>
       </c>
       <c r="E243" t="n">
-        <v>33.17202351532898</v>
+        <v>33.17202720107906</v>
       </c>
       <c r="F243" t="n">
         <v>9166770</v>
@@ -5312,16 +5312,16 @@
         <v>44509</v>
       </c>
       <c r="B245" t="n">
-        <v>34.50664138793945</v>
+        <v>34.50664520263672</v>
       </c>
       <c r="C245" t="n">
-        <v>35.1062534768846</v>
+        <v>35.10625735786877</v>
       </c>
       <c r="D245" t="n">
-        <v>32.63044017132788</v>
+        <v>32.63044377861175</v>
       </c>
       <c r="E245" t="n">
-        <v>33.89736055406007</v>
+        <v>33.89736430140155</v>
       </c>
       <c r="F245" t="n">
         <v>7032350</v>
@@ -5372,16 +5372,16 @@
         <v>44512</v>
       </c>
       <c r="B248" t="n">
-        <v>30.94766044616699</v>
+        <v>30.94766235351562</v>
       </c>
       <c r="C248" t="n">
-        <v>33.11399707089411</v>
+        <v>33.11399911175717</v>
       </c>
       <c r="D248" t="n">
-        <v>30.69620937113922</v>
+        <v>30.69621126299056</v>
       </c>
       <c r="E248" t="n">
-        <v>32.10819651835855</v>
+        <v>32.10819849723269</v>
       </c>
       <c r="F248" t="n">
         <v>3403064</v>
@@ -5552,16 +5552,16 @@
         <v>44526</v>
       </c>
       <c r="B257" t="n">
-        <v>26.69235801696777</v>
+        <v>26.69235992431641</v>
       </c>
       <c r="C257" t="n">
-        <v>27.61111551515892</v>
+        <v>27.61111748815896</v>
       </c>
       <c r="D257" t="n">
-        <v>25.85096734243463</v>
+        <v>25.85096918966023</v>
       </c>
       <c r="E257" t="n">
-        <v>26.59564620826666</v>
+        <v>26.59564810870458</v>
       </c>
       <c r="F257" t="n">
         <v>3664026</v>
@@ -5592,16 +5592,16 @@
         <v>44530</v>
       </c>
       <c r="B259" t="n">
-        <v>26.71169853210449</v>
+        <v>26.71170043945312</v>
       </c>
       <c r="C259" t="n">
-        <v>26.71169853210449</v>
+        <v>26.71170043945312</v>
       </c>
       <c r="D259" t="n">
-        <v>25.48346440355603</v>
+        <v>25.48346622320262</v>
       </c>
       <c r="E259" t="n">
-        <v>26.53761803066504</v>
+        <v>26.53761992558345</v>
       </c>
       <c r="F259" t="n">
         <v>4757647</v>
@@ -5612,16 +5612,16 @@
         <v>44531</v>
       </c>
       <c r="B260" t="n">
-        <v>26.69235801696777</v>
+        <v>26.69235992431641</v>
       </c>
       <c r="C260" t="n">
-        <v>28.01730398743094</v>
+        <v>28.01730598945588</v>
       </c>
       <c r="D260" t="n">
-        <v>26.32485389341864</v>
+        <v>26.32485577450663</v>
       </c>
       <c r="E260" t="n">
-        <v>27.17591518668557</v>
+        <v>27.17591712858762</v>
       </c>
       <c r="F260" t="n">
         <v>3467467</v>
@@ -5752,16 +5752,16 @@
         <v>44540</v>
       </c>
       <c r="B267" t="n">
-        <v>29.43896293640137</v>
+        <v>29.43896102905273</v>
       </c>
       <c r="C267" t="n">
-        <v>29.76778272429381</v>
+        <v>29.76778079564096</v>
       </c>
       <c r="D267" t="n">
-        <v>28.76198212238038</v>
+        <v>28.76198025889329</v>
       </c>
       <c r="E267" t="n">
-        <v>29.57435909920557</v>
+        <v>29.57435718308462</v>
       </c>
       <c r="F267" t="n">
         <v>1281952</v>
@@ -5832,16 +5832,16 @@
         <v>44546</v>
       </c>
       <c r="B271" t="n">
-        <v>30.62851333618164</v>
+        <v>30.62851524353027</v>
       </c>
       <c r="C271" t="n">
-        <v>30.86062130141829</v>
+        <v>30.86062322322113</v>
       </c>
       <c r="D271" t="n">
-        <v>29.25521052973079</v>
+        <v>29.25521235155887</v>
       </c>
       <c r="E271" t="n">
-        <v>29.4969891136642</v>
+        <v>29.49699095054871</v>
       </c>
       <c r="F271" t="n">
         <v>3477726</v>
@@ -5952,16 +5952,16 @@
         <v>44557</v>
       </c>
       <c r="B277" t="n">
-        <v>30.72522354125977</v>
+        <v>30.7252254486084</v>
       </c>
       <c r="C277" t="n">
-        <v>31.01535896880716</v>
+        <v>31.01536089416671</v>
       </c>
       <c r="D277" t="n">
-        <v>29.98054654550914</v>
+        <v>29.98054840663</v>
       </c>
       <c r="E277" t="n">
-        <v>29.98054654550914</v>
+        <v>29.98054840663</v>
       </c>
       <c r="F277" t="n">
         <v>1273927</v>
@@ -6132,16 +6132,16 @@
         <v>44571</v>
       </c>
       <c r="B286" t="n">
-        <v>33.37511444091797</v>
+        <v>33.37511825561523</v>
       </c>
       <c r="C286" t="n">
-        <v>33.89735778992546</v>
+        <v>33.89736166431392</v>
       </c>
       <c r="D286" t="n">
-        <v>32.24359030771443</v>
+        <v>32.24359399308115</v>
       </c>
       <c r="E286" t="n">
-        <v>32.37898645393302</v>
+        <v>32.3789901547752</v>
       </c>
       <c r="F286" t="n">
         <v>2829132</v>
@@ -6152,16 +6152,16 @@
         <v>44572</v>
       </c>
       <c r="B287" t="n">
-        <v>35.10625457763672</v>
+        <v>35.10625076293945</v>
       </c>
       <c r="C287" t="n">
-        <v>35.63816673084244</v>
+        <v>35.63816285834681</v>
       </c>
       <c r="D287" t="n">
-        <v>33.18169458570739</v>
+        <v>33.18169098013564</v>
       </c>
       <c r="E287" t="n">
-        <v>33.55886933935793</v>
+        <v>33.55886569280182</v>
       </c>
       <c r="F287" t="n">
         <v>3953735</v>
@@ -6172,16 +6172,16 @@
         <v>44573</v>
       </c>
       <c r="B288" t="n">
-        <v>34.89348983764648</v>
+        <v>34.89348602294922</v>
       </c>
       <c r="C288" t="n">
-        <v>35.98632787872025</v>
+        <v>35.98632394454952</v>
       </c>
       <c r="D288" t="n">
-        <v>34.13914032772324</v>
+        <v>34.13913659549451</v>
       </c>
       <c r="E288" t="n">
-        <v>35.34803329265463</v>
+        <v>35.34802942826484</v>
       </c>
       <c r="F288" t="n">
         <v>3302601</v>
@@ -6292,16 +6292,16 @@
         <v>44581</v>
       </c>
       <c r="B294" t="n">
-        <v>35.29967498779297</v>
+        <v>35.2996711730957</v>
       </c>
       <c r="C294" t="n">
-        <v>36.17007943172774</v>
+        <v>36.17007552296929</v>
       </c>
       <c r="D294" t="n">
-        <v>34.98052769103708</v>
+        <v>34.98052391082881</v>
       </c>
       <c r="E294" t="n">
-        <v>35.87027337331519</v>
+        <v>35.8702694969556</v>
       </c>
       <c r="F294" t="n">
         <v>3650414</v>
@@ -6332,16 +6332,16 @@
         <v>44585</v>
       </c>
       <c r="B296" t="n">
-        <v>34.35190200805664</v>
+        <v>34.35190582275391</v>
       </c>
       <c r="C296" t="n">
-        <v>35.3190162904272</v>
+        <v>35.31902021252021</v>
       </c>
       <c r="D296" t="n">
-        <v>34.05209598090971</v>
+        <v>34.05209976231423</v>
       </c>
       <c r="E296" t="n">
-        <v>34.23584709494806</v>
+        <v>34.2358508967577</v>
       </c>
       <c r="F296" t="n">
         <v>2113697</v>
@@ -6392,16 +6392,16 @@
         <v>44588</v>
       </c>
       <c r="B299" t="n">
-        <v>36.09271240234375</v>
+        <v>36.09270858764648</v>
       </c>
       <c r="C299" t="n">
-        <v>37.1081818022467</v>
+        <v>37.10817788022283</v>
       </c>
       <c r="D299" t="n">
-        <v>35.68652389286739</v>
+        <v>35.68652012110085</v>
       </c>
       <c r="E299" t="n">
-        <v>35.87994752798603</v>
+        <v>35.87994373577622</v>
       </c>
       <c r="F299" t="n">
         <v>3171460</v>
@@ -6492,16 +6492,16 @@
         <v>44595</v>
       </c>
       <c r="B304" t="n">
-        <v>35.29967498779297</v>
+        <v>35.2996711730957</v>
       </c>
       <c r="C304" t="n">
-        <v>35.58981230082171</v>
+        <v>35.58980845477045</v>
       </c>
       <c r="D304" t="n">
-        <v>33.84900341295216</v>
+        <v>33.84899975502328</v>
       </c>
       <c r="E304" t="n">
-        <v>34.98052769103708</v>
+        <v>34.98052391082881</v>
       </c>
       <c r="F304" t="n">
         <v>4177823</v>
@@ -6592,16 +6592,16 @@
         <v>44602</v>
       </c>
       <c r="B309" t="n">
-        <v>37.28226470947266</v>
+        <v>37.28226089477539</v>
       </c>
       <c r="C309" t="n">
-        <v>38.3847753224369</v>
+        <v>38.38477139493146</v>
       </c>
       <c r="D309" t="n">
-        <v>36.33449150769526</v>
+        <v>36.33448778997354</v>
       </c>
       <c r="E309" t="n">
-        <v>36.36350524073979</v>
+        <v>36.3635015200494</v>
       </c>
       <c r="F309" t="n">
         <v>7025951</v>
@@ -6612,16 +6612,16 @@
         <v>44603</v>
       </c>
       <c r="B310" t="n">
-        <v>38.07529067993164</v>
+        <v>38.07529449462891</v>
       </c>
       <c r="C310" t="n">
-        <v>38.49115162219439</v>
+        <v>38.49115547855604</v>
       </c>
       <c r="D310" t="n">
-        <v>37.37896869306991</v>
+        <v>37.37897243800389</v>
       </c>
       <c r="E310" t="n">
-        <v>37.78515714333515</v>
+        <v>37.78516092896444</v>
       </c>
       <c r="F310" t="n">
         <v>5486491</v>
@@ -6632,16 +6632,16 @@
         <v>44606</v>
       </c>
       <c r="B311" t="n">
-        <v>37.57239151000977</v>
+        <v>37.57239532470703</v>
       </c>
       <c r="C311" t="n">
-        <v>38.84898429079868</v>
+        <v>38.84898823510746</v>
       </c>
       <c r="D311" t="n">
-        <v>36.95343822941596</v>
+        <v>36.95344198127135</v>
       </c>
       <c r="E311" t="n">
-        <v>38.29772721003804</v>
+        <v>38.2977310983781</v>
       </c>
       <c r="F311" t="n">
         <v>3902640</v>
@@ -6652,16 +6652,16 @@
         <v>44607</v>
       </c>
       <c r="B312" t="n">
-        <v>35.79290008544922</v>
+        <v>35.79290390014648</v>
       </c>
       <c r="C312" t="n">
-        <v>36.65363192612031</v>
+        <v>36.65363583255173</v>
       </c>
       <c r="D312" t="n">
-        <v>35.63816270338088</v>
+        <v>35.63816650158672</v>
       </c>
       <c r="E312" t="n">
-        <v>36.55692199922141</v>
+        <v>36.55692589534578</v>
       </c>
       <c r="F312" t="n">
         <v>3810709</v>
@@ -6672,16 +6672,16 @@
         <v>44608</v>
       </c>
       <c r="B313" t="n">
-        <v>35.92830276489258</v>
+        <v>35.92829895019531</v>
       </c>
       <c r="C313" t="n">
-        <v>36.80837600146183</v>
+        <v>36.80837209332255</v>
       </c>
       <c r="D313" t="n">
-        <v>35.69619664958365</v>
+        <v>35.69619285953032</v>
       </c>
       <c r="E313" t="n">
-        <v>36.44087371532872</v>
+        <v>36.4408698462091</v>
       </c>
       <c r="F313" t="n">
         <v>4244663</v>
@@ -6692,16 +6692,16 @@
         <v>44609</v>
       </c>
       <c r="B314" t="n">
-        <v>35.29967498779297</v>
+        <v>35.2996711730957</v>
       </c>
       <c r="C314" t="n">
-        <v>35.89928710461807</v>
+        <v>35.89928322512308</v>
       </c>
       <c r="D314" t="n">
-        <v>34.41960179847439</v>
+        <v>34.41959807888318</v>
       </c>
       <c r="E314" t="n">
-        <v>35.68652224011414</v>
+        <v>35.68651838361181</v>
       </c>
       <c r="F314" t="n">
         <v>4430658</v>
@@ -6712,16 +6712,16 @@
         <v>44610</v>
       </c>
       <c r="B315" t="n">
-        <v>34.48730087280273</v>
+        <v>34.48729705810547</v>
       </c>
       <c r="C315" t="n">
-        <v>35.41572900804387</v>
+        <v>35.41572509065163</v>
       </c>
       <c r="D315" t="n">
-        <v>33.80064757961473</v>
+        <v>33.80064384086931</v>
       </c>
       <c r="E315" t="n">
-        <v>34.83546189196511</v>
+        <v>34.83545803875718</v>
       </c>
       <c r="F315" t="n">
         <v>4069741</v>
@@ -6852,16 +6852,16 @@
         <v>44623</v>
       </c>
       <c r="B322" t="n">
-        <v>37.34028625488281</v>
+        <v>37.34028244018555</v>
       </c>
       <c r="C322" t="n">
-        <v>37.88187465766974</v>
+        <v>37.88187078764361</v>
       </c>
       <c r="D322" t="n">
-        <v>36.31514815474819</v>
+        <v>36.31514444477941</v>
       </c>
       <c r="E322" t="n">
-        <v>37.12752138998924</v>
+        <v>37.12751759702811</v>
       </c>
       <c r="F322" t="n">
         <v>9786414</v>
@@ -6892,16 +6892,16 @@
         <v>44627</v>
       </c>
       <c r="B324" t="n">
-        <v>37.04048156738281</v>
+        <v>37.04048538208008</v>
       </c>
       <c r="C324" t="n">
-        <v>39.28418499781101</v>
+        <v>39.28418904358112</v>
       </c>
       <c r="D324" t="n">
-        <v>36.65363433916909</v>
+        <v>36.65363811402602</v>
       </c>
       <c r="E324" t="n">
-        <v>38.17200577495368</v>
+        <v>38.17200970618351</v>
       </c>
       <c r="F324" t="n">
         <v>5025922</v>
@@ -6952,16 +6952,16 @@
         <v>44630</v>
       </c>
       <c r="B327" t="n">
-        <v>35.7252082824707</v>
+        <v>35.72520446777344</v>
       </c>
       <c r="C327" t="n">
-        <v>37.22423481932497</v>
+        <v>37.22423084456335</v>
       </c>
       <c r="D327" t="n">
-        <v>35.51244341905014</v>
+        <v>35.51243962707166</v>
       </c>
       <c r="E327" t="n">
-        <v>36.75034637550812</v>
+        <v>36.75034245134777</v>
       </c>
       <c r="F327" t="n">
         <v>4502679</v>
@@ -7032,16 +7032,16 @@
         <v>44636</v>
       </c>
       <c r="B331" t="n">
-        <v>32.84320449829102</v>
+        <v>32.84320831298828</v>
       </c>
       <c r="C331" t="n">
-        <v>34.44861337459189</v>
+        <v>34.44861737575539</v>
       </c>
       <c r="D331" t="n">
-        <v>32.34030609979657</v>
+        <v>32.34030985608281</v>
       </c>
       <c r="E331" t="n">
-        <v>34.10045236831488</v>
+        <v>34.10045632903992</v>
       </c>
       <c r="F331" t="n">
         <v>3899288</v>
@@ -7092,16 +7092,16 @@
         <v>44641</v>
       </c>
       <c r="B334" t="n">
-        <v>36.61494827270508</v>
+        <v>36.61495208740234</v>
       </c>
       <c r="C334" t="n">
-        <v>36.86639934686866</v>
+        <v>36.86640318776314</v>
       </c>
       <c r="D334" t="n">
-        <v>35.88961252740777</v>
+        <v>35.88961626653654</v>
       </c>
       <c r="E334" t="n">
-        <v>35.97665371626157</v>
+        <v>35.97665746445866</v>
       </c>
       <c r="F334" t="n">
         <v>3600944</v>
@@ -7212,16 +7212,16 @@
         <v>44649</v>
       </c>
       <c r="B340" t="n">
-        <v>40.11590194702148</v>
+        <v>40.11590576171875</v>
       </c>
       <c r="C340" t="n">
-        <v>40.60913158587444</v>
+        <v>40.60913544747385</v>
       </c>
       <c r="D340" t="n">
-        <v>37.81417112752509</v>
+        <v>37.8141747233464</v>
       </c>
       <c r="E340" t="n">
-        <v>38.00759473575618</v>
+        <v>38.00759834997051</v>
       </c>
       <c r="F340" t="n">
         <v>6952609</v>
@@ -7252,16 +7252,16 @@
         <v>44651</v>
       </c>
       <c r="B342" t="n">
-        <v>40.47373962402344</v>
+        <v>40.47373580932617</v>
       </c>
       <c r="C342" t="n">
-        <v>41.13137921056172</v>
+        <v>41.13137533388116</v>
       </c>
       <c r="D342" t="n">
-        <v>39.67103512697872</v>
+        <v>39.6710313879373</v>
       </c>
       <c r="E342" t="n">
-        <v>40.135251085266</v>
+        <v>40.13524730247168</v>
       </c>
       <c r="F342" t="n">
         <v>3810811</v>
@@ -7312,16 +7312,16 @@
         <v>44656</v>
       </c>
       <c r="B345" t="n">
-        <v>41.97276306152344</v>
+        <v>41.9727668762207</v>
       </c>
       <c r="C345" t="n">
-        <v>43.03659106395681</v>
+        <v>43.03659497534015</v>
       </c>
       <c r="D345" t="n">
-        <v>41.57624708903781</v>
+        <v>41.5762508676977</v>
       </c>
       <c r="E345" t="n">
-        <v>42.30158283032514</v>
+        <v>42.30158667490721</v>
       </c>
       <c r="F345" t="n">
         <v>5903074</v>
@@ -7432,16 +7432,16 @@
         <v>44664</v>
       </c>
       <c r="B351" t="n">
-        <v>43.62652969360352</v>
+        <v>43.62653350830078</v>
       </c>
       <c r="C351" t="n">
-        <v>43.71356713249195</v>
+        <v>43.71357095479976</v>
       </c>
       <c r="D351" t="n">
-        <v>42.8431665105797</v>
+        <v>42.8431702567798</v>
       </c>
       <c r="E351" t="n">
-        <v>43.30738242414481</v>
+        <v>43.30738621093589</v>
       </c>
       <c r="F351" t="n">
         <v>3238402</v>
@@ -7452,16 +7452,16 @@
         <v>44665</v>
       </c>
       <c r="B352" t="n">
-        <v>42.93988037109375</v>
+        <v>42.93987655639648</v>
       </c>
       <c r="C352" t="n">
-        <v>43.62653368593358</v>
+        <v>43.62652981023535</v>
       </c>
       <c r="D352" t="n">
-        <v>42.2242170723533</v>
+        <v>42.2242133212342</v>
       </c>
       <c r="E352" t="n">
-        <v>43.62653368593358</v>
+        <v>43.62652981023535</v>
       </c>
       <c r="F352" t="n">
         <v>2345809</v>
@@ -7552,16 +7552,16 @@
         <v>44676</v>
       </c>
       <c r="B357" t="n">
-        <v>41.94375228881836</v>
+        <v>41.94374847412109</v>
       </c>
       <c r="C357" t="n">
-        <v>42.40796824528748</v>
+        <v>42.40796438837074</v>
       </c>
       <c r="D357" t="n">
-        <v>40.64782185452133</v>
+        <v>40.64781815768625</v>
       </c>
       <c r="E357" t="n">
-        <v>40.75420428750637</v>
+        <v>40.75420058099602</v>
       </c>
       <c r="F357" t="n">
         <v>3287465</v>
@@ -7592,16 +7592,16 @@
         <v>44678</v>
       </c>
       <c r="B359" t="n">
-        <v>42.16618728637695</v>
+        <v>42.16619110107422</v>
       </c>
       <c r="C359" t="n">
-        <v>43.58784506009413</v>
+        <v>43.58784900340616</v>
       </c>
       <c r="D359" t="n">
-        <v>41.46986526445734</v>
+        <v>41.46986901615963</v>
       </c>
       <c r="E359" t="n">
-        <v>43.52014885542929</v>
+        <v>43.52015279261696</v>
       </c>
       <c r="F359" t="n">
         <v>3779727</v>
@@ -7672,16 +7672,16 @@
         <v>44684</v>
       </c>
       <c r="B363" t="n">
-        <v>42.12750244140625</v>
+        <v>42.12749862670898</v>
       </c>
       <c r="C363" t="n">
-        <v>42.54336341820335</v>
+        <v>42.54335956584936</v>
       </c>
       <c r="D363" t="n">
-        <v>41.25710175933607</v>
+        <v>41.25709802345466</v>
       </c>
       <c r="E363" t="n">
-        <v>42.54336341820335</v>
+        <v>42.54335956584936</v>
       </c>
       <c r="F363" t="n">
         <v>4458389</v>
@@ -7692,16 +7692,16 @@
         <v>44685</v>
       </c>
       <c r="B364" t="n">
-        <v>44.10041427612305</v>
+        <v>44.10041809082031</v>
       </c>
       <c r="C364" t="n">
-        <v>44.32285161417975</v>
+        <v>44.32285544811791</v>
       </c>
       <c r="D364" t="n">
-        <v>42.16618567842227</v>
+        <v>42.16618932580826</v>
       </c>
       <c r="E364" t="n">
-        <v>43.04625879095802</v>
+        <v>43.04626251447057</v>
       </c>
       <c r="F364" t="n">
         <v>5759540</v>
@@ -7712,16 +7712,16 @@
         <v>44686</v>
       </c>
       <c r="B365" t="n">
-        <v>42.92053985595703</v>
+        <v>42.92053604125977</v>
       </c>
       <c r="C365" t="n">
-        <v>44.57430384010176</v>
+        <v>44.57429987842104</v>
       </c>
       <c r="D365" t="n">
-        <v>42.01145291457887</v>
+        <v>42.01144918067956</v>
       </c>
       <c r="E365" t="n">
-        <v>44.09074663744735</v>
+        <v>44.09074271874429</v>
       </c>
       <c r="F365" t="n">
         <v>4814532</v>
@@ -7732,16 +7732,16 @@
         <v>44687</v>
       </c>
       <c r="B366" t="n">
-        <v>42.55303573608398</v>
+        <v>42.55303192138672</v>
       </c>
       <c r="C366" t="n">
-        <v>43.90699359626386</v>
+        <v>43.90698966019007</v>
       </c>
       <c r="D366" t="n">
-        <v>41.82769996355259</v>
+        <v>41.82769621387857</v>
       </c>
       <c r="E366" t="n">
-        <v>43.33639522245434</v>
+        <v>43.33639133753226</v>
       </c>
       <c r="F366" t="n">
         <v>4093307</v>
@@ -7892,16 +7892,16 @@
         <v>44699</v>
       </c>
       <c r="B374" t="n">
-        <v>39.99985504150391</v>
+        <v>39.99985122680664</v>
       </c>
       <c r="C374" t="n">
-        <v>42.22421740419406</v>
+        <v>42.2242133773643</v>
       </c>
       <c r="D374" t="n">
-        <v>39.72906271064676</v>
+        <v>39.72905892177436</v>
       </c>
       <c r="E374" t="n">
-        <v>42.13717620908088</v>
+        <v>42.13717219055205</v>
       </c>
       <c r="F374" t="n">
         <v>1865839</v>
@@ -7952,16 +7952,16 @@
         <v>44704</v>
       </c>
       <c r="B377" t="n">
-        <v>42.28224563598633</v>
+        <v>42.28224182128906</v>
       </c>
       <c r="C377" t="n">
-        <v>42.79481657531103</v>
+        <v>42.7948127143697</v>
       </c>
       <c r="D377" t="n">
-        <v>41.35381369972519</v>
+        <v>41.3538099687909</v>
       </c>
       <c r="E377" t="n">
-        <v>41.42151365745766</v>
+        <v>41.42150992041549</v>
       </c>
       <c r="F377" t="n">
         <v>3400119</v>
@@ -8012,16 +8012,16 @@
         <v>44707</v>
       </c>
       <c r="B380" t="n">
-        <v>46.5955696105957</v>
+        <v>46.59557342529297</v>
       </c>
       <c r="C380" t="n">
-        <v>47.1661679572728</v>
+        <v>47.16617181868395</v>
       </c>
       <c r="D380" t="n">
-        <v>45.10621566046026</v>
+        <v>45.10621935322675</v>
       </c>
       <c r="E380" t="n">
-        <v>45.2512805595232</v>
+        <v>45.25128426416589</v>
       </c>
       <c r="F380" t="n">
         <v>4582217</v>
@@ -8072,16 +8072,16 @@
         <v>44712</v>
       </c>
       <c r="B383" t="n">
-        <v>47.14682769775391</v>
+        <v>47.14683151245117</v>
       </c>
       <c r="C383" t="n">
-        <v>49.5452685563496</v>
+        <v>49.54527256510714</v>
       </c>
       <c r="D383" t="n">
-        <v>47.11781396782467</v>
+        <v>47.11781778017441</v>
       </c>
       <c r="E383" t="n">
-        <v>48.22032446240879</v>
+        <v>48.22032836396376</v>
       </c>
       <c r="F383" t="n">
         <v>6322705</v>
@@ -8152,16 +8152,16 @@
         <v>44718</v>
       </c>
       <c r="B387" t="n">
-        <v>45.3189811706543</v>
+        <v>45.31898498535156</v>
       </c>
       <c r="C387" t="n">
-        <v>47.4563021942838</v>
+        <v>47.45630618888874</v>
       </c>
       <c r="D387" t="n">
-        <v>45.13522629971035</v>
+        <v>45.13523009894016</v>
       </c>
       <c r="E387" t="n">
-        <v>47.15649615191405</v>
+        <v>47.156500121283</v>
       </c>
       <c r="F387" t="n">
         <v>1711233</v>
@@ -8172,16 +8172,16 @@
         <v>44719</v>
       </c>
       <c r="B388" t="n">
-        <v>45.3189811706543</v>
+        <v>45.31898498535156</v>
       </c>
       <c r="C388" t="n">
-        <v>45.84122081100923</v>
+        <v>45.84122466966569</v>
       </c>
       <c r="D388" t="n">
-        <v>44.73871032322317</v>
+        <v>44.73871408907649</v>
       </c>
       <c r="E388" t="n">
-        <v>44.98048890609225</v>
+        <v>44.98049269229714</v>
       </c>
       <c r="F388" t="n">
         <v>1887578</v>
@@ -8192,16 +8192,16 @@
         <v>44720</v>
       </c>
       <c r="B389" t="n">
-        <v>45.25128555297852</v>
+        <v>45.25128173828125</v>
       </c>
       <c r="C389" t="n">
-        <v>46.00563510358936</v>
+        <v>46.00563122530019</v>
       </c>
       <c r="D389" t="n">
-        <v>44.92246574936335</v>
+        <v>44.9224619623857</v>
       </c>
       <c r="E389" t="n">
-        <v>45.31898551140559</v>
+        <v>45.31898169100119</v>
       </c>
       <c r="F389" t="n">
         <v>1920490</v>
@@ -8212,16 +8212,16 @@
         <v>44721</v>
       </c>
       <c r="B390" t="n">
-        <v>44.5066032409668</v>
+        <v>44.50660705566406</v>
       </c>
       <c r="C390" t="n">
-        <v>45.59944121195702</v>
+        <v>45.59944512032232</v>
       </c>
       <c r="D390" t="n">
-        <v>44.32285212169327</v>
+        <v>44.32285592064108</v>
       </c>
       <c r="E390" t="n">
-        <v>45.22226648118356</v>
+        <v>45.2222703572209</v>
       </c>
       <c r="F390" t="n">
         <v>1644697</v>
@@ -8472,16 +8472,16 @@
         <v>44741</v>
       </c>
       <c r="B403" t="n">
-        <v>34.71940612792969</v>
+        <v>34.71940994262695</v>
       </c>
       <c r="C403" t="n">
-        <v>35.41572814937177</v>
+        <v>35.41573204057546</v>
       </c>
       <c r="D403" t="n">
-        <v>34.09078031110602</v>
+        <v>34.0907840567348</v>
       </c>
       <c r="E403" t="n">
-        <v>35.29967322993957</v>
+        <v>35.29967710839206</v>
       </c>
       <c r="F403" t="n">
         <v>2690880</v>
@@ -8532,16 +8532,16 @@
         <v>44746</v>
       </c>
       <c r="B406" t="n">
-        <v>35.08691024780273</v>
+        <v>35.08690643310547</v>
       </c>
       <c r="C406" t="n">
-        <v>35.60915366553204</v>
+        <v>35.60914979405575</v>
       </c>
       <c r="D406" t="n">
-        <v>34.1971683099429</v>
+        <v>34.19716459197961</v>
       </c>
       <c r="E406" t="n">
-        <v>34.57433932306729</v>
+        <v>34.57433556409744</v>
       </c>
       <c r="F406" t="n">
         <v>2359523</v>
@@ -8612,16 +8612,16 @@
         <v>44750</v>
       </c>
       <c r="B410" t="n">
-        <v>31.81806373596191</v>
+        <v>31.81806564331055</v>
       </c>
       <c r="C410" t="n">
-        <v>32.48537204040704</v>
+        <v>32.48537398775778</v>
       </c>
       <c r="D410" t="n">
-        <v>31.19911039968697</v>
+        <v>31.19911226993215</v>
       </c>
       <c r="E410" t="n">
-        <v>31.3151653213559</v>
+        <v>31.31516719855805</v>
       </c>
       <c r="F410" t="n">
         <v>4375906</v>
@@ -8712,16 +8712,16 @@
         <v>44757</v>
       </c>
       <c r="B415" t="n">
-        <v>27.79486846923828</v>
+        <v>27.79486656188965</v>
       </c>
       <c r="C415" t="n">
-        <v>29.07146143004599</v>
+        <v>29.07145943509457</v>
       </c>
       <c r="D415" t="n">
-        <v>27.79486846923828</v>
+        <v>27.79486656188965</v>
       </c>
       <c r="E415" t="n">
-        <v>29.06178893688788</v>
+        <v>29.06178694260021</v>
       </c>
       <c r="F415" t="n">
         <v>4618481</v>
@@ -8752,16 +8752,16 @@
         <v>44761</v>
       </c>
       <c r="B417" t="n">
-        <v>29.43896293640137</v>
+        <v>29.43896102905273</v>
       </c>
       <c r="C417" t="n">
-        <v>29.53567474894549</v>
+        <v>29.5356728353309</v>
       </c>
       <c r="D417" t="n">
-        <v>28.11401691328927</v>
+        <v>28.11401509178381</v>
       </c>
       <c r="E417" t="n">
-        <v>28.14303064443129</v>
+        <v>28.14302882104603</v>
       </c>
       <c r="F417" t="n">
         <v>4570230</v>
@@ -8772,16 +8772,16 @@
         <v>44762</v>
       </c>
       <c r="B418" t="n">
-        <v>30.59950065612793</v>
+        <v>30.5994987487793</v>
       </c>
       <c r="C418" t="n">
-        <v>30.97667540990739</v>
+        <v>30.97667347904845</v>
       </c>
       <c r="D418" t="n">
-        <v>29.21652718353251</v>
+        <v>29.21652536238831</v>
       </c>
       <c r="E418" t="n">
-        <v>29.21652718353251</v>
+        <v>29.21652536238831</v>
       </c>
       <c r="F418" t="n">
         <v>5027446</v>
@@ -8792,16 +8792,16 @@
         <v>44763</v>
       </c>
       <c r="B419" t="n">
-        <v>29.44863510131836</v>
+        <v>29.44863319396973</v>
       </c>
       <c r="C419" t="n">
-        <v>29.86449233042948</v>
+        <v>29.86449039614633</v>
       </c>
       <c r="D419" t="n">
-        <v>28.83935237548546</v>
+        <v>28.83935050759925</v>
       </c>
       <c r="E419" t="n">
-        <v>29.86449233042948</v>
+        <v>29.86449039614633</v>
       </c>
       <c r="F419" t="n">
         <v>5437325</v>
@@ -8832,16 +8832,16 @@
         <v>44767</v>
       </c>
       <c r="B421" t="n">
-        <v>29.2648811340332</v>
+        <v>29.26488304138184</v>
       </c>
       <c r="C421" t="n">
-        <v>29.7194245717984</v>
+        <v>29.71942650877206</v>
       </c>
       <c r="D421" t="n">
-        <v>28.43316295561438</v>
+        <v>28.43316480875549</v>
       </c>
       <c r="E421" t="n">
-        <v>28.87803577468757</v>
+        <v>28.87803765682343</v>
       </c>
       <c r="F421" t="n">
         <v>3521914</v>
@@ -8852,16 +8852,16 @@
         <v>44768</v>
       </c>
       <c r="B422" t="n">
-        <v>28.95540428161621</v>
+        <v>28.95540618896484</v>
       </c>
       <c r="C422" t="n">
-        <v>30.15462657412001</v>
+        <v>30.15462856046375</v>
       </c>
       <c r="D422" t="n">
-        <v>28.81033750703789</v>
+        <v>28.81033940483069</v>
       </c>
       <c r="E422" t="n">
-        <v>29.88383426222034</v>
+        <v>29.88383623072646</v>
       </c>
       <c r="F422" t="n">
         <v>2984449</v>
@@ -8872,16 +8872,16 @@
         <v>44769</v>
       </c>
       <c r="B423" t="n">
-        <v>29.66139984130859</v>
+        <v>29.66139793395996</v>
       </c>
       <c r="C423" t="n">
-        <v>29.76778227135207</v>
+        <v>29.76778035716261</v>
       </c>
       <c r="D423" t="n">
-        <v>28.61691490502781</v>
+        <v>28.6169130648438</v>
       </c>
       <c r="E423" t="n">
-        <v>28.95540530688788</v>
+        <v>28.95540344493757</v>
       </c>
       <c r="F423" t="n">
         <v>2554762</v>
@@ -8892,16 +8892,16 @@
         <v>44770</v>
       </c>
       <c r="B424" t="n">
-        <v>30.78325271606445</v>
+        <v>30.78325080871582</v>
       </c>
       <c r="C424" t="n">
-        <v>30.88963514995402</v>
+        <v>30.88963323601387</v>
       </c>
       <c r="D424" t="n">
-        <v>29.53567536735125</v>
+        <v>29.53567353730325</v>
       </c>
       <c r="E424" t="n">
-        <v>29.96120510290952</v>
+        <v>29.96120324649545</v>
       </c>
       <c r="F424" t="n">
         <v>4208906</v>
@@ -8952,16 +8952,16 @@
         <v>44775</v>
       </c>
       <c r="B427" t="n">
-        <v>31.85674858093262</v>
+        <v>31.85675048828125</v>
       </c>
       <c r="C427" t="n">
-        <v>32.0791821744082</v>
+        <v>32.07918409507452</v>
       </c>
       <c r="D427" t="n">
-        <v>30.94765985359998</v>
+        <v>30.94766170651904</v>
       </c>
       <c r="E427" t="n">
-        <v>31.32483458513196</v>
+        <v>31.32483646063348</v>
       </c>
       <c r="F427" t="n">
         <v>3020206</v>
@@ -9072,16 +9072,16 @@
         <v>44783</v>
       </c>
       <c r="B433" t="n">
-        <v>33.26873397827148</v>
+        <v>33.26873779296875</v>
       </c>
       <c r="C433" t="n">
-        <v>33.97472847846024</v>
+        <v>33.97473237410905</v>
       </c>
       <c r="D433" t="n">
-        <v>32.87221800802422</v>
+        <v>32.87222177725572</v>
       </c>
       <c r="E433" t="n">
-        <v>33.62656747451073</v>
+        <v>33.62657133023831</v>
       </c>
       <c r="F433" t="n">
         <v>3325457</v>
@@ -9152,16 +9152,16 @@
         <v>44789</v>
       </c>
       <c r="B437" t="n">
-        <v>32.27260589599609</v>
+        <v>32.27260971069336</v>
       </c>
       <c r="C437" t="n">
-        <v>32.61109815484615</v>
+        <v>32.61110200955398</v>
       </c>
       <c r="D437" t="n">
-        <v>31.73102127989639</v>
+        <v>31.73102503057709</v>
       </c>
       <c r="E437" t="n">
-        <v>32.39832955774229</v>
+        <v>32.39833338730038</v>
       </c>
       <c r="F437" t="n">
         <v>2684074</v>
@@ -9172,16 +9172,16 @@
         <v>44790</v>
       </c>
       <c r="B438" t="n">
-        <v>32.53372955322266</v>
+        <v>32.53372573852539</v>
       </c>
       <c r="C438" t="n">
-        <v>32.93024931741367</v>
+        <v>32.93024545622303</v>
       </c>
       <c r="D438" t="n">
-        <v>31.80839373121048</v>
+        <v>31.80839000156146</v>
       </c>
       <c r="E438" t="n">
-        <v>31.8180662246313</v>
+        <v>31.81806249384815</v>
       </c>
       <c r="F438" t="n">
         <v>3057587</v>
@@ -9252,16 +9252,16 @@
         <v>44796</v>
       </c>
       <c r="B442" t="n">
-        <v>35.11592102050781</v>
+        <v>35.11592483520508</v>
       </c>
       <c r="C442" t="n">
-        <v>35.54145071517264</v>
+        <v>35.54145457609587</v>
       </c>
       <c r="D442" t="n">
-        <v>33.43314347863087</v>
+        <v>33.43314711052539</v>
       </c>
       <c r="E442" t="n">
-        <v>33.46215720759215</v>
+        <v>33.46216084263848</v>
       </c>
       <c r="F442" t="n">
         <v>5706007</v>
@@ -9292,16 +9292,16 @@
         <v>44798</v>
       </c>
       <c r="B444" t="n">
-        <v>35.7348747253418</v>
+        <v>35.73487854003906</v>
       </c>
       <c r="C444" t="n">
-        <v>36.56659288719009</v>
+        <v>36.56659679067325</v>
       </c>
       <c r="D444" t="n">
-        <v>35.39638621377552</v>
+        <v>35.39638999233915</v>
       </c>
       <c r="E444" t="n">
-        <v>35.8606021347718</v>
+        <v>35.86060596289047</v>
       </c>
       <c r="F444" t="n">
         <v>2850362</v>
@@ -9372,16 +9372,16 @@
         <v>44804</v>
       </c>
       <c r="B448" t="n">
-        <v>36.16040420532227</v>
+        <v>36.16040802001953</v>
       </c>
       <c r="C448" t="n">
-        <v>36.46021024107181</v>
+        <v>36.46021408739674</v>
       </c>
       <c r="D448" t="n">
-        <v>35.22230362431106</v>
+        <v>35.22230734004456</v>
       </c>
       <c r="E448" t="n">
-        <v>35.91862562779205</v>
+        <v>35.91862941698318</v>
       </c>
       <c r="F448" t="n">
         <v>3394125</v>
@@ -9392,16 +9392,16 @@
         <v>44805</v>
       </c>
       <c r="B449" t="n">
-        <v>35.58013534545898</v>
+        <v>35.58013916015625</v>
       </c>
       <c r="C449" t="n">
-        <v>36.22810235066332</v>
+        <v>36.22810623483188</v>
       </c>
       <c r="D449" t="n">
-        <v>35.00953703150028</v>
+        <v>35.00954078502128</v>
       </c>
       <c r="E449" t="n">
-        <v>35.8412551468599</v>
+        <v>35.84125898955293</v>
       </c>
       <c r="F449" t="n">
         <v>3340084</v>
@@ -9492,16 +9492,16 @@
         <v>44813</v>
       </c>
       <c r="B454" t="n">
-        <v>35.92830276489258</v>
+        <v>35.92829895019531</v>
       </c>
       <c r="C454" t="n">
-        <v>36.37317375612866</v>
+        <v>36.3731698941971</v>
       </c>
       <c r="D454" t="n">
-        <v>35.60915545100184</v>
+        <v>35.60915167019012</v>
       </c>
       <c r="E454" t="n">
-        <v>35.79290659406839</v>
+        <v>35.79290279374685</v>
       </c>
       <c r="F454" t="n">
         <v>3544465</v>
@@ -9552,16 +9552,16 @@
         <v>44818</v>
       </c>
       <c r="B457" t="n">
-        <v>37.25324630737305</v>
+        <v>37.25325012207031</v>
       </c>
       <c r="C457" t="n">
-        <v>37.57239358328728</v>
+        <v>37.57239743066493</v>
       </c>
       <c r="D457" t="n">
-        <v>35.96698471138824</v>
+        <v>35.96698839437353</v>
       </c>
       <c r="E457" t="n">
-        <v>36.05402215203722</v>
+        <v>36.05402584393507</v>
       </c>
       <c r="F457" t="n">
         <v>4057043</v>
@@ -9592,16 +9592,16 @@
         <v>44820</v>
       </c>
       <c r="B459" t="n">
-        <v>36.79870223999023</v>
+        <v>36.7987060546875</v>
       </c>
       <c r="C459" t="n">
-        <v>36.79870223999023</v>
+        <v>36.7987060546875</v>
       </c>
       <c r="D459" t="n">
-        <v>35.78322922342723</v>
+        <v>35.7832329328566</v>
       </c>
       <c r="E459" t="n">
-        <v>36.14106271488564</v>
+        <v>36.14106646140942</v>
       </c>
       <c r="F459" t="n">
         <v>2974596</v>
@@ -9612,16 +9612,16 @@
         <v>44823</v>
       </c>
       <c r="B460" t="n">
-        <v>36.8470573425293</v>
+        <v>36.84706115722656</v>
       </c>
       <c r="C460" t="n">
-        <v>37.3983144462179</v>
+        <v>37.39831831798563</v>
       </c>
       <c r="D460" t="n">
-        <v>35.7929018485589</v>
+        <v>35.79290555412169</v>
       </c>
       <c r="E460" t="n">
-        <v>35.7929018485589</v>
+        <v>35.79290555412169</v>
       </c>
       <c r="F460" t="n">
         <v>3461677</v>
@@ -9652,16 +9652,16 @@
         <v>44825</v>
       </c>
       <c r="B462" t="n">
-        <v>38.0366096496582</v>
+        <v>38.03661346435547</v>
       </c>
       <c r="C462" t="n">
-        <v>38.79095912196355</v>
+        <v>38.79096301231463</v>
       </c>
       <c r="D462" t="n">
-        <v>37.62074869162363</v>
+        <v>37.62075246461414</v>
       </c>
       <c r="E462" t="n">
-        <v>37.9398959687412</v>
+        <v>37.93989977373904</v>
       </c>
       <c r="F462" t="n">
         <v>4689181</v>
@@ -9732,16 +9732,16 @@
         <v>44831</v>
       </c>
       <c r="B466" t="n">
-        <v>33.61689758300781</v>
+        <v>33.61689376831055</v>
       </c>
       <c r="C466" t="n">
-        <v>34.44861580943209</v>
+        <v>34.44861190035511</v>
       </c>
       <c r="D466" t="n">
-        <v>33.32676401519949</v>
+        <v>33.3267602334253</v>
       </c>
       <c r="E466" t="n">
-        <v>34.44861580943209</v>
+        <v>34.44861190035511</v>
       </c>
       <c r="F466" t="n">
         <v>5480701</v>
@@ -9752,16 +9752,16 @@
         <v>44832</v>
       </c>
       <c r="B467" t="n">
-        <v>34.5743408203125</v>
+        <v>34.57433700561523</v>
       </c>
       <c r="C467" t="n">
-        <v>34.99987431683395</v>
+        <v>34.99987045518622</v>
       </c>
       <c r="D467" t="n">
-        <v>33.19136913623947</v>
+        <v>33.19136547412988</v>
       </c>
       <c r="E467" t="n">
-        <v>33.66525385709685</v>
+        <v>33.66525014270204</v>
       </c>
       <c r="F467" t="n">
         <v>4399676</v>
@@ -9772,16 +9772,16 @@
         <v>44833</v>
       </c>
       <c r="B468" t="n">
-        <v>33.90702819824219</v>
+        <v>33.90703201293945</v>
       </c>
       <c r="C468" t="n">
-        <v>34.69039138641359</v>
+        <v>34.69039528924284</v>
       </c>
       <c r="D468" t="n">
-        <v>33.09465502863428</v>
+        <v>33.09465875193581</v>
       </c>
       <c r="E468" t="n">
-        <v>34.61302269157358</v>
+        <v>34.61302658569848</v>
       </c>
       <c r="F468" t="n">
         <v>4499631</v>
@@ -9812,16 +9812,16 @@
         <v>44837</v>
       </c>
       <c r="B470" t="n">
-        <v>36.79870223999023</v>
+        <v>36.7987060546875</v>
       </c>
       <c r="C470" t="n">
-        <v>36.91475715561467</v>
+        <v>36.91476098234264</v>
       </c>
       <c r="D470" t="n">
-        <v>35.52210941084767</v>
+        <v>35.52211309320833</v>
       </c>
       <c r="E470" t="n">
-        <v>36.26678637509517</v>
+        <v>36.26679013465196</v>
       </c>
       <c r="F470" t="n">
         <v>4419789</v>
@@ -9852,16 +9852,16 @@
         <v>44839</v>
       </c>
       <c r="B472" t="n">
-        <v>41.63427352905273</v>
+        <v>41.63427734375</v>
       </c>
       <c r="C472" t="n">
-        <v>42.48533291211138</v>
+        <v>42.48533680478608</v>
       </c>
       <c r="D472" t="n">
-        <v>40.55110431601417</v>
+        <v>40.55110803146717</v>
       </c>
       <c r="E472" t="n">
-        <v>40.61880426561678</v>
+        <v>40.61880798727272</v>
       </c>
       <c r="F472" t="n">
         <v>6927519</v>
@@ -9892,16 +9892,16 @@
         <v>44841</v>
       </c>
       <c r="B474" t="n">
-        <v>41.47954177856445</v>
+        <v>41.47953796386719</v>
       </c>
       <c r="C474" t="n">
-        <v>42.45632495390688</v>
+        <v>42.45632104937901</v>
       </c>
       <c r="D474" t="n">
-        <v>41.22809067776815</v>
+        <v>41.22808688619578</v>
       </c>
       <c r="E474" t="n">
-        <v>41.59559296175236</v>
+        <v>41.59558913638236</v>
       </c>
       <c r="F474" t="n">
         <v>3503020</v>
@@ -10072,16 +10072,16 @@
         <v>44855</v>
       </c>
       <c r="B483" t="n">
-        <v>44.22613906860352</v>
+        <v>44.22614288330078</v>
       </c>
       <c r="C483" t="n">
-        <v>44.68068250090031</v>
+        <v>44.68068635480393</v>
       </c>
       <c r="D483" t="n">
-        <v>42.41763783177974</v>
+        <v>42.41764149048589</v>
       </c>
       <c r="E483" t="n">
-        <v>42.96889119740864</v>
+        <v>42.9688949036628</v>
       </c>
       <c r="F483" t="n">
         <v>5360835</v>
@@ -10112,16 +10112,16 @@
         <v>44859</v>
       </c>
       <c r="B485" t="n">
-        <v>42.69809722900391</v>
+        <v>42.69810104370117</v>
       </c>
       <c r="C485" t="n">
-        <v>44.7193669863075</v>
+        <v>44.71937098158734</v>
       </c>
       <c r="D485" t="n">
-        <v>42.52401860625056</v>
+        <v>42.52402240539543</v>
       </c>
       <c r="E485" t="n">
-        <v>43.43310543554394</v>
+        <v>43.43310931590769</v>
       </c>
       <c r="F485" t="n">
         <v>3364870</v>
@@ -10232,16 +10232,16 @@
         <v>44868</v>
       </c>
       <c r="B491" t="n">
-        <v>46.30543518066406</v>
+        <v>46.30543899536133</v>
       </c>
       <c r="C491" t="n">
-        <v>46.4311588402996</v>
+        <v>46.43116266535413</v>
       </c>
       <c r="D491" t="n">
-        <v>44.51627522669133</v>
+        <v>44.51627889399545</v>
       </c>
       <c r="E491" t="n">
-        <v>44.98048739191887</v>
+        <v>44.98049109746535</v>
       </c>
       <c r="F491" t="n">
         <v>3262984</v>
@@ -10312,16 +10312,16 @@
         <v>44874</v>
       </c>
       <c r="B495" t="n">
-        <v>44.69035339355469</v>
+        <v>44.69035720825195</v>
       </c>
       <c r="C495" t="n">
-        <v>46.49885831321781</v>
+        <v>46.49886228228617</v>
       </c>
       <c r="D495" t="n">
-        <v>44.23580997752845</v>
+        <v>44.23581375342662</v>
       </c>
       <c r="E495" t="n">
-        <v>45.35766165335595</v>
+        <v>45.35766552501359</v>
       </c>
       <c r="F495" t="n">
         <v>4884014</v>
@@ -10332,16 +10332,16 @@
         <v>44875</v>
       </c>
       <c r="B496" t="n">
-        <v>42.0598030090332</v>
+        <v>42.05980682373047</v>
       </c>
       <c r="C496" t="n">
-        <v>44.68068109462947</v>
+        <v>44.68068514703247</v>
       </c>
       <c r="D496" t="n">
-        <v>41.64394206412777</v>
+        <v>41.6439458411077</v>
       </c>
       <c r="E496" t="n">
-        <v>43.65554309181744</v>
+        <v>43.65554705124352</v>
       </c>
       <c r="F496" t="n">
         <v>5453172</v>
@@ -10472,16 +10472,16 @@
         <v>44887</v>
       </c>
       <c r="B503" t="n">
-        <v>35.7252082824707</v>
+        <v>35.72520446777344</v>
       </c>
       <c r="C503" t="n">
-        <v>38.01726681069696</v>
+        <v>38.01726275125628</v>
       </c>
       <c r="D503" t="n">
-        <v>35.41572973267442</v>
+        <v>35.41572595102293</v>
       </c>
       <c r="E503" t="n">
-        <v>37.37897222043525</v>
+        <v>37.37896822915095</v>
       </c>
       <c r="F503" t="n">
         <v>4879239</v>
@@ -10492,16 +10492,16 @@
         <v>44888</v>
       </c>
       <c r="B504" t="n">
-        <v>34.29387664794922</v>
+        <v>34.29388046264648</v>
       </c>
       <c r="C504" t="n">
-        <v>35.59947950993321</v>
+        <v>35.59948346985989</v>
       </c>
       <c r="D504" t="n">
-        <v>33.84900195222058</v>
+        <v>33.84900571743197</v>
       </c>
       <c r="E504" t="n">
-        <v>35.37704590964446</v>
+        <v>35.37704984482862</v>
       </c>
       <c r="F504" t="n">
         <v>5644348</v>
@@ -10532,16 +10532,16 @@
         <v>44890</v>
       </c>
       <c r="B506" t="n">
-        <v>34.2358512878418</v>
+        <v>34.23584747314453</v>
       </c>
       <c r="C506" t="n">
-        <v>36.49889988516448</v>
+        <v>36.49889581830917</v>
       </c>
       <c r="D506" t="n">
-        <v>34.11012761496025</v>
+        <v>34.11012381427162</v>
       </c>
       <c r="E506" t="n">
-        <v>36.17008008946956</v>
+        <v>36.17007605925269</v>
       </c>
       <c r="F506" t="n">
         <v>4398253</v>
@@ -10552,16 +10552,16 @@
         <v>44893</v>
       </c>
       <c r="B507" t="n">
-        <v>33.64591217041016</v>
+        <v>33.64590835571289</v>
       </c>
       <c r="C507" t="n">
-        <v>34.11012813925738</v>
+        <v>34.11012427192836</v>
       </c>
       <c r="D507" t="n">
-        <v>32.92057635865081</v>
+        <v>32.92057262619048</v>
       </c>
       <c r="E507" t="n">
-        <v>33.36544734092983</v>
+        <v>33.36544355803103</v>
       </c>
       <c r="F507" t="n">
         <v>4077054</v>
@@ -10652,16 +10652,16 @@
         <v>44900</v>
       </c>
       <c r="B512" t="n">
-        <v>34.04242706298828</v>
+        <v>34.04242324829102</v>
       </c>
       <c r="C512" t="n">
-        <v>35.879945891439</v>
+        <v>35.87994187083461</v>
       </c>
       <c r="D512" t="n">
-        <v>33.77163473568869</v>
+        <v>33.77163095133564</v>
       </c>
       <c r="E512" t="n">
-        <v>35.57046733984986</v>
+        <v>35.57046335392476</v>
       </c>
       <c r="F512" t="n">
         <v>5158181</v>
@@ -10732,16 +10732,16 @@
         <v>44904</v>
       </c>
       <c r="B516" t="n">
-        <v>31.69233894348145</v>
+        <v>31.69234085083008</v>
       </c>
       <c r="C516" t="n">
-        <v>32.74649445099531</v>
+        <v>32.74649642178647</v>
       </c>
       <c r="D516" t="n">
-        <v>31.48924283777486</v>
+        <v>31.4892447329005</v>
       </c>
       <c r="E516" t="n">
-        <v>32.22425106961099</v>
+        <v>32.22425300897184</v>
       </c>
       <c r="F516" t="n">
         <v>2885712</v>
@@ -10752,16 +10752,16 @@
         <v>44907</v>
       </c>
       <c r="B517" t="n">
-        <v>32.23392105102539</v>
+        <v>32.23392486572266</v>
       </c>
       <c r="C517" t="n">
-        <v>32.41767215777701</v>
+        <v>32.41767599422015</v>
       </c>
       <c r="D517" t="n">
-        <v>31.06371071712008</v>
+        <v>31.06371439332975</v>
       </c>
       <c r="E517" t="n">
-        <v>31.59562280181559</v>
+        <v>31.59562654097396</v>
       </c>
       <c r="F517" t="n">
         <v>3445728</v>
@@ -10772,16 +10772,16 @@
         <v>44908</v>
       </c>
       <c r="B518" t="n">
-        <v>32.52405548095703</v>
+        <v>32.5240592956543</v>
       </c>
       <c r="C518" t="n">
-        <v>33.41380105995531</v>
+        <v>33.41380497900949</v>
       </c>
       <c r="D518" t="n">
-        <v>31.9824708896037</v>
+        <v>31.98247464077933</v>
       </c>
       <c r="E518" t="n">
-        <v>32.39832807738018</v>
+        <v>32.39833187733107</v>
       </c>
       <c r="F518" t="n">
         <v>3369136</v>
@@ -10872,16 +10872,16 @@
         <v>44915</v>
       </c>
       <c r="B523" t="n">
-        <v>31.63431358337402</v>
+        <v>31.63431167602539</v>
       </c>
       <c r="C523" t="n">
-        <v>31.83740595497857</v>
+        <v>31.83740403538475</v>
       </c>
       <c r="D523" t="n">
-        <v>30.62851484937437</v>
+        <v>30.62851300266902</v>
       </c>
       <c r="E523" t="n">
-        <v>30.76391101296931</v>
+        <v>30.76390915810044</v>
       </c>
       <c r="F523" t="n">
         <v>3472546</v>
@@ -10892,16 +10892,16 @@
         <v>44916</v>
       </c>
       <c r="B524" t="n">
-        <v>32.19524002075195</v>
+        <v>32.19523620605469</v>
       </c>
       <c r="C524" t="n">
-        <v>32.50471857745117</v>
+        <v>32.50471472608491</v>
       </c>
       <c r="D524" t="n">
-        <v>31.22812562087756</v>
+        <v>31.22812192077017</v>
       </c>
       <c r="E524" t="n">
-        <v>32.34997742531367</v>
+        <v>32.34997359228213</v>
       </c>
       <c r="F524" t="n">
         <v>3938295</v>
@@ -10912,16 +10912,16 @@
         <v>44917</v>
       </c>
       <c r="B525" t="n">
-        <v>32.0114860534668</v>
+        <v>32.01148986816406</v>
       </c>
       <c r="C525" t="n">
-        <v>32.78517675543017</v>
+        <v>32.78518066232546</v>
       </c>
       <c r="D525" t="n">
-        <v>31.5376013885634</v>
+        <v>31.53760514678948</v>
       </c>
       <c r="E525" t="n">
-        <v>32.41767451520204</v>
+        <v>32.41767837830338</v>
       </c>
       <c r="F525" t="n">
         <v>3822391</v>
@@ -10932,16 +10932,16 @@
         <v>44918</v>
       </c>
       <c r="B526" t="n">
-        <v>34.68072509765625</v>
+        <v>34.68072128295898</v>
       </c>
       <c r="C526" t="n">
-        <v>34.88381746754605</v>
+        <v>34.88381363050969</v>
       </c>
       <c r="D526" t="n">
-        <v>32.68846888482701</v>
+        <v>32.68846528926745</v>
       </c>
       <c r="E526" t="n">
-        <v>33.17202607250107</v>
+        <v>33.17202242375276</v>
       </c>
       <c r="F526" t="n">
         <v>6955860</v>
@@ -11012,16 +11012,16 @@
         <v>44924</v>
       </c>
       <c r="B530" t="n">
-        <v>36.50856399536133</v>
+        <v>36.50856781005859</v>
       </c>
       <c r="C530" t="n">
-        <v>37.23389970387844</v>
+        <v>37.23390359436439</v>
       </c>
       <c r="D530" t="n">
-        <v>35.61882215744662</v>
+        <v>35.61882587917678</v>
       </c>
       <c r="E530" t="n">
-        <v>35.87994196319169</v>
+        <v>35.87994571220566</v>
       </c>
       <c r="F530" t="n">
         <v>4887264</v>
@@ -11032,16 +11032,16 @@
         <v>44928</v>
       </c>
       <c r="B531" t="n">
-        <v>35.21263885498047</v>
+        <v>35.2126350402832</v>
       </c>
       <c r="C531" t="n">
-        <v>36.68265172299981</v>
+        <v>36.68264774905137</v>
       </c>
       <c r="D531" t="n">
-        <v>34.78710911009928</v>
+        <v>34.78710534150101</v>
       </c>
       <c r="E531" t="n">
-        <v>36.01534337329287</v>
+        <v>36.01533947163607</v>
       </c>
       <c r="F531" t="n">
         <v>2924313</v>
@@ -11152,16 +11152,16 @@
         <v>44936</v>
       </c>
       <c r="B537" t="n">
-        <v>37.79483413696289</v>
+        <v>37.79483032226562</v>
       </c>
       <c r="C537" t="n">
-        <v>38.07529521496675</v>
+        <v>38.07529137196207</v>
       </c>
       <c r="D537" t="n">
-        <v>36.49889993855829</v>
+        <v>36.49889625466188</v>
       </c>
       <c r="E537" t="n">
-        <v>37.09850831958851</v>
+        <v>37.0985045751726</v>
       </c>
       <c r="F537" t="n">
         <v>3183751</v>
@@ -11192,16 +11192,16 @@
         <v>44938</v>
       </c>
       <c r="B539" t="n">
-        <v>43.42343521118164</v>
+        <v>43.42343902587891</v>
       </c>
       <c r="C539" t="n">
-        <v>44.72904181410123</v>
+        <v>44.7290457434945</v>
       </c>
       <c r="D539" t="n">
-        <v>43.19132911953119</v>
+        <v>43.19133291383822</v>
       </c>
       <c r="E539" t="n">
-        <v>43.40409397377132</v>
+        <v>43.40409778676949</v>
       </c>
       <c r="F539" t="n">
         <v>7341055</v>
@@ -11212,16 +11212,16 @@
         <v>44939</v>
       </c>
       <c r="B540" t="n">
-        <v>42.75613021850586</v>
+        <v>42.75612640380859</v>
       </c>
       <c r="C540" t="n">
-        <v>43.50080726582102</v>
+        <v>43.50080338468374</v>
       </c>
       <c r="D540" t="n">
-        <v>42.35961420932546</v>
+        <v>42.35961043000531</v>
       </c>
       <c r="E540" t="n">
-        <v>43.42343856263282</v>
+        <v>43.42343468839838</v>
       </c>
       <c r="F540" t="n">
         <v>4249336</v>
@@ -11272,16 +11272,16 @@
         <v>44944</v>
       </c>
       <c r="B543" t="n">
-        <v>44.53562164306641</v>
+        <v>44.53561782836914</v>
       </c>
       <c r="C543" t="n">
-        <v>45.24161621271021</v>
+        <v>45.241612337541</v>
       </c>
       <c r="D543" t="n">
-        <v>43.22034619346439</v>
+        <v>43.220342491427</v>
       </c>
       <c r="E543" t="n">
-        <v>43.42343857092518</v>
+        <v>43.42343485149192</v>
       </c>
       <c r="F543" t="n">
         <v>6730959</v>
@@ -11332,16 +11332,16 @@
         <v>44949</v>
       </c>
       <c r="B546" t="n">
-        <v>46.45050811767578</v>
+        <v>46.45050430297852</v>
       </c>
       <c r="C546" t="n">
-        <v>48.53947429699662</v>
+        <v>48.53947031074529</v>
       </c>
       <c r="D546" t="n">
-        <v>45.88958222216792</v>
+        <v>45.88957845353607</v>
       </c>
       <c r="E546" t="n">
-        <v>47.67874234150205</v>
+        <v>47.67873842593739</v>
       </c>
       <c r="F546" t="n">
         <v>5971946</v>
@@ -11392,16 +11392,16 @@
         <v>44952</v>
       </c>
       <c r="B549" t="n">
-        <v>45.26095581054688</v>
+        <v>45.26095199584961</v>
       </c>
       <c r="C549" t="n">
-        <v>46.77932358255676</v>
+        <v>46.77931963988798</v>
       </c>
       <c r="D549" t="n">
-        <v>45.24161457234137</v>
+        <v>45.24161075927422</v>
       </c>
       <c r="E549" t="n">
-        <v>45.92826413060603</v>
+        <v>45.92826025966649</v>
       </c>
       <c r="F549" t="n">
         <v>3327082</v>
@@ -11412,16 +11412,16 @@
         <v>44953</v>
       </c>
       <c r="B550" t="n">
-        <v>44.5066032409668</v>
+        <v>44.50660705566406</v>
       </c>
       <c r="C550" t="n">
-        <v>46.34412192885299</v>
+        <v>46.34412590104548</v>
       </c>
       <c r="D550" t="n">
-        <v>44.16811098394805</v>
+        <v>44.16811476963287</v>
       </c>
       <c r="E550" t="n">
-        <v>46.20872577556058</v>
+        <v>46.20872973614816</v>
       </c>
       <c r="F550" t="n">
         <v>4035914</v>
@@ -11432,16 +11432,16 @@
         <v>44956</v>
       </c>
       <c r="B551" t="n">
-        <v>43.79094314575195</v>
+        <v>43.79093933105469</v>
       </c>
       <c r="C551" t="n">
-        <v>44.43890648207057</v>
+        <v>44.43890261092821</v>
       </c>
       <c r="D551" t="n">
-        <v>43.13330356893655</v>
+        <v>43.13329981152729</v>
       </c>
       <c r="E551" t="n">
-        <v>44.31318281197527</v>
+        <v>44.3131789517849</v>
       </c>
       <c r="F551" t="n">
         <v>3870439</v>
@@ -11572,16 +11572,16 @@
         <v>44965</v>
       </c>
       <c r="B558" t="n">
-        <v>43.12362670898438</v>
+        <v>43.12363052368164</v>
       </c>
       <c r="C558" t="n">
-        <v>43.13329920092593</v>
+        <v>43.13330301647882</v>
       </c>
       <c r="D558" t="n">
-        <v>42.08881622667597</v>
+        <v>42.08881994983436</v>
       </c>
       <c r="E558" t="n">
-        <v>42.57237336739773</v>
+        <v>42.57237713333137</v>
       </c>
       <c r="F558" t="n">
         <v>2757212</v>
@@ -11672,16 +11672,16 @@
         <v>44972</v>
       </c>
       <c r="B563" t="n">
-        <v>40.04821014404297</v>
+        <v>40.0482063293457</v>
       </c>
       <c r="C563" t="n">
-        <v>40.52209485081966</v>
+        <v>40.52209099098364</v>
       </c>
       <c r="D563" t="n">
-        <v>38.90701335343782</v>
+        <v>38.90700964744255</v>
       </c>
       <c r="E563" t="n">
-        <v>38.92635833968847</v>
+        <v>38.92635463185054</v>
       </c>
       <c r="F563" t="n">
         <v>3495706</v>
@@ -11752,16 +11752,16 @@
         <v>44980</v>
       </c>
       <c r="B567" t="n">
-        <v>38.00759887695312</v>
+        <v>38.00759506225586</v>
       </c>
       <c r="C567" t="n">
-        <v>39.07142321677222</v>
+        <v>39.07141929530241</v>
       </c>
       <c r="D567" t="n">
-        <v>37.73680654543994</v>
+        <v>37.7368027579212</v>
       </c>
       <c r="E567" t="n">
-        <v>37.95924390652058</v>
+        <v>37.95924009667655</v>
       </c>
       <c r="F567" t="n">
         <v>3548732</v>
@@ -11812,16 +11812,16 @@
         <v>44985</v>
       </c>
       <c r="B570" t="n">
-        <v>35.21263885498047</v>
+        <v>35.2126350402832</v>
       </c>
       <c r="C570" t="n">
-        <v>38.49115688632073</v>
+        <v>38.49115271645117</v>
       </c>
       <c r="D570" t="n">
-        <v>35.21263885498047</v>
+        <v>35.2126350402832</v>
       </c>
       <c r="E570" t="n">
-        <v>37.13719520026616</v>
+        <v>37.13719117707558</v>
       </c>
       <c r="F570" t="n">
         <v>11036876</v>
@@ -11832,16 +11832,16 @@
         <v>44986</v>
       </c>
       <c r="B571" t="n">
-        <v>31.52793121337891</v>
+        <v>31.52792930603027</v>
       </c>
       <c r="C571" t="n">
-        <v>35.21263762145776</v>
+        <v>35.21263549119504</v>
       </c>
       <c r="D571" t="n">
-        <v>29.89350662783602</v>
+        <v>29.89350481936535</v>
       </c>
       <c r="E571" t="n">
-        <v>35.10625518896411</v>
+        <v>35.10625306513723</v>
       </c>
       <c r="F571" t="n">
         <v>24633899</v>
@@ -11872,16 +11872,16 @@
         <v>44988</v>
       </c>
       <c r="B573" t="n">
-        <v>31.74069595336914</v>
+        <v>31.74069404602051</v>
       </c>
       <c r="C573" t="n">
-        <v>31.93411957920744</v>
+        <v>31.93411766023568</v>
       </c>
       <c r="D573" t="n">
-        <v>30.40607743217574</v>
+        <v>30.40607560502645</v>
       </c>
       <c r="E573" t="n">
-        <v>30.47377551384036</v>
+        <v>30.47377368262298</v>
       </c>
       <c r="F573" t="n">
         <v>7573675</v>
@@ -11892,16 +11892,16 @@
         <v>44991</v>
       </c>
       <c r="B574" t="n">
-        <v>31.86642074584961</v>
+        <v>31.86641883850098</v>
       </c>
       <c r="C574" t="n">
-        <v>32.34997795368473</v>
+        <v>32.34997601739302</v>
       </c>
       <c r="D574" t="n">
-        <v>30.94766317523564</v>
+        <v>30.94766132287878</v>
       </c>
       <c r="E574" t="n">
-        <v>31.74069707103675</v>
+        <v>31.74069517121325</v>
       </c>
       <c r="F574" t="n">
         <v>5963007</v>
@@ -11992,16 +11992,16 @@
         <v>44998</v>
       </c>
       <c r="B579" t="n">
-        <v>26.45058059692383</v>
+        <v>26.4505786895752</v>
       </c>
       <c r="C579" t="n">
-        <v>27.32098316598858</v>
+        <v>27.32098119587531</v>
       </c>
       <c r="D579" t="n">
-        <v>25.76392728704381</v>
+        <v>25.76392542920967</v>
       </c>
       <c r="E579" t="n">
-        <v>26.59564737946998</v>
+        <v>26.59564546166059</v>
       </c>
       <c r="F579" t="n">
         <v>13860726</v>
@@ -12032,16 +12032,16 @@
         <v>45000</v>
       </c>
       <c r="B581" t="n">
-        <v>26.28616905212402</v>
+        <v>26.28617095947266</v>
       </c>
       <c r="C581" t="n">
-        <v>26.82775179788365</v>
+        <v>26.82775374453002</v>
       </c>
       <c r="D581" t="n">
-        <v>25.62853138858268</v>
+        <v>25.62853324821252</v>
       </c>
       <c r="E581" t="n">
-        <v>26.58597321755539</v>
+        <v>26.58597514665809</v>
       </c>
       <c r="F581" t="n">
         <v>12174787</v>
@@ -12072,16 +12072,16 @@
         <v>45002</v>
       </c>
       <c r="B583" t="n">
-        <v>30.70588302612305</v>
+        <v>30.70588111877441</v>
       </c>
       <c r="C583" t="n">
-        <v>30.88963415624145</v>
+        <v>30.8896322374788</v>
       </c>
       <c r="D583" t="n">
-        <v>27.73684184447329</v>
+        <v>27.73684012155175</v>
       </c>
       <c r="E583" t="n">
-        <v>30.45443194157511</v>
+        <v>30.45443004984579</v>
       </c>
       <c r="F583" t="n">
         <v>23193684</v>
@@ -12092,16 +12092,16 @@
         <v>45005</v>
       </c>
       <c r="B584" t="n">
-        <v>29.79679489135742</v>
+        <v>29.79679679870605</v>
       </c>
       <c r="C584" t="n">
-        <v>31.20878203377826</v>
+        <v>31.20878403151084</v>
       </c>
       <c r="D584" t="n">
-        <v>29.32290834641774</v>
+        <v>29.32291022343201</v>
       </c>
       <c r="E584" t="n">
-        <v>30.70588175921954</v>
+        <v>30.70588372476053</v>
       </c>
       <c r="F584" t="n">
         <v>7729094</v>
@@ -12252,16 +12252,16 @@
         <v>45015</v>
       </c>
       <c r="B592" t="n">
-        <v>29.38093376159668</v>
+        <v>29.38093566894531</v>
       </c>
       <c r="C592" t="n">
-        <v>30.51245796745546</v>
+        <v>30.51245994826028</v>
       </c>
       <c r="D592" t="n">
-        <v>29.2745513361352</v>
+        <v>29.27455323657771</v>
       </c>
       <c r="E592" t="n">
-        <v>29.95153211069714</v>
+        <v>29.95153405508782</v>
       </c>
       <c r="F592" t="n">
         <v>5560645</v>
@@ -12312,16 +12312,16 @@
         <v>45020</v>
       </c>
       <c r="B595" t="n">
-        <v>27.92059135437012</v>
+        <v>27.92059326171875</v>
       </c>
       <c r="C595" t="n">
-        <v>29.70975320425825</v>
+        <v>29.70975523383049</v>
       </c>
       <c r="D595" t="n">
-        <v>27.91092073592187</v>
+        <v>27.91092264260987</v>
       </c>
       <c r="E595" t="n">
-        <v>29.57435705083184</v>
+        <v>29.57435907115471</v>
       </c>
       <c r="F595" t="n">
         <v>7552242</v>
@@ -12332,16 +12332,16 @@
         <v>45021</v>
       </c>
       <c r="B596" t="n">
-        <v>26.76972770690918</v>
+        <v>26.76972579956055</v>
       </c>
       <c r="C596" t="n">
-        <v>27.8528951326722</v>
+        <v>27.85289314814766</v>
       </c>
       <c r="D596" t="n">
-        <v>26.23781367622606</v>
+        <v>26.23781180677641</v>
       </c>
       <c r="E596" t="n">
-        <v>27.65947338188658</v>
+        <v>27.65947141114338</v>
       </c>
       <c r="F596" t="n">
         <v>12382825</v>
@@ -12372,16 +12372,16 @@
         <v>45026</v>
       </c>
       <c r="B598" t="n">
-        <v>29.6517276763916</v>
+        <v>29.65172576904297</v>
       </c>
       <c r="C598" t="n">
-        <v>29.83547880780963</v>
+        <v>29.8354768886412</v>
       </c>
       <c r="D598" t="n">
-        <v>28.19138549654949</v>
+        <v>28.19138368313743</v>
       </c>
       <c r="E598" t="n">
-        <v>28.33645227786835</v>
+        <v>28.33645045512486</v>
       </c>
       <c r="F598" t="n">
         <v>8774363</v>
@@ -12552,16 +12552,16 @@
         <v>45040</v>
       </c>
       <c r="B607" t="n">
-        <v>26.96700477600098</v>
+        <v>26.96700286865234</v>
       </c>
       <c r="C607" t="n">
-        <v>27.07506799883479</v>
+        <v>27.07506608384296</v>
       </c>
       <c r="D607" t="n">
-        <v>26.23020138729918</v>
+        <v>26.23019953206389</v>
       </c>
       <c r="E607" t="n">
-        <v>26.86876394941649</v>
+        <v>26.86876204901633</v>
       </c>
       <c r="F607" t="n">
         <v>6680100</v>
@@ -12572,16 +12572,16 @@
         <v>45041</v>
       </c>
       <c r="B608" t="n">
-        <v>27.21260261535645</v>
+        <v>27.21260452270508</v>
       </c>
       <c r="C608" t="n">
-        <v>27.45820371522866</v>
+        <v>27.45820563979163</v>
       </c>
       <c r="D608" t="n">
-        <v>26.42667797149275</v>
+        <v>26.42667982375542</v>
       </c>
       <c r="E608" t="n">
-        <v>26.79999269261962</v>
+        <v>26.79999457104816</v>
       </c>
       <c r="F608" t="n">
         <v>5323000</v>
@@ -12612,16 +12612,16 @@
         <v>45043</v>
       </c>
       <c r="B610" t="n">
-        <v>29.90439414978027</v>
+        <v>29.90439224243164</v>
       </c>
       <c r="C610" t="n">
-        <v>30.26788277330051</v>
+        <v>30.267880842768</v>
       </c>
       <c r="D610" t="n">
-        <v>26.73122612224756</v>
+        <v>26.73122441728851</v>
       </c>
       <c r="E610" t="n">
-        <v>26.73122612224756</v>
+        <v>26.73122441728851</v>
       </c>
       <c r="F610" t="n">
         <v>20933600</v>
@@ -12672,16 +12672,16 @@
         <v>45049</v>
       </c>
       <c r="B613" t="n">
-        <v>29.14794158935547</v>
+        <v>29.14793968200684</v>
       </c>
       <c r="C613" t="n">
-        <v>29.61949529963673</v>
+        <v>29.61949336143113</v>
       </c>
       <c r="D613" t="n">
-        <v>28.33254592932366</v>
+        <v>28.33254407533193</v>
       </c>
       <c r="E613" t="n">
-        <v>29.26583095381972</v>
+        <v>29.26582903875679</v>
       </c>
       <c r="F613" t="n">
         <v>9250000</v>
@@ -12692,16 +12692,16 @@
         <v>45050</v>
       </c>
       <c r="B614" t="n">
-        <v>29.27565383911133</v>
+        <v>29.2756519317627</v>
       </c>
       <c r="C614" t="n">
-        <v>29.95351348008578</v>
+        <v>29.95351152857367</v>
       </c>
       <c r="D614" t="n">
-        <v>29.17741488650197</v>
+        <v>29.17741298555374</v>
       </c>
       <c r="E614" t="n">
-        <v>29.47213549190587</v>
+        <v>29.47213357175619</v>
       </c>
       <c r="F614" t="n">
         <v>6670900</v>
@@ -12792,16 +12792,16 @@
         <v>45057</v>
       </c>
       <c r="B619" t="n">
-        <v>31.66289710998535</v>
+        <v>31.66289520263672</v>
       </c>
       <c r="C619" t="n">
-        <v>31.81025928645763</v>
+        <v>31.81025737023202</v>
       </c>
       <c r="D619" t="n">
-        <v>31.10292683551199</v>
+        <v>31.10292496189554</v>
       </c>
       <c r="E619" t="n">
-        <v>31.71201658628417</v>
+        <v>31.71201467597662</v>
       </c>
       <c r="F619" t="n">
         <v>4858000</v>
@@ -12812,16 +12812,16 @@
         <v>45058</v>
       </c>
       <c r="B620" t="n">
-        <v>32.49794387817383</v>
+        <v>32.49794006347656</v>
       </c>
       <c r="C620" t="n">
-        <v>32.64530231015733</v>
+        <v>32.64529847816273</v>
       </c>
       <c r="D620" t="n">
-        <v>31.46641611640984</v>
+        <v>31.46641242279611</v>
       </c>
       <c r="E620" t="n">
-        <v>31.55483267463029</v>
+        <v>31.554828970638</v>
       </c>
       <c r="F620" t="n">
         <v>5317000</v>
@@ -12852,16 +12852,16 @@
         <v>45062</v>
       </c>
       <c r="B622" t="n">
-        <v>29.90439414978027</v>
+        <v>29.90439224243164</v>
       </c>
       <c r="C622" t="n">
-        <v>32.08533151226543</v>
+        <v>32.08532946581322</v>
       </c>
       <c r="D622" t="n">
-        <v>29.70791249602647</v>
+        <v>29.70791060120974</v>
       </c>
       <c r="E622" t="n">
-        <v>31.86920131837866</v>
+        <v>31.86919928571158</v>
       </c>
       <c r="F622" t="n">
         <v>13269700</v>
@@ -12912,16 +12912,16 @@
         <v>45065</v>
       </c>
       <c r="B625" t="n">
-        <v>32.49794387817383</v>
+        <v>32.49794006347656</v>
       </c>
       <c r="C625" t="n">
-        <v>34.87536105853923</v>
+        <v>34.87535696477425</v>
       </c>
       <c r="D625" t="n">
-        <v>31.0439837395418</v>
+        <v>31.04398009551434</v>
       </c>
       <c r="E625" t="n">
-        <v>31.86920182661951</v>
+        <v>31.8691980857257</v>
       </c>
       <c r="F625" t="n">
         <v>19443700</v>
@@ -12972,16 +12972,16 @@
         <v>45070</v>
       </c>
       <c r="B628" t="n">
-        <v>31.48606109619141</v>
+        <v>31.48606300354004</v>
       </c>
       <c r="C628" t="n">
-        <v>31.86919822262693</v>
+        <v>31.86920015318507</v>
       </c>
       <c r="D628" t="n">
-        <v>30.46436146776744</v>
+        <v>30.464363313224</v>
       </c>
       <c r="E628" t="n">
-        <v>31.04398022887067</v>
+        <v>31.04398210943912</v>
       </c>
       <c r="F628" t="n">
         <v>7685200</v>
@@ -13212,16 +13212,16 @@
         <v>45089</v>
       </c>
       <c r="B640" t="n">
-        <v>31.26011085510254</v>
+        <v>31.26010894775391</v>
       </c>
       <c r="C640" t="n">
-        <v>31.86920059509758</v>
+        <v>31.86919865058509</v>
       </c>
       <c r="D640" t="n">
-        <v>30.47418800549994</v>
+        <v>30.47418614610471</v>
       </c>
       <c r="E640" t="n">
-        <v>31.61377707431765</v>
+        <v>31.61377514538992</v>
       </c>
       <c r="F640" t="n">
         <v>7223600</v>
@@ -13252,16 +13252,16 @@
         <v>45091</v>
       </c>
       <c r="B642" t="n">
-        <v>31.14222145080566</v>
+        <v>31.1422233581543</v>
       </c>
       <c r="C642" t="n">
-        <v>31.71201407641177</v>
+        <v>31.71201601865814</v>
       </c>
       <c r="D642" t="n">
-        <v>30.5724269514118</v>
+        <v>30.57242882386257</v>
       </c>
       <c r="E642" t="n">
-        <v>31.33870121423831</v>
+        <v>31.33870313362062</v>
       </c>
       <c r="F642" t="n">
         <v>8288400</v>
@@ -13292,16 +13292,16 @@
         <v>45093</v>
       </c>
       <c r="B644" t="n">
-        <v>31.9183235168457</v>
+        <v>31.91832160949707</v>
       </c>
       <c r="C644" t="n">
-        <v>31.9183235168457</v>
+        <v>31.91832160949707</v>
       </c>
       <c r="D644" t="n">
-        <v>31.19134254558997</v>
+        <v>31.19134068168367</v>
       </c>
       <c r="E644" t="n">
-        <v>31.4271193982454</v>
+        <v>31.42711752024974</v>
       </c>
       <c r="F644" t="n">
         <v>5722800</v>
@@ -13332,16 +13332,16 @@
         <v>45097</v>
       </c>
       <c r="B646" t="n">
-        <v>32.16392517089844</v>
+        <v>32.16392135620117</v>
       </c>
       <c r="C646" t="n">
-        <v>32.2916350584061</v>
+        <v>32.29163122856222</v>
       </c>
       <c r="D646" t="n">
-        <v>31.48606366340425</v>
+        <v>31.48605992910253</v>
       </c>
       <c r="E646" t="n">
-        <v>32.12462809124572</v>
+        <v>32.12462428120915</v>
       </c>
       <c r="F646" t="n">
         <v>4954700</v>
@@ -13352,16 +13352,16 @@
         <v>45098</v>
       </c>
       <c r="B647" t="n">
-        <v>32.06567764282227</v>
+        <v>32.06568145751953</v>
       </c>
       <c r="C647" t="n">
-        <v>32.36039820068254</v>
+        <v>32.36040205044127</v>
       </c>
       <c r="D647" t="n">
-        <v>31.4860589217478</v>
+        <v>31.48606266749066</v>
       </c>
       <c r="E647" t="n">
-        <v>32.1246232534244</v>
+        <v>32.12462707513414</v>
       </c>
       <c r="F647" t="n">
         <v>4670300</v>
@@ -13412,16 +13412,16 @@
         <v>45103</v>
       </c>
       <c r="B650" t="n">
-        <v>30.53312873840332</v>
+        <v>30.53313064575195</v>
       </c>
       <c r="C650" t="n">
-        <v>30.83767357835474</v>
+        <v>30.83767550472773</v>
       </c>
       <c r="D650" t="n">
-        <v>30.30717617565832</v>
+        <v>30.30717806889212</v>
       </c>
       <c r="E650" t="n">
-        <v>30.58224820898695</v>
+        <v>30.58225011940398</v>
       </c>
       <c r="F650" t="n">
         <v>2874500</v>
@@ -13452,16 +13452,16 @@
         <v>45105</v>
       </c>
       <c r="B652" t="n">
-        <v>29.37389373779297</v>
+        <v>29.37389183044434</v>
       </c>
       <c r="C652" t="n">
-        <v>30.06157762706682</v>
+        <v>30.06157567506449</v>
       </c>
       <c r="D652" t="n">
-        <v>29.30512572362315</v>
+        <v>29.30512382073987</v>
       </c>
       <c r="E652" t="n">
-        <v>29.75703276126285</v>
+        <v>29.75703082903567</v>
       </c>
       <c r="F652" t="n">
         <v>4532500</v>
@@ -13532,16 +13532,16 @@
         <v>45111</v>
       </c>
       <c r="B656" t="n">
-        <v>29.80615043640137</v>
+        <v>29.80615234375</v>
       </c>
       <c r="C656" t="n">
-        <v>30.15981662939312</v>
+        <v>30.15981855937348</v>
       </c>
       <c r="D656" t="n">
-        <v>29.57037359900278</v>
+        <v>29.57037549126363</v>
       </c>
       <c r="E656" t="n">
-        <v>29.80615043640137</v>
+        <v>29.80615234375</v>
       </c>
       <c r="F656" t="n">
         <v>2514900</v>
@@ -13552,16 +13552,16 @@
         <v>45112</v>
       </c>
       <c r="B657" t="n">
-        <v>30.40541839599609</v>
+        <v>30.40542030334473</v>
       </c>
       <c r="C657" t="n">
-        <v>30.70996325002402</v>
+        <v>30.70996517647691</v>
       </c>
       <c r="D657" t="n">
-        <v>29.34442166777476</v>
+        <v>29.34442350856649</v>
       </c>
       <c r="E657" t="n">
-        <v>29.60966944448926</v>
+        <v>29.60967130192012</v>
       </c>
       <c r="F657" t="n">
         <v>5394800</v>
@@ -13612,16 +13612,16 @@
         <v>45117</v>
       </c>
       <c r="B660" t="n">
-        <v>31.07345199584961</v>
+        <v>31.07345390319824</v>
       </c>
       <c r="C660" t="n">
-        <v>31.93796708924193</v>
+        <v>31.93796904965617</v>
       </c>
       <c r="D660" t="n">
-        <v>30.84749942157282</v>
+        <v>30.84750131505205</v>
       </c>
       <c r="E660" t="n">
-        <v>31.56465609569361</v>
+        <v>31.56465803319331</v>
       </c>
       <c r="F660" t="n">
         <v>7339200</v>
@@ -13652,16 +13652,16 @@
         <v>45119</v>
       </c>
       <c r="B662" t="n">
-        <v>31.07345199584961</v>
+        <v>31.07345390319824</v>
       </c>
       <c r="C662" t="n">
-        <v>32.08532925608902</v>
+        <v>32.08533122554864</v>
       </c>
       <c r="D662" t="n">
-        <v>31.04398106151042</v>
+        <v>31.04398296705007</v>
       </c>
       <c r="E662" t="n">
-        <v>31.77096013121909</v>
+        <v>31.77096208138212</v>
       </c>
       <c r="F662" t="n">
         <v>4503800</v>
@@ -13732,16 +13732,16 @@
         <v>45125</v>
       </c>
       <c r="B666" t="n">
-        <v>32.91055297851562</v>
+        <v>32.91054916381836</v>
       </c>
       <c r="C666" t="n">
-        <v>33.03826662148488</v>
+        <v>33.03826279198419</v>
       </c>
       <c r="D666" t="n">
-        <v>32.03621351392245</v>
+        <v>32.0362098005708</v>
       </c>
       <c r="E666" t="n">
-        <v>32.18357195035527</v>
+        <v>32.18356821992315</v>
       </c>
       <c r="F666" t="n">
         <v>4775600</v>
@@ -13752,16 +13752,16 @@
         <v>45126</v>
       </c>
       <c r="B667" t="n">
-        <v>33.6473503112793</v>
+        <v>33.64735412597656</v>
       </c>
       <c r="C667" t="n">
-        <v>34.04031356576963</v>
+        <v>34.04031742501827</v>
       </c>
       <c r="D667" t="n">
-        <v>33.04808303459044</v>
+        <v>33.04808678134705</v>
       </c>
       <c r="E667" t="n">
-        <v>33.04808303459044</v>
+        <v>33.04808678134705</v>
       </c>
       <c r="F667" t="n">
         <v>7484200</v>
@@ -13772,16 +13772,16 @@
         <v>45127</v>
       </c>
       <c r="B668" t="n">
-        <v>33.92242813110352</v>
+        <v>33.92242431640625</v>
       </c>
       <c r="C668" t="n">
-        <v>34.11890979188617</v>
+        <v>34.11890595509385</v>
       </c>
       <c r="D668" t="n">
-        <v>33.64735605455338</v>
+        <v>33.64735227078894</v>
       </c>
       <c r="E668" t="n">
-        <v>33.91260573447357</v>
+        <v>33.91260192088087</v>
       </c>
       <c r="F668" t="n">
         <v>3587900</v>
@@ -13952,16 +13952,16 @@
         <v>45140</v>
       </c>
       <c r="B677" t="n">
-        <v>34.4431037902832</v>
+        <v>34.44309997558594</v>
       </c>
       <c r="C677" t="n">
-        <v>34.5806398233511</v>
+        <v>34.58063599342123</v>
       </c>
       <c r="D677" t="n">
-        <v>33.71612279718397</v>
+        <v>33.71611906300245</v>
       </c>
       <c r="E677" t="n">
-        <v>34.38415817000732</v>
+        <v>34.38415436183849</v>
       </c>
       <c r="F677" t="n">
         <v>3408800</v>
@@ -14012,16 +14012,16 @@
         <v>45145</v>
       </c>
       <c r="B680" t="n">
-        <v>35.68092727661133</v>
+        <v>35.68093109130859</v>
       </c>
       <c r="C680" t="n">
-        <v>36.15248093584172</v>
+        <v>36.15248480095344</v>
       </c>
       <c r="D680" t="n">
-        <v>35.09148613946717</v>
+        <v>35.09148989114647</v>
       </c>
       <c r="E680" t="n">
-        <v>36.05424199550948</v>
+        <v>36.05424585011833</v>
       </c>
       <c r="F680" t="n">
         <v>3820600</v>
@@ -14032,16 +14032,16 @@
         <v>45146</v>
       </c>
       <c r="B681" t="n">
-        <v>36.34896469116211</v>
+        <v>36.34896850585938</v>
       </c>
       <c r="C681" t="n">
-        <v>36.51597164901496</v>
+        <v>36.51597548123902</v>
       </c>
       <c r="D681" t="n">
-        <v>34.30556163401185</v>
+        <v>34.30556523426109</v>
       </c>
       <c r="E681" t="n">
-        <v>34.76729292525891</v>
+        <v>34.76729657396523</v>
       </c>
       <c r="F681" t="n">
         <v>5274900</v>
@@ -14172,16 +14172,16 @@
         <v>45155</v>
       </c>
       <c r="B688" t="n">
-        <v>31.26993370056152</v>
+        <v>31.26993560791016</v>
       </c>
       <c r="C688" t="n">
-        <v>31.74148926263102</v>
+        <v>31.74149119874277</v>
       </c>
       <c r="D688" t="n">
-        <v>30.9653888444364</v>
+        <v>30.96539073320894</v>
       </c>
       <c r="E688" t="n">
-        <v>31.46641346711834</v>
+        <v>31.4664153864515</v>
       </c>
       <c r="F688" t="n">
         <v>4529600</v>
@@ -14252,16 +14252,16 @@
         <v>45161</v>
       </c>
       <c r="B692" t="n">
-        <v>31.05380630493164</v>
+        <v>31.05380439758301</v>
       </c>
       <c r="C692" t="n">
-        <v>31.2404618075605</v>
+        <v>31.24045988874735</v>
       </c>
       <c r="D692" t="n">
-        <v>30.68049155209822</v>
+        <v>30.68048966767887</v>
       </c>
       <c r="E692" t="n">
-        <v>31.09310150987904</v>
+        <v>31.09309960011686</v>
       </c>
       <c r="F692" t="n">
         <v>4847400</v>
@@ -14272,16 +14272,16 @@
         <v>45162</v>
       </c>
       <c r="B693" t="n">
-        <v>30.91626930236816</v>
+        <v>30.91626739501953</v>
       </c>
       <c r="C693" t="n">
-        <v>31.30923260599883</v>
+        <v>31.30923067440671</v>
       </c>
       <c r="D693" t="n">
-        <v>30.56260495240363</v>
+        <v>30.56260306687397</v>
       </c>
       <c r="E693" t="n">
-        <v>31.05380720815405</v>
+        <v>31.05380529232016</v>
       </c>
       <c r="F693" t="n">
         <v>3471700</v>
@@ -14332,16 +14332,16 @@
         <v>45167</v>
       </c>
       <c r="B696" t="n">
-        <v>31.29940795898438</v>
+        <v>31.29940605163574</v>
       </c>
       <c r="C696" t="n">
-        <v>31.55483147996431</v>
+        <v>31.55482955705047</v>
       </c>
       <c r="D696" t="n">
-        <v>30.63137259940515</v>
+        <v>30.63137073276579</v>
       </c>
       <c r="E696" t="n">
-        <v>31.06363110391898</v>
+        <v>31.06362921093831</v>
       </c>
       <c r="F696" t="n">
         <v>3743200</v>
@@ -14352,16 +14352,16 @@
         <v>45168</v>
       </c>
       <c r="B697" t="n">
-        <v>31.6334228515625</v>
+        <v>31.63342475891113</v>
       </c>
       <c r="C697" t="n">
-        <v>31.70219086067396</v>
+        <v>31.70219277216898</v>
       </c>
       <c r="D697" t="n">
-        <v>30.96538755084366</v>
+        <v>30.96538941791287</v>
       </c>
       <c r="E697" t="n">
-        <v>31.49588683333958</v>
+        <v>31.49588873239543</v>
       </c>
       <c r="F697" t="n">
         <v>3276100</v>
@@ -14412,16 +14412,16 @@
         <v>45173</v>
       </c>
       <c r="B700" t="n">
-        <v>32.2719841003418</v>
+        <v>32.27198791503906</v>
       </c>
       <c r="C700" t="n">
-        <v>32.55688228511206</v>
+        <v>32.55688613348561</v>
       </c>
       <c r="D700" t="n">
-        <v>32.06568006898767</v>
+        <v>32.06568385929886</v>
       </c>
       <c r="E700" t="n">
-        <v>32.22286462824446</v>
+        <v>32.22286843713558</v>
       </c>
       <c r="F700" t="n">
         <v>2652900</v>
@@ -14432,16 +14432,16 @@
         <v>45174</v>
       </c>
       <c r="B701" t="n">
-        <v>32.63547515869141</v>
+        <v>32.63547897338867</v>
       </c>
       <c r="C701" t="n">
-        <v>32.93019572729314</v>
+        <v>32.93019957643972</v>
       </c>
       <c r="D701" t="n">
-        <v>32.07550495407551</v>
+        <v>32.07550870331895</v>
       </c>
       <c r="E701" t="n">
-        <v>32.27198283475976</v>
+        <v>32.27198660696912</v>
       </c>
       <c r="F701" t="n">
         <v>6036900</v>
@@ -14452,16 +14452,16 @@
         <v>45175</v>
       </c>
       <c r="B702" t="n">
-        <v>32.00674057006836</v>
+        <v>32.00673675537109</v>
       </c>
       <c r="C702" t="n">
-        <v>32.71406926527997</v>
+        <v>32.71406536628031</v>
       </c>
       <c r="D702" t="n">
-        <v>31.92814641083608</v>
+        <v>31.928142605506</v>
       </c>
       <c r="E702" t="n">
-        <v>32.65512739343153</v>
+        <v>32.65512350145682</v>
       </c>
       <c r="F702" t="n">
         <v>4505300</v>
@@ -14512,16 +14512,16 @@
         <v>45181</v>
       </c>
       <c r="B705" t="n">
-        <v>32.3309326171875</v>
+        <v>32.33092880249023</v>
       </c>
       <c r="C705" t="n">
-        <v>32.6453017639165</v>
+        <v>32.64529791212711</v>
       </c>
       <c r="D705" t="n">
-        <v>31.76113994408213</v>
+        <v>31.76113619661418</v>
       </c>
       <c r="E705" t="n">
-        <v>31.97726639022342</v>
+        <v>31.97726261725491</v>
       </c>
       <c r="F705" t="n">
         <v>3620500</v>
@@ -14532,16 +14532,16 @@
         <v>45182</v>
       </c>
       <c r="B706" t="n">
-        <v>31.6334228515625</v>
+        <v>31.63342475891113</v>
       </c>
       <c r="C706" t="n">
-        <v>32.11479891534272</v>
+        <v>32.1148008517161</v>
       </c>
       <c r="D706" t="n">
-        <v>31.44676361462388</v>
+        <v>31.44676551071783</v>
       </c>
       <c r="E706" t="n">
-        <v>31.60394817081799</v>
+        <v>31.60395007638945</v>
       </c>
       <c r="F706" t="n">
         <v>7302700</v>
@@ -14552,16 +14552,16 @@
         <v>45183</v>
       </c>
       <c r="B707" t="n">
-        <v>32.311279296875</v>
+        <v>32.31128311157227</v>
       </c>
       <c r="C707" t="n">
-        <v>32.311279296875</v>
+        <v>32.31128311157227</v>
       </c>
       <c r="D707" t="n">
-        <v>31.74148670806588</v>
+        <v>31.74149045549294</v>
       </c>
       <c r="E707" t="n">
-        <v>31.83972564654409</v>
+        <v>31.83972940556933</v>
       </c>
       <c r="F707" t="n">
         <v>4362300</v>
@@ -14592,16 +14592,16 @@
         <v>45187</v>
       </c>
       <c r="B709" t="n">
-        <v>31.98709297180176</v>
+        <v>31.98709106445312</v>
       </c>
       <c r="C709" t="n">
-        <v>32.71407022822005</v>
+        <v>32.7140682775227</v>
       </c>
       <c r="D709" t="n">
-        <v>31.75131423474054</v>
+        <v>31.75131234145109</v>
       </c>
       <c r="E709" t="n">
-        <v>32.55688565270453</v>
+        <v>32.5568837113799</v>
       </c>
       <c r="F709" t="n">
         <v>5099000</v>
@@ -14692,16 +14692,16 @@
         <v>45194</v>
       </c>
       <c r="B714" t="n">
-        <v>30.95556640625</v>
+        <v>30.95556449890137</v>
       </c>
       <c r="C714" t="n">
-        <v>31.20116753431566</v>
+        <v>31.20116561183414</v>
       </c>
       <c r="D714" t="n">
-        <v>29.99281043394172</v>
+        <v>29.99280858591396</v>
       </c>
       <c r="E714" t="n">
-        <v>30.45453988014151</v>
+        <v>30.45453800366397</v>
       </c>
       <c r="F714" t="n">
         <v>6350700</v>
@@ -14712,16 +14712,16 @@
         <v>45195</v>
       </c>
       <c r="B715" t="n">
-        <v>30.32682800292969</v>
+        <v>30.32682609558105</v>
       </c>
       <c r="C715" t="n">
-        <v>30.83767692328888</v>
+        <v>30.83767498381136</v>
       </c>
       <c r="D715" t="n">
-        <v>30.19911436749897</v>
+        <v>30.19911246818264</v>
       </c>
       <c r="E715" t="n">
-        <v>30.75908463755763</v>
+        <v>30.75908270302303</v>
       </c>
       <c r="F715" t="n">
         <v>3433500</v>
@@ -14732,16 +14732,16 @@
         <v>45196</v>
       </c>
       <c r="B716" t="n">
-        <v>30.86714744567871</v>
+        <v>30.86714935302734</v>
       </c>
       <c r="C716" t="n">
-        <v>31.07345147776449</v>
+        <v>31.0734533978611</v>
       </c>
       <c r="D716" t="n">
-        <v>30.42506470008381</v>
+        <v>30.42506658011519</v>
       </c>
       <c r="E716" t="n">
-        <v>30.65101914438107</v>
+        <v>30.65102103837466</v>
       </c>
       <c r="F716" t="n">
         <v>4307600</v>
@@ -14752,16 +14752,16 @@
         <v>45197</v>
       </c>
       <c r="B717" t="n">
-        <v>30.58225059509277</v>
+        <v>30.58224868774414</v>
       </c>
       <c r="C717" t="n">
-        <v>31.21099073558775</v>
+        <v>31.21098878902595</v>
       </c>
       <c r="D717" t="n">
-        <v>30.41524175877521</v>
+        <v>30.41523986184255</v>
       </c>
       <c r="E717" t="n">
-        <v>30.82785171474873</v>
+        <v>30.82784979208249</v>
       </c>
       <c r="F717" t="n">
         <v>4298000</v>
@@ -14772,16 +14772,16 @@
         <v>45198</v>
       </c>
       <c r="B718" t="n">
-        <v>31.02433204650879</v>
+        <v>31.02433395385742</v>
       </c>
       <c r="C718" t="n">
-        <v>31.60394894047274</v>
+        <v>31.60395088345571</v>
       </c>
       <c r="D718" t="n">
-        <v>30.47418608643163</v>
+        <v>30.47418795995777</v>
       </c>
       <c r="E718" t="n">
-        <v>30.86714748648674</v>
+        <v>30.86714938417181</v>
       </c>
       <c r="F718" t="n">
         <v>5846000</v>
@@ -14852,16 +14852,16 @@
         <v>45204</v>
       </c>
       <c r="B722" t="n">
-        <v>28.0378246307373</v>
+        <v>28.03782272338867</v>
       </c>
       <c r="C722" t="n">
-        <v>28.78445038319864</v>
+        <v>28.78444842505877</v>
       </c>
       <c r="D722" t="n">
-        <v>27.72345362458937</v>
+        <v>27.72345173862667</v>
       </c>
       <c r="E722" t="n">
-        <v>28.62726581701858</v>
+        <v>28.62726386957162</v>
       </c>
       <c r="F722" t="n">
         <v>8409300</v>
@@ -14912,16 +14912,16 @@
         <v>45209</v>
       </c>
       <c r="B725" t="n">
-        <v>30.2777042388916</v>
+        <v>30.27770614624023</v>
       </c>
       <c r="C725" t="n">
-        <v>30.40541786413846</v>
+        <v>30.40541977953243</v>
       </c>
       <c r="D725" t="n">
-        <v>29.43283582930937</v>
+        <v>29.43283768343539</v>
       </c>
       <c r="E725" t="n">
-        <v>29.7570310901109</v>
+        <v>29.75703296465965</v>
       </c>
       <c r="F725" t="n">
         <v>7018100</v>
@@ -14972,16 +14972,16 @@
         <v>45215</v>
       </c>
       <c r="B728" t="n">
-        <v>31.67272186279297</v>
+        <v>31.67271995544434</v>
       </c>
       <c r="C728" t="n">
-        <v>32.01656192935982</v>
+        <v>32.01656000130495</v>
       </c>
       <c r="D728" t="n">
-        <v>31.32887804865046</v>
+        <v>31.32887616200829</v>
       </c>
       <c r="E728" t="n">
-        <v>31.91832298107662</v>
+        <v>31.91832105893775</v>
       </c>
       <c r="F728" t="n">
         <v>3741500</v>
@@ -15012,16 +15012,16 @@
         <v>45217</v>
       </c>
       <c r="B730" t="n">
-        <v>32.06567764282227</v>
+        <v>32.06568145751953</v>
       </c>
       <c r="C730" t="n">
-        <v>33.06773053760736</v>
+        <v>33.06773447151397</v>
       </c>
       <c r="D730" t="n">
-        <v>31.63342107446555</v>
+        <v>31.63342483773936</v>
       </c>
       <c r="E730" t="n">
-        <v>32.52740889026767</v>
+        <v>32.52741275989484</v>
       </c>
       <c r="F730" t="n">
         <v>7439800</v>
@@ -15132,16 +15132,16 @@
         <v>45225</v>
       </c>
       <c r="B736" t="n">
-        <v>31.98709297180176</v>
+        <v>31.98709106445312</v>
       </c>
       <c r="C736" t="n">
-        <v>32.12462900693085</v>
+        <v>32.12462709138111</v>
       </c>
       <c r="D736" t="n">
-        <v>31.19134395024304</v>
+        <v>31.19134209034388</v>
       </c>
       <c r="E736" t="n">
-        <v>31.57448111883861</v>
+        <v>31.57447923609348</v>
       </c>
       <c r="F736" t="n">
         <v>2923500</v>
@@ -15152,16 +15152,16 @@
         <v>45226</v>
       </c>
       <c r="B737" t="n">
-        <v>31.52536010742188</v>
+        <v>31.52535820007324</v>
       </c>
       <c r="C737" t="n">
-        <v>32.55688406826494</v>
+        <v>32.556882098507</v>
       </c>
       <c r="D737" t="n">
-        <v>31.24046190704763</v>
+        <v>31.24046001693592</v>
       </c>
       <c r="E737" t="n">
-        <v>32.32110909025403</v>
+        <v>32.32110713476096</v>
       </c>
       <c r="F737" t="n">
         <v>3378100</v>
@@ -15172,16 +15172,16 @@
         <v>45229</v>
       </c>
       <c r="B738" t="n">
-        <v>31.07345199584961</v>
+        <v>31.07345390319824</v>
       </c>
       <c r="C738" t="n">
-        <v>32.11480019042821</v>
+        <v>32.11480216169681</v>
       </c>
       <c r="D738" t="n">
-        <v>30.98503731904426</v>
+        <v>30.98503922096583</v>
       </c>
       <c r="E738" t="n">
-        <v>31.5450075569423</v>
+        <v>31.54500949323592</v>
       </c>
       <c r="F738" t="n">
         <v>3227500</v>
@@ -15192,16 +15192,16 @@
         <v>45230</v>
       </c>
       <c r="B739" t="n">
-        <v>31.86919975280762</v>
+        <v>31.86919784545898</v>
       </c>
       <c r="C739" t="n">
-        <v>32.10497847524474</v>
+        <v>32.10497655378492</v>
       </c>
       <c r="D739" t="n">
-        <v>31.2011662851952</v>
+        <v>31.20116441782789</v>
       </c>
       <c r="E739" t="n">
-        <v>31.2011662851952</v>
+        <v>31.20116441782789</v>
       </c>
       <c r="F739" t="n">
         <v>3372100</v>
@@ -15212,16 +15212,16 @@
         <v>45231</v>
       </c>
       <c r="B740" t="n">
-        <v>32.06567764282227</v>
+        <v>32.06568145751953</v>
       </c>
       <c r="C740" t="n">
-        <v>32.74353904823363</v>
+        <v>32.74354294357276</v>
       </c>
       <c r="D740" t="n">
-        <v>31.9477901691932</v>
+        <v>31.94779396986597</v>
       </c>
       <c r="E740" t="n">
-        <v>32.07550378504357</v>
+        <v>32.0755076009098</v>
       </c>
       <c r="F740" t="n">
         <v>4282500</v>
@@ -15232,16 +15232,16 @@
         <v>45233</v>
       </c>
       <c r="B741" t="n">
-        <v>32.69441986083984</v>
+        <v>32.69441604614258</v>
       </c>
       <c r="C741" t="n">
-        <v>32.94984712401398</v>
+        <v>32.94984327951414</v>
       </c>
       <c r="D741" t="n">
-        <v>32.46846728038622</v>
+        <v>32.4684634920525</v>
       </c>
       <c r="E741" t="n">
-        <v>32.73371693941674</v>
+        <v>32.7337131201344</v>
       </c>
       <c r="F741" t="n">
         <v>3190300</v>
@@ -15272,16 +15272,16 @@
         <v>45237</v>
       </c>
       <c r="B743" t="n">
-        <v>32.48811721801758</v>
+        <v>32.48811340332031</v>
       </c>
       <c r="C743" t="n">
-        <v>32.63547939523581</v>
+        <v>32.63547556323554</v>
       </c>
       <c r="D743" t="n">
-        <v>31.81025944748058</v>
+        <v>31.81025571237618</v>
       </c>
       <c r="E743" t="n">
-        <v>31.8790274641622</v>
+        <v>31.87902372098318</v>
       </c>
       <c r="F743" t="n">
         <v>3324000</v>
@@ -15312,16 +15312,16 @@
         <v>45239</v>
       </c>
       <c r="B745" t="n">
-        <v>30.81802749633789</v>
+        <v>30.81802940368652</v>
       </c>
       <c r="C745" t="n">
-        <v>33.77506502697286</v>
+        <v>33.77506711733456</v>
       </c>
       <c r="D745" t="n">
-        <v>30.67066533422895</v>
+        <v>30.67066723245724</v>
       </c>
       <c r="E745" t="n">
-        <v>33.41157269312426</v>
+        <v>33.41157476098916</v>
       </c>
       <c r="F745" t="n">
         <v>15431300</v>
@@ -15332,16 +15332,16 @@
         <v>45240</v>
       </c>
       <c r="B746" t="n">
-        <v>31.25028610229492</v>
+        <v>31.25028419494629</v>
       </c>
       <c r="C746" t="n">
-        <v>32.06568174882637</v>
+        <v>32.06567979171039</v>
       </c>
       <c r="D746" t="n">
-        <v>31.04398206013306</v>
+        <v>31.04398016537612</v>
       </c>
       <c r="E746" t="n">
-        <v>31.05380632982475</v>
+        <v>31.05380443446818</v>
       </c>
       <c r="F746" t="n">
         <v>4738300</v>
@@ -15352,16 +15352,16 @@
         <v>45243</v>
       </c>
       <c r="B747" t="n">
-        <v>30.94573974609375</v>
+        <v>30.94574165344238</v>
       </c>
       <c r="C747" t="n">
-        <v>31.41729342584897</v>
+        <v>31.41729536226194</v>
       </c>
       <c r="D747" t="n">
-        <v>30.67066582934266</v>
+        <v>30.67066771973704</v>
       </c>
       <c r="E747" t="n">
-        <v>31.21098939362647</v>
+        <v>31.21099131732383</v>
       </c>
       <c r="F747" t="n">
         <v>3172300</v>
@@ -15392,16 +15392,16 @@
         <v>45246</v>
       </c>
       <c r="B749" t="n">
-        <v>31.13239860534668</v>
+        <v>31.13239669799805</v>
       </c>
       <c r="C749" t="n">
-        <v>32.13444975439192</v>
+        <v>32.13444778565191</v>
       </c>
       <c r="D749" t="n">
-        <v>30.68049156858774</v>
+        <v>30.68048968892551</v>
       </c>
       <c r="E749" t="n">
-        <v>31.78078354073604</v>
+        <v>31.78078159366364</v>
       </c>
       <c r="F749" t="n">
         <v>5148500</v>
@@ -15492,16 +15492,16 @@
         <v>45253</v>
       </c>
       <c r="B754" t="n">
-        <v>31.81025505065918</v>
+        <v>31.81025886535645</v>
       </c>
       <c r="C754" t="n">
-        <v>32.00673667726713</v>
+        <v>32.00674051552654</v>
       </c>
       <c r="D754" t="n">
-        <v>31.5843024917114</v>
+        <v>31.58430627931235</v>
       </c>
       <c r="E754" t="n">
-        <v>31.82990358807751</v>
+        <v>31.82990740513103</v>
       </c>
       <c r="F754" t="n">
         <v>2086300</v>
@@ -15552,16 +15552,16 @@
         <v>45258</v>
       </c>
       <c r="B757" t="n">
-        <v>29.80615043640137</v>
+        <v>29.80615234375</v>
       </c>
       <c r="C757" t="n">
-        <v>30.21876037029583</v>
+        <v>30.21876230404811</v>
       </c>
       <c r="D757" t="n">
-        <v>29.63914160902057</v>
+        <v>29.63914350568201</v>
       </c>
       <c r="E757" t="n">
-        <v>30.17946329383553</v>
+        <v>30.17946522507312</v>
       </c>
       <c r="F757" t="n">
         <v>5777500</v>
@@ -15592,16 +15592,16 @@
         <v>45260</v>
       </c>
       <c r="B759" t="n">
-        <v>29.45248603820801</v>
+        <v>29.45248413085938</v>
       </c>
       <c r="C759" t="n">
-        <v>29.83562506189301</v>
+        <v>29.83562312973222</v>
       </c>
       <c r="D759" t="n">
-        <v>29.1774139813743</v>
+        <v>29.17741209183939</v>
       </c>
       <c r="E759" t="n">
-        <v>29.66861622433489</v>
+        <v>29.66861430298963</v>
       </c>
       <c r="F759" t="n">
         <v>4483800</v>
@@ -15732,16 +15732,16 @@
         <v>45271</v>
       </c>
       <c r="B766" t="n">
-        <v>26.91788101196289</v>
+        <v>26.91788291931152</v>
       </c>
       <c r="C766" t="n">
-        <v>27.08488984004369</v>
+        <v>27.08489175922624</v>
       </c>
       <c r="D766" t="n">
-        <v>26.48562253802652</v>
+        <v>26.48562441474616</v>
       </c>
       <c r="E766" t="n">
-        <v>26.96700235774415</v>
+        <v>26.96700426857343</v>
       </c>
       <c r="F766" t="n">
         <v>6627000</v>
@@ -15792,16 +15792,16 @@
         <v>45274</v>
       </c>
       <c r="B769" t="n">
-        <v>27.00629997253418</v>
+        <v>27.00629806518555</v>
       </c>
       <c r="C769" t="n">
-        <v>27.20278162563166</v>
+        <v>27.2027797044063</v>
       </c>
       <c r="D769" t="n">
-        <v>26.49544917351107</v>
+        <v>26.49544730224182</v>
       </c>
       <c r="E769" t="n">
-        <v>26.82946685950403</v>
+        <v>26.82946496464443</v>
       </c>
       <c r="F769" t="n">
         <v>14011300</v>
@@ -15812,16 +15812,16 @@
         <v>45275</v>
       </c>
       <c r="B770" t="n">
-        <v>25.8863582611084</v>
+        <v>25.88635635375977</v>
       </c>
       <c r="C770" t="n">
-        <v>27.21260467558413</v>
+        <v>27.21260267051552</v>
       </c>
       <c r="D770" t="n">
-        <v>25.8863582611084</v>
+        <v>25.88635635375977</v>
       </c>
       <c r="E770" t="n">
-        <v>27.16348332761816</v>
+        <v>27.1634813261689</v>
       </c>
       <c r="F770" t="n">
         <v>11924000</v>
@@ -15832,16 +15832,16 @@
         <v>45278</v>
       </c>
       <c r="B771" t="n">
-        <v>26.21055221557617</v>
+        <v>26.21055030822754</v>
       </c>
       <c r="C771" t="n">
-        <v>26.76069820788825</v>
+        <v>26.76069626050536</v>
       </c>
       <c r="D771" t="n">
-        <v>25.94530255232668</v>
+        <v>25.94530066428034</v>
       </c>
       <c r="E771" t="n">
-        <v>26.12213566115967</v>
+        <v>26.12213376024514</v>
       </c>
       <c r="F771" t="n">
         <v>4958200</v>
@@ -15852,16 +15852,16 @@
         <v>45279</v>
       </c>
       <c r="B772" t="n">
-        <v>26.32843780517578</v>
+        <v>26.32843971252441</v>
       </c>
       <c r="C772" t="n">
-        <v>26.52491943942738</v>
+        <v>26.52492136101001</v>
       </c>
       <c r="D772" t="n">
-        <v>26.13195804471192</v>
+        <v>26.13195993782669</v>
       </c>
       <c r="E772" t="n">
-        <v>26.30879114078081</v>
+        <v>26.30879304670615</v>
       </c>
       <c r="F772" t="n">
         <v>3900900</v>
@@ -15872,16 +15872,16 @@
         <v>45280</v>
       </c>
       <c r="B773" t="n">
-        <v>25.85688400268555</v>
+        <v>25.85688591003418</v>
       </c>
       <c r="C773" t="n">
-        <v>26.54456784535201</v>
+        <v>26.54456980342805</v>
       </c>
       <c r="D773" t="n">
-        <v>25.68987517654013</v>
+        <v>25.68987707156926</v>
       </c>
       <c r="E773" t="n">
-        <v>26.54456784535201</v>
+        <v>26.54456980342805</v>
       </c>
       <c r="F773" t="n">
         <v>6168300</v>
@@ -15912,16 +15912,16 @@
         <v>45282</v>
       </c>
       <c r="B775" t="n">
-        <v>25.95512771606445</v>
+        <v>25.95512580871582</v>
       </c>
       <c r="C775" t="n">
-        <v>26.22037738844958</v>
+        <v>26.2203754616087</v>
       </c>
       <c r="D775" t="n">
-        <v>25.79794314141873</v>
+        <v>25.79794124562103</v>
       </c>
       <c r="E775" t="n">
-        <v>26.03372000338731</v>
+        <v>26.03371809026321</v>
       </c>
       <c r="F775" t="n">
         <v>3644200</v>
@@ -16012,16 +16012,16 @@
         <v>45294</v>
       </c>
       <c r="B780" t="n">
-        <v>25.8863582611084</v>
+        <v>25.88635635375977</v>
       </c>
       <c r="C780" t="n">
-        <v>26.28914394549015</v>
+        <v>26.28914200846361</v>
       </c>
       <c r="D780" t="n">
-        <v>25.35585894580298</v>
+        <v>25.35585707754239</v>
       </c>
       <c r="E780" t="n">
-        <v>25.64075714264207</v>
+        <v>25.64075525338972</v>
       </c>
       <c r="F780" t="n">
         <v>5734800</v>
@@ -16052,16 +16052,16 @@
         <v>45296</v>
       </c>
       <c r="B782" t="n">
-        <v>25.68987655639648</v>
+        <v>25.68987464904785</v>
       </c>
       <c r="C782" t="n">
-        <v>25.97477475256549</v>
+        <v>25.97477282406455</v>
       </c>
       <c r="D782" t="n">
-        <v>25.21832285975933</v>
+        <v>25.21832098742127</v>
       </c>
       <c r="E782" t="n">
-        <v>25.36568315573496</v>
+        <v>25.36568127245611</v>
       </c>
       <c r="F782" t="n">
         <v>3417300</v>
@@ -16092,16 +16092,16 @@
         <v>45300</v>
       </c>
       <c r="B784" t="n">
-        <v>28.0181770324707</v>
+        <v>28.01817512512207</v>
       </c>
       <c r="C784" t="n">
-        <v>28.24412961971936</v>
+        <v>28.24412769698892</v>
       </c>
       <c r="D784" t="n">
-        <v>26.7999956667704</v>
+        <v>26.79999384234995</v>
       </c>
       <c r="E784" t="n">
-        <v>27.01612398407939</v>
+        <v>27.01612214494592</v>
       </c>
       <c r="F784" t="n">
         <v>10290300</v>
@@ -16152,16 +16152,16 @@
         <v>45303</v>
       </c>
       <c r="B787" t="n">
-        <v>28.20483016967773</v>
+        <v>28.20483207702637</v>
       </c>
       <c r="C787" t="n">
-        <v>28.86304121001741</v>
+        <v>28.86304316187749</v>
       </c>
       <c r="D787" t="n">
-        <v>27.82169304316834</v>
+        <v>27.82169492460737</v>
       </c>
       <c r="E787" t="n">
-        <v>28.63708864175739</v>
+        <v>28.63709057833746</v>
       </c>
       <c r="F787" t="n">
         <v>5067700</v>
@@ -16172,16 +16172,16 @@
         <v>45306</v>
       </c>
       <c r="B788" t="n">
-        <v>28.52902603149414</v>
+        <v>28.52902793884277</v>
       </c>
       <c r="C788" t="n">
-        <v>28.68621059306261</v>
+        <v>28.68621251092004</v>
       </c>
       <c r="D788" t="n">
-        <v>27.90028591143248</v>
+        <v>27.9002877767458</v>
       </c>
       <c r="E788" t="n">
-        <v>28.06729474232245</v>
+        <v>28.06729661880138</v>
       </c>
       <c r="F788" t="n">
         <v>3859400</v>
@@ -16252,16 +16252,16 @@
         <v>45310</v>
       </c>
       <c r="B792" t="n">
-        <v>29.03005218505859</v>
+        <v>29.03005027770996</v>
       </c>
       <c r="C792" t="n">
-        <v>29.19706102477754</v>
+        <v>29.197059106456</v>
       </c>
       <c r="D792" t="n">
-        <v>28.05747195626752</v>
+        <v>28.0574701128199</v>
       </c>
       <c r="E792" t="n">
-        <v>28.73533158498416</v>
+        <v>28.73532969699943</v>
       </c>
       <c r="F792" t="n">
         <v>7851200</v>
@@ -16312,16 +16312,16 @@
         <v>45315</v>
       </c>
       <c r="B795" t="n">
-        <v>27.86099052429199</v>
+        <v>27.86099243164062</v>
       </c>
       <c r="C795" t="n">
-        <v>28.52902584344861</v>
+        <v>28.52902779653059</v>
       </c>
       <c r="D795" t="n">
-        <v>27.63503607896236</v>
+        <v>27.63503797084227</v>
       </c>
       <c r="E795" t="n">
-        <v>28.04764601880687</v>
+        <v>28.04764793893384</v>
       </c>
       <c r="F795" t="n">
         <v>4070600</v>
@@ -16352,16 +16352,16 @@
         <v>45317</v>
       </c>
       <c r="B797" t="n">
-        <v>28.2441291809082</v>
+        <v>28.24412727355957</v>
       </c>
       <c r="C797" t="n">
-        <v>28.2441291809082</v>
+        <v>28.24412727355957</v>
       </c>
       <c r="D797" t="n">
-        <v>27.50732581097147</v>
+        <v>27.50732395337975</v>
       </c>
       <c r="E797" t="n">
-        <v>27.65468611020124</v>
+        <v>27.65468424265817</v>
       </c>
       <c r="F797" t="n">
         <v>2761100</v>
@@ -16392,16 +16392,16 @@
         <v>45321</v>
       </c>
       <c r="B799" t="n">
-        <v>27.24207496643066</v>
+        <v>27.2420768737793</v>
       </c>
       <c r="C799" t="n">
-        <v>27.54662169525507</v>
+        <v>27.54662362392648</v>
       </c>
       <c r="D799" t="n">
-        <v>26.97682531504984</v>
+        <v>26.97682720382707</v>
       </c>
       <c r="E799" t="n">
-        <v>27.36978859433452</v>
+        <v>27.369790510625</v>
       </c>
       <c r="F799" t="n">
         <v>2184900</v>
@@ -16432,16 +16432,16 @@
         <v>45323</v>
       </c>
       <c r="B801" t="n">
-        <v>26.24002075195312</v>
+        <v>26.24002265930176</v>
       </c>
       <c r="C801" t="n">
-        <v>27.4090825182884</v>
+        <v>27.40908451061442</v>
       </c>
       <c r="D801" t="n">
-        <v>26.10248473489757</v>
+        <v>26.10248663224892</v>
       </c>
       <c r="E801" t="n">
-        <v>27.31084170305399</v>
+        <v>27.31084368823903</v>
       </c>
       <c r="F801" t="n">
         <v>7611700</v>
@@ -16532,16 +16532,16 @@
         <v>45330</v>
       </c>
       <c r="B806" t="n">
-        <v>28.79427337646484</v>
+        <v>28.79427528381348</v>
       </c>
       <c r="C806" t="n">
-        <v>28.81392191481336</v>
+        <v>28.81392382346353</v>
       </c>
       <c r="D806" t="n">
-        <v>27.39925900811183</v>
+        <v>27.39926082305394</v>
       </c>
       <c r="E806" t="n">
-        <v>28.71568109685852</v>
+        <v>28.71568299900116</v>
       </c>
       <c r="F806" t="n">
         <v>6908300</v>
@@ -16552,16 +16552,16 @@
         <v>45331</v>
       </c>
       <c r="B807" t="n">
-        <v>27.69398307800293</v>
+        <v>27.6939811706543</v>
       </c>
       <c r="C807" t="n">
-        <v>28.9121644198793</v>
+        <v>28.9121624286317</v>
       </c>
       <c r="D807" t="n">
-        <v>27.52697423987057</v>
+        <v>27.52697234402422</v>
       </c>
       <c r="E807" t="n">
-        <v>28.83357213568689</v>
+        <v>28.83357014985212</v>
       </c>
       <c r="F807" t="n">
         <v>5513900</v>
@@ -16592,16 +16592,16 @@
         <v>45337</v>
       </c>
       <c r="B809" t="n">
-        <v>28.00835037231445</v>
+        <v>28.00835227966309</v>
       </c>
       <c r="C809" t="n">
-        <v>28.26377574758426</v>
+        <v>28.26377767232718</v>
       </c>
       <c r="D809" t="n">
-        <v>27.28137132291011</v>
+        <v>27.28137318075199</v>
       </c>
       <c r="E809" t="n">
-        <v>27.40908307365115</v>
+        <v>27.40908494019011</v>
       </c>
       <c r="F809" t="n">
         <v>2788300</v>
@@ -16632,16 +16632,16 @@
         <v>45341</v>
       </c>
       <c r="B811" t="n">
-        <v>28.6763858795166</v>
+        <v>28.67638778686523</v>
       </c>
       <c r="C811" t="n">
-        <v>28.76480242825268</v>
+        <v>28.76480434148215</v>
       </c>
       <c r="D811" t="n">
-        <v>28.2343031358362</v>
+        <v>28.23430501378064</v>
       </c>
       <c r="E811" t="n">
-        <v>28.74515388991405</v>
+        <v>28.74515580183664</v>
       </c>
       <c r="F811" t="n">
         <v>1698200</v>
@@ -16672,16 +16672,16 @@
         <v>45343</v>
       </c>
       <c r="B813" t="n">
-        <v>28.92198753356934</v>
+        <v>28.92198944091797</v>
       </c>
       <c r="C813" t="n">
-        <v>28.98093127591061</v>
+        <v>28.98093318714647</v>
       </c>
       <c r="D813" t="n">
-        <v>28.36201729685779</v>
+        <v>28.36201916727748</v>
       </c>
       <c r="E813" t="n">
-        <v>28.63708934364225</v>
+        <v>28.6370912322024</v>
       </c>
       <c r="F813" t="n">
         <v>2751400</v>
@@ -16792,16 +16792,16 @@
         <v>45351</v>
       </c>
       <c r="B819" t="n">
-        <v>27.45820426940918</v>
+        <v>27.45820617675781</v>
       </c>
       <c r="C819" t="n">
-        <v>28.14588623865804</v>
+        <v>28.14588819377561</v>
       </c>
       <c r="D819" t="n">
-        <v>27.45820426940918</v>
+        <v>27.45820617675781</v>
       </c>
       <c r="E819" t="n">
-        <v>27.98870168147043</v>
+        <v>27.98870362566938</v>
       </c>
       <c r="F819" t="n">
         <v>2784300</v>
@@ -16972,16 +16972,16 @@
         <v>45364</v>
       </c>
       <c r="B828" t="n">
-        <v>29.13811492919922</v>
+        <v>29.13811683654785</v>
       </c>
       <c r="C828" t="n">
-        <v>29.36406749594983</v>
+        <v>29.36406941808906</v>
       </c>
       <c r="D828" t="n">
-        <v>28.98093037199986</v>
+        <v>28.98093226905937</v>
       </c>
       <c r="E828" t="n">
-        <v>28.98093037199986</v>
+        <v>28.98093226905937</v>
       </c>
       <c r="F828" t="n">
         <v>2596400</v>
@@ -17032,16 +17032,16 @@
         <v>45369</v>
       </c>
       <c r="B831" t="n">
-        <v>28.98093223571777</v>
+        <v>28.98093032836914</v>
       </c>
       <c r="C831" t="n">
-        <v>29.28547710065286</v>
+        <v>29.28547517326093</v>
       </c>
       <c r="D831" t="n">
-        <v>28.61744175270144</v>
+        <v>28.61743986927554</v>
       </c>
       <c r="E831" t="n">
-        <v>28.77462819379693</v>
+        <v>28.77462630002598</v>
       </c>
       <c r="F831" t="n">
         <v>4710300</v>
@@ -17112,16 +17112,16 @@
         <v>45373</v>
       </c>
       <c r="B835" t="n">
-        <v>29.71773529052734</v>
+        <v>29.71773338317871</v>
       </c>
       <c r="C835" t="n">
-        <v>30.0026334869456</v>
+        <v>30.00263156131158</v>
       </c>
       <c r="D835" t="n">
-        <v>29.28547679800454</v>
+        <v>29.28547491839919</v>
       </c>
       <c r="E835" t="n">
-        <v>29.88474412578926</v>
+        <v>29.88474220772164</v>
       </c>
       <c r="F835" t="n">
         <v>3854000</v>
@@ -17152,16 +17152,16 @@
         <v>45377</v>
       </c>
       <c r="B837" t="n">
-        <v>30.81802749633789</v>
+        <v>30.81802940368652</v>
       </c>
       <c r="C837" t="n">
-        <v>31.22081315885015</v>
+        <v>31.22081509112746</v>
       </c>
       <c r="D837" t="n">
-        <v>30.51348077684796</v>
+        <v>30.51348266534799</v>
       </c>
       <c r="E837" t="n">
-        <v>30.61172159365801</v>
+        <v>30.61172348823823</v>
       </c>
       <c r="F837" t="n">
         <v>3327200</v>
@@ -17172,16 +17172,16 @@
         <v>45378</v>
       </c>
       <c r="B838" t="n">
-        <v>31.48606109619141</v>
+        <v>31.48606300354004</v>
       </c>
       <c r="C838" t="n">
-        <v>31.91832144197546</v>
+        <v>31.91832337550937</v>
       </c>
       <c r="D838" t="n">
-        <v>30.3857691886579</v>
+        <v>30.38577102935353</v>
       </c>
       <c r="E838" t="n">
-        <v>30.65101883332299</v>
+        <v>30.6510206900868</v>
       </c>
       <c r="F838" t="n">
         <v>9071000</v>
@@ -17372,16 +17372,16 @@
         <v>45393</v>
       </c>
       <c r="B848" t="n">
-        <v>35.62198638916016</v>
+        <v>35.62198257446289</v>
       </c>
       <c r="C848" t="n">
-        <v>35.91671074440308</v>
+        <v>35.91670689814429</v>
       </c>
       <c r="D848" t="n">
-        <v>34.59046238853748</v>
+        <v>34.59045868430435</v>
       </c>
       <c r="E848" t="n">
-        <v>34.74764696246498</v>
+        <v>34.74764324139922</v>
       </c>
       <c r="F848" t="n">
         <v>5960900</v>
@@ -17412,16 +17412,16 @@
         <v>45397</v>
       </c>
       <c r="B850" t="n">
-        <v>34.06978607177734</v>
+        <v>34.06978988647461</v>
       </c>
       <c r="C850" t="n">
-        <v>34.52169121201051</v>
+        <v>34.52169507730631</v>
       </c>
       <c r="D850" t="n">
-        <v>33.83400735867823</v>
+        <v>33.83401114697602</v>
       </c>
       <c r="E850" t="n">
-        <v>34.43327466304528</v>
+        <v>34.43327851844133</v>
       </c>
       <c r="F850" t="n">
         <v>4151100</v>
@@ -17472,16 +17472,16 @@
         <v>45400</v>
       </c>
       <c r="B853" t="n">
-        <v>32.3309326171875</v>
+        <v>32.33092880249023</v>
       </c>
       <c r="C853" t="n">
-        <v>33.28386620122118</v>
+        <v>33.28386227408815</v>
       </c>
       <c r="D853" t="n">
-        <v>31.93796930998834</v>
+        <v>31.93796554165645</v>
       </c>
       <c r="E853" t="n">
-        <v>33.00879038715143</v>
+        <v>33.00878649247434</v>
       </c>
       <c r="F853" t="n">
         <v>4478700</v>
@@ -17632,16 +17632,16 @@
         <v>45412</v>
       </c>
       <c r="B861" t="n">
-        <v>32.58635711669922</v>
+        <v>32.58635330200195</v>
       </c>
       <c r="C861" t="n">
-        <v>33.66700436998067</v>
+        <v>33.66700042877825</v>
       </c>
       <c r="D861" t="n">
-        <v>32.43899868278081</v>
+        <v>32.43899488533395</v>
       </c>
       <c r="E861" t="n">
-        <v>33.60805874786774</v>
+        <v>33.60805481356574</v>
       </c>
       <c r="F861" t="n">
         <v>6661700</v>
@@ -29531,20 +29531,32 @@
       <c r="A1456" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B1456" t="n">
-        <v>17.52</v>
-      </c>
-      <c r="C1456" t="n">
-        <v>17.79</v>
-      </c>
-      <c r="D1456" t="n">
+      <c r="B1456" t="inlineStr"/>
+      <c r="C1456" t="inlineStr"/>
+      <c r="D1456" t="inlineStr"/>
+      <c r="E1456" t="inlineStr"/>
+      <c r="F1456" t="n">
+        <v>10412200</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B1457" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="C1457" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="D1457" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="E1457" t="n">
         <v>17.5</v>
       </c>
-      <c r="E1456" t="n">
-        <v>17.61</v>
-      </c>
-      <c r="F1456" t="n">
-        <v>2811000</v>
+      <c r="F1457" t="n">
+        <v>10423000</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1457"/>
+  <dimension ref="A1:F1458"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,16 +512,16 @@
         <v>44152</v>
       </c>
       <c r="B5" t="n">
-        <v>20.17695617675781</v>
+        <v>20.17695426940918</v>
       </c>
       <c r="C5" t="n">
-        <v>20.17695617675781</v>
+        <v>20.17695426940918</v>
       </c>
       <c r="D5" t="n">
-        <v>19.85012633435968</v>
+        <v>19.85012445790661</v>
       </c>
       <c r="E5" t="n">
-        <v>20.12889164196659</v>
+        <v>20.12888973916155</v>
       </c>
       <c r="F5" t="n">
         <v>262242</v>
@@ -572,16 +572,16 @@
         <v>44158</v>
       </c>
       <c r="B8" t="n">
-        <v>20.2057933807373</v>
+        <v>20.20579147338867</v>
       </c>
       <c r="C8" t="n">
-        <v>20.52301068477087</v>
+        <v>20.52300874747816</v>
       </c>
       <c r="D8" t="n">
-        <v>20.14811818865408</v>
+        <v>20.14811628674976</v>
       </c>
       <c r="E8" t="n">
-        <v>20.14811818865408</v>
+        <v>20.14811628674976</v>
       </c>
       <c r="F8" t="n">
         <v>79408</v>
@@ -632,16 +632,16 @@
         <v>44161</v>
       </c>
       <c r="B11" t="n">
-        <v>22.87811088562012</v>
+        <v>22.87810897827148</v>
       </c>
       <c r="C11" t="n">
-        <v>22.87811088562012</v>
+        <v>22.87810897827148</v>
       </c>
       <c r="D11" t="n">
-        <v>22.3109640047031</v>
+        <v>22.31096214463751</v>
       </c>
       <c r="E11" t="n">
-        <v>22.3109640047031</v>
+        <v>22.31096214463751</v>
       </c>
       <c r="F11" t="n">
         <v>72970</v>
@@ -652,16 +652,16 @@
         <v>44162</v>
       </c>
       <c r="B12" t="n">
-        <v>23.07036209106445</v>
+        <v>23.07036399841309</v>
       </c>
       <c r="C12" t="n">
-        <v>23.55099428329309</v>
+        <v>23.55099623037812</v>
       </c>
       <c r="D12" t="n">
-        <v>22.10909770660719</v>
+        <v>22.10909953448302</v>
       </c>
       <c r="E12" t="n">
-        <v>23.07036209106445</v>
+        <v>23.07036399841309</v>
       </c>
       <c r="F12" t="n">
         <v>72050</v>
@@ -692,16 +692,16 @@
         <v>44166</v>
       </c>
       <c r="B14" t="n">
-        <v>23.07036209106445</v>
+        <v>23.07036399841309</v>
       </c>
       <c r="C14" t="n">
-        <v>23.1664892790253</v>
+        <v>23.16649119432127</v>
       </c>
       <c r="D14" t="n">
-        <v>23.03191196539523</v>
+        <v>23.03191386956499</v>
       </c>
       <c r="E14" t="n">
-        <v>23.12803727956828</v>
+        <v>23.12803919168523</v>
       </c>
       <c r="F14" t="n">
         <v>93512</v>
@@ -792,16 +792,16 @@
         <v>44173</v>
       </c>
       <c r="B19" t="n">
-        <v>26.33866500854492</v>
+        <v>26.33866310119629</v>
       </c>
       <c r="C19" t="n">
-        <v>26.57898205078916</v>
+        <v>26.57898012603766</v>
       </c>
       <c r="D19" t="n">
-        <v>25.56965309666637</v>
+        <v>25.56965124500673</v>
       </c>
       <c r="E19" t="n">
-        <v>25.56965309666637</v>
+        <v>25.56965124500673</v>
       </c>
       <c r="F19" t="n">
         <v>126420</v>
@@ -812,16 +812,16 @@
         <v>44174</v>
       </c>
       <c r="B20" t="n">
-        <v>26.83852005004883</v>
+        <v>26.83852195739746</v>
       </c>
       <c r="C20" t="n">
-        <v>27.77094867230641</v>
+        <v>27.77095064592048</v>
       </c>
       <c r="D20" t="n">
-        <v>26.27137510044991</v>
+        <v>26.27137696749292</v>
       </c>
       <c r="E20" t="n">
-        <v>26.4924651869397</v>
+        <v>26.49246706969505</v>
       </c>
       <c r="F20" t="n">
         <v>212880</v>
@@ -892,16 +892,16 @@
         <v>44180</v>
       </c>
       <c r="B24" t="n">
-        <v>33.00984191894531</v>
+        <v>33.00984573364258</v>
       </c>
       <c r="C24" t="n">
-        <v>33.9807187406613</v>
+        <v>33.98072266755544</v>
       </c>
       <c r="D24" t="n">
-        <v>30.7604798048412</v>
+        <v>30.76048335959674</v>
       </c>
       <c r="E24" t="n">
-        <v>30.7604798048412</v>
+        <v>30.76048335959674</v>
       </c>
       <c r="F24" t="n">
         <v>887803</v>
@@ -912,16 +912,16 @@
         <v>44181</v>
       </c>
       <c r="B25" t="n">
-        <v>32.68301773071289</v>
+        <v>32.68301391601562</v>
       </c>
       <c r="C25" t="n">
-        <v>34.4517423806715</v>
+        <v>34.45173835953219</v>
       </c>
       <c r="D25" t="n">
-        <v>32.10625830770921</v>
+        <v>32.10625456033017</v>
       </c>
       <c r="E25" t="n">
-        <v>33.62505712226533</v>
+        <v>33.62505319761509</v>
       </c>
       <c r="F25" t="n">
         <v>376808</v>
@@ -932,16 +932,16 @@
         <v>44182</v>
       </c>
       <c r="B26" t="n">
-        <v>32.10625457763672</v>
+        <v>32.10625839233398</v>
       </c>
       <c r="C26" t="n">
-        <v>33.64427827776851</v>
+        <v>33.64428227520571</v>
       </c>
       <c r="D26" t="n">
-        <v>31.64484559380946</v>
+        <v>31.64484935368452</v>
       </c>
       <c r="E26" t="n">
-        <v>33.62505321574033</v>
+        <v>33.6250572108933</v>
       </c>
       <c r="F26" t="n">
         <v>258257</v>
@@ -972,16 +972,16 @@
         <v>44186</v>
       </c>
       <c r="B28" t="n">
-        <v>32.18315505981445</v>
+        <v>32.18315887451172</v>
       </c>
       <c r="C28" t="n">
-        <v>33.33667378019659</v>
+        <v>33.33667773162143</v>
       </c>
       <c r="D28" t="n">
-        <v>29.12633082555934</v>
+        <v>29.12633427792858</v>
       </c>
       <c r="E28" t="n">
-        <v>31.86593778646691</v>
+        <v>31.86594156356414</v>
       </c>
       <c r="F28" t="n">
         <v>236079</v>
@@ -992,16 +992,16 @@
         <v>44187</v>
       </c>
       <c r="B29" t="n">
-        <v>33.16364669799805</v>
+        <v>33.16364288330078</v>
       </c>
       <c r="C29" t="n">
-        <v>33.47125146089823</v>
+        <v>33.47124761081827</v>
       </c>
       <c r="D29" t="n">
-        <v>32.59649983084212</v>
+        <v>32.59649608138177</v>
       </c>
       <c r="E29" t="n">
-        <v>33.21170935664249</v>
+        <v>33.21170553641675</v>
       </c>
       <c r="F29" t="n">
         <v>167504</v>
@@ -1032,16 +1032,16 @@
         <v>44193</v>
       </c>
       <c r="B31" t="n">
-        <v>36.21085357666016</v>
+        <v>36.21085739135742</v>
       </c>
       <c r="C31" t="n">
-        <v>36.66265002370312</v>
+        <v>36.66265388599569</v>
       </c>
       <c r="D31" t="n">
-        <v>35.56680651179074</v>
+        <v>35.56681025863972</v>
       </c>
       <c r="E31" t="n">
-        <v>35.56680651179074</v>
+        <v>35.56681025863972</v>
       </c>
       <c r="F31" t="n">
         <v>451822</v>
@@ -1052,16 +1052,16 @@
         <v>44194</v>
       </c>
       <c r="B32" t="n">
-        <v>36.09550857543945</v>
+        <v>36.09550476074219</v>
       </c>
       <c r="C32" t="n">
-        <v>37.06638558261441</v>
+        <v>37.06638166531152</v>
       </c>
       <c r="D32" t="n">
-        <v>35.95131684304462</v>
+        <v>35.95131304358604</v>
       </c>
       <c r="E32" t="n">
-        <v>36.52807627747203</v>
+        <v>36.52807241705953</v>
       </c>
       <c r="F32" t="n">
         <v>337154</v>
@@ -1092,16 +1092,16 @@
         <v>44200</v>
       </c>
       <c r="B34" t="n">
-        <v>34.99966430664062</v>
+        <v>34.99966049194336</v>
       </c>
       <c r="C34" t="n">
-        <v>36.62420472682393</v>
+        <v>36.62420073506411</v>
       </c>
       <c r="D34" t="n">
-        <v>34.98043924232432</v>
+        <v>34.98043542972244</v>
       </c>
       <c r="E34" t="n">
-        <v>36.52807565766651</v>
+        <v>36.52807167638402</v>
       </c>
       <c r="F34" t="n">
         <v>331840</v>
@@ -1112,16 +1112,16 @@
         <v>44201</v>
       </c>
       <c r="B35" t="n">
-        <v>36.13395309448242</v>
+        <v>36.13395690917969</v>
       </c>
       <c r="C35" t="n">
-        <v>36.32620745863368</v>
+        <v>36.32621129362743</v>
       </c>
       <c r="D35" t="n">
-        <v>34.60554195482727</v>
+        <v>34.60554560816865</v>
       </c>
       <c r="E35" t="n">
-        <v>35.45145591048728</v>
+        <v>35.45145965313264</v>
       </c>
       <c r="F35" t="n">
         <v>328059</v>
@@ -1172,16 +1172,16 @@
         <v>44204</v>
       </c>
       <c r="B38" t="n">
-        <v>34.134521484375</v>
+        <v>34.13452529907227</v>
       </c>
       <c r="C38" t="n">
-        <v>35.75906172916622</v>
+        <v>35.75906572541368</v>
       </c>
       <c r="D38" t="n">
-        <v>34.134521484375</v>
+        <v>34.13452529907227</v>
       </c>
       <c r="E38" t="n">
-        <v>35.16307730455386</v>
+        <v>35.16308123419719</v>
       </c>
       <c r="F38" t="n">
         <v>367201</v>
@@ -1272,16 +1272,16 @@
         <v>44211</v>
       </c>
       <c r="B43" t="n">
-        <v>33.9422721862793</v>
+        <v>33.94226837158203</v>
       </c>
       <c r="C43" t="n">
-        <v>35.0477245509764</v>
+        <v>35.04772061203977</v>
       </c>
       <c r="D43" t="n">
-        <v>33.16364589242556</v>
+        <v>33.16364216523639</v>
       </c>
       <c r="E43" t="n">
-        <v>34.60554435461268</v>
+        <v>34.60554046537172</v>
       </c>
       <c r="F43" t="n">
         <v>319883</v>
@@ -1292,16 +1292,16 @@
         <v>44214</v>
       </c>
       <c r="B44" t="n">
-        <v>34.04800796508789</v>
+        <v>34.04801177978516</v>
       </c>
       <c r="C44" t="n">
-        <v>34.50941694399793</v>
+        <v>34.5094208103909</v>
       </c>
       <c r="D44" t="n">
-        <v>33.27899799700501</v>
+        <v>33.27900172554335</v>
       </c>
       <c r="E44" t="n">
-        <v>34.11529568146945</v>
+        <v>34.11529950370554</v>
       </c>
       <c r="F44" t="n">
         <v>117631</v>
@@ -1332,16 +1332,16 @@
         <v>44216</v>
       </c>
       <c r="B46" t="n">
-        <v>34.12491226196289</v>
+        <v>34.12490844726562</v>
       </c>
       <c r="C46" t="n">
-        <v>35.28804363060232</v>
+        <v>35.28803968588292</v>
       </c>
       <c r="D46" t="n">
-        <v>33.66350697587357</v>
+        <v>33.66350321275509</v>
       </c>
       <c r="E46" t="n">
-        <v>34.60554635973278</v>
+        <v>34.60554249130722</v>
       </c>
       <c r="F46" t="n">
         <v>359332</v>
@@ -1372,16 +1372,16 @@
         <v>44218</v>
       </c>
       <c r="B48" t="n">
-        <v>32.95216751098633</v>
+        <v>32.95216369628906</v>
       </c>
       <c r="C48" t="n">
-        <v>33.45202665996278</v>
+        <v>33.45202278739948</v>
       </c>
       <c r="D48" t="n">
-        <v>32.53882489582456</v>
+        <v>32.53882112897777</v>
       </c>
       <c r="E48" t="n">
-        <v>33.19248455367023</v>
+        <v>33.19248071115274</v>
       </c>
       <c r="F48" t="n">
         <v>220341</v>
@@ -1472,16 +1472,16 @@
         <v>44228</v>
       </c>
       <c r="B53" t="n">
-        <v>31.77942657470703</v>
+        <v>31.7794246673584</v>
       </c>
       <c r="C53" t="n">
-        <v>33.11558345161116</v>
+        <v>33.1155814640686</v>
       </c>
       <c r="D53" t="n">
-        <v>31.66407244843196</v>
+        <v>31.66407054800669</v>
       </c>
       <c r="E53" t="n">
-        <v>32.68301578391271</v>
+        <v>32.68301382233215</v>
       </c>
       <c r="F53" t="n">
         <v>610435</v>
@@ -1492,16 +1492,16 @@
         <v>44229</v>
       </c>
       <c r="B54" t="n">
-        <v>32.63495254516602</v>
+        <v>32.63494873046875</v>
       </c>
       <c r="C54" t="n">
-        <v>33.65389597951643</v>
+        <v>33.65389204571495</v>
       </c>
       <c r="D54" t="n">
-        <v>31.97168030813476</v>
+        <v>31.97167657096734</v>
       </c>
       <c r="E54" t="n">
-        <v>33.64428344702543</v>
+        <v>33.64427951434755</v>
       </c>
       <c r="F54" t="n">
         <v>582228</v>
@@ -1532,16 +1532,16 @@
         <v>44231</v>
       </c>
       <c r="B56" t="n">
-        <v>32.68301773071289</v>
+        <v>32.68301391601562</v>
       </c>
       <c r="C56" t="n">
-        <v>34.11530000851534</v>
+        <v>34.11529602664492</v>
       </c>
       <c r="D56" t="n">
-        <v>32.44270067986538</v>
+        <v>32.44269689321744</v>
       </c>
       <c r="E56" t="n">
-        <v>33.06752276352339</v>
+        <v>33.06751890394745</v>
       </c>
       <c r="F56" t="n">
         <v>466743</v>
@@ -1612,16 +1612,16 @@
         <v>44237</v>
       </c>
       <c r="B60" t="n">
-        <v>34.83625030517578</v>
+        <v>34.83624649047852</v>
       </c>
       <c r="C60" t="n">
-        <v>35.33610571127585</v>
+        <v>35.33610184184258</v>
       </c>
       <c r="D60" t="n">
-        <v>34.23065330065825</v>
+        <v>34.23064955227608</v>
       </c>
       <c r="E60" t="n">
-        <v>34.43251647044691</v>
+        <v>34.43251269995998</v>
       </c>
       <c r="F60" t="n">
         <v>186206</v>
@@ -1652,16 +1652,16 @@
         <v>44239</v>
       </c>
       <c r="B62" t="n">
-        <v>34.4036750793457</v>
+        <v>34.40367889404297</v>
       </c>
       <c r="C62" t="n">
-        <v>34.52864172776623</v>
+        <v>34.52864555631986</v>
       </c>
       <c r="D62" t="n">
-        <v>32.67339704372985</v>
+        <v>32.673400666573</v>
       </c>
       <c r="E62" t="n">
-        <v>33.67311524079254</v>
+        <v>33.67311897448496</v>
       </c>
       <c r="F62" t="n">
         <v>218195</v>
@@ -1692,16 +1692,16 @@
         <v>44245</v>
       </c>
       <c r="B64" t="n">
-        <v>37.00870513916016</v>
+        <v>37.00870895385742</v>
       </c>
       <c r="C64" t="n">
-        <v>37.38359759408829</v>
+        <v>37.38360144742785</v>
       </c>
       <c r="D64" t="n">
-        <v>35.71099846956061</v>
+        <v>35.71100215049589</v>
       </c>
       <c r="E64" t="n">
-        <v>36.37427060079703</v>
+        <v>36.37427435009953</v>
       </c>
       <c r="F64" t="n">
         <v>661534</v>
@@ -1812,16 +1812,16 @@
         <v>44253</v>
       </c>
       <c r="B70" t="n">
-        <v>34.57670974731445</v>
+        <v>34.57670593261719</v>
       </c>
       <c r="C70" t="n">
-        <v>37.21057733278074</v>
+        <v>37.21057322750037</v>
       </c>
       <c r="D70" t="n">
-        <v>33.75002072456356</v>
+        <v>33.75001700107128</v>
       </c>
       <c r="E70" t="n">
-        <v>36.53768882724342</v>
+        <v>36.5376847961999</v>
       </c>
       <c r="F70" t="n">
         <v>410022</v>
@@ -1932,16 +1932,16 @@
         <v>44263</v>
       </c>
       <c r="B76" t="n">
-        <v>41.91115570068359</v>
+        <v>41.91115951538086</v>
       </c>
       <c r="C76" t="n">
-        <v>44.60269808495321</v>
+        <v>44.60270214463106</v>
       </c>
       <c r="D76" t="n">
-        <v>40.70957434605565</v>
+        <v>40.70957805138659</v>
       </c>
       <c r="E76" t="n">
-        <v>43.55492097253444</v>
+        <v>43.55492493684502</v>
       </c>
       <c r="F76" t="n">
         <v>1012691</v>
@@ -1952,16 +1952,16 @@
         <v>44264</v>
       </c>
       <c r="B77" t="n">
-        <v>43.50685882568359</v>
+        <v>43.50686264038086</v>
       </c>
       <c r="C77" t="n">
-        <v>43.50685882568359</v>
+        <v>43.50686264038086</v>
       </c>
       <c r="D77" t="n">
-        <v>39.89249844113039</v>
+        <v>39.89250193891922</v>
       </c>
       <c r="E77" t="n">
-        <v>42.29566117843103</v>
+        <v>42.29566488693005</v>
       </c>
       <c r="F77" t="n">
         <v>563525</v>
@@ -1972,16 +1972,16 @@
         <v>44265</v>
       </c>
       <c r="B78" t="n">
-        <v>44.69882965087891</v>
+        <v>44.69882583618164</v>
       </c>
       <c r="C78" t="n">
-        <v>44.89108404365759</v>
+        <v>44.89108021255291</v>
       </c>
       <c r="D78" t="n">
-        <v>43.38189774093629</v>
+        <v>43.38189403862891</v>
       </c>
       <c r="E78" t="n">
-        <v>43.83369425231464</v>
+        <v>43.83369051144994</v>
       </c>
       <c r="F78" t="n">
         <v>425454</v>
@@ -2012,16 +2012,16 @@
         <v>44267</v>
       </c>
       <c r="B80" t="n">
-        <v>45.66009140014648</v>
+        <v>45.66009521484375</v>
       </c>
       <c r="C80" t="n">
-        <v>49.01490590711195</v>
+        <v>49.01491000208902</v>
       </c>
       <c r="D80" t="n">
-        <v>45.18906989096082</v>
+        <v>45.18907366630634</v>
       </c>
       <c r="E80" t="n">
-        <v>47.15005242731743</v>
+        <v>47.15005636649431</v>
       </c>
       <c r="F80" t="n">
         <v>954539</v>
@@ -2052,16 +2052,16 @@
         <v>44271</v>
       </c>
       <c r="B82" t="n">
-        <v>42.7570686340332</v>
+        <v>42.75707244873047</v>
       </c>
       <c r="C82" t="n">
-        <v>45.18906887745489</v>
+        <v>45.18907290913018</v>
       </c>
       <c r="D82" t="n">
-        <v>42.7570686340332</v>
+        <v>42.75707244873047</v>
       </c>
       <c r="E82" t="n">
-        <v>44.5065717038056</v>
+        <v>44.50657567458991</v>
       </c>
       <c r="F82" t="n">
         <v>561175</v>
@@ -2092,16 +2092,16 @@
         <v>44273</v>
       </c>
       <c r="B84" t="n">
-        <v>40.89221572875977</v>
+        <v>40.89221954345703</v>
       </c>
       <c r="C84" t="n">
-        <v>45.02565269480871</v>
+        <v>45.0256568951004</v>
       </c>
       <c r="D84" t="n">
-        <v>40.57499846451049</v>
+        <v>40.57500224961562</v>
       </c>
       <c r="E84" t="n">
-        <v>44.01632571721106</v>
+        <v>44.01632982334604</v>
       </c>
       <c r="F84" t="n">
         <v>572621</v>
@@ -2112,16 +2112,16 @@
         <v>44274</v>
       </c>
       <c r="B85" t="n">
-        <v>42.2956657409668</v>
+        <v>42.29566192626953</v>
       </c>
       <c r="C85" t="n">
-        <v>44.17013572642225</v>
+        <v>44.17013174266427</v>
       </c>
       <c r="D85" t="n">
-        <v>41.45936795627186</v>
+        <v>41.4593642170013</v>
       </c>
       <c r="E85" t="n">
-        <v>41.45936795627186</v>
+        <v>41.4593642170013</v>
       </c>
       <c r="F85" t="n">
         <v>639255</v>
@@ -2212,16 +2212,16 @@
         <v>44281</v>
       </c>
       <c r="B90" t="n">
-        <v>37.87384796142578</v>
+        <v>37.87384414672852</v>
       </c>
       <c r="C90" t="n">
-        <v>40.94989565175231</v>
+        <v>40.949891527232</v>
       </c>
       <c r="D90" t="n">
-        <v>37.56624319239313</v>
+        <v>37.56623940867817</v>
       </c>
       <c r="E90" t="n">
-        <v>39.95979362121066</v>
+        <v>39.95978959641457</v>
       </c>
       <c r="F90" t="n">
         <v>840076</v>
@@ -2312,16 +2312,16 @@
         <v>44291</v>
       </c>
       <c r="B95" t="n">
-        <v>35.68216323852539</v>
+        <v>35.68215942382812</v>
       </c>
       <c r="C95" t="n">
-        <v>37.01832012039754</v>
+        <v>37.01831616285484</v>
       </c>
       <c r="D95" t="n">
-        <v>35.09579131613852</v>
+        <v>35.09578756412892</v>
       </c>
       <c r="E95" t="n">
-        <v>37.01832012039754</v>
+        <v>37.01831616285484</v>
       </c>
       <c r="F95" t="n">
         <v>1091895</v>
@@ -2512,16 +2512,16 @@
         <v>44305</v>
       </c>
       <c r="B105" t="n">
-        <v>41.33440017700195</v>
+        <v>41.33439636230469</v>
       </c>
       <c r="C105" t="n">
-        <v>42.23798940934727</v>
+        <v>42.23798551125894</v>
       </c>
       <c r="D105" t="n">
-        <v>40.2097189655786</v>
+        <v>40.20971525467667</v>
       </c>
       <c r="E105" t="n">
-        <v>40.38274828563441</v>
+        <v>40.38274455876383</v>
       </c>
       <c r="F105" t="n">
         <v>1793083</v>
@@ -2552,16 +2552,16 @@
         <v>44308</v>
       </c>
       <c r="B107" t="n">
-        <v>42.37256622314453</v>
+        <v>42.3725700378418</v>
       </c>
       <c r="C107" t="n">
-        <v>42.77629628383934</v>
+        <v>42.77630013488342</v>
       </c>
       <c r="D107" t="n">
-        <v>41.0460181707321</v>
+        <v>41.04602186600353</v>
       </c>
       <c r="E107" t="n">
-        <v>42.58404191096891</v>
+        <v>42.58404574470481</v>
       </c>
       <c r="F107" t="n">
         <v>1175903</v>
@@ -2572,16 +2572,16 @@
         <v>44309</v>
       </c>
       <c r="B108" t="n">
-        <v>44.09323120117188</v>
+        <v>44.09323501586914</v>
       </c>
       <c r="C108" t="n">
-        <v>44.3143194172334</v>
+        <v>44.31432325105797</v>
       </c>
       <c r="D108" t="n">
-        <v>42.38217817402538</v>
+        <v>42.38218184069201</v>
       </c>
       <c r="E108" t="n">
-        <v>42.82435835372392</v>
+        <v>42.82436205864548</v>
       </c>
       <c r="F108" t="n">
         <v>1899574</v>
@@ -2612,16 +2612,16 @@
         <v>44313</v>
       </c>
       <c r="B110" t="n">
-        <v>43.73756408691406</v>
+        <v>43.7375602722168</v>
       </c>
       <c r="C110" t="n">
-        <v>44.31432350323168</v>
+        <v>44.31431963823069</v>
       </c>
       <c r="D110" t="n">
-        <v>43.04545428636325</v>
+        <v>43.04545053203033</v>
       </c>
       <c r="E110" t="n">
-        <v>43.40112171865809</v>
+        <v>43.40111793330461</v>
       </c>
       <c r="F110" t="n">
         <v>1146163</v>
@@ -2732,16 +2732,16 @@
         <v>44321</v>
       </c>
       <c r="B116" t="n">
-        <v>39.74831008911133</v>
+        <v>39.74831390380859</v>
       </c>
       <c r="C116" t="n">
-        <v>40.6422867086336</v>
+        <v>40.64229060912697</v>
       </c>
       <c r="D116" t="n">
-        <v>39.07542542863015</v>
+        <v>39.0754291787498</v>
       </c>
       <c r="E116" t="n">
-        <v>39.89249805311069</v>
+        <v>39.89250188164586</v>
       </c>
       <c r="F116" t="n">
         <v>3650961</v>
@@ -2772,16 +2772,16 @@
         <v>44323</v>
       </c>
       <c r="B118" t="n">
-        <v>38.83511352539062</v>
+        <v>38.83510971069336</v>
       </c>
       <c r="C118" t="n">
-        <v>39.99824491189721</v>
+        <v>39.99824098294782</v>
       </c>
       <c r="D118" t="n">
-        <v>37.51818162368365</v>
+        <v>37.51817793834604</v>
       </c>
       <c r="E118" t="n">
-        <v>39.66180253732045</v>
+        <v>39.66179864141913</v>
       </c>
       <c r="F118" t="n">
         <v>2227429</v>
@@ -2832,16 +2832,16 @@
         <v>44328</v>
       </c>
       <c r="B121" t="n">
-        <v>37.05676651000977</v>
+        <v>37.05677032470703</v>
       </c>
       <c r="C121" t="n">
-        <v>38.70052798471127</v>
+        <v>38.70053196862062</v>
       </c>
       <c r="D121" t="n">
-        <v>37.05676651000977</v>
+        <v>37.05677032470703</v>
       </c>
       <c r="E121" t="n">
-        <v>37.81616767208757</v>
+        <v>37.8161715649591</v>
       </c>
       <c r="F121" t="n">
         <v>783049</v>
@@ -2892,16 +2892,16 @@
         <v>44333</v>
       </c>
       <c r="B124" t="n">
-        <v>36.43194961547852</v>
+        <v>36.43194580078125</v>
       </c>
       <c r="C124" t="n">
-        <v>37.13367194429578</v>
+        <v>37.13366805612294</v>
       </c>
       <c r="D124" t="n">
-        <v>35.93209045798972</v>
+        <v>35.93208669563144</v>
       </c>
       <c r="E124" t="n">
-        <v>36.52807493515874</v>
+        <v>36.52807111039643</v>
       </c>
       <c r="F124" t="n">
         <v>946466</v>
@@ -2912,16 +2912,16 @@
         <v>44334</v>
       </c>
       <c r="B125" t="n">
-        <v>35.14385223388672</v>
+        <v>35.14385604858398</v>
       </c>
       <c r="C125" t="n">
-        <v>36.91258044505902</v>
+        <v>36.91258445174329</v>
       </c>
       <c r="D125" t="n">
-        <v>34.59593046500746</v>
+        <v>34.59593422023043</v>
       </c>
       <c r="E125" t="n">
-        <v>36.52807170518645</v>
+        <v>36.52807567013412</v>
       </c>
       <c r="F125" t="n">
         <v>2070451</v>
@@ -2952,16 +2952,16 @@
         <v>44336</v>
       </c>
       <c r="B127" t="n">
-        <v>34.63438034057617</v>
+        <v>34.63438415527344</v>
       </c>
       <c r="C127" t="n">
-        <v>35.26881488495837</v>
+        <v>35.26881876953347</v>
       </c>
       <c r="D127" t="n">
-        <v>34.51902996798866</v>
+        <v>34.51903376998102</v>
       </c>
       <c r="E127" t="n">
-        <v>34.51902996798866</v>
+        <v>34.51903376998102</v>
       </c>
       <c r="F127" t="n">
         <v>943604</v>
@@ -3012,16 +3012,16 @@
         <v>44341</v>
       </c>
       <c r="B130" t="n">
-        <v>37.29708480834961</v>
+        <v>37.29708862304688</v>
       </c>
       <c r="C130" t="n">
-        <v>38.78704584439543</v>
+        <v>38.78704981148397</v>
       </c>
       <c r="D130" t="n">
-        <v>37.22979709165812</v>
+        <v>37.22980089947328</v>
       </c>
       <c r="E130" t="n">
-        <v>37.52778929886728</v>
+        <v>37.52779313716071</v>
       </c>
       <c r="F130" t="n">
         <v>1731150</v>
@@ -3092,16 +3092,16 @@
         <v>44347</v>
       </c>
       <c r="B134" t="n">
-        <v>39.38302993774414</v>
+        <v>39.38303375244141</v>
       </c>
       <c r="C134" t="n">
-        <v>40.11358977958957</v>
+        <v>40.11359366504992</v>
       </c>
       <c r="D134" t="n">
-        <v>39.02736254769899</v>
+        <v>39.02736632794579</v>
       </c>
       <c r="E134" t="n">
-        <v>39.3926424686217</v>
+        <v>39.39264628425005</v>
       </c>
       <c r="F134" t="n">
         <v>715598</v>
@@ -3192,16 +3192,16 @@
         <v>44355</v>
       </c>
       <c r="B139" t="n">
-        <v>38.46022033691406</v>
+        <v>38.4602165222168</v>
       </c>
       <c r="C139" t="n">
-        <v>38.85433789767048</v>
+        <v>38.85433404388245</v>
       </c>
       <c r="D139" t="n">
-        <v>37.72004412796937</v>
+        <v>37.72004038668688</v>
       </c>
       <c r="E139" t="n">
-        <v>38.43138274082768</v>
+        <v>38.43137892899068</v>
       </c>
       <c r="F139" t="n">
         <v>978352</v>
@@ -3212,16 +3212,16 @@
         <v>44356</v>
       </c>
       <c r="B140" t="n">
-        <v>38.01803207397461</v>
+        <v>38.01803588867188</v>
       </c>
       <c r="C140" t="n">
-        <v>38.66207914230487</v>
+        <v>38.66208302162527</v>
       </c>
       <c r="D140" t="n">
-        <v>37.29708475810054</v>
+        <v>37.29708850045856</v>
       </c>
       <c r="E140" t="n">
-        <v>38.48905358533129</v>
+        <v>38.48905744729046</v>
       </c>
       <c r="F140" t="n">
         <v>837521</v>
@@ -3332,16 +3332,16 @@
         <v>44364</v>
       </c>
       <c r="B146" t="n">
-        <v>42.48791885375977</v>
+        <v>42.4879150390625</v>
       </c>
       <c r="C146" t="n">
-        <v>44.00671761209134</v>
+        <v>44.0067136610316</v>
       </c>
       <c r="D146" t="n">
-        <v>41.62277975128091</v>
+        <v>41.62277601425852</v>
       </c>
       <c r="E146" t="n">
-        <v>42.95894040588714</v>
+        <v>42.95893654890009</v>
       </c>
       <c r="F146" t="n">
         <v>1582144</v>
@@ -3372,16 +3372,16 @@
         <v>44368</v>
       </c>
       <c r="B148" t="n">
-        <v>46.96741104125977</v>
+        <v>46.96741485595703</v>
       </c>
       <c r="C148" t="n">
-        <v>47.24617818755916</v>
+        <v>47.24618202489792</v>
       </c>
       <c r="D148" t="n">
-        <v>43.53569625432814</v>
+        <v>43.53569979030122</v>
       </c>
       <c r="E148" t="n">
-        <v>43.73755940512824</v>
+        <v>43.73756295749668</v>
       </c>
       <c r="F148" t="n">
         <v>2655439</v>
@@ -3452,16 +3452,16 @@
         <v>44372</v>
       </c>
       <c r="B152" t="n">
-        <v>44.45851516723633</v>
+        <v>44.45851135253906</v>
       </c>
       <c r="C152" t="n">
-        <v>44.9872081751215</v>
+        <v>44.98720431506052</v>
       </c>
       <c r="D152" t="n">
-        <v>43.97788107180344</v>
+        <v>43.97787729834627</v>
       </c>
       <c r="E152" t="n">
-        <v>44.9872081751215</v>
+        <v>44.98720431506052</v>
       </c>
       <c r="F152" t="n">
         <v>1347904</v>
@@ -3472,16 +3472,16 @@
         <v>44375</v>
       </c>
       <c r="B153" t="n">
-        <v>44.53541564941406</v>
+        <v>44.5354118347168</v>
       </c>
       <c r="C153" t="n">
-        <v>44.64115350201283</v>
+        <v>44.64114967825854</v>
       </c>
       <c r="D153" t="n">
-        <v>43.20886748802305</v>
+        <v>43.20886378695175</v>
       </c>
       <c r="E153" t="n">
-        <v>44.13168555555202</v>
+        <v>44.13168177543641</v>
       </c>
       <c r="F153" t="n">
         <v>1110393</v>
@@ -3512,16 +3512,16 @@
         <v>44377</v>
       </c>
       <c r="B155" t="n">
-        <v>43.58375930786133</v>
+        <v>43.58376312255859</v>
       </c>
       <c r="C155" t="n">
-        <v>44.45851087872119</v>
+        <v>44.45851476998166</v>
       </c>
       <c r="D155" t="n">
-        <v>43.50685905923421</v>
+        <v>43.50686286720073</v>
       </c>
       <c r="E155" t="n">
-        <v>44.21819385418598</v>
+        <v>44.21819772441255</v>
       </c>
       <c r="F155" t="n">
         <v>1274116</v>
@@ -3572,16 +3572,16 @@
         <v>44382</v>
       </c>
       <c r="B158" t="n">
-        <v>45.04488754272461</v>
+        <v>45.04488372802734</v>
       </c>
       <c r="C158" t="n">
-        <v>46.21763144885693</v>
+        <v>46.21762753484401</v>
       </c>
       <c r="D158" t="n">
-        <v>44.42967424579171</v>
+        <v>44.42967048319475</v>
       </c>
       <c r="E158" t="n">
-        <v>44.98720860256699</v>
+        <v>44.98720479275436</v>
       </c>
       <c r="F158" t="n">
         <v>3391068</v>
@@ -3592,16 +3592,16 @@
         <v>44383</v>
       </c>
       <c r="B159" t="n">
-        <v>44.37199783325195</v>
+        <v>44.37199401855469</v>
       </c>
       <c r="C159" t="n">
-        <v>45.94847553926477</v>
+        <v>45.94847158903642</v>
       </c>
       <c r="D159" t="n">
-        <v>43.75678830080941</v>
+        <v>43.75678453900221</v>
       </c>
       <c r="E159" t="n">
-        <v>45.78505875053358</v>
+        <v>45.7850548143543</v>
       </c>
       <c r="F159" t="n">
         <v>1563442</v>
@@ -3652,16 +3652,16 @@
         <v>44389</v>
       </c>
       <c r="B162" t="n">
-        <v>44.72766494750977</v>
+        <v>44.72766876220703</v>
       </c>
       <c r="C162" t="n">
-        <v>45.75621700299953</v>
+        <v>45.75622090541913</v>
       </c>
       <c r="D162" t="n">
-        <v>44.08361413043626</v>
+        <v>44.08361789020423</v>
       </c>
       <c r="E162" t="n">
-        <v>45.75621700299953</v>
+        <v>45.75622090541913</v>
       </c>
       <c r="F162" t="n">
         <v>1597780</v>
@@ -3732,16 +3732,16 @@
         <v>44393</v>
       </c>
       <c r="B166" t="n">
-        <v>41.70929336547852</v>
+        <v>41.70928955078125</v>
       </c>
       <c r="C166" t="n">
-        <v>41.91116028433812</v>
+        <v>41.91115645117827</v>
       </c>
       <c r="D166" t="n">
-        <v>40.45003668764308</v>
+        <v>40.45003298811638</v>
       </c>
       <c r="E166" t="n">
-        <v>41.62278057778546</v>
+        <v>41.62277677100059</v>
       </c>
       <c r="F166" t="n">
         <v>1471156</v>
@@ -3752,16 +3752,16 @@
         <v>44396</v>
       </c>
       <c r="B167" t="n">
-        <v>40.22894668579102</v>
+        <v>40.22894287109375</v>
       </c>
       <c r="C167" t="n">
-        <v>41.05563189370605</v>
+        <v>41.05562800061862</v>
       </c>
       <c r="D167" t="n">
-        <v>39.50799557728174</v>
+        <v>39.50799183094843</v>
       </c>
       <c r="E167" t="n">
-        <v>40.46925997438512</v>
+        <v>40.46925613690023</v>
       </c>
       <c r="F167" t="n">
         <v>1632835</v>
@@ -3792,16 +3792,16 @@
         <v>44398</v>
       </c>
       <c r="B169" t="n">
-        <v>40.45964813232422</v>
+        <v>40.45964431762695</v>
       </c>
       <c r="C169" t="n">
-        <v>41.40169122996932</v>
+        <v>41.40168732645247</v>
       </c>
       <c r="D169" t="n">
-        <v>40.22894737134245</v>
+        <v>40.22894357839657</v>
       </c>
       <c r="E169" t="n">
-        <v>40.37313534695605</v>
+        <v>40.37313154041556</v>
       </c>
       <c r="F169" t="n">
         <v>985812</v>
@@ -3812,16 +3812,16 @@
         <v>44399</v>
       </c>
       <c r="B170" t="n">
-        <v>40.89221572875977</v>
+        <v>40.89221954345703</v>
       </c>
       <c r="C170" t="n">
-        <v>41.15175780815924</v>
+        <v>41.15176164706832</v>
       </c>
       <c r="D170" t="n">
-        <v>40.39235663157741</v>
+        <v>40.3923603996445</v>
       </c>
       <c r="E170" t="n">
-        <v>41.08446634492577</v>
+        <v>41.08447017755746</v>
       </c>
       <c r="F170" t="n">
         <v>757704</v>
@@ -3832,16 +3832,16 @@
         <v>44400</v>
       </c>
       <c r="B171" t="n">
-        <v>40.56539154052734</v>
+        <v>40.56538772583008</v>
       </c>
       <c r="C171" t="n">
-        <v>40.8633837843476</v>
+        <v>40.86337994162768</v>
       </c>
       <c r="D171" t="n">
-        <v>40.20010782417279</v>
+        <v>40.20010404382616</v>
       </c>
       <c r="E171" t="n">
-        <v>40.62306673334884</v>
+        <v>40.6230629132279</v>
       </c>
       <c r="F171" t="n">
         <v>715496</v>
@@ -3872,16 +3872,16 @@
         <v>44404</v>
       </c>
       <c r="B173" t="n">
-        <v>38.54673385620117</v>
+        <v>38.54673004150391</v>
       </c>
       <c r="C173" t="n">
-        <v>40.84415903525979</v>
+        <v>40.84415499320262</v>
       </c>
       <c r="D173" t="n">
-        <v>38.32564186777011</v>
+        <v>38.32563807495276</v>
       </c>
       <c r="E173" t="n">
-        <v>40.62306704682872</v>
+        <v>40.62306302665147</v>
       </c>
       <c r="F173" t="n">
         <v>1543819</v>
@@ -3932,16 +3932,16 @@
         <v>44407</v>
       </c>
       <c r="B176" t="n">
-        <v>37.21057510375977</v>
+        <v>37.2105712890625</v>
       </c>
       <c r="C176" t="n">
-        <v>38.26796483899034</v>
+        <v>38.26796091589321</v>
       </c>
       <c r="D176" t="n">
-        <v>36.33582347177977</v>
+        <v>36.33581974675896</v>
       </c>
       <c r="E176" t="n">
-        <v>37.56624252608663</v>
+        <v>37.5662386749276</v>
       </c>
       <c r="F176" t="n">
         <v>1168442</v>
@@ -3952,16 +3952,16 @@
         <v>44410</v>
       </c>
       <c r="B177" t="n">
-        <v>39.04659271240234</v>
+        <v>39.04658889770508</v>
       </c>
       <c r="C177" t="n">
-        <v>40.34429954077027</v>
+        <v>40.3442955992922</v>
       </c>
       <c r="D177" t="n">
-        <v>38.19106610976557</v>
+        <v>38.19106237864987</v>
       </c>
       <c r="E177" t="n">
-        <v>39.17155563014188</v>
+        <v>39.17155180323623</v>
       </c>
       <c r="F177" t="n">
         <v>3352028</v>
@@ -4052,16 +4052,16 @@
         <v>44417</v>
       </c>
       <c r="B182" t="n">
-        <v>37.10483551025391</v>
+        <v>37.10483169555664</v>
       </c>
       <c r="C182" t="n">
-        <v>37.44127788724551</v>
+        <v>37.44127403795907</v>
       </c>
       <c r="D182" t="n">
-        <v>35.94170411539885</v>
+        <v>35.94170042028153</v>
       </c>
       <c r="E182" t="n">
-        <v>36.11473344381713</v>
+        <v>36.1147297309109</v>
       </c>
       <c r="F182" t="n">
         <v>1206460</v>
@@ -4092,16 +4092,16 @@
         <v>44419</v>
       </c>
       <c r="B184" t="n">
-        <v>36.43194961547852</v>
+        <v>36.43194580078125</v>
       </c>
       <c r="C184" t="n">
-        <v>36.74916691799907</v>
+        <v>36.74916307008678</v>
       </c>
       <c r="D184" t="n">
-        <v>36.09550724902192</v>
+        <v>36.09550346955268</v>
       </c>
       <c r="E184" t="n">
-        <v>36.4703997433506</v>
+        <v>36.47039592462733</v>
       </c>
       <c r="F184" t="n">
         <v>786524</v>
@@ -4112,16 +4112,16 @@
         <v>44420</v>
       </c>
       <c r="B185" t="n">
-        <v>36.12434005737305</v>
+        <v>36.12434387207031</v>
       </c>
       <c r="C185" t="n">
-        <v>36.95102893978947</v>
+        <v>36.95103284178433</v>
       </c>
       <c r="D185" t="n">
-        <v>35.47068047502529</v>
+        <v>35.4706842206967</v>
       </c>
       <c r="E185" t="n">
-        <v>36.19162777223157</v>
+        <v>36.19163159403436</v>
       </c>
       <c r="F185" t="n">
         <v>689639</v>
@@ -4132,16 +4132,16 @@
         <v>44421</v>
       </c>
       <c r="B186" t="n">
-        <v>34.75934600830078</v>
+        <v>34.75934219360352</v>
       </c>
       <c r="C186" t="n">
-        <v>35.97054000708643</v>
+        <v>35.97053605946554</v>
       </c>
       <c r="D186" t="n">
-        <v>34.59593296747376</v>
+        <v>34.59592917071041</v>
       </c>
       <c r="E186" t="n">
-        <v>35.69177658449917</v>
+        <v>35.69177266747142</v>
       </c>
       <c r="F186" t="n">
         <v>915908</v>
@@ -4252,16 +4252,16 @@
         <v>44431</v>
       </c>
       <c r="B192" t="n">
-        <v>33.16364669799805</v>
+        <v>33.16364288330078</v>
       </c>
       <c r="C192" t="n">
-        <v>34.42290334478545</v>
+        <v>34.42289938524034</v>
       </c>
       <c r="D192" t="n">
-        <v>32.77914168126674</v>
+        <v>32.77913791079774</v>
       </c>
       <c r="E192" t="n">
-        <v>33.74040609688286</v>
+        <v>33.740402215843</v>
       </c>
       <c r="F192" t="n">
         <v>2084044</v>
@@ -4272,16 +4272,16 @@
         <v>44432</v>
       </c>
       <c r="B193" t="n">
-        <v>35.43223190307617</v>
+        <v>35.43223571777344</v>
       </c>
       <c r="C193" t="n">
-        <v>35.43223190307617</v>
+        <v>35.43223571777344</v>
       </c>
       <c r="D193" t="n">
-        <v>33.47124932262768</v>
+        <v>33.47125292620207</v>
       </c>
       <c r="E193" t="n">
-        <v>33.93265831128927</v>
+        <v>33.93266196453976</v>
       </c>
       <c r="F193" t="n">
         <v>1429663</v>
@@ -4332,16 +4332,16 @@
         <v>44435</v>
       </c>
       <c r="B196" t="n">
-        <v>36.43194961547852</v>
+        <v>36.43194580078125</v>
       </c>
       <c r="C196" t="n">
-        <v>36.66265413028687</v>
+        <v>36.66265029143312</v>
       </c>
       <c r="D196" t="n">
-        <v>35.02850121026817</v>
+        <v>35.02849754252244</v>
       </c>
       <c r="E196" t="n">
-        <v>35.75906488256532</v>
+        <v>35.75906113832411</v>
       </c>
       <c r="F196" t="n">
         <v>2701327</v>
@@ -4392,16 +4392,16 @@
         <v>44440</v>
       </c>
       <c r="B199" t="n">
-        <v>36.00899505615234</v>
+        <v>36.00899124145508</v>
       </c>
       <c r="C199" t="n">
-        <v>37.2298016265613</v>
+        <v>37.22979768253502</v>
       </c>
       <c r="D199" t="n">
-        <v>35.47068576189898</v>
+        <v>35.47068200422877</v>
       </c>
       <c r="E199" t="n">
-        <v>37.10483496133683</v>
+        <v>37.10483103054919</v>
       </c>
       <c r="F199" t="n">
         <v>1150659</v>
@@ -4712,16 +4712,16 @@
         <v>44463</v>
       </c>
       <c r="B215" t="n">
-        <v>34.54787063598633</v>
+        <v>34.54786682128906</v>
       </c>
       <c r="C215" t="n">
-        <v>35.65332304773112</v>
+        <v>35.65331911097231</v>
       </c>
       <c r="D215" t="n">
-        <v>33.88459469184851</v>
+        <v>33.88459095038866</v>
       </c>
       <c r="E215" t="n">
-        <v>34.46135784884584</v>
+        <v>34.46135404370111</v>
       </c>
       <c r="F215" t="n">
         <v>2639905</v>
@@ -4852,16 +4852,16 @@
         <v>44474</v>
       </c>
       <c r="B222" t="n">
-        <v>41.2382698059082</v>
+        <v>41.23827362060547</v>
       </c>
       <c r="C222" t="n">
-        <v>43.07428564103963</v>
+        <v>43.07428962557536</v>
       </c>
       <c r="D222" t="n">
-        <v>40.94989013953506</v>
+        <v>40.9498939275561</v>
       </c>
       <c r="E222" t="n">
-        <v>41.82464166928109</v>
+        <v>41.82464553821999</v>
       </c>
       <c r="F222" t="n">
         <v>3033780</v>
@@ -4952,16 +4952,16 @@
         <v>44482</v>
       </c>
       <c r="B227" t="n">
-        <v>39.66180038452148</v>
+        <v>39.66179656982422</v>
       </c>
       <c r="C227" t="n">
-        <v>40.05591793090613</v>
+        <v>40.05591407830239</v>
       </c>
       <c r="D227" t="n">
-        <v>38.88317407585477</v>
+        <v>38.88317033604628</v>
       </c>
       <c r="E227" t="n">
-        <v>39.43109587666738</v>
+        <v>39.43109208415942</v>
       </c>
       <c r="F227" t="n">
         <v>1130628</v>
@@ -5012,16 +5012,16 @@
         <v>44487</v>
       </c>
       <c r="B230" t="n">
-        <v>39.87327575683594</v>
+        <v>39.87327194213867</v>
       </c>
       <c r="C230" t="n">
-        <v>41.44975342469183</v>
+        <v>41.44974945917212</v>
       </c>
       <c r="D230" t="n">
-        <v>39.18116598648377</v>
+        <v>39.18116223800101</v>
       </c>
       <c r="E230" t="n">
-        <v>39.72908778283576</v>
+        <v>39.72908398193304</v>
       </c>
       <c r="F230" t="n">
         <v>2573169</v>
@@ -5032,16 +5032,16 @@
         <v>44488</v>
       </c>
       <c r="B231" t="n">
-        <v>37.58546829223633</v>
+        <v>37.58546447753906</v>
       </c>
       <c r="C231" t="n">
-        <v>40.08475657457366</v>
+        <v>40.08475250621378</v>
       </c>
       <c r="D231" t="n">
-        <v>36.86452090235465</v>
+        <v>36.86451716082918</v>
       </c>
       <c r="E231" t="n">
-        <v>39.57528488714614</v>
+        <v>39.57528087049455</v>
       </c>
       <c r="F231" t="n">
         <v>2915331</v>
@@ -5072,16 +5072,16 @@
         <v>44490</v>
       </c>
       <c r="B233" t="n">
-        <v>34.41329193115234</v>
+        <v>34.41328811645508</v>
       </c>
       <c r="C233" t="n">
-        <v>36.09550752381791</v>
+        <v>36.09550352264783</v>
       </c>
       <c r="D233" t="n">
-        <v>33.48086508042814</v>
+        <v>33.48086136908995</v>
       </c>
       <c r="E233" t="n">
-        <v>35.62448595864728</v>
+        <v>35.62448200968972</v>
       </c>
       <c r="F233" t="n">
         <v>3113087</v>
@@ -5092,16 +5092,16 @@
         <v>44491</v>
       </c>
       <c r="B234" t="n">
-        <v>32.63495254516602</v>
+        <v>32.63494873046875</v>
       </c>
       <c r="C234" t="n">
-        <v>34.06723862420559</v>
+        <v>34.06723464208851</v>
       </c>
       <c r="D234" t="n">
-        <v>31.04886594627039</v>
+        <v>31.04886231697067</v>
       </c>
       <c r="E234" t="n">
-        <v>33.63467091453443</v>
+        <v>33.63466698298016</v>
       </c>
       <c r="F234" t="n">
         <v>4894520</v>
@@ -5112,16 +5112,16 @@
         <v>44494</v>
       </c>
       <c r="B235" t="n">
-        <v>36.84706115722656</v>
+        <v>36.8470573425293</v>
       </c>
       <c r="C235" t="n">
-        <v>37.31127712193275</v>
+        <v>37.3112732591762</v>
       </c>
       <c r="D235" t="n">
-        <v>32.95926229019877</v>
+        <v>32.95925887799699</v>
       </c>
       <c r="E235" t="n">
-        <v>32.95926229019877</v>
+        <v>32.95925887799699</v>
       </c>
       <c r="F235" t="n">
         <v>3449995</v>
@@ -5152,16 +5152,16 @@
         <v>44496</v>
       </c>
       <c r="B237" t="n">
-        <v>35.29000473022461</v>
+        <v>35.29000854492188</v>
       </c>
       <c r="C237" t="n">
-        <v>36.07336794668348</v>
+        <v>36.07337184605893</v>
       </c>
       <c r="D237" t="n">
-        <v>34.47762778370612</v>
+        <v>34.47763151058894</v>
       </c>
       <c r="E237" t="n">
-        <v>36.07336794668348</v>
+        <v>36.07337184605893</v>
       </c>
       <c r="F237" t="n">
         <v>2270538</v>
@@ -5272,16 +5272,16 @@
         <v>44505</v>
       </c>
       <c r="B243" t="n">
-        <v>34.33256149291992</v>
+        <v>34.33255767822266</v>
       </c>
       <c r="C243" t="n">
-        <v>35.80257809171644</v>
+        <v>35.80257411368536</v>
       </c>
       <c r="D243" t="n">
-        <v>31.73102433433615</v>
+        <v>31.73102080869616</v>
       </c>
       <c r="E243" t="n">
-        <v>33.17202720107906</v>
+        <v>33.17202351532898</v>
       </c>
       <c r="F243" t="n">
         <v>9166770</v>
@@ -5312,16 +5312,16 @@
         <v>44509</v>
       </c>
       <c r="B245" t="n">
-        <v>34.50664520263672</v>
+        <v>34.50664138793945</v>
       </c>
       <c r="C245" t="n">
-        <v>35.10625735786877</v>
+        <v>35.1062534768846</v>
       </c>
       <c r="D245" t="n">
-        <v>32.63044377861175</v>
+        <v>32.63044017132788</v>
       </c>
       <c r="E245" t="n">
-        <v>33.89736430140155</v>
+        <v>33.89736055406007</v>
       </c>
       <c r="F245" t="n">
         <v>7032350</v>
@@ -5372,16 +5372,16 @@
         <v>44512</v>
       </c>
       <c r="B248" t="n">
-        <v>30.94766235351562</v>
+        <v>30.94766044616699</v>
       </c>
       <c r="C248" t="n">
-        <v>33.11399911175717</v>
+        <v>33.11399707089411</v>
       </c>
       <c r="D248" t="n">
-        <v>30.69621126299056</v>
+        <v>30.69620937113922</v>
       </c>
       <c r="E248" t="n">
-        <v>32.10819849723269</v>
+        <v>32.10819651835855</v>
       </c>
       <c r="F248" t="n">
         <v>3403064</v>
@@ -5552,16 +5552,16 @@
         <v>44526</v>
       </c>
       <c r="B257" t="n">
-        <v>26.69235992431641</v>
+        <v>26.69235801696777</v>
       </c>
       <c r="C257" t="n">
-        <v>27.61111748815896</v>
+        <v>27.61111551515892</v>
       </c>
       <c r="D257" t="n">
-        <v>25.85096918966023</v>
+        <v>25.85096734243463</v>
       </c>
       <c r="E257" t="n">
-        <v>26.59564810870458</v>
+        <v>26.59564620826666</v>
       </c>
       <c r="F257" t="n">
         <v>3664026</v>
@@ -5592,16 +5592,16 @@
         <v>44530</v>
       </c>
       <c r="B259" t="n">
-        <v>26.71170043945312</v>
+        <v>26.71169853210449</v>
       </c>
       <c r="C259" t="n">
-        <v>26.71170043945312</v>
+        <v>26.71169853210449</v>
       </c>
       <c r="D259" t="n">
-        <v>25.48346622320262</v>
+        <v>25.48346440355603</v>
       </c>
       <c r="E259" t="n">
-        <v>26.53761992558345</v>
+        <v>26.53761803066504</v>
       </c>
       <c r="F259" t="n">
         <v>4757647</v>
@@ -5612,16 +5612,16 @@
         <v>44531</v>
       </c>
       <c r="B260" t="n">
-        <v>26.69235992431641</v>
+        <v>26.69235801696777</v>
       </c>
       <c r="C260" t="n">
-        <v>28.01730598945588</v>
+        <v>28.01730398743094</v>
       </c>
       <c r="D260" t="n">
-        <v>26.32485577450663</v>
+        <v>26.32485389341864</v>
       </c>
       <c r="E260" t="n">
-        <v>27.17591712858762</v>
+        <v>27.17591518668557</v>
       </c>
       <c r="F260" t="n">
         <v>3467467</v>
@@ -5752,16 +5752,16 @@
         <v>44540</v>
       </c>
       <c r="B267" t="n">
-        <v>29.43896102905273</v>
+        <v>29.43896293640137</v>
       </c>
       <c r="C267" t="n">
-        <v>29.76778079564096</v>
+        <v>29.76778272429381</v>
       </c>
       <c r="D267" t="n">
-        <v>28.76198025889329</v>
+        <v>28.76198212238038</v>
       </c>
       <c r="E267" t="n">
-        <v>29.57435718308462</v>
+        <v>29.57435909920557</v>
       </c>
       <c r="F267" t="n">
         <v>1281952</v>
@@ -5832,16 +5832,16 @@
         <v>44546</v>
       </c>
       <c r="B271" t="n">
-        <v>30.62851524353027</v>
+        <v>30.62851333618164</v>
       </c>
       <c r="C271" t="n">
-        <v>30.86062322322113</v>
+        <v>30.86062130141829</v>
       </c>
       <c r="D271" t="n">
-        <v>29.25521235155887</v>
+        <v>29.25521052973079</v>
       </c>
       <c r="E271" t="n">
-        <v>29.49699095054871</v>
+        <v>29.4969891136642</v>
       </c>
       <c r="F271" t="n">
         <v>3477726</v>
@@ -5952,16 +5952,16 @@
         <v>44557</v>
       </c>
       <c r="B277" t="n">
-        <v>30.7252254486084</v>
+        <v>30.72522354125977</v>
       </c>
       <c r="C277" t="n">
-        <v>31.01536089416671</v>
+        <v>31.01535896880716</v>
       </c>
       <c r="D277" t="n">
-        <v>29.98054840663</v>
+        <v>29.98054654550914</v>
       </c>
       <c r="E277" t="n">
-        <v>29.98054840663</v>
+        <v>29.98054654550914</v>
       </c>
       <c r="F277" t="n">
         <v>1273927</v>
@@ -6132,16 +6132,16 @@
         <v>44571</v>
       </c>
       <c r="B286" t="n">
-        <v>33.37511825561523</v>
+        <v>33.37511444091797</v>
       </c>
       <c r="C286" t="n">
-        <v>33.89736166431392</v>
+        <v>33.89735778992546</v>
       </c>
       <c r="D286" t="n">
-        <v>32.24359399308115</v>
+        <v>32.24359030771443</v>
       </c>
       <c r="E286" t="n">
-        <v>32.3789901547752</v>
+        <v>32.37898645393302</v>
       </c>
       <c r="F286" t="n">
         <v>2829132</v>
@@ -6152,16 +6152,16 @@
         <v>44572</v>
       </c>
       <c r="B287" t="n">
-        <v>35.10625076293945</v>
+        <v>35.10625457763672</v>
       </c>
       <c r="C287" t="n">
-        <v>35.63816285834681</v>
+        <v>35.63816673084244</v>
       </c>
       <c r="D287" t="n">
-        <v>33.18169098013564</v>
+        <v>33.18169458570739</v>
       </c>
       <c r="E287" t="n">
-        <v>33.55886569280182</v>
+        <v>33.55886933935793</v>
       </c>
       <c r="F287" t="n">
         <v>3953735</v>
@@ -6172,16 +6172,16 @@
         <v>44573</v>
       </c>
       <c r="B288" t="n">
-        <v>34.89348602294922</v>
+        <v>34.89348983764648</v>
       </c>
       <c r="C288" t="n">
-        <v>35.98632394454952</v>
+        <v>35.98632787872025</v>
       </c>
       <c r="D288" t="n">
-        <v>34.13913659549451</v>
+        <v>34.13914032772324</v>
       </c>
       <c r="E288" t="n">
-        <v>35.34802942826484</v>
+        <v>35.34803329265463</v>
       </c>
       <c r="F288" t="n">
         <v>3302601</v>
@@ -6292,16 +6292,16 @@
         <v>44581</v>
       </c>
       <c r="B294" t="n">
-        <v>35.2996711730957</v>
+        <v>35.29967498779297</v>
       </c>
       <c r="C294" t="n">
-        <v>36.17007552296929</v>
+        <v>36.17007943172774</v>
       </c>
       <c r="D294" t="n">
-        <v>34.98052391082881</v>
+        <v>34.98052769103708</v>
       </c>
       <c r="E294" t="n">
-        <v>35.8702694969556</v>
+        <v>35.87027337331519</v>
       </c>
       <c r="F294" t="n">
         <v>3650414</v>
@@ -6332,16 +6332,16 @@
         <v>44585</v>
       </c>
       <c r="B296" t="n">
-        <v>34.35190582275391</v>
+        <v>34.35190200805664</v>
       </c>
       <c r="C296" t="n">
-        <v>35.31902021252021</v>
+        <v>35.3190162904272</v>
       </c>
       <c r="D296" t="n">
-        <v>34.05209976231423</v>
+        <v>34.05209598090971</v>
       </c>
       <c r="E296" t="n">
-        <v>34.2358508967577</v>
+        <v>34.23584709494806</v>
       </c>
       <c r="F296" t="n">
         <v>2113697</v>
@@ -6392,16 +6392,16 @@
         <v>44588</v>
       </c>
       <c r="B299" t="n">
-        <v>36.09270858764648</v>
+        <v>36.09271240234375</v>
       </c>
       <c r="C299" t="n">
-        <v>37.10817788022283</v>
+        <v>37.1081818022467</v>
       </c>
       <c r="D299" t="n">
-        <v>35.68652012110085</v>
+        <v>35.68652389286739</v>
       </c>
       <c r="E299" t="n">
-        <v>35.87994373577622</v>
+        <v>35.87994752798603</v>
       </c>
       <c r="F299" t="n">
         <v>3171460</v>
@@ -6492,16 +6492,16 @@
         <v>44595</v>
       </c>
       <c r="B304" t="n">
-        <v>35.2996711730957</v>
+        <v>35.29967498779297</v>
       </c>
       <c r="C304" t="n">
-        <v>35.58980845477045</v>
+        <v>35.58981230082171</v>
       </c>
       <c r="D304" t="n">
-        <v>33.84899975502328</v>
+        <v>33.84900341295216</v>
       </c>
       <c r="E304" t="n">
-        <v>34.98052391082881</v>
+        <v>34.98052769103708</v>
       </c>
       <c r="F304" t="n">
         <v>4177823</v>
@@ -6592,16 +6592,16 @@
         <v>44602</v>
       </c>
       <c r="B309" t="n">
-        <v>37.28226089477539</v>
+        <v>37.28226470947266</v>
       </c>
       <c r="C309" t="n">
-        <v>38.38477139493146</v>
+        <v>38.3847753224369</v>
       </c>
       <c r="D309" t="n">
-        <v>36.33448778997354</v>
+        <v>36.33449150769526</v>
       </c>
       <c r="E309" t="n">
-        <v>36.3635015200494</v>
+        <v>36.36350524073979</v>
       </c>
       <c r="F309" t="n">
         <v>7025951</v>
@@ -6612,16 +6612,16 @@
         <v>44603</v>
       </c>
       <c r="B310" t="n">
-        <v>38.07529449462891</v>
+        <v>38.07529067993164</v>
       </c>
       <c r="C310" t="n">
-        <v>38.49115547855604</v>
+        <v>38.49115162219439</v>
       </c>
       <c r="D310" t="n">
-        <v>37.37897243800389</v>
+        <v>37.37896869306991</v>
       </c>
       <c r="E310" t="n">
-        <v>37.78516092896444</v>
+        <v>37.78515714333515</v>
       </c>
       <c r="F310" t="n">
         <v>5486491</v>
@@ -6632,16 +6632,16 @@
         <v>44606</v>
       </c>
       <c r="B311" t="n">
-        <v>37.57239532470703</v>
+        <v>37.57239151000977</v>
       </c>
       <c r="C311" t="n">
-        <v>38.84898823510746</v>
+        <v>38.84898429079868</v>
       </c>
       <c r="D311" t="n">
-        <v>36.95344198127135</v>
+        <v>36.95343822941596</v>
       </c>
       <c r="E311" t="n">
-        <v>38.2977310983781</v>
+        <v>38.29772721003804</v>
       </c>
       <c r="F311" t="n">
         <v>3902640</v>
@@ -6652,16 +6652,16 @@
         <v>44607</v>
       </c>
       <c r="B312" t="n">
-        <v>35.79290390014648</v>
+        <v>35.79290008544922</v>
       </c>
       <c r="C312" t="n">
-        <v>36.65363583255173</v>
+        <v>36.65363192612031</v>
       </c>
       <c r="D312" t="n">
-        <v>35.63816650158672</v>
+        <v>35.63816270338088</v>
       </c>
       <c r="E312" t="n">
-        <v>36.55692589534578</v>
+        <v>36.55692199922141</v>
       </c>
       <c r="F312" t="n">
         <v>3810709</v>
@@ -6672,16 +6672,16 @@
         <v>44608</v>
       </c>
       <c r="B313" t="n">
-        <v>35.92829895019531</v>
+        <v>35.92830276489258</v>
       </c>
       <c r="C313" t="n">
-        <v>36.80837209332255</v>
+        <v>36.80837600146183</v>
       </c>
       <c r="D313" t="n">
-        <v>35.69619285953032</v>
+        <v>35.69619664958365</v>
       </c>
       <c r="E313" t="n">
-        <v>36.4408698462091</v>
+        <v>36.44087371532872</v>
       </c>
       <c r="F313" t="n">
         <v>4244663</v>
@@ -6692,16 +6692,16 @@
         <v>44609</v>
       </c>
       <c r="B314" t="n">
-        <v>35.2996711730957</v>
+        <v>35.29967498779297</v>
       </c>
       <c r="C314" t="n">
-        <v>35.89928322512308</v>
+        <v>35.89928710461807</v>
       </c>
       <c r="D314" t="n">
-        <v>34.41959807888318</v>
+        <v>34.41960179847439</v>
       </c>
       <c r="E314" t="n">
-        <v>35.68651838361181</v>
+        <v>35.68652224011414</v>
       </c>
       <c r="F314" t="n">
         <v>4430658</v>
@@ -6712,16 +6712,16 @@
         <v>44610</v>
       </c>
       <c r="B315" t="n">
-        <v>34.48729705810547</v>
+        <v>34.48730087280273</v>
       </c>
       <c r="C315" t="n">
-        <v>35.41572509065163</v>
+        <v>35.41572900804387</v>
       </c>
       <c r="D315" t="n">
-        <v>33.80064384086931</v>
+        <v>33.80064757961473</v>
       </c>
       <c r="E315" t="n">
-        <v>34.83545803875718</v>
+        <v>34.83546189196511</v>
       </c>
       <c r="F315" t="n">
         <v>4069741</v>
@@ -6852,16 +6852,16 @@
         <v>44623</v>
       </c>
       <c r="B322" t="n">
-        <v>37.34028244018555</v>
+        <v>37.34028625488281</v>
       </c>
       <c r="C322" t="n">
-        <v>37.88187078764361</v>
+        <v>37.88187465766974</v>
       </c>
       <c r="D322" t="n">
-        <v>36.31514444477941</v>
+        <v>36.31514815474819</v>
       </c>
       <c r="E322" t="n">
-        <v>37.12751759702811</v>
+        <v>37.12752138998924</v>
       </c>
       <c r="F322" t="n">
         <v>9786414</v>
@@ -6892,16 +6892,16 @@
         <v>44627</v>
       </c>
       <c r="B324" t="n">
-        <v>37.04048538208008</v>
+        <v>37.04048156738281</v>
       </c>
       <c r="C324" t="n">
-        <v>39.28418904358112</v>
+        <v>39.28418499781101</v>
       </c>
       <c r="D324" t="n">
-        <v>36.65363811402602</v>
+        <v>36.65363433916909</v>
       </c>
       <c r="E324" t="n">
-        <v>38.17200970618351</v>
+        <v>38.17200577495368</v>
       </c>
       <c r="F324" t="n">
         <v>5025922</v>
@@ -6952,16 +6952,16 @@
         <v>44630</v>
       </c>
       <c r="B327" t="n">
-        <v>35.72520446777344</v>
+        <v>35.7252082824707</v>
       </c>
       <c r="C327" t="n">
-        <v>37.22423084456335</v>
+        <v>37.22423481932497</v>
       </c>
       <c r="D327" t="n">
-        <v>35.51243962707166</v>
+        <v>35.51244341905014</v>
       </c>
       <c r="E327" t="n">
-        <v>36.75034245134777</v>
+        <v>36.75034637550812</v>
       </c>
       <c r="F327" t="n">
         <v>4502679</v>
@@ -7032,16 +7032,16 @@
         <v>44636</v>
       </c>
       <c r="B331" t="n">
-        <v>32.84320831298828</v>
+        <v>32.84320449829102</v>
       </c>
       <c r="C331" t="n">
-        <v>34.44861737575539</v>
+        <v>34.44861337459189</v>
       </c>
       <c r="D331" t="n">
-        <v>32.34030985608281</v>
+        <v>32.34030609979657</v>
       </c>
       <c r="E331" t="n">
-        <v>34.10045632903992</v>
+        <v>34.10045236831488</v>
       </c>
       <c r="F331" t="n">
         <v>3899288</v>
@@ -7092,16 +7092,16 @@
         <v>44641</v>
       </c>
       <c r="B334" t="n">
-        <v>36.61495208740234</v>
+        <v>36.61494827270508</v>
       </c>
       <c r="C334" t="n">
-        <v>36.86640318776314</v>
+        <v>36.86639934686866</v>
       </c>
       <c r="D334" t="n">
-        <v>35.88961626653654</v>
+        <v>35.88961252740777</v>
       </c>
       <c r="E334" t="n">
-        <v>35.97665746445866</v>
+        <v>35.97665371626157</v>
       </c>
       <c r="F334" t="n">
         <v>3600944</v>
@@ -7212,16 +7212,16 @@
         <v>44649</v>
       </c>
       <c r="B340" t="n">
-        <v>40.11590576171875</v>
+        <v>40.11590194702148</v>
       </c>
       <c r="C340" t="n">
-        <v>40.60913544747385</v>
+        <v>40.60913158587444</v>
       </c>
       <c r="D340" t="n">
-        <v>37.8141747233464</v>
+        <v>37.81417112752509</v>
       </c>
       <c r="E340" t="n">
-        <v>38.00759834997051</v>
+        <v>38.00759473575618</v>
       </c>
       <c r="F340" t="n">
         <v>6952609</v>
@@ -7252,16 +7252,16 @@
         <v>44651</v>
       </c>
       <c r="B342" t="n">
-        <v>40.47373580932617</v>
+        <v>40.47373962402344</v>
       </c>
       <c r="C342" t="n">
-        <v>41.13137533388116</v>
+        <v>41.13137921056172</v>
       </c>
       <c r="D342" t="n">
-        <v>39.6710313879373</v>
+        <v>39.67103512697872</v>
       </c>
       <c r="E342" t="n">
-        <v>40.13524730247168</v>
+        <v>40.135251085266</v>
       </c>
       <c r="F342" t="n">
         <v>3810811</v>
@@ -7312,16 +7312,16 @@
         <v>44656</v>
       </c>
       <c r="B345" t="n">
-        <v>41.9727668762207</v>
+        <v>41.97276306152344</v>
       </c>
       <c r="C345" t="n">
-        <v>43.03659497534015</v>
+        <v>43.03659106395681</v>
       </c>
       <c r="D345" t="n">
-        <v>41.5762508676977</v>
+        <v>41.57624708903781</v>
       </c>
       <c r="E345" t="n">
-        <v>42.30158667490721</v>
+        <v>42.30158283032514</v>
       </c>
       <c r="F345" t="n">
         <v>5903074</v>
@@ -7432,16 +7432,16 @@
         <v>44664</v>
       </c>
       <c r="B351" t="n">
-        <v>43.62653350830078</v>
+        <v>43.62652969360352</v>
       </c>
       <c r="C351" t="n">
-        <v>43.71357095479976</v>
+        <v>43.71356713249195</v>
       </c>
       <c r="D351" t="n">
-        <v>42.8431702567798</v>
+        <v>42.8431665105797</v>
       </c>
       <c r="E351" t="n">
-        <v>43.30738621093589</v>
+        <v>43.30738242414481</v>
       </c>
       <c r="F351" t="n">
         <v>3238402</v>
@@ -7452,16 +7452,16 @@
         <v>44665</v>
       </c>
       <c r="B352" t="n">
-        <v>42.93987655639648</v>
+        <v>42.93988037109375</v>
       </c>
       <c r="C352" t="n">
-        <v>43.62652981023535</v>
+        <v>43.62653368593358</v>
       </c>
       <c r="D352" t="n">
-        <v>42.2242133212342</v>
+        <v>42.2242170723533</v>
       </c>
       <c r="E352" t="n">
-        <v>43.62652981023535</v>
+        <v>43.62653368593358</v>
       </c>
       <c r="F352" t="n">
         <v>2345809</v>
@@ -7552,16 +7552,16 @@
         <v>44676</v>
       </c>
       <c r="B357" t="n">
-        <v>41.94374847412109</v>
+        <v>41.94375228881836</v>
       </c>
       <c r="C357" t="n">
-        <v>42.40796438837074</v>
+        <v>42.40796824528748</v>
       </c>
       <c r="D357" t="n">
-        <v>40.64781815768625</v>
+        <v>40.64782185452133</v>
       </c>
       <c r="E357" t="n">
-        <v>40.75420058099602</v>
+        <v>40.75420428750637</v>
       </c>
       <c r="F357" t="n">
         <v>3287465</v>
@@ -7592,16 +7592,16 @@
         <v>44678</v>
       </c>
       <c r="B359" t="n">
-        <v>42.16619110107422</v>
+        <v>42.16618728637695</v>
       </c>
       <c r="C359" t="n">
-        <v>43.58784900340616</v>
+        <v>43.58784506009413</v>
       </c>
       <c r="D359" t="n">
-        <v>41.46986901615963</v>
+        <v>41.46986526445734</v>
       </c>
       <c r="E359" t="n">
-        <v>43.52015279261696</v>
+        <v>43.52014885542929</v>
       </c>
       <c r="F359" t="n">
         <v>3779727</v>
@@ -7672,16 +7672,16 @@
         <v>44684</v>
       </c>
       <c r="B363" t="n">
-        <v>42.12749862670898</v>
+        <v>42.12750244140625</v>
       </c>
       <c r="C363" t="n">
-        <v>42.54335956584936</v>
+        <v>42.54336341820335</v>
       </c>
       <c r="D363" t="n">
-        <v>41.25709802345466</v>
+        <v>41.25710175933607</v>
       </c>
       <c r="E363" t="n">
-        <v>42.54335956584936</v>
+        <v>42.54336341820335</v>
       </c>
       <c r="F363" t="n">
         <v>4458389</v>
@@ -7692,16 +7692,16 @@
         <v>44685</v>
       </c>
       <c r="B364" t="n">
-        <v>44.10041809082031</v>
+        <v>44.10041427612305</v>
       </c>
       <c r="C364" t="n">
-        <v>44.32285544811791</v>
+        <v>44.32285161417975</v>
       </c>
       <c r="D364" t="n">
-        <v>42.16618932580826</v>
+        <v>42.16618567842227</v>
       </c>
       <c r="E364" t="n">
-        <v>43.04626251447057</v>
+        <v>43.04625879095802</v>
       </c>
       <c r="F364" t="n">
         <v>5759540</v>
@@ -7712,16 +7712,16 @@
         <v>44686</v>
       </c>
       <c r="B365" t="n">
-        <v>42.92053604125977</v>
+        <v>42.92053985595703</v>
       </c>
       <c r="C365" t="n">
-        <v>44.57429987842104</v>
+        <v>44.57430384010176</v>
       </c>
       <c r="D365" t="n">
-        <v>42.01144918067956</v>
+        <v>42.01145291457887</v>
       </c>
       <c r="E365" t="n">
-        <v>44.09074271874429</v>
+        <v>44.09074663744735</v>
       </c>
       <c r="F365" t="n">
         <v>4814532</v>
@@ -7732,16 +7732,16 @@
         <v>44687</v>
       </c>
       <c r="B366" t="n">
-        <v>42.55303192138672</v>
+        <v>42.55303573608398</v>
       </c>
       <c r="C366" t="n">
-        <v>43.90698966019007</v>
+        <v>43.90699359626386</v>
       </c>
       <c r="D366" t="n">
-        <v>41.82769621387857</v>
+        <v>41.82769996355259</v>
       </c>
       <c r="E366" t="n">
-        <v>43.33639133753226</v>
+        <v>43.33639522245434</v>
       </c>
       <c r="F366" t="n">
         <v>4093307</v>
@@ -7892,16 +7892,16 @@
         <v>44699</v>
       </c>
       <c r="B374" t="n">
-        <v>39.99985122680664</v>
+        <v>39.99985504150391</v>
       </c>
       <c r="C374" t="n">
-        <v>42.2242133773643</v>
+        <v>42.22421740419406</v>
       </c>
       <c r="D374" t="n">
-        <v>39.72905892177436</v>
+        <v>39.72906271064676</v>
       </c>
       <c r="E374" t="n">
-        <v>42.13717219055205</v>
+        <v>42.13717620908088</v>
       </c>
       <c r="F374" t="n">
         <v>1865839</v>
@@ -7952,16 +7952,16 @@
         <v>44704</v>
       </c>
       <c r="B377" t="n">
-        <v>42.28224182128906</v>
+        <v>42.28224563598633</v>
       </c>
       <c r="C377" t="n">
-        <v>42.7948127143697</v>
+        <v>42.79481657531103</v>
       </c>
       <c r="D377" t="n">
-        <v>41.3538099687909</v>
+        <v>41.35381369972519</v>
       </c>
       <c r="E377" t="n">
-        <v>41.42150992041549</v>
+        <v>41.42151365745766</v>
       </c>
       <c r="F377" t="n">
         <v>3400119</v>
@@ -8012,16 +8012,16 @@
         <v>44707</v>
       </c>
       <c r="B380" t="n">
-        <v>46.59557342529297</v>
+        <v>46.5955696105957</v>
       </c>
       <c r="C380" t="n">
-        <v>47.16617181868395</v>
+        <v>47.1661679572728</v>
       </c>
       <c r="D380" t="n">
-        <v>45.10621935322675</v>
+        <v>45.10621566046026</v>
       </c>
       <c r="E380" t="n">
-        <v>45.25128426416589</v>
+        <v>45.2512805595232</v>
       </c>
       <c r="F380" t="n">
         <v>4582217</v>
@@ -8072,16 +8072,16 @@
         <v>44712</v>
       </c>
       <c r="B383" t="n">
-        <v>47.14683151245117</v>
+        <v>47.14682769775391</v>
       </c>
       <c r="C383" t="n">
-        <v>49.54527256510714</v>
+        <v>49.5452685563496</v>
       </c>
       <c r="D383" t="n">
-        <v>47.11781778017441</v>
+        <v>47.11781396782467</v>
       </c>
       <c r="E383" t="n">
-        <v>48.22032836396376</v>
+        <v>48.22032446240879</v>
       </c>
       <c r="F383" t="n">
         <v>6322705</v>
@@ -8152,16 +8152,16 @@
         <v>44718</v>
       </c>
       <c r="B387" t="n">
-        <v>45.31898498535156</v>
+        <v>45.3189811706543</v>
       </c>
       <c r="C387" t="n">
-        <v>47.45630618888874</v>
+        <v>47.4563021942838</v>
       </c>
       <c r="D387" t="n">
-        <v>45.13523009894016</v>
+        <v>45.13522629971035</v>
       </c>
       <c r="E387" t="n">
-        <v>47.156500121283</v>
+        <v>47.15649615191405</v>
       </c>
       <c r="F387" t="n">
         <v>1711233</v>
@@ -8172,16 +8172,16 @@
         <v>44719</v>
       </c>
       <c r="B388" t="n">
-        <v>45.31898498535156</v>
+        <v>45.3189811706543</v>
       </c>
       <c r="C388" t="n">
-        <v>45.84122466966569</v>
+        <v>45.84122081100923</v>
       </c>
       <c r="D388" t="n">
-        <v>44.73871408907649</v>
+        <v>44.73871032322317</v>
       </c>
       <c r="E388" t="n">
-        <v>44.98049269229714</v>
+        <v>44.98048890609225</v>
       </c>
       <c r="F388" t="n">
         <v>1887578</v>
@@ -8192,16 +8192,16 @@
         <v>44720</v>
       </c>
       <c r="B389" t="n">
-        <v>45.25128173828125</v>
+        <v>45.25128555297852</v>
       </c>
       <c r="C389" t="n">
-        <v>46.00563122530019</v>
+        <v>46.00563510358936</v>
       </c>
       <c r="D389" t="n">
-        <v>44.9224619623857</v>
+        <v>44.92246574936335</v>
       </c>
       <c r="E389" t="n">
-        <v>45.31898169100119</v>
+        <v>45.31898551140559</v>
       </c>
       <c r="F389" t="n">
         <v>1920490</v>
@@ -8212,16 +8212,16 @@
         <v>44721</v>
       </c>
       <c r="B390" t="n">
-        <v>44.50660705566406</v>
+        <v>44.5066032409668</v>
       </c>
       <c r="C390" t="n">
-        <v>45.59944512032232</v>
+        <v>45.59944121195702</v>
       </c>
       <c r="D390" t="n">
-        <v>44.32285592064108</v>
+        <v>44.32285212169327</v>
       </c>
       <c r="E390" t="n">
-        <v>45.2222703572209</v>
+        <v>45.22226648118356</v>
       </c>
       <c r="F390" t="n">
         <v>1644697</v>
@@ -8472,16 +8472,16 @@
         <v>44741</v>
       </c>
       <c r="B403" t="n">
-        <v>34.71940994262695</v>
+        <v>34.71940612792969</v>
       </c>
       <c r="C403" t="n">
-        <v>35.41573204057546</v>
+        <v>35.41572814937177</v>
       </c>
       <c r="D403" t="n">
-        <v>34.0907840567348</v>
+        <v>34.09078031110602</v>
       </c>
       <c r="E403" t="n">
-        <v>35.29967710839206</v>
+        <v>35.29967322993957</v>
       </c>
       <c r="F403" t="n">
         <v>2690880</v>
@@ -8532,16 +8532,16 @@
         <v>44746</v>
       </c>
       <c r="B406" t="n">
-        <v>35.08690643310547</v>
+        <v>35.08691024780273</v>
       </c>
       <c r="C406" t="n">
-        <v>35.60914979405575</v>
+        <v>35.60915366553204</v>
       </c>
       <c r="D406" t="n">
-        <v>34.19716459197961</v>
+        <v>34.1971683099429</v>
       </c>
       <c r="E406" t="n">
-        <v>34.57433556409744</v>
+        <v>34.57433932306729</v>
       </c>
       <c r="F406" t="n">
         <v>2359523</v>
@@ -8612,16 +8612,16 @@
         <v>44750</v>
       </c>
       <c r="B410" t="n">
-        <v>31.81806564331055</v>
+        <v>31.81806373596191</v>
       </c>
       <c r="C410" t="n">
-        <v>32.48537398775778</v>
+        <v>32.48537204040704</v>
       </c>
       <c r="D410" t="n">
-        <v>31.19911226993215</v>
+        <v>31.19911039968697</v>
       </c>
       <c r="E410" t="n">
-        <v>31.31516719855805</v>
+        <v>31.3151653213559</v>
       </c>
       <c r="F410" t="n">
         <v>4375906</v>
@@ -8712,16 +8712,16 @@
         <v>44757</v>
       </c>
       <c r="B415" t="n">
-        <v>27.79486656188965</v>
+        <v>27.79486846923828</v>
       </c>
       <c r="C415" t="n">
-        <v>29.07145943509457</v>
+        <v>29.07146143004599</v>
       </c>
       <c r="D415" t="n">
-        <v>27.79486656188965</v>
+        <v>27.79486846923828</v>
       </c>
       <c r="E415" t="n">
-        <v>29.06178694260021</v>
+        <v>29.06178893688788</v>
       </c>
       <c r="F415" t="n">
         <v>4618481</v>
@@ -8752,16 +8752,16 @@
         <v>44761</v>
       </c>
       <c r="B417" t="n">
-        <v>29.43896102905273</v>
+        <v>29.43896293640137</v>
       </c>
       <c r="C417" t="n">
-        <v>29.5356728353309</v>
+        <v>29.53567474894549</v>
       </c>
       <c r="D417" t="n">
-        <v>28.11401509178381</v>
+        <v>28.11401691328927</v>
       </c>
       <c r="E417" t="n">
-        <v>28.14302882104603</v>
+        <v>28.14303064443129</v>
       </c>
       <c r="F417" t="n">
         <v>4570230</v>
@@ -8772,16 +8772,16 @@
         <v>44762</v>
       </c>
       <c r="B418" t="n">
-        <v>30.5994987487793</v>
+        <v>30.59950065612793</v>
       </c>
       <c r="C418" t="n">
-        <v>30.97667347904845</v>
+        <v>30.97667540990739</v>
       </c>
       <c r="D418" t="n">
-        <v>29.21652536238831</v>
+        <v>29.21652718353251</v>
       </c>
       <c r="E418" t="n">
-        <v>29.21652536238831</v>
+        <v>29.21652718353251</v>
       </c>
       <c r="F418" t="n">
         <v>5027446</v>
@@ -8792,16 +8792,16 @@
         <v>44763</v>
       </c>
       <c r="B419" t="n">
-        <v>29.44863319396973</v>
+        <v>29.44863510131836</v>
       </c>
       <c r="C419" t="n">
-        <v>29.86449039614633</v>
+        <v>29.86449233042948</v>
       </c>
       <c r="D419" t="n">
-        <v>28.83935050759925</v>
+        <v>28.83935237548546</v>
       </c>
       <c r="E419" t="n">
-        <v>29.86449039614633</v>
+        <v>29.86449233042948</v>
       </c>
       <c r="F419" t="n">
         <v>5437325</v>
@@ -8832,16 +8832,16 @@
         <v>44767</v>
       </c>
       <c r="B421" t="n">
-        <v>29.26488304138184</v>
+        <v>29.2648811340332</v>
       </c>
       <c r="C421" t="n">
-        <v>29.71942650877206</v>
+        <v>29.7194245717984</v>
       </c>
       <c r="D421" t="n">
-        <v>28.43316480875549</v>
+        <v>28.43316295561438</v>
       </c>
       <c r="E421" t="n">
-        <v>28.87803765682343</v>
+        <v>28.87803577468757</v>
       </c>
       <c r="F421" t="n">
         <v>3521914</v>
@@ -8852,16 +8852,16 @@
         <v>44768</v>
       </c>
       <c r="B422" t="n">
-        <v>28.95540618896484</v>
+        <v>28.95540428161621</v>
       </c>
       <c r="C422" t="n">
-        <v>30.15462856046375</v>
+        <v>30.15462657412001</v>
       </c>
       <c r="D422" t="n">
-        <v>28.81033940483069</v>
+        <v>28.81033750703789</v>
       </c>
       <c r="E422" t="n">
-        <v>29.88383623072646</v>
+        <v>29.88383426222034</v>
       </c>
       <c r="F422" t="n">
         <v>2984449</v>
@@ -8872,16 +8872,16 @@
         <v>44769</v>
       </c>
       <c r="B423" t="n">
-        <v>29.66139793395996</v>
+        <v>29.66139984130859</v>
       </c>
       <c r="C423" t="n">
-        <v>29.76778035716261</v>
+        <v>29.76778227135207</v>
       </c>
       <c r="D423" t="n">
-        <v>28.6169130648438</v>
+        <v>28.61691490502781</v>
       </c>
       <c r="E423" t="n">
-        <v>28.95540344493757</v>
+        <v>28.95540530688788</v>
       </c>
       <c r="F423" t="n">
         <v>2554762</v>
@@ -8892,16 +8892,16 @@
         <v>44770</v>
       </c>
       <c r="B424" t="n">
-        <v>30.78325080871582</v>
+        <v>30.78325271606445</v>
       </c>
       <c r="C424" t="n">
-        <v>30.88963323601387</v>
+        <v>30.88963514995402</v>
       </c>
       <c r="D424" t="n">
-        <v>29.53567353730325</v>
+        <v>29.53567536735125</v>
       </c>
       <c r="E424" t="n">
-        <v>29.96120324649545</v>
+        <v>29.96120510290952</v>
       </c>
       <c r="F424" t="n">
         <v>4208906</v>
@@ -8952,16 +8952,16 @@
         <v>44775</v>
       </c>
       <c r="B427" t="n">
-        <v>31.85675048828125</v>
+        <v>31.85674858093262</v>
       </c>
       <c r="C427" t="n">
-        <v>32.07918409507452</v>
+        <v>32.0791821744082</v>
       </c>
       <c r="D427" t="n">
-        <v>30.94766170651904</v>
+        <v>30.94765985359998</v>
       </c>
       <c r="E427" t="n">
-        <v>31.32483646063348</v>
+        <v>31.32483458513196</v>
       </c>
       <c r="F427" t="n">
         <v>3020206</v>
@@ -9072,16 +9072,16 @@
         <v>44783</v>
       </c>
       <c r="B433" t="n">
-        <v>33.26873779296875</v>
+        <v>33.26873397827148</v>
       </c>
       <c r="C433" t="n">
-        <v>33.97473237410905</v>
+        <v>33.97472847846024</v>
       </c>
       <c r="D433" t="n">
-        <v>32.87222177725572</v>
+        <v>32.87221800802422</v>
       </c>
       <c r="E433" t="n">
-        <v>33.62657133023831</v>
+        <v>33.62656747451073</v>
       </c>
       <c r="F433" t="n">
         <v>3325457</v>
@@ -9152,16 +9152,16 @@
         <v>44789</v>
       </c>
       <c r="B437" t="n">
-        <v>32.27260971069336</v>
+        <v>32.27260589599609</v>
       </c>
       <c r="C437" t="n">
-        <v>32.61110200955398</v>
+        <v>32.61109815484615</v>
       </c>
       <c r="D437" t="n">
-        <v>31.73102503057709</v>
+        <v>31.73102127989639</v>
       </c>
       <c r="E437" t="n">
-        <v>32.39833338730038</v>
+        <v>32.39832955774229</v>
       </c>
       <c r="F437" t="n">
         <v>2684074</v>
@@ -9172,16 +9172,16 @@
         <v>44790</v>
       </c>
       <c r="B438" t="n">
-        <v>32.53372573852539</v>
+        <v>32.53372955322266</v>
       </c>
       <c r="C438" t="n">
-        <v>32.93024545622303</v>
+        <v>32.93024931741367</v>
       </c>
       <c r="D438" t="n">
-        <v>31.80839000156146</v>
+        <v>31.80839373121048</v>
       </c>
       <c r="E438" t="n">
-        <v>31.81806249384815</v>
+        <v>31.8180662246313</v>
       </c>
       <c r="F438" t="n">
         <v>3057587</v>
@@ -9252,16 +9252,16 @@
         <v>44796</v>
       </c>
       <c r="B442" t="n">
-        <v>35.11592483520508</v>
+        <v>35.11592102050781</v>
       </c>
       <c r="C442" t="n">
-        <v>35.54145457609587</v>
+        <v>35.54145071517264</v>
       </c>
       <c r="D442" t="n">
-        <v>33.43314711052539</v>
+        <v>33.43314347863087</v>
       </c>
       <c r="E442" t="n">
-        <v>33.46216084263848</v>
+        <v>33.46215720759215</v>
       </c>
       <c r="F442" t="n">
         <v>5706007</v>
@@ -9292,16 +9292,16 @@
         <v>44798</v>
       </c>
       <c r="B444" t="n">
-        <v>35.73487854003906</v>
+        <v>35.7348747253418</v>
       </c>
       <c r="C444" t="n">
-        <v>36.56659679067325</v>
+        <v>36.56659288719009</v>
       </c>
       <c r="D444" t="n">
-        <v>35.39638999233915</v>
+        <v>35.39638621377552</v>
       </c>
       <c r="E444" t="n">
-        <v>35.86060596289047</v>
+        <v>35.8606021347718</v>
       </c>
       <c r="F444" t="n">
         <v>2850362</v>
@@ -9372,16 +9372,16 @@
         <v>44804</v>
       </c>
       <c r="B448" t="n">
-        <v>36.16040802001953</v>
+        <v>36.16040420532227</v>
       </c>
       <c r="C448" t="n">
-        <v>36.46021408739674</v>
+        <v>36.46021024107181</v>
       </c>
       <c r="D448" t="n">
-        <v>35.22230734004456</v>
+        <v>35.22230362431106</v>
       </c>
       <c r="E448" t="n">
-        <v>35.91862941698318</v>
+        <v>35.91862562779205</v>
       </c>
       <c r="F448" t="n">
         <v>3394125</v>
@@ -9392,16 +9392,16 @@
         <v>44805</v>
       </c>
       <c r="B449" t="n">
-        <v>35.58013916015625</v>
+        <v>35.58013534545898</v>
       </c>
       <c r="C449" t="n">
-        <v>36.22810623483188</v>
+        <v>36.22810235066332</v>
       </c>
       <c r="D449" t="n">
-        <v>35.00954078502128</v>
+        <v>35.00953703150028</v>
       </c>
       <c r="E449" t="n">
-        <v>35.84125898955293</v>
+        <v>35.8412551468599</v>
       </c>
       <c r="F449" t="n">
         <v>3340084</v>
@@ -9492,16 +9492,16 @@
         <v>44813</v>
       </c>
       <c r="B454" t="n">
-        <v>35.92829895019531</v>
+        <v>35.92830276489258</v>
       </c>
       <c r="C454" t="n">
-        <v>36.3731698941971</v>
+        <v>36.37317375612866</v>
       </c>
       <c r="D454" t="n">
-        <v>35.60915167019012</v>
+        <v>35.60915545100184</v>
       </c>
       <c r="E454" t="n">
-        <v>35.79290279374685</v>
+        <v>35.79290659406839</v>
       </c>
       <c r="F454" t="n">
         <v>3544465</v>
@@ -9552,16 +9552,16 @@
         <v>44818</v>
       </c>
       <c r="B457" t="n">
-        <v>37.25325012207031</v>
+        <v>37.25324630737305</v>
       </c>
       <c r="C457" t="n">
-        <v>37.57239743066493</v>
+        <v>37.57239358328728</v>
       </c>
       <c r="D457" t="n">
-        <v>35.96698839437353</v>
+        <v>35.96698471138824</v>
       </c>
       <c r="E457" t="n">
-        <v>36.05402584393507</v>
+        <v>36.05402215203722</v>
       </c>
       <c r="F457" t="n">
         <v>4057043</v>
@@ -9592,16 +9592,16 @@
         <v>44820</v>
       </c>
       <c r="B459" t="n">
-        <v>36.7987060546875</v>
+        <v>36.79870223999023</v>
       </c>
       <c r="C459" t="n">
-        <v>36.7987060546875</v>
+        <v>36.79870223999023</v>
       </c>
       <c r="D459" t="n">
-        <v>35.7832329328566</v>
+        <v>35.78322922342723</v>
       </c>
       <c r="E459" t="n">
-        <v>36.14106646140942</v>
+        <v>36.14106271488564</v>
       </c>
       <c r="F459" t="n">
         <v>2974596</v>
@@ -9612,16 +9612,16 @@
         <v>44823</v>
       </c>
       <c r="B460" t="n">
-        <v>36.84706115722656</v>
+        <v>36.8470573425293</v>
       </c>
       <c r="C460" t="n">
-        <v>37.39831831798563</v>
+        <v>37.3983144462179</v>
       </c>
       <c r="D460" t="n">
-        <v>35.79290555412169</v>
+        <v>35.7929018485589</v>
       </c>
       <c r="E460" t="n">
-        <v>35.79290555412169</v>
+        <v>35.7929018485589</v>
       </c>
       <c r="F460" t="n">
         <v>3461677</v>
@@ -9652,16 +9652,16 @@
         <v>44825</v>
       </c>
       <c r="B462" t="n">
-        <v>38.03661346435547</v>
+        <v>38.0366096496582</v>
       </c>
       <c r="C462" t="n">
-        <v>38.79096301231463</v>
+        <v>38.79095912196355</v>
       </c>
       <c r="D462" t="n">
-        <v>37.62075246461414</v>
+        <v>37.62074869162363</v>
       </c>
       <c r="E462" t="n">
-        <v>37.93989977373904</v>
+        <v>37.9398959687412</v>
       </c>
       <c r="F462" t="n">
         <v>4689181</v>
@@ -9732,16 +9732,16 @@
         <v>44831</v>
       </c>
       <c r="B466" t="n">
-        <v>33.61689376831055</v>
+        <v>33.61689758300781</v>
       </c>
       <c r="C466" t="n">
-        <v>34.44861190035511</v>
+        <v>34.44861580943209</v>
       </c>
       <c r="D466" t="n">
-        <v>33.3267602334253</v>
+        <v>33.32676401519949</v>
       </c>
       <c r="E466" t="n">
-        <v>34.44861190035511</v>
+        <v>34.44861580943209</v>
       </c>
       <c r="F466" t="n">
         <v>5480701</v>
@@ -9752,16 +9752,16 @@
         <v>44832</v>
       </c>
       <c r="B467" t="n">
-        <v>34.57433700561523</v>
+        <v>34.5743408203125</v>
       </c>
       <c r="C467" t="n">
-        <v>34.99987045518622</v>
+        <v>34.99987431683395</v>
       </c>
       <c r="D467" t="n">
-        <v>33.19136547412988</v>
+        <v>33.19136913623947</v>
       </c>
       <c r="E467" t="n">
-        <v>33.66525014270204</v>
+        <v>33.66525385709685</v>
       </c>
       <c r="F467" t="n">
         <v>4399676</v>
@@ -9772,16 +9772,16 @@
         <v>44833</v>
       </c>
       <c r="B468" t="n">
-        <v>33.90703201293945</v>
+        <v>33.90702819824219</v>
       </c>
       <c r="C468" t="n">
-        <v>34.69039528924284</v>
+        <v>34.69039138641359</v>
       </c>
       <c r="D468" t="n">
-        <v>33.09465875193581</v>
+        <v>33.09465502863428</v>
       </c>
       <c r="E468" t="n">
-        <v>34.61302658569848</v>
+        <v>34.61302269157358</v>
       </c>
       <c r="F468" t="n">
         <v>4499631</v>
@@ -9812,16 +9812,16 @@
         <v>44837</v>
       </c>
       <c r="B470" t="n">
-        <v>36.7987060546875</v>
+        <v>36.79870223999023</v>
       </c>
       <c r="C470" t="n">
-        <v>36.91476098234264</v>
+        <v>36.91475715561467</v>
       </c>
       <c r="D470" t="n">
-        <v>35.52211309320833</v>
+        <v>35.52210941084767</v>
       </c>
       <c r="E470" t="n">
-        <v>36.26679013465196</v>
+        <v>36.26678637509517</v>
       </c>
       <c r="F470" t="n">
         <v>4419789</v>
@@ -9852,16 +9852,16 @@
         <v>44839</v>
       </c>
       <c r="B472" t="n">
-        <v>41.63427734375</v>
+        <v>41.63427352905273</v>
       </c>
       <c r="C472" t="n">
-        <v>42.48533680478608</v>
+        <v>42.48533291211138</v>
       </c>
       <c r="D472" t="n">
-        <v>40.55110803146717</v>
+        <v>40.55110431601417</v>
       </c>
       <c r="E472" t="n">
-        <v>40.61880798727272</v>
+        <v>40.61880426561678</v>
       </c>
       <c r="F472" t="n">
         <v>6927519</v>
@@ -9892,16 +9892,16 @@
         <v>44841</v>
       </c>
       <c r="B474" t="n">
-        <v>41.47953796386719</v>
+        <v>41.47954177856445</v>
       </c>
       <c r="C474" t="n">
-        <v>42.45632104937901</v>
+        <v>42.45632495390688</v>
       </c>
       <c r="D474" t="n">
-        <v>41.22808688619578</v>
+        <v>41.22809067776815</v>
       </c>
       <c r="E474" t="n">
-        <v>41.59558913638236</v>
+        <v>41.59559296175236</v>
       </c>
       <c r="F474" t="n">
         <v>3503020</v>
@@ -10072,16 +10072,16 @@
         <v>44855</v>
       </c>
       <c r="B483" t="n">
-        <v>44.22614288330078</v>
+        <v>44.22613906860352</v>
       </c>
       <c r="C483" t="n">
-        <v>44.68068635480393</v>
+        <v>44.68068250090031</v>
       </c>
       <c r="D483" t="n">
-        <v>42.41764149048589</v>
+        <v>42.41763783177974</v>
       </c>
       <c r="E483" t="n">
-        <v>42.9688949036628</v>
+        <v>42.96889119740864</v>
       </c>
       <c r="F483" t="n">
         <v>5360835</v>
@@ -10112,16 +10112,16 @@
         <v>44859</v>
       </c>
       <c r="B485" t="n">
-        <v>42.69810104370117</v>
+        <v>42.69809722900391</v>
       </c>
       <c r="C485" t="n">
-        <v>44.71937098158734</v>
+        <v>44.7193669863075</v>
       </c>
       <c r="D485" t="n">
-        <v>42.52402240539543</v>
+        <v>42.52401860625056</v>
       </c>
       <c r="E485" t="n">
-        <v>43.43310931590769</v>
+        <v>43.43310543554394</v>
       </c>
       <c r="F485" t="n">
         <v>3364870</v>
@@ -10232,16 +10232,16 @@
         <v>44868</v>
       </c>
       <c r="B491" t="n">
-        <v>46.30543899536133</v>
+        <v>46.30543518066406</v>
       </c>
       <c r="C491" t="n">
-        <v>46.43116266535413</v>
+        <v>46.4311588402996</v>
       </c>
       <c r="D491" t="n">
-        <v>44.51627889399545</v>
+        <v>44.51627522669133</v>
       </c>
       <c r="E491" t="n">
-        <v>44.98049109746535</v>
+        <v>44.98048739191887</v>
       </c>
       <c r="F491" t="n">
         <v>3262984</v>
@@ -10312,16 +10312,16 @@
         <v>44874</v>
       </c>
       <c r="B495" t="n">
-        <v>44.69035720825195</v>
+        <v>44.69035339355469</v>
       </c>
       <c r="C495" t="n">
-        <v>46.49886228228617</v>
+        <v>46.49885831321781</v>
       </c>
       <c r="D495" t="n">
-        <v>44.23581375342662</v>
+        <v>44.23580997752845</v>
       </c>
       <c r="E495" t="n">
-        <v>45.35766552501359</v>
+        <v>45.35766165335595</v>
       </c>
       <c r="F495" t="n">
         <v>4884014</v>
@@ -10332,16 +10332,16 @@
         <v>44875</v>
       </c>
       <c r="B496" t="n">
-        <v>42.05980682373047</v>
+        <v>42.0598030090332</v>
       </c>
       <c r="C496" t="n">
-        <v>44.68068514703247</v>
+        <v>44.68068109462947</v>
       </c>
       <c r="D496" t="n">
-        <v>41.6439458411077</v>
+        <v>41.64394206412777</v>
       </c>
       <c r="E496" t="n">
-        <v>43.65554705124352</v>
+        <v>43.65554309181744</v>
       </c>
       <c r="F496" t="n">
         <v>5453172</v>
@@ -10472,16 +10472,16 @@
         <v>44887</v>
       </c>
       <c r="B503" t="n">
-        <v>35.72520446777344</v>
+        <v>35.7252082824707</v>
       </c>
       <c r="C503" t="n">
-        <v>38.01726275125628</v>
+        <v>38.01726681069696</v>
       </c>
       <c r="D503" t="n">
-        <v>35.41572595102293</v>
+        <v>35.41572973267442</v>
       </c>
       <c r="E503" t="n">
-        <v>37.37896822915095</v>
+        <v>37.37897222043525</v>
       </c>
       <c r="F503" t="n">
         <v>4879239</v>
@@ -10492,16 +10492,16 @@
         <v>44888</v>
       </c>
       <c r="B504" t="n">
-        <v>34.29388046264648</v>
+        <v>34.29387664794922</v>
       </c>
       <c r="C504" t="n">
-        <v>35.59948346985989</v>
+        <v>35.59947950993321</v>
       </c>
       <c r="D504" t="n">
-        <v>33.84900571743197</v>
+        <v>33.84900195222058</v>
       </c>
       <c r="E504" t="n">
-        <v>35.37704984482862</v>
+        <v>35.37704590964446</v>
       </c>
       <c r="F504" t="n">
         <v>5644348</v>
@@ -10532,16 +10532,16 @@
         <v>44890</v>
       </c>
       <c r="B506" t="n">
-        <v>34.23584747314453</v>
+        <v>34.2358512878418</v>
       </c>
       <c r="C506" t="n">
-        <v>36.49889581830917</v>
+        <v>36.49889988516448</v>
       </c>
       <c r="D506" t="n">
-        <v>34.11012381427162</v>
+        <v>34.11012761496025</v>
       </c>
       <c r="E506" t="n">
-        <v>36.17007605925269</v>
+        <v>36.17008008946956</v>
       </c>
       <c r="F506" t="n">
         <v>4398253</v>
@@ -10552,16 +10552,16 @@
         <v>44893</v>
       </c>
       <c r="B507" t="n">
-        <v>33.64590835571289</v>
+        <v>33.64591217041016</v>
       </c>
       <c r="C507" t="n">
-        <v>34.11012427192836</v>
+        <v>34.11012813925738</v>
       </c>
       <c r="D507" t="n">
-        <v>32.92057262619048</v>
+        <v>32.92057635865081</v>
       </c>
       <c r="E507" t="n">
-        <v>33.36544355803103</v>
+        <v>33.36544734092983</v>
       </c>
       <c r="F507" t="n">
         <v>4077054</v>
@@ -10652,16 +10652,16 @@
         <v>44900</v>
       </c>
       <c r="B512" t="n">
-        <v>34.04242324829102</v>
+        <v>34.04242706298828</v>
       </c>
       <c r="C512" t="n">
-        <v>35.87994187083461</v>
+        <v>35.879945891439</v>
       </c>
       <c r="D512" t="n">
-        <v>33.77163095133564</v>
+        <v>33.77163473568869</v>
       </c>
       <c r="E512" t="n">
-        <v>35.57046335392476</v>
+        <v>35.57046733984986</v>
       </c>
       <c r="F512" t="n">
         <v>5158181</v>
@@ -10732,16 +10732,16 @@
         <v>44904</v>
       </c>
       <c r="B516" t="n">
-        <v>31.69234085083008</v>
+        <v>31.69233894348145</v>
       </c>
       <c r="C516" t="n">
-        <v>32.74649642178647</v>
+        <v>32.74649445099531</v>
       </c>
       <c r="D516" t="n">
-        <v>31.4892447329005</v>
+        <v>31.48924283777486</v>
       </c>
       <c r="E516" t="n">
-        <v>32.22425300897184</v>
+        <v>32.22425106961099</v>
       </c>
       <c r="F516" t="n">
         <v>2885712</v>
@@ -10752,16 +10752,16 @@
         <v>44907</v>
       </c>
       <c r="B517" t="n">
-        <v>32.23392486572266</v>
+        <v>32.23392105102539</v>
       </c>
       <c r="C517" t="n">
-        <v>32.41767599422015</v>
+        <v>32.41767215777701</v>
       </c>
       <c r="D517" t="n">
-        <v>31.06371439332975</v>
+        <v>31.06371071712008</v>
       </c>
       <c r="E517" t="n">
-        <v>31.59562654097396</v>
+        <v>31.59562280181559</v>
       </c>
       <c r="F517" t="n">
         <v>3445728</v>
@@ -10772,16 +10772,16 @@
         <v>44908</v>
       </c>
       <c r="B518" t="n">
-        <v>32.5240592956543</v>
+        <v>32.52405548095703</v>
       </c>
       <c r="C518" t="n">
-        <v>33.41380497900949</v>
+        <v>33.41380105995531</v>
       </c>
       <c r="D518" t="n">
-        <v>31.98247464077933</v>
+        <v>31.9824708896037</v>
       </c>
       <c r="E518" t="n">
-        <v>32.39833187733107</v>
+        <v>32.39832807738018</v>
       </c>
       <c r="F518" t="n">
         <v>3369136</v>
@@ -10872,16 +10872,16 @@
         <v>44915</v>
       </c>
       <c r="B523" t="n">
-        <v>31.63431167602539</v>
+        <v>31.63431358337402</v>
       </c>
       <c r="C523" t="n">
-        <v>31.83740403538475</v>
+        <v>31.83740595497857</v>
       </c>
       <c r="D523" t="n">
-        <v>30.62851300266902</v>
+        <v>30.62851484937437</v>
       </c>
       <c r="E523" t="n">
-        <v>30.76390915810044</v>
+        <v>30.76391101296931</v>
       </c>
       <c r="F523" t="n">
         <v>3472546</v>
@@ -10892,16 +10892,16 @@
         <v>44916</v>
       </c>
       <c r="B524" t="n">
-        <v>32.19523620605469</v>
+        <v>32.19524002075195</v>
       </c>
       <c r="C524" t="n">
-        <v>32.50471472608491</v>
+        <v>32.50471857745117</v>
       </c>
       <c r="D524" t="n">
-        <v>31.22812192077017</v>
+        <v>31.22812562087756</v>
       </c>
       <c r="E524" t="n">
-        <v>32.34997359228213</v>
+        <v>32.34997742531367</v>
       </c>
       <c r="F524" t="n">
         <v>3938295</v>
@@ -10912,16 +10912,16 @@
         <v>44917</v>
       </c>
       <c r="B525" t="n">
-        <v>32.01148986816406</v>
+        <v>32.0114860534668</v>
       </c>
       <c r="C525" t="n">
-        <v>32.78518066232546</v>
+        <v>32.78517675543017</v>
       </c>
       <c r="D525" t="n">
-        <v>31.53760514678948</v>
+        <v>31.5376013885634</v>
       </c>
       <c r="E525" t="n">
-        <v>32.41767837830338</v>
+        <v>32.41767451520204</v>
       </c>
       <c r="F525" t="n">
         <v>3822391</v>
@@ -10932,16 +10932,16 @@
         <v>44918</v>
       </c>
       <c r="B526" t="n">
-        <v>34.68072128295898</v>
+        <v>34.68072509765625</v>
       </c>
       <c r="C526" t="n">
-        <v>34.88381363050969</v>
+        <v>34.88381746754605</v>
       </c>
       <c r="D526" t="n">
-        <v>32.68846528926745</v>
+        <v>32.68846888482701</v>
       </c>
       <c r="E526" t="n">
-        <v>33.17202242375276</v>
+        <v>33.17202607250107</v>
       </c>
       <c r="F526" t="n">
         <v>6955860</v>
@@ -11012,16 +11012,16 @@
         <v>44924</v>
       </c>
       <c r="B530" t="n">
-        <v>36.50856781005859</v>
+        <v>36.50856399536133</v>
       </c>
       <c r="C530" t="n">
-        <v>37.23390359436439</v>
+        <v>37.23389970387844</v>
       </c>
       <c r="D530" t="n">
-        <v>35.61882587917678</v>
+        <v>35.61882215744662</v>
       </c>
       <c r="E530" t="n">
-        <v>35.87994571220566</v>
+        <v>35.87994196319169</v>
       </c>
       <c r="F530" t="n">
         <v>4887264</v>
@@ -11032,16 +11032,16 @@
         <v>44928</v>
       </c>
       <c r="B531" t="n">
-        <v>35.2126350402832</v>
+        <v>35.21263885498047</v>
       </c>
       <c r="C531" t="n">
-        <v>36.68264774905137</v>
+        <v>36.68265172299981</v>
       </c>
       <c r="D531" t="n">
-        <v>34.78710534150101</v>
+        <v>34.78710911009928</v>
       </c>
       <c r="E531" t="n">
-        <v>36.01533947163607</v>
+        <v>36.01534337329287</v>
       </c>
       <c r="F531" t="n">
         <v>2924313</v>
@@ -11152,16 +11152,16 @@
         <v>44936</v>
       </c>
       <c r="B537" t="n">
-        <v>37.79483032226562</v>
+        <v>37.79483413696289</v>
       </c>
       <c r="C537" t="n">
-        <v>38.07529137196207</v>
+        <v>38.07529521496675</v>
       </c>
       <c r="D537" t="n">
-        <v>36.49889625466188</v>
+        <v>36.49889993855829</v>
       </c>
       <c r="E537" t="n">
-        <v>37.0985045751726</v>
+        <v>37.09850831958851</v>
       </c>
       <c r="F537" t="n">
         <v>3183751</v>
@@ -11192,16 +11192,16 @@
         <v>44938</v>
       </c>
       <c r="B539" t="n">
-        <v>43.42343902587891</v>
+        <v>43.42343521118164</v>
       </c>
       <c r="C539" t="n">
-        <v>44.7290457434945</v>
+        <v>44.72904181410123</v>
       </c>
       <c r="D539" t="n">
-        <v>43.19133291383822</v>
+        <v>43.19132911953119</v>
       </c>
       <c r="E539" t="n">
-        <v>43.40409778676949</v>
+        <v>43.40409397377132</v>
       </c>
       <c r="F539" t="n">
         <v>7341055</v>
@@ -11212,16 +11212,16 @@
         <v>44939</v>
       </c>
       <c r="B540" t="n">
-        <v>42.75612640380859</v>
+        <v>42.75613021850586</v>
       </c>
       <c r="C540" t="n">
-        <v>43.50080338468374</v>
+        <v>43.50080726582102</v>
       </c>
       <c r="D540" t="n">
-        <v>42.35961043000531</v>
+        <v>42.35961420932546</v>
       </c>
       <c r="E540" t="n">
-        <v>43.42343468839838</v>
+        <v>43.42343856263282</v>
       </c>
       <c r="F540" t="n">
         <v>4249336</v>
@@ -11272,16 +11272,16 @@
         <v>44944</v>
       </c>
       <c r="B543" t="n">
-        <v>44.53561782836914</v>
+        <v>44.53562164306641</v>
       </c>
       <c r="C543" t="n">
-        <v>45.241612337541</v>
+        <v>45.24161621271021</v>
       </c>
       <c r="D543" t="n">
-        <v>43.220342491427</v>
+        <v>43.22034619346439</v>
       </c>
       <c r="E543" t="n">
-        <v>43.42343485149192</v>
+        <v>43.42343857092518</v>
       </c>
       <c r="F543" t="n">
         <v>6730959</v>
@@ -11332,16 +11332,16 @@
         <v>44949</v>
       </c>
       <c r="B546" t="n">
-        <v>46.45050430297852</v>
+        <v>46.45050811767578</v>
       </c>
       <c r="C546" t="n">
-        <v>48.53947031074529</v>
+        <v>48.53947429699662</v>
       </c>
       <c r="D546" t="n">
-        <v>45.88957845353607</v>
+        <v>45.88958222216792</v>
       </c>
       <c r="E546" t="n">
-        <v>47.67873842593739</v>
+        <v>47.67874234150205</v>
       </c>
       <c r="F546" t="n">
         <v>5971946</v>
@@ -11392,16 +11392,16 @@
         <v>44952</v>
       </c>
       <c r="B549" t="n">
-        <v>45.26095199584961</v>
+        <v>45.26095581054688</v>
       </c>
       <c r="C549" t="n">
-        <v>46.77931963988798</v>
+        <v>46.77932358255676</v>
       </c>
       <c r="D549" t="n">
-        <v>45.24161075927422</v>
+        <v>45.24161457234137</v>
       </c>
       <c r="E549" t="n">
-        <v>45.92826025966649</v>
+        <v>45.92826413060603</v>
       </c>
       <c r="F549" t="n">
         <v>3327082</v>
@@ -11412,16 +11412,16 @@
         <v>44953</v>
       </c>
       <c r="B550" t="n">
-        <v>44.50660705566406</v>
+        <v>44.5066032409668</v>
       </c>
       <c r="C550" t="n">
-        <v>46.34412590104548</v>
+        <v>46.34412192885299</v>
       </c>
       <c r="D550" t="n">
-        <v>44.16811476963287</v>
+        <v>44.16811098394805</v>
       </c>
       <c r="E550" t="n">
-        <v>46.20872973614816</v>
+        <v>46.20872577556058</v>
       </c>
       <c r="F550" t="n">
         <v>4035914</v>
@@ -11432,16 +11432,16 @@
         <v>44956</v>
       </c>
       <c r="B551" t="n">
-        <v>43.79093933105469</v>
+        <v>43.79094314575195</v>
       </c>
       <c r="C551" t="n">
-        <v>44.43890261092821</v>
+        <v>44.43890648207057</v>
       </c>
       <c r="D551" t="n">
-        <v>43.13329981152729</v>
+        <v>43.13330356893655</v>
       </c>
       <c r="E551" t="n">
-        <v>44.3131789517849</v>
+        <v>44.31318281197527</v>
       </c>
       <c r="F551" t="n">
         <v>3870439</v>
@@ -11572,16 +11572,16 @@
         <v>44965</v>
       </c>
       <c r="B558" t="n">
-        <v>43.12363052368164</v>
+        <v>43.12362670898438</v>
       </c>
       <c r="C558" t="n">
-        <v>43.13330301647882</v>
+        <v>43.13329920092593</v>
       </c>
       <c r="D558" t="n">
-        <v>42.08881994983436</v>
+        <v>42.08881622667597</v>
       </c>
       <c r="E558" t="n">
-        <v>42.57237713333137</v>
+        <v>42.57237336739773</v>
       </c>
       <c r="F558" t="n">
         <v>2757212</v>
@@ -11672,16 +11672,16 @@
         <v>44972</v>
       </c>
       <c r="B563" t="n">
-        <v>40.0482063293457</v>
+        <v>40.04821014404297</v>
       </c>
       <c r="C563" t="n">
-        <v>40.52209099098364</v>
+        <v>40.52209485081966</v>
       </c>
       <c r="D563" t="n">
-        <v>38.90700964744255</v>
+        <v>38.90701335343782</v>
       </c>
       <c r="E563" t="n">
-        <v>38.92635463185054</v>
+        <v>38.92635833968847</v>
       </c>
       <c r="F563" t="n">
         <v>3495706</v>
@@ -11752,16 +11752,16 @@
         <v>44980</v>
       </c>
       <c r="B567" t="n">
-        <v>38.00759506225586</v>
+        <v>38.00759887695312</v>
       </c>
       <c r="C567" t="n">
-        <v>39.07141929530241</v>
+        <v>39.07142321677222</v>
       </c>
       <c r="D567" t="n">
-        <v>37.7368027579212</v>
+        <v>37.73680654543994</v>
       </c>
       <c r="E567" t="n">
-        <v>37.95924009667655</v>
+        <v>37.95924390652058</v>
       </c>
       <c r="F567" t="n">
         <v>3548732</v>
@@ -11812,16 +11812,16 @@
         <v>44985</v>
       </c>
       <c r="B570" t="n">
-        <v>35.2126350402832</v>
+        <v>35.21263885498047</v>
       </c>
       <c r="C570" t="n">
-        <v>38.49115271645117</v>
+        <v>38.49115688632073</v>
       </c>
       <c r="D570" t="n">
-        <v>35.2126350402832</v>
+        <v>35.21263885498047</v>
       </c>
       <c r="E570" t="n">
-        <v>37.13719117707558</v>
+        <v>37.13719520026616</v>
       </c>
       <c r="F570" t="n">
         <v>11036876</v>
@@ -11832,16 +11832,16 @@
         <v>44986</v>
       </c>
       <c r="B571" t="n">
-        <v>31.52792930603027</v>
+        <v>31.52793121337891</v>
       </c>
       <c r="C571" t="n">
-        <v>35.21263549119504</v>
+        <v>35.21263762145776</v>
       </c>
       <c r="D571" t="n">
-        <v>29.89350481936535</v>
+        <v>29.89350662783602</v>
       </c>
       <c r="E571" t="n">
-        <v>35.10625306513723</v>
+        <v>35.10625518896411</v>
       </c>
       <c r="F571" t="n">
         <v>24633899</v>
@@ -11872,16 +11872,16 @@
         <v>44988</v>
       </c>
       <c r="B573" t="n">
-        <v>31.74069404602051</v>
+        <v>31.74069595336914</v>
       </c>
       <c r="C573" t="n">
-        <v>31.93411766023568</v>
+        <v>31.93411957920744</v>
       </c>
       <c r="D573" t="n">
-        <v>30.40607560502645</v>
+        <v>30.40607743217574</v>
       </c>
       <c r="E573" t="n">
-        <v>30.47377368262298</v>
+        <v>30.47377551384036</v>
       </c>
       <c r="F573" t="n">
         <v>7573675</v>
@@ -11892,16 +11892,16 @@
         <v>44991</v>
       </c>
       <c r="B574" t="n">
-        <v>31.86641883850098</v>
+        <v>31.86642074584961</v>
       </c>
       <c r="C574" t="n">
-        <v>32.34997601739302</v>
+        <v>32.34997795368473</v>
       </c>
       <c r="D574" t="n">
-        <v>30.94766132287878</v>
+        <v>30.94766317523564</v>
       </c>
       <c r="E574" t="n">
-        <v>31.74069517121325</v>
+        <v>31.74069707103675</v>
       </c>
       <c r="F574" t="n">
         <v>5963007</v>
@@ -11992,16 +11992,16 @@
         <v>44998</v>
       </c>
       <c r="B579" t="n">
-        <v>26.4505786895752</v>
+        <v>26.45058059692383</v>
       </c>
       <c r="C579" t="n">
-        <v>27.32098119587531</v>
+        <v>27.32098316598858</v>
       </c>
       <c r="D579" t="n">
-        <v>25.76392542920967</v>
+        <v>25.76392728704381</v>
       </c>
       <c r="E579" t="n">
-        <v>26.59564546166059</v>
+        <v>26.59564737946998</v>
       </c>
       <c r="F579" t="n">
         <v>13860726</v>
@@ -12032,16 +12032,16 @@
         <v>45000</v>
       </c>
       <c r="B581" t="n">
-        <v>26.28617095947266</v>
+        <v>26.28616905212402</v>
       </c>
       <c r="C581" t="n">
-        <v>26.82775374453002</v>
+        <v>26.82775179788365</v>
       </c>
       <c r="D581" t="n">
-        <v>25.62853324821252</v>
+        <v>25.62853138858268</v>
       </c>
       <c r="E581" t="n">
-        <v>26.58597514665809</v>
+        <v>26.58597321755539</v>
       </c>
       <c r="F581" t="n">
         <v>12174787</v>
@@ -12072,16 +12072,16 @@
         <v>45002</v>
       </c>
       <c r="B583" t="n">
-        <v>30.70588111877441</v>
+        <v>30.70588302612305</v>
       </c>
       <c r="C583" t="n">
-        <v>30.8896322374788</v>
+        <v>30.88963415624145</v>
       </c>
       <c r="D583" t="n">
-        <v>27.73684012155175</v>
+        <v>27.73684184447329</v>
       </c>
       <c r="E583" t="n">
-        <v>30.45443004984579</v>
+        <v>30.45443194157511</v>
       </c>
       <c r="F583" t="n">
         <v>23193684</v>
@@ -12092,16 +12092,16 @@
         <v>45005</v>
       </c>
       <c r="B584" t="n">
-        <v>29.79679679870605</v>
+        <v>29.79679489135742</v>
       </c>
       <c r="C584" t="n">
-        <v>31.20878403151084</v>
+        <v>31.20878203377826</v>
       </c>
       <c r="D584" t="n">
-        <v>29.32291022343201</v>
+        <v>29.32290834641774</v>
       </c>
       <c r="E584" t="n">
-        <v>30.70588372476053</v>
+        <v>30.70588175921954</v>
       </c>
       <c r="F584" t="n">
         <v>7729094</v>
@@ -12252,16 +12252,16 @@
         <v>45015</v>
       </c>
       <c r="B592" t="n">
-        <v>29.38093566894531</v>
+        <v>29.38093376159668</v>
       </c>
       <c r="C592" t="n">
-        <v>30.51245994826028</v>
+        <v>30.51245796745546</v>
       </c>
       <c r="D592" t="n">
-        <v>29.27455323657771</v>
+        <v>29.2745513361352</v>
       </c>
       <c r="E592" t="n">
-        <v>29.95153405508782</v>
+        <v>29.95153211069714</v>
       </c>
       <c r="F592" t="n">
         <v>5560645</v>
@@ -12312,16 +12312,16 @@
         <v>45020</v>
       </c>
       <c r="B595" t="n">
-        <v>27.92059326171875</v>
+        <v>27.92059135437012</v>
       </c>
       <c r="C595" t="n">
-        <v>29.70975523383049</v>
+        <v>29.70975320425825</v>
       </c>
       <c r="D595" t="n">
-        <v>27.91092264260987</v>
+        <v>27.91092073592187</v>
       </c>
       <c r="E595" t="n">
-        <v>29.57435907115471</v>
+        <v>29.57435705083184</v>
       </c>
       <c r="F595" t="n">
         <v>7552242</v>
@@ -12332,16 +12332,16 @@
         <v>45021</v>
       </c>
       <c r="B596" t="n">
-        <v>26.76972579956055</v>
+        <v>26.76972770690918</v>
       </c>
       <c r="C596" t="n">
-        <v>27.85289314814766</v>
+        <v>27.8528951326722</v>
       </c>
       <c r="D596" t="n">
-        <v>26.23781180677641</v>
+        <v>26.23781367622606</v>
       </c>
       <c r="E596" t="n">
-        <v>27.65947141114338</v>
+        <v>27.65947338188658</v>
       </c>
       <c r="F596" t="n">
         <v>12382825</v>
@@ -12372,16 +12372,16 @@
         <v>45026</v>
       </c>
       <c r="B598" t="n">
-        <v>29.65172576904297</v>
+        <v>29.6517276763916</v>
       </c>
       <c r="C598" t="n">
-        <v>29.8354768886412</v>
+        <v>29.83547880780963</v>
       </c>
       <c r="D598" t="n">
-        <v>28.19138368313743</v>
+        <v>28.19138549654949</v>
       </c>
       <c r="E598" t="n">
-        <v>28.33645045512486</v>
+        <v>28.33645227786835</v>
       </c>
       <c r="F598" t="n">
         <v>8774363</v>
@@ -12552,16 +12552,16 @@
         <v>45040</v>
       </c>
       <c r="B607" t="n">
-        <v>26.96700286865234</v>
+        <v>26.96700477600098</v>
       </c>
       <c r="C607" t="n">
-        <v>27.07506608384296</v>
+        <v>27.07506799883479</v>
       </c>
       <c r="D607" t="n">
-        <v>26.23019953206389</v>
+        <v>26.23020138729918</v>
       </c>
       <c r="E607" t="n">
-        <v>26.86876204901633</v>
+        <v>26.86876394941649</v>
       </c>
       <c r="F607" t="n">
         <v>6680100</v>
@@ -12572,16 +12572,16 @@
         <v>45041</v>
       </c>
       <c r="B608" t="n">
-        <v>27.21260452270508</v>
+        <v>27.21260261535645</v>
       </c>
       <c r="C608" t="n">
-        <v>27.45820563979163</v>
+        <v>27.45820371522866</v>
       </c>
       <c r="D608" t="n">
-        <v>26.42667982375542</v>
+        <v>26.42667797149275</v>
       </c>
       <c r="E608" t="n">
-        <v>26.79999457104816</v>
+        <v>26.79999269261962</v>
       </c>
       <c r="F608" t="n">
         <v>5323000</v>
@@ -12612,16 +12612,16 @@
         <v>45043</v>
       </c>
       <c r="B610" t="n">
-        <v>29.90439224243164</v>
+        <v>29.90439414978027</v>
       </c>
       <c r="C610" t="n">
-        <v>30.267880842768</v>
+        <v>30.26788277330051</v>
       </c>
       <c r="D610" t="n">
-        <v>26.73122441728851</v>
+        <v>26.73122612224756</v>
       </c>
       <c r="E610" t="n">
-        <v>26.73122441728851</v>
+        <v>26.73122612224756</v>
       </c>
       <c r="F610" t="n">
         <v>20933600</v>
@@ -12672,16 +12672,16 @@
         <v>45049</v>
       </c>
       <c r="B613" t="n">
-        <v>29.14793968200684</v>
+        <v>29.14794158935547</v>
       </c>
       <c r="C613" t="n">
-        <v>29.61949336143113</v>
+        <v>29.61949529963673</v>
       </c>
       <c r="D613" t="n">
-        <v>28.33254407533193</v>
+        <v>28.33254592932366</v>
       </c>
       <c r="E613" t="n">
-        <v>29.26582903875679</v>
+        <v>29.26583095381972</v>
       </c>
       <c r="F613" t="n">
         <v>9250000</v>
@@ -12692,16 +12692,16 @@
         <v>45050</v>
       </c>
       <c r="B614" t="n">
-        <v>29.2756519317627</v>
+        <v>29.27565383911133</v>
       </c>
       <c r="C614" t="n">
-        <v>29.95351152857367</v>
+        <v>29.95351348008578</v>
       </c>
       <c r="D614" t="n">
-        <v>29.17741298555374</v>
+        <v>29.17741488650197</v>
       </c>
       <c r="E614" t="n">
-        <v>29.47213357175619</v>
+        <v>29.47213549190587</v>
       </c>
       <c r="F614" t="n">
         <v>6670900</v>
@@ -12792,16 +12792,16 @@
         <v>45057</v>
       </c>
       <c r="B619" t="n">
-        <v>31.66289520263672</v>
+        <v>31.66289710998535</v>
       </c>
       <c r="C619" t="n">
-        <v>31.81025737023202</v>
+        <v>31.81025928645763</v>
       </c>
       <c r="D619" t="n">
-        <v>31.10292496189554</v>
+        <v>31.10292683551199</v>
       </c>
       <c r="E619" t="n">
-        <v>31.71201467597662</v>
+        <v>31.71201658628417</v>
       </c>
       <c r="F619" t="n">
         <v>4858000</v>
@@ -12812,16 +12812,16 @@
         <v>45058</v>
       </c>
       <c r="B620" t="n">
-        <v>32.49794006347656</v>
+        <v>32.49794387817383</v>
       </c>
       <c r="C620" t="n">
-        <v>32.64529847816273</v>
+        <v>32.64530231015733</v>
       </c>
       <c r="D620" t="n">
-        <v>31.46641242279611</v>
+        <v>31.46641611640984</v>
       </c>
       <c r="E620" t="n">
-        <v>31.554828970638</v>
+        <v>31.55483267463029</v>
       </c>
       <c r="F620" t="n">
         <v>5317000</v>
@@ -12852,16 +12852,16 @@
         <v>45062</v>
       </c>
       <c r="B622" t="n">
-        <v>29.90439224243164</v>
+        <v>29.90439414978027</v>
       </c>
       <c r="C622" t="n">
-        <v>32.08532946581322</v>
+        <v>32.08533151226543</v>
       </c>
       <c r="D622" t="n">
-        <v>29.70791060120974</v>
+        <v>29.70791249602647</v>
       </c>
       <c r="E622" t="n">
-        <v>31.86919928571158</v>
+        <v>31.86920131837866</v>
       </c>
       <c r="F622" t="n">
         <v>13269700</v>
@@ -12912,16 +12912,16 @@
         <v>45065</v>
       </c>
       <c r="B625" t="n">
-        <v>32.49794006347656</v>
+        <v>32.49794387817383</v>
       </c>
       <c r="C625" t="n">
-        <v>34.87535696477425</v>
+        <v>34.87536105853923</v>
       </c>
       <c r="D625" t="n">
-        <v>31.04398009551434</v>
+        <v>31.0439837395418</v>
       </c>
       <c r="E625" t="n">
-        <v>31.8691980857257</v>
+        <v>31.86920182661951</v>
       </c>
       <c r="F625" t="n">
         <v>19443700</v>
@@ -12972,16 +12972,16 @@
         <v>45070</v>
       </c>
       <c r="B628" t="n">
-        <v>31.48606300354004</v>
+        <v>31.48606109619141</v>
       </c>
       <c r="C628" t="n">
-        <v>31.86920015318507</v>
+        <v>31.86919822262693</v>
       </c>
       <c r="D628" t="n">
-        <v>30.464363313224</v>
+        <v>30.46436146776744</v>
       </c>
       <c r="E628" t="n">
-        <v>31.04398210943912</v>
+        <v>31.04398022887067</v>
       </c>
       <c r="F628" t="n">
         <v>7685200</v>
@@ -13212,16 +13212,16 @@
         <v>45089</v>
       </c>
       <c r="B640" t="n">
-        <v>31.26010894775391</v>
+        <v>31.26011085510254</v>
       </c>
       <c r="C640" t="n">
-        <v>31.86919865058509</v>
+        <v>31.86920059509758</v>
       </c>
       <c r="D640" t="n">
-        <v>30.47418614610471</v>
+        <v>30.47418800549994</v>
       </c>
       <c r="E640" t="n">
-        <v>31.61377514538992</v>
+        <v>31.61377707431765</v>
       </c>
       <c r="F640" t="n">
         <v>7223600</v>
@@ -13252,16 +13252,16 @@
         <v>45091</v>
       </c>
       <c r="B642" t="n">
-        <v>31.1422233581543</v>
+        <v>31.14222145080566</v>
       </c>
       <c r="C642" t="n">
-        <v>31.71201601865814</v>
+        <v>31.71201407641177</v>
       </c>
       <c r="D642" t="n">
-        <v>30.57242882386257</v>
+        <v>30.5724269514118</v>
       </c>
       <c r="E642" t="n">
-        <v>31.33870313362062</v>
+        <v>31.33870121423831</v>
       </c>
       <c r="F642" t="n">
         <v>8288400</v>
@@ -13292,16 +13292,16 @@
         <v>45093</v>
       </c>
       <c r="B644" t="n">
-        <v>31.91832160949707</v>
+        <v>31.9183235168457</v>
       </c>
       <c r="C644" t="n">
-        <v>31.91832160949707</v>
+        <v>31.9183235168457</v>
       </c>
       <c r="D644" t="n">
-        <v>31.19134068168367</v>
+        <v>31.19134254558997</v>
       </c>
       <c r="E644" t="n">
-        <v>31.42711752024974</v>
+        <v>31.4271193982454</v>
       </c>
       <c r="F644" t="n">
         <v>5722800</v>
@@ -13332,16 +13332,16 @@
         <v>45097</v>
       </c>
       <c r="B646" t="n">
-        <v>32.16392135620117</v>
+        <v>32.16392517089844</v>
       </c>
       <c r="C646" t="n">
-        <v>32.29163122856222</v>
+        <v>32.2916350584061</v>
       </c>
       <c r="D646" t="n">
-        <v>31.48605992910253</v>
+        <v>31.48606366340425</v>
       </c>
       <c r="E646" t="n">
-        <v>32.12462428120915</v>
+        <v>32.12462809124572</v>
       </c>
       <c r="F646" t="n">
         <v>4954700</v>
@@ -13352,16 +13352,16 @@
         <v>45098</v>
       </c>
       <c r="B647" t="n">
-        <v>32.06568145751953</v>
+        <v>32.06567764282227</v>
       </c>
       <c r="C647" t="n">
-        <v>32.36040205044127</v>
+        <v>32.36039820068254</v>
       </c>
       <c r="D647" t="n">
-        <v>31.48606266749066</v>
+        <v>31.4860589217478</v>
       </c>
       <c r="E647" t="n">
-        <v>32.12462707513414</v>
+        <v>32.1246232534244</v>
       </c>
       <c r="F647" t="n">
         <v>4670300</v>
@@ -13412,16 +13412,16 @@
         <v>45103</v>
       </c>
       <c r="B650" t="n">
-        <v>30.53313064575195</v>
+        <v>30.53312873840332</v>
       </c>
       <c r="C650" t="n">
-        <v>30.83767550472773</v>
+        <v>30.83767357835474</v>
       </c>
       <c r="D650" t="n">
-        <v>30.30717806889212</v>
+        <v>30.30717617565832</v>
       </c>
       <c r="E650" t="n">
-        <v>30.58225011940398</v>
+        <v>30.58224820898695</v>
       </c>
       <c r="F650" t="n">
         <v>2874500</v>
@@ -13452,16 +13452,16 @@
         <v>45105</v>
       </c>
       <c r="B652" t="n">
-        <v>29.37389183044434</v>
+        <v>29.37389373779297</v>
       </c>
       <c r="C652" t="n">
-        <v>30.06157567506449</v>
+        <v>30.06157762706682</v>
       </c>
       <c r="D652" t="n">
-        <v>29.30512382073987</v>
+        <v>29.30512572362315</v>
       </c>
       <c r="E652" t="n">
-        <v>29.75703082903567</v>
+        <v>29.75703276126285</v>
       </c>
       <c r="F652" t="n">
         <v>4532500</v>
@@ -13532,16 +13532,16 @@
         <v>45111</v>
       </c>
       <c r="B656" t="n">
-        <v>29.80615234375</v>
+        <v>29.80615043640137</v>
       </c>
       <c r="C656" t="n">
-        <v>30.15981855937348</v>
+        <v>30.15981662939312</v>
       </c>
       <c r="D656" t="n">
-        <v>29.57037549126363</v>
+        <v>29.57037359900278</v>
       </c>
       <c r="E656" t="n">
-        <v>29.80615234375</v>
+        <v>29.80615043640137</v>
       </c>
       <c r="F656" t="n">
         <v>2514900</v>
@@ -13552,16 +13552,16 @@
         <v>45112</v>
       </c>
       <c r="B657" t="n">
-        <v>30.40542030334473</v>
+        <v>30.40541839599609</v>
       </c>
       <c r="C657" t="n">
-        <v>30.70996517647691</v>
+        <v>30.70996325002402</v>
       </c>
       <c r="D657" t="n">
-        <v>29.34442350856649</v>
+        <v>29.34442166777476</v>
       </c>
       <c r="E657" t="n">
-        <v>29.60967130192012</v>
+        <v>29.60966944448926</v>
       </c>
       <c r="F657" t="n">
         <v>5394800</v>
@@ -13612,16 +13612,16 @@
         <v>45117</v>
       </c>
       <c r="B660" t="n">
-        <v>31.07345390319824</v>
+        <v>31.07345199584961</v>
       </c>
       <c r="C660" t="n">
-        <v>31.93796904965617</v>
+        <v>31.93796708924193</v>
       </c>
       <c r="D660" t="n">
-        <v>30.84750131505205</v>
+        <v>30.84749942157282</v>
       </c>
       <c r="E660" t="n">
-        <v>31.56465803319331</v>
+        <v>31.56465609569361</v>
       </c>
       <c r="F660" t="n">
         <v>7339200</v>
@@ -13652,16 +13652,16 @@
         <v>45119</v>
       </c>
       <c r="B662" t="n">
-        <v>31.07345390319824</v>
+        <v>31.07345199584961</v>
       </c>
       <c r="C662" t="n">
-        <v>32.08533122554864</v>
+        <v>32.08532925608902</v>
       </c>
       <c r="D662" t="n">
-        <v>31.04398296705007</v>
+        <v>31.04398106151042</v>
       </c>
       <c r="E662" t="n">
-        <v>31.77096208138212</v>
+        <v>31.77096013121909</v>
       </c>
       <c r="F662" t="n">
         <v>4503800</v>
@@ -13732,16 +13732,16 @@
         <v>45125</v>
       </c>
       <c r="B666" t="n">
-        <v>32.91054916381836</v>
+        <v>32.91055297851562</v>
       </c>
       <c r="C666" t="n">
-        <v>33.03826279198419</v>
+        <v>33.03826662148488</v>
       </c>
       <c r="D666" t="n">
-        <v>32.0362098005708</v>
+        <v>32.03621351392245</v>
       </c>
       <c r="E666" t="n">
-        <v>32.18356821992315</v>
+        <v>32.18357195035527</v>
       </c>
       <c r="F666" t="n">
         <v>4775600</v>
@@ -13752,16 +13752,16 @@
         <v>45126</v>
       </c>
       <c r="B667" t="n">
-        <v>33.64735412597656</v>
+        <v>33.6473503112793</v>
       </c>
       <c r="C667" t="n">
-        <v>34.04031742501827</v>
+        <v>34.04031356576963</v>
       </c>
       <c r="D667" t="n">
-        <v>33.04808678134705</v>
+        <v>33.04808303459044</v>
       </c>
       <c r="E667" t="n">
-        <v>33.04808678134705</v>
+        <v>33.04808303459044</v>
       </c>
       <c r="F667" t="n">
         <v>7484200</v>
@@ -13772,16 +13772,16 @@
         <v>45127</v>
       </c>
       <c r="B668" t="n">
-        <v>33.92242431640625</v>
+        <v>33.92242813110352</v>
       </c>
       <c r="C668" t="n">
-        <v>34.11890595509385</v>
+        <v>34.11890979188617</v>
       </c>
       <c r="D668" t="n">
-        <v>33.64735227078894</v>
+        <v>33.64735605455338</v>
       </c>
       <c r="E668" t="n">
-        <v>33.91260192088087</v>
+        <v>33.91260573447357</v>
       </c>
       <c r="F668" t="n">
         <v>3587900</v>
@@ -13952,16 +13952,16 @@
         <v>45140</v>
       </c>
       <c r="B677" t="n">
-        <v>34.44309997558594</v>
+        <v>34.4431037902832</v>
       </c>
       <c r="C677" t="n">
-        <v>34.58063599342123</v>
+        <v>34.5806398233511</v>
       </c>
       <c r="D677" t="n">
-        <v>33.71611906300245</v>
+        <v>33.71612279718397</v>
       </c>
       <c r="E677" t="n">
-        <v>34.38415436183849</v>
+        <v>34.38415817000732</v>
       </c>
       <c r="F677" t="n">
         <v>3408800</v>
@@ -14012,16 +14012,16 @@
         <v>45145</v>
       </c>
       <c r="B680" t="n">
-        <v>35.68093109130859</v>
+        <v>35.68092727661133</v>
       </c>
       <c r="C680" t="n">
-        <v>36.15248480095344</v>
+        <v>36.15248093584172</v>
       </c>
       <c r="D680" t="n">
-        <v>35.09148989114647</v>
+        <v>35.09148613946717</v>
       </c>
       <c r="E680" t="n">
-        <v>36.05424585011833</v>
+        <v>36.05424199550948</v>
       </c>
       <c r="F680" t="n">
         <v>3820600</v>
@@ -14032,16 +14032,16 @@
         <v>45146</v>
       </c>
       <c r="B681" t="n">
-        <v>36.34896850585938</v>
+        <v>36.34896469116211</v>
       </c>
       <c r="C681" t="n">
-        <v>36.51597548123902</v>
+        <v>36.51597164901496</v>
       </c>
       <c r="D681" t="n">
-        <v>34.30556523426109</v>
+        <v>34.30556163401185</v>
       </c>
       <c r="E681" t="n">
-        <v>34.76729657396523</v>
+        <v>34.76729292525891</v>
       </c>
       <c r="F681" t="n">
         <v>5274900</v>
@@ -14172,16 +14172,16 @@
         <v>45155</v>
       </c>
       <c r="B688" t="n">
-        <v>31.26993560791016</v>
+        <v>31.26993370056152</v>
       </c>
       <c r="C688" t="n">
-        <v>31.74149119874277</v>
+        <v>31.74148926263102</v>
       </c>
       <c r="D688" t="n">
-        <v>30.96539073320894</v>
+        <v>30.9653888444364</v>
       </c>
       <c r="E688" t="n">
-        <v>31.4664153864515</v>
+        <v>31.46641346711834</v>
       </c>
       <c r="F688" t="n">
         <v>4529600</v>
@@ -14252,16 +14252,16 @@
         <v>45161</v>
       </c>
       <c r="B692" t="n">
-        <v>31.05380439758301</v>
+        <v>31.05380630493164</v>
       </c>
       <c r="C692" t="n">
-        <v>31.24045988874735</v>
+        <v>31.2404618075605</v>
       </c>
       <c r="D692" t="n">
-        <v>30.68048966767887</v>
+        <v>30.68049155209822</v>
       </c>
       <c r="E692" t="n">
-        <v>31.09309960011686</v>
+        <v>31.09310150987904</v>
       </c>
       <c r="F692" t="n">
         <v>4847400</v>
@@ -14272,16 +14272,16 @@
         <v>45162</v>
       </c>
       <c r="B693" t="n">
-        <v>30.91626739501953</v>
+        <v>30.91626930236816</v>
       </c>
       <c r="C693" t="n">
-        <v>31.30923067440671</v>
+        <v>31.30923260599883</v>
       </c>
       <c r="D693" t="n">
-        <v>30.56260306687397</v>
+        <v>30.56260495240363</v>
       </c>
       <c r="E693" t="n">
-        <v>31.05380529232016</v>
+        <v>31.05380720815405</v>
       </c>
       <c r="F693" t="n">
         <v>3471700</v>
@@ -14332,16 +14332,16 @@
         <v>45167</v>
       </c>
       <c r="B696" t="n">
-        <v>31.29940605163574</v>
+        <v>31.29940795898438</v>
       </c>
       <c r="C696" t="n">
-        <v>31.55482955705047</v>
+        <v>31.55483147996431</v>
       </c>
       <c r="D696" t="n">
-        <v>30.63137073276579</v>
+        <v>30.63137259940515</v>
       </c>
       <c r="E696" t="n">
-        <v>31.06362921093831</v>
+        <v>31.06363110391898</v>
       </c>
       <c r="F696" t="n">
         <v>3743200</v>
@@ -14352,16 +14352,16 @@
         <v>45168</v>
       </c>
       <c r="B697" t="n">
-        <v>31.63342475891113</v>
+        <v>31.6334228515625</v>
       </c>
       <c r="C697" t="n">
-        <v>31.70219277216898</v>
+        <v>31.70219086067396</v>
       </c>
       <c r="D697" t="n">
-        <v>30.96538941791287</v>
+        <v>30.96538755084366</v>
       </c>
       <c r="E697" t="n">
-        <v>31.49588873239543</v>
+        <v>31.49588683333958</v>
       </c>
       <c r="F697" t="n">
         <v>3276100</v>
@@ -14412,16 +14412,16 @@
         <v>45173</v>
       </c>
       <c r="B700" t="n">
-        <v>32.27198791503906</v>
+        <v>32.2719841003418</v>
       </c>
       <c r="C700" t="n">
-        <v>32.55688613348561</v>
+        <v>32.55688228511206</v>
       </c>
       <c r="D700" t="n">
-        <v>32.06568385929886</v>
+        <v>32.06568006898767</v>
       </c>
       <c r="E700" t="n">
-        <v>32.22286843713558</v>
+        <v>32.22286462824446</v>
       </c>
       <c r="F700" t="n">
         <v>2652900</v>
@@ -14432,16 +14432,16 @@
         <v>45174</v>
       </c>
       <c r="B701" t="n">
-        <v>32.63547897338867</v>
+        <v>32.63547515869141</v>
       </c>
       <c r="C701" t="n">
-        <v>32.93019957643972</v>
+        <v>32.93019572729314</v>
       </c>
       <c r="D701" t="n">
-        <v>32.07550870331895</v>
+        <v>32.07550495407551</v>
       </c>
       <c r="E701" t="n">
-        <v>32.27198660696912</v>
+        <v>32.27198283475976</v>
       </c>
       <c r="F701" t="n">
         <v>6036900</v>
@@ -14452,16 +14452,16 @@
         <v>45175</v>
       </c>
       <c r="B702" t="n">
-        <v>32.00673675537109</v>
+        <v>32.00674057006836</v>
       </c>
       <c r="C702" t="n">
-        <v>32.71406536628031</v>
+        <v>32.71406926527997</v>
       </c>
       <c r="D702" t="n">
-        <v>31.928142605506</v>
+        <v>31.92814641083608</v>
       </c>
       <c r="E702" t="n">
-        <v>32.65512350145682</v>
+        <v>32.65512739343153</v>
       </c>
       <c r="F702" t="n">
         <v>4505300</v>
@@ -14512,16 +14512,16 @@
         <v>45181</v>
       </c>
       <c r="B705" t="n">
-        <v>32.33092880249023</v>
+        <v>32.3309326171875</v>
       </c>
       <c r="C705" t="n">
-        <v>32.64529791212711</v>
+        <v>32.6453017639165</v>
       </c>
       <c r="D705" t="n">
-        <v>31.76113619661418</v>
+        <v>31.76113994408213</v>
       </c>
       <c r="E705" t="n">
-        <v>31.97726261725491</v>
+        <v>31.97726639022342</v>
       </c>
       <c r="F705" t="n">
         <v>3620500</v>
@@ -14532,16 +14532,16 @@
         <v>45182</v>
       </c>
       <c r="B706" t="n">
-        <v>31.63342475891113</v>
+        <v>31.6334228515625</v>
       </c>
       <c r="C706" t="n">
-        <v>32.1148008517161</v>
+        <v>32.11479891534272</v>
       </c>
       <c r="D706" t="n">
-        <v>31.44676551071783</v>
+        <v>31.44676361462388</v>
       </c>
       <c r="E706" t="n">
-        <v>31.60395007638945</v>
+        <v>31.60394817081799</v>
       </c>
       <c r="F706" t="n">
         <v>7302700</v>
@@ -14552,16 +14552,16 @@
         <v>45183</v>
       </c>
       <c r="B707" t="n">
-        <v>32.31128311157227</v>
+        <v>32.311279296875</v>
       </c>
       <c r="C707" t="n">
-        <v>32.31128311157227</v>
+        <v>32.311279296875</v>
       </c>
       <c r="D707" t="n">
-        <v>31.74149045549294</v>
+        <v>31.74148670806588</v>
       </c>
       <c r="E707" t="n">
-        <v>31.83972940556933</v>
+        <v>31.83972564654409</v>
       </c>
       <c r="F707" t="n">
         <v>4362300</v>
@@ -14592,16 +14592,16 @@
         <v>45187</v>
       </c>
       <c r="B709" t="n">
-        <v>31.98709106445312</v>
+        <v>31.98709297180176</v>
       </c>
       <c r="C709" t="n">
-        <v>32.7140682775227</v>
+        <v>32.71407022822005</v>
       </c>
       <c r="D709" t="n">
-        <v>31.75131234145109</v>
+        <v>31.75131423474054</v>
       </c>
       <c r="E709" t="n">
-        <v>32.5568837113799</v>
+        <v>32.55688565270453</v>
       </c>
       <c r="F709" t="n">
         <v>5099000</v>
@@ -14692,16 +14692,16 @@
         <v>45194</v>
       </c>
       <c r="B714" t="n">
-        <v>30.95556449890137</v>
+        <v>30.95556640625</v>
       </c>
       <c r="C714" t="n">
-        <v>31.20116561183414</v>
+        <v>31.20116753431566</v>
       </c>
       <c r="D714" t="n">
-        <v>29.99280858591396</v>
+        <v>29.99281043394172</v>
       </c>
       <c r="E714" t="n">
-        <v>30.45453800366397</v>
+        <v>30.45453988014151</v>
       </c>
       <c r="F714" t="n">
         <v>6350700</v>
@@ -14712,16 +14712,16 @@
         <v>45195</v>
       </c>
       <c r="B715" t="n">
-        <v>30.32682609558105</v>
+        <v>30.32682800292969</v>
       </c>
       <c r="C715" t="n">
-        <v>30.83767498381136</v>
+        <v>30.83767692328888</v>
       </c>
       <c r="D715" t="n">
-        <v>30.19911246818264</v>
+        <v>30.19911436749897</v>
       </c>
       <c r="E715" t="n">
-        <v>30.75908270302303</v>
+        <v>30.75908463755763</v>
       </c>
       <c r="F715" t="n">
         <v>3433500</v>
@@ -14732,16 +14732,16 @@
         <v>45196</v>
       </c>
       <c r="B716" t="n">
-        <v>30.86714935302734</v>
+        <v>30.86714744567871</v>
       </c>
       <c r="C716" t="n">
-        <v>31.0734533978611</v>
+        <v>31.07345147776449</v>
       </c>
       <c r="D716" t="n">
-        <v>30.42506658011519</v>
+        <v>30.42506470008381</v>
       </c>
       <c r="E716" t="n">
-        <v>30.65102103837466</v>
+        <v>30.65101914438107</v>
       </c>
       <c r="F716" t="n">
         <v>4307600</v>
@@ -14752,16 +14752,16 @@
         <v>45197</v>
       </c>
       <c r="B717" t="n">
-        <v>30.58224868774414</v>
+        <v>30.58225059509277</v>
       </c>
       <c r="C717" t="n">
-        <v>31.21098878902595</v>
+        <v>31.21099073558775</v>
       </c>
       <c r="D717" t="n">
-        <v>30.41523986184255</v>
+        <v>30.41524175877521</v>
       </c>
       <c r="E717" t="n">
-        <v>30.82784979208249</v>
+        <v>30.82785171474873</v>
       </c>
       <c r="F717" t="n">
         <v>4298000</v>
@@ -14772,16 +14772,16 @@
         <v>45198</v>
       </c>
       <c r="B718" t="n">
-        <v>31.02433395385742</v>
+        <v>31.02433204650879</v>
       </c>
       <c r="C718" t="n">
-        <v>31.60395088345571</v>
+        <v>31.60394894047274</v>
       </c>
       <c r="D718" t="n">
-        <v>30.47418795995777</v>
+        <v>30.47418608643163</v>
       </c>
       <c r="E718" t="n">
-        <v>30.86714938417181</v>
+        <v>30.86714748648674</v>
       </c>
       <c r="F718" t="n">
         <v>5846000</v>
@@ -14852,16 +14852,16 @@
         <v>45204</v>
       </c>
       <c r="B722" t="n">
-        <v>28.03782272338867</v>
+        <v>28.0378246307373</v>
       </c>
       <c r="C722" t="n">
-        <v>28.78444842505877</v>
+        <v>28.78445038319864</v>
       </c>
       <c r="D722" t="n">
-        <v>27.72345173862667</v>
+        <v>27.72345362458937</v>
       </c>
       <c r="E722" t="n">
-        <v>28.62726386957162</v>
+        <v>28.62726581701858</v>
       </c>
       <c r="F722" t="n">
         <v>8409300</v>
@@ -14912,16 +14912,16 @@
         <v>45209</v>
       </c>
       <c r="B725" t="n">
-        <v>30.27770614624023</v>
+        <v>30.2777042388916</v>
       </c>
       <c r="C725" t="n">
-        <v>30.40541977953243</v>
+        <v>30.40541786413846</v>
       </c>
       <c r="D725" t="n">
-        <v>29.43283768343539</v>
+        <v>29.43283582930937</v>
       </c>
       <c r="E725" t="n">
-        <v>29.75703296465965</v>
+        <v>29.7570310901109</v>
       </c>
       <c r="F725" t="n">
         <v>7018100</v>
@@ -14972,16 +14972,16 @@
         <v>45215</v>
       </c>
       <c r="B728" t="n">
-        <v>31.67271995544434</v>
+        <v>31.67272186279297</v>
       </c>
       <c r="C728" t="n">
-        <v>32.01656000130495</v>
+        <v>32.01656192935982</v>
       </c>
       <c r="D728" t="n">
-        <v>31.32887616200829</v>
+        <v>31.32887804865046</v>
       </c>
       <c r="E728" t="n">
-        <v>31.91832105893775</v>
+        <v>31.91832298107662</v>
       </c>
       <c r="F728" t="n">
         <v>3741500</v>
@@ -15012,16 +15012,16 @@
         <v>45217</v>
       </c>
       <c r="B730" t="n">
-        <v>32.06568145751953</v>
+        <v>32.06567764282227</v>
       </c>
       <c r="C730" t="n">
-        <v>33.06773447151397</v>
+        <v>33.06773053760736</v>
       </c>
       <c r="D730" t="n">
-        <v>31.63342483773936</v>
+        <v>31.63342107446555</v>
       </c>
       <c r="E730" t="n">
-        <v>32.52741275989484</v>
+        <v>32.52740889026767</v>
       </c>
       <c r="F730" t="n">
         <v>7439800</v>
@@ -15132,16 +15132,16 @@
         <v>45225</v>
       </c>
       <c r="B736" t="n">
-        <v>31.98709106445312</v>
+        <v>31.98709297180176</v>
       </c>
       <c r="C736" t="n">
-        <v>32.12462709138111</v>
+        <v>32.12462900693085</v>
       </c>
       <c r="D736" t="n">
-        <v>31.19134209034388</v>
+        <v>31.19134395024304</v>
       </c>
       <c r="E736" t="n">
-        <v>31.57447923609348</v>
+        <v>31.57448111883861</v>
       </c>
       <c r="F736" t="n">
         <v>2923500</v>
@@ -15152,16 +15152,16 @@
         <v>45226</v>
       </c>
       <c r="B737" t="n">
-        <v>31.52535820007324</v>
+        <v>31.52536010742188</v>
       </c>
       <c r="C737" t="n">
-        <v>32.556882098507</v>
+        <v>32.55688406826494</v>
       </c>
       <c r="D737" t="n">
-        <v>31.24046001693592</v>
+        <v>31.24046190704763</v>
       </c>
       <c r="E737" t="n">
-        <v>32.32110713476096</v>
+        <v>32.32110909025403</v>
       </c>
       <c r="F737" t="n">
         <v>3378100</v>
@@ -15172,16 +15172,16 @@
         <v>45229</v>
       </c>
       <c r="B738" t="n">
-        <v>31.07345390319824</v>
+        <v>31.07345199584961</v>
       </c>
       <c r="C738" t="n">
-        <v>32.11480216169681</v>
+        <v>32.11480019042821</v>
       </c>
       <c r="D738" t="n">
-        <v>30.98503922096583</v>
+        <v>30.98503731904426</v>
       </c>
       <c r="E738" t="n">
-        <v>31.54500949323592</v>
+        <v>31.5450075569423</v>
       </c>
       <c r="F738" t="n">
         <v>3227500</v>
@@ -15192,16 +15192,16 @@
         <v>45230</v>
       </c>
       <c r="B739" t="n">
-        <v>31.86919784545898</v>
+        <v>31.86919975280762</v>
       </c>
       <c r="C739" t="n">
-        <v>32.10497655378492</v>
+        <v>32.10497847524474</v>
       </c>
       <c r="D739" t="n">
-        <v>31.20116441782789</v>
+        <v>31.2011662851952</v>
       </c>
       <c r="E739" t="n">
-        <v>31.20116441782789</v>
+        <v>31.2011662851952</v>
       </c>
       <c r="F739" t="n">
         <v>3372100</v>
@@ -15212,16 +15212,16 @@
         <v>45231</v>
       </c>
       <c r="B740" t="n">
-        <v>32.06568145751953</v>
+        <v>32.06567764282227</v>
       </c>
       <c r="C740" t="n">
-        <v>32.74354294357276</v>
+        <v>32.74353904823363</v>
       </c>
       <c r="D740" t="n">
-        <v>31.94779396986597</v>
+        <v>31.9477901691932</v>
       </c>
       <c r="E740" t="n">
-        <v>32.0755076009098</v>
+        <v>32.07550378504357</v>
       </c>
       <c r="F740" t="n">
         <v>4282500</v>
@@ -15232,16 +15232,16 @@
         <v>45233</v>
       </c>
       <c r="B741" t="n">
-        <v>32.69441604614258</v>
+        <v>32.69441986083984</v>
       </c>
       <c r="C741" t="n">
-        <v>32.94984327951414</v>
+        <v>32.94984712401398</v>
       </c>
       <c r="D741" t="n">
-        <v>32.4684634920525</v>
+        <v>32.46846728038622</v>
       </c>
       <c r="E741" t="n">
-        <v>32.7337131201344</v>
+        <v>32.73371693941674</v>
       </c>
       <c r="F741" t="n">
         <v>3190300</v>
@@ -15272,16 +15272,16 @@
         <v>45237</v>
       </c>
       <c r="B743" t="n">
-        <v>32.48811340332031</v>
+        <v>32.48811721801758</v>
       </c>
       <c r="C743" t="n">
-        <v>32.63547556323554</v>
+        <v>32.63547939523581</v>
       </c>
       <c r="D743" t="n">
-        <v>31.81025571237618</v>
+        <v>31.81025944748058</v>
       </c>
       <c r="E743" t="n">
-        <v>31.87902372098318</v>
+        <v>31.8790274641622</v>
       </c>
       <c r="F743" t="n">
         <v>3324000</v>
@@ -15312,16 +15312,16 @@
         <v>45239</v>
       </c>
       <c r="B745" t="n">
-        <v>30.81802940368652</v>
+        <v>30.81802749633789</v>
       </c>
       <c r="C745" t="n">
-        <v>33.77506711733456</v>
+        <v>33.77506502697286</v>
       </c>
       <c r="D745" t="n">
-        <v>30.67066723245724</v>
+        <v>30.67066533422895</v>
       </c>
       <c r="E745" t="n">
-        <v>33.41157476098916</v>
+        <v>33.41157269312426</v>
       </c>
       <c r="F745" t="n">
         <v>15431300</v>
@@ -15332,16 +15332,16 @@
         <v>45240</v>
       </c>
       <c r="B746" t="n">
-        <v>31.25028419494629</v>
+        <v>31.25028610229492</v>
       </c>
       <c r="C746" t="n">
-        <v>32.06567979171039</v>
+        <v>32.06568174882637</v>
       </c>
       <c r="D746" t="n">
-        <v>31.04398016537612</v>
+        <v>31.04398206013306</v>
       </c>
       <c r="E746" t="n">
-        <v>31.05380443446818</v>
+        <v>31.05380632982475</v>
       </c>
       <c r="F746" t="n">
         <v>4738300</v>
@@ -15352,16 +15352,16 @@
         <v>45243</v>
       </c>
       <c r="B747" t="n">
-        <v>30.94574165344238</v>
+        <v>30.94573974609375</v>
       </c>
       <c r="C747" t="n">
-        <v>31.41729536226194</v>
+        <v>31.41729342584897</v>
       </c>
       <c r="D747" t="n">
-        <v>30.67066771973704</v>
+        <v>30.67066582934266</v>
       </c>
       <c r="E747" t="n">
-        <v>31.21099131732383</v>
+        <v>31.21098939362647</v>
       </c>
       <c r="F747" t="n">
         <v>3172300</v>
@@ -15392,16 +15392,16 @@
         <v>45246</v>
       </c>
       <c r="B749" t="n">
-        <v>31.13239669799805</v>
+        <v>31.13239860534668</v>
       </c>
       <c r="C749" t="n">
-        <v>32.13444778565191</v>
+        <v>32.13444975439192</v>
       </c>
       <c r="D749" t="n">
-        <v>30.68048968892551</v>
+        <v>30.68049156858774</v>
       </c>
       <c r="E749" t="n">
-        <v>31.78078159366364</v>
+        <v>31.78078354073604</v>
       </c>
       <c r="F749" t="n">
         <v>5148500</v>
@@ -15492,16 +15492,16 @@
         <v>45253</v>
       </c>
       <c r="B754" t="n">
-        <v>31.81025886535645</v>
+        <v>31.81025505065918</v>
       </c>
       <c r="C754" t="n">
-        <v>32.00674051552654</v>
+        <v>32.00673667726713</v>
       </c>
       <c r="D754" t="n">
-        <v>31.58430627931235</v>
+        <v>31.5843024917114</v>
       </c>
       <c r="E754" t="n">
-        <v>31.82990740513103</v>
+        <v>31.82990358807751</v>
       </c>
       <c r="F754" t="n">
         <v>2086300</v>
@@ -15552,16 +15552,16 @@
         <v>45258</v>
       </c>
       <c r="B757" t="n">
-        <v>29.80615234375</v>
+        <v>29.80615043640137</v>
       </c>
       <c r="C757" t="n">
-        <v>30.21876230404811</v>
+        <v>30.21876037029583</v>
       </c>
       <c r="D757" t="n">
-        <v>29.63914350568201</v>
+        <v>29.63914160902057</v>
       </c>
       <c r="E757" t="n">
-        <v>30.17946522507312</v>
+        <v>30.17946329383553</v>
       </c>
       <c r="F757" t="n">
         <v>5777500</v>
@@ -15592,16 +15592,16 @@
         <v>45260</v>
       </c>
       <c r="B759" t="n">
-        <v>29.45248413085938</v>
+        <v>29.45248603820801</v>
       </c>
       <c r="C759" t="n">
-        <v>29.83562312973222</v>
+        <v>29.83562506189301</v>
       </c>
       <c r="D759" t="n">
-        <v>29.17741209183939</v>
+        <v>29.1774139813743</v>
       </c>
       <c r="E759" t="n">
-        <v>29.66861430298963</v>
+        <v>29.66861622433489</v>
       </c>
       <c r="F759" t="n">
         <v>4483800</v>
@@ -15732,16 +15732,16 @@
         <v>45271</v>
       </c>
       <c r="B766" t="n">
-        <v>26.91788291931152</v>
+        <v>26.91788101196289</v>
       </c>
       <c r="C766" t="n">
-        <v>27.08489175922624</v>
+        <v>27.08488984004369</v>
       </c>
       <c r="D766" t="n">
-        <v>26.48562441474616</v>
+        <v>26.48562253802652</v>
       </c>
       <c r="E766" t="n">
-        <v>26.96700426857343</v>
+        <v>26.96700235774415</v>
       </c>
       <c r="F766" t="n">
         <v>6627000</v>
@@ -15792,16 +15792,16 @@
         <v>45274</v>
       </c>
       <c r="B769" t="n">
-        <v>27.00629806518555</v>
+        <v>27.00629997253418</v>
       </c>
       <c r="C769" t="n">
-        <v>27.2027797044063</v>
+        <v>27.20278162563166</v>
       </c>
       <c r="D769" t="n">
-        <v>26.49544730224182</v>
+        <v>26.49544917351107</v>
       </c>
       <c r="E769" t="n">
-        <v>26.82946496464443</v>
+        <v>26.82946685950403</v>
       </c>
       <c r="F769" t="n">
         <v>14011300</v>
@@ -15812,16 +15812,16 @@
         <v>45275</v>
       </c>
       <c r="B770" t="n">
-        <v>25.88635635375977</v>
+        <v>25.8863582611084</v>
       </c>
       <c r="C770" t="n">
-        <v>27.21260267051552</v>
+        <v>27.21260467558413</v>
       </c>
       <c r="D770" t="n">
-        <v>25.88635635375977</v>
+        <v>25.8863582611084</v>
       </c>
       <c r="E770" t="n">
-        <v>27.1634813261689</v>
+        <v>27.16348332761816</v>
       </c>
       <c r="F770" t="n">
         <v>11924000</v>
@@ -15832,16 +15832,16 @@
         <v>45278</v>
       </c>
       <c r="B771" t="n">
-        <v>26.21055030822754</v>
+        <v>26.21055221557617</v>
       </c>
       <c r="C771" t="n">
-        <v>26.76069626050536</v>
+        <v>26.76069820788825</v>
       </c>
       <c r="D771" t="n">
-        <v>25.94530066428034</v>
+        <v>25.94530255232668</v>
       </c>
       <c r="E771" t="n">
-        <v>26.12213376024514</v>
+        <v>26.12213566115967</v>
       </c>
       <c r="F771" t="n">
         <v>4958200</v>
@@ -15852,16 +15852,16 @@
         <v>45279</v>
       </c>
       <c r="B772" t="n">
-        <v>26.32843971252441</v>
+        <v>26.32843780517578</v>
       </c>
       <c r="C772" t="n">
-        <v>26.52492136101001</v>
+        <v>26.52491943942738</v>
       </c>
       <c r="D772" t="n">
-        <v>26.13195993782669</v>
+        <v>26.13195804471192</v>
       </c>
       <c r="E772" t="n">
-        <v>26.30879304670615</v>
+        <v>26.30879114078081</v>
       </c>
       <c r="F772" t="n">
         <v>3900900</v>
@@ -15872,16 +15872,16 @@
         <v>45280</v>
       </c>
       <c r="B773" t="n">
-        <v>25.85688591003418</v>
+        <v>25.85688400268555</v>
       </c>
       <c r="C773" t="n">
-        <v>26.54456980342805</v>
+        <v>26.54456784535201</v>
       </c>
       <c r="D773" t="n">
-        <v>25.68987707156926</v>
+        <v>25.68987517654013</v>
       </c>
       <c r="E773" t="n">
-        <v>26.54456980342805</v>
+        <v>26.54456784535201</v>
       </c>
       <c r="F773" t="n">
         <v>6168300</v>
@@ -15912,16 +15912,16 @@
         <v>45282</v>
       </c>
       <c r="B775" t="n">
-        <v>25.95512580871582</v>
+        <v>25.95512771606445</v>
       </c>
       <c r="C775" t="n">
-        <v>26.2203754616087</v>
+        <v>26.22037738844958</v>
       </c>
       <c r="D775" t="n">
-        <v>25.79794124562103</v>
+        <v>25.79794314141873</v>
       </c>
       <c r="E775" t="n">
-        <v>26.03371809026321</v>
+        <v>26.03372000338731</v>
       </c>
       <c r="F775" t="n">
         <v>3644200</v>
@@ -16012,16 +16012,16 @@
         <v>45294</v>
       </c>
       <c r="B780" t="n">
-        <v>25.88635635375977</v>
+        <v>25.8863582611084</v>
       </c>
       <c r="C780" t="n">
-        <v>26.28914200846361</v>
+        <v>26.28914394549015</v>
       </c>
       <c r="D780" t="n">
-        <v>25.35585707754239</v>
+        <v>25.35585894580298</v>
       </c>
       <c r="E780" t="n">
-        <v>25.64075525338972</v>
+        <v>25.64075714264207</v>
       </c>
       <c r="F780" t="n">
         <v>5734800</v>
@@ -16052,16 +16052,16 @@
         <v>45296</v>
       </c>
       <c r="B782" t="n">
-        <v>25.68987464904785</v>
+        <v>25.68987655639648</v>
       </c>
       <c r="C782" t="n">
-        <v>25.97477282406455</v>
+        <v>25.97477475256549</v>
       </c>
       <c r="D782" t="n">
-        <v>25.21832098742127</v>
+        <v>25.21832285975933</v>
       </c>
       <c r="E782" t="n">
-        <v>25.36568127245611</v>
+        <v>25.36568315573496</v>
       </c>
       <c r="F782" t="n">
         <v>3417300</v>
@@ -16092,16 +16092,16 @@
         <v>45300</v>
       </c>
       <c r="B784" t="n">
-        <v>28.01817512512207</v>
+        <v>28.0181770324707</v>
       </c>
       <c r="C784" t="n">
-        <v>28.24412769698892</v>
+        <v>28.24412961971936</v>
       </c>
       <c r="D784" t="n">
-        <v>26.79999384234995</v>
+        <v>26.7999956667704</v>
       </c>
       <c r="E784" t="n">
-        <v>27.01612214494592</v>
+        <v>27.01612398407939</v>
       </c>
       <c r="F784" t="n">
         <v>10290300</v>
@@ -16152,16 +16152,16 @@
         <v>45303</v>
       </c>
       <c r="B787" t="n">
-        <v>28.20483207702637</v>
+        <v>28.20483016967773</v>
       </c>
       <c r="C787" t="n">
-        <v>28.86304316187749</v>
+        <v>28.86304121001741</v>
       </c>
       <c r="D787" t="n">
-        <v>27.82169492460737</v>
+        <v>27.82169304316834</v>
       </c>
       <c r="E787" t="n">
-        <v>28.63709057833746</v>
+        <v>28.63708864175739</v>
       </c>
       <c r="F787" t="n">
         <v>5067700</v>
@@ -16172,16 +16172,16 @@
         <v>45306</v>
       </c>
       <c r="B788" t="n">
-        <v>28.52902793884277</v>
+        <v>28.52902603149414</v>
       </c>
       <c r="C788" t="n">
-        <v>28.68621251092004</v>
+        <v>28.68621059306261</v>
       </c>
       <c r="D788" t="n">
-        <v>27.9002877767458</v>
+        <v>27.90028591143248</v>
       </c>
       <c r="E788" t="n">
-        <v>28.06729661880138</v>
+        <v>28.06729474232245</v>
       </c>
       <c r="F788" t="n">
         <v>3859400</v>
@@ -16252,16 +16252,16 @@
         <v>45310</v>
       </c>
       <c r="B792" t="n">
-        <v>29.03005027770996</v>
+        <v>29.03005218505859</v>
       </c>
       <c r="C792" t="n">
-        <v>29.197059106456</v>
+        <v>29.19706102477754</v>
       </c>
       <c r="D792" t="n">
-        <v>28.0574701128199</v>
+        <v>28.05747195626752</v>
       </c>
       <c r="E792" t="n">
-        <v>28.73532969699943</v>
+        <v>28.73533158498416</v>
       </c>
       <c r="F792" t="n">
         <v>7851200</v>
@@ -16312,16 +16312,16 @@
         <v>45315</v>
       </c>
       <c r="B795" t="n">
-        <v>27.86099243164062</v>
+        <v>27.86099052429199</v>
       </c>
       <c r="C795" t="n">
-        <v>28.52902779653059</v>
+        <v>28.52902584344861</v>
       </c>
       <c r="D795" t="n">
-        <v>27.63503797084227</v>
+        <v>27.63503607896236</v>
       </c>
       <c r="E795" t="n">
-        <v>28.04764793893384</v>
+        <v>28.04764601880687</v>
       </c>
       <c r="F795" t="n">
         <v>4070600</v>
@@ -16352,16 +16352,16 @@
         <v>45317</v>
       </c>
       <c r="B797" t="n">
-        <v>28.24412727355957</v>
+        <v>28.2441291809082</v>
       </c>
       <c r="C797" t="n">
-        <v>28.24412727355957</v>
+        <v>28.2441291809082</v>
       </c>
       <c r="D797" t="n">
-        <v>27.50732395337975</v>
+        <v>27.50732581097147</v>
       </c>
       <c r="E797" t="n">
-        <v>27.65468424265817</v>
+        <v>27.65468611020124</v>
       </c>
       <c r="F797" t="n">
         <v>2761100</v>
@@ -16392,16 +16392,16 @@
         <v>45321</v>
       </c>
       <c r="B799" t="n">
-        <v>27.2420768737793</v>
+        <v>27.24207496643066</v>
       </c>
       <c r="C799" t="n">
-        <v>27.54662362392648</v>
+        <v>27.54662169525507</v>
       </c>
       <c r="D799" t="n">
-        <v>26.97682720382707</v>
+        <v>26.97682531504984</v>
       </c>
       <c r="E799" t="n">
-        <v>27.369790510625</v>
+        <v>27.36978859433452</v>
       </c>
       <c r="F799" t="n">
         <v>2184900</v>
@@ -16432,16 +16432,16 @@
         <v>45323</v>
       </c>
       <c r="B801" t="n">
-        <v>26.24002265930176</v>
+        <v>26.24002075195312</v>
       </c>
       <c r="C801" t="n">
-        <v>27.40908451061442</v>
+        <v>27.4090825182884</v>
       </c>
       <c r="D801" t="n">
-        <v>26.10248663224892</v>
+        <v>26.10248473489757</v>
       </c>
       <c r="E801" t="n">
-        <v>27.31084368823903</v>
+        <v>27.31084170305399</v>
       </c>
       <c r="F801" t="n">
         <v>7611700</v>
@@ -16532,16 +16532,16 @@
         <v>45330</v>
       </c>
       <c r="B806" t="n">
-        <v>28.79427528381348</v>
+        <v>28.79427337646484</v>
       </c>
       <c r="C806" t="n">
-        <v>28.81392382346353</v>
+        <v>28.81392191481336</v>
       </c>
       <c r="D806" t="n">
-        <v>27.39926082305394</v>
+        <v>27.39925900811183</v>
       </c>
       <c r="E806" t="n">
-        <v>28.71568299900116</v>
+        <v>28.71568109685852</v>
       </c>
       <c r="F806" t="n">
         <v>6908300</v>
@@ -16552,16 +16552,16 @@
         <v>45331</v>
       </c>
       <c r="B807" t="n">
-        <v>27.6939811706543</v>
+        <v>27.69398307800293</v>
       </c>
       <c r="C807" t="n">
-        <v>28.9121624286317</v>
+        <v>28.9121644198793</v>
       </c>
       <c r="D807" t="n">
-        <v>27.52697234402422</v>
+        <v>27.52697423987057</v>
       </c>
       <c r="E807" t="n">
-        <v>28.83357014985212</v>
+        <v>28.83357213568689</v>
       </c>
       <c r="F807" t="n">
         <v>5513900</v>
@@ -16592,16 +16592,16 @@
         <v>45337</v>
       </c>
       <c r="B809" t="n">
-        <v>28.00835227966309</v>
+        <v>28.00835037231445</v>
       </c>
       <c r="C809" t="n">
-        <v>28.26377767232718</v>
+        <v>28.26377574758426</v>
       </c>
       <c r="D809" t="n">
-        <v>27.28137318075199</v>
+        <v>27.28137132291011</v>
       </c>
       <c r="E809" t="n">
-        <v>27.40908494019011</v>
+        <v>27.40908307365115</v>
       </c>
       <c r="F809" t="n">
         <v>2788300</v>
@@ -16632,16 +16632,16 @@
         <v>45341</v>
       </c>
       <c r="B811" t="n">
-        <v>28.67638778686523</v>
+        <v>28.6763858795166</v>
       </c>
       <c r="C811" t="n">
-        <v>28.76480434148215</v>
+        <v>28.76480242825268</v>
       </c>
       <c r="D811" t="n">
-        <v>28.23430501378064</v>
+        <v>28.2343031358362</v>
       </c>
       <c r="E811" t="n">
-        <v>28.74515580183664</v>
+        <v>28.74515388991405</v>
       </c>
       <c r="F811" t="n">
         <v>1698200</v>
@@ -16672,16 +16672,16 @@
         <v>45343</v>
       </c>
       <c r="B813" t="n">
-        <v>28.92198944091797</v>
+        <v>28.92198753356934</v>
       </c>
       <c r="C813" t="n">
-        <v>28.98093318714647</v>
+        <v>28.98093127591061</v>
       </c>
       <c r="D813" t="n">
-        <v>28.36201916727748</v>
+        <v>28.36201729685779</v>
       </c>
       <c r="E813" t="n">
-        <v>28.6370912322024</v>
+        <v>28.63708934364225</v>
       </c>
       <c r="F813" t="n">
         <v>2751400</v>
@@ -16792,16 +16792,16 @@
         <v>45351</v>
       </c>
       <c r="B819" t="n">
-        <v>27.45820617675781</v>
+        <v>27.45820426940918</v>
       </c>
       <c r="C819" t="n">
-        <v>28.14588819377561</v>
+        <v>28.14588623865804</v>
       </c>
       <c r="D819" t="n">
-        <v>27.45820617675781</v>
+        <v>27.45820426940918</v>
       </c>
       <c r="E819" t="n">
-        <v>27.98870362566938</v>
+        <v>27.98870168147043</v>
       </c>
       <c r="F819" t="n">
         <v>2784300</v>
@@ -16972,16 +16972,16 @@
         <v>45364</v>
       </c>
       <c r="B828" t="n">
-        <v>29.13811683654785</v>
+        <v>29.13811492919922</v>
       </c>
       <c r="C828" t="n">
-        <v>29.36406941808906</v>
+        <v>29.36406749594983</v>
       </c>
       <c r="D828" t="n">
-        <v>28.98093226905937</v>
+        <v>28.98093037199986</v>
       </c>
       <c r="E828" t="n">
-        <v>28.98093226905937</v>
+        <v>28.98093037199986</v>
       </c>
       <c r="F828" t="n">
         <v>2596400</v>
@@ -17032,16 +17032,16 @@
         <v>45369</v>
       </c>
       <c r="B831" t="n">
-        <v>28.98093032836914</v>
+        <v>28.98093223571777</v>
       </c>
       <c r="C831" t="n">
-        <v>29.28547517326093</v>
+        <v>29.28547710065286</v>
       </c>
       <c r="D831" t="n">
-        <v>28.61743986927554</v>
+        <v>28.61744175270144</v>
       </c>
       <c r="E831" t="n">
-        <v>28.77462630002598</v>
+        <v>28.77462819379693</v>
       </c>
       <c r="F831" t="n">
         <v>4710300</v>
@@ -17112,16 +17112,16 @@
         <v>45373</v>
       </c>
       <c r="B835" t="n">
-        <v>29.71773338317871</v>
+        <v>29.71773529052734</v>
       </c>
       <c r="C835" t="n">
-        <v>30.00263156131158</v>
+        <v>30.0026334869456</v>
       </c>
       <c r="D835" t="n">
-        <v>29.28547491839919</v>
+        <v>29.28547679800454</v>
       </c>
       <c r="E835" t="n">
-        <v>29.88474220772164</v>
+        <v>29.88474412578926</v>
       </c>
       <c r="F835" t="n">
         <v>3854000</v>
@@ -17152,16 +17152,16 @@
         <v>45377</v>
       </c>
       <c r="B837" t="n">
-        <v>30.81802940368652</v>
+        <v>30.81802749633789</v>
       </c>
       <c r="C837" t="n">
-        <v>31.22081509112746</v>
+        <v>31.22081315885015</v>
       </c>
       <c r="D837" t="n">
-        <v>30.51348266534799</v>
+        <v>30.51348077684796</v>
       </c>
       <c r="E837" t="n">
-        <v>30.61172348823823</v>
+        <v>30.61172159365801</v>
       </c>
       <c r="F837" t="n">
         <v>3327200</v>
@@ -17172,16 +17172,16 @@
         <v>45378</v>
       </c>
       <c r="B838" t="n">
-        <v>31.48606300354004</v>
+        <v>31.48606109619141</v>
       </c>
       <c r="C838" t="n">
-        <v>31.91832337550937</v>
+        <v>31.91832144197546</v>
       </c>
       <c r="D838" t="n">
-        <v>30.38577102935353</v>
+        <v>30.3857691886579</v>
       </c>
       <c r="E838" t="n">
-        <v>30.6510206900868</v>
+        <v>30.65101883332299</v>
       </c>
       <c r="F838" t="n">
         <v>9071000</v>
@@ -17372,16 +17372,16 @@
         <v>45393</v>
       </c>
       <c r="B848" t="n">
-        <v>35.62198257446289</v>
+        <v>35.62198638916016</v>
       </c>
       <c r="C848" t="n">
-        <v>35.91670689814429</v>
+        <v>35.91671074440308</v>
       </c>
       <c r="D848" t="n">
-        <v>34.59045868430435</v>
+        <v>34.59046238853748</v>
       </c>
       <c r="E848" t="n">
-        <v>34.74764324139922</v>
+        <v>34.74764696246498</v>
       </c>
       <c r="F848" t="n">
         <v>5960900</v>
@@ -17412,16 +17412,16 @@
         <v>45397</v>
       </c>
       <c r="B850" t="n">
-        <v>34.06978988647461</v>
+        <v>34.06978607177734</v>
       </c>
       <c r="C850" t="n">
-        <v>34.52169507730631</v>
+        <v>34.52169121201051</v>
       </c>
       <c r="D850" t="n">
-        <v>33.83401114697602</v>
+        <v>33.83400735867823</v>
       </c>
       <c r="E850" t="n">
-        <v>34.43327851844133</v>
+        <v>34.43327466304528</v>
       </c>
       <c r="F850" t="n">
         <v>4151100</v>
@@ -17472,16 +17472,16 @@
         <v>45400</v>
       </c>
       <c r="B853" t="n">
-        <v>32.33092880249023</v>
+        <v>32.3309326171875</v>
       </c>
       <c r="C853" t="n">
-        <v>33.28386227408815</v>
+        <v>33.28386620122118</v>
       </c>
       <c r="D853" t="n">
-        <v>31.93796554165645</v>
+        <v>31.93796930998834</v>
       </c>
       <c r="E853" t="n">
-        <v>33.00878649247434</v>
+        <v>33.00879038715143</v>
       </c>
       <c r="F853" t="n">
         <v>4478700</v>
@@ -17632,16 +17632,16 @@
         <v>45412</v>
       </c>
       <c r="B861" t="n">
-        <v>32.58635330200195</v>
+        <v>32.58635711669922</v>
       </c>
       <c r="C861" t="n">
-        <v>33.66700042877825</v>
+        <v>33.66700436998067</v>
       </c>
       <c r="D861" t="n">
-        <v>32.43899488533395</v>
+        <v>32.43899868278081</v>
       </c>
       <c r="E861" t="n">
-        <v>33.60805481356574</v>
+        <v>33.60805874786774</v>
       </c>
       <c r="F861" t="n">
         <v>6661700</v>
@@ -29531,12 +29531,20 @@
       <c r="A1456" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B1456" t="inlineStr"/>
-      <c r="C1456" t="inlineStr"/>
-      <c r="D1456" t="inlineStr"/>
-      <c r="E1456" t="inlineStr"/>
+      <c r="B1456" t="n">
+        <v>17.52000045776367</v>
+      </c>
+      <c r="C1456" t="n">
+        <v>17.79000091552734</v>
+      </c>
+      <c r="D1456" t="n">
+        <v>17.51000022888184</v>
+      </c>
+      <c r="E1456" t="n">
+        <v>17.61000061035156</v>
+      </c>
       <c r="F1456" t="n">
-        <v>10412200</v>
+        <v>2811000</v>
       </c>
     </row>
     <row r="1457">
@@ -29544,19 +29552,39 @@
         <v>46283</v>
       </c>
       <c r="B1457" t="n">
-        <v>17.35</v>
+        <v>17.35000038146973</v>
       </c>
       <c r="C1457" t="n">
-        <v>17.54</v>
+        <v>17.54000091552734</v>
       </c>
       <c r="D1457" t="n">
-        <v>17.34</v>
+        <v>17.34000015258789</v>
       </c>
       <c r="E1457" t="n">
         <v>17.5</v>
       </c>
       <c r="F1457" t="n">
         <v>10423000</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B1458" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="C1458" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="D1458" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="E1458" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="F1458" t="n">
+        <v>2112600</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1458"/>
+  <dimension ref="A1:F1459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29572,19 +29572,39 @@
         <v>46286</v>
       </c>
       <c r="B1458" t="n">
-        <v>17.4</v>
+        <v>17.39999961853027</v>
       </c>
       <c r="C1458" t="n">
-        <v>17.41</v>
+        <v>17.40999984741211</v>
       </c>
       <c r="D1458" t="n">
-        <v>17.08</v>
+        <v>17.07999992370605</v>
       </c>
       <c r="E1458" t="n">
-        <v>17.31</v>
+        <v>17.30999946594238</v>
       </c>
       <c r="F1458" t="n">
         <v>2112600</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1459" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="C1459" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="D1459" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="E1459" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="F1459" t="n">
+        <v>3016800</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1459"/>
+  <dimension ref="A1:F1460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,16 +512,16 @@
         <v>44152</v>
       </c>
       <c r="B5" t="n">
-        <v>20.17695426940918</v>
+        <v>20.17695617675781</v>
       </c>
       <c r="C5" t="n">
-        <v>20.17695426940918</v>
+        <v>20.17695617675781</v>
       </c>
       <c r="D5" t="n">
-        <v>19.85012445790661</v>
+        <v>19.85012633435968</v>
       </c>
       <c r="E5" t="n">
-        <v>20.12888973916155</v>
+        <v>20.12889164196659</v>
       </c>
       <c r="F5" t="n">
         <v>262242</v>
@@ -572,16 +572,16 @@
         <v>44158</v>
       </c>
       <c r="B8" t="n">
-        <v>20.20579147338867</v>
+        <v>20.2057933807373</v>
       </c>
       <c r="C8" t="n">
-        <v>20.52300874747816</v>
+        <v>20.52301068477087</v>
       </c>
       <c r="D8" t="n">
-        <v>20.14811628674976</v>
+        <v>20.14811818865408</v>
       </c>
       <c r="E8" t="n">
-        <v>20.14811628674976</v>
+        <v>20.14811818865408</v>
       </c>
       <c r="F8" t="n">
         <v>79408</v>
@@ -632,16 +632,16 @@
         <v>44161</v>
       </c>
       <c r="B11" t="n">
-        <v>22.87810897827148</v>
+        <v>22.87811088562012</v>
       </c>
       <c r="C11" t="n">
-        <v>22.87810897827148</v>
+        <v>22.87811088562012</v>
       </c>
       <c r="D11" t="n">
-        <v>22.31096214463751</v>
+        <v>22.3109640047031</v>
       </c>
       <c r="E11" t="n">
-        <v>22.31096214463751</v>
+        <v>22.3109640047031</v>
       </c>
       <c r="F11" t="n">
         <v>72970</v>
@@ -652,16 +652,16 @@
         <v>44162</v>
       </c>
       <c r="B12" t="n">
-        <v>23.07036399841309</v>
+        <v>23.07036209106445</v>
       </c>
       <c r="C12" t="n">
-        <v>23.55099623037812</v>
+        <v>23.55099428329309</v>
       </c>
       <c r="D12" t="n">
-        <v>22.10909953448302</v>
+        <v>22.10909770660719</v>
       </c>
       <c r="E12" t="n">
-        <v>23.07036399841309</v>
+        <v>23.07036209106445</v>
       </c>
       <c r="F12" t="n">
         <v>72050</v>
@@ -692,16 +692,16 @@
         <v>44166</v>
       </c>
       <c r="B14" t="n">
-        <v>23.07036399841309</v>
+        <v>23.07036209106445</v>
       </c>
       <c r="C14" t="n">
-        <v>23.16649119432127</v>
+        <v>23.1664892790253</v>
       </c>
       <c r="D14" t="n">
-        <v>23.03191386956499</v>
+        <v>23.03191196539523</v>
       </c>
       <c r="E14" t="n">
-        <v>23.12803919168523</v>
+        <v>23.12803727956828</v>
       </c>
       <c r="F14" t="n">
         <v>93512</v>
@@ -792,16 +792,16 @@
         <v>44173</v>
       </c>
       <c r="B19" t="n">
-        <v>26.33866310119629</v>
+        <v>26.33866500854492</v>
       </c>
       <c r="C19" t="n">
-        <v>26.57898012603766</v>
+        <v>26.57898205078916</v>
       </c>
       <c r="D19" t="n">
-        <v>25.56965124500673</v>
+        <v>25.56965309666637</v>
       </c>
       <c r="E19" t="n">
-        <v>25.56965124500673</v>
+        <v>25.56965309666637</v>
       </c>
       <c r="F19" t="n">
         <v>126420</v>
@@ -812,16 +812,16 @@
         <v>44174</v>
       </c>
       <c r="B20" t="n">
-        <v>26.83852195739746</v>
+        <v>26.83852005004883</v>
       </c>
       <c r="C20" t="n">
-        <v>27.77095064592048</v>
+        <v>27.77094867230641</v>
       </c>
       <c r="D20" t="n">
-        <v>26.27137696749292</v>
+        <v>26.27137510044991</v>
       </c>
       <c r="E20" t="n">
-        <v>26.49246706969505</v>
+        <v>26.4924651869397</v>
       </c>
       <c r="F20" t="n">
         <v>212880</v>
@@ -892,16 +892,16 @@
         <v>44180</v>
       </c>
       <c r="B24" t="n">
-        <v>33.00984573364258</v>
+        <v>33.00984191894531</v>
       </c>
       <c r="C24" t="n">
-        <v>33.98072266755544</v>
+        <v>33.9807187406613</v>
       </c>
       <c r="D24" t="n">
-        <v>30.76048335959674</v>
+        <v>30.7604798048412</v>
       </c>
       <c r="E24" t="n">
-        <v>30.76048335959674</v>
+        <v>30.7604798048412</v>
       </c>
       <c r="F24" t="n">
         <v>887803</v>
@@ -912,16 +912,16 @@
         <v>44181</v>
       </c>
       <c r="B25" t="n">
-        <v>32.68301391601562</v>
+        <v>32.68301773071289</v>
       </c>
       <c r="C25" t="n">
-        <v>34.45173835953219</v>
+        <v>34.4517423806715</v>
       </c>
       <c r="D25" t="n">
-        <v>32.10625456033017</v>
+        <v>32.10625830770921</v>
       </c>
       <c r="E25" t="n">
-        <v>33.62505319761509</v>
+        <v>33.62505712226533</v>
       </c>
       <c r="F25" t="n">
         <v>376808</v>
@@ -932,16 +932,16 @@
         <v>44182</v>
       </c>
       <c r="B26" t="n">
-        <v>32.10625839233398</v>
+        <v>32.10625457763672</v>
       </c>
       <c r="C26" t="n">
-        <v>33.64428227520571</v>
+        <v>33.64427827776851</v>
       </c>
       <c r="D26" t="n">
-        <v>31.64484935368452</v>
+        <v>31.64484559380946</v>
       </c>
       <c r="E26" t="n">
-        <v>33.6250572108933</v>
+        <v>33.62505321574033</v>
       </c>
       <c r="F26" t="n">
         <v>258257</v>
@@ -972,16 +972,16 @@
         <v>44186</v>
       </c>
       <c r="B28" t="n">
-        <v>32.18315887451172</v>
+        <v>32.18315505981445</v>
       </c>
       <c r="C28" t="n">
-        <v>33.33667773162143</v>
+        <v>33.33667378019659</v>
       </c>
       <c r="D28" t="n">
-        <v>29.12633427792858</v>
+        <v>29.12633082555934</v>
       </c>
       <c r="E28" t="n">
-        <v>31.86594156356414</v>
+        <v>31.86593778646691</v>
       </c>
       <c r="F28" t="n">
         <v>236079</v>
@@ -992,16 +992,16 @@
         <v>44187</v>
       </c>
       <c r="B29" t="n">
-        <v>33.16364288330078</v>
+        <v>33.16364669799805</v>
       </c>
       <c r="C29" t="n">
-        <v>33.47124761081827</v>
+        <v>33.47125146089823</v>
       </c>
       <c r="D29" t="n">
-        <v>32.59649608138177</v>
+        <v>32.59649983084212</v>
       </c>
       <c r="E29" t="n">
-        <v>33.21170553641675</v>
+        <v>33.21170935664249</v>
       </c>
       <c r="F29" t="n">
         <v>167504</v>
@@ -1032,16 +1032,16 @@
         <v>44193</v>
       </c>
       <c r="B31" t="n">
-        <v>36.21085739135742</v>
+        <v>36.21085357666016</v>
       </c>
       <c r="C31" t="n">
-        <v>36.66265388599569</v>
+        <v>36.66265002370312</v>
       </c>
       <c r="D31" t="n">
-        <v>35.56681025863972</v>
+        <v>35.56680651179074</v>
       </c>
       <c r="E31" t="n">
-        <v>35.56681025863972</v>
+        <v>35.56680651179074</v>
       </c>
       <c r="F31" t="n">
         <v>451822</v>
@@ -1052,16 +1052,16 @@
         <v>44194</v>
       </c>
       <c r="B32" t="n">
-        <v>36.09550476074219</v>
+        <v>36.09550857543945</v>
       </c>
       <c r="C32" t="n">
-        <v>37.06638166531152</v>
+        <v>37.06638558261441</v>
       </c>
       <c r="D32" t="n">
-        <v>35.95131304358604</v>
+        <v>35.95131684304462</v>
       </c>
       <c r="E32" t="n">
-        <v>36.52807241705953</v>
+        <v>36.52807627747203</v>
       </c>
       <c r="F32" t="n">
         <v>337154</v>
@@ -1092,16 +1092,16 @@
         <v>44200</v>
       </c>
       <c r="B34" t="n">
-        <v>34.99966049194336</v>
+        <v>34.99966430664062</v>
       </c>
       <c r="C34" t="n">
-        <v>36.62420073506411</v>
+        <v>36.62420472682393</v>
       </c>
       <c r="D34" t="n">
-        <v>34.98043542972244</v>
+        <v>34.98043924232432</v>
       </c>
       <c r="E34" t="n">
-        <v>36.52807167638402</v>
+        <v>36.52807565766651</v>
       </c>
       <c r="F34" t="n">
         <v>331840</v>
@@ -1112,16 +1112,16 @@
         <v>44201</v>
       </c>
       <c r="B35" t="n">
-        <v>36.13395690917969</v>
+        <v>36.13395309448242</v>
       </c>
       <c r="C35" t="n">
-        <v>36.32621129362743</v>
+        <v>36.32620745863368</v>
       </c>
       <c r="D35" t="n">
-        <v>34.60554560816865</v>
+        <v>34.60554195482727</v>
       </c>
       <c r="E35" t="n">
-        <v>35.45145965313264</v>
+        <v>35.45145591048728</v>
       </c>
       <c r="F35" t="n">
         <v>328059</v>
@@ -1172,16 +1172,16 @@
         <v>44204</v>
       </c>
       <c r="B38" t="n">
-        <v>34.13452529907227</v>
+        <v>34.134521484375</v>
       </c>
       <c r="C38" t="n">
-        <v>35.75906572541368</v>
+        <v>35.75906172916622</v>
       </c>
       <c r="D38" t="n">
-        <v>34.13452529907227</v>
+        <v>34.134521484375</v>
       </c>
       <c r="E38" t="n">
-        <v>35.16308123419719</v>
+        <v>35.16307730455386</v>
       </c>
       <c r="F38" t="n">
         <v>367201</v>
@@ -1272,16 +1272,16 @@
         <v>44211</v>
       </c>
       <c r="B43" t="n">
-        <v>33.94226837158203</v>
+        <v>33.9422721862793</v>
       </c>
       <c r="C43" t="n">
-        <v>35.04772061203977</v>
+        <v>35.0477245509764</v>
       </c>
       <c r="D43" t="n">
-        <v>33.16364216523639</v>
+        <v>33.16364589242556</v>
       </c>
       <c r="E43" t="n">
-        <v>34.60554046537172</v>
+        <v>34.60554435461268</v>
       </c>
       <c r="F43" t="n">
         <v>319883</v>
@@ -1292,16 +1292,16 @@
         <v>44214</v>
       </c>
       <c r="B44" t="n">
-        <v>34.04801177978516</v>
+        <v>34.04800796508789</v>
       </c>
       <c r="C44" t="n">
-        <v>34.5094208103909</v>
+        <v>34.50941694399793</v>
       </c>
       <c r="D44" t="n">
-        <v>33.27900172554335</v>
+        <v>33.27899799700501</v>
       </c>
       <c r="E44" t="n">
-        <v>34.11529950370554</v>
+        <v>34.11529568146945</v>
       </c>
       <c r="F44" t="n">
         <v>117631</v>
@@ -1332,16 +1332,16 @@
         <v>44216</v>
       </c>
       <c r="B46" t="n">
-        <v>34.12490844726562</v>
+        <v>34.12491226196289</v>
       </c>
       <c r="C46" t="n">
-        <v>35.28803968588292</v>
+        <v>35.28804363060232</v>
       </c>
       <c r="D46" t="n">
-        <v>33.66350321275509</v>
+        <v>33.66350697587357</v>
       </c>
       <c r="E46" t="n">
-        <v>34.60554249130722</v>
+        <v>34.60554635973278</v>
       </c>
       <c r="F46" t="n">
         <v>359332</v>
@@ -1372,16 +1372,16 @@
         <v>44218</v>
       </c>
       <c r="B48" t="n">
-        <v>32.95216369628906</v>
+        <v>32.95216751098633</v>
       </c>
       <c r="C48" t="n">
-        <v>33.45202278739948</v>
+        <v>33.45202665996278</v>
       </c>
       <c r="D48" t="n">
-        <v>32.53882112897777</v>
+        <v>32.53882489582456</v>
       </c>
       <c r="E48" t="n">
-        <v>33.19248071115274</v>
+        <v>33.19248455367023</v>
       </c>
       <c r="F48" t="n">
         <v>220341</v>
@@ -1472,16 +1472,16 @@
         <v>44228</v>
       </c>
       <c r="B53" t="n">
-        <v>31.7794246673584</v>
+        <v>31.77942657470703</v>
       </c>
       <c r="C53" t="n">
-        <v>33.1155814640686</v>
+        <v>33.11558345161116</v>
       </c>
       <c r="D53" t="n">
-        <v>31.66407054800669</v>
+        <v>31.66407244843196</v>
       </c>
       <c r="E53" t="n">
-        <v>32.68301382233215</v>
+        <v>32.68301578391271</v>
       </c>
       <c r="F53" t="n">
         <v>610435</v>
@@ -1492,16 +1492,16 @@
         <v>44229</v>
       </c>
       <c r="B54" t="n">
-        <v>32.63494873046875</v>
+        <v>32.63495254516602</v>
       </c>
       <c r="C54" t="n">
-        <v>33.65389204571495</v>
+        <v>33.65389597951643</v>
       </c>
       <c r="D54" t="n">
-        <v>31.97167657096734</v>
+        <v>31.97168030813476</v>
       </c>
       <c r="E54" t="n">
-        <v>33.64427951434755</v>
+        <v>33.64428344702543</v>
       </c>
       <c r="F54" t="n">
         <v>582228</v>
@@ -1532,16 +1532,16 @@
         <v>44231</v>
       </c>
       <c r="B56" t="n">
-        <v>32.68301391601562</v>
+        <v>32.68301773071289</v>
       </c>
       <c r="C56" t="n">
-        <v>34.11529602664492</v>
+        <v>34.11530000851534</v>
       </c>
       <c r="D56" t="n">
-        <v>32.44269689321744</v>
+        <v>32.44270067986538</v>
       </c>
       <c r="E56" t="n">
-        <v>33.06751890394745</v>
+        <v>33.06752276352339</v>
       </c>
       <c r="F56" t="n">
         <v>466743</v>
@@ -1612,16 +1612,16 @@
         <v>44237</v>
       </c>
       <c r="B60" t="n">
-        <v>34.83624649047852</v>
+        <v>34.83625030517578</v>
       </c>
       <c r="C60" t="n">
-        <v>35.33610184184258</v>
+        <v>35.33610571127585</v>
       </c>
       <c r="D60" t="n">
-        <v>34.23064955227608</v>
+        <v>34.23065330065825</v>
       </c>
       <c r="E60" t="n">
-        <v>34.43251269995998</v>
+        <v>34.43251647044691</v>
       </c>
       <c r="F60" t="n">
         <v>186206</v>
@@ -1652,16 +1652,16 @@
         <v>44239</v>
       </c>
       <c r="B62" t="n">
-        <v>34.40367889404297</v>
+        <v>34.4036750793457</v>
       </c>
       <c r="C62" t="n">
-        <v>34.52864555631986</v>
+        <v>34.52864172776623</v>
       </c>
       <c r="D62" t="n">
-        <v>32.673400666573</v>
+        <v>32.67339704372985</v>
       </c>
       <c r="E62" t="n">
-        <v>33.67311897448496</v>
+        <v>33.67311524079254</v>
       </c>
       <c r="F62" t="n">
         <v>218195</v>
@@ -1692,16 +1692,16 @@
         <v>44245</v>
       </c>
       <c r="B64" t="n">
-        <v>37.00870895385742</v>
+        <v>37.00870513916016</v>
       </c>
       <c r="C64" t="n">
-        <v>37.38360144742785</v>
+        <v>37.38359759408829</v>
       </c>
       <c r="D64" t="n">
-        <v>35.71100215049589</v>
+        <v>35.71099846956061</v>
       </c>
       <c r="E64" t="n">
-        <v>36.37427435009953</v>
+        <v>36.37427060079703</v>
       </c>
       <c r="F64" t="n">
         <v>661534</v>
@@ -1812,16 +1812,16 @@
         <v>44253</v>
       </c>
       <c r="B70" t="n">
-        <v>34.57670593261719</v>
+        <v>34.57670974731445</v>
       </c>
       <c r="C70" t="n">
-        <v>37.21057322750037</v>
+        <v>37.21057733278074</v>
       </c>
       <c r="D70" t="n">
-        <v>33.75001700107128</v>
+        <v>33.75002072456356</v>
       </c>
       <c r="E70" t="n">
-        <v>36.5376847961999</v>
+        <v>36.53768882724342</v>
       </c>
       <c r="F70" t="n">
         <v>410022</v>
@@ -1932,16 +1932,16 @@
         <v>44263</v>
       </c>
       <c r="B76" t="n">
-        <v>41.91115951538086</v>
+        <v>41.91115570068359</v>
       </c>
       <c r="C76" t="n">
-        <v>44.60270214463106</v>
+        <v>44.60269808495321</v>
       </c>
       <c r="D76" t="n">
-        <v>40.70957805138659</v>
+        <v>40.70957434605565</v>
       </c>
       <c r="E76" t="n">
-        <v>43.55492493684502</v>
+        <v>43.55492097253444</v>
       </c>
       <c r="F76" t="n">
         <v>1012691</v>
@@ -1952,16 +1952,16 @@
         <v>44264</v>
       </c>
       <c r="B77" t="n">
-        <v>43.50686264038086</v>
+        <v>43.50685882568359</v>
       </c>
       <c r="C77" t="n">
-        <v>43.50686264038086</v>
+        <v>43.50685882568359</v>
       </c>
       <c r="D77" t="n">
-        <v>39.89250193891922</v>
+        <v>39.89249844113039</v>
       </c>
       <c r="E77" t="n">
-        <v>42.29566488693005</v>
+        <v>42.29566117843103</v>
       </c>
       <c r="F77" t="n">
         <v>563525</v>
@@ -1972,16 +1972,16 @@
         <v>44265</v>
       </c>
       <c r="B78" t="n">
-        <v>44.69882583618164</v>
+        <v>44.69882965087891</v>
       </c>
       <c r="C78" t="n">
-        <v>44.89108021255291</v>
+        <v>44.89108404365759</v>
       </c>
       <c r="D78" t="n">
-        <v>43.38189403862891</v>
+        <v>43.38189774093629</v>
       </c>
       <c r="E78" t="n">
-        <v>43.83369051144994</v>
+        <v>43.83369425231464</v>
       </c>
       <c r="F78" t="n">
         <v>425454</v>
@@ -2012,16 +2012,16 @@
         <v>44267</v>
       </c>
       <c r="B80" t="n">
-        <v>45.66009521484375</v>
+        <v>45.66009140014648</v>
       </c>
       <c r="C80" t="n">
-        <v>49.01491000208902</v>
+        <v>49.01490590711195</v>
       </c>
       <c r="D80" t="n">
-        <v>45.18907366630634</v>
+        <v>45.18906989096082</v>
       </c>
       <c r="E80" t="n">
-        <v>47.15005636649431</v>
+        <v>47.15005242731743</v>
       </c>
       <c r="F80" t="n">
         <v>954539</v>
@@ -2052,16 +2052,16 @@
         <v>44271</v>
       </c>
       <c r="B82" t="n">
-        <v>42.75707244873047</v>
+        <v>42.7570686340332</v>
       </c>
       <c r="C82" t="n">
-        <v>45.18907290913018</v>
+        <v>45.18906887745489</v>
       </c>
       <c r="D82" t="n">
-        <v>42.75707244873047</v>
+        <v>42.7570686340332</v>
       </c>
       <c r="E82" t="n">
-        <v>44.50657567458991</v>
+        <v>44.5065717038056</v>
       </c>
       <c r="F82" t="n">
         <v>561175</v>
@@ -2092,16 +2092,16 @@
         <v>44273</v>
       </c>
       <c r="B84" t="n">
-        <v>40.89221954345703</v>
+        <v>40.89221572875977</v>
       </c>
       <c r="C84" t="n">
-        <v>45.0256568951004</v>
+        <v>45.02565269480871</v>
       </c>
       <c r="D84" t="n">
-        <v>40.57500224961562</v>
+        <v>40.57499846451049</v>
       </c>
       <c r="E84" t="n">
-        <v>44.01632982334604</v>
+        <v>44.01632571721106</v>
       </c>
       <c r="F84" t="n">
         <v>572621</v>
@@ -2112,16 +2112,16 @@
         <v>44274</v>
       </c>
       <c r="B85" t="n">
-        <v>42.29566192626953</v>
+        <v>42.2956657409668</v>
       </c>
       <c r="C85" t="n">
-        <v>44.17013174266427</v>
+        <v>44.17013572642225</v>
       </c>
       <c r="D85" t="n">
-        <v>41.4593642170013</v>
+        <v>41.45936795627186</v>
       </c>
       <c r="E85" t="n">
-        <v>41.4593642170013</v>
+        <v>41.45936795627186</v>
       </c>
       <c r="F85" t="n">
         <v>639255</v>
@@ -2212,16 +2212,16 @@
         <v>44281</v>
       </c>
       <c r="B90" t="n">
-        <v>37.87384414672852</v>
+        <v>37.87384796142578</v>
       </c>
       <c r="C90" t="n">
-        <v>40.949891527232</v>
+        <v>40.94989565175231</v>
       </c>
       <c r="D90" t="n">
-        <v>37.56623940867817</v>
+        <v>37.56624319239313</v>
       </c>
       <c r="E90" t="n">
-        <v>39.95978959641457</v>
+        <v>39.95979362121066</v>
       </c>
       <c r="F90" t="n">
         <v>840076</v>
@@ -2312,16 +2312,16 @@
         <v>44291</v>
       </c>
       <c r="B95" t="n">
-        <v>35.68215942382812</v>
+        <v>35.68216323852539</v>
       </c>
       <c r="C95" t="n">
-        <v>37.01831616285484</v>
+        <v>37.01832012039754</v>
       </c>
       <c r="D95" t="n">
-        <v>35.09578756412892</v>
+        <v>35.09579131613852</v>
       </c>
       <c r="E95" t="n">
-        <v>37.01831616285484</v>
+        <v>37.01832012039754</v>
       </c>
       <c r="F95" t="n">
         <v>1091895</v>
@@ -2512,16 +2512,16 @@
         <v>44305</v>
       </c>
       <c r="B105" t="n">
-        <v>41.33439636230469</v>
+        <v>41.33440017700195</v>
       </c>
       <c r="C105" t="n">
-        <v>42.23798551125894</v>
+        <v>42.23798940934727</v>
       </c>
       <c r="D105" t="n">
-        <v>40.20971525467667</v>
+        <v>40.2097189655786</v>
       </c>
       <c r="E105" t="n">
-        <v>40.38274455876383</v>
+        <v>40.38274828563441</v>
       </c>
       <c r="F105" t="n">
         <v>1793083</v>
@@ -2552,16 +2552,16 @@
         <v>44308</v>
       </c>
       <c r="B107" t="n">
-        <v>42.3725700378418</v>
+        <v>42.37256622314453</v>
       </c>
       <c r="C107" t="n">
-        <v>42.77630013488342</v>
+        <v>42.77629628383934</v>
       </c>
       <c r="D107" t="n">
-        <v>41.04602186600353</v>
+        <v>41.0460181707321</v>
       </c>
       <c r="E107" t="n">
-        <v>42.58404574470481</v>
+        <v>42.58404191096891</v>
       </c>
       <c r="F107" t="n">
         <v>1175903</v>
@@ -2572,16 +2572,16 @@
         <v>44309</v>
       </c>
       <c r="B108" t="n">
-        <v>44.09323501586914</v>
+        <v>44.09323120117188</v>
       </c>
       <c r="C108" t="n">
-        <v>44.31432325105797</v>
+        <v>44.3143194172334</v>
       </c>
       <c r="D108" t="n">
-        <v>42.38218184069201</v>
+        <v>42.38217817402538</v>
       </c>
       <c r="E108" t="n">
-        <v>42.82436205864548</v>
+        <v>42.82435835372392</v>
       </c>
       <c r="F108" t="n">
         <v>1899574</v>
@@ -2612,16 +2612,16 @@
         <v>44313</v>
       </c>
       <c r="B110" t="n">
-        <v>43.7375602722168</v>
+        <v>43.73756408691406</v>
       </c>
       <c r="C110" t="n">
-        <v>44.31431963823069</v>
+        <v>44.31432350323168</v>
       </c>
       <c r="D110" t="n">
-        <v>43.04545053203033</v>
+        <v>43.04545428636325</v>
       </c>
       <c r="E110" t="n">
-        <v>43.40111793330461</v>
+        <v>43.40112171865809</v>
       </c>
       <c r="F110" t="n">
         <v>1146163</v>
@@ -2732,16 +2732,16 @@
         <v>44321</v>
       </c>
       <c r="B116" t="n">
-        <v>39.74831390380859</v>
+        <v>39.74831008911133</v>
       </c>
       <c r="C116" t="n">
-        <v>40.64229060912697</v>
+        <v>40.6422867086336</v>
       </c>
       <c r="D116" t="n">
-        <v>39.0754291787498</v>
+        <v>39.07542542863015</v>
       </c>
       <c r="E116" t="n">
-        <v>39.89250188164586</v>
+        <v>39.89249805311069</v>
       </c>
       <c r="F116" t="n">
         <v>3650961</v>
@@ -2772,16 +2772,16 @@
         <v>44323</v>
       </c>
       <c r="B118" t="n">
-        <v>38.83510971069336</v>
+        <v>38.83511352539062</v>
       </c>
       <c r="C118" t="n">
-        <v>39.99824098294782</v>
+        <v>39.99824491189721</v>
       </c>
       <c r="D118" t="n">
-        <v>37.51817793834604</v>
+        <v>37.51818162368365</v>
       </c>
       <c r="E118" t="n">
-        <v>39.66179864141913</v>
+        <v>39.66180253732045</v>
       </c>
       <c r="F118" t="n">
         <v>2227429</v>
@@ -2832,16 +2832,16 @@
         <v>44328</v>
       </c>
       <c r="B121" t="n">
-        <v>37.05677032470703</v>
+        <v>37.05676651000977</v>
       </c>
       <c r="C121" t="n">
-        <v>38.70053196862062</v>
+        <v>38.70052798471127</v>
       </c>
       <c r="D121" t="n">
-        <v>37.05677032470703</v>
+        <v>37.05676651000977</v>
       </c>
       <c r="E121" t="n">
-        <v>37.8161715649591</v>
+        <v>37.81616767208757</v>
       </c>
       <c r="F121" t="n">
         <v>783049</v>
@@ -2892,16 +2892,16 @@
         <v>44333</v>
       </c>
       <c r="B124" t="n">
-        <v>36.43194580078125</v>
+        <v>36.43194961547852</v>
       </c>
       <c r="C124" t="n">
-        <v>37.13366805612294</v>
+        <v>37.13367194429578</v>
       </c>
       <c r="D124" t="n">
-        <v>35.93208669563144</v>
+        <v>35.93209045798972</v>
       </c>
       <c r="E124" t="n">
-        <v>36.52807111039643</v>
+        <v>36.52807493515874</v>
       </c>
       <c r="F124" t="n">
         <v>946466</v>
@@ -2912,16 +2912,16 @@
         <v>44334</v>
       </c>
       <c r="B125" t="n">
-        <v>35.14385604858398</v>
+        <v>35.14385223388672</v>
       </c>
       <c r="C125" t="n">
-        <v>36.91258445174329</v>
+        <v>36.91258044505902</v>
       </c>
       <c r="D125" t="n">
-        <v>34.59593422023043</v>
+        <v>34.59593046500746</v>
       </c>
       <c r="E125" t="n">
-        <v>36.52807567013412</v>
+        <v>36.52807170518645</v>
       </c>
       <c r="F125" t="n">
         <v>2070451</v>
@@ -2952,16 +2952,16 @@
         <v>44336</v>
       </c>
       <c r="B127" t="n">
-        <v>34.63438415527344</v>
+        <v>34.63438034057617</v>
       </c>
       <c r="C127" t="n">
-        <v>35.26881876953347</v>
+        <v>35.26881488495837</v>
       </c>
       <c r="D127" t="n">
-        <v>34.51903376998102</v>
+        <v>34.51902996798866</v>
       </c>
       <c r="E127" t="n">
-        <v>34.51903376998102</v>
+        <v>34.51902996798866</v>
       </c>
       <c r="F127" t="n">
         <v>943604</v>
@@ -3012,16 +3012,16 @@
         <v>44341</v>
       </c>
       <c r="B130" t="n">
-        <v>37.29708862304688</v>
+        <v>37.29708480834961</v>
       </c>
       <c r="C130" t="n">
-        <v>38.78704981148397</v>
+        <v>38.78704584439543</v>
       </c>
       <c r="D130" t="n">
-        <v>37.22980089947328</v>
+        <v>37.22979709165812</v>
       </c>
       <c r="E130" t="n">
-        <v>37.52779313716071</v>
+        <v>37.52778929886728</v>
       </c>
       <c r="F130" t="n">
         <v>1731150</v>
@@ -3092,16 +3092,16 @@
         <v>44347</v>
       </c>
       <c r="B134" t="n">
-        <v>39.38303375244141</v>
+        <v>39.38302993774414</v>
       </c>
       <c r="C134" t="n">
-        <v>40.11359366504992</v>
+        <v>40.11358977958957</v>
       </c>
       <c r="D134" t="n">
-        <v>39.02736632794579</v>
+        <v>39.02736254769899</v>
       </c>
       <c r="E134" t="n">
-        <v>39.39264628425005</v>
+        <v>39.3926424686217</v>
       </c>
       <c r="F134" t="n">
         <v>715598</v>
@@ -3192,16 +3192,16 @@
         <v>44355</v>
       </c>
       <c r="B139" t="n">
-        <v>38.4602165222168</v>
+        <v>38.46022033691406</v>
       </c>
       <c r="C139" t="n">
-        <v>38.85433404388245</v>
+        <v>38.85433789767048</v>
       </c>
       <c r="D139" t="n">
-        <v>37.72004038668688</v>
+        <v>37.72004412796937</v>
       </c>
       <c r="E139" t="n">
-        <v>38.43137892899068</v>
+        <v>38.43138274082768</v>
       </c>
       <c r="F139" t="n">
         <v>978352</v>
@@ -3212,16 +3212,16 @@
         <v>44356</v>
       </c>
       <c r="B140" t="n">
-        <v>38.01803588867188</v>
+        <v>38.01803207397461</v>
       </c>
       <c r="C140" t="n">
-        <v>38.66208302162527</v>
+        <v>38.66207914230487</v>
       </c>
       <c r="D140" t="n">
-        <v>37.29708850045856</v>
+        <v>37.29708475810054</v>
       </c>
       <c r="E140" t="n">
-        <v>38.48905744729046</v>
+        <v>38.48905358533129</v>
       </c>
       <c r="F140" t="n">
         <v>837521</v>
@@ -3332,16 +3332,16 @@
         <v>44364</v>
       </c>
       <c r="B146" t="n">
-        <v>42.4879150390625</v>
+        <v>42.48791885375977</v>
       </c>
       <c r="C146" t="n">
-        <v>44.0067136610316</v>
+        <v>44.00671761209134</v>
       </c>
       <c r="D146" t="n">
-        <v>41.62277601425852</v>
+        <v>41.62277975128091</v>
       </c>
       <c r="E146" t="n">
-        <v>42.95893654890009</v>
+        <v>42.95894040588714</v>
       </c>
       <c r="F146" t="n">
         <v>1582144</v>
@@ -3372,16 +3372,16 @@
         <v>44368</v>
       </c>
       <c r="B148" t="n">
-        <v>46.96741485595703</v>
+        <v>46.96741104125977</v>
       </c>
       <c r="C148" t="n">
-        <v>47.24618202489792</v>
+        <v>47.24617818755916</v>
       </c>
       <c r="D148" t="n">
-        <v>43.53569979030122</v>
+        <v>43.53569625432814</v>
       </c>
       <c r="E148" t="n">
-        <v>43.73756295749668</v>
+        <v>43.73755940512824</v>
       </c>
       <c r="F148" t="n">
         <v>2655439</v>
@@ -3452,16 +3452,16 @@
         <v>44372</v>
       </c>
       <c r="B152" t="n">
-        <v>44.45851135253906</v>
+        <v>44.45851516723633</v>
       </c>
       <c r="C152" t="n">
-        <v>44.98720431506052</v>
+        <v>44.9872081751215</v>
       </c>
       <c r="D152" t="n">
-        <v>43.97787729834627</v>
+        <v>43.97788107180344</v>
       </c>
       <c r="E152" t="n">
-        <v>44.98720431506052</v>
+        <v>44.9872081751215</v>
       </c>
       <c r="F152" t="n">
         <v>1347904</v>
@@ -3472,16 +3472,16 @@
         <v>44375</v>
       </c>
       <c r="B153" t="n">
-        <v>44.5354118347168</v>
+        <v>44.53541564941406</v>
       </c>
       <c r="C153" t="n">
-        <v>44.64114967825854</v>
+        <v>44.64115350201283</v>
       </c>
       <c r="D153" t="n">
-        <v>43.20886378695175</v>
+        <v>43.20886748802305</v>
       </c>
       <c r="E153" t="n">
-        <v>44.13168177543641</v>
+        <v>44.13168555555202</v>
       </c>
       <c r="F153" t="n">
         <v>1110393</v>
@@ -3512,16 +3512,16 @@
         <v>44377</v>
       </c>
       <c r="B155" t="n">
-        <v>43.58376312255859</v>
+        <v>43.58375930786133</v>
       </c>
       <c r="C155" t="n">
-        <v>44.45851476998166</v>
+        <v>44.45851087872119</v>
       </c>
       <c r="D155" t="n">
-        <v>43.50686286720073</v>
+        <v>43.50685905923421</v>
       </c>
       <c r="E155" t="n">
-        <v>44.21819772441255</v>
+        <v>44.21819385418598</v>
       </c>
       <c r="F155" t="n">
         <v>1274116</v>
@@ -3572,16 +3572,16 @@
         <v>44382</v>
       </c>
       <c r="B158" t="n">
-        <v>45.04488372802734</v>
+        <v>45.04488754272461</v>
       </c>
       <c r="C158" t="n">
-        <v>46.21762753484401</v>
+        <v>46.21763144885693</v>
       </c>
       <c r="D158" t="n">
-        <v>44.42967048319475</v>
+        <v>44.42967424579171</v>
       </c>
       <c r="E158" t="n">
-        <v>44.98720479275436</v>
+        <v>44.98720860256699</v>
       </c>
       <c r="F158" t="n">
         <v>3391068</v>
@@ -3592,16 +3592,16 @@
         <v>44383</v>
       </c>
       <c r="B159" t="n">
-        <v>44.37199401855469</v>
+        <v>44.37199783325195</v>
       </c>
       <c r="C159" t="n">
-        <v>45.94847158903642</v>
+        <v>45.94847553926477</v>
       </c>
       <c r="D159" t="n">
-        <v>43.75678453900221</v>
+        <v>43.75678830080941</v>
       </c>
       <c r="E159" t="n">
-        <v>45.7850548143543</v>
+        <v>45.78505875053358</v>
       </c>
       <c r="F159" t="n">
         <v>1563442</v>
@@ -3652,16 +3652,16 @@
         <v>44389</v>
       </c>
       <c r="B162" t="n">
-        <v>44.72766876220703</v>
+        <v>44.72766494750977</v>
       </c>
       <c r="C162" t="n">
-        <v>45.75622090541913</v>
+        <v>45.75621700299953</v>
       </c>
       <c r="D162" t="n">
-        <v>44.08361789020423</v>
+        <v>44.08361413043626</v>
       </c>
       <c r="E162" t="n">
-        <v>45.75622090541913</v>
+        <v>45.75621700299953</v>
       </c>
       <c r="F162" t="n">
         <v>1597780</v>
@@ -3732,16 +3732,16 @@
         <v>44393</v>
       </c>
       <c r="B166" t="n">
-        <v>41.70928955078125</v>
+        <v>41.70929336547852</v>
       </c>
       <c r="C166" t="n">
-        <v>41.91115645117827</v>
+        <v>41.91116028433812</v>
       </c>
       <c r="D166" t="n">
-        <v>40.45003298811638</v>
+        <v>40.45003668764308</v>
       </c>
       <c r="E166" t="n">
-        <v>41.62277677100059</v>
+        <v>41.62278057778546</v>
       </c>
       <c r="F166" t="n">
         <v>1471156</v>
@@ -3752,16 +3752,16 @@
         <v>44396</v>
       </c>
       <c r="B167" t="n">
-        <v>40.22894287109375</v>
+        <v>40.22894668579102</v>
       </c>
       <c r="C167" t="n">
-        <v>41.05562800061862</v>
+        <v>41.05563189370605</v>
       </c>
       <c r="D167" t="n">
-        <v>39.50799183094843</v>
+        <v>39.50799557728174</v>
       </c>
       <c r="E167" t="n">
-        <v>40.46925613690023</v>
+        <v>40.46925997438512</v>
       </c>
       <c r="F167" t="n">
         <v>1632835</v>
@@ -3792,16 +3792,16 @@
         <v>44398</v>
       </c>
       <c r="B169" t="n">
-        <v>40.45964431762695</v>
+        <v>40.45964813232422</v>
       </c>
       <c r="C169" t="n">
-        <v>41.40168732645247</v>
+        <v>41.40169122996932</v>
       </c>
       <c r="D169" t="n">
-        <v>40.22894357839657</v>
+        <v>40.22894737134245</v>
       </c>
       <c r="E169" t="n">
-        <v>40.37313154041556</v>
+        <v>40.37313534695605</v>
       </c>
       <c r="F169" t="n">
         <v>985812</v>
@@ -3812,16 +3812,16 @@
         <v>44399</v>
       </c>
       <c r="B170" t="n">
-        <v>40.89221954345703</v>
+        <v>40.89221572875977</v>
       </c>
       <c r="C170" t="n">
-        <v>41.15176164706832</v>
+        <v>41.15175780815924</v>
       </c>
       <c r="D170" t="n">
-        <v>40.3923603996445</v>
+        <v>40.39235663157741</v>
       </c>
       <c r="E170" t="n">
-        <v>41.08447017755746</v>
+        <v>41.08446634492577</v>
       </c>
       <c r="F170" t="n">
         <v>757704</v>
@@ -3832,16 +3832,16 @@
         <v>44400</v>
       </c>
       <c r="B171" t="n">
-        <v>40.56538772583008</v>
+        <v>40.56539154052734</v>
       </c>
       <c r="C171" t="n">
-        <v>40.86337994162768</v>
+        <v>40.8633837843476</v>
       </c>
       <c r="D171" t="n">
-        <v>40.20010404382616</v>
+        <v>40.20010782417279</v>
       </c>
       <c r="E171" t="n">
-        <v>40.6230629132279</v>
+        <v>40.62306673334884</v>
       </c>
       <c r="F171" t="n">
         <v>715496</v>
@@ -3872,16 +3872,16 @@
         <v>44404</v>
       </c>
       <c r="B173" t="n">
-        <v>38.54673004150391</v>
+        <v>38.54673385620117</v>
       </c>
       <c r="C173" t="n">
-        <v>40.84415499320262</v>
+        <v>40.84415903525979</v>
       </c>
       <c r="D173" t="n">
-        <v>38.32563807495276</v>
+        <v>38.32564186777011</v>
       </c>
       <c r="E173" t="n">
-        <v>40.62306302665147</v>
+        <v>40.62306704682872</v>
       </c>
       <c r="F173" t="n">
         <v>1543819</v>
@@ -3932,16 +3932,16 @@
         <v>44407</v>
       </c>
       <c r="B176" t="n">
-        <v>37.2105712890625</v>
+        <v>37.21057510375977</v>
       </c>
       <c r="C176" t="n">
-        <v>38.26796091589321</v>
+        <v>38.26796483899034</v>
       </c>
       <c r="D176" t="n">
-        <v>36.33581974675896</v>
+        <v>36.33582347177977</v>
       </c>
       <c r="E176" t="n">
-        <v>37.5662386749276</v>
+        <v>37.56624252608663</v>
       </c>
       <c r="F176" t="n">
         <v>1168442</v>
@@ -3952,16 +3952,16 @@
         <v>44410</v>
       </c>
       <c r="B177" t="n">
-        <v>39.04658889770508</v>
+        <v>39.04659271240234</v>
       </c>
       <c r="C177" t="n">
-        <v>40.3442955992922</v>
+        <v>40.34429954077027</v>
       </c>
       <c r="D177" t="n">
-        <v>38.19106237864987</v>
+        <v>38.19106610976557</v>
       </c>
       <c r="E177" t="n">
-        <v>39.17155180323623</v>
+        <v>39.17155563014188</v>
       </c>
       <c r="F177" t="n">
         <v>3352028</v>
@@ -4052,16 +4052,16 @@
         <v>44417</v>
       </c>
       <c r="B182" t="n">
-        <v>37.10483169555664</v>
+        <v>37.10483551025391</v>
       </c>
       <c r="C182" t="n">
-        <v>37.44127403795907</v>
+        <v>37.44127788724551</v>
       </c>
       <c r="D182" t="n">
-        <v>35.94170042028153</v>
+        <v>35.94170411539885</v>
       </c>
       <c r="E182" t="n">
-        <v>36.1147297309109</v>
+        <v>36.11473344381713</v>
       </c>
       <c r="F182" t="n">
         <v>1206460</v>
@@ -4092,16 +4092,16 @@
         <v>44419</v>
       </c>
       <c r="B184" t="n">
-        <v>36.43194580078125</v>
+        <v>36.43194961547852</v>
       </c>
       <c r="C184" t="n">
-        <v>36.74916307008678</v>
+        <v>36.74916691799907</v>
       </c>
       <c r="D184" t="n">
-        <v>36.09550346955268</v>
+        <v>36.09550724902192</v>
       </c>
       <c r="E184" t="n">
-        <v>36.47039592462733</v>
+        <v>36.4703997433506</v>
       </c>
       <c r="F184" t="n">
         <v>786524</v>
@@ -4112,16 +4112,16 @@
         <v>44420</v>
       </c>
       <c r="B185" t="n">
-        <v>36.12434387207031</v>
+        <v>36.12434005737305</v>
       </c>
       <c r="C185" t="n">
-        <v>36.95103284178433</v>
+        <v>36.95102893978947</v>
       </c>
       <c r="D185" t="n">
-        <v>35.4706842206967</v>
+        <v>35.47068047502529</v>
       </c>
       <c r="E185" t="n">
-        <v>36.19163159403436</v>
+        <v>36.19162777223157</v>
       </c>
       <c r="F185" t="n">
         <v>689639</v>
@@ -4132,16 +4132,16 @@
         <v>44421</v>
       </c>
       <c r="B186" t="n">
-        <v>34.75934219360352</v>
+        <v>34.75934600830078</v>
       </c>
       <c r="C186" t="n">
-        <v>35.97053605946554</v>
+        <v>35.97054000708643</v>
       </c>
       <c r="D186" t="n">
-        <v>34.59592917071041</v>
+        <v>34.59593296747376</v>
       </c>
       <c r="E186" t="n">
-        <v>35.69177266747142</v>
+        <v>35.69177658449917</v>
       </c>
       <c r="F186" t="n">
         <v>915908</v>
@@ -4252,16 +4252,16 @@
         <v>44431</v>
       </c>
       <c r="B192" t="n">
-        <v>33.16364288330078</v>
+        <v>33.16364669799805</v>
       </c>
       <c r="C192" t="n">
-        <v>34.42289938524034</v>
+        <v>34.42290334478545</v>
       </c>
       <c r="D192" t="n">
-        <v>32.77913791079774</v>
+        <v>32.77914168126674</v>
       </c>
       <c r="E192" t="n">
-        <v>33.740402215843</v>
+        <v>33.74040609688286</v>
       </c>
       <c r="F192" t="n">
         <v>2084044</v>
@@ -4272,16 +4272,16 @@
         <v>44432</v>
       </c>
       <c r="B193" t="n">
-        <v>35.43223571777344</v>
+        <v>35.43223190307617</v>
       </c>
       <c r="C193" t="n">
-        <v>35.43223571777344</v>
+        <v>35.43223190307617</v>
       </c>
       <c r="D193" t="n">
-        <v>33.47125292620207</v>
+        <v>33.47124932262768</v>
       </c>
       <c r="E193" t="n">
-        <v>33.93266196453976</v>
+        <v>33.93265831128927</v>
       </c>
       <c r="F193" t="n">
         <v>1429663</v>
@@ -4332,16 +4332,16 @@
         <v>44435</v>
       </c>
       <c r="B196" t="n">
-        <v>36.43194580078125</v>
+        <v>36.43194961547852</v>
       </c>
       <c r="C196" t="n">
-        <v>36.66265029143312</v>
+        <v>36.66265413028687</v>
       </c>
       <c r="D196" t="n">
-        <v>35.02849754252244</v>
+        <v>35.02850121026817</v>
       </c>
       <c r="E196" t="n">
-        <v>35.75906113832411</v>
+        <v>35.75906488256532</v>
       </c>
       <c r="F196" t="n">
         <v>2701327</v>
@@ -4392,16 +4392,16 @@
         <v>44440</v>
       </c>
       <c r="B199" t="n">
-        <v>36.00899124145508</v>
+        <v>36.00899505615234</v>
       </c>
       <c r="C199" t="n">
-        <v>37.22979768253502</v>
+        <v>37.2298016265613</v>
       </c>
       <c r="D199" t="n">
-        <v>35.47068200422877</v>
+        <v>35.47068576189898</v>
       </c>
       <c r="E199" t="n">
-        <v>37.10483103054919</v>
+        <v>37.10483496133683</v>
       </c>
       <c r="F199" t="n">
         <v>1150659</v>
@@ -4712,16 +4712,16 @@
         <v>44463</v>
       </c>
       <c r="B215" t="n">
-        <v>34.54786682128906</v>
+        <v>34.54787063598633</v>
       </c>
       <c r="C215" t="n">
-        <v>35.65331911097231</v>
+        <v>35.65332304773112</v>
       </c>
       <c r="D215" t="n">
-        <v>33.88459095038866</v>
+        <v>33.88459469184851</v>
       </c>
       <c r="E215" t="n">
-        <v>34.46135404370111</v>
+        <v>34.46135784884584</v>
       </c>
       <c r="F215" t="n">
         <v>2639905</v>
@@ -4852,16 +4852,16 @@
         <v>44474</v>
       </c>
       <c r="B222" t="n">
-        <v>41.23827362060547</v>
+        <v>41.2382698059082</v>
       </c>
       <c r="C222" t="n">
-        <v>43.07428962557536</v>
+        <v>43.07428564103963</v>
       </c>
       <c r="D222" t="n">
-        <v>40.9498939275561</v>
+        <v>40.94989013953506</v>
       </c>
       <c r="E222" t="n">
-        <v>41.82464553821999</v>
+        <v>41.82464166928109</v>
       </c>
       <c r="F222" t="n">
         <v>3033780</v>
@@ -4952,16 +4952,16 @@
         <v>44482</v>
       </c>
       <c r="B227" t="n">
-        <v>39.66179656982422</v>
+        <v>39.66180038452148</v>
       </c>
       <c r="C227" t="n">
-        <v>40.05591407830239</v>
+        <v>40.05591793090613</v>
       </c>
       <c r="D227" t="n">
-        <v>38.88317033604628</v>
+        <v>38.88317407585477</v>
       </c>
       <c r="E227" t="n">
-        <v>39.43109208415942</v>
+        <v>39.43109587666738</v>
       </c>
       <c r="F227" t="n">
         <v>1130628</v>
@@ -5012,16 +5012,16 @@
         <v>44487</v>
       </c>
       <c r="B230" t="n">
-        <v>39.87327194213867</v>
+        <v>39.87327575683594</v>
       </c>
       <c r="C230" t="n">
-        <v>41.44974945917212</v>
+        <v>41.44975342469183</v>
       </c>
       <c r="D230" t="n">
-        <v>39.18116223800101</v>
+        <v>39.18116598648377</v>
       </c>
       <c r="E230" t="n">
-        <v>39.72908398193304</v>
+        <v>39.72908778283576</v>
       </c>
       <c r="F230" t="n">
         <v>2573169</v>
@@ -5032,16 +5032,16 @@
         <v>44488</v>
       </c>
       <c r="B231" t="n">
-        <v>37.58546447753906</v>
+        <v>37.58546829223633</v>
       </c>
       <c r="C231" t="n">
-        <v>40.08475250621378</v>
+        <v>40.08475657457366</v>
       </c>
       <c r="D231" t="n">
-        <v>36.86451716082918</v>
+        <v>36.86452090235465</v>
       </c>
       <c r="E231" t="n">
-        <v>39.57528087049455</v>
+        <v>39.57528488714614</v>
       </c>
       <c r="F231" t="n">
         <v>2915331</v>
@@ -5072,16 +5072,16 @@
         <v>44490</v>
       </c>
       <c r="B233" t="n">
-        <v>34.41328811645508</v>
+        <v>34.41329193115234</v>
       </c>
       <c r="C233" t="n">
-        <v>36.09550352264783</v>
+        <v>36.09550752381791</v>
       </c>
       <c r="D233" t="n">
-        <v>33.48086136908995</v>
+        <v>33.48086508042814</v>
       </c>
       <c r="E233" t="n">
-        <v>35.62448200968972</v>
+        <v>35.62448595864728</v>
       </c>
       <c r="F233" t="n">
         <v>3113087</v>
@@ -5092,16 +5092,16 @@
         <v>44491</v>
       </c>
       <c r="B234" t="n">
-        <v>32.63494873046875</v>
+        <v>32.63495254516602</v>
       </c>
       <c r="C234" t="n">
-        <v>34.06723464208851</v>
+        <v>34.06723862420559</v>
       </c>
       <c r="D234" t="n">
-        <v>31.04886231697067</v>
+        <v>31.04886594627039</v>
       </c>
       <c r="E234" t="n">
-        <v>33.63466698298016</v>
+        <v>33.63467091453443</v>
       </c>
       <c r="F234" t="n">
         <v>4894520</v>
@@ -5112,16 +5112,16 @@
         <v>44494</v>
       </c>
       <c r="B235" t="n">
-        <v>36.8470573425293</v>
+        <v>36.84706115722656</v>
       </c>
       <c r="C235" t="n">
-        <v>37.3112732591762</v>
+        <v>37.31127712193275</v>
       </c>
       <c r="D235" t="n">
-        <v>32.95925887799699</v>
+        <v>32.95926229019877</v>
       </c>
       <c r="E235" t="n">
-        <v>32.95925887799699</v>
+        <v>32.95926229019877</v>
       </c>
       <c r="F235" t="n">
         <v>3449995</v>
@@ -5152,16 +5152,16 @@
         <v>44496</v>
       </c>
       <c r="B237" t="n">
-        <v>35.29000854492188</v>
+        <v>35.29000473022461</v>
       </c>
       <c r="C237" t="n">
-        <v>36.07337184605893</v>
+        <v>36.07336794668348</v>
       </c>
       <c r="D237" t="n">
-        <v>34.47763151058894</v>
+        <v>34.47762778370612</v>
       </c>
       <c r="E237" t="n">
-        <v>36.07337184605893</v>
+        <v>36.07336794668348</v>
       </c>
       <c r="F237" t="n">
         <v>2270538</v>
@@ -5272,16 +5272,16 @@
         <v>44505</v>
       </c>
       <c r="B243" t="n">
-        <v>34.33255767822266</v>
+        <v>34.33256149291992</v>
       </c>
       <c r="C243" t="n">
-        <v>35.80257411368536</v>
+        <v>35.80257809171644</v>
       </c>
       <c r="D243" t="n">
-        <v>31.73102080869616</v>
+        <v>31.73102433433615</v>
       </c>
       <c r="E243" t="n">
-        <v>33.17202351532898</v>
+        <v>33.17202720107906</v>
       </c>
       <c r="F243" t="n">
         <v>9166770</v>
@@ -5312,16 +5312,16 @@
         <v>44509</v>
       </c>
       <c r="B245" t="n">
-        <v>34.50664138793945</v>
+        <v>34.50664520263672</v>
       </c>
       <c r="C245" t="n">
-        <v>35.1062534768846</v>
+        <v>35.10625735786877</v>
       </c>
       <c r="D245" t="n">
-        <v>32.63044017132788</v>
+        <v>32.63044377861175</v>
       </c>
       <c r="E245" t="n">
-        <v>33.89736055406007</v>
+        <v>33.89736430140155</v>
       </c>
       <c r="F245" t="n">
         <v>7032350</v>
@@ -5372,16 +5372,16 @@
         <v>44512</v>
       </c>
       <c r="B248" t="n">
-        <v>30.94766044616699</v>
+        <v>30.94766235351562</v>
       </c>
       <c r="C248" t="n">
-        <v>33.11399707089411</v>
+        <v>33.11399911175717</v>
       </c>
       <c r="D248" t="n">
-        <v>30.69620937113922</v>
+        <v>30.69621126299056</v>
       </c>
       <c r="E248" t="n">
-        <v>32.10819651835855</v>
+        <v>32.10819849723269</v>
       </c>
       <c r="F248" t="n">
         <v>3403064</v>
@@ -5552,16 +5552,16 @@
         <v>44526</v>
       </c>
       <c r="B257" t="n">
-        <v>26.69235801696777</v>
+        <v>26.69235992431641</v>
       </c>
       <c r="C257" t="n">
-        <v>27.61111551515892</v>
+        <v>27.61111748815896</v>
       </c>
       <c r="D257" t="n">
-        <v>25.85096734243463</v>
+        <v>25.85096918966023</v>
       </c>
       <c r="E257" t="n">
-        <v>26.59564620826666</v>
+        <v>26.59564810870458</v>
       </c>
       <c r="F257" t="n">
         <v>3664026</v>
@@ -5592,16 +5592,16 @@
         <v>44530</v>
       </c>
       <c r="B259" t="n">
-        <v>26.71169853210449</v>
+        <v>26.71170043945312</v>
       </c>
       <c r="C259" t="n">
-        <v>26.71169853210449</v>
+        <v>26.71170043945312</v>
       </c>
       <c r="D259" t="n">
-        <v>25.48346440355603</v>
+        <v>25.48346622320262</v>
       </c>
       <c r="E259" t="n">
-        <v>26.53761803066504</v>
+        <v>26.53761992558345</v>
       </c>
       <c r="F259" t="n">
         <v>4757647</v>
@@ -5612,16 +5612,16 @@
         <v>44531</v>
       </c>
       <c r="B260" t="n">
-        <v>26.69235801696777</v>
+        <v>26.69235992431641</v>
       </c>
       <c r="C260" t="n">
-        <v>28.01730398743094</v>
+        <v>28.01730598945588</v>
       </c>
       <c r="D260" t="n">
-        <v>26.32485389341864</v>
+        <v>26.32485577450663</v>
       </c>
       <c r="E260" t="n">
-        <v>27.17591518668557</v>
+        <v>27.17591712858762</v>
       </c>
       <c r="F260" t="n">
         <v>3467467</v>
@@ -5752,16 +5752,16 @@
         <v>44540</v>
       </c>
       <c r="B267" t="n">
-        <v>29.43896293640137</v>
+        <v>29.43896102905273</v>
       </c>
       <c r="C267" t="n">
-        <v>29.76778272429381</v>
+        <v>29.76778079564096</v>
       </c>
       <c r="D267" t="n">
-        <v>28.76198212238038</v>
+        <v>28.76198025889329</v>
       </c>
       <c r="E267" t="n">
-        <v>29.57435909920557</v>
+        <v>29.57435718308462</v>
       </c>
       <c r="F267" t="n">
         <v>1281952</v>
@@ -5832,16 +5832,16 @@
         <v>44546</v>
       </c>
       <c r="B271" t="n">
-        <v>30.62851333618164</v>
+        <v>30.62851524353027</v>
       </c>
       <c r="C271" t="n">
-        <v>30.86062130141829</v>
+        <v>30.86062322322113</v>
       </c>
       <c r="D271" t="n">
-        <v>29.25521052973079</v>
+        <v>29.25521235155887</v>
       </c>
       <c r="E271" t="n">
-        <v>29.4969891136642</v>
+        <v>29.49699095054871</v>
       </c>
       <c r="F271" t="n">
         <v>3477726</v>
@@ -5952,16 +5952,16 @@
         <v>44557</v>
       </c>
       <c r="B277" t="n">
-        <v>30.72522354125977</v>
+        <v>30.7252254486084</v>
       </c>
       <c r="C277" t="n">
-        <v>31.01535896880716</v>
+        <v>31.01536089416671</v>
       </c>
       <c r="D277" t="n">
-        <v>29.98054654550914</v>
+        <v>29.98054840663</v>
       </c>
       <c r="E277" t="n">
-        <v>29.98054654550914</v>
+        <v>29.98054840663</v>
       </c>
       <c r="F277" t="n">
         <v>1273927</v>
@@ -6132,16 +6132,16 @@
         <v>44571</v>
       </c>
       <c r="B286" t="n">
-        <v>33.37511444091797</v>
+        <v>33.37511825561523</v>
       </c>
       <c r="C286" t="n">
-        <v>33.89735778992546</v>
+        <v>33.89736166431392</v>
       </c>
       <c r="D286" t="n">
-        <v>32.24359030771443</v>
+        <v>32.24359399308115</v>
       </c>
       <c r="E286" t="n">
-        <v>32.37898645393302</v>
+        <v>32.3789901547752</v>
       </c>
       <c r="F286" t="n">
         <v>2829132</v>
@@ -6152,16 +6152,16 @@
         <v>44572</v>
       </c>
       <c r="B287" t="n">
-        <v>35.10625457763672</v>
+        <v>35.10625076293945</v>
       </c>
       <c r="C287" t="n">
-        <v>35.63816673084244</v>
+        <v>35.63816285834681</v>
       </c>
       <c r="D287" t="n">
-        <v>33.18169458570739</v>
+        <v>33.18169098013564</v>
       </c>
       <c r="E287" t="n">
-        <v>33.55886933935793</v>
+        <v>33.55886569280182</v>
       </c>
       <c r="F287" t="n">
         <v>3953735</v>
@@ -6172,16 +6172,16 @@
         <v>44573</v>
       </c>
       <c r="B288" t="n">
-        <v>34.89348983764648</v>
+        <v>34.89348602294922</v>
       </c>
       <c r="C288" t="n">
-        <v>35.98632787872025</v>
+        <v>35.98632394454952</v>
       </c>
       <c r="D288" t="n">
-        <v>34.13914032772324</v>
+        <v>34.13913659549451</v>
       </c>
       <c r="E288" t="n">
-        <v>35.34803329265463</v>
+        <v>35.34802942826484</v>
       </c>
       <c r="F288" t="n">
         <v>3302601</v>
@@ -6292,16 +6292,16 @@
         <v>44581</v>
       </c>
       <c r="B294" t="n">
-        <v>35.29967498779297</v>
+        <v>35.2996711730957</v>
       </c>
       <c r="C294" t="n">
-        <v>36.17007943172774</v>
+        <v>36.17007552296929</v>
       </c>
       <c r="D294" t="n">
-        <v>34.98052769103708</v>
+        <v>34.98052391082881</v>
       </c>
       <c r="E294" t="n">
-        <v>35.87027337331519</v>
+        <v>35.8702694969556</v>
       </c>
       <c r="F294" t="n">
         <v>3650414</v>
@@ -6332,16 +6332,16 @@
         <v>44585</v>
       </c>
       <c r="B296" t="n">
-        <v>34.35190200805664</v>
+        <v>34.35190582275391</v>
       </c>
       <c r="C296" t="n">
-        <v>35.3190162904272</v>
+        <v>35.31902021252021</v>
       </c>
       <c r="D296" t="n">
-        <v>34.05209598090971</v>
+        <v>34.05209976231423</v>
       </c>
       <c r="E296" t="n">
-        <v>34.23584709494806</v>
+        <v>34.2358508967577</v>
       </c>
       <c r="F296" t="n">
         <v>2113697</v>
@@ -6392,16 +6392,16 @@
         <v>44588</v>
       </c>
       <c r="B299" t="n">
-        <v>36.09271240234375</v>
+        <v>36.09270858764648</v>
       </c>
       <c r="C299" t="n">
-        <v>37.1081818022467</v>
+        <v>37.10817788022283</v>
       </c>
       <c r="D299" t="n">
-        <v>35.68652389286739</v>
+        <v>35.68652012110085</v>
       </c>
       <c r="E299" t="n">
-        <v>35.87994752798603</v>
+        <v>35.87994373577622</v>
       </c>
       <c r="F299" t="n">
         <v>3171460</v>
@@ -6492,16 +6492,16 @@
         <v>44595</v>
       </c>
       <c r="B304" t="n">
-        <v>35.29967498779297</v>
+        <v>35.2996711730957</v>
       </c>
       <c r="C304" t="n">
-        <v>35.58981230082171</v>
+        <v>35.58980845477045</v>
       </c>
       <c r="D304" t="n">
-        <v>33.84900341295216</v>
+        <v>33.84899975502328</v>
       </c>
       <c r="E304" t="n">
-        <v>34.98052769103708</v>
+        <v>34.98052391082881</v>
       </c>
       <c r="F304" t="n">
         <v>4177823</v>
@@ -6592,16 +6592,16 @@
         <v>44602</v>
       </c>
       <c r="B309" t="n">
-        <v>37.28226470947266</v>
+        <v>37.28226089477539</v>
       </c>
       <c r="C309" t="n">
-        <v>38.3847753224369</v>
+        <v>38.38477139493146</v>
       </c>
       <c r="D309" t="n">
-        <v>36.33449150769526</v>
+        <v>36.33448778997354</v>
       </c>
       <c r="E309" t="n">
-        <v>36.36350524073979</v>
+        <v>36.3635015200494</v>
       </c>
       <c r="F309" t="n">
         <v>7025951</v>
@@ -6612,16 +6612,16 @@
         <v>44603</v>
       </c>
       <c r="B310" t="n">
-        <v>38.07529067993164</v>
+        <v>38.07529449462891</v>
       </c>
       <c r="C310" t="n">
-        <v>38.49115162219439</v>
+        <v>38.49115547855604</v>
       </c>
       <c r="D310" t="n">
-        <v>37.37896869306991</v>
+        <v>37.37897243800389</v>
       </c>
       <c r="E310" t="n">
-        <v>37.78515714333515</v>
+        <v>37.78516092896444</v>
       </c>
       <c r="F310" t="n">
         <v>5486491</v>
@@ -6632,16 +6632,16 @@
         <v>44606</v>
       </c>
       <c r="B311" t="n">
-        <v>37.57239151000977</v>
+        <v>37.57239532470703</v>
       </c>
       <c r="C311" t="n">
-        <v>38.84898429079868</v>
+        <v>38.84898823510746</v>
       </c>
       <c r="D311" t="n">
-        <v>36.95343822941596</v>
+        <v>36.95344198127135</v>
       </c>
       <c r="E311" t="n">
-        <v>38.29772721003804</v>
+        <v>38.2977310983781</v>
       </c>
       <c r="F311" t="n">
         <v>3902640</v>
@@ -6652,16 +6652,16 @@
         <v>44607</v>
       </c>
       <c r="B312" t="n">
-        <v>35.79290008544922</v>
+        <v>35.79290390014648</v>
       </c>
       <c r="C312" t="n">
-        <v>36.65363192612031</v>
+        <v>36.65363583255173</v>
       </c>
       <c r="D312" t="n">
-        <v>35.63816270338088</v>
+        <v>35.63816650158672</v>
       </c>
       <c r="E312" t="n">
-        <v>36.55692199922141</v>
+        <v>36.55692589534578</v>
       </c>
       <c r="F312" t="n">
         <v>3810709</v>
@@ -6672,16 +6672,16 @@
         <v>44608</v>
       </c>
       <c r="B313" t="n">
-        <v>35.92830276489258</v>
+        <v>35.92829895019531</v>
       </c>
       <c r="C313" t="n">
-        <v>36.80837600146183</v>
+        <v>36.80837209332255</v>
       </c>
       <c r="D313" t="n">
-        <v>35.69619664958365</v>
+        <v>35.69619285953032</v>
       </c>
       <c r="E313" t="n">
-        <v>36.44087371532872</v>
+        <v>36.4408698462091</v>
       </c>
       <c r="F313" t="n">
         <v>4244663</v>
@@ -6692,16 +6692,16 @@
         <v>44609</v>
       </c>
       <c r="B314" t="n">
-        <v>35.29967498779297</v>
+        <v>35.2996711730957</v>
       </c>
       <c r="C314" t="n">
-        <v>35.89928710461807</v>
+        <v>35.89928322512308</v>
       </c>
       <c r="D314" t="n">
-        <v>34.41960179847439</v>
+        <v>34.41959807888318</v>
       </c>
       <c r="E314" t="n">
-        <v>35.68652224011414</v>
+        <v>35.68651838361181</v>
       </c>
       <c r="F314" t="n">
         <v>4430658</v>
@@ -6712,16 +6712,16 @@
         <v>44610</v>
       </c>
       <c r="B315" t="n">
-        <v>34.48730087280273</v>
+        <v>34.48729705810547</v>
       </c>
       <c r="C315" t="n">
-        <v>35.41572900804387</v>
+        <v>35.41572509065163</v>
       </c>
       <c r="D315" t="n">
-        <v>33.80064757961473</v>
+        <v>33.80064384086931</v>
       </c>
       <c r="E315" t="n">
-        <v>34.83546189196511</v>
+        <v>34.83545803875718</v>
       </c>
       <c r="F315" t="n">
         <v>4069741</v>
@@ -6852,16 +6852,16 @@
         <v>44623</v>
       </c>
       <c r="B322" t="n">
-        <v>37.34028625488281</v>
+        <v>37.34028244018555</v>
       </c>
       <c r="C322" t="n">
-        <v>37.88187465766974</v>
+        <v>37.88187078764361</v>
       </c>
       <c r="D322" t="n">
-        <v>36.31514815474819</v>
+        <v>36.31514444477941</v>
       </c>
       <c r="E322" t="n">
-        <v>37.12752138998924</v>
+        <v>37.12751759702811</v>
       </c>
       <c r="F322" t="n">
         <v>9786414</v>
@@ -6892,16 +6892,16 @@
         <v>44627</v>
       </c>
       <c r="B324" t="n">
-        <v>37.04048156738281</v>
+        <v>37.04048538208008</v>
       </c>
       <c r="C324" t="n">
-        <v>39.28418499781101</v>
+        <v>39.28418904358112</v>
       </c>
       <c r="D324" t="n">
-        <v>36.65363433916909</v>
+        <v>36.65363811402602</v>
       </c>
       <c r="E324" t="n">
-        <v>38.17200577495368</v>
+        <v>38.17200970618351</v>
       </c>
       <c r="F324" t="n">
         <v>5025922</v>
@@ -6952,16 +6952,16 @@
         <v>44630</v>
       </c>
       <c r="B327" t="n">
-        <v>35.7252082824707</v>
+        <v>35.72520446777344</v>
       </c>
       <c r="C327" t="n">
-        <v>37.22423481932497</v>
+        <v>37.22423084456335</v>
       </c>
       <c r="D327" t="n">
-        <v>35.51244341905014</v>
+        <v>35.51243962707166</v>
       </c>
       <c r="E327" t="n">
-        <v>36.75034637550812</v>
+        <v>36.75034245134777</v>
       </c>
       <c r="F327" t="n">
         <v>4502679</v>
@@ -7032,16 +7032,16 @@
         <v>44636</v>
       </c>
       <c r="B331" t="n">
-        <v>32.84320449829102</v>
+        <v>32.84320831298828</v>
       </c>
       <c r="C331" t="n">
-        <v>34.44861337459189</v>
+        <v>34.44861737575539</v>
       </c>
       <c r="D331" t="n">
-        <v>32.34030609979657</v>
+        <v>32.34030985608281</v>
       </c>
       <c r="E331" t="n">
-        <v>34.10045236831488</v>
+        <v>34.10045632903992</v>
       </c>
       <c r="F331" t="n">
         <v>3899288</v>
@@ -7092,16 +7092,16 @@
         <v>44641</v>
       </c>
       <c r="B334" t="n">
-        <v>36.61494827270508</v>
+        <v>36.61495208740234</v>
       </c>
       <c r="C334" t="n">
-        <v>36.86639934686866</v>
+        <v>36.86640318776314</v>
       </c>
       <c r="D334" t="n">
-        <v>35.88961252740777</v>
+        <v>35.88961626653654</v>
       </c>
       <c r="E334" t="n">
-        <v>35.97665371626157</v>
+        <v>35.97665746445866</v>
       </c>
       <c r="F334" t="n">
         <v>3600944</v>
@@ -7212,16 +7212,16 @@
         <v>44649</v>
       </c>
       <c r="B340" t="n">
-        <v>40.11590194702148</v>
+        <v>40.11590576171875</v>
       </c>
       <c r="C340" t="n">
-        <v>40.60913158587444</v>
+        <v>40.60913544747385</v>
       </c>
       <c r="D340" t="n">
-        <v>37.81417112752509</v>
+        <v>37.8141747233464</v>
       </c>
       <c r="E340" t="n">
-        <v>38.00759473575618</v>
+        <v>38.00759834997051</v>
       </c>
       <c r="F340" t="n">
         <v>6952609</v>
@@ -7252,16 +7252,16 @@
         <v>44651</v>
       </c>
       <c r="B342" t="n">
-        <v>40.47373962402344</v>
+        <v>40.47373580932617</v>
       </c>
       <c r="C342" t="n">
-        <v>41.13137921056172</v>
+        <v>41.13137533388116</v>
       </c>
       <c r="D342" t="n">
-        <v>39.67103512697872</v>
+        <v>39.6710313879373</v>
       </c>
       <c r="E342" t="n">
-        <v>40.135251085266</v>
+        <v>40.13524730247168</v>
       </c>
       <c r="F342" t="n">
         <v>3810811</v>
@@ -7312,16 +7312,16 @@
         <v>44656</v>
       </c>
       <c r="B345" t="n">
-        <v>41.97276306152344</v>
+        <v>41.9727668762207</v>
       </c>
       <c r="C345" t="n">
-        <v>43.03659106395681</v>
+        <v>43.03659497534015</v>
       </c>
       <c r="D345" t="n">
-        <v>41.57624708903781</v>
+        <v>41.5762508676977</v>
       </c>
       <c r="E345" t="n">
-        <v>42.30158283032514</v>
+        <v>42.30158667490721</v>
       </c>
       <c r="F345" t="n">
         <v>5903074</v>
@@ -7432,16 +7432,16 @@
         <v>44664</v>
       </c>
       <c r="B351" t="n">
-        <v>43.62652969360352</v>
+        <v>43.62653350830078</v>
       </c>
       <c r="C351" t="n">
-        <v>43.71356713249195</v>
+        <v>43.71357095479976</v>
       </c>
       <c r="D351" t="n">
-        <v>42.8431665105797</v>
+        <v>42.8431702567798</v>
       </c>
       <c r="E351" t="n">
-        <v>43.30738242414481</v>
+        <v>43.30738621093589</v>
       </c>
       <c r="F351" t="n">
         <v>3238402</v>
@@ -7452,16 +7452,16 @@
         <v>44665</v>
       </c>
       <c r="B352" t="n">
-        <v>42.93988037109375</v>
+        <v>42.93987655639648</v>
       </c>
       <c r="C352" t="n">
-        <v>43.62653368593358</v>
+        <v>43.62652981023535</v>
       </c>
       <c r="D352" t="n">
-        <v>42.2242170723533</v>
+        <v>42.2242133212342</v>
       </c>
       <c r="E352" t="n">
-        <v>43.62653368593358</v>
+        <v>43.62652981023535</v>
       </c>
       <c r="F352" t="n">
         <v>2345809</v>
@@ -7552,16 +7552,16 @@
         <v>44676</v>
       </c>
       <c r="B357" t="n">
-        <v>41.94375228881836</v>
+        <v>41.94374847412109</v>
       </c>
       <c r="C357" t="n">
-        <v>42.40796824528748</v>
+        <v>42.40796438837074</v>
       </c>
       <c r="D357" t="n">
-        <v>40.64782185452133</v>
+        <v>40.64781815768625</v>
       </c>
       <c r="E357" t="n">
-        <v>40.75420428750637</v>
+        <v>40.75420058099602</v>
       </c>
       <c r="F357" t="n">
         <v>3287465</v>
@@ -7592,16 +7592,16 @@
         <v>44678</v>
       </c>
       <c r="B359" t="n">
-        <v>42.16618728637695</v>
+        <v>42.16619110107422</v>
       </c>
       <c r="C359" t="n">
-        <v>43.58784506009413</v>
+        <v>43.58784900340616</v>
       </c>
       <c r="D359" t="n">
-        <v>41.46986526445734</v>
+        <v>41.46986901615963</v>
       </c>
       <c r="E359" t="n">
-        <v>43.52014885542929</v>
+        <v>43.52015279261696</v>
       </c>
       <c r="F359" t="n">
         <v>3779727</v>
@@ -7672,16 +7672,16 @@
         <v>44684</v>
       </c>
       <c r="B363" t="n">
-        <v>42.12750244140625</v>
+        <v>42.12749862670898</v>
       </c>
       <c r="C363" t="n">
-        <v>42.54336341820335</v>
+        <v>42.54335956584936</v>
       </c>
       <c r="D363" t="n">
-        <v>41.25710175933607</v>
+        <v>41.25709802345466</v>
       </c>
       <c r="E363" t="n">
-        <v>42.54336341820335</v>
+        <v>42.54335956584936</v>
       </c>
       <c r="F363" t="n">
         <v>4458389</v>
@@ -7692,16 +7692,16 @@
         <v>44685</v>
       </c>
       <c r="B364" t="n">
-        <v>44.10041427612305</v>
+        <v>44.10041809082031</v>
       </c>
       <c r="C364" t="n">
-        <v>44.32285161417975</v>
+        <v>44.32285544811791</v>
       </c>
       <c r="D364" t="n">
-        <v>42.16618567842227</v>
+        <v>42.16618932580826</v>
       </c>
       <c r="E364" t="n">
-        <v>43.04625879095802</v>
+        <v>43.04626251447057</v>
       </c>
       <c r="F364" t="n">
         <v>5759540</v>
@@ -7712,16 +7712,16 @@
         <v>44686</v>
       </c>
       <c r="B365" t="n">
-        <v>42.92053985595703</v>
+        <v>42.92053604125977</v>
       </c>
       <c r="C365" t="n">
-        <v>44.57430384010176</v>
+        <v>44.57429987842104</v>
       </c>
       <c r="D365" t="n">
-        <v>42.01145291457887</v>
+        <v>42.01144918067956</v>
       </c>
       <c r="E365" t="n">
-        <v>44.09074663744735</v>
+        <v>44.09074271874429</v>
       </c>
       <c r="F365" t="n">
         <v>4814532</v>
@@ -7732,16 +7732,16 @@
         <v>44687</v>
       </c>
       <c r="B366" t="n">
-        <v>42.55303573608398</v>
+        <v>42.55303192138672</v>
       </c>
       <c r="C366" t="n">
-        <v>43.90699359626386</v>
+        <v>43.90698966019007</v>
       </c>
       <c r="D366" t="n">
-        <v>41.82769996355259</v>
+        <v>41.82769621387857</v>
       </c>
       <c r="E366" t="n">
-        <v>43.33639522245434</v>
+        <v>43.33639133753226</v>
       </c>
       <c r="F366" t="n">
         <v>4093307</v>
@@ -7892,16 +7892,16 @@
         <v>44699</v>
       </c>
       <c r="B374" t="n">
-        <v>39.99985504150391</v>
+        <v>39.99985122680664</v>
       </c>
       <c r="C374" t="n">
-        <v>42.22421740419406</v>
+        <v>42.2242133773643</v>
       </c>
       <c r="D374" t="n">
-        <v>39.72906271064676</v>
+        <v>39.72905892177436</v>
       </c>
       <c r="E374" t="n">
-        <v>42.13717620908088</v>
+        <v>42.13717219055205</v>
       </c>
       <c r="F374" t="n">
         <v>1865839</v>
@@ -7952,16 +7952,16 @@
         <v>44704</v>
       </c>
       <c r="B377" t="n">
-        <v>42.28224563598633</v>
+        <v>42.28224182128906</v>
       </c>
       <c r="C377" t="n">
-        <v>42.79481657531103</v>
+        <v>42.7948127143697</v>
       </c>
       <c r="D377" t="n">
-        <v>41.35381369972519</v>
+        <v>41.3538099687909</v>
       </c>
       <c r="E377" t="n">
-        <v>41.42151365745766</v>
+        <v>41.42150992041549</v>
       </c>
       <c r="F377" t="n">
         <v>3400119</v>
@@ -8012,16 +8012,16 @@
         <v>44707</v>
       </c>
       <c r="B380" t="n">
-        <v>46.5955696105957</v>
+        <v>46.59557342529297</v>
       </c>
       <c r="C380" t="n">
-        <v>47.1661679572728</v>
+        <v>47.16617181868395</v>
       </c>
       <c r="D380" t="n">
-        <v>45.10621566046026</v>
+        <v>45.10621935322675</v>
       </c>
       <c r="E380" t="n">
-        <v>45.2512805595232</v>
+        <v>45.25128426416589</v>
       </c>
       <c r="F380" t="n">
         <v>4582217</v>
@@ -8072,16 +8072,16 @@
         <v>44712</v>
       </c>
       <c r="B383" t="n">
-        <v>47.14682769775391</v>
+        <v>47.14683151245117</v>
       </c>
       <c r="C383" t="n">
-        <v>49.5452685563496</v>
+        <v>49.54527256510714</v>
       </c>
       <c r="D383" t="n">
-        <v>47.11781396782467</v>
+        <v>47.11781778017441</v>
       </c>
       <c r="E383" t="n">
-        <v>48.22032446240879</v>
+        <v>48.22032836396376</v>
       </c>
       <c r="F383" t="n">
         <v>6322705</v>
@@ -8152,16 +8152,16 @@
         <v>44718</v>
       </c>
       <c r="B387" t="n">
-        <v>45.3189811706543</v>
+        <v>45.31898498535156</v>
       </c>
       <c r="C387" t="n">
-        <v>47.4563021942838</v>
+        <v>47.45630618888874</v>
       </c>
       <c r="D387" t="n">
-        <v>45.13522629971035</v>
+        <v>45.13523009894016</v>
       </c>
       <c r="E387" t="n">
-        <v>47.15649615191405</v>
+        <v>47.156500121283</v>
       </c>
       <c r="F387" t="n">
         <v>1711233</v>
@@ -8172,16 +8172,16 @@
         <v>44719</v>
       </c>
       <c r="B388" t="n">
-        <v>45.3189811706543</v>
+        <v>45.31898498535156</v>
       </c>
       <c r="C388" t="n">
-        <v>45.84122081100923</v>
+        <v>45.84122466966569</v>
       </c>
       <c r="D388" t="n">
-        <v>44.73871032322317</v>
+        <v>44.73871408907649</v>
       </c>
       <c r="E388" t="n">
-        <v>44.98048890609225</v>
+        <v>44.98049269229714</v>
       </c>
       <c r="F388" t="n">
         <v>1887578</v>
@@ -8192,16 +8192,16 @@
         <v>44720</v>
       </c>
       <c r="B389" t="n">
-        <v>45.25128555297852</v>
+        <v>45.25128173828125</v>
       </c>
       <c r="C389" t="n">
-        <v>46.00563510358936</v>
+        <v>46.00563122530019</v>
       </c>
       <c r="D389" t="n">
-        <v>44.92246574936335</v>
+        <v>44.9224619623857</v>
       </c>
       <c r="E389" t="n">
-        <v>45.31898551140559</v>
+        <v>45.31898169100119</v>
       </c>
       <c r="F389" t="n">
         <v>1920490</v>
@@ -8212,16 +8212,16 @@
         <v>44721</v>
       </c>
       <c r="B390" t="n">
-        <v>44.5066032409668</v>
+        <v>44.50660705566406</v>
       </c>
       <c r="C390" t="n">
-        <v>45.59944121195702</v>
+        <v>45.59944512032232</v>
       </c>
       <c r="D390" t="n">
-        <v>44.32285212169327</v>
+        <v>44.32285592064108</v>
       </c>
       <c r="E390" t="n">
-        <v>45.22226648118356</v>
+        <v>45.2222703572209</v>
       </c>
       <c r="F390" t="n">
         <v>1644697</v>
@@ -8472,16 +8472,16 @@
         <v>44741</v>
       </c>
       <c r="B403" t="n">
-        <v>34.71940612792969</v>
+        <v>34.71940994262695</v>
       </c>
       <c r="C403" t="n">
-        <v>35.41572814937177</v>
+        <v>35.41573204057546</v>
       </c>
       <c r="D403" t="n">
-        <v>34.09078031110602</v>
+        <v>34.0907840567348</v>
       </c>
       <c r="E403" t="n">
-        <v>35.29967322993957</v>
+        <v>35.29967710839206</v>
       </c>
       <c r="F403" t="n">
         <v>2690880</v>
@@ -8532,16 +8532,16 @@
         <v>44746</v>
       </c>
       <c r="B406" t="n">
-        <v>35.08691024780273</v>
+        <v>35.08690643310547</v>
       </c>
       <c r="C406" t="n">
-        <v>35.60915366553204</v>
+        <v>35.60914979405575</v>
       </c>
       <c r="D406" t="n">
-        <v>34.1971683099429</v>
+        <v>34.19716459197961</v>
       </c>
       <c r="E406" t="n">
-        <v>34.57433932306729</v>
+        <v>34.57433556409744</v>
       </c>
       <c r="F406" t="n">
         <v>2359523</v>
@@ -8612,16 +8612,16 @@
         <v>44750</v>
       </c>
       <c r="B410" t="n">
-        <v>31.81806373596191</v>
+        <v>31.81806564331055</v>
       </c>
       <c r="C410" t="n">
-        <v>32.48537204040704</v>
+        <v>32.48537398775778</v>
       </c>
       <c r="D410" t="n">
-        <v>31.19911039968697</v>
+        <v>31.19911226993215</v>
       </c>
       <c r="E410" t="n">
-        <v>31.3151653213559</v>
+        <v>31.31516719855805</v>
       </c>
       <c r="F410" t="n">
         <v>4375906</v>
@@ -8712,16 +8712,16 @@
         <v>44757</v>
       </c>
       <c r="B415" t="n">
-        <v>27.79486846923828</v>
+        <v>27.79486656188965</v>
       </c>
       <c r="C415" t="n">
-        <v>29.07146143004599</v>
+        <v>29.07145943509457</v>
       </c>
       <c r="D415" t="n">
-        <v>27.79486846923828</v>
+        <v>27.79486656188965</v>
       </c>
       <c r="E415" t="n">
-        <v>29.06178893688788</v>
+        <v>29.06178694260021</v>
       </c>
       <c r="F415" t="n">
         <v>4618481</v>
@@ -8752,16 +8752,16 @@
         <v>44761</v>
       </c>
       <c r="B417" t="n">
-        <v>29.43896293640137</v>
+        <v>29.43896102905273</v>
       </c>
       <c r="C417" t="n">
-        <v>29.53567474894549</v>
+        <v>29.5356728353309</v>
       </c>
       <c r="D417" t="n">
-        <v>28.11401691328927</v>
+        <v>28.11401509178381</v>
       </c>
       <c r="E417" t="n">
-        <v>28.14303064443129</v>
+        <v>28.14302882104603</v>
       </c>
       <c r="F417" t="n">
         <v>4570230</v>
@@ -8772,16 +8772,16 @@
         <v>44762</v>
       </c>
       <c r="B418" t="n">
-        <v>30.59950065612793</v>
+        <v>30.5994987487793</v>
       </c>
       <c r="C418" t="n">
-        <v>30.97667540990739</v>
+        <v>30.97667347904845</v>
       </c>
       <c r="D418" t="n">
-        <v>29.21652718353251</v>
+        <v>29.21652536238831</v>
       </c>
       <c r="E418" t="n">
-        <v>29.21652718353251</v>
+        <v>29.21652536238831</v>
       </c>
       <c r="F418" t="n">
         <v>5027446</v>
@@ -8792,16 +8792,16 @@
         <v>44763</v>
       </c>
       <c r="B419" t="n">
-        <v>29.44863510131836</v>
+        <v>29.44863319396973</v>
       </c>
       <c r="C419" t="n">
-        <v>29.86449233042948</v>
+        <v>29.86449039614633</v>
       </c>
       <c r="D419" t="n">
-        <v>28.83935237548546</v>
+        <v>28.83935050759925</v>
       </c>
       <c r="E419" t="n">
-        <v>29.86449233042948</v>
+        <v>29.86449039614633</v>
       </c>
       <c r="F419" t="n">
         <v>5437325</v>
@@ -8832,16 +8832,16 @@
         <v>44767</v>
       </c>
       <c r="B421" t="n">
-        <v>29.2648811340332</v>
+        <v>29.26488304138184</v>
       </c>
       <c r="C421" t="n">
-        <v>29.7194245717984</v>
+        <v>29.71942650877206</v>
       </c>
       <c r="D421" t="n">
-        <v>28.43316295561438</v>
+        <v>28.43316480875549</v>
       </c>
       <c r="E421" t="n">
-        <v>28.87803577468757</v>
+        <v>28.87803765682343</v>
       </c>
       <c r="F421" t="n">
         <v>3521914</v>
@@ -8852,16 +8852,16 @@
         <v>44768</v>
       </c>
       <c r="B422" t="n">
-        <v>28.95540428161621</v>
+        <v>28.95540618896484</v>
       </c>
       <c r="C422" t="n">
-        <v>30.15462657412001</v>
+        <v>30.15462856046375</v>
       </c>
       <c r="D422" t="n">
-        <v>28.81033750703789</v>
+        <v>28.81033940483069</v>
       </c>
       <c r="E422" t="n">
-        <v>29.88383426222034</v>
+        <v>29.88383623072646</v>
       </c>
       <c r="F422" t="n">
         <v>2984449</v>
@@ -8872,16 +8872,16 @@
         <v>44769</v>
       </c>
       <c r="B423" t="n">
-        <v>29.66139984130859</v>
+        <v>29.66139793395996</v>
       </c>
       <c r="C423" t="n">
-        <v>29.76778227135207</v>
+        <v>29.76778035716261</v>
       </c>
       <c r="D423" t="n">
-        <v>28.61691490502781</v>
+        <v>28.6169130648438</v>
       </c>
       <c r="E423" t="n">
-        <v>28.95540530688788</v>
+        <v>28.95540344493757</v>
       </c>
       <c r="F423" t="n">
         <v>2554762</v>
@@ -8892,16 +8892,16 @@
         <v>44770</v>
       </c>
       <c r="B424" t="n">
-        <v>30.78325271606445</v>
+        <v>30.78325080871582</v>
       </c>
       <c r="C424" t="n">
-        <v>30.88963514995402</v>
+        <v>30.88963323601387</v>
       </c>
       <c r="D424" t="n">
-        <v>29.53567536735125</v>
+        <v>29.53567353730325</v>
       </c>
       <c r="E424" t="n">
-        <v>29.96120510290952</v>
+        <v>29.96120324649545</v>
       </c>
       <c r="F424" t="n">
         <v>4208906</v>
@@ -8952,16 +8952,16 @@
         <v>44775</v>
       </c>
       <c r="B427" t="n">
-        <v>31.85674858093262</v>
+        <v>31.85675048828125</v>
       </c>
       <c r="C427" t="n">
-        <v>32.0791821744082</v>
+        <v>32.07918409507452</v>
       </c>
       <c r="D427" t="n">
-        <v>30.94765985359998</v>
+        <v>30.94766170651904</v>
       </c>
       <c r="E427" t="n">
-        <v>31.32483458513196</v>
+        <v>31.32483646063348</v>
       </c>
       <c r="F427" t="n">
         <v>3020206</v>
@@ -9072,16 +9072,16 @@
         <v>44783</v>
       </c>
       <c r="B433" t="n">
-        <v>33.26873397827148</v>
+        <v>33.26873779296875</v>
       </c>
       <c r="C433" t="n">
-        <v>33.97472847846024</v>
+        <v>33.97473237410905</v>
       </c>
       <c r="D433" t="n">
-        <v>32.87221800802422</v>
+        <v>32.87222177725572</v>
       </c>
       <c r="E433" t="n">
-        <v>33.62656747451073</v>
+        <v>33.62657133023831</v>
       </c>
       <c r="F433" t="n">
         <v>3325457</v>
@@ -9152,16 +9152,16 @@
         <v>44789</v>
       </c>
       <c r="B437" t="n">
-        <v>32.27260589599609</v>
+        <v>32.27260971069336</v>
       </c>
       <c r="C437" t="n">
-        <v>32.61109815484615</v>
+        <v>32.61110200955398</v>
       </c>
       <c r="D437" t="n">
-        <v>31.73102127989639</v>
+        <v>31.73102503057709</v>
       </c>
       <c r="E437" t="n">
-        <v>32.39832955774229</v>
+        <v>32.39833338730038</v>
       </c>
       <c r="F437" t="n">
         <v>2684074</v>
@@ -9172,16 +9172,16 @@
         <v>44790</v>
       </c>
       <c r="B438" t="n">
-        <v>32.53372955322266</v>
+        <v>32.53372573852539</v>
       </c>
       <c r="C438" t="n">
-        <v>32.93024931741367</v>
+        <v>32.93024545622303</v>
       </c>
       <c r="D438" t="n">
-        <v>31.80839373121048</v>
+        <v>31.80839000156146</v>
       </c>
       <c r="E438" t="n">
-        <v>31.8180662246313</v>
+        <v>31.81806249384815</v>
       </c>
       <c r="F438" t="n">
         <v>3057587</v>
@@ -9252,16 +9252,16 @@
         <v>44796</v>
       </c>
       <c r="B442" t="n">
-        <v>35.11592102050781</v>
+        <v>35.11592483520508</v>
       </c>
       <c r="C442" t="n">
-        <v>35.54145071517264</v>
+        <v>35.54145457609587</v>
       </c>
       <c r="D442" t="n">
-        <v>33.43314347863087</v>
+        <v>33.43314711052539</v>
       </c>
       <c r="E442" t="n">
-        <v>33.46215720759215</v>
+        <v>33.46216084263848</v>
       </c>
       <c r="F442" t="n">
         <v>5706007</v>
@@ -9292,16 +9292,16 @@
         <v>44798</v>
       </c>
       <c r="B444" t="n">
-        <v>35.7348747253418</v>
+        <v>35.73487854003906</v>
       </c>
       <c r="C444" t="n">
-        <v>36.56659288719009</v>
+        <v>36.56659679067325</v>
       </c>
       <c r="D444" t="n">
-        <v>35.39638621377552</v>
+        <v>35.39638999233915</v>
       </c>
       <c r="E444" t="n">
-        <v>35.8606021347718</v>
+        <v>35.86060596289047</v>
       </c>
       <c r="F444" t="n">
         <v>2850362</v>
@@ -9372,16 +9372,16 @@
         <v>44804</v>
       </c>
       <c r="B448" t="n">
-        <v>36.16040420532227</v>
+        <v>36.16040802001953</v>
       </c>
       <c r="C448" t="n">
-        <v>36.46021024107181</v>
+        <v>36.46021408739674</v>
       </c>
       <c r="D448" t="n">
-        <v>35.22230362431106</v>
+        <v>35.22230734004456</v>
       </c>
       <c r="E448" t="n">
-        <v>35.91862562779205</v>
+        <v>35.91862941698318</v>
       </c>
       <c r="F448" t="n">
         <v>3394125</v>
@@ -9392,16 +9392,16 @@
         <v>44805</v>
       </c>
       <c r="B449" t="n">
-        <v>35.58013534545898</v>
+        <v>35.58013916015625</v>
       </c>
       <c r="C449" t="n">
-        <v>36.22810235066332</v>
+        <v>36.22810623483188</v>
       </c>
       <c r="D449" t="n">
-        <v>35.00953703150028</v>
+        <v>35.00954078502128</v>
       </c>
       <c r="E449" t="n">
-        <v>35.8412551468599</v>
+        <v>35.84125898955293</v>
       </c>
       <c r="F449" t="n">
         <v>3340084</v>
@@ -9492,16 +9492,16 @@
         <v>44813</v>
       </c>
       <c r="B454" t="n">
-        <v>35.92830276489258</v>
+        <v>35.92829895019531</v>
       </c>
       <c r="C454" t="n">
-        <v>36.37317375612866</v>
+        <v>36.3731698941971</v>
       </c>
       <c r="D454" t="n">
-        <v>35.60915545100184</v>
+        <v>35.60915167019012</v>
       </c>
       <c r="E454" t="n">
-        <v>35.79290659406839</v>
+        <v>35.79290279374685</v>
       </c>
       <c r="F454" t="n">
         <v>3544465</v>
@@ -9552,16 +9552,16 @@
         <v>44818</v>
       </c>
       <c r="B457" t="n">
-        <v>37.25324630737305</v>
+        <v>37.25325012207031</v>
       </c>
       <c r="C457" t="n">
-        <v>37.57239358328728</v>
+        <v>37.57239743066493</v>
       </c>
       <c r="D457" t="n">
-        <v>35.96698471138824</v>
+        <v>35.96698839437353</v>
       </c>
       <c r="E457" t="n">
-        <v>36.05402215203722</v>
+        <v>36.05402584393507</v>
       </c>
       <c r="F457" t="n">
         <v>4057043</v>
@@ -9592,16 +9592,16 @@
         <v>44820</v>
       </c>
       <c r="B459" t="n">
-        <v>36.79870223999023</v>
+        <v>36.7987060546875</v>
       </c>
       <c r="C459" t="n">
-        <v>36.79870223999023</v>
+        <v>36.7987060546875</v>
       </c>
       <c r="D459" t="n">
-        <v>35.78322922342723</v>
+        <v>35.7832329328566</v>
       </c>
       <c r="E459" t="n">
-        <v>36.14106271488564</v>
+        <v>36.14106646140942</v>
       </c>
       <c r="F459" t="n">
         <v>2974596</v>
@@ -9612,16 +9612,16 @@
         <v>44823</v>
       </c>
       <c r="B460" t="n">
-        <v>36.8470573425293</v>
+        <v>36.84706115722656</v>
       </c>
       <c r="C460" t="n">
-        <v>37.3983144462179</v>
+        <v>37.39831831798563</v>
       </c>
       <c r="D460" t="n">
-        <v>35.7929018485589</v>
+        <v>35.79290555412169</v>
       </c>
       <c r="E460" t="n">
-        <v>35.7929018485589</v>
+        <v>35.79290555412169</v>
       </c>
       <c r="F460" t="n">
         <v>3461677</v>
@@ -9652,16 +9652,16 @@
         <v>44825</v>
       </c>
       <c r="B462" t="n">
-        <v>38.0366096496582</v>
+        <v>38.03661346435547</v>
       </c>
       <c r="C462" t="n">
-        <v>38.79095912196355</v>
+        <v>38.79096301231463</v>
       </c>
       <c r="D462" t="n">
-        <v>37.62074869162363</v>
+        <v>37.62075246461414</v>
       </c>
       <c r="E462" t="n">
-        <v>37.9398959687412</v>
+        <v>37.93989977373904</v>
       </c>
       <c r="F462" t="n">
         <v>4689181</v>
@@ -9732,16 +9732,16 @@
         <v>44831</v>
       </c>
       <c r="B466" t="n">
-        <v>33.61689758300781</v>
+        <v>33.61689376831055</v>
       </c>
       <c r="C466" t="n">
-        <v>34.44861580943209</v>
+        <v>34.44861190035511</v>
       </c>
       <c r="D466" t="n">
-        <v>33.32676401519949</v>
+        <v>33.3267602334253</v>
       </c>
       <c r="E466" t="n">
-        <v>34.44861580943209</v>
+        <v>34.44861190035511</v>
       </c>
       <c r="F466" t="n">
         <v>5480701</v>
@@ -9752,16 +9752,16 @@
         <v>44832</v>
       </c>
       <c r="B467" t="n">
-        <v>34.5743408203125</v>
+        <v>34.57433700561523</v>
       </c>
       <c r="C467" t="n">
-        <v>34.99987431683395</v>
+        <v>34.99987045518622</v>
       </c>
       <c r="D467" t="n">
-        <v>33.19136913623947</v>
+        <v>33.19136547412988</v>
       </c>
       <c r="E467" t="n">
-        <v>33.66525385709685</v>
+        <v>33.66525014270204</v>
       </c>
       <c r="F467" t="n">
         <v>4399676</v>
@@ -9772,16 +9772,16 @@
         <v>44833</v>
       </c>
       <c r="B468" t="n">
-        <v>33.90702819824219</v>
+        <v>33.90703201293945</v>
       </c>
       <c r="C468" t="n">
-        <v>34.69039138641359</v>
+        <v>34.69039528924284</v>
       </c>
       <c r="D468" t="n">
-        <v>33.09465502863428</v>
+        <v>33.09465875193581</v>
       </c>
       <c r="E468" t="n">
-        <v>34.61302269157358</v>
+        <v>34.61302658569848</v>
       </c>
       <c r="F468" t="n">
         <v>4499631</v>
@@ -9812,16 +9812,16 @@
         <v>44837</v>
       </c>
       <c r="B470" t="n">
-        <v>36.79870223999023</v>
+        <v>36.7987060546875</v>
       </c>
       <c r="C470" t="n">
-        <v>36.91475715561467</v>
+        <v>36.91476098234264</v>
       </c>
       <c r="D470" t="n">
-        <v>35.52210941084767</v>
+        <v>35.52211309320833</v>
       </c>
       <c r="E470" t="n">
-        <v>36.26678637509517</v>
+        <v>36.26679013465196</v>
       </c>
       <c r="F470" t="n">
         <v>4419789</v>
@@ -9852,16 +9852,16 @@
         <v>44839</v>
       </c>
       <c r="B472" t="n">
-        <v>41.63427352905273</v>
+        <v>41.63427734375</v>
       </c>
       <c r="C472" t="n">
-        <v>42.48533291211138</v>
+        <v>42.48533680478608</v>
       </c>
       <c r="D472" t="n">
-        <v>40.55110431601417</v>
+        <v>40.55110803146717</v>
       </c>
       <c r="E472" t="n">
-        <v>40.61880426561678</v>
+        <v>40.61880798727272</v>
       </c>
       <c r="F472" t="n">
         <v>6927519</v>
@@ -9892,16 +9892,16 @@
         <v>44841</v>
       </c>
       <c r="B474" t="n">
-        <v>41.47954177856445</v>
+        <v>41.47953796386719</v>
       </c>
       <c r="C474" t="n">
-        <v>42.45632495390688</v>
+        <v>42.45632104937901</v>
       </c>
       <c r="D474" t="n">
-        <v>41.22809067776815</v>
+        <v>41.22808688619578</v>
       </c>
       <c r="E474" t="n">
-        <v>41.59559296175236</v>
+        <v>41.59558913638236</v>
       </c>
       <c r="F474" t="n">
         <v>3503020</v>
@@ -10072,16 +10072,16 @@
         <v>44855</v>
       </c>
       <c r="B483" t="n">
-        <v>44.22613906860352</v>
+        <v>44.22614288330078</v>
       </c>
       <c r="C483" t="n">
-        <v>44.68068250090031</v>
+        <v>44.68068635480393</v>
       </c>
       <c r="D483" t="n">
-        <v>42.41763783177974</v>
+        <v>42.41764149048589</v>
       </c>
       <c r="E483" t="n">
-        <v>42.96889119740864</v>
+        <v>42.9688949036628</v>
       </c>
       <c r="F483" t="n">
         <v>5360835</v>
@@ -10112,16 +10112,16 @@
         <v>44859</v>
       </c>
       <c r="B485" t="n">
-        <v>42.69809722900391</v>
+        <v>42.69810104370117</v>
       </c>
       <c r="C485" t="n">
-        <v>44.7193669863075</v>
+        <v>44.71937098158734</v>
       </c>
       <c r="D485" t="n">
-        <v>42.52401860625056</v>
+        <v>42.52402240539543</v>
       </c>
       <c r="E485" t="n">
-        <v>43.43310543554394</v>
+        <v>43.43310931590769</v>
       </c>
       <c r="F485" t="n">
         <v>3364870</v>
@@ -10232,16 +10232,16 @@
         <v>44868</v>
       </c>
       <c r="B491" t="n">
-        <v>46.30543518066406</v>
+        <v>46.30543899536133</v>
       </c>
       <c r="C491" t="n">
-        <v>46.4311588402996</v>
+        <v>46.43116266535413</v>
       </c>
       <c r="D491" t="n">
-        <v>44.51627522669133</v>
+        <v>44.51627889399545</v>
       </c>
       <c r="E491" t="n">
-        <v>44.98048739191887</v>
+        <v>44.98049109746535</v>
       </c>
       <c r="F491" t="n">
         <v>3262984</v>
@@ -10312,16 +10312,16 @@
         <v>44874</v>
       </c>
       <c r="B495" t="n">
-        <v>44.69035339355469</v>
+        <v>44.69035720825195</v>
       </c>
       <c r="C495" t="n">
-        <v>46.49885831321781</v>
+        <v>46.49886228228617</v>
       </c>
       <c r="D495" t="n">
-        <v>44.23580997752845</v>
+        <v>44.23581375342662</v>
       </c>
       <c r="E495" t="n">
-        <v>45.35766165335595</v>
+        <v>45.35766552501359</v>
       </c>
       <c r="F495" t="n">
         <v>4884014</v>
@@ -10332,16 +10332,16 @@
         <v>44875</v>
       </c>
       <c r="B496" t="n">
-        <v>42.0598030090332</v>
+        <v>42.05980682373047</v>
       </c>
       <c r="C496" t="n">
-        <v>44.68068109462947</v>
+        <v>44.68068514703247</v>
       </c>
       <c r="D496" t="n">
-        <v>41.64394206412777</v>
+        <v>41.6439458411077</v>
       </c>
       <c r="E496" t="n">
-        <v>43.65554309181744</v>
+        <v>43.65554705124352</v>
       </c>
       <c r="F496" t="n">
         <v>5453172</v>
@@ -10472,16 +10472,16 @@
         <v>44887</v>
       </c>
       <c r="B503" t="n">
-        <v>35.7252082824707</v>
+        <v>35.72520446777344</v>
       </c>
       <c r="C503" t="n">
-        <v>38.01726681069696</v>
+        <v>38.01726275125628</v>
       </c>
       <c r="D503" t="n">
-        <v>35.41572973267442</v>
+        <v>35.41572595102293</v>
       </c>
       <c r="E503" t="n">
-        <v>37.37897222043525</v>
+        <v>37.37896822915095</v>
       </c>
       <c r="F503" t="n">
         <v>4879239</v>
@@ -10492,16 +10492,16 @@
         <v>44888</v>
       </c>
       <c r="B504" t="n">
-        <v>34.29387664794922</v>
+        <v>34.29388046264648</v>
       </c>
       <c r="C504" t="n">
-        <v>35.59947950993321</v>
+        <v>35.59948346985989</v>
       </c>
       <c r="D504" t="n">
-        <v>33.84900195222058</v>
+        <v>33.84900571743197</v>
       </c>
       <c r="E504" t="n">
-        <v>35.37704590964446</v>
+        <v>35.37704984482862</v>
       </c>
       <c r="F504" t="n">
         <v>5644348</v>
@@ -10532,16 +10532,16 @@
         <v>44890</v>
       </c>
       <c r="B506" t="n">
-        <v>34.2358512878418</v>
+        <v>34.23584747314453</v>
       </c>
       <c r="C506" t="n">
-        <v>36.49889988516448</v>
+        <v>36.49889581830917</v>
       </c>
       <c r="D506" t="n">
-        <v>34.11012761496025</v>
+        <v>34.11012381427162</v>
       </c>
       <c r="E506" t="n">
-        <v>36.17008008946956</v>
+        <v>36.17007605925269</v>
       </c>
       <c r="F506" t="n">
         <v>4398253</v>
@@ -10552,16 +10552,16 @@
         <v>44893</v>
       </c>
       <c r="B507" t="n">
-        <v>33.64591217041016</v>
+        <v>33.64590835571289</v>
       </c>
       <c r="C507" t="n">
-        <v>34.11012813925738</v>
+        <v>34.11012427192836</v>
       </c>
       <c r="D507" t="n">
-        <v>32.92057635865081</v>
+        <v>32.92057262619048</v>
       </c>
       <c r="E507" t="n">
-        <v>33.36544734092983</v>
+        <v>33.36544355803103</v>
       </c>
       <c r="F507" t="n">
         <v>4077054</v>
@@ -10652,16 +10652,16 @@
         <v>44900</v>
       </c>
       <c r="B512" t="n">
-        <v>34.04242706298828</v>
+        <v>34.04242324829102</v>
       </c>
       <c r="C512" t="n">
-        <v>35.879945891439</v>
+        <v>35.87994187083461</v>
       </c>
       <c r="D512" t="n">
-        <v>33.77163473568869</v>
+        <v>33.77163095133564</v>
       </c>
       <c r="E512" t="n">
-        <v>35.57046733984986</v>
+        <v>35.57046335392476</v>
       </c>
       <c r="F512" t="n">
         <v>5158181</v>
@@ -10732,16 +10732,16 @@
         <v>44904</v>
       </c>
       <c r="B516" t="n">
-        <v>31.69233894348145</v>
+        <v>31.69234085083008</v>
       </c>
       <c r="C516" t="n">
-        <v>32.74649445099531</v>
+        <v>32.74649642178647</v>
       </c>
       <c r="D516" t="n">
-        <v>31.48924283777486</v>
+        <v>31.4892447329005</v>
       </c>
       <c r="E516" t="n">
-        <v>32.22425106961099</v>
+        <v>32.22425300897184</v>
       </c>
       <c r="F516" t="n">
         <v>2885712</v>
@@ -10752,16 +10752,16 @@
         <v>44907</v>
       </c>
       <c r="B517" t="n">
-        <v>32.23392105102539</v>
+        <v>32.23392486572266</v>
       </c>
       <c r="C517" t="n">
-        <v>32.41767215777701</v>
+        <v>32.41767599422015</v>
       </c>
       <c r="D517" t="n">
-        <v>31.06371071712008</v>
+        <v>31.06371439332975</v>
       </c>
       <c r="E517" t="n">
-        <v>31.59562280181559</v>
+        <v>31.59562654097396</v>
       </c>
       <c r="F517" t="n">
         <v>3445728</v>
@@ -10772,16 +10772,16 @@
         <v>44908</v>
       </c>
       <c r="B518" t="n">
-        <v>32.52405548095703</v>
+        <v>32.5240592956543</v>
       </c>
       <c r="C518" t="n">
-        <v>33.41380105995531</v>
+        <v>33.41380497900949</v>
       </c>
       <c r="D518" t="n">
-        <v>31.9824708896037</v>
+        <v>31.98247464077933</v>
       </c>
       <c r="E518" t="n">
-        <v>32.39832807738018</v>
+        <v>32.39833187733107</v>
       </c>
       <c r="F518" t="n">
         <v>3369136</v>
@@ -10872,16 +10872,16 @@
         <v>44915</v>
       </c>
       <c r="B523" t="n">
-        <v>31.63431358337402</v>
+        <v>31.63431167602539</v>
       </c>
       <c r="C523" t="n">
-        <v>31.83740595497857</v>
+        <v>31.83740403538475</v>
       </c>
       <c r="D523" t="n">
-        <v>30.62851484937437</v>
+        <v>30.62851300266902</v>
       </c>
       <c r="E523" t="n">
-        <v>30.76391101296931</v>
+        <v>30.76390915810044</v>
       </c>
       <c r="F523" t="n">
         <v>3472546</v>
@@ -10892,16 +10892,16 @@
         <v>44916</v>
       </c>
       <c r="B524" t="n">
-        <v>32.19524002075195</v>
+        <v>32.19523620605469</v>
       </c>
       <c r="C524" t="n">
-        <v>32.50471857745117</v>
+        <v>32.50471472608491</v>
       </c>
       <c r="D524" t="n">
-        <v>31.22812562087756</v>
+        <v>31.22812192077017</v>
       </c>
       <c r="E524" t="n">
-        <v>32.34997742531367</v>
+        <v>32.34997359228213</v>
       </c>
       <c r="F524" t="n">
         <v>3938295</v>
@@ -10912,16 +10912,16 @@
         <v>44917</v>
       </c>
       <c r="B525" t="n">
-        <v>32.0114860534668</v>
+        <v>32.01148986816406</v>
       </c>
       <c r="C525" t="n">
-        <v>32.78517675543017</v>
+        <v>32.78518066232546</v>
       </c>
       <c r="D525" t="n">
-        <v>31.5376013885634</v>
+        <v>31.53760514678948</v>
       </c>
       <c r="E525" t="n">
-        <v>32.41767451520204</v>
+        <v>32.41767837830338</v>
       </c>
       <c r="F525" t="n">
         <v>3822391</v>
@@ -10932,16 +10932,16 @@
         <v>44918</v>
       </c>
       <c r="B526" t="n">
-        <v>34.68072509765625</v>
+        <v>34.68072128295898</v>
       </c>
       <c r="C526" t="n">
-        <v>34.88381746754605</v>
+        <v>34.88381363050969</v>
       </c>
       <c r="D526" t="n">
-        <v>32.68846888482701</v>
+        <v>32.68846528926745</v>
       </c>
       <c r="E526" t="n">
-        <v>33.17202607250107</v>
+        <v>33.17202242375276</v>
       </c>
       <c r="F526" t="n">
         <v>6955860</v>
@@ -11012,16 +11012,16 @@
         <v>44924</v>
       </c>
       <c r="B530" t="n">
-        <v>36.50856399536133</v>
+        <v>36.50856781005859</v>
       </c>
       <c r="C530" t="n">
-        <v>37.23389970387844</v>
+        <v>37.23390359436439</v>
       </c>
       <c r="D530" t="n">
-        <v>35.61882215744662</v>
+        <v>35.61882587917678</v>
       </c>
       <c r="E530" t="n">
-        <v>35.87994196319169</v>
+        <v>35.87994571220566</v>
       </c>
       <c r="F530" t="n">
         <v>4887264</v>
@@ -11032,16 +11032,16 @@
         <v>44928</v>
       </c>
       <c r="B531" t="n">
-        <v>35.21263885498047</v>
+        <v>35.2126350402832</v>
       </c>
       <c r="C531" t="n">
-        <v>36.68265172299981</v>
+        <v>36.68264774905137</v>
       </c>
       <c r="D531" t="n">
-        <v>34.78710911009928</v>
+        <v>34.78710534150101</v>
       </c>
       <c r="E531" t="n">
-        <v>36.01534337329287</v>
+        <v>36.01533947163607</v>
       </c>
       <c r="F531" t="n">
         <v>2924313</v>
@@ -11152,16 +11152,16 @@
         <v>44936</v>
       </c>
       <c r="B537" t="n">
-        <v>37.79483413696289</v>
+        <v>37.79483032226562</v>
       </c>
       <c r="C537" t="n">
-        <v>38.07529521496675</v>
+        <v>38.07529137196207</v>
       </c>
       <c r="D537" t="n">
-        <v>36.49889993855829</v>
+        <v>36.49889625466188</v>
       </c>
       <c r="E537" t="n">
-        <v>37.09850831958851</v>
+        <v>37.0985045751726</v>
       </c>
       <c r="F537" t="n">
         <v>3183751</v>
@@ -11192,16 +11192,16 @@
         <v>44938</v>
       </c>
       <c r="B539" t="n">
-        <v>43.42343521118164</v>
+        <v>43.42343902587891</v>
       </c>
       <c r="C539" t="n">
-        <v>44.72904181410123</v>
+        <v>44.7290457434945</v>
       </c>
       <c r="D539" t="n">
-        <v>43.19132911953119</v>
+        <v>43.19133291383822</v>
       </c>
       <c r="E539" t="n">
-        <v>43.40409397377132</v>
+        <v>43.40409778676949</v>
       </c>
       <c r="F539" t="n">
         <v>7341055</v>
@@ -11212,16 +11212,16 @@
         <v>44939</v>
       </c>
       <c r="B540" t="n">
-        <v>42.75613021850586</v>
+        <v>42.75612640380859</v>
       </c>
       <c r="C540" t="n">
-        <v>43.50080726582102</v>
+        <v>43.50080338468374</v>
       </c>
       <c r="D540" t="n">
-        <v>42.35961420932546</v>
+        <v>42.35961043000531</v>
       </c>
       <c r="E540" t="n">
-        <v>43.42343856263282</v>
+        <v>43.42343468839838</v>
       </c>
       <c r="F540" t="n">
         <v>4249336</v>
@@ -11272,16 +11272,16 @@
         <v>44944</v>
       </c>
       <c r="B543" t="n">
-        <v>44.53562164306641</v>
+        <v>44.53561782836914</v>
       </c>
       <c r="C543" t="n">
-        <v>45.24161621271021</v>
+        <v>45.241612337541</v>
       </c>
       <c r="D543" t="n">
-        <v>43.22034619346439</v>
+        <v>43.220342491427</v>
       </c>
       <c r="E543" t="n">
-        <v>43.42343857092518</v>
+        <v>43.42343485149192</v>
       </c>
       <c r="F543" t="n">
         <v>6730959</v>
@@ -11332,16 +11332,16 @@
         <v>44949</v>
       </c>
       <c r="B546" t="n">
-        <v>46.45050811767578</v>
+        <v>46.45050430297852</v>
       </c>
       <c r="C546" t="n">
-        <v>48.53947429699662</v>
+        <v>48.53947031074529</v>
       </c>
       <c r="D546" t="n">
-        <v>45.88958222216792</v>
+        <v>45.88957845353607</v>
       </c>
       <c r="E546" t="n">
-        <v>47.67874234150205</v>
+        <v>47.67873842593739</v>
       </c>
       <c r="F546" t="n">
         <v>5971946</v>
@@ -11392,16 +11392,16 @@
         <v>44952</v>
       </c>
       <c r="B549" t="n">
-        <v>45.26095581054688</v>
+        <v>45.26095199584961</v>
       </c>
       <c r="C549" t="n">
-        <v>46.77932358255676</v>
+        <v>46.77931963988798</v>
       </c>
       <c r="D549" t="n">
-        <v>45.24161457234137</v>
+        <v>45.24161075927422</v>
       </c>
       <c r="E549" t="n">
-        <v>45.92826413060603</v>
+        <v>45.92826025966649</v>
       </c>
       <c r="F549" t="n">
         <v>3327082</v>
@@ -11412,16 +11412,16 @@
         <v>44953</v>
       </c>
       <c r="B550" t="n">
-        <v>44.5066032409668</v>
+        <v>44.50660705566406</v>
       </c>
       <c r="C550" t="n">
-        <v>46.34412192885299</v>
+        <v>46.34412590104548</v>
       </c>
       <c r="D550" t="n">
-        <v>44.16811098394805</v>
+        <v>44.16811476963287</v>
       </c>
       <c r="E550" t="n">
-        <v>46.20872577556058</v>
+        <v>46.20872973614816</v>
       </c>
       <c r="F550" t="n">
         <v>4035914</v>
@@ -11432,16 +11432,16 @@
         <v>44956</v>
       </c>
       <c r="B551" t="n">
-        <v>43.79094314575195</v>
+        <v>43.79093933105469</v>
       </c>
       <c r="C551" t="n">
-        <v>44.43890648207057</v>
+        <v>44.43890261092821</v>
       </c>
       <c r="D551" t="n">
-        <v>43.13330356893655</v>
+        <v>43.13329981152729</v>
       </c>
       <c r="E551" t="n">
-        <v>44.31318281197527</v>
+        <v>44.3131789517849</v>
       </c>
       <c r="F551" t="n">
         <v>3870439</v>
@@ -11572,16 +11572,16 @@
         <v>44965</v>
       </c>
       <c r="B558" t="n">
-        <v>43.12362670898438</v>
+        <v>43.12363052368164</v>
       </c>
       <c r="C558" t="n">
-        <v>43.13329920092593</v>
+        <v>43.13330301647882</v>
       </c>
       <c r="D558" t="n">
-        <v>42.08881622667597</v>
+        <v>42.08881994983436</v>
       </c>
       <c r="E558" t="n">
-        <v>42.57237336739773</v>
+        <v>42.57237713333137</v>
       </c>
       <c r="F558" t="n">
         <v>2757212</v>
@@ -11672,16 +11672,16 @@
         <v>44972</v>
       </c>
       <c r="B563" t="n">
-        <v>40.04821014404297</v>
+        <v>40.0482063293457</v>
       </c>
       <c r="C563" t="n">
-        <v>40.52209485081966</v>
+        <v>40.52209099098364</v>
       </c>
       <c r="D563" t="n">
-        <v>38.90701335343782</v>
+        <v>38.90700964744255</v>
       </c>
       <c r="E563" t="n">
-        <v>38.92635833968847</v>
+        <v>38.92635463185054</v>
       </c>
       <c r="F563" t="n">
         <v>3495706</v>
@@ -11752,16 +11752,16 @@
         <v>44980</v>
       </c>
       <c r="B567" t="n">
-        <v>38.00759887695312</v>
+        <v>38.00759506225586</v>
       </c>
       <c r="C567" t="n">
-        <v>39.07142321677222</v>
+        <v>39.07141929530241</v>
       </c>
       <c r="D567" t="n">
-        <v>37.73680654543994</v>
+        <v>37.7368027579212</v>
       </c>
       <c r="E567" t="n">
-        <v>37.95924390652058</v>
+        <v>37.95924009667655</v>
       </c>
       <c r="F567" t="n">
         <v>3548732</v>
@@ -11812,16 +11812,16 @@
         <v>44985</v>
       </c>
       <c r="B570" t="n">
-        <v>35.21263885498047</v>
+        <v>35.2126350402832</v>
       </c>
       <c r="C570" t="n">
-        <v>38.49115688632073</v>
+        <v>38.49115271645117</v>
       </c>
       <c r="D570" t="n">
-        <v>35.21263885498047</v>
+        <v>35.2126350402832</v>
       </c>
       <c r="E570" t="n">
-        <v>37.13719520026616</v>
+        <v>37.13719117707558</v>
       </c>
       <c r="F570" t="n">
         <v>11036876</v>
@@ -11832,16 +11832,16 @@
         <v>44986</v>
       </c>
       <c r="B571" t="n">
-        <v>31.52793121337891</v>
+        <v>31.52792930603027</v>
       </c>
       <c r="C571" t="n">
-        <v>35.21263762145776</v>
+        <v>35.21263549119504</v>
       </c>
       <c r="D571" t="n">
-        <v>29.89350662783602</v>
+        <v>29.89350481936535</v>
       </c>
       <c r="E571" t="n">
-        <v>35.10625518896411</v>
+        <v>35.10625306513723</v>
       </c>
       <c r="F571" t="n">
         <v>24633899</v>
@@ -11872,16 +11872,16 @@
         <v>44988</v>
       </c>
       <c r="B573" t="n">
-        <v>31.74069595336914</v>
+        <v>31.74069404602051</v>
       </c>
       <c r="C573" t="n">
-        <v>31.93411957920744</v>
+        <v>31.93411766023568</v>
       </c>
       <c r="D573" t="n">
-        <v>30.40607743217574</v>
+        <v>30.40607560502645</v>
       </c>
       <c r="E573" t="n">
-        <v>30.47377551384036</v>
+        <v>30.47377368262298</v>
       </c>
       <c r="F573" t="n">
         <v>7573675</v>
@@ -11892,16 +11892,16 @@
         <v>44991</v>
       </c>
       <c r="B574" t="n">
-        <v>31.86642074584961</v>
+        <v>31.86641883850098</v>
       </c>
       <c r="C574" t="n">
-        <v>32.34997795368473</v>
+        <v>32.34997601739302</v>
       </c>
       <c r="D574" t="n">
-        <v>30.94766317523564</v>
+        <v>30.94766132287878</v>
       </c>
       <c r="E574" t="n">
-        <v>31.74069707103675</v>
+        <v>31.74069517121325</v>
       </c>
       <c r="F574" t="n">
         <v>5963007</v>
@@ -11992,16 +11992,16 @@
         <v>44998</v>
       </c>
       <c r="B579" t="n">
-        <v>26.45058059692383</v>
+        <v>26.4505786895752</v>
       </c>
       <c r="C579" t="n">
-        <v>27.32098316598858</v>
+        <v>27.32098119587531</v>
       </c>
       <c r="D579" t="n">
-        <v>25.76392728704381</v>
+        <v>25.76392542920967</v>
       </c>
       <c r="E579" t="n">
-        <v>26.59564737946998</v>
+        <v>26.59564546166059</v>
       </c>
       <c r="F579" t="n">
         <v>13860726</v>
@@ -12032,16 +12032,16 @@
         <v>45000</v>
       </c>
       <c r="B581" t="n">
-        <v>26.28616905212402</v>
+        <v>26.28617095947266</v>
       </c>
       <c r="C581" t="n">
-        <v>26.82775179788365</v>
+        <v>26.82775374453002</v>
       </c>
       <c r="D581" t="n">
-        <v>25.62853138858268</v>
+        <v>25.62853324821252</v>
       </c>
       <c r="E581" t="n">
-        <v>26.58597321755539</v>
+        <v>26.58597514665809</v>
       </c>
       <c r="F581" t="n">
         <v>12174787</v>
@@ -12072,16 +12072,16 @@
         <v>45002</v>
       </c>
       <c r="B583" t="n">
-        <v>30.70588302612305</v>
+        <v>30.70588111877441</v>
       </c>
       <c r="C583" t="n">
-        <v>30.88963415624145</v>
+        <v>30.8896322374788</v>
       </c>
       <c r="D583" t="n">
-        <v>27.73684184447329</v>
+        <v>27.73684012155175</v>
       </c>
       <c r="E583" t="n">
-        <v>30.45443194157511</v>
+        <v>30.45443004984579</v>
       </c>
       <c r="F583" t="n">
         <v>23193684</v>
@@ -12092,16 +12092,16 @@
         <v>45005</v>
       </c>
       <c r="B584" t="n">
-        <v>29.79679489135742</v>
+        <v>29.79679679870605</v>
       </c>
       <c r="C584" t="n">
-        <v>31.20878203377826</v>
+        <v>31.20878403151084</v>
       </c>
       <c r="D584" t="n">
-        <v>29.32290834641774</v>
+        <v>29.32291022343201</v>
       </c>
       <c r="E584" t="n">
-        <v>30.70588175921954</v>
+        <v>30.70588372476053</v>
       </c>
       <c r="F584" t="n">
         <v>7729094</v>
@@ -12252,16 +12252,16 @@
         <v>45015</v>
       </c>
       <c r="B592" t="n">
-        <v>29.38093376159668</v>
+        <v>29.38093566894531</v>
       </c>
       <c r="C592" t="n">
-        <v>30.51245796745546</v>
+        <v>30.51245994826028</v>
       </c>
       <c r="D592" t="n">
-        <v>29.2745513361352</v>
+        <v>29.27455323657771</v>
       </c>
       <c r="E592" t="n">
-        <v>29.95153211069714</v>
+        <v>29.95153405508782</v>
       </c>
       <c r="F592" t="n">
         <v>5560645</v>
@@ -12312,16 +12312,16 @@
         <v>45020</v>
       </c>
       <c r="B595" t="n">
-        <v>27.92059135437012</v>
+        <v>27.92059326171875</v>
       </c>
       <c r="C595" t="n">
-        <v>29.70975320425825</v>
+        <v>29.70975523383049</v>
       </c>
       <c r="D595" t="n">
-        <v>27.91092073592187</v>
+        <v>27.91092264260987</v>
       </c>
       <c r="E595" t="n">
-        <v>29.57435705083184</v>
+        <v>29.57435907115471</v>
       </c>
       <c r="F595" t="n">
         <v>7552242</v>
@@ -12332,16 +12332,16 @@
         <v>45021</v>
       </c>
       <c r="B596" t="n">
-        <v>26.76972770690918</v>
+        <v>26.76972579956055</v>
       </c>
       <c r="C596" t="n">
-        <v>27.8528951326722</v>
+        <v>27.85289314814766</v>
       </c>
       <c r="D596" t="n">
-        <v>26.23781367622606</v>
+        <v>26.23781180677641</v>
       </c>
       <c r="E596" t="n">
-        <v>27.65947338188658</v>
+        <v>27.65947141114338</v>
       </c>
       <c r="F596" t="n">
         <v>12382825</v>
@@ -12372,16 +12372,16 @@
         <v>45026</v>
       </c>
       <c r="B598" t="n">
-        <v>29.6517276763916</v>
+        <v>29.65172576904297</v>
       </c>
       <c r="C598" t="n">
-        <v>29.83547880780963</v>
+        <v>29.8354768886412</v>
       </c>
       <c r="D598" t="n">
-        <v>28.19138549654949</v>
+        <v>28.19138368313743</v>
       </c>
       <c r="E598" t="n">
-        <v>28.33645227786835</v>
+        <v>28.33645045512486</v>
       </c>
       <c r="F598" t="n">
         <v>8774363</v>
@@ -12552,16 +12552,16 @@
         <v>45040</v>
       </c>
       <c r="B607" t="n">
-        <v>26.96700477600098</v>
+        <v>26.96700286865234</v>
       </c>
       <c r="C607" t="n">
-        <v>27.07506799883479</v>
+        <v>27.07506608384296</v>
       </c>
       <c r="D607" t="n">
-        <v>26.23020138729918</v>
+        <v>26.23019953206389</v>
       </c>
       <c r="E607" t="n">
-        <v>26.86876394941649</v>
+        <v>26.86876204901633</v>
       </c>
       <c r="F607" t="n">
         <v>6680100</v>
@@ -12572,16 +12572,16 @@
         <v>45041</v>
       </c>
       <c r="B608" t="n">
-        <v>27.21260261535645</v>
+        <v>27.21260452270508</v>
       </c>
       <c r="C608" t="n">
-        <v>27.45820371522866</v>
+        <v>27.45820563979163</v>
       </c>
       <c r="D608" t="n">
-        <v>26.42667797149275</v>
+        <v>26.42667982375542</v>
       </c>
       <c r="E608" t="n">
-        <v>26.79999269261962</v>
+        <v>26.79999457104816</v>
       </c>
       <c r="F608" t="n">
         <v>5323000</v>
@@ -12612,16 +12612,16 @@
         <v>45043</v>
       </c>
       <c r="B610" t="n">
-        <v>29.90439414978027</v>
+        <v>29.90439224243164</v>
       </c>
       <c r="C610" t="n">
-        <v>30.26788277330051</v>
+        <v>30.267880842768</v>
       </c>
       <c r="D610" t="n">
-        <v>26.73122612224756</v>
+        <v>26.73122441728851</v>
       </c>
       <c r="E610" t="n">
-        <v>26.73122612224756</v>
+        <v>26.73122441728851</v>
       </c>
       <c r="F610" t="n">
         <v>20933600</v>
@@ -12672,16 +12672,16 @@
         <v>45049</v>
       </c>
       <c r="B613" t="n">
-        <v>29.14794158935547</v>
+        <v>29.14793968200684</v>
       </c>
       <c r="C613" t="n">
-        <v>29.61949529963673</v>
+        <v>29.61949336143113</v>
       </c>
       <c r="D613" t="n">
-        <v>28.33254592932366</v>
+        <v>28.33254407533193</v>
       </c>
       <c r="E613" t="n">
-        <v>29.26583095381972</v>
+        <v>29.26582903875679</v>
       </c>
       <c r="F613" t="n">
         <v>9250000</v>
@@ -12692,16 +12692,16 @@
         <v>45050</v>
       </c>
       <c r="B614" t="n">
-        <v>29.27565383911133</v>
+        <v>29.2756519317627</v>
       </c>
       <c r="C614" t="n">
-        <v>29.95351348008578</v>
+        <v>29.95351152857367</v>
       </c>
       <c r="D614" t="n">
-        <v>29.17741488650197</v>
+        <v>29.17741298555374</v>
       </c>
       <c r="E614" t="n">
-        <v>29.47213549190587</v>
+        <v>29.47213357175619</v>
       </c>
       <c r="F614" t="n">
         <v>6670900</v>
@@ -12792,16 +12792,16 @@
         <v>45057</v>
       </c>
       <c r="B619" t="n">
-        <v>31.66289710998535</v>
+        <v>31.66289520263672</v>
       </c>
       <c r="C619" t="n">
-        <v>31.81025928645763</v>
+        <v>31.81025737023202</v>
       </c>
       <c r="D619" t="n">
-        <v>31.10292683551199</v>
+        <v>31.10292496189554</v>
       </c>
       <c r="E619" t="n">
-        <v>31.71201658628417</v>
+        <v>31.71201467597662</v>
       </c>
       <c r="F619" t="n">
         <v>4858000</v>
@@ -12812,16 +12812,16 @@
         <v>45058</v>
       </c>
       <c r="B620" t="n">
-        <v>32.49794387817383</v>
+        <v>32.49794006347656</v>
       </c>
       <c r="C620" t="n">
-        <v>32.64530231015733</v>
+        <v>32.64529847816273</v>
       </c>
       <c r="D620" t="n">
-        <v>31.46641611640984</v>
+        <v>31.46641242279611</v>
       </c>
       <c r="E620" t="n">
-        <v>31.55483267463029</v>
+        <v>31.554828970638</v>
       </c>
       <c r="F620" t="n">
         <v>5317000</v>
@@ -12852,16 +12852,16 @@
         <v>45062</v>
       </c>
       <c r="B622" t="n">
-        <v>29.90439414978027</v>
+        <v>29.90439224243164</v>
       </c>
       <c r="C622" t="n">
-        <v>32.08533151226543</v>
+        <v>32.08532946581322</v>
       </c>
       <c r="D622" t="n">
-        <v>29.70791249602647</v>
+        <v>29.70791060120974</v>
       </c>
       <c r="E622" t="n">
-        <v>31.86920131837866</v>
+        <v>31.86919928571158</v>
       </c>
       <c r="F622" t="n">
         <v>13269700</v>
@@ -12912,16 +12912,16 @@
         <v>45065</v>
       </c>
       <c r="B625" t="n">
-        <v>32.49794387817383</v>
+        <v>32.49794006347656</v>
       </c>
       <c r="C625" t="n">
-        <v>34.87536105853923</v>
+        <v>34.87535696477425</v>
       </c>
       <c r="D625" t="n">
-        <v>31.0439837395418</v>
+        <v>31.04398009551434</v>
       </c>
       <c r="E625" t="n">
-        <v>31.86920182661951</v>
+        <v>31.8691980857257</v>
       </c>
       <c r="F625" t="n">
         <v>19443700</v>
@@ -12972,16 +12972,16 @@
         <v>45070</v>
       </c>
       <c r="B628" t="n">
-        <v>31.48606109619141</v>
+        <v>31.48606300354004</v>
       </c>
       <c r="C628" t="n">
-        <v>31.86919822262693</v>
+        <v>31.86920015318507</v>
       </c>
       <c r="D628" t="n">
-        <v>30.46436146776744</v>
+        <v>30.464363313224</v>
       </c>
       <c r="E628" t="n">
-        <v>31.04398022887067</v>
+        <v>31.04398210943912</v>
       </c>
       <c r="F628" t="n">
         <v>7685200</v>
@@ -13212,16 +13212,16 @@
         <v>45089</v>
       </c>
       <c r="B640" t="n">
-        <v>31.26011085510254</v>
+        <v>31.26010894775391</v>
       </c>
       <c r="C640" t="n">
-        <v>31.86920059509758</v>
+        <v>31.86919865058509</v>
       </c>
       <c r="D640" t="n">
-        <v>30.47418800549994</v>
+        <v>30.47418614610471</v>
       </c>
       <c r="E640" t="n">
-        <v>31.61377707431765</v>
+        <v>31.61377514538992</v>
       </c>
       <c r="F640" t="n">
         <v>7223600</v>
@@ -13252,16 +13252,16 @@
         <v>45091</v>
       </c>
       <c r="B642" t="n">
-        <v>31.14222145080566</v>
+        <v>31.1422233581543</v>
       </c>
       <c r="C642" t="n">
-        <v>31.71201407641177</v>
+        <v>31.71201601865814</v>
       </c>
       <c r="D642" t="n">
-        <v>30.5724269514118</v>
+        <v>30.57242882386257</v>
       </c>
       <c r="E642" t="n">
-        <v>31.33870121423831</v>
+        <v>31.33870313362062</v>
       </c>
       <c r="F642" t="n">
         <v>8288400</v>
@@ -13292,16 +13292,16 @@
         <v>45093</v>
       </c>
       <c r="B644" t="n">
-        <v>31.9183235168457</v>
+        <v>31.91832160949707</v>
       </c>
       <c r="C644" t="n">
-        <v>31.9183235168457</v>
+        <v>31.91832160949707</v>
       </c>
       <c r="D644" t="n">
-        <v>31.19134254558997</v>
+        <v>31.19134068168367</v>
       </c>
       <c r="E644" t="n">
-        <v>31.4271193982454</v>
+        <v>31.42711752024974</v>
       </c>
       <c r="F644" t="n">
         <v>5722800</v>
@@ -13332,16 +13332,16 @@
         <v>45097</v>
       </c>
       <c r="B646" t="n">
-        <v>32.16392517089844</v>
+        <v>32.16392135620117</v>
       </c>
       <c r="C646" t="n">
-        <v>32.2916350584061</v>
+        <v>32.29163122856222</v>
       </c>
       <c r="D646" t="n">
-        <v>31.48606366340425</v>
+        <v>31.48605992910253</v>
       </c>
       <c r="E646" t="n">
-        <v>32.12462809124572</v>
+        <v>32.12462428120915</v>
       </c>
       <c r="F646" t="n">
         <v>4954700</v>
@@ -13352,16 +13352,16 @@
         <v>45098</v>
       </c>
       <c r="B647" t="n">
-        <v>32.06567764282227</v>
+        <v>32.06568145751953</v>
       </c>
       <c r="C647" t="n">
-        <v>32.36039820068254</v>
+        <v>32.36040205044127</v>
       </c>
       <c r="D647" t="n">
-        <v>31.4860589217478</v>
+        <v>31.48606266749066</v>
       </c>
       <c r="E647" t="n">
-        <v>32.1246232534244</v>
+        <v>32.12462707513414</v>
       </c>
       <c r="F647" t="n">
         <v>4670300</v>
@@ -13412,16 +13412,16 @@
         <v>45103</v>
       </c>
       <c r="B650" t="n">
-        <v>30.53312873840332</v>
+        <v>30.53313064575195</v>
       </c>
       <c r="C650" t="n">
-        <v>30.83767357835474</v>
+        <v>30.83767550472773</v>
       </c>
       <c r="D650" t="n">
-        <v>30.30717617565832</v>
+        <v>30.30717806889212</v>
       </c>
       <c r="E650" t="n">
-        <v>30.58224820898695</v>
+        <v>30.58225011940398</v>
       </c>
       <c r="F650" t="n">
         <v>2874500</v>
@@ -13452,16 +13452,16 @@
         <v>45105</v>
       </c>
       <c r="B652" t="n">
-        <v>29.37389373779297</v>
+        <v>29.37389183044434</v>
       </c>
       <c r="C652" t="n">
-        <v>30.06157762706682</v>
+        <v>30.06157567506449</v>
       </c>
       <c r="D652" t="n">
-        <v>29.30512572362315</v>
+        <v>29.30512382073987</v>
       </c>
       <c r="E652" t="n">
-        <v>29.75703276126285</v>
+        <v>29.75703082903567</v>
       </c>
       <c r="F652" t="n">
         <v>4532500</v>
@@ -13532,16 +13532,16 @@
         <v>45111</v>
       </c>
       <c r="B656" t="n">
-        <v>29.80615043640137</v>
+        <v>29.80615234375</v>
       </c>
       <c r="C656" t="n">
-        <v>30.15981662939312</v>
+        <v>30.15981855937348</v>
       </c>
       <c r="D656" t="n">
-        <v>29.57037359900278</v>
+        <v>29.57037549126363</v>
       </c>
       <c r="E656" t="n">
-        <v>29.80615043640137</v>
+        <v>29.80615234375</v>
       </c>
       <c r="F656" t="n">
         <v>2514900</v>
@@ -13552,16 +13552,16 @@
         <v>45112</v>
       </c>
       <c r="B657" t="n">
-        <v>30.40541839599609</v>
+        <v>30.40542030334473</v>
       </c>
       <c r="C657" t="n">
-        <v>30.70996325002402</v>
+        <v>30.70996517647691</v>
       </c>
       <c r="D657" t="n">
-        <v>29.34442166777476</v>
+        <v>29.34442350856649</v>
       </c>
       <c r="E657" t="n">
-        <v>29.60966944448926</v>
+        <v>29.60967130192012</v>
       </c>
       <c r="F657" t="n">
         <v>5394800</v>
@@ -13612,16 +13612,16 @@
         <v>45117</v>
       </c>
       <c r="B660" t="n">
-        <v>31.07345199584961</v>
+        <v>31.07345390319824</v>
       </c>
       <c r="C660" t="n">
-        <v>31.93796708924193</v>
+        <v>31.93796904965617</v>
       </c>
       <c r="D660" t="n">
-        <v>30.84749942157282</v>
+        <v>30.84750131505205</v>
       </c>
       <c r="E660" t="n">
-        <v>31.56465609569361</v>
+        <v>31.56465803319331</v>
       </c>
       <c r="F660" t="n">
         <v>7339200</v>
@@ -13652,16 +13652,16 @@
         <v>45119</v>
       </c>
       <c r="B662" t="n">
-        <v>31.07345199584961</v>
+        <v>31.07345390319824</v>
       </c>
       <c r="C662" t="n">
-        <v>32.08532925608902</v>
+        <v>32.08533122554864</v>
       </c>
       <c r="D662" t="n">
-        <v>31.04398106151042</v>
+        <v>31.04398296705007</v>
       </c>
       <c r="E662" t="n">
-        <v>31.77096013121909</v>
+        <v>31.77096208138212</v>
       </c>
       <c r="F662" t="n">
         <v>4503800</v>
@@ -13732,16 +13732,16 @@
         <v>45125</v>
       </c>
       <c r="B666" t="n">
-        <v>32.91055297851562</v>
+        <v>32.91054916381836</v>
       </c>
       <c r="C666" t="n">
-        <v>33.03826662148488</v>
+        <v>33.03826279198419</v>
       </c>
       <c r="D666" t="n">
-        <v>32.03621351392245</v>
+        <v>32.0362098005708</v>
       </c>
       <c r="E666" t="n">
-        <v>32.18357195035527</v>
+        <v>32.18356821992315</v>
       </c>
       <c r="F666" t="n">
         <v>4775600</v>
@@ -13752,16 +13752,16 @@
         <v>45126</v>
       </c>
       <c r="B667" t="n">
-        <v>33.6473503112793</v>
+        <v>33.64735412597656</v>
       </c>
       <c r="C667" t="n">
-        <v>34.04031356576963</v>
+        <v>34.04031742501827</v>
       </c>
       <c r="D667" t="n">
-        <v>33.04808303459044</v>
+        <v>33.04808678134705</v>
       </c>
       <c r="E667" t="n">
-        <v>33.04808303459044</v>
+        <v>33.04808678134705</v>
       </c>
       <c r="F667" t="n">
         <v>7484200</v>
@@ -13772,16 +13772,16 @@
         <v>45127</v>
       </c>
       <c r="B668" t="n">
-        <v>33.92242813110352</v>
+        <v>33.92242431640625</v>
       </c>
       <c r="C668" t="n">
-        <v>34.11890979188617</v>
+        <v>34.11890595509385</v>
       </c>
       <c r="D668" t="n">
-        <v>33.64735605455338</v>
+        <v>33.64735227078894</v>
       </c>
       <c r="E668" t="n">
-        <v>33.91260573447357</v>
+        <v>33.91260192088087</v>
       </c>
       <c r="F668" t="n">
         <v>3587900</v>
@@ -13952,16 +13952,16 @@
         <v>45140</v>
       </c>
       <c r="B677" t="n">
-        <v>34.4431037902832</v>
+        <v>34.44309997558594</v>
       </c>
       <c r="C677" t="n">
-        <v>34.5806398233511</v>
+        <v>34.58063599342123</v>
       </c>
       <c r="D677" t="n">
-        <v>33.71612279718397</v>
+        <v>33.71611906300245</v>
       </c>
       <c r="E677" t="n">
-        <v>34.38415817000732</v>
+        <v>34.38415436183849</v>
       </c>
       <c r="F677" t="n">
         <v>3408800</v>
@@ -14012,16 +14012,16 @@
         <v>45145</v>
       </c>
       <c r="B680" t="n">
-        <v>35.68092727661133</v>
+        <v>35.68093109130859</v>
       </c>
       <c r="C680" t="n">
-        <v>36.15248093584172</v>
+        <v>36.15248480095344</v>
       </c>
       <c r="D680" t="n">
-        <v>35.09148613946717</v>
+        <v>35.09148989114647</v>
       </c>
       <c r="E680" t="n">
-        <v>36.05424199550948</v>
+        <v>36.05424585011833</v>
       </c>
       <c r="F680" t="n">
         <v>3820600</v>
@@ -14032,16 +14032,16 @@
         <v>45146</v>
       </c>
       <c r="B681" t="n">
-        <v>36.34896469116211</v>
+        <v>36.34896850585938</v>
       </c>
       <c r="C681" t="n">
-        <v>36.51597164901496</v>
+        <v>36.51597548123902</v>
       </c>
       <c r="D681" t="n">
-        <v>34.30556163401185</v>
+        <v>34.30556523426109</v>
       </c>
       <c r="E681" t="n">
-        <v>34.76729292525891</v>
+        <v>34.76729657396523</v>
       </c>
       <c r="F681" t="n">
         <v>5274900</v>
@@ -14172,16 +14172,16 @@
         <v>45155</v>
       </c>
       <c r="B688" t="n">
-        <v>31.26993370056152</v>
+        <v>31.26993560791016</v>
       </c>
       <c r="C688" t="n">
-        <v>31.74148926263102</v>
+        <v>31.74149119874277</v>
       </c>
       <c r="D688" t="n">
-        <v>30.9653888444364</v>
+        <v>30.96539073320894</v>
       </c>
       <c r="E688" t="n">
-        <v>31.46641346711834</v>
+        <v>31.4664153864515</v>
       </c>
       <c r="F688" t="n">
         <v>4529600</v>
@@ -14252,16 +14252,16 @@
         <v>45161</v>
       </c>
       <c r="B692" t="n">
-        <v>31.05380630493164</v>
+        <v>31.05380439758301</v>
       </c>
       <c r="C692" t="n">
-        <v>31.2404618075605</v>
+        <v>31.24045988874735</v>
       </c>
       <c r="D692" t="n">
-        <v>30.68049155209822</v>
+        <v>30.68048966767887</v>
       </c>
       <c r="E692" t="n">
-        <v>31.09310150987904</v>
+        <v>31.09309960011686</v>
       </c>
       <c r="F692" t="n">
         <v>4847400</v>
@@ -14272,16 +14272,16 @@
         <v>45162</v>
       </c>
       <c r="B693" t="n">
-        <v>30.91626930236816</v>
+        <v>30.91626739501953</v>
       </c>
       <c r="C693" t="n">
-        <v>31.30923260599883</v>
+        <v>31.30923067440671</v>
       </c>
       <c r="D693" t="n">
-        <v>30.56260495240363</v>
+        <v>30.56260306687397</v>
       </c>
       <c r="E693" t="n">
-        <v>31.05380720815405</v>
+        <v>31.05380529232016</v>
       </c>
       <c r="F693" t="n">
         <v>3471700</v>
@@ -14332,16 +14332,16 @@
         <v>45167</v>
       </c>
       <c r="B696" t="n">
-        <v>31.29940795898438</v>
+        <v>31.29940605163574</v>
       </c>
       <c r="C696" t="n">
-        <v>31.55483147996431</v>
+        <v>31.55482955705047</v>
       </c>
       <c r="D696" t="n">
-        <v>30.63137259940515</v>
+        <v>30.63137073276579</v>
       </c>
       <c r="E696" t="n">
-        <v>31.06363110391898</v>
+        <v>31.06362921093831</v>
       </c>
       <c r="F696" t="n">
         <v>3743200</v>
@@ -14352,16 +14352,16 @@
         <v>45168</v>
       </c>
       <c r="B697" t="n">
-        <v>31.6334228515625</v>
+        <v>31.63342475891113</v>
       </c>
       <c r="C697" t="n">
-        <v>31.70219086067396</v>
+        <v>31.70219277216898</v>
       </c>
       <c r="D697" t="n">
-        <v>30.96538755084366</v>
+        <v>30.96538941791287</v>
       </c>
       <c r="E697" t="n">
-        <v>31.49588683333958</v>
+        <v>31.49588873239543</v>
       </c>
       <c r="F697" t="n">
         <v>3276100</v>
@@ -14412,16 +14412,16 @@
         <v>45173</v>
       </c>
       <c r="B700" t="n">
-        <v>32.2719841003418</v>
+        <v>32.27198791503906</v>
       </c>
       <c r="C700" t="n">
-        <v>32.55688228511206</v>
+        <v>32.55688613348561</v>
       </c>
       <c r="D700" t="n">
-        <v>32.06568006898767</v>
+        <v>32.06568385929886</v>
       </c>
       <c r="E700" t="n">
-        <v>32.22286462824446</v>
+        <v>32.22286843713558</v>
       </c>
       <c r="F700" t="n">
         <v>2652900</v>
@@ -14432,16 +14432,16 @@
         <v>45174</v>
       </c>
       <c r="B701" t="n">
-        <v>32.63547515869141</v>
+        <v>32.63547897338867</v>
       </c>
       <c r="C701" t="n">
-        <v>32.93019572729314</v>
+        <v>32.93019957643972</v>
       </c>
       <c r="D701" t="n">
-        <v>32.07550495407551</v>
+        <v>32.07550870331895</v>
       </c>
       <c r="E701" t="n">
-        <v>32.27198283475976</v>
+        <v>32.27198660696912</v>
       </c>
       <c r="F701" t="n">
         <v>6036900</v>
@@ -14452,16 +14452,16 @@
         <v>45175</v>
       </c>
       <c r="B702" t="n">
-        <v>32.00674057006836</v>
+        <v>32.00673675537109</v>
       </c>
       <c r="C702" t="n">
-        <v>32.71406926527997</v>
+        <v>32.71406536628031</v>
       </c>
       <c r="D702" t="n">
-        <v>31.92814641083608</v>
+        <v>31.928142605506</v>
       </c>
       <c r="E702" t="n">
-        <v>32.65512739343153</v>
+        <v>32.65512350145682</v>
       </c>
       <c r="F702" t="n">
         <v>4505300</v>
@@ -14512,16 +14512,16 @@
         <v>45181</v>
       </c>
       <c r="B705" t="n">
-        <v>32.3309326171875</v>
+        <v>32.33092880249023</v>
       </c>
       <c r="C705" t="n">
-        <v>32.6453017639165</v>
+        <v>32.64529791212711</v>
       </c>
       <c r="D705" t="n">
-        <v>31.76113994408213</v>
+        <v>31.76113619661418</v>
       </c>
       <c r="E705" t="n">
-        <v>31.97726639022342</v>
+        <v>31.97726261725491</v>
       </c>
       <c r="F705" t="n">
         <v>3620500</v>
@@ -14532,16 +14532,16 @@
         <v>45182</v>
       </c>
       <c r="B706" t="n">
-        <v>31.6334228515625</v>
+        <v>31.63342475891113</v>
       </c>
       <c r="C706" t="n">
-        <v>32.11479891534272</v>
+        <v>32.1148008517161</v>
       </c>
       <c r="D706" t="n">
-        <v>31.44676361462388</v>
+        <v>31.44676551071783</v>
       </c>
       <c r="E706" t="n">
-        <v>31.60394817081799</v>
+        <v>31.60395007638945</v>
       </c>
       <c r="F706" t="n">
         <v>7302700</v>
@@ -14552,16 +14552,16 @@
         <v>45183</v>
       </c>
       <c r="B707" t="n">
-        <v>32.311279296875</v>
+        <v>32.31128311157227</v>
       </c>
       <c r="C707" t="n">
-        <v>32.311279296875</v>
+        <v>32.31128311157227</v>
       </c>
       <c r="D707" t="n">
-        <v>31.74148670806588</v>
+        <v>31.74149045549294</v>
       </c>
       <c r="E707" t="n">
-        <v>31.83972564654409</v>
+        <v>31.83972940556933</v>
       </c>
       <c r="F707" t="n">
         <v>4362300</v>
@@ -14592,16 +14592,16 @@
         <v>45187</v>
       </c>
       <c r="B709" t="n">
-        <v>31.98709297180176</v>
+        <v>31.98709106445312</v>
       </c>
       <c r="C709" t="n">
-        <v>32.71407022822005</v>
+        <v>32.7140682775227</v>
       </c>
       <c r="D709" t="n">
-        <v>31.75131423474054</v>
+        <v>31.75131234145109</v>
       </c>
       <c r="E709" t="n">
-        <v>32.55688565270453</v>
+        <v>32.5568837113799</v>
       </c>
       <c r="F709" t="n">
         <v>5099000</v>
@@ -14692,16 +14692,16 @@
         <v>45194</v>
       </c>
       <c r="B714" t="n">
-        <v>30.95556640625</v>
+        <v>30.95556449890137</v>
       </c>
       <c r="C714" t="n">
-        <v>31.20116753431566</v>
+        <v>31.20116561183414</v>
       </c>
       <c r="D714" t="n">
-        <v>29.99281043394172</v>
+        <v>29.99280858591396</v>
       </c>
       <c r="E714" t="n">
-        <v>30.45453988014151</v>
+        <v>30.45453800366397</v>
       </c>
       <c r="F714" t="n">
         <v>6350700</v>
@@ -14712,16 +14712,16 @@
         <v>45195</v>
       </c>
       <c r="B715" t="n">
-        <v>30.32682800292969</v>
+        <v>30.32682609558105</v>
       </c>
       <c r="C715" t="n">
-        <v>30.83767692328888</v>
+        <v>30.83767498381136</v>
       </c>
       <c r="D715" t="n">
-        <v>30.19911436749897</v>
+        <v>30.19911246818264</v>
       </c>
       <c r="E715" t="n">
-        <v>30.75908463755763</v>
+        <v>30.75908270302303</v>
       </c>
       <c r="F715" t="n">
         <v>3433500</v>
@@ -14732,16 +14732,16 @@
         <v>45196</v>
       </c>
       <c r="B716" t="n">
-        <v>30.86714744567871</v>
+        <v>30.86714935302734</v>
       </c>
       <c r="C716" t="n">
-        <v>31.07345147776449</v>
+        <v>31.0734533978611</v>
       </c>
       <c r="D716" t="n">
-        <v>30.42506470008381</v>
+        <v>30.42506658011519</v>
       </c>
       <c r="E716" t="n">
-        <v>30.65101914438107</v>
+        <v>30.65102103837466</v>
       </c>
       <c r="F716" t="n">
         <v>4307600</v>
@@ -14752,16 +14752,16 @@
         <v>45197</v>
       </c>
       <c r="B717" t="n">
-        <v>30.58225059509277</v>
+        <v>30.58224868774414</v>
       </c>
       <c r="C717" t="n">
-        <v>31.21099073558775</v>
+        <v>31.21098878902595</v>
       </c>
       <c r="D717" t="n">
-        <v>30.41524175877521</v>
+        <v>30.41523986184255</v>
       </c>
       <c r="E717" t="n">
-        <v>30.82785171474873</v>
+        <v>30.82784979208249</v>
       </c>
       <c r="F717" t="n">
         <v>4298000</v>
@@ -14772,16 +14772,16 @@
         <v>45198</v>
       </c>
       <c r="B718" t="n">
-        <v>31.02433204650879</v>
+        <v>31.02433395385742</v>
       </c>
       <c r="C718" t="n">
-        <v>31.60394894047274</v>
+        <v>31.60395088345571</v>
       </c>
       <c r="D718" t="n">
-        <v>30.47418608643163</v>
+        <v>30.47418795995777</v>
       </c>
       <c r="E718" t="n">
-        <v>30.86714748648674</v>
+        <v>30.86714938417181</v>
       </c>
       <c r="F718" t="n">
         <v>5846000</v>
@@ -14852,16 +14852,16 @@
         <v>45204</v>
       </c>
       <c r="B722" t="n">
-        <v>28.0378246307373</v>
+        <v>28.03782272338867</v>
       </c>
       <c r="C722" t="n">
-        <v>28.78445038319864</v>
+        <v>28.78444842505877</v>
       </c>
       <c r="D722" t="n">
-        <v>27.72345362458937</v>
+        <v>27.72345173862667</v>
       </c>
       <c r="E722" t="n">
-        <v>28.62726581701858</v>
+        <v>28.62726386957162</v>
       </c>
       <c r="F722" t="n">
         <v>8409300</v>
@@ -14912,16 +14912,16 @@
         <v>45209</v>
       </c>
       <c r="B725" t="n">
-        <v>30.2777042388916</v>
+        <v>30.27770614624023</v>
       </c>
       <c r="C725" t="n">
-        <v>30.40541786413846</v>
+        <v>30.40541977953243</v>
       </c>
       <c r="D725" t="n">
-        <v>29.43283582930937</v>
+        <v>29.43283768343539</v>
       </c>
       <c r="E725" t="n">
-        <v>29.7570310901109</v>
+        <v>29.75703296465965</v>
       </c>
       <c r="F725" t="n">
         <v>7018100</v>
@@ -14972,16 +14972,16 @@
         <v>45215</v>
       </c>
       <c r="B728" t="n">
-        <v>31.67272186279297</v>
+        <v>31.67271995544434</v>
       </c>
       <c r="C728" t="n">
-        <v>32.01656192935982</v>
+        <v>32.01656000130495</v>
       </c>
       <c r="D728" t="n">
-        <v>31.32887804865046</v>
+        <v>31.32887616200829</v>
       </c>
       <c r="E728" t="n">
-        <v>31.91832298107662</v>
+        <v>31.91832105893775</v>
       </c>
       <c r="F728" t="n">
         <v>3741500</v>
@@ -15012,16 +15012,16 @@
         <v>45217</v>
       </c>
       <c r="B730" t="n">
-        <v>32.06567764282227</v>
+        <v>32.06568145751953</v>
       </c>
       <c r="C730" t="n">
-        <v>33.06773053760736</v>
+        <v>33.06773447151397</v>
       </c>
       <c r="D730" t="n">
-        <v>31.63342107446555</v>
+        <v>31.63342483773936</v>
       </c>
       <c r="E730" t="n">
-        <v>32.52740889026767</v>
+        <v>32.52741275989484</v>
       </c>
       <c r="F730" t="n">
         <v>7439800</v>
@@ -15132,16 +15132,16 @@
         <v>45225</v>
       </c>
       <c r="B736" t="n">
-        <v>31.98709297180176</v>
+        <v>31.98709106445312</v>
       </c>
       <c r="C736" t="n">
-        <v>32.12462900693085</v>
+        <v>32.12462709138111</v>
       </c>
       <c r="D736" t="n">
-        <v>31.19134395024304</v>
+        <v>31.19134209034388</v>
       </c>
       <c r="E736" t="n">
-        <v>31.57448111883861</v>
+        <v>31.57447923609348</v>
       </c>
       <c r="F736" t="n">
         <v>2923500</v>
@@ -15152,16 +15152,16 @@
         <v>45226</v>
       </c>
       <c r="B737" t="n">
-        <v>31.52536010742188</v>
+        <v>31.52535820007324</v>
       </c>
       <c r="C737" t="n">
-        <v>32.55688406826494</v>
+        <v>32.556882098507</v>
       </c>
       <c r="D737" t="n">
-        <v>31.24046190704763</v>
+        <v>31.24046001693592</v>
       </c>
       <c r="E737" t="n">
-        <v>32.32110909025403</v>
+        <v>32.32110713476096</v>
       </c>
       <c r="F737" t="n">
         <v>3378100</v>
@@ -15172,16 +15172,16 @@
         <v>45229</v>
       </c>
       <c r="B738" t="n">
-        <v>31.07345199584961</v>
+        <v>31.07345390319824</v>
       </c>
       <c r="C738" t="n">
-        <v>32.11480019042821</v>
+        <v>32.11480216169681</v>
       </c>
       <c r="D738" t="n">
-        <v>30.98503731904426</v>
+        <v>30.98503922096583</v>
       </c>
       <c r="E738" t="n">
-        <v>31.5450075569423</v>
+        <v>31.54500949323592</v>
       </c>
       <c r="F738" t="n">
         <v>3227500</v>
@@ -15192,16 +15192,16 @@
         <v>45230</v>
       </c>
       <c r="B739" t="n">
-        <v>31.86919975280762</v>
+        <v>31.86919784545898</v>
       </c>
       <c r="C739" t="n">
-        <v>32.10497847524474</v>
+        <v>32.10497655378492</v>
       </c>
       <c r="D739" t="n">
-        <v>31.2011662851952</v>
+        <v>31.20116441782789</v>
       </c>
       <c r="E739" t="n">
-        <v>31.2011662851952</v>
+        <v>31.20116441782789</v>
       </c>
       <c r="F739" t="n">
         <v>3372100</v>
@@ -15212,16 +15212,16 @@
         <v>45231</v>
       </c>
       <c r="B740" t="n">
-        <v>32.06567764282227</v>
+        <v>32.06568145751953</v>
       </c>
       <c r="C740" t="n">
-        <v>32.74353904823363</v>
+        <v>32.74354294357276</v>
       </c>
       <c r="D740" t="n">
-        <v>31.9477901691932</v>
+        <v>31.94779396986597</v>
       </c>
       <c r="E740" t="n">
-        <v>32.07550378504357</v>
+        <v>32.0755076009098</v>
       </c>
       <c r="F740" t="n">
         <v>4282500</v>
@@ -15232,16 +15232,16 @@
         <v>45233</v>
       </c>
       <c r="B741" t="n">
-        <v>32.69441986083984</v>
+        <v>32.69441604614258</v>
       </c>
       <c r="C741" t="n">
-        <v>32.94984712401398</v>
+        <v>32.94984327951414</v>
       </c>
       <c r="D741" t="n">
-        <v>32.46846728038622</v>
+        <v>32.4684634920525</v>
       </c>
       <c r="E741" t="n">
-        <v>32.73371693941674</v>
+        <v>32.7337131201344</v>
       </c>
       <c r="F741" t="n">
         <v>3190300</v>
@@ -15272,16 +15272,16 @@
         <v>45237</v>
       </c>
       <c r="B743" t="n">
-        <v>32.48811721801758</v>
+        <v>32.48811340332031</v>
       </c>
       <c r="C743" t="n">
-        <v>32.63547939523581</v>
+        <v>32.63547556323554</v>
       </c>
       <c r="D743" t="n">
-        <v>31.81025944748058</v>
+        <v>31.81025571237618</v>
       </c>
       <c r="E743" t="n">
-        <v>31.8790274641622</v>
+        <v>31.87902372098318</v>
       </c>
       <c r="F743" t="n">
         <v>3324000</v>
@@ -15312,16 +15312,16 @@
         <v>45239</v>
       </c>
       <c r="B745" t="n">
-        <v>30.81802749633789</v>
+        <v>30.81802940368652</v>
       </c>
       <c r="C745" t="n">
-        <v>33.77506502697286</v>
+        <v>33.77506711733456</v>
       </c>
       <c r="D745" t="n">
-        <v>30.67066533422895</v>
+        <v>30.67066723245724</v>
       </c>
       <c r="E745" t="n">
-        <v>33.41157269312426</v>
+        <v>33.41157476098916</v>
       </c>
       <c r="F745" t="n">
         <v>15431300</v>
@@ -15332,16 +15332,16 @@
         <v>45240</v>
       </c>
       <c r="B746" t="n">
-        <v>31.25028610229492</v>
+        <v>31.25028419494629</v>
       </c>
       <c r="C746" t="n">
-        <v>32.06568174882637</v>
+        <v>32.06567979171039</v>
       </c>
       <c r="D746" t="n">
-        <v>31.04398206013306</v>
+        <v>31.04398016537612</v>
       </c>
       <c r="E746" t="n">
-        <v>31.05380632982475</v>
+        <v>31.05380443446818</v>
       </c>
       <c r="F746" t="n">
         <v>4738300</v>
@@ -15352,16 +15352,16 @@
         <v>45243</v>
       </c>
       <c r="B747" t="n">
-        <v>30.94573974609375</v>
+        <v>30.94574165344238</v>
       </c>
       <c r="C747" t="n">
-        <v>31.41729342584897</v>
+        <v>31.41729536226194</v>
       </c>
       <c r="D747" t="n">
-        <v>30.67066582934266</v>
+        <v>30.67066771973704</v>
       </c>
       <c r="E747" t="n">
-        <v>31.21098939362647</v>
+        <v>31.21099131732383</v>
       </c>
       <c r="F747" t="n">
         <v>3172300</v>
@@ -15392,16 +15392,16 @@
         <v>45246</v>
       </c>
       <c r="B749" t="n">
-        <v>31.13239860534668</v>
+        <v>31.13239669799805</v>
       </c>
       <c r="C749" t="n">
-        <v>32.13444975439192</v>
+        <v>32.13444778565191</v>
       </c>
       <c r="D749" t="n">
-        <v>30.68049156858774</v>
+        <v>30.68048968892551</v>
       </c>
       <c r="E749" t="n">
-        <v>31.78078354073604</v>
+        <v>31.78078159366364</v>
       </c>
       <c r="F749" t="n">
         <v>5148500</v>
@@ -15492,16 +15492,16 @@
         <v>45253</v>
       </c>
       <c r="B754" t="n">
-        <v>31.81025505065918</v>
+        <v>31.81025886535645</v>
       </c>
       <c r="C754" t="n">
-        <v>32.00673667726713</v>
+        <v>32.00674051552654</v>
       </c>
       <c r="D754" t="n">
-        <v>31.5843024917114</v>
+        <v>31.58430627931235</v>
       </c>
       <c r="E754" t="n">
-        <v>31.82990358807751</v>
+        <v>31.82990740513103</v>
       </c>
       <c r="F754" t="n">
         <v>2086300</v>
@@ -15552,16 +15552,16 @@
         <v>45258</v>
       </c>
       <c r="B757" t="n">
-        <v>29.80615043640137</v>
+        <v>29.80615234375</v>
       </c>
       <c r="C757" t="n">
-        <v>30.21876037029583</v>
+        <v>30.21876230404811</v>
       </c>
       <c r="D757" t="n">
-        <v>29.63914160902057</v>
+        <v>29.63914350568201</v>
       </c>
       <c r="E757" t="n">
-        <v>30.17946329383553</v>
+        <v>30.17946522507312</v>
       </c>
       <c r="F757" t="n">
         <v>5777500</v>
@@ -15592,16 +15592,16 @@
         <v>45260</v>
       </c>
       <c r="B759" t="n">
-        <v>29.45248603820801</v>
+        <v>29.45248413085938</v>
       </c>
       <c r="C759" t="n">
-        <v>29.83562506189301</v>
+        <v>29.83562312973222</v>
       </c>
       <c r="D759" t="n">
-        <v>29.1774139813743</v>
+        <v>29.17741209183939</v>
       </c>
       <c r="E759" t="n">
-        <v>29.66861622433489</v>
+        <v>29.66861430298963</v>
       </c>
       <c r="F759" t="n">
         <v>4483800</v>
@@ -15732,16 +15732,16 @@
         <v>45271</v>
       </c>
       <c r="B766" t="n">
-        <v>26.91788101196289</v>
+        <v>26.91788291931152</v>
       </c>
       <c r="C766" t="n">
-        <v>27.08488984004369</v>
+        <v>27.08489175922624</v>
       </c>
       <c r="D766" t="n">
-        <v>26.48562253802652</v>
+        <v>26.48562441474616</v>
       </c>
       <c r="E766" t="n">
-        <v>26.96700235774415</v>
+        <v>26.96700426857343</v>
       </c>
       <c r="F766" t="n">
         <v>6627000</v>
@@ -15792,16 +15792,16 @@
         <v>45274</v>
       </c>
       <c r="B769" t="n">
-        <v>27.00629997253418</v>
+        <v>27.00629806518555</v>
       </c>
       <c r="C769" t="n">
-        <v>27.20278162563166</v>
+        <v>27.2027797044063</v>
       </c>
       <c r="D769" t="n">
-        <v>26.49544917351107</v>
+        <v>26.49544730224182</v>
       </c>
       <c r="E769" t="n">
-        <v>26.82946685950403</v>
+        <v>26.82946496464443</v>
       </c>
       <c r="F769" t="n">
         <v>14011300</v>
@@ -15812,16 +15812,16 @@
         <v>45275</v>
       </c>
       <c r="B770" t="n">
-        <v>25.8863582611084</v>
+        <v>25.88635635375977</v>
       </c>
       <c r="C770" t="n">
-        <v>27.21260467558413</v>
+        <v>27.21260267051552</v>
       </c>
       <c r="D770" t="n">
-        <v>25.8863582611084</v>
+        <v>25.88635635375977</v>
       </c>
       <c r="E770" t="n">
-        <v>27.16348332761816</v>
+        <v>27.1634813261689</v>
       </c>
       <c r="F770" t="n">
         <v>11924000</v>
@@ -15832,16 +15832,16 @@
         <v>45278</v>
       </c>
       <c r="B771" t="n">
-        <v>26.21055221557617</v>
+        <v>26.21055030822754</v>
       </c>
       <c r="C771" t="n">
-        <v>26.76069820788825</v>
+        <v>26.76069626050536</v>
       </c>
       <c r="D771" t="n">
-        <v>25.94530255232668</v>
+        <v>25.94530066428034</v>
       </c>
       <c r="E771" t="n">
-        <v>26.12213566115967</v>
+        <v>26.12213376024514</v>
       </c>
       <c r="F771" t="n">
         <v>4958200</v>
@@ -15852,16 +15852,16 @@
         <v>45279</v>
       </c>
       <c r="B772" t="n">
-        <v>26.32843780517578</v>
+        <v>26.32843971252441</v>
       </c>
       <c r="C772" t="n">
-        <v>26.52491943942738</v>
+        <v>26.52492136101001</v>
       </c>
       <c r="D772" t="n">
-        <v>26.13195804471192</v>
+        <v>26.13195993782669</v>
       </c>
       <c r="E772" t="n">
-        <v>26.30879114078081</v>
+        <v>26.30879304670615</v>
       </c>
       <c r="F772" t="n">
         <v>3900900</v>
@@ -15872,16 +15872,16 @@
         <v>45280</v>
       </c>
       <c r="B773" t="n">
-        <v>25.85688400268555</v>
+        <v>25.85688591003418</v>
       </c>
       <c r="C773" t="n">
-        <v>26.54456784535201</v>
+        <v>26.54456980342805</v>
       </c>
       <c r="D773" t="n">
-        <v>25.68987517654013</v>
+        <v>25.68987707156926</v>
       </c>
       <c r="E773" t="n">
-        <v>26.54456784535201</v>
+        <v>26.54456980342805</v>
       </c>
       <c r="F773" t="n">
         <v>6168300</v>
@@ -15912,16 +15912,16 @@
         <v>45282</v>
       </c>
       <c r="B775" t="n">
-        <v>25.95512771606445</v>
+        <v>25.95512580871582</v>
       </c>
       <c r="C775" t="n">
-        <v>26.22037738844958</v>
+        <v>26.2203754616087</v>
       </c>
       <c r="D775" t="n">
-        <v>25.79794314141873</v>
+        <v>25.79794124562103</v>
       </c>
       <c r="E775" t="n">
-        <v>26.03372000338731</v>
+        <v>26.03371809026321</v>
       </c>
       <c r="F775" t="n">
         <v>3644200</v>
@@ -16012,16 +16012,16 @@
         <v>45294</v>
       </c>
       <c r="B780" t="n">
-        <v>25.8863582611084</v>
+        <v>25.88635635375977</v>
       </c>
       <c r="C780" t="n">
-        <v>26.28914394549015</v>
+        <v>26.28914200846361</v>
       </c>
       <c r="D780" t="n">
-        <v>25.35585894580298</v>
+        <v>25.35585707754239</v>
       </c>
       <c r="E780" t="n">
-        <v>25.64075714264207</v>
+        <v>25.64075525338972</v>
       </c>
       <c r="F780" t="n">
         <v>5734800</v>
@@ -16052,16 +16052,16 @@
         <v>45296</v>
       </c>
       <c r="B782" t="n">
-        <v>25.68987655639648</v>
+        <v>25.68987464904785</v>
       </c>
       <c r="C782" t="n">
-        <v>25.97477475256549</v>
+        <v>25.97477282406455</v>
       </c>
       <c r="D782" t="n">
-        <v>25.21832285975933</v>
+        <v>25.21832098742127</v>
       </c>
       <c r="E782" t="n">
-        <v>25.36568315573496</v>
+        <v>25.36568127245611</v>
       </c>
       <c r="F782" t="n">
         <v>3417300</v>
@@ -16092,16 +16092,16 @@
         <v>45300</v>
       </c>
       <c r="B784" t="n">
-        <v>28.0181770324707</v>
+        <v>28.01817512512207</v>
       </c>
       <c r="C784" t="n">
-        <v>28.24412961971936</v>
+        <v>28.24412769698892</v>
       </c>
       <c r="D784" t="n">
-        <v>26.7999956667704</v>
+        <v>26.79999384234995</v>
       </c>
       <c r="E784" t="n">
-        <v>27.01612398407939</v>
+        <v>27.01612214494592</v>
       </c>
       <c r="F784" t="n">
         <v>10290300</v>
@@ -16152,16 +16152,16 @@
         <v>45303</v>
       </c>
       <c r="B787" t="n">
-        <v>28.20483016967773</v>
+        <v>28.20483207702637</v>
       </c>
       <c r="C787" t="n">
-        <v>28.86304121001741</v>
+        <v>28.86304316187749</v>
       </c>
       <c r="D787" t="n">
-        <v>27.82169304316834</v>
+        <v>27.82169492460737</v>
       </c>
       <c r="E787" t="n">
-        <v>28.63708864175739</v>
+        <v>28.63709057833746</v>
       </c>
       <c r="F787" t="n">
         <v>5067700</v>
@@ -16172,16 +16172,16 @@
         <v>45306</v>
       </c>
       <c r="B788" t="n">
-        <v>28.52902603149414</v>
+        <v>28.52902793884277</v>
       </c>
       <c r="C788" t="n">
-        <v>28.68621059306261</v>
+        <v>28.68621251092004</v>
       </c>
       <c r="D788" t="n">
-        <v>27.90028591143248</v>
+        <v>27.9002877767458</v>
       </c>
       <c r="E788" t="n">
-        <v>28.06729474232245</v>
+        <v>28.06729661880138</v>
       </c>
       <c r="F788" t="n">
         <v>3859400</v>
@@ -16252,16 +16252,16 @@
         <v>45310</v>
       </c>
       <c r="B792" t="n">
-        <v>29.03005218505859</v>
+        <v>29.03005027770996</v>
       </c>
       <c r="C792" t="n">
-        <v>29.19706102477754</v>
+        <v>29.197059106456</v>
       </c>
       <c r="D792" t="n">
-        <v>28.05747195626752</v>
+        <v>28.0574701128199</v>
       </c>
       <c r="E792" t="n">
-        <v>28.73533158498416</v>
+        <v>28.73532969699943</v>
       </c>
       <c r="F792" t="n">
         <v>7851200</v>
@@ -16312,16 +16312,16 @@
         <v>45315</v>
       </c>
       <c r="B795" t="n">
-        <v>27.86099052429199</v>
+        <v>27.86099243164062</v>
       </c>
       <c r="C795" t="n">
-        <v>28.52902584344861</v>
+        <v>28.52902779653059</v>
       </c>
       <c r="D795" t="n">
-        <v>27.63503607896236</v>
+        <v>27.63503797084227</v>
       </c>
       <c r="E795" t="n">
-        <v>28.04764601880687</v>
+        <v>28.04764793893384</v>
       </c>
       <c r="F795" t="n">
         <v>4070600</v>
@@ -16352,16 +16352,16 @@
         <v>45317</v>
       </c>
       <c r="B797" t="n">
-        <v>28.2441291809082</v>
+        <v>28.24412727355957</v>
       </c>
       <c r="C797" t="n">
-        <v>28.2441291809082</v>
+        <v>28.24412727355957</v>
       </c>
       <c r="D797" t="n">
-        <v>27.50732581097147</v>
+        <v>27.50732395337975</v>
       </c>
       <c r="E797" t="n">
-        <v>27.65468611020124</v>
+        <v>27.65468424265817</v>
       </c>
       <c r="F797" t="n">
         <v>2761100</v>
@@ -16392,16 +16392,16 @@
         <v>45321</v>
       </c>
       <c r="B799" t="n">
-        <v>27.24207496643066</v>
+        <v>27.2420768737793</v>
       </c>
       <c r="C799" t="n">
-        <v>27.54662169525507</v>
+        <v>27.54662362392648</v>
       </c>
       <c r="D799" t="n">
-        <v>26.97682531504984</v>
+        <v>26.97682720382707</v>
       </c>
       <c r="E799" t="n">
-        <v>27.36978859433452</v>
+        <v>27.369790510625</v>
       </c>
       <c r="F799" t="n">
         <v>2184900</v>
@@ -16432,16 +16432,16 @@
         <v>45323</v>
       </c>
       <c r="B801" t="n">
-        <v>26.24002075195312</v>
+        <v>26.24002265930176</v>
       </c>
       <c r="C801" t="n">
-        <v>27.4090825182884</v>
+        <v>27.40908451061442</v>
       </c>
       <c r="D801" t="n">
-        <v>26.10248473489757</v>
+        <v>26.10248663224892</v>
       </c>
       <c r="E801" t="n">
-        <v>27.31084170305399</v>
+        <v>27.31084368823903</v>
       </c>
       <c r="F801" t="n">
         <v>7611700</v>
@@ -16532,16 +16532,16 @@
         <v>45330</v>
       </c>
       <c r="B806" t="n">
-        <v>28.79427337646484</v>
+        <v>28.79427528381348</v>
       </c>
       <c r="C806" t="n">
-        <v>28.81392191481336</v>
+        <v>28.81392382346353</v>
       </c>
       <c r="D806" t="n">
-        <v>27.39925900811183</v>
+        <v>27.39926082305394</v>
       </c>
       <c r="E806" t="n">
-        <v>28.71568109685852</v>
+        <v>28.71568299900116</v>
       </c>
       <c r="F806" t="n">
         <v>6908300</v>
@@ -16552,16 +16552,16 @@
         <v>45331</v>
       </c>
       <c r="B807" t="n">
-        <v>27.69398307800293</v>
+        <v>27.6939811706543</v>
       </c>
       <c r="C807" t="n">
-        <v>28.9121644198793</v>
+        <v>28.9121624286317</v>
       </c>
       <c r="D807" t="n">
-        <v>27.52697423987057</v>
+        <v>27.52697234402422</v>
       </c>
       <c r="E807" t="n">
-        <v>28.83357213568689</v>
+        <v>28.83357014985212</v>
       </c>
       <c r="F807" t="n">
         <v>5513900</v>
@@ -16592,16 +16592,16 @@
         <v>45337</v>
       </c>
       <c r="B809" t="n">
-        <v>28.00835037231445</v>
+        <v>28.00835227966309</v>
       </c>
       <c r="C809" t="n">
-        <v>28.26377574758426</v>
+        <v>28.26377767232718</v>
       </c>
       <c r="D809" t="n">
-        <v>27.28137132291011</v>
+        <v>27.28137318075199</v>
       </c>
       <c r="E809" t="n">
-        <v>27.40908307365115</v>
+        <v>27.40908494019011</v>
       </c>
       <c r="F809" t="n">
         <v>2788300</v>
@@ -16632,16 +16632,16 @@
         <v>45341</v>
       </c>
       <c r="B811" t="n">
-        <v>28.6763858795166</v>
+        <v>28.67638778686523</v>
       </c>
       <c r="C811" t="n">
-        <v>28.76480242825268</v>
+        <v>28.76480434148215</v>
       </c>
       <c r="D811" t="n">
-        <v>28.2343031358362</v>
+        <v>28.23430501378064</v>
       </c>
       <c r="E811" t="n">
-        <v>28.74515388991405</v>
+        <v>28.74515580183664</v>
       </c>
       <c r="F811" t="n">
         <v>1698200</v>
@@ -16672,16 +16672,16 @@
         <v>45343</v>
       </c>
       <c r="B813" t="n">
-        <v>28.92198753356934</v>
+        <v>28.92198944091797</v>
       </c>
       <c r="C813" t="n">
-        <v>28.98093127591061</v>
+        <v>28.98093318714647</v>
       </c>
       <c r="D813" t="n">
-        <v>28.36201729685779</v>
+        <v>28.36201916727748</v>
       </c>
       <c r="E813" t="n">
-        <v>28.63708934364225</v>
+        <v>28.6370912322024</v>
       </c>
       <c r="F813" t="n">
         <v>2751400</v>
@@ -16792,16 +16792,16 @@
         <v>45351</v>
       </c>
       <c r="B819" t="n">
-        <v>27.45820426940918</v>
+        <v>27.45820617675781</v>
       </c>
       <c r="C819" t="n">
-        <v>28.14588623865804</v>
+        <v>28.14588819377561</v>
       </c>
       <c r="D819" t="n">
-        <v>27.45820426940918</v>
+        <v>27.45820617675781</v>
       </c>
       <c r="E819" t="n">
-        <v>27.98870168147043</v>
+        <v>27.98870362566938</v>
       </c>
       <c r="F819" t="n">
         <v>2784300</v>
@@ -16972,16 +16972,16 @@
         <v>45364</v>
       </c>
       <c r="B828" t="n">
-        <v>29.13811492919922</v>
+        <v>29.13811683654785</v>
       </c>
       <c r="C828" t="n">
-        <v>29.36406749594983</v>
+        <v>29.36406941808906</v>
       </c>
       <c r="D828" t="n">
-        <v>28.98093037199986</v>
+        <v>28.98093226905937</v>
       </c>
       <c r="E828" t="n">
-        <v>28.98093037199986</v>
+        <v>28.98093226905937</v>
       </c>
       <c r="F828" t="n">
         <v>2596400</v>
@@ -17032,16 +17032,16 @@
         <v>45369</v>
       </c>
       <c r="B831" t="n">
-        <v>28.98093223571777</v>
+        <v>28.98093032836914</v>
       </c>
       <c r="C831" t="n">
-        <v>29.28547710065286</v>
+        <v>29.28547517326093</v>
       </c>
       <c r="D831" t="n">
-        <v>28.61744175270144</v>
+        <v>28.61743986927554</v>
       </c>
       <c r="E831" t="n">
-        <v>28.77462819379693</v>
+        <v>28.77462630002598</v>
       </c>
       <c r="F831" t="n">
         <v>4710300</v>
@@ -17112,16 +17112,16 @@
         <v>45373</v>
       </c>
       <c r="B835" t="n">
-        <v>29.71773529052734</v>
+        <v>29.71773338317871</v>
       </c>
       <c r="C835" t="n">
-        <v>30.0026334869456</v>
+        <v>30.00263156131158</v>
       </c>
       <c r="D835" t="n">
-        <v>29.28547679800454</v>
+        <v>29.28547491839919</v>
       </c>
       <c r="E835" t="n">
-        <v>29.88474412578926</v>
+        <v>29.88474220772164</v>
       </c>
       <c r="F835" t="n">
         <v>3854000</v>
@@ -17152,16 +17152,16 @@
         <v>45377</v>
       </c>
       <c r="B837" t="n">
-        <v>30.81802749633789</v>
+        <v>30.81802940368652</v>
       </c>
       <c r="C837" t="n">
-        <v>31.22081315885015</v>
+        <v>31.22081509112746</v>
       </c>
       <c r="D837" t="n">
-        <v>30.51348077684796</v>
+        <v>30.51348266534799</v>
       </c>
       <c r="E837" t="n">
-        <v>30.61172159365801</v>
+        <v>30.61172348823823</v>
       </c>
       <c r="F837" t="n">
         <v>3327200</v>
@@ -17172,16 +17172,16 @@
         <v>45378</v>
       </c>
       <c r="B838" t="n">
-        <v>31.48606109619141</v>
+        <v>31.48606300354004</v>
       </c>
       <c r="C838" t="n">
-        <v>31.91832144197546</v>
+        <v>31.91832337550937</v>
       </c>
       <c r="D838" t="n">
-        <v>30.3857691886579</v>
+        <v>30.38577102935353</v>
       </c>
       <c r="E838" t="n">
-        <v>30.65101883332299</v>
+        <v>30.6510206900868</v>
       </c>
       <c r="F838" t="n">
         <v>9071000</v>
@@ -17372,16 +17372,16 @@
         <v>45393</v>
       </c>
       <c r="B848" t="n">
-        <v>35.62198638916016</v>
+        <v>35.62198257446289</v>
       </c>
       <c r="C848" t="n">
-        <v>35.91671074440308</v>
+        <v>35.91670689814429</v>
       </c>
       <c r="D848" t="n">
-        <v>34.59046238853748</v>
+        <v>34.59045868430435</v>
       </c>
       <c r="E848" t="n">
-        <v>34.74764696246498</v>
+        <v>34.74764324139922</v>
       </c>
       <c r="F848" t="n">
         <v>5960900</v>
@@ -17412,16 +17412,16 @@
         <v>45397</v>
       </c>
       <c r="B850" t="n">
-        <v>34.06978607177734</v>
+        <v>34.06978988647461</v>
       </c>
       <c r="C850" t="n">
-        <v>34.52169121201051</v>
+        <v>34.52169507730631</v>
       </c>
       <c r="D850" t="n">
-        <v>33.83400735867823</v>
+        <v>33.83401114697602</v>
       </c>
       <c r="E850" t="n">
-        <v>34.43327466304528</v>
+        <v>34.43327851844133</v>
       </c>
       <c r="F850" t="n">
         <v>4151100</v>
@@ -17472,16 +17472,16 @@
         <v>45400</v>
       </c>
       <c r="B853" t="n">
-        <v>32.3309326171875</v>
+        <v>32.33092880249023</v>
       </c>
       <c r="C853" t="n">
-        <v>33.28386620122118</v>
+        <v>33.28386227408815</v>
       </c>
       <c r="D853" t="n">
-        <v>31.93796930998834</v>
+        <v>31.93796554165645</v>
       </c>
       <c r="E853" t="n">
-        <v>33.00879038715143</v>
+        <v>33.00878649247434</v>
       </c>
       <c r="F853" t="n">
         <v>4478700</v>
@@ -17632,16 +17632,16 @@
         <v>45412</v>
       </c>
       <c r="B861" t="n">
-        <v>32.58635711669922</v>
+        <v>32.58635330200195</v>
       </c>
       <c r="C861" t="n">
-        <v>33.66700436998067</v>
+        <v>33.66700042877825</v>
       </c>
       <c r="D861" t="n">
-        <v>32.43899868278081</v>
+        <v>32.43899488533395</v>
       </c>
       <c r="E861" t="n">
-        <v>33.60805874786774</v>
+        <v>33.60805481356574</v>
       </c>
       <c r="F861" t="n">
         <v>6661700</v>
@@ -29592,19 +29592,39 @@
         <v>46287</v>
       </c>
       <c r="B1459" t="n">
-        <v>17.89</v>
+        <v>17.88999938964844</v>
       </c>
       <c r="C1459" t="n">
-        <v>17.89</v>
+        <v>17.88999938964844</v>
       </c>
       <c r="D1459" t="n">
-        <v>17.18</v>
+        <v>17.18000030517578</v>
       </c>
       <c r="E1459" t="n">
-        <v>17.18</v>
+        <v>17.18000030517578</v>
       </c>
       <c r="F1459" t="n">
         <v>3016800</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B1460" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="C1460" t="n">
+        <v>18.02</v>
+      </c>
+      <c r="D1460" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="E1460" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F1460" t="n">
+        <v>2251900</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1460"/>
+  <dimension ref="A1:F1461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,16 +512,16 @@
         <v>44152</v>
       </c>
       <c r="B5" t="n">
-        <v>20.17695617675781</v>
+        <v>20.17695426940918</v>
       </c>
       <c r="C5" t="n">
-        <v>20.17695617675781</v>
+        <v>20.17695426940918</v>
       </c>
       <c r="D5" t="n">
-        <v>19.85012633435968</v>
+        <v>19.85012445790661</v>
       </c>
       <c r="E5" t="n">
-        <v>20.12889164196659</v>
+        <v>20.12888973916155</v>
       </c>
       <c r="F5" t="n">
         <v>262242</v>
@@ -572,16 +572,16 @@
         <v>44158</v>
       </c>
       <c r="B8" t="n">
-        <v>20.2057933807373</v>
+        <v>20.20579147338867</v>
       </c>
       <c r="C8" t="n">
-        <v>20.52301068477087</v>
+        <v>20.52300874747816</v>
       </c>
       <c r="D8" t="n">
-        <v>20.14811818865408</v>
+        <v>20.14811628674976</v>
       </c>
       <c r="E8" t="n">
-        <v>20.14811818865408</v>
+        <v>20.14811628674976</v>
       </c>
       <c r="F8" t="n">
         <v>79408</v>
@@ -632,16 +632,16 @@
         <v>44161</v>
       </c>
       <c r="B11" t="n">
-        <v>22.87811088562012</v>
+        <v>22.87810897827148</v>
       </c>
       <c r="C11" t="n">
-        <v>22.87811088562012</v>
+        <v>22.87810897827148</v>
       </c>
       <c r="D11" t="n">
-        <v>22.3109640047031</v>
+        <v>22.31096214463751</v>
       </c>
       <c r="E11" t="n">
-        <v>22.3109640047031</v>
+        <v>22.31096214463751</v>
       </c>
       <c r="F11" t="n">
         <v>72970</v>
@@ -652,16 +652,16 @@
         <v>44162</v>
       </c>
       <c r="B12" t="n">
-        <v>23.07036209106445</v>
+        <v>23.07036399841309</v>
       </c>
       <c r="C12" t="n">
-        <v>23.55099428329309</v>
+        <v>23.55099623037812</v>
       </c>
       <c r="D12" t="n">
-        <v>22.10909770660719</v>
+        <v>22.10909953448302</v>
       </c>
       <c r="E12" t="n">
-        <v>23.07036209106445</v>
+        <v>23.07036399841309</v>
       </c>
       <c r="F12" t="n">
         <v>72050</v>
@@ -692,16 +692,16 @@
         <v>44166</v>
       </c>
       <c r="B14" t="n">
-        <v>23.07036209106445</v>
+        <v>23.07036399841309</v>
       </c>
       <c r="C14" t="n">
-        <v>23.1664892790253</v>
+        <v>23.16649119432127</v>
       </c>
       <c r="D14" t="n">
-        <v>23.03191196539523</v>
+        <v>23.03191386956499</v>
       </c>
       <c r="E14" t="n">
-        <v>23.12803727956828</v>
+        <v>23.12803919168523</v>
       </c>
       <c r="F14" t="n">
         <v>93512</v>
@@ -792,16 +792,16 @@
         <v>44173</v>
       </c>
       <c r="B19" t="n">
-        <v>26.33866500854492</v>
+        <v>26.33866310119629</v>
       </c>
       <c r="C19" t="n">
-        <v>26.57898205078916</v>
+        <v>26.57898012603766</v>
       </c>
       <c r="D19" t="n">
-        <v>25.56965309666637</v>
+        <v>25.56965124500673</v>
       </c>
       <c r="E19" t="n">
-        <v>25.56965309666637</v>
+        <v>25.56965124500673</v>
       </c>
       <c r="F19" t="n">
         <v>126420</v>
@@ -812,16 +812,16 @@
         <v>44174</v>
       </c>
       <c r="B20" t="n">
-        <v>26.83852005004883</v>
+        <v>26.83852195739746</v>
       </c>
       <c r="C20" t="n">
-        <v>27.77094867230641</v>
+        <v>27.77095064592048</v>
       </c>
       <c r="D20" t="n">
-        <v>26.27137510044991</v>
+        <v>26.27137696749292</v>
       </c>
       <c r="E20" t="n">
-        <v>26.4924651869397</v>
+        <v>26.49246706969505</v>
       </c>
       <c r="F20" t="n">
         <v>212880</v>
@@ -892,16 +892,16 @@
         <v>44180</v>
       </c>
       <c r="B24" t="n">
-        <v>33.00984191894531</v>
+        <v>33.00984573364258</v>
       </c>
       <c r="C24" t="n">
-        <v>33.9807187406613</v>
+        <v>33.98072266755544</v>
       </c>
       <c r="D24" t="n">
-        <v>30.7604798048412</v>
+        <v>30.76048335959674</v>
       </c>
       <c r="E24" t="n">
-        <v>30.7604798048412</v>
+        <v>30.76048335959674</v>
       </c>
       <c r="F24" t="n">
         <v>887803</v>
@@ -912,16 +912,16 @@
         <v>44181</v>
       </c>
       <c r="B25" t="n">
-        <v>32.68301773071289</v>
+        <v>32.68301391601562</v>
       </c>
       <c r="C25" t="n">
-        <v>34.4517423806715</v>
+        <v>34.45173835953219</v>
       </c>
       <c r="D25" t="n">
-        <v>32.10625830770921</v>
+        <v>32.10625456033017</v>
       </c>
       <c r="E25" t="n">
-        <v>33.62505712226533</v>
+        <v>33.62505319761509</v>
       </c>
       <c r="F25" t="n">
         <v>376808</v>
@@ -932,16 +932,16 @@
         <v>44182</v>
       </c>
       <c r="B26" t="n">
-        <v>32.10625457763672</v>
+        <v>32.10625839233398</v>
       </c>
       <c r="C26" t="n">
-        <v>33.64427827776851</v>
+        <v>33.64428227520571</v>
       </c>
       <c r="D26" t="n">
-        <v>31.64484559380946</v>
+        <v>31.64484935368452</v>
       </c>
       <c r="E26" t="n">
-        <v>33.62505321574033</v>
+        <v>33.6250572108933</v>
       </c>
       <c r="F26" t="n">
         <v>258257</v>
@@ -972,16 +972,16 @@
         <v>44186</v>
       </c>
       <c r="B28" t="n">
-        <v>32.18315505981445</v>
+        <v>32.18315887451172</v>
       </c>
       <c r="C28" t="n">
-        <v>33.33667378019659</v>
+        <v>33.33667773162143</v>
       </c>
       <c r="D28" t="n">
-        <v>29.12633082555934</v>
+        <v>29.12633427792858</v>
       </c>
       <c r="E28" t="n">
-        <v>31.86593778646691</v>
+        <v>31.86594156356414</v>
       </c>
       <c r="F28" t="n">
         <v>236079</v>
@@ -992,16 +992,16 @@
         <v>44187</v>
       </c>
       <c r="B29" t="n">
-        <v>33.16364669799805</v>
+        <v>33.16364288330078</v>
       </c>
       <c r="C29" t="n">
-        <v>33.47125146089823</v>
+        <v>33.47124761081827</v>
       </c>
       <c r="D29" t="n">
-        <v>32.59649983084212</v>
+        <v>32.59649608138177</v>
       </c>
       <c r="E29" t="n">
-        <v>33.21170935664249</v>
+        <v>33.21170553641675</v>
       </c>
       <c r="F29" t="n">
         <v>167504</v>
@@ -1032,16 +1032,16 @@
         <v>44193</v>
       </c>
       <c r="B31" t="n">
-        <v>36.21085357666016</v>
+        <v>36.21085739135742</v>
       </c>
       <c r="C31" t="n">
-        <v>36.66265002370312</v>
+        <v>36.66265388599569</v>
       </c>
       <c r="D31" t="n">
-        <v>35.56680651179074</v>
+        <v>35.56681025863972</v>
       </c>
       <c r="E31" t="n">
-        <v>35.56680651179074</v>
+        <v>35.56681025863972</v>
       </c>
       <c r="F31" t="n">
         <v>451822</v>
@@ -1052,16 +1052,16 @@
         <v>44194</v>
       </c>
       <c r="B32" t="n">
-        <v>36.09550857543945</v>
+        <v>36.09550476074219</v>
       </c>
       <c r="C32" t="n">
-        <v>37.06638558261441</v>
+        <v>37.06638166531152</v>
       </c>
       <c r="D32" t="n">
-        <v>35.95131684304462</v>
+        <v>35.95131304358604</v>
       </c>
       <c r="E32" t="n">
-        <v>36.52807627747203</v>
+        <v>36.52807241705953</v>
       </c>
       <c r="F32" t="n">
         <v>337154</v>
@@ -1092,16 +1092,16 @@
         <v>44200</v>
       </c>
       <c r="B34" t="n">
-        <v>34.99966430664062</v>
+        <v>34.99966049194336</v>
       </c>
       <c r="C34" t="n">
-        <v>36.62420472682393</v>
+        <v>36.62420073506411</v>
       </c>
       <c r="D34" t="n">
-        <v>34.98043924232432</v>
+        <v>34.98043542972244</v>
       </c>
       <c r="E34" t="n">
-        <v>36.52807565766651</v>
+        <v>36.52807167638402</v>
       </c>
       <c r="F34" t="n">
         <v>331840</v>
@@ -1112,16 +1112,16 @@
         <v>44201</v>
       </c>
       <c r="B35" t="n">
-        <v>36.13395309448242</v>
+        <v>36.13395690917969</v>
       </c>
       <c r="C35" t="n">
-        <v>36.32620745863368</v>
+        <v>36.32621129362743</v>
       </c>
       <c r="D35" t="n">
-        <v>34.60554195482727</v>
+        <v>34.60554560816865</v>
       </c>
       <c r="E35" t="n">
-        <v>35.45145591048728</v>
+        <v>35.45145965313264</v>
       </c>
       <c r="F35" t="n">
         <v>328059</v>
@@ -1172,16 +1172,16 @@
         <v>44204</v>
       </c>
       <c r="B38" t="n">
-        <v>34.134521484375</v>
+        <v>34.13452529907227</v>
       </c>
       <c r="C38" t="n">
-        <v>35.75906172916622</v>
+        <v>35.75906572541368</v>
       </c>
       <c r="D38" t="n">
-        <v>34.134521484375</v>
+        <v>34.13452529907227</v>
       </c>
       <c r="E38" t="n">
-        <v>35.16307730455386</v>
+        <v>35.16308123419719</v>
       </c>
       <c r="F38" t="n">
         <v>367201</v>
@@ -1272,16 +1272,16 @@
         <v>44211</v>
       </c>
       <c r="B43" t="n">
-        <v>33.9422721862793</v>
+        <v>33.94226837158203</v>
       </c>
       <c r="C43" t="n">
-        <v>35.0477245509764</v>
+        <v>35.04772061203977</v>
       </c>
       <c r="D43" t="n">
-        <v>33.16364589242556</v>
+        <v>33.16364216523639</v>
       </c>
       <c r="E43" t="n">
-        <v>34.60554435461268</v>
+        <v>34.60554046537172</v>
       </c>
       <c r="F43" t="n">
         <v>319883</v>
@@ -1292,16 +1292,16 @@
         <v>44214</v>
       </c>
       <c r="B44" t="n">
-        <v>34.04800796508789</v>
+        <v>34.04801177978516</v>
       </c>
       <c r="C44" t="n">
-        <v>34.50941694399793</v>
+        <v>34.5094208103909</v>
       </c>
       <c r="D44" t="n">
-        <v>33.27899799700501</v>
+        <v>33.27900172554335</v>
       </c>
       <c r="E44" t="n">
-        <v>34.11529568146945</v>
+        <v>34.11529950370554</v>
       </c>
       <c r="F44" t="n">
         <v>117631</v>
@@ -1332,16 +1332,16 @@
         <v>44216</v>
       </c>
       <c r="B46" t="n">
-        <v>34.12491226196289</v>
+        <v>34.12490844726562</v>
       </c>
       <c r="C46" t="n">
-        <v>35.28804363060232</v>
+        <v>35.28803968588292</v>
       </c>
       <c r="D46" t="n">
-        <v>33.66350697587357</v>
+        <v>33.66350321275509</v>
       </c>
       <c r="E46" t="n">
-        <v>34.60554635973278</v>
+        <v>34.60554249130722</v>
       </c>
       <c r="F46" t="n">
         <v>359332</v>
@@ -1372,16 +1372,16 @@
         <v>44218</v>
       </c>
       <c r="B48" t="n">
-        <v>32.95216751098633</v>
+        <v>32.95216369628906</v>
       </c>
       <c r="C48" t="n">
-        <v>33.45202665996278</v>
+        <v>33.45202278739948</v>
       </c>
       <c r="D48" t="n">
-        <v>32.53882489582456</v>
+        <v>32.53882112897777</v>
       </c>
       <c r="E48" t="n">
-        <v>33.19248455367023</v>
+        <v>33.19248071115274</v>
       </c>
       <c r="F48" t="n">
         <v>220341</v>
@@ -1472,16 +1472,16 @@
         <v>44228</v>
       </c>
       <c r="B53" t="n">
-        <v>31.77942657470703</v>
+        <v>31.7794246673584</v>
       </c>
       <c r="C53" t="n">
-        <v>33.11558345161116</v>
+        <v>33.1155814640686</v>
       </c>
       <c r="D53" t="n">
-        <v>31.66407244843196</v>
+        <v>31.66407054800669</v>
       </c>
       <c r="E53" t="n">
-        <v>32.68301578391271</v>
+        <v>32.68301382233215</v>
       </c>
       <c r="F53" t="n">
         <v>610435</v>
@@ -1492,16 +1492,16 @@
         <v>44229</v>
       </c>
       <c r="B54" t="n">
-        <v>32.63495254516602</v>
+        <v>32.63494873046875</v>
       </c>
       <c r="C54" t="n">
-        <v>33.65389597951643</v>
+        <v>33.65389204571495</v>
       </c>
       <c r="D54" t="n">
-        <v>31.97168030813476</v>
+        <v>31.97167657096734</v>
       </c>
       <c r="E54" t="n">
-        <v>33.64428344702543</v>
+        <v>33.64427951434755</v>
       </c>
       <c r="F54" t="n">
         <v>582228</v>
@@ -1532,16 +1532,16 @@
         <v>44231</v>
       </c>
       <c r="B56" t="n">
-        <v>32.68301773071289</v>
+        <v>32.68301391601562</v>
       </c>
       <c r="C56" t="n">
-        <v>34.11530000851534</v>
+        <v>34.11529602664492</v>
       </c>
       <c r="D56" t="n">
-        <v>32.44270067986538</v>
+        <v>32.44269689321744</v>
       </c>
       <c r="E56" t="n">
-        <v>33.06752276352339</v>
+        <v>33.06751890394745</v>
       </c>
       <c r="F56" t="n">
         <v>466743</v>
@@ -1612,16 +1612,16 @@
         <v>44237</v>
       </c>
       <c r="B60" t="n">
-        <v>34.83625030517578</v>
+        <v>34.83624649047852</v>
       </c>
       <c r="C60" t="n">
-        <v>35.33610571127585</v>
+        <v>35.33610184184258</v>
       </c>
       <c r="D60" t="n">
-        <v>34.23065330065825</v>
+        <v>34.23064955227608</v>
       </c>
       <c r="E60" t="n">
-        <v>34.43251647044691</v>
+        <v>34.43251269995998</v>
       </c>
       <c r="F60" t="n">
         <v>186206</v>
@@ -1652,16 +1652,16 @@
         <v>44239</v>
       </c>
       <c r="B62" t="n">
-        <v>34.4036750793457</v>
+        <v>34.40367889404297</v>
       </c>
       <c r="C62" t="n">
-        <v>34.52864172776623</v>
+        <v>34.52864555631986</v>
       </c>
       <c r="D62" t="n">
-        <v>32.67339704372985</v>
+        <v>32.673400666573</v>
       </c>
       <c r="E62" t="n">
-        <v>33.67311524079254</v>
+        <v>33.67311897448496</v>
       </c>
       <c r="F62" t="n">
         <v>218195</v>
@@ -1692,16 +1692,16 @@
         <v>44245</v>
       </c>
       <c r="B64" t="n">
-        <v>37.00870513916016</v>
+        <v>37.00870895385742</v>
       </c>
       <c r="C64" t="n">
-        <v>37.38359759408829</v>
+        <v>37.38360144742785</v>
       </c>
       <c r="D64" t="n">
-        <v>35.71099846956061</v>
+        <v>35.71100215049589</v>
       </c>
       <c r="E64" t="n">
-        <v>36.37427060079703</v>
+        <v>36.37427435009953</v>
       </c>
       <c r="F64" t="n">
         <v>661534</v>
@@ -1812,16 +1812,16 @@
         <v>44253</v>
       </c>
       <c r="B70" t="n">
-        <v>34.57670974731445</v>
+        <v>34.57670593261719</v>
       </c>
       <c r="C70" t="n">
-        <v>37.21057733278074</v>
+        <v>37.21057322750037</v>
       </c>
       <c r="D70" t="n">
-        <v>33.75002072456356</v>
+        <v>33.75001700107128</v>
       </c>
       <c r="E70" t="n">
-        <v>36.53768882724342</v>
+        <v>36.5376847961999</v>
       </c>
       <c r="F70" t="n">
         <v>410022</v>
@@ -1932,16 +1932,16 @@
         <v>44263</v>
       </c>
       <c r="B76" t="n">
-        <v>41.91115570068359</v>
+        <v>41.91115951538086</v>
       </c>
       <c r="C76" t="n">
-        <v>44.60269808495321</v>
+        <v>44.60270214463106</v>
       </c>
       <c r="D76" t="n">
-        <v>40.70957434605565</v>
+        <v>40.70957805138659</v>
       </c>
       <c r="E76" t="n">
-        <v>43.55492097253444</v>
+        <v>43.55492493684502</v>
       </c>
       <c r="F76" t="n">
         <v>1012691</v>
@@ -1952,16 +1952,16 @@
         <v>44264</v>
       </c>
       <c r="B77" t="n">
-        <v>43.50685882568359</v>
+        <v>43.50686264038086</v>
       </c>
       <c r="C77" t="n">
-        <v>43.50685882568359</v>
+        <v>43.50686264038086</v>
       </c>
       <c r="D77" t="n">
-        <v>39.89249844113039</v>
+        <v>39.89250193891922</v>
       </c>
       <c r="E77" t="n">
-        <v>42.29566117843103</v>
+        <v>42.29566488693005</v>
       </c>
       <c r="F77" t="n">
         <v>563525</v>
@@ -1972,16 +1972,16 @@
         <v>44265</v>
       </c>
       <c r="B78" t="n">
-        <v>44.69882965087891</v>
+        <v>44.69882583618164</v>
       </c>
       <c r="C78" t="n">
-        <v>44.89108404365759</v>
+        <v>44.89108021255291</v>
       </c>
       <c r="D78" t="n">
-        <v>43.38189774093629</v>
+        <v>43.38189403862891</v>
       </c>
       <c r="E78" t="n">
-        <v>43.83369425231464</v>
+        <v>43.83369051144994</v>
       </c>
       <c r="F78" t="n">
         <v>425454</v>
@@ -2012,16 +2012,16 @@
         <v>44267</v>
       </c>
       <c r="B80" t="n">
-        <v>45.66009140014648</v>
+        <v>45.66009521484375</v>
       </c>
       <c r="C80" t="n">
-        <v>49.01490590711195</v>
+        <v>49.01491000208902</v>
       </c>
       <c r="D80" t="n">
-        <v>45.18906989096082</v>
+        <v>45.18907366630634</v>
       </c>
       <c r="E80" t="n">
-        <v>47.15005242731743</v>
+        <v>47.15005636649431</v>
       </c>
       <c r="F80" t="n">
         <v>954539</v>
@@ -2052,16 +2052,16 @@
         <v>44271</v>
       </c>
       <c r="B82" t="n">
-        <v>42.7570686340332</v>
+        <v>42.75707244873047</v>
       </c>
       <c r="C82" t="n">
-        <v>45.18906887745489</v>
+        <v>45.18907290913018</v>
       </c>
       <c r="D82" t="n">
-        <v>42.7570686340332</v>
+        <v>42.75707244873047</v>
       </c>
       <c r="E82" t="n">
-        <v>44.5065717038056</v>
+        <v>44.50657567458991</v>
       </c>
       <c r="F82" t="n">
         <v>561175</v>
@@ -2092,16 +2092,16 @@
         <v>44273</v>
       </c>
       <c r="B84" t="n">
-        <v>40.89221572875977</v>
+        <v>40.89221954345703</v>
       </c>
       <c r="C84" t="n">
-        <v>45.02565269480871</v>
+        <v>45.0256568951004</v>
       </c>
       <c r="D84" t="n">
-        <v>40.57499846451049</v>
+        <v>40.57500224961562</v>
       </c>
       <c r="E84" t="n">
-        <v>44.01632571721106</v>
+        <v>44.01632982334604</v>
       </c>
       <c r="F84" t="n">
         <v>572621</v>
@@ -2112,16 +2112,16 @@
         <v>44274</v>
       </c>
       <c r="B85" t="n">
-        <v>42.2956657409668</v>
+        <v>42.29566192626953</v>
       </c>
       <c r="C85" t="n">
-        <v>44.17013572642225</v>
+        <v>44.17013174266427</v>
       </c>
       <c r="D85" t="n">
-        <v>41.45936795627186</v>
+        <v>41.4593642170013</v>
       </c>
       <c r="E85" t="n">
-        <v>41.45936795627186</v>
+        <v>41.4593642170013</v>
       </c>
       <c r="F85" t="n">
         <v>639255</v>
@@ -2212,16 +2212,16 @@
         <v>44281</v>
       </c>
       <c r="B90" t="n">
-        <v>37.87384796142578</v>
+        <v>37.87384414672852</v>
       </c>
       <c r="C90" t="n">
-        <v>40.94989565175231</v>
+        <v>40.949891527232</v>
       </c>
       <c r="D90" t="n">
-        <v>37.56624319239313</v>
+        <v>37.56623940867817</v>
       </c>
       <c r="E90" t="n">
-        <v>39.95979362121066</v>
+        <v>39.95978959641457</v>
       </c>
       <c r="F90" t="n">
         <v>840076</v>
@@ -2312,16 +2312,16 @@
         <v>44291</v>
       </c>
       <c r="B95" t="n">
-        <v>35.68216323852539</v>
+        <v>35.68215942382812</v>
       </c>
       <c r="C95" t="n">
-        <v>37.01832012039754</v>
+        <v>37.01831616285484</v>
       </c>
       <c r="D95" t="n">
-        <v>35.09579131613852</v>
+        <v>35.09578756412892</v>
       </c>
       <c r="E95" t="n">
-        <v>37.01832012039754</v>
+        <v>37.01831616285484</v>
       </c>
       <c r="F95" t="n">
         <v>1091895</v>
@@ -2512,16 +2512,16 @@
         <v>44305</v>
       </c>
       <c r="B105" t="n">
-        <v>41.33440017700195</v>
+        <v>41.33439636230469</v>
       </c>
       <c r="C105" t="n">
-        <v>42.23798940934727</v>
+        <v>42.23798551125894</v>
       </c>
       <c r="D105" t="n">
-        <v>40.2097189655786</v>
+        <v>40.20971525467667</v>
       </c>
       <c r="E105" t="n">
-        <v>40.38274828563441</v>
+        <v>40.38274455876383</v>
       </c>
       <c r="F105" t="n">
         <v>1793083</v>
@@ -2552,16 +2552,16 @@
         <v>44308</v>
       </c>
       <c r="B107" t="n">
-        <v>42.37256622314453</v>
+        <v>42.3725700378418</v>
       </c>
       <c r="C107" t="n">
-        <v>42.77629628383934</v>
+        <v>42.77630013488342</v>
       </c>
       <c r="D107" t="n">
-        <v>41.0460181707321</v>
+        <v>41.04602186600353</v>
       </c>
       <c r="E107" t="n">
-        <v>42.58404191096891</v>
+        <v>42.58404574470481</v>
       </c>
       <c r="F107" t="n">
         <v>1175903</v>
@@ -2572,16 +2572,16 @@
         <v>44309</v>
       </c>
       <c r="B108" t="n">
-        <v>44.09323120117188</v>
+        <v>44.09323501586914</v>
       </c>
       <c r="C108" t="n">
-        <v>44.3143194172334</v>
+        <v>44.31432325105797</v>
       </c>
       <c r="D108" t="n">
-        <v>42.38217817402538</v>
+        <v>42.38218184069201</v>
       </c>
       <c r="E108" t="n">
-        <v>42.82435835372392</v>
+        <v>42.82436205864548</v>
       </c>
       <c r="F108" t="n">
         <v>1899574</v>
@@ -2612,16 +2612,16 @@
         <v>44313</v>
       </c>
       <c r="B110" t="n">
-        <v>43.73756408691406</v>
+        <v>43.7375602722168</v>
       </c>
       <c r="C110" t="n">
-        <v>44.31432350323168</v>
+        <v>44.31431963823069</v>
       </c>
       <c r="D110" t="n">
-        <v>43.04545428636325</v>
+        <v>43.04545053203033</v>
       </c>
       <c r="E110" t="n">
-        <v>43.40112171865809</v>
+        <v>43.40111793330461</v>
       </c>
       <c r="F110" t="n">
         <v>1146163</v>
@@ -2732,16 +2732,16 @@
         <v>44321</v>
       </c>
       <c r="B116" t="n">
-        <v>39.74831008911133</v>
+        <v>39.74831390380859</v>
       </c>
       <c r="C116" t="n">
-        <v>40.6422867086336</v>
+        <v>40.64229060912697</v>
       </c>
       <c r="D116" t="n">
-        <v>39.07542542863015</v>
+        <v>39.0754291787498</v>
       </c>
       <c r="E116" t="n">
-        <v>39.89249805311069</v>
+        <v>39.89250188164586</v>
       </c>
       <c r="F116" t="n">
         <v>3650961</v>
@@ -2772,16 +2772,16 @@
         <v>44323</v>
       </c>
       <c r="B118" t="n">
-        <v>38.83511352539062</v>
+        <v>38.83510971069336</v>
       </c>
       <c r="C118" t="n">
-        <v>39.99824491189721</v>
+        <v>39.99824098294782</v>
       </c>
       <c r="D118" t="n">
-        <v>37.51818162368365</v>
+        <v>37.51817793834604</v>
       </c>
       <c r="E118" t="n">
-        <v>39.66180253732045</v>
+        <v>39.66179864141913</v>
       </c>
       <c r="F118" t="n">
         <v>2227429</v>
@@ -2832,16 +2832,16 @@
         <v>44328</v>
       </c>
       <c r="B121" t="n">
-        <v>37.05676651000977</v>
+        <v>37.05677032470703</v>
       </c>
       <c r="C121" t="n">
-        <v>38.70052798471127</v>
+        <v>38.70053196862062</v>
       </c>
       <c r="D121" t="n">
-        <v>37.05676651000977</v>
+        <v>37.05677032470703</v>
       </c>
       <c r="E121" t="n">
-        <v>37.81616767208757</v>
+        <v>37.8161715649591</v>
       </c>
       <c r="F121" t="n">
         <v>783049</v>
@@ -2892,16 +2892,16 @@
         <v>44333</v>
       </c>
       <c r="B124" t="n">
-        <v>36.43194961547852</v>
+        <v>36.43194580078125</v>
       </c>
       <c r="C124" t="n">
-        <v>37.13367194429578</v>
+        <v>37.13366805612294</v>
       </c>
       <c r="D124" t="n">
-        <v>35.93209045798972</v>
+        <v>35.93208669563144</v>
       </c>
       <c r="E124" t="n">
-        <v>36.52807493515874</v>
+        <v>36.52807111039643</v>
       </c>
       <c r="F124" t="n">
         <v>946466</v>
@@ -2912,16 +2912,16 @@
         <v>44334</v>
       </c>
       <c r="B125" t="n">
-        <v>35.14385223388672</v>
+        <v>35.14385604858398</v>
       </c>
       <c r="C125" t="n">
-        <v>36.91258044505902</v>
+        <v>36.91258445174329</v>
       </c>
       <c r="D125" t="n">
-        <v>34.59593046500746</v>
+        <v>34.59593422023043</v>
       </c>
       <c r="E125" t="n">
-        <v>36.52807170518645</v>
+        <v>36.52807567013412</v>
       </c>
       <c r="F125" t="n">
         <v>2070451</v>
@@ -2952,16 +2952,16 @@
         <v>44336</v>
       </c>
       <c r="B127" t="n">
-        <v>34.63438034057617</v>
+        <v>34.63438415527344</v>
       </c>
       <c r="C127" t="n">
-        <v>35.26881488495837</v>
+        <v>35.26881876953347</v>
       </c>
       <c r="D127" t="n">
-        <v>34.51902996798866</v>
+        <v>34.51903376998102</v>
       </c>
       <c r="E127" t="n">
-        <v>34.51902996798866</v>
+        <v>34.51903376998102</v>
       </c>
       <c r="F127" t="n">
         <v>943604</v>
@@ -3012,16 +3012,16 @@
         <v>44341</v>
       </c>
       <c r="B130" t="n">
-        <v>37.29708480834961</v>
+        <v>37.29708862304688</v>
       </c>
       <c r="C130" t="n">
-        <v>38.78704584439543</v>
+        <v>38.78704981148397</v>
       </c>
       <c r="D130" t="n">
-        <v>37.22979709165812</v>
+        <v>37.22980089947328</v>
       </c>
       <c r="E130" t="n">
-        <v>37.52778929886728</v>
+        <v>37.52779313716071</v>
       </c>
       <c r="F130" t="n">
         <v>1731150</v>
@@ -3092,16 +3092,16 @@
         <v>44347</v>
       </c>
       <c r="B134" t="n">
-        <v>39.38302993774414</v>
+        <v>39.38303375244141</v>
       </c>
       <c r="C134" t="n">
-        <v>40.11358977958957</v>
+        <v>40.11359366504992</v>
       </c>
       <c r="D134" t="n">
-        <v>39.02736254769899</v>
+        <v>39.02736632794579</v>
       </c>
       <c r="E134" t="n">
-        <v>39.3926424686217</v>
+        <v>39.39264628425005</v>
       </c>
       <c r="F134" t="n">
         <v>715598</v>
@@ -3192,16 +3192,16 @@
         <v>44355</v>
       </c>
       <c r="B139" t="n">
-        <v>38.46022033691406</v>
+        <v>38.4602165222168</v>
       </c>
       <c r="C139" t="n">
-        <v>38.85433789767048</v>
+        <v>38.85433404388245</v>
       </c>
       <c r="D139" t="n">
-        <v>37.72004412796937</v>
+        <v>37.72004038668688</v>
       </c>
       <c r="E139" t="n">
-        <v>38.43138274082768</v>
+        <v>38.43137892899068</v>
       </c>
       <c r="F139" t="n">
         <v>978352</v>
@@ -3212,16 +3212,16 @@
         <v>44356</v>
       </c>
       <c r="B140" t="n">
-        <v>38.01803207397461</v>
+        <v>38.01803588867188</v>
       </c>
       <c r="C140" t="n">
-        <v>38.66207914230487</v>
+        <v>38.66208302162527</v>
       </c>
       <c r="D140" t="n">
-        <v>37.29708475810054</v>
+        <v>37.29708850045856</v>
       </c>
       <c r="E140" t="n">
-        <v>38.48905358533129</v>
+        <v>38.48905744729046</v>
       </c>
       <c r="F140" t="n">
         <v>837521</v>
@@ -3332,16 +3332,16 @@
         <v>44364</v>
       </c>
       <c r="B146" t="n">
-        <v>42.48791885375977</v>
+        <v>42.4879150390625</v>
       </c>
       <c r="C146" t="n">
-        <v>44.00671761209134</v>
+        <v>44.0067136610316</v>
       </c>
       <c r="D146" t="n">
-        <v>41.62277975128091</v>
+        <v>41.62277601425852</v>
       </c>
       <c r="E146" t="n">
-        <v>42.95894040588714</v>
+        <v>42.95893654890009</v>
       </c>
       <c r="F146" t="n">
         <v>1582144</v>
@@ -3372,16 +3372,16 @@
         <v>44368</v>
       </c>
       <c r="B148" t="n">
-        <v>46.96741104125977</v>
+        <v>46.96741485595703</v>
       </c>
       <c r="C148" t="n">
-        <v>47.24617818755916</v>
+        <v>47.24618202489792</v>
       </c>
       <c r="D148" t="n">
-        <v>43.53569625432814</v>
+        <v>43.53569979030122</v>
       </c>
       <c r="E148" t="n">
-        <v>43.73755940512824</v>
+        <v>43.73756295749668</v>
       </c>
       <c r="F148" t="n">
         <v>2655439</v>
@@ -3452,16 +3452,16 @@
         <v>44372</v>
       </c>
       <c r="B152" t="n">
-        <v>44.45851516723633</v>
+        <v>44.45851135253906</v>
       </c>
       <c r="C152" t="n">
-        <v>44.9872081751215</v>
+        <v>44.98720431506052</v>
       </c>
       <c r="D152" t="n">
-        <v>43.97788107180344</v>
+        <v>43.97787729834627</v>
       </c>
       <c r="E152" t="n">
-        <v>44.9872081751215</v>
+        <v>44.98720431506052</v>
       </c>
       <c r="F152" t="n">
         <v>1347904</v>
@@ -3472,16 +3472,16 @@
         <v>44375</v>
       </c>
       <c r="B153" t="n">
-        <v>44.53541564941406</v>
+        <v>44.5354118347168</v>
       </c>
       <c r="C153" t="n">
-        <v>44.64115350201283</v>
+        <v>44.64114967825854</v>
       </c>
       <c r="D153" t="n">
-        <v>43.20886748802305</v>
+        <v>43.20886378695175</v>
       </c>
       <c r="E153" t="n">
-        <v>44.13168555555202</v>
+        <v>44.13168177543641</v>
       </c>
       <c r="F153" t="n">
         <v>1110393</v>
@@ -3512,16 +3512,16 @@
         <v>44377</v>
       </c>
       <c r="B155" t="n">
-        <v>43.58375930786133</v>
+        <v>43.58376312255859</v>
       </c>
       <c r="C155" t="n">
-        <v>44.45851087872119</v>
+        <v>44.45851476998166</v>
       </c>
       <c r="D155" t="n">
-        <v>43.50685905923421</v>
+        <v>43.50686286720073</v>
       </c>
       <c r="E155" t="n">
-        <v>44.21819385418598</v>
+        <v>44.21819772441255</v>
       </c>
       <c r="F155" t="n">
         <v>1274116</v>
@@ -3572,16 +3572,16 @@
         <v>44382</v>
       </c>
       <c r="B158" t="n">
-        <v>45.04488754272461</v>
+        <v>45.04488372802734</v>
       </c>
       <c r="C158" t="n">
-        <v>46.21763144885693</v>
+        <v>46.21762753484401</v>
       </c>
       <c r="D158" t="n">
-        <v>44.42967424579171</v>
+        <v>44.42967048319475</v>
       </c>
       <c r="E158" t="n">
-        <v>44.98720860256699</v>
+        <v>44.98720479275436</v>
       </c>
       <c r="F158" t="n">
         <v>3391068</v>
@@ -3592,16 +3592,16 @@
         <v>44383</v>
       </c>
       <c r="B159" t="n">
-        <v>44.37199783325195</v>
+        <v>44.37199401855469</v>
       </c>
       <c r="C159" t="n">
-        <v>45.94847553926477</v>
+        <v>45.94847158903642</v>
       </c>
       <c r="D159" t="n">
-        <v>43.75678830080941</v>
+        <v>43.75678453900221</v>
       </c>
       <c r="E159" t="n">
-        <v>45.78505875053358</v>
+        <v>45.7850548143543</v>
       </c>
       <c r="F159" t="n">
         <v>1563442</v>
@@ -3652,16 +3652,16 @@
         <v>44389</v>
       </c>
       <c r="B162" t="n">
-        <v>44.72766494750977</v>
+        <v>44.72766876220703</v>
       </c>
       <c r="C162" t="n">
-        <v>45.75621700299953</v>
+        <v>45.75622090541913</v>
       </c>
       <c r="D162" t="n">
-        <v>44.08361413043626</v>
+        <v>44.08361789020423</v>
       </c>
       <c r="E162" t="n">
-        <v>45.75621700299953</v>
+        <v>45.75622090541913</v>
       </c>
       <c r="F162" t="n">
         <v>1597780</v>
@@ -3732,16 +3732,16 @@
         <v>44393</v>
       </c>
       <c r="B166" t="n">
-        <v>41.70929336547852</v>
+        <v>41.70928955078125</v>
       </c>
       <c r="C166" t="n">
-        <v>41.91116028433812</v>
+        <v>41.91115645117827</v>
       </c>
       <c r="D166" t="n">
-        <v>40.45003668764308</v>
+        <v>40.45003298811638</v>
       </c>
       <c r="E166" t="n">
-        <v>41.62278057778546</v>
+        <v>41.62277677100059</v>
       </c>
       <c r="F166" t="n">
         <v>1471156</v>
@@ -3752,16 +3752,16 @@
         <v>44396</v>
       </c>
       <c r="B167" t="n">
-        <v>40.22894668579102</v>
+        <v>40.22894287109375</v>
       </c>
       <c r="C167" t="n">
-        <v>41.05563189370605</v>
+        <v>41.05562800061862</v>
       </c>
       <c r="D167" t="n">
-        <v>39.50799557728174</v>
+        <v>39.50799183094843</v>
       </c>
       <c r="E167" t="n">
-        <v>40.46925997438512</v>
+        <v>40.46925613690023</v>
       </c>
       <c r="F167" t="n">
         <v>1632835</v>
@@ -3792,16 +3792,16 @@
         <v>44398</v>
       </c>
       <c r="B169" t="n">
-        <v>40.45964813232422</v>
+        <v>40.45964431762695</v>
       </c>
       <c r="C169" t="n">
-        <v>41.40169122996932</v>
+        <v>41.40168732645247</v>
       </c>
       <c r="D169" t="n">
-        <v>40.22894737134245</v>
+        <v>40.22894357839657</v>
       </c>
       <c r="E169" t="n">
-        <v>40.37313534695605</v>
+        <v>40.37313154041556</v>
       </c>
       <c r="F169" t="n">
         <v>985812</v>
@@ -3812,16 +3812,16 @@
         <v>44399</v>
       </c>
       <c r="B170" t="n">
-        <v>40.89221572875977</v>
+        <v>40.89221954345703</v>
       </c>
       <c r="C170" t="n">
-        <v>41.15175780815924</v>
+        <v>41.15176164706832</v>
       </c>
       <c r="D170" t="n">
-        <v>40.39235663157741</v>
+        <v>40.3923603996445</v>
       </c>
       <c r="E170" t="n">
-        <v>41.08446634492577</v>
+        <v>41.08447017755746</v>
       </c>
       <c r="F170" t="n">
         <v>757704</v>
@@ -3832,16 +3832,16 @@
         <v>44400</v>
       </c>
       <c r="B171" t="n">
-        <v>40.56539154052734</v>
+        <v>40.56538772583008</v>
       </c>
       <c r="C171" t="n">
-        <v>40.8633837843476</v>
+        <v>40.86337994162768</v>
       </c>
       <c r="D171" t="n">
-        <v>40.20010782417279</v>
+        <v>40.20010404382616</v>
       </c>
       <c r="E171" t="n">
-        <v>40.62306673334884</v>
+        <v>40.6230629132279</v>
       </c>
       <c r="F171" t="n">
         <v>715496</v>
@@ -3872,16 +3872,16 @@
         <v>44404</v>
       </c>
       <c r="B173" t="n">
-        <v>38.54673385620117</v>
+        <v>38.54673004150391</v>
       </c>
       <c r="C173" t="n">
-        <v>40.84415903525979</v>
+        <v>40.84415499320262</v>
       </c>
       <c r="D173" t="n">
-        <v>38.32564186777011</v>
+        <v>38.32563807495276</v>
       </c>
       <c r="E173" t="n">
-        <v>40.62306704682872</v>
+        <v>40.62306302665147</v>
       </c>
       <c r="F173" t="n">
         <v>1543819</v>
@@ -3932,16 +3932,16 @@
         <v>44407</v>
       </c>
       <c r="B176" t="n">
-        <v>37.21057510375977</v>
+        <v>37.2105712890625</v>
       </c>
       <c r="C176" t="n">
-        <v>38.26796483899034</v>
+        <v>38.26796091589321</v>
       </c>
       <c r="D176" t="n">
-        <v>36.33582347177977</v>
+        <v>36.33581974675896</v>
       </c>
       <c r="E176" t="n">
-        <v>37.56624252608663</v>
+        <v>37.5662386749276</v>
       </c>
       <c r="F176" t="n">
         <v>1168442</v>
@@ -3952,16 +3952,16 @@
         <v>44410</v>
       </c>
       <c r="B177" t="n">
-        <v>39.04659271240234</v>
+        <v>39.04658889770508</v>
       </c>
       <c r="C177" t="n">
-        <v>40.34429954077027</v>
+        <v>40.3442955992922</v>
       </c>
       <c r="D177" t="n">
-        <v>38.19106610976557</v>
+        <v>38.19106237864987</v>
       </c>
       <c r="E177" t="n">
-        <v>39.17155563014188</v>
+        <v>39.17155180323623</v>
       </c>
       <c r="F177" t="n">
         <v>3352028</v>
@@ -4052,16 +4052,16 @@
         <v>44417</v>
       </c>
       <c r="B182" t="n">
-        <v>37.10483551025391</v>
+        <v>37.10483169555664</v>
       </c>
       <c r="C182" t="n">
-        <v>37.44127788724551</v>
+        <v>37.44127403795907</v>
       </c>
       <c r="D182" t="n">
-        <v>35.94170411539885</v>
+        <v>35.94170042028153</v>
       </c>
       <c r="E182" t="n">
-        <v>36.11473344381713</v>
+        <v>36.1147297309109</v>
       </c>
       <c r="F182" t="n">
         <v>1206460</v>
@@ -4092,16 +4092,16 @@
         <v>44419</v>
       </c>
       <c r="B184" t="n">
-        <v>36.43194961547852</v>
+        <v>36.43194580078125</v>
       </c>
       <c r="C184" t="n">
-        <v>36.74916691799907</v>
+        <v>36.74916307008678</v>
       </c>
       <c r="D184" t="n">
-        <v>36.09550724902192</v>
+        <v>36.09550346955268</v>
       </c>
       <c r="E184" t="n">
-        <v>36.4703997433506</v>
+        <v>36.47039592462733</v>
       </c>
       <c r="F184" t="n">
         <v>786524</v>
@@ -4112,16 +4112,16 @@
         <v>44420</v>
       </c>
       <c r="B185" t="n">
-        <v>36.12434005737305</v>
+        <v>36.12434387207031</v>
       </c>
       <c r="C185" t="n">
-        <v>36.95102893978947</v>
+        <v>36.95103284178433</v>
       </c>
       <c r="D185" t="n">
-        <v>35.47068047502529</v>
+        <v>35.4706842206967</v>
       </c>
       <c r="E185" t="n">
-        <v>36.19162777223157</v>
+        <v>36.19163159403436</v>
       </c>
       <c r="F185" t="n">
         <v>689639</v>
@@ -4132,16 +4132,16 @@
         <v>44421</v>
       </c>
       <c r="B186" t="n">
-        <v>34.75934600830078</v>
+        <v>34.75934219360352</v>
       </c>
       <c r="C186" t="n">
-        <v>35.97054000708643</v>
+        <v>35.97053605946554</v>
       </c>
       <c r="D186" t="n">
-        <v>34.59593296747376</v>
+        <v>34.59592917071041</v>
       </c>
       <c r="E186" t="n">
-        <v>35.69177658449917</v>
+        <v>35.69177266747142</v>
       </c>
       <c r="F186" t="n">
         <v>915908</v>
@@ -4252,16 +4252,16 @@
         <v>44431</v>
       </c>
       <c r="B192" t="n">
-        <v>33.16364669799805</v>
+        <v>33.16364288330078</v>
       </c>
       <c r="C192" t="n">
-        <v>34.42290334478545</v>
+        <v>34.42289938524034</v>
       </c>
       <c r="D192" t="n">
-        <v>32.77914168126674</v>
+        <v>32.77913791079774</v>
       </c>
       <c r="E192" t="n">
-        <v>33.74040609688286</v>
+        <v>33.740402215843</v>
       </c>
       <c r="F192" t="n">
         <v>2084044</v>
@@ -4272,16 +4272,16 @@
         <v>44432</v>
       </c>
       <c r="B193" t="n">
-        <v>35.43223190307617</v>
+        <v>35.43223571777344</v>
       </c>
       <c r="C193" t="n">
-        <v>35.43223190307617</v>
+        <v>35.43223571777344</v>
       </c>
       <c r="D193" t="n">
-        <v>33.47124932262768</v>
+        <v>33.47125292620207</v>
       </c>
       <c r="E193" t="n">
-        <v>33.93265831128927</v>
+        <v>33.93266196453976</v>
       </c>
       <c r="F193" t="n">
         <v>1429663</v>
@@ -4332,16 +4332,16 @@
         <v>44435</v>
       </c>
       <c r="B196" t="n">
-        <v>36.43194961547852</v>
+        <v>36.43194580078125</v>
       </c>
       <c r="C196" t="n">
-        <v>36.66265413028687</v>
+        <v>36.66265029143312</v>
       </c>
       <c r="D196" t="n">
-        <v>35.02850121026817</v>
+        <v>35.02849754252244</v>
       </c>
       <c r="E196" t="n">
-        <v>35.75906488256532</v>
+        <v>35.75906113832411</v>
       </c>
       <c r="F196" t="n">
         <v>2701327</v>
@@ -4392,16 +4392,16 @@
         <v>44440</v>
       </c>
       <c r="B199" t="n">
-        <v>36.00899505615234</v>
+        <v>36.00899124145508</v>
       </c>
       <c r="C199" t="n">
-        <v>37.2298016265613</v>
+        <v>37.22979768253502</v>
       </c>
       <c r="D199" t="n">
-        <v>35.47068576189898</v>
+        <v>35.47068200422877</v>
       </c>
       <c r="E199" t="n">
-        <v>37.10483496133683</v>
+        <v>37.10483103054919</v>
       </c>
       <c r="F199" t="n">
         <v>1150659</v>
@@ -4712,16 +4712,16 @@
         <v>44463</v>
       </c>
       <c r="B215" t="n">
-        <v>34.54787063598633</v>
+        <v>34.54786682128906</v>
       </c>
       <c r="C215" t="n">
-        <v>35.65332304773112</v>
+        <v>35.65331911097231</v>
       </c>
       <c r="D215" t="n">
-        <v>33.88459469184851</v>
+        <v>33.88459095038866</v>
       </c>
       <c r="E215" t="n">
-        <v>34.46135784884584</v>
+        <v>34.46135404370111</v>
       </c>
       <c r="F215" t="n">
         <v>2639905</v>
@@ -4852,16 +4852,16 @@
         <v>44474</v>
       </c>
       <c r="B222" t="n">
-        <v>41.2382698059082</v>
+        <v>41.23827362060547</v>
       </c>
       <c r="C222" t="n">
-        <v>43.07428564103963</v>
+        <v>43.07428962557536</v>
       </c>
       <c r="D222" t="n">
-        <v>40.94989013953506</v>
+        <v>40.9498939275561</v>
       </c>
       <c r="E222" t="n">
-        <v>41.82464166928109</v>
+        <v>41.82464553821999</v>
       </c>
       <c r="F222" t="n">
         <v>3033780</v>
@@ -4952,16 +4952,16 @@
         <v>44482</v>
       </c>
       <c r="B227" t="n">
-        <v>39.66180038452148</v>
+        <v>39.66179656982422</v>
       </c>
       <c r="C227" t="n">
-        <v>40.05591793090613</v>
+        <v>40.05591407830239</v>
       </c>
       <c r="D227" t="n">
-        <v>38.88317407585477</v>
+        <v>38.88317033604628</v>
       </c>
       <c r="E227" t="n">
-        <v>39.43109587666738</v>
+        <v>39.43109208415942</v>
       </c>
       <c r="F227" t="n">
         <v>1130628</v>
@@ -5012,16 +5012,16 @@
         <v>44487</v>
       </c>
       <c r="B230" t="n">
-        <v>39.87327575683594</v>
+        <v>39.87327194213867</v>
       </c>
       <c r="C230" t="n">
-        <v>41.44975342469183</v>
+        <v>41.44974945917212</v>
       </c>
       <c r="D230" t="n">
-        <v>39.18116598648377</v>
+        <v>39.18116223800101</v>
       </c>
       <c r="E230" t="n">
-        <v>39.72908778283576</v>
+        <v>39.72908398193304</v>
       </c>
       <c r="F230" t="n">
         <v>2573169</v>
@@ -5032,16 +5032,16 @@
         <v>44488</v>
       </c>
       <c r="B231" t="n">
-        <v>37.58546829223633</v>
+        <v>37.58546447753906</v>
       </c>
       <c r="C231" t="n">
-        <v>40.08475657457366</v>
+        <v>40.08475250621378</v>
       </c>
       <c r="D231" t="n">
-        <v>36.86452090235465</v>
+        <v>36.86451716082918</v>
       </c>
       <c r="E231" t="n">
-        <v>39.57528488714614</v>
+        <v>39.57528087049455</v>
       </c>
       <c r="F231" t="n">
         <v>2915331</v>
@@ -5072,16 +5072,16 @@
         <v>44490</v>
       </c>
       <c r="B233" t="n">
-        <v>34.41329193115234</v>
+        <v>34.41328811645508</v>
       </c>
       <c r="C233" t="n">
-        <v>36.09550752381791</v>
+        <v>36.09550352264783</v>
       </c>
       <c r="D233" t="n">
-        <v>33.48086508042814</v>
+        <v>33.48086136908995</v>
       </c>
       <c r="E233" t="n">
-        <v>35.62448595864728</v>
+        <v>35.62448200968972</v>
       </c>
       <c r="F233" t="n">
         <v>3113087</v>
@@ -5092,16 +5092,16 @@
         <v>44491</v>
       </c>
       <c r="B234" t="n">
-        <v>32.63495254516602</v>
+        <v>32.63494873046875</v>
       </c>
       <c r="C234" t="n">
-        <v>34.06723862420559</v>
+        <v>34.06723464208851</v>
       </c>
       <c r="D234" t="n">
-        <v>31.04886594627039</v>
+        <v>31.04886231697067</v>
       </c>
       <c r="E234" t="n">
-        <v>33.63467091453443</v>
+        <v>33.63466698298016</v>
       </c>
       <c r="F234" t="n">
         <v>4894520</v>
@@ -5112,16 +5112,16 @@
         <v>44494</v>
       </c>
       <c r="B235" t="n">
-        <v>36.84706115722656</v>
+        <v>36.8470573425293</v>
       </c>
       <c r="C235" t="n">
-        <v>37.31127712193275</v>
+        <v>37.3112732591762</v>
       </c>
       <c r="D235" t="n">
-        <v>32.95926229019877</v>
+        <v>32.95925887799699</v>
       </c>
       <c r="E235" t="n">
-        <v>32.95926229019877</v>
+        <v>32.95925887799699</v>
       </c>
       <c r="F235" t="n">
         <v>3449995</v>
@@ -5152,16 +5152,16 @@
         <v>44496</v>
       </c>
       <c r="B237" t="n">
-        <v>35.29000473022461</v>
+        <v>35.29000854492188</v>
       </c>
       <c r="C237" t="n">
-        <v>36.07336794668348</v>
+        <v>36.07337184605893</v>
       </c>
       <c r="D237" t="n">
-        <v>34.47762778370612</v>
+        <v>34.47763151058894</v>
       </c>
       <c r="E237" t="n">
-        <v>36.07336794668348</v>
+        <v>36.07337184605893</v>
       </c>
       <c r="F237" t="n">
         <v>2270538</v>
@@ -5272,16 +5272,16 @@
         <v>44505</v>
       </c>
       <c r="B243" t="n">
-        <v>34.33256149291992</v>
+        <v>34.33255767822266</v>
       </c>
       <c r="C243" t="n">
-        <v>35.80257809171644</v>
+        <v>35.80257411368536</v>
       </c>
       <c r="D243" t="n">
-        <v>31.73102433433615</v>
+        <v>31.73102080869616</v>
       </c>
       <c r="E243" t="n">
-        <v>33.17202720107906</v>
+        <v>33.17202351532898</v>
       </c>
       <c r="F243" t="n">
         <v>9166770</v>
@@ -5312,16 +5312,16 @@
         <v>44509</v>
       </c>
       <c r="B245" t="n">
-        <v>34.50664520263672</v>
+        <v>34.50664138793945</v>
       </c>
       <c r="C245" t="n">
-        <v>35.10625735786877</v>
+        <v>35.1062534768846</v>
       </c>
       <c r="D245" t="n">
-        <v>32.63044377861175</v>
+        <v>32.63044017132788</v>
       </c>
       <c r="E245" t="n">
-        <v>33.89736430140155</v>
+        <v>33.89736055406007</v>
       </c>
       <c r="F245" t="n">
         <v>7032350</v>
@@ -5372,16 +5372,16 @@
         <v>44512</v>
       </c>
       <c r="B248" t="n">
-        <v>30.94766235351562</v>
+        <v>30.94766044616699</v>
       </c>
       <c r="C248" t="n">
-        <v>33.11399911175717</v>
+        <v>33.11399707089411</v>
       </c>
       <c r="D248" t="n">
-        <v>30.69621126299056</v>
+        <v>30.69620937113922</v>
       </c>
       <c r="E248" t="n">
-        <v>32.10819849723269</v>
+        <v>32.10819651835855</v>
       </c>
       <c r="F248" t="n">
         <v>3403064</v>
@@ -5552,16 +5552,16 @@
         <v>44526</v>
       </c>
       <c r="B257" t="n">
-        <v>26.69235992431641</v>
+        <v>26.69235801696777</v>
       </c>
       <c r="C257" t="n">
-        <v>27.61111748815896</v>
+        <v>27.61111551515892</v>
       </c>
       <c r="D257" t="n">
-        <v>25.85096918966023</v>
+        <v>25.85096734243463</v>
       </c>
       <c r="E257" t="n">
-        <v>26.59564810870458</v>
+        <v>26.59564620826666</v>
       </c>
       <c r="F257" t="n">
         <v>3664026</v>
@@ -5592,16 +5592,16 @@
         <v>44530</v>
       </c>
       <c r="B259" t="n">
-        <v>26.71170043945312</v>
+        <v>26.71169853210449</v>
       </c>
       <c r="C259" t="n">
-        <v>26.71170043945312</v>
+        <v>26.71169853210449</v>
       </c>
       <c r="D259" t="n">
-        <v>25.48346622320262</v>
+        <v>25.48346440355603</v>
       </c>
       <c r="E259" t="n">
-        <v>26.53761992558345</v>
+        <v>26.53761803066504</v>
       </c>
       <c r="F259" t="n">
         <v>4757647</v>
@@ -5612,16 +5612,16 @@
         <v>44531</v>
       </c>
       <c r="B260" t="n">
-        <v>26.69235992431641</v>
+        <v>26.69235801696777</v>
       </c>
       <c r="C260" t="n">
-        <v>28.01730598945588</v>
+        <v>28.01730398743094</v>
       </c>
       <c r="D260" t="n">
-        <v>26.32485577450663</v>
+        <v>26.32485389341864</v>
       </c>
       <c r="E260" t="n">
-        <v>27.17591712858762</v>
+        <v>27.17591518668557</v>
       </c>
       <c r="F260" t="n">
         <v>3467467</v>
@@ -5752,16 +5752,16 @@
         <v>44540</v>
       </c>
       <c r="B267" t="n">
-        <v>29.43896102905273</v>
+        <v>29.43896293640137</v>
       </c>
       <c r="C267" t="n">
-        <v>29.76778079564096</v>
+        <v>29.76778272429381</v>
       </c>
       <c r="D267" t="n">
-        <v>28.76198025889329</v>
+        <v>28.76198212238038</v>
       </c>
       <c r="E267" t="n">
-        <v>29.57435718308462</v>
+        <v>29.57435909920557</v>
       </c>
       <c r="F267" t="n">
         <v>1281952</v>
@@ -5832,16 +5832,16 @@
         <v>44546</v>
       </c>
       <c r="B271" t="n">
-        <v>30.62851524353027</v>
+        <v>30.62851333618164</v>
       </c>
       <c r="C271" t="n">
-        <v>30.86062322322113</v>
+        <v>30.86062130141829</v>
       </c>
       <c r="D271" t="n">
-        <v>29.25521235155887</v>
+        <v>29.25521052973079</v>
       </c>
       <c r="E271" t="n">
-        <v>29.49699095054871</v>
+        <v>29.4969891136642</v>
       </c>
       <c r="F271" t="n">
         <v>3477726</v>
@@ -5952,16 +5952,16 @@
         <v>44557</v>
       </c>
       <c r="B277" t="n">
-        <v>30.7252254486084</v>
+        <v>30.72522354125977</v>
       </c>
       <c r="C277" t="n">
-        <v>31.01536089416671</v>
+        <v>31.01535896880716</v>
       </c>
       <c r="D277" t="n">
-        <v>29.98054840663</v>
+        <v>29.98054654550914</v>
       </c>
       <c r="E277" t="n">
-        <v>29.98054840663</v>
+        <v>29.98054654550914</v>
       </c>
       <c r="F277" t="n">
         <v>1273927</v>
@@ -6132,16 +6132,16 @@
         <v>44571</v>
       </c>
       <c r="B286" t="n">
-        <v>33.37511825561523</v>
+        <v>33.37511444091797</v>
       </c>
       <c r="C286" t="n">
-        <v>33.89736166431392</v>
+        <v>33.89735778992546</v>
       </c>
       <c r="D286" t="n">
-        <v>32.24359399308115</v>
+        <v>32.24359030771443</v>
       </c>
       <c r="E286" t="n">
-        <v>32.3789901547752</v>
+        <v>32.37898645393302</v>
       </c>
       <c r="F286" t="n">
         <v>2829132</v>
@@ -6152,16 +6152,16 @@
         <v>44572</v>
       </c>
       <c r="B287" t="n">
-        <v>35.10625076293945</v>
+        <v>35.10625457763672</v>
       </c>
       <c r="C287" t="n">
-        <v>35.63816285834681</v>
+        <v>35.63816673084244</v>
       </c>
       <c r="D287" t="n">
-        <v>33.18169098013564</v>
+        <v>33.18169458570739</v>
       </c>
       <c r="E287" t="n">
-        <v>33.55886569280182</v>
+        <v>33.55886933935793</v>
       </c>
       <c r="F287" t="n">
         <v>3953735</v>
@@ -6172,16 +6172,16 @@
         <v>44573</v>
       </c>
       <c r="B288" t="n">
-        <v>34.89348602294922</v>
+        <v>34.89348983764648</v>
       </c>
       <c r="C288" t="n">
-        <v>35.98632394454952</v>
+        <v>35.98632787872025</v>
       </c>
       <c r="D288" t="n">
-        <v>34.13913659549451</v>
+        <v>34.13914032772324</v>
       </c>
       <c r="E288" t="n">
-        <v>35.34802942826484</v>
+        <v>35.34803329265463</v>
       </c>
       <c r="F288" t="n">
         <v>3302601</v>
@@ -6292,16 +6292,16 @@
         <v>44581</v>
       </c>
       <c r="B294" t="n">
-        <v>35.2996711730957</v>
+        <v>35.29967498779297</v>
       </c>
       <c r="C294" t="n">
-        <v>36.17007552296929</v>
+        <v>36.17007943172774</v>
       </c>
       <c r="D294" t="n">
-        <v>34.98052391082881</v>
+        <v>34.98052769103708</v>
       </c>
       <c r="E294" t="n">
-        <v>35.8702694969556</v>
+        <v>35.87027337331519</v>
       </c>
       <c r="F294" t="n">
         <v>3650414</v>
@@ -6332,16 +6332,16 @@
         <v>44585</v>
       </c>
       <c r="B296" t="n">
-        <v>34.35190582275391</v>
+        <v>34.35190200805664</v>
       </c>
       <c r="C296" t="n">
-        <v>35.31902021252021</v>
+        <v>35.3190162904272</v>
       </c>
       <c r="D296" t="n">
-        <v>34.05209976231423</v>
+        <v>34.05209598090971</v>
       </c>
       <c r="E296" t="n">
-        <v>34.2358508967577</v>
+        <v>34.23584709494806</v>
       </c>
       <c r="F296" t="n">
         <v>2113697</v>
@@ -6392,16 +6392,16 @@
         <v>44588</v>
       </c>
       <c r="B299" t="n">
-        <v>36.09270858764648</v>
+        <v>36.09271240234375</v>
       </c>
       <c r="C299" t="n">
-        <v>37.10817788022283</v>
+        <v>37.1081818022467</v>
       </c>
       <c r="D299" t="n">
-        <v>35.68652012110085</v>
+        <v>35.68652389286739</v>
       </c>
       <c r="E299" t="n">
-        <v>35.87994373577622</v>
+        <v>35.87994752798603</v>
       </c>
       <c r="F299" t="n">
         <v>3171460</v>
@@ -6492,16 +6492,16 @@
         <v>44595</v>
       </c>
       <c r="B304" t="n">
-        <v>35.2996711730957</v>
+        <v>35.29967498779297</v>
       </c>
       <c r="C304" t="n">
-        <v>35.58980845477045</v>
+        <v>35.58981230082171</v>
       </c>
       <c r="D304" t="n">
-        <v>33.84899975502328</v>
+        <v>33.84900341295216</v>
       </c>
       <c r="E304" t="n">
-        <v>34.98052391082881</v>
+        <v>34.98052769103708</v>
       </c>
       <c r="F304" t="n">
         <v>4177823</v>
@@ -6592,16 +6592,16 @@
         <v>44602</v>
       </c>
       <c r="B309" t="n">
-        <v>37.28226089477539</v>
+        <v>37.28226470947266</v>
       </c>
       <c r="C309" t="n">
-        <v>38.38477139493146</v>
+        <v>38.3847753224369</v>
       </c>
       <c r="D309" t="n">
-        <v>36.33448778997354</v>
+        <v>36.33449150769526</v>
       </c>
       <c r="E309" t="n">
-        <v>36.3635015200494</v>
+        <v>36.36350524073979</v>
       </c>
       <c r="F309" t="n">
         <v>7025951</v>
@@ -6612,16 +6612,16 @@
         <v>44603</v>
       </c>
       <c r="B310" t="n">
-        <v>38.07529449462891</v>
+        <v>38.07529067993164</v>
       </c>
       <c r="C310" t="n">
-        <v>38.49115547855604</v>
+        <v>38.49115162219439</v>
       </c>
       <c r="D310" t="n">
-        <v>37.37897243800389</v>
+        <v>37.37896869306991</v>
       </c>
       <c r="E310" t="n">
-        <v>37.78516092896444</v>
+        <v>37.78515714333515</v>
       </c>
       <c r="F310" t="n">
         <v>5486491</v>
@@ -6632,16 +6632,16 @@
         <v>44606</v>
       </c>
       <c r="B311" t="n">
-        <v>37.57239532470703</v>
+        <v>37.57239151000977</v>
       </c>
       <c r="C311" t="n">
-        <v>38.84898823510746</v>
+        <v>38.84898429079868</v>
       </c>
       <c r="D311" t="n">
-        <v>36.95344198127135</v>
+        <v>36.95343822941596</v>
       </c>
       <c r="E311" t="n">
-        <v>38.2977310983781</v>
+        <v>38.29772721003804</v>
       </c>
       <c r="F311" t="n">
         <v>3902640</v>
@@ -6652,16 +6652,16 @@
         <v>44607</v>
       </c>
       <c r="B312" t="n">
-        <v>35.79290390014648</v>
+        <v>35.79290008544922</v>
       </c>
       <c r="C312" t="n">
-        <v>36.65363583255173</v>
+        <v>36.65363192612031</v>
       </c>
       <c r="D312" t="n">
-        <v>35.63816650158672</v>
+        <v>35.63816270338088</v>
       </c>
       <c r="E312" t="n">
-        <v>36.55692589534578</v>
+        <v>36.55692199922141</v>
       </c>
       <c r="F312" t="n">
         <v>3810709</v>
@@ -6672,16 +6672,16 @@
         <v>44608</v>
       </c>
       <c r="B313" t="n">
-        <v>35.92829895019531</v>
+        <v>35.92830276489258</v>
       </c>
       <c r="C313" t="n">
-        <v>36.80837209332255</v>
+        <v>36.80837600146183</v>
       </c>
       <c r="D313" t="n">
-        <v>35.69619285953032</v>
+        <v>35.69619664958365</v>
       </c>
       <c r="E313" t="n">
-        <v>36.4408698462091</v>
+        <v>36.44087371532872</v>
       </c>
       <c r="F313" t="n">
         <v>4244663</v>
@@ -6692,16 +6692,16 @@
         <v>44609</v>
       </c>
       <c r="B314" t="n">
-        <v>35.2996711730957</v>
+        <v>35.29967498779297</v>
       </c>
       <c r="C314" t="n">
-        <v>35.89928322512308</v>
+        <v>35.89928710461807</v>
       </c>
       <c r="D314" t="n">
-        <v>34.41959807888318</v>
+        <v>34.41960179847439</v>
       </c>
       <c r="E314" t="n">
-        <v>35.68651838361181</v>
+        <v>35.68652224011414</v>
       </c>
       <c r="F314" t="n">
         <v>4430658</v>
@@ -6712,16 +6712,16 @@
         <v>44610</v>
       </c>
       <c r="B315" t="n">
-        <v>34.48729705810547</v>
+        <v>34.48730087280273</v>
       </c>
       <c r="C315" t="n">
-        <v>35.41572509065163</v>
+        <v>35.41572900804387</v>
       </c>
       <c r="D315" t="n">
-        <v>33.80064384086931</v>
+        <v>33.80064757961473</v>
       </c>
       <c r="E315" t="n">
-        <v>34.83545803875718</v>
+        <v>34.83546189196511</v>
       </c>
       <c r="F315" t="n">
         <v>4069741</v>
@@ -6852,16 +6852,16 @@
         <v>44623</v>
       </c>
       <c r="B322" t="n">
-        <v>37.34028244018555</v>
+        <v>37.34028625488281</v>
       </c>
       <c r="C322" t="n">
-        <v>37.88187078764361</v>
+        <v>37.88187465766974</v>
       </c>
       <c r="D322" t="n">
-        <v>36.31514444477941</v>
+        <v>36.31514815474819</v>
       </c>
       <c r="E322" t="n">
-        <v>37.12751759702811</v>
+        <v>37.12752138998924</v>
       </c>
       <c r="F322" t="n">
         <v>9786414</v>
@@ -6892,16 +6892,16 @@
         <v>44627</v>
       </c>
       <c r="B324" t="n">
-        <v>37.04048538208008</v>
+        <v>37.04048156738281</v>
       </c>
       <c r="C324" t="n">
-        <v>39.28418904358112</v>
+        <v>39.28418499781101</v>
       </c>
       <c r="D324" t="n">
-        <v>36.65363811402602</v>
+        <v>36.65363433916909</v>
       </c>
       <c r="E324" t="n">
-        <v>38.17200970618351</v>
+        <v>38.17200577495368</v>
       </c>
       <c r="F324" t="n">
         <v>5025922</v>
@@ -6952,16 +6952,16 @@
         <v>44630</v>
       </c>
       <c r="B327" t="n">
-        <v>35.72520446777344</v>
+        <v>35.7252082824707</v>
       </c>
       <c r="C327" t="n">
-        <v>37.22423084456335</v>
+        <v>37.22423481932497</v>
       </c>
       <c r="D327" t="n">
-        <v>35.51243962707166</v>
+        <v>35.51244341905014</v>
       </c>
       <c r="E327" t="n">
-        <v>36.75034245134777</v>
+        <v>36.75034637550812</v>
       </c>
       <c r="F327" t="n">
         <v>4502679</v>
@@ -7032,16 +7032,16 @@
         <v>44636</v>
       </c>
       <c r="B331" t="n">
-        <v>32.84320831298828</v>
+        <v>32.84320449829102</v>
       </c>
       <c r="C331" t="n">
-        <v>34.44861737575539</v>
+        <v>34.44861337459189</v>
       </c>
       <c r="D331" t="n">
-        <v>32.34030985608281</v>
+        <v>32.34030609979657</v>
       </c>
       <c r="E331" t="n">
-        <v>34.10045632903992</v>
+        <v>34.10045236831488</v>
       </c>
       <c r="F331" t="n">
         <v>3899288</v>
@@ -7092,16 +7092,16 @@
         <v>44641</v>
       </c>
       <c r="B334" t="n">
-        <v>36.61495208740234</v>
+        <v>36.61494827270508</v>
       </c>
       <c r="C334" t="n">
-        <v>36.86640318776314</v>
+        <v>36.86639934686866</v>
       </c>
       <c r="D334" t="n">
-        <v>35.88961626653654</v>
+        <v>35.88961252740777</v>
       </c>
       <c r="E334" t="n">
-        <v>35.97665746445866</v>
+        <v>35.97665371626157</v>
       </c>
       <c r="F334" t="n">
         <v>3600944</v>
@@ -7212,16 +7212,16 @@
         <v>44649</v>
       </c>
       <c r="B340" t="n">
-        <v>40.11590576171875</v>
+        <v>40.11590194702148</v>
       </c>
       <c r="C340" t="n">
-        <v>40.60913544747385</v>
+        <v>40.60913158587444</v>
       </c>
       <c r="D340" t="n">
-        <v>37.8141747233464</v>
+        <v>37.81417112752509</v>
       </c>
       <c r="E340" t="n">
-        <v>38.00759834997051</v>
+        <v>38.00759473575618</v>
       </c>
       <c r="F340" t="n">
         <v>6952609</v>
@@ -7252,16 +7252,16 @@
         <v>44651</v>
       </c>
       <c r="B342" t="n">
-        <v>40.47373580932617</v>
+        <v>40.47373962402344</v>
       </c>
       <c r="C342" t="n">
-        <v>41.13137533388116</v>
+        <v>41.13137921056172</v>
       </c>
       <c r="D342" t="n">
-        <v>39.6710313879373</v>
+        <v>39.67103512697872</v>
       </c>
       <c r="E342" t="n">
-        <v>40.13524730247168</v>
+        <v>40.135251085266</v>
       </c>
       <c r="F342" t="n">
         <v>3810811</v>
@@ -7312,16 +7312,16 @@
         <v>44656</v>
       </c>
       <c r="B345" t="n">
-        <v>41.9727668762207</v>
+        <v>41.97276306152344</v>
       </c>
       <c r="C345" t="n">
-        <v>43.03659497534015</v>
+        <v>43.03659106395681</v>
       </c>
       <c r="D345" t="n">
-        <v>41.5762508676977</v>
+        <v>41.57624708903781</v>
       </c>
       <c r="E345" t="n">
-        <v>42.30158667490721</v>
+        <v>42.30158283032514</v>
       </c>
       <c r="F345" t="n">
         <v>5903074</v>
@@ -7432,16 +7432,16 @@
         <v>44664</v>
       </c>
       <c r="B351" t="n">
-        <v>43.62653350830078</v>
+        <v>43.62652969360352</v>
       </c>
       <c r="C351" t="n">
-        <v>43.71357095479976</v>
+        <v>43.71356713249195</v>
       </c>
       <c r="D351" t="n">
-        <v>42.8431702567798</v>
+        <v>42.8431665105797</v>
       </c>
       <c r="E351" t="n">
-        <v>43.30738621093589</v>
+        <v>43.30738242414481</v>
       </c>
       <c r="F351" t="n">
         <v>3238402</v>
@@ -7452,16 +7452,16 @@
         <v>44665</v>
       </c>
       <c r="B352" t="n">
-        <v>42.93987655639648</v>
+        <v>42.93988037109375</v>
       </c>
       <c r="C352" t="n">
-        <v>43.62652981023535</v>
+        <v>43.62653368593358</v>
       </c>
       <c r="D352" t="n">
-        <v>42.2242133212342</v>
+        <v>42.2242170723533</v>
       </c>
       <c r="E352" t="n">
-        <v>43.62652981023535</v>
+        <v>43.62653368593358</v>
       </c>
       <c r="F352" t="n">
         <v>2345809</v>
@@ -7552,16 +7552,16 @@
         <v>44676</v>
       </c>
       <c r="B357" t="n">
-        <v>41.94374847412109</v>
+        <v>41.94375228881836</v>
       </c>
       <c r="C357" t="n">
-        <v>42.40796438837074</v>
+        <v>42.40796824528748</v>
       </c>
       <c r="D357" t="n">
-        <v>40.64781815768625</v>
+        <v>40.64782185452133</v>
       </c>
       <c r="E357" t="n">
-        <v>40.75420058099602</v>
+        <v>40.75420428750637</v>
       </c>
       <c r="F357" t="n">
         <v>3287465</v>
@@ -7592,16 +7592,16 @@
         <v>44678</v>
       </c>
       <c r="B359" t="n">
-        <v>42.16619110107422</v>
+        <v>42.16618728637695</v>
       </c>
       <c r="C359" t="n">
-        <v>43.58784900340616</v>
+        <v>43.58784506009413</v>
       </c>
       <c r="D359" t="n">
-        <v>41.46986901615963</v>
+        <v>41.46986526445734</v>
       </c>
       <c r="E359" t="n">
-        <v>43.52015279261696</v>
+        <v>43.52014885542929</v>
       </c>
       <c r="F359" t="n">
         <v>3779727</v>
@@ -7672,16 +7672,16 @@
         <v>44684</v>
       </c>
       <c r="B363" t="n">
-        <v>42.12749862670898</v>
+        <v>42.12750244140625</v>
       </c>
       <c r="C363" t="n">
-        <v>42.54335956584936</v>
+        <v>42.54336341820335</v>
       </c>
       <c r="D363" t="n">
-        <v>41.25709802345466</v>
+        <v>41.25710175933607</v>
       </c>
       <c r="E363" t="n">
-        <v>42.54335956584936</v>
+        <v>42.54336341820335</v>
       </c>
       <c r="F363" t="n">
         <v>4458389</v>
@@ -7692,16 +7692,16 @@
         <v>44685</v>
       </c>
       <c r="B364" t="n">
-        <v>44.10041809082031</v>
+        <v>44.10041427612305</v>
       </c>
       <c r="C364" t="n">
-        <v>44.32285544811791</v>
+        <v>44.32285161417975</v>
       </c>
       <c r="D364" t="n">
-        <v>42.16618932580826</v>
+        <v>42.16618567842227</v>
       </c>
       <c r="E364" t="n">
-        <v>43.04626251447057</v>
+        <v>43.04625879095802</v>
       </c>
       <c r="F364" t="n">
         <v>5759540</v>
@@ -7712,16 +7712,16 @@
         <v>44686</v>
       </c>
       <c r="B365" t="n">
-        <v>42.92053604125977</v>
+        <v>42.92053985595703</v>
       </c>
       <c r="C365" t="n">
-        <v>44.57429987842104</v>
+        <v>44.57430384010176</v>
       </c>
       <c r="D365" t="n">
-        <v>42.01144918067956</v>
+        <v>42.01145291457887</v>
       </c>
       <c r="E365" t="n">
-        <v>44.09074271874429</v>
+        <v>44.09074663744735</v>
       </c>
       <c r="F365" t="n">
         <v>4814532</v>
@@ -7732,16 +7732,16 @@
         <v>44687</v>
       </c>
       <c r="B366" t="n">
-        <v>42.55303192138672</v>
+        <v>42.55303573608398</v>
       </c>
       <c r="C366" t="n">
-        <v>43.90698966019007</v>
+        <v>43.90699359626386</v>
       </c>
       <c r="D366" t="n">
-        <v>41.82769621387857</v>
+        <v>41.82769996355259</v>
       </c>
       <c r="E366" t="n">
-        <v>43.33639133753226</v>
+        <v>43.33639522245434</v>
       </c>
       <c r="F366" t="n">
         <v>4093307</v>
@@ -7892,16 +7892,16 @@
         <v>44699</v>
       </c>
       <c r="B374" t="n">
-        <v>39.99985122680664</v>
+        <v>39.99985504150391</v>
       </c>
       <c r="C374" t="n">
-        <v>42.2242133773643</v>
+        <v>42.22421740419406</v>
       </c>
       <c r="D374" t="n">
-        <v>39.72905892177436</v>
+        <v>39.72906271064676</v>
       </c>
       <c r="E374" t="n">
-        <v>42.13717219055205</v>
+        <v>42.13717620908088</v>
       </c>
       <c r="F374" t="n">
         <v>1865839</v>
@@ -7952,16 +7952,16 @@
         <v>44704</v>
       </c>
       <c r="B377" t="n">
-        <v>42.28224182128906</v>
+        <v>42.28224563598633</v>
       </c>
       <c r="C377" t="n">
-        <v>42.7948127143697</v>
+        <v>42.79481657531103</v>
       </c>
       <c r="D377" t="n">
-        <v>41.3538099687909</v>
+        <v>41.35381369972519</v>
       </c>
       <c r="E377" t="n">
-        <v>41.42150992041549</v>
+        <v>41.42151365745766</v>
       </c>
       <c r="F377" t="n">
         <v>3400119</v>
@@ -8012,16 +8012,16 @@
         <v>44707</v>
       </c>
       <c r="B380" t="n">
-        <v>46.59557342529297</v>
+        <v>46.5955696105957</v>
       </c>
       <c r="C380" t="n">
-        <v>47.16617181868395</v>
+        <v>47.1661679572728</v>
       </c>
       <c r="D380" t="n">
-        <v>45.10621935322675</v>
+        <v>45.10621566046026</v>
       </c>
       <c r="E380" t="n">
-        <v>45.25128426416589</v>
+        <v>45.2512805595232</v>
       </c>
       <c r="F380" t="n">
         <v>4582217</v>
@@ -8072,16 +8072,16 @@
         <v>44712</v>
       </c>
       <c r="B383" t="n">
-        <v>47.14683151245117</v>
+        <v>47.14682769775391</v>
       </c>
       <c r="C383" t="n">
-        <v>49.54527256510714</v>
+        <v>49.5452685563496</v>
       </c>
       <c r="D383" t="n">
-        <v>47.11781778017441</v>
+        <v>47.11781396782467</v>
       </c>
       <c r="E383" t="n">
-        <v>48.22032836396376</v>
+        <v>48.22032446240879</v>
       </c>
       <c r="F383" t="n">
         <v>6322705</v>
@@ -8152,16 +8152,16 @@
         <v>44718</v>
       </c>
       <c r="B387" t="n">
-        <v>45.31898498535156</v>
+        <v>45.3189811706543</v>
       </c>
       <c r="C387" t="n">
-        <v>47.45630618888874</v>
+        <v>47.4563021942838</v>
       </c>
       <c r="D387" t="n">
-        <v>45.13523009894016</v>
+        <v>45.13522629971035</v>
       </c>
       <c r="E387" t="n">
-        <v>47.156500121283</v>
+        <v>47.15649615191405</v>
       </c>
       <c r="F387" t="n">
         <v>1711233</v>
@@ -8172,16 +8172,16 @@
         <v>44719</v>
       </c>
       <c r="B388" t="n">
-        <v>45.31898498535156</v>
+        <v>45.3189811706543</v>
       </c>
       <c r="C388" t="n">
-        <v>45.84122466966569</v>
+        <v>45.84122081100923</v>
       </c>
       <c r="D388" t="n">
-        <v>44.73871408907649</v>
+        <v>44.73871032322317</v>
       </c>
       <c r="E388" t="n">
-        <v>44.98049269229714</v>
+        <v>44.98048890609225</v>
       </c>
       <c r="F388" t="n">
         <v>1887578</v>
@@ -8192,16 +8192,16 @@
         <v>44720</v>
       </c>
       <c r="B389" t="n">
-        <v>45.25128173828125</v>
+        <v>45.25128555297852</v>
       </c>
       <c r="C389" t="n">
-        <v>46.00563122530019</v>
+        <v>46.00563510358936</v>
       </c>
       <c r="D389" t="n">
-        <v>44.9224619623857</v>
+        <v>44.92246574936335</v>
       </c>
       <c r="E389" t="n">
-        <v>45.31898169100119</v>
+        <v>45.31898551140559</v>
       </c>
       <c r="F389" t="n">
         <v>1920490</v>
@@ -8212,16 +8212,16 @@
         <v>44721</v>
       </c>
       <c r="B390" t="n">
-        <v>44.50660705566406</v>
+        <v>44.5066032409668</v>
       </c>
       <c r="C390" t="n">
-        <v>45.59944512032232</v>
+        <v>45.59944121195702</v>
       </c>
       <c r="D390" t="n">
-        <v>44.32285592064108</v>
+        <v>44.32285212169327</v>
       </c>
       <c r="E390" t="n">
-        <v>45.2222703572209</v>
+        <v>45.22226648118356</v>
       </c>
       <c r="F390" t="n">
         <v>1644697</v>
@@ -8472,16 +8472,16 @@
         <v>44741</v>
       </c>
       <c r="B403" t="n">
-        <v>34.71940994262695</v>
+        <v>34.71940612792969</v>
       </c>
       <c r="C403" t="n">
-        <v>35.41573204057546</v>
+        <v>35.41572814937177</v>
       </c>
       <c r="D403" t="n">
-        <v>34.0907840567348</v>
+        <v>34.09078031110602</v>
       </c>
       <c r="E403" t="n">
-        <v>35.29967710839206</v>
+        <v>35.29967322993957</v>
       </c>
       <c r="F403" t="n">
         <v>2690880</v>
@@ -8532,16 +8532,16 @@
         <v>44746</v>
       </c>
       <c r="B406" t="n">
-        <v>35.08690643310547</v>
+        <v>35.08691024780273</v>
       </c>
       <c r="C406" t="n">
-        <v>35.60914979405575</v>
+        <v>35.60915366553204</v>
       </c>
       <c r="D406" t="n">
-        <v>34.19716459197961</v>
+        <v>34.1971683099429</v>
       </c>
       <c r="E406" t="n">
-        <v>34.57433556409744</v>
+        <v>34.57433932306729</v>
       </c>
       <c r="F406" t="n">
         <v>2359523</v>
@@ -8612,16 +8612,16 @@
         <v>44750</v>
       </c>
       <c r="B410" t="n">
-        <v>31.81806564331055</v>
+        <v>31.81806373596191</v>
       </c>
       <c r="C410" t="n">
-        <v>32.48537398775778</v>
+        <v>32.48537204040704</v>
       </c>
       <c r="D410" t="n">
-        <v>31.19911226993215</v>
+        <v>31.19911039968697</v>
       </c>
       <c r="E410" t="n">
-        <v>31.31516719855805</v>
+        <v>31.3151653213559</v>
       </c>
       <c r="F410" t="n">
         <v>4375906</v>
@@ -8712,16 +8712,16 @@
         <v>44757</v>
       </c>
       <c r="B415" t="n">
-        <v>27.79486656188965</v>
+        <v>27.79486846923828</v>
       </c>
       <c r="C415" t="n">
-        <v>29.07145943509457</v>
+        <v>29.07146143004599</v>
       </c>
       <c r="D415" t="n">
-        <v>27.79486656188965</v>
+        <v>27.79486846923828</v>
       </c>
       <c r="E415" t="n">
-        <v>29.06178694260021</v>
+        <v>29.06178893688788</v>
       </c>
       <c r="F415" t="n">
         <v>4618481</v>
@@ -8752,16 +8752,16 @@
         <v>44761</v>
       </c>
       <c r="B417" t="n">
-        <v>29.43896102905273</v>
+        <v>29.43896293640137</v>
       </c>
       <c r="C417" t="n">
-        <v>29.5356728353309</v>
+        <v>29.53567474894549</v>
       </c>
       <c r="D417" t="n">
-        <v>28.11401509178381</v>
+        <v>28.11401691328927</v>
       </c>
       <c r="E417" t="n">
-        <v>28.14302882104603</v>
+        <v>28.14303064443129</v>
       </c>
       <c r="F417" t="n">
         <v>4570230</v>
@@ -8772,16 +8772,16 @@
         <v>44762</v>
       </c>
       <c r="B418" t="n">
-        <v>30.5994987487793</v>
+        <v>30.59950065612793</v>
       </c>
       <c r="C418" t="n">
-        <v>30.97667347904845</v>
+        <v>30.97667540990739</v>
       </c>
       <c r="D418" t="n">
-        <v>29.21652536238831</v>
+        <v>29.21652718353251</v>
       </c>
       <c r="E418" t="n">
-        <v>29.21652536238831</v>
+        <v>29.21652718353251</v>
       </c>
       <c r="F418" t="n">
         <v>5027446</v>
@@ -8792,16 +8792,16 @@
         <v>44763</v>
       </c>
       <c r="B419" t="n">
-        <v>29.44863319396973</v>
+        <v>29.44863510131836</v>
       </c>
       <c r="C419" t="n">
-        <v>29.86449039614633</v>
+        <v>29.86449233042948</v>
       </c>
       <c r="D419" t="n">
-        <v>28.83935050759925</v>
+        <v>28.83935237548546</v>
       </c>
       <c r="E419" t="n">
-        <v>29.86449039614633</v>
+        <v>29.86449233042948</v>
       </c>
       <c r="F419" t="n">
         <v>5437325</v>
@@ -8832,16 +8832,16 @@
         <v>44767</v>
       </c>
       <c r="B421" t="n">
-        <v>29.26488304138184</v>
+        <v>29.2648811340332</v>
       </c>
       <c r="C421" t="n">
-        <v>29.71942650877206</v>
+        <v>29.7194245717984</v>
       </c>
       <c r="D421" t="n">
-        <v>28.43316480875549</v>
+        <v>28.43316295561438</v>
       </c>
       <c r="E421" t="n">
-        <v>28.87803765682343</v>
+        <v>28.87803577468757</v>
       </c>
       <c r="F421" t="n">
         <v>3521914</v>
@@ -8852,16 +8852,16 @@
         <v>44768</v>
       </c>
       <c r="B422" t="n">
-        <v>28.95540618896484</v>
+        <v>28.95540428161621</v>
       </c>
       <c r="C422" t="n">
-        <v>30.15462856046375</v>
+        <v>30.15462657412001</v>
       </c>
       <c r="D422" t="n">
-        <v>28.81033940483069</v>
+        <v>28.81033750703789</v>
       </c>
       <c r="E422" t="n">
-        <v>29.88383623072646</v>
+        <v>29.88383426222034</v>
       </c>
       <c r="F422" t="n">
         <v>2984449</v>
@@ -8872,16 +8872,16 @@
         <v>44769</v>
       </c>
       <c r="B423" t="n">
-        <v>29.66139793395996</v>
+        <v>29.66139984130859</v>
       </c>
       <c r="C423" t="n">
-        <v>29.76778035716261</v>
+        <v>29.76778227135207</v>
       </c>
       <c r="D423" t="n">
-        <v>28.6169130648438</v>
+        <v>28.61691490502781</v>
       </c>
       <c r="E423" t="n">
-        <v>28.95540344493757</v>
+        <v>28.95540530688788</v>
       </c>
       <c r="F423" t="n">
         <v>2554762</v>
@@ -8892,16 +8892,16 @@
         <v>44770</v>
       </c>
       <c r="B424" t="n">
-        <v>30.78325080871582</v>
+        <v>30.78325271606445</v>
       </c>
       <c r="C424" t="n">
-        <v>30.88963323601387</v>
+        <v>30.88963514995402</v>
       </c>
       <c r="D424" t="n">
-        <v>29.53567353730325</v>
+        <v>29.53567536735125</v>
       </c>
       <c r="E424" t="n">
-        <v>29.96120324649545</v>
+        <v>29.96120510290952</v>
       </c>
       <c r="F424" t="n">
         <v>4208906</v>
@@ -8952,16 +8952,16 @@
         <v>44775</v>
       </c>
       <c r="B427" t="n">
-        <v>31.85675048828125</v>
+        <v>31.85674858093262</v>
       </c>
       <c r="C427" t="n">
-        <v>32.07918409507452</v>
+        <v>32.0791821744082</v>
       </c>
       <c r="D427" t="n">
-        <v>30.94766170651904</v>
+        <v>30.94765985359998</v>
       </c>
       <c r="E427" t="n">
-        <v>31.32483646063348</v>
+        <v>31.32483458513196</v>
       </c>
       <c r="F427" t="n">
         <v>3020206</v>
@@ -9072,16 +9072,16 @@
         <v>44783</v>
       </c>
       <c r="B433" t="n">
-        <v>33.26873779296875</v>
+        <v>33.26873397827148</v>
       </c>
       <c r="C433" t="n">
-        <v>33.97473237410905</v>
+        <v>33.97472847846024</v>
       </c>
       <c r="D433" t="n">
-        <v>32.87222177725572</v>
+        <v>32.87221800802422</v>
       </c>
       <c r="E433" t="n">
-        <v>33.62657133023831</v>
+        <v>33.62656747451073</v>
       </c>
       <c r="F433" t="n">
         <v>3325457</v>
@@ -9152,16 +9152,16 @@
         <v>44789</v>
       </c>
       <c r="B437" t="n">
-        <v>32.27260971069336</v>
+        <v>32.27260589599609</v>
       </c>
       <c r="C437" t="n">
-        <v>32.61110200955398</v>
+        <v>32.61109815484615</v>
       </c>
       <c r="D437" t="n">
-        <v>31.73102503057709</v>
+        <v>31.73102127989639</v>
       </c>
       <c r="E437" t="n">
-        <v>32.39833338730038</v>
+        <v>32.39832955774229</v>
       </c>
       <c r="F437" t="n">
         <v>2684074</v>
@@ -9172,16 +9172,16 @@
         <v>44790</v>
       </c>
       <c r="B438" t="n">
-        <v>32.53372573852539</v>
+        <v>32.53372955322266</v>
       </c>
       <c r="C438" t="n">
-        <v>32.93024545622303</v>
+        <v>32.93024931741367</v>
       </c>
       <c r="D438" t="n">
-        <v>31.80839000156146</v>
+        <v>31.80839373121048</v>
       </c>
       <c r="E438" t="n">
-        <v>31.81806249384815</v>
+        <v>31.8180662246313</v>
       </c>
       <c r="F438" t="n">
         <v>3057587</v>
@@ -9252,16 +9252,16 @@
         <v>44796</v>
       </c>
       <c r="B442" t="n">
-        <v>35.11592483520508</v>
+        <v>35.11592102050781</v>
       </c>
       <c r="C442" t="n">
-        <v>35.54145457609587</v>
+        <v>35.54145071517264</v>
       </c>
       <c r="D442" t="n">
-        <v>33.43314711052539</v>
+        <v>33.43314347863087</v>
       </c>
       <c r="E442" t="n">
-        <v>33.46216084263848</v>
+        <v>33.46215720759215</v>
       </c>
       <c r="F442" t="n">
         <v>5706007</v>
@@ -9292,16 +9292,16 @@
         <v>44798</v>
       </c>
       <c r="B444" t="n">
-        <v>35.73487854003906</v>
+        <v>35.7348747253418</v>
       </c>
       <c r="C444" t="n">
-        <v>36.56659679067325</v>
+        <v>36.56659288719009</v>
       </c>
       <c r="D444" t="n">
-        <v>35.39638999233915</v>
+        <v>35.39638621377552</v>
       </c>
       <c r="E444" t="n">
-        <v>35.86060596289047</v>
+        <v>35.8606021347718</v>
       </c>
       <c r="F444" t="n">
         <v>2850362</v>
@@ -9372,16 +9372,16 @@
         <v>44804</v>
       </c>
       <c r="B448" t="n">
-        <v>36.16040802001953</v>
+        <v>36.16040420532227</v>
       </c>
       <c r="C448" t="n">
-        <v>36.46021408739674</v>
+        <v>36.46021024107181</v>
       </c>
       <c r="D448" t="n">
-        <v>35.22230734004456</v>
+        <v>35.22230362431106</v>
       </c>
       <c r="E448" t="n">
-        <v>35.91862941698318</v>
+        <v>35.91862562779205</v>
       </c>
       <c r="F448" t="n">
         <v>3394125</v>
@@ -9392,16 +9392,16 @@
         <v>44805</v>
       </c>
       <c r="B449" t="n">
-        <v>35.58013916015625</v>
+        <v>35.58013534545898</v>
       </c>
       <c r="C449" t="n">
-        <v>36.22810623483188</v>
+        <v>36.22810235066332</v>
       </c>
       <c r="D449" t="n">
-        <v>35.00954078502128</v>
+        <v>35.00953703150028</v>
       </c>
       <c r="E449" t="n">
-        <v>35.84125898955293</v>
+        <v>35.8412551468599</v>
       </c>
       <c r="F449" t="n">
         <v>3340084</v>
@@ -9492,16 +9492,16 @@
         <v>44813</v>
       </c>
       <c r="B454" t="n">
-        <v>35.92829895019531</v>
+        <v>35.92830276489258</v>
       </c>
       <c r="C454" t="n">
-        <v>36.3731698941971</v>
+        <v>36.37317375612866</v>
       </c>
       <c r="D454" t="n">
-        <v>35.60915167019012</v>
+        <v>35.60915545100184</v>
       </c>
       <c r="E454" t="n">
-        <v>35.79290279374685</v>
+        <v>35.79290659406839</v>
       </c>
       <c r="F454" t="n">
         <v>3544465</v>
@@ -9552,16 +9552,16 @@
         <v>44818</v>
       </c>
       <c r="B457" t="n">
-        <v>37.25325012207031</v>
+        <v>37.25324630737305</v>
       </c>
       <c r="C457" t="n">
-        <v>37.57239743066493</v>
+        <v>37.57239358328728</v>
       </c>
       <c r="D457" t="n">
-        <v>35.96698839437353</v>
+        <v>35.96698471138824</v>
       </c>
       <c r="E457" t="n">
-        <v>36.05402584393507</v>
+        <v>36.05402215203722</v>
       </c>
       <c r="F457" t="n">
         <v>4057043</v>
@@ -9592,16 +9592,16 @@
         <v>44820</v>
       </c>
       <c r="B459" t="n">
-        <v>36.7987060546875</v>
+        <v>36.79870223999023</v>
       </c>
       <c r="C459" t="n">
-        <v>36.7987060546875</v>
+        <v>36.79870223999023</v>
       </c>
       <c r="D459" t="n">
-        <v>35.7832329328566</v>
+        <v>35.78322922342723</v>
       </c>
       <c r="E459" t="n">
-        <v>36.14106646140942</v>
+        <v>36.14106271488564</v>
       </c>
       <c r="F459" t="n">
         <v>2974596</v>
@@ -9612,16 +9612,16 @@
         <v>44823</v>
       </c>
       <c r="B460" t="n">
-        <v>36.84706115722656</v>
+        <v>36.8470573425293</v>
       </c>
       <c r="C460" t="n">
-        <v>37.39831831798563</v>
+        <v>37.3983144462179</v>
       </c>
       <c r="D460" t="n">
-        <v>35.79290555412169</v>
+        <v>35.7929018485589</v>
       </c>
       <c r="E460" t="n">
-        <v>35.79290555412169</v>
+        <v>35.7929018485589</v>
       </c>
       <c r="F460" t="n">
         <v>3461677</v>
@@ -9652,16 +9652,16 @@
         <v>44825</v>
       </c>
       <c r="B462" t="n">
-        <v>38.03661346435547</v>
+        <v>38.0366096496582</v>
       </c>
       <c r="C462" t="n">
-        <v>38.79096301231463</v>
+        <v>38.79095912196355</v>
       </c>
       <c r="D462" t="n">
-        <v>37.62075246461414</v>
+        <v>37.62074869162363</v>
       </c>
       <c r="E462" t="n">
-        <v>37.93989977373904</v>
+        <v>37.9398959687412</v>
       </c>
       <c r="F462" t="n">
         <v>4689181</v>
@@ -9732,16 +9732,16 @@
         <v>44831</v>
       </c>
       <c r="B466" t="n">
-        <v>33.61689376831055</v>
+        <v>33.61689758300781</v>
       </c>
       <c r="C466" t="n">
-        <v>34.44861190035511</v>
+        <v>34.44861580943209</v>
       </c>
       <c r="D466" t="n">
-        <v>33.3267602334253</v>
+        <v>33.32676401519949</v>
       </c>
       <c r="E466" t="n">
-        <v>34.44861190035511</v>
+        <v>34.44861580943209</v>
       </c>
       <c r="F466" t="n">
         <v>5480701</v>
@@ -9752,16 +9752,16 @@
         <v>44832</v>
       </c>
       <c r="B467" t="n">
-        <v>34.57433700561523</v>
+        <v>34.5743408203125</v>
       </c>
       <c r="C467" t="n">
-        <v>34.99987045518622</v>
+        <v>34.99987431683395</v>
       </c>
       <c r="D467" t="n">
-        <v>33.19136547412988</v>
+        <v>33.19136913623947</v>
       </c>
       <c r="E467" t="n">
-        <v>33.66525014270204</v>
+        <v>33.66525385709685</v>
       </c>
       <c r="F467" t="n">
         <v>4399676</v>
@@ -9772,16 +9772,16 @@
         <v>44833</v>
       </c>
       <c r="B468" t="n">
-        <v>33.90703201293945</v>
+        <v>33.90702819824219</v>
       </c>
       <c r="C468" t="n">
-        <v>34.69039528924284</v>
+        <v>34.69039138641359</v>
       </c>
       <c r="D468" t="n">
-        <v>33.09465875193581</v>
+        <v>33.09465502863428</v>
       </c>
       <c r="E468" t="n">
-        <v>34.61302658569848</v>
+        <v>34.61302269157358</v>
       </c>
       <c r="F468" t="n">
         <v>4499631</v>
@@ -9812,16 +9812,16 @@
         <v>44837</v>
       </c>
       <c r="B470" t="n">
-        <v>36.7987060546875</v>
+        <v>36.79870223999023</v>
       </c>
       <c r="C470" t="n">
-        <v>36.91476098234264</v>
+        <v>36.91475715561467</v>
       </c>
       <c r="D470" t="n">
-        <v>35.52211309320833</v>
+        <v>35.52210941084767</v>
       </c>
       <c r="E470" t="n">
-        <v>36.26679013465196</v>
+        <v>36.26678637509517</v>
       </c>
       <c r="F470" t="n">
         <v>4419789</v>
@@ -9852,16 +9852,16 @@
         <v>44839</v>
       </c>
       <c r="B472" t="n">
-        <v>41.63427734375</v>
+        <v>41.63427352905273</v>
       </c>
       <c r="C472" t="n">
-        <v>42.48533680478608</v>
+        <v>42.48533291211138</v>
       </c>
       <c r="D472" t="n">
-        <v>40.55110803146717</v>
+        <v>40.55110431601417</v>
       </c>
       <c r="E472" t="n">
-        <v>40.61880798727272</v>
+        <v>40.61880426561678</v>
       </c>
       <c r="F472" t="n">
         <v>6927519</v>
@@ -9892,16 +9892,16 @@
         <v>44841</v>
       </c>
       <c r="B474" t="n">
-        <v>41.47953796386719</v>
+        <v>41.47954177856445</v>
       </c>
       <c r="C474" t="n">
-        <v>42.45632104937901</v>
+        <v>42.45632495390688</v>
       </c>
       <c r="D474" t="n">
-        <v>41.22808688619578</v>
+        <v>41.22809067776815</v>
       </c>
       <c r="E474" t="n">
-        <v>41.59558913638236</v>
+        <v>41.59559296175236</v>
       </c>
       <c r="F474" t="n">
         <v>3503020</v>
@@ -10072,16 +10072,16 @@
         <v>44855</v>
       </c>
       <c r="B483" t="n">
-        <v>44.22614288330078</v>
+        <v>44.22613906860352</v>
       </c>
       <c r="C483" t="n">
-        <v>44.68068635480393</v>
+        <v>44.68068250090031</v>
       </c>
       <c r="D483" t="n">
-        <v>42.41764149048589</v>
+        <v>42.41763783177974</v>
       </c>
       <c r="E483" t="n">
-        <v>42.9688949036628</v>
+        <v>42.96889119740864</v>
       </c>
       <c r="F483" t="n">
         <v>5360835</v>
@@ -10112,16 +10112,16 @@
         <v>44859</v>
       </c>
       <c r="B485" t="n">
-        <v>42.69810104370117</v>
+        <v>42.69809722900391</v>
       </c>
       <c r="C485" t="n">
-        <v>44.71937098158734</v>
+        <v>44.7193669863075</v>
       </c>
       <c r="D485" t="n">
-        <v>42.52402240539543</v>
+        <v>42.52401860625056</v>
       </c>
       <c r="E485" t="n">
-        <v>43.43310931590769</v>
+        <v>43.43310543554394</v>
       </c>
       <c r="F485" t="n">
         <v>3364870</v>
@@ -10232,16 +10232,16 @@
         <v>44868</v>
       </c>
       <c r="B491" t="n">
-        <v>46.30543899536133</v>
+        <v>46.30543518066406</v>
       </c>
       <c r="C491" t="n">
-        <v>46.43116266535413</v>
+        <v>46.4311588402996</v>
       </c>
       <c r="D491" t="n">
-        <v>44.51627889399545</v>
+        <v>44.51627522669133</v>
       </c>
       <c r="E491" t="n">
-        <v>44.98049109746535</v>
+        <v>44.98048739191887</v>
       </c>
       <c r="F491" t="n">
         <v>3262984</v>
@@ -10312,16 +10312,16 @@
         <v>44874</v>
       </c>
       <c r="B495" t="n">
-        <v>44.69035720825195</v>
+        <v>44.69035339355469</v>
       </c>
       <c r="C495" t="n">
-        <v>46.49886228228617</v>
+        <v>46.49885831321781</v>
       </c>
       <c r="D495" t="n">
-        <v>44.23581375342662</v>
+        <v>44.23580997752845</v>
       </c>
       <c r="E495" t="n">
-        <v>45.35766552501359</v>
+        <v>45.35766165335595</v>
       </c>
       <c r="F495" t="n">
         <v>4884014</v>
@@ -10332,16 +10332,16 @@
         <v>44875</v>
       </c>
       <c r="B496" t="n">
-        <v>42.05980682373047</v>
+        <v>42.0598030090332</v>
       </c>
       <c r="C496" t="n">
-        <v>44.68068514703247</v>
+        <v>44.68068109462947</v>
       </c>
       <c r="D496" t="n">
-        <v>41.6439458411077</v>
+        <v>41.64394206412777</v>
       </c>
       <c r="E496" t="n">
-        <v>43.65554705124352</v>
+        <v>43.65554309181744</v>
       </c>
       <c r="F496" t="n">
         <v>5453172</v>
@@ -10472,16 +10472,16 @@
         <v>44887</v>
       </c>
       <c r="B503" t="n">
-        <v>35.72520446777344</v>
+        <v>35.7252082824707</v>
       </c>
       <c r="C503" t="n">
-        <v>38.01726275125628</v>
+        <v>38.01726681069696</v>
       </c>
       <c r="D503" t="n">
-        <v>35.41572595102293</v>
+        <v>35.41572973267442</v>
       </c>
       <c r="E503" t="n">
-        <v>37.37896822915095</v>
+        <v>37.37897222043525</v>
       </c>
       <c r="F503" t="n">
         <v>4879239</v>
@@ -10492,16 +10492,16 @@
         <v>44888</v>
       </c>
       <c r="B504" t="n">
-        <v>34.29388046264648</v>
+        <v>34.29387664794922</v>
       </c>
       <c r="C504" t="n">
-        <v>35.59948346985989</v>
+        <v>35.59947950993321</v>
       </c>
       <c r="D504" t="n">
-        <v>33.84900571743197</v>
+        <v>33.84900195222058</v>
       </c>
       <c r="E504" t="n">
-        <v>35.37704984482862</v>
+        <v>35.37704590964446</v>
       </c>
       <c r="F504" t="n">
         <v>5644348</v>
@@ -10532,16 +10532,16 @@
         <v>44890</v>
       </c>
       <c r="B506" t="n">
-        <v>34.23584747314453</v>
+        <v>34.2358512878418</v>
       </c>
       <c r="C506" t="n">
-        <v>36.49889581830917</v>
+        <v>36.49889988516448</v>
       </c>
       <c r="D506" t="n">
-        <v>34.11012381427162</v>
+        <v>34.11012761496025</v>
       </c>
       <c r="E506" t="n">
-        <v>36.17007605925269</v>
+        <v>36.17008008946956</v>
       </c>
       <c r="F506" t="n">
         <v>4398253</v>
@@ -10552,16 +10552,16 @@
         <v>44893</v>
       </c>
       <c r="B507" t="n">
-        <v>33.64590835571289</v>
+        <v>33.64591217041016</v>
       </c>
       <c r="C507" t="n">
-        <v>34.11012427192836</v>
+        <v>34.11012813925738</v>
       </c>
       <c r="D507" t="n">
-        <v>32.92057262619048</v>
+        <v>32.92057635865081</v>
       </c>
       <c r="E507" t="n">
-        <v>33.36544355803103</v>
+        <v>33.36544734092983</v>
       </c>
       <c r="F507" t="n">
         <v>4077054</v>
@@ -10652,16 +10652,16 @@
         <v>44900</v>
       </c>
       <c r="B512" t="n">
-        <v>34.04242324829102</v>
+        <v>34.04242706298828</v>
       </c>
       <c r="C512" t="n">
-        <v>35.87994187083461</v>
+        <v>35.879945891439</v>
       </c>
       <c r="D512" t="n">
-        <v>33.77163095133564</v>
+        <v>33.77163473568869</v>
       </c>
       <c r="E512" t="n">
-        <v>35.57046335392476</v>
+        <v>35.57046733984986</v>
       </c>
       <c r="F512" t="n">
         <v>5158181</v>
@@ -10732,16 +10732,16 @@
         <v>44904</v>
       </c>
       <c r="B516" t="n">
-        <v>31.69234085083008</v>
+        <v>31.69233894348145</v>
       </c>
       <c r="C516" t="n">
-        <v>32.74649642178647</v>
+        <v>32.74649445099531</v>
       </c>
       <c r="D516" t="n">
-        <v>31.4892447329005</v>
+        <v>31.48924283777486</v>
       </c>
       <c r="E516" t="n">
-        <v>32.22425300897184</v>
+        <v>32.22425106961099</v>
       </c>
       <c r="F516" t="n">
         <v>2885712</v>
@@ -10752,16 +10752,16 @@
         <v>44907</v>
       </c>
       <c r="B517" t="n">
-        <v>32.23392486572266</v>
+        <v>32.23392105102539</v>
       </c>
       <c r="C517" t="n">
-        <v>32.41767599422015</v>
+        <v>32.41767215777701</v>
       </c>
       <c r="D517" t="n">
-        <v>31.06371439332975</v>
+        <v>31.06371071712008</v>
       </c>
       <c r="E517" t="n">
-        <v>31.59562654097396</v>
+        <v>31.59562280181559</v>
       </c>
       <c r="F517" t="n">
         <v>3445728</v>
@@ -10772,16 +10772,16 @@
         <v>44908</v>
       </c>
       <c r="B518" t="n">
-        <v>32.5240592956543</v>
+        <v>32.52405548095703</v>
       </c>
       <c r="C518" t="n">
-        <v>33.41380497900949</v>
+        <v>33.41380105995531</v>
       </c>
       <c r="D518" t="n">
-        <v>31.98247464077933</v>
+        <v>31.9824708896037</v>
       </c>
       <c r="E518" t="n">
-        <v>32.39833187733107</v>
+        <v>32.39832807738018</v>
       </c>
       <c r="F518" t="n">
         <v>3369136</v>
@@ -10872,16 +10872,16 @@
         <v>44915</v>
       </c>
       <c r="B523" t="n">
-        <v>31.63431167602539</v>
+        <v>31.63431358337402</v>
       </c>
       <c r="C523" t="n">
-        <v>31.83740403538475</v>
+        <v>31.83740595497857</v>
       </c>
       <c r="D523" t="n">
-        <v>30.62851300266902</v>
+        <v>30.62851484937437</v>
       </c>
       <c r="E523" t="n">
-        <v>30.76390915810044</v>
+        <v>30.76391101296931</v>
       </c>
       <c r="F523" t="n">
         <v>3472546</v>
@@ -10892,16 +10892,16 @@
         <v>44916</v>
       </c>
       <c r="B524" t="n">
-        <v>32.19523620605469</v>
+        <v>32.19524002075195</v>
       </c>
       <c r="C524" t="n">
-        <v>32.50471472608491</v>
+        <v>32.50471857745117</v>
       </c>
       <c r="D524" t="n">
-        <v>31.22812192077017</v>
+        <v>31.22812562087756</v>
       </c>
       <c r="E524" t="n">
-        <v>32.34997359228213</v>
+        <v>32.34997742531367</v>
       </c>
       <c r="F524" t="n">
         <v>3938295</v>
@@ -10912,16 +10912,16 @@
         <v>44917</v>
       </c>
       <c r="B525" t="n">
-        <v>32.01148986816406</v>
+        <v>32.0114860534668</v>
       </c>
       <c r="C525" t="n">
-        <v>32.78518066232546</v>
+        <v>32.78517675543017</v>
       </c>
       <c r="D525" t="n">
-        <v>31.53760514678948</v>
+        <v>31.5376013885634</v>
       </c>
       <c r="E525" t="n">
-        <v>32.41767837830338</v>
+        <v>32.41767451520204</v>
       </c>
       <c r="F525" t="n">
         <v>3822391</v>
@@ -10932,16 +10932,16 @@
         <v>44918</v>
       </c>
       <c r="B526" t="n">
-        <v>34.68072128295898</v>
+        <v>34.68072509765625</v>
       </c>
       <c r="C526" t="n">
-        <v>34.88381363050969</v>
+        <v>34.88381746754605</v>
       </c>
       <c r="D526" t="n">
-        <v>32.68846528926745</v>
+        <v>32.68846888482701</v>
       </c>
       <c r="E526" t="n">
-        <v>33.17202242375276</v>
+        <v>33.17202607250107</v>
       </c>
       <c r="F526" t="n">
         <v>6955860</v>
@@ -11012,16 +11012,16 @@
         <v>44924</v>
       </c>
       <c r="B530" t="n">
-        <v>36.50856781005859</v>
+        <v>36.50856399536133</v>
       </c>
       <c r="C530" t="n">
-        <v>37.23390359436439</v>
+        <v>37.23389970387844</v>
       </c>
       <c r="D530" t="n">
-        <v>35.61882587917678</v>
+        <v>35.61882215744662</v>
       </c>
       <c r="E530" t="n">
-        <v>35.87994571220566</v>
+        <v>35.87994196319169</v>
       </c>
       <c r="F530" t="n">
         <v>4887264</v>
@@ -11032,16 +11032,16 @@
         <v>44928</v>
       </c>
       <c r="B531" t="n">
-        <v>35.2126350402832</v>
+        <v>35.21263885498047</v>
       </c>
       <c r="C531" t="n">
-        <v>36.68264774905137</v>
+        <v>36.68265172299981</v>
       </c>
       <c r="D531" t="n">
-        <v>34.78710534150101</v>
+        <v>34.78710911009928</v>
       </c>
       <c r="E531" t="n">
-        <v>36.01533947163607</v>
+        <v>36.01534337329287</v>
       </c>
       <c r="F531" t="n">
         <v>2924313</v>
@@ -11152,16 +11152,16 @@
         <v>44936</v>
       </c>
       <c r="B537" t="n">
-        <v>37.79483032226562</v>
+        <v>37.79483413696289</v>
       </c>
       <c r="C537" t="n">
-        <v>38.07529137196207</v>
+        <v>38.07529521496675</v>
       </c>
       <c r="D537" t="n">
-        <v>36.49889625466188</v>
+        <v>36.49889993855829</v>
       </c>
       <c r="E537" t="n">
-        <v>37.0985045751726</v>
+        <v>37.09850831958851</v>
       </c>
       <c r="F537" t="n">
         <v>3183751</v>
@@ -11192,16 +11192,16 @@
         <v>44938</v>
       </c>
       <c r="B539" t="n">
-        <v>43.42343902587891</v>
+        <v>43.42343521118164</v>
       </c>
       <c r="C539" t="n">
-        <v>44.7290457434945</v>
+        <v>44.72904181410123</v>
       </c>
       <c r="D539" t="n">
-        <v>43.19133291383822</v>
+        <v>43.19132911953119</v>
       </c>
       <c r="E539" t="n">
-        <v>43.40409778676949</v>
+        <v>43.40409397377132</v>
       </c>
       <c r="F539" t="n">
         <v>7341055</v>
@@ -11212,16 +11212,16 @@
         <v>44939</v>
       </c>
       <c r="B540" t="n">
-        <v>42.75612640380859</v>
+        <v>42.75613021850586</v>
       </c>
       <c r="C540" t="n">
-        <v>43.50080338468374</v>
+        <v>43.50080726582102</v>
       </c>
       <c r="D540" t="n">
-        <v>42.35961043000531</v>
+        <v>42.35961420932546</v>
       </c>
       <c r="E540" t="n">
-        <v>43.42343468839838</v>
+        <v>43.42343856263282</v>
       </c>
       <c r="F540" t="n">
         <v>4249336</v>
@@ -11272,16 +11272,16 @@
         <v>44944</v>
       </c>
       <c r="B543" t="n">
-        <v>44.53561782836914</v>
+        <v>44.53562164306641</v>
       </c>
       <c r="C543" t="n">
-        <v>45.241612337541</v>
+        <v>45.24161621271021</v>
       </c>
       <c r="D543" t="n">
-        <v>43.220342491427</v>
+        <v>43.22034619346439</v>
       </c>
       <c r="E543" t="n">
-        <v>43.42343485149192</v>
+        <v>43.42343857092518</v>
       </c>
       <c r="F543" t="n">
         <v>6730959</v>
@@ -11332,16 +11332,16 @@
         <v>44949</v>
       </c>
       <c r="B546" t="n">
-        <v>46.45050430297852</v>
+        <v>46.45050811767578</v>
       </c>
       <c r="C546" t="n">
-        <v>48.53947031074529</v>
+        <v>48.53947429699662</v>
       </c>
       <c r="D546" t="n">
-        <v>45.88957845353607</v>
+        <v>45.88958222216792</v>
       </c>
       <c r="E546" t="n">
-        <v>47.67873842593739</v>
+        <v>47.67874234150205</v>
       </c>
       <c r="F546" t="n">
         <v>5971946</v>
@@ -11392,16 +11392,16 @@
         <v>44952</v>
       </c>
       <c r="B549" t="n">
-        <v>45.26095199584961</v>
+        <v>45.26095581054688</v>
       </c>
       <c r="C549" t="n">
-        <v>46.77931963988798</v>
+        <v>46.77932358255676</v>
       </c>
       <c r="D549" t="n">
-        <v>45.24161075927422</v>
+        <v>45.24161457234137</v>
       </c>
       <c r="E549" t="n">
-        <v>45.92826025966649</v>
+        <v>45.92826413060603</v>
       </c>
       <c r="F549" t="n">
         <v>3327082</v>
@@ -11412,16 +11412,16 @@
         <v>44953</v>
       </c>
       <c r="B550" t="n">
-        <v>44.50660705566406</v>
+        <v>44.5066032409668</v>
       </c>
       <c r="C550" t="n">
-        <v>46.34412590104548</v>
+        <v>46.34412192885299</v>
       </c>
       <c r="D550" t="n">
-        <v>44.16811476963287</v>
+        <v>44.16811098394805</v>
       </c>
       <c r="E550" t="n">
-        <v>46.20872973614816</v>
+        <v>46.20872577556058</v>
       </c>
       <c r="F550" t="n">
         <v>4035914</v>
@@ -11432,16 +11432,16 @@
         <v>44956</v>
       </c>
       <c r="B551" t="n">
-        <v>43.79093933105469</v>
+        <v>43.79094314575195</v>
       </c>
       <c r="C551" t="n">
-        <v>44.43890261092821</v>
+        <v>44.43890648207057</v>
       </c>
       <c r="D551" t="n">
-        <v>43.13329981152729</v>
+        <v>43.13330356893655</v>
       </c>
       <c r="E551" t="n">
-        <v>44.3131789517849</v>
+        <v>44.31318281197527</v>
       </c>
       <c r="F551" t="n">
         <v>3870439</v>
@@ -11572,16 +11572,16 @@
         <v>44965</v>
       </c>
       <c r="B558" t="n">
-        <v>43.12363052368164</v>
+        <v>43.12362670898438</v>
       </c>
       <c r="C558" t="n">
-        <v>43.13330301647882</v>
+        <v>43.13329920092593</v>
       </c>
       <c r="D558" t="n">
-        <v>42.08881994983436</v>
+        <v>42.08881622667597</v>
       </c>
       <c r="E558" t="n">
-        <v>42.57237713333137</v>
+        <v>42.57237336739773</v>
       </c>
       <c r="F558" t="n">
         <v>2757212</v>
@@ -11672,16 +11672,16 @@
         <v>44972</v>
       </c>
       <c r="B563" t="n">
-        <v>40.0482063293457</v>
+        <v>40.04821014404297</v>
       </c>
       <c r="C563" t="n">
-        <v>40.52209099098364</v>
+        <v>40.52209485081966</v>
       </c>
       <c r="D563" t="n">
-        <v>38.90700964744255</v>
+        <v>38.90701335343782</v>
       </c>
       <c r="E563" t="n">
-        <v>38.92635463185054</v>
+        <v>38.92635833968847</v>
       </c>
       <c r="F563" t="n">
         <v>3495706</v>
@@ -11752,16 +11752,16 @@
         <v>44980</v>
       </c>
       <c r="B567" t="n">
-        <v>38.00759506225586</v>
+        <v>38.00759887695312</v>
       </c>
       <c r="C567" t="n">
-        <v>39.07141929530241</v>
+        <v>39.07142321677222</v>
       </c>
       <c r="D567" t="n">
-        <v>37.7368027579212</v>
+        <v>37.73680654543994</v>
       </c>
       <c r="E567" t="n">
-        <v>37.95924009667655</v>
+        <v>37.95924390652058</v>
       </c>
       <c r="F567" t="n">
         <v>3548732</v>
@@ -11812,16 +11812,16 @@
         <v>44985</v>
       </c>
       <c r="B570" t="n">
-        <v>35.2126350402832</v>
+        <v>35.21263885498047</v>
       </c>
       <c r="C570" t="n">
-        <v>38.49115271645117</v>
+        <v>38.49115688632073</v>
       </c>
       <c r="D570" t="n">
-        <v>35.2126350402832</v>
+        <v>35.21263885498047</v>
       </c>
       <c r="E570" t="n">
-        <v>37.13719117707558</v>
+        <v>37.13719520026616</v>
       </c>
       <c r="F570" t="n">
         <v>11036876</v>
@@ -11832,16 +11832,16 @@
         <v>44986</v>
       </c>
       <c r="B571" t="n">
-        <v>31.52792930603027</v>
+        <v>31.52793121337891</v>
       </c>
       <c r="C571" t="n">
-        <v>35.21263549119504</v>
+        <v>35.21263762145776</v>
       </c>
       <c r="D571" t="n">
-        <v>29.89350481936535</v>
+        <v>29.89350662783602</v>
       </c>
       <c r="E571" t="n">
-        <v>35.10625306513723</v>
+        <v>35.10625518896411</v>
       </c>
       <c r="F571" t="n">
         <v>24633899</v>
@@ -11872,16 +11872,16 @@
         <v>44988</v>
       </c>
       <c r="B573" t="n">
-        <v>31.74069404602051</v>
+        <v>31.74069595336914</v>
       </c>
       <c r="C573" t="n">
-        <v>31.93411766023568</v>
+        <v>31.93411957920744</v>
       </c>
       <c r="D573" t="n">
-        <v>30.40607560502645</v>
+        <v>30.40607743217574</v>
       </c>
       <c r="E573" t="n">
-        <v>30.47377368262298</v>
+        <v>30.47377551384036</v>
       </c>
       <c r="F573" t="n">
         <v>7573675</v>
@@ -11892,16 +11892,16 @@
         <v>44991</v>
       </c>
       <c r="B574" t="n">
-        <v>31.86641883850098</v>
+        <v>31.86642074584961</v>
       </c>
       <c r="C574" t="n">
-        <v>32.34997601739302</v>
+        <v>32.34997795368473</v>
       </c>
       <c r="D574" t="n">
-        <v>30.94766132287878</v>
+        <v>30.94766317523564</v>
       </c>
       <c r="E574" t="n">
-        <v>31.74069517121325</v>
+        <v>31.74069707103675</v>
       </c>
       <c r="F574" t="n">
         <v>5963007</v>
@@ -11992,16 +11992,16 @@
         <v>44998</v>
       </c>
       <c r="B579" t="n">
-        <v>26.4505786895752</v>
+        <v>26.45058059692383</v>
       </c>
       <c r="C579" t="n">
-        <v>27.32098119587531</v>
+        <v>27.32098316598858</v>
       </c>
       <c r="D579" t="n">
-        <v>25.76392542920967</v>
+        <v>25.76392728704381</v>
       </c>
       <c r="E579" t="n">
-        <v>26.59564546166059</v>
+        <v>26.59564737946998</v>
       </c>
       <c r="F579" t="n">
         <v>13860726</v>
@@ -12032,16 +12032,16 @@
         <v>45000</v>
       </c>
       <c r="B581" t="n">
-        <v>26.28617095947266</v>
+        <v>26.28616905212402</v>
       </c>
       <c r="C581" t="n">
-        <v>26.82775374453002</v>
+        <v>26.82775179788365</v>
       </c>
       <c r="D581" t="n">
-        <v>25.62853324821252</v>
+        <v>25.62853138858268</v>
       </c>
       <c r="E581" t="n">
-        <v>26.58597514665809</v>
+        <v>26.58597321755539</v>
       </c>
       <c r="F581" t="n">
         <v>12174787</v>
@@ -12072,16 +12072,16 @@
         <v>45002</v>
       </c>
       <c r="B583" t="n">
-        <v>30.70588111877441</v>
+        <v>30.70588302612305</v>
       </c>
       <c r="C583" t="n">
-        <v>30.8896322374788</v>
+        <v>30.88963415624145</v>
       </c>
       <c r="D583" t="n">
-        <v>27.73684012155175</v>
+        <v>27.73684184447329</v>
       </c>
       <c r="E583" t="n">
-        <v>30.45443004984579</v>
+        <v>30.45443194157511</v>
       </c>
       <c r="F583" t="n">
         <v>23193684</v>
@@ -12092,16 +12092,16 @@
         <v>45005</v>
       </c>
       <c r="B584" t="n">
-        <v>29.79679679870605</v>
+        <v>29.79679489135742</v>
       </c>
       <c r="C584" t="n">
-        <v>31.20878403151084</v>
+        <v>31.20878203377826</v>
       </c>
       <c r="D584" t="n">
-        <v>29.32291022343201</v>
+        <v>29.32290834641774</v>
       </c>
       <c r="E584" t="n">
-        <v>30.70588372476053</v>
+        <v>30.70588175921954</v>
       </c>
       <c r="F584" t="n">
         <v>7729094</v>
@@ -12252,16 +12252,16 @@
         <v>45015</v>
       </c>
       <c r="B592" t="n">
-        <v>29.38093566894531</v>
+        <v>29.38093376159668</v>
       </c>
       <c r="C592" t="n">
-        <v>30.51245994826028</v>
+        <v>30.51245796745546</v>
       </c>
       <c r="D592" t="n">
-        <v>29.27455323657771</v>
+        <v>29.2745513361352</v>
       </c>
       <c r="E592" t="n">
-        <v>29.95153405508782</v>
+        <v>29.95153211069714</v>
       </c>
       <c r="F592" t="n">
         <v>5560645</v>
@@ -12312,16 +12312,16 @@
         <v>45020</v>
       </c>
       <c r="B595" t="n">
-        <v>27.92059326171875</v>
+        <v>27.92059135437012</v>
       </c>
       <c r="C595" t="n">
-        <v>29.70975523383049</v>
+        <v>29.70975320425825</v>
       </c>
       <c r="D595" t="n">
-        <v>27.91092264260987</v>
+        <v>27.91092073592187</v>
       </c>
       <c r="E595" t="n">
-        <v>29.57435907115471</v>
+        <v>29.57435705083184</v>
       </c>
       <c r="F595" t="n">
         <v>7552242</v>
@@ -12332,16 +12332,16 @@
         <v>45021</v>
       </c>
       <c r="B596" t="n">
-        <v>26.76972579956055</v>
+        <v>26.76972770690918</v>
       </c>
       <c r="C596" t="n">
-        <v>27.85289314814766</v>
+        <v>27.8528951326722</v>
       </c>
       <c r="D596" t="n">
-        <v>26.23781180677641</v>
+        <v>26.23781367622606</v>
       </c>
       <c r="E596" t="n">
-        <v>27.65947141114338</v>
+        <v>27.65947338188658</v>
       </c>
       <c r="F596" t="n">
         <v>12382825</v>
@@ -12372,16 +12372,16 @@
         <v>45026</v>
       </c>
       <c r="B598" t="n">
-        <v>29.65172576904297</v>
+        <v>29.6517276763916</v>
       </c>
       <c r="C598" t="n">
-        <v>29.8354768886412</v>
+        <v>29.83547880780963</v>
       </c>
       <c r="D598" t="n">
-        <v>28.19138368313743</v>
+        <v>28.19138549654949</v>
       </c>
       <c r="E598" t="n">
-        <v>28.33645045512486</v>
+        <v>28.33645227786835</v>
       </c>
       <c r="F598" t="n">
         <v>8774363</v>
@@ -12552,16 +12552,16 @@
         <v>45040</v>
       </c>
       <c r="B607" t="n">
-        <v>26.96700286865234</v>
+        <v>26.96700477600098</v>
       </c>
       <c r="C607" t="n">
-        <v>27.07506608384296</v>
+        <v>27.07506799883479</v>
       </c>
       <c r="D607" t="n">
-        <v>26.23019953206389</v>
+        <v>26.23020138729918</v>
       </c>
       <c r="E607" t="n">
-        <v>26.86876204901633</v>
+        <v>26.86876394941649</v>
       </c>
       <c r="F607" t="n">
         <v>6680100</v>
@@ -12572,16 +12572,16 @@
         <v>45041</v>
       </c>
       <c r="B608" t="n">
-        <v>27.21260452270508</v>
+        <v>27.21260261535645</v>
       </c>
       <c r="C608" t="n">
-        <v>27.45820563979163</v>
+        <v>27.45820371522866</v>
       </c>
       <c r="D608" t="n">
-        <v>26.42667982375542</v>
+        <v>26.42667797149275</v>
       </c>
       <c r="E608" t="n">
-        <v>26.79999457104816</v>
+        <v>26.79999269261962</v>
       </c>
       <c r="F608" t="n">
         <v>5323000</v>
@@ -12612,16 +12612,16 @@
         <v>45043</v>
       </c>
       <c r="B610" t="n">
-        <v>29.90439224243164</v>
+        <v>29.90439414978027</v>
       </c>
       <c r="C610" t="n">
-        <v>30.267880842768</v>
+        <v>30.26788277330051</v>
       </c>
       <c r="D610" t="n">
-        <v>26.73122441728851</v>
+        <v>26.73122612224756</v>
       </c>
       <c r="E610" t="n">
-        <v>26.73122441728851</v>
+        <v>26.73122612224756</v>
       </c>
       <c r="F610" t="n">
         <v>20933600</v>
@@ -12672,16 +12672,16 @@
         <v>45049</v>
       </c>
       <c r="B613" t="n">
-        <v>29.14793968200684</v>
+        <v>29.14794158935547</v>
       </c>
       <c r="C613" t="n">
-        <v>29.61949336143113</v>
+        <v>29.61949529963673</v>
       </c>
       <c r="D613" t="n">
-        <v>28.33254407533193</v>
+        <v>28.33254592932366</v>
       </c>
       <c r="E613" t="n">
-        <v>29.26582903875679</v>
+        <v>29.26583095381972</v>
       </c>
       <c r="F613" t="n">
         <v>9250000</v>
@@ -12692,16 +12692,16 @@
         <v>45050</v>
       </c>
       <c r="B614" t="n">
-        <v>29.2756519317627</v>
+        <v>29.27565383911133</v>
       </c>
       <c r="C614" t="n">
-        <v>29.95351152857367</v>
+        <v>29.95351348008578</v>
       </c>
       <c r="D614" t="n">
-        <v>29.17741298555374</v>
+        <v>29.17741488650197</v>
       </c>
       <c r="E614" t="n">
-        <v>29.47213357175619</v>
+        <v>29.47213549190587</v>
       </c>
       <c r="F614" t="n">
         <v>6670900</v>
@@ -12792,16 +12792,16 @@
         <v>45057</v>
       </c>
       <c r="B619" t="n">
-        <v>31.66289520263672</v>
+        <v>31.66289710998535</v>
       </c>
       <c r="C619" t="n">
-        <v>31.81025737023202</v>
+        <v>31.81025928645763</v>
       </c>
       <c r="D619" t="n">
-        <v>31.10292496189554</v>
+        <v>31.10292683551199</v>
       </c>
       <c r="E619" t="n">
-        <v>31.71201467597662</v>
+        <v>31.71201658628417</v>
       </c>
       <c r="F619" t="n">
         <v>4858000</v>
@@ -12812,16 +12812,16 @@
         <v>45058</v>
       </c>
       <c r="B620" t="n">
-        <v>32.49794006347656</v>
+        <v>32.49794387817383</v>
       </c>
       <c r="C620" t="n">
-        <v>32.64529847816273</v>
+        <v>32.64530231015733</v>
       </c>
       <c r="D620" t="n">
-        <v>31.46641242279611</v>
+        <v>31.46641611640984</v>
       </c>
       <c r="E620" t="n">
-        <v>31.554828970638</v>
+        <v>31.55483267463029</v>
       </c>
       <c r="F620" t="n">
         <v>5317000</v>
@@ -12852,16 +12852,16 @@
         <v>45062</v>
       </c>
       <c r="B622" t="n">
-        <v>29.90439224243164</v>
+        <v>29.90439414978027</v>
       </c>
       <c r="C622" t="n">
-        <v>32.08532946581322</v>
+        <v>32.08533151226543</v>
       </c>
       <c r="D622" t="n">
-        <v>29.70791060120974</v>
+        <v>29.70791249602647</v>
       </c>
       <c r="E622" t="n">
-        <v>31.86919928571158</v>
+        <v>31.86920131837866</v>
       </c>
       <c r="F622" t="n">
         <v>13269700</v>
@@ -12912,16 +12912,16 @@
         <v>45065</v>
       </c>
       <c r="B625" t="n">
-        <v>32.49794006347656</v>
+        <v>32.49794387817383</v>
       </c>
       <c r="C625" t="n">
-        <v>34.87535696477425</v>
+        <v>34.87536105853923</v>
       </c>
       <c r="D625" t="n">
-        <v>31.04398009551434</v>
+        <v>31.0439837395418</v>
       </c>
       <c r="E625" t="n">
-        <v>31.8691980857257</v>
+        <v>31.86920182661951</v>
       </c>
       <c r="F625" t="n">
         <v>19443700</v>
@@ -12972,16 +12972,16 @@
         <v>45070</v>
       </c>
       <c r="B628" t="n">
-        <v>31.48606300354004</v>
+        <v>31.48606109619141</v>
       </c>
       <c r="C628" t="n">
-        <v>31.86920015318507</v>
+        <v>31.86919822262693</v>
       </c>
       <c r="D628" t="n">
-        <v>30.464363313224</v>
+        <v>30.46436146776744</v>
       </c>
       <c r="E628" t="n">
-        <v>31.04398210943912</v>
+        <v>31.04398022887067</v>
       </c>
       <c r="F628" t="n">
         <v>7685200</v>
@@ -13212,16 +13212,16 @@
         <v>45089</v>
       </c>
       <c r="B640" t="n">
-        <v>31.26010894775391</v>
+        <v>31.26011085510254</v>
       </c>
       <c r="C640" t="n">
-        <v>31.86919865058509</v>
+        <v>31.86920059509758</v>
       </c>
       <c r="D640" t="n">
-        <v>30.47418614610471</v>
+        <v>30.47418800549994</v>
       </c>
       <c r="E640" t="n">
-        <v>31.61377514538992</v>
+        <v>31.61377707431765</v>
       </c>
       <c r="F640" t="n">
         <v>7223600</v>
@@ -13252,16 +13252,16 @@
         <v>45091</v>
       </c>
       <c r="B642" t="n">
-        <v>31.1422233581543</v>
+        <v>31.14222145080566</v>
       </c>
       <c r="C642" t="n">
-        <v>31.71201601865814</v>
+        <v>31.71201407641177</v>
       </c>
       <c r="D642" t="n">
-        <v>30.57242882386257</v>
+        <v>30.5724269514118</v>
       </c>
       <c r="E642" t="n">
-        <v>31.33870313362062</v>
+        <v>31.33870121423831</v>
       </c>
       <c r="F642" t="n">
         <v>8288400</v>
@@ -13292,16 +13292,16 @@
         <v>45093</v>
       </c>
       <c r="B644" t="n">
-        <v>31.91832160949707</v>
+        <v>31.9183235168457</v>
       </c>
       <c r="C644" t="n">
-        <v>31.91832160949707</v>
+        <v>31.9183235168457</v>
       </c>
       <c r="D644" t="n">
-        <v>31.19134068168367</v>
+        <v>31.19134254558997</v>
       </c>
       <c r="E644" t="n">
-        <v>31.42711752024974</v>
+        <v>31.4271193982454</v>
       </c>
       <c r="F644" t="n">
         <v>5722800</v>
@@ -13332,16 +13332,16 @@
         <v>45097</v>
       </c>
       <c r="B646" t="n">
-        <v>32.16392135620117</v>
+        <v>32.16392517089844</v>
       </c>
       <c r="C646" t="n">
-        <v>32.29163122856222</v>
+        <v>32.2916350584061</v>
       </c>
       <c r="D646" t="n">
-        <v>31.48605992910253</v>
+        <v>31.48606366340425</v>
       </c>
       <c r="E646" t="n">
-        <v>32.12462428120915</v>
+        <v>32.12462809124572</v>
       </c>
       <c r="F646" t="n">
         <v>4954700</v>
@@ -13352,16 +13352,16 @@
         <v>45098</v>
       </c>
       <c r="B647" t="n">
-        <v>32.06568145751953</v>
+        <v>32.06567764282227</v>
       </c>
       <c r="C647" t="n">
-        <v>32.36040205044127</v>
+        <v>32.36039820068254</v>
       </c>
       <c r="D647" t="n">
-        <v>31.48606266749066</v>
+        <v>31.4860589217478</v>
       </c>
       <c r="E647" t="n">
-        <v>32.12462707513414</v>
+        <v>32.1246232534244</v>
       </c>
       <c r="F647" t="n">
         <v>4670300</v>
@@ -13412,16 +13412,16 @@
         <v>45103</v>
       </c>
       <c r="B650" t="n">
-        <v>30.53313064575195</v>
+        <v>30.53312873840332</v>
       </c>
       <c r="C650" t="n">
-        <v>30.83767550472773</v>
+        <v>30.83767357835474</v>
       </c>
       <c r="D650" t="n">
-        <v>30.30717806889212</v>
+        <v>30.30717617565832</v>
       </c>
       <c r="E650" t="n">
-        <v>30.58225011940398</v>
+        <v>30.58224820898695</v>
       </c>
       <c r="F650" t="n">
         <v>2874500</v>
@@ -13452,16 +13452,16 @@
         <v>45105</v>
       </c>
       <c r="B652" t="n">
-        <v>29.37389183044434</v>
+        <v>29.37389373779297</v>
       </c>
       <c r="C652" t="n">
-        <v>30.06157567506449</v>
+        <v>30.06157762706682</v>
       </c>
       <c r="D652" t="n">
-        <v>29.30512382073987</v>
+        <v>29.30512572362315</v>
       </c>
       <c r="E652" t="n">
-        <v>29.75703082903567</v>
+        <v>29.75703276126285</v>
       </c>
       <c r="F652" t="n">
         <v>4532500</v>
@@ -13532,16 +13532,16 @@
         <v>45111</v>
       </c>
       <c r="B656" t="n">
-        <v>29.80615234375</v>
+        <v>29.80615043640137</v>
       </c>
       <c r="C656" t="n">
-        <v>30.15981855937348</v>
+        <v>30.15981662939312</v>
       </c>
       <c r="D656" t="n">
-        <v>29.57037549126363</v>
+        <v>29.57037359900278</v>
       </c>
       <c r="E656" t="n">
-        <v>29.80615234375</v>
+        <v>29.80615043640137</v>
       </c>
       <c r="F656" t="n">
         <v>2514900</v>
@@ -13552,16 +13552,16 @@
         <v>45112</v>
       </c>
       <c r="B657" t="n">
-        <v>30.40542030334473</v>
+        <v>30.40541839599609</v>
       </c>
       <c r="C657" t="n">
-        <v>30.70996517647691</v>
+        <v>30.70996325002402</v>
       </c>
       <c r="D657" t="n">
-        <v>29.34442350856649</v>
+        <v>29.34442166777476</v>
       </c>
       <c r="E657" t="n">
-        <v>29.60967130192012</v>
+        <v>29.60966944448926</v>
       </c>
       <c r="F657" t="n">
         <v>5394800</v>
@@ -13612,16 +13612,16 @@
         <v>45117</v>
       </c>
       <c r="B660" t="n">
-        <v>31.07345390319824</v>
+        <v>31.07345199584961</v>
       </c>
       <c r="C660" t="n">
-        <v>31.93796904965617</v>
+        <v>31.93796708924193</v>
       </c>
       <c r="D660" t="n">
-        <v>30.84750131505205</v>
+        <v>30.84749942157282</v>
       </c>
       <c r="E660" t="n">
-        <v>31.56465803319331</v>
+        <v>31.56465609569361</v>
       </c>
       <c r="F660" t="n">
         <v>7339200</v>
@@ -13652,16 +13652,16 @@
         <v>45119</v>
       </c>
       <c r="B662" t="n">
-        <v>31.07345390319824</v>
+        <v>31.07345199584961</v>
       </c>
       <c r="C662" t="n">
-        <v>32.08533122554864</v>
+        <v>32.08532925608902</v>
       </c>
       <c r="D662" t="n">
-        <v>31.04398296705007</v>
+        <v>31.04398106151042</v>
       </c>
       <c r="E662" t="n">
-        <v>31.77096208138212</v>
+        <v>31.77096013121909</v>
       </c>
       <c r="F662" t="n">
         <v>4503800</v>
@@ -13732,16 +13732,16 @@
         <v>45125</v>
       </c>
       <c r="B666" t="n">
-        <v>32.91054916381836</v>
+        <v>32.91055297851562</v>
       </c>
       <c r="C666" t="n">
-        <v>33.03826279198419</v>
+        <v>33.03826662148488</v>
       </c>
       <c r="D666" t="n">
-        <v>32.0362098005708</v>
+        <v>32.03621351392245</v>
       </c>
       <c r="E666" t="n">
-        <v>32.18356821992315</v>
+        <v>32.18357195035527</v>
       </c>
       <c r="F666" t="n">
         <v>4775600</v>
@@ -13752,16 +13752,16 @@
         <v>45126</v>
       </c>
       <c r="B667" t="n">
-        <v>33.64735412597656</v>
+        <v>33.6473503112793</v>
       </c>
       <c r="C667" t="n">
-        <v>34.04031742501827</v>
+        <v>34.04031356576963</v>
       </c>
       <c r="D667" t="n">
-        <v>33.04808678134705</v>
+        <v>33.04808303459044</v>
       </c>
       <c r="E667" t="n">
-        <v>33.04808678134705</v>
+        <v>33.04808303459044</v>
       </c>
       <c r="F667" t="n">
         <v>7484200</v>
@@ -13772,16 +13772,16 @@
         <v>45127</v>
       </c>
       <c r="B668" t="n">
-        <v>33.92242431640625</v>
+        <v>33.92242813110352</v>
       </c>
       <c r="C668" t="n">
-        <v>34.11890595509385</v>
+        <v>34.11890979188617</v>
       </c>
       <c r="D668" t="n">
-        <v>33.64735227078894</v>
+        <v>33.64735605455338</v>
       </c>
       <c r="E668" t="n">
-        <v>33.91260192088087</v>
+        <v>33.91260573447357</v>
       </c>
       <c r="F668" t="n">
         <v>3587900</v>
@@ -13952,16 +13952,16 @@
         <v>45140</v>
       </c>
       <c r="B677" t="n">
-        <v>34.44309997558594</v>
+        <v>34.4431037902832</v>
       </c>
       <c r="C677" t="n">
-        <v>34.58063599342123</v>
+        <v>34.5806398233511</v>
       </c>
       <c r="D677" t="n">
-        <v>33.71611906300245</v>
+        <v>33.71612279718397</v>
       </c>
       <c r="E677" t="n">
-        <v>34.38415436183849</v>
+        <v>34.38415817000732</v>
       </c>
       <c r="F677" t="n">
         <v>3408800</v>
@@ -14012,16 +14012,16 @@
         <v>45145</v>
       </c>
       <c r="B680" t="n">
-        <v>35.68093109130859</v>
+        <v>35.68092727661133</v>
       </c>
       <c r="C680" t="n">
-        <v>36.15248480095344</v>
+        <v>36.15248093584172</v>
       </c>
       <c r="D680" t="n">
-        <v>35.09148989114647</v>
+        <v>35.09148613946717</v>
       </c>
       <c r="E680" t="n">
-        <v>36.05424585011833</v>
+        <v>36.05424199550948</v>
       </c>
       <c r="F680" t="n">
         <v>3820600</v>
@@ -14032,16 +14032,16 @@
         <v>45146</v>
       </c>
       <c r="B681" t="n">
-        <v>36.34896850585938</v>
+        <v>36.34896469116211</v>
       </c>
       <c r="C681" t="n">
-        <v>36.51597548123902</v>
+        <v>36.51597164901496</v>
       </c>
       <c r="D681" t="n">
-        <v>34.30556523426109</v>
+        <v>34.30556163401185</v>
       </c>
       <c r="E681" t="n">
-        <v>34.76729657396523</v>
+        <v>34.76729292525891</v>
       </c>
       <c r="F681" t="n">
         <v>5274900</v>
@@ -14172,16 +14172,16 @@
         <v>45155</v>
       </c>
       <c r="B688" t="n">
-        <v>31.26993560791016</v>
+        <v>31.26993370056152</v>
       </c>
       <c r="C688" t="n">
-        <v>31.74149119874277</v>
+        <v>31.74148926263102</v>
       </c>
       <c r="D688" t="n">
-        <v>30.96539073320894</v>
+        <v>30.9653888444364</v>
       </c>
       <c r="E688" t="n">
-        <v>31.4664153864515</v>
+        <v>31.46641346711834</v>
       </c>
       <c r="F688" t="n">
         <v>4529600</v>
@@ -14252,16 +14252,16 @@
         <v>45161</v>
       </c>
       <c r="B692" t="n">
-        <v>31.05380439758301</v>
+        <v>31.05380630493164</v>
       </c>
       <c r="C692" t="n">
-        <v>31.24045988874735</v>
+        <v>31.2404618075605</v>
       </c>
       <c r="D692" t="n">
-        <v>30.68048966767887</v>
+        <v>30.68049155209822</v>
       </c>
       <c r="E692" t="n">
-        <v>31.09309960011686</v>
+        <v>31.09310150987904</v>
       </c>
       <c r="F692" t="n">
         <v>4847400</v>
@@ -14272,16 +14272,16 @@
         <v>45162</v>
       </c>
       <c r="B693" t="n">
-        <v>30.91626739501953</v>
+        <v>30.91626930236816</v>
       </c>
       <c r="C693" t="n">
-        <v>31.30923067440671</v>
+        <v>31.30923260599883</v>
       </c>
       <c r="D693" t="n">
-        <v>30.56260306687397</v>
+        <v>30.56260495240363</v>
       </c>
       <c r="E693" t="n">
-        <v>31.05380529232016</v>
+        <v>31.05380720815405</v>
       </c>
       <c r="F693" t="n">
         <v>3471700</v>
@@ -14332,16 +14332,16 @@
         <v>45167</v>
       </c>
       <c r="B696" t="n">
-        <v>31.29940605163574</v>
+        <v>31.29940795898438</v>
       </c>
       <c r="C696" t="n">
-        <v>31.55482955705047</v>
+        <v>31.55483147996431</v>
       </c>
       <c r="D696" t="n">
-        <v>30.63137073276579</v>
+        <v>30.63137259940515</v>
       </c>
       <c r="E696" t="n">
-        <v>31.06362921093831</v>
+        <v>31.06363110391898</v>
       </c>
       <c r="F696" t="n">
         <v>3743200</v>
@@ -14352,16 +14352,16 @@
         <v>45168</v>
       </c>
       <c r="B697" t="n">
-        <v>31.63342475891113</v>
+        <v>31.6334228515625</v>
       </c>
       <c r="C697" t="n">
-        <v>31.70219277216898</v>
+        <v>31.70219086067396</v>
       </c>
       <c r="D697" t="n">
-        <v>30.96538941791287</v>
+        <v>30.96538755084366</v>
       </c>
       <c r="E697" t="n">
-        <v>31.49588873239543</v>
+        <v>31.49588683333958</v>
       </c>
       <c r="F697" t="n">
         <v>3276100</v>
@@ -14412,16 +14412,16 @@
         <v>45173</v>
       </c>
       <c r="B700" t="n">
-        <v>32.27198791503906</v>
+        <v>32.2719841003418</v>
       </c>
       <c r="C700" t="n">
-        <v>32.55688613348561</v>
+        <v>32.55688228511206</v>
       </c>
       <c r="D700" t="n">
-        <v>32.06568385929886</v>
+        <v>32.06568006898767</v>
       </c>
       <c r="E700" t="n">
-        <v>32.22286843713558</v>
+        <v>32.22286462824446</v>
       </c>
       <c r="F700" t="n">
         <v>2652900</v>
@@ -14432,16 +14432,16 @@
         <v>45174</v>
       </c>
       <c r="B701" t="n">
-        <v>32.63547897338867</v>
+        <v>32.63547515869141</v>
       </c>
       <c r="C701" t="n">
-        <v>32.93019957643972</v>
+        <v>32.93019572729314</v>
       </c>
       <c r="D701" t="n">
-        <v>32.07550870331895</v>
+        <v>32.07550495407551</v>
       </c>
       <c r="E701" t="n">
-        <v>32.27198660696912</v>
+        <v>32.27198283475976</v>
       </c>
       <c r="F701" t="n">
         <v>6036900</v>
@@ -14452,16 +14452,16 @@
         <v>45175</v>
       </c>
       <c r="B702" t="n">
-        <v>32.00673675537109</v>
+        <v>32.00674057006836</v>
       </c>
       <c r="C702" t="n">
-        <v>32.71406536628031</v>
+        <v>32.71406926527997</v>
       </c>
       <c r="D702" t="n">
-        <v>31.928142605506</v>
+        <v>31.92814641083608</v>
       </c>
       <c r="E702" t="n">
-        <v>32.65512350145682</v>
+        <v>32.65512739343153</v>
       </c>
       <c r="F702" t="n">
         <v>4505300</v>
@@ -14512,16 +14512,16 @@
         <v>45181</v>
       </c>
       <c r="B705" t="n">
-        <v>32.33092880249023</v>
+        <v>32.3309326171875</v>
       </c>
       <c r="C705" t="n">
-        <v>32.64529791212711</v>
+        <v>32.6453017639165</v>
       </c>
       <c r="D705" t="n">
-        <v>31.76113619661418</v>
+        <v>31.76113994408213</v>
       </c>
       <c r="E705" t="n">
-        <v>31.97726261725491</v>
+        <v>31.97726639022342</v>
       </c>
       <c r="F705" t="n">
         <v>3620500</v>
@@ -14532,16 +14532,16 @@
         <v>45182</v>
       </c>
       <c r="B706" t="n">
-        <v>31.63342475891113</v>
+        <v>31.6334228515625</v>
       </c>
       <c r="C706" t="n">
-        <v>32.1148008517161</v>
+        <v>32.11479891534272</v>
       </c>
       <c r="D706" t="n">
-        <v>31.44676551071783</v>
+        <v>31.44676361462388</v>
       </c>
       <c r="E706" t="n">
-        <v>31.60395007638945</v>
+        <v>31.60394817081799</v>
       </c>
       <c r="F706" t="n">
         <v>7302700</v>
@@ -14552,16 +14552,16 @@
         <v>45183</v>
       </c>
       <c r="B707" t="n">
-        <v>32.31128311157227</v>
+        <v>32.311279296875</v>
       </c>
       <c r="C707" t="n">
-        <v>32.31128311157227</v>
+        <v>32.311279296875</v>
       </c>
       <c r="D707" t="n">
-        <v>31.74149045549294</v>
+        <v>31.74148670806588</v>
       </c>
       <c r="E707" t="n">
-        <v>31.83972940556933</v>
+        <v>31.83972564654409</v>
       </c>
       <c r="F707" t="n">
         <v>4362300</v>
@@ -14592,16 +14592,16 @@
         <v>45187</v>
       </c>
       <c r="B709" t="n">
-        <v>31.98709106445312</v>
+        <v>31.98709297180176</v>
       </c>
       <c r="C709" t="n">
-        <v>32.7140682775227</v>
+        <v>32.71407022822005</v>
       </c>
       <c r="D709" t="n">
-        <v>31.75131234145109</v>
+        <v>31.75131423474054</v>
       </c>
       <c r="E709" t="n">
-        <v>32.5568837113799</v>
+        <v>32.55688565270453</v>
       </c>
       <c r="F709" t="n">
         <v>5099000</v>
@@ -14692,16 +14692,16 @@
         <v>45194</v>
       </c>
       <c r="B714" t="n">
-        <v>30.95556449890137</v>
+        <v>30.95556640625</v>
       </c>
       <c r="C714" t="n">
-        <v>31.20116561183414</v>
+        <v>31.20116753431566</v>
       </c>
       <c r="D714" t="n">
-        <v>29.99280858591396</v>
+        <v>29.99281043394172</v>
       </c>
       <c r="E714" t="n">
-        <v>30.45453800366397</v>
+        <v>30.45453988014151</v>
       </c>
       <c r="F714" t="n">
         <v>6350700</v>
@@ -14712,16 +14712,16 @@
         <v>45195</v>
       </c>
       <c r="B715" t="n">
-        <v>30.32682609558105</v>
+        <v>30.32682800292969</v>
       </c>
       <c r="C715" t="n">
-        <v>30.83767498381136</v>
+        <v>30.83767692328888</v>
       </c>
       <c r="D715" t="n">
-        <v>30.19911246818264</v>
+        <v>30.19911436749897</v>
       </c>
       <c r="E715" t="n">
-        <v>30.75908270302303</v>
+        <v>30.75908463755763</v>
       </c>
       <c r="F715" t="n">
         <v>3433500</v>
@@ -14732,16 +14732,16 @@
         <v>45196</v>
       </c>
       <c r="B716" t="n">
-        <v>30.86714935302734</v>
+        <v>30.86714744567871</v>
       </c>
       <c r="C716" t="n">
-        <v>31.0734533978611</v>
+        <v>31.07345147776449</v>
       </c>
       <c r="D716" t="n">
-        <v>30.42506658011519</v>
+        <v>30.42506470008381</v>
       </c>
       <c r="E716" t="n">
-        <v>30.65102103837466</v>
+        <v>30.65101914438107</v>
       </c>
       <c r="F716" t="n">
         <v>4307600</v>
@@ -14752,16 +14752,16 @@
         <v>45197</v>
       </c>
       <c r="B717" t="n">
-        <v>30.58224868774414</v>
+        <v>30.58225059509277</v>
       </c>
       <c r="C717" t="n">
-        <v>31.21098878902595</v>
+        <v>31.21099073558775</v>
       </c>
       <c r="D717" t="n">
-        <v>30.41523986184255</v>
+        <v>30.41524175877521</v>
       </c>
       <c r="E717" t="n">
-        <v>30.82784979208249</v>
+        <v>30.82785171474873</v>
       </c>
       <c r="F717" t="n">
         <v>4298000</v>
@@ -14772,16 +14772,16 @@
         <v>45198</v>
       </c>
       <c r="B718" t="n">
-        <v>31.02433395385742</v>
+        <v>31.02433204650879</v>
       </c>
       <c r="C718" t="n">
-        <v>31.60395088345571</v>
+        <v>31.60394894047274</v>
       </c>
       <c r="D718" t="n">
-        <v>30.47418795995777</v>
+        <v>30.47418608643163</v>
       </c>
       <c r="E718" t="n">
-        <v>30.86714938417181</v>
+        <v>30.86714748648674</v>
       </c>
       <c r="F718" t="n">
         <v>5846000</v>
@@ -14852,16 +14852,16 @@
         <v>45204</v>
       </c>
       <c r="B722" t="n">
-        <v>28.03782272338867</v>
+        <v>28.0378246307373</v>
       </c>
       <c r="C722" t="n">
-        <v>28.78444842505877</v>
+        <v>28.78445038319864</v>
       </c>
       <c r="D722" t="n">
-        <v>27.72345173862667</v>
+        <v>27.72345362458937</v>
       </c>
       <c r="E722" t="n">
-        <v>28.62726386957162</v>
+        <v>28.62726581701858</v>
       </c>
       <c r="F722" t="n">
         <v>8409300</v>
@@ -14912,16 +14912,16 @@
         <v>45209</v>
       </c>
       <c r="B725" t="n">
-        <v>30.27770614624023</v>
+        <v>30.2777042388916</v>
       </c>
       <c r="C725" t="n">
-        <v>30.40541977953243</v>
+        <v>30.40541786413846</v>
       </c>
       <c r="D725" t="n">
-        <v>29.43283768343539</v>
+        <v>29.43283582930937</v>
       </c>
       <c r="E725" t="n">
-        <v>29.75703296465965</v>
+        <v>29.7570310901109</v>
       </c>
       <c r="F725" t="n">
         <v>7018100</v>
@@ -14972,16 +14972,16 @@
         <v>45215</v>
       </c>
       <c r="B728" t="n">
-        <v>31.67271995544434</v>
+        <v>31.67272186279297</v>
       </c>
       <c r="C728" t="n">
-        <v>32.01656000130495</v>
+        <v>32.01656192935982</v>
       </c>
       <c r="D728" t="n">
-        <v>31.32887616200829</v>
+        <v>31.32887804865046</v>
       </c>
       <c r="E728" t="n">
-        <v>31.91832105893775</v>
+        <v>31.91832298107662</v>
       </c>
       <c r="F728" t="n">
         <v>3741500</v>
@@ -15012,16 +15012,16 @@
         <v>45217</v>
       </c>
       <c r="B730" t="n">
-        <v>32.06568145751953</v>
+        <v>32.06567764282227</v>
       </c>
       <c r="C730" t="n">
-        <v>33.06773447151397</v>
+        <v>33.06773053760736</v>
       </c>
       <c r="D730" t="n">
-        <v>31.63342483773936</v>
+        <v>31.63342107446555</v>
       </c>
       <c r="E730" t="n">
-        <v>32.52741275989484</v>
+        <v>32.52740889026767</v>
       </c>
       <c r="F730" t="n">
         <v>7439800</v>
@@ -15132,16 +15132,16 @@
         <v>45225</v>
       </c>
       <c r="B736" t="n">
-        <v>31.98709106445312</v>
+        <v>31.98709297180176</v>
       </c>
       <c r="C736" t="n">
-        <v>32.12462709138111</v>
+        <v>32.12462900693085</v>
       </c>
       <c r="D736" t="n">
-        <v>31.19134209034388</v>
+        <v>31.19134395024304</v>
       </c>
       <c r="E736" t="n">
-        <v>31.57447923609348</v>
+        <v>31.57448111883861</v>
       </c>
       <c r="F736" t="n">
         <v>2923500</v>
@@ -15152,16 +15152,16 @@
         <v>45226</v>
       </c>
       <c r="B737" t="n">
-        <v>31.52535820007324</v>
+        <v>31.52536010742188</v>
       </c>
       <c r="C737" t="n">
-        <v>32.556882098507</v>
+        <v>32.55688406826494</v>
       </c>
       <c r="D737" t="n">
-        <v>31.24046001693592</v>
+        <v>31.24046190704763</v>
       </c>
       <c r="E737" t="n">
-        <v>32.32110713476096</v>
+        <v>32.32110909025403</v>
       </c>
       <c r="F737" t="n">
         <v>3378100</v>
@@ -15172,16 +15172,16 @@
         <v>45229</v>
       </c>
       <c r="B738" t="n">
-        <v>31.07345390319824</v>
+        <v>31.07345199584961</v>
       </c>
       <c r="C738" t="n">
-        <v>32.11480216169681</v>
+        <v>32.11480019042821</v>
       </c>
       <c r="D738" t="n">
-        <v>30.98503922096583</v>
+        <v>30.98503731904426</v>
       </c>
       <c r="E738" t="n">
-        <v>31.54500949323592</v>
+        <v>31.5450075569423</v>
       </c>
       <c r="F738" t="n">
         <v>3227500</v>
@@ -15192,16 +15192,16 @@
         <v>45230</v>
       </c>
       <c r="B739" t="n">
-        <v>31.86919784545898</v>
+        <v>31.86919975280762</v>
       </c>
       <c r="C739" t="n">
-        <v>32.10497655378492</v>
+        <v>32.10497847524474</v>
       </c>
       <c r="D739" t="n">
-        <v>31.20116441782789</v>
+        <v>31.2011662851952</v>
       </c>
       <c r="E739" t="n">
-        <v>31.20116441782789</v>
+        <v>31.2011662851952</v>
       </c>
       <c r="F739" t="n">
         <v>3372100</v>
@@ -15212,16 +15212,16 @@
         <v>45231</v>
       </c>
       <c r="B740" t="n">
-        <v>32.06568145751953</v>
+        <v>32.06567764282227</v>
       </c>
       <c r="C740" t="n">
-        <v>32.74354294357276</v>
+        <v>32.74353904823363</v>
       </c>
       <c r="D740" t="n">
-        <v>31.94779396986597</v>
+        <v>31.9477901691932</v>
       </c>
       <c r="E740" t="n">
-        <v>32.0755076009098</v>
+        <v>32.07550378504357</v>
       </c>
       <c r="F740" t="n">
         <v>4282500</v>
@@ -15232,16 +15232,16 @@
         <v>45233</v>
       </c>
       <c r="B741" t="n">
-        <v>32.69441604614258</v>
+        <v>32.69441986083984</v>
       </c>
       <c r="C741" t="n">
-        <v>32.94984327951414</v>
+        <v>32.94984712401398</v>
       </c>
       <c r="D741" t="n">
-        <v>32.4684634920525</v>
+        <v>32.46846728038622</v>
       </c>
       <c r="E741" t="n">
-        <v>32.7337131201344</v>
+        <v>32.73371693941674</v>
       </c>
       <c r="F741" t="n">
         <v>3190300</v>
@@ -15272,16 +15272,16 @@
         <v>45237</v>
       </c>
       <c r="B743" t="n">
-        <v>32.48811340332031</v>
+        <v>32.48811721801758</v>
       </c>
       <c r="C743" t="n">
-        <v>32.63547556323554</v>
+        <v>32.63547939523581</v>
       </c>
       <c r="D743" t="n">
-        <v>31.81025571237618</v>
+        <v>31.81025944748058</v>
       </c>
       <c r="E743" t="n">
-        <v>31.87902372098318</v>
+        <v>31.8790274641622</v>
       </c>
       <c r="F743" t="n">
         <v>3324000</v>
@@ -15312,16 +15312,16 @@
         <v>45239</v>
       </c>
       <c r="B745" t="n">
-        <v>30.81802940368652</v>
+        <v>30.81802749633789</v>
       </c>
       <c r="C745" t="n">
-        <v>33.77506711733456</v>
+        <v>33.77506502697286</v>
       </c>
       <c r="D745" t="n">
-        <v>30.67066723245724</v>
+        <v>30.67066533422895</v>
       </c>
       <c r="E745" t="n">
-        <v>33.41157476098916</v>
+        <v>33.41157269312426</v>
       </c>
       <c r="F745" t="n">
         <v>15431300</v>
@@ -15332,16 +15332,16 @@
         <v>45240</v>
       </c>
       <c r="B746" t="n">
-        <v>31.25028419494629</v>
+        <v>31.25028610229492</v>
       </c>
       <c r="C746" t="n">
-        <v>32.06567979171039</v>
+        <v>32.06568174882637</v>
       </c>
       <c r="D746" t="n">
-        <v>31.04398016537612</v>
+        <v>31.04398206013306</v>
       </c>
       <c r="E746" t="n">
-        <v>31.05380443446818</v>
+        <v>31.05380632982475</v>
       </c>
       <c r="F746" t="n">
         <v>4738300</v>
@@ -15352,16 +15352,16 @@
         <v>45243</v>
       </c>
       <c r="B747" t="n">
-        <v>30.94574165344238</v>
+        <v>30.94573974609375</v>
       </c>
       <c r="C747" t="n">
-        <v>31.41729536226194</v>
+        <v>31.41729342584897</v>
       </c>
       <c r="D747" t="n">
-        <v>30.67066771973704</v>
+        <v>30.67066582934266</v>
       </c>
       <c r="E747" t="n">
-        <v>31.21099131732383</v>
+        <v>31.21098939362647</v>
       </c>
       <c r="F747" t="n">
         <v>3172300</v>
@@ -15392,16 +15392,16 @@
         <v>45246</v>
       </c>
       <c r="B749" t="n">
-        <v>31.13239669799805</v>
+        <v>31.13239860534668</v>
       </c>
       <c r="C749" t="n">
-        <v>32.13444778565191</v>
+        <v>32.13444975439192</v>
       </c>
       <c r="D749" t="n">
-        <v>30.68048968892551</v>
+        <v>30.68049156858774</v>
       </c>
       <c r="E749" t="n">
-        <v>31.78078159366364</v>
+        <v>31.78078354073604</v>
       </c>
       <c r="F749" t="n">
         <v>5148500</v>
@@ -15492,16 +15492,16 @@
         <v>45253</v>
       </c>
       <c r="B754" t="n">
-        <v>31.81025886535645</v>
+        <v>31.81025505065918</v>
       </c>
       <c r="C754" t="n">
-        <v>32.00674051552654</v>
+        <v>32.00673667726713</v>
       </c>
       <c r="D754" t="n">
-        <v>31.58430627931235</v>
+        <v>31.5843024917114</v>
       </c>
       <c r="E754" t="n">
-        <v>31.82990740513103</v>
+        <v>31.82990358807751</v>
       </c>
       <c r="F754" t="n">
         <v>2086300</v>
@@ -15552,16 +15552,16 @@
         <v>45258</v>
       </c>
       <c r="B757" t="n">
-        <v>29.80615234375</v>
+        <v>29.80615043640137</v>
       </c>
       <c r="C757" t="n">
-        <v>30.21876230404811</v>
+        <v>30.21876037029583</v>
       </c>
       <c r="D757" t="n">
-        <v>29.63914350568201</v>
+        <v>29.63914160902057</v>
       </c>
       <c r="E757" t="n">
-        <v>30.17946522507312</v>
+        <v>30.17946329383553</v>
       </c>
       <c r="F757" t="n">
         <v>5777500</v>
@@ -15592,16 +15592,16 @@
         <v>45260</v>
       </c>
       <c r="B759" t="n">
-        <v>29.45248413085938</v>
+        <v>29.45248603820801</v>
       </c>
       <c r="C759" t="n">
-        <v>29.83562312973222</v>
+        <v>29.83562506189301</v>
       </c>
       <c r="D759" t="n">
-        <v>29.17741209183939</v>
+        <v>29.1774139813743</v>
       </c>
       <c r="E759" t="n">
-        <v>29.66861430298963</v>
+        <v>29.66861622433489</v>
       </c>
       <c r="F759" t="n">
         <v>4483800</v>
@@ -15732,16 +15732,16 @@
         <v>45271</v>
       </c>
       <c r="B766" t="n">
-        <v>26.91788291931152</v>
+        <v>26.91788101196289</v>
       </c>
       <c r="C766" t="n">
-        <v>27.08489175922624</v>
+        <v>27.08488984004369</v>
       </c>
       <c r="D766" t="n">
-        <v>26.48562441474616</v>
+        <v>26.48562253802652</v>
       </c>
       <c r="E766" t="n">
-        <v>26.96700426857343</v>
+        <v>26.96700235774415</v>
       </c>
       <c r="F766" t="n">
         <v>6627000</v>
@@ -15792,16 +15792,16 @@
         <v>45274</v>
       </c>
       <c r="B769" t="n">
-        <v>27.00629806518555</v>
+        <v>27.00629997253418</v>
       </c>
       <c r="C769" t="n">
-        <v>27.2027797044063</v>
+        <v>27.20278162563166</v>
       </c>
       <c r="D769" t="n">
-        <v>26.49544730224182</v>
+        <v>26.49544917351107</v>
       </c>
       <c r="E769" t="n">
-        <v>26.82946496464443</v>
+        <v>26.82946685950403</v>
       </c>
       <c r="F769" t="n">
         <v>14011300</v>
@@ -15812,16 +15812,16 @@
         <v>45275</v>
       </c>
       <c r="B770" t="n">
-        <v>25.88635635375977</v>
+        <v>25.8863582611084</v>
       </c>
       <c r="C770" t="n">
-        <v>27.21260267051552</v>
+        <v>27.21260467558413</v>
       </c>
       <c r="D770" t="n">
-        <v>25.88635635375977</v>
+        <v>25.8863582611084</v>
       </c>
       <c r="E770" t="n">
-        <v>27.1634813261689</v>
+        <v>27.16348332761816</v>
       </c>
       <c r="F770" t="n">
         <v>11924000</v>
@@ -15832,16 +15832,16 @@
         <v>45278</v>
       </c>
       <c r="B771" t="n">
-        <v>26.21055030822754</v>
+        <v>26.21055221557617</v>
       </c>
       <c r="C771" t="n">
-        <v>26.76069626050536</v>
+        <v>26.76069820788825</v>
       </c>
       <c r="D771" t="n">
-        <v>25.94530066428034</v>
+        <v>25.94530255232668</v>
       </c>
       <c r="E771" t="n">
-        <v>26.12213376024514</v>
+        <v>26.12213566115967</v>
       </c>
       <c r="F771" t="n">
         <v>4958200</v>
@@ -15852,16 +15852,16 @@
         <v>45279</v>
       </c>
       <c r="B772" t="n">
-        <v>26.32843971252441</v>
+        <v>26.32843780517578</v>
       </c>
       <c r="C772" t="n">
-        <v>26.52492136101001</v>
+        <v>26.52491943942738</v>
       </c>
       <c r="D772" t="n">
-        <v>26.13195993782669</v>
+        <v>26.13195804471192</v>
       </c>
       <c r="E772" t="n">
-        <v>26.30879304670615</v>
+        <v>26.30879114078081</v>
       </c>
       <c r="F772" t="n">
         <v>3900900</v>
@@ -15872,16 +15872,16 @@
         <v>45280</v>
       </c>
       <c r="B773" t="n">
-        <v>25.85688591003418</v>
+        <v>25.85688400268555</v>
       </c>
       <c r="C773" t="n">
-        <v>26.54456980342805</v>
+        <v>26.54456784535201</v>
       </c>
       <c r="D773" t="n">
-        <v>25.68987707156926</v>
+        <v>25.68987517654013</v>
       </c>
       <c r="E773" t="n">
-        <v>26.54456980342805</v>
+        <v>26.54456784535201</v>
       </c>
       <c r="F773" t="n">
         <v>6168300</v>
@@ -15912,16 +15912,16 @@
         <v>45282</v>
       </c>
       <c r="B775" t="n">
-        <v>25.95512580871582</v>
+        <v>25.95512771606445</v>
       </c>
       <c r="C775" t="n">
-        <v>26.2203754616087</v>
+        <v>26.22037738844958</v>
       </c>
       <c r="D775" t="n">
-        <v>25.79794124562103</v>
+        <v>25.79794314141873</v>
       </c>
       <c r="E775" t="n">
-        <v>26.03371809026321</v>
+        <v>26.03372000338731</v>
       </c>
       <c r="F775" t="n">
         <v>3644200</v>
@@ -16012,16 +16012,16 @@
         <v>45294</v>
       </c>
       <c r="B780" t="n">
-        <v>25.88635635375977</v>
+        <v>25.8863582611084</v>
       </c>
       <c r="C780" t="n">
-        <v>26.28914200846361</v>
+        <v>26.28914394549015</v>
       </c>
       <c r="D780" t="n">
-        <v>25.35585707754239</v>
+        <v>25.35585894580298</v>
       </c>
       <c r="E780" t="n">
-        <v>25.64075525338972</v>
+        <v>25.64075714264207</v>
       </c>
       <c r="F780" t="n">
         <v>5734800</v>
@@ -16052,16 +16052,16 @@
         <v>45296</v>
       </c>
       <c r="B782" t="n">
-        <v>25.68987464904785</v>
+        <v>25.68987655639648</v>
       </c>
       <c r="C782" t="n">
-        <v>25.97477282406455</v>
+        <v>25.97477475256549</v>
       </c>
       <c r="D782" t="n">
-        <v>25.21832098742127</v>
+        <v>25.21832285975933</v>
       </c>
       <c r="E782" t="n">
-        <v>25.36568127245611</v>
+        <v>25.36568315573496</v>
       </c>
       <c r="F782" t="n">
         <v>3417300</v>
@@ -16092,16 +16092,16 @@
         <v>45300</v>
       </c>
       <c r="B784" t="n">
-        <v>28.01817512512207</v>
+        <v>28.0181770324707</v>
       </c>
       <c r="C784" t="n">
-        <v>28.24412769698892</v>
+        <v>28.24412961971936</v>
       </c>
       <c r="D784" t="n">
-        <v>26.79999384234995</v>
+        <v>26.7999956667704</v>
       </c>
       <c r="E784" t="n">
-        <v>27.01612214494592</v>
+        <v>27.01612398407939</v>
       </c>
       <c r="F784" t="n">
         <v>10290300</v>
@@ -16152,16 +16152,16 @@
         <v>45303</v>
       </c>
       <c r="B787" t="n">
-        <v>28.20483207702637</v>
+        <v>28.20483016967773</v>
       </c>
       <c r="C787" t="n">
-        <v>28.86304316187749</v>
+        <v>28.86304121001741</v>
       </c>
       <c r="D787" t="n">
-        <v>27.82169492460737</v>
+        <v>27.82169304316834</v>
       </c>
       <c r="E787" t="n">
-        <v>28.63709057833746</v>
+        <v>28.63708864175739</v>
       </c>
       <c r="F787" t="n">
         <v>5067700</v>
@@ -16172,16 +16172,16 @@
         <v>45306</v>
       </c>
       <c r="B788" t="n">
-        <v>28.52902793884277</v>
+        <v>28.52902603149414</v>
       </c>
       <c r="C788" t="n">
-        <v>28.68621251092004</v>
+        <v>28.68621059306261</v>
       </c>
       <c r="D788" t="n">
-        <v>27.9002877767458</v>
+        <v>27.90028591143248</v>
       </c>
       <c r="E788" t="n">
-        <v>28.06729661880138</v>
+        <v>28.06729474232245</v>
       </c>
       <c r="F788" t="n">
         <v>3859400</v>
@@ -16252,16 +16252,16 @@
         <v>45310</v>
       </c>
       <c r="B792" t="n">
-        <v>29.03005027770996</v>
+        <v>29.03005218505859</v>
       </c>
       <c r="C792" t="n">
-        <v>29.197059106456</v>
+        <v>29.19706102477754</v>
       </c>
       <c r="D792" t="n">
-        <v>28.0574701128199</v>
+        <v>28.05747195626752</v>
       </c>
       <c r="E792" t="n">
-        <v>28.73532969699943</v>
+        <v>28.73533158498416</v>
       </c>
       <c r="F792" t="n">
         <v>7851200</v>
@@ -16312,16 +16312,16 @@
         <v>45315</v>
       </c>
       <c r="B795" t="n">
-        <v>27.86099243164062</v>
+        <v>27.86099052429199</v>
       </c>
       <c r="C795" t="n">
-        <v>28.52902779653059</v>
+        <v>28.52902584344861</v>
       </c>
       <c r="D795" t="n">
-        <v>27.63503797084227</v>
+        <v>27.63503607896236</v>
       </c>
       <c r="E795" t="n">
-        <v>28.04764793893384</v>
+        <v>28.04764601880687</v>
       </c>
       <c r="F795" t="n">
         <v>4070600</v>
@@ -16352,16 +16352,16 @@
         <v>45317</v>
       </c>
       <c r="B797" t="n">
-        <v>28.24412727355957</v>
+        <v>28.2441291809082</v>
       </c>
       <c r="C797" t="n">
-        <v>28.24412727355957</v>
+        <v>28.2441291809082</v>
       </c>
       <c r="D797" t="n">
-        <v>27.50732395337975</v>
+        <v>27.50732581097147</v>
       </c>
       <c r="E797" t="n">
-        <v>27.65468424265817</v>
+        <v>27.65468611020124</v>
       </c>
       <c r="F797" t="n">
         <v>2761100</v>
@@ -16392,16 +16392,16 @@
         <v>45321</v>
       </c>
       <c r="B799" t="n">
-        <v>27.2420768737793</v>
+        <v>27.24207496643066</v>
       </c>
       <c r="C799" t="n">
-        <v>27.54662362392648</v>
+        <v>27.54662169525507</v>
       </c>
       <c r="D799" t="n">
-        <v>26.97682720382707</v>
+        <v>26.97682531504984</v>
       </c>
       <c r="E799" t="n">
-        <v>27.369790510625</v>
+        <v>27.36978859433452</v>
       </c>
       <c r="F799" t="n">
         <v>2184900</v>
@@ -16432,16 +16432,16 @@
         <v>45323</v>
       </c>
       <c r="B801" t="n">
-        <v>26.24002265930176</v>
+        <v>26.24002075195312</v>
       </c>
       <c r="C801" t="n">
-        <v>27.40908451061442</v>
+        <v>27.4090825182884</v>
       </c>
       <c r="D801" t="n">
-        <v>26.10248663224892</v>
+        <v>26.10248473489757</v>
       </c>
       <c r="E801" t="n">
-        <v>27.31084368823903</v>
+        <v>27.31084170305399</v>
       </c>
       <c r="F801" t="n">
         <v>7611700</v>
@@ -16532,16 +16532,16 @@
         <v>45330</v>
       </c>
       <c r="B806" t="n">
-        <v>28.79427528381348</v>
+        <v>28.79427337646484</v>
       </c>
       <c r="C806" t="n">
-        <v>28.81392382346353</v>
+        <v>28.81392191481336</v>
       </c>
       <c r="D806" t="n">
-        <v>27.39926082305394</v>
+        <v>27.39925900811183</v>
       </c>
       <c r="E806" t="n">
-        <v>28.71568299900116</v>
+        <v>28.71568109685852</v>
       </c>
       <c r="F806" t="n">
         <v>6908300</v>
@@ -16552,16 +16552,16 @@
         <v>45331</v>
       </c>
       <c r="B807" t="n">
-        <v>27.6939811706543</v>
+        <v>27.69398307800293</v>
       </c>
       <c r="C807" t="n">
-        <v>28.9121624286317</v>
+        <v>28.9121644198793</v>
       </c>
       <c r="D807" t="n">
-        <v>27.52697234402422</v>
+        <v>27.52697423987057</v>
       </c>
       <c r="E807" t="n">
-        <v>28.83357014985212</v>
+        <v>28.83357213568689</v>
       </c>
       <c r="F807" t="n">
         <v>5513900</v>
@@ -16592,16 +16592,16 @@
         <v>45337</v>
       </c>
       <c r="B809" t="n">
-        <v>28.00835227966309</v>
+        <v>28.00835037231445</v>
       </c>
       <c r="C809" t="n">
-        <v>28.26377767232718</v>
+        <v>28.26377574758426</v>
       </c>
       <c r="D809" t="n">
-        <v>27.28137318075199</v>
+        <v>27.28137132291011</v>
       </c>
       <c r="E809" t="n">
-        <v>27.40908494019011</v>
+        <v>27.40908307365115</v>
       </c>
       <c r="F809" t="n">
         <v>2788300</v>
@@ -16632,16 +16632,16 @@
         <v>45341</v>
       </c>
       <c r="B811" t="n">
-        <v>28.67638778686523</v>
+        <v>28.6763858795166</v>
       </c>
       <c r="C811" t="n">
-        <v>28.76480434148215</v>
+        <v>28.76480242825268</v>
       </c>
       <c r="D811" t="n">
-        <v>28.23430501378064</v>
+        <v>28.2343031358362</v>
       </c>
       <c r="E811" t="n">
-        <v>28.74515580183664</v>
+        <v>28.74515388991405</v>
       </c>
       <c r="F811" t="n">
         <v>1698200</v>
@@ -16672,16 +16672,16 @@
         <v>45343</v>
       </c>
       <c r="B813" t="n">
-        <v>28.92198944091797</v>
+        <v>28.92198753356934</v>
       </c>
       <c r="C813" t="n">
-        <v>28.98093318714647</v>
+        <v>28.98093127591061</v>
       </c>
       <c r="D813" t="n">
-        <v>28.36201916727748</v>
+        <v>28.36201729685779</v>
       </c>
       <c r="E813" t="n">
-        <v>28.6370912322024</v>
+        <v>28.63708934364225</v>
       </c>
       <c r="F813" t="n">
         <v>2751400</v>
@@ -16792,16 +16792,16 @@
         <v>45351</v>
       </c>
       <c r="B819" t="n">
-        <v>27.45820617675781</v>
+        <v>27.45820426940918</v>
       </c>
       <c r="C819" t="n">
-        <v>28.14588819377561</v>
+        <v>28.14588623865804</v>
       </c>
       <c r="D819" t="n">
-        <v>27.45820617675781</v>
+        <v>27.45820426940918</v>
       </c>
       <c r="E819" t="n">
-        <v>27.98870362566938</v>
+        <v>27.98870168147043</v>
       </c>
       <c r="F819" t="n">
         <v>2784300</v>
@@ -16972,16 +16972,16 @@
         <v>45364</v>
       </c>
       <c r="B828" t="n">
-        <v>29.13811683654785</v>
+        <v>29.13811492919922</v>
       </c>
       <c r="C828" t="n">
-        <v>29.36406941808906</v>
+        <v>29.36406749594983</v>
       </c>
       <c r="D828" t="n">
-        <v>28.98093226905937</v>
+        <v>28.98093037199986</v>
       </c>
       <c r="E828" t="n">
-        <v>28.98093226905937</v>
+        <v>28.98093037199986</v>
       </c>
       <c r="F828" t="n">
         <v>2596400</v>
@@ -17032,16 +17032,16 @@
         <v>45369</v>
       </c>
       <c r="B831" t="n">
-        <v>28.98093032836914</v>
+        <v>28.98093223571777</v>
       </c>
       <c r="C831" t="n">
-        <v>29.28547517326093</v>
+        <v>29.28547710065286</v>
       </c>
       <c r="D831" t="n">
-        <v>28.61743986927554</v>
+        <v>28.61744175270144</v>
       </c>
       <c r="E831" t="n">
-        <v>28.77462630002598</v>
+        <v>28.77462819379693</v>
       </c>
       <c r="F831" t="n">
         <v>4710300</v>
@@ -17112,16 +17112,16 @@
         <v>45373</v>
       </c>
       <c r="B835" t="n">
-        <v>29.71773338317871</v>
+        <v>29.71773529052734</v>
       </c>
       <c r="C835" t="n">
-        <v>30.00263156131158</v>
+        <v>30.0026334869456</v>
       </c>
       <c r="D835" t="n">
-        <v>29.28547491839919</v>
+        <v>29.28547679800454</v>
       </c>
       <c r="E835" t="n">
-        <v>29.88474220772164</v>
+        <v>29.88474412578926</v>
       </c>
       <c r="F835" t="n">
         <v>3854000</v>
@@ -17152,16 +17152,16 @@
         <v>45377</v>
       </c>
       <c r="B837" t="n">
-        <v>30.81802940368652</v>
+        <v>30.81802749633789</v>
       </c>
       <c r="C837" t="n">
-        <v>31.22081509112746</v>
+        <v>31.22081315885015</v>
       </c>
       <c r="D837" t="n">
-        <v>30.51348266534799</v>
+        <v>30.51348077684796</v>
       </c>
       <c r="E837" t="n">
-        <v>30.61172348823823</v>
+        <v>30.61172159365801</v>
       </c>
       <c r="F837" t="n">
         <v>3327200</v>
@@ -17172,16 +17172,16 @@
         <v>45378</v>
       </c>
       <c r="B838" t="n">
-        <v>31.48606300354004</v>
+        <v>31.48606109619141</v>
       </c>
       <c r="C838" t="n">
-        <v>31.91832337550937</v>
+        <v>31.91832144197546</v>
       </c>
       <c r="D838" t="n">
-        <v>30.38577102935353</v>
+        <v>30.3857691886579</v>
       </c>
       <c r="E838" t="n">
-        <v>30.6510206900868</v>
+        <v>30.65101883332299</v>
       </c>
       <c r="F838" t="n">
         <v>9071000</v>
@@ -17372,16 +17372,16 @@
         <v>45393</v>
       </c>
       <c r="B848" t="n">
-        <v>35.62198257446289</v>
+        <v>35.62198638916016</v>
       </c>
       <c r="C848" t="n">
-        <v>35.91670689814429</v>
+        <v>35.91671074440308</v>
       </c>
       <c r="D848" t="n">
-        <v>34.59045868430435</v>
+        <v>34.59046238853748</v>
       </c>
       <c r="E848" t="n">
-        <v>34.74764324139922</v>
+        <v>34.74764696246498</v>
       </c>
       <c r="F848" t="n">
         <v>5960900</v>
@@ -17412,16 +17412,16 @@
         <v>45397</v>
       </c>
       <c r="B850" t="n">
-        <v>34.06978988647461</v>
+        <v>34.06978607177734</v>
       </c>
       <c r="C850" t="n">
-        <v>34.52169507730631</v>
+        <v>34.52169121201051</v>
       </c>
       <c r="D850" t="n">
-        <v>33.83401114697602</v>
+        <v>33.83400735867823</v>
       </c>
       <c r="E850" t="n">
-        <v>34.43327851844133</v>
+        <v>34.43327466304528</v>
       </c>
       <c r="F850" t="n">
         <v>4151100</v>
@@ -17472,16 +17472,16 @@
         <v>45400</v>
       </c>
       <c r="B853" t="n">
-        <v>32.33092880249023</v>
+        <v>32.3309326171875</v>
       </c>
       <c r="C853" t="n">
-        <v>33.28386227408815</v>
+        <v>33.28386620122118</v>
       </c>
       <c r="D853" t="n">
-        <v>31.93796554165645</v>
+        <v>31.93796930998834</v>
       </c>
       <c r="E853" t="n">
-        <v>33.00878649247434</v>
+        <v>33.00879038715143</v>
       </c>
       <c r="F853" t="n">
         <v>4478700</v>
@@ -17632,16 +17632,16 @@
         <v>45412</v>
       </c>
       <c r="B861" t="n">
-        <v>32.58635330200195</v>
+        <v>32.58635711669922</v>
       </c>
       <c r="C861" t="n">
-        <v>33.66700042877825</v>
+        <v>33.66700436998067</v>
       </c>
       <c r="D861" t="n">
-        <v>32.43899488533395</v>
+        <v>32.43899868278081</v>
       </c>
       <c r="E861" t="n">
-        <v>33.60805481356574</v>
+        <v>33.60805874786774</v>
       </c>
       <c r="F861" t="n">
         <v>6661700</v>
@@ -29612,19 +29612,39 @@
         <v>46288</v>
       </c>
       <c r="B1460" t="n">
-        <v>17.6</v>
+        <v>17.60000038146973</v>
       </c>
       <c r="C1460" t="n">
-        <v>18.02</v>
+        <v>18.02000045776367</v>
       </c>
       <c r="D1460" t="n">
-        <v>17.57</v>
+        <v>17.56999969482422</v>
       </c>
       <c r="E1460" t="n">
-        <v>17.8</v>
+        <v>17.79999923706055</v>
       </c>
       <c r="F1460" t="n">
         <v>2251900</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B1461" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="C1461" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="D1461" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="E1461" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="F1461" t="n">
+        <v>1398600</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1461"/>
+  <dimension ref="A1:F1462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,16 +512,16 @@
         <v>44152</v>
       </c>
       <c r="B5" t="n">
-        <v>20.17695426940918</v>
+        <v>20.17695617675781</v>
       </c>
       <c r="C5" t="n">
-        <v>20.17695426940918</v>
+        <v>20.17695617675781</v>
       </c>
       <c r="D5" t="n">
-        <v>19.85012445790661</v>
+        <v>19.85012633435968</v>
       </c>
       <c r="E5" t="n">
-        <v>20.12888973916155</v>
+        <v>20.12889164196659</v>
       </c>
       <c r="F5" t="n">
         <v>262242</v>
@@ -572,16 +572,16 @@
         <v>44158</v>
       </c>
       <c r="B8" t="n">
-        <v>20.20579147338867</v>
+        <v>20.2057933807373</v>
       </c>
       <c r="C8" t="n">
-        <v>20.52300874747816</v>
+        <v>20.52301068477087</v>
       </c>
       <c r="D8" t="n">
-        <v>20.14811628674976</v>
+        <v>20.14811818865408</v>
       </c>
       <c r="E8" t="n">
-        <v>20.14811628674976</v>
+        <v>20.14811818865408</v>
       </c>
       <c r="F8" t="n">
         <v>79408</v>
@@ -632,16 +632,16 @@
         <v>44161</v>
       </c>
       <c r="B11" t="n">
-        <v>22.87810897827148</v>
+        <v>22.87811088562012</v>
       </c>
       <c r="C11" t="n">
-        <v>22.87810897827148</v>
+        <v>22.87811088562012</v>
       </c>
       <c r="D11" t="n">
-        <v>22.31096214463751</v>
+        <v>22.3109640047031</v>
       </c>
       <c r="E11" t="n">
-        <v>22.31096214463751</v>
+        <v>22.3109640047031</v>
       </c>
       <c r="F11" t="n">
         <v>72970</v>
@@ -652,16 +652,16 @@
         <v>44162</v>
       </c>
       <c r="B12" t="n">
-        <v>23.07036399841309</v>
+        <v>23.07036209106445</v>
       </c>
       <c r="C12" t="n">
-        <v>23.55099623037812</v>
+        <v>23.55099428329309</v>
       </c>
       <c r="D12" t="n">
-        <v>22.10909953448302</v>
+        <v>22.10909770660719</v>
       </c>
       <c r="E12" t="n">
-        <v>23.07036399841309</v>
+        <v>23.07036209106445</v>
       </c>
       <c r="F12" t="n">
         <v>72050</v>
@@ -692,16 +692,16 @@
         <v>44166</v>
       </c>
       <c r="B14" t="n">
-        <v>23.07036399841309</v>
+        <v>23.07036209106445</v>
       </c>
       <c r="C14" t="n">
-        <v>23.16649119432127</v>
+        <v>23.1664892790253</v>
       </c>
       <c r="D14" t="n">
-        <v>23.03191386956499</v>
+        <v>23.03191196539523</v>
       </c>
       <c r="E14" t="n">
-        <v>23.12803919168523</v>
+        <v>23.12803727956828</v>
       </c>
       <c r="F14" t="n">
         <v>93512</v>
@@ -792,16 +792,16 @@
         <v>44173</v>
       </c>
       <c r="B19" t="n">
-        <v>26.33866310119629</v>
+        <v>26.33866500854492</v>
       </c>
       <c r="C19" t="n">
-        <v>26.57898012603766</v>
+        <v>26.57898205078916</v>
       </c>
       <c r="D19" t="n">
-        <v>25.56965124500673</v>
+        <v>25.56965309666637</v>
       </c>
       <c r="E19" t="n">
-        <v>25.56965124500673</v>
+        <v>25.56965309666637</v>
       </c>
       <c r="F19" t="n">
         <v>126420</v>
@@ -812,16 +812,16 @@
         <v>44174</v>
       </c>
       <c r="B20" t="n">
-        <v>26.83852195739746</v>
+        <v>26.83852005004883</v>
       </c>
       <c r="C20" t="n">
-        <v>27.77095064592048</v>
+        <v>27.77094867230641</v>
       </c>
       <c r="D20" t="n">
-        <v>26.27137696749292</v>
+        <v>26.27137510044991</v>
       </c>
       <c r="E20" t="n">
-        <v>26.49246706969505</v>
+        <v>26.4924651869397</v>
       </c>
       <c r="F20" t="n">
         <v>212880</v>
@@ -892,16 +892,16 @@
         <v>44180</v>
       </c>
       <c r="B24" t="n">
-        <v>33.00984573364258</v>
+        <v>33.00984191894531</v>
       </c>
       <c r="C24" t="n">
-        <v>33.98072266755544</v>
+        <v>33.9807187406613</v>
       </c>
       <c r="D24" t="n">
-        <v>30.76048335959674</v>
+        <v>30.7604798048412</v>
       </c>
       <c r="E24" t="n">
-        <v>30.76048335959674</v>
+        <v>30.7604798048412</v>
       </c>
       <c r="F24" t="n">
         <v>887803</v>
@@ -912,16 +912,16 @@
         <v>44181</v>
       </c>
       <c r="B25" t="n">
-        <v>32.68301391601562</v>
+        <v>32.68301773071289</v>
       </c>
       <c r="C25" t="n">
-        <v>34.45173835953219</v>
+        <v>34.4517423806715</v>
       </c>
       <c r="D25" t="n">
-        <v>32.10625456033017</v>
+        <v>32.10625830770921</v>
       </c>
       <c r="E25" t="n">
-        <v>33.62505319761509</v>
+        <v>33.62505712226533</v>
       </c>
       <c r="F25" t="n">
         <v>376808</v>
@@ -932,16 +932,16 @@
         <v>44182</v>
       </c>
       <c r="B26" t="n">
-        <v>32.10625839233398</v>
+        <v>32.10625457763672</v>
       </c>
       <c r="C26" t="n">
-        <v>33.64428227520571</v>
+        <v>33.64427827776851</v>
       </c>
       <c r="D26" t="n">
-        <v>31.64484935368452</v>
+        <v>31.64484559380946</v>
       </c>
       <c r="E26" t="n">
-        <v>33.6250572108933</v>
+        <v>33.62505321574033</v>
       </c>
       <c r="F26" t="n">
         <v>258257</v>
@@ -972,16 +972,16 @@
         <v>44186</v>
       </c>
       <c r="B28" t="n">
-        <v>32.18315887451172</v>
+        <v>32.18315505981445</v>
       </c>
       <c r="C28" t="n">
-        <v>33.33667773162143</v>
+        <v>33.33667378019659</v>
       </c>
       <c r="D28" t="n">
-        <v>29.12633427792858</v>
+        <v>29.12633082555934</v>
       </c>
       <c r="E28" t="n">
-        <v>31.86594156356414</v>
+        <v>31.86593778646691</v>
       </c>
       <c r="F28" t="n">
         <v>236079</v>
@@ -992,16 +992,16 @@
         <v>44187</v>
       </c>
       <c r="B29" t="n">
-        <v>33.16364288330078</v>
+        <v>33.16364669799805</v>
       </c>
       <c r="C29" t="n">
-        <v>33.47124761081827</v>
+        <v>33.47125146089823</v>
       </c>
       <c r="D29" t="n">
-        <v>32.59649608138177</v>
+        <v>32.59649983084212</v>
       </c>
       <c r="E29" t="n">
-        <v>33.21170553641675</v>
+        <v>33.21170935664249</v>
       </c>
       <c r="F29" t="n">
         <v>167504</v>
@@ -1032,16 +1032,16 @@
         <v>44193</v>
       </c>
       <c r="B31" t="n">
-        <v>36.21085739135742</v>
+        <v>36.21085357666016</v>
       </c>
       <c r="C31" t="n">
-        <v>36.66265388599569</v>
+        <v>36.66265002370312</v>
       </c>
       <c r="D31" t="n">
-        <v>35.56681025863972</v>
+        <v>35.56680651179074</v>
       </c>
       <c r="E31" t="n">
-        <v>35.56681025863972</v>
+        <v>35.56680651179074</v>
       </c>
       <c r="F31" t="n">
         <v>451822</v>
@@ -1052,16 +1052,16 @@
         <v>44194</v>
       </c>
       <c r="B32" t="n">
-        <v>36.09550476074219</v>
+        <v>36.09550857543945</v>
       </c>
       <c r="C32" t="n">
-        <v>37.06638166531152</v>
+        <v>37.06638558261441</v>
       </c>
       <c r="D32" t="n">
-        <v>35.95131304358604</v>
+        <v>35.95131684304462</v>
       </c>
       <c r="E32" t="n">
-        <v>36.52807241705953</v>
+        <v>36.52807627747203</v>
       </c>
       <c r="F32" t="n">
         <v>337154</v>
@@ -1092,16 +1092,16 @@
         <v>44200</v>
       </c>
       <c r="B34" t="n">
-        <v>34.99966049194336</v>
+        <v>34.99966430664062</v>
       </c>
       <c r="C34" t="n">
-        <v>36.62420073506411</v>
+        <v>36.62420472682393</v>
       </c>
       <c r="D34" t="n">
-        <v>34.98043542972244</v>
+        <v>34.98043924232432</v>
       </c>
       <c r="E34" t="n">
-        <v>36.52807167638402</v>
+        <v>36.52807565766651</v>
       </c>
       <c r="F34" t="n">
         <v>331840</v>
@@ -1112,16 +1112,16 @@
         <v>44201</v>
       </c>
       <c r="B35" t="n">
-        <v>36.13395690917969</v>
+        <v>36.13395309448242</v>
       </c>
       <c r="C35" t="n">
-        <v>36.32621129362743</v>
+        <v>36.32620745863368</v>
       </c>
       <c r="D35" t="n">
-        <v>34.60554560816865</v>
+        <v>34.60554195482727</v>
       </c>
       <c r="E35" t="n">
-        <v>35.45145965313264</v>
+        <v>35.45145591048728</v>
       </c>
       <c r="F35" t="n">
         <v>328059</v>
@@ -1172,16 +1172,16 @@
         <v>44204</v>
       </c>
       <c r="B38" t="n">
-        <v>34.13452529907227</v>
+        <v>34.134521484375</v>
       </c>
       <c r="C38" t="n">
-        <v>35.75906572541368</v>
+        <v>35.75906172916622</v>
       </c>
       <c r="D38" t="n">
-        <v>34.13452529907227</v>
+        <v>34.134521484375</v>
       </c>
       <c r="E38" t="n">
-        <v>35.16308123419719</v>
+        <v>35.16307730455386</v>
       </c>
       <c r="F38" t="n">
         <v>367201</v>
@@ -1272,16 +1272,16 @@
         <v>44211</v>
       </c>
       <c r="B43" t="n">
-        <v>33.94226837158203</v>
+        <v>33.9422721862793</v>
       </c>
       <c r="C43" t="n">
-        <v>35.04772061203977</v>
+        <v>35.0477245509764</v>
       </c>
       <c r="D43" t="n">
-        <v>33.16364216523639</v>
+        <v>33.16364589242556</v>
       </c>
       <c r="E43" t="n">
-        <v>34.60554046537172</v>
+        <v>34.60554435461268</v>
       </c>
       <c r="F43" t="n">
         <v>319883</v>
@@ -1292,16 +1292,16 @@
         <v>44214</v>
       </c>
       <c r="B44" t="n">
-        <v>34.04801177978516</v>
+        <v>34.04800796508789</v>
       </c>
       <c r="C44" t="n">
-        <v>34.5094208103909</v>
+        <v>34.50941694399793</v>
       </c>
       <c r="D44" t="n">
-        <v>33.27900172554335</v>
+        <v>33.27899799700501</v>
       </c>
       <c r="E44" t="n">
-        <v>34.11529950370554</v>
+        <v>34.11529568146945</v>
       </c>
       <c r="F44" t="n">
         <v>117631</v>
@@ -1332,16 +1332,16 @@
         <v>44216</v>
       </c>
       <c r="B46" t="n">
-        <v>34.12490844726562</v>
+        <v>34.12491226196289</v>
       </c>
       <c r="C46" t="n">
-        <v>35.28803968588292</v>
+        <v>35.28804363060232</v>
       </c>
       <c r="D46" t="n">
-        <v>33.66350321275509</v>
+        <v>33.66350697587357</v>
       </c>
       <c r="E46" t="n">
-        <v>34.60554249130722</v>
+        <v>34.60554635973278</v>
       </c>
       <c r="F46" t="n">
         <v>359332</v>
@@ -1372,16 +1372,16 @@
         <v>44218</v>
       </c>
       <c r="B48" t="n">
-        <v>32.95216369628906</v>
+        <v>32.95216751098633</v>
       </c>
       <c r="C48" t="n">
-        <v>33.45202278739948</v>
+        <v>33.45202665996278</v>
       </c>
       <c r="D48" t="n">
-        <v>32.53882112897777</v>
+        <v>32.53882489582456</v>
       </c>
       <c r="E48" t="n">
-        <v>33.19248071115274</v>
+        <v>33.19248455367023</v>
       </c>
       <c r="F48" t="n">
         <v>220341</v>
@@ -1472,16 +1472,16 @@
         <v>44228</v>
       </c>
       <c r="B53" t="n">
-        <v>31.7794246673584</v>
+        <v>31.77942657470703</v>
       </c>
       <c r="C53" t="n">
-        <v>33.1155814640686</v>
+        <v>33.11558345161116</v>
       </c>
       <c r="D53" t="n">
-        <v>31.66407054800669</v>
+        <v>31.66407244843196</v>
       </c>
       <c r="E53" t="n">
-        <v>32.68301382233215</v>
+        <v>32.68301578391271</v>
       </c>
       <c r="F53" t="n">
         <v>610435</v>
@@ -1492,16 +1492,16 @@
         <v>44229</v>
       </c>
       <c r="B54" t="n">
-        <v>32.63494873046875</v>
+        <v>32.63495254516602</v>
       </c>
       <c r="C54" t="n">
-        <v>33.65389204571495</v>
+        <v>33.65389597951643</v>
       </c>
       <c r="D54" t="n">
-        <v>31.97167657096734</v>
+        <v>31.97168030813476</v>
       </c>
       <c r="E54" t="n">
-        <v>33.64427951434755</v>
+        <v>33.64428344702543</v>
       </c>
       <c r="F54" t="n">
         <v>582228</v>
@@ -1532,16 +1532,16 @@
         <v>44231</v>
       </c>
       <c r="B56" t="n">
-        <v>32.68301391601562</v>
+        <v>32.68301773071289</v>
       </c>
       <c r="C56" t="n">
-        <v>34.11529602664492</v>
+        <v>34.11530000851534</v>
       </c>
       <c r="D56" t="n">
-        <v>32.44269689321744</v>
+        <v>32.44270067986538</v>
       </c>
       <c r="E56" t="n">
-        <v>33.06751890394745</v>
+        <v>33.06752276352339</v>
       </c>
       <c r="F56" t="n">
         <v>466743</v>
@@ -1612,16 +1612,16 @@
         <v>44237</v>
       </c>
       <c r="B60" t="n">
-        <v>34.83624649047852</v>
+        <v>34.83625030517578</v>
       </c>
       <c r="C60" t="n">
-        <v>35.33610184184258</v>
+        <v>35.33610571127585</v>
       </c>
       <c r="D60" t="n">
-        <v>34.23064955227608</v>
+        <v>34.23065330065825</v>
       </c>
       <c r="E60" t="n">
-        <v>34.43251269995998</v>
+        <v>34.43251647044691</v>
       </c>
       <c r="F60" t="n">
         <v>186206</v>
@@ -1652,16 +1652,16 @@
         <v>44239</v>
       </c>
       <c r="B62" t="n">
-        <v>34.40367889404297</v>
+        <v>34.4036750793457</v>
       </c>
       <c r="C62" t="n">
-        <v>34.52864555631986</v>
+        <v>34.52864172776623</v>
       </c>
       <c r="D62" t="n">
-        <v>32.673400666573</v>
+        <v>32.67339704372985</v>
       </c>
       <c r="E62" t="n">
-        <v>33.67311897448496</v>
+        <v>33.67311524079254</v>
       </c>
       <c r="F62" t="n">
         <v>218195</v>
@@ -1692,16 +1692,16 @@
         <v>44245</v>
       </c>
       <c r="B64" t="n">
-        <v>37.00870895385742</v>
+        <v>37.00870513916016</v>
       </c>
       <c r="C64" t="n">
-        <v>37.38360144742785</v>
+        <v>37.38359759408829</v>
       </c>
       <c r="D64" t="n">
-        <v>35.71100215049589</v>
+        <v>35.71099846956061</v>
       </c>
       <c r="E64" t="n">
-        <v>36.37427435009953</v>
+        <v>36.37427060079703</v>
       </c>
       <c r="F64" t="n">
         <v>661534</v>
@@ -1812,16 +1812,16 @@
         <v>44253</v>
       </c>
       <c r="B70" t="n">
-        <v>34.57670593261719</v>
+        <v>34.57670974731445</v>
       </c>
       <c r="C70" t="n">
-        <v>37.21057322750037</v>
+        <v>37.21057733278074</v>
       </c>
       <c r="D70" t="n">
-        <v>33.75001700107128</v>
+        <v>33.75002072456356</v>
       </c>
       <c r="E70" t="n">
-        <v>36.5376847961999</v>
+        <v>36.53768882724342</v>
       </c>
       <c r="F70" t="n">
         <v>410022</v>
@@ -1932,16 +1932,16 @@
         <v>44263</v>
       </c>
       <c r="B76" t="n">
-        <v>41.91115951538086</v>
+        <v>41.91115570068359</v>
       </c>
       <c r="C76" t="n">
-        <v>44.60270214463106</v>
+        <v>44.60269808495321</v>
       </c>
       <c r="D76" t="n">
-        <v>40.70957805138659</v>
+        <v>40.70957434605565</v>
       </c>
       <c r="E76" t="n">
-        <v>43.55492493684502</v>
+        <v>43.55492097253444</v>
       </c>
       <c r="F76" t="n">
         <v>1012691</v>
@@ -1952,16 +1952,16 @@
         <v>44264</v>
       </c>
       <c r="B77" t="n">
-        <v>43.50686264038086</v>
+        <v>43.50685882568359</v>
       </c>
       <c r="C77" t="n">
-        <v>43.50686264038086</v>
+        <v>43.50685882568359</v>
       </c>
       <c r="D77" t="n">
-        <v>39.89250193891922</v>
+        <v>39.89249844113039</v>
       </c>
       <c r="E77" t="n">
-        <v>42.29566488693005</v>
+        <v>42.29566117843103</v>
       </c>
       <c r="F77" t="n">
         <v>563525</v>
@@ -1972,16 +1972,16 @@
         <v>44265</v>
       </c>
       <c r="B78" t="n">
-        <v>44.69882583618164</v>
+        <v>44.69882965087891</v>
       </c>
       <c r="C78" t="n">
-        <v>44.89108021255291</v>
+        <v>44.89108404365759</v>
       </c>
       <c r="D78" t="n">
-        <v>43.38189403862891</v>
+        <v>43.38189774093629</v>
       </c>
       <c r="E78" t="n">
-        <v>43.83369051144994</v>
+        <v>43.83369425231464</v>
       </c>
       <c r="F78" t="n">
         <v>425454</v>
@@ -2012,16 +2012,16 @@
         <v>44267</v>
       </c>
       <c r="B80" t="n">
-        <v>45.66009521484375</v>
+        <v>45.66009140014648</v>
       </c>
       <c r="C80" t="n">
-        <v>49.01491000208902</v>
+        <v>49.01490590711195</v>
       </c>
       <c r="D80" t="n">
-        <v>45.18907366630634</v>
+        <v>45.18906989096082</v>
       </c>
       <c r="E80" t="n">
-        <v>47.15005636649431</v>
+        <v>47.15005242731743</v>
       </c>
       <c r="F80" t="n">
         <v>954539</v>
@@ -2052,16 +2052,16 @@
         <v>44271</v>
       </c>
       <c r="B82" t="n">
-        <v>42.75707244873047</v>
+        <v>42.7570686340332</v>
       </c>
       <c r="C82" t="n">
-        <v>45.18907290913018</v>
+        <v>45.18906887745489</v>
       </c>
       <c r="D82" t="n">
-        <v>42.75707244873047</v>
+        <v>42.7570686340332</v>
       </c>
       <c r="E82" t="n">
-        <v>44.50657567458991</v>
+        <v>44.5065717038056</v>
       </c>
       <c r="F82" t="n">
         <v>561175</v>
@@ -2092,16 +2092,16 @@
         <v>44273</v>
       </c>
       <c r="B84" t="n">
-        <v>40.89221954345703</v>
+        <v>40.89221572875977</v>
       </c>
       <c r="C84" t="n">
-        <v>45.0256568951004</v>
+        <v>45.02565269480871</v>
       </c>
       <c r="D84" t="n">
-        <v>40.57500224961562</v>
+        <v>40.57499846451049</v>
       </c>
       <c r="E84" t="n">
-        <v>44.01632982334604</v>
+        <v>44.01632571721106</v>
       </c>
       <c r="F84" t="n">
         <v>572621</v>
@@ -2112,16 +2112,16 @@
         <v>44274</v>
       </c>
       <c r="B85" t="n">
-        <v>42.29566192626953</v>
+        <v>42.2956657409668</v>
       </c>
       <c r="C85" t="n">
-        <v>44.17013174266427</v>
+        <v>44.17013572642225</v>
       </c>
       <c r="D85" t="n">
-        <v>41.4593642170013</v>
+        <v>41.45936795627186</v>
       </c>
       <c r="E85" t="n">
-        <v>41.4593642170013</v>
+        <v>41.45936795627186</v>
       </c>
       <c r="F85" t="n">
         <v>639255</v>
@@ -2212,16 +2212,16 @@
         <v>44281</v>
       </c>
       <c r="B90" t="n">
-        <v>37.87384414672852</v>
+        <v>37.87384796142578</v>
       </c>
       <c r="C90" t="n">
-        <v>40.949891527232</v>
+        <v>40.94989565175231</v>
       </c>
       <c r="D90" t="n">
-        <v>37.56623940867817</v>
+        <v>37.56624319239313</v>
       </c>
       <c r="E90" t="n">
-        <v>39.95978959641457</v>
+        <v>39.95979362121066</v>
       </c>
       <c r="F90" t="n">
         <v>840076</v>
@@ -2312,16 +2312,16 @@
         <v>44291</v>
       </c>
       <c r="B95" t="n">
-        <v>35.68215942382812</v>
+        <v>35.68216323852539</v>
       </c>
       <c r="C95" t="n">
-        <v>37.01831616285484</v>
+        <v>37.01832012039754</v>
       </c>
       <c r="D95" t="n">
-        <v>35.09578756412892</v>
+        <v>35.09579131613852</v>
       </c>
       <c r="E95" t="n">
-        <v>37.01831616285484</v>
+        <v>37.01832012039754</v>
       </c>
       <c r="F95" t="n">
         <v>1091895</v>
@@ -2512,16 +2512,16 @@
         <v>44305</v>
       </c>
       <c r="B105" t="n">
-        <v>41.33439636230469</v>
+        <v>41.33440017700195</v>
       </c>
       <c r="C105" t="n">
-        <v>42.23798551125894</v>
+        <v>42.23798940934727</v>
       </c>
       <c r="D105" t="n">
-        <v>40.20971525467667</v>
+        <v>40.2097189655786</v>
       </c>
       <c r="E105" t="n">
-        <v>40.38274455876383</v>
+        <v>40.38274828563441</v>
       </c>
       <c r="F105" t="n">
         <v>1793083</v>
@@ -2552,16 +2552,16 @@
         <v>44308</v>
       </c>
       <c r="B107" t="n">
-        <v>42.3725700378418</v>
+        <v>42.37256622314453</v>
       </c>
       <c r="C107" t="n">
-        <v>42.77630013488342</v>
+        <v>42.77629628383934</v>
       </c>
       <c r="D107" t="n">
-        <v>41.04602186600353</v>
+        <v>41.0460181707321</v>
       </c>
       <c r="E107" t="n">
-        <v>42.58404574470481</v>
+        <v>42.58404191096891</v>
       </c>
       <c r="F107" t="n">
         <v>1175903</v>
@@ -2572,16 +2572,16 @@
         <v>44309</v>
       </c>
       <c r="B108" t="n">
-        <v>44.09323501586914</v>
+        <v>44.09323120117188</v>
       </c>
       <c r="C108" t="n">
-        <v>44.31432325105797</v>
+        <v>44.3143194172334</v>
       </c>
       <c r="D108" t="n">
-        <v>42.38218184069201</v>
+        <v>42.38217817402538</v>
       </c>
       <c r="E108" t="n">
-        <v>42.82436205864548</v>
+        <v>42.82435835372392</v>
       </c>
       <c r="F108" t="n">
         <v>1899574</v>
@@ -2612,16 +2612,16 @@
         <v>44313</v>
       </c>
       <c r="B110" t="n">
-        <v>43.7375602722168</v>
+        <v>43.73756408691406</v>
       </c>
       <c r="C110" t="n">
-        <v>44.31431963823069</v>
+        <v>44.31432350323168</v>
       </c>
       <c r="D110" t="n">
-        <v>43.04545053203033</v>
+        <v>43.04545428636325</v>
       </c>
       <c r="E110" t="n">
-        <v>43.40111793330461</v>
+        <v>43.40112171865809</v>
       </c>
       <c r="F110" t="n">
         <v>1146163</v>
@@ -2732,16 +2732,16 @@
         <v>44321</v>
       </c>
       <c r="B116" t="n">
-        <v>39.74831390380859</v>
+        <v>39.74831008911133</v>
       </c>
       <c r="C116" t="n">
-        <v>40.64229060912697</v>
+        <v>40.6422867086336</v>
       </c>
       <c r="D116" t="n">
-        <v>39.0754291787498</v>
+        <v>39.07542542863015</v>
       </c>
       <c r="E116" t="n">
-        <v>39.89250188164586</v>
+        <v>39.89249805311069</v>
       </c>
       <c r="F116" t="n">
         <v>3650961</v>
@@ -2772,16 +2772,16 @@
         <v>44323</v>
       </c>
       <c r="B118" t="n">
-        <v>38.83510971069336</v>
+        <v>38.83511352539062</v>
       </c>
       <c r="C118" t="n">
-        <v>39.99824098294782</v>
+        <v>39.99824491189721</v>
       </c>
       <c r="D118" t="n">
-        <v>37.51817793834604</v>
+        <v>37.51818162368365</v>
       </c>
       <c r="E118" t="n">
-        <v>39.66179864141913</v>
+        <v>39.66180253732045</v>
       </c>
       <c r="F118" t="n">
         <v>2227429</v>
@@ -2832,16 +2832,16 @@
         <v>44328</v>
       </c>
       <c r="B121" t="n">
-        <v>37.05677032470703</v>
+        <v>37.05676651000977</v>
       </c>
       <c r="C121" t="n">
-        <v>38.70053196862062</v>
+        <v>38.70052798471127</v>
       </c>
       <c r="D121" t="n">
-        <v>37.05677032470703</v>
+        <v>37.05676651000977</v>
       </c>
       <c r="E121" t="n">
-        <v>37.8161715649591</v>
+        <v>37.81616767208757</v>
       </c>
       <c r="F121" t="n">
         <v>783049</v>
@@ -2892,16 +2892,16 @@
         <v>44333</v>
       </c>
       <c r="B124" t="n">
-        <v>36.43194580078125</v>
+        <v>36.43194961547852</v>
       </c>
       <c r="C124" t="n">
-        <v>37.13366805612294</v>
+        <v>37.13367194429578</v>
       </c>
       <c r="D124" t="n">
-        <v>35.93208669563144</v>
+        <v>35.93209045798972</v>
       </c>
       <c r="E124" t="n">
-        <v>36.52807111039643</v>
+        <v>36.52807493515874</v>
       </c>
       <c r="F124" t="n">
         <v>946466</v>
@@ -2912,16 +2912,16 @@
         <v>44334</v>
       </c>
       <c r="B125" t="n">
-        <v>35.14385604858398</v>
+        <v>35.14385223388672</v>
       </c>
       <c r="C125" t="n">
-        <v>36.91258445174329</v>
+        <v>36.91258044505902</v>
       </c>
       <c r="D125" t="n">
-        <v>34.59593422023043</v>
+        <v>34.59593046500746</v>
       </c>
       <c r="E125" t="n">
-        <v>36.52807567013412</v>
+        <v>36.52807170518645</v>
       </c>
       <c r="F125" t="n">
         <v>2070451</v>
@@ -2952,16 +2952,16 @@
         <v>44336</v>
       </c>
       <c r="B127" t="n">
-        <v>34.63438415527344</v>
+        <v>34.63438034057617</v>
       </c>
       <c r="C127" t="n">
-        <v>35.26881876953347</v>
+        <v>35.26881488495837</v>
       </c>
       <c r="D127" t="n">
-        <v>34.51903376998102</v>
+        <v>34.51902996798866</v>
       </c>
       <c r="E127" t="n">
-        <v>34.51903376998102</v>
+        <v>34.51902996798866</v>
       </c>
       <c r="F127" t="n">
         <v>943604</v>
@@ -3012,16 +3012,16 @@
         <v>44341</v>
       </c>
       <c r="B130" t="n">
-        <v>37.29708862304688</v>
+        <v>37.29708480834961</v>
       </c>
       <c r="C130" t="n">
-        <v>38.78704981148397</v>
+        <v>38.78704584439543</v>
       </c>
       <c r="D130" t="n">
-        <v>37.22980089947328</v>
+        <v>37.22979709165812</v>
       </c>
       <c r="E130" t="n">
-        <v>37.52779313716071</v>
+        <v>37.52778929886728</v>
       </c>
       <c r="F130" t="n">
         <v>1731150</v>
@@ -3092,16 +3092,16 @@
         <v>44347</v>
       </c>
       <c r="B134" t="n">
-        <v>39.38303375244141</v>
+        <v>39.38302993774414</v>
       </c>
       <c r="C134" t="n">
-        <v>40.11359366504992</v>
+        <v>40.11358977958957</v>
       </c>
       <c r="D134" t="n">
-        <v>39.02736632794579</v>
+        <v>39.02736254769899</v>
       </c>
       <c r="E134" t="n">
-        <v>39.39264628425005</v>
+        <v>39.3926424686217</v>
       </c>
       <c r="F134" t="n">
         <v>715598</v>
@@ -3192,16 +3192,16 @@
         <v>44355</v>
       </c>
       <c r="B139" t="n">
-        <v>38.4602165222168</v>
+        <v>38.46022033691406</v>
       </c>
       <c r="C139" t="n">
-        <v>38.85433404388245</v>
+        <v>38.85433789767048</v>
       </c>
       <c r="D139" t="n">
-        <v>37.72004038668688</v>
+        <v>37.72004412796937</v>
       </c>
       <c r="E139" t="n">
-        <v>38.43137892899068</v>
+        <v>38.43138274082768</v>
       </c>
       <c r="F139" t="n">
         <v>978352</v>
@@ -3212,16 +3212,16 @@
         <v>44356</v>
       </c>
       <c r="B140" t="n">
-        <v>38.01803588867188</v>
+        <v>38.01803207397461</v>
       </c>
       <c r="C140" t="n">
-        <v>38.66208302162527</v>
+        <v>38.66207914230487</v>
       </c>
       <c r="D140" t="n">
-        <v>37.29708850045856</v>
+        <v>37.29708475810054</v>
       </c>
       <c r="E140" t="n">
-        <v>38.48905744729046</v>
+        <v>38.48905358533129</v>
       </c>
       <c r="F140" t="n">
         <v>837521</v>
@@ -3332,16 +3332,16 @@
         <v>44364</v>
       </c>
       <c r="B146" t="n">
-        <v>42.4879150390625</v>
+        <v>42.48791885375977</v>
       </c>
       <c r="C146" t="n">
-        <v>44.0067136610316</v>
+        <v>44.00671761209134</v>
       </c>
       <c r="D146" t="n">
-        <v>41.62277601425852</v>
+        <v>41.62277975128091</v>
       </c>
       <c r="E146" t="n">
-        <v>42.95893654890009</v>
+        <v>42.95894040588714</v>
       </c>
       <c r="F146" t="n">
         <v>1582144</v>
@@ -3372,16 +3372,16 @@
         <v>44368</v>
       </c>
       <c r="B148" t="n">
-        <v>46.96741485595703</v>
+        <v>46.96741104125977</v>
       </c>
       <c r="C148" t="n">
-        <v>47.24618202489792</v>
+        <v>47.24617818755916</v>
       </c>
       <c r="D148" t="n">
-        <v>43.53569979030122</v>
+        <v>43.53569625432814</v>
       </c>
       <c r="E148" t="n">
-        <v>43.73756295749668</v>
+        <v>43.73755940512824</v>
       </c>
       <c r="F148" t="n">
         <v>2655439</v>
@@ -3452,16 +3452,16 @@
         <v>44372</v>
       </c>
       <c r="B152" t="n">
-        <v>44.45851135253906</v>
+        <v>44.45851516723633</v>
       </c>
       <c r="C152" t="n">
-        <v>44.98720431506052</v>
+        <v>44.9872081751215</v>
       </c>
       <c r="D152" t="n">
-        <v>43.97787729834627</v>
+        <v>43.97788107180344</v>
       </c>
       <c r="E152" t="n">
-        <v>44.98720431506052</v>
+        <v>44.9872081751215</v>
       </c>
       <c r="F152" t="n">
         <v>1347904</v>
@@ -3472,16 +3472,16 @@
         <v>44375</v>
       </c>
       <c r="B153" t="n">
-        <v>44.5354118347168</v>
+        <v>44.53541564941406</v>
       </c>
       <c r="C153" t="n">
-        <v>44.64114967825854</v>
+        <v>44.64115350201283</v>
       </c>
       <c r="D153" t="n">
-        <v>43.20886378695175</v>
+        <v>43.20886748802305</v>
       </c>
       <c r="E153" t="n">
-        <v>44.13168177543641</v>
+        <v>44.13168555555202</v>
       </c>
       <c r="F153" t="n">
         <v>1110393</v>
@@ -3512,16 +3512,16 @@
         <v>44377</v>
       </c>
       <c r="B155" t="n">
-        <v>43.58376312255859</v>
+        <v>43.58375930786133</v>
       </c>
       <c r="C155" t="n">
-        <v>44.45851476998166</v>
+        <v>44.45851087872119</v>
       </c>
       <c r="D155" t="n">
-        <v>43.50686286720073</v>
+        <v>43.50685905923421</v>
       </c>
       <c r="E155" t="n">
-        <v>44.21819772441255</v>
+        <v>44.21819385418598</v>
       </c>
       <c r="F155" t="n">
         <v>1274116</v>
@@ -3572,16 +3572,16 @@
         <v>44382</v>
       </c>
       <c r="B158" t="n">
-        <v>45.04488372802734</v>
+        <v>45.04488754272461</v>
       </c>
       <c r="C158" t="n">
-        <v>46.21762753484401</v>
+        <v>46.21763144885693</v>
       </c>
       <c r="D158" t="n">
-        <v>44.42967048319475</v>
+        <v>44.42967424579171</v>
       </c>
       <c r="E158" t="n">
-        <v>44.98720479275436</v>
+        <v>44.98720860256699</v>
       </c>
       <c r="F158" t="n">
         <v>3391068</v>
@@ -3592,16 +3592,16 @@
         <v>44383</v>
       </c>
       <c r="B159" t="n">
-        <v>44.37199401855469</v>
+        <v>44.37199783325195</v>
       </c>
       <c r="C159" t="n">
-        <v>45.94847158903642</v>
+        <v>45.94847553926477</v>
       </c>
       <c r="D159" t="n">
-        <v>43.75678453900221</v>
+        <v>43.75678830080941</v>
       </c>
       <c r="E159" t="n">
-        <v>45.7850548143543</v>
+        <v>45.78505875053358</v>
       </c>
       <c r="F159" t="n">
         <v>1563442</v>
@@ -3652,16 +3652,16 @@
         <v>44389</v>
       </c>
       <c r="B162" t="n">
-        <v>44.72766876220703</v>
+        <v>44.72766494750977</v>
       </c>
       <c r="C162" t="n">
-        <v>45.75622090541913</v>
+        <v>45.75621700299953</v>
       </c>
       <c r="D162" t="n">
-        <v>44.08361789020423</v>
+        <v>44.08361413043626</v>
       </c>
       <c r="E162" t="n">
-        <v>45.75622090541913</v>
+        <v>45.75621700299953</v>
       </c>
       <c r="F162" t="n">
         <v>1597780</v>
@@ -3732,16 +3732,16 @@
         <v>44393</v>
       </c>
       <c r="B166" t="n">
-        <v>41.70928955078125</v>
+        <v>41.70929336547852</v>
       </c>
       <c r="C166" t="n">
-        <v>41.91115645117827</v>
+        <v>41.91116028433812</v>
       </c>
       <c r="D166" t="n">
-        <v>40.45003298811638</v>
+        <v>40.45003668764308</v>
       </c>
       <c r="E166" t="n">
-        <v>41.62277677100059</v>
+        <v>41.62278057778546</v>
       </c>
       <c r="F166" t="n">
         <v>1471156</v>
@@ -3752,16 +3752,16 @@
         <v>44396</v>
       </c>
       <c r="B167" t="n">
-        <v>40.22894287109375</v>
+        <v>40.22894668579102</v>
       </c>
       <c r="C167" t="n">
-        <v>41.05562800061862</v>
+        <v>41.05563189370605</v>
       </c>
       <c r="D167" t="n">
-        <v>39.50799183094843</v>
+        <v>39.50799557728174</v>
       </c>
       <c r="E167" t="n">
-        <v>40.46925613690023</v>
+        <v>40.46925997438512</v>
       </c>
       <c r="F167" t="n">
         <v>1632835</v>
@@ -3792,16 +3792,16 @@
         <v>44398</v>
       </c>
       <c r="B169" t="n">
-        <v>40.45964431762695</v>
+        <v>40.45964813232422</v>
       </c>
       <c r="C169" t="n">
-        <v>41.40168732645247</v>
+        <v>41.40169122996932</v>
       </c>
       <c r="D169" t="n">
-        <v>40.22894357839657</v>
+        <v>40.22894737134245</v>
       </c>
       <c r="E169" t="n">
-        <v>40.37313154041556</v>
+        <v>40.37313534695605</v>
       </c>
       <c r="F169" t="n">
         <v>985812</v>
@@ -3812,16 +3812,16 @@
         <v>44399</v>
       </c>
       <c r="B170" t="n">
-        <v>40.89221954345703</v>
+        <v>40.89221572875977</v>
       </c>
       <c r="C170" t="n">
-        <v>41.15176164706832</v>
+        <v>41.15175780815924</v>
       </c>
       <c r="D170" t="n">
-        <v>40.3923603996445</v>
+        <v>40.39235663157741</v>
       </c>
       <c r="E170" t="n">
-        <v>41.08447017755746</v>
+        <v>41.08446634492577</v>
       </c>
       <c r="F170" t="n">
         <v>757704</v>
@@ -3832,16 +3832,16 @@
         <v>44400</v>
       </c>
       <c r="B171" t="n">
-        <v>40.56538772583008</v>
+        <v>40.56539154052734</v>
       </c>
       <c r="C171" t="n">
-        <v>40.86337994162768</v>
+        <v>40.8633837843476</v>
       </c>
       <c r="D171" t="n">
-        <v>40.20010404382616</v>
+        <v>40.20010782417279</v>
       </c>
       <c r="E171" t="n">
-        <v>40.6230629132279</v>
+        <v>40.62306673334884</v>
       </c>
       <c r="F171" t="n">
         <v>715496</v>
@@ -3872,16 +3872,16 @@
         <v>44404</v>
       </c>
       <c r="B173" t="n">
-        <v>38.54673004150391</v>
+        <v>38.54673385620117</v>
       </c>
       <c r="C173" t="n">
-        <v>40.84415499320262</v>
+        <v>40.84415903525979</v>
       </c>
       <c r="D173" t="n">
-        <v>38.32563807495276</v>
+        <v>38.32564186777011</v>
       </c>
       <c r="E173" t="n">
-        <v>40.62306302665147</v>
+        <v>40.62306704682872</v>
       </c>
       <c r="F173" t="n">
         <v>1543819</v>
@@ -3932,16 +3932,16 @@
         <v>44407</v>
       </c>
       <c r="B176" t="n">
-        <v>37.2105712890625</v>
+        <v>37.21057510375977</v>
       </c>
       <c r="C176" t="n">
-        <v>38.26796091589321</v>
+        <v>38.26796483899034</v>
       </c>
       <c r="D176" t="n">
-        <v>36.33581974675896</v>
+        <v>36.33582347177977</v>
       </c>
       <c r="E176" t="n">
-        <v>37.5662386749276</v>
+        <v>37.56624252608663</v>
       </c>
       <c r="F176" t="n">
         <v>1168442</v>
@@ -3952,16 +3952,16 @@
         <v>44410</v>
       </c>
       <c r="B177" t="n">
-        <v>39.04658889770508</v>
+        <v>39.04659271240234</v>
       </c>
       <c r="C177" t="n">
-        <v>40.3442955992922</v>
+        <v>40.34429954077027</v>
       </c>
       <c r="D177" t="n">
-        <v>38.19106237864987</v>
+        <v>38.19106610976557</v>
       </c>
       <c r="E177" t="n">
-        <v>39.17155180323623</v>
+        <v>39.17155563014188</v>
       </c>
       <c r="F177" t="n">
         <v>3352028</v>
@@ -4052,16 +4052,16 @@
         <v>44417</v>
       </c>
       <c r="B182" t="n">
-        <v>37.10483169555664</v>
+        <v>37.10483551025391</v>
       </c>
       <c r="C182" t="n">
-        <v>37.44127403795907</v>
+        <v>37.44127788724551</v>
       </c>
       <c r="D182" t="n">
-        <v>35.94170042028153</v>
+        <v>35.94170411539885</v>
       </c>
       <c r="E182" t="n">
-        <v>36.1147297309109</v>
+        <v>36.11473344381713</v>
       </c>
       <c r="F182" t="n">
         <v>1206460</v>
@@ -4092,16 +4092,16 @@
         <v>44419</v>
       </c>
       <c r="B184" t="n">
-        <v>36.43194580078125</v>
+        <v>36.43194961547852</v>
       </c>
       <c r="C184" t="n">
-        <v>36.74916307008678</v>
+        <v>36.74916691799907</v>
       </c>
       <c r="D184" t="n">
-        <v>36.09550346955268</v>
+        <v>36.09550724902192</v>
       </c>
       <c r="E184" t="n">
-        <v>36.47039592462733</v>
+        <v>36.4703997433506</v>
       </c>
       <c r="F184" t="n">
         <v>786524</v>
@@ -4112,16 +4112,16 @@
         <v>44420</v>
       </c>
       <c r="B185" t="n">
-        <v>36.12434387207031</v>
+        <v>36.12434005737305</v>
       </c>
       <c r="C185" t="n">
-        <v>36.95103284178433</v>
+        <v>36.95102893978947</v>
       </c>
       <c r="D185" t="n">
-        <v>35.4706842206967</v>
+        <v>35.47068047502529</v>
       </c>
       <c r="E185" t="n">
-        <v>36.19163159403436</v>
+        <v>36.19162777223157</v>
       </c>
       <c r="F185" t="n">
         <v>689639</v>
@@ -4132,16 +4132,16 @@
         <v>44421</v>
       </c>
       <c r="B186" t="n">
-        <v>34.75934219360352</v>
+        <v>34.75934600830078</v>
       </c>
       <c r="C186" t="n">
-        <v>35.97053605946554</v>
+        <v>35.97054000708643</v>
       </c>
       <c r="D186" t="n">
-        <v>34.59592917071041</v>
+        <v>34.59593296747376</v>
       </c>
       <c r="E186" t="n">
-        <v>35.69177266747142</v>
+        <v>35.69177658449917</v>
       </c>
       <c r="F186" t="n">
         <v>915908</v>
@@ -4252,16 +4252,16 @@
         <v>44431</v>
       </c>
       <c r="B192" t="n">
-        <v>33.16364288330078</v>
+        <v>33.16364669799805</v>
       </c>
       <c r="C192" t="n">
-        <v>34.42289938524034</v>
+        <v>34.42290334478545</v>
       </c>
       <c r="D192" t="n">
-        <v>32.77913791079774</v>
+        <v>32.77914168126674</v>
       </c>
       <c r="E192" t="n">
-        <v>33.740402215843</v>
+        <v>33.74040609688286</v>
       </c>
       <c r="F192" t="n">
         <v>2084044</v>
@@ -4272,16 +4272,16 @@
         <v>44432</v>
       </c>
       <c r="B193" t="n">
-        <v>35.43223571777344</v>
+        <v>35.43223190307617</v>
       </c>
       <c r="C193" t="n">
-        <v>35.43223571777344</v>
+        <v>35.43223190307617</v>
       </c>
       <c r="D193" t="n">
-        <v>33.47125292620207</v>
+        <v>33.47124932262768</v>
       </c>
       <c r="E193" t="n">
-        <v>33.93266196453976</v>
+        <v>33.93265831128927</v>
       </c>
       <c r="F193" t="n">
         <v>1429663</v>
@@ -4332,16 +4332,16 @@
         <v>44435</v>
       </c>
       <c r="B196" t="n">
-        <v>36.43194580078125</v>
+        <v>36.43194961547852</v>
       </c>
       <c r="C196" t="n">
-        <v>36.66265029143312</v>
+        <v>36.66265413028687</v>
       </c>
       <c r="D196" t="n">
-        <v>35.02849754252244</v>
+        <v>35.02850121026817</v>
       </c>
       <c r="E196" t="n">
-        <v>35.75906113832411</v>
+        <v>35.75906488256532</v>
       </c>
       <c r="F196" t="n">
         <v>2701327</v>
@@ -4392,16 +4392,16 @@
         <v>44440</v>
       </c>
       <c r="B199" t="n">
-        <v>36.00899124145508</v>
+        <v>36.00899505615234</v>
       </c>
       <c r="C199" t="n">
-        <v>37.22979768253502</v>
+        <v>37.2298016265613</v>
       </c>
       <c r="D199" t="n">
-        <v>35.47068200422877</v>
+        <v>35.47068576189898</v>
       </c>
       <c r="E199" t="n">
-        <v>37.10483103054919</v>
+        <v>37.10483496133683</v>
       </c>
       <c r="F199" t="n">
         <v>1150659</v>
@@ -4712,16 +4712,16 @@
         <v>44463</v>
       </c>
       <c r="B215" t="n">
-        <v>34.54786682128906</v>
+        <v>34.54787063598633</v>
       </c>
       <c r="C215" t="n">
-        <v>35.65331911097231</v>
+        <v>35.65332304773112</v>
       </c>
       <c r="D215" t="n">
-        <v>33.88459095038866</v>
+        <v>33.88459469184851</v>
       </c>
       <c r="E215" t="n">
-        <v>34.46135404370111</v>
+        <v>34.46135784884584</v>
       </c>
       <c r="F215" t="n">
         <v>2639905</v>
@@ -4852,16 +4852,16 @@
         <v>44474</v>
       </c>
       <c r="B222" t="n">
-        <v>41.23827362060547</v>
+        <v>41.2382698059082</v>
       </c>
       <c r="C222" t="n">
-        <v>43.07428962557536</v>
+        <v>43.07428564103963</v>
       </c>
       <c r="D222" t="n">
-        <v>40.9498939275561</v>
+        <v>40.94989013953506</v>
       </c>
       <c r="E222" t="n">
-        <v>41.82464553821999</v>
+        <v>41.82464166928109</v>
       </c>
       <c r="F222" t="n">
         <v>3033780</v>
@@ -4952,16 +4952,16 @@
         <v>44482</v>
       </c>
       <c r="B227" t="n">
-        <v>39.66179656982422</v>
+        <v>39.66180038452148</v>
       </c>
       <c r="C227" t="n">
-        <v>40.05591407830239</v>
+        <v>40.05591793090613</v>
       </c>
       <c r="D227" t="n">
-        <v>38.88317033604628</v>
+        <v>38.88317407585477</v>
       </c>
       <c r="E227" t="n">
-        <v>39.43109208415942</v>
+        <v>39.43109587666738</v>
       </c>
       <c r="F227" t="n">
         <v>1130628</v>
@@ -5012,16 +5012,16 @@
         <v>44487</v>
       </c>
       <c r="B230" t="n">
-        <v>39.87327194213867</v>
+        <v>39.87327575683594</v>
       </c>
       <c r="C230" t="n">
-        <v>41.44974945917212</v>
+        <v>41.44975342469183</v>
       </c>
       <c r="D230" t="n">
-        <v>39.18116223800101</v>
+        <v>39.18116598648377</v>
       </c>
       <c r="E230" t="n">
-        <v>39.72908398193304</v>
+        <v>39.72908778283576</v>
       </c>
       <c r="F230" t="n">
         <v>2573169</v>
@@ -5032,16 +5032,16 @@
         <v>44488</v>
       </c>
       <c r="B231" t="n">
-        <v>37.58546447753906</v>
+        <v>37.58546829223633</v>
       </c>
       <c r="C231" t="n">
-        <v>40.08475250621378</v>
+        <v>40.08475657457366</v>
       </c>
       <c r="D231" t="n">
-        <v>36.86451716082918</v>
+        <v>36.86452090235465</v>
       </c>
       <c r="E231" t="n">
-        <v>39.57528087049455</v>
+        <v>39.57528488714614</v>
       </c>
       <c r="F231" t="n">
         <v>2915331</v>
@@ -5072,16 +5072,16 @@
         <v>44490</v>
       </c>
       <c r="B233" t="n">
-        <v>34.41328811645508</v>
+        <v>34.41329193115234</v>
       </c>
       <c r="C233" t="n">
-        <v>36.09550352264783</v>
+        <v>36.09550752381791</v>
       </c>
       <c r="D233" t="n">
-        <v>33.48086136908995</v>
+        <v>33.48086508042814</v>
       </c>
       <c r="E233" t="n">
-        <v>35.62448200968972</v>
+        <v>35.62448595864728</v>
       </c>
       <c r="F233" t="n">
         <v>3113087</v>
@@ -5092,16 +5092,16 @@
         <v>44491</v>
       </c>
       <c r="B234" t="n">
-        <v>32.63494873046875</v>
+        <v>32.63495254516602</v>
       </c>
       <c r="C234" t="n">
-        <v>34.06723464208851</v>
+        <v>34.06723862420559</v>
       </c>
       <c r="D234" t="n">
-        <v>31.04886231697067</v>
+        <v>31.04886594627039</v>
       </c>
       <c r="E234" t="n">
-        <v>33.63466698298016</v>
+        <v>33.63467091453443</v>
       </c>
       <c r="F234" t="n">
         <v>4894520</v>
@@ -5112,16 +5112,16 @@
         <v>44494</v>
       </c>
       <c r="B235" t="n">
-        <v>36.8470573425293</v>
+        <v>36.84706115722656</v>
       </c>
       <c r="C235" t="n">
-        <v>37.3112732591762</v>
+        <v>37.31127712193275</v>
       </c>
       <c r="D235" t="n">
-        <v>32.95925887799699</v>
+        <v>32.95926229019877</v>
       </c>
       <c r="E235" t="n">
-        <v>32.95925887799699</v>
+        <v>32.95926229019877</v>
       </c>
       <c r="F235" t="n">
         <v>3449995</v>
@@ -5152,16 +5152,16 @@
         <v>44496</v>
       </c>
       <c r="B237" t="n">
-        <v>35.29000854492188</v>
+        <v>35.29000473022461</v>
       </c>
       <c r="C237" t="n">
-        <v>36.07337184605893</v>
+        <v>36.07336794668348</v>
       </c>
       <c r="D237" t="n">
-        <v>34.47763151058894</v>
+        <v>34.47762778370612</v>
       </c>
       <c r="E237" t="n">
-        <v>36.07337184605893</v>
+        <v>36.07336794668348</v>
       </c>
       <c r="F237" t="n">
         <v>2270538</v>
@@ -5272,16 +5272,16 @@
         <v>44505</v>
       </c>
       <c r="B243" t="n">
-        <v>34.33255767822266</v>
+        <v>34.33256149291992</v>
       </c>
       <c r="C243" t="n">
-        <v>35.80257411368536</v>
+        <v>35.80257809171644</v>
       </c>
       <c r="D243" t="n">
-        <v>31.73102080869616</v>
+        <v>31.73102433433615</v>
       </c>
       <c r="E243" t="n">
-        <v>33.17202351532898</v>
+        <v>33.17202720107906</v>
       </c>
       <c r="F243" t="n">
         <v>9166770</v>
@@ -5312,16 +5312,16 @@
         <v>44509</v>
       </c>
       <c r="B245" t="n">
-        <v>34.50664138793945</v>
+        <v>34.50664520263672</v>
       </c>
       <c r="C245" t="n">
-        <v>35.1062534768846</v>
+        <v>35.10625735786877</v>
       </c>
       <c r="D245" t="n">
-        <v>32.63044017132788</v>
+        <v>32.63044377861175</v>
       </c>
       <c r="E245" t="n">
-        <v>33.89736055406007</v>
+        <v>33.89736430140155</v>
       </c>
       <c r="F245" t="n">
         <v>7032350</v>
@@ -5372,16 +5372,16 @@
         <v>44512</v>
       </c>
       <c r="B248" t="n">
-        <v>30.94766044616699</v>
+        <v>30.94766235351562</v>
       </c>
       <c r="C248" t="n">
-        <v>33.11399707089411</v>
+        <v>33.11399911175717</v>
       </c>
       <c r="D248" t="n">
-        <v>30.69620937113922</v>
+        <v>30.69621126299056</v>
       </c>
       <c r="E248" t="n">
-        <v>32.10819651835855</v>
+        <v>32.10819849723269</v>
       </c>
       <c r="F248" t="n">
         <v>3403064</v>
@@ -5552,16 +5552,16 @@
         <v>44526</v>
       </c>
       <c r="B257" t="n">
-        <v>26.69235801696777</v>
+        <v>26.69235992431641</v>
       </c>
       <c r="C257" t="n">
-        <v>27.61111551515892</v>
+        <v>27.61111748815896</v>
       </c>
       <c r="D257" t="n">
-        <v>25.85096734243463</v>
+        <v>25.85096918966023</v>
       </c>
       <c r="E257" t="n">
-        <v>26.59564620826666</v>
+        <v>26.59564810870458</v>
       </c>
       <c r="F257" t="n">
         <v>3664026</v>
@@ -5592,16 +5592,16 @@
         <v>44530</v>
       </c>
       <c r="B259" t="n">
-        <v>26.71169853210449</v>
+        <v>26.71170043945312</v>
       </c>
       <c r="C259" t="n">
-        <v>26.71169853210449</v>
+        <v>26.71170043945312</v>
       </c>
       <c r="D259" t="n">
-        <v>25.48346440355603</v>
+        <v>25.48346622320262</v>
       </c>
       <c r="E259" t="n">
-        <v>26.53761803066504</v>
+        <v>26.53761992558345</v>
       </c>
       <c r="F259" t="n">
         <v>4757647</v>
@@ -5612,16 +5612,16 @@
         <v>44531</v>
       </c>
       <c r="B260" t="n">
-        <v>26.69235801696777</v>
+        <v>26.69235992431641</v>
       </c>
       <c r="C260" t="n">
-        <v>28.01730398743094</v>
+        <v>28.01730598945588</v>
       </c>
       <c r="D260" t="n">
-        <v>26.32485389341864</v>
+        <v>26.32485577450663</v>
       </c>
       <c r="E260" t="n">
-        <v>27.17591518668557</v>
+        <v>27.17591712858762</v>
       </c>
       <c r="F260" t="n">
         <v>3467467</v>
@@ -5752,16 +5752,16 @@
         <v>44540</v>
       </c>
       <c r="B267" t="n">
-        <v>29.43896293640137</v>
+        <v>29.43896102905273</v>
       </c>
       <c r="C267" t="n">
-        <v>29.76778272429381</v>
+        <v>29.76778079564096</v>
       </c>
       <c r="D267" t="n">
-        <v>28.76198212238038</v>
+        <v>28.76198025889329</v>
       </c>
       <c r="E267" t="n">
-        <v>29.57435909920557</v>
+        <v>29.57435718308462</v>
       </c>
       <c r="F267" t="n">
         <v>1281952</v>
@@ -5832,16 +5832,16 @@
         <v>44546</v>
       </c>
       <c r="B271" t="n">
-        <v>30.62851333618164</v>
+        <v>30.62851524353027</v>
       </c>
       <c r="C271" t="n">
-        <v>30.86062130141829</v>
+        <v>30.86062322322113</v>
       </c>
       <c r="D271" t="n">
-        <v>29.25521052973079</v>
+        <v>29.25521235155887</v>
       </c>
       <c r="E271" t="n">
-        <v>29.4969891136642</v>
+        <v>29.49699095054871</v>
       </c>
       <c r="F271" t="n">
         <v>3477726</v>
@@ -5952,16 +5952,16 @@
         <v>44557</v>
       </c>
       <c r="B277" t="n">
-        <v>30.72522354125977</v>
+        <v>30.7252254486084</v>
       </c>
       <c r="C277" t="n">
-        <v>31.01535896880716</v>
+        <v>31.01536089416671</v>
       </c>
       <c r="D277" t="n">
-        <v>29.98054654550914</v>
+        <v>29.98054840663</v>
       </c>
       <c r="E277" t="n">
-        <v>29.98054654550914</v>
+        <v>29.98054840663</v>
       </c>
       <c r="F277" t="n">
         <v>1273927</v>
@@ -6132,16 +6132,16 @@
         <v>44571</v>
       </c>
       <c r="B286" t="n">
-        <v>33.37511444091797</v>
+        <v>33.37511825561523</v>
       </c>
       <c r="C286" t="n">
-        <v>33.89735778992546</v>
+        <v>33.89736166431392</v>
       </c>
       <c r="D286" t="n">
-        <v>32.24359030771443</v>
+        <v>32.24359399308115</v>
       </c>
       <c r="E286" t="n">
-        <v>32.37898645393302</v>
+        <v>32.3789901547752</v>
       </c>
       <c r="F286" t="n">
         <v>2829132</v>
@@ -6152,16 +6152,16 @@
         <v>44572</v>
       </c>
       <c r="B287" t="n">
-        <v>35.10625457763672</v>
+        <v>35.10625076293945</v>
       </c>
       <c r="C287" t="n">
-        <v>35.63816673084244</v>
+        <v>35.63816285834681</v>
       </c>
       <c r="D287" t="n">
-        <v>33.18169458570739</v>
+        <v>33.18169098013564</v>
       </c>
       <c r="E287" t="n">
-        <v>33.55886933935793</v>
+        <v>33.55886569280182</v>
       </c>
       <c r="F287" t="n">
         <v>3953735</v>
@@ -6172,16 +6172,16 @@
         <v>44573</v>
       </c>
       <c r="B288" t="n">
-        <v>34.89348983764648</v>
+        <v>34.89348602294922</v>
       </c>
       <c r="C288" t="n">
-        <v>35.98632787872025</v>
+        <v>35.98632394454952</v>
       </c>
       <c r="D288" t="n">
-        <v>34.13914032772324</v>
+        <v>34.13913659549451</v>
       </c>
       <c r="E288" t="n">
-        <v>35.34803329265463</v>
+        <v>35.34802942826484</v>
       </c>
       <c r="F288" t="n">
         <v>3302601</v>
@@ -6292,16 +6292,16 @@
         <v>44581</v>
       </c>
       <c r="B294" t="n">
-        <v>35.29967498779297</v>
+        <v>35.2996711730957</v>
       </c>
       <c r="C294" t="n">
-        <v>36.17007943172774</v>
+        <v>36.17007552296929</v>
       </c>
       <c r="D294" t="n">
-        <v>34.98052769103708</v>
+        <v>34.98052391082881</v>
       </c>
       <c r="E294" t="n">
-        <v>35.87027337331519</v>
+        <v>35.8702694969556</v>
       </c>
       <c r="F294" t="n">
         <v>3650414</v>
@@ -6332,16 +6332,16 @@
         <v>44585</v>
       </c>
       <c r="B296" t="n">
-        <v>34.35190200805664</v>
+        <v>34.35190582275391</v>
       </c>
       <c r="C296" t="n">
-        <v>35.3190162904272</v>
+        <v>35.31902021252021</v>
       </c>
       <c r="D296" t="n">
-        <v>34.05209598090971</v>
+        <v>34.05209976231423</v>
       </c>
       <c r="E296" t="n">
-        <v>34.23584709494806</v>
+        <v>34.2358508967577</v>
       </c>
       <c r="F296" t="n">
         <v>2113697</v>
@@ -6392,16 +6392,16 @@
         <v>44588</v>
       </c>
       <c r="B299" t="n">
-        <v>36.09271240234375</v>
+        <v>36.09270858764648</v>
       </c>
       <c r="C299" t="n">
-        <v>37.1081818022467</v>
+        <v>37.10817788022283</v>
       </c>
       <c r="D299" t="n">
-        <v>35.68652389286739</v>
+        <v>35.68652012110085</v>
       </c>
       <c r="E299" t="n">
-        <v>35.87994752798603</v>
+        <v>35.87994373577622</v>
       </c>
       <c r="F299" t="n">
         <v>3171460</v>
@@ -6492,16 +6492,16 @@
         <v>44595</v>
       </c>
       <c r="B304" t="n">
-        <v>35.29967498779297</v>
+        <v>35.2996711730957</v>
       </c>
       <c r="C304" t="n">
-        <v>35.58981230082171</v>
+        <v>35.58980845477045</v>
       </c>
       <c r="D304" t="n">
-        <v>33.84900341295216</v>
+        <v>33.84899975502328</v>
       </c>
       <c r="E304" t="n">
-        <v>34.98052769103708</v>
+        <v>34.98052391082881</v>
       </c>
       <c r="F304" t="n">
         <v>4177823</v>
@@ -6592,16 +6592,16 @@
         <v>44602</v>
       </c>
       <c r="B309" t="n">
-        <v>37.28226470947266</v>
+        <v>37.28226089477539</v>
       </c>
       <c r="C309" t="n">
-        <v>38.3847753224369</v>
+        <v>38.38477139493146</v>
       </c>
       <c r="D309" t="n">
-        <v>36.33449150769526</v>
+        <v>36.33448778997354</v>
       </c>
       <c r="E309" t="n">
-        <v>36.36350524073979</v>
+        <v>36.3635015200494</v>
       </c>
       <c r="F309" t="n">
         <v>7025951</v>
@@ -6612,16 +6612,16 @@
         <v>44603</v>
       </c>
       <c r="B310" t="n">
-        <v>38.07529067993164</v>
+        <v>38.07529449462891</v>
       </c>
       <c r="C310" t="n">
-        <v>38.49115162219439</v>
+        <v>38.49115547855604</v>
       </c>
       <c r="D310" t="n">
-        <v>37.37896869306991</v>
+        <v>37.37897243800389</v>
       </c>
       <c r="E310" t="n">
-        <v>37.78515714333515</v>
+        <v>37.78516092896444</v>
       </c>
       <c r="F310" t="n">
         <v>5486491</v>
@@ -6632,16 +6632,16 @@
         <v>44606</v>
       </c>
       <c r="B311" t="n">
-        <v>37.57239151000977</v>
+        <v>37.57239532470703</v>
       </c>
       <c r="C311" t="n">
-        <v>38.84898429079868</v>
+        <v>38.84898823510746</v>
       </c>
       <c r="D311" t="n">
-        <v>36.95343822941596</v>
+        <v>36.95344198127135</v>
       </c>
       <c r="E311" t="n">
-        <v>38.29772721003804</v>
+        <v>38.2977310983781</v>
       </c>
       <c r="F311" t="n">
         <v>3902640</v>
@@ -6652,16 +6652,16 @@
         <v>44607</v>
       </c>
       <c r="B312" t="n">
-        <v>35.79290008544922</v>
+        <v>35.79290390014648</v>
       </c>
       <c r="C312" t="n">
-        <v>36.65363192612031</v>
+        <v>36.65363583255173</v>
       </c>
       <c r="D312" t="n">
-        <v>35.63816270338088</v>
+        <v>35.63816650158672</v>
       </c>
       <c r="E312" t="n">
-        <v>36.55692199922141</v>
+        <v>36.55692589534578</v>
       </c>
       <c r="F312" t="n">
         <v>3810709</v>
@@ -6672,16 +6672,16 @@
         <v>44608</v>
       </c>
       <c r="B313" t="n">
-        <v>35.92830276489258</v>
+        <v>35.92829895019531</v>
       </c>
       <c r="C313" t="n">
-        <v>36.80837600146183</v>
+        <v>36.80837209332255</v>
       </c>
       <c r="D313" t="n">
-        <v>35.69619664958365</v>
+        <v>35.69619285953032</v>
       </c>
       <c r="E313" t="n">
-        <v>36.44087371532872</v>
+        <v>36.4408698462091</v>
       </c>
       <c r="F313" t="n">
         <v>4244663</v>
@@ -6692,16 +6692,16 @@
         <v>44609</v>
       </c>
       <c r="B314" t="n">
-        <v>35.29967498779297</v>
+        <v>35.2996711730957</v>
       </c>
       <c r="C314" t="n">
-        <v>35.89928710461807</v>
+        <v>35.89928322512308</v>
       </c>
       <c r="D314" t="n">
-        <v>34.41960179847439</v>
+        <v>34.41959807888318</v>
       </c>
       <c r="E314" t="n">
-        <v>35.68652224011414</v>
+        <v>35.68651838361181</v>
       </c>
       <c r="F314" t="n">
         <v>4430658</v>
@@ -6712,16 +6712,16 @@
         <v>44610</v>
       </c>
       <c r="B315" t="n">
-        <v>34.48730087280273</v>
+        <v>34.48729705810547</v>
       </c>
       <c r="C315" t="n">
-        <v>35.41572900804387</v>
+        <v>35.41572509065163</v>
       </c>
       <c r="D315" t="n">
-        <v>33.80064757961473</v>
+        <v>33.80064384086931</v>
       </c>
       <c r="E315" t="n">
-        <v>34.83546189196511</v>
+        <v>34.83545803875718</v>
       </c>
       <c r="F315" t="n">
         <v>4069741</v>
@@ -6852,16 +6852,16 @@
         <v>44623</v>
       </c>
       <c r="B322" t="n">
-        <v>37.34028625488281</v>
+        <v>37.34028244018555</v>
       </c>
       <c r="C322" t="n">
-        <v>37.88187465766974</v>
+        <v>37.88187078764361</v>
       </c>
       <c r="D322" t="n">
-        <v>36.31514815474819</v>
+        <v>36.31514444477941</v>
       </c>
       <c r="E322" t="n">
-        <v>37.12752138998924</v>
+        <v>37.12751759702811</v>
       </c>
       <c r="F322" t="n">
         <v>9786414</v>
@@ -6892,16 +6892,16 @@
         <v>44627</v>
       </c>
       <c r="B324" t="n">
-        <v>37.04048156738281</v>
+        <v>37.04048538208008</v>
       </c>
       <c r="C324" t="n">
-        <v>39.28418499781101</v>
+        <v>39.28418904358112</v>
       </c>
       <c r="D324" t="n">
-        <v>36.65363433916909</v>
+        <v>36.65363811402602</v>
       </c>
       <c r="E324" t="n">
-        <v>38.17200577495368</v>
+        <v>38.17200970618351</v>
       </c>
       <c r="F324" t="n">
         <v>5025922</v>
@@ -6952,16 +6952,16 @@
         <v>44630</v>
       </c>
       <c r="B327" t="n">
-        <v>35.7252082824707</v>
+        <v>35.72520446777344</v>
       </c>
       <c r="C327" t="n">
-        <v>37.22423481932497</v>
+        <v>37.22423084456335</v>
       </c>
       <c r="D327" t="n">
-        <v>35.51244341905014</v>
+        <v>35.51243962707166</v>
       </c>
       <c r="E327" t="n">
-        <v>36.75034637550812</v>
+        <v>36.75034245134777</v>
       </c>
       <c r="F327" t="n">
         <v>4502679</v>
@@ -7032,16 +7032,16 @@
         <v>44636</v>
       </c>
       <c r="B331" t="n">
-        <v>32.84320449829102</v>
+        <v>32.84320831298828</v>
       </c>
       <c r="C331" t="n">
-        <v>34.44861337459189</v>
+        <v>34.44861737575539</v>
       </c>
       <c r="D331" t="n">
-        <v>32.34030609979657</v>
+        <v>32.34030985608281</v>
       </c>
       <c r="E331" t="n">
-        <v>34.10045236831488</v>
+        <v>34.10045632903992</v>
       </c>
       <c r="F331" t="n">
         <v>3899288</v>
@@ -7092,16 +7092,16 @@
         <v>44641</v>
       </c>
       <c r="B334" t="n">
-        <v>36.61494827270508</v>
+        <v>36.61495208740234</v>
       </c>
       <c r="C334" t="n">
-        <v>36.86639934686866</v>
+        <v>36.86640318776314</v>
       </c>
       <c r="D334" t="n">
-        <v>35.88961252740777</v>
+        <v>35.88961626653654</v>
       </c>
       <c r="E334" t="n">
-        <v>35.97665371626157</v>
+        <v>35.97665746445866</v>
       </c>
       <c r="F334" t="n">
         <v>3600944</v>
@@ -7212,16 +7212,16 @@
         <v>44649</v>
       </c>
       <c r="B340" t="n">
-        <v>40.11590194702148</v>
+        <v>40.11590576171875</v>
       </c>
       <c r="C340" t="n">
-        <v>40.60913158587444</v>
+        <v>40.60913544747385</v>
       </c>
       <c r="D340" t="n">
-        <v>37.81417112752509</v>
+        <v>37.8141747233464</v>
       </c>
       <c r="E340" t="n">
-        <v>38.00759473575618</v>
+        <v>38.00759834997051</v>
       </c>
       <c r="F340" t="n">
         <v>6952609</v>
@@ -7252,16 +7252,16 @@
         <v>44651</v>
       </c>
       <c r="B342" t="n">
-        <v>40.47373962402344</v>
+        <v>40.47373580932617</v>
       </c>
       <c r="C342" t="n">
-        <v>41.13137921056172</v>
+        <v>41.13137533388116</v>
       </c>
       <c r="D342" t="n">
-        <v>39.67103512697872</v>
+        <v>39.6710313879373</v>
       </c>
       <c r="E342" t="n">
-        <v>40.135251085266</v>
+        <v>40.13524730247168</v>
       </c>
       <c r="F342" t="n">
         <v>3810811</v>
@@ -7312,16 +7312,16 @@
         <v>44656</v>
       </c>
       <c r="B345" t="n">
-        <v>41.97276306152344</v>
+        <v>41.9727668762207</v>
       </c>
       <c r="C345" t="n">
-        <v>43.03659106395681</v>
+        <v>43.03659497534015</v>
       </c>
       <c r="D345" t="n">
-        <v>41.57624708903781</v>
+        <v>41.5762508676977</v>
       </c>
       <c r="E345" t="n">
-        <v>42.30158283032514</v>
+        <v>42.30158667490721</v>
       </c>
       <c r="F345" t="n">
         <v>5903074</v>
@@ -7432,16 +7432,16 @@
         <v>44664</v>
       </c>
       <c r="B351" t="n">
-        <v>43.62652969360352</v>
+        <v>43.62653350830078</v>
       </c>
       <c r="C351" t="n">
-        <v>43.71356713249195</v>
+        <v>43.71357095479976</v>
       </c>
       <c r="D351" t="n">
-        <v>42.8431665105797</v>
+        <v>42.8431702567798</v>
       </c>
       <c r="E351" t="n">
-        <v>43.30738242414481</v>
+        <v>43.30738621093589</v>
       </c>
       <c r="F351" t="n">
         <v>3238402</v>
@@ -7452,16 +7452,16 @@
         <v>44665</v>
       </c>
       <c r="B352" t="n">
-        <v>42.93988037109375</v>
+        <v>42.93987655639648</v>
       </c>
       <c r="C352" t="n">
-        <v>43.62653368593358</v>
+        <v>43.62652981023535</v>
       </c>
       <c r="D352" t="n">
-        <v>42.2242170723533</v>
+        <v>42.2242133212342</v>
       </c>
       <c r="E352" t="n">
-        <v>43.62653368593358</v>
+        <v>43.62652981023535</v>
       </c>
       <c r="F352" t="n">
         <v>2345809</v>
@@ -7552,16 +7552,16 @@
         <v>44676</v>
       </c>
       <c r="B357" t="n">
-        <v>41.94375228881836</v>
+        <v>41.94374847412109</v>
       </c>
       <c r="C357" t="n">
-        <v>42.40796824528748</v>
+        <v>42.40796438837074</v>
       </c>
       <c r="D357" t="n">
-        <v>40.64782185452133</v>
+        <v>40.64781815768625</v>
       </c>
       <c r="E357" t="n">
-        <v>40.75420428750637</v>
+        <v>40.75420058099602</v>
       </c>
       <c r="F357" t="n">
         <v>3287465</v>
@@ -7592,16 +7592,16 @@
         <v>44678</v>
       </c>
       <c r="B359" t="n">
-        <v>42.16618728637695</v>
+        <v>42.16619110107422</v>
       </c>
       <c r="C359" t="n">
-        <v>43.58784506009413</v>
+        <v>43.58784900340616</v>
       </c>
       <c r="D359" t="n">
-        <v>41.46986526445734</v>
+        <v>41.46986901615963</v>
       </c>
       <c r="E359" t="n">
-        <v>43.52014885542929</v>
+        <v>43.52015279261696</v>
       </c>
       <c r="F359" t="n">
         <v>3779727</v>
@@ -7672,16 +7672,16 @@
         <v>44684</v>
       </c>
       <c r="B363" t="n">
-        <v>42.12750244140625</v>
+        <v>42.12749862670898</v>
       </c>
       <c r="C363" t="n">
-        <v>42.54336341820335</v>
+        <v>42.54335956584936</v>
       </c>
       <c r="D363" t="n">
-        <v>41.25710175933607</v>
+        <v>41.25709802345466</v>
       </c>
       <c r="E363" t="n">
-        <v>42.54336341820335</v>
+        <v>42.54335956584936</v>
       </c>
       <c r="F363" t="n">
         <v>4458389</v>
@@ -7692,16 +7692,16 @@
         <v>44685</v>
       </c>
       <c r="B364" t="n">
-        <v>44.10041427612305</v>
+        <v>44.10041809082031</v>
       </c>
       <c r="C364" t="n">
-        <v>44.32285161417975</v>
+        <v>44.32285544811791</v>
       </c>
       <c r="D364" t="n">
-        <v>42.16618567842227</v>
+        <v>42.16618932580826</v>
       </c>
       <c r="E364" t="n">
-        <v>43.04625879095802</v>
+        <v>43.04626251447057</v>
       </c>
       <c r="F364" t="n">
         <v>5759540</v>
@@ -7712,16 +7712,16 @@
         <v>44686</v>
       </c>
       <c r="B365" t="n">
-        <v>42.92053985595703</v>
+        <v>42.92053604125977</v>
       </c>
       <c r="C365" t="n">
-        <v>44.57430384010176</v>
+        <v>44.57429987842104</v>
       </c>
       <c r="D365" t="n">
-        <v>42.01145291457887</v>
+        <v>42.01144918067956</v>
       </c>
       <c r="E365" t="n">
-        <v>44.09074663744735</v>
+        <v>44.09074271874429</v>
       </c>
       <c r="F365" t="n">
         <v>4814532</v>
@@ -7732,16 +7732,16 @@
         <v>44687</v>
       </c>
       <c r="B366" t="n">
-        <v>42.55303573608398</v>
+        <v>42.55303192138672</v>
       </c>
       <c r="C366" t="n">
-        <v>43.90699359626386</v>
+        <v>43.90698966019007</v>
       </c>
       <c r="D366" t="n">
-        <v>41.82769996355259</v>
+        <v>41.82769621387857</v>
       </c>
       <c r="E366" t="n">
-        <v>43.33639522245434</v>
+        <v>43.33639133753226</v>
       </c>
       <c r="F366" t="n">
         <v>4093307</v>
@@ -7892,16 +7892,16 @@
         <v>44699</v>
       </c>
       <c r="B374" t="n">
-        <v>39.99985504150391</v>
+        <v>39.99985122680664</v>
       </c>
       <c r="C374" t="n">
-        <v>42.22421740419406</v>
+        <v>42.2242133773643</v>
       </c>
       <c r="D374" t="n">
-        <v>39.72906271064676</v>
+        <v>39.72905892177436</v>
       </c>
       <c r="E374" t="n">
-        <v>42.13717620908088</v>
+        <v>42.13717219055205</v>
       </c>
       <c r="F374" t="n">
         <v>1865839</v>
@@ -7952,16 +7952,16 @@
         <v>44704</v>
       </c>
       <c r="B377" t="n">
-        <v>42.28224563598633</v>
+        <v>42.28224182128906</v>
       </c>
       <c r="C377" t="n">
-        <v>42.79481657531103</v>
+        <v>42.7948127143697</v>
       </c>
       <c r="D377" t="n">
-        <v>41.35381369972519</v>
+        <v>41.3538099687909</v>
       </c>
       <c r="E377" t="n">
-        <v>41.42151365745766</v>
+        <v>41.42150992041549</v>
       </c>
       <c r="F377" t="n">
         <v>3400119</v>
@@ -8012,16 +8012,16 @@
         <v>44707</v>
       </c>
       <c r="B380" t="n">
-        <v>46.5955696105957</v>
+        <v>46.59557342529297</v>
       </c>
       <c r="C380" t="n">
-        <v>47.1661679572728</v>
+        <v>47.16617181868395</v>
       </c>
       <c r="D380" t="n">
-        <v>45.10621566046026</v>
+        <v>45.10621935322675</v>
       </c>
       <c r="E380" t="n">
-        <v>45.2512805595232</v>
+        <v>45.25128426416589</v>
       </c>
       <c r="F380" t="n">
         <v>4582217</v>
@@ -8072,16 +8072,16 @@
         <v>44712</v>
       </c>
       <c r="B383" t="n">
-        <v>47.14682769775391</v>
+        <v>47.14683151245117</v>
       </c>
       <c r="C383" t="n">
-        <v>49.5452685563496</v>
+        <v>49.54527256510714</v>
       </c>
       <c r="D383" t="n">
-        <v>47.11781396782467</v>
+        <v>47.11781778017441</v>
       </c>
       <c r="E383" t="n">
-        <v>48.22032446240879</v>
+        <v>48.22032836396376</v>
       </c>
       <c r="F383" t="n">
         <v>6322705</v>
@@ -8152,16 +8152,16 @@
         <v>44718</v>
       </c>
       <c r="B387" t="n">
-        <v>45.3189811706543</v>
+        <v>45.31898498535156</v>
       </c>
       <c r="C387" t="n">
-        <v>47.4563021942838</v>
+        <v>47.45630618888874</v>
       </c>
       <c r="D387" t="n">
-        <v>45.13522629971035</v>
+        <v>45.13523009894016</v>
       </c>
       <c r="E387" t="n">
-        <v>47.15649615191405</v>
+        <v>47.156500121283</v>
       </c>
       <c r="F387" t="n">
         <v>1711233</v>
@@ -8172,16 +8172,16 @@
         <v>44719</v>
       </c>
       <c r="B388" t="n">
-        <v>45.3189811706543</v>
+        <v>45.31898498535156</v>
       </c>
       <c r="C388" t="n">
-        <v>45.84122081100923</v>
+        <v>45.84122466966569</v>
       </c>
       <c r="D388" t="n">
-        <v>44.73871032322317</v>
+        <v>44.73871408907649</v>
       </c>
       <c r="E388" t="n">
-        <v>44.98048890609225</v>
+        <v>44.98049269229714</v>
       </c>
       <c r="F388" t="n">
         <v>1887578</v>
@@ -8192,16 +8192,16 @@
         <v>44720</v>
       </c>
       <c r="B389" t="n">
-        <v>45.25128555297852</v>
+        <v>45.25128173828125</v>
       </c>
       <c r="C389" t="n">
-        <v>46.00563510358936</v>
+        <v>46.00563122530019</v>
       </c>
       <c r="D389" t="n">
-        <v>44.92246574936335</v>
+        <v>44.9224619623857</v>
       </c>
       <c r="E389" t="n">
-        <v>45.31898551140559</v>
+        <v>45.31898169100119</v>
       </c>
       <c r="F389" t="n">
         <v>1920490</v>
@@ -8212,16 +8212,16 @@
         <v>44721</v>
       </c>
       <c r="B390" t="n">
-        <v>44.5066032409668</v>
+        <v>44.50660705566406</v>
       </c>
       <c r="C390" t="n">
-        <v>45.59944121195702</v>
+        <v>45.59944512032232</v>
       </c>
       <c r="D390" t="n">
-        <v>44.32285212169327</v>
+        <v>44.32285592064108</v>
       </c>
       <c r="E390" t="n">
-        <v>45.22226648118356</v>
+        <v>45.2222703572209</v>
       </c>
       <c r="F390" t="n">
         <v>1644697</v>
@@ -8472,16 +8472,16 @@
         <v>44741</v>
       </c>
       <c r="B403" t="n">
-        <v>34.71940612792969</v>
+        <v>34.71940994262695</v>
       </c>
       <c r="C403" t="n">
-        <v>35.41572814937177</v>
+        <v>35.41573204057546</v>
       </c>
       <c r="D403" t="n">
-        <v>34.09078031110602</v>
+        <v>34.0907840567348</v>
       </c>
       <c r="E403" t="n">
-        <v>35.29967322993957</v>
+        <v>35.29967710839206</v>
       </c>
       <c r="F403" t="n">
         <v>2690880</v>
@@ -8532,16 +8532,16 @@
         <v>44746</v>
       </c>
       <c r="B406" t="n">
-        <v>35.08691024780273</v>
+        <v>35.08690643310547</v>
       </c>
       <c r="C406" t="n">
-        <v>35.60915366553204</v>
+        <v>35.60914979405575</v>
       </c>
       <c r="D406" t="n">
-        <v>34.1971683099429</v>
+        <v>34.19716459197961</v>
       </c>
       <c r="E406" t="n">
-        <v>34.57433932306729</v>
+        <v>34.57433556409744</v>
       </c>
       <c r="F406" t="n">
         <v>2359523</v>
@@ -8612,16 +8612,16 @@
         <v>44750</v>
       </c>
       <c r="B410" t="n">
-        <v>31.81806373596191</v>
+        <v>31.81806564331055</v>
       </c>
       <c r="C410" t="n">
-        <v>32.48537204040704</v>
+        <v>32.48537398775778</v>
       </c>
       <c r="D410" t="n">
-        <v>31.19911039968697</v>
+        <v>31.19911226993215</v>
       </c>
       <c r="E410" t="n">
-        <v>31.3151653213559</v>
+        <v>31.31516719855805</v>
       </c>
       <c r="F410" t="n">
         <v>4375906</v>
@@ -8712,16 +8712,16 @@
         <v>44757</v>
       </c>
       <c r="B415" t="n">
-        <v>27.79486846923828</v>
+        <v>27.79486656188965</v>
       </c>
       <c r="C415" t="n">
-        <v>29.07146143004599</v>
+        <v>29.07145943509457</v>
       </c>
       <c r="D415" t="n">
-        <v>27.79486846923828</v>
+        <v>27.79486656188965</v>
       </c>
       <c r="E415" t="n">
-        <v>29.06178893688788</v>
+        <v>29.06178694260021</v>
       </c>
       <c r="F415" t="n">
         <v>4618481</v>
@@ -8752,16 +8752,16 @@
         <v>44761</v>
       </c>
       <c r="B417" t="n">
-        <v>29.43896293640137</v>
+        <v>29.43896102905273</v>
       </c>
       <c r="C417" t="n">
-        <v>29.53567474894549</v>
+        <v>29.5356728353309</v>
       </c>
       <c r="D417" t="n">
-        <v>28.11401691328927</v>
+        <v>28.11401509178381</v>
       </c>
       <c r="E417" t="n">
-        <v>28.14303064443129</v>
+        <v>28.14302882104603</v>
       </c>
       <c r="F417" t="n">
         <v>4570230</v>
@@ -8772,16 +8772,16 @@
         <v>44762</v>
       </c>
       <c r="B418" t="n">
-        <v>30.59950065612793</v>
+        <v>30.5994987487793</v>
       </c>
       <c r="C418" t="n">
-        <v>30.97667540990739</v>
+        <v>30.97667347904845</v>
       </c>
       <c r="D418" t="n">
-        <v>29.21652718353251</v>
+        <v>29.21652536238831</v>
       </c>
       <c r="E418" t="n">
-        <v>29.21652718353251</v>
+        <v>29.21652536238831</v>
       </c>
       <c r="F418" t="n">
         <v>5027446</v>
@@ -8792,16 +8792,16 @@
         <v>44763</v>
       </c>
       <c r="B419" t="n">
-        <v>29.44863510131836</v>
+        <v>29.44863319396973</v>
       </c>
       <c r="C419" t="n">
-        <v>29.86449233042948</v>
+        <v>29.86449039614633</v>
       </c>
       <c r="D419" t="n">
-        <v>28.83935237548546</v>
+        <v>28.83935050759925</v>
       </c>
       <c r="E419" t="n">
-        <v>29.86449233042948</v>
+        <v>29.86449039614633</v>
       </c>
       <c r="F419" t="n">
         <v>5437325</v>
@@ -8832,16 +8832,16 @@
         <v>44767</v>
       </c>
       <c r="B421" t="n">
-        <v>29.2648811340332</v>
+        <v>29.26488304138184</v>
       </c>
       <c r="C421" t="n">
-        <v>29.7194245717984</v>
+        <v>29.71942650877206</v>
       </c>
       <c r="D421" t="n">
-        <v>28.43316295561438</v>
+        <v>28.43316480875549</v>
       </c>
       <c r="E421" t="n">
-        <v>28.87803577468757</v>
+        <v>28.87803765682343</v>
       </c>
       <c r="F421" t="n">
         <v>3521914</v>
@@ -8852,16 +8852,16 @@
         <v>44768</v>
       </c>
       <c r="B422" t="n">
-        <v>28.95540428161621</v>
+        <v>28.95540618896484</v>
       </c>
       <c r="C422" t="n">
-        <v>30.15462657412001</v>
+        <v>30.15462856046375</v>
       </c>
       <c r="D422" t="n">
-        <v>28.81033750703789</v>
+        <v>28.81033940483069</v>
       </c>
       <c r="E422" t="n">
-        <v>29.88383426222034</v>
+        <v>29.88383623072646</v>
       </c>
       <c r="F422" t="n">
         <v>2984449</v>
@@ -8872,16 +8872,16 @@
         <v>44769</v>
       </c>
       <c r="B423" t="n">
-        <v>29.66139984130859</v>
+        <v>29.66139793395996</v>
       </c>
       <c r="C423" t="n">
-        <v>29.76778227135207</v>
+        <v>29.76778035716261</v>
       </c>
       <c r="D423" t="n">
-        <v>28.61691490502781</v>
+        <v>28.6169130648438</v>
       </c>
       <c r="E423" t="n">
-        <v>28.95540530688788</v>
+        <v>28.95540344493757</v>
       </c>
       <c r="F423" t="n">
         <v>2554762</v>
@@ -8892,16 +8892,16 @@
         <v>44770</v>
       </c>
       <c r="B424" t="n">
-        <v>30.78325271606445</v>
+        <v>30.78325080871582</v>
       </c>
       <c r="C424" t="n">
-        <v>30.88963514995402</v>
+        <v>30.88963323601387</v>
       </c>
       <c r="D424" t="n">
-        <v>29.53567536735125</v>
+        <v>29.53567353730325</v>
       </c>
       <c r="E424" t="n">
-        <v>29.96120510290952</v>
+        <v>29.96120324649545</v>
       </c>
       <c r="F424" t="n">
         <v>4208906</v>
@@ -8952,16 +8952,16 @@
         <v>44775</v>
       </c>
       <c r="B427" t="n">
-        <v>31.85674858093262</v>
+        <v>31.85675048828125</v>
       </c>
       <c r="C427" t="n">
-        <v>32.0791821744082</v>
+        <v>32.07918409507452</v>
       </c>
       <c r="D427" t="n">
-        <v>30.94765985359998</v>
+        <v>30.94766170651904</v>
       </c>
       <c r="E427" t="n">
-        <v>31.32483458513196</v>
+        <v>31.32483646063348</v>
       </c>
       <c r="F427" t="n">
         <v>3020206</v>
@@ -9072,16 +9072,16 @@
         <v>44783</v>
       </c>
       <c r="B433" t="n">
-        <v>33.26873397827148</v>
+        <v>33.26873779296875</v>
       </c>
       <c r="C433" t="n">
-        <v>33.97472847846024</v>
+        <v>33.97473237410905</v>
       </c>
       <c r="D433" t="n">
-        <v>32.87221800802422</v>
+        <v>32.87222177725572</v>
       </c>
       <c r="E433" t="n">
-        <v>33.62656747451073</v>
+        <v>33.62657133023831</v>
       </c>
       <c r="F433" t="n">
         <v>3325457</v>
@@ -9152,16 +9152,16 @@
         <v>44789</v>
       </c>
       <c r="B437" t="n">
-        <v>32.27260589599609</v>
+        <v>32.27260971069336</v>
       </c>
       <c r="C437" t="n">
-        <v>32.61109815484615</v>
+        <v>32.61110200955398</v>
       </c>
       <c r="D437" t="n">
-        <v>31.73102127989639</v>
+        <v>31.73102503057709</v>
       </c>
       <c r="E437" t="n">
-        <v>32.39832955774229</v>
+        <v>32.39833338730038</v>
       </c>
       <c r="F437" t="n">
         <v>2684074</v>
@@ -9172,16 +9172,16 @@
         <v>44790</v>
       </c>
       <c r="B438" t="n">
-        <v>32.53372955322266</v>
+        <v>32.53372573852539</v>
       </c>
       <c r="C438" t="n">
-        <v>32.93024931741367</v>
+        <v>32.93024545622303</v>
       </c>
       <c r="D438" t="n">
-        <v>31.80839373121048</v>
+        <v>31.80839000156146</v>
       </c>
       <c r="E438" t="n">
-        <v>31.8180662246313</v>
+        <v>31.81806249384815</v>
       </c>
       <c r="F438" t="n">
         <v>3057587</v>
@@ -9252,16 +9252,16 @@
         <v>44796</v>
       </c>
       <c r="B442" t="n">
-        <v>35.11592102050781</v>
+        <v>35.11592483520508</v>
       </c>
       <c r="C442" t="n">
-        <v>35.54145071517264</v>
+        <v>35.54145457609587</v>
       </c>
       <c r="D442" t="n">
-        <v>33.43314347863087</v>
+        <v>33.43314711052539</v>
       </c>
       <c r="E442" t="n">
-        <v>33.46215720759215</v>
+        <v>33.46216084263848</v>
       </c>
       <c r="F442" t="n">
         <v>5706007</v>
@@ -9292,16 +9292,16 @@
         <v>44798</v>
       </c>
       <c r="B444" t="n">
-        <v>35.7348747253418</v>
+        <v>35.73487854003906</v>
       </c>
       <c r="C444" t="n">
-        <v>36.56659288719009</v>
+        <v>36.56659679067325</v>
       </c>
       <c r="D444" t="n">
-        <v>35.39638621377552</v>
+        <v>35.39638999233915</v>
       </c>
       <c r="E444" t="n">
-        <v>35.8606021347718</v>
+        <v>35.86060596289047</v>
       </c>
       <c r="F444" t="n">
         <v>2850362</v>
@@ -9372,16 +9372,16 @@
         <v>44804</v>
       </c>
       <c r="B448" t="n">
-        <v>36.16040420532227</v>
+        <v>36.16040802001953</v>
       </c>
       <c r="C448" t="n">
-        <v>36.46021024107181</v>
+        <v>36.46021408739674</v>
       </c>
       <c r="D448" t="n">
-        <v>35.22230362431106</v>
+        <v>35.22230734004456</v>
       </c>
       <c r="E448" t="n">
-        <v>35.91862562779205</v>
+        <v>35.91862941698318</v>
       </c>
       <c r="F448" t="n">
         <v>3394125</v>
@@ -9392,16 +9392,16 @@
         <v>44805</v>
       </c>
       <c r="B449" t="n">
-        <v>35.58013534545898</v>
+        <v>35.58013916015625</v>
       </c>
       <c r="C449" t="n">
-        <v>36.22810235066332</v>
+        <v>36.22810623483188</v>
       </c>
       <c r="D449" t="n">
-        <v>35.00953703150028</v>
+        <v>35.00954078502128</v>
       </c>
       <c r="E449" t="n">
-        <v>35.8412551468599</v>
+        <v>35.84125898955293</v>
       </c>
       <c r="F449" t="n">
         <v>3340084</v>
@@ -9492,16 +9492,16 @@
         <v>44813</v>
       </c>
       <c r="B454" t="n">
-        <v>35.92830276489258</v>
+        <v>35.92829895019531</v>
       </c>
       <c r="C454" t="n">
-        <v>36.37317375612866</v>
+        <v>36.3731698941971</v>
       </c>
       <c r="D454" t="n">
-        <v>35.60915545100184</v>
+        <v>35.60915167019012</v>
       </c>
       <c r="E454" t="n">
-        <v>35.79290659406839</v>
+        <v>35.79290279374685</v>
       </c>
       <c r="F454" t="n">
         <v>3544465</v>
@@ -9552,16 +9552,16 @@
         <v>44818</v>
       </c>
       <c r="B457" t="n">
-        <v>37.25324630737305</v>
+        <v>37.25325012207031</v>
       </c>
       <c r="C457" t="n">
-        <v>37.57239358328728</v>
+        <v>37.57239743066493</v>
       </c>
       <c r="D457" t="n">
-        <v>35.96698471138824</v>
+        <v>35.96698839437353</v>
       </c>
       <c r="E457" t="n">
-        <v>36.05402215203722</v>
+        <v>36.05402584393507</v>
       </c>
       <c r="F457" t="n">
         <v>4057043</v>
@@ -9592,16 +9592,16 @@
         <v>44820</v>
       </c>
       <c r="B459" t="n">
-        <v>36.79870223999023</v>
+        <v>36.7987060546875</v>
       </c>
       <c r="C459" t="n">
-        <v>36.79870223999023</v>
+        <v>36.7987060546875</v>
       </c>
       <c r="D459" t="n">
-        <v>35.78322922342723</v>
+        <v>35.7832329328566</v>
       </c>
       <c r="E459" t="n">
-        <v>36.14106271488564</v>
+        <v>36.14106646140942</v>
       </c>
       <c r="F459" t="n">
         <v>2974596</v>
@@ -9612,16 +9612,16 @@
         <v>44823</v>
       </c>
       <c r="B460" t="n">
-        <v>36.8470573425293</v>
+        <v>36.84706115722656</v>
       </c>
       <c r="C460" t="n">
-        <v>37.3983144462179</v>
+        <v>37.39831831798563</v>
       </c>
       <c r="D460" t="n">
-        <v>35.7929018485589</v>
+        <v>35.79290555412169</v>
       </c>
       <c r="E460" t="n">
-        <v>35.7929018485589</v>
+        <v>35.79290555412169</v>
       </c>
       <c r="F460" t="n">
         <v>3461677</v>
@@ -9652,16 +9652,16 @@
         <v>44825</v>
       </c>
       <c r="B462" t="n">
-        <v>38.0366096496582</v>
+        <v>38.03661346435547</v>
       </c>
       <c r="C462" t="n">
-        <v>38.79095912196355</v>
+        <v>38.79096301231463</v>
       </c>
       <c r="D462" t="n">
-        <v>37.62074869162363</v>
+        <v>37.62075246461414</v>
       </c>
       <c r="E462" t="n">
-        <v>37.9398959687412</v>
+        <v>37.93989977373904</v>
       </c>
       <c r="F462" t="n">
         <v>4689181</v>
@@ -9732,16 +9732,16 @@
         <v>44831</v>
       </c>
       <c r="B466" t="n">
-        <v>33.61689758300781</v>
+        <v>33.61689376831055</v>
       </c>
       <c r="C466" t="n">
-        <v>34.44861580943209</v>
+        <v>34.44861190035511</v>
       </c>
       <c r="D466" t="n">
-        <v>33.32676401519949</v>
+        <v>33.3267602334253</v>
       </c>
       <c r="E466" t="n">
-        <v>34.44861580943209</v>
+        <v>34.44861190035511</v>
       </c>
       <c r="F466" t="n">
         <v>5480701</v>
@@ -9752,16 +9752,16 @@
         <v>44832</v>
       </c>
       <c r="B467" t="n">
-        <v>34.5743408203125</v>
+        <v>34.57433700561523</v>
       </c>
       <c r="C467" t="n">
-        <v>34.99987431683395</v>
+        <v>34.99987045518622</v>
       </c>
       <c r="D467" t="n">
-        <v>33.19136913623947</v>
+        <v>33.19136547412988</v>
       </c>
       <c r="E467" t="n">
-        <v>33.66525385709685</v>
+        <v>33.66525014270204</v>
       </c>
       <c r="F467" t="n">
         <v>4399676</v>
@@ -9772,16 +9772,16 @@
         <v>44833</v>
       </c>
       <c r="B468" t="n">
-        <v>33.90702819824219</v>
+        <v>33.90703201293945</v>
       </c>
       <c r="C468" t="n">
-        <v>34.69039138641359</v>
+        <v>34.69039528924284</v>
       </c>
       <c r="D468" t="n">
-        <v>33.09465502863428</v>
+        <v>33.09465875193581</v>
       </c>
       <c r="E468" t="n">
-        <v>34.61302269157358</v>
+        <v>34.61302658569848</v>
       </c>
       <c r="F468" t="n">
         <v>4499631</v>
@@ -9812,16 +9812,16 @@
         <v>44837</v>
       </c>
       <c r="B470" t="n">
-        <v>36.79870223999023</v>
+        <v>36.7987060546875</v>
       </c>
       <c r="C470" t="n">
-        <v>36.91475715561467</v>
+        <v>36.91476098234264</v>
       </c>
       <c r="D470" t="n">
-        <v>35.52210941084767</v>
+        <v>35.52211309320833</v>
       </c>
       <c r="E470" t="n">
-        <v>36.26678637509517</v>
+        <v>36.26679013465196</v>
       </c>
       <c r="F470" t="n">
         <v>4419789</v>
@@ -9852,16 +9852,16 @@
         <v>44839</v>
       </c>
       <c r="B472" t="n">
-        <v>41.63427352905273</v>
+        <v>41.63427734375</v>
       </c>
       <c r="C472" t="n">
-        <v>42.48533291211138</v>
+        <v>42.48533680478608</v>
       </c>
       <c r="D472" t="n">
-        <v>40.55110431601417</v>
+        <v>40.55110803146717</v>
       </c>
       <c r="E472" t="n">
-        <v>40.61880426561678</v>
+        <v>40.61880798727272</v>
       </c>
       <c r="F472" t="n">
         <v>6927519</v>
@@ -9892,16 +9892,16 @@
         <v>44841</v>
       </c>
       <c r="B474" t="n">
-        <v>41.47954177856445</v>
+        <v>41.47953796386719</v>
       </c>
       <c r="C474" t="n">
-        <v>42.45632495390688</v>
+        <v>42.45632104937901</v>
       </c>
       <c r="D474" t="n">
-        <v>41.22809067776815</v>
+        <v>41.22808688619578</v>
       </c>
       <c r="E474" t="n">
-        <v>41.59559296175236</v>
+        <v>41.59558913638236</v>
       </c>
       <c r="F474" t="n">
         <v>3503020</v>
@@ -10072,16 +10072,16 @@
         <v>44855</v>
       </c>
       <c r="B483" t="n">
-        <v>44.22613906860352</v>
+        <v>44.22614288330078</v>
       </c>
       <c r="C483" t="n">
-        <v>44.68068250090031</v>
+        <v>44.68068635480393</v>
       </c>
       <c r="D483" t="n">
-        <v>42.41763783177974</v>
+        <v>42.41764149048589</v>
       </c>
       <c r="E483" t="n">
-        <v>42.96889119740864</v>
+        <v>42.9688949036628</v>
       </c>
       <c r="F483" t="n">
         <v>5360835</v>
@@ -10112,16 +10112,16 @@
         <v>44859</v>
       </c>
       <c r="B485" t="n">
-        <v>42.69809722900391</v>
+        <v>42.69810104370117</v>
       </c>
       <c r="C485" t="n">
-        <v>44.7193669863075</v>
+        <v>44.71937098158734</v>
       </c>
       <c r="D485" t="n">
-        <v>42.52401860625056</v>
+        <v>42.52402240539543</v>
       </c>
       <c r="E485" t="n">
-        <v>43.43310543554394</v>
+        <v>43.43310931590769</v>
       </c>
       <c r="F485" t="n">
         <v>3364870</v>
@@ -10232,16 +10232,16 @@
         <v>44868</v>
       </c>
       <c r="B491" t="n">
-        <v>46.30543518066406</v>
+        <v>46.30543899536133</v>
       </c>
       <c r="C491" t="n">
-        <v>46.4311588402996</v>
+        <v>46.43116266535413</v>
       </c>
       <c r="D491" t="n">
-        <v>44.51627522669133</v>
+        <v>44.51627889399545</v>
       </c>
       <c r="E491" t="n">
-        <v>44.98048739191887</v>
+        <v>44.98049109746535</v>
       </c>
       <c r="F491" t="n">
         <v>3262984</v>
@@ -10312,16 +10312,16 @@
         <v>44874</v>
       </c>
       <c r="B495" t="n">
-        <v>44.69035339355469</v>
+        <v>44.69035720825195</v>
       </c>
       <c r="C495" t="n">
-        <v>46.49885831321781</v>
+        <v>46.49886228228617</v>
       </c>
       <c r="D495" t="n">
-        <v>44.23580997752845</v>
+        <v>44.23581375342662</v>
       </c>
       <c r="E495" t="n">
-        <v>45.35766165335595</v>
+        <v>45.35766552501359</v>
       </c>
       <c r="F495" t="n">
         <v>4884014</v>
@@ -10332,16 +10332,16 @@
         <v>44875</v>
       </c>
       <c r="B496" t="n">
-        <v>42.0598030090332</v>
+        <v>42.05980682373047</v>
       </c>
       <c r="C496" t="n">
-        <v>44.68068109462947</v>
+        <v>44.68068514703247</v>
       </c>
       <c r="D496" t="n">
-        <v>41.64394206412777</v>
+        <v>41.6439458411077</v>
       </c>
       <c r="E496" t="n">
-        <v>43.65554309181744</v>
+        <v>43.65554705124352</v>
       </c>
       <c r="F496" t="n">
         <v>5453172</v>
@@ -10472,16 +10472,16 @@
         <v>44887</v>
       </c>
       <c r="B503" t="n">
-        <v>35.7252082824707</v>
+        <v>35.72520446777344</v>
       </c>
       <c r="C503" t="n">
-        <v>38.01726681069696</v>
+        <v>38.01726275125628</v>
       </c>
       <c r="D503" t="n">
-        <v>35.41572973267442</v>
+        <v>35.41572595102293</v>
       </c>
       <c r="E503" t="n">
-        <v>37.37897222043525</v>
+        <v>37.37896822915095</v>
       </c>
       <c r="F503" t="n">
         <v>4879239</v>
@@ -10492,16 +10492,16 @@
         <v>44888</v>
       </c>
       <c r="B504" t="n">
-        <v>34.29387664794922</v>
+        <v>34.29388046264648</v>
       </c>
       <c r="C504" t="n">
-        <v>35.59947950993321</v>
+        <v>35.59948346985989</v>
       </c>
       <c r="D504" t="n">
-        <v>33.84900195222058</v>
+        <v>33.84900571743197</v>
       </c>
       <c r="E504" t="n">
-        <v>35.37704590964446</v>
+        <v>35.37704984482862</v>
       </c>
       <c r="F504" t="n">
         <v>5644348</v>
@@ -10532,16 +10532,16 @@
         <v>44890</v>
       </c>
       <c r="B506" t="n">
-        <v>34.2358512878418</v>
+        <v>34.23584747314453</v>
       </c>
       <c r="C506" t="n">
-        <v>36.49889988516448</v>
+        <v>36.49889581830917</v>
       </c>
       <c r="D506" t="n">
-        <v>34.11012761496025</v>
+        <v>34.11012381427162</v>
       </c>
       <c r="E506" t="n">
-        <v>36.17008008946956</v>
+        <v>36.17007605925269</v>
       </c>
       <c r="F506" t="n">
         <v>4398253</v>
@@ -10552,16 +10552,16 @@
         <v>44893</v>
       </c>
       <c r="B507" t="n">
-        <v>33.64591217041016</v>
+        <v>33.64590835571289</v>
       </c>
       <c r="C507" t="n">
-        <v>34.11012813925738</v>
+        <v>34.11012427192836</v>
       </c>
       <c r="D507" t="n">
-        <v>32.92057635865081</v>
+        <v>32.92057262619048</v>
       </c>
       <c r="E507" t="n">
-        <v>33.36544734092983</v>
+        <v>33.36544355803103</v>
       </c>
       <c r="F507" t="n">
         <v>4077054</v>
@@ -10652,16 +10652,16 @@
         <v>44900</v>
       </c>
       <c r="B512" t="n">
-        <v>34.04242706298828</v>
+        <v>34.04242324829102</v>
       </c>
       <c r="C512" t="n">
-        <v>35.879945891439</v>
+        <v>35.87994187083461</v>
       </c>
       <c r="D512" t="n">
-        <v>33.77163473568869</v>
+        <v>33.77163095133564</v>
       </c>
       <c r="E512" t="n">
-        <v>35.57046733984986</v>
+        <v>35.57046335392476</v>
       </c>
       <c r="F512" t="n">
         <v>5158181</v>
@@ -10732,16 +10732,16 @@
         <v>44904</v>
       </c>
       <c r="B516" t="n">
-        <v>31.69233894348145</v>
+        <v>31.69234085083008</v>
       </c>
       <c r="C516" t="n">
-        <v>32.74649445099531</v>
+        <v>32.74649642178647</v>
       </c>
       <c r="D516" t="n">
-        <v>31.48924283777486</v>
+        <v>31.4892447329005</v>
       </c>
       <c r="E516" t="n">
-        <v>32.22425106961099</v>
+        <v>32.22425300897184</v>
       </c>
       <c r="F516" t="n">
         <v>2885712</v>
@@ -10752,16 +10752,16 @@
         <v>44907</v>
       </c>
       <c r="B517" t="n">
-        <v>32.23392105102539</v>
+        <v>32.23392486572266</v>
       </c>
       <c r="C517" t="n">
-        <v>32.41767215777701</v>
+        <v>32.41767599422015</v>
       </c>
       <c r="D517" t="n">
-        <v>31.06371071712008</v>
+        <v>31.06371439332975</v>
       </c>
       <c r="E517" t="n">
-        <v>31.59562280181559</v>
+        <v>31.59562654097396</v>
       </c>
       <c r="F517" t="n">
         <v>3445728</v>
@@ -10772,16 +10772,16 @@
         <v>44908</v>
       </c>
       <c r="B518" t="n">
-        <v>32.52405548095703</v>
+        <v>32.5240592956543</v>
       </c>
       <c r="C518" t="n">
-        <v>33.41380105995531</v>
+        <v>33.41380497900949</v>
       </c>
       <c r="D518" t="n">
-        <v>31.9824708896037</v>
+        <v>31.98247464077933</v>
       </c>
       <c r="E518" t="n">
-        <v>32.39832807738018</v>
+        <v>32.39833187733107</v>
       </c>
       <c r="F518" t="n">
         <v>3369136</v>
@@ -10872,16 +10872,16 @@
         <v>44915</v>
       </c>
       <c r="B523" t="n">
-        <v>31.63431358337402</v>
+        <v>31.63431167602539</v>
       </c>
       <c r="C523" t="n">
-        <v>31.83740595497857</v>
+        <v>31.83740403538475</v>
       </c>
       <c r="D523" t="n">
-        <v>30.62851484937437</v>
+        <v>30.62851300266902</v>
       </c>
       <c r="E523" t="n">
-        <v>30.76391101296931</v>
+        <v>30.76390915810044</v>
       </c>
       <c r="F523" t="n">
         <v>3472546</v>
@@ -10892,16 +10892,16 @@
         <v>44916</v>
       </c>
       <c r="B524" t="n">
-        <v>32.19524002075195</v>
+        <v>32.19523620605469</v>
       </c>
       <c r="C524" t="n">
-        <v>32.50471857745117</v>
+        <v>32.50471472608491</v>
       </c>
       <c r="D524" t="n">
-        <v>31.22812562087756</v>
+        <v>31.22812192077017</v>
       </c>
       <c r="E524" t="n">
-        <v>32.34997742531367</v>
+        <v>32.34997359228213</v>
       </c>
       <c r="F524" t="n">
         <v>3938295</v>
@@ -10912,16 +10912,16 @@
         <v>44917</v>
       </c>
       <c r="B525" t="n">
-        <v>32.0114860534668</v>
+        <v>32.01148986816406</v>
       </c>
       <c r="C525" t="n">
-        <v>32.78517675543017</v>
+        <v>32.78518066232546</v>
       </c>
       <c r="D525" t="n">
-        <v>31.5376013885634</v>
+        <v>31.53760514678948</v>
       </c>
       <c r="E525" t="n">
-        <v>32.41767451520204</v>
+        <v>32.41767837830338</v>
       </c>
       <c r="F525" t="n">
         <v>3822391</v>
@@ -10932,16 +10932,16 @@
         <v>44918</v>
       </c>
       <c r="B526" t="n">
-        <v>34.68072509765625</v>
+        <v>34.68072128295898</v>
       </c>
       <c r="C526" t="n">
-        <v>34.88381746754605</v>
+        <v>34.88381363050969</v>
       </c>
       <c r="D526" t="n">
-        <v>32.68846888482701</v>
+        <v>32.68846528926745</v>
       </c>
       <c r="E526" t="n">
-        <v>33.17202607250107</v>
+        <v>33.17202242375276</v>
       </c>
       <c r="F526" t="n">
         <v>6955860</v>
@@ -11012,16 +11012,16 @@
         <v>44924</v>
       </c>
       <c r="B530" t="n">
-        <v>36.50856399536133</v>
+        <v>36.50856781005859</v>
       </c>
       <c r="C530" t="n">
-        <v>37.23389970387844</v>
+        <v>37.23390359436439</v>
       </c>
       <c r="D530" t="n">
-        <v>35.61882215744662</v>
+        <v>35.61882587917678</v>
       </c>
       <c r="E530" t="n">
-        <v>35.87994196319169</v>
+        <v>35.87994571220566</v>
       </c>
       <c r="F530" t="n">
         <v>4887264</v>
@@ -11032,16 +11032,16 @@
         <v>44928</v>
       </c>
       <c r="B531" t="n">
-        <v>35.21263885498047</v>
+        <v>35.2126350402832</v>
       </c>
       <c r="C531" t="n">
-        <v>36.68265172299981</v>
+        <v>36.68264774905137</v>
       </c>
       <c r="D531" t="n">
-        <v>34.78710911009928</v>
+        <v>34.78710534150101</v>
       </c>
       <c r="E531" t="n">
-        <v>36.01534337329287</v>
+        <v>36.01533947163607</v>
       </c>
       <c r="F531" t="n">
         <v>2924313</v>
@@ -11152,16 +11152,16 @@
         <v>44936</v>
       </c>
       <c r="B537" t="n">
-        <v>37.79483413696289</v>
+        <v>37.79483032226562</v>
       </c>
       <c r="C537" t="n">
-        <v>38.07529521496675</v>
+        <v>38.07529137196207</v>
       </c>
       <c r="D537" t="n">
-        <v>36.49889993855829</v>
+        <v>36.49889625466188</v>
       </c>
       <c r="E537" t="n">
-        <v>37.09850831958851</v>
+        <v>37.0985045751726</v>
       </c>
       <c r="F537" t="n">
         <v>3183751</v>
@@ -11192,16 +11192,16 @@
         <v>44938</v>
       </c>
       <c r="B539" t="n">
-        <v>43.42343521118164</v>
+        <v>43.42343902587891</v>
       </c>
       <c r="C539" t="n">
-        <v>44.72904181410123</v>
+        <v>44.7290457434945</v>
       </c>
       <c r="D539" t="n">
-        <v>43.19132911953119</v>
+        <v>43.19133291383822</v>
       </c>
       <c r="E539" t="n">
-        <v>43.40409397377132</v>
+        <v>43.40409778676949</v>
       </c>
       <c r="F539" t="n">
         <v>7341055</v>
@@ -11212,16 +11212,16 @@
         <v>44939</v>
       </c>
       <c r="B540" t="n">
-        <v>42.75613021850586</v>
+        <v>42.75612640380859</v>
       </c>
       <c r="C540" t="n">
-        <v>43.50080726582102</v>
+        <v>43.50080338468374</v>
       </c>
       <c r="D540" t="n">
-        <v>42.35961420932546</v>
+        <v>42.35961043000531</v>
       </c>
       <c r="E540" t="n">
-        <v>43.42343856263282</v>
+        <v>43.42343468839838</v>
       </c>
       <c r="F540" t="n">
         <v>4249336</v>
@@ -11272,16 +11272,16 @@
         <v>44944</v>
       </c>
       <c r="B543" t="n">
-        <v>44.53562164306641</v>
+        <v>44.53561782836914</v>
       </c>
       <c r="C543" t="n">
-        <v>45.24161621271021</v>
+        <v>45.241612337541</v>
       </c>
       <c r="D543" t="n">
-        <v>43.22034619346439</v>
+        <v>43.220342491427</v>
       </c>
       <c r="E543" t="n">
-        <v>43.42343857092518</v>
+        <v>43.42343485149192</v>
       </c>
       <c r="F543" t="n">
         <v>6730959</v>
@@ -11332,16 +11332,16 @@
         <v>44949</v>
       </c>
       <c r="B546" t="n">
-        <v>46.45050811767578</v>
+        <v>46.45050430297852</v>
       </c>
       <c r="C546" t="n">
-        <v>48.53947429699662</v>
+        <v>48.53947031074529</v>
       </c>
       <c r="D546" t="n">
-        <v>45.88958222216792</v>
+        <v>45.88957845353607</v>
       </c>
       <c r="E546" t="n">
-        <v>47.67874234150205</v>
+        <v>47.67873842593739</v>
       </c>
       <c r="F546" t="n">
         <v>5971946</v>
@@ -11392,16 +11392,16 @@
         <v>44952</v>
       </c>
       <c r="B549" t="n">
-        <v>45.26095581054688</v>
+        <v>45.26095199584961</v>
       </c>
       <c r="C549" t="n">
-        <v>46.77932358255676</v>
+        <v>46.77931963988798</v>
       </c>
       <c r="D549" t="n">
-        <v>45.24161457234137</v>
+        <v>45.24161075927422</v>
       </c>
       <c r="E549" t="n">
-        <v>45.92826413060603</v>
+        <v>45.92826025966649</v>
       </c>
       <c r="F549" t="n">
         <v>3327082</v>
@@ -11412,16 +11412,16 @@
         <v>44953</v>
       </c>
       <c r="B550" t="n">
-        <v>44.5066032409668</v>
+        <v>44.50660705566406</v>
       </c>
       <c r="C550" t="n">
-        <v>46.34412192885299</v>
+        <v>46.34412590104548</v>
       </c>
       <c r="D550" t="n">
-        <v>44.16811098394805</v>
+        <v>44.16811476963287</v>
       </c>
       <c r="E550" t="n">
-        <v>46.20872577556058</v>
+        <v>46.20872973614816</v>
       </c>
       <c r="F550" t="n">
         <v>4035914</v>
@@ -11432,16 +11432,16 @@
         <v>44956</v>
       </c>
       <c r="B551" t="n">
-        <v>43.79094314575195</v>
+        <v>43.79093933105469</v>
       </c>
       <c r="C551" t="n">
-        <v>44.43890648207057</v>
+        <v>44.43890261092821</v>
       </c>
       <c r="D551" t="n">
-        <v>43.13330356893655</v>
+        <v>43.13329981152729</v>
       </c>
       <c r="E551" t="n">
-        <v>44.31318281197527</v>
+        <v>44.3131789517849</v>
       </c>
       <c r="F551" t="n">
         <v>3870439</v>
@@ -11572,16 +11572,16 @@
         <v>44965</v>
       </c>
       <c r="B558" t="n">
-        <v>43.12362670898438</v>
+        <v>43.12363052368164</v>
       </c>
       <c r="C558" t="n">
-        <v>43.13329920092593</v>
+        <v>43.13330301647882</v>
       </c>
       <c r="D558" t="n">
-        <v>42.08881622667597</v>
+        <v>42.08881994983436</v>
       </c>
       <c r="E558" t="n">
-        <v>42.57237336739773</v>
+        <v>42.57237713333137</v>
       </c>
       <c r="F558" t="n">
         <v>2757212</v>
@@ -11672,16 +11672,16 @@
         <v>44972</v>
       </c>
       <c r="B563" t="n">
-        <v>40.04821014404297</v>
+        <v>40.0482063293457</v>
       </c>
       <c r="C563" t="n">
-        <v>40.52209485081966</v>
+        <v>40.52209099098364</v>
       </c>
       <c r="D563" t="n">
-        <v>38.90701335343782</v>
+        <v>38.90700964744255</v>
       </c>
       <c r="E563" t="n">
-        <v>38.92635833968847</v>
+        <v>38.92635463185054</v>
       </c>
       <c r="F563" t="n">
         <v>3495706</v>
@@ -11752,16 +11752,16 @@
         <v>44980</v>
       </c>
       <c r="B567" t="n">
-        <v>38.00759887695312</v>
+        <v>38.00759506225586</v>
       </c>
       <c r="C567" t="n">
-        <v>39.07142321677222</v>
+        <v>39.07141929530241</v>
       </c>
       <c r="D567" t="n">
-        <v>37.73680654543994</v>
+        <v>37.7368027579212</v>
       </c>
       <c r="E567" t="n">
-        <v>37.95924390652058</v>
+        <v>37.95924009667655</v>
       </c>
       <c r="F567" t="n">
         <v>3548732</v>
@@ -11812,16 +11812,16 @@
         <v>44985</v>
       </c>
       <c r="B570" t="n">
-        <v>35.21263885498047</v>
+        <v>35.2126350402832</v>
       </c>
       <c r="C570" t="n">
-        <v>38.49115688632073</v>
+        <v>38.49115271645117</v>
       </c>
       <c r="D570" t="n">
-        <v>35.21263885498047</v>
+        <v>35.2126350402832</v>
       </c>
       <c r="E570" t="n">
-        <v>37.13719520026616</v>
+        <v>37.13719117707558</v>
       </c>
       <c r="F570" t="n">
         <v>11036876</v>
@@ -11832,16 +11832,16 @@
         <v>44986</v>
       </c>
       <c r="B571" t="n">
-        <v>31.52793121337891</v>
+        <v>31.52792930603027</v>
       </c>
       <c r="C571" t="n">
-        <v>35.21263762145776</v>
+        <v>35.21263549119504</v>
       </c>
       <c r="D571" t="n">
-        <v>29.89350662783602</v>
+        <v>29.89350481936535</v>
       </c>
       <c r="E571" t="n">
-        <v>35.10625518896411</v>
+        <v>35.10625306513723</v>
       </c>
       <c r="F571" t="n">
         <v>24633899</v>
@@ -11872,16 +11872,16 @@
         <v>44988</v>
       </c>
       <c r="B573" t="n">
-        <v>31.74069595336914</v>
+        <v>31.74069404602051</v>
       </c>
       <c r="C573" t="n">
-        <v>31.93411957920744</v>
+        <v>31.93411766023568</v>
       </c>
       <c r="D573" t="n">
-        <v>30.40607743217574</v>
+        <v>30.40607560502645</v>
       </c>
       <c r="E573" t="n">
-        <v>30.47377551384036</v>
+        <v>30.47377368262298</v>
       </c>
       <c r="F573" t="n">
         <v>7573675</v>
@@ -11892,16 +11892,16 @@
         <v>44991</v>
       </c>
       <c r="B574" t="n">
-        <v>31.86642074584961</v>
+        <v>31.86641883850098</v>
       </c>
       <c r="C574" t="n">
-        <v>32.34997795368473</v>
+        <v>32.34997601739302</v>
       </c>
       <c r="D574" t="n">
-        <v>30.94766317523564</v>
+        <v>30.94766132287878</v>
       </c>
       <c r="E574" t="n">
-        <v>31.74069707103675</v>
+        <v>31.74069517121325</v>
       </c>
       <c r="F574" t="n">
         <v>5963007</v>
@@ -11992,16 +11992,16 @@
         <v>44998</v>
       </c>
       <c r="B579" t="n">
-        <v>26.45058059692383</v>
+        <v>26.4505786895752</v>
       </c>
       <c r="C579" t="n">
-        <v>27.32098316598858</v>
+        <v>27.32098119587531</v>
       </c>
       <c r="D579" t="n">
-        <v>25.76392728704381</v>
+        <v>25.76392542920967</v>
       </c>
       <c r="E579" t="n">
-        <v>26.59564737946998</v>
+        <v>26.59564546166059</v>
       </c>
       <c r="F579" t="n">
         <v>13860726</v>
@@ -12032,16 +12032,16 @@
         <v>45000</v>
       </c>
       <c r="B581" t="n">
-        <v>26.28616905212402</v>
+        <v>26.28617095947266</v>
       </c>
       <c r="C581" t="n">
-        <v>26.82775179788365</v>
+        <v>26.82775374453002</v>
       </c>
       <c r="D581" t="n">
-        <v>25.62853138858268</v>
+        <v>25.62853324821252</v>
       </c>
       <c r="E581" t="n">
-        <v>26.58597321755539</v>
+        <v>26.58597514665809</v>
       </c>
       <c r="F581" t="n">
         <v>12174787</v>
@@ -12072,16 +12072,16 @@
         <v>45002</v>
       </c>
       <c r="B583" t="n">
-        <v>30.70588302612305</v>
+        <v>30.70588111877441</v>
       </c>
       <c r="C583" t="n">
-        <v>30.88963415624145</v>
+        <v>30.8896322374788</v>
       </c>
       <c r="D583" t="n">
-        <v>27.73684184447329</v>
+        <v>27.73684012155175</v>
       </c>
       <c r="E583" t="n">
-        <v>30.45443194157511</v>
+        <v>30.45443004984579</v>
       </c>
       <c r="F583" t="n">
         <v>23193684</v>
@@ -12092,16 +12092,16 @@
         <v>45005</v>
       </c>
       <c r="B584" t="n">
-        <v>29.79679489135742</v>
+        <v>29.79679679870605</v>
       </c>
       <c r="C584" t="n">
-        <v>31.20878203377826</v>
+        <v>31.20878403151084</v>
       </c>
       <c r="D584" t="n">
-        <v>29.32290834641774</v>
+        <v>29.32291022343201</v>
       </c>
       <c r="E584" t="n">
-        <v>30.70588175921954</v>
+        <v>30.70588372476053</v>
       </c>
       <c r="F584" t="n">
         <v>7729094</v>
@@ -12252,16 +12252,16 @@
         <v>45015</v>
       </c>
       <c r="B592" t="n">
-        <v>29.38093376159668</v>
+        <v>29.38093566894531</v>
       </c>
       <c r="C592" t="n">
-        <v>30.51245796745546</v>
+        <v>30.51245994826028</v>
       </c>
       <c r="D592" t="n">
-        <v>29.2745513361352</v>
+        <v>29.27455323657771</v>
       </c>
       <c r="E592" t="n">
-        <v>29.95153211069714</v>
+        <v>29.95153405508782</v>
       </c>
       <c r="F592" t="n">
         <v>5560645</v>
@@ -12312,16 +12312,16 @@
         <v>45020</v>
       </c>
       <c r="B595" t="n">
-        <v>27.92059135437012</v>
+        <v>27.92059326171875</v>
       </c>
       <c r="C595" t="n">
-        <v>29.70975320425825</v>
+        <v>29.70975523383049</v>
       </c>
       <c r="D595" t="n">
-        <v>27.91092073592187</v>
+        <v>27.91092264260987</v>
       </c>
       <c r="E595" t="n">
-        <v>29.57435705083184</v>
+        <v>29.57435907115471</v>
       </c>
       <c r="F595" t="n">
         <v>7552242</v>
@@ -12332,16 +12332,16 @@
         <v>45021</v>
       </c>
       <c r="B596" t="n">
-        <v>26.76972770690918</v>
+        <v>26.76972579956055</v>
       </c>
       <c r="C596" t="n">
-        <v>27.8528951326722</v>
+        <v>27.85289314814766</v>
       </c>
       <c r="D596" t="n">
-        <v>26.23781367622606</v>
+        <v>26.23781180677641</v>
       </c>
       <c r="E596" t="n">
-        <v>27.65947338188658</v>
+        <v>27.65947141114338</v>
       </c>
       <c r="F596" t="n">
         <v>12382825</v>
@@ -12372,16 +12372,16 @@
         <v>45026</v>
       </c>
       <c r="B598" t="n">
-        <v>29.6517276763916</v>
+        <v>29.65172576904297</v>
       </c>
       <c r="C598" t="n">
-        <v>29.83547880780963</v>
+        <v>29.8354768886412</v>
       </c>
       <c r="D598" t="n">
-        <v>28.19138549654949</v>
+        <v>28.19138368313743</v>
       </c>
       <c r="E598" t="n">
-        <v>28.33645227786835</v>
+        <v>28.33645045512486</v>
       </c>
       <c r="F598" t="n">
         <v>8774363</v>
@@ -12552,16 +12552,16 @@
         <v>45040</v>
       </c>
       <c r="B607" t="n">
-        <v>26.96700477600098</v>
+        <v>26.96700286865234</v>
       </c>
       <c r="C607" t="n">
-        <v>27.07506799883479</v>
+        <v>27.07506608384296</v>
       </c>
       <c r="D607" t="n">
-        <v>26.23020138729918</v>
+        <v>26.23019953206389</v>
       </c>
       <c r="E607" t="n">
-        <v>26.86876394941649</v>
+        <v>26.86876204901633</v>
       </c>
       <c r="F607" t="n">
         <v>6680100</v>
@@ -12572,16 +12572,16 @@
         <v>45041</v>
       </c>
       <c r="B608" t="n">
-        <v>27.21260261535645</v>
+        <v>27.21260452270508</v>
       </c>
       <c r="C608" t="n">
-        <v>27.45820371522866</v>
+        <v>27.45820563979163</v>
       </c>
       <c r="D608" t="n">
-        <v>26.42667797149275</v>
+        <v>26.42667982375542</v>
       </c>
       <c r="E608" t="n">
-        <v>26.79999269261962</v>
+        <v>26.79999457104816</v>
       </c>
       <c r="F608" t="n">
         <v>5323000</v>
@@ -12612,16 +12612,16 @@
         <v>45043</v>
       </c>
       <c r="B610" t="n">
-        <v>29.90439414978027</v>
+        <v>29.90439224243164</v>
       </c>
       <c r="C610" t="n">
-        <v>30.26788277330051</v>
+        <v>30.267880842768</v>
       </c>
       <c r="D610" t="n">
-        <v>26.73122612224756</v>
+        <v>26.73122441728851</v>
       </c>
       <c r="E610" t="n">
-        <v>26.73122612224756</v>
+        <v>26.73122441728851</v>
       </c>
       <c r="F610" t="n">
         <v>20933600</v>
@@ -12672,16 +12672,16 @@
         <v>45049</v>
       </c>
       <c r="B613" t="n">
-        <v>29.14794158935547</v>
+        <v>29.14793968200684</v>
       </c>
       <c r="C613" t="n">
-        <v>29.61949529963673</v>
+        <v>29.61949336143113</v>
       </c>
       <c r="D613" t="n">
-        <v>28.33254592932366</v>
+        <v>28.33254407533193</v>
       </c>
       <c r="E613" t="n">
-        <v>29.26583095381972</v>
+        <v>29.26582903875679</v>
       </c>
       <c r="F613" t="n">
         <v>9250000</v>
@@ -12692,16 +12692,16 @@
         <v>45050</v>
       </c>
       <c r="B614" t="n">
-        <v>29.27565383911133</v>
+        <v>29.2756519317627</v>
       </c>
       <c r="C614" t="n">
-        <v>29.95351348008578</v>
+        <v>29.95351152857367</v>
       </c>
       <c r="D614" t="n">
-        <v>29.17741488650197</v>
+        <v>29.17741298555374</v>
       </c>
       <c r="E614" t="n">
-        <v>29.47213549190587</v>
+        <v>29.47213357175619</v>
       </c>
       <c r="F614" t="n">
         <v>6670900</v>
@@ -12792,16 +12792,16 @@
         <v>45057</v>
       </c>
       <c r="B619" t="n">
-        <v>31.66289710998535</v>
+        <v>31.66289520263672</v>
       </c>
       <c r="C619" t="n">
-        <v>31.81025928645763</v>
+        <v>31.81025737023202</v>
       </c>
       <c r="D619" t="n">
-        <v>31.10292683551199</v>
+        <v>31.10292496189554</v>
       </c>
       <c r="E619" t="n">
-        <v>31.71201658628417</v>
+        <v>31.71201467597662</v>
       </c>
       <c r="F619" t="n">
         <v>4858000</v>
@@ -12812,16 +12812,16 @@
         <v>45058</v>
       </c>
       <c r="B620" t="n">
-        <v>32.49794387817383</v>
+        <v>32.49794006347656</v>
       </c>
       <c r="C620" t="n">
-        <v>32.64530231015733</v>
+        <v>32.64529847816273</v>
       </c>
       <c r="D620" t="n">
-        <v>31.46641611640984</v>
+        <v>31.46641242279611</v>
       </c>
       <c r="E620" t="n">
-        <v>31.55483267463029</v>
+        <v>31.554828970638</v>
       </c>
       <c r="F620" t="n">
         <v>5317000</v>
@@ -12852,16 +12852,16 @@
         <v>45062</v>
       </c>
       <c r="B622" t="n">
-        <v>29.90439414978027</v>
+        <v>29.90439224243164</v>
       </c>
       <c r="C622" t="n">
-        <v>32.08533151226543</v>
+        <v>32.08532946581322</v>
       </c>
       <c r="D622" t="n">
-        <v>29.70791249602647</v>
+        <v>29.70791060120974</v>
       </c>
       <c r="E622" t="n">
-        <v>31.86920131837866</v>
+        <v>31.86919928571158</v>
       </c>
       <c r="F622" t="n">
         <v>13269700</v>
@@ -12912,16 +12912,16 @@
         <v>45065</v>
       </c>
       <c r="B625" t="n">
-        <v>32.49794387817383</v>
+        <v>32.49794006347656</v>
       </c>
       <c r="C625" t="n">
-        <v>34.87536105853923</v>
+        <v>34.87535696477425</v>
       </c>
       <c r="D625" t="n">
-        <v>31.0439837395418</v>
+        <v>31.04398009551434</v>
       </c>
       <c r="E625" t="n">
-        <v>31.86920182661951</v>
+        <v>31.8691980857257</v>
       </c>
       <c r="F625" t="n">
         <v>19443700</v>
@@ -12972,16 +12972,16 @@
         <v>45070</v>
       </c>
       <c r="B628" t="n">
-        <v>31.48606109619141</v>
+        <v>31.48606300354004</v>
       </c>
       <c r="C628" t="n">
-        <v>31.86919822262693</v>
+        <v>31.86920015318507</v>
       </c>
       <c r="D628" t="n">
-        <v>30.46436146776744</v>
+        <v>30.464363313224</v>
       </c>
       <c r="E628" t="n">
-        <v>31.04398022887067</v>
+        <v>31.04398210943912</v>
       </c>
       <c r="F628" t="n">
         <v>7685200</v>
@@ -13212,16 +13212,16 @@
         <v>45089</v>
       </c>
       <c r="B640" t="n">
-        <v>31.26011085510254</v>
+        <v>31.26010894775391</v>
       </c>
       <c r="C640" t="n">
-        <v>31.86920059509758</v>
+        <v>31.86919865058509</v>
       </c>
       <c r="D640" t="n">
-        <v>30.47418800549994</v>
+        <v>30.47418614610471</v>
       </c>
       <c r="E640" t="n">
-        <v>31.61377707431765</v>
+        <v>31.61377514538992</v>
       </c>
       <c r="F640" t="n">
         <v>7223600</v>
@@ -13252,16 +13252,16 @@
         <v>45091</v>
       </c>
       <c r="B642" t="n">
-        <v>31.14222145080566</v>
+        <v>31.1422233581543</v>
       </c>
       <c r="C642" t="n">
-        <v>31.71201407641177</v>
+        <v>31.71201601865814</v>
       </c>
       <c r="D642" t="n">
-        <v>30.5724269514118</v>
+        <v>30.57242882386257</v>
       </c>
       <c r="E642" t="n">
-        <v>31.33870121423831</v>
+        <v>31.33870313362062</v>
       </c>
       <c r="F642" t="n">
         <v>8288400</v>
@@ -13292,16 +13292,16 @@
         <v>45093</v>
       </c>
       <c r="B644" t="n">
-        <v>31.9183235168457</v>
+        <v>31.91832160949707</v>
       </c>
       <c r="C644" t="n">
-        <v>31.9183235168457</v>
+        <v>31.91832160949707</v>
       </c>
       <c r="D644" t="n">
-        <v>31.19134254558997</v>
+        <v>31.19134068168367</v>
       </c>
       <c r="E644" t="n">
-        <v>31.4271193982454</v>
+        <v>31.42711752024974</v>
       </c>
       <c r="F644" t="n">
         <v>5722800</v>
@@ -13332,16 +13332,16 @@
         <v>45097</v>
       </c>
       <c r="B646" t="n">
-        <v>32.16392517089844</v>
+        <v>32.16392135620117</v>
       </c>
       <c r="C646" t="n">
-        <v>32.2916350584061</v>
+        <v>32.29163122856222</v>
       </c>
       <c r="D646" t="n">
-        <v>31.48606366340425</v>
+        <v>31.48605992910253</v>
       </c>
       <c r="E646" t="n">
-        <v>32.12462809124572</v>
+        <v>32.12462428120915</v>
       </c>
       <c r="F646" t="n">
         <v>4954700</v>
@@ -13352,16 +13352,16 @@
         <v>45098</v>
       </c>
       <c r="B647" t="n">
-        <v>32.06567764282227</v>
+        <v>32.06568145751953</v>
       </c>
       <c r="C647" t="n">
-        <v>32.36039820068254</v>
+        <v>32.36040205044127</v>
       </c>
       <c r="D647" t="n">
-        <v>31.4860589217478</v>
+        <v>31.48606266749066</v>
       </c>
       <c r="E647" t="n">
-        <v>32.1246232534244</v>
+        <v>32.12462707513414</v>
       </c>
       <c r="F647" t="n">
         <v>4670300</v>
@@ -13412,16 +13412,16 @@
         <v>45103</v>
       </c>
       <c r="B650" t="n">
-        <v>30.53312873840332</v>
+        <v>30.53313064575195</v>
       </c>
       <c r="C650" t="n">
-        <v>30.83767357835474</v>
+        <v>30.83767550472773</v>
       </c>
       <c r="D650" t="n">
-        <v>30.30717617565832</v>
+        <v>30.30717806889212</v>
       </c>
       <c r="E650" t="n">
-        <v>30.58224820898695</v>
+        <v>30.58225011940398</v>
       </c>
       <c r="F650" t="n">
         <v>2874500</v>
@@ -13452,16 +13452,16 @@
         <v>45105</v>
       </c>
       <c r="B652" t="n">
-        <v>29.37389373779297</v>
+        <v>29.37389183044434</v>
       </c>
       <c r="C652" t="n">
-        <v>30.06157762706682</v>
+        <v>30.06157567506449</v>
       </c>
       <c r="D652" t="n">
-        <v>29.30512572362315</v>
+        <v>29.30512382073987</v>
       </c>
       <c r="E652" t="n">
-        <v>29.75703276126285</v>
+        <v>29.75703082903567</v>
       </c>
       <c r="F652" t="n">
         <v>4532500</v>
@@ -13532,16 +13532,16 @@
         <v>45111</v>
       </c>
       <c r="B656" t="n">
-        <v>29.80615043640137</v>
+        <v>29.80615234375</v>
       </c>
       <c r="C656" t="n">
-        <v>30.15981662939312</v>
+        <v>30.15981855937348</v>
       </c>
       <c r="D656" t="n">
-        <v>29.57037359900278</v>
+        <v>29.57037549126363</v>
       </c>
       <c r="E656" t="n">
-        <v>29.80615043640137</v>
+        <v>29.80615234375</v>
       </c>
       <c r="F656" t="n">
         <v>2514900</v>
@@ -13552,16 +13552,16 @@
         <v>45112</v>
       </c>
       <c r="B657" t="n">
-        <v>30.40541839599609</v>
+        <v>30.40542030334473</v>
       </c>
       <c r="C657" t="n">
-        <v>30.70996325002402</v>
+        <v>30.70996517647691</v>
       </c>
       <c r="D657" t="n">
-        <v>29.34442166777476</v>
+        <v>29.34442350856649</v>
       </c>
       <c r="E657" t="n">
-        <v>29.60966944448926</v>
+        <v>29.60967130192012</v>
       </c>
       <c r="F657" t="n">
         <v>5394800</v>
@@ -13612,16 +13612,16 @@
         <v>45117</v>
       </c>
       <c r="B660" t="n">
-        <v>31.07345199584961</v>
+        <v>31.07345390319824</v>
       </c>
       <c r="C660" t="n">
-        <v>31.93796708924193</v>
+        <v>31.93796904965617</v>
       </c>
       <c r="D660" t="n">
-        <v>30.84749942157282</v>
+        <v>30.84750131505205</v>
       </c>
       <c r="E660" t="n">
-        <v>31.56465609569361</v>
+        <v>31.56465803319331</v>
       </c>
       <c r="F660" t="n">
         <v>7339200</v>
@@ -13652,16 +13652,16 @@
         <v>45119</v>
       </c>
       <c r="B662" t="n">
-        <v>31.07345199584961</v>
+        <v>31.07345390319824</v>
       </c>
       <c r="C662" t="n">
-        <v>32.08532925608902</v>
+        <v>32.08533122554864</v>
       </c>
       <c r="D662" t="n">
-        <v>31.04398106151042</v>
+        <v>31.04398296705007</v>
       </c>
       <c r="E662" t="n">
-        <v>31.77096013121909</v>
+        <v>31.77096208138212</v>
       </c>
       <c r="F662" t="n">
         <v>4503800</v>
@@ -13732,16 +13732,16 @@
         <v>45125</v>
       </c>
       <c r="B666" t="n">
-        <v>32.91055297851562</v>
+        <v>32.91054916381836</v>
       </c>
       <c r="C666" t="n">
-        <v>33.03826662148488</v>
+        <v>33.03826279198419</v>
       </c>
       <c r="D666" t="n">
-        <v>32.03621351392245</v>
+        <v>32.0362098005708</v>
       </c>
       <c r="E666" t="n">
-        <v>32.18357195035527</v>
+        <v>32.18356821992315</v>
       </c>
       <c r="F666" t="n">
         <v>4775600</v>
@@ -13752,16 +13752,16 @@
         <v>45126</v>
       </c>
       <c r="B667" t="n">
-        <v>33.6473503112793</v>
+        <v>33.64735412597656</v>
       </c>
       <c r="C667" t="n">
-        <v>34.04031356576963</v>
+        <v>34.04031742501827</v>
       </c>
       <c r="D667" t="n">
-        <v>33.04808303459044</v>
+        <v>33.04808678134705</v>
       </c>
       <c r="E667" t="n">
-        <v>33.04808303459044</v>
+        <v>33.04808678134705</v>
       </c>
       <c r="F667" t="n">
         <v>7484200</v>
@@ -13772,16 +13772,16 @@
         <v>45127</v>
       </c>
       <c r="B668" t="n">
-        <v>33.92242813110352</v>
+        <v>33.92242431640625</v>
       </c>
       <c r="C668" t="n">
-        <v>34.11890979188617</v>
+        <v>34.11890595509385</v>
       </c>
       <c r="D668" t="n">
-        <v>33.64735605455338</v>
+        <v>33.64735227078894</v>
       </c>
       <c r="E668" t="n">
-        <v>33.91260573447357</v>
+        <v>33.91260192088087</v>
       </c>
       <c r="F668" t="n">
         <v>3587900</v>
@@ -13952,16 +13952,16 @@
         <v>45140</v>
       </c>
       <c r="B677" t="n">
-        <v>34.4431037902832</v>
+        <v>34.44309997558594</v>
       </c>
       <c r="C677" t="n">
-        <v>34.5806398233511</v>
+        <v>34.58063599342123</v>
       </c>
       <c r="D677" t="n">
-        <v>33.71612279718397</v>
+        <v>33.71611906300245</v>
       </c>
       <c r="E677" t="n">
-        <v>34.38415817000732</v>
+        <v>34.38415436183849</v>
       </c>
       <c r="F677" t="n">
         <v>3408800</v>
@@ -14012,16 +14012,16 @@
         <v>45145</v>
       </c>
       <c r="B680" t="n">
-        <v>35.68092727661133</v>
+        <v>35.68093109130859</v>
       </c>
       <c r="C680" t="n">
-        <v>36.15248093584172</v>
+        <v>36.15248480095344</v>
       </c>
       <c r="D680" t="n">
-        <v>35.09148613946717</v>
+        <v>35.09148989114647</v>
       </c>
       <c r="E680" t="n">
-        <v>36.05424199550948</v>
+        <v>36.05424585011833</v>
       </c>
       <c r="F680" t="n">
         <v>3820600</v>
@@ -14032,16 +14032,16 @@
         <v>45146</v>
       </c>
       <c r="B681" t="n">
-        <v>36.34896469116211</v>
+        <v>36.34896850585938</v>
       </c>
       <c r="C681" t="n">
-        <v>36.51597164901496</v>
+        <v>36.51597548123902</v>
       </c>
       <c r="D681" t="n">
-        <v>34.30556163401185</v>
+        <v>34.30556523426109</v>
       </c>
       <c r="E681" t="n">
-        <v>34.76729292525891</v>
+        <v>34.76729657396523</v>
       </c>
       <c r="F681" t="n">
         <v>5274900</v>
@@ -14172,16 +14172,16 @@
         <v>45155</v>
       </c>
       <c r="B688" t="n">
-        <v>31.26993370056152</v>
+        <v>31.26993560791016</v>
       </c>
       <c r="C688" t="n">
-        <v>31.74148926263102</v>
+        <v>31.74149119874277</v>
       </c>
       <c r="D688" t="n">
-        <v>30.9653888444364</v>
+        <v>30.96539073320894</v>
       </c>
       <c r="E688" t="n">
-        <v>31.46641346711834</v>
+        <v>31.4664153864515</v>
       </c>
       <c r="F688" t="n">
         <v>4529600</v>
@@ -14252,16 +14252,16 @@
         <v>45161</v>
       </c>
       <c r="B692" t="n">
-        <v>31.05380630493164</v>
+        <v>31.05380439758301</v>
       </c>
       <c r="C692" t="n">
-        <v>31.2404618075605</v>
+        <v>31.24045988874735</v>
       </c>
       <c r="D692" t="n">
-        <v>30.68049155209822</v>
+        <v>30.68048966767887</v>
       </c>
       <c r="E692" t="n">
-        <v>31.09310150987904</v>
+        <v>31.09309960011686</v>
       </c>
       <c r="F692" t="n">
         <v>4847400</v>
@@ -14272,16 +14272,16 @@
         <v>45162</v>
       </c>
       <c r="B693" t="n">
-        <v>30.91626930236816</v>
+        <v>30.91626739501953</v>
       </c>
       <c r="C693" t="n">
-        <v>31.30923260599883</v>
+        <v>31.30923067440671</v>
       </c>
       <c r="D693" t="n">
-        <v>30.56260495240363</v>
+        <v>30.56260306687397</v>
       </c>
       <c r="E693" t="n">
-        <v>31.05380720815405</v>
+        <v>31.05380529232016</v>
       </c>
       <c r="F693" t="n">
         <v>3471700</v>
@@ -14332,16 +14332,16 @@
         <v>45167</v>
       </c>
       <c r="B696" t="n">
-        <v>31.29940795898438</v>
+        <v>31.29940605163574</v>
       </c>
       <c r="C696" t="n">
-        <v>31.55483147996431</v>
+        <v>31.55482955705047</v>
       </c>
       <c r="D696" t="n">
-        <v>30.63137259940515</v>
+        <v>30.63137073276579</v>
       </c>
       <c r="E696" t="n">
-        <v>31.06363110391898</v>
+        <v>31.06362921093831</v>
       </c>
       <c r="F696" t="n">
         <v>3743200</v>
@@ -14352,16 +14352,16 @@
         <v>45168</v>
       </c>
       <c r="B697" t="n">
-        <v>31.6334228515625</v>
+        <v>31.63342475891113</v>
       </c>
       <c r="C697" t="n">
-        <v>31.70219086067396</v>
+        <v>31.70219277216898</v>
       </c>
       <c r="D697" t="n">
-        <v>30.96538755084366</v>
+        <v>30.96538941791287</v>
       </c>
       <c r="E697" t="n">
-        <v>31.49588683333958</v>
+        <v>31.49588873239543</v>
       </c>
       <c r="F697" t="n">
         <v>3276100</v>
@@ -14412,16 +14412,16 @@
         <v>45173</v>
       </c>
       <c r="B700" t="n">
-        <v>32.2719841003418</v>
+        <v>32.27198791503906</v>
       </c>
       <c r="C700" t="n">
-        <v>32.55688228511206</v>
+        <v>32.55688613348561</v>
       </c>
       <c r="D700" t="n">
-        <v>32.06568006898767</v>
+        <v>32.06568385929886</v>
       </c>
       <c r="E700" t="n">
-        <v>32.22286462824446</v>
+        <v>32.22286843713558</v>
       </c>
       <c r="F700" t="n">
         <v>2652900</v>
@@ -14432,16 +14432,16 @@
         <v>45174</v>
       </c>
       <c r="B701" t="n">
-        <v>32.63547515869141</v>
+        <v>32.63547897338867</v>
       </c>
       <c r="C701" t="n">
-        <v>32.93019572729314</v>
+        <v>32.93019957643972</v>
       </c>
       <c r="D701" t="n">
-        <v>32.07550495407551</v>
+        <v>32.07550870331895</v>
       </c>
       <c r="E701" t="n">
-        <v>32.27198283475976</v>
+        <v>32.27198660696912</v>
       </c>
       <c r="F701" t="n">
         <v>6036900</v>
@@ -14452,16 +14452,16 @@
         <v>45175</v>
       </c>
       <c r="B702" t="n">
-        <v>32.00674057006836</v>
+        <v>32.00673675537109</v>
       </c>
       <c r="C702" t="n">
-        <v>32.71406926527997</v>
+        <v>32.71406536628031</v>
       </c>
       <c r="D702" t="n">
-        <v>31.92814641083608</v>
+        <v>31.928142605506</v>
       </c>
       <c r="E702" t="n">
-        <v>32.65512739343153</v>
+        <v>32.65512350145682</v>
       </c>
       <c r="F702" t="n">
         <v>4505300</v>
@@ -14512,16 +14512,16 @@
         <v>45181</v>
       </c>
       <c r="B705" t="n">
-        <v>32.3309326171875</v>
+        <v>32.33092880249023</v>
       </c>
       <c r="C705" t="n">
-        <v>32.6453017639165</v>
+        <v>32.64529791212711</v>
       </c>
       <c r="D705" t="n">
-        <v>31.76113994408213</v>
+        <v>31.76113619661418</v>
       </c>
       <c r="E705" t="n">
-        <v>31.97726639022342</v>
+        <v>31.97726261725491</v>
       </c>
       <c r="F705" t="n">
         <v>3620500</v>
@@ -14532,16 +14532,16 @@
         <v>45182</v>
       </c>
       <c r="B706" t="n">
-        <v>31.6334228515625</v>
+        <v>31.63342475891113</v>
       </c>
       <c r="C706" t="n">
-        <v>32.11479891534272</v>
+        <v>32.1148008517161</v>
       </c>
       <c r="D706" t="n">
-        <v>31.44676361462388</v>
+        <v>31.44676551071783</v>
       </c>
       <c r="E706" t="n">
-        <v>31.60394817081799</v>
+        <v>31.60395007638945</v>
       </c>
       <c r="F706" t="n">
         <v>7302700</v>
@@ -14552,16 +14552,16 @@
         <v>45183</v>
       </c>
       <c r="B707" t="n">
-        <v>32.311279296875</v>
+        <v>32.31128311157227</v>
       </c>
       <c r="C707" t="n">
-        <v>32.311279296875</v>
+        <v>32.31128311157227</v>
       </c>
       <c r="D707" t="n">
-        <v>31.74148670806588</v>
+        <v>31.74149045549294</v>
       </c>
       <c r="E707" t="n">
-        <v>31.83972564654409</v>
+        <v>31.83972940556933</v>
       </c>
       <c r="F707" t="n">
         <v>4362300</v>
@@ -14592,16 +14592,16 @@
         <v>45187</v>
       </c>
       <c r="B709" t="n">
-        <v>31.98709297180176</v>
+        <v>31.98709106445312</v>
       </c>
       <c r="C709" t="n">
-        <v>32.71407022822005</v>
+        <v>32.7140682775227</v>
       </c>
       <c r="D709" t="n">
-        <v>31.75131423474054</v>
+        <v>31.75131234145109</v>
       </c>
       <c r="E709" t="n">
-        <v>32.55688565270453</v>
+        <v>32.5568837113799</v>
       </c>
       <c r="F709" t="n">
         <v>5099000</v>
@@ -14692,16 +14692,16 @@
         <v>45194</v>
       </c>
       <c r="B714" t="n">
-        <v>30.95556640625</v>
+        <v>30.95556449890137</v>
       </c>
       <c r="C714" t="n">
-        <v>31.20116753431566</v>
+        <v>31.20116561183414</v>
       </c>
       <c r="D714" t="n">
-        <v>29.99281043394172</v>
+        <v>29.99280858591396</v>
       </c>
       <c r="E714" t="n">
-        <v>30.45453988014151</v>
+        <v>30.45453800366397</v>
       </c>
       <c r="F714" t="n">
         <v>6350700</v>
@@ -14712,16 +14712,16 @@
         <v>45195</v>
       </c>
       <c r="B715" t="n">
-        <v>30.32682800292969</v>
+        <v>30.32682609558105</v>
       </c>
       <c r="C715" t="n">
-        <v>30.83767692328888</v>
+        <v>30.83767498381136</v>
       </c>
       <c r="D715" t="n">
-        <v>30.19911436749897</v>
+        <v>30.19911246818264</v>
       </c>
       <c r="E715" t="n">
-        <v>30.75908463755763</v>
+        <v>30.75908270302303</v>
       </c>
       <c r="F715" t="n">
         <v>3433500</v>
@@ -14732,16 +14732,16 @@
         <v>45196</v>
       </c>
       <c r="B716" t="n">
-        <v>30.86714744567871</v>
+        <v>30.86714935302734</v>
       </c>
       <c r="C716" t="n">
-        <v>31.07345147776449</v>
+        <v>31.0734533978611</v>
       </c>
       <c r="D716" t="n">
-        <v>30.42506470008381</v>
+        <v>30.42506658011519</v>
       </c>
       <c r="E716" t="n">
-        <v>30.65101914438107</v>
+        <v>30.65102103837466</v>
       </c>
       <c r="F716" t="n">
         <v>4307600</v>
@@ -14752,16 +14752,16 @@
         <v>45197</v>
       </c>
       <c r="B717" t="n">
-        <v>30.58225059509277</v>
+        <v>30.58224868774414</v>
       </c>
       <c r="C717" t="n">
-        <v>31.21099073558775</v>
+        <v>31.21098878902595</v>
       </c>
       <c r="D717" t="n">
-        <v>30.41524175877521</v>
+        <v>30.41523986184255</v>
       </c>
       <c r="E717" t="n">
-        <v>30.82785171474873</v>
+        <v>30.82784979208249</v>
       </c>
       <c r="F717" t="n">
         <v>4298000</v>
@@ -14772,16 +14772,16 @@
         <v>45198</v>
       </c>
       <c r="B718" t="n">
-        <v>31.02433204650879</v>
+        <v>31.02433395385742</v>
       </c>
       <c r="C718" t="n">
-        <v>31.60394894047274</v>
+        <v>31.60395088345571</v>
       </c>
       <c r="D718" t="n">
-        <v>30.47418608643163</v>
+        <v>30.47418795995777</v>
       </c>
       <c r="E718" t="n">
-        <v>30.86714748648674</v>
+        <v>30.86714938417181</v>
       </c>
       <c r="F718" t="n">
         <v>5846000</v>
@@ -14852,16 +14852,16 @@
         <v>45204</v>
       </c>
       <c r="B722" t="n">
-        <v>28.0378246307373</v>
+        <v>28.03782272338867</v>
       </c>
       <c r="C722" t="n">
-        <v>28.78445038319864</v>
+        <v>28.78444842505877</v>
       </c>
       <c r="D722" t="n">
-        <v>27.72345362458937</v>
+        <v>27.72345173862667</v>
       </c>
       <c r="E722" t="n">
-        <v>28.62726581701858</v>
+        <v>28.62726386957162</v>
       </c>
       <c r="F722" t="n">
         <v>8409300</v>
@@ -14912,16 +14912,16 @@
         <v>45209</v>
       </c>
       <c r="B725" t="n">
-        <v>30.2777042388916</v>
+        <v>30.27770614624023</v>
       </c>
       <c r="C725" t="n">
-        <v>30.40541786413846</v>
+        <v>30.40541977953243</v>
       </c>
       <c r="D725" t="n">
-        <v>29.43283582930937</v>
+        <v>29.43283768343539</v>
       </c>
       <c r="E725" t="n">
-        <v>29.7570310901109</v>
+        <v>29.75703296465965</v>
       </c>
       <c r="F725" t="n">
         <v>7018100</v>
@@ -14972,16 +14972,16 @@
         <v>45215</v>
       </c>
       <c r="B728" t="n">
-        <v>31.67272186279297</v>
+        <v>31.67271995544434</v>
       </c>
       <c r="C728" t="n">
-        <v>32.01656192935982</v>
+        <v>32.01656000130495</v>
       </c>
       <c r="D728" t="n">
-        <v>31.32887804865046</v>
+        <v>31.32887616200829</v>
       </c>
       <c r="E728" t="n">
-        <v>31.91832298107662</v>
+        <v>31.91832105893775</v>
       </c>
       <c r="F728" t="n">
         <v>3741500</v>
@@ -15012,16 +15012,16 @@
         <v>45217</v>
       </c>
       <c r="B730" t="n">
-        <v>32.06567764282227</v>
+        <v>32.06568145751953</v>
       </c>
       <c r="C730" t="n">
-        <v>33.06773053760736</v>
+        <v>33.06773447151397</v>
       </c>
       <c r="D730" t="n">
-        <v>31.63342107446555</v>
+        <v>31.63342483773936</v>
       </c>
       <c r="E730" t="n">
-        <v>32.52740889026767</v>
+        <v>32.52741275989484</v>
       </c>
       <c r="F730" t="n">
         <v>7439800</v>
@@ -15132,16 +15132,16 @@
         <v>45225</v>
       </c>
       <c r="B736" t="n">
-        <v>31.98709297180176</v>
+        <v>31.98709106445312</v>
       </c>
       <c r="C736" t="n">
-        <v>32.12462900693085</v>
+        <v>32.12462709138111</v>
       </c>
       <c r="D736" t="n">
-        <v>31.19134395024304</v>
+        <v>31.19134209034388</v>
       </c>
       <c r="E736" t="n">
-        <v>31.57448111883861</v>
+        <v>31.57447923609348</v>
       </c>
       <c r="F736" t="n">
         <v>2923500</v>
@@ -15152,16 +15152,16 @@
         <v>45226</v>
       </c>
       <c r="B737" t="n">
-        <v>31.52536010742188</v>
+        <v>31.52535820007324</v>
       </c>
       <c r="C737" t="n">
-        <v>32.55688406826494</v>
+        <v>32.556882098507</v>
       </c>
       <c r="D737" t="n">
-        <v>31.24046190704763</v>
+        <v>31.24046001693592</v>
       </c>
       <c r="E737" t="n">
-        <v>32.32110909025403</v>
+        <v>32.32110713476096</v>
       </c>
       <c r="F737" t="n">
         <v>3378100</v>
@@ -15172,16 +15172,16 @@
         <v>45229</v>
       </c>
       <c r="B738" t="n">
-        <v>31.07345199584961</v>
+        <v>31.07345390319824</v>
       </c>
       <c r="C738" t="n">
-        <v>32.11480019042821</v>
+        <v>32.11480216169681</v>
       </c>
       <c r="D738" t="n">
-        <v>30.98503731904426</v>
+        <v>30.98503922096583</v>
       </c>
       <c r="E738" t="n">
-        <v>31.5450075569423</v>
+        <v>31.54500949323592</v>
       </c>
       <c r="F738" t="n">
         <v>3227500</v>
@@ -15192,16 +15192,16 @@
         <v>45230</v>
       </c>
       <c r="B739" t="n">
-        <v>31.86919975280762</v>
+        <v>31.86919784545898</v>
       </c>
       <c r="C739" t="n">
-        <v>32.10497847524474</v>
+        <v>32.10497655378492</v>
       </c>
       <c r="D739" t="n">
-        <v>31.2011662851952</v>
+        <v>31.20116441782789</v>
       </c>
       <c r="E739" t="n">
-        <v>31.2011662851952</v>
+        <v>31.20116441782789</v>
       </c>
       <c r="F739" t="n">
         <v>3372100</v>
@@ -15212,16 +15212,16 @@
         <v>45231</v>
       </c>
       <c r="B740" t="n">
-        <v>32.06567764282227</v>
+        <v>32.06568145751953</v>
       </c>
       <c r="C740" t="n">
-        <v>32.74353904823363</v>
+        <v>32.74354294357276</v>
       </c>
       <c r="D740" t="n">
-        <v>31.9477901691932</v>
+        <v>31.94779396986597</v>
       </c>
       <c r="E740" t="n">
-        <v>32.07550378504357</v>
+        <v>32.0755076009098</v>
       </c>
       <c r="F740" t="n">
         <v>4282500</v>
@@ -15232,16 +15232,16 @@
         <v>45233</v>
       </c>
       <c r="B741" t="n">
-        <v>32.69441986083984</v>
+        <v>32.69441604614258</v>
       </c>
       <c r="C741" t="n">
-        <v>32.94984712401398</v>
+        <v>32.94984327951414</v>
       </c>
       <c r="D741" t="n">
-        <v>32.46846728038622</v>
+        <v>32.4684634920525</v>
       </c>
       <c r="E741" t="n">
-        <v>32.73371693941674</v>
+        <v>32.7337131201344</v>
       </c>
       <c r="F741" t="n">
         <v>3190300</v>
@@ -15272,16 +15272,16 @@
         <v>45237</v>
       </c>
       <c r="B743" t="n">
-        <v>32.48811721801758</v>
+        <v>32.48811340332031</v>
       </c>
       <c r="C743" t="n">
-        <v>32.63547939523581</v>
+        <v>32.63547556323554</v>
       </c>
       <c r="D743" t="n">
-        <v>31.81025944748058</v>
+        <v>31.81025571237618</v>
       </c>
       <c r="E743" t="n">
-        <v>31.8790274641622</v>
+        <v>31.87902372098318</v>
       </c>
       <c r="F743" t="n">
         <v>3324000</v>
@@ -15312,16 +15312,16 @@
         <v>45239</v>
       </c>
       <c r="B745" t="n">
-        <v>30.81802749633789</v>
+        <v>30.81802940368652</v>
       </c>
       <c r="C745" t="n">
-        <v>33.77506502697286</v>
+        <v>33.77506711733456</v>
       </c>
       <c r="D745" t="n">
-        <v>30.67066533422895</v>
+        <v>30.67066723245724</v>
       </c>
       <c r="E745" t="n">
-        <v>33.41157269312426</v>
+        <v>33.41157476098916</v>
       </c>
       <c r="F745" t="n">
         <v>15431300</v>
@@ -15332,16 +15332,16 @@
         <v>45240</v>
       </c>
       <c r="B746" t="n">
-        <v>31.25028610229492</v>
+        <v>31.25028419494629</v>
       </c>
       <c r="C746" t="n">
-        <v>32.06568174882637</v>
+        <v>32.06567979171039</v>
       </c>
       <c r="D746" t="n">
-        <v>31.04398206013306</v>
+        <v>31.04398016537612</v>
       </c>
       <c r="E746" t="n">
-        <v>31.05380632982475</v>
+        <v>31.05380443446818</v>
       </c>
       <c r="F746" t="n">
         <v>4738300</v>
@@ -15352,16 +15352,16 @@
         <v>45243</v>
       </c>
       <c r="B747" t="n">
-        <v>30.94573974609375</v>
+        <v>30.94574165344238</v>
       </c>
       <c r="C747" t="n">
-        <v>31.41729342584897</v>
+        <v>31.41729536226194</v>
       </c>
       <c r="D747" t="n">
-        <v>30.67066582934266</v>
+        <v>30.67066771973704</v>
       </c>
       <c r="E747" t="n">
-        <v>31.21098939362647</v>
+        <v>31.21099131732383</v>
       </c>
       <c r="F747" t="n">
         <v>3172300</v>
@@ -15392,16 +15392,16 @@
         <v>45246</v>
       </c>
       <c r="B749" t="n">
-        <v>31.13239860534668</v>
+        <v>31.13239669799805</v>
       </c>
       <c r="C749" t="n">
-        <v>32.13444975439192</v>
+        <v>32.13444778565191</v>
       </c>
       <c r="D749" t="n">
-        <v>30.68049156858774</v>
+        <v>30.68048968892551</v>
       </c>
       <c r="E749" t="n">
-        <v>31.78078354073604</v>
+        <v>31.78078159366364</v>
       </c>
       <c r="F749" t="n">
         <v>5148500</v>
@@ -15492,16 +15492,16 @@
         <v>45253</v>
       </c>
       <c r="B754" t="n">
-        <v>31.81025505065918</v>
+        <v>31.81025886535645</v>
       </c>
       <c r="C754" t="n">
-        <v>32.00673667726713</v>
+        <v>32.00674051552654</v>
       </c>
       <c r="D754" t="n">
-        <v>31.5843024917114</v>
+        <v>31.58430627931235</v>
       </c>
       <c r="E754" t="n">
-        <v>31.82990358807751</v>
+        <v>31.82990740513103</v>
       </c>
       <c r="F754" t="n">
         <v>2086300</v>
@@ -15552,16 +15552,16 @@
         <v>45258</v>
       </c>
       <c r="B757" t="n">
-        <v>29.80615043640137</v>
+        <v>29.80615234375</v>
       </c>
       <c r="C757" t="n">
-        <v>30.21876037029583</v>
+        <v>30.21876230404811</v>
       </c>
       <c r="D757" t="n">
-        <v>29.63914160902057</v>
+        <v>29.63914350568201</v>
       </c>
       <c r="E757" t="n">
-        <v>30.17946329383553</v>
+        <v>30.17946522507312</v>
       </c>
       <c r="F757" t="n">
         <v>5777500</v>
@@ -15592,16 +15592,16 @@
         <v>45260</v>
       </c>
       <c r="B759" t="n">
-        <v>29.45248603820801</v>
+        <v>29.45248413085938</v>
       </c>
       <c r="C759" t="n">
-        <v>29.83562506189301</v>
+        <v>29.83562312973222</v>
       </c>
       <c r="D759" t="n">
-        <v>29.1774139813743</v>
+        <v>29.17741209183939</v>
       </c>
       <c r="E759" t="n">
-        <v>29.66861622433489</v>
+        <v>29.66861430298963</v>
       </c>
       <c r="F759" t="n">
         <v>4483800</v>
@@ -15732,16 +15732,16 @@
         <v>45271</v>
       </c>
       <c r="B766" t="n">
-        <v>26.91788101196289</v>
+        <v>26.91788291931152</v>
       </c>
       <c r="C766" t="n">
-        <v>27.08488984004369</v>
+        <v>27.08489175922624</v>
       </c>
       <c r="D766" t="n">
-        <v>26.48562253802652</v>
+        <v>26.48562441474616</v>
       </c>
       <c r="E766" t="n">
-        <v>26.96700235774415</v>
+        <v>26.96700426857343</v>
       </c>
       <c r="F766" t="n">
         <v>6627000</v>
@@ -15792,16 +15792,16 @@
         <v>45274</v>
       </c>
       <c r="B769" t="n">
-        <v>27.00629997253418</v>
+        <v>27.00629806518555</v>
       </c>
       <c r="C769" t="n">
-        <v>27.20278162563166</v>
+        <v>27.2027797044063</v>
       </c>
       <c r="D769" t="n">
-        <v>26.49544917351107</v>
+        <v>26.49544730224182</v>
       </c>
       <c r="E769" t="n">
-        <v>26.82946685950403</v>
+        <v>26.82946496464443</v>
       </c>
       <c r="F769" t="n">
         <v>14011300</v>
@@ -15812,16 +15812,16 @@
         <v>45275</v>
       </c>
       <c r="B770" t="n">
-        <v>25.8863582611084</v>
+        <v>25.88635635375977</v>
       </c>
       <c r="C770" t="n">
-        <v>27.21260467558413</v>
+        <v>27.21260267051552</v>
       </c>
       <c r="D770" t="n">
-        <v>25.8863582611084</v>
+        <v>25.88635635375977</v>
       </c>
       <c r="E770" t="n">
-        <v>27.16348332761816</v>
+        <v>27.1634813261689</v>
       </c>
       <c r="F770" t="n">
         <v>11924000</v>
@@ -15832,16 +15832,16 @@
         <v>45278</v>
       </c>
       <c r="B771" t="n">
-        <v>26.21055221557617</v>
+        <v>26.21055030822754</v>
       </c>
       <c r="C771" t="n">
-        <v>26.76069820788825</v>
+        <v>26.76069626050536</v>
       </c>
       <c r="D771" t="n">
-        <v>25.94530255232668</v>
+        <v>25.94530066428034</v>
       </c>
       <c r="E771" t="n">
-        <v>26.12213566115967</v>
+        <v>26.12213376024514</v>
       </c>
       <c r="F771" t="n">
         <v>4958200</v>
@@ -15852,16 +15852,16 @@
         <v>45279</v>
       </c>
       <c r="B772" t="n">
-        <v>26.32843780517578</v>
+        <v>26.32843971252441</v>
       </c>
       <c r="C772" t="n">
-        <v>26.52491943942738</v>
+        <v>26.52492136101001</v>
       </c>
       <c r="D772" t="n">
-        <v>26.13195804471192</v>
+        <v>26.13195993782669</v>
       </c>
       <c r="E772" t="n">
-        <v>26.30879114078081</v>
+        <v>26.30879304670615</v>
       </c>
       <c r="F772" t="n">
         <v>3900900</v>
@@ -15872,16 +15872,16 @@
         <v>45280</v>
       </c>
       <c r="B773" t="n">
-        <v>25.85688400268555</v>
+        <v>25.85688591003418</v>
       </c>
       <c r="C773" t="n">
-        <v>26.54456784535201</v>
+        <v>26.54456980342805</v>
       </c>
       <c r="D773" t="n">
-        <v>25.68987517654013</v>
+        <v>25.68987707156926</v>
       </c>
       <c r="E773" t="n">
-        <v>26.54456784535201</v>
+        <v>26.54456980342805</v>
       </c>
       <c r="F773" t="n">
         <v>6168300</v>
@@ -15912,16 +15912,16 @@
         <v>45282</v>
       </c>
       <c r="B775" t="n">
-        <v>25.95512771606445</v>
+        <v>25.95512580871582</v>
       </c>
       <c r="C775" t="n">
-        <v>26.22037738844958</v>
+        <v>26.2203754616087</v>
       </c>
       <c r="D775" t="n">
-        <v>25.79794314141873</v>
+        <v>25.79794124562103</v>
       </c>
       <c r="E775" t="n">
-        <v>26.03372000338731</v>
+        <v>26.03371809026321</v>
       </c>
       <c r="F775" t="n">
         <v>3644200</v>
@@ -16012,16 +16012,16 @@
         <v>45294</v>
       </c>
       <c r="B780" t="n">
-        <v>25.8863582611084</v>
+        <v>25.88635635375977</v>
       </c>
       <c r="C780" t="n">
-        <v>26.28914394549015</v>
+        <v>26.28914200846361</v>
       </c>
       <c r="D780" t="n">
-        <v>25.35585894580298</v>
+        <v>25.35585707754239</v>
       </c>
       <c r="E780" t="n">
-        <v>25.64075714264207</v>
+        <v>25.64075525338972</v>
       </c>
       <c r="F780" t="n">
         <v>5734800</v>
@@ -16052,16 +16052,16 @@
         <v>45296</v>
       </c>
       <c r="B782" t="n">
-        <v>25.68987655639648</v>
+        <v>25.68987464904785</v>
       </c>
       <c r="C782" t="n">
-        <v>25.97477475256549</v>
+        <v>25.97477282406455</v>
       </c>
       <c r="D782" t="n">
-        <v>25.21832285975933</v>
+        <v>25.21832098742127</v>
       </c>
       <c r="E782" t="n">
-        <v>25.36568315573496</v>
+        <v>25.36568127245611</v>
       </c>
       <c r="F782" t="n">
         <v>3417300</v>
@@ -16092,16 +16092,16 @@
         <v>45300</v>
       </c>
       <c r="B784" t="n">
-        <v>28.0181770324707</v>
+        <v>28.01817512512207</v>
       </c>
       <c r="C784" t="n">
-        <v>28.24412961971936</v>
+        <v>28.24412769698892</v>
       </c>
       <c r="D784" t="n">
-        <v>26.7999956667704</v>
+        <v>26.79999384234995</v>
       </c>
       <c r="E784" t="n">
-        <v>27.01612398407939</v>
+        <v>27.01612214494592</v>
       </c>
       <c r="F784" t="n">
         <v>10290300</v>
@@ -16152,16 +16152,16 @@
         <v>45303</v>
       </c>
       <c r="B787" t="n">
-        <v>28.20483016967773</v>
+        <v>28.20483207702637</v>
       </c>
       <c r="C787" t="n">
-        <v>28.86304121001741</v>
+        <v>28.86304316187749</v>
       </c>
       <c r="D787" t="n">
-        <v>27.82169304316834</v>
+        <v>27.82169492460737</v>
       </c>
       <c r="E787" t="n">
-        <v>28.63708864175739</v>
+        <v>28.63709057833746</v>
       </c>
       <c r="F787" t="n">
         <v>5067700</v>
@@ -16172,16 +16172,16 @@
         <v>45306</v>
       </c>
       <c r="B788" t="n">
-        <v>28.52902603149414</v>
+        <v>28.52902793884277</v>
       </c>
       <c r="C788" t="n">
-        <v>28.68621059306261</v>
+        <v>28.68621251092004</v>
       </c>
       <c r="D788" t="n">
-        <v>27.90028591143248</v>
+        <v>27.9002877767458</v>
       </c>
       <c r="E788" t="n">
-        <v>28.06729474232245</v>
+        <v>28.06729661880138</v>
       </c>
       <c r="F788" t="n">
         <v>3859400</v>
@@ -16252,16 +16252,16 @@
         <v>45310</v>
       </c>
       <c r="B792" t="n">
-        <v>29.03005218505859</v>
+        <v>29.03005027770996</v>
       </c>
       <c r="C792" t="n">
-        <v>29.19706102477754</v>
+        <v>29.197059106456</v>
       </c>
       <c r="D792" t="n">
-        <v>28.05747195626752</v>
+        <v>28.0574701128199</v>
       </c>
       <c r="E792" t="n">
-        <v>28.73533158498416</v>
+        <v>28.73532969699943</v>
       </c>
       <c r="F792" t="n">
         <v>7851200</v>
@@ -16312,16 +16312,16 @@
         <v>45315</v>
       </c>
       <c r="B795" t="n">
-        <v>27.86099052429199</v>
+        <v>27.86099243164062</v>
       </c>
       <c r="C795" t="n">
-        <v>28.52902584344861</v>
+        <v>28.52902779653059</v>
       </c>
       <c r="D795" t="n">
-        <v>27.63503607896236</v>
+        <v>27.63503797084227</v>
       </c>
       <c r="E795" t="n">
-        <v>28.04764601880687</v>
+        <v>28.04764793893384</v>
       </c>
       <c r="F795" t="n">
         <v>4070600</v>
@@ -16352,16 +16352,16 @@
         <v>45317</v>
       </c>
       <c r="B797" t="n">
-        <v>28.2441291809082</v>
+        <v>28.24412727355957</v>
       </c>
       <c r="C797" t="n">
-        <v>28.2441291809082</v>
+        <v>28.24412727355957</v>
       </c>
       <c r="D797" t="n">
-        <v>27.50732581097147</v>
+        <v>27.50732395337975</v>
       </c>
       <c r="E797" t="n">
-        <v>27.65468611020124</v>
+        <v>27.65468424265817</v>
       </c>
       <c r="F797" t="n">
         <v>2761100</v>
@@ -16392,16 +16392,16 @@
         <v>45321</v>
       </c>
       <c r="B799" t="n">
-        <v>27.24207496643066</v>
+        <v>27.2420768737793</v>
       </c>
       <c r="C799" t="n">
-        <v>27.54662169525507</v>
+        <v>27.54662362392648</v>
       </c>
       <c r="D799" t="n">
-        <v>26.97682531504984</v>
+        <v>26.97682720382707</v>
       </c>
       <c r="E799" t="n">
-        <v>27.36978859433452</v>
+        <v>27.369790510625</v>
       </c>
       <c r="F799" t="n">
         <v>2184900</v>
@@ -16432,16 +16432,16 @@
         <v>45323</v>
       </c>
       <c r="B801" t="n">
-        <v>26.24002075195312</v>
+        <v>26.24002265930176</v>
       </c>
       <c r="C801" t="n">
-        <v>27.4090825182884</v>
+        <v>27.40908451061442</v>
       </c>
       <c r="D801" t="n">
-        <v>26.10248473489757</v>
+        <v>26.10248663224892</v>
       </c>
       <c r="E801" t="n">
-        <v>27.31084170305399</v>
+        <v>27.31084368823903</v>
       </c>
       <c r="F801" t="n">
         <v>7611700</v>
@@ -16532,16 +16532,16 @@
         <v>45330</v>
       </c>
       <c r="B806" t="n">
-        <v>28.79427337646484</v>
+        <v>28.79427528381348</v>
       </c>
       <c r="C806" t="n">
-        <v>28.81392191481336</v>
+        <v>28.81392382346353</v>
       </c>
       <c r="D806" t="n">
-        <v>27.39925900811183</v>
+        <v>27.39926082305394</v>
       </c>
       <c r="E806" t="n">
-        <v>28.71568109685852</v>
+        <v>28.71568299900116</v>
       </c>
       <c r="F806" t="n">
         <v>6908300</v>
@@ -16552,16 +16552,16 @@
         <v>45331</v>
       </c>
       <c r="B807" t="n">
-        <v>27.69398307800293</v>
+        <v>27.6939811706543</v>
       </c>
       <c r="C807" t="n">
-        <v>28.9121644198793</v>
+        <v>28.9121624286317</v>
       </c>
       <c r="D807" t="n">
-        <v>27.52697423987057</v>
+        <v>27.52697234402422</v>
       </c>
       <c r="E807" t="n">
-        <v>28.83357213568689</v>
+        <v>28.83357014985212</v>
       </c>
       <c r="F807" t="n">
         <v>5513900</v>
@@ -16592,16 +16592,16 @@
         <v>45337</v>
       </c>
       <c r="B809" t="n">
-        <v>28.00835037231445</v>
+        <v>28.00835227966309</v>
       </c>
       <c r="C809" t="n">
-        <v>28.26377574758426</v>
+        <v>28.26377767232718</v>
       </c>
       <c r="D809" t="n">
-        <v>27.28137132291011</v>
+        <v>27.28137318075199</v>
       </c>
       <c r="E809" t="n">
-        <v>27.40908307365115</v>
+        <v>27.40908494019011</v>
       </c>
       <c r="F809" t="n">
         <v>2788300</v>
@@ -16632,16 +16632,16 @@
         <v>45341</v>
       </c>
       <c r="B811" t="n">
-        <v>28.6763858795166</v>
+        <v>28.67638778686523</v>
       </c>
       <c r="C811" t="n">
-        <v>28.76480242825268</v>
+        <v>28.76480434148215</v>
       </c>
       <c r="D811" t="n">
-        <v>28.2343031358362</v>
+        <v>28.23430501378064</v>
       </c>
       <c r="E811" t="n">
-        <v>28.74515388991405</v>
+        <v>28.74515580183664</v>
       </c>
       <c r="F811" t="n">
         <v>1698200</v>
@@ -16672,16 +16672,16 @@
         <v>45343</v>
       </c>
       <c r="B813" t="n">
-        <v>28.92198753356934</v>
+        <v>28.92198944091797</v>
       </c>
       <c r="C813" t="n">
-        <v>28.98093127591061</v>
+        <v>28.98093318714647</v>
       </c>
       <c r="D813" t="n">
-        <v>28.36201729685779</v>
+        <v>28.36201916727748</v>
       </c>
       <c r="E813" t="n">
-        <v>28.63708934364225</v>
+        <v>28.6370912322024</v>
       </c>
       <c r="F813" t="n">
         <v>2751400</v>
@@ -16792,16 +16792,16 @@
         <v>45351</v>
       </c>
       <c r="B819" t="n">
-        <v>27.45820426940918</v>
+        <v>27.45820617675781</v>
       </c>
       <c r="C819" t="n">
-        <v>28.14588623865804</v>
+        <v>28.14588819377561</v>
       </c>
       <c r="D819" t="n">
-        <v>27.45820426940918</v>
+        <v>27.45820617675781</v>
       </c>
       <c r="E819" t="n">
-        <v>27.98870168147043</v>
+        <v>27.98870362566938</v>
       </c>
       <c r="F819" t="n">
         <v>2784300</v>
@@ -16972,16 +16972,16 @@
         <v>45364</v>
       </c>
       <c r="B828" t="n">
-        <v>29.13811492919922</v>
+        <v>29.13811683654785</v>
       </c>
       <c r="C828" t="n">
-        <v>29.36406749594983</v>
+        <v>29.36406941808906</v>
       </c>
       <c r="D828" t="n">
-        <v>28.98093037199986</v>
+        <v>28.98093226905937</v>
       </c>
       <c r="E828" t="n">
-        <v>28.98093037199986</v>
+        <v>28.98093226905937</v>
       </c>
       <c r="F828" t="n">
         <v>2596400</v>
@@ -17032,16 +17032,16 @@
         <v>45369</v>
       </c>
       <c r="B831" t="n">
-        <v>28.98093223571777</v>
+        <v>28.98093032836914</v>
       </c>
       <c r="C831" t="n">
-        <v>29.28547710065286</v>
+        <v>29.28547517326093</v>
       </c>
       <c r="D831" t="n">
-        <v>28.61744175270144</v>
+        <v>28.61743986927554</v>
       </c>
       <c r="E831" t="n">
-        <v>28.77462819379693</v>
+        <v>28.77462630002598</v>
       </c>
       <c r="F831" t="n">
         <v>4710300</v>
@@ -17112,16 +17112,16 @@
         <v>45373</v>
       </c>
       <c r="B835" t="n">
-        <v>29.71773529052734</v>
+        <v>29.71773338317871</v>
       </c>
       <c r="C835" t="n">
-        <v>30.0026334869456</v>
+        <v>30.00263156131158</v>
       </c>
       <c r="D835" t="n">
-        <v>29.28547679800454</v>
+        <v>29.28547491839919</v>
       </c>
       <c r="E835" t="n">
-        <v>29.88474412578926</v>
+        <v>29.88474220772164</v>
       </c>
       <c r="F835" t="n">
         <v>3854000</v>
@@ -17152,16 +17152,16 @@
         <v>45377</v>
       </c>
       <c r="B837" t="n">
-        <v>30.81802749633789</v>
+        <v>30.81802940368652</v>
       </c>
       <c r="C837" t="n">
-        <v>31.22081315885015</v>
+        <v>31.22081509112746</v>
       </c>
       <c r="D837" t="n">
-        <v>30.51348077684796</v>
+        <v>30.51348266534799</v>
       </c>
       <c r="E837" t="n">
-        <v>30.61172159365801</v>
+        <v>30.61172348823823</v>
       </c>
       <c r="F837" t="n">
         <v>3327200</v>
@@ -17172,16 +17172,16 @@
         <v>45378</v>
       </c>
       <c r="B838" t="n">
-        <v>31.48606109619141</v>
+        <v>31.48606300354004</v>
       </c>
       <c r="C838" t="n">
-        <v>31.91832144197546</v>
+        <v>31.91832337550937</v>
       </c>
       <c r="D838" t="n">
-        <v>30.3857691886579</v>
+        <v>30.38577102935353</v>
       </c>
       <c r="E838" t="n">
-        <v>30.65101883332299</v>
+        <v>30.6510206900868</v>
       </c>
       <c r="F838" t="n">
         <v>9071000</v>
@@ -17372,16 +17372,16 @@
         <v>45393</v>
       </c>
       <c r="B848" t="n">
-        <v>35.62198638916016</v>
+        <v>35.62198257446289</v>
       </c>
       <c r="C848" t="n">
-        <v>35.91671074440308</v>
+        <v>35.91670689814429</v>
       </c>
       <c r="D848" t="n">
-        <v>34.59046238853748</v>
+        <v>34.59045868430435</v>
       </c>
       <c r="E848" t="n">
-        <v>34.74764696246498</v>
+        <v>34.74764324139922</v>
       </c>
       <c r="F848" t="n">
         <v>5960900</v>
@@ -17412,16 +17412,16 @@
         <v>45397</v>
       </c>
       <c r="B850" t="n">
-        <v>34.06978607177734</v>
+        <v>34.06978988647461</v>
       </c>
       <c r="C850" t="n">
-        <v>34.52169121201051</v>
+        <v>34.52169507730631</v>
       </c>
       <c r="D850" t="n">
-        <v>33.83400735867823</v>
+        <v>33.83401114697602</v>
       </c>
       <c r="E850" t="n">
-        <v>34.43327466304528</v>
+        <v>34.43327851844133</v>
       </c>
       <c r="F850" t="n">
         <v>4151100</v>
@@ -17472,16 +17472,16 @@
         <v>45400</v>
       </c>
       <c r="B853" t="n">
-        <v>32.3309326171875</v>
+        <v>32.33092880249023</v>
       </c>
       <c r="C853" t="n">
-        <v>33.28386620122118</v>
+        <v>33.28386227408815</v>
       </c>
       <c r="D853" t="n">
-        <v>31.93796930998834</v>
+        <v>31.93796554165645</v>
       </c>
       <c r="E853" t="n">
-        <v>33.00879038715143</v>
+        <v>33.00878649247434</v>
       </c>
       <c r="F853" t="n">
         <v>4478700</v>
@@ -17632,16 +17632,16 @@
         <v>45412</v>
       </c>
       <c r="B861" t="n">
-        <v>32.58635711669922</v>
+        <v>32.58635330200195</v>
       </c>
       <c r="C861" t="n">
-        <v>33.66700436998067</v>
+        <v>33.66700042877825</v>
       </c>
       <c r="D861" t="n">
-        <v>32.43899868278081</v>
+        <v>32.43899488533395</v>
       </c>
       <c r="E861" t="n">
-        <v>33.60805874786774</v>
+        <v>33.60805481356574</v>
       </c>
       <c r="F861" t="n">
         <v>6661700</v>
@@ -29632,19 +29632,39 @@
         <v>46289</v>
       </c>
       <c r="B1461" t="n">
-        <v>17.48</v>
+        <v>17.47999954223633</v>
       </c>
       <c r="C1461" t="n">
         <v>17.75</v>
       </c>
       <c r="D1461" t="n">
-        <v>17.48</v>
+        <v>17.47999954223633</v>
       </c>
       <c r="E1461" t="n">
-        <v>17.65</v>
+        <v>17.64999961853027</v>
       </c>
       <c r="F1461" t="n">
         <v>1398600</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1462" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="C1462" t="n">
+        <v>17.53</v>
+      </c>
+      <c r="D1462" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="E1462" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="F1462" t="n">
+        <v>1425800</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1462"/>
+  <dimension ref="A1:F1463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29652,19 +29652,39 @@
         <v>46290</v>
       </c>
       <c r="B1462" t="n">
-        <v>17.41</v>
+        <v>17.40999984741211</v>
       </c>
       <c r="C1462" t="n">
-        <v>17.53</v>
+        <v>17.53000068664551</v>
       </c>
       <c r="D1462" t="n">
-        <v>17.3</v>
+        <v>17.29999923706055</v>
       </c>
       <c r="E1462" t="n">
-        <v>17.41</v>
+        <v>17.40999984741211</v>
       </c>
       <c r="F1462" t="n">
         <v>1425800</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B1463" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="C1463" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="D1463" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="E1463" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="F1463" t="n">
+        <v>2470500</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1463"/>
+  <dimension ref="A1:F1464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29672,19 +29672,39 @@
         <v>46293</v>
       </c>
       <c r="B1463" t="n">
-        <v>17.96</v>
+        <v>17.95999908447266</v>
       </c>
       <c r="C1463" t="n">
-        <v>18.03</v>
+        <v>18.03000068664551</v>
       </c>
       <c r="D1463" t="n">
-        <v>17.38</v>
+        <v>17.3799991607666</v>
       </c>
       <c r="E1463" t="n">
-        <v>17.43</v>
+        <v>17.43000030517578</v>
       </c>
       <c r="F1463" t="n">
         <v>2470500</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B1464" t="n">
+        <v>18.23</v>
+      </c>
+      <c r="C1464" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="D1464" t="n">
+        <v>17.62</v>
+      </c>
+      <c r="E1464" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="F1464" t="n">
+        <v>3499500</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1464"/>
+  <dimension ref="A1:F1465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29692,19 +29692,39 @@
         <v>46294</v>
       </c>
       <c r="B1464" t="n">
-        <v>18.23</v>
+        <v>18.22999954223633</v>
       </c>
       <c r="C1464" t="n">
-        <v>18.42</v>
+        <v>18.42000007629395</v>
       </c>
       <c r="D1464" t="n">
-        <v>17.62</v>
+        <v>17.6200008392334</v>
       </c>
       <c r="E1464" t="n">
         <v>17.75</v>
       </c>
       <c r="F1464" t="n">
         <v>3499500</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1465" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="C1465" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="D1465" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="E1465" t="n">
+        <v>18.49</v>
+      </c>
+      <c r="F1465" t="n">
+        <v>1866200</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1465"/>
+  <dimension ref="A1:F1466"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29712,19 +29712,39 @@
         <v>46295</v>
       </c>
       <c r="B1465" t="n">
-        <v>18.12</v>
+        <v>18.1200008392334</v>
       </c>
       <c r="C1465" t="n">
-        <v>18.59</v>
+        <v>18.59000015258789</v>
       </c>
       <c r="D1465" t="n">
-        <v>18.12</v>
+        <v>18.1200008392334</v>
       </c>
       <c r="E1465" t="n">
-        <v>18.49</v>
+        <v>18.48999977111816</v>
       </c>
       <c r="F1465" t="n">
         <v>1866200</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1466" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="C1466" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="D1466" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="E1466" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="F1466" t="n">
+        <v>5236000</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1466"/>
+  <dimension ref="A1:F1467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29732,19 +29732,39 @@
         <v>46296</v>
       </c>
       <c r="B1466" t="n">
-        <v>18.18</v>
+        <v>18.25</v>
       </c>
       <c r="C1466" t="n">
-        <v>18.5</v>
+        <v>18.59000015258789</v>
       </c>
       <c r="D1466" t="n">
-        <v>18.13</v>
+        <v>18.1200008392334</v>
       </c>
       <c r="E1466" t="n">
-        <v>18.26</v>
+        <v>18.48999977111816</v>
       </c>
       <c r="F1466" t="n">
         <v>5236000</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B1467" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="C1467" t="n">
+        <v>19</v>
+      </c>
+      <c r="D1467" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="E1467" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="F1467" t="n">
+        <v>3277100</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1467"/>
+  <dimension ref="A1:F1468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,16 +512,16 @@
         <v>44152</v>
       </c>
       <c r="B5" t="n">
-        <v>20.17695617675781</v>
+        <v>20.17695426940918</v>
       </c>
       <c r="C5" t="n">
-        <v>20.17695617675781</v>
+        <v>20.17695426940918</v>
       </c>
       <c r="D5" t="n">
-        <v>19.85012633435968</v>
+        <v>19.85012445790661</v>
       </c>
       <c r="E5" t="n">
-        <v>20.12889164196659</v>
+        <v>20.12888973916155</v>
       </c>
       <c r="F5" t="n">
         <v>262242</v>
@@ -572,16 +572,16 @@
         <v>44158</v>
       </c>
       <c r="B8" t="n">
-        <v>20.2057933807373</v>
+        <v>20.20579147338867</v>
       </c>
       <c r="C8" t="n">
-        <v>20.52301068477087</v>
+        <v>20.52300874747816</v>
       </c>
       <c r="D8" t="n">
-        <v>20.14811818865408</v>
+        <v>20.14811628674976</v>
       </c>
       <c r="E8" t="n">
-        <v>20.14811818865408</v>
+        <v>20.14811628674976</v>
       </c>
       <c r="F8" t="n">
         <v>79408</v>
@@ -632,16 +632,16 @@
         <v>44161</v>
       </c>
       <c r="B11" t="n">
-        <v>22.87811088562012</v>
+        <v>22.87810897827148</v>
       </c>
       <c r="C11" t="n">
-        <v>22.87811088562012</v>
+        <v>22.87810897827148</v>
       </c>
       <c r="D11" t="n">
-        <v>22.3109640047031</v>
+        <v>22.31096214463751</v>
       </c>
       <c r="E11" t="n">
-        <v>22.3109640047031</v>
+        <v>22.31096214463751</v>
       </c>
       <c r="F11" t="n">
         <v>72970</v>
@@ -652,16 +652,16 @@
         <v>44162</v>
       </c>
       <c r="B12" t="n">
-        <v>23.07036209106445</v>
+        <v>23.07036399841309</v>
       </c>
       <c r="C12" t="n">
-        <v>23.55099428329309</v>
+        <v>23.55099623037812</v>
       </c>
       <c r="D12" t="n">
-        <v>22.10909770660719</v>
+        <v>22.10909953448302</v>
       </c>
       <c r="E12" t="n">
-        <v>23.07036209106445</v>
+        <v>23.07036399841309</v>
       </c>
       <c r="F12" t="n">
         <v>72050</v>
@@ -692,16 +692,16 @@
         <v>44166</v>
       </c>
       <c r="B14" t="n">
-        <v>23.07036209106445</v>
+        <v>23.07036399841309</v>
       </c>
       <c r="C14" t="n">
-        <v>23.1664892790253</v>
+        <v>23.16649119432127</v>
       </c>
       <c r="D14" t="n">
-        <v>23.03191196539523</v>
+        <v>23.03191386956499</v>
       </c>
       <c r="E14" t="n">
-        <v>23.12803727956828</v>
+        <v>23.12803919168523</v>
       </c>
       <c r="F14" t="n">
         <v>93512</v>
@@ -792,16 +792,16 @@
         <v>44173</v>
       </c>
       <c r="B19" t="n">
-        <v>26.33866500854492</v>
+        <v>26.33866310119629</v>
       </c>
       <c r="C19" t="n">
-        <v>26.57898205078916</v>
+        <v>26.57898012603766</v>
       </c>
       <c r="D19" t="n">
-        <v>25.56965309666637</v>
+        <v>25.56965124500673</v>
       </c>
       <c r="E19" t="n">
-        <v>25.56965309666637</v>
+        <v>25.56965124500673</v>
       </c>
       <c r="F19" t="n">
         <v>126420</v>
@@ -812,16 +812,16 @@
         <v>44174</v>
       </c>
       <c r="B20" t="n">
-        <v>26.83852005004883</v>
+        <v>26.83852195739746</v>
       </c>
       <c r="C20" t="n">
-        <v>27.77094867230641</v>
+        <v>27.77095064592048</v>
       </c>
       <c r="D20" t="n">
-        <v>26.27137510044991</v>
+        <v>26.27137696749292</v>
       </c>
       <c r="E20" t="n">
-        <v>26.4924651869397</v>
+        <v>26.49246706969505</v>
       </c>
       <c r="F20" t="n">
         <v>212880</v>
@@ -892,16 +892,16 @@
         <v>44180</v>
       </c>
       <c r="B24" t="n">
-        <v>33.00984191894531</v>
+        <v>33.00984573364258</v>
       </c>
       <c r="C24" t="n">
-        <v>33.9807187406613</v>
+        <v>33.98072266755544</v>
       </c>
       <c r="D24" t="n">
-        <v>30.7604798048412</v>
+        <v>30.76048335959674</v>
       </c>
       <c r="E24" t="n">
-        <v>30.7604798048412</v>
+        <v>30.76048335959674</v>
       </c>
       <c r="F24" t="n">
         <v>887803</v>
@@ -912,16 +912,16 @@
         <v>44181</v>
       </c>
       <c r="B25" t="n">
-        <v>32.68301773071289</v>
+        <v>32.68301391601562</v>
       </c>
       <c r="C25" t="n">
-        <v>34.4517423806715</v>
+        <v>34.45173835953219</v>
       </c>
       <c r="D25" t="n">
-        <v>32.10625830770921</v>
+        <v>32.10625456033017</v>
       </c>
       <c r="E25" t="n">
-        <v>33.62505712226533</v>
+        <v>33.62505319761509</v>
       </c>
       <c r="F25" t="n">
         <v>376808</v>
@@ -932,16 +932,16 @@
         <v>44182</v>
       </c>
       <c r="B26" t="n">
-        <v>32.10625457763672</v>
+        <v>32.10625839233398</v>
       </c>
       <c r="C26" t="n">
-        <v>33.64427827776851</v>
+        <v>33.64428227520571</v>
       </c>
       <c r="D26" t="n">
-        <v>31.64484559380946</v>
+        <v>31.64484935368452</v>
       </c>
       <c r="E26" t="n">
-        <v>33.62505321574033</v>
+        <v>33.6250572108933</v>
       </c>
       <c r="F26" t="n">
         <v>258257</v>
@@ -972,16 +972,16 @@
         <v>44186</v>
       </c>
       <c r="B28" t="n">
-        <v>32.18315505981445</v>
+        <v>32.18315887451172</v>
       </c>
       <c r="C28" t="n">
-        <v>33.33667378019659</v>
+        <v>33.33667773162143</v>
       </c>
       <c r="D28" t="n">
-        <v>29.12633082555934</v>
+        <v>29.12633427792858</v>
       </c>
       <c r="E28" t="n">
-        <v>31.86593778646691</v>
+        <v>31.86594156356414</v>
       </c>
       <c r="F28" t="n">
         <v>236079</v>
@@ -992,16 +992,16 @@
         <v>44187</v>
       </c>
       <c r="B29" t="n">
-        <v>33.16364669799805</v>
+        <v>33.16364288330078</v>
       </c>
       <c r="C29" t="n">
-        <v>33.47125146089823</v>
+        <v>33.47124761081827</v>
       </c>
       <c r="D29" t="n">
-        <v>32.59649983084212</v>
+        <v>32.59649608138177</v>
       </c>
       <c r="E29" t="n">
-        <v>33.21170935664249</v>
+        <v>33.21170553641675</v>
       </c>
       <c r="F29" t="n">
         <v>167504</v>
@@ -1032,16 +1032,16 @@
         <v>44193</v>
       </c>
       <c r="B31" t="n">
-        <v>36.21085357666016</v>
+        <v>36.21085739135742</v>
       </c>
       <c r="C31" t="n">
-        <v>36.66265002370312</v>
+        <v>36.66265388599569</v>
       </c>
       <c r="D31" t="n">
-        <v>35.56680651179074</v>
+        <v>35.56681025863972</v>
       </c>
       <c r="E31" t="n">
-        <v>35.56680651179074</v>
+        <v>35.56681025863972</v>
       </c>
       <c r="F31" t="n">
         <v>451822</v>
@@ -1052,16 +1052,16 @@
         <v>44194</v>
       </c>
       <c r="B32" t="n">
-        <v>36.09550857543945</v>
+        <v>36.09550476074219</v>
       </c>
       <c r="C32" t="n">
-        <v>37.06638558261441</v>
+        <v>37.06638166531152</v>
       </c>
       <c r="D32" t="n">
-        <v>35.95131684304462</v>
+        <v>35.95131304358604</v>
       </c>
       <c r="E32" t="n">
-        <v>36.52807627747203</v>
+        <v>36.52807241705953</v>
       </c>
       <c r="F32" t="n">
         <v>337154</v>
@@ -1092,16 +1092,16 @@
         <v>44200</v>
       </c>
       <c r="B34" t="n">
-        <v>34.99966430664062</v>
+        <v>34.99966049194336</v>
       </c>
       <c r="C34" t="n">
-        <v>36.62420472682393</v>
+        <v>36.62420073506411</v>
       </c>
       <c r="D34" t="n">
-        <v>34.98043924232432</v>
+        <v>34.98043542972244</v>
       </c>
       <c r="E34" t="n">
-        <v>36.52807565766651</v>
+        <v>36.52807167638402</v>
       </c>
       <c r="F34" t="n">
         <v>331840</v>
@@ -1112,16 +1112,16 @@
         <v>44201</v>
       </c>
       <c r="B35" t="n">
-        <v>36.13395309448242</v>
+        <v>36.13395690917969</v>
       </c>
       <c r="C35" t="n">
-        <v>36.32620745863368</v>
+        <v>36.32621129362743</v>
       </c>
       <c r="D35" t="n">
-        <v>34.60554195482727</v>
+        <v>34.60554560816865</v>
       </c>
       <c r="E35" t="n">
-        <v>35.45145591048728</v>
+        <v>35.45145965313264</v>
       </c>
       <c r="F35" t="n">
         <v>328059</v>
@@ -1172,16 +1172,16 @@
         <v>44204</v>
       </c>
       <c r="B38" t="n">
-        <v>34.134521484375</v>
+        <v>34.13452529907227</v>
       </c>
       <c r="C38" t="n">
-        <v>35.75906172916622</v>
+        <v>35.75906572541368</v>
       </c>
       <c r="D38" t="n">
-        <v>34.134521484375</v>
+        <v>34.13452529907227</v>
       </c>
       <c r="E38" t="n">
-        <v>35.16307730455386</v>
+        <v>35.16308123419719</v>
       </c>
       <c r="F38" t="n">
         <v>367201</v>
@@ -1272,16 +1272,16 @@
         <v>44211</v>
       </c>
       <c r="B43" t="n">
-        <v>33.9422721862793</v>
+        <v>33.94226837158203</v>
       </c>
       <c r="C43" t="n">
-        <v>35.0477245509764</v>
+        <v>35.04772061203977</v>
       </c>
       <c r="D43" t="n">
-        <v>33.16364589242556</v>
+        <v>33.16364216523639</v>
       </c>
       <c r="E43" t="n">
-        <v>34.60554435461268</v>
+        <v>34.60554046537172</v>
       </c>
       <c r="F43" t="n">
         <v>319883</v>
@@ -1292,16 +1292,16 @@
         <v>44214</v>
       </c>
       <c r="B44" t="n">
-        <v>34.04800796508789</v>
+        <v>34.04801177978516</v>
       </c>
       <c r="C44" t="n">
-        <v>34.50941694399793</v>
+        <v>34.5094208103909</v>
       </c>
       <c r="D44" t="n">
-        <v>33.27899799700501</v>
+        <v>33.27900172554335</v>
       </c>
       <c r="E44" t="n">
-        <v>34.11529568146945</v>
+        <v>34.11529950370554</v>
       </c>
       <c r="F44" t="n">
         <v>117631</v>
@@ -1332,16 +1332,16 @@
         <v>44216</v>
       </c>
       <c r="B46" t="n">
-        <v>34.12491226196289</v>
+        <v>34.12490844726562</v>
       </c>
       <c r="C46" t="n">
-        <v>35.28804363060232</v>
+        <v>35.28803968588292</v>
       </c>
       <c r="D46" t="n">
-        <v>33.66350697587357</v>
+        <v>33.66350321275509</v>
       </c>
       <c r="E46" t="n">
-        <v>34.60554635973278</v>
+        <v>34.60554249130722</v>
       </c>
       <c r="F46" t="n">
         <v>359332</v>
@@ -1372,16 +1372,16 @@
         <v>44218</v>
       </c>
       <c r="B48" t="n">
-        <v>32.95216751098633</v>
+        <v>32.95216369628906</v>
       </c>
       <c r="C48" t="n">
-        <v>33.45202665996278</v>
+        <v>33.45202278739948</v>
       </c>
       <c r="D48" t="n">
-        <v>32.53882489582456</v>
+        <v>32.53882112897777</v>
       </c>
       <c r="E48" t="n">
-        <v>33.19248455367023</v>
+        <v>33.19248071115274</v>
       </c>
       <c r="F48" t="n">
         <v>220341</v>
@@ -1472,16 +1472,16 @@
         <v>44228</v>
       </c>
       <c r="B53" t="n">
-        <v>31.77942657470703</v>
+        <v>31.7794246673584</v>
       </c>
       <c r="C53" t="n">
-        <v>33.11558345161116</v>
+        <v>33.1155814640686</v>
       </c>
       <c r="D53" t="n">
-        <v>31.66407244843196</v>
+        <v>31.66407054800669</v>
       </c>
       <c r="E53" t="n">
-        <v>32.68301578391271</v>
+        <v>32.68301382233215</v>
       </c>
       <c r="F53" t="n">
         <v>610435</v>
@@ -1492,16 +1492,16 @@
         <v>44229</v>
       </c>
       <c r="B54" t="n">
-        <v>32.63495254516602</v>
+        <v>32.63494873046875</v>
       </c>
       <c r="C54" t="n">
-        <v>33.65389597951643</v>
+        <v>33.65389204571495</v>
       </c>
       <c r="D54" t="n">
-        <v>31.97168030813476</v>
+        <v>31.97167657096734</v>
       </c>
       <c r="E54" t="n">
-        <v>33.64428344702543</v>
+        <v>33.64427951434755</v>
       </c>
       <c r="F54" t="n">
         <v>582228</v>
@@ -1532,16 +1532,16 @@
         <v>44231</v>
       </c>
       <c r="B56" t="n">
-        <v>32.68301773071289</v>
+        <v>32.68301391601562</v>
       </c>
       <c r="C56" t="n">
-        <v>34.11530000851534</v>
+        <v>34.11529602664492</v>
       </c>
       <c r="D56" t="n">
-        <v>32.44270067986538</v>
+        <v>32.44269689321744</v>
       </c>
       <c r="E56" t="n">
-        <v>33.06752276352339</v>
+        <v>33.06751890394745</v>
       </c>
       <c r="F56" t="n">
         <v>466743</v>
@@ -1612,16 +1612,16 @@
         <v>44237</v>
       </c>
       <c r="B60" t="n">
-        <v>34.83625030517578</v>
+        <v>34.83624649047852</v>
       </c>
       <c r="C60" t="n">
-        <v>35.33610571127585</v>
+        <v>35.33610184184258</v>
       </c>
       <c r="D60" t="n">
-        <v>34.23065330065825</v>
+        <v>34.23064955227608</v>
       </c>
       <c r="E60" t="n">
-        <v>34.43251647044691</v>
+        <v>34.43251269995998</v>
       </c>
       <c r="F60" t="n">
         <v>186206</v>
@@ -1652,16 +1652,16 @@
         <v>44239</v>
       </c>
       <c r="B62" t="n">
-        <v>34.4036750793457</v>
+        <v>34.40367889404297</v>
       </c>
       <c r="C62" t="n">
-        <v>34.52864172776623</v>
+        <v>34.52864555631986</v>
       </c>
       <c r="D62" t="n">
-        <v>32.67339704372985</v>
+        <v>32.673400666573</v>
       </c>
       <c r="E62" t="n">
-        <v>33.67311524079254</v>
+        <v>33.67311897448496</v>
       </c>
       <c r="F62" t="n">
         <v>218195</v>
@@ -1692,16 +1692,16 @@
         <v>44245</v>
       </c>
       <c r="B64" t="n">
-        <v>37.00870513916016</v>
+        <v>37.00870895385742</v>
       </c>
       <c r="C64" t="n">
-        <v>37.38359759408829</v>
+        <v>37.38360144742785</v>
       </c>
       <c r="D64" t="n">
-        <v>35.71099846956061</v>
+        <v>35.71100215049589</v>
       </c>
       <c r="E64" t="n">
-        <v>36.37427060079703</v>
+        <v>36.37427435009953</v>
       </c>
       <c r="F64" t="n">
         <v>661534</v>
@@ -1812,16 +1812,16 @@
         <v>44253</v>
       </c>
       <c r="B70" t="n">
-        <v>34.57670974731445</v>
+        <v>34.57670593261719</v>
       </c>
       <c r="C70" t="n">
-        <v>37.21057733278074</v>
+        <v>37.21057322750037</v>
       </c>
       <c r="D70" t="n">
-        <v>33.75002072456356</v>
+        <v>33.75001700107128</v>
       </c>
       <c r="E70" t="n">
-        <v>36.53768882724342</v>
+        <v>36.5376847961999</v>
       </c>
       <c r="F70" t="n">
         <v>410022</v>
@@ -1932,16 +1932,16 @@
         <v>44263</v>
       </c>
       <c r="B76" t="n">
-        <v>41.91115570068359</v>
+        <v>41.91115951538086</v>
       </c>
       <c r="C76" t="n">
-        <v>44.60269808495321</v>
+        <v>44.60270214463106</v>
       </c>
       <c r="D76" t="n">
-        <v>40.70957434605565</v>
+        <v>40.70957805138659</v>
       </c>
       <c r="E76" t="n">
-        <v>43.55492097253444</v>
+        <v>43.55492493684502</v>
       </c>
       <c r="F76" t="n">
         <v>1012691</v>
@@ -1952,16 +1952,16 @@
         <v>44264</v>
       </c>
       <c r="B77" t="n">
-        <v>43.50685882568359</v>
+        <v>43.50686264038086</v>
       </c>
       <c r="C77" t="n">
-        <v>43.50685882568359</v>
+        <v>43.50686264038086</v>
       </c>
       <c r="D77" t="n">
-        <v>39.89249844113039</v>
+        <v>39.89250193891922</v>
       </c>
       <c r="E77" t="n">
-        <v>42.29566117843103</v>
+        <v>42.29566488693005</v>
       </c>
       <c r="F77" t="n">
         <v>563525</v>
@@ -1972,16 +1972,16 @@
         <v>44265</v>
       </c>
       <c r="B78" t="n">
-        <v>44.69882965087891</v>
+        <v>44.69882583618164</v>
       </c>
       <c r="C78" t="n">
-        <v>44.89108404365759</v>
+        <v>44.89108021255291</v>
       </c>
       <c r="D78" t="n">
-        <v>43.38189774093629</v>
+        <v>43.38189403862891</v>
       </c>
       <c r="E78" t="n">
-        <v>43.83369425231464</v>
+        <v>43.83369051144994</v>
       </c>
       <c r="F78" t="n">
         <v>425454</v>
@@ -2012,16 +2012,16 @@
         <v>44267</v>
       </c>
       <c r="B80" t="n">
-        <v>45.66009140014648</v>
+        <v>45.66009521484375</v>
       </c>
       <c r="C80" t="n">
-        <v>49.01490590711195</v>
+        <v>49.01491000208902</v>
       </c>
       <c r="D80" t="n">
-        <v>45.18906989096082</v>
+        <v>45.18907366630634</v>
       </c>
       <c r="E80" t="n">
-        <v>47.15005242731743</v>
+        <v>47.15005636649431</v>
       </c>
       <c r="F80" t="n">
         <v>954539</v>
@@ -2052,16 +2052,16 @@
         <v>44271</v>
       </c>
       <c r="B82" t="n">
-        <v>42.7570686340332</v>
+        <v>42.75707244873047</v>
       </c>
       <c r="C82" t="n">
-        <v>45.18906887745489</v>
+        <v>45.18907290913018</v>
       </c>
       <c r="D82" t="n">
-        <v>42.7570686340332</v>
+        <v>42.75707244873047</v>
       </c>
       <c r="E82" t="n">
-        <v>44.5065717038056</v>
+        <v>44.50657567458991</v>
       </c>
       <c r="F82" t="n">
         <v>561175</v>
@@ -2092,16 +2092,16 @@
         <v>44273</v>
       </c>
       <c r="B84" t="n">
-        <v>40.89221572875977</v>
+        <v>40.89221954345703</v>
       </c>
       <c r="C84" t="n">
-        <v>45.02565269480871</v>
+        <v>45.0256568951004</v>
       </c>
       <c r="D84" t="n">
-        <v>40.57499846451049</v>
+        <v>40.57500224961562</v>
       </c>
       <c r="E84" t="n">
-        <v>44.01632571721106</v>
+        <v>44.01632982334604</v>
       </c>
       <c r="F84" t="n">
         <v>572621</v>
@@ -2112,16 +2112,16 @@
         <v>44274</v>
       </c>
       <c r="B85" t="n">
-        <v>42.2956657409668</v>
+        <v>42.29566192626953</v>
       </c>
       <c r="C85" t="n">
-        <v>44.17013572642225</v>
+        <v>44.17013174266427</v>
       </c>
       <c r="D85" t="n">
-        <v>41.45936795627186</v>
+        <v>41.4593642170013</v>
       </c>
       <c r="E85" t="n">
-        <v>41.45936795627186</v>
+        <v>41.4593642170013</v>
       </c>
       <c r="F85" t="n">
         <v>639255</v>
@@ -2212,16 +2212,16 @@
         <v>44281</v>
       </c>
       <c r="B90" t="n">
-        <v>37.87384796142578</v>
+        <v>37.87384414672852</v>
       </c>
       <c r="C90" t="n">
-        <v>40.94989565175231</v>
+        <v>40.949891527232</v>
       </c>
       <c r="D90" t="n">
-        <v>37.56624319239313</v>
+        <v>37.56623940867817</v>
       </c>
       <c r="E90" t="n">
-        <v>39.95979362121066</v>
+        <v>39.95978959641457</v>
       </c>
       <c r="F90" t="n">
         <v>840076</v>
@@ -2312,16 +2312,16 @@
         <v>44291</v>
       </c>
       <c r="B95" t="n">
-        <v>35.68216323852539</v>
+        <v>35.68215942382812</v>
       </c>
       <c r="C95" t="n">
-        <v>37.01832012039754</v>
+        <v>37.01831616285484</v>
       </c>
       <c r="D95" t="n">
-        <v>35.09579131613852</v>
+        <v>35.09578756412892</v>
       </c>
       <c r="E95" t="n">
-        <v>37.01832012039754</v>
+        <v>37.01831616285484</v>
       </c>
       <c r="F95" t="n">
         <v>1091895</v>
@@ -2512,16 +2512,16 @@
         <v>44305</v>
       </c>
       <c r="B105" t="n">
-        <v>41.33440017700195</v>
+        <v>41.33439636230469</v>
       </c>
       <c r="C105" t="n">
-        <v>42.23798940934727</v>
+        <v>42.23798551125894</v>
       </c>
       <c r="D105" t="n">
-        <v>40.2097189655786</v>
+        <v>40.20971525467667</v>
       </c>
       <c r="E105" t="n">
-        <v>40.38274828563441</v>
+        <v>40.38274455876383</v>
       </c>
       <c r="F105" t="n">
         <v>1793083</v>
@@ -2552,16 +2552,16 @@
         <v>44308</v>
       </c>
       <c r="B107" t="n">
-        <v>42.37256622314453</v>
+        <v>42.3725700378418</v>
       </c>
       <c r="C107" t="n">
-        <v>42.77629628383934</v>
+        <v>42.77630013488342</v>
       </c>
       <c r="D107" t="n">
-        <v>41.0460181707321</v>
+        <v>41.04602186600353</v>
       </c>
       <c r="E107" t="n">
-        <v>42.58404191096891</v>
+        <v>42.58404574470481</v>
       </c>
       <c r="F107" t="n">
         <v>1175903</v>
@@ -2572,16 +2572,16 @@
         <v>44309</v>
       </c>
       <c r="B108" t="n">
-        <v>44.09323120117188</v>
+        <v>44.09323501586914</v>
       </c>
       <c r="C108" t="n">
-        <v>44.3143194172334</v>
+        <v>44.31432325105797</v>
       </c>
       <c r="D108" t="n">
-        <v>42.38217817402538</v>
+        <v>42.38218184069201</v>
       </c>
       <c r="E108" t="n">
-        <v>42.82435835372392</v>
+        <v>42.82436205864548</v>
       </c>
       <c r="F108" t="n">
         <v>1899574</v>
@@ -2612,16 +2612,16 @@
         <v>44313</v>
       </c>
       <c r="B110" t="n">
-        <v>43.73756408691406</v>
+        <v>43.7375602722168</v>
       </c>
       <c r="C110" t="n">
-        <v>44.31432350323168</v>
+        <v>44.31431963823069</v>
       </c>
       <c r="D110" t="n">
-        <v>43.04545428636325</v>
+        <v>43.04545053203033</v>
       </c>
       <c r="E110" t="n">
-        <v>43.40112171865809</v>
+        <v>43.40111793330461</v>
       </c>
       <c r="F110" t="n">
         <v>1146163</v>
@@ -2732,16 +2732,16 @@
         <v>44321</v>
       </c>
       <c r="B116" t="n">
-        <v>39.74831008911133</v>
+        <v>39.74831390380859</v>
       </c>
       <c r="C116" t="n">
-        <v>40.6422867086336</v>
+        <v>40.64229060912697</v>
       </c>
       <c r="D116" t="n">
-        <v>39.07542542863015</v>
+        <v>39.0754291787498</v>
       </c>
       <c r="E116" t="n">
-        <v>39.89249805311069</v>
+        <v>39.89250188164586</v>
       </c>
       <c r="F116" t="n">
         <v>3650961</v>
@@ -2772,16 +2772,16 @@
         <v>44323</v>
       </c>
       <c r="B118" t="n">
-        <v>38.83511352539062</v>
+        <v>38.83510971069336</v>
       </c>
       <c r="C118" t="n">
-        <v>39.99824491189721</v>
+        <v>39.99824098294782</v>
       </c>
       <c r="D118" t="n">
-        <v>37.51818162368365</v>
+        <v>37.51817793834604</v>
       </c>
       <c r="E118" t="n">
-        <v>39.66180253732045</v>
+        <v>39.66179864141913</v>
       </c>
       <c r="F118" t="n">
         <v>2227429</v>
@@ -2832,16 +2832,16 @@
         <v>44328</v>
       </c>
       <c r="B121" t="n">
-        <v>37.05676651000977</v>
+        <v>37.05677032470703</v>
       </c>
       <c r="C121" t="n">
-        <v>38.70052798471127</v>
+        <v>38.70053196862062</v>
       </c>
       <c r="D121" t="n">
-        <v>37.05676651000977</v>
+        <v>37.05677032470703</v>
       </c>
       <c r="E121" t="n">
-        <v>37.81616767208757</v>
+        <v>37.8161715649591</v>
       </c>
       <c r="F121" t="n">
         <v>783049</v>
@@ -2892,16 +2892,16 @@
         <v>44333</v>
       </c>
       <c r="B124" t="n">
-        <v>36.43194961547852</v>
+        <v>36.43194580078125</v>
       </c>
       <c r="C124" t="n">
-        <v>37.13367194429578</v>
+        <v>37.13366805612294</v>
       </c>
       <c r="D124" t="n">
-        <v>35.93209045798972</v>
+        <v>35.93208669563144</v>
       </c>
       <c r="E124" t="n">
-        <v>36.52807493515874</v>
+        <v>36.52807111039643</v>
       </c>
       <c r="F124" t="n">
         <v>946466</v>
@@ -2912,16 +2912,16 @@
         <v>44334</v>
       </c>
       <c r="B125" t="n">
-        <v>35.14385223388672</v>
+        <v>35.14385604858398</v>
       </c>
       <c r="C125" t="n">
-        <v>36.91258044505902</v>
+        <v>36.91258445174329</v>
       </c>
       <c r="D125" t="n">
-        <v>34.59593046500746</v>
+        <v>34.59593422023043</v>
       </c>
       <c r="E125" t="n">
-        <v>36.52807170518645</v>
+        <v>36.52807567013412</v>
       </c>
       <c r="F125" t="n">
         <v>2070451</v>
@@ -2952,16 +2952,16 @@
         <v>44336</v>
       </c>
       <c r="B127" t="n">
-        <v>34.63438034057617</v>
+        <v>34.63438415527344</v>
       </c>
       <c r="C127" t="n">
-        <v>35.26881488495837</v>
+        <v>35.26881876953347</v>
       </c>
       <c r="D127" t="n">
-        <v>34.51902996798866</v>
+        <v>34.51903376998102</v>
       </c>
       <c r="E127" t="n">
-        <v>34.51902996798866</v>
+        <v>34.51903376998102</v>
       </c>
       <c r="F127" t="n">
         <v>943604</v>
@@ -3012,16 +3012,16 @@
         <v>44341</v>
       </c>
       <c r="B130" t="n">
-        <v>37.29708480834961</v>
+        <v>37.29708862304688</v>
       </c>
       <c r="C130" t="n">
-        <v>38.78704584439543</v>
+        <v>38.78704981148397</v>
       </c>
       <c r="D130" t="n">
-        <v>37.22979709165812</v>
+        <v>37.22980089947328</v>
       </c>
       <c r="E130" t="n">
-        <v>37.52778929886728</v>
+        <v>37.52779313716071</v>
       </c>
       <c r="F130" t="n">
         <v>1731150</v>
@@ -3092,16 +3092,16 @@
         <v>44347</v>
       </c>
       <c r="B134" t="n">
-        <v>39.38302993774414</v>
+        <v>39.38303375244141</v>
       </c>
       <c r="C134" t="n">
-        <v>40.11358977958957</v>
+        <v>40.11359366504992</v>
       </c>
       <c r="D134" t="n">
-        <v>39.02736254769899</v>
+        <v>39.02736632794579</v>
       </c>
       <c r="E134" t="n">
-        <v>39.3926424686217</v>
+        <v>39.39264628425005</v>
       </c>
       <c r="F134" t="n">
         <v>715598</v>
@@ -3192,16 +3192,16 @@
         <v>44355</v>
       </c>
       <c r="B139" t="n">
-        <v>38.46022033691406</v>
+        <v>38.4602165222168</v>
       </c>
       <c r="C139" t="n">
-        <v>38.85433789767048</v>
+        <v>38.85433404388245</v>
       </c>
       <c r="D139" t="n">
-        <v>37.72004412796937</v>
+        <v>37.72004038668688</v>
       </c>
       <c r="E139" t="n">
-        <v>38.43138274082768</v>
+        <v>38.43137892899068</v>
       </c>
       <c r="F139" t="n">
         <v>978352</v>
@@ -3212,16 +3212,16 @@
         <v>44356</v>
       </c>
       <c r="B140" t="n">
-        <v>38.01803207397461</v>
+        <v>38.01803588867188</v>
       </c>
       <c r="C140" t="n">
-        <v>38.66207914230487</v>
+        <v>38.66208302162527</v>
       </c>
       <c r="D140" t="n">
-        <v>37.29708475810054</v>
+        <v>37.29708850045856</v>
       </c>
       <c r="E140" t="n">
-        <v>38.48905358533129</v>
+        <v>38.48905744729046</v>
       </c>
       <c r="F140" t="n">
         <v>837521</v>
@@ -3332,16 +3332,16 @@
         <v>44364</v>
       </c>
       <c r="B146" t="n">
-        <v>42.48791885375977</v>
+        <v>42.4879150390625</v>
       </c>
       <c r="C146" t="n">
-        <v>44.00671761209134</v>
+        <v>44.0067136610316</v>
       </c>
       <c r="D146" t="n">
-        <v>41.62277975128091</v>
+        <v>41.62277601425852</v>
       </c>
       <c r="E146" t="n">
-        <v>42.95894040588714</v>
+        <v>42.95893654890009</v>
       </c>
       <c r="F146" t="n">
         <v>1582144</v>
@@ -3372,16 +3372,16 @@
         <v>44368</v>
       </c>
       <c r="B148" t="n">
-        <v>46.96741104125977</v>
+        <v>46.96741485595703</v>
       </c>
       <c r="C148" t="n">
-        <v>47.24617818755916</v>
+        <v>47.24618202489792</v>
       </c>
       <c r="D148" t="n">
-        <v>43.53569625432814</v>
+        <v>43.53569979030122</v>
       </c>
       <c r="E148" t="n">
-        <v>43.73755940512824</v>
+        <v>43.73756295749668</v>
       </c>
       <c r="F148" t="n">
         <v>2655439</v>
@@ -3452,16 +3452,16 @@
         <v>44372</v>
       </c>
       <c r="B152" t="n">
-        <v>44.45851516723633</v>
+        <v>44.45851135253906</v>
       </c>
       <c r="C152" t="n">
-        <v>44.9872081751215</v>
+        <v>44.98720431506052</v>
       </c>
       <c r="D152" t="n">
-        <v>43.97788107180344</v>
+        <v>43.97787729834627</v>
       </c>
       <c r="E152" t="n">
-        <v>44.9872081751215</v>
+        <v>44.98720431506052</v>
       </c>
       <c r="F152" t="n">
         <v>1347904</v>
@@ -3472,16 +3472,16 @@
         <v>44375</v>
       </c>
       <c r="B153" t="n">
-        <v>44.53541564941406</v>
+        <v>44.5354118347168</v>
       </c>
       <c r="C153" t="n">
-        <v>44.64115350201283</v>
+        <v>44.64114967825854</v>
       </c>
       <c r="D153" t="n">
-        <v>43.20886748802305</v>
+        <v>43.20886378695175</v>
       </c>
       <c r="E153" t="n">
-        <v>44.13168555555202</v>
+        <v>44.13168177543641</v>
       </c>
       <c r="F153" t="n">
         <v>1110393</v>
@@ -3512,16 +3512,16 @@
         <v>44377</v>
       </c>
       <c r="B155" t="n">
-        <v>43.58375930786133</v>
+        <v>43.58376312255859</v>
       </c>
       <c r="C155" t="n">
-        <v>44.45851087872119</v>
+        <v>44.45851476998166</v>
       </c>
       <c r="D155" t="n">
-        <v>43.50685905923421</v>
+        <v>43.50686286720073</v>
       </c>
       <c r="E155" t="n">
-        <v>44.21819385418598</v>
+        <v>44.21819772441255</v>
       </c>
       <c r="F155" t="n">
         <v>1274116</v>
@@ -3572,16 +3572,16 @@
         <v>44382</v>
       </c>
       <c r="B158" t="n">
-        <v>45.04488754272461</v>
+        <v>45.04488372802734</v>
       </c>
       <c r="C158" t="n">
-        <v>46.21763144885693</v>
+        <v>46.21762753484401</v>
       </c>
       <c r="D158" t="n">
-        <v>44.42967424579171</v>
+        <v>44.42967048319475</v>
       </c>
       <c r="E158" t="n">
-        <v>44.98720860256699</v>
+        <v>44.98720479275436</v>
       </c>
       <c r="F158" t="n">
         <v>3391068</v>
@@ -3592,16 +3592,16 @@
         <v>44383</v>
       </c>
       <c r="B159" t="n">
-        <v>44.37199783325195</v>
+        <v>44.37199401855469</v>
       </c>
       <c r="C159" t="n">
-        <v>45.94847553926477</v>
+        <v>45.94847158903642</v>
       </c>
       <c r="D159" t="n">
-        <v>43.75678830080941</v>
+        <v>43.75678453900221</v>
       </c>
       <c r="E159" t="n">
-        <v>45.78505875053358</v>
+        <v>45.7850548143543</v>
       </c>
       <c r="F159" t="n">
         <v>1563442</v>
@@ -3652,16 +3652,16 @@
         <v>44389</v>
       </c>
       <c r="B162" t="n">
-        <v>44.72766494750977</v>
+        <v>44.72766876220703</v>
       </c>
       <c r="C162" t="n">
-        <v>45.75621700299953</v>
+        <v>45.75622090541913</v>
       </c>
       <c r="D162" t="n">
-        <v>44.08361413043626</v>
+        <v>44.08361789020423</v>
       </c>
       <c r="E162" t="n">
-        <v>45.75621700299953</v>
+        <v>45.75622090541913</v>
       </c>
       <c r="F162" t="n">
         <v>1597780</v>
@@ -3732,16 +3732,16 @@
         <v>44393</v>
       </c>
       <c r="B166" t="n">
-        <v>41.70929336547852</v>
+        <v>41.70928955078125</v>
       </c>
       <c r="C166" t="n">
-        <v>41.91116028433812</v>
+        <v>41.91115645117827</v>
       </c>
       <c r="D166" t="n">
-        <v>40.45003668764308</v>
+        <v>40.45003298811638</v>
       </c>
       <c r="E166" t="n">
-        <v>41.62278057778546</v>
+        <v>41.62277677100059</v>
       </c>
       <c r="F166" t="n">
         <v>1471156</v>
@@ -3752,16 +3752,16 @@
         <v>44396</v>
       </c>
       <c r="B167" t="n">
-        <v>40.22894668579102</v>
+        <v>40.22894287109375</v>
       </c>
       <c r="C167" t="n">
-        <v>41.05563189370605</v>
+        <v>41.05562800061862</v>
       </c>
       <c r="D167" t="n">
-        <v>39.50799557728174</v>
+        <v>39.50799183094843</v>
       </c>
       <c r="E167" t="n">
-        <v>40.46925997438512</v>
+        <v>40.46925613690023</v>
       </c>
       <c r="F167" t="n">
         <v>1632835</v>
@@ -3792,16 +3792,16 @@
         <v>44398</v>
       </c>
       <c r="B169" t="n">
-        <v>40.45964813232422</v>
+        <v>40.45964431762695</v>
       </c>
       <c r="C169" t="n">
-        <v>41.40169122996932</v>
+        <v>41.40168732645247</v>
       </c>
       <c r="D169" t="n">
-        <v>40.22894737134245</v>
+        <v>40.22894357839657</v>
       </c>
       <c r="E169" t="n">
-        <v>40.37313534695605</v>
+        <v>40.37313154041556</v>
       </c>
       <c r="F169" t="n">
         <v>985812</v>
@@ -3812,16 +3812,16 @@
         <v>44399</v>
       </c>
       <c r="B170" t="n">
-        <v>40.89221572875977</v>
+        <v>40.89221954345703</v>
       </c>
       <c r="C170" t="n">
-        <v>41.15175780815924</v>
+        <v>41.15176164706832</v>
       </c>
       <c r="D170" t="n">
-        <v>40.39235663157741</v>
+        <v>40.3923603996445</v>
       </c>
       <c r="E170" t="n">
-        <v>41.08446634492577</v>
+        <v>41.08447017755746</v>
       </c>
       <c r="F170" t="n">
         <v>757704</v>
@@ -3832,16 +3832,16 @@
         <v>44400</v>
       </c>
       <c r="B171" t="n">
-        <v>40.56539154052734</v>
+        <v>40.56538772583008</v>
       </c>
       <c r="C171" t="n">
-        <v>40.8633837843476</v>
+        <v>40.86337994162768</v>
       </c>
       <c r="D171" t="n">
-        <v>40.20010782417279</v>
+        <v>40.20010404382616</v>
       </c>
       <c r="E171" t="n">
-        <v>40.62306673334884</v>
+        <v>40.6230629132279</v>
       </c>
       <c r="F171" t="n">
         <v>715496</v>
@@ -3872,16 +3872,16 @@
         <v>44404</v>
       </c>
       <c r="B173" t="n">
-        <v>38.54673385620117</v>
+        <v>38.54673004150391</v>
       </c>
       <c r="C173" t="n">
-        <v>40.84415903525979</v>
+        <v>40.84415499320262</v>
       </c>
       <c r="D173" t="n">
-        <v>38.32564186777011</v>
+        <v>38.32563807495276</v>
       </c>
       <c r="E173" t="n">
-        <v>40.62306704682872</v>
+        <v>40.62306302665147</v>
       </c>
       <c r="F173" t="n">
         <v>1543819</v>
@@ -3932,16 +3932,16 @@
         <v>44407</v>
       </c>
       <c r="B176" t="n">
-        <v>37.21057510375977</v>
+        <v>37.2105712890625</v>
       </c>
       <c r="C176" t="n">
-        <v>38.26796483899034</v>
+        <v>38.26796091589321</v>
       </c>
       <c r="D176" t="n">
-        <v>36.33582347177977</v>
+        <v>36.33581974675896</v>
       </c>
       <c r="E176" t="n">
-        <v>37.56624252608663</v>
+        <v>37.5662386749276</v>
       </c>
       <c r="F176" t="n">
         <v>1168442</v>
@@ -3952,16 +3952,16 @@
         <v>44410</v>
       </c>
       <c r="B177" t="n">
-        <v>39.04659271240234</v>
+        <v>39.04658889770508</v>
       </c>
       <c r="C177" t="n">
-        <v>40.34429954077027</v>
+        <v>40.3442955992922</v>
       </c>
       <c r="D177" t="n">
-        <v>38.19106610976557</v>
+        <v>38.19106237864987</v>
       </c>
       <c r="E177" t="n">
-        <v>39.17155563014188</v>
+        <v>39.17155180323623</v>
       </c>
       <c r="F177" t="n">
         <v>3352028</v>
@@ -4052,16 +4052,16 @@
         <v>44417</v>
       </c>
       <c r="B182" t="n">
-        <v>37.10483551025391</v>
+        <v>37.10483169555664</v>
       </c>
       <c r="C182" t="n">
-        <v>37.44127788724551</v>
+        <v>37.44127403795907</v>
       </c>
       <c r="D182" t="n">
-        <v>35.94170411539885</v>
+        <v>35.94170042028153</v>
       </c>
       <c r="E182" t="n">
-        <v>36.11473344381713</v>
+        <v>36.1147297309109</v>
       </c>
       <c r="F182" t="n">
         <v>1206460</v>
@@ -4092,16 +4092,16 @@
         <v>44419</v>
       </c>
       <c r="B184" t="n">
-        <v>36.43194961547852</v>
+        <v>36.43194580078125</v>
       </c>
       <c r="C184" t="n">
-        <v>36.74916691799907</v>
+        <v>36.74916307008678</v>
       </c>
       <c r="D184" t="n">
-        <v>36.09550724902192</v>
+        <v>36.09550346955268</v>
       </c>
       <c r="E184" t="n">
-        <v>36.4703997433506</v>
+        <v>36.47039592462733</v>
       </c>
       <c r="F184" t="n">
         <v>786524</v>
@@ -4112,16 +4112,16 @@
         <v>44420</v>
       </c>
       <c r="B185" t="n">
-        <v>36.12434005737305</v>
+        <v>36.12434387207031</v>
       </c>
       <c r="C185" t="n">
-        <v>36.95102893978947</v>
+        <v>36.95103284178433</v>
       </c>
       <c r="D185" t="n">
-        <v>35.47068047502529</v>
+        <v>35.4706842206967</v>
       </c>
       <c r="E185" t="n">
-        <v>36.19162777223157</v>
+        <v>36.19163159403436</v>
       </c>
       <c r="F185" t="n">
         <v>689639</v>
@@ -4132,16 +4132,16 @@
         <v>44421</v>
       </c>
       <c r="B186" t="n">
-        <v>34.75934600830078</v>
+        <v>34.75934219360352</v>
       </c>
       <c r="C186" t="n">
-        <v>35.97054000708643</v>
+        <v>35.97053605946554</v>
       </c>
       <c r="D186" t="n">
-        <v>34.59593296747376</v>
+        <v>34.59592917071041</v>
       </c>
       <c r="E186" t="n">
-        <v>35.69177658449917</v>
+        <v>35.69177266747142</v>
       </c>
       <c r="F186" t="n">
         <v>915908</v>
@@ -4252,16 +4252,16 @@
         <v>44431</v>
       </c>
       <c r="B192" t="n">
-        <v>33.16364669799805</v>
+        <v>33.16364288330078</v>
       </c>
       <c r="C192" t="n">
-        <v>34.42290334478545</v>
+        <v>34.42289938524034</v>
       </c>
       <c r="D192" t="n">
-        <v>32.77914168126674</v>
+        <v>32.77913791079774</v>
       </c>
       <c r="E192" t="n">
-        <v>33.74040609688286</v>
+        <v>33.740402215843</v>
       </c>
       <c r="F192" t="n">
         <v>2084044</v>
@@ -4272,16 +4272,16 @@
         <v>44432</v>
       </c>
       <c r="B193" t="n">
-        <v>35.43223190307617</v>
+        <v>35.43223571777344</v>
       </c>
       <c r="C193" t="n">
-        <v>35.43223190307617</v>
+        <v>35.43223571777344</v>
       </c>
       <c r="D193" t="n">
-        <v>33.47124932262768</v>
+        <v>33.47125292620207</v>
       </c>
       <c r="E193" t="n">
-        <v>33.93265831128927</v>
+        <v>33.93266196453976</v>
       </c>
       <c r="F193" t="n">
         <v>1429663</v>
@@ -4332,16 +4332,16 @@
         <v>44435</v>
       </c>
       <c r="B196" t="n">
-        <v>36.43194961547852</v>
+        <v>36.43194580078125</v>
       </c>
       <c r="C196" t="n">
-        <v>36.66265413028687</v>
+        <v>36.66265029143312</v>
       </c>
       <c r="D196" t="n">
-        <v>35.02850121026817</v>
+        <v>35.02849754252244</v>
       </c>
       <c r="E196" t="n">
-        <v>35.75906488256532</v>
+        <v>35.75906113832411</v>
       </c>
       <c r="F196" t="n">
         <v>2701327</v>
@@ -4392,16 +4392,16 @@
         <v>44440</v>
       </c>
       <c r="B199" t="n">
-        <v>36.00899505615234</v>
+        <v>36.00899124145508</v>
       </c>
       <c r="C199" t="n">
-        <v>37.2298016265613</v>
+        <v>37.22979768253502</v>
       </c>
       <c r="D199" t="n">
-        <v>35.47068576189898</v>
+        <v>35.47068200422877</v>
       </c>
       <c r="E199" t="n">
-        <v>37.10483496133683</v>
+        <v>37.10483103054919</v>
       </c>
       <c r="F199" t="n">
         <v>1150659</v>
@@ -4712,16 +4712,16 @@
         <v>44463</v>
       </c>
       <c r="B215" t="n">
-        <v>34.54787063598633</v>
+        <v>34.54786682128906</v>
       </c>
       <c r="C215" t="n">
-        <v>35.65332304773112</v>
+        <v>35.65331911097231</v>
       </c>
       <c r="D215" t="n">
-        <v>33.88459469184851</v>
+        <v>33.88459095038866</v>
       </c>
       <c r="E215" t="n">
-        <v>34.46135784884584</v>
+        <v>34.46135404370111</v>
       </c>
       <c r="F215" t="n">
         <v>2639905</v>
@@ -4852,16 +4852,16 @@
         <v>44474</v>
       </c>
       <c r="B222" t="n">
-        <v>41.2382698059082</v>
+        <v>41.23827362060547</v>
       </c>
       <c r="C222" t="n">
-        <v>43.07428564103963</v>
+        <v>43.07428962557536</v>
       </c>
       <c r="D222" t="n">
-        <v>40.94989013953506</v>
+        <v>40.9498939275561</v>
       </c>
       <c r="E222" t="n">
-        <v>41.82464166928109</v>
+        <v>41.82464553821999</v>
       </c>
       <c r="F222" t="n">
         <v>3033780</v>
@@ -4952,16 +4952,16 @@
         <v>44482</v>
       </c>
       <c r="B227" t="n">
-        <v>39.66180038452148</v>
+        <v>39.66179656982422</v>
       </c>
       <c r="C227" t="n">
-        <v>40.05591793090613</v>
+        <v>40.05591407830239</v>
       </c>
       <c r="D227" t="n">
-        <v>38.88317407585477</v>
+        <v>38.88317033604628</v>
       </c>
       <c r="E227" t="n">
-        <v>39.43109587666738</v>
+        <v>39.43109208415942</v>
       </c>
       <c r="F227" t="n">
         <v>1130628</v>
@@ -5012,16 +5012,16 @@
         <v>44487</v>
       </c>
       <c r="B230" t="n">
-        <v>39.87327575683594</v>
+        <v>39.87327194213867</v>
       </c>
       <c r="C230" t="n">
-        <v>41.44975342469183</v>
+        <v>41.44974945917212</v>
       </c>
       <c r="D230" t="n">
-        <v>39.18116598648377</v>
+        <v>39.18116223800101</v>
       </c>
       <c r="E230" t="n">
-        <v>39.72908778283576</v>
+        <v>39.72908398193304</v>
       </c>
       <c r="F230" t="n">
         <v>2573169</v>
@@ -5032,16 +5032,16 @@
         <v>44488</v>
       </c>
       <c r="B231" t="n">
-        <v>37.58546829223633</v>
+        <v>37.58546447753906</v>
       </c>
       <c r="C231" t="n">
-        <v>40.08475657457366</v>
+        <v>40.08475250621378</v>
       </c>
       <c r="D231" t="n">
-        <v>36.86452090235465</v>
+        <v>36.86451716082918</v>
       </c>
       <c r="E231" t="n">
-        <v>39.57528488714614</v>
+        <v>39.57528087049455</v>
       </c>
       <c r="F231" t="n">
         <v>2915331</v>
@@ -5072,16 +5072,16 @@
         <v>44490</v>
       </c>
       <c r="B233" t="n">
-        <v>34.41329193115234</v>
+        <v>34.41328811645508</v>
       </c>
       <c r="C233" t="n">
-        <v>36.09550752381791</v>
+        <v>36.09550352264783</v>
       </c>
       <c r="D233" t="n">
-        <v>33.48086508042814</v>
+        <v>33.48086136908995</v>
       </c>
       <c r="E233" t="n">
-        <v>35.62448595864728</v>
+        <v>35.62448200968972</v>
       </c>
       <c r="F233" t="n">
         <v>3113087</v>
@@ -5092,16 +5092,16 @@
         <v>44491</v>
       </c>
       <c r="B234" t="n">
-        <v>32.63495254516602</v>
+        <v>32.63494873046875</v>
       </c>
       <c r="C234" t="n">
-        <v>34.06723862420559</v>
+        <v>34.06723464208851</v>
       </c>
       <c r="D234" t="n">
-        <v>31.04886594627039</v>
+        <v>31.04886231697067</v>
       </c>
       <c r="E234" t="n">
-        <v>33.63467091453443</v>
+        <v>33.63466698298016</v>
       </c>
       <c r="F234" t="n">
         <v>4894520</v>
@@ -5112,16 +5112,16 @@
         <v>44494</v>
       </c>
       <c r="B235" t="n">
-        <v>36.84706115722656</v>
+        <v>36.8470573425293</v>
       </c>
       <c r="C235" t="n">
-        <v>37.31127712193275</v>
+        <v>37.3112732591762</v>
       </c>
       <c r="D235" t="n">
-        <v>32.95926229019877</v>
+        <v>32.95925887799699</v>
       </c>
       <c r="E235" t="n">
-        <v>32.95926229019877</v>
+        <v>32.95925887799699</v>
       </c>
       <c r="F235" t="n">
         <v>3449995</v>
@@ -5152,16 +5152,16 @@
         <v>44496</v>
       </c>
       <c r="B237" t="n">
-        <v>35.29000473022461</v>
+        <v>35.29000854492188</v>
       </c>
       <c r="C237" t="n">
-        <v>36.07336794668348</v>
+        <v>36.07337184605893</v>
       </c>
       <c r="D237" t="n">
-        <v>34.47762778370612</v>
+        <v>34.47763151058894</v>
       </c>
       <c r="E237" t="n">
-        <v>36.07336794668348</v>
+        <v>36.07337184605893</v>
       </c>
       <c r="F237" t="n">
         <v>2270538</v>
@@ -5272,16 +5272,16 @@
         <v>44505</v>
       </c>
       <c r="B243" t="n">
-        <v>34.33256149291992</v>
+        <v>34.33255767822266</v>
       </c>
       <c r="C243" t="n">
-        <v>35.80257809171644</v>
+        <v>35.80257411368536</v>
       </c>
       <c r="D243" t="n">
-        <v>31.73102433433615</v>
+        <v>31.73102080869616</v>
       </c>
       <c r="E243" t="n">
-        <v>33.17202720107906</v>
+        <v>33.17202351532898</v>
       </c>
       <c r="F243" t="n">
         <v>9166770</v>
@@ -5312,16 +5312,16 @@
         <v>44509</v>
       </c>
       <c r="B245" t="n">
-        <v>34.50664520263672</v>
+        <v>34.50664138793945</v>
       </c>
       <c r="C245" t="n">
-        <v>35.10625735786877</v>
+        <v>35.1062534768846</v>
       </c>
       <c r="D245" t="n">
-        <v>32.63044377861175</v>
+        <v>32.63044017132788</v>
       </c>
       <c r="E245" t="n">
-        <v>33.89736430140155</v>
+        <v>33.89736055406007</v>
       </c>
       <c r="F245" t="n">
         <v>7032350</v>
@@ -5372,16 +5372,16 @@
         <v>44512</v>
       </c>
       <c r="B248" t="n">
-        <v>30.94766235351562</v>
+        <v>30.94766044616699</v>
       </c>
       <c r="C248" t="n">
-        <v>33.11399911175717</v>
+        <v>33.11399707089411</v>
       </c>
       <c r="D248" t="n">
-        <v>30.69621126299056</v>
+        <v>30.69620937113922</v>
       </c>
       <c r="E248" t="n">
-        <v>32.10819849723269</v>
+        <v>32.10819651835855</v>
       </c>
       <c r="F248" t="n">
         <v>3403064</v>
@@ -5552,16 +5552,16 @@
         <v>44526</v>
       </c>
       <c r="B257" t="n">
-        <v>26.69235992431641</v>
+        <v>26.69235801696777</v>
       </c>
       <c r="C257" t="n">
-        <v>27.61111748815896</v>
+        <v>27.61111551515892</v>
       </c>
       <c r="D257" t="n">
-        <v>25.85096918966023</v>
+        <v>25.85096734243463</v>
       </c>
       <c r="E257" t="n">
-        <v>26.59564810870458</v>
+        <v>26.59564620826666</v>
       </c>
       <c r="F257" t="n">
         <v>3664026</v>
@@ -5592,16 +5592,16 @@
         <v>44530</v>
       </c>
       <c r="B259" t="n">
-        <v>26.71170043945312</v>
+        <v>26.71169853210449</v>
       </c>
       <c r="C259" t="n">
-        <v>26.71170043945312</v>
+        <v>26.71169853210449</v>
       </c>
       <c r="D259" t="n">
-        <v>25.48346622320262</v>
+        <v>25.48346440355603</v>
       </c>
       <c r="E259" t="n">
-        <v>26.53761992558345</v>
+        <v>26.53761803066504</v>
       </c>
       <c r="F259" t="n">
         <v>4757647</v>
@@ -5612,16 +5612,16 @@
         <v>44531</v>
       </c>
       <c r="B260" t="n">
-        <v>26.69235992431641</v>
+        <v>26.69235801696777</v>
       </c>
       <c r="C260" t="n">
-        <v>28.01730598945588</v>
+        <v>28.01730398743094</v>
       </c>
       <c r="D260" t="n">
-        <v>26.32485577450663</v>
+        <v>26.32485389341864</v>
       </c>
       <c r="E260" t="n">
-        <v>27.17591712858762</v>
+        <v>27.17591518668557</v>
       </c>
       <c r="F260" t="n">
         <v>3467467</v>
@@ -5752,16 +5752,16 @@
         <v>44540</v>
       </c>
       <c r="B267" t="n">
-        <v>29.43896102905273</v>
+        <v>29.43896293640137</v>
       </c>
       <c r="C267" t="n">
-        <v>29.76778079564096</v>
+        <v>29.76778272429381</v>
       </c>
       <c r="D267" t="n">
-        <v>28.76198025889329</v>
+        <v>28.76198212238038</v>
       </c>
       <c r="E267" t="n">
-        <v>29.57435718308462</v>
+        <v>29.57435909920557</v>
       </c>
       <c r="F267" t="n">
         <v>1281952</v>
@@ -5832,16 +5832,16 @@
         <v>44546</v>
       </c>
       <c r="B271" t="n">
-        <v>30.62851524353027</v>
+        <v>30.62851333618164</v>
       </c>
       <c r="C271" t="n">
-        <v>30.86062322322113</v>
+        <v>30.86062130141829</v>
       </c>
       <c r="D271" t="n">
-        <v>29.25521235155887</v>
+        <v>29.25521052973079</v>
       </c>
       <c r="E271" t="n">
-        <v>29.49699095054871</v>
+        <v>29.4969891136642</v>
       </c>
       <c r="F271" t="n">
         <v>3477726</v>
@@ -5952,16 +5952,16 @@
         <v>44557</v>
       </c>
       <c r="B277" t="n">
-        <v>30.7252254486084</v>
+        <v>30.72522354125977</v>
       </c>
       <c r="C277" t="n">
-        <v>31.01536089416671</v>
+        <v>31.01535896880716</v>
       </c>
       <c r="D277" t="n">
-        <v>29.98054840663</v>
+        <v>29.98054654550914</v>
       </c>
       <c r="E277" t="n">
-        <v>29.98054840663</v>
+        <v>29.98054654550914</v>
       </c>
       <c r="F277" t="n">
         <v>1273927</v>
@@ -6132,16 +6132,16 @@
         <v>44571</v>
       </c>
       <c r="B286" t="n">
-        <v>33.37511825561523</v>
+        <v>33.37511444091797</v>
       </c>
       <c r="C286" t="n">
-        <v>33.89736166431392</v>
+        <v>33.89735778992546</v>
       </c>
       <c r="D286" t="n">
-        <v>32.24359399308115</v>
+        <v>32.24359030771443</v>
       </c>
       <c r="E286" t="n">
-        <v>32.3789901547752</v>
+        <v>32.37898645393302</v>
       </c>
       <c r="F286" t="n">
         <v>2829132</v>
@@ -6152,16 +6152,16 @@
         <v>44572</v>
       </c>
       <c r="B287" t="n">
-        <v>35.10625076293945</v>
+        <v>35.10625457763672</v>
       </c>
       <c r="C287" t="n">
-        <v>35.63816285834681</v>
+        <v>35.63816673084244</v>
       </c>
       <c r="D287" t="n">
-        <v>33.18169098013564</v>
+        <v>33.18169458570739</v>
       </c>
       <c r="E287" t="n">
-        <v>33.55886569280182</v>
+        <v>33.55886933935793</v>
       </c>
       <c r="F287" t="n">
         <v>3953735</v>
@@ -6172,16 +6172,16 @@
         <v>44573</v>
       </c>
       <c r="B288" t="n">
-        <v>34.89348602294922</v>
+        <v>34.89348983764648</v>
       </c>
       <c r="C288" t="n">
-        <v>35.98632394454952</v>
+        <v>35.98632787872025</v>
       </c>
       <c r="D288" t="n">
-        <v>34.13913659549451</v>
+        <v>34.13914032772324</v>
       </c>
       <c r="E288" t="n">
-        <v>35.34802942826484</v>
+        <v>35.34803329265463</v>
       </c>
       <c r="F288" t="n">
         <v>3302601</v>
@@ -6292,16 +6292,16 @@
         <v>44581</v>
       </c>
       <c r="B294" t="n">
-        <v>35.2996711730957</v>
+        <v>35.29967498779297</v>
       </c>
       <c r="C294" t="n">
-        <v>36.17007552296929</v>
+        <v>36.17007943172774</v>
       </c>
       <c r="D294" t="n">
-        <v>34.98052391082881</v>
+        <v>34.98052769103708</v>
       </c>
       <c r="E294" t="n">
-        <v>35.8702694969556</v>
+        <v>35.87027337331519</v>
       </c>
       <c r="F294" t="n">
         <v>3650414</v>
@@ -6332,16 +6332,16 @@
         <v>44585</v>
       </c>
       <c r="B296" t="n">
-        <v>34.35190582275391</v>
+        <v>34.35190200805664</v>
       </c>
       <c r="C296" t="n">
-        <v>35.31902021252021</v>
+        <v>35.3190162904272</v>
       </c>
       <c r="D296" t="n">
-        <v>34.05209976231423</v>
+        <v>34.05209598090971</v>
       </c>
       <c r="E296" t="n">
-        <v>34.2358508967577</v>
+        <v>34.23584709494806</v>
       </c>
       <c r="F296" t="n">
         <v>2113697</v>
@@ -6392,16 +6392,16 @@
         <v>44588</v>
       </c>
       <c r="B299" t="n">
-        <v>36.09270858764648</v>
+        <v>36.09271240234375</v>
       </c>
       <c r="C299" t="n">
-        <v>37.10817788022283</v>
+        <v>37.1081818022467</v>
       </c>
       <c r="D299" t="n">
-        <v>35.68652012110085</v>
+        <v>35.68652389286739</v>
       </c>
       <c r="E299" t="n">
-        <v>35.87994373577622</v>
+        <v>35.87994752798603</v>
       </c>
       <c r="F299" t="n">
         <v>3171460</v>
@@ -6492,16 +6492,16 @@
         <v>44595</v>
       </c>
       <c r="B304" t="n">
-        <v>35.2996711730957</v>
+        <v>35.29967498779297</v>
       </c>
       <c r="C304" t="n">
-        <v>35.58980845477045</v>
+        <v>35.58981230082171</v>
       </c>
       <c r="D304" t="n">
-        <v>33.84899975502328</v>
+        <v>33.84900341295216</v>
       </c>
       <c r="E304" t="n">
-        <v>34.98052391082881</v>
+        <v>34.98052769103708</v>
       </c>
       <c r="F304" t="n">
         <v>4177823</v>
@@ -6592,16 +6592,16 @@
         <v>44602</v>
       </c>
       <c r="B309" t="n">
-        <v>37.28226089477539</v>
+        <v>37.28226470947266</v>
       </c>
       <c r="C309" t="n">
-        <v>38.38477139493146</v>
+        <v>38.3847753224369</v>
       </c>
       <c r="D309" t="n">
-        <v>36.33448778997354</v>
+        <v>36.33449150769526</v>
       </c>
       <c r="E309" t="n">
-        <v>36.3635015200494</v>
+        <v>36.36350524073979</v>
       </c>
       <c r="F309" t="n">
         <v>7025951</v>
@@ -6612,16 +6612,16 @@
         <v>44603</v>
       </c>
       <c r="B310" t="n">
-        <v>38.07529449462891</v>
+        <v>38.07529067993164</v>
       </c>
       <c r="C310" t="n">
-        <v>38.49115547855604</v>
+        <v>38.49115162219439</v>
       </c>
       <c r="D310" t="n">
-        <v>37.37897243800389</v>
+        <v>37.37896869306991</v>
       </c>
       <c r="E310" t="n">
-        <v>37.78516092896444</v>
+        <v>37.78515714333515</v>
       </c>
       <c r="F310" t="n">
         <v>5486491</v>
@@ -6632,16 +6632,16 @@
         <v>44606</v>
       </c>
       <c r="B311" t="n">
-        <v>37.57239532470703</v>
+        <v>37.57239151000977</v>
       </c>
       <c r="C311" t="n">
-        <v>38.84898823510746</v>
+        <v>38.84898429079868</v>
       </c>
       <c r="D311" t="n">
-        <v>36.95344198127135</v>
+        <v>36.95343822941596</v>
       </c>
       <c r="E311" t="n">
-        <v>38.2977310983781</v>
+        <v>38.29772721003804</v>
       </c>
       <c r="F311" t="n">
         <v>3902640</v>
@@ -6652,16 +6652,16 @@
         <v>44607</v>
       </c>
       <c r="B312" t="n">
-        <v>35.79290390014648</v>
+        <v>35.79290008544922</v>
       </c>
       <c r="C312" t="n">
-        <v>36.65363583255173</v>
+        <v>36.65363192612031</v>
       </c>
       <c r="D312" t="n">
-        <v>35.63816650158672</v>
+        <v>35.63816270338088</v>
       </c>
       <c r="E312" t="n">
-        <v>36.55692589534578</v>
+        <v>36.55692199922141</v>
       </c>
       <c r="F312" t="n">
         <v>3810709</v>
@@ -6672,16 +6672,16 @@
         <v>44608</v>
       </c>
       <c r="B313" t="n">
-        <v>35.92829895019531</v>
+        <v>35.92830276489258</v>
       </c>
       <c r="C313" t="n">
-        <v>36.80837209332255</v>
+        <v>36.80837600146183</v>
       </c>
       <c r="D313" t="n">
-        <v>35.69619285953032</v>
+        <v>35.69619664958365</v>
       </c>
       <c r="E313" t="n">
-        <v>36.4408698462091</v>
+        <v>36.44087371532872</v>
       </c>
       <c r="F313" t="n">
         <v>4244663</v>
@@ -6692,16 +6692,16 @@
         <v>44609</v>
       </c>
       <c r="B314" t="n">
-        <v>35.2996711730957</v>
+        <v>35.29967498779297</v>
       </c>
       <c r="C314" t="n">
-        <v>35.89928322512308</v>
+        <v>35.89928710461807</v>
       </c>
       <c r="D314" t="n">
-        <v>34.41959807888318</v>
+        <v>34.41960179847439</v>
       </c>
       <c r="E314" t="n">
-        <v>35.68651838361181</v>
+        <v>35.68652224011414</v>
       </c>
       <c r="F314" t="n">
         <v>4430658</v>
@@ -6712,16 +6712,16 @@
         <v>44610</v>
       </c>
       <c r="B315" t="n">
-        <v>34.48729705810547</v>
+        <v>34.48730087280273</v>
       </c>
       <c r="C315" t="n">
-        <v>35.41572509065163</v>
+        <v>35.41572900804387</v>
       </c>
       <c r="D315" t="n">
-        <v>33.80064384086931</v>
+        <v>33.80064757961473</v>
       </c>
       <c r="E315" t="n">
-        <v>34.83545803875718</v>
+        <v>34.83546189196511</v>
       </c>
       <c r="F315" t="n">
         <v>4069741</v>
@@ -6852,16 +6852,16 @@
         <v>44623</v>
       </c>
       <c r="B322" t="n">
-        <v>37.34028244018555</v>
+        <v>37.34028625488281</v>
       </c>
       <c r="C322" t="n">
-        <v>37.88187078764361</v>
+        <v>37.88187465766974</v>
       </c>
       <c r="D322" t="n">
-        <v>36.31514444477941</v>
+        <v>36.31514815474819</v>
       </c>
       <c r="E322" t="n">
-        <v>37.12751759702811</v>
+        <v>37.12752138998924</v>
       </c>
       <c r="F322" t="n">
         <v>9786414</v>
@@ -6892,16 +6892,16 @@
         <v>44627</v>
       </c>
       <c r="B324" t="n">
-        <v>37.04048538208008</v>
+        <v>37.04048156738281</v>
       </c>
       <c r="C324" t="n">
-        <v>39.28418904358112</v>
+        <v>39.28418499781101</v>
       </c>
       <c r="D324" t="n">
-        <v>36.65363811402602</v>
+        <v>36.65363433916909</v>
       </c>
       <c r="E324" t="n">
-        <v>38.17200970618351</v>
+        <v>38.17200577495368</v>
       </c>
       <c r="F324" t="n">
         <v>5025922</v>
@@ -6952,16 +6952,16 @@
         <v>44630</v>
       </c>
       <c r="B327" t="n">
-        <v>35.72520446777344</v>
+        <v>35.7252082824707</v>
       </c>
       <c r="C327" t="n">
-        <v>37.22423084456335</v>
+        <v>37.22423481932497</v>
       </c>
       <c r="D327" t="n">
-        <v>35.51243962707166</v>
+        <v>35.51244341905014</v>
       </c>
       <c r="E327" t="n">
-        <v>36.75034245134777</v>
+        <v>36.75034637550812</v>
       </c>
       <c r="F327" t="n">
         <v>4502679</v>
@@ -7032,16 +7032,16 @@
         <v>44636</v>
       </c>
       <c r="B331" t="n">
-        <v>32.84320831298828</v>
+        <v>32.84320449829102</v>
       </c>
       <c r="C331" t="n">
-        <v>34.44861737575539</v>
+        <v>34.44861337459189</v>
       </c>
       <c r="D331" t="n">
-        <v>32.34030985608281</v>
+        <v>32.34030609979657</v>
       </c>
       <c r="E331" t="n">
-        <v>34.10045632903992</v>
+        <v>34.10045236831488</v>
       </c>
       <c r="F331" t="n">
         <v>3899288</v>
@@ -7092,16 +7092,16 @@
         <v>44641</v>
       </c>
       <c r="B334" t="n">
-        <v>36.61495208740234</v>
+        <v>36.61494827270508</v>
       </c>
       <c r="C334" t="n">
-        <v>36.86640318776314</v>
+        <v>36.86639934686866</v>
       </c>
       <c r="D334" t="n">
-        <v>35.88961626653654</v>
+        <v>35.88961252740777</v>
       </c>
       <c r="E334" t="n">
-        <v>35.97665746445866</v>
+        <v>35.97665371626157</v>
       </c>
       <c r="F334" t="n">
         <v>3600944</v>
@@ -7212,16 +7212,16 @@
         <v>44649</v>
       </c>
       <c r="B340" t="n">
-        <v>40.11590576171875</v>
+        <v>40.11590194702148</v>
       </c>
       <c r="C340" t="n">
-        <v>40.60913544747385</v>
+        <v>40.60913158587444</v>
       </c>
       <c r="D340" t="n">
-        <v>37.8141747233464</v>
+        <v>37.81417112752509</v>
       </c>
       <c r="E340" t="n">
-        <v>38.00759834997051</v>
+        <v>38.00759473575618</v>
       </c>
       <c r="F340" t="n">
         <v>6952609</v>
@@ -7252,16 +7252,16 @@
         <v>44651</v>
       </c>
       <c r="B342" t="n">
-        <v>40.47373580932617</v>
+        <v>40.47373962402344</v>
       </c>
       <c r="C342" t="n">
-        <v>41.13137533388116</v>
+        <v>41.13137921056172</v>
       </c>
       <c r="D342" t="n">
-        <v>39.6710313879373</v>
+        <v>39.67103512697872</v>
       </c>
       <c r="E342" t="n">
-        <v>40.13524730247168</v>
+        <v>40.135251085266</v>
       </c>
       <c r="F342" t="n">
         <v>3810811</v>
@@ -7312,16 +7312,16 @@
         <v>44656</v>
       </c>
       <c r="B345" t="n">
-        <v>41.9727668762207</v>
+        <v>41.97276306152344</v>
       </c>
       <c r="C345" t="n">
-        <v>43.03659497534015</v>
+        <v>43.03659106395681</v>
       </c>
       <c r="D345" t="n">
-        <v>41.5762508676977</v>
+        <v>41.57624708903781</v>
       </c>
       <c r="E345" t="n">
-        <v>42.30158667490721</v>
+        <v>42.30158283032514</v>
       </c>
       <c r="F345" t="n">
         <v>5903074</v>
@@ -7432,16 +7432,16 @@
         <v>44664</v>
       </c>
       <c r="B351" t="n">
-        <v>43.62653350830078</v>
+        <v>43.62652969360352</v>
       </c>
       <c r="C351" t="n">
-        <v>43.71357095479976</v>
+        <v>43.71356713249195</v>
       </c>
       <c r="D351" t="n">
-        <v>42.8431702567798</v>
+        <v>42.8431665105797</v>
       </c>
       <c r="E351" t="n">
-        <v>43.30738621093589</v>
+        <v>43.30738242414481</v>
       </c>
       <c r="F351" t="n">
         <v>3238402</v>
@@ -7452,16 +7452,16 @@
         <v>44665</v>
       </c>
       <c r="B352" t="n">
-        <v>42.93987655639648</v>
+        <v>42.93988037109375</v>
       </c>
       <c r="C352" t="n">
-        <v>43.62652981023535</v>
+        <v>43.62653368593358</v>
       </c>
       <c r="D352" t="n">
-        <v>42.2242133212342</v>
+        <v>42.2242170723533</v>
       </c>
       <c r="E352" t="n">
-        <v>43.62652981023535</v>
+        <v>43.62653368593358</v>
       </c>
       <c r="F352" t="n">
         <v>2345809</v>
@@ -7552,16 +7552,16 @@
         <v>44676</v>
       </c>
       <c r="B357" t="n">
-        <v>41.94374847412109</v>
+        <v>41.94375228881836</v>
       </c>
       <c r="C357" t="n">
-        <v>42.40796438837074</v>
+        <v>42.40796824528748</v>
       </c>
       <c r="D357" t="n">
-        <v>40.64781815768625</v>
+        <v>40.64782185452133</v>
       </c>
       <c r="E357" t="n">
-        <v>40.75420058099602</v>
+        <v>40.75420428750637</v>
       </c>
       <c r="F357" t="n">
         <v>3287465</v>
@@ -7592,16 +7592,16 @@
         <v>44678</v>
       </c>
       <c r="B359" t="n">
-        <v>42.16619110107422</v>
+        <v>42.16618728637695</v>
       </c>
       <c r="C359" t="n">
-        <v>43.58784900340616</v>
+        <v>43.58784506009413</v>
       </c>
       <c r="D359" t="n">
-        <v>41.46986901615963</v>
+        <v>41.46986526445734</v>
       </c>
       <c r="E359" t="n">
-        <v>43.52015279261696</v>
+        <v>43.52014885542929</v>
       </c>
       <c r="F359" t="n">
         <v>3779727</v>
@@ -7672,16 +7672,16 @@
         <v>44684</v>
       </c>
       <c r="B363" t="n">
-        <v>42.12749862670898</v>
+        <v>42.12750244140625</v>
       </c>
       <c r="C363" t="n">
-        <v>42.54335956584936</v>
+        <v>42.54336341820335</v>
       </c>
       <c r="D363" t="n">
-        <v>41.25709802345466</v>
+        <v>41.25710175933607</v>
       </c>
       <c r="E363" t="n">
-        <v>42.54335956584936</v>
+        <v>42.54336341820335</v>
       </c>
       <c r="F363" t="n">
         <v>4458389</v>
@@ -7692,16 +7692,16 @@
         <v>44685</v>
       </c>
       <c r="B364" t="n">
-        <v>44.10041809082031</v>
+        <v>44.10041427612305</v>
       </c>
       <c r="C364" t="n">
-        <v>44.32285544811791</v>
+        <v>44.32285161417975</v>
       </c>
       <c r="D364" t="n">
-        <v>42.16618932580826</v>
+        <v>42.16618567842227</v>
       </c>
       <c r="E364" t="n">
-        <v>43.04626251447057</v>
+        <v>43.04625879095802</v>
       </c>
       <c r="F364" t="n">
         <v>5759540</v>
@@ -7712,16 +7712,16 @@
         <v>44686</v>
       </c>
       <c r="B365" t="n">
-        <v>42.92053604125977</v>
+        <v>42.92053985595703</v>
       </c>
       <c r="C365" t="n">
-        <v>44.57429987842104</v>
+        <v>44.57430384010176</v>
       </c>
       <c r="D365" t="n">
-        <v>42.01144918067956</v>
+        <v>42.01145291457887</v>
       </c>
       <c r="E365" t="n">
-        <v>44.09074271874429</v>
+        <v>44.09074663744735</v>
       </c>
       <c r="F365" t="n">
         <v>4814532</v>
@@ -7732,16 +7732,16 @@
         <v>44687</v>
       </c>
       <c r="B366" t="n">
-        <v>42.55303192138672</v>
+        <v>42.55303573608398</v>
       </c>
       <c r="C366" t="n">
-        <v>43.90698966019007</v>
+        <v>43.90699359626386</v>
       </c>
       <c r="D366" t="n">
-        <v>41.82769621387857</v>
+        <v>41.82769996355259</v>
       </c>
       <c r="E366" t="n">
-        <v>43.33639133753226</v>
+        <v>43.33639522245434</v>
       </c>
       <c r="F366" t="n">
         <v>4093307</v>
@@ -7892,16 +7892,16 @@
         <v>44699</v>
       </c>
       <c r="B374" t="n">
-        <v>39.99985122680664</v>
+        <v>39.99985504150391</v>
       </c>
       <c r="C374" t="n">
-        <v>42.2242133773643</v>
+        <v>42.22421740419406</v>
       </c>
       <c r="D374" t="n">
-        <v>39.72905892177436</v>
+        <v>39.72906271064676</v>
       </c>
       <c r="E374" t="n">
-        <v>42.13717219055205</v>
+        <v>42.13717620908088</v>
       </c>
       <c r="F374" t="n">
         <v>1865839</v>
@@ -7952,16 +7952,16 @@
         <v>44704</v>
       </c>
       <c r="B377" t="n">
-        <v>42.28224182128906</v>
+        <v>42.28224563598633</v>
       </c>
       <c r="C377" t="n">
-        <v>42.7948127143697</v>
+        <v>42.79481657531103</v>
       </c>
       <c r="D377" t="n">
-        <v>41.3538099687909</v>
+        <v>41.35381369972519</v>
       </c>
       <c r="E377" t="n">
-        <v>41.42150992041549</v>
+        <v>41.42151365745766</v>
       </c>
       <c r="F377" t="n">
         <v>3400119</v>
@@ -8012,16 +8012,16 @@
         <v>44707</v>
       </c>
       <c r="B380" t="n">
-        <v>46.59557342529297</v>
+        <v>46.5955696105957</v>
       </c>
       <c r="C380" t="n">
-        <v>47.16617181868395</v>
+        <v>47.1661679572728</v>
       </c>
       <c r="D380" t="n">
-        <v>45.10621935322675</v>
+        <v>45.10621566046026</v>
       </c>
       <c r="E380" t="n">
-        <v>45.25128426416589</v>
+        <v>45.2512805595232</v>
       </c>
       <c r="F380" t="n">
         <v>4582217</v>
@@ -8072,16 +8072,16 @@
         <v>44712</v>
       </c>
       <c r="B383" t="n">
-        <v>47.14683151245117</v>
+        <v>47.14682769775391</v>
       </c>
       <c r="C383" t="n">
-        <v>49.54527256510714</v>
+        <v>49.5452685563496</v>
       </c>
       <c r="D383" t="n">
-        <v>47.11781778017441</v>
+        <v>47.11781396782467</v>
       </c>
       <c r="E383" t="n">
-        <v>48.22032836396376</v>
+        <v>48.22032446240879</v>
       </c>
       <c r="F383" t="n">
         <v>6322705</v>
@@ -8152,16 +8152,16 @@
         <v>44718</v>
       </c>
       <c r="B387" t="n">
-        <v>45.31898498535156</v>
+        <v>45.3189811706543</v>
       </c>
       <c r="C387" t="n">
-        <v>47.45630618888874</v>
+        <v>47.4563021942838</v>
       </c>
       <c r="D387" t="n">
-        <v>45.13523009894016</v>
+        <v>45.13522629971035</v>
       </c>
       <c r="E387" t="n">
-        <v>47.156500121283</v>
+        <v>47.15649615191405</v>
       </c>
       <c r="F387" t="n">
         <v>1711233</v>
@@ -8172,16 +8172,16 @@
         <v>44719</v>
       </c>
       <c r="B388" t="n">
-        <v>45.31898498535156</v>
+        <v>45.3189811706543</v>
       </c>
       <c r="C388" t="n">
-        <v>45.84122466966569</v>
+        <v>45.84122081100923</v>
       </c>
       <c r="D388" t="n">
-        <v>44.73871408907649</v>
+        <v>44.73871032322317</v>
       </c>
       <c r="E388" t="n">
-        <v>44.98049269229714</v>
+        <v>44.98048890609225</v>
       </c>
       <c r="F388" t="n">
         <v>1887578</v>
@@ -8192,16 +8192,16 @@
         <v>44720</v>
       </c>
       <c r="B389" t="n">
-        <v>45.25128173828125</v>
+        <v>45.25128555297852</v>
       </c>
       <c r="C389" t="n">
-        <v>46.00563122530019</v>
+        <v>46.00563510358936</v>
       </c>
       <c r="D389" t="n">
-        <v>44.9224619623857</v>
+        <v>44.92246574936335</v>
       </c>
       <c r="E389" t="n">
-        <v>45.31898169100119</v>
+        <v>45.31898551140559</v>
       </c>
       <c r="F389" t="n">
         <v>1920490</v>
@@ -8212,16 +8212,16 @@
         <v>44721</v>
       </c>
       <c r="B390" t="n">
-        <v>44.50660705566406</v>
+        <v>44.5066032409668</v>
       </c>
       <c r="C390" t="n">
-        <v>45.59944512032232</v>
+        <v>45.59944121195702</v>
       </c>
       <c r="D390" t="n">
-        <v>44.32285592064108</v>
+        <v>44.32285212169327</v>
       </c>
       <c r="E390" t="n">
-        <v>45.2222703572209</v>
+        <v>45.22226648118356</v>
       </c>
       <c r="F390" t="n">
         <v>1644697</v>
@@ -8472,16 +8472,16 @@
         <v>44741</v>
       </c>
       <c r="B403" t="n">
-        <v>34.71940994262695</v>
+        <v>34.71940612792969</v>
       </c>
       <c r="C403" t="n">
-        <v>35.41573204057546</v>
+        <v>35.41572814937177</v>
       </c>
       <c r="D403" t="n">
-        <v>34.0907840567348</v>
+        <v>34.09078031110602</v>
       </c>
       <c r="E403" t="n">
-        <v>35.29967710839206</v>
+        <v>35.29967322993957</v>
       </c>
       <c r="F403" t="n">
         <v>2690880</v>
@@ -8532,16 +8532,16 @@
         <v>44746</v>
       </c>
       <c r="B406" t="n">
-        <v>35.08690643310547</v>
+        <v>35.08691024780273</v>
       </c>
       <c r="C406" t="n">
-        <v>35.60914979405575</v>
+        <v>35.60915366553204</v>
       </c>
       <c r="D406" t="n">
-        <v>34.19716459197961</v>
+        <v>34.1971683099429</v>
       </c>
       <c r="E406" t="n">
-        <v>34.57433556409744</v>
+        <v>34.57433932306729</v>
       </c>
       <c r="F406" t="n">
         <v>2359523</v>
@@ -8612,16 +8612,16 @@
         <v>44750</v>
       </c>
       <c r="B410" t="n">
-        <v>31.81806564331055</v>
+        <v>31.81806373596191</v>
       </c>
       <c r="C410" t="n">
-        <v>32.48537398775778</v>
+        <v>32.48537204040704</v>
       </c>
       <c r="D410" t="n">
-        <v>31.19911226993215</v>
+        <v>31.19911039968697</v>
       </c>
       <c r="E410" t="n">
-        <v>31.31516719855805</v>
+        <v>31.3151653213559</v>
       </c>
       <c r="F410" t="n">
         <v>4375906</v>
@@ -8712,16 +8712,16 @@
         <v>44757</v>
       </c>
       <c r="B415" t="n">
-        <v>27.79486656188965</v>
+        <v>27.79486846923828</v>
       </c>
       <c r="C415" t="n">
-        <v>29.07145943509457</v>
+        <v>29.07146143004599</v>
       </c>
       <c r="D415" t="n">
-        <v>27.79486656188965</v>
+        <v>27.79486846923828</v>
       </c>
       <c r="E415" t="n">
-        <v>29.06178694260021</v>
+        <v>29.06178893688788</v>
       </c>
       <c r="F415" t="n">
         <v>4618481</v>
@@ -8752,16 +8752,16 @@
         <v>44761</v>
       </c>
       <c r="B417" t="n">
-        <v>29.43896102905273</v>
+        <v>29.43896293640137</v>
       </c>
       <c r="C417" t="n">
-        <v>29.5356728353309</v>
+        <v>29.53567474894549</v>
       </c>
       <c r="D417" t="n">
-        <v>28.11401509178381</v>
+        <v>28.11401691328927</v>
       </c>
       <c r="E417" t="n">
-        <v>28.14302882104603</v>
+        <v>28.14303064443129</v>
       </c>
       <c r="F417" t="n">
         <v>4570230</v>
@@ -8772,16 +8772,16 @@
         <v>44762</v>
       </c>
       <c r="B418" t="n">
-        <v>30.5994987487793</v>
+        <v>30.59950065612793</v>
       </c>
       <c r="C418" t="n">
-        <v>30.97667347904845</v>
+        <v>30.97667540990739</v>
       </c>
       <c r="D418" t="n">
-        <v>29.21652536238831</v>
+        <v>29.21652718353251</v>
       </c>
       <c r="E418" t="n">
-        <v>29.21652536238831</v>
+        <v>29.21652718353251</v>
       </c>
       <c r="F418" t="n">
         <v>5027446</v>
@@ -8792,16 +8792,16 @@
         <v>44763</v>
       </c>
       <c r="B419" t="n">
-        <v>29.44863319396973</v>
+        <v>29.44863510131836</v>
       </c>
       <c r="C419" t="n">
-        <v>29.86449039614633</v>
+        <v>29.86449233042948</v>
       </c>
       <c r="D419" t="n">
-        <v>28.83935050759925</v>
+        <v>28.83935237548546</v>
       </c>
       <c r="E419" t="n">
-        <v>29.86449039614633</v>
+        <v>29.86449233042948</v>
       </c>
       <c r="F419" t="n">
         <v>5437325</v>
@@ -8832,16 +8832,16 @@
         <v>44767</v>
       </c>
       <c r="B421" t="n">
-        <v>29.26488304138184</v>
+        <v>29.2648811340332</v>
       </c>
       <c r="C421" t="n">
-        <v>29.71942650877206</v>
+        <v>29.7194245717984</v>
       </c>
       <c r="D421" t="n">
-        <v>28.43316480875549</v>
+        <v>28.43316295561438</v>
       </c>
       <c r="E421" t="n">
-        <v>28.87803765682343</v>
+        <v>28.87803577468757</v>
       </c>
       <c r="F421" t="n">
         <v>3521914</v>
@@ -8852,16 +8852,16 @@
         <v>44768</v>
       </c>
       <c r="B422" t="n">
-        <v>28.95540618896484</v>
+        <v>28.95540428161621</v>
       </c>
       <c r="C422" t="n">
-        <v>30.15462856046375</v>
+        <v>30.15462657412001</v>
       </c>
       <c r="D422" t="n">
-        <v>28.81033940483069</v>
+        <v>28.81033750703789</v>
       </c>
       <c r="E422" t="n">
-        <v>29.88383623072646</v>
+        <v>29.88383426222034</v>
       </c>
       <c r="F422" t="n">
         <v>2984449</v>
@@ -8872,16 +8872,16 @@
         <v>44769</v>
       </c>
       <c r="B423" t="n">
-        <v>29.66139793395996</v>
+        <v>29.66139984130859</v>
       </c>
       <c r="C423" t="n">
-        <v>29.76778035716261</v>
+        <v>29.76778227135207</v>
       </c>
       <c r="D423" t="n">
-        <v>28.6169130648438</v>
+        <v>28.61691490502781</v>
       </c>
       <c r="E423" t="n">
-        <v>28.95540344493757</v>
+        <v>28.95540530688788</v>
       </c>
       <c r="F423" t="n">
         <v>2554762</v>
@@ -8892,16 +8892,16 @@
         <v>44770</v>
       </c>
       <c r="B424" t="n">
-        <v>30.78325080871582</v>
+        <v>30.78325271606445</v>
       </c>
       <c r="C424" t="n">
-        <v>30.88963323601387</v>
+        <v>30.88963514995402</v>
       </c>
       <c r="D424" t="n">
-        <v>29.53567353730325</v>
+        <v>29.53567536735125</v>
       </c>
       <c r="E424" t="n">
-        <v>29.96120324649545</v>
+        <v>29.96120510290952</v>
       </c>
       <c r="F424" t="n">
         <v>4208906</v>
@@ -8952,16 +8952,16 @@
         <v>44775</v>
       </c>
       <c r="B427" t="n">
-        <v>31.85675048828125</v>
+        <v>31.85674858093262</v>
       </c>
       <c r="C427" t="n">
-        <v>32.07918409507452</v>
+        <v>32.0791821744082</v>
       </c>
       <c r="D427" t="n">
-        <v>30.94766170651904</v>
+        <v>30.94765985359998</v>
       </c>
       <c r="E427" t="n">
-        <v>31.32483646063348</v>
+        <v>31.32483458513196</v>
       </c>
       <c r="F427" t="n">
         <v>3020206</v>
@@ -9072,16 +9072,16 @@
         <v>44783</v>
       </c>
       <c r="B433" t="n">
-        <v>33.26873779296875</v>
+        <v>33.26873397827148</v>
       </c>
       <c r="C433" t="n">
-        <v>33.97473237410905</v>
+        <v>33.97472847846024</v>
       </c>
       <c r="D433" t="n">
-        <v>32.87222177725572</v>
+        <v>32.87221800802422</v>
       </c>
       <c r="E433" t="n">
-        <v>33.62657133023831</v>
+        <v>33.62656747451073</v>
       </c>
       <c r="F433" t="n">
         <v>3325457</v>
@@ -9152,16 +9152,16 @@
         <v>44789</v>
       </c>
       <c r="B437" t="n">
-        <v>32.27260971069336</v>
+        <v>32.27260589599609</v>
       </c>
       <c r="C437" t="n">
-        <v>32.61110200955398</v>
+        <v>32.61109815484615</v>
       </c>
       <c r="D437" t="n">
-        <v>31.73102503057709</v>
+        <v>31.73102127989639</v>
       </c>
       <c r="E437" t="n">
-        <v>32.39833338730038</v>
+        <v>32.39832955774229</v>
       </c>
       <c r="F437" t="n">
         <v>2684074</v>
@@ -9172,16 +9172,16 @@
         <v>44790</v>
       </c>
       <c r="B438" t="n">
-        <v>32.53372573852539</v>
+        <v>32.53372955322266</v>
       </c>
       <c r="C438" t="n">
-        <v>32.93024545622303</v>
+        <v>32.93024931741367</v>
       </c>
       <c r="D438" t="n">
-        <v>31.80839000156146</v>
+        <v>31.80839373121048</v>
       </c>
       <c r="E438" t="n">
-        <v>31.81806249384815</v>
+        <v>31.8180662246313</v>
       </c>
       <c r="F438" t="n">
         <v>3057587</v>
@@ -9252,16 +9252,16 @@
         <v>44796</v>
       </c>
       <c r="B442" t="n">
-        <v>35.11592483520508</v>
+        <v>35.11592102050781</v>
       </c>
       <c r="C442" t="n">
-        <v>35.54145457609587</v>
+        <v>35.54145071517264</v>
       </c>
       <c r="D442" t="n">
-        <v>33.43314711052539</v>
+        <v>33.43314347863087</v>
       </c>
       <c r="E442" t="n">
-        <v>33.46216084263848</v>
+        <v>33.46215720759215</v>
       </c>
       <c r="F442" t="n">
         <v>5706007</v>
@@ -9292,16 +9292,16 @@
         <v>44798</v>
       </c>
       <c r="B444" t="n">
-        <v>35.73487854003906</v>
+        <v>35.7348747253418</v>
       </c>
       <c r="C444" t="n">
-        <v>36.56659679067325</v>
+        <v>36.56659288719009</v>
       </c>
       <c r="D444" t="n">
-        <v>35.39638999233915</v>
+        <v>35.39638621377552</v>
       </c>
       <c r="E444" t="n">
-        <v>35.86060596289047</v>
+        <v>35.8606021347718</v>
       </c>
       <c r="F444" t="n">
         <v>2850362</v>
@@ -9372,16 +9372,16 @@
         <v>44804</v>
       </c>
       <c r="B448" t="n">
-        <v>36.16040802001953</v>
+        <v>36.16040420532227</v>
       </c>
       <c r="C448" t="n">
-        <v>36.46021408739674</v>
+        <v>36.46021024107181</v>
       </c>
       <c r="D448" t="n">
-        <v>35.22230734004456</v>
+        <v>35.22230362431106</v>
       </c>
       <c r="E448" t="n">
-        <v>35.91862941698318</v>
+        <v>35.91862562779205</v>
       </c>
       <c r="F448" t="n">
         <v>3394125</v>
@@ -9392,16 +9392,16 @@
         <v>44805</v>
       </c>
       <c r="B449" t="n">
-        <v>35.58013916015625</v>
+        <v>35.58013534545898</v>
       </c>
       <c r="C449" t="n">
-        <v>36.22810623483188</v>
+        <v>36.22810235066332</v>
       </c>
       <c r="D449" t="n">
-        <v>35.00954078502128</v>
+        <v>35.00953703150028</v>
       </c>
       <c r="E449" t="n">
-        <v>35.84125898955293</v>
+        <v>35.8412551468599</v>
       </c>
       <c r="F449" t="n">
         <v>3340084</v>
@@ -9492,16 +9492,16 @@
         <v>44813</v>
       </c>
       <c r="B454" t="n">
-        <v>35.92829895019531</v>
+        <v>35.92830276489258</v>
       </c>
       <c r="C454" t="n">
-        <v>36.3731698941971</v>
+        <v>36.37317375612866</v>
       </c>
       <c r="D454" t="n">
-        <v>35.60915167019012</v>
+        <v>35.60915545100184</v>
       </c>
       <c r="E454" t="n">
-        <v>35.79290279374685</v>
+        <v>35.79290659406839</v>
       </c>
       <c r="F454" t="n">
         <v>3544465</v>
@@ -9552,16 +9552,16 @@
         <v>44818</v>
       </c>
       <c r="B457" t="n">
-        <v>37.25325012207031</v>
+        <v>37.25324630737305</v>
       </c>
       <c r="C457" t="n">
-        <v>37.57239743066493</v>
+        <v>37.57239358328728</v>
       </c>
       <c r="D457" t="n">
-        <v>35.96698839437353</v>
+        <v>35.96698471138824</v>
       </c>
       <c r="E457" t="n">
-        <v>36.05402584393507</v>
+        <v>36.05402215203722</v>
       </c>
       <c r="F457" t="n">
         <v>4057043</v>
@@ -9592,16 +9592,16 @@
         <v>44820</v>
       </c>
       <c r="B459" t="n">
-        <v>36.7987060546875</v>
+        <v>36.79870223999023</v>
       </c>
       <c r="C459" t="n">
-        <v>36.7987060546875</v>
+        <v>36.79870223999023</v>
       </c>
       <c r="D459" t="n">
-        <v>35.7832329328566</v>
+        <v>35.78322922342723</v>
       </c>
       <c r="E459" t="n">
-        <v>36.14106646140942</v>
+        <v>36.14106271488564</v>
       </c>
       <c r="F459" t="n">
         <v>2974596</v>
@@ -9612,16 +9612,16 @@
         <v>44823</v>
       </c>
       <c r="B460" t="n">
-        <v>36.84706115722656</v>
+        <v>36.8470573425293</v>
       </c>
       <c r="C460" t="n">
-        <v>37.39831831798563</v>
+        <v>37.3983144462179</v>
       </c>
       <c r="D460" t="n">
-        <v>35.79290555412169</v>
+        <v>35.7929018485589</v>
       </c>
       <c r="E460" t="n">
-        <v>35.79290555412169</v>
+        <v>35.7929018485589</v>
       </c>
       <c r="F460" t="n">
         <v>3461677</v>
@@ -9652,16 +9652,16 @@
         <v>44825</v>
       </c>
       <c r="B462" t="n">
-        <v>38.03661346435547</v>
+        <v>38.0366096496582</v>
       </c>
       <c r="C462" t="n">
-        <v>38.79096301231463</v>
+        <v>38.79095912196355</v>
       </c>
       <c r="D462" t="n">
-        <v>37.62075246461414</v>
+        <v>37.62074869162363</v>
       </c>
       <c r="E462" t="n">
-        <v>37.93989977373904</v>
+        <v>37.9398959687412</v>
       </c>
       <c r="F462" t="n">
         <v>4689181</v>
@@ -9732,16 +9732,16 @@
         <v>44831</v>
       </c>
       <c r="B466" t="n">
-        <v>33.61689376831055</v>
+        <v>33.61689758300781</v>
       </c>
       <c r="C466" t="n">
-        <v>34.44861190035511</v>
+        <v>34.44861580943209</v>
       </c>
       <c r="D466" t="n">
-        <v>33.3267602334253</v>
+        <v>33.32676401519949</v>
       </c>
       <c r="E466" t="n">
-        <v>34.44861190035511</v>
+        <v>34.44861580943209</v>
       </c>
       <c r="F466" t="n">
         <v>5480701</v>
@@ -9752,16 +9752,16 @@
         <v>44832</v>
       </c>
       <c r="B467" t="n">
-        <v>34.57433700561523</v>
+        <v>34.5743408203125</v>
       </c>
       <c r="C467" t="n">
-        <v>34.99987045518622</v>
+        <v>34.99987431683395</v>
       </c>
       <c r="D467" t="n">
-        <v>33.19136547412988</v>
+        <v>33.19136913623947</v>
       </c>
       <c r="E467" t="n">
-        <v>33.66525014270204</v>
+        <v>33.66525385709685</v>
       </c>
       <c r="F467" t="n">
         <v>4399676</v>
@@ -9772,16 +9772,16 @@
         <v>44833</v>
       </c>
       <c r="B468" t="n">
-        <v>33.90703201293945</v>
+        <v>33.90702819824219</v>
       </c>
       <c r="C468" t="n">
-        <v>34.69039528924284</v>
+        <v>34.69039138641359</v>
       </c>
       <c r="D468" t="n">
-        <v>33.09465875193581</v>
+        <v>33.09465502863428</v>
       </c>
       <c r="E468" t="n">
-        <v>34.61302658569848</v>
+        <v>34.61302269157358</v>
       </c>
       <c r="F468" t="n">
         <v>4499631</v>
@@ -9812,16 +9812,16 @@
         <v>44837</v>
       </c>
       <c r="B470" t="n">
-        <v>36.7987060546875</v>
+        <v>36.79870223999023</v>
       </c>
       <c r="C470" t="n">
-        <v>36.91476098234264</v>
+        <v>36.91475715561467</v>
       </c>
       <c r="D470" t="n">
-        <v>35.52211309320833</v>
+        <v>35.52210941084767</v>
       </c>
       <c r="E470" t="n">
-        <v>36.26679013465196</v>
+        <v>36.26678637509517</v>
       </c>
       <c r="F470" t="n">
         <v>4419789</v>
@@ -9852,16 +9852,16 @@
         <v>44839</v>
       </c>
       <c r="B472" t="n">
-        <v>41.63427734375</v>
+        <v>41.63427352905273</v>
       </c>
       <c r="C472" t="n">
-        <v>42.48533680478608</v>
+        <v>42.48533291211138</v>
       </c>
       <c r="D472" t="n">
-        <v>40.55110803146717</v>
+        <v>40.55110431601417</v>
       </c>
       <c r="E472" t="n">
-        <v>40.61880798727272</v>
+        <v>40.61880426561678</v>
       </c>
       <c r="F472" t="n">
         <v>6927519</v>
@@ -9892,16 +9892,16 @@
         <v>44841</v>
       </c>
       <c r="B474" t="n">
-        <v>41.47953796386719</v>
+        <v>41.47954177856445</v>
       </c>
       <c r="C474" t="n">
-        <v>42.45632104937901</v>
+        <v>42.45632495390688</v>
       </c>
       <c r="D474" t="n">
-        <v>41.22808688619578</v>
+        <v>41.22809067776815</v>
       </c>
       <c r="E474" t="n">
-        <v>41.59558913638236</v>
+        <v>41.59559296175236</v>
       </c>
       <c r="F474" t="n">
         <v>3503020</v>
@@ -10072,16 +10072,16 @@
         <v>44855</v>
       </c>
       <c r="B483" t="n">
-        <v>44.22614288330078</v>
+        <v>44.22613906860352</v>
       </c>
       <c r="C483" t="n">
-        <v>44.68068635480393</v>
+        <v>44.68068250090031</v>
       </c>
       <c r="D483" t="n">
-        <v>42.41764149048589</v>
+        <v>42.41763783177974</v>
       </c>
       <c r="E483" t="n">
-        <v>42.9688949036628</v>
+        <v>42.96889119740864</v>
       </c>
       <c r="F483" t="n">
         <v>5360835</v>
@@ -10112,16 +10112,16 @@
         <v>44859</v>
       </c>
       <c r="B485" t="n">
-        <v>42.69810104370117</v>
+        <v>42.69809722900391</v>
       </c>
       <c r="C485" t="n">
-        <v>44.71937098158734</v>
+        <v>44.7193669863075</v>
       </c>
       <c r="D485" t="n">
-        <v>42.52402240539543</v>
+        <v>42.52401860625056</v>
       </c>
       <c r="E485" t="n">
-        <v>43.43310931590769</v>
+        <v>43.43310543554394</v>
       </c>
       <c r="F485" t="n">
         <v>3364870</v>
@@ -10232,16 +10232,16 @@
         <v>44868</v>
       </c>
       <c r="B491" t="n">
-        <v>46.30543899536133</v>
+        <v>46.30543518066406</v>
       </c>
       <c r="C491" t="n">
-        <v>46.43116266535413</v>
+        <v>46.4311588402996</v>
       </c>
       <c r="D491" t="n">
-        <v>44.51627889399545</v>
+        <v>44.51627522669133</v>
       </c>
       <c r="E491" t="n">
-        <v>44.98049109746535</v>
+        <v>44.98048739191887</v>
       </c>
       <c r="F491" t="n">
         <v>3262984</v>
@@ -10312,16 +10312,16 @@
         <v>44874</v>
       </c>
       <c r="B495" t="n">
-        <v>44.69035720825195</v>
+        <v>44.69035339355469</v>
       </c>
       <c r="C495" t="n">
-        <v>46.49886228228617</v>
+        <v>46.49885831321781</v>
       </c>
       <c r="D495" t="n">
-        <v>44.23581375342662</v>
+        <v>44.23580997752845</v>
       </c>
       <c r="E495" t="n">
-        <v>45.35766552501359</v>
+        <v>45.35766165335595</v>
       </c>
       <c r="F495" t="n">
         <v>4884014</v>
@@ -10332,16 +10332,16 @@
         <v>44875</v>
       </c>
       <c r="B496" t="n">
-        <v>42.05980682373047</v>
+        <v>42.0598030090332</v>
       </c>
       <c r="C496" t="n">
-        <v>44.68068514703247</v>
+        <v>44.68068109462947</v>
       </c>
       <c r="D496" t="n">
-        <v>41.6439458411077</v>
+        <v>41.64394206412777</v>
       </c>
       <c r="E496" t="n">
-        <v>43.65554705124352</v>
+        <v>43.65554309181744</v>
       </c>
       <c r="F496" t="n">
         <v>5453172</v>
@@ -10472,16 +10472,16 @@
         <v>44887</v>
       </c>
       <c r="B503" t="n">
-        <v>35.72520446777344</v>
+        <v>35.7252082824707</v>
       </c>
       <c r="C503" t="n">
-        <v>38.01726275125628</v>
+        <v>38.01726681069696</v>
       </c>
       <c r="D503" t="n">
-        <v>35.41572595102293</v>
+        <v>35.41572973267442</v>
       </c>
       <c r="E503" t="n">
-        <v>37.37896822915095</v>
+        <v>37.37897222043525</v>
       </c>
       <c r="F503" t="n">
         <v>4879239</v>
@@ -10492,16 +10492,16 @@
         <v>44888</v>
       </c>
       <c r="B504" t="n">
-        <v>34.29388046264648</v>
+        <v>34.29387664794922</v>
       </c>
       <c r="C504" t="n">
-        <v>35.59948346985989</v>
+        <v>35.59947950993321</v>
       </c>
       <c r="D504" t="n">
-        <v>33.84900571743197</v>
+        <v>33.84900195222058</v>
       </c>
       <c r="E504" t="n">
-        <v>35.37704984482862</v>
+        <v>35.37704590964446</v>
       </c>
       <c r="F504" t="n">
         <v>5644348</v>
@@ -10532,16 +10532,16 @@
         <v>44890</v>
       </c>
       <c r="B506" t="n">
-        <v>34.23584747314453</v>
+        <v>34.2358512878418</v>
       </c>
       <c r="C506" t="n">
-        <v>36.49889581830917</v>
+        <v>36.49889988516448</v>
       </c>
       <c r="D506" t="n">
-        <v>34.11012381427162</v>
+        <v>34.11012761496025</v>
       </c>
       <c r="E506" t="n">
-        <v>36.17007605925269</v>
+        <v>36.17008008946956</v>
       </c>
       <c r="F506" t="n">
         <v>4398253</v>
@@ -10552,16 +10552,16 @@
         <v>44893</v>
       </c>
       <c r="B507" t="n">
-        <v>33.64590835571289</v>
+        <v>33.64591217041016</v>
       </c>
       <c r="C507" t="n">
-        <v>34.11012427192836</v>
+        <v>34.11012813925738</v>
       </c>
       <c r="D507" t="n">
-        <v>32.92057262619048</v>
+        <v>32.92057635865081</v>
       </c>
       <c r="E507" t="n">
-        <v>33.36544355803103</v>
+        <v>33.36544734092983</v>
       </c>
       <c r="F507" t="n">
         <v>4077054</v>
@@ -10652,16 +10652,16 @@
         <v>44900</v>
       </c>
       <c r="B512" t="n">
-        <v>34.04242324829102</v>
+        <v>34.04242706298828</v>
       </c>
       <c r="C512" t="n">
-        <v>35.87994187083461</v>
+        <v>35.879945891439</v>
       </c>
       <c r="D512" t="n">
-        <v>33.77163095133564</v>
+        <v>33.77163473568869</v>
       </c>
       <c r="E512" t="n">
-        <v>35.57046335392476</v>
+        <v>35.57046733984986</v>
       </c>
       <c r="F512" t="n">
         <v>5158181</v>
@@ -10732,16 +10732,16 @@
         <v>44904</v>
       </c>
       <c r="B516" t="n">
-        <v>31.69234085083008</v>
+        <v>31.69233894348145</v>
       </c>
       <c r="C516" t="n">
-        <v>32.74649642178647</v>
+        <v>32.74649445099531</v>
       </c>
       <c r="D516" t="n">
-        <v>31.4892447329005</v>
+        <v>31.48924283777486</v>
       </c>
       <c r="E516" t="n">
-        <v>32.22425300897184</v>
+        <v>32.22425106961099</v>
       </c>
       <c r="F516" t="n">
         <v>2885712</v>
@@ -10752,16 +10752,16 @@
         <v>44907</v>
       </c>
       <c r="B517" t="n">
-        <v>32.23392486572266</v>
+        <v>32.23392105102539</v>
       </c>
       <c r="C517" t="n">
-        <v>32.41767599422015</v>
+        <v>32.41767215777701</v>
       </c>
       <c r="D517" t="n">
-        <v>31.06371439332975</v>
+        <v>31.06371071712008</v>
       </c>
       <c r="E517" t="n">
-        <v>31.59562654097396</v>
+        <v>31.59562280181559</v>
       </c>
       <c r="F517" t="n">
         <v>3445728</v>
@@ -10772,16 +10772,16 @@
         <v>44908</v>
       </c>
       <c r="B518" t="n">
-        <v>32.5240592956543</v>
+        <v>32.52405548095703</v>
       </c>
       <c r="C518" t="n">
-        <v>33.41380497900949</v>
+        <v>33.41380105995531</v>
       </c>
       <c r="D518" t="n">
-        <v>31.98247464077933</v>
+        <v>31.9824708896037</v>
       </c>
       <c r="E518" t="n">
-        <v>32.39833187733107</v>
+        <v>32.39832807738018</v>
       </c>
       <c r="F518" t="n">
         <v>3369136</v>
@@ -10872,16 +10872,16 @@
         <v>44915</v>
       </c>
       <c r="B523" t="n">
-        <v>31.63431167602539</v>
+        <v>31.63431358337402</v>
       </c>
       <c r="C523" t="n">
-        <v>31.83740403538475</v>
+        <v>31.83740595497857</v>
       </c>
       <c r="D523" t="n">
-        <v>30.62851300266902</v>
+        <v>30.62851484937437</v>
       </c>
       <c r="E523" t="n">
-        <v>30.76390915810044</v>
+        <v>30.76391101296931</v>
       </c>
       <c r="F523" t="n">
         <v>3472546</v>
@@ -10892,16 +10892,16 @@
         <v>44916</v>
       </c>
       <c r="B524" t="n">
-        <v>32.19523620605469</v>
+        <v>32.19524002075195</v>
       </c>
       <c r="C524" t="n">
-        <v>32.50471472608491</v>
+        <v>32.50471857745117</v>
       </c>
       <c r="D524" t="n">
-        <v>31.22812192077017</v>
+        <v>31.22812562087756</v>
       </c>
       <c r="E524" t="n">
-        <v>32.34997359228213</v>
+        <v>32.34997742531367</v>
       </c>
       <c r="F524" t="n">
         <v>3938295</v>
@@ -10912,16 +10912,16 @@
         <v>44917</v>
       </c>
       <c r="B525" t="n">
-        <v>32.01148986816406</v>
+        <v>32.0114860534668</v>
       </c>
       <c r="C525" t="n">
-        <v>32.78518066232546</v>
+        <v>32.78517675543017</v>
       </c>
       <c r="D525" t="n">
-        <v>31.53760514678948</v>
+        <v>31.5376013885634</v>
       </c>
       <c r="E525" t="n">
-        <v>32.41767837830338</v>
+        <v>32.41767451520204</v>
       </c>
       <c r="F525" t="n">
         <v>3822391</v>
@@ -10932,16 +10932,16 @@
         <v>44918</v>
       </c>
       <c r="B526" t="n">
-        <v>34.68072128295898</v>
+        <v>34.68072509765625</v>
       </c>
       <c r="C526" t="n">
-        <v>34.88381363050969</v>
+        <v>34.88381746754605</v>
       </c>
       <c r="D526" t="n">
-        <v>32.68846528926745</v>
+        <v>32.68846888482701</v>
       </c>
       <c r="E526" t="n">
-        <v>33.17202242375276</v>
+        <v>33.17202607250107</v>
       </c>
       <c r="F526" t="n">
         <v>6955860</v>
@@ -11012,16 +11012,16 @@
         <v>44924</v>
       </c>
       <c r="B530" t="n">
-        <v>36.50856781005859</v>
+        <v>36.50856399536133</v>
       </c>
       <c r="C530" t="n">
-        <v>37.23390359436439</v>
+        <v>37.23389970387844</v>
       </c>
       <c r="D530" t="n">
-        <v>35.61882587917678</v>
+        <v>35.61882215744662</v>
       </c>
       <c r="E530" t="n">
-        <v>35.87994571220566</v>
+        <v>35.87994196319169</v>
       </c>
       <c r="F530" t="n">
         <v>4887264</v>
@@ -11032,16 +11032,16 @@
         <v>44928</v>
       </c>
       <c r="B531" t="n">
-        <v>35.2126350402832</v>
+        <v>35.21263885498047</v>
       </c>
       <c r="C531" t="n">
-        <v>36.68264774905137</v>
+        <v>36.68265172299981</v>
       </c>
       <c r="D531" t="n">
-        <v>34.78710534150101</v>
+        <v>34.78710911009928</v>
       </c>
       <c r="E531" t="n">
-        <v>36.01533947163607</v>
+        <v>36.01534337329287</v>
       </c>
       <c r="F531" t="n">
         <v>2924313</v>
@@ -11152,16 +11152,16 @@
         <v>44936</v>
       </c>
       <c r="B537" t="n">
-        <v>37.79483032226562</v>
+        <v>37.79483413696289</v>
       </c>
       <c r="C537" t="n">
-        <v>38.07529137196207</v>
+        <v>38.07529521496675</v>
       </c>
       <c r="D537" t="n">
-        <v>36.49889625466188</v>
+        <v>36.49889993855829</v>
       </c>
       <c r="E537" t="n">
-        <v>37.0985045751726</v>
+        <v>37.09850831958851</v>
       </c>
       <c r="F537" t="n">
         <v>3183751</v>
@@ -11192,16 +11192,16 @@
         <v>44938</v>
       </c>
       <c r="B539" t="n">
-        <v>43.42343902587891</v>
+        <v>43.42343521118164</v>
       </c>
       <c r="C539" t="n">
-        <v>44.7290457434945</v>
+        <v>44.72904181410123</v>
       </c>
       <c r="D539" t="n">
-        <v>43.19133291383822</v>
+        <v>43.19132911953119</v>
       </c>
       <c r="E539" t="n">
-        <v>43.40409778676949</v>
+        <v>43.40409397377132</v>
       </c>
       <c r="F539" t="n">
         <v>7341055</v>
@@ -11212,16 +11212,16 @@
         <v>44939</v>
       </c>
       <c r="B540" t="n">
-        <v>42.75612640380859</v>
+        <v>42.75613021850586</v>
       </c>
       <c r="C540" t="n">
-        <v>43.50080338468374</v>
+        <v>43.50080726582102</v>
       </c>
       <c r="D540" t="n">
-        <v>42.35961043000531</v>
+        <v>42.35961420932546</v>
       </c>
       <c r="E540" t="n">
-        <v>43.42343468839838</v>
+        <v>43.42343856263282</v>
       </c>
       <c r="F540" t="n">
         <v>4249336</v>
@@ -11272,16 +11272,16 @@
         <v>44944</v>
       </c>
       <c r="B543" t="n">
-        <v>44.53561782836914</v>
+        <v>44.53562164306641</v>
       </c>
       <c r="C543" t="n">
-        <v>45.241612337541</v>
+        <v>45.24161621271021</v>
       </c>
       <c r="D543" t="n">
-        <v>43.220342491427</v>
+        <v>43.22034619346439</v>
       </c>
       <c r="E543" t="n">
-        <v>43.42343485149192</v>
+        <v>43.42343857092518</v>
       </c>
       <c r="F543" t="n">
         <v>6730959</v>
@@ -11332,16 +11332,16 @@
         <v>44949</v>
       </c>
       <c r="B546" t="n">
-        <v>46.45050430297852</v>
+        <v>46.45050811767578</v>
       </c>
       <c r="C546" t="n">
-        <v>48.53947031074529</v>
+        <v>48.53947429699662</v>
       </c>
       <c r="D546" t="n">
-        <v>45.88957845353607</v>
+        <v>45.88958222216792</v>
       </c>
       <c r="E546" t="n">
-        <v>47.67873842593739</v>
+        <v>47.67874234150205</v>
       </c>
       <c r="F546" t="n">
         <v>5971946</v>
@@ -11392,16 +11392,16 @@
         <v>44952</v>
       </c>
       <c r="B549" t="n">
-        <v>45.26095199584961</v>
+        <v>45.26095581054688</v>
       </c>
       <c r="C549" t="n">
-        <v>46.77931963988798</v>
+        <v>46.77932358255676</v>
       </c>
       <c r="D549" t="n">
-        <v>45.24161075927422</v>
+        <v>45.24161457234137</v>
       </c>
       <c r="E549" t="n">
-        <v>45.92826025966649</v>
+        <v>45.92826413060603</v>
       </c>
       <c r="F549" t="n">
         <v>3327082</v>
@@ -11412,16 +11412,16 @@
         <v>44953</v>
       </c>
       <c r="B550" t="n">
-        <v>44.50660705566406</v>
+        <v>44.5066032409668</v>
       </c>
       <c r="C550" t="n">
-        <v>46.34412590104548</v>
+        <v>46.34412192885299</v>
       </c>
       <c r="D550" t="n">
-        <v>44.16811476963287</v>
+        <v>44.16811098394805</v>
       </c>
       <c r="E550" t="n">
-        <v>46.20872973614816</v>
+        <v>46.20872577556058</v>
       </c>
       <c r="F550" t="n">
         <v>4035914</v>
@@ -11432,16 +11432,16 @@
         <v>44956</v>
       </c>
       <c r="B551" t="n">
-        <v>43.79093933105469</v>
+        <v>43.79094314575195</v>
       </c>
       <c r="C551" t="n">
-        <v>44.43890261092821</v>
+        <v>44.43890648207057</v>
       </c>
       <c r="D551" t="n">
-        <v>43.13329981152729</v>
+        <v>43.13330356893655</v>
       </c>
       <c r="E551" t="n">
-        <v>44.3131789517849</v>
+        <v>44.31318281197527</v>
       </c>
       <c r="F551" t="n">
         <v>3870439</v>
@@ -11572,16 +11572,16 @@
         <v>44965</v>
       </c>
       <c r="B558" t="n">
-        <v>43.12363052368164</v>
+        <v>43.12362670898438</v>
       </c>
       <c r="C558" t="n">
-        <v>43.13330301647882</v>
+        <v>43.13329920092593</v>
       </c>
       <c r="D558" t="n">
-        <v>42.08881994983436</v>
+        <v>42.08881622667597</v>
       </c>
       <c r="E558" t="n">
-        <v>42.57237713333137</v>
+        <v>42.57237336739773</v>
       </c>
       <c r="F558" t="n">
         <v>2757212</v>
@@ -11672,16 +11672,16 @@
         <v>44972</v>
       </c>
       <c r="B563" t="n">
-        <v>40.0482063293457</v>
+        <v>40.04821014404297</v>
       </c>
       <c r="C563" t="n">
-        <v>40.52209099098364</v>
+        <v>40.52209485081966</v>
       </c>
       <c r="D563" t="n">
-        <v>38.90700964744255</v>
+        <v>38.90701335343782</v>
       </c>
       <c r="E563" t="n">
-        <v>38.92635463185054</v>
+        <v>38.92635833968847</v>
       </c>
       <c r="F563" t="n">
         <v>3495706</v>
@@ -11752,16 +11752,16 @@
         <v>44980</v>
       </c>
       <c r="B567" t="n">
-        <v>38.00759506225586</v>
+        <v>38.00759887695312</v>
       </c>
       <c r="C567" t="n">
-        <v>39.07141929530241</v>
+        <v>39.07142321677222</v>
       </c>
       <c r="D567" t="n">
-        <v>37.7368027579212</v>
+        <v>37.73680654543994</v>
       </c>
       <c r="E567" t="n">
-        <v>37.95924009667655</v>
+        <v>37.95924390652058</v>
       </c>
       <c r="F567" t="n">
         <v>3548732</v>
@@ -11812,16 +11812,16 @@
         <v>44985</v>
       </c>
       <c r="B570" t="n">
-        <v>35.2126350402832</v>
+        <v>35.21263885498047</v>
       </c>
       <c r="C570" t="n">
-        <v>38.49115271645117</v>
+        <v>38.49115688632073</v>
       </c>
       <c r="D570" t="n">
-        <v>35.2126350402832</v>
+        <v>35.21263885498047</v>
       </c>
       <c r="E570" t="n">
-        <v>37.13719117707558</v>
+        <v>37.13719520026616</v>
       </c>
       <c r="F570" t="n">
         <v>11036876</v>
@@ -11832,16 +11832,16 @@
         <v>44986</v>
       </c>
       <c r="B571" t="n">
-        <v>31.52792930603027</v>
+        <v>31.52793121337891</v>
       </c>
       <c r="C571" t="n">
-        <v>35.21263549119504</v>
+        <v>35.21263762145776</v>
       </c>
       <c r="D571" t="n">
-        <v>29.89350481936535</v>
+        <v>29.89350662783602</v>
       </c>
       <c r="E571" t="n">
-        <v>35.10625306513723</v>
+        <v>35.10625518896411</v>
       </c>
       <c r="F571" t="n">
         <v>24633899</v>
@@ -11872,16 +11872,16 @@
         <v>44988</v>
       </c>
       <c r="B573" t="n">
-        <v>31.74069404602051</v>
+        <v>31.74069595336914</v>
       </c>
       <c r="C573" t="n">
-        <v>31.93411766023568</v>
+        <v>31.93411957920744</v>
       </c>
       <c r="D573" t="n">
-        <v>30.40607560502645</v>
+        <v>30.40607743217574</v>
       </c>
       <c r="E573" t="n">
-        <v>30.47377368262298</v>
+        <v>30.47377551384036</v>
       </c>
       <c r="F573" t="n">
         <v>7573675</v>
@@ -11892,16 +11892,16 @@
         <v>44991</v>
       </c>
       <c r="B574" t="n">
-        <v>31.86641883850098</v>
+        <v>31.86642074584961</v>
       </c>
       <c r="C574" t="n">
-        <v>32.34997601739302</v>
+        <v>32.34997795368473</v>
       </c>
       <c r="D574" t="n">
-        <v>30.94766132287878</v>
+        <v>30.94766317523564</v>
       </c>
       <c r="E574" t="n">
-        <v>31.74069517121325</v>
+        <v>31.74069707103675</v>
       </c>
       <c r="F574" t="n">
         <v>5963007</v>
@@ -11992,16 +11992,16 @@
         <v>44998</v>
       </c>
       <c r="B579" t="n">
-        <v>26.4505786895752</v>
+        <v>26.45058059692383</v>
       </c>
       <c r="C579" t="n">
-        <v>27.32098119587531</v>
+        <v>27.32098316598858</v>
       </c>
       <c r="D579" t="n">
-        <v>25.76392542920967</v>
+        <v>25.76392728704381</v>
       </c>
       <c r="E579" t="n">
-        <v>26.59564546166059</v>
+        <v>26.59564737946998</v>
       </c>
       <c r="F579" t="n">
         <v>13860726</v>
@@ -12032,16 +12032,16 @@
         <v>45000</v>
       </c>
       <c r="B581" t="n">
-        <v>26.28617095947266</v>
+        <v>26.28616905212402</v>
       </c>
       <c r="C581" t="n">
-        <v>26.82775374453002</v>
+        <v>26.82775179788365</v>
       </c>
       <c r="D581" t="n">
-        <v>25.62853324821252</v>
+        <v>25.62853138858268</v>
       </c>
       <c r="E581" t="n">
-        <v>26.58597514665809</v>
+        <v>26.58597321755539</v>
       </c>
       <c r="F581" t="n">
         <v>12174787</v>
@@ -12072,16 +12072,16 @@
         <v>45002</v>
       </c>
       <c r="B583" t="n">
-        <v>30.70588111877441</v>
+        <v>30.70588302612305</v>
       </c>
       <c r="C583" t="n">
-        <v>30.8896322374788</v>
+        <v>30.88963415624145</v>
       </c>
       <c r="D583" t="n">
-        <v>27.73684012155175</v>
+        <v>27.73684184447329</v>
       </c>
       <c r="E583" t="n">
-        <v>30.45443004984579</v>
+        <v>30.45443194157511</v>
       </c>
       <c r="F583" t="n">
         <v>23193684</v>
@@ -12092,16 +12092,16 @@
         <v>45005</v>
       </c>
       <c r="B584" t="n">
-        <v>29.79679679870605</v>
+        <v>29.79679489135742</v>
       </c>
       <c r="C584" t="n">
-        <v>31.20878403151084</v>
+        <v>31.20878203377826</v>
       </c>
       <c r="D584" t="n">
-        <v>29.32291022343201</v>
+        <v>29.32290834641774</v>
       </c>
       <c r="E584" t="n">
-        <v>30.70588372476053</v>
+        <v>30.70588175921954</v>
       </c>
       <c r="F584" t="n">
         <v>7729094</v>
@@ -12252,16 +12252,16 @@
         <v>45015</v>
       </c>
       <c r="B592" t="n">
-        <v>29.38093566894531</v>
+        <v>29.38093376159668</v>
       </c>
       <c r="C592" t="n">
-        <v>30.51245994826028</v>
+        <v>30.51245796745546</v>
       </c>
       <c r="D592" t="n">
-        <v>29.27455323657771</v>
+        <v>29.2745513361352</v>
       </c>
       <c r="E592" t="n">
-        <v>29.95153405508782</v>
+        <v>29.95153211069714</v>
       </c>
       <c r="F592" t="n">
         <v>5560645</v>
@@ -12312,16 +12312,16 @@
         <v>45020</v>
       </c>
       <c r="B595" t="n">
-        <v>27.92059326171875</v>
+        <v>27.92059135437012</v>
       </c>
       <c r="C595" t="n">
-        <v>29.70975523383049</v>
+        <v>29.70975320425825</v>
       </c>
       <c r="D595" t="n">
-        <v>27.91092264260987</v>
+        <v>27.91092073592187</v>
       </c>
       <c r="E595" t="n">
-        <v>29.57435907115471</v>
+        <v>29.57435705083184</v>
       </c>
       <c r="F595" t="n">
         <v>7552242</v>
@@ -12332,16 +12332,16 @@
         <v>45021</v>
       </c>
       <c r="B596" t="n">
-        <v>26.76972579956055</v>
+        <v>26.76972770690918</v>
       </c>
       <c r="C596" t="n">
-        <v>27.85289314814766</v>
+        <v>27.8528951326722</v>
       </c>
       <c r="D596" t="n">
-        <v>26.23781180677641</v>
+        <v>26.23781367622606</v>
       </c>
       <c r="E596" t="n">
-        <v>27.65947141114338</v>
+        <v>27.65947338188658</v>
       </c>
       <c r="F596" t="n">
         <v>12382825</v>
@@ -12372,16 +12372,16 @@
         <v>45026</v>
       </c>
       <c r="B598" t="n">
-        <v>29.65172576904297</v>
+        <v>29.6517276763916</v>
       </c>
       <c r="C598" t="n">
-        <v>29.8354768886412</v>
+        <v>29.83547880780963</v>
       </c>
       <c r="D598" t="n">
-        <v>28.19138368313743</v>
+        <v>28.19138549654949</v>
       </c>
       <c r="E598" t="n">
-        <v>28.33645045512486</v>
+        <v>28.33645227786835</v>
       </c>
       <c r="F598" t="n">
         <v>8774363</v>
@@ -12552,16 +12552,16 @@
         <v>45040</v>
       </c>
       <c r="B607" t="n">
-        <v>26.96700286865234</v>
+        <v>26.96700477600098</v>
       </c>
       <c r="C607" t="n">
-        <v>27.07506608384296</v>
+        <v>27.07506799883479</v>
       </c>
       <c r="D607" t="n">
-        <v>26.23019953206389</v>
+        <v>26.23020138729918</v>
       </c>
       <c r="E607" t="n">
-        <v>26.86876204901633</v>
+        <v>26.86876394941649</v>
       </c>
       <c r="F607" t="n">
         <v>6680100</v>
@@ -12572,16 +12572,16 @@
         <v>45041</v>
       </c>
       <c r="B608" t="n">
-        <v>27.21260452270508</v>
+        <v>27.21260261535645</v>
       </c>
       <c r="C608" t="n">
-        <v>27.45820563979163</v>
+        <v>27.45820371522866</v>
       </c>
       <c r="D608" t="n">
-        <v>26.42667982375542</v>
+        <v>26.42667797149275</v>
       </c>
       <c r="E608" t="n">
-        <v>26.79999457104816</v>
+        <v>26.79999269261962</v>
       </c>
       <c r="F608" t="n">
         <v>5323000</v>
@@ -12612,16 +12612,16 @@
         <v>45043</v>
       </c>
       <c r="B610" t="n">
-        <v>29.90439224243164</v>
+        <v>29.90439414978027</v>
       </c>
       <c r="C610" t="n">
-        <v>30.267880842768</v>
+        <v>30.26788277330051</v>
       </c>
       <c r="D610" t="n">
-        <v>26.73122441728851</v>
+        <v>26.73122612224756</v>
       </c>
       <c r="E610" t="n">
-        <v>26.73122441728851</v>
+        <v>26.73122612224756</v>
       </c>
       <c r="F610" t="n">
         <v>20933600</v>
@@ -12672,16 +12672,16 @@
         <v>45049</v>
       </c>
       <c r="B613" t="n">
-        <v>29.14793968200684</v>
+        <v>29.14794158935547</v>
       </c>
       <c r="C613" t="n">
-        <v>29.61949336143113</v>
+        <v>29.61949529963673</v>
       </c>
       <c r="D613" t="n">
-        <v>28.33254407533193</v>
+        <v>28.33254592932366</v>
       </c>
       <c r="E613" t="n">
-        <v>29.26582903875679</v>
+        <v>29.26583095381972</v>
       </c>
       <c r="F613" t="n">
         <v>9250000</v>
@@ -12692,16 +12692,16 @@
         <v>45050</v>
       </c>
       <c r="B614" t="n">
-        <v>29.2756519317627</v>
+        <v>29.27565383911133</v>
       </c>
       <c r="C614" t="n">
-        <v>29.95351152857367</v>
+        <v>29.95351348008578</v>
       </c>
       <c r="D614" t="n">
-        <v>29.17741298555374</v>
+        <v>29.17741488650197</v>
       </c>
       <c r="E614" t="n">
-        <v>29.47213357175619</v>
+        <v>29.47213549190587</v>
       </c>
       <c r="F614" t="n">
         <v>6670900</v>
@@ -12792,16 +12792,16 @@
         <v>45057</v>
       </c>
       <c r="B619" t="n">
-        <v>31.66289520263672</v>
+        <v>31.66289710998535</v>
       </c>
       <c r="C619" t="n">
-        <v>31.81025737023202</v>
+        <v>31.81025928645763</v>
       </c>
       <c r="D619" t="n">
-        <v>31.10292496189554</v>
+        <v>31.10292683551199</v>
       </c>
       <c r="E619" t="n">
-        <v>31.71201467597662</v>
+        <v>31.71201658628417</v>
       </c>
       <c r="F619" t="n">
         <v>4858000</v>
@@ -12812,16 +12812,16 @@
         <v>45058</v>
       </c>
       <c r="B620" t="n">
-        <v>32.49794006347656</v>
+        <v>32.49794387817383</v>
       </c>
       <c r="C620" t="n">
-        <v>32.64529847816273</v>
+        <v>32.64530231015733</v>
       </c>
       <c r="D620" t="n">
-        <v>31.46641242279611</v>
+        <v>31.46641611640984</v>
       </c>
       <c r="E620" t="n">
-        <v>31.554828970638</v>
+        <v>31.55483267463029</v>
       </c>
       <c r="F620" t="n">
         <v>5317000</v>
@@ -12852,16 +12852,16 @@
         <v>45062</v>
       </c>
       <c r="B622" t="n">
-        <v>29.90439224243164</v>
+        <v>29.90439414978027</v>
       </c>
       <c r="C622" t="n">
-        <v>32.08532946581322</v>
+        <v>32.08533151226543</v>
       </c>
       <c r="D622" t="n">
-        <v>29.70791060120974</v>
+        <v>29.70791249602647</v>
       </c>
       <c r="E622" t="n">
-        <v>31.86919928571158</v>
+        <v>31.86920131837866</v>
       </c>
       <c r="F622" t="n">
         <v>13269700</v>
@@ -12912,16 +12912,16 @@
         <v>45065</v>
       </c>
       <c r="B625" t="n">
-        <v>32.49794006347656</v>
+        <v>32.49794387817383</v>
       </c>
       <c r="C625" t="n">
-        <v>34.87535696477425</v>
+        <v>34.87536105853923</v>
       </c>
       <c r="D625" t="n">
-        <v>31.04398009551434</v>
+        <v>31.0439837395418</v>
       </c>
       <c r="E625" t="n">
-        <v>31.8691980857257</v>
+        <v>31.86920182661951</v>
       </c>
       <c r="F625" t="n">
         <v>19443700</v>
@@ -12972,16 +12972,16 @@
         <v>45070</v>
       </c>
       <c r="B628" t="n">
-        <v>31.48606300354004</v>
+        <v>31.48606109619141</v>
       </c>
       <c r="C628" t="n">
-        <v>31.86920015318507</v>
+        <v>31.86919822262693</v>
       </c>
       <c r="D628" t="n">
-        <v>30.464363313224</v>
+        <v>30.46436146776744</v>
       </c>
       <c r="E628" t="n">
-        <v>31.04398210943912</v>
+        <v>31.04398022887067</v>
       </c>
       <c r="F628" t="n">
         <v>7685200</v>
@@ -13212,16 +13212,16 @@
         <v>45089</v>
       </c>
       <c r="B640" t="n">
-        <v>31.26010894775391</v>
+        <v>31.26011085510254</v>
       </c>
       <c r="C640" t="n">
-        <v>31.86919865058509</v>
+        <v>31.86920059509758</v>
       </c>
       <c r="D640" t="n">
-        <v>30.47418614610471</v>
+        <v>30.47418800549994</v>
       </c>
       <c r="E640" t="n">
-        <v>31.61377514538992</v>
+        <v>31.61377707431765</v>
       </c>
       <c r="F640" t="n">
         <v>7223600</v>
@@ -13252,16 +13252,16 @@
         <v>45091</v>
       </c>
       <c r="B642" t="n">
-        <v>31.1422233581543</v>
+        <v>31.14222145080566</v>
       </c>
       <c r="C642" t="n">
-        <v>31.71201601865814</v>
+        <v>31.71201407641177</v>
       </c>
       <c r="D642" t="n">
-        <v>30.57242882386257</v>
+        <v>30.5724269514118</v>
       </c>
       <c r="E642" t="n">
-        <v>31.33870313362062</v>
+        <v>31.33870121423831</v>
       </c>
       <c r="F642" t="n">
         <v>8288400</v>
@@ -13292,16 +13292,16 @@
         <v>45093</v>
       </c>
       <c r="B644" t="n">
-        <v>31.91832160949707</v>
+        <v>31.9183235168457</v>
       </c>
       <c r="C644" t="n">
-        <v>31.91832160949707</v>
+        <v>31.9183235168457</v>
       </c>
       <c r="D644" t="n">
-        <v>31.19134068168367</v>
+        <v>31.19134254558997</v>
       </c>
       <c r="E644" t="n">
-        <v>31.42711752024974</v>
+        <v>31.4271193982454</v>
       </c>
       <c r="F644" t="n">
         <v>5722800</v>
@@ -13332,16 +13332,16 @@
         <v>45097</v>
       </c>
       <c r="B646" t="n">
-        <v>32.16392135620117</v>
+        <v>32.16392517089844</v>
       </c>
       <c r="C646" t="n">
-        <v>32.29163122856222</v>
+        <v>32.2916350584061</v>
       </c>
       <c r="D646" t="n">
-        <v>31.48605992910253</v>
+        <v>31.48606366340425</v>
       </c>
       <c r="E646" t="n">
-        <v>32.12462428120915</v>
+        <v>32.12462809124572</v>
       </c>
       <c r="F646" t="n">
         <v>4954700</v>
@@ -13352,16 +13352,16 @@
         <v>45098</v>
       </c>
       <c r="B647" t="n">
-        <v>32.06568145751953</v>
+        <v>32.06567764282227</v>
       </c>
       <c r="C647" t="n">
-        <v>32.36040205044127</v>
+        <v>32.36039820068254</v>
       </c>
       <c r="D647" t="n">
-        <v>31.48606266749066</v>
+        <v>31.4860589217478</v>
       </c>
       <c r="E647" t="n">
-        <v>32.12462707513414</v>
+        <v>32.1246232534244</v>
       </c>
       <c r="F647" t="n">
         <v>4670300</v>
@@ -13412,16 +13412,16 @@
         <v>45103</v>
       </c>
       <c r="B650" t="n">
-        <v>30.53313064575195</v>
+        <v>30.53312873840332</v>
       </c>
       <c r="C650" t="n">
-        <v>30.83767550472773</v>
+        <v>30.83767357835474</v>
       </c>
       <c r="D650" t="n">
-        <v>30.30717806889212</v>
+        <v>30.30717617565832</v>
       </c>
       <c r="E650" t="n">
-        <v>30.58225011940398</v>
+        <v>30.58224820898695</v>
       </c>
       <c r="F650" t="n">
         <v>2874500</v>
@@ -13452,16 +13452,16 @@
         <v>45105</v>
       </c>
       <c r="B652" t="n">
-        <v>29.37389183044434</v>
+        <v>29.37389373779297</v>
       </c>
       <c r="C652" t="n">
-        <v>30.06157567506449</v>
+        <v>30.06157762706682</v>
       </c>
       <c r="D652" t="n">
-        <v>29.30512382073987</v>
+        <v>29.30512572362315</v>
       </c>
       <c r="E652" t="n">
-        <v>29.75703082903567</v>
+        <v>29.75703276126285</v>
       </c>
       <c r="F652" t="n">
         <v>4532500</v>
@@ -13532,16 +13532,16 @@
         <v>45111</v>
       </c>
       <c r="B656" t="n">
-        <v>29.80615234375</v>
+        <v>29.80615043640137</v>
       </c>
       <c r="C656" t="n">
-        <v>30.15981855937348</v>
+        <v>30.15981662939312</v>
       </c>
       <c r="D656" t="n">
-        <v>29.57037549126363</v>
+        <v>29.57037359900278</v>
       </c>
       <c r="E656" t="n">
-        <v>29.80615234375</v>
+        <v>29.80615043640137</v>
       </c>
       <c r="F656" t="n">
         <v>2514900</v>
@@ -13552,16 +13552,16 @@
         <v>45112</v>
       </c>
       <c r="B657" t="n">
-        <v>30.40542030334473</v>
+        <v>30.40541839599609</v>
       </c>
       <c r="C657" t="n">
-        <v>30.70996517647691</v>
+        <v>30.70996325002402</v>
       </c>
       <c r="D657" t="n">
-        <v>29.34442350856649</v>
+        <v>29.34442166777476</v>
       </c>
       <c r="E657" t="n">
-        <v>29.60967130192012</v>
+        <v>29.60966944448926</v>
       </c>
       <c r="F657" t="n">
         <v>5394800</v>
@@ -13612,16 +13612,16 @@
         <v>45117</v>
       </c>
       <c r="B660" t="n">
-        <v>31.07345390319824</v>
+        <v>31.07345199584961</v>
       </c>
       <c r="C660" t="n">
-        <v>31.93796904965617</v>
+        <v>31.93796708924193</v>
       </c>
       <c r="D660" t="n">
-        <v>30.84750131505205</v>
+        <v>30.84749942157282</v>
       </c>
       <c r="E660" t="n">
-        <v>31.56465803319331</v>
+        <v>31.56465609569361</v>
       </c>
       <c r="F660" t="n">
         <v>7339200</v>
@@ -13652,16 +13652,16 @@
         <v>45119</v>
       </c>
       <c r="B662" t="n">
-        <v>31.07345390319824</v>
+        <v>31.07345199584961</v>
       </c>
       <c r="C662" t="n">
-        <v>32.08533122554864</v>
+        <v>32.08532925608902</v>
       </c>
       <c r="D662" t="n">
-        <v>31.04398296705007</v>
+        <v>31.04398106151042</v>
       </c>
       <c r="E662" t="n">
-        <v>31.77096208138212</v>
+        <v>31.77096013121909</v>
       </c>
       <c r="F662" t="n">
         <v>4503800</v>
@@ -13732,16 +13732,16 @@
         <v>45125</v>
       </c>
       <c r="B666" t="n">
-        <v>32.91054916381836</v>
+        <v>32.91055297851562</v>
       </c>
       <c r="C666" t="n">
-        <v>33.03826279198419</v>
+        <v>33.03826662148488</v>
       </c>
       <c r="D666" t="n">
-        <v>32.0362098005708</v>
+        <v>32.03621351392245</v>
       </c>
       <c r="E666" t="n">
-        <v>32.18356821992315</v>
+        <v>32.18357195035527</v>
       </c>
       <c r="F666" t="n">
         <v>4775600</v>
@@ -13752,16 +13752,16 @@
         <v>45126</v>
       </c>
       <c r="B667" t="n">
-        <v>33.64735412597656</v>
+        <v>33.6473503112793</v>
       </c>
       <c r="C667" t="n">
-        <v>34.04031742501827</v>
+        <v>34.04031356576963</v>
       </c>
       <c r="D667" t="n">
-        <v>33.04808678134705</v>
+        <v>33.04808303459044</v>
       </c>
       <c r="E667" t="n">
-        <v>33.04808678134705</v>
+        <v>33.04808303459044</v>
       </c>
       <c r="F667" t="n">
         <v>7484200</v>
@@ -13772,16 +13772,16 @@
         <v>45127</v>
       </c>
       <c r="B668" t="n">
-        <v>33.92242431640625</v>
+        <v>33.92242813110352</v>
       </c>
       <c r="C668" t="n">
-        <v>34.11890595509385</v>
+        <v>34.11890979188617</v>
       </c>
       <c r="D668" t="n">
-        <v>33.64735227078894</v>
+        <v>33.64735605455338</v>
       </c>
       <c r="E668" t="n">
-        <v>33.91260192088087</v>
+        <v>33.91260573447357</v>
       </c>
       <c r="F668" t="n">
         <v>3587900</v>
@@ -13952,16 +13952,16 @@
         <v>45140</v>
       </c>
       <c r="B677" t="n">
-        <v>34.44309997558594</v>
+        <v>34.4431037902832</v>
       </c>
       <c r="C677" t="n">
-        <v>34.58063599342123</v>
+        <v>34.5806398233511</v>
       </c>
       <c r="D677" t="n">
-        <v>33.71611906300245</v>
+        <v>33.71612279718397</v>
       </c>
       <c r="E677" t="n">
-        <v>34.38415436183849</v>
+        <v>34.38415817000732</v>
       </c>
       <c r="F677" t="n">
         <v>3408800</v>
@@ -14012,16 +14012,16 @@
         <v>45145</v>
       </c>
       <c r="B680" t="n">
-        <v>35.68093109130859</v>
+        <v>35.68092727661133</v>
       </c>
       <c r="C680" t="n">
-        <v>36.15248480095344</v>
+        <v>36.15248093584172</v>
       </c>
       <c r="D680" t="n">
-        <v>35.09148989114647</v>
+        <v>35.09148613946717</v>
       </c>
       <c r="E680" t="n">
-        <v>36.05424585011833</v>
+        <v>36.05424199550948</v>
       </c>
       <c r="F680" t="n">
         <v>3820600</v>
@@ -14032,16 +14032,16 @@
         <v>45146</v>
       </c>
       <c r="B681" t="n">
-        <v>36.34896850585938</v>
+        <v>36.34896469116211</v>
       </c>
       <c r="C681" t="n">
-        <v>36.51597548123902</v>
+        <v>36.51597164901496</v>
       </c>
       <c r="D681" t="n">
-        <v>34.30556523426109</v>
+        <v>34.30556163401185</v>
       </c>
       <c r="E681" t="n">
-        <v>34.76729657396523</v>
+        <v>34.76729292525891</v>
       </c>
       <c r="F681" t="n">
         <v>5274900</v>
@@ -14172,16 +14172,16 @@
         <v>45155</v>
       </c>
       <c r="B688" t="n">
-        <v>31.26993560791016</v>
+        <v>31.26993370056152</v>
       </c>
       <c r="C688" t="n">
-        <v>31.74149119874277</v>
+        <v>31.74148926263102</v>
       </c>
       <c r="D688" t="n">
-        <v>30.96539073320894</v>
+        <v>30.9653888444364</v>
       </c>
       <c r="E688" t="n">
-        <v>31.4664153864515</v>
+        <v>31.46641346711834</v>
       </c>
       <c r="F688" t="n">
         <v>4529600</v>
@@ -14252,16 +14252,16 @@
         <v>45161</v>
       </c>
       <c r="B692" t="n">
-        <v>31.05380439758301</v>
+        <v>31.05380630493164</v>
       </c>
       <c r="C692" t="n">
-        <v>31.24045988874735</v>
+        <v>31.2404618075605</v>
       </c>
       <c r="D692" t="n">
-        <v>30.68048966767887</v>
+        <v>30.68049155209822</v>
       </c>
       <c r="E692" t="n">
-        <v>31.09309960011686</v>
+        <v>31.09310150987904</v>
       </c>
       <c r="F692" t="n">
         <v>4847400</v>
@@ -14272,16 +14272,16 @@
         <v>45162</v>
       </c>
       <c r="B693" t="n">
-        <v>30.91626739501953</v>
+        <v>30.91626930236816</v>
       </c>
       <c r="C693" t="n">
-        <v>31.30923067440671</v>
+        <v>31.30923260599883</v>
       </c>
       <c r="D693" t="n">
-        <v>30.56260306687397</v>
+        <v>30.56260495240363</v>
       </c>
       <c r="E693" t="n">
-        <v>31.05380529232016</v>
+        <v>31.05380720815405</v>
       </c>
       <c r="F693" t="n">
         <v>3471700</v>
@@ -14332,16 +14332,16 @@
         <v>45167</v>
       </c>
       <c r="B696" t="n">
-        <v>31.29940605163574</v>
+        <v>31.29940795898438</v>
       </c>
       <c r="C696" t="n">
-        <v>31.55482955705047</v>
+        <v>31.55483147996431</v>
       </c>
       <c r="D696" t="n">
-        <v>30.63137073276579</v>
+        <v>30.63137259940515</v>
       </c>
       <c r="E696" t="n">
-        <v>31.06362921093831</v>
+        <v>31.06363110391898</v>
       </c>
       <c r="F696" t="n">
         <v>3743200</v>
@@ -14352,16 +14352,16 @@
         <v>45168</v>
       </c>
       <c r="B697" t="n">
-        <v>31.63342475891113</v>
+        <v>31.6334228515625</v>
       </c>
       <c r="C697" t="n">
-        <v>31.70219277216898</v>
+        <v>31.70219086067396</v>
       </c>
       <c r="D697" t="n">
-        <v>30.96538941791287</v>
+        <v>30.96538755084366</v>
       </c>
       <c r="E697" t="n">
-        <v>31.49588873239543</v>
+        <v>31.49588683333958</v>
       </c>
       <c r="F697" t="n">
         <v>3276100</v>
@@ -14412,16 +14412,16 @@
         <v>45173</v>
       </c>
       <c r="B700" t="n">
-        <v>32.27198791503906</v>
+        <v>32.2719841003418</v>
       </c>
       <c r="C700" t="n">
-        <v>32.55688613348561</v>
+        <v>32.55688228511206</v>
       </c>
       <c r="D700" t="n">
-        <v>32.06568385929886</v>
+        <v>32.06568006898767</v>
       </c>
       <c r="E700" t="n">
-        <v>32.22286843713558</v>
+        <v>32.22286462824446</v>
       </c>
       <c r="F700" t="n">
         <v>2652900</v>
@@ -14432,16 +14432,16 @@
         <v>45174</v>
       </c>
       <c r="B701" t="n">
-        <v>32.63547897338867</v>
+        <v>32.63547515869141</v>
       </c>
       <c r="C701" t="n">
-        <v>32.93019957643972</v>
+        <v>32.93019572729314</v>
       </c>
       <c r="D701" t="n">
-        <v>32.07550870331895</v>
+        <v>32.07550495407551</v>
       </c>
       <c r="E701" t="n">
-        <v>32.27198660696912</v>
+        <v>32.27198283475976</v>
       </c>
       <c r="F701" t="n">
         <v>6036900</v>
@@ -14452,16 +14452,16 @@
         <v>45175</v>
       </c>
       <c r="B702" t="n">
-        <v>32.00673675537109</v>
+        <v>32.00674057006836</v>
       </c>
       <c r="C702" t="n">
-        <v>32.71406536628031</v>
+        <v>32.71406926527997</v>
       </c>
       <c r="D702" t="n">
-        <v>31.928142605506</v>
+        <v>31.92814641083608</v>
       </c>
       <c r="E702" t="n">
-        <v>32.65512350145682</v>
+        <v>32.65512739343153</v>
       </c>
       <c r="F702" t="n">
         <v>4505300</v>
@@ -14512,16 +14512,16 @@
         <v>45181</v>
       </c>
       <c r="B705" t="n">
-        <v>32.33092880249023</v>
+        <v>32.3309326171875</v>
       </c>
       <c r="C705" t="n">
-        <v>32.64529791212711</v>
+        <v>32.6453017639165</v>
       </c>
       <c r="D705" t="n">
-        <v>31.76113619661418</v>
+        <v>31.76113994408213</v>
       </c>
       <c r="E705" t="n">
-        <v>31.97726261725491</v>
+        <v>31.97726639022342</v>
       </c>
       <c r="F705" t="n">
         <v>3620500</v>
@@ -14532,16 +14532,16 @@
         <v>45182</v>
       </c>
       <c r="B706" t="n">
-        <v>31.63342475891113</v>
+        <v>31.6334228515625</v>
       </c>
       <c r="C706" t="n">
-        <v>32.1148008517161</v>
+        <v>32.11479891534272</v>
       </c>
       <c r="D706" t="n">
-        <v>31.44676551071783</v>
+        <v>31.44676361462388</v>
       </c>
       <c r="E706" t="n">
-        <v>31.60395007638945</v>
+        <v>31.60394817081799</v>
       </c>
       <c r="F706" t="n">
         <v>7302700</v>
@@ -14552,16 +14552,16 @@
         <v>45183</v>
       </c>
       <c r="B707" t="n">
-        <v>32.31128311157227</v>
+        <v>32.311279296875</v>
       </c>
       <c r="C707" t="n">
-        <v>32.31128311157227</v>
+        <v>32.311279296875</v>
       </c>
       <c r="D707" t="n">
-        <v>31.74149045549294</v>
+        <v>31.74148670806588</v>
       </c>
       <c r="E707" t="n">
-        <v>31.83972940556933</v>
+        <v>31.83972564654409</v>
       </c>
       <c r="F707" t="n">
         <v>4362300</v>
@@ -14592,16 +14592,16 @@
         <v>45187</v>
       </c>
       <c r="B709" t="n">
-        <v>31.98709106445312</v>
+        <v>31.98709297180176</v>
       </c>
       <c r="C709" t="n">
-        <v>32.7140682775227</v>
+        <v>32.71407022822005</v>
       </c>
       <c r="D709" t="n">
-        <v>31.75131234145109</v>
+        <v>31.75131423474054</v>
       </c>
       <c r="E709" t="n">
-        <v>32.5568837113799</v>
+        <v>32.55688565270453</v>
       </c>
       <c r="F709" t="n">
         <v>5099000</v>
@@ -14692,16 +14692,16 @@
         <v>45194</v>
       </c>
       <c r="B714" t="n">
-        <v>30.95556449890137</v>
+        <v>30.95556640625</v>
       </c>
       <c r="C714" t="n">
-        <v>31.20116561183414</v>
+        <v>31.20116753431566</v>
       </c>
       <c r="D714" t="n">
-        <v>29.99280858591396</v>
+        <v>29.99281043394172</v>
       </c>
       <c r="E714" t="n">
-        <v>30.45453800366397</v>
+        <v>30.45453988014151</v>
       </c>
       <c r="F714" t="n">
         <v>6350700</v>
@@ -14712,16 +14712,16 @@
         <v>45195</v>
       </c>
       <c r="B715" t="n">
-        <v>30.32682609558105</v>
+        <v>30.32682800292969</v>
       </c>
       <c r="C715" t="n">
-        <v>30.83767498381136</v>
+        <v>30.83767692328888</v>
       </c>
       <c r="D715" t="n">
-        <v>30.19911246818264</v>
+        <v>30.19911436749897</v>
       </c>
       <c r="E715" t="n">
-        <v>30.75908270302303</v>
+        <v>30.75908463755763</v>
       </c>
       <c r="F715" t="n">
         <v>3433500</v>
@@ -14732,16 +14732,16 @@
         <v>45196</v>
       </c>
       <c r="B716" t="n">
-        <v>30.86714935302734</v>
+        <v>30.86714744567871</v>
       </c>
       <c r="C716" t="n">
-        <v>31.0734533978611</v>
+        <v>31.07345147776449</v>
       </c>
       <c r="D716" t="n">
-        <v>30.42506658011519</v>
+        <v>30.42506470008381</v>
       </c>
       <c r="E716" t="n">
-        <v>30.65102103837466</v>
+        <v>30.65101914438107</v>
       </c>
       <c r="F716" t="n">
         <v>4307600</v>
@@ -14752,16 +14752,16 @@
         <v>45197</v>
       </c>
       <c r="B717" t="n">
-        <v>30.58224868774414</v>
+        <v>30.58225059509277</v>
       </c>
       <c r="C717" t="n">
-        <v>31.21098878902595</v>
+        <v>31.21099073558775</v>
       </c>
       <c r="D717" t="n">
-        <v>30.41523986184255</v>
+        <v>30.41524175877521</v>
       </c>
       <c r="E717" t="n">
-        <v>30.82784979208249</v>
+        <v>30.82785171474873</v>
       </c>
       <c r="F717" t="n">
         <v>4298000</v>
@@ -14772,16 +14772,16 @@
         <v>45198</v>
       </c>
       <c r="B718" t="n">
-        <v>31.02433395385742</v>
+        <v>31.02433204650879</v>
       </c>
       <c r="C718" t="n">
-        <v>31.60395088345571</v>
+        <v>31.60394894047274</v>
       </c>
       <c r="D718" t="n">
-        <v>30.47418795995777</v>
+        <v>30.47418608643163</v>
       </c>
       <c r="E718" t="n">
-        <v>30.86714938417181</v>
+        <v>30.86714748648674</v>
       </c>
       <c r="F718" t="n">
         <v>5846000</v>
@@ -14852,16 +14852,16 @@
         <v>45204</v>
       </c>
       <c r="B722" t="n">
-        <v>28.03782272338867</v>
+        <v>28.0378246307373</v>
       </c>
       <c r="C722" t="n">
-        <v>28.78444842505877</v>
+        <v>28.78445038319864</v>
       </c>
       <c r="D722" t="n">
-        <v>27.72345173862667</v>
+        <v>27.72345362458937</v>
       </c>
       <c r="E722" t="n">
-        <v>28.62726386957162</v>
+        <v>28.62726581701858</v>
       </c>
       <c r="F722" t="n">
         <v>8409300</v>
@@ -14912,16 +14912,16 @@
         <v>45209</v>
       </c>
       <c r="B725" t="n">
-        <v>30.27770614624023</v>
+        <v>30.2777042388916</v>
       </c>
       <c r="C725" t="n">
-        <v>30.40541977953243</v>
+        <v>30.40541786413846</v>
       </c>
       <c r="D725" t="n">
-        <v>29.43283768343539</v>
+        <v>29.43283582930937</v>
       </c>
       <c r="E725" t="n">
-        <v>29.75703296465965</v>
+        <v>29.7570310901109</v>
       </c>
       <c r="F725" t="n">
         <v>7018100</v>
@@ -14972,16 +14972,16 @@
         <v>45215</v>
       </c>
       <c r="B728" t="n">
-        <v>31.67271995544434</v>
+        <v>31.67272186279297</v>
       </c>
       <c r="C728" t="n">
-        <v>32.01656000130495</v>
+        <v>32.01656192935982</v>
       </c>
       <c r="D728" t="n">
-        <v>31.32887616200829</v>
+        <v>31.32887804865046</v>
       </c>
       <c r="E728" t="n">
-        <v>31.91832105893775</v>
+        <v>31.91832298107662</v>
       </c>
       <c r="F728" t="n">
         <v>3741500</v>
@@ -15012,16 +15012,16 @@
         <v>45217</v>
       </c>
       <c r="B730" t="n">
-        <v>32.06568145751953</v>
+        <v>32.06567764282227</v>
       </c>
       <c r="C730" t="n">
-        <v>33.06773447151397</v>
+        <v>33.06773053760736</v>
       </c>
       <c r="D730" t="n">
-        <v>31.63342483773936</v>
+        <v>31.63342107446555</v>
       </c>
       <c r="E730" t="n">
-        <v>32.52741275989484</v>
+        <v>32.52740889026767</v>
       </c>
       <c r="F730" t="n">
         <v>7439800</v>
@@ -15132,16 +15132,16 @@
         <v>45225</v>
       </c>
       <c r="B736" t="n">
-        <v>31.98709106445312</v>
+        <v>31.98709297180176</v>
       </c>
       <c r="C736" t="n">
-        <v>32.12462709138111</v>
+        <v>32.12462900693085</v>
       </c>
       <c r="D736" t="n">
-        <v>31.19134209034388</v>
+        <v>31.19134395024304</v>
       </c>
       <c r="E736" t="n">
-        <v>31.57447923609348</v>
+        <v>31.57448111883861</v>
       </c>
       <c r="F736" t="n">
         <v>2923500</v>
@@ -15152,16 +15152,16 @@
         <v>45226</v>
       </c>
       <c r="B737" t="n">
-        <v>31.52535820007324</v>
+        <v>31.52536010742188</v>
       </c>
       <c r="C737" t="n">
-        <v>32.556882098507</v>
+        <v>32.55688406826494</v>
       </c>
       <c r="D737" t="n">
-        <v>31.24046001693592</v>
+        <v>31.24046190704763</v>
       </c>
       <c r="E737" t="n">
-        <v>32.32110713476096</v>
+        <v>32.32110909025403</v>
       </c>
       <c r="F737" t="n">
         <v>3378100</v>
@@ -15172,16 +15172,16 @@
         <v>45229</v>
       </c>
       <c r="B738" t="n">
-        <v>31.07345390319824</v>
+        <v>31.07345199584961</v>
       </c>
       <c r="C738" t="n">
-        <v>32.11480216169681</v>
+        <v>32.11480019042821</v>
       </c>
       <c r="D738" t="n">
-        <v>30.98503922096583</v>
+        <v>30.98503731904426</v>
       </c>
       <c r="E738" t="n">
-        <v>31.54500949323592</v>
+        <v>31.5450075569423</v>
       </c>
       <c r="F738" t="n">
         <v>3227500</v>
@@ -15192,16 +15192,16 @@
         <v>45230</v>
       </c>
       <c r="B739" t="n">
-        <v>31.86919784545898</v>
+        <v>31.86919975280762</v>
       </c>
       <c r="C739" t="n">
-        <v>32.10497655378492</v>
+        <v>32.10497847524474</v>
       </c>
       <c r="D739" t="n">
-        <v>31.20116441782789</v>
+        <v>31.2011662851952</v>
       </c>
       <c r="E739" t="n">
-        <v>31.20116441782789</v>
+        <v>31.2011662851952</v>
       </c>
       <c r="F739" t="n">
         <v>3372100</v>
@@ -15212,16 +15212,16 @@
         <v>45231</v>
       </c>
       <c r="B740" t="n">
-        <v>32.06568145751953</v>
+        <v>32.06567764282227</v>
       </c>
       <c r="C740" t="n">
-        <v>32.74354294357276</v>
+        <v>32.74353904823363</v>
       </c>
       <c r="D740" t="n">
-        <v>31.94779396986597</v>
+        <v>31.9477901691932</v>
       </c>
       <c r="E740" t="n">
-        <v>32.0755076009098</v>
+        <v>32.07550378504357</v>
       </c>
       <c r="F740" t="n">
         <v>4282500</v>
@@ -15232,16 +15232,16 @@
         <v>45233</v>
       </c>
       <c r="B741" t="n">
-        <v>32.69441604614258</v>
+        <v>32.69441986083984</v>
       </c>
       <c r="C741" t="n">
-        <v>32.94984327951414</v>
+        <v>32.94984712401398</v>
       </c>
       <c r="D741" t="n">
-        <v>32.4684634920525</v>
+        <v>32.46846728038622</v>
       </c>
       <c r="E741" t="n">
-        <v>32.7337131201344</v>
+        <v>32.73371693941674</v>
       </c>
       <c r="F741" t="n">
         <v>3190300</v>
@@ -15272,16 +15272,16 @@
         <v>45237</v>
       </c>
       <c r="B743" t="n">
-        <v>32.48811340332031</v>
+        <v>32.48811721801758</v>
       </c>
       <c r="C743" t="n">
-        <v>32.63547556323554</v>
+        <v>32.63547939523581</v>
       </c>
       <c r="D743" t="n">
-        <v>31.81025571237618</v>
+        <v>31.81025944748058</v>
       </c>
       <c r="E743" t="n">
-        <v>31.87902372098318</v>
+        <v>31.8790274641622</v>
       </c>
       <c r="F743" t="n">
         <v>3324000</v>
@@ -15312,16 +15312,16 @@
         <v>45239</v>
       </c>
       <c r="B745" t="n">
-        <v>30.81802940368652</v>
+        <v>30.81802749633789</v>
       </c>
       <c r="C745" t="n">
-        <v>33.77506711733456</v>
+        <v>33.77506502697286</v>
       </c>
       <c r="D745" t="n">
-        <v>30.67066723245724</v>
+        <v>30.67066533422895</v>
       </c>
       <c r="E745" t="n">
-        <v>33.41157476098916</v>
+        <v>33.41157269312426</v>
       </c>
       <c r="F745" t="n">
         <v>15431300</v>
@@ -15332,16 +15332,16 @@
         <v>45240</v>
       </c>
       <c r="B746" t="n">
-        <v>31.25028419494629</v>
+        <v>31.25028610229492</v>
       </c>
       <c r="C746" t="n">
-        <v>32.06567979171039</v>
+        <v>32.06568174882637</v>
       </c>
       <c r="D746" t="n">
-        <v>31.04398016537612</v>
+        <v>31.04398206013306</v>
       </c>
       <c r="E746" t="n">
-        <v>31.05380443446818</v>
+        <v>31.05380632982475</v>
       </c>
       <c r="F746" t="n">
         <v>4738300</v>
@@ -15352,16 +15352,16 @@
         <v>45243</v>
       </c>
       <c r="B747" t="n">
-        <v>30.94574165344238</v>
+        <v>30.94573974609375</v>
       </c>
       <c r="C747" t="n">
-        <v>31.41729536226194</v>
+        <v>31.41729342584897</v>
       </c>
       <c r="D747" t="n">
-        <v>30.67066771973704</v>
+        <v>30.67066582934266</v>
       </c>
       <c r="E747" t="n">
-        <v>31.21099131732383</v>
+        <v>31.21098939362647</v>
       </c>
       <c r="F747" t="n">
         <v>3172300</v>
@@ -15392,16 +15392,16 @@
         <v>45246</v>
       </c>
       <c r="B749" t="n">
-        <v>31.13239669799805</v>
+        <v>31.13239860534668</v>
       </c>
       <c r="C749" t="n">
-        <v>32.13444778565191</v>
+        <v>32.13444975439192</v>
       </c>
       <c r="D749" t="n">
-        <v>30.68048968892551</v>
+        <v>30.68049156858774</v>
       </c>
       <c r="E749" t="n">
-        <v>31.78078159366364</v>
+        <v>31.78078354073604</v>
       </c>
       <c r="F749" t="n">
         <v>5148500</v>
@@ -15492,16 +15492,16 @@
         <v>45253</v>
       </c>
       <c r="B754" t="n">
-        <v>31.81025886535645</v>
+        <v>31.81025505065918</v>
       </c>
       <c r="C754" t="n">
-        <v>32.00674051552654</v>
+        <v>32.00673667726713</v>
       </c>
       <c r="D754" t="n">
-        <v>31.58430627931235</v>
+        <v>31.5843024917114</v>
       </c>
       <c r="E754" t="n">
-        <v>31.82990740513103</v>
+        <v>31.82990358807751</v>
       </c>
       <c r="F754" t="n">
         <v>2086300</v>
@@ -15552,16 +15552,16 @@
         <v>45258</v>
       </c>
       <c r="B757" t="n">
-        <v>29.80615234375</v>
+        <v>29.80615043640137</v>
       </c>
       <c r="C757" t="n">
-        <v>30.21876230404811</v>
+        <v>30.21876037029583</v>
       </c>
       <c r="D757" t="n">
-        <v>29.63914350568201</v>
+        <v>29.63914160902057</v>
       </c>
       <c r="E757" t="n">
-        <v>30.17946522507312</v>
+        <v>30.17946329383553</v>
       </c>
       <c r="F757" t="n">
         <v>5777500</v>
@@ -15592,16 +15592,16 @@
         <v>45260</v>
       </c>
       <c r="B759" t="n">
-        <v>29.45248413085938</v>
+        <v>29.45248603820801</v>
       </c>
       <c r="C759" t="n">
-        <v>29.83562312973222</v>
+        <v>29.83562506189301</v>
       </c>
       <c r="D759" t="n">
-        <v>29.17741209183939</v>
+        <v>29.1774139813743</v>
       </c>
       <c r="E759" t="n">
-        <v>29.66861430298963</v>
+        <v>29.66861622433489</v>
       </c>
       <c r="F759" t="n">
         <v>4483800</v>
@@ -15732,16 +15732,16 @@
         <v>45271</v>
       </c>
       <c r="B766" t="n">
-        <v>26.91788291931152</v>
+        <v>26.91788101196289</v>
       </c>
       <c r="C766" t="n">
-        <v>27.08489175922624</v>
+        <v>27.08488984004369</v>
       </c>
       <c r="D766" t="n">
-        <v>26.48562441474616</v>
+        <v>26.48562253802652</v>
       </c>
       <c r="E766" t="n">
-        <v>26.96700426857343</v>
+        <v>26.96700235774415</v>
       </c>
       <c r="F766" t="n">
         <v>6627000</v>
@@ -15792,16 +15792,16 @@
         <v>45274</v>
       </c>
       <c r="B769" t="n">
-        <v>27.00629806518555</v>
+        <v>27.00629997253418</v>
       </c>
       <c r="C769" t="n">
-        <v>27.2027797044063</v>
+        <v>27.20278162563166</v>
       </c>
       <c r="D769" t="n">
-        <v>26.49544730224182</v>
+        <v>26.49544917351107</v>
       </c>
       <c r="E769" t="n">
-        <v>26.82946496464443</v>
+        <v>26.82946685950403</v>
       </c>
       <c r="F769" t="n">
         <v>14011300</v>
@@ -15812,16 +15812,16 @@
         <v>45275</v>
       </c>
       <c r="B770" t="n">
-        <v>25.88635635375977</v>
+        <v>25.8863582611084</v>
       </c>
       <c r="C770" t="n">
-        <v>27.21260267051552</v>
+        <v>27.21260467558413</v>
       </c>
       <c r="D770" t="n">
-        <v>25.88635635375977</v>
+        <v>25.8863582611084</v>
       </c>
       <c r="E770" t="n">
-        <v>27.1634813261689</v>
+        <v>27.16348332761816</v>
       </c>
       <c r="F770" t="n">
         <v>11924000</v>
@@ -15832,16 +15832,16 @@
         <v>45278</v>
       </c>
       <c r="B771" t="n">
-        <v>26.21055030822754</v>
+        <v>26.21055221557617</v>
       </c>
       <c r="C771" t="n">
-        <v>26.76069626050536</v>
+        <v>26.76069820788825</v>
       </c>
       <c r="D771" t="n">
-        <v>25.94530066428034</v>
+        <v>25.94530255232668</v>
       </c>
       <c r="E771" t="n">
-        <v>26.12213376024514</v>
+        <v>26.12213566115967</v>
       </c>
       <c r="F771" t="n">
         <v>4958200</v>
@@ -15852,16 +15852,16 @@
         <v>45279</v>
       </c>
       <c r="B772" t="n">
-        <v>26.32843971252441</v>
+        <v>26.32843780517578</v>
       </c>
       <c r="C772" t="n">
-        <v>26.52492136101001</v>
+        <v>26.52491943942738</v>
       </c>
       <c r="D772" t="n">
-        <v>26.13195993782669</v>
+        <v>26.13195804471192</v>
       </c>
       <c r="E772" t="n">
-        <v>26.30879304670615</v>
+        <v>26.30879114078081</v>
       </c>
       <c r="F772" t="n">
         <v>3900900</v>
@@ -15872,16 +15872,16 @@
         <v>45280</v>
       </c>
       <c r="B773" t="n">
-        <v>25.85688591003418</v>
+        <v>25.85688400268555</v>
       </c>
       <c r="C773" t="n">
-        <v>26.54456980342805</v>
+        <v>26.54456784535201</v>
       </c>
       <c r="D773" t="n">
-        <v>25.68987707156926</v>
+        <v>25.68987517654013</v>
       </c>
       <c r="E773" t="n">
-        <v>26.54456980342805</v>
+        <v>26.54456784535201</v>
       </c>
       <c r="F773" t="n">
         <v>6168300</v>
@@ -15912,16 +15912,16 @@
         <v>45282</v>
       </c>
       <c r="B775" t="n">
-        <v>25.95512580871582</v>
+        <v>25.95512771606445</v>
       </c>
       <c r="C775" t="n">
-        <v>26.2203754616087</v>
+        <v>26.22037738844958</v>
       </c>
       <c r="D775" t="n">
-        <v>25.79794124562103</v>
+        <v>25.79794314141873</v>
       </c>
       <c r="E775" t="n">
-        <v>26.03371809026321</v>
+        <v>26.03372000338731</v>
       </c>
       <c r="F775" t="n">
         <v>3644200</v>
@@ -16012,16 +16012,16 @@
         <v>45294</v>
       </c>
       <c r="B780" t="n">
-        <v>25.88635635375977</v>
+        <v>25.8863582611084</v>
       </c>
       <c r="C780" t="n">
-        <v>26.28914200846361</v>
+        <v>26.28914394549015</v>
       </c>
       <c r="D780" t="n">
-        <v>25.35585707754239</v>
+        <v>25.35585894580298</v>
       </c>
       <c r="E780" t="n">
-        <v>25.64075525338972</v>
+        <v>25.64075714264207</v>
       </c>
       <c r="F780" t="n">
         <v>5734800</v>
@@ -16052,16 +16052,16 @@
         <v>45296</v>
       </c>
       <c r="B782" t="n">
-        <v>25.68987464904785</v>
+        <v>25.68987655639648</v>
       </c>
       <c r="C782" t="n">
-        <v>25.97477282406455</v>
+        <v>25.97477475256549</v>
       </c>
       <c r="D782" t="n">
-        <v>25.21832098742127</v>
+        <v>25.21832285975933</v>
       </c>
       <c r="E782" t="n">
-        <v>25.36568127245611</v>
+        <v>25.36568315573496</v>
       </c>
       <c r="F782" t="n">
         <v>3417300</v>
@@ -16092,16 +16092,16 @@
         <v>45300</v>
       </c>
       <c r="B784" t="n">
-        <v>28.01817512512207</v>
+        <v>28.0181770324707</v>
       </c>
       <c r="C784" t="n">
-        <v>28.24412769698892</v>
+        <v>28.24412961971936</v>
       </c>
       <c r="D784" t="n">
-        <v>26.79999384234995</v>
+        <v>26.7999956667704</v>
       </c>
       <c r="E784" t="n">
-        <v>27.01612214494592</v>
+        <v>27.01612398407939</v>
       </c>
       <c r="F784" t="n">
         <v>10290300</v>
@@ -16152,16 +16152,16 @@
         <v>45303</v>
       </c>
       <c r="B787" t="n">
-        <v>28.20483207702637</v>
+        <v>28.20483016967773</v>
       </c>
       <c r="C787" t="n">
-        <v>28.86304316187749</v>
+        <v>28.86304121001741</v>
       </c>
       <c r="D787" t="n">
-        <v>27.82169492460737</v>
+        <v>27.82169304316834</v>
       </c>
       <c r="E787" t="n">
-        <v>28.63709057833746</v>
+        <v>28.63708864175739</v>
       </c>
       <c r="F787" t="n">
         <v>5067700</v>
@@ -16172,16 +16172,16 @@
         <v>45306</v>
       </c>
       <c r="B788" t="n">
-        <v>28.52902793884277</v>
+        <v>28.52902603149414</v>
       </c>
       <c r="C788" t="n">
-        <v>28.68621251092004</v>
+        <v>28.68621059306261</v>
       </c>
       <c r="D788" t="n">
-        <v>27.9002877767458</v>
+        <v>27.90028591143248</v>
       </c>
       <c r="E788" t="n">
-        <v>28.06729661880138</v>
+        <v>28.06729474232245</v>
       </c>
       <c r="F788" t="n">
         <v>3859400</v>
@@ -16252,16 +16252,16 @@
         <v>45310</v>
       </c>
       <c r="B792" t="n">
-        <v>29.03005027770996</v>
+        <v>29.03005218505859</v>
       </c>
       <c r="C792" t="n">
-        <v>29.197059106456</v>
+        <v>29.19706102477754</v>
       </c>
       <c r="D792" t="n">
-        <v>28.0574701128199</v>
+        <v>28.05747195626752</v>
       </c>
       <c r="E792" t="n">
-        <v>28.73532969699943</v>
+        <v>28.73533158498416</v>
       </c>
       <c r="F792" t="n">
         <v>7851200</v>
@@ -16312,16 +16312,16 @@
         <v>45315</v>
       </c>
       <c r="B795" t="n">
-        <v>27.86099243164062</v>
+        <v>27.86099052429199</v>
       </c>
       <c r="C795" t="n">
-        <v>28.52902779653059</v>
+        <v>28.52902584344861</v>
       </c>
       <c r="D795" t="n">
-        <v>27.63503797084227</v>
+        <v>27.63503607896236</v>
       </c>
       <c r="E795" t="n">
-        <v>28.04764793893384</v>
+        <v>28.04764601880687</v>
       </c>
       <c r="F795" t="n">
         <v>4070600</v>
@@ -16352,16 +16352,16 @@
         <v>45317</v>
       </c>
       <c r="B797" t="n">
-        <v>28.24412727355957</v>
+        <v>28.2441291809082</v>
       </c>
       <c r="C797" t="n">
-        <v>28.24412727355957</v>
+        <v>28.2441291809082</v>
       </c>
       <c r="D797" t="n">
-        <v>27.50732395337975</v>
+        <v>27.50732581097147</v>
       </c>
       <c r="E797" t="n">
-        <v>27.65468424265817</v>
+        <v>27.65468611020124</v>
       </c>
       <c r="F797" t="n">
         <v>2761100</v>
@@ -16392,16 +16392,16 @@
         <v>45321</v>
       </c>
       <c r="B799" t="n">
-        <v>27.2420768737793</v>
+        <v>27.24207496643066</v>
       </c>
       <c r="C799" t="n">
-        <v>27.54662362392648</v>
+        <v>27.54662169525507</v>
       </c>
       <c r="D799" t="n">
-        <v>26.97682720382707</v>
+        <v>26.97682531504984</v>
       </c>
       <c r="E799" t="n">
-        <v>27.369790510625</v>
+        <v>27.36978859433452</v>
       </c>
       <c r="F799" t="n">
         <v>2184900</v>
@@ -16432,16 +16432,16 @@
         <v>45323</v>
       </c>
       <c r="B801" t="n">
-        <v>26.24002265930176</v>
+        <v>26.24002075195312</v>
       </c>
       <c r="C801" t="n">
-        <v>27.40908451061442</v>
+        <v>27.4090825182884</v>
       </c>
       <c r="D801" t="n">
-        <v>26.10248663224892</v>
+        <v>26.10248473489757</v>
       </c>
       <c r="E801" t="n">
-        <v>27.31084368823903</v>
+        <v>27.31084170305399</v>
       </c>
       <c r="F801" t="n">
         <v>7611700</v>
@@ -16532,16 +16532,16 @@
         <v>45330</v>
       </c>
       <c r="B806" t="n">
-        <v>28.79427528381348</v>
+        <v>28.79427337646484</v>
       </c>
       <c r="C806" t="n">
-        <v>28.81392382346353</v>
+        <v>28.81392191481336</v>
       </c>
       <c r="D806" t="n">
-        <v>27.39926082305394</v>
+        <v>27.39925900811183</v>
       </c>
       <c r="E806" t="n">
-        <v>28.71568299900116</v>
+        <v>28.71568109685852</v>
       </c>
       <c r="F806" t="n">
         <v>6908300</v>
@@ -16552,16 +16552,16 @@
         <v>45331</v>
       </c>
       <c r="B807" t="n">
-        <v>27.6939811706543</v>
+        <v>27.69398307800293</v>
       </c>
       <c r="C807" t="n">
-        <v>28.9121624286317</v>
+        <v>28.9121644198793</v>
       </c>
       <c r="D807" t="n">
-        <v>27.52697234402422</v>
+        <v>27.52697423987057</v>
       </c>
       <c r="E807" t="n">
-        <v>28.83357014985212</v>
+        <v>28.83357213568689</v>
       </c>
       <c r="F807" t="n">
         <v>5513900</v>
@@ -16592,16 +16592,16 @@
         <v>45337</v>
       </c>
       <c r="B809" t="n">
-        <v>28.00835227966309</v>
+        <v>28.00835037231445</v>
       </c>
       <c r="C809" t="n">
-        <v>28.26377767232718</v>
+        <v>28.26377574758426</v>
       </c>
       <c r="D809" t="n">
-        <v>27.28137318075199</v>
+        <v>27.28137132291011</v>
       </c>
       <c r="E809" t="n">
-        <v>27.40908494019011</v>
+        <v>27.40908307365115</v>
       </c>
       <c r="F809" t="n">
         <v>2788300</v>
@@ -16632,16 +16632,16 @@
         <v>45341</v>
       </c>
       <c r="B811" t="n">
-        <v>28.67638778686523</v>
+        <v>28.6763858795166</v>
       </c>
       <c r="C811" t="n">
-        <v>28.76480434148215</v>
+        <v>28.76480242825268</v>
       </c>
       <c r="D811" t="n">
-        <v>28.23430501378064</v>
+        <v>28.2343031358362</v>
       </c>
       <c r="E811" t="n">
-        <v>28.74515580183664</v>
+        <v>28.74515388991405</v>
       </c>
       <c r="F811" t="n">
         <v>1698200</v>
@@ -16672,16 +16672,16 @@
         <v>45343</v>
       </c>
       <c r="B813" t="n">
-        <v>28.92198944091797</v>
+        <v>28.92198753356934</v>
       </c>
       <c r="C813" t="n">
-        <v>28.98093318714647</v>
+        <v>28.98093127591061</v>
       </c>
       <c r="D813" t="n">
-        <v>28.36201916727748</v>
+        <v>28.36201729685779</v>
       </c>
       <c r="E813" t="n">
-        <v>28.6370912322024</v>
+        <v>28.63708934364225</v>
       </c>
       <c r="F813" t="n">
         <v>2751400</v>
@@ -16792,16 +16792,16 @@
         <v>45351</v>
       </c>
       <c r="B819" t="n">
-        <v>27.45820617675781</v>
+        <v>27.45820426940918</v>
       </c>
       <c r="C819" t="n">
-        <v>28.14588819377561</v>
+        <v>28.14588623865804</v>
       </c>
       <c r="D819" t="n">
-        <v>27.45820617675781</v>
+        <v>27.45820426940918</v>
       </c>
       <c r="E819" t="n">
-        <v>27.98870362566938</v>
+        <v>27.98870168147043</v>
       </c>
       <c r="F819" t="n">
         <v>2784300</v>
@@ -16972,16 +16972,16 @@
         <v>45364</v>
       </c>
       <c r="B828" t="n">
-        <v>29.13811683654785</v>
+        <v>29.13811492919922</v>
       </c>
       <c r="C828" t="n">
-        <v>29.36406941808906</v>
+        <v>29.36406749594983</v>
       </c>
       <c r="D828" t="n">
-        <v>28.98093226905937</v>
+        <v>28.98093037199986</v>
       </c>
       <c r="E828" t="n">
-        <v>28.98093226905937</v>
+        <v>28.98093037199986</v>
       </c>
       <c r="F828" t="n">
         <v>2596400</v>
@@ -17032,16 +17032,16 @@
         <v>45369</v>
       </c>
       <c r="B831" t="n">
-        <v>28.98093032836914</v>
+        <v>28.98093223571777</v>
       </c>
       <c r="C831" t="n">
-        <v>29.28547517326093</v>
+        <v>29.28547710065286</v>
       </c>
       <c r="D831" t="n">
-        <v>28.61743986927554</v>
+        <v>28.61744175270144</v>
       </c>
       <c r="E831" t="n">
-        <v>28.77462630002598</v>
+        <v>28.77462819379693</v>
       </c>
       <c r="F831" t="n">
         <v>4710300</v>
@@ -17112,16 +17112,16 @@
         <v>45373</v>
       </c>
       <c r="B835" t="n">
-        <v>29.71773338317871</v>
+        <v>29.71773529052734</v>
       </c>
       <c r="C835" t="n">
-        <v>30.00263156131158</v>
+        <v>30.0026334869456</v>
       </c>
       <c r="D835" t="n">
-        <v>29.28547491839919</v>
+        <v>29.28547679800454</v>
       </c>
       <c r="E835" t="n">
-        <v>29.88474220772164</v>
+        <v>29.88474412578926</v>
       </c>
       <c r="F835" t="n">
         <v>3854000</v>
@@ -17152,16 +17152,16 @@
         <v>45377</v>
       </c>
       <c r="B837" t="n">
-        <v>30.81802940368652</v>
+        <v>30.81802749633789</v>
       </c>
       <c r="C837" t="n">
-        <v>31.22081509112746</v>
+        <v>31.22081315885015</v>
       </c>
       <c r="D837" t="n">
-        <v>30.51348266534799</v>
+        <v>30.51348077684796</v>
       </c>
       <c r="E837" t="n">
-        <v>30.61172348823823</v>
+        <v>30.61172159365801</v>
       </c>
       <c r="F837" t="n">
         <v>3327200</v>
@@ -17172,16 +17172,16 @@
         <v>45378</v>
       </c>
       <c r="B838" t="n">
-        <v>31.48606300354004</v>
+        <v>31.48606109619141</v>
       </c>
       <c r="C838" t="n">
-        <v>31.91832337550937</v>
+        <v>31.91832144197546</v>
       </c>
       <c r="D838" t="n">
-        <v>30.38577102935353</v>
+        <v>30.3857691886579</v>
       </c>
       <c r="E838" t="n">
-        <v>30.6510206900868</v>
+        <v>30.65101883332299</v>
       </c>
       <c r="F838" t="n">
         <v>9071000</v>
@@ -17372,16 +17372,16 @@
         <v>45393</v>
       </c>
       <c r="B848" t="n">
-        <v>35.62198257446289</v>
+        <v>35.62198638916016</v>
       </c>
       <c r="C848" t="n">
-        <v>35.91670689814429</v>
+        <v>35.91671074440308</v>
       </c>
       <c r="D848" t="n">
-        <v>34.59045868430435</v>
+        <v>34.59046238853748</v>
       </c>
       <c r="E848" t="n">
-        <v>34.74764324139922</v>
+        <v>34.74764696246498</v>
       </c>
       <c r="F848" t="n">
         <v>5960900</v>
@@ -17412,16 +17412,16 @@
         <v>45397</v>
       </c>
       <c r="B850" t="n">
-        <v>34.06978988647461</v>
+        <v>34.06978607177734</v>
       </c>
       <c r="C850" t="n">
-        <v>34.52169507730631</v>
+        <v>34.52169121201051</v>
       </c>
       <c r="D850" t="n">
-        <v>33.83401114697602</v>
+        <v>33.83400735867823</v>
       </c>
       <c r="E850" t="n">
-        <v>34.43327851844133</v>
+        <v>34.43327466304528</v>
       </c>
       <c r="F850" t="n">
         <v>4151100</v>
@@ -17472,16 +17472,16 @@
         <v>45400</v>
       </c>
       <c r="B853" t="n">
-        <v>32.33092880249023</v>
+        <v>32.3309326171875</v>
       </c>
       <c r="C853" t="n">
-        <v>33.28386227408815</v>
+        <v>33.28386620122118</v>
       </c>
       <c r="D853" t="n">
-        <v>31.93796554165645</v>
+        <v>31.93796930998834</v>
       </c>
       <c r="E853" t="n">
-        <v>33.00878649247434</v>
+        <v>33.00879038715143</v>
       </c>
       <c r="F853" t="n">
         <v>4478700</v>
@@ -17632,16 +17632,16 @@
         <v>45412</v>
       </c>
       <c r="B861" t="n">
-        <v>32.58635330200195</v>
+        <v>32.58635711669922</v>
       </c>
       <c r="C861" t="n">
-        <v>33.66700042877825</v>
+        <v>33.66700436998067</v>
       </c>
       <c r="D861" t="n">
-        <v>32.43899488533395</v>
+        <v>32.43899868278081</v>
       </c>
       <c r="E861" t="n">
-        <v>33.60805481356574</v>
+        <v>33.60805874786774</v>
       </c>
       <c r="F861" t="n">
         <v>6661700</v>
@@ -29752,19 +29752,39 @@
         <v>46297</v>
       </c>
       <c r="B1467" t="n">
-        <v>18.9</v>
+        <v>18.89999961853027</v>
       </c>
       <c r="C1467" t="n">
-        <v>19</v>
+        <v>18.98999977111816</v>
       </c>
       <c r="D1467" t="n">
-        <v>18.05</v>
+        <v>18.04999923706055</v>
       </c>
       <c r="E1467" t="n">
-        <v>18.05</v>
+        <v>18.04999923706055</v>
       </c>
       <c r="F1467" t="n">
         <v>3277100</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1468" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="C1468" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="D1468" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="E1468" t="n">
+        <v>19</v>
+      </c>
+      <c r="F1468" t="n">
+        <v>5137500</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1468"/>
+  <dimension ref="A1:F1469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29772,19 +29772,39 @@
         <v>46300</v>
       </c>
       <c r="B1468" t="n">
-        <v>19.1</v>
+        <v>19.10000038146973</v>
       </c>
       <c r="C1468" t="n">
-        <v>19.8</v>
+        <v>19.79999923706055</v>
       </c>
       <c r="D1468" t="n">
-        <v>18.86</v>
+        <v>18.86000061035156</v>
       </c>
       <c r="E1468" t="n">
         <v>19</v>
       </c>
       <c r="F1468" t="n">
         <v>5137500</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1469" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="C1469" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="D1469" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E1469" t="n">
+        <v>19</v>
+      </c>
+      <c r="F1469" t="n">
+        <v>4257200</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1469"/>
+  <dimension ref="A1:F1470"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,16 +512,16 @@
         <v>44152</v>
       </c>
       <c r="B5" t="n">
-        <v>20.17695426940918</v>
+        <v>20.17695617675781</v>
       </c>
       <c r="C5" t="n">
-        <v>20.17695426940918</v>
+        <v>20.17695617675781</v>
       </c>
       <c r="D5" t="n">
-        <v>19.85012445790661</v>
+        <v>19.85012633435968</v>
       </c>
       <c r="E5" t="n">
-        <v>20.12888973916155</v>
+        <v>20.12889164196659</v>
       </c>
       <c r="F5" t="n">
         <v>262242</v>
@@ -572,16 +572,16 @@
         <v>44158</v>
       </c>
       <c r="B8" t="n">
-        <v>20.20579147338867</v>
+        <v>20.2057933807373</v>
       </c>
       <c r="C8" t="n">
-        <v>20.52300874747816</v>
+        <v>20.52301068477087</v>
       </c>
       <c r="D8" t="n">
-        <v>20.14811628674976</v>
+        <v>20.14811818865408</v>
       </c>
       <c r="E8" t="n">
-        <v>20.14811628674976</v>
+        <v>20.14811818865408</v>
       </c>
       <c r="F8" t="n">
         <v>79408</v>
@@ -632,16 +632,16 @@
         <v>44161</v>
       </c>
       <c r="B11" t="n">
-        <v>22.87810897827148</v>
+        <v>22.87811088562012</v>
       </c>
       <c r="C11" t="n">
-        <v>22.87810897827148</v>
+        <v>22.87811088562012</v>
       </c>
       <c r="D11" t="n">
-        <v>22.31096214463751</v>
+        <v>22.3109640047031</v>
       </c>
       <c r="E11" t="n">
-        <v>22.31096214463751</v>
+        <v>22.3109640047031</v>
       </c>
       <c r="F11" t="n">
         <v>72970</v>
@@ -652,16 +652,16 @@
         <v>44162</v>
       </c>
       <c r="B12" t="n">
-        <v>23.07036399841309</v>
+        <v>23.07036209106445</v>
       </c>
       <c r="C12" t="n">
-        <v>23.55099623037812</v>
+        <v>23.55099428329309</v>
       </c>
       <c r="D12" t="n">
-        <v>22.10909953448302</v>
+        <v>22.10909770660719</v>
       </c>
       <c r="E12" t="n">
-        <v>23.07036399841309</v>
+        <v>23.07036209106445</v>
       </c>
       <c r="F12" t="n">
         <v>72050</v>
@@ -692,16 +692,16 @@
         <v>44166</v>
       </c>
       <c r="B14" t="n">
-        <v>23.07036399841309</v>
+        <v>23.07036209106445</v>
       </c>
       <c r="C14" t="n">
-        <v>23.16649119432127</v>
+        <v>23.1664892790253</v>
       </c>
       <c r="D14" t="n">
-        <v>23.03191386956499</v>
+        <v>23.03191196539523</v>
       </c>
       <c r="E14" t="n">
-        <v>23.12803919168523</v>
+        <v>23.12803727956828</v>
       </c>
       <c r="F14" t="n">
         <v>93512</v>
@@ -792,16 +792,16 @@
         <v>44173</v>
       </c>
       <c r="B19" t="n">
-        <v>26.33866310119629</v>
+        <v>26.33866500854492</v>
       </c>
       <c r="C19" t="n">
-        <v>26.57898012603766</v>
+        <v>26.57898205078916</v>
       </c>
       <c r="D19" t="n">
-        <v>25.56965124500673</v>
+        <v>25.56965309666637</v>
       </c>
       <c r="E19" t="n">
-        <v>25.56965124500673</v>
+        <v>25.56965309666637</v>
       </c>
       <c r="F19" t="n">
         <v>126420</v>
@@ -812,16 +812,16 @@
         <v>44174</v>
       </c>
       <c r="B20" t="n">
-        <v>26.83852195739746</v>
+        <v>26.83852005004883</v>
       </c>
       <c r="C20" t="n">
-        <v>27.77095064592048</v>
+        <v>27.77094867230641</v>
       </c>
       <c r="D20" t="n">
-        <v>26.27137696749292</v>
+        <v>26.27137510044991</v>
       </c>
       <c r="E20" t="n">
-        <v>26.49246706969505</v>
+        <v>26.4924651869397</v>
       </c>
       <c r="F20" t="n">
         <v>212880</v>
@@ -892,16 +892,16 @@
         <v>44180</v>
       </c>
       <c r="B24" t="n">
-        <v>33.00984573364258</v>
+        <v>33.00984191894531</v>
       </c>
       <c r="C24" t="n">
-        <v>33.98072266755544</v>
+        <v>33.9807187406613</v>
       </c>
       <c r="D24" t="n">
-        <v>30.76048335959674</v>
+        <v>30.7604798048412</v>
       </c>
       <c r="E24" t="n">
-        <v>30.76048335959674</v>
+        <v>30.7604798048412</v>
       </c>
       <c r="F24" t="n">
         <v>887803</v>
@@ -912,16 +912,16 @@
         <v>44181</v>
       </c>
       <c r="B25" t="n">
-        <v>32.68301391601562</v>
+        <v>32.68301773071289</v>
       </c>
       <c r="C25" t="n">
-        <v>34.45173835953219</v>
+        <v>34.4517423806715</v>
       </c>
       <c r="D25" t="n">
-        <v>32.10625456033017</v>
+        <v>32.10625830770921</v>
       </c>
       <c r="E25" t="n">
-        <v>33.62505319761509</v>
+        <v>33.62505712226533</v>
       </c>
       <c r="F25" t="n">
         <v>376808</v>
@@ -932,16 +932,16 @@
         <v>44182</v>
       </c>
       <c r="B26" t="n">
-        <v>32.10625839233398</v>
+        <v>32.10625457763672</v>
       </c>
       <c r="C26" t="n">
-        <v>33.64428227520571</v>
+        <v>33.64427827776851</v>
       </c>
       <c r="D26" t="n">
-        <v>31.64484935368452</v>
+        <v>31.64484559380946</v>
       </c>
       <c r="E26" t="n">
-        <v>33.6250572108933</v>
+        <v>33.62505321574033</v>
       </c>
       <c r="F26" t="n">
         <v>258257</v>
@@ -972,16 +972,16 @@
         <v>44186</v>
       </c>
       <c r="B28" t="n">
-        <v>32.18315887451172</v>
+        <v>32.18315505981445</v>
       </c>
       <c r="C28" t="n">
-        <v>33.33667773162143</v>
+        <v>33.33667378019659</v>
       </c>
       <c r="D28" t="n">
-        <v>29.12633427792858</v>
+        <v>29.12633082555934</v>
       </c>
       <c r="E28" t="n">
-        <v>31.86594156356414</v>
+        <v>31.86593778646691</v>
       </c>
       <c r="F28" t="n">
         <v>236079</v>
@@ -992,16 +992,16 @@
         <v>44187</v>
       </c>
       <c r="B29" t="n">
-        <v>33.16364288330078</v>
+        <v>33.16364669799805</v>
       </c>
       <c r="C29" t="n">
-        <v>33.47124761081827</v>
+        <v>33.47125146089823</v>
       </c>
       <c r="D29" t="n">
-        <v>32.59649608138177</v>
+        <v>32.59649983084212</v>
       </c>
       <c r="E29" t="n">
-        <v>33.21170553641675</v>
+        <v>33.21170935664249</v>
       </c>
       <c r="F29" t="n">
         <v>167504</v>
@@ -1032,16 +1032,16 @@
         <v>44193</v>
       </c>
       <c r="B31" t="n">
-        <v>36.21085739135742</v>
+        <v>36.21085357666016</v>
       </c>
       <c r="C31" t="n">
-        <v>36.66265388599569</v>
+        <v>36.66265002370312</v>
       </c>
       <c r="D31" t="n">
-        <v>35.56681025863972</v>
+        <v>35.56680651179074</v>
       </c>
       <c r="E31" t="n">
-        <v>35.56681025863972</v>
+        <v>35.56680651179074</v>
       </c>
       <c r="F31" t="n">
         <v>451822</v>
@@ -1052,16 +1052,16 @@
         <v>44194</v>
       </c>
       <c r="B32" t="n">
-        <v>36.09550476074219</v>
+        <v>36.09550857543945</v>
       </c>
       <c r="C32" t="n">
-        <v>37.06638166531152</v>
+        <v>37.06638558261441</v>
       </c>
       <c r="D32" t="n">
-        <v>35.95131304358604</v>
+        <v>35.95131684304462</v>
       </c>
       <c r="E32" t="n">
-        <v>36.52807241705953</v>
+        <v>36.52807627747203</v>
       </c>
       <c r="F32" t="n">
         <v>337154</v>
@@ -1092,16 +1092,16 @@
         <v>44200</v>
       </c>
       <c r="B34" t="n">
-        <v>34.99966049194336</v>
+        <v>34.99966430664062</v>
       </c>
       <c r="C34" t="n">
-        <v>36.62420073506411</v>
+        <v>36.62420472682393</v>
       </c>
       <c r="D34" t="n">
-        <v>34.98043542972244</v>
+        <v>34.98043924232432</v>
       </c>
       <c r="E34" t="n">
-        <v>36.52807167638402</v>
+        <v>36.52807565766651</v>
       </c>
       <c r="F34" t="n">
         <v>331840</v>
@@ -1112,16 +1112,16 @@
         <v>44201</v>
       </c>
       <c r="B35" t="n">
-        <v>36.13395690917969</v>
+        <v>36.13395309448242</v>
       </c>
       <c r="C35" t="n">
-        <v>36.32621129362743</v>
+        <v>36.32620745863368</v>
       </c>
       <c r="D35" t="n">
-        <v>34.60554560816865</v>
+        <v>34.60554195482727</v>
       </c>
       <c r="E35" t="n">
-        <v>35.45145965313264</v>
+        <v>35.45145591048728</v>
       </c>
       <c r="F35" t="n">
         <v>328059</v>
@@ -1172,16 +1172,16 @@
         <v>44204</v>
       </c>
       <c r="B38" t="n">
-        <v>34.13452529907227</v>
+        <v>34.134521484375</v>
       </c>
       <c r="C38" t="n">
-        <v>35.75906572541368</v>
+        <v>35.75906172916622</v>
       </c>
       <c r="D38" t="n">
-        <v>34.13452529907227</v>
+        <v>34.134521484375</v>
       </c>
       <c r="E38" t="n">
-        <v>35.16308123419719</v>
+        <v>35.16307730455386</v>
       </c>
       <c r="F38" t="n">
         <v>367201</v>
@@ -1272,16 +1272,16 @@
         <v>44211</v>
       </c>
       <c r="B43" t="n">
-        <v>33.94226837158203</v>
+        <v>33.9422721862793</v>
       </c>
       <c r="C43" t="n">
-        <v>35.04772061203977</v>
+        <v>35.0477245509764</v>
       </c>
       <c r="D43" t="n">
-        <v>33.16364216523639</v>
+        <v>33.16364589242556</v>
       </c>
       <c r="E43" t="n">
-        <v>34.60554046537172</v>
+        <v>34.60554435461268</v>
       </c>
       <c r="F43" t="n">
         <v>319883</v>
@@ -1292,16 +1292,16 @@
         <v>44214</v>
       </c>
       <c r="B44" t="n">
-        <v>34.04801177978516</v>
+        <v>34.04800796508789</v>
       </c>
       <c r="C44" t="n">
-        <v>34.5094208103909</v>
+        <v>34.50941694399793</v>
       </c>
       <c r="D44" t="n">
-        <v>33.27900172554335</v>
+        <v>33.27899799700501</v>
       </c>
       <c r="E44" t="n">
-        <v>34.11529950370554</v>
+        <v>34.11529568146945</v>
       </c>
       <c r="F44" t="n">
         <v>117631</v>
@@ -1332,16 +1332,16 @@
         <v>44216</v>
       </c>
       <c r="B46" t="n">
-        <v>34.12490844726562</v>
+        <v>34.12491226196289</v>
       </c>
       <c r="C46" t="n">
-        <v>35.28803968588292</v>
+        <v>35.28804363060232</v>
       </c>
       <c r="D46" t="n">
-        <v>33.66350321275509</v>
+        <v>33.66350697587357</v>
       </c>
       <c r="E46" t="n">
-        <v>34.60554249130722</v>
+        <v>34.60554635973278</v>
       </c>
       <c r="F46" t="n">
         <v>359332</v>
@@ -1372,16 +1372,16 @@
         <v>44218</v>
       </c>
       <c r="B48" t="n">
-        <v>32.95216369628906</v>
+        <v>32.95216751098633</v>
       </c>
       <c r="C48" t="n">
-        <v>33.45202278739948</v>
+        <v>33.45202665996278</v>
       </c>
       <c r="D48" t="n">
-        <v>32.53882112897777</v>
+        <v>32.53882489582456</v>
       </c>
       <c r="E48" t="n">
-        <v>33.19248071115274</v>
+        <v>33.19248455367023</v>
       </c>
       <c r="F48" t="n">
         <v>220341</v>
@@ -1472,16 +1472,16 @@
         <v>44228</v>
       </c>
       <c r="B53" t="n">
-        <v>31.7794246673584</v>
+        <v>31.77942657470703</v>
       </c>
       <c r="C53" t="n">
-        <v>33.1155814640686</v>
+        <v>33.11558345161116</v>
       </c>
       <c r="D53" t="n">
-        <v>31.66407054800669</v>
+        <v>31.66407244843196</v>
       </c>
       <c r="E53" t="n">
-        <v>32.68301382233215</v>
+        <v>32.68301578391271</v>
       </c>
       <c r="F53" t="n">
         <v>610435</v>
@@ -1492,16 +1492,16 @@
         <v>44229</v>
       </c>
       <c r="B54" t="n">
-        <v>32.63494873046875</v>
+        <v>32.63495254516602</v>
       </c>
       <c r="C54" t="n">
-        <v>33.65389204571495</v>
+        <v>33.65389597951643</v>
       </c>
       <c r="D54" t="n">
-        <v>31.97167657096734</v>
+        <v>31.97168030813476</v>
       </c>
       <c r="E54" t="n">
-        <v>33.64427951434755</v>
+        <v>33.64428344702543</v>
       </c>
       <c r="F54" t="n">
         <v>582228</v>
@@ -1532,16 +1532,16 @@
         <v>44231</v>
       </c>
       <c r="B56" t="n">
-        <v>32.68301391601562</v>
+        <v>32.68301773071289</v>
       </c>
       <c r="C56" t="n">
-        <v>34.11529602664492</v>
+        <v>34.11530000851534</v>
       </c>
       <c r="D56" t="n">
-        <v>32.44269689321744</v>
+        <v>32.44270067986538</v>
       </c>
       <c r="E56" t="n">
-        <v>33.06751890394745</v>
+        <v>33.06752276352339</v>
       </c>
       <c r="F56" t="n">
         <v>466743</v>
@@ -1612,16 +1612,16 @@
         <v>44237</v>
       </c>
       <c r="B60" t="n">
-        <v>34.83624649047852</v>
+        <v>34.83625030517578</v>
       </c>
       <c r="C60" t="n">
-        <v>35.33610184184258</v>
+        <v>35.33610571127585</v>
       </c>
       <c r="D60" t="n">
-        <v>34.23064955227608</v>
+        <v>34.23065330065825</v>
       </c>
       <c r="E60" t="n">
-        <v>34.43251269995998</v>
+        <v>34.43251647044691</v>
       </c>
       <c r="F60" t="n">
         <v>186206</v>
@@ -1652,16 +1652,16 @@
         <v>44239</v>
       </c>
       <c r="B62" t="n">
-        <v>34.40367889404297</v>
+        <v>34.4036750793457</v>
       </c>
       <c r="C62" t="n">
-        <v>34.52864555631986</v>
+        <v>34.52864172776623</v>
       </c>
       <c r="D62" t="n">
-        <v>32.673400666573</v>
+        <v>32.67339704372985</v>
       </c>
       <c r="E62" t="n">
-        <v>33.67311897448496</v>
+        <v>33.67311524079254</v>
       </c>
       <c r="F62" t="n">
         <v>218195</v>
@@ -1692,16 +1692,16 @@
         <v>44245</v>
       </c>
       <c r="B64" t="n">
-        <v>37.00870895385742</v>
+        <v>37.00870513916016</v>
       </c>
       <c r="C64" t="n">
-        <v>37.38360144742785</v>
+        <v>37.38359759408829</v>
       </c>
       <c r="D64" t="n">
-        <v>35.71100215049589</v>
+        <v>35.71099846956061</v>
       </c>
       <c r="E64" t="n">
-        <v>36.37427435009953</v>
+        <v>36.37427060079703</v>
       </c>
       <c r="F64" t="n">
         <v>661534</v>
@@ -1812,16 +1812,16 @@
         <v>44253</v>
       </c>
       <c r="B70" t="n">
-        <v>34.57670593261719</v>
+        <v>34.57670974731445</v>
       </c>
       <c r="C70" t="n">
-        <v>37.21057322750037</v>
+        <v>37.21057733278074</v>
       </c>
       <c r="D70" t="n">
-        <v>33.75001700107128</v>
+        <v>33.75002072456356</v>
       </c>
       <c r="E70" t="n">
-        <v>36.5376847961999</v>
+        <v>36.53768882724342</v>
       </c>
       <c r="F70" t="n">
         <v>410022</v>
@@ -1932,16 +1932,16 @@
         <v>44263</v>
       </c>
       <c r="B76" t="n">
-        <v>41.91115951538086</v>
+        <v>41.91115570068359</v>
       </c>
       <c r="C76" t="n">
-        <v>44.60270214463106</v>
+        <v>44.60269808495321</v>
       </c>
       <c r="D76" t="n">
-        <v>40.70957805138659</v>
+        <v>40.70957434605565</v>
       </c>
       <c r="E76" t="n">
-        <v>43.55492493684502</v>
+        <v>43.55492097253444</v>
       </c>
       <c r="F76" t="n">
         <v>1012691</v>
@@ -1952,16 +1952,16 @@
         <v>44264</v>
       </c>
       <c r="B77" t="n">
-        <v>43.50686264038086</v>
+        <v>43.50685882568359</v>
       </c>
       <c r="C77" t="n">
-        <v>43.50686264038086</v>
+        <v>43.50685882568359</v>
       </c>
       <c r="D77" t="n">
-        <v>39.89250193891922</v>
+        <v>39.89249844113039</v>
       </c>
       <c r="E77" t="n">
-        <v>42.29566488693005</v>
+        <v>42.29566117843103</v>
       </c>
       <c r="F77" t="n">
         <v>563525</v>
@@ -1972,16 +1972,16 @@
         <v>44265</v>
       </c>
       <c r="B78" t="n">
-        <v>44.69882583618164</v>
+        <v>44.69882965087891</v>
       </c>
       <c r="C78" t="n">
-        <v>44.89108021255291</v>
+        <v>44.89108404365759</v>
       </c>
       <c r="D78" t="n">
-        <v>43.38189403862891</v>
+        <v>43.38189774093629</v>
       </c>
       <c r="E78" t="n">
-        <v>43.83369051144994</v>
+        <v>43.83369425231464</v>
       </c>
       <c r="F78" t="n">
         <v>425454</v>
@@ -2012,16 +2012,16 @@
         <v>44267</v>
       </c>
       <c r="B80" t="n">
-        <v>45.66009521484375</v>
+        <v>45.66009140014648</v>
       </c>
       <c r="C80" t="n">
-        <v>49.01491000208902</v>
+        <v>49.01490590711195</v>
       </c>
       <c r="D80" t="n">
-        <v>45.18907366630634</v>
+        <v>45.18906989096082</v>
       </c>
       <c r="E80" t="n">
-        <v>47.15005636649431</v>
+        <v>47.15005242731743</v>
       </c>
       <c r="F80" t="n">
         <v>954539</v>
@@ -2052,16 +2052,16 @@
         <v>44271</v>
       </c>
       <c r="B82" t="n">
-        <v>42.75707244873047</v>
+        <v>42.7570686340332</v>
       </c>
       <c r="C82" t="n">
-        <v>45.18907290913018</v>
+        <v>45.18906887745489</v>
       </c>
       <c r="D82" t="n">
-        <v>42.75707244873047</v>
+        <v>42.7570686340332</v>
       </c>
       <c r="E82" t="n">
-        <v>44.50657567458991</v>
+        <v>44.5065717038056</v>
       </c>
       <c r="F82" t="n">
         <v>561175</v>
@@ -2092,16 +2092,16 @@
         <v>44273</v>
       </c>
       <c r="B84" t="n">
-        <v>40.89221954345703</v>
+        <v>40.89221572875977</v>
       </c>
       <c r="C84" t="n">
-        <v>45.0256568951004</v>
+        <v>45.02565269480871</v>
       </c>
       <c r="D84" t="n">
-        <v>40.57500224961562</v>
+        <v>40.57499846451049</v>
       </c>
       <c r="E84" t="n">
-        <v>44.01632982334604</v>
+        <v>44.01632571721106</v>
       </c>
       <c r="F84" t="n">
         <v>572621</v>
@@ -2112,16 +2112,16 @@
         <v>44274</v>
       </c>
       <c r="B85" t="n">
-        <v>42.29566192626953</v>
+        <v>42.2956657409668</v>
       </c>
       <c r="C85" t="n">
-        <v>44.17013174266427</v>
+        <v>44.17013572642225</v>
       </c>
       <c r="D85" t="n">
-        <v>41.4593642170013</v>
+        <v>41.45936795627186</v>
       </c>
       <c r="E85" t="n">
-        <v>41.4593642170013</v>
+        <v>41.45936795627186</v>
       </c>
       <c r="F85" t="n">
         <v>639255</v>
@@ -2212,16 +2212,16 @@
         <v>44281</v>
       </c>
       <c r="B90" t="n">
-        <v>37.87384414672852</v>
+        <v>37.87384796142578</v>
       </c>
       <c r="C90" t="n">
-        <v>40.949891527232</v>
+        <v>40.94989565175231</v>
       </c>
       <c r="D90" t="n">
-        <v>37.56623940867817</v>
+        <v>37.56624319239313</v>
       </c>
       <c r="E90" t="n">
-        <v>39.95978959641457</v>
+        <v>39.95979362121066</v>
       </c>
       <c r="F90" t="n">
         <v>840076</v>
@@ -2312,16 +2312,16 @@
         <v>44291</v>
       </c>
       <c r="B95" t="n">
-        <v>35.68215942382812</v>
+        <v>35.68216323852539</v>
       </c>
       <c r="C95" t="n">
-        <v>37.01831616285484</v>
+        <v>37.01832012039754</v>
       </c>
       <c r="D95" t="n">
-        <v>35.09578756412892</v>
+        <v>35.09579131613852</v>
       </c>
       <c r="E95" t="n">
-        <v>37.01831616285484</v>
+        <v>37.01832012039754</v>
       </c>
       <c r="F95" t="n">
         <v>1091895</v>
@@ -2512,16 +2512,16 @@
         <v>44305</v>
       </c>
       <c r="B105" t="n">
-        <v>41.33439636230469</v>
+        <v>41.33440017700195</v>
       </c>
       <c r="C105" t="n">
-        <v>42.23798551125894</v>
+        <v>42.23798940934727</v>
       </c>
       <c r="D105" t="n">
-        <v>40.20971525467667</v>
+        <v>40.2097189655786</v>
       </c>
       <c r="E105" t="n">
-        <v>40.38274455876383</v>
+        <v>40.38274828563441</v>
       </c>
       <c r="F105" t="n">
         <v>1793083</v>
@@ -2552,16 +2552,16 @@
         <v>44308</v>
       </c>
       <c r="B107" t="n">
-        <v>42.3725700378418</v>
+        <v>42.37256622314453</v>
       </c>
       <c r="C107" t="n">
-        <v>42.77630013488342</v>
+        <v>42.77629628383934</v>
       </c>
       <c r="D107" t="n">
-        <v>41.04602186600353</v>
+        <v>41.0460181707321</v>
       </c>
       <c r="E107" t="n">
-        <v>42.58404574470481</v>
+        <v>42.58404191096891</v>
       </c>
       <c r="F107" t="n">
         <v>1175903</v>
@@ -2572,16 +2572,16 @@
         <v>44309</v>
       </c>
       <c r="B108" t="n">
-        <v>44.09323501586914</v>
+        <v>44.09323120117188</v>
       </c>
       <c r="C108" t="n">
-        <v>44.31432325105797</v>
+        <v>44.3143194172334</v>
       </c>
       <c r="D108" t="n">
-        <v>42.38218184069201</v>
+        <v>42.38217817402538</v>
       </c>
       <c r="E108" t="n">
-        <v>42.82436205864548</v>
+        <v>42.82435835372392</v>
       </c>
       <c r="F108" t="n">
         <v>1899574</v>
@@ -2612,16 +2612,16 @@
         <v>44313</v>
       </c>
       <c r="B110" t="n">
-        <v>43.7375602722168</v>
+        <v>43.73756408691406</v>
       </c>
       <c r="C110" t="n">
-        <v>44.31431963823069</v>
+        <v>44.31432350323168</v>
       </c>
       <c r="D110" t="n">
-        <v>43.04545053203033</v>
+        <v>43.04545428636325</v>
       </c>
       <c r="E110" t="n">
-        <v>43.40111793330461</v>
+        <v>43.40112171865809</v>
       </c>
       <c r="F110" t="n">
         <v>1146163</v>
@@ -2732,16 +2732,16 @@
         <v>44321</v>
       </c>
       <c r="B116" t="n">
-        <v>39.74831390380859</v>
+        <v>39.74831008911133</v>
       </c>
       <c r="C116" t="n">
-        <v>40.64229060912697</v>
+        <v>40.6422867086336</v>
       </c>
       <c r="D116" t="n">
-        <v>39.0754291787498</v>
+        <v>39.07542542863015</v>
       </c>
       <c r="E116" t="n">
-        <v>39.89250188164586</v>
+        <v>39.89249805311069</v>
       </c>
       <c r="F116" t="n">
         <v>3650961</v>
@@ -2772,16 +2772,16 @@
         <v>44323</v>
       </c>
       <c r="B118" t="n">
-        <v>38.83510971069336</v>
+        <v>38.83511352539062</v>
       </c>
       <c r="C118" t="n">
-        <v>39.99824098294782</v>
+        <v>39.99824491189721</v>
       </c>
       <c r="D118" t="n">
-        <v>37.51817793834604</v>
+        <v>37.51818162368365</v>
       </c>
       <c r="E118" t="n">
-        <v>39.66179864141913</v>
+        <v>39.66180253732045</v>
       </c>
       <c r="F118" t="n">
         <v>2227429</v>
@@ -2832,16 +2832,16 @@
         <v>44328</v>
       </c>
       <c r="B121" t="n">
-        <v>37.05677032470703</v>
+        <v>37.05676651000977</v>
       </c>
       <c r="C121" t="n">
-        <v>38.70053196862062</v>
+        <v>38.70052798471127</v>
       </c>
       <c r="D121" t="n">
-        <v>37.05677032470703</v>
+        <v>37.05676651000977</v>
       </c>
       <c r="E121" t="n">
-        <v>37.8161715649591</v>
+        <v>37.81616767208757</v>
       </c>
       <c r="F121" t="n">
         <v>783049</v>
@@ -2892,16 +2892,16 @@
         <v>44333</v>
       </c>
       <c r="B124" t="n">
-        <v>36.43194580078125</v>
+        <v>36.43194961547852</v>
       </c>
       <c r="C124" t="n">
-        <v>37.13366805612294</v>
+        <v>37.13367194429578</v>
       </c>
       <c r="D124" t="n">
-        <v>35.93208669563144</v>
+        <v>35.93209045798972</v>
       </c>
       <c r="E124" t="n">
-        <v>36.52807111039643</v>
+        <v>36.52807493515874</v>
       </c>
       <c r="F124" t="n">
         <v>946466</v>
@@ -2912,16 +2912,16 @@
         <v>44334</v>
       </c>
       <c r="B125" t="n">
-        <v>35.14385604858398</v>
+        <v>35.14385223388672</v>
       </c>
       <c r="C125" t="n">
-        <v>36.91258445174329</v>
+        <v>36.91258044505902</v>
       </c>
       <c r="D125" t="n">
-        <v>34.59593422023043</v>
+        <v>34.59593046500746</v>
       </c>
       <c r="E125" t="n">
-        <v>36.52807567013412</v>
+        <v>36.52807170518645</v>
       </c>
       <c r="F125" t="n">
         <v>2070451</v>
@@ -2952,16 +2952,16 @@
         <v>44336</v>
       </c>
       <c r="B127" t="n">
-        <v>34.63438415527344</v>
+        <v>34.63438034057617</v>
       </c>
       <c r="C127" t="n">
-        <v>35.26881876953347</v>
+        <v>35.26881488495837</v>
       </c>
       <c r="D127" t="n">
-        <v>34.51903376998102</v>
+        <v>34.51902996798866</v>
       </c>
       <c r="E127" t="n">
-        <v>34.51903376998102</v>
+        <v>34.51902996798866</v>
       </c>
       <c r="F127" t="n">
         <v>943604</v>
@@ -3012,16 +3012,16 @@
         <v>44341</v>
       </c>
       <c r="B130" t="n">
-        <v>37.29708862304688</v>
+        <v>37.29708480834961</v>
       </c>
       <c r="C130" t="n">
-        <v>38.78704981148397</v>
+        <v>38.78704584439543</v>
       </c>
       <c r="D130" t="n">
-        <v>37.22980089947328</v>
+        <v>37.22979709165812</v>
       </c>
       <c r="E130" t="n">
-        <v>37.52779313716071</v>
+        <v>37.52778929886728</v>
       </c>
       <c r="F130" t="n">
         <v>1731150</v>
@@ -3092,16 +3092,16 @@
         <v>44347</v>
       </c>
       <c r="B134" t="n">
-        <v>39.38303375244141</v>
+        <v>39.38302993774414</v>
       </c>
       <c r="C134" t="n">
-        <v>40.11359366504992</v>
+        <v>40.11358977958957</v>
       </c>
       <c r="D134" t="n">
-        <v>39.02736632794579</v>
+        <v>39.02736254769899</v>
       </c>
       <c r="E134" t="n">
-        <v>39.39264628425005</v>
+        <v>39.3926424686217</v>
       </c>
       <c r="F134" t="n">
         <v>715598</v>
@@ -3192,16 +3192,16 @@
         <v>44355</v>
       </c>
       <c r="B139" t="n">
-        <v>38.4602165222168</v>
+        <v>38.46022033691406</v>
       </c>
       <c r="C139" t="n">
-        <v>38.85433404388245</v>
+        <v>38.85433789767048</v>
       </c>
       <c r="D139" t="n">
-        <v>37.72004038668688</v>
+        <v>37.72004412796937</v>
       </c>
       <c r="E139" t="n">
-        <v>38.43137892899068</v>
+        <v>38.43138274082768</v>
       </c>
       <c r="F139" t="n">
         <v>978352</v>
@@ -3212,16 +3212,16 @@
         <v>44356</v>
       </c>
       <c r="B140" t="n">
-        <v>38.01803588867188</v>
+        <v>38.01803207397461</v>
       </c>
       <c r="C140" t="n">
-        <v>38.66208302162527</v>
+        <v>38.66207914230487</v>
       </c>
       <c r="D140" t="n">
-        <v>37.29708850045856</v>
+        <v>37.29708475810054</v>
       </c>
       <c r="E140" t="n">
-        <v>38.48905744729046</v>
+        <v>38.48905358533129</v>
       </c>
       <c r="F140" t="n">
         <v>837521</v>
@@ -3332,16 +3332,16 @@
         <v>44364</v>
       </c>
       <c r="B146" t="n">
-        <v>42.4879150390625</v>
+        <v>42.48791885375977</v>
       </c>
       <c r="C146" t="n">
-        <v>44.0067136610316</v>
+        <v>44.00671761209134</v>
       </c>
       <c r="D146" t="n">
-        <v>41.62277601425852</v>
+        <v>41.62277975128091</v>
       </c>
       <c r="E146" t="n">
-        <v>42.95893654890009</v>
+        <v>42.95894040588714</v>
       </c>
       <c r="F146" t="n">
         <v>1582144</v>
@@ -3372,16 +3372,16 @@
         <v>44368</v>
       </c>
       <c r="B148" t="n">
-        <v>46.96741485595703</v>
+        <v>46.96741104125977</v>
       </c>
       <c r="C148" t="n">
-        <v>47.24618202489792</v>
+        <v>47.24617818755916</v>
       </c>
       <c r="D148" t="n">
-        <v>43.53569979030122</v>
+        <v>43.53569625432814</v>
       </c>
       <c r="E148" t="n">
-        <v>43.73756295749668</v>
+        <v>43.73755940512824</v>
       </c>
       <c r="F148" t="n">
         <v>2655439</v>
@@ -3452,16 +3452,16 @@
         <v>44372</v>
       </c>
       <c r="B152" t="n">
-        <v>44.45851135253906</v>
+        <v>44.45851516723633</v>
       </c>
       <c r="C152" t="n">
-        <v>44.98720431506052</v>
+        <v>44.9872081751215</v>
       </c>
       <c r="D152" t="n">
-        <v>43.97787729834627</v>
+        <v>43.97788107180344</v>
       </c>
       <c r="E152" t="n">
-        <v>44.98720431506052</v>
+        <v>44.9872081751215</v>
       </c>
       <c r="F152" t="n">
         <v>1347904</v>
@@ -3472,16 +3472,16 @@
         <v>44375</v>
       </c>
       <c r="B153" t="n">
-        <v>44.5354118347168</v>
+        <v>44.53541564941406</v>
       </c>
       <c r="C153" t="n">
-        <v>44.64114967825854</v>
+        <v>44.64115350201283</v>
       </c>
       <c r="D153" t="n">
-        <v>43.20886378695175</v>
+        <v>43.20886748802305</v>
       </c>
       <c r="E153" t="n">
-        <v>44.13168177543641</v>
+        <v>44.13168555555202</v>
       </c>
       <c r="F153" t="n">
         <v>1110393</v>
@@ -3512,16 +3512,16 @@
         <v>44377</v>
       </c>
       <c r="B155" t="n">
-        <v>43.58376312255859</v>
+        <v>43.58375930786133</v>
       </c>
       <c r="C155" t="n">
-        <v>44.45851476998166</v>
+        <v>44.45851087872119</v>
       </c>
       <c r="D155" t="n">
-        <v>43.50686286720073</v>
+        <v>43.50685905923421</v>
       </c>
       <c r="E155" t="n">
-        <v>44.21819772441255</v>
+        <v>44.21819385418598</v>
       </c>
       <c r="F155" t="n">
         <v>1274116</v>
@@ -3572,16 +3572,16 @@
         <v>44382</v>
       </c>
       <c r="B158" t="n">
-        <v>45.04488372802734</v>
+        <v>45.04488754272461</v>
       </c>
       <c r="C158" t="n">
-        <v>46.21762753484401</v>
+        <v>46.21763144885693</v>
       </c>
       <c r="D158" t="n">
-        <v>44.42967048319475</v>
+        <v>44.42967424579171</v>
       </c>
       <c r="E158" t="n">
-        <v>44.98720479275436</v>
+        <v>44.98720860256699</v>
       </c>
       <c r="F158" t="n">
         <v>3391068</v>
@@ -3592,16 +3592,16 @@
         <v>44383</v>
       </c>
       <c r="B159" t="n">
-        <v>44.37199401855469</v>
+        <v>44.37199783325195</v>
       </c>
       <c r="C159" t="n">
-        <v>45.94847158903642</v>
+        <v>45.94847553926477</v>
       </c>
       <c r="D159" t="n">
-        <v>43.75678453900221</v>
+        <v>43.75678830080941</v>
       </c>
       <c r="E159" t="n">
-        <v>45.7850548143543</v>
+        <v>45.78505875053358</v>
       </c>
       <c r="F159" t="n">
         <v>1563442</v>
@@ -3652,16 +3652,16 @@
         <v>44389</v>
       </c>
       <c r="B162" t="n">
-        <v>44.72766876220703</v>
+        <v>44.72766494750977</v>
       </c>
       <c r="C162" t="n">
-        <v>45.75622090541913</v>
+        <v>45.75621700299953</v>
       </c>
       <c r="D162" t="n">
-        <v>44.08361789020423</v>
+        <v>44.08361413043626</v>
       </c>
       <c r="E162" t="n">
-        <v>45.75622090541913</v>
+        <v>45.75621700299953</v>
       </c>
       <c r="F162" t="n">
         <v>1597780</v>
@@ -3732,16 +3732,16 @@
         <v>44393</v>
       </c>
       <c r="B166" t="n">
-        <v>41.70928955078125</v>
+        <v>41.70929336547852</v>
       </c>
       <c r="C166" t="n">
-        <v>41.91115645117827</v>
+        <v>41.91116028433812</v>
       </c>
       <c r="D166" t="n">
-        <v>40.45003298811638</v>
+        <v>40.45003668764308</v>
       </c>
       <c r="E166" t="n">
-        <v>41.62277677100059</v>
+        <v>41.62278057778546</v>
       </c>
       <c r="F166" t="n">
         <v>1471156</v>
@@ -3752,16 +3752,16 @@
         <v>44396</v>
       </c>
       <c r="B167" t="n">
-        <v>40.22894287109375</v>
+        <v>40.22894668579102</v>
       </c>
       <c r="C167" t="n">
-        <v>41.05562800061862</v>
+        <v>41.05563189370605</v>
       </c>
       <c r="D167" t="n">
-        <v>39.50799183094843</v>
+        <v>39.50799557728174</v>
       </c>
       <c r="E167" t="n">
-        <v>40.46925613690023</v>
+        <v>40.46925997438512</v>
       </c>
       <c r="F167" t="n">
         <v>1632835</v>
@@ -3792,16 +3792,16 @@
         <v>44398</v>
       </c>
       <c r="B169" t="n">
-        <v>40.45964431762695</v>
+        <v>40.45964813232422</v>
       </c>
       <c r="C169" t="n">
-        <v>41.40168732645247</v>
+        <v>41.40169122996932</v>
       </c>
       <c r="D169" t="n">
-        <v>40.22894357839657</v>
+        <v>40.22894737134245</v>
       </c>
       <c r="E169" t="n">
-        <v>40.37313154041556</v>
+        <v>40.37313534695605</v>
       </c>
       <c r="F169" t="n">
         <v>985812</v>
@@ -3812,16 +3812,16 @@
         <v>44399</v>
       </c>
       <c r="B170" t="n">
-        <v>40.89221954345703</v>
+        <v>40.89221572875977</v>
       </c>
       <c r="C170" t="n">
-        <v>41.15176164706832</v>
+        <v>41.15175780815924</v>
       </c>
       <c r="D170" t="n">
-        <v>40.3923603996445</v>
+        <v>40.39235663157741</v>
       </c>
       <c r="E170" t="n">
-        <v>41.08447017755746</v>
+        <v>41.08446634492577</v>
       </c>
       <c r="F170" t="n">
         <v>757704</v>
@@ -3832,16 +3832,16 @@
         <v>44400</v>
       </c>
       <c r="B171" t="n">
-        <v>40.56538772583008</v>
+        <v>40.56539154052734</v>
       </c>
       <c r="C171" t="n">
-        <v>40.86337994162768</v>
+        <v>40.8633837843476</v>
       </c>
       <c r="D171" t="n">
-        <v>40.20010404382616</v>
+        <v>40.20010782417279</v>
       </c>
       <c r="E171" t="n">
-        <v>40.6230629132279</v>
+        <v>40.62306673334884</v>
       </c>
       <c r="F171" t="n">
         <v>715496</v>
@@ -3872,16 +3872,16 @@
         <v>44404</v>
       </c>
       <c r="B173" t="n">
-        <v>38.54673004150391</v>
+        <v>38.54673385620117</v>
       </c>
       <c r="C173" t="n">
-        <v>40.84415499320262</v>
+        <v>40.84415903525979</v>
       </c>
       <c r="D173" t="n">
-        <v>38.32563807495276</v>
+        <v>38.32564186777011</v>
       </c>
       <c r="E173" t="n">
-        <v>40.62306302665147</v>
+        <v>40.62306704682872</v>
       </c>
       <c r="F173" t="n">
         <v>1543819</v>
@@ -3932,16 +3932,16 @@
         <v>44407</v>
       </c>
       <c r="B176" t="n">
-        <v>37.2105712890625</v>
+        <v>37.21057510375977</v>
       </c>
       <c r="C176" t="n">
-        <v>38.26796091589321</v>
+        <v>38.26796483899034</v>
       </c>
       <c r="D176" t="n">
-        <v>36.33581974675896</v>
+        <v>36.33582347177977</v>
       </c>
       <c r="E176" t="n">
-        <v>37.5662386749276</v>
+        <v>37.56624252608663</v>
       </c>
       <c r="F176" t="n">
         <v>1168442</v>
@@ -3952,16 +3952,16 @@
         <v>44410</v>
       </c>
       <c r="B177" t="n">
-        <v>39.04658889770508</v>
+        <v>39.04659271240234</v>
       </c>
       <c r="C177" t="n">
-        <v>40.3442955992922</v>
+        <v>40.34429954077027</v>
       </c>
       <c r="D177" t="n">
-        <v>38.19106237864987</v>
+        <v>38.19106610976557</v>
       </c>
       <c r="E177" t="n">
-        <v>39.17155180323623</v>
+        <v>39.17155563014188</v>
       </c>
       <c r="F177" t="n">
         <v>3352028</v>
@@ -4052,16 +4052,16 @@
         <v>44417</v>
       </c>
       <c r="B182" t="n">
-        <v>37.10483169555664</v>
+        <v>37.10483551025391</v>
       </c>
       <c r="C182" t="n">
-        <v>37.44127403795907</v>
+        <v>37.44127788724551</v>
       </c>
       <c r="D182" t="n">
-        <v>35.94170042028153</v>
+        <v>35.94170411539885</v>
       </c>
       <c r="E182" t="n">
-        <v>36.1147297309109</v>
+        <v>36.11473344381713</v>
       </c>
       <c r="F182" t="n">
         <v>1206460</v>
@@ -4092,16 +4092,16 @@
         <v>44419</v>
       </c>
       <c r="B184" t="n">
-        <v>36.43194580078125</v>
+        <v>36.43194961547852</v>
       </c>
       <c r="C184" t="n">
-        <v>36.74916307008678</v>
+        <v>36.74916691799907</v>
       </c>
       <c r="D184" t="n">
-        <v>36.09550346955268</v>
+        <v>36.09550724902192</v>
       </c>
       <c r="E184" t="n">
-        <v>36.47039592462733</v>
+        <v>36.4703997433506</v>
       </c>
       <c r="F184" t="n">
         <v>786524</v>
@@ -4112,16 +4112,16 @@
         <v>44420</v>
       </c>
       <c r="B185" t="n">
-        <v>36.12434387207031</v>
+        <v>36.12434005737305</v>
       </c>
       <c r="C185" t="n">
-        <v>36.95103284178433</v>
+        <v>36.95102893978947</v>
       </c>
       <c r="D185" t="n">
-        <v>35.4706842206967</v>
+        <v>35.47068047502529</v>
       </c>
       <c r="E185" t="n">
-        <v>36.19163159403436</v>
+        <v>36.19162777223157</v>
       </c>
       <c r="F185" t="n">
         <v>689639</v>
@@ -4132,16 +4132,16 @@
         <v>44421</v>
       </c>
       <c r="B186" t="n">
-        <v>34.75934219360352</v>
+        <v>34.75934600830078</v>
       </c>
       <c r="C186" t="n">
-        <v>35.97053605946554</v>
+        <v>35.97054000708643</v>
       </c>
       <c r="D186" t="n">
-        <v>34.59592917071041</v>
+        <v>34.59593296747376</v>
       </c>
       <c r="E186" t="n">
-        <v>35.69177266747142</v>
+        <v>35.69177658449917</v>
       </c>
       <c r="F186" t="n">
         <v>915908</v>
@@ -4252,16 +4252,16 @@
         <v>44431</v>
       </c>
       <c r="B192" t="n">
-        <v>33.16364288330078</v>
+        <v>33.16364669799805</v>
       </c>
       <c r="C192" t="n">
-        <v>34.42289938524034</v>
+        <v>34.42290334478545</v>
       </c>
       <c r="D192" t="n">
-        <v>32.77913791079774</v>
+        <v>32.77914168126674</v>
       </c>
       <c r="E192" t="n">
-        <v>33.740402215843</v>
+        <v>33.74040609688286</v>
       </c>
       <c r="F192" t="n">
         <v>2084044</v>
@@ -4272,16 +4272,16 @@
         <v>44432</v>
       </c>
       <c r="B193" t="n">
-        <v>35.43223571777344</v>
+        <v>35.43223190307617</v>
       </c>
       <c r="C193" t="n">
-        <v>35.43223571777344</v>
+        <v>35.43223190307617</v>
       </c>
       <c r="D193" t="n">
-        <v>33.47125292620207</v>
+        <v>33.47124932262768</v>
       </c>
       <c r="E193" t="n">
-        <v>33.93266196453976</v>
+        <v>33.93265831128927</v>
       </c>
       <c r="F193" t="n">
         <v>1429663</v>
@@ -4332,16 +4332,16 @@
         <v>44435</v>
       </c>
       <c r="B196" t="n">
-        <v>36.43194580078125</v>
+        <v>36.43194961547852</v>
       </c>
       <c r="C196" t="n">
-        <v>36.66265029143312</v>
+        <v>36.66265413028687</v>
       </c>
       <c r="D196" t="n">
-        <v>35.02849754252244</v>
+        <v>35.02850121026817</v>
       </c>
       <c r="E196" t="n">
-        <v>35.75906113832411</v>
+        <v>35.75906488256532</v>
       </c>
       <c r="F196" t="n">
         <v>2701327</v>
@@ -4392,16 +4392,16 @@
         <v>44440</v>
       </c>
       <c r="B199" t="n">
-        <v>36.00899124145508</v>
+        <v>36.00899505615234</v>
       </c>
       <c r="C199" t="n">
-        <v>37.22979768253502</v>
+        <v>37.2298016265613</v>
       </c>
       <c r="D199" t="n">
-        <v>35.47068200422877</v>
+        <v>35.47068576189898</v>
       </c>
       <c r="E199" t="n">
-        <v>37.10483103054919</v>
+        <v>37.10483496133683</v>
       </c>
       <c r="F199" t="n">
         <v>1150659</v>
@@ -4712,16 +4712,16 @@
         <v>44463</v>
       </c>
       <c r="B215" t="n">
-        <v>34.54786682128906</v>
+        <v>34.54787063598633</v>
       </c>
       <c r="C215" t="n">
-        <v>35.65331911097231</v>
+        <v>35.65332304773112</v>
       </c>
       <c r="D215" t="n">
-        <v>33.88459095038866</v>
+        <v>33.88459469184851</v>
       </c>
       <c r="E215" t="n">
-        <v>34.46135404370111</v>
+        <v>34.46135784884584</v>
       </c>
       <c r="F215" t="n">
         <v>2639905</v>
@@ -4852,16 +4852,16 @@
         <v>44474</v>
       </c>
       <c r="B222" t="n">
-        <v>41.23827362060547</v>
+        <v>41.2382698059082</v>
       </c>
       <c r="C222" t="n">
-        <v>43.07428962557536</v>
+        <v>43.07428564103963</v>
       </c>
       <c r="D222" t="n">
-        <v>40.9498939275561</v>
+        <v>40.94989013953506</v>
       </c>
       <c r="E222" t="n">
-        <v>41.82464553821999</v>
+        <v>41.82464166928109</v>
       </c>
       <c r="F222" t="n">
         <v>3033780</v>
@@ -4952,16 +4952,16 @@
         <v>44482</v>
       </c>
       <c r="B227" t="n">
-        <v>39.66179656982422</v>
+        <v>39.66180038452148</v>
       </c>
       <c r="C227" t="n">
-        <v>40.05591407830239</v>
+        <v>40.05591793090613</v>
       </c>
       <c r="D227" t="n">
-        <v>38.88317033604628</v>
+        <v>38.88317407585477</v>
       </c>
       <c r="E227" t="n">
-        <v>39.43109208415942</v>
+        <v>39.43109587666738</v>
       </c>
       <c r="F227" t="n">
         <v>1130628</v>
@@ -5012,16 +5012,16 @@
         <v>44487</v>
       </c>
       <c r="B230" t="n">
-        <v>39.87327194213867</v>
+        <v>39.87327575683594</v>
       </c>
       <c r="C230" t="n">
-        <v>41.44974945917212</v>
+        <v>41.44975342469183</v>
       </c>
       <c r="D230" t="n">
-        <v>39.18116223800101</v>
+        <v>39.18116598648377</v>
       </c>
       <c r="E230" t="n">
-        <v>39.72908398193304</v>
+        <v>39.72908778283576</v>
       </c>
       <c r="F230" t="n">
         <v>2573169</v>
@@ -5032,16 +5032,16 @@
         <v>44488</v>
       </c>
       <c r="B231" t="n">
-        <v>37.58546447753906</v>
+        <v>37.58546829223633</v>
       </c>
       <c r="C231" t="n">
-        <v>40.08475250621378</v>
+        <v>40.08475657457366</v>
       </c>
       <c r="D231" t="n">
-        <v>36.86451716082918</v>
+        <v>36.86452090235465</v>
       </c>
       <c r="E231" t="n">
-        <v>39.57528087049455</v>
+        <v>39.57528488714614</v>
       </c>
       <c r="F231" t="n">
         <v>2915331</v>
@@ -5072,16 +5072,16 @@
         <v>44490</v>
       </c>
       <c r="B233" t="n">
-        <v>34.41328811645508</v>
+        <v>34.41329193115234</v>
       </c>
       <c r="C233" t="n">
-        <v>36.09550352264783</v>
+        <v>36.09550752381791</v>
       </c>
       <c r="D233" t="n">
-        <v>33.48086136908995</v>
+        <v>33.48086508042814</v>
       </c>
       <c r="E233" t="n">
-        <v>35.62448200968972</v>
+        <v>35.62448595864728</v>
       </c>
       <c r="F233" t="n">
         <v>3113087</v>
@@ -5092,16 +5092,16 @@
         <v>44491</v>
       </c>
       <c r="B234" t="n">
-        <v>32.63494873046875</v>
+        <v>32.63495254516602</v>
       </c>
       <c r="C234" t="n">
-        <v>34.06723464208851</v>
+        <v>34.06723862420559</v>
       </c>
       <c r="D234" t="n">
-        <v>31.04886231697067</v>
+        <v>31.04886594627039</v>
       </c>
       <c r="E234" t="n">
-        <v>33.63466698298016</v>
+        <v>33.63467091453443</v>
       </c>
       <c r="F234" t="n">
         <v>4894520</v>
@@ -5112,16 +5112,16 @@
         <v>44494</v>
       </c>
       <c r="B235" t="n">
-        <v>36.8470573425293</v>
+        <v>36.84706115722656</v>
       </c>
       <c r="C235" t="n">
-        <v>37.3112732591762</v>
+        <v>37.31127712193275</v>
       </c>
       <c r="D235" t="n">
-        <v>32.95925887799699</v>
+        <v>32.95926229019877</v>
       </c>
       <c r="E235" t="n">
-        <v>32.95925887799699</v>
+        <v>32.95926229019877</v>
       </c>
       <c r="F235" t="n">
         <v>3449995</v>
@@ -5152,16 +5152,16 @@
         <v>44496</v>
       </c>
       <c r="B237" t="n">
-        <v>35.29000854492188</v>
+        <v>35.29000473022461</v>
       </c>
       <c r="C237" t="n">
-        <v>36.07337184605893</v>
+        <v>36.07336794668348</v>
       </c>
       <c r="D237" t="n">
-        <v>34.47763151058894</v>
+        <v>34.47762778370612</v>
       </c>
       <c r="E237" t="n">
-        <v>36.07337184605893</v>
+        <v>36.07336794668348</v>
       </c>
       <c r="F237" t="n">
         <v>2270538</v>
@@ -5272,16 +5272,16 @@
         <v>44505</v>
       </c>
       <c r="B243" t="n">
-        <v>34.33255767822266</v>
+        <v>34.33256149291992</v>
       </c>
       <c r="C243" t="n">
-        <v>35.80257411368536</v>
+        <v>35.80257809171644</v>
       </c>
       <c r="D243" t="n">
-        <v>31.73102080869616</v>
+        <v>31.73102433433615</v>
       </c>
       <c r="E243" t="n">
-        <v>33.17202351532898</v>
+        <v>33.17202720107906</v>
       </c>
       <c r="F243" t="n">
         <v>9166770</v>
@@ -5312,16 +5312,16 @@
         <v>44509</v>
       </c>
       <c r="B245" t="n">
-        <v>34.50664138793945</v>
+        <v>34.50664520263672</v>
       </c>
       <c r="C245" t="n">
-        <v>35.1062534768846</v>
+        <v>35.10625735786877</v>
       </c>
       <c r="D245" t="n">
-        <v>32.63044017132788</v>
+        <v>32.63044377861175</v>
       </c>
       <c r="E245" t="n">
-        <v>33.89736055406007</v>
+        <v>33.89736430140155</v>
       </c>
       <c r="F245" t="n">
         <v>7032350</v>
@@ -5372,16 +5372,16 @@
         <v>44512</v>
       </c>
       <c r="B248" t="n">
-        <v>30.94766044616699</v>
+        <v>30.94766235351562</v>
       </c>
       <c r="C248" t="n">
-        <v>33.11399707089411</v>
+        <v>33.11399911175717</v>
       </c>
       <c r="D248" t="n">
-        <v>30.69620937113922</v>
+        <v>30.69621126299056</v>
       </c>
       <c r="E248" t="n">
-        <v>32.10819651835855</v>
+        <v>32.10819849723269</v>
       </c>
       <c r="F248" t="n">
         <v>3403064</v>
@@ -5552,16 +5552,16 @@
         <v>44526</v>
       </c>
       <c r="B257" t="n">
-        <v>26.69235801696777</v>
+        <v>26.69235992431641</v>
       </c>
       <c r="C257" t="n">
-        <v>27.61111551515892</v>
+        <v>27.61111748815896</v>
       </c>
       <c r="D257" t="n">
-        <v>25.85096734243463</v>
+        <v>25.85096918966023</v>
       </c>
       <c r="E257" t="n">
-        <v>26.59564620826666</v>
+        <v>26.59564810870458</v>
       </c>
       <c r="F257" t="n">
         <v>3664026</v>
@@ -5592,16 +5592,16 @@
         <v>44530</v>
       </c>
       <c r="B259" t="n">
-        <v>26.71169853210449</v>
+        <v>26.71170043945312</v>
       </c>
       <c r="C259" t="n">
-        <v>26.71169853210449</v>
+        <v>26.71170043945312</v>
       </c>
       <c r="D259" t="n">
-        <v>25.48346440355603</v>
+        <v>25.48346622320262</v>
       </c>
       <c r="E259" t="n">
-        <v>26.53761803066504</v>
+        <v>26.53761992558345</v>
       </c>
       <c r="F259" t="n">
         <v>4757647</v>
@@ -5612,16 +5612,16 @@
         <v>44531</v>
       </c>
       <c r="B260" t="n">
-        <v>26.69235801696777</v>
+        <v>26.69235992431641</v>
       </c>
       <c r="C260" t="n">
-        <v>28.01730398743094</v>
+        <v>28.01730598945588</v>
       </c>
       <c r="D260" t="n">
-        <v>26.32485389341864</v>
+        <v>26.32485577450663</v>
       </c>
       <c r="E260" t="n">
-        <v>27.17591518668557</v>
+        <v>27.17591712858762</v>
       </c>
       <c r="F260" t="n">
         <v>3467467</v>
@@ -5752,16 +5752,16 @@
         <v>44540</v>
       </c>
       <c r="B267" t="n">
-        <v>29.43896293640137</v>
+        <v>29.43896102905273</v>
       </c>
       <c r="C267" t="n">
-        <v>29.76778272429381</v>
+        <v>29.76778079564096</v>
       </c>
       <c r="D267" t="n">
-        <v>28.76198212238038</v>
+        <v>28.76198025889329</v>
       </c>
       <c r="E267" t="n">
-        <v>29.57435909920557</v>
+        <v>29.57435718308462</v>
       </c>
       <c r="F267" t="n">
         <v>1281952</v>
@@ -5832,16 +5832,16 @@
         <v>44546</v>
       </c>
       <c r="B271" t="n">
-        <v>30.62851333618164</v>
+        <v>30.62851524353027</v>
       </c>
       <c r="C271" t="n">
-        <v>30.86062130141829</v>
+        <v>30.86062322322113</v>
       </c>
       <c r="D271" t="n">
-        <v>29.25521052973079</v>
+        <v>29.25521235155887</v>
       </c>
       <c r="E271" t="n">
-        <v>29.4969891136642</v>
+        <v>29.49699095054871</v>
       </c>
       <c r="F271" t="n">
         <v>3477726</v>
@@ -5952,16 +5952,16 @@
         <v>44557</v>
       </c>
       <c r="B277" t="n">
-        <v>30.72522354125977</v>
+        <v>30.7252254486084</v>
       </c>
       <c r="C277" t="n">
-        <v>31.01535896880716</v>
+        <v>31.01536089416671</v>
       </c>
       <c r="D277" t="n">
-        <v>29.98054654550914</v>
+        <v>29.98054840663</v>
       </c>
       <c r="E277" t="n">
-        <v>29.98054654550914</v>
+        <v>29.98054840663</v>
       </c>
       <c r="F277" t="n">
         <v>1273927</v>
@@ -6132,16 +6132,16 @@
         <v>44571</v>
       </c>
       <c r="B286" t="n">
-        <v>33.37511444091797</v>
+        <v>33.37511825561523</v>
       </c>
       <c r="C286" t="n">
-        <v>33.89735778992546</v>
+        <v>33.89736166431392</v>
       </c>
       <c r="D286" t="n">
-        <v>32.24359030771443</v>
+        <v>32.24359399308115</v>
       </c>
       <c r="E286" t="n">
-        <v>32.37898645393302</v>
+        <v>32.3789901547752</v>
       </c>
       <c r="F286" t="n">
         <v>2829132</v>
@@ -6152,16 +6152,16 @@
         <v>44572</v>
       </c>
       <c r="B287" t="n">
-        <v>35.10625457763672</v>
+        <v>35.10625076293945</v>
       </c>
       <c r="C287" t="n">
-        <v>35.63816673084244</v>
+        <v>35.63816285834681</v>
       </c>
       <c r="D287" t="n">
-        <v>33.18169458570739</v>
+        <v>33.18169098013564</v>
       </c>
       <c r="E287" t="n">
-        <v>33.55886933935793</v>
+        <v>33.55886569280182</v>
       </c>
       <c r="F287" t="n">
         <v>3953735</v>
@@ -6172,16 +6172,16 @@
         <v>44573</v>
       </c>
       <c r="B288" t="n">
-        <v>34.89348983764648</v>
+        <v>34.89348602294922</v>
       </c>
       <c r="C288" t="n">
-        <v>35.98632787872025</v>
+        <v>35.98632394454952</v>
       </c>
       <c r="D288" t="n">
-        <v>34.13914032772324</v>
+        <v>34.13913659549451</v>
       </c>
       <c r="E288" t="n">
-        <v>35.34803329265463</v>
+        <v>35.34802942826484</v>
       </c>
       <c r="F288" t="n">
         <v>3302601</v>
@@ -6292,16 +6292,16 @@
         <v>44581</v>
       </c>
       <c r="B294" t="n">
-        <v>35.29967498779297</v>
+        <v>35.2996711730957</v>
       </c>
       <c r="C294" t="n">
-        <v>36.17007943172774</v>
+        <v>36.17007552296929</v>
       </c>
       <c r="D294" t="n">
-        <v>34.98052769103708</v>
+        <v>34.98052391082881</v>
       </c>
       <c r="E294" t="n">
-        <v>35.87027337331519</v>
+        <v>35.8702694969556</v>
       </c>
       <c r="F294" t="n">
         <v>3650414</v>
@@ -6332,16 +6332,16 @@
         <v>44585</v>
       </c>
       <c r="B296" t="n">
-        <v>34.35190200805664</v>
+        <v>34.35190582275391</v>
       </c>
       <c r="C296" t="n">
-        <v>35.3190162904272</v>
+        <v>35.31902021252021</v>
       </c>
       <c r="D296" t="n">
-        <v>34.05209598090971</v>
+        <v>34.05209976231423</v>
       </c>
       <c r="E296" t="n">
-        <v>34.23584709494806</v>
+        <v>34.2358508967577</v>
       </c>
       <c r="F296" t="n">
         <v>2113697</v>
@@ -6392,16 +6392,16 @@
         <v>44588</v>
       </c>
       <c r="B299" t="n">
-        <v>36.09271240234375</v>
+        <v>36.09270858764648</v>
       </c>
       <c r="C299" t="n">
-        <v>37.1081818022467</v>
+        <v>37.10817788022283</v>
       </c>
       <c r="D299" t="n">
-        <v>35.68652389286739</v>
+        <v>35.68652012110085</v>
       </c>
       <c r="E299" t="n">
-        <v>35.87994752798603</v>
+        <v>35.87994373577622</v>
       </c>
       <c r="F299" t="n">
         <v>3171460</v>
@@ -6492,16 +6492,16 @@
         <v>44595</v>
       </c>
       <c r="B304" t="n">
-        <v>35.29967498779297</v>
+        <v>35.2996711730957</v>
       </c>
       <c r="C304" t="n">
-        <v>35.58981230082171</v>
+        <v>35.58980845477045</v>
       </c>
       <c r="D304" t="n">
-        <v>33.84900341295216</v>
+        <v>33.84899975502328</v>
       </c>
       <c r="E304" t="n">
-        <v>34.98052769103708</v>
+        <v>34.98052391082881</v>
       </c>
       <c r="F304" t="n">
         <v>4177823</v>
@@ -6592,16 +6592,16 @@
         <v>44602</v>
       </c>
       <c r="B309" t="n">
-        <v>37.28226470947266</v>
+        <v>37.28226089477539</v>
       </c>
       <c r="C309" t="n">
-        <v>38.3847753224369</v>
+        <v>38.38477139493146</v>
       </c>
       <c r="D309" t="n">
-        <v>36.33449150769526</v>
+        <v>36.33448778997354</v>
       </c>
       <c r="E309" t="n">
-        <v>36.36350524073979</v>
+        <v>36.3635015200494</v>
       </c>
       <c r="F309" t="n">
         <v>7025951</v>
@@ -6612,16 +6612,16 @@
         <v>44603</v>
       </c>
       <c r="B310" t="n">
-        <v>38.07529067993164</v>
+        <v>38.07529449462891</v>
       </c>
       <c r="C310" t="n">
-        <v>38.49115162219439</v>
+        <v>38.49115547855604</v>
       </c>
       <c r="D310" t="n">
-        <v>37.37896869306991</v>
+        <v>37.37897243800389</v>
       </c>
       <c r="E310" t="n">
-        <v>37.78515714333515</v>
+        <v>37.78516092896444</v>
       </c>
       <c r="F310" t="n">
         <v>5486491</v>
@@ -6632,16 +6632,16 @@
         <v>44606</v>
       </c>
       <c r="B311" t="n">
-        <v>37.57239151000977</v>
+        <v>37.57239532470703</v>
       </c>
       <c r="C311" t="n">
-        <v>38.84898429079868</v>
+        <v>38.84898823510746</v>
       </c>
       <c r="D311" t="n">
-        <v>36.95343822941596</v>
+        <v>36.95344198127135</v>
       </c>
       <c r="E311" t="n">
-        <v>38.29772721003804</v>
+        <v>38.2977310983781</v>
       </c>
       <c r="F311" t="n">
         <v>3902640</v>
@@ -6652,16 +6652,16 @@
         <v>44607</v>
       </c>
       <c r="B312" t="n">
-        <v>35.79290008544922</v>
+        <v>35.79290390014648</v>
       </c>
       <c r="C312" t="n">
-        <v>36.65363192612031</v>
+        <v>36.65363583255173</v>
       </c>
       <c r="D312" t="n">
-        <v>35.63816270338088</v>
+        <v>35.63816650158672</v>
       </c>
       <c r="E312" t="n">
-        <v>36.55692199922141</v>
+        <v>36.55692589534578</v>
       </c>
       <c r="F312" t="n">
         <v>3810709</v>
@@ -6672,16 +6672,16 @@
         <v>44608</v>
       </c>
       <c r="B313" t="n">
-        <v>35.92830276489258</v>
+        <v>35.92829895019531</v>
       </c>
       <c r="C313" t="n">
-        <v>36.80837600146183</v>
+        <v>36.80837209332255</v>
       </c>
       <c r="D313" t="n">
-        <v>35.69619664958365</v>
+        <v>35.69619285953032</v>
       </c>
       <c r="E313" t="n">
-        <v>36.44087371532872</v>
+        <v>36.4408698462091</v>
       </c>
       <c r="F313" t="n">
         <v>4244663</v>
@@ -6692,16 +6692,16 @@
         <v>44609</v>
       </c>
       <c r="B314" t="n">
-        <v>35.29967498779297</v>
+        <v>35.2996711730957</v>
       </c>
       <c r="C314" t="n">
-        <v>35.89928710461807</v>
+        <v>35.89928322512308</v>
       </c>
       <c r="D314" t="n">
-        <v>34.41960179847439</v>
+        <v>34.41959807888318</v>
       </c>
       <c r="E314" t="n">
-        <v>35.68652224011414</v>
+        <v>35.68651838361181</v>
       </c>
       <c r="F314" t="n">
         <v>4430658</v>
@@ -6712,16 +6712,16 @@
         <v>44610</v>
       </c>
       <c r="B315" t="n">
-        <v>34.48730087280273</v>
+        <v>34.48729705810547</v>
       </c>
       <c r="C315" t="n">
-        <v>35.41572900804387</v>
+        <v>35.41572509065163</v>
       </c>
       <c r="D315" t="n">
-        <v>33.80064757961473</v>
+        <v>33.80064384086931</v>
       </c>
       <c r="E315" t="n">
-        <v>34.83546189196511</v>
+        <v>34.83545803875718</v>
       </c>
       <c r="F315" t="n">
         <v>4069741</v>
@@ -6852,16 +6852,16 @@
         <v>44623</v>
       </c>
       <c r="B322" t="n">
-        <v>37.34028625488281</v>
+        <v>37.34028244018555</v>
       </c>
       <c r="C322" t="n">
-        <v>37.88187465766974</v>
+        <v>37.88187078764361</v>
       </c>
       <c r="D322" t="n">
-        <v>36.31514815474819</v>
+        <v>36.31514444477941</v>
       </c>
       <c r="E322" t="n">
-        <v>37.12752138998924</v>
+        <v>37.12751759702811</v>
       </c>
       <c r="F322" t="n">
         <v>9786414</v>
@@ -6892,16 +6892,16 @@
         <v>44627</v>
       </c>
       <c r="B324" t="n">
-        <v>37.04048156738281</v>
+        <v>37.04048538208008</v>
       </c>
       <c r="C324" t="n">
-        <v>39.28418499781101</v>
+        <v>39.28418904358112</v>
       </c>
       <c r="D324" t="n">
-        <v>36.65363433916909</v>
+        <v>36.65363811402602</v>
       </c>
       <c r="E324" t="n">
-        <v>38.17200577495368</v>
+        <v>38.17200970618351</v>
       </c>
       <c r="F324" t="n">
         <v>5025922</v>
@@ -6952,16 +6952,16 @@
         <v>44630</v>
       </c>
       <c r="B327" t="n">
-        <v>35.7252082824707</v>
+        <v>35.72520446777344</v>
       </c>
       <c r="C327" t="n">
-        <v>37.22423481932497</v>
+        <v>37.22423084456335</v>
       </c>
       <c r="D327" t="n">
-        <v>35.51244341905014</v>
+        <v>35.51243962707166</v>
       </c>
       <c r="E327" t="n">
-        <v>36.75034637550812</v>
+        <v>36.75034245134777</v>
       </c>
       <c r="F327" t="n">
         <v>4502679</v>
@@ -7032,16 +7032,16 @@
         <v>44636</v>
       </c>
       <c r="B331" t="n">
-        <v>32.84320449829102</v>
+        <v>32.84320831298828</v>
       </c>
       <c r="C331" t="n">
-        <v>34.44861337459189</v>
+        <v>34.44861737575539</v>
       </c>
       <c r="D331" t="n">
-        <v>32.34030609979657</v>
+        <v>32.34030985608281</v>
       </c>
       <c r="E331" t="n">
-        <v>34.10045236831488</v>
+        <v>34.10045632903992</v>
       </c>
       <c r="F331" t="n">
         <v>3899288</v>
@@ -7092,16 +7092,16 @@
         <v>44641</v>
       </c>
       <c r="B334" t="n">
-        <v>36.61494827270508</v>
+        <v>36.61495208740234</v>
       </c>
       <c r="C334" t="n">
-        <v>36.86639934686866</v>
+        <v>36.86640318776314</v>
       </c>
       <c r="D334" t="n">
-        <v>35.88961252740777</v>
+        <v>35.88961626653654</v>
       </c>
       <c r="E334" t="n">
-        <v>35.97665371626157</v>
+        <v>35.97665746445866</v>
       </c>
       <c r="F334" t="n">
         <v>3600944</v>
@@ -7212,16 +7212,16 @@
         <v>44649</v>
       </c>
       <c r="B340" t="n">
-        <v>40.11590194702148</v>
+        <v>40.11590576171875</v>
       </c>
       <c r="C340" t="n">
-        <v>40.60913158587444</v>
+        <v>40.60913544747385</v>
       </c>
       <c r="D340" t="n">
-        <v>37.81417112752509</v>
+        <v>37.8141747233464</v>
       </c>
       <c r="E340" t="n">
-        <v>38.00759473575618</v>
+        <v>38.00759834997051</v>
       </c>
       <c r="F340" t="n">
         <v>6952609</v>
@@ -7252,16 +7252,16 @@
         <v>44651</v>
       </c>
       <c r="B342" t="n">
-        <v>40.47373962402344</v>
+        <v>40.47373580932617</v>
       </c>
       <c r="C342" t="n">
-        <v>41.13137921056172</v>
+        <v>41.13137533388116</v>
       </c>
       <c r="D342" t="n">
-        <v>39.67103512697872</v>
+        <v>39.6710313879373</v>
       </c>
       <c r="E342" t="n">
-        <v>40.135251085266</v>
+        <v>40.13524730247168</v>
       </c>
       <c r="F342" t="n">
         <v>3810811</v>
@@ -7312,16 +7312,16 @@
         <v>44656</v>
       </c>
       <c r="B345" t="n">
-        <v>41.97276306152344</v>
+        <v>41.9727668762207</v>
       </c>
       <c r="C345" t="n">
-        <v>43.03659106395681</v>
+        <v>43.03659497534015</v>
       </c>
       <c r="D345" t="n">
-        <v>41.57624708903781</v>
+        <v>41.5762508676977</v>
       </c>
       <c r="E345" t="n">
-        <v>42.30158283032514</v>
+        <v>42.30158667490721</v>
       </c>
       <c r="F345" t="n">
         <v>5903074</v>
@@ -7432,16 +7432,16 @@
         <v>44664</v>
       </c>
       <c r="B351" t="n">
-        <v>43.62652969360352</v>
+        <v>43.62653350830078</v>
       </c>
       <c r="C351" t="n">
-        <v>43.71356713249195</v>
+        <v>43.71357095479976</v>
       </c>
       <c r="D351" t="n">
-        <v>42.8431665105797</v>
+        <v>42.8431702567798</v>
       </c>
       <c r="E351" t="n">
-        <v>43.30738242414481</v>
+        <v>43.30738621093589</v>
       </c>
       <c r="F351" t="n">
         <v>3238402</v>
@@ -7452,16 +7452,16 @@
         <v>44665</v>
       </c>
       <c r="B352" t="n">
-        <v>42.93988037109375</v>
+        <v>42.93987655639648</v>
       </c>
       <c r="C352" t="n">
-        <v>43.62653368593358</v>
+        <v>43.62652981023535</v>
       </c>
       <c r="D352" t="n">
-        <v>42.2242170723533</v>
+        <v>42.2242133212342</v>
       </c>
       <c r="E352" t="n">
-        <v>43.62653368593358</v>
+        <v>43.62652981023535</v>
       </c>
       <c r="F352" t="n">
         <v>2345809</v>
@@ -7552,16 +7552,16 @@
         <v>44676</v>
       </c>
       <c r="B357" t="n">
-        <v>41.94375228881836</v>
+        <v>41.94374847412109</v>
       </c>
       <c r="C357" t="n">
-        <v>42.40796824528748</v>
+        <v>42.40796438837074</v>
       </c>
       <c r="D357" t="n">
-        <v>40.64782185452133</v>
+        <v>40.64781815768625</v>
       </c>
       <c r="E357" t="n">
-        <v>40.75420428750637</v>
+        <v>40.75420058099602</v>
       </c>
       <c r="F357" t="n">
         <v>3287465</v>
@@ -7592,16 +7592,16 @@
         <v>44678</v>
       </c>
       <c r="B359" t="n">
-        <v>42.16618728637695</v>
+        <v>42.16619110107422</v>
       </c>
       <c r="C359" t="n">
-        <v>43.58784506009413</v>
+        <v>43.58784900340616</v>
       </c>
       <c r="D359" t="n">
-        <v>41.46986526445734</v>
+        <v>41.46986901615963</v>
       </c>
       <c r="E359" t="n">
-        <v>43.52014885542929</v>
+        <v>43.52015279261696</v>
       </c>
       <c r="F359" t="n">
         <v>3779727</v>
@@ -7672,16 +7672,16 @@
         <v>44684</v>
       </c>
       <c r="B363" t="n">
-        <v>42.12750244140625</v>
+        <v>42.12749862670898</v>
       </c>
       <c r="C363" t="n">
-        <v>42.54336341820335</v>
+        <v>42.54335956584936</v>
       </c>
       <c r="D363" t="n">
-        <v>41.25710175933607</v>
+        <v>41.25709802345466</v>
       </c>
       <c r="E363" t="n">
-        <v>42.54336341820335</v>
+        <v>42.54335956584936</v>
       </c>
       <c r="F363" t="n">
         <v>4458389</v>
@@ -7692,16 +7692,16 @@
         <v>44685</v>
       </c>
       <c r="B364" t="n">
-        <v>44.10041427612305</v>
+        <v>44.10041809082031</v>
       </c>
       <c r="C364" t="n">
-        <v>44.32285161417975</v>
+        <v>44.32285544811791</v>
       </c>
       <c r="D364" t="n">
-        <v>42.16618567842227</v>
+        <v>42.16618932580826</v>
       </c>
       <c r="E364" t="n">
-        <v>43.04625879095802</v>
+        <v>43.04626251447057</v>
       </c>
       <c r="F364" t="n">
         <v>5759540</v>
@@ -7712,16 +7712,16 @@
         <v>44686</v>
       </c>
       <c r="B365" t="n">
-        <v>42.92053985595703</v>
+        <v>42.92053604125977</v>
       </c>
       <c r="C365" t="n">
-        <v>44.57430384010176</v>
+        <v>44.57429987842104</v>
       </c>
       <c r="D365" t="n">
-        <v>42.01145291457887</v>
+        <v>42.01144918067956</v>
       </c>
       <c r="E365" t="n">
-        <v>44.09074663744735</v>
+        <v>44.09074271874429</v>
       </c>
       <c r="F365" t="n">
         <v>4814532</v>
@@ -7732,16 +7732,16 @@
         <v>44687</v>
       </c>
       <c r="B366" t="n">
-        <v>42.55303573608398</v>
+        <v>42.55303192138672</v>
       </c>
       <c r="C366" t="n">
-        <v>43.90699359626386</v>
+        <v>43.90698966019007</v>
       </c>
       <c r="D366" t="n">
-        <v>41.82769996355259</v>
+        <v>41.82769621387857</v>
       </c>
       <c r="E366" t="n">
-        <v>43.33639522245434</v>
+        <v>43.33639133753226</v>
       </c>
       <c r="F366" t="n">
         <v>4093307</v>
@@ -7892,16 +7892,16 @@
         <v>44699</v>
       </c>
       <c r="B374" t="n">
-        <v>39.99985504150391</v>
+        <v>39.99985122680664</v>
       </c>
       <c r="C374" t="n">
-        <v>42.22421740419406</v>
+        <v>42.2242133773643</v>
       </c>
       <c r="D374" t="n">
-        <v>39.72906271064676</v>
+        <v>39.72905892177436</v>
       </c>
       <c r="E374" t="n">
-        <v>42.13717620908088</v>
+        <v>42.13717219055205</v>
       </c>
       <c r="F374" t="n">
         <v>1865839</v>
@@ -7952,16 +7952,16 @@
         <v>44704</v>
       </c>
       <c r="B377" t="n">
-        <v>42.28224563598633</v>
+        <v>42.28224182128906</v>
       </c>
       <c r="C377" t="n">
-        <v>42.79481657531103</v>
+        <v>42.7948127143697</v>
       </c>
       <c r="D377" t="n">
-        <v>41.35381369972519</v>
+        <v>41.3538099687909</v>
       </c>
       <c r="E377" t="n">
-        <v>41.42151365745766</v>
+        <v>41.42150992041549</v>
       </c>
       <c r="F377" t="n">
         <v>3400119</v>
@@ -8012,16 +8012,16 @@
         <v>44707</v>
       </c>
       <c r="B380" t="n">
-        <v>46.5955696105957</v>
+        <v>46.59557342529297</v>
       </c>
       <c r="C380" t="n">
-        <v>47.1661679572728</v>
+        <v>47.16617181868395</v>
       </c>
       <c r="D380" t="n">
-        <v>45.10621566046026</v>
+        <v>45.10621935322675</v>
       </c>
       <c r="E380" t="n">
-        <v>45.2512805595232</v>
+        <v>45.25128426416589</v>
       </c>
       <c r="F380" t="n">
         <v>4582217</v>
@@ -8072,16 +8072,16 @@
         <v>44712</v>
       </c>
       <c r="B383" t="n">
-        <v>47.14682769775391</v>
+        <v>47.14683151245117</v>
       </c>
       <c r="C383" t="n">
-        <v>49.5452685563496</v>
+        <v>49.54527256510714</v>
       </c>
       <c r="D383" t="n">
-        <v>47.11781396782467</v>
+        <v>47.11781778017441</v>
       </c>
       <c r="E383" t="n">
-        <v>48.22032446240879</v>
+        <v>48.22032836396376</v>
       </c>
       <c r="F383" t="n">
         <v>6322705</v>
@@ -8152,16 +8152,16 @@
         <v>44718</v>
       </c>
       <c r="B387" t="n">
-        <v>45.3189811706543</v>
+        <v>45.31898498535156</v>
       </c>
       <c r="C387" t="n">
-        <v>47.4563021942838</v>
+        <v>47.45630618888874</v>
       </c>
       <c r="D387" t="n">
-        <v>45.13522629971035</v>
+        <v>45.13523009894016</v>
       </c>
       <c r="E387" t="n">
-        <v>47.15649615191405</v>
+        <v>47.156500121283</v>
       </c>
       <c r="F387" t="n">
         <v>1711233</v>
@@ -8172,16 +8172,16 @@
         <v>44719</v>
       </c>
       <c r="B388" t="n">
-        <v>45.3189811706543</v>
+        <v>45.31898498535156</v>
       </c>
       <c r="C388" t="n">
-        <v>45.84122081100923</v>
+        <v>45.84122466966569</v>
       </c>
       <c r="D388" t="n">
-        <v>44.73871032322317</v>
+        <v>44.73871408907649</v>
       </c>
       <c r="E388" t="n">
-        <v>44.98048890609225</v>
+        <v>44.98049269229714</v>
       </c>
       <c r="F388" t="n">
         <v>1887578</v>
@@ -8192,16 +8192,16 @@
         <v>44720</v>
       </c>
       <c r="B389" t="n">
-        <v>45.25128555297852</v>
+        <v>45.25128173828125</v>
       </c>
       <c r="C389" t="n">
-        <v>46.00563510358936</v>
+        <v>46.00563122530019</v>
       </c>
       <c r="D389" t="n">
-        <v>44.92246574936335</v>
+        <v>44.9224619623857</v>
       </c>
       <c r="E389" t="n">
-        <v>45.31898551140559</v>
+        <v>45.31898169100119</v>
       </c>
       <c r="F389" t="n">
         <v>1920490</v>
@@ -8212,16 +8212,16 @@
         <v>44721</v>
       </c>
       <c r="B390" t="n">
-        <v>44.5066032409668</v>
+        <v>44.50660705566406</v>
       </c>
       <c r="C390" t="n">
-        <v>45.59944121195702</v>
+        <v>45.59944512032232</v>
       </c>
       <c r="D390" t="n">
-        <v>44.32285212169327</v>
+        <v>44.32285592064108</v>
       </c>
       <c r="E390" t="n">
-        <v>45.22226648118356</v>
+        <v>45.2222703572209</v>
       </c>
       <c r="F390" t="n">
         <v>1644697</v>
@@ -8472,16 +8472,16 @@
         <v>44741</v>
       </c>
       <c r="B403" t="n">
-        <v>34.71940612792969</v>
+        <v>34.71940994262695</v>
       </c>
       <c r="C403" t="n">
-        <v>35.41572814937177</v>
+        <v>35.41573204057546</v>
       </c>
       <c r="D403" t="n">
-        <v>34.09078031110602</v>
+        <v>34.0907840567348</v>
       </c>
       <c r="E403" t="n">
-        <v>35.29967322993957</v>
+        <v>35.29967710839206</v>
       </c>
       <c r="F403" t="n">
         <v>2690880</v>
@@ -8532,16 +8532,16 @@
         <v>44746</v>
       </c>
       <c r="B406" t="n">
-        <v>35.08691024780273</v>
+        <v>35.08690643310547</v>
       </c>
       <c r="C406" t="n">
-        <v>35.60915366553204</v>
+        <v>35.60914979405575</v>
       </c>
       <c r="D406" t="n">
-        <v>34.1971683099429</v>
+        <v>34.19716459197961</v>
       </c>
       <c r="E406" t="n">
-        <v>34.57433932306729</v>
+        <v>34.57433556409744</v>
       </c>
       <c r="F406" t="n">
         <v>2359523</v>
@@ -8612,16 +8612,16 @@
         <v>44750</v>
       </c>
       <c r="B410" t="n">
-        <v>31.81806373596191</v>
+        <v>31.81806564331055</v>
       </c>
       <c r="C410" t="n">
-        <v>32.48537204040704</v>
+        <v>32.48537398775778</v>
       </c>
       <c r="D410" t="n">
-        <v>31.19911039968697</v>
+        <v>31.19911226993215</v>
       </c>
       <c r="E410" t="n">
-        <v>31.3151653213559</v>
+        <v>31.31516719855805</v>
       </c>
       <c r="F410" t="n">
         <v>4375906</v>
@@ -8712,16 +8712,16 @@
         <v>44757</v>
       </c>
       <c r="B415" t="n">
-        <v>27.79486846923828</v>
+        <v>27.79486656188965</v>
       </c>
       <c r="C415" t="n">
-        <v>29.07146143004599</v>
+        <v>29.07145943509457</v>
       </c>
       <c r="D415" t="n">
-        <v>27.79486846923828</v>
+        <v>27.79486656188965</v>
       </c>
       <c r="E415" t="n">
-        <v>29.06178893688788</v>
+        <v>29.06178694260021</v>
       </c>
       <c r="F415" t="n">
         <v>4618481</v>
@@ -8752,16 +8752,16 @@
         <v>44761</v>
       </c>
       <c r="B417" t="n">
-        <v>29.43896293640137</v>
+        <v>29.43896102905273</v>
       </c>
       <c r="C417" t="n">
-        <v>29.53567474894549</v>
+        <v>29.5356728353309</v>
       </c>
       <c r="D417" t="n">
-        <v>28.11401691328927</v>
+        <v>28.11401509178381</v>
       </c>
       <c r="E417" t="n">
-        <v>28.14303064443129</v>
+        <v>28.14302882104603</v>
       </c>
       <c r="F417" t="n">
         <v>4570230</v>
@@ -8772,16 +8772,16 @@
         <v>44762</v>
       </c>
       <c r="B418" t="n">
-        <v>30.59950065612793</v>
+        <v>30.5994987487793</v>
       </c>
       <c r="C418" t="n">
-        <v>30.97667540990739</v>
+        <v>30.97667347904845</v>
       </c>
       <c r="D418" t="n">
-        <v>29.21652718353251</v>
+        <v>29.21652536238831</v>
       </c>
       <c r="E418" t="n">
-        <v>29.21652718353251</v>
+        <v>29.21652536238831</v>
       </c>
       <c r="F418" t="n">
         <v>5027446</v>
@@ -8792,16 +8792,16 @@
         <v>44763</v>
       </c>
       <c r="B419" t="n">
-        <v>29.44863510131836</v>
+        <v>29.44863319396973</v>
       </c>
       <c r="C419" t="n">
-        <v>29.86449233042948</v>
+        <v>29.86449039614633</v>
       </c>
       <c r="D419" t="n">
-        <v>28.83935237548546</v>
+        <v>28.83935050759925</v>
       </c>
       <c r="E419" t="n">
-        <v>29.86449233042948</v>
+        <v>29.86449039614633</v>
       </c>
       <c r="F419" t="n">
         <v>5437325</v>
@@ -8832,16 +8832,16 @@
         <v>44767</v>
       </c>
       <c r="B421" t="n">
-        <v>29.2648811340332</v>
+        <v>29.26488304138184</v>
       </c>
       <c r="C421" t="n">
-        <v>29.7194245717984</v>
+        <v>29.71942650877206</v>
       </c>
       <c r="D421" t="n">
-        <v>28.43316295561438</v>
+        <v>28.43316480875549</v>
       </c>
       <c r="E421" t="n">
-        <v>28.87803577468757</v>
+        <v>28.87803765682343</v>
       </c>
       <c r="F421" t="n">
         <v>3521914</v>
@@ -8852,16 +8852,16 @@
         <v>44768</v>
       </c>
       <c r="B422" t="n">
-        <v>28.95540428161621</v>
+        <v>28.95540618896484</v>
       </c>
       <c r="C422" t="n">
-        <v>30.15462657412001</v>
+        <v>30.15462856046375</v>
       </c>
       <c r="D422" t="n">
-        <v>28.81033750703789</v>
+        <v>28.81033940483069</v>
       </c>
       <c r="E422" t="n">
-        <v>29.88383426222034</v>
+        <v>29.88383623072646</v>
       </c>
       <c r="F422" t="n">
         <v>2984449</v>
@@ -8872,16 +8872,16 @@
         <v>44769</v>
       </c>
       <c r="B423" t="n">
-        <v>29.66139984130859</v>
+        <v>29.66139793395996</v>
       </c>
       <c r="C423" t="n">
-        <v>29.76778227135207</v>
+        <v>29.76778035716261</v>
       </c>
       <c r="D423" t="n">
-        <v>28.61691490502781</v>
+        <v>28.6169130648438</v>
       </c>
       <c r="E423" t="n">
-        <v>28.95540530688788</v>
+        <v>28.95540344493757</v>
       </c>
       <c r="F423" t="n">
         <v>2554762</v>
@@ -8892,16 +8892,16 @@
         <v>44770</v>
       </c>
       <c r="B424" t="n">
-        <v>30.78325271606445</v>
+        <v>30.78325080871582</v>
       </c>
       <c r="C424" t="n">
-        <v>30.88963514995402</v>
+        <v>30.88963323601387</v>
       </c>
       <c r="D424" t="n">
-        <v>29.53567536735125</v>
+        <v>29.53567353730325</v>
       </c>
       <c r="E424" t="n">
-        <v>29.96120510290952</v>
+        <v>29.96120324649545</v>
       </c>
       <c r="F424" t="n">
         <v>4208906</v>
@@ -8952,16 +8952,16 @@
         <v>44775</v>
       </c>
       <c r="B427" t="n">
-        <v>31.85674858093262</v>
+        <v>31.85675048828125</v>
       </c>
       <c r="C427" t="n">
-        <v>32.0791821744082</v>
+        <v>32.07918409507452</v>
       </c>
       <c r="D427" t="n">
-        <v>30.94765985359998</v>
+        <v>30.94766170651904</v>
       </c>
       <c r="E427" t="n">
-        <v>31.32483458513196</v>
+        <v>31.32483646063348</v>
       </c>
       <c r="F427" t="n">
         <v>3020206</v>
@@ -9072,16 +9072,16 @@
         <v>44783</v>
       </c>
       <c r="B433" t="n">
-        <v>33.26873397827148</v>
+        <v>33.26873779296875</v>
       </c>
       <c r="C433" t="n">
-        <v>33.97472847846024</v>
+        <v>33.97473237410905</v>
       </c>
       <c r="D433" t="n">
-        <v>32.87221800802422</v>
+        <v>32.87222177725572</v>
       </c>
       <c r="E433" t="n">
-        <v>33.62656747451073</v>
+        <v>33.62657133023831</v>
       </c>
       <c r="F433" t="n">
         <v>3325457</v>
@@ -9152,16 +9152,16 @@
         <v>44789</v>
       </c>
       <c r="B437" t="n">
-        <v>32.27260589599609</v>
+        <v>32.27260971069336</v>
       </c>
       <c r="C437" t="n">
-        <v>32.61109815484615</v>
+        <v>32.61110200955398</v>
       </c>
       <c r="D437" t="n">
-        <v>31.73102127989639</v>
+        <v>31.73102503057709</v>
       </c>
       <c r="E437" t="n">
-        <v>32.39832955774229</v>
+        <v>32.39833338730038</v>
       </c>
       <c r="F437" t="n">
         <v>2684074</v>
@@ -9172,16 +9172,16 @@
         <v>44790</v>
       </c>
       <c r="B438" t="n">
-        <v>32.53372955322266</v>
+        <v>32.53372573852539</v>
       </c>
       <c r="C438" t="n">
-        <v>32.93024931741367</v>
+        <v>32.93024545622303</v>
       </c>
       <c r="D438" t="n">
-        <v>31.80839373121048</v>
+        <v>31.80839000156146</v>
       </c>
       <c r="E438" t="n">
-        <v>31.8180662246313</v>
+        <v>31.81806249384815</v>
       </c>
       <c r="F438" t="n">
         <v>3057587</v>
@@ -9252,16 +9252,16 @@
         <v>44796</v>
       </c>
       <c r="B442" t="n">
-        <v>35.11592102050781</v>
+        <v>35.11592483520508</v>
       </c>
       <c r="C442" t="n">
-        <v>35.54145071517264</v>
+        <v>35.54145457609587</v>
       </c>
       <c r="D442" t="n">
-        <v>33.43314347863087</v>
+        <v>33.43314711052539</v>
       </c>
       <c r="E442" t="n">
-        <v>33.46215720759215</v>
+        <v>33.46216084263848</v>
       </c>
       <c r="F442" t="n">
         <v>5706007</v>
@@ -9292,16 +9292,16 @@
         <v>44798</v>
       </c>
       <c r="B444" t="n">
-        <v>35.7348747253418</v>
+        <v>35.73487854003906</v>
       </c>
       <c r="C444" t="n">
-        <v>36.56659288719009</v>
+        <v>36.56659679067325</v>
       </c>
       <c r="D444" t="n">
-        <v>35.39638621377552</v>
+        <v>35.39638999233915</v>
       </c>
       <c r="E444" t="n">
-        <v>35.8606021347718</v>
+        <v>35.86060596289047</v>
       </c>
       <c r="F444" t="n">
         <v>2850362</v>
@@ -9372,16 +9372,16 @@
         <v>44804</v>
       </c>
       <c r="B448" t="n">
-        <v>36.16040420532227</v>
+        <v>36.16040802001953</v>
       </c>
       <c r="C448" t="n">
-        <v>36.46021024107181</v>
+        <v>36.46021408739674</v>
       </c>
       <c r="D448" t="n">
-        <v>35.22230362431106</v>
+        <v>35.22230734004456</v>
       </c>
       <c r="E448" t="n">
-        <v>35.91862562779205</v>
+        <v>35.91862941698318</v>
       </c>
       <c r="F448" t="n">
         <v>3394125</v>
@@ -9392,16 +9392,16 @@
         <v>44805</v>
       </c>
       <c r="B449" t="n">
-        <v>35.58013534545898</v>
+        <v>35.58013916015625</v>
       </c>
       <c r="C449" t="n">
-        <v>36.22810235066332</v>
+        <v>36.22810623483188</v>
       </c>
       <c r="D449" t="n">
-        <v>35.00953703150028</v>
+        <v>35.00954078502128</v>
       </c>
       <c r="E449" t="n">
-        <v>35.8412551468599</v>
+        <v>35.84125898955293</v>
       </c>
       <c r="F449" t="n">
         <v>3340084</v>
@@ -9492,16 +9492,16 @@
         <v>44813</v>
       </c>
       <c r="B454" t="n">
-        <v>35.92830276489258</v>
+        <v>35.92829895019531</v>
       </c>
       <c r="C454" t="n">
-        <v>36.37317375612866</v>
+        <v>36.3731698941971</v>
       </c>
       <c r="D454" t="n">
-        <v>35.60915545100184</v>
+        <v>35.60915167019012</v>
       </c>
       <c r="E454" t="n">
-        <v>35.79290659406839</v>
+        <v>35.79290279374685</v>
       </c>
       <c r="F454" t="n">
         <v>3544465</v>
@@ -9552,16 +9552,16 @@
         <v>44818</v>
       </c>
       <c r="B457" t="n">
-        <v>37.25324630737305</v>
+        <v>37.25325012207031</v>
       </c>
       <c r="C457" t="n">
-        <v>37.57239358328728</v>
+        <v>37.57239743066493</v>
       </c>
       <c r="D457" t="n">
-        <v>35.96698471138824</v>
+        <v>35.96698839437353</v>
       </c>
       <c r="E457" t="n">
-        <v>36.05402215203722</v>
+        <v>36.05402584393507</v>
       </c>
       <c r="F457" t="n">
         <v>4057043</v>
@@ -9592,16 +9592,16 @@
         <v>44820</v>
       </c>
       <c r="B459" t="n">
-        <v>36.79870223999023</v>
+        <v>36.7987060546875</v>
       </c>
       <c r="C459" t="n">
-        <v>36.79870223999023</v>
+        <v>36.7987060546875</v>
       </c>
       <c r="D459" t="n">
-        <v>35.78322922342723</v>
+        <v>35.7832329328566</v>
       </c>
       <c r="E459" t="n">
-        <v>36.14106271488564</v>
+        <v>36.14106646140942</v>
       </c>
       <c r="F459" t="n">
         <v>2974596</v>
@@ -9612,16 +9612,16 @@
         <v>44823</v>
       </c>
       <c r="B460" t="n">
-        <v>36.8470573425293</v>
+        <v>36.84706115722656</v>
       </c>
       <c r="C460" t="n">
-        <v>37.3983144462179</v>
+        <v>37.39831831798563</v>
       </c>
       <c r="D460" t="n">
-        <v>35.7929018485589</v>
+        <v>35.79290555412169</v>
       </c>
       <c r="E460" t="n">
-        <v>35.7929018485589</v>
+        <v>35.79290555412169</v>
       </c>
       <c r="F460" t="n">
         <v>3461677</v>
@@ -9652,16 +9652,16 @@
         <v>44825</v>
       </c>
       <c r="B462" t="n">
-        <v>38.0366096496582</v>
+        <v>38.03661346435547</v>
       </c>
       <c r="C462" t="n">
-        <v>38.79095912196355</v>
+        <v>38.79096301231463</v>
       </c>
       <c r="D462" t="n">
-        <v>37.62074869162363</v>
+        <v>37.62075246461414</v>
       </c>
       <c r="E462" t="n">
-        <v>37.9398959687412</v>
+        <v>37.93989977373904</v>
       </c>
       <c r="F462" t="n">
         <v>4689181</v>
@@ -9732,16 +9732,16 @@
         <v>44831</v>
       </c>
       <c r="B466" t="n">
-        <v>33.61689758300781</v>
+        <v>33.61689376831055</v>
       </c>
       <c r="C466" t="n">
-        <v>34.44861580943209</v>
+        <v>34.44861190035511</v>
       </c>
       <c r="D466" t="n">
-        <v>33.32676401519949</v>
+        <v>33.3267602334253</v>
       </c>
       <c r="E466" t="n">
-        <v>34.44861580943209</v>
+        <v>34.44861190035511</v>
       </c>
       <c r="F466" t="n">
         <v>5480701</v>
@@ -9752,16 +9752,16 @@
         <v>44832</v>
       </c>
       <c r="B467" t="n">
-        <v>34.5743408203125</v>
+        <v>34.57433700561523</v>
       </c>
       <c r="C467" t="n">
-        <v>34.99987431683395</v>
+        <v>34.99987045518622</v>
       </c>
       <c r="D467" t="n">
-        <v>33.19136913623947</v>
+        <v>33.19136547412988</v>
       </c>
       <c r="E467" t="n">
-        <v>33.66525385709685</v>
+        <v>33.66525014270204</v>
       </c>
       <c r="F467" t="n">
         <v>4399676</v>
@@ -9772,16 +9772,16 @@
         <v>44833</v>
       </c>
       <c r="B468" t="n">
-        <v>33.90702819824219</v>
+        <v>33.90703201293945</v>
       </c>
       <c r="C468" t="n">
-        <v>34.69039138641359</v>
+        <v>34.69039528924284</v>
       </c>
       <c r="D468" t="n">
-        <v>33.09465502863428</v>
+        <v>33.09465875193581</v>
       </c>
       <c r="E468" t="n">
-        <v>34.61302269157358</v>
+        <v>34.61302658569848</v>
       </c>
       <c r="F468" t="n">
         <v>4499631</v>
@@ -9812,16 +9812,16 @@
         <v>44837</v>
       </c>
       <c r="B470" t="n">
-        <v>36.79870223999023</v>
+        <v>36.7987060546875</v>
       </c>
       <c r="C470" t="n">
-        <v>36.91475715561467</v>
+        <v>36.91476098234264</v>
       </c>
       <c r="D470" t="n">
-        <v>35.52210941084767</v>
+        <v>35.52211309320833</v>
       </c>
       <c r="E470" t="n">
-        <v>36.26678637509517</v>
+        <v>36.26679013465196</v>
       </c>
       <c r="F470" t="n">
         <v>4419789</v>
@@ -9852,16 +9852,16 @@
         <v>44839</v>
       </c>
       <c r="B472" t="n">
-        <v>41.63427352905273</v>
+        <v>41.63427734375</v>
       </c>
       <c r="C472" t="n">
-        <v>42.48533291211138</v>
+        <v>42.48533680478608</v>
       </c>
       <c r="D472" t="n">
-        <v>40.55110431601417</v>
+        <v>40.55110803146717</v>
       </c>
       <c r="E472" t="n">
-        <v>40.61880426561678</v>
+        <v>40.61880798727272</v>
       </c>
       <c r="F472" t="n">
         <v>6927519</v>
@@ -9892,16 +9892,16 @@
         <v>44841</v>
       </c>
       <c r="B474" t="n">
-        <v>41.47954177856445</v>
+        <v>41.47953796386719</v>
       </c>
       <c r="C474" t="n">
-        <v>42.45632495390688</v>
+        <v>42.45632104937901</v>
       </c>
       <c r="D474" t="n">
-        <v>41.22809067776815</v>
+        <v>41.22808688619578</v>
       </c>
       <c r="E474" t="n">
-        <v>41.59559296175236</v>
+        <v>41.59558913638236</v>
       </c>
       <c r="F474" t="n">
         <v>3503020</v>
@@ -10072,16 +10072,16 @@
         <v>44855</v>
       </c>
       <c r="B483" t="n">
-        <v>44.22613906860352</v>
+        <v>44.22614288330078</v>
       </c>
       <c r="C483" t="n">
-        <v>44.68068250090031</v>
+        <v>44.68068635480393</v>
       </c>
       <c r="D483" t="n">
-        <v>42.41763783177974</v>
+        <v>42.41764149048589</v>
       </c>
       <c r="E483" t="n">
-        <v>42.96889119740864</v>
+        <v>42.9688949036628</v>
       </c>
       <c r="F483" t="n">
         <v>5360835</v>
@@ -10112,16 +10112,16 @@
         <v>44859</v>
       </c>
       <c r="B485" t="n">
-        <v>42.69809722900391</v>
+        <v>42.69810104370117</v>
       </c>
       <c r="C485" t="n">
-        <v>44.7193669863075</v>
+        <v>44.71937098158734</v>
       </c>
       <c r="D485" t="n">
-        <v>42.52401860625056</v>
+        <v>42.52402240539543</v>
       </c>
       <c r="E485" t="n">
-        <v>43.43310543554394</v>
+        <v>43.43310931590769</v>
       </c>
       <c r="F485" t="n">
         <v>3364870</v>
@@ -10232,16 +10232,16 @@
         <v>44868</v>
       </c>
       <c r="B491" t="n">
-        <v>46.30543518066406</v>
+        <v>46.30543899536133</v>
       </c>
       <c r="C491" t="n">
-        <v>46.4311588402996</v>
+        <v>46.43116266535413</v>
       </c>
       <c r="D491" t="n">
-        <v>44.51627522669133</v>
+        <v>44.51627889399545</v>
       </c>
       <c r="E491" t="n">
-        <v>44.98048739191887</v>
+        <v>44.98049109746535</v>
       </c>
       <c r="F491" t="n">
         <v>3262984</v>
@@ -10312,16 +10312,16 @@
         <v>44874</v>
       </c>
       <c r="B495" t="n">
-        <v>44.69035339355469</v>
+        <v>44.69035720825195</v>
       </c>
       <c r="C495" t="n">
-        <v>46.49885831321781</v>
+        <v>46.49886228228617</v>
       </c>
       <c r="D495" t="n">
-        <v>44.23580997752845</v>
+        <v>44.23581375342662</v>
       </c>
       <c r="E495" t="n">
-        <v>45.35766165335595</v>
+        <v>45.35766552501359</v>
       </c>
       <c r="F495" t="n">
         <v>4884014</v>
@@ -10332,16 +10332,16 @@
         <v>44875</v>
       </c>
       <c r="B496" t="n">
-        <v>42.0598030090332</v>
+        <v>42.05980682373047</v>
       </c>
       <c r="C496" t="n">
-        <v>44.68068109462947</v>
+        <v>44.68068514703247</v>
       </c>
       <c r="D496" t="n">
-        <v>41.64394206412777</v>
+        <v>41.6439458411077</v>
       </c>
       <c r="E496" t="n">
-        <v>43.65554309181744</v>
+        <v>43.65554705124352</v>
       </c>
       <c r="F496" t="n">
         <v>5453172</v>
@@ -10472,16 +10472,16 @@
         <v>44887</v>
       </c>
       <c r="B503" t="n">
-        <v>35.7252082824707</v>
+        <v>35.72520446777344</v>
       </c>
       <c r="C503" t="n">
-        <v>38.01726681069696</v>
+        <v>38.01726275125628</v>
       </c>
       <c r="D503" t="n">
-        <v>35.41572973267442</v>
+        <v>35.41572595102293</v>
       </c>
       <c r="E503" t="n">
-        <v>37.37897222043525</v>
+        <v>37.37896822915095</v>
       </c>
       <c r="F503" t="n">
         <v>4879239</v>
@@ -10492,16 +10492,16 @@
         <v>44888</v>
       </c>
       <c r="B504" t="n">
-        <v>34.29387664794922</v>
+        <v>34.29388046264648</v>
       </c>
       <c r="C504" t="n">
-        <v>35.59947950993321</v>
+        <v>35.59948346985989</v>
       </c>
       <c r="D504" t="n">
-        <v>33.84900195222058</v>
+        <v>33.84900571743197</v>
       </c>
       <c r="E504" t="n">
-        <v>35.37704590964446</v>
+        <v>35.37704984482862</v>
       </c>
       <c r="F504" t="n">
         <v>5644348</v>
@@ -10532,16 +10532,16 @@
         <v>44890</v>
       </c>
       <c r="B506" t="n">
-        <v>34.2358512878418</v>
+        <v>34.23584747314453</v>
       </c>
       <c r="C506" t="n">
-        <v>36.49889988516448</v>
+        <v>36.49889581830917</v>
       </c>
       <c r="D506" t="n">
-        <v>34.11012761496025</v>
+        <v>34.11012381427162</v>
       </c>
       <c r="E506" t="n">
-        <v>36.17008008946956</v>
+        <v>36.17007605925269</v>
       </c>
       <c r="F506" t="n">
         <v>4398253</v>
@@ -10552,16 +10552,16 @@
         <v>44893</v>
       </c>
       <c r="B507" t="n">
-        <v>33.64591217041016</v>
+        <v>33.64590835571289</v>
       </c>
       <c r="C507" t="n">
-        <v>34.11012813925738</v>
+        <v>34.11012427192836</v>
       </c>
       <c r="D507" t="n">
-        <v>32.92057635865081</v>
+        <v>32.92057262619048</v>
       </c>
       <c r="E507" t="n">
-        <v>33.36544734092983</v>
+        <v>33.36544355803103</v>
       </c>
       <c r="F507" t="n">
         <v>4077054</v>
@@ -10652,16 +10652,16 @@
         <v>44900</v>
       </c>
       <c r="B512" t="n">
-        <v>34.04242706298828</v>
+        <v>34.04242324829102</v>
       </c>
       <c r="C512" t="n">
-        <v>35.879945891439</v>
+        <v>35.87994187083461</v>
       </c>
       <c r="D512" t="n">
-        <v>33.77163473568869</v>
+        <v>33.77163095133564</v>
       </c>
       <c r="E512" t="n">
-        <v>35.57046733984986</v>
+        <v>35.57046335392476</v>
       </c>
       <c r="F512" t="n">
         <v>5158181</v>
@@ -10732,16 +10732,16 @@
         <v>44904</v>
       </c>
       <c r="B516" t="n">
-        <v>31.69233894348145</v>
+        <v>31.69234085083008</v>
       </c>
       <c r="C516" t="n">
-        <v>32.74649445099531</v>
+        <v>32.74649642178647</v>
       </c>
       <c r="D516" t="n">
-        <v>31.48924283777486</v>
+        <v>31.4892447329005</v>
       </c>
       <c r="E516" t="n">
-        <v>32.22425106961099</v>
+        <v>32.22425300897184</v>
       </c>
       <c r="F516" t="n">
         <v>2885712</v>
@@ -10752,16 +10752,16 @@
         <v>44907</v>
       </c>
       <c r="B517" t="n">
-        <v>32.23392105102539</v>
+        <v>32.23392486572266</v>
       </c>
       <c r="C517" t="n">
-        <v>32.41767215777701</v>
+        <v>32.41767599422015</v>
       </c>
       <c r="D517" t="n">
-        <v>31.06371071712008</v>
+        <v>31.06371439332975</v>
       </c>
       <c r="E517" t="n">
-        <v>31.59562280181559</v>
+        <v>31.59562654097396</v>
       </c>
       <c r="F517" t="n">
         <v>3445728</v>
@@ -10772,16 +10772,16 @@
         <v>44908</v>
       </c>
       <c r="B518" t="n">
-        <v>32.52405548095703</v>
+        <v>32.5240592956543</v>
       </c>
       <c r="C518" t="n">
-        <v>33.41380105995531</v>
+        <v>33.41380497900949</v>
       </c>
       <c r="D518" t="n">
-        <v>31.9824708896037</v>
+        <v>31.98247464077933</v>
       </c>
       <c r="E518" t="n">
-        <v>32.39832807738018</v>
+        <v>32.39833187733107</v>
       </c>
       <c r="F518" t="n">
         <v>3369136</v>
@@ -10872,16 +10872,16 @@
         <v>44915</v>
       </c>
       <c r="B523" t="n">
-        <v>31.63431358337402</v>
+        <v>31.63431167602539</v>
       </c>
       <c r="C523" t="n">
-        <v>31.83740595497857</v>
+        <v>31.83740403538475</v>
       </c>
       <c r="D523" t="n">
-        <v>30.62851484937437</v>
+        <v>30.62851300266902</v>
       </c>
       <c r="E523" t="n">
-        <v>30.76391101296931</v>
+        <v>30.76390915810044</v>
       </c>
       <c r="F523" t="n">
         <v>3472546</v>
@@ -10892,16 +10892,16 @@
         <v>44916</v>
       </c>
       <c r="B524" t="n">
-        <v>32.19524002075195</v>
+        <v>32.19523620605469</v>
       </c>
       <c r="C524" t="n">
-        <v>32.50471857745117</v>
+        <v>32.50471472608491</v>
       </c>
       <c r="D524" t="n">
-        <v>31.22812562087756</v>
+        <v>31.22812192077017</v>
       </c>
       <c r="E524" t="n">
-        <v>32.34997742531367</v>
+        <v>32.34997359228213</v>
       </c>
       <c r="F524" t="n">
         <v>3938295</v>
@@ -10912,16 +10912,16 @@
         <v>44917</v>
       </c>
       <c r="B525" t="n">
-        <v>32.0114860534668</v>
+        <v>32.01148986816406</v>
       </c>
       <c r="C525" t="n">
-        <v>32.78517675543017</v>
+        <v>32.78518066232546</v>
       </c>
       <c r="D525" t="n">
-        <v>31.5376013885634</v>
+        <v>31.53760514678948</v>
       </c>
       <c r="E525" t="n">
-        <v>32.41767451520204</v>
+        <v>32.41767837830338</v>
       </c>
       <c r="F525" t="n">
         <v>3822391</v>
@@ -10932,16 +10932,16 @@
         <v>44918</v>
       </c>
       <c r="B526" t="n">
-        <v>34.68072509765625</v>
+        <v>34.68072128295898</v>
       </c>
       <c r="C526" t="n">
-        <v>34.88381746754605</v>
+        <v>34.88381363050969</v>
       </c>
       <c r="D526" t="n">
-        <v>32.68846888482701</v>
+        <v>32.68846528926745</v>
       </c>
       <c r="E526" t="n">
-        <v>33.17202607250107</v>
+        <v>33.17202242375276</v>
       </c>
       <c r="F526" t="n">
         <v>6955860</v>
@@ -11012,16 +11012,16 @@
         <v>44924</v>
       </c>
       <c r="B530" t="n">
-        <v>36.50856399536133</v>
+        <v>36.50856781005859</v>
       </c>
       <c r="C530" t="n">
-        <v>37.23389970387844</v>
+        <v>37.23390359436439</v>
       </c>
       <c r="D530" t="n">
-        <v>35.61882215744662</v>
+        <v>35.61882587917678</v>
       </c>
       <c r="E530" t="n">
-        <v>35.87994196319169</v>
+        <v>35.87994571220566</v>
       </c>
       <c r="F530" t="n">
         <v>4887264</v>
@@ -11032,16 +11032,16 @@
         <v>44928</v>
       </c>
       <c r="B531" t="n">
-        <v>35.21263885498047</v>
+        <v>35.2126350402832</v>
       </c>
       <c r="C531" t="n">
-        <v>36.68265172299981</v>
+        <v>36.68264774905137</v>
       </c>
       <c r="D531" t="n">
-        <v>34.78710911009928</v>
+        <v>34.78710534150101</v>
       </c>
       <c r="E531" t="n">
-        <v>36.01534337329287</v>
+        <v>36.01533947163607</v>
       </c>
       <c r="F531" t="n">
         <v>2924313</v>
@@ -11152,16 +11152,16 @@
         <v>44936</v>
       </c>
       <c r="B537" t="n">
-        <v>37.79483413696289</v>
+        <v>37.79483032226562</v>
       </c>
       <c r="C537" t="n">
-        <v>38.07529521496675</v>
+        <v>38.07529137196207</v>
       </c>
       <c r="D537" t="n">
-        <v>36.49889993855829</v>
+        <v>36.49889625466188</v>
       </c>
       <c r="E537" t="n">
-        <v>37.09850831958851</v>
+        <v>37.0985045751726</v>
       </c>
       <c r="F537" t="n">
         <v>3183751</v>
@@ -11192,16 +11192,16 @@
         <v>44938</v>
       </c>
       <c r="B539" t="n">
-        <v>43.42343521118164</v>
+        <v>43.42343902587891</v>
       </c>
       <c r="C539" t="n">
-        <v>44.72904181410123</v>
+        <v>44.7290457434945</v>
       </c>
       <c r="D539" t="n">
-        <v>43.19132911953119</v>
+        <v>43.19133291383822</v>
       </c>
       <c r="E539" t="n">
-        <v>43.40409397377132</v>
+        <v>43.40409778676949</v>
       </c>
       <c r="F539" t="n">
         <v>7341055</v>
@@ -11212,16 +11212,16 @@
         <v>44939</v>
       </c>
       <c r="B540" t="n">
-        <v>42.75613021850586</v>
+        <v>42.75612640380859</v>
       </c>
       <c r="C540" t="n">
-        <v>43.50080726582102</v>
+        <v>43.50080338468374</v>
       </c>
       <c r="D540" t="n">
-        <v>42.35961420932546</v>
+        <v>42.35961043000531</v>
       </c>
       <c r="E540" t="n">
-        <v>43.42343856263282</v>
+        <v>43.42343468839838</v>
       </c>
       <c r="F540" t="n">
         <v>4249336</v>
@@ -11272,16 +11272,16 @@
         <v>44944</v>
       </c>
       <c r="B543" t="n">
-        <v>44.53562164306641</v>
+        <v>44.53561782836914</v>
       </c>
       <c r="C543" t="n">
-        <v>45.24161621271021</v>
+        <v>45.241612337541</v>
       </c>
       <c r="D543" t="n">
-        <v>43.22034619346439</v>
+        <v>43.220342491427</v>
       </c>
       <c r="E543" t="n">
-        <v>43.42343857092518</v>
+        <v>43.42343485149192</v>
       </c>
       <c r="F543" t="n">
         <v>6730959</v>
@@ -11332,16 +11332,16 @@
         <v>44949</v>
       </c>
       <c r="B546" t="n">
-        <v>46.45050811767578</v>
+        <v>46.45050430297852</v>
       </c>
       <c r="C546" t="n">
-        <v>48.53947429699662</v>
+        <v>48.53947031074529</v>
       </c>
       <c r="D546" t="n">
-        <v>45.88958222216792</v>
+        <v>45.88957845353607</v>
       </c>
       <c r="E546" t="n">
-        <v>47.67874234150205</v>
+        <v>47.67873842593739</v>
       </c>
       <c r="F546" t="n">
         <v>5971946</v>
@@ -11392,16 +11392,16 @@
         <v>44952</v>
       </c>
       <c r="B549" t="n">
-        <v>45.26095581054688</v>
+        <v>45.26095199584961</v>
       </c>
       <c r="C549" t="n">
-        <v>46.77932358255676</v>
+        <v>46.77931963988798</v>
       </c>
       <c r="D549" t="n">
-        <v>45.24161457234137</v>
+        <v>45.24161075927422</v>
       </c>
       <c r="E549" t="n">
-        <v>45.92826413060603</v>
+        <v>45.92826025966649</v>
       </c>
       <c r="F549" t="n">
         <v>3327082</v>
@@ -11412,16 +11412,16 @@
         <v>44953</v>
       </c>
       <c r="B550" t="n">
-        <v>44.5066032409668</v>
+        <v>44.50660705566406</v>
       </c>
       <c r="C550" t="n">
-        <v>46.34412192885299</v>
+        <v>46.34412590104548</v>
       </c>
       <c r="D550" t="n">
-        <v>44.16811098394805</v>
+        <v>44.16811476963287</v>
       </c>
       <c r="E550" t="n">
-        <v>46.20872577556058</v>
+        <v>46.20872973614816</v>
       </c>
       <c r="F550" t="n">
         <v>4035914</v>
@@ -11432,16 +11432,16 @@
         <v>44956</v>
       </c>
       <c r="B551" t="n">
-        <v>43.79094314575195</v>
+        <v>43.79093933105469</v>
       </c>
       <c r="C551" t="n">
-        <v>44.43890648207057</v>
+        <v>44.43890261092821</v>
       </c>
       <c r="D551" t="n">
-        <v>43.13330356893655</v>
+        <v>43.13329981152729</v>
       </c>
       <c r="E551" t="n">
-        <v>44.31318281197527</v>
+        <v>44.3131789517849</v>
       </c>
       <c r="F551" t="n">
         <v>3870439</v>
@@ -11572,16 +11572,16 @@
         <v>44965</v>
       </c>
       <c r="B558" t="n">
-        <v>43.12362670898438</v>
+        <v>43.12363052368164</v>
       </c>
       <c r="C558" t="n">
-        <v>43.13329920092593</v>
+        <v>43.13330301647882</v>
       </c>
       <c r="D558" t="n">
-        <v>42.08881622667597</v>
+        <v>42.08881994983436</v>
       </c>
       <c r="E558" t="n">
-        <v>42.57237336739773</v>
+        <v>42.57237713333137</v>
       </c>
       <c r="F558" t="n">
         <v>2757212</v>
@@ -11672,16 +11672,16 @@
         <v>44972</v>
       </c>
       <c r="B563" t="n">
-        <v>40.04821014404297</v>
+        <v>40.0482063293457</v>
       </c>
       <c r="C563" t="n">
-        <v>40.52209485081966</v>
+        <v>40.52209099098364</v>
       </c>
       <c r="D563" t="n">
-        <v>38.90701335343782</v>
+        <v>38.90700964744255</v>
       </c>
       <c r="E563" t="n">
-        <v>38.92635833968847</v>
+        <v>38.92635463185054</v>
       </c>
       <c r="F563" t="n">
         <v>3495706</v>
@@ -11752,16 +11752,16 @@
         <v>44980</v>
       </c>
       <c r="B567" t="n">
-        <v>38.00759887695312</v>
+        <v>38.00759506225586</v>
       </c>
       <c r="C567" t="n">
-        <v>39.07142321677222</v>
+        <v>39.07141929530241</v>
       </c>
       <c r="D567" t="n">
-        <v>37.73680654543994</v>
+        <v>37.7368027579212</v>
       </c>
       <c r="E567" t="n">
-        <v>37.95924390652058</v>
+        <v>37.95924009667655</v>
       </c>
       <c r="F567" t="n">
         <v>3548732</v>
@@ -11812,16 +11812,16 @@
         <v>44985</v>
       </c>
       <c r="B570" t="n">
-        <v>35.21263885498047</v>
+        <v>35.2126350402832</v>
       </c>
       <c r="C570" t="n">
-        <v>38.49115688632073</v>
+        <v>38.49115271645117</v>
       </c>
       <c r="D570" t="n">
-        <v>35.21263885498047</v>
+        <v>35.2126350402832</v>
       </c>
       <c r="E570" t="n">
-        <v>37.13719520026616</v>
+        <v>37.13719117707558</v>
       </c>
       <c r="F570" t="n">
         <v>11036876</v>
@@ -11832,16 +11832,16 @@
         <v>44986</v>
       </c>
       <c r="B571" t="n">
-        <v>31.52793121337891</v>
+        <v>31.52792930603027</v>
       </c>
       <c r="C571" t="n">
-        <v>35.21263762145776</v>
+        <v>35.21263549119504</v>
       </c>
       <c r="D571" t="n">
-        <v>29.89350662783602</v>
+        <v>29.89350481936535</v>
       </c>
       <c r="E571" t="n">
-        <v>35.10625518896411</v>
+        <v>35.10625306513723</v>
       </c>
       <c r="F571" t="n">
         <v>24633899</v>
@@ -11872,16 +11872,16 @@
         <v>44988</v>
       </c>
       <c r="B573" t="n">
-        <v>31.74069595336914</v>
+        <v>31.74069404602051</v>
       </c>
       <c r="C573" t="n">
-        <v>31.93411957920744</v>
+        <v>31.93411766023568</v>
       </c>
       <c r="D573" t="n">
-        <v>30.40607743217574</v>
+        <v>30.40607560502645</v>
       </c>
       <c r="E573" t="n">
-        <v>30.47377551384036</v>
+        <v>30.47377368262298</v>
       </c>
       <c r="F573" t="n">
         <v>7573675</v>
@@ -11892,16 +11892,16 @@
         <v>44991</v>
       </c>
       <c r="B574" t="n">
-        <v>31.86642074584961</v>
+        <v>31.86641883850098</v>
       </c>
       <c r="C574" t="n">
-        <v>32.34997795368473</v>
+        <v>32.34997601739302</v>
       </c>
       <c r="D574" t="n">
-        <v>30.94766317523564</v>
+        <v>30.94766132287878</v>
       </c>
       <c r="E574" t="n">
-        <v>31.74069707103675</v>
+        <v>31.74069517121325</v>
       </c>
       <c r="F574" t="n">
         <v>5963007</v>
@@ -11992,16 +11992,16 @@
         <v>44998</v>
       </c>
       <c r="B579" t="n">
-        <v>26.45058059692383</v>
+        <v>26.4505786895752</v>
       </c>
       <c r="C579" t="n">
-        <v>27.32098316598858</v>
+        <v>27.32098119587531</v>
       </c>
       <c r="D579" t="n">
-        <v>25.76392728704381</v>
+        <v>25.76392542920967</v>
       </c>
       <c r="E579" t="n">
-        <v>26.59564737946998</v>
+        <v>26.59564546166059</v>
       </c>
       <c r="F579" t="n">
         <v>13860726</v>
@@ -12032,16 +12032,16 @@
         <v>45000</v>
       </c>
       <c r="B581" t="n">
-        <v>26.28616905212402</v>
+        <v>26.28617095947266</v>
       </c>
       <c r="C581" t="n">
-        <v>26.82775179788365</v>
+        <v>26.82775374453002</v>
       </c>
       <c r="D581" t="n">
-        <v>25.62853138858268</v>
+        <v>25.62853324821252</v>
       </c>
       <c r="E581" t="n">
-        <v>26.58597321755539</v>
+        <v>26.58597514665809</v>
       </c>
       <c r="F581" t="n">
         <v>12174787</v>
@@ -12072,16 +12072,16 @@
         <v>45002</v>
       </c>
       <c r="B583" t="n">
-        <v>30.70588302612305</v>
+        <v>30.70588111877441</v>
       </c>
       <c r="C583" t="n">
-        <v>30.88963415624145</v>
+        <v>30.8896322374788</v>
       </c>
       <c r="D583" t="n">
-        <v>27.73684184447329</v>
+        <v>27.73684012155175</v>
       </c>
       <c r="E583" t="n">
-        <v>30.45443194157511</v>
+        <v>30.45443004984579</v>
       </c>
       <c r="F583" t="n">
         <v>23193684</v>
@@ -12092,16 +12092,16 @@
         <v>45005</v>
       </c>
       <c r="B584" t="n">
-        <v>29.79679489135742</v>
+        <v>29.79679679870605</v>
       </c>
       <c r="C584" t="n">
-        <v>31.20878203377826</v>
+        <v>31.20878403151084</v>
       </c>
       <c r="D584" t="n">
-        <v>29.32290834641774</v>
+        <v>29.32291022343201</v>
       </c>
       <c r="E584" t="n">
-        <v>30.70588175921954</v>
+        <v>30.70588372476053</v>
       </c>
       <c r="F584" t="n">
         <v>7729094</v>
@@ -12252,16 +12252,16 @@
         <v>45015</v>
       </c>
       <c r="B592" t="n">
-        <v>29.38093376159668</v>
+        <v>29.38093566894531</v>
       </c>
       <c r="C592" t="n">
-        <v>30.51245796745546</v>
+        <v>30.51245994826028</v>
       </c>
       <c r="D592" t="n">
-        <v>29.2745513361352</v>
+        <v>29.27455323657771</v>
       </c>
       <c r="E592" t="n">
-        <v>29.95153211069714</v>
+        <v>29.95153405508782</v>
       </c>
       <c r="F592" t="n">
         <v>5560645</v>
@@ -12312,16 +12312,16 @@
         <v>45020</v>
       </c>
       <c r="B595" t="n">
-        <v>27.92059135437012</v>
+        <v>27.92059326171875</v>
       </c>
       <c r="C595" t="n">
-        <v>29.70975320425825</v>
+        <v>29.70975523383049</v>
       </c>
       <c r="D595" t="n">
-        <v>27.91092073592187</v>
+        <v>27.91092264260987</v>
       </c>
       <c r="E595" t="n">
-        <v>29.57435705083184</v>
+        <v>29.57435907115471</v>
       </c>
       <c r="F595" t="n">
         <v>7552242</v>
@@ -12332,16 +12332,16 @@
         <v>45021</v>
       </c>
       <c r="B596" t="n">
-        <v>26.76972770690918</v>
+        <v>26.76972579956055</v>
       </c>
       <c r="C596" t="n">
-        <v>27.8528951326722</v>
+        <v>27.85289314814766</v>
       </c>
       <c r="D596" t="n">
-        <v>26.23781367622606</v>
+        <v>26.23781180677641</v>
       </c>
       <c r="E596" t="n">
-        <v>27.65947338188658</v>
+        <v>27.65947141114338</v>
       </c>
       <c r="F596" t="n">
         <v>12382825</v>
@@ -12372,16 +12372,16 @@
         <v>45026</v>
       </c>
       <c r="B598" t="n">
-        <v>29.6517276763916</v>
+        <v>29.65172576904297</v>
       </c>
       <c r="C598" t="n">
-        <v>29.83547880780963</v>
+        <v>29.8354768886412</v>
       </c>
       <c r="D598" t="n">
-        <v>28.19138549654949</v>
+        <v>28.19138368313743</v>
       </c>
       <c r="E598" t="n">
-        <v>28.33645227786835</v>
+        <v>28.33645045512486</v>
       </c>
       <c r="F598" t="n">
         <v>8774363</v>
@@ -12552,16 +12552,16 @@
         <v>45040</v>
       </c>
       <c r="B607" t="n">
-        <v>26.96700477600098</v>
+        <v>26.96700286865234</v>
       </c>
       <c r="C607" t="n">
-        <v>27.07506799883479</v>
+        <v>27.07506608384296</v>
       </c>
       <c r="D607" t="n">
-        <v>26.23020138729918</v>
+        <v>26.23019953206389</v>
       </c>
       <c r="E607" t="n">
-        <v>26.86876394941649</v>
+        <v>26.86876204901633</v>
       </c>
       <c r="F607" t="n">
         <v>6680100</v>
@@ -12572,16 +12572,16 @@
         <v>45041</v>
       </c>
       <c r="B608" t="n">
-        <v>27.21260261535645</v>
+        <v>27.21260452270508</v>
       </c>
       <c r="C608" t="n">
-        <v>27.45820371522866</v>
+        <v>27.45820563979163</v>
       </c>
       <c r="D608" t="n">
-        <v>26.42667797149275</v>
+        <v>26.42667982375542</v>
       </c>
       <c r="E608" t="n">
-        <v>26.79999269261962</v>
+        <v>26.79999457104816</v>
       </c>
       <c r="F608" t="n">
         <v>5323000</v>
@@ -12612,16 +12612,16 @@
         <v>45043</v>
       </c>
       <c r="B610" t="n">
-        <v>29.90439414978027</v>
+        <v>29.90439224243164</v>
       </c>
       <c r="C610" t="n">
-        <v>30.26788277330051</v>
+        <v>30.267880842768</v>
       </c>
       <c r="D610" t="n">
-        <v>26.73122612224756</v>
+        <v>26.73122441728851</v>
       </c>
       <c r="E610" t="n">
-        <v>26.73122612224756</v>
+        <v>26.73122441728851</v>
       </c>
       <c r="F610" t="n">
         <v>20933600</v>
@@ -12672,16 +12672,16 @@
         <v>45049</v>
       </c>
       <c r="B613" t="n">
-        <v>29.14794158935547</v>
+        <v>29.14793968200684</v>
       </c>
       <c r="C613" t="n">
-        <v>29.61949529963673</v>
+        <v>29.61949336143113</v>
       </c>
       <c r="D613" t="n">
-        <v>28.33254592932366</v>
+        <v>28.33254407533193</v>
       </c>
       <c r="E613" t="n">
-        <v>29.26583095381972</v>
+        <v>29.26582903875679</v>
       </c>
       <c r="F613" t="n">
         <v>9250000</v>
@@ -12692,16 +12692,16 @@
         <v>45050</v>
       </c>
       <c r="B614" t="n">
-        <v>29.27565383911133</v>
+        <v>29.2756519317627</v>
       </c>
       <c r="C614" t="n">
-        <v>29.95351348008578</v>
+        <v>29.95351152857367</v>
       </c>
       <c r="D614" t="n">
-        <v>29.17741488650197</v>
+        <v>29.17741298555374</v>
       </c>
       <c r="E614" t="n">
-        <v>29.47213549190587</v>
+        <v>29.47213357175619</v>
       </c>
       <c r="F614" t="n">
         <v>6670900</v>
@@ -12792,16 +12792,16 @@
         <v>45057</v>
       </c>
       <c r="B619" t="n">
-        <v>31.66289710998535</v>
+        <v>31.66289520263672</v>
       </c>
       <c r="C619" t="n">
-        <v>31.81025928645763</v>
+        <v>31.81025737023202</v>
       </c>
       <c r="D619" t="n">
-        <v>31.10292683551199</v>
+        <v>31.10292496189554</v>
       </c>
       <c r="E619" t="n">
-        <v>31.71201658628417</v>
+        <v>31.71201467597662</v>
       </c>
       <c r="F619" t="n">
         <v>4858000</v>
@@ -12812,16 +12812,16 @@
         <v>45058</v>
       </c>
       <c r="B620" t="n">
-        <v>32.49794387817383</v>
+        <v>32.49794006347656</v>
       </c>
       <c r="C620" t="n">
-        <v>32.64530231015733</v>
+        <v>32.64529847816273</v>
       </c>
       <c r="D620" t="n">
-        <v>31.46641611640984</v>
+        <v>31.46641242279611</v>
       </c>
       <c r="E620" t="n">
-        <v>31.55483267463029</v>
+        <v>31.554828970638</v>
       </c>
       <c r="F620" t="n">
         <v>5317000</v>
@@ -12852,16 +12852,16 @@
         <v>45062</v>
       </c>
       <c r="B622" t="n">
-        <v>29.90439414978027</v>
+        <v>29.90439224243164</v>
       </c>
       <c r="C622" t="n">
-        <v>32.08533151226543</v>
+        <v>32.08532946581322</v>
       </c>
       <c r="D622" t="n">
-        <v>29.70791249602647</v>
+        <v>29.70791060120974</v>
       </c>
       <c r="E622" t="n">
-        <v>31.86920131837866</v>
+        <v>31.86919928571158</v>
       </c>
       <c r="F622" t="n">
         <v>13269700</v>
@@ -12912,16 +12912,16 @@
         <v>45065</v>
       </c>
       <c r="B625" t="n">
-        <v>32.49794387817383</v>
+        <v>32.49794006347656</v>
       </c>
       <c r="C625" t="n">
-        <v>34.87536105853923</v>
+        <v>34.87535696477425</v>
       </c>
       <c r="D625" t="n">
-        <v>31.0439837395418</v>
+        <v>31.04398009551434</v>
       </c>
       <c r="E625" t="n">
-        <v>31.86920182661951</v>
+        <v>31.8691980857257</v>
       </c>
       <c r="F625" t="n">
         <v>19443700</v>
@@ -12972,16 +12972,16 @@
         <v>45070</v>
       </c>
       <c r="B628" t="n">
-        <v>31.48606109619141</v>
+        <v>31.48606300354004</v>
       </c>
       <c r="C628" t="n">
-        <v>31.86919822262693</v>
+        <v>31.86920015318507</v>
       </c>
       <c r="D628" t="n">
-        <v>30.46436146776744</v>
+        <v>30.464363313224</v>
       </c>
       <c r="E628" t="n">
-        <v>31.04398022887067</v>
+        <v>31.04398210943912</v>
       </c>
       <c r="F628" t="n">
         <v>7685200</v>
@@ -13212,16 +13212,16 @@
         <v>45089</v>
       </c>
       <c r="B640" t="n">
-        <v>31.26011085510254</v>
+        <v>31.26010894775391</v>
       </c>
       <c r="C640" t="n">
-        <v>31.86920059509758</v>
+        <v>31.86919865058509</v>
       </c>
       <c r="D640" t="n">
-        <v>30.47418800549994</v>
+        <v>30.47418614610471</v>
       </c>
       <c r="E640" t="n">
-        <v>31.61377707431765</v>
+        <v>31.61377514538992</v>
       </c>
       <c r="F640" t="n">
         <v>7223600</v>
@@ -13252,16 +13252,16 @@
         <v>45091</v>
       </c>
       <c r="B642" t="n">
-        <v>31.14222145080566</v>
+        <v>31.1422233581543</v>
       </c>
       <c r="C642" t="n">
-        <v>31.71201407641177</v>
+        <v>31.71201601865814</v>
       </c>
       <c r="D642" t="n">
-        <v>30.5724269514118</v>
+        <v>30.57242882386257</v>
       </c>
       <c r="E642" t="n">
-        <v>31.33870121423831</v>
+        <v>31.33870313362062</v>
       </c>
       <c r="F642" t="n">
         <v>8288400</v>
@@ -13292,16 +13292,16 @@
         <v>45093</v>
       </c>
       <c r="B644" t="n">
-        <v>31.9183235168457</v>
+        <v>31.91832160949707</v>
       </c>
       <c r="C644" t="n">
-        <v>31.9183235168457</v>
+        <v>31.91832160949707</v>
       </c>
       <c r="D644" t="n">
-        <v>31.19134254558997</v>
+        <v>31.19134068168367</v>
       </c>
       <c r="E644" t="n">
-        <v>31.4271193982454</v>
+        <v>31.42711752024974</v>
       </c>
       <c r="F644" t="n">
         <v>5722800</v>
@@ -13332,16 +13332,16 @@
         <v>45097</v>
       </c>
       <c r="B646" t="n">
-        <v>32.16392517089844</v>
+        <v>32.16392135620117</v>
       </c>
       <c r="C646" t="n">
-        <v>32.2916350584061</v>
+        <v>32.29163122856222</v>
       </c>
       <c r="D646" t="n">
-        <v>31.48606366340425</v>
+        <v>31.48605992910253</v>
       </c>
       <c r="E646" t="n">
-        <v>32.12462809124572</v>
+        <v>32.12462428120915</v>
       </c>
       <c r="F646" t="n">
         <v>4954700</v>
@@ -13352,16 +13352,16 @@
         <v>45098</v>
       </c>
       <c r="B647" t="n">
-        <v>32.06567764282227</v>
+        <v>32.06568145751953</v>
       </c>
       <c r="C647" t="n">
-        <v>32.36039820068254</v>
+        <v>32.36040205044127</v>
       </c>
       <c r="D647" t="n">
-        <v>31.4860589217478</v>
+        <v>31.48606266749066</v>
       </c>
       <c r="E647" t="n">
-        <v>32.1246232534244</v>
+        <v>32.12462707513414</v>
       </c>
       <c r="F647" t="n">
         <v>4670300</v>
@@ -13412,16 +13412,16 @@
         <v>45103</v>
       </c>
       <c r="B650" t="n">
-        <v>30.53312873840332</v>
+        <v>30.53313064575195</v>
       </c>
       <c r="C650" t="n">
-        <v>30.83767357835474</v>
+        <v>30.83767550472773</v>
       </c>
       <c r="D650" t="n">
-        <v>30.30717617565832</v>
+        <v>30.30717806889212</v>
       </c>
       <c r="E650" t="n">
-        <v>30.58224820898695</v>
+        <v>30.58225011940398</v>
       </c>
       <c r="F650" t="n">
         <v>2874500</v>
@@ -13452,16 +13452,16 @@
         <v>45105</v>
       </c>
       <c r="B652" t="n">
-        <v>29.37389373779297</v>
+        <v>29.37389183044434</v>
       </c>
       <c r="C652" t="n">
-        <v>30.06157762706682</v>
+        <v>30.06157567506449</v>
       </c>
       <c r="D652" t="n">
-        <v>29.30512572362315</v>
+        <v>29.30512382073987</v>
       </c>
       <c r="E652" t="n">
-        <v>29.75703276126285</v>
+        <v>29.75703082903567</v>
       </c>
       <c r="F652" t="n">
         <v>4532500</v>
@@ -13532,16 +13532,16 @@
         <v>45111</v>
       </c>
       <c r="B656" t="n">
-        <v>29.80615043640137</v>
+        <v>29.80615234375</v>
       </c>
       <c r="C656" t="n">
-        <v>30.15981662939312</v>
+        <v>30.15981855937348</v>
       </c>
       <c r="D656" t="n">
-        <v>29.57037359900278</v>
+        <v>29.57037549126363</v>
       </c>
       <c r="E656" t="n">
-        <v>29.80615043640137</v>
+        <v>29.80615234375</v>
       </c>
       <c r="F656" t="n">
         <v>2514900</v>
@@ -13552,16 +13552,16 @@
         <v>45112</v>
       </c>
       <c r="B657" t="n">
-        <v>30.40541839599609</v>
+        <v>30.40542030334473</v>
       </c>
       <c r="C657" t="n">
-        <v>30.70996325002402</v>
+        <v>30.70996517647691</v>
       </c>
       <c r="D657" t="n">
-        <v>29.34442166777476</v>
+        <v>29.34442350856649</v>
       </c>
       <c r="E657" t="n">
-        <v>29.60966944448926</v>
+        <v>29.60967130192012</v>
       </c>
       <c r="F657" t="n">
         <v>5394800</v>
@@ -13612,16 +13612,16 @@
         <v>45117</v>
       </c>
       <c r="B660" t="n">
-        <v>31.07345199584961</v>
+        <v>31.07345390319824</v>
       </c>
       <c r="C660" t="n">
-        <v>31.93796708924193</v>
+        <v>31.93796904965617</v>
       </c>
       <c r="D660" t="n">
-        <v>30.84749942157282</v>
+        <v>30.84750131505205</v>
       </c>
       <c r="E660" t="n">
-        <v>31.56465609569361</v>
+        <v>31.56465803319331</v>
       </c>
       <c r="F660" t="n">
         <v>7339200</v>
@@ -13652,16 +13652,16 @@
         <v>45119</v>
       </c>
       <c r="B662" t="n">
-        <v>31.07345199584961</v>
+        <v>31.07345390319824</v>
       </c>
       <c r="C662" t="n">
-        <v>32.08532925608902</v>
+        <v>32.08533122554864</v>
       </c>
       <c r="D662" t="n">
-        <v>31.04398106151042</v>
+        <v>31.04398296705007</v>
       </c>
       <c r="E662" t="n">
-        <v>31.77096013121909</v>
+        <v>31.77096208138212</v>
       </c>
       <c r="F662" t="n">
         <v>4503800</v>
@@ -13732,16 +13732,16 @@
         <v>45125</v>
       </c>
       <c r="B666" t="n">
-        <v>32.91055297851562</v>
+        <v>32.91054916381836</v>
       </c>
       <c r="C666" t="n">
-        <v>33.03826662148488</v>
+        <v>33.03826279198419</v>
       </c>
       <c r="D666" t="n">
-        <v>32.03621351392245</v>
+        <v>32.0362098005708</v>
       </c>
       <c r="E666" t="n">
-        <v>32.18357195035527</v>
+        <v>32.18356821992315</v>
       </c>
       <c r="F666" t="n">
         <v>4775600</v>
@@ -13752,16 +13752,16 @@
         <v>45126</v>
       </c>
       <c r="B667" t="n">
-        <v>33.6473503112793</v>
+        <v>33.64735412597656</v>
       </c>
       <c r="C667" t="n">
-        <v>34.04031356576963</v>
+        <v>34.04031742501827</v>
       </c>
       <c r="D667" t="n">
-        <v>33.04808303459044</v>
+        <v>33.04808678134705</v>
       </c>
       <c r="E667" t="n">
-        <v>33.04808303459044</v>
+        <v>33.04808678134705</v>
       </c>
       <c r="F667" t="n">
         <v>7484200</v>
@@ -13772,16 +13772,16 @@
         <v>45127</v>
       </c>
       <c r="B668" t="n">
-        <v>33.92242813110352</v>
+        <v>33.92242431640625</v>
       </c>
       <c r="C668" t="n">
-        <v>34.11890979188617</v>
+        <v>34.11890595509385</v>
       </c>
       <c r="D668" t="n">
-        <v>33.64735605455338</v>
+        <v>33.64735227078894</v>
       </c>
       <c r="E668" t="n">
-        <v>33.91260573447357</v>
+        <v>33.91260192088087</v>
       </c>
       <c r="F668" t="n">
         <v>3587900</v>
@@ -13952,16 +13952,16 @@
         <v>45140</v>
       </c>
       <c r="B677" t="n">
-        <v>34.4431037902832</v>
+        <v>34.44309997558594</v>
       </c>
       <c r="C677" t="n">
-        <v>34.5806398233511</v>
+        <v>34.58063599342123</v>
       </c>
       <c r="D677" t="n">
-        <v>33.71612279718397</v>
+        <v>33.71611906300245</v>
       </c>
       <c r="E677" t="n">
-        <v>34.38415817000732</v>
+        <v>34.38415436183849</v>
       </c>
       <c r="F677" t="n">
         <v>3408800</v>
@@ -14012,16 +14012,16 @@
         <v>45145</v>
       </c>
       <c r="B680" t="n">
-        <v>35.68092727661133</v>
+        <v>35.68093109130859</v>
       </c>
       <c r="C680" t="n">
-        <v>36.15248093584172</v>
+        <v>36.15248480095344</v>
       </c>
       <c r="D680" t="n">
-        <v>35.09148613946717</v>
+        <v>35.09148989114647</v>
       </c>
       <c r="E680" t="n">
-        <v>36.05424199550948</v>
+        <v>36.05424585011833</v>
       </c>
       <c r="F680" t="n">
         <v>3820600</v>
@@ -14032,16 +14032,16 @@
         <v>45146</v>
       </c>
       <c r="B681" t="n">
-        <v>36.34896469116211</v>
+        <v>36.34896850585938</v>
       </c>
       <c r="C681" t="n">
-        <v>36.51597164901496</v>
+        <v>36.51597548123902</v>
       </c>
       <c r="D681" t="n">
-        <v>34.30556163401185</v>
+        <v>34.30556523426109</v>
       </c>
       <c r="E681" t="n">
-        <v>34.76729292525891</v>
+        <v>34.76729657396523</v>
       </c>
       <c r="F681" t="n">
         <v>5274900</v>
@@ -14172,16 +14172,16 @@
         <v>45155</v>
       </c>
       <c r="B688" t="n">
-        <v>31.26993370056152</v>
+        <v>31.26993560791016</v>
       </c>
       <c r="C688" t="n">
-        <v>31.74148926263102</v>
+        <v>31.74149119874277</v>
       </c>
       <c r="D688" t="n">
-        <v>30.9653888444364</v>
+        <v>30.96539073320894</v>
       </c>
       <c r="E688" t="n">
-        <v>31.46641346711834</v>
+        <v>31.4664153864515</v>
       </c>
       <c r="F688" t="n">
         <v>4529600</v>
@@ -14252,16 +14252,16 @@
         <v>45161</v>
       </c>
       <c r="B692" t="n">
-        <v>31.05380630493164</v>
+        <v>31.05380439758301</v>
       </c>
       <c r="C692" t="n">
-        <v>31.2404618075605</v>
+        <v>31.24045988874735</v>
       </c>
       <c r="D692" t="n">
-        <v>30.68049155209822</v>
+        <v>30.68048966767887</v>
       </c>
       <c r="E692" t="n">
-        <v>31.09310150987904</v>
+        <v>31.09309960011686</v>
       </c>
       <c r="F692" t="n">
         <v>4847400</v>
@@ -14272,16 +14272,16 @@
         <v>45162</v>
       </c>
       <c r="B693" t="n">
-        <v>30.91626930236816</v>
+        <v>30.91626739501953</v>
       </c>
       <c r="C693" t="n">
-        <v>31.30923260599883</v>
+        <v>31.30923067440671</v>
       </c>
       <c r="D693" t="n">
-        <v>30.56260495240363</v>
+        <v>30.56260306687397</v>
       </c>
       <c r="E693" t="n">
-        <v>31.05380720815405</v>
+        <v>31.05380529232016</v>
       </c>
       <c r="F693" t="n">
         <v>3471700</v>
@@ -14332,16 +14332,16 @@
         <v>45167</v>
       </c>
       <c r="B696" t="n">
-        <v>31.29940795898438</v>
+        <v>31.29940605163574</v>
       </c>
       <c r="C696" t="n">
-        <v>31.55483147996431</v>
+        <v>31.55482955705047</v>
       </c>
       <c r="D696" t="n">
-        <v>30.63137259940515</v>
+        <v>30.63137073276579</v>
       </c>
       <c r="E696" t="n">
-        <v>31.06363110391898</v>
+        <v>31.06362921093831</v>
       </c>
       <c r="F696" t="n">
         <v>3743200</v>
@@ -14352,16 +14352,16 @@
         <v>45168</v>
       </c>
       <c r="B697" t="n">
-        <v>31.6334228515625</v>
+        <v>31.63342475891113</v>
       </c>
       <c r="C697" t="n">
-        <v>31.70219086067396</v>
+        <v>31.70219277216898</v>
       </c>
       <c r="D697" t="n">
-        <v>30.96538755084366</v>
+        <v>30.96538941791287</v>
       </c>
       <c r="E697" t="n">
-        <v>31.49588683333958</v>
+        <v>31.49588873239543</v>
       </c>
       <c r="F697" t="n">
         <v>3276100</v>
@@ -14412,16 +14412,16 @@
         <v>45173</v>
       </c>
       <c r="B700" t="n">
-        <v>32.2719841003418</v>
+        <v>32.27198791503906</v>
       </c>
       <c r="C700" t="n">
-        <v>32.55688228511206</v>
+        <v>32.55688613348561</v>
       </c>
       <c r="D700" t="n">
-        <v>32.06568006898767</v>
+        <v>32.06568385929886</v>
       </c>
       <c r="E700" t="n">
-        <v>32.22286462824446</v>
+        <v>32.22286843713558</v>
       </c>
       <c r="F700" t="n">
         <v>2652900</v>
@@ -14432,16 +14432,16 @@
         <v>45174</v>
       </c>
       <c r="B701" t="n">
-        <v>32.63547515869141</v>
+        <v>32.63547897338867</v>
       </c>
       <c r="C701" t="n">
-        <v>32.93019572729314</v>
+        <v>32.93019957643972</v>
       </c>
       <c r="D701" t="n">
-        <v>32.07550495407551</v>
+        <v>32.07550870331895</v>
       </c>
       <c r="E701" t="n">
-        <v>32.27198283475976</v>
+        <v>32.27198660696912</v>
       </c>
       <c r="F701" t="n">
         <v>6036900</v>
@@ -14452,16 +14452,16 @@
         <v>45175</v>
       </c>
       <c r="B702" t="n">
-        <v>32.00674057006836</v>
+        <v>32.00673675537109</v>
       </c>
       <c r="C702" t="n">
-        <v>32.71406926527997</v>
+        <v>32.71406536628031</v>
       </c>
       <c r="D702" t="n">
-        <v>31.92814641083608</v>
+        <v>31.928142605506</v>
       </c>
       <c r="E702" t="n">
-        <v>32.65512739343153</v>
+        <v>32.65512350145682</v>
       </c>
       <c r="F702" t="n">
         <v>4505300</v>
@@ -14512,16 +14512,16 @@
         <v>45181</v>
       </c>
       <c r="B705" t="n">
-        <v>32.3309326171875</v>
+        <v>32.33092880249023</v>
       </c>
       <c r="C705" t="n">
-        <v>32.6453017639165</v>
+        <v>32.64529791212711</v>
       </c>
       <c r="D705" t="n">
-        <v>31.76113994408213</v>
+        <v>31.76113619661418</v>
       </c>
       <c r="E705" t="n">
-        <v>31.97726639022342</v>
+        <v>31.97726261725491</v>
       </c>
       <c r="F705" t="n">
         <v>3620500</v>
@@ -14532,16 +14532,16 @@
         <v>45182</v>
       </c>
       <c r="B706" t="n">
-        <v>31.6334228515625</v>
+        <v>31.63342475891113</v>
       </c>
       <c r="C706" t="n">
-        <v>32.11479891534272</v>
+        <v>32.1148008517161</v>
       </c>
       <c r="D706" t="n">
-        <v>31.44676361462388</v>
+        <v>31.44676551071783</v>
       </c>
       <c r="E706" t="n">
-        <v>31.60394817081799</v>
+        <v>31.60395007638945</v>
       </c>
       <c r="F706" t="n">
         <v>7302700</v>
@@ -14552,16 +14552,16 @@
         <v>45183</v>
       </c>
       <c r="B707" t="n">
-        <v>32.311279296875</v>
+        <v>32.31128311157227</v>
       </c>
       <c r="C707" t="n">
-        <v>32.311279296875</v>
+        <v>32.31128311157227</v>
       </c>
       <c r="D707" t="n">
-        <v>31.74148670806588</v>
+        <v>31.74149045549294</v>
       </c>
       <c r="E707" t="n">
-        <v>31.83972564654409</v>
+        <v>31.83972940556933</v>
       </c>
       <c r="F707" t="n">
         <v>4362300</v>
@@ -14592,16 +14592,16 @@
         <v>45187</v>
       </c>
       <c r="B709" t="n">
-        <v>31.98709297180176</v>
+        <v>31.98709106445312</v>
       </c>
       <c r="C709" t="n">
-        <v>32.71407022822005</v>
+        <v>32.7140682775227</v>
       </c>
       <c r="D709" t="n">
-        <v>31.75131423474054</v>
+        <v>31.75131234145109</v>
       </c>
       <c r="E709" t="n">
-        <v>32.55688565270453</v>
+        <v>32.5568837113799</v>
       </c>
       <c r="F709" t="n">
         <v>5099000</v>
@@ -14692,16 +14692,16 @@
         <v>45194</v>
       </c>
       <c r="B714" t="n">
-        <v>30.95556640625</v>
+        <v>30.95556449890137</v>
       </c>
       <c r="C714" t="n">
-        <v>31.20116753431566</v>
+        <v>31.20116561183414</v>
       </c>
       <c r="D714" t="n">
-        <v>29.99281043394172</v>
+        <v>29.99280858591396</v>
       </c>
       <c r="E714" t="n">
-        <v>30.45453988014151</v>
+        <v>30.45453800366397</v>
       </c>
       <c r="F714" t="n">
         <v>6350700</v>
@@ -14712,16 +14712,16 @@
         <v>45195</v>
       </c>
       <c r="B715" t="n">
-        <v>30.32682800292969</v>
+        <v>30.32682609558105</v>
       </c>
       <c r="C715" t="n">
-        <v>30.83767692328888</v>
+        <v>30.83767498381136</v>
       </c>
       <c r="D715" t="n">
-        <v>30.19911436749897</v>
+        <v>30.19911246818264</v>
       </c>
       <c r="E715" t="n">
-        <v>30.75908463755763</v>
+        <v>30.75908270302303</v>
       </c>
       <c r="F715" t="n">
         <v>3433500</v>
@@ -14732,16 +14732,16 @@
         <v>45196</v>
       </c>
       <c r="B716" t="n">
-        <v>30.86714744567871</v>
+        <v>30.86714935302734</v>
       </c>
       <c r="C716" t="n">
-        <v>31.07345147776449</v>
+        <v>31.0734533978611</v>
       </c>
       <c r="D716" t="n">
-        <v>30.42506470008381</v>
+        <v>30.42506658011519</v>
       </c>
       <c r="E716" t="n">
-        <v>30.65101914438107</v>
+        <v>30.65102103837466</v>
       </c>
       <c r="F716" t="n">
         <v>4307600</v>
@@ -14752,16 +14752,16 @@
         <v>45197</v>
       </c>
       <c r="B717" t="n">
-        <v>30.58225059509277</v>
+        <v>30.58224868774414</v>
       </c>
       <c r="C717" t="n">
-        <v>31.21099073558775</v>
+        <v>31.21098878902595</v>
       </c>
       <c r="D717" t="n">
-        <v>30.41524175877521</v>
+        <v>30.41523986184255</v>
       </c>
       <c r="E717" t="n">
-        <v>30.82785171474873</v>
+        <v>30.82784979208249</v>
       </c>
       <c r="F717" t="n">
         <v>4298000</v>
@@ -14772,16 +14772,16 @@
         <v>45198</v>
       </c>
       <c r="B718" t="n">
-        <v>31.02433204650879</v>
+        <v>31.02433395385742</v>
       </c>
       <c r="C718" t="n">
-        <v>31.60394894047274</v>
+        <v>31.60395088345571</v>
       </c>
       <c r="D718" t="n">
-        <v>30.47418608643163</v>
+        <v>30.47418795995777</v>
       </c>
       <c r="E718" t="n">
-        <v>30.86714748648674</v>
+        <v>30.86714938417181</v>
       </c>
       <c r="F718" t="n">
         <v>5846000</v>
@@ -14852,16 +14852,16 @@
         <v>45204</v>
       </c>
       <c r="B722" t="n">
-        <v>28.0378246307373</v>
+        <v>28.03782272338867</v>
       </c>
       <c r="C722" t="n">
-        <v>28.78445038319864</v>
+        <v>28.78444842505877</v>
       </c>
       <c r="D722" t="n">
-        <v>27.72345362458937</v>
+        <v>27.72345173862667</v>
       </c>
       <c r="E722" t="n">
-        <v>28.62726581701858</v>
+        <v>28.62726386957162</v>
       </c>
       <c r="F722" t="n">
         <v>8409300</v>
@@ -14912,16 +14912,16 @@
         <v>45209</v>
       </c>
       <c r="B725" t="n">
-        <v>30.2777042388916</v>
+        <v>30.27770614624023</v>
       </c>
       <c r="C725" t="n">
-        <v>30.40541786413846</v>
+        <v>30.40541977953243</v>
       </c>
       <c r="D725" t="n">
-        <v>29.43283582930937</v>
+        <v>29.43283768343539</v>
       </c>
       <c r="E725" t="n">
-        <v>29.7570310901109</v>
+        <v>29.75703296465965</v>
       </c>
       <c r="F725" t="n">
         <v>7018100</v>
@@ -14972,16 +14972,16 @@
         <v>45215</v>
       </c>
       <c r="B728" t="n">
-        <v>31.67272186279297</v>
+        <v>31.67271995544434</v>
       </c>
       <c r="C728" t="n">
-        <v>32.01656192935982</v>
+        <v>32.01656000130495</v>
       </c>
       <c r="D728" t="n">
-        <v>31.32887804865046</v>
+        <v>31.32887616200829</v>
       </c>
       <c r="E728" t="n">
-        <v>31.91832298107662</v>
+        <v>31.91832105893775</v>
       </c>
       <c r="F728" t="n">
         <v>3741500</v>
@@ -15012,16 +15012,16 @@
         <v>45217</v>
       </c>
       <c r="B730" t="n">
-        <v>32.06567764282227</v>
+        <v>32.06568145751953</v>
       </c>
       <c r="C730" t="n">
-        <v>33.06773053760736</v>
+        <v>33.06773447151397</v>
       </c>
       <c r="D730" t="n">
-        <v>31.63342107446555</v>
+        <v>31.63342483773936</v>
       </c>
       <c r="E730" t="n">
-        <v>32.52740889026767</v>
+        <v>32.52741275989484</v>
       </c>
       <c r="F730" t="n">
         <v>7439800</v>
@@ -15132,16 +15132,16 @@
         <v>45225</v>
       </c>
       <c r="B736" t="n">
-        <v>31.98709297180176</v>
+        <v>31.98709106445312</v>
       </c>
       <c r="C736" t="n">
-        <v>32.12462900693085</v>
+        <v>32.12462709138111</v>
       </c>
       <c r="D736" t="n">
-        <v>31.19134395024304</v>
+        <v>31.19134209034388</v>
       </c>
       <c r="E736" t="n">
-        <v>31.57448111883861</v>
+        <v>31.57447923609348</v>
       </c>
       <c r="F736" t="n">
         <v>2923500</v>
@@ -15152,16 +15152,16 @@
         <v>45226</v>
       </c>
       <c r="B737" t="n">
-        <v>31.52536010742188</v>
+        <v>31.52535820007324</v>
       </c>
       <c r="C737" t="n">
-        <v>32.55688406826494</v>
+        <v>32.556882098507</v>
       </c>
       <c r="D737" t="n">
-        <v>31.24046190704763</v>
+        <v>31.24046001693592</v>
       </c>
       <c r="E737" t="n">
-        <v>32.32110909025403</v>
+        <v>32.32110713476096</v>
       </c>
       <c r="F737" t="n">
         <v>3378100</v>
@@ -15172,16 +15172,16 @@
         <v>45229</v>
       </c>
       <c r="B738" t="n">
-        <v>31.07345199584961</v>
+        <v>31.07345390319824</v>
       </c>
       <c r="C738" t="n">
-        <v>32.11480019042821</v>
+        <v>32.11480216169681</v>
       </c>
       <c r="D738" t="n">
-        <v>30.98503731904426</v>
+        <v>30.98503922096583</v>
       </c>
       <c r="E738" t="n">
-        <v>31.5450075569423</v>
+        <v>31.54500949323592</v>
       </c>
       <c r="F738" t="n">
         <v>3227500</v>
@@ -15192,16 +15192,16 @@
         <v>45230</v>
       </c>
       <c r="B739" t="n">
-        <v>31.86919975280762</v>
+        <v>31.86919784545898</v>
       </c>
       <c r="C739" t="n">
-        <v>32.10497847524474</v>
+        <v>32.10497655378492</v>
       </c>
       <c r="D739" t="n">
-        <v>31.2011662851952</v>
+        <v>31.20116441782789</v>
       </c>
       <c r="E739" t="n">
-        <v>31.2011662851952</v>
+        <v>31.20116441782789</v>
       </c>
       <c r="F739" t="n">
         <v>3372100</v>
@@ -15212,16 +15212,16 @@
         <v>45231</v>
       </c>
       <c r="B740" t="n">
-        <v>32.06567764282227</v>
+        <v>32.06568145751953</v>
       </c>
       <c r="C740" t="n">
-        <v>32.74353904823363</v>
+        <v>32.74354294357276</v>
       </c>
       <c r="D740" t="n">
-        <v>31.9477901691932</v>
+        <v>31.94779396986597</v>
       </c>
       <c r="E740" t="n">
-        <v>32.07550378504357</v>
+        <v>32.0755076009098</v>
       </c>
       <c r="F740" t="n">
         <v>4282500</v>
@@ -15232,16 +15232,16 @@
         <v>45233</v>
       </c>
       <c r="B741" t="n">
-        <v>32.69441986083984</v>
+        <v>32.69441604614258</v>
       </c>
       <c r="C741" t="n">
-        <v>32.94984712401398</v>
+        <v>32.94984327951414</v>
       </c>
       <c r="D741" t="n">
-        <v>32.46846728038622</v>
+        <v>32.4684634920525</v>
       </c>
       <c r="E741" t="n">
-        <v>32.73371693941674</v>
+        <v>32.7337131201344</v>
       </c>
       <c r="F741" t="n">
         <v>3190300</v>
@@ -15272,16 +15272,16 @@
         <v>45237</v>
       </c>
       <c r="B743" t="n">
-        <v>32.48811721801758</v>
+        <v>32.48811340332031</v>
       </c>
       <c r="C743" t="n">
-        <v>32.63547939523581</v>
+        <v>32.63547556323554</v>
       </c>
       <c r="D743" t="n">
-        <v>31.81025944748058</v>
+        <v>31.81025571237618</v>
       </c>
       <c r="E743" t="n">
-        <v>31.8790274641622</v>
+        <v>31.87902372098318</v>
       </c>
       <c r="F743" t="n">
         <v>3324000</v>
@@ -15312,16 +15312,16 @@
         <v>45239</v>
       </c>
       <c r="B745" t="n">
-        <v>30.81802749633789</v>
+        <v>30.81802940368652</v>
       </c>
       <c r="C745" t="n">
-        <v>33.77506502697286</v>
+        <v>33.77506711733456</v>
       </c>
       <c r="D745" t="n">
-        <v>30.67066533422895</v>
+        <v>30.67066723245724</v>
       </c>
       <c r="E745" t="n">
-        <v>33.41157269312426</v>
+        <v>33.41157476098916</v>
       </c>
       <c r="F745" t="n">
         <v>15431300</v>
@@ -15332,16 +15332,16 @@
         <v>45240</v>
       </c>
       <c r="B746" t="n">
-        <v>31.25028610229492</v>
+        <v>31.25028419494629</v>
       </c>
       <c r="C746" t="n">
-        <v>32.06568174882637</v>
+        <v>32.06567979171039</v>
       </c>
       <c r="D746" t="n">
-        <v>31.04398206013306</v>
+        <v>31.04398016537612</v>
       </c>
       <c r="E746" t="n">
-        <v>31.05380632982475</v>
+        <v>31.05380443446818</v>
       </c>
       <c r="F746" t="n">
         <v>4738300</v>
@@ -15352,16 +15352,16 @@
         <v>45243</v>
       </c>
       <c r="B747" t="n">
-        <v>30.94573974609375</v>
+        <v>30.94574165344238</v>
       </c>
       <c r="C747" t="n">
-        <v>31.41729342584897</v>
+        <v>31.41729536226194</v>
       </c>
       <c r="D747" t="n">
-        <v>30.67066582934266</v>
+        <v>30.67066771973704</v>
       </c>
       <c r="E747" t="n">
-        <v>31.21098939362647</v>
+        <v>31.21099131732383</v>
       </c>
       <c r="F747" t="n">
         <v>3172300</v>
@@ -15392,16 +15392,16 @@
         <v>45246</v>
       </c>
       <c r="B749" t="n">
-        <v>31.13239860534668</v>
+        <v>31.13239669799805</v>
       </c>
       <c r="C749" t="n">
-        <v>32.13444975439192</v>
+        <v>32.13444778565191</v>
       </c>
       <c r="D749" t="n">
-        <v>30.68049156858774</v>
+        <v>30.68048968892551</v>
       </c>
       <c r="E749" t="n">
-        <v>31.78078354073604</v>
+        <v>31.78078159366364</v>
       </c>
       <c r="F749" t="n">
         <v>5148500</v>
@@ -15492,16 +15492,16 @@
         <v>45253</v>
       </c>
       <c r="B754" t="n">
-        <v>31.81025505065918</v>
+        <v>31.81025886535645</v>
       </c>
       <c r="C754" t="n">
-        <v>32.00673667726713</v>
+        <v>32.00674051552654</v>
       </c>
       <c r="D754" t="n">
-        <v>31.5843024917114</v>
+        <v>31.58430627931235</v>
       </c>
       <c r="E754" t="n">
-        <v>31.82990358807751</v>
+        <v>31.82990740513103</v>
       </c>
       <c r="F754" t="n">
         <v>2086300</v>
@@ -15552,16 +15552,16 @@
         <v>45258</v>
       </c>
       <c r="B757" t="n">
-        <v>29.80615043640137</v>
+        <v>29.80615234375</v>
       </c>
       <c r="C757" t="n">
-        <v>30.21876037029583</v>
+        <v>30.21876230404811</v>
       </c>
       <c r="D757" t="n">
-        <v>29.63914160902057</v>
+        <v>29.63914350568201</v>
       </c>
       <c r="E757" t="n">
-        <v>30.17946329383553</v>
+        <v>30.17946522507312</v>
       </c>
       <c r="F757" t="n">
         <v>5777500</v>
@@ -15592,16 +15592,16 @@
         <v>45260</v>
       </c>
       <c r="B759" t="n">
-        <v>29.45248603820801</v>
+        <v>29.45248413085938</v>
       </c>
       <c r="C759" t="n">
-        <v>29.83562506189301</v>
+        <v>29.83562312973222</v>
       </c>
       <c r="D759" t="n">
-        <v>29.1774139813743</v>
+        <v>29.17741209183939</v>
       </c>
       <c r="E759" t="n">
-        <v>29.66861622433489</v>
+        <v>29.66861430298963</v>
       </c>
       <c r="F759" t="n">
         <v>4483800</v>
@@ -15732,16 +15732,16 @@
         <v>45271</v>
       </c>
       <c r="B766" t="n">
-        <v>26.91788101196289</v>
+        <v>26.91788291931152</v>
       </c>
       <c r="C766" t="n">
-        <v>27.08488984004369</v>
+        <v>27.08489175922624</v>
       </c>
       <c r="D766" t="n">
-        <v>26.48562253802652</v>
+        <v>26.48562441474616</v>
       </c>
       <c r="E766" t="n">
-        <v>26.96700235774415</v>
+        <v>26.96700426857343</v>
       </c>
       <c r="F766" t="n">
         <v>6627000</v>
@@ -15792,16 +15792,16 @@
         <v>45274</v>
       </c>
       <c r="B769" t="n">
-        <v>27.00629997253418</v>
+        <v>27.00629806518555</v>
       </c>
       <c r="C769" t="n">
-        <v>27.20278162563166</v>
+        <v>27.2027797044063</v>
       </c>
       <c r="D769" t="n">
-        <v>26.49544917351107</v>
+        <v>26.49544730224182</v>
       </c>
       <c r="E769" t="n">
-        <v>26.82946685950403</v>
+        <v>26.82946496464443</v>
       </c>
       <c r="F769" t="n">
         <v>14011300</v>
@@ -15812,16 +15812,16 @@
         <v>45275</v>
       </c>
       <c r="B770" t="n">
-        <v>25.8863582611084</v>
+        <v>25.88635635375977</v>
       </c>
       <c r="C770" t="n">
-        <v>27.21260467558413</v>
+        <v>27.21260267051552</v>
       </c>
       <c r="D770" t="n">
-        <v>25.8863582611084</v>
+        <v>25.88635635375977</v>
       </c>
       <c r="E770" t="n">
-        <v>27.16348332761816</v>
+        <v>27.1634813261689</v>
       </c>
       <c r="F770" t="n">
         <v>11924000</v>
@@ -15832,16 +15832,16 @@
         <v>45278</v>
       </c>
       <c r="B771" t="n">
-        <v>26.21055221557617</v>
+        <v>26.21055030822754</v>
       </c>
       <c r="C771" t="n">
-        <v>26.76069820788825</v>
+        <v>26.76069626050536</v>
       </c>
       <c r="D771" t="n">
-        <v>25.94530255232668</v>
+        <v>25.94530066428034</v>
       </c>
       <c r="E771" t="n">
-        <v>26.12213566115967</v>
+        <v>26.12213376024514</v>
       </c>
       <c r="F771" t="n">
         <v>4958200</v>
@@ -15852,16 +15852,16 @@
         <v>45279</v>
       </c>
       <c r="B772" t="n">
-        <v>26.32843780517578</v>
+        <v>26.32843971252441</v>
       </c>
       <c r="C772" t="n">
-        <v>26.52491943942738</v>
+        <v>26.52492136101001</v>
       </c>
       <c r="D772" t="n">
-        <v>26.13195804471192</v>
+        <v>26.13195993782669</v>
       </c>
       <c r="E772" t="n">
-        <v>26.30879114078081</v>
+        <v>26.30879304670615</v>
       </c>
       <c r="F772" t="n">
         <v>3900900</v>
@@ -15872,16 +15872,16 @@
         <v>45280</v>
       </c>
       <c r="B773" t="n">
-        <v>25.85688400268555</v>
+        <v>25.85688591003418</v>
       </c>
       <c r="C773" t="n">
-        <v>26.54456784535201</v>
+        <v>26.54456980342805</v>
       </c>
       <c r="D773" t="n">
-        <v>25.68987517654013</v>
+        <v>25.68987707156926</v>
       </c>
       <c r="E773" t="n">
-        <v>26.54456784535201</v>
+        <v>26.54456980342805</v>
       </c>
       <c r="F773" t="n">
         <v>6168300</v>
@@ -15912,16 +15912,16 @@
         <v>45282</v>
       </c>
       <c r="B775" t="n">
-        <v>25.95512771606445</v>
+        <v>25.95512580871582</v>
       </c>
       <c r="C775" t="n">
-        <v>26.22037738844958</v>
+        <v>26.2203754616087</v>
       </c>
       <c r="D775" t="n">
-        <v>25.79794314141873</v>
+        <v>25.79794124562103</v>
       </c>
       <c r="E775" t="n">
-        <v>26.03372000338731</v>
+        <v>26.03371809026321</v>
       </c>
       <c r="F775" t="n">
         <v>3644200</v>
@@ -16012,16 +16012,16 @@
         <v>45294</v>
       </c>
       <c r="B780" t="n">
-        <v>25.8863582611084</v>
+        <v>25.88635635375977</v>
       </c>
       <c r="C780" t="n">
-        <v>26.28914394549015</v>
+        <v>26.28914200846361</v>
       </c>
       <c r="D780" t="n">
-        <v>25.35585894580298</v>
+        <v>25.35585707754239</v>
       </c>
       <c r="E780" t="n">
-        <v>25.64075714264207</v>
+        <v>25.64075525338972</v>
       </c>
       <c r="F780" t="n">
         <v>5734800</v>
@@ -16052,16 +16052,16 @@
         <v>45296</v>
       </c>
       <c r="B782" t="n">
-        <v>25.68987655639648</v>
+        <v>25.68987464904785</v>
       </c>
       <c r="C782" t="n">
-        <v>25.97477475256549</v>
+        <v>25.97477282406455</v>
       </c>
       <c r="D782" t="n">
-        <v>25.21832285975933</v>
+        <v>25.21832098742127</v>
       </c>
       <c r="E782" t="n">
-        <v>25.36568315573496</v>
+        <v>25.36568127245611</v>
       </c>
       <c r="F782" t="n">
         <v>3417300</v>
@@ -16092,16 +16092,16 @@
         <v>45300</v>
       </c>
       <c r="B784" t="n">
-        <v>28.0181770324707</v>
+        <v>28.01817512512207</v>
       </c>
       <c r="C784" t="n">
-        <v>28.24412961971936</v>
+        <v>28.24412769698892</v>
       </c>
       <c r="D784" t="n">
-        <v>26.7999956667704</v>
+        <v>26.79999384234995</v>
       </c>
       <c r="E784" t="n">
-        <v>27.01612398407939</v>
+        <v>27.01612214494592</v>
       </c>
       <c r="F784" t="n">
         <v>10290300</v>
@@ -16152,16 +16152,16 @@
         <v>45303</v>
       </c>
       <c r="B787" t="n">
-        <v>28.20483016967773</v>
+        <v>28.20483207702637</v>
       </c>
       <c r="C787" t="n">
-        <v>28.86304121001741</v>
+        <v>28.86304316187749</v>
       </c>
       <c r="D787" t="n">
-        <v>27.82169304316834</v>
+        <v>27.82169492460737</v>
       </c>
       <c r="E787" t="n">
-        <v>28.63708864175739</v>
+        <v>28.63709057833746</v>
       </c>
       <c r="F787" t="n">
         <v>5067700</v>
@@ -16172,16 +16172,16 @@
         <v>45306</v>
       </c>
       <c r="B788" t="n">
-        <v>28.52902603149414</v>
+        <v>28.52902793884277</v>
       </c>
       <c r="C788" t="n">
-        <v>28.68621059306261</v>
+        <v>28.68621251092004</v>
       </c>
       <c r="D788" t="n">
-        <v>27.90028591143248</v>
+        <v>27.9002877767458</v>
       </c>
       <c r="E788" t="n">
-        <v>28.06729474232245</v>
+        <v>28.06729661880138</v>
       </c>
       <c r="F788" t="n">
         <v>3859400</v>
@@ -16252,16 +16252,16 @@
         <v>45310</v>
       </c>
       <c r="B792" t="n">
-        <v>29.03005218505859</v>
+        <v>29.03005027770996</v>
       </c>
       <c r="C792" t="n">
-        <v>29.19706102477754</v>
+        <v>29.197059106456</v>
       </c>
       <c r="D792" t="n">
-        <v>28.05747195626752</v>
+        <v>28.0574701128199</v>
       </c>
       <c r="E792" t="n">
-        <v>28.73533158498416</v>
+        <v>28.73532969699943</v>
       </c>
       <c r="F792" t="n">
         <v>7851200</v>
@@ -16312,16 +16312,16 @@
         <v>45315</v>
       </c>
       <c r="B795" t="n">
-        <v>27.86099052429199</v>
+        <v>27.86099243164062</v>
       </c>
       <c r="C795" t="n">
-        <v>28.52902584344861</v>
+        <v>28.52902779653059</v>
       </c>
       <c r="D795" t="n">
-        <v>27.63503607896236</v>
+        <v>27.63503797084227</v>
       </c>
       <c r="E795" t="n">
-        <v>28.04764601880687</v>
+        <v>28.04764793893384</v>
       </c>
       <c r="F795" t="n">
         <v>4070600</v>
@@ -16352,16 +16352,16 @@
         <v>45317</v>
       </c>
       <c r="B797" t="n">
-        <v>28.2441291809082</v>
+        <v>28.24412727355957</v>
       </c>
       <c r="C797" t="n">
-        <v>28.2441291809082</v>
+        <v>28.24412727355957</v>
       </c>
       <c r="D797" t="n">
-        <v>27.50732581097147</v>
+        <v>27.50732395337975</v>
       </c>
       <c r="E797" t="n">
-        <v>27.65468611020124</v>
+        <v>27.65468424265817</v>
       </c>
       <c r="F797" t="n">
         <v>2761100</v>
@@ -16392,16 +16392,16 @@
         <v>45321</v>
       </c>
       <c r="B799" t="n">
-        <v>27.24207496643066</v>
+        <v>27.2420768737793</v>
       </c>
       <c r="C799" t="n">
-        <v>27.54662169525507</v>
+        <v>27.54662362392648</v>
       </c>
       <c r="D799" t="n">
-        <v>26.97682531504984</v>
+        <v>26.97682720382707</v>
       </c>
       <c r="E799" t="n">
-        <v>27.36978859433452</v>
+        <v>27.369790510625</v>
       </c>
       <c r="F799" t="n">
         <v>2184900</v>
@@ -16432,16 +16432,16 @@
         <v>45323</v>
       </c>
       <c r="B801" t="n">
-        <v>26.24002075195312</v>
+        <v>26.24002265930176</v>
       </c>
       <c r="C801" t="n">
-        <v>27.4090825182884</v>
+        <v>27.40908451061442</v>
       </c>
       <c r="D801" t="n">
-        <v>26.10248473489757</v>
+        <v>26.10248663224892</v>
       </c>
       <c r="E801" t="n">
-        <v>27.31084170305399</v>
+        <v>27.31084368823903</v>
       </c>
       <c r="F801" t="n">
         <v>7611700</v>
@@ -16532,16 +16532,16 @@
         <v>45330</v>
       </c>
       <c r="B806" t="n">
-        <v>28.79427337646484</v>
+        <v>28.79427528381348</v>
       </c>
       <c r="C806" t="n">
-        <v>28.81392191481336</v>
+        <v>28.81392382346353</v>
       </c>
       <c r="D806" t="n">
-        <v>27.39925900811183</v>
+        <v>27.39926082305394</v>
       </c>
       <c r="E806" t="n">
-        <v>28.71568109685852</v>
+        <v>28.71568299900116</v>
       </c>
       <c r="F806" t="n">
         <v>6908300</v>
@@ -16552,16 +16552,16 @@
         <v>45331</v>
       </c>
       <c r="B807" t="n">
-        <v>27.69398307800293</v>
+        <v>27.6939811706543</v>
       </c>
       <c r="C807" t="n">
-        <v>28.9121644198793</v>
+        <v>28.9121624286317</v>
       </c>
       <c r="D807" t="n">
-        <v>27.52697423987057</v>
+        <v>27.52697234402422</v>
       </c>
       <c r="E807" t="n">
-        <v>28.83357213568689</v>
+        <v>28.83357014985212</v>
       </c>
       <c r="F807" t="n">
         <v>5513900</v>
@@ -16592,16 +16592,16 @@
         <v>45337</v>
       </c>
       <c r="B809" t="n">
-        <v>28.00835037231445</v>
+        <v>28.00835227966309</v>
       </c>
       <c r="C809" t="n">
-        <v>28.26377574758426</v>
+        <v>28.26377767232718</v>
       </c>
       <c r="D809" t="n">
-        <v>27.28137132291011</v>
+        <v>27.28137318075199</v>
       </c>
       <c r="E809" t="n">
-        <v>27.40908307365115</v>
+        <v>27.40908494019011</v>
       </c>
       <c r="F809" t="n">
         <v>2788300</v>
@@ -16632,16 +16632,16 @@
         <v>45341</v>
       </c>
       <c r="B811" t="n">
-        <v>28.6763858795166</v>
+        <v>28.67638778686523</v>
       </c>
       <c r="C811" t="n">
-        <v>28.76480242825268</v>
+        <v>28.76480434148215</v>
       </c>
       <c r="D811" t="n">
-        <v>28.2343031358362</v>
+        <v>28.23430501378064</v>
       </c>
       <c r="E811" t="n">
-        <v>28.74515388991405</v>
+        <v>28.74515580183664</v>
       </c>
       <c r="F811" t="n">
         <v>1698200</v>
@@ -16672,16 +16672,16 @@
         <v>45343</v>
       </c>
       <c r="B813" t="n">
-        <v>28.92198753356934</v>
+        <v>28.92198944091797</v>
       </c>
       <c r="C813" t="n">
-        <v>28.98093127591061</v>
+        <v>28.98093318714647</v>
       </c>
       <c r="D813" t="n">
-        <v>28.36201729685779</v>
+        <v>28.36201916727748</v>
       </c>
       <c r="E813" t="n">
-        <v>28.63708934364225</v>
+        <v>28.6370912322024</v>
       </c>
       <c r="F813" t="n">
         <v>2751400</v>
@@ -16792,16 +16792,16 @@
         <v>45351</v>
       </c>
       <c r="B819" t="n">
-        <v>27.45820426940918</v>
+        <v>27.45820617675781</v>
       </c>
       <c r="C819" t="n">
-        <v>28.14588623865804</v>
+        <v>28.14588819377561</v>
       </c>
       <c r="D819" t="n">
-        <v>27.45820426940918</v>
+        <v>27.45820617675781</v>
       </c>
       <c r="E819" t="n">
-        <v>27.98870168147043</v>
+        <v>27.98870362566938</v>
       </c>
       <c r="F819" t="n">
         <v>2784300</v>
@@ -16972,16 +16972,16 @@
         <v>45364</v>
       </c>
       <c r="B828" t="n">
-        <v>29.13811492919922</v>
+        <v>29.13811683654785</v>
       </c>
       <c r="C828" t="n">
-        <v>29.36406749594983</v>
+        <v>29.36406941808906</v>
       </c>
       <c r="D828" t="n">
-        <v>28.98093037199986</v>
+        <v>28.98093226905937</v>
       </c>
       <c r="E828" t="n">
-        <v>28.98093037199986</v>
+        <v>28.98093226905937</v>
       </c>
       <c r="F828" t="n">
         <v>2596400</v>
@@ -17032,16 +17032,16 @@
         <v>45369</v>
       </c>
       <c r="B831" t="n">
-        <v>28.98093223571777</v>
+        <v>28.98093032836914</v>
       </c>
       <c r="C831" t="n">
-        <v>29.28547710065286</v>
+        <v>29.28547517326093</v>
       </c>
       <c r="D831" t="n">
-        <v>28.61744175270144</v>
+        <v>28.61743986927554</v>
       </c>
       <c r="E831" t="n">
-        <v>28.77462819379693</v>
+        <v>28.77462630002598</v>
       </c>
       <c r="F831" t="n">
         <v>4710300</v>
@@ -17112,16 +17112,16 @@
         <v>45373</v>
       </c>
       <c r="B835" t="n">
-        <v>29.71773529052734</v>
+        <v>29.71773338317871</v>
       </c>
       <c r="C835" t="n">
-        <v>30.0026334869456</v>
+        <v>30.00263156131158</v>
       </c>
       <c r="D835" t="n">
-        <v>29.28547679800454</v>
+        <v>29.28547491839919</v>
       </c>
       <c r="E835" t="n">
-        <v>29.88474412578926</v>
+        <v>29.88474220772164</v>
       </c>
       <c r="F835" t="n">
         <v>3854000</v>
@@ -17152,16 +17152,16 @@
         <v>45377</v>
       </c>
       <c r="B837" t="n">
-        <v>30.81802749633789</v>
+        <v>30.81802940368652</v>
       </c>
       <c r="C837" t="n">
-        <v>31.22081315885015</v>
+        <v>31.22081509112746</v>
       </c>
       <c r="D837" t="n">
-        <v>30.51348077684796</v>
+        <v>30.51348266534799</v>
       </c>
       <c r="E837" t="n">
-        <v>30.61172159365801</v>
+        <v>30.61172348823823</v>
       </c>
       <c r="F837" t="n">
         <v>3327200</v>
@@ -17172,16 +17172,16 @@
         <v>45378</v>
       </c>
       <c r="B838" t="n">
-        <v>31.48606109619141</v>
+        <v>31.48606300354004</v>
       </c>
       <c r="C838" t="n">
-        <v>31.91832144197546</v>
+        <v>31.91832337550937</v>
       </c>
       <c r="D838" t="n">
-        <v>30.3857691886579</v>
+        <v>30.38577102935353</v>
       </c>
       <c r="E838" t="n">
-        <v>30.65101883332299</v>
+        <v>30.6510206900868</v>
       </c>
       <c r="F838" t="n">
         <v>9071000</v>
@@ -17372,16 +17372,16 @@
         <v>45393</v>
       </c>
       <c r="B848" t="n">
-        <v>35.62198638916016</v>
+        <v>35.62198257446289</v>
       </c>
       <c r="C848" t="n">
-        <v>35.91671074440308</v>
+        <v>35.91670689814429</v>
       </c>
       <c r="D848" t="n">
-        <v>34.59046238853748</v>
+        <v>34.59045868430435</v>
       </c>
       <c r="E848" t="n">
-        <v>34.74764696246498</v>
+        <v>34.74764324139922</v>
       </c>
       <c r="F848" t="n">
         <v>5960900</v>
@@ -17412,16 +17412,16 @@
         <v>45397</v>
       </c>
       <c r="B850" t="n">
-        <v>34.06978607177734</v>
+        <v>34.06978988647461</v>
       </c>
       <c r="C850" t="n">
-        <v>34.52169121201051</v>
+        <v>34.52169507730631</v>
       </c>
       <c r="D850" t="n">
-        <v>33.83400735867823</v>
+        <v>33.83401114697602</v>
       </c>
       <c r="E850" t="n">
-        <v>34.43327466304528</v>
+        <v>34.43327851844133</v>
       </c>
       <c r="F850" t="n">
         <v>4151100</v>
@@ -17472,16 +17472,16 @@
         <v>45400</v>
       </c>
       <c r="B853" t="n">
-        <v>32.3309326171875</v>
+        <v>32.33092880249023</v>
       </c>
       <c r="C853" t="n">
-        <v>33.28386620122118</v>
+        <v>33.28386227408815</v>
       </c>
       <c r="D853" t="n">
-        <v>31.93796930998834</v>
+        <v>31.93796554165645</v>
       </c>
       <c r="E853" t="n">
-        <v>33.00879038715143</v>
+        <v>33.00878649247434</v>
       </c>
       <c r="F853" t="n">
         <v>4478700</v>
@@ -17632,16 +17632,16 @@
         <v>45412</v>
       </c>
       <c r="B861" t="n">
-        <v>32.58635711669922</v>
+        <v>32.58635330200195</v>
       </c>
       <c r="C861" t="n">
-        <v>33.66700436998067</v>
+        <v>33.66700042877825</v>
       </c>
       <c r="D861" t="n">
-        <v>32.43899868278081</v>
+        <v>32.43899488533395</v>
       </c>
       <c r="E861" t="n">
-        <v>33.60805874786774</v>
+        <v>33.60805481356574</v>
       </c>
       <c r="F861" t="n">
         <v>6661700</v>
@@ -29795,16 +29795,36 @@
         <v>19.25</v>
       </c>
       <c r="C1469" t="n">
-        <v>19.51</v>
+        <v>19.51000022888184</v>
       </c>
       <c r="D1469" t="n">
-        <v>18.9</v>
+        <v>18.89999961853027</v>
       </c>
       <c r="E1469" t="n">
         <v>19</v>
       </c>
       <c r="F1469" t="n">
         <v>4257200</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1470" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="C1470" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="D1470" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="E1470" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="F1470" t="n">
+        <v>4890000</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1470"/>
+  <dimension ref="A1:F1471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29812,19 +29812,39 @@
         <v>46302</v>
       </c>
       <c r="B1470" t="n">
-        <v>19.89</v>
+        <v>19.88999938964844</v>
       </c>
       <c r="C1470" t="n">
-        <v>19.99</v>
+        <v>19.98999977111816</v>
       </c>
       <c r="D1470" t="n">
-        <v>19.4</v>
+        <v>19.39999961853027</v>
       </c>
       <c r="E1470" t="n">
-        <v>19.44</v>
+        <v>19.44000053405762</v>
       </c>
       <c r="F1470" t="n">
         <v>4890000</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1471" t="n">
+        <v>20.57</v>
+      </c>
+      <c r="C1471" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="D1471" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="E1471" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F1471" t="n">
+        <v>5536900</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1471"/>
+  <dimension ref="A1:F1472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,16 +512,16 @@
         <v>44152</v>
       </c>
       <c r="B5" t="n">
-        <v>20.17695617675781</v>
+        <v>20.17695426940918</v>
       </c>
       <c r="C5" t="n">
-        <v>20.17695617675781</v>
+        <v>20.17695426940918</v>
       </c>
       <c r="D5" t="n">
-        <v>19.85012633435968</v>
+        <v>19.85012445790661</v>
       </c>
       <c r="E5" t="n">
-        <v>20.12889164196659</v>
+        <v>20.12888973916155</v>
       </c>
       <c r="F5" t="n">
         <v>262242</v>
@@ -572,16 +572,16 @@
         <v>44158</v>
       </c>
       <c r="B8" t="n">
-        <v>20.2057933807373</v>
+        <v>20.20579147338867</v>
       </c>
       <c r="C8" t="n">
-        <v>20.52301068477087</v>
+        <v>20.52300874747816</v>
       </c>
       <c r="D8" t="n">
-        <v>20.14811818865408</v>
+        <v>20.14811628674976</v>
       </c>
       <c r="E8" t="n">
-        <v>20.14811818865408</v>
+        <v>20.14811628674976</v>
       </c>
       <c r="F8" t="n">
         <v>79408</v>
@@ -632,16 +632,16 @@
         <v>44161</v>
       </c>
       <c r="B11" t="n">
-        <v>22.87811088562012</v>
+        <v>22.87810897827148</v>
       </c>
       <c r="C11" t="n">
-        <v>22.87811088562012</v>
+        <v>22.87810897827148</v>
       </c>
       <c r="D11" t="n">
-        <v>22.3109640047031</v>
+        <v>22.31096214463751</v>
       </c>
       <c r="E11" t="n">
-        <v>22.3109640047031</v>
+        <v>22.31096214463751</v>
       </c>
       <c r="F11" t="n">
         <v>72970</v>
@@ -652,16 +652,16 @@
         <v>44162</v>
       </c>
       <c r="B12" t="n">
-        <v>23.07036209106445</v>
+        <v>23.07036399841309</v>
       </c>
       <c r="C12" t="n">
-        <v>23.55099428329309</v>
+        <v>23.55099623037812</v>
       </c>
       <c r="D12" t="n">
-        <v>22.10909770660719</v>
+        <v>22.10909953448302</v>
       </c>
       <c r="E12" t="n">
-        <v>23.07036209106445</v>
+        <v>23.07036399841309</v>
       </c>
       <c r="F12" t="n">
         <v>72050</v>
@@ -692,16 +692,16 @@
         <v>44166</v>
       </c>
       <c r="B14" t="n">
-        <v>23.07036209106445</v>
+        <v>23.07036399841309</v>
       </c>
       <c r="C14" t="n">
-        <v>23.1664892790253</v>
+        <v>23.16649119432127</v>
       </c>
       <c r="D14" t="n">
-        <v>23.03191196539523</v>
+        <v>23.03191386956499</v>
       </c>
       <c r="E14" t="n">
-        <v>23.12803727956828</v>
+        <v>23.12803919168523</v>
       </c>
       <c r="F14" t="n">
         <v>93512</v>
@@ -792,16 +792,16 @@
         <v>44173</v>
       </c>
       <c r="B19" t="n">
-        <v>26.33866500854492</v>
+        <v>26.33866310119629</v>
       </c>
       <c r="C19" t="n">
-        <v>26.57898205078916</v>
+        <v>26.57898012603766</v>
       </c>
       <c r="D19" t="n">
-        <v>25.56965309666637</v>
+        <v>25.56965124500673</v>
       </c>
       <c r="E19" t="n">
-        <v>25.56965309666637</v>
+        <v>25.56965124500673</v>
       </c>
       <c r="F19" t="n">
         <v>126420</v>
@@ -812,16 +812,16 @@
         <v>44174</v>
       </c>
       <c r="B20" t="n">
-        <v>26.83852005004883</v>
+        <v>26.83852195739746</v>
       </c>
       <c r="C20" t="n">
-        <v>27.77094867230641</v>
+        <v>27.77095064592048</v>
       </c>
       <c r="D20" t="n">
-        <v>26.27137510044991</v>
+        <v>26.27137696749292</v>
       </c>
       <c r="E20" t="n">
-        <v>26.4924651869397</v>
+        <v>26.49246706969505</v>
       </c>
       <c r="F20" t="n">
         <v>212880</v>
@@ -892,16 +892,16 @@
         <v>44180</v>
       </c>
       <c r="B24" t="n">
-        <v>33.00984191894531</v>
+        <v>33.00984573364258</v>
       </c>
       <c r="C24" t="n">
-        <v>33.9807187406613</v>
+        <v>33.98072266755544</v>
       </c>
       <c r="D24" t="n">
-        <v>30.7604798048412</v>
+        <v>30.76048335959674</v>
       </c>
       <c r="E24" t="n">
-        <v>30.7604798048412</v>
+        <v>30.76048335959674</v>
       </c>
       <c r="F24" t="n">
         <v>887803</v>
@@ -912,16 +912,16 @@
         <v>44181</v>
       </c>
       <c r="B25" t="n">
-        <v>32.68301773071289</v>
+        <v>32.68301391601562</v>
       </c>
       <c r="C25" t="n">
-        <v>34.4517423806715</v>
+        <v>34.45173835953219</v>
       </c>
       <c r="D25" t="n">
-        <v>32.10625830770921</v>
+        <v>32.10625456033017</v>
       </c>
       <c r="E25" t="n">
-        <v>33.62505712226533</v>
+        <v>33.62505319761509</v>
       </c>
       <c r="F25" t="n">
         <v>376808</v>
@@ -932,16 +932,16 @@
         <v>44182</v>
       </c>
       <c r="B26" t="n">
-        <v>32.10625457763672</v>
+        <v>32.10625839233398</v>
       </c>
       <c r="C26" t="n">
-        <v>33.64427827776851</v>
+        <v>33.64428227520571</v>
       </c>
       <c r="D26" t="n">
-        <v>31.64484559380946</v>
+        <v>31.64484935368452</v>
       </c>
       <c r="E26" t="n">
-        <v>33.62505321574033</v>
+        <v>33.6250572108933</v>
       </c>
       <c r="F26" t="n">
         <v>258257</v>
@@ -972,16 +972,16 @@
         <v>44186</v>
       </c>
       <c r="B28" t="n">
-        <v>32.18315505981445</v>
+        <v>32.18315887451172</v>
       </c>
       <c r="C28" t="n">
-        <v>33.33667378019659</v>
+        <v>33.33667773162143</v>
       </c>
       <c r="D28" t="n">
-        <v>29.12633082555934</v>
+        <v>29.12633427792858</v>
       </c>
       <c r="E28" t="n">
-        <v>31.86593778646691</v>
+        <v>31.86594156356414</v>
       </c>
       <c r="F28" t="n">
         <v>236079</v>
@@ -992,16 +992,16 @@
         <v>44187</v>
       </c>
       <c r="B29" t="n">
-        <v>33.16364669799805</v>
+        <v>33.16364288330078</v>
       </c>
       <c r="C29" t="n">
-        <v>33.47125146089823</v>
+        <v>33.47124761081827</v>
       </c>
       <c r="D29" t="n">
-        <v>32.59649983084212</v>
+        <v>32.59649608138177</v>
       </c>
       <c r="E29" t="n">
-        <v>33.21170935664249</v>
+        <v>33.21170553641675</v>
       </c>
       <c r="F29" t="n">
         <v>167504</v>
@@ -1032,16 +1032,16 @@
         <v>44193</v>
       </c>
       <c r="B31" t="n">
-        <v>36.21085357666016</v>
+        <v>36.21085739135742</v>
       </c>
       <c r="C31" t="n">
-        <v>36.66265002370312</v>
+        <v>36.66265388599569</v>
       </c>
       <c r="D31" t="n">
-        <v>35.56680651179074</v>
+        <v>35.56681025863972</v>
       </c>
       <c r="E31" t="n">
-        <v>35.56680651179074</v>
+        <v>35.56681025863972</v>
       </c>
       <c r="F31" t="n">
         <v>451822</v>
@@ -1052,16 +1052,16 @@
         <v>44194</v>
       </c>
       <c r="B32" t="n">
-        <v>36.09550857543945</v>
+        <v>36.09550476074219</v>
       </c>
       <c r="C32" t="n">
-        <v>37.06638558261441</v>
+        <v>37.06638166531152</v>
       </c>
       <c r="D32" t="n">
-        <v>35.95131684304462</v>
+        <v>35.95131304358604</v>
       </c>
       <c r="E32" t="n">
-        <v>36.52807627747203</v>
+        <v>36.52807241705953</v>
       </c>
       <c r="F32" t="n">
         <v>337154</v>
@@ -1092,16 +1092,16 @@
         <v>44200</v>
       </c>
       <c r="B34" t="n">
-        <v>34.99966430664062</v>
+        <v>34.99966049194336</v>
       </c>
       <c r="C34" t="n">
-        <v>36.62420472682393</v>
+        <v>36.62420073506411</v>
       </c>
       <c r="D34" t="n">
-        <v>34.98043924232432</v>
+        <v>34.98043542972244</v>
       </c>
       <c r="E34" t="n">
-        <v>36.52807565766651</v>
+        <v>36.52807167638402</v>
       </c>
       <c r="F34" t="n">
         <v>331840</v>
@@ -1112,16 +1112,16 @@
         <v>44201</v>
       </c>
       <c r="B35" t="n">
-        <v>36.13395309448242</v>
+        <v>36.13395690917969</v>
       </c>
       <c r="C35" t="n">
-        <v>36.32620745863368</v>
+        <v>36.32621129362743</v>
       </c>
       <c r="D35" t="n">
-        <v>34.60554195482727</v>
+        <v>34.60554560816865</v>
       </c>
       <c r="E35" t="n">
-        <v>35.45145591048728</v>
+        <v>35.45145965313264</v>
       </c>
       <c r="F35" t="n">
         <v>328059</v>
@@ -1172,16 +1172,16 @@
         <v>44204</v>
       </c>
       <c r="B38" t="n">
-        <v>34.134521484375</v>
+        <v>34.13452529907227</v>
       </c>
       <c r="C38" t="n">
-        <v>35.75906172916622</v>
+        <v>35.75906572541368</v>
       </c>
       <c r="D38" t="n">
-        <v>34.134521484375</v>
+        <v>34.13452529907227</v>
       </c>
       <c r="E38" t="n">
-        <v>35.16307730455386</v>
+        <v>35.16308123419719</v>
       </c>
       <c r="F38" t="n">
         <v>367201</v>
@@ -1272,16 +1272,16 @@
         <v>44211</v>
       </c>
       <c r="B43" t="n">
-        <v>33.9422721862793</v>
+        <v>33.94226837158203</v>
       </c>
       <c r="C43" t="n">
-        <v>35.0477245509764</v>
+        <v>35.04772061203977</v>
       </c>
       <c r="D43" t="n">
-        <v>33.16364589242556</v>
+        <v>33.16364216523639</v>
       </c>
       <c r="E43" t="n">
-        <v>34.60554435461268</v>
+        <v>34.60554046537172</v>
       </c>
       <c r="F43" t="n">
         <v>319883</v>
@@ -1292,16 +1292,16 @@
         <v>44214</v>
       </c>
       <c r="B44" t="n">
-        <v>34.04800796508789</v>
+        <v>34.04801177978516</v>
       </c>
       <c r="C44" t="n">
-        <v>34.50941694399793</v>
+        <v>34.5094208103909</v>
       </c>
       <c r="D44" t="n">
-        <v>33.27899799700501</v>
+        <v>33.27900172554335</v>
       </c>
       <c r="E44" t="n">
-        <v>34.11529568146945</v>
+        <v>34.11529950370554</v>
       </c>
       <c r="F44" t="n">
         <v>117631</v>
@@ -1332,16 +1332,16 @@
         <v>44216</v>
       </c>
       <c r="B46" t="n">
-        <v>34.12491226196289</v>
+        <v>34.12490844726562</v>
       </c>
       <c r="C46" t="n">
-        <v>35.28804363060232</v>
+        <v>35.28803968588292</v>
       </c>
       <c r="D46" t="n">
-        <v>33.66350697587357</v>
+        <v>33.66350321275509</v>
       </c>
       <c r="E46" t="n">
-        <v>34.60554635973278</v>
+        <v>34.60554249130722</v>
       </c>
       <c r="F46" t="n">
         <v>359332</v>
@@ -1372,16 +1372,16 @@
         <v>44218</v>
       </c>
       <c r="B48" t="n">
-        <v>32.95216751098633</v>
+        <v>32.95216369628906</v>
       </c>
       <c r="C48" t="n">
-        <v>33.45202665996278</v>
+        <v>33.45202278739948</v>
       </c>
       <c r="D48" t="n">
-        <v>32.53882489582456</v>
+        <v>32.53882112897777</v>
       </c>
       <c r="E48" t="n">
-        <v>33.19248455367023</v>
+        <v>33.19248071115274</v>
       </c>
       <c r="F48" t="n">
         <v>220341</v>
@@ -1472,16 +1472,16 @@
         <v>44228</v>
       </c>
       <c r="B53" t="n">
-        <v>31.77942657470703</v>
+        <v>31.7794246673584</v>
       </c>
       <c r="C53" t="n">
-        <v>33.11558345161116</v>
+        <v>33.1155814640686</v>
       </c>
       <c r="D53" t="n">
-        <v>31.66407244843196</v>
+        <v>31.66407054800669</v>
       </c>
       <c r="E53" t="n">
-        <v>32.68301578391271</v>
+        <v>32.68301382233215</v>
       </c>
       <c r="F53" t="n">
         <v>610435</v>
@@ -1492,16 +1492,16 @@
         <v>44229</v>
       </c>
       <c r="B54" t="n">
-        <v>32.63495254516602</v>
+        <v>32.63494873046875</v>
       </c>
       <c r="C54" t="n">
-        <v>33.65389597951643</v>
+        <v>33.65389204571495</v>
       </c>
       <c r="D54" t="n">
-        <v>31.97168030813476</v>
+        <v>31.97167657096734</v>
       </c>
       <c r="E54" t="n">
-        <v>33.64428344702543</v>
+        <v>33.64427951434755</v>
       </c>
       <c r="F54" t="n">
         <v>582228</v>
@@ -1532,16 +1532,16 @@
         <v>44231</v>
       </c>
       <c r="B56" t="n">
-        <v>32.68301773071289</v>
+        <v>32.68301391601562</v>
       </c>
       <c r="C56" t="n">
-        <v>34.11530000851534</v>
+        <v>34.11529602664492</v>
       </c>
       <c r="D56" t="n">
-        <v>32.44270067986538</v>
+        <v>32.44269689321744</v>
       </c>
       <c r="E56" t="n">
-        <v>33.06752276352339</v>
+        <v>33.06751890394745</v>
       </c>
       <c r="F56" t="n">
         <v>466743</v>
@@ -1612,16 +1612,16 @@
         <v>44237</v>
       </c>
       <c r="B60" t="n">
-        <v>34.83625030517578</v>
+        <v>34.83624649047852</v>
       </c>
       <c r="C60" t="n">
-        <v>35.33610571127585</v>
+        <v>35.33610184184258</v>
       </c>
       <c r="D60" t="n">
-        <v>34.23065330065825</v>
+        <v>34.23064955227608</v>
       </c>
       <c r="E60" t="n">
-        <v>34.43251647044691</v>
+        <v>34.43251269995998</v>
       </c>
       <c r="F60" t="n">
         <v>186206</v>
@@ -1652,16 +1652,16 @@
         <v>44239</v>
       </c>
       <c r="B62" t="n">
-        <v>34.4036750793457</v>
+        <v>34.40367889404297</v>
       </c>
       <c r="C62" t="n">
-        <v>34.52864172776623</v>
+        <v>34.52864555631986</v>
       </c>
       <c r="D62" t="n">
-        <v>32.67339704372985</v>
+        <v>32.673400666573</v>
       </c>
       <c r="E62" t="n">
-        <v>33.67311524079254</v>
+        <v>33.67311897448496</v>
       </c>
       <c r="F62" t="n">
         <v>218195</v>
@@ -1692,16 +1692,16 @@
         <v>44245</v>
       </c>
       <c r="B64" t="n">
-        <v>37.00870513916016</v>
+        <v>37.00870895385742</v>
       </c>
       <c r="C64" t="n">
-        <v>37.38359759408829</v>
+        <v>37.38360144742785</v>
       </c>
       <c r="D64" t="n">
-        <v>35.71099846956061</v>
+        <v>35.71100215049589</v>
       </c>
       <c r="E64" t="n">
-        <v>36.37427060079703</v>
+        <v>36.37427435009953</v>
       </c>
       <c r="F64" t="n">
         <v>661534</v>
@@ -1812,16 +1812,16 @@
         <v>44253</v>
       </c>
       <c r="B70" t="n">
-        <v>34.57670974731445</v>
+        <v>34.57670593261719</v>
       </c>
       <c r="C70" t="n">
-        <v>37.21057733278074</v>
+        <v>37.21057322750037</v>
       </c>
       <c r="D70" t="n">
-        <v>33.75002072456356</v>
+        <v>33.75001700107128</v>
       </c>
       <c r="E70" t="n">
-        <v>36.53768882724342</v>
+        <v>36.5376847961999</v>
       </c>
       <c r="F70" t="n">
         <v>410022</v>
@@ -1932,16 +1932,16 @@
         <v>44263</v>
       </c>
       <c r="B76" t="n">
-        <v>41.91115570068359</v>
+        <v>41.91115951538086</v>
       </c>
       <c r="C76" t="n">
-        <v>44.60269808495321</v>
+        <v>44.60270214463106</v>
       </c>
       <c r="D76" t="n">
-        <v>40.70957434605565</v>
+        <v>40.70957805138659</v>
       </c>
       <c r="E76" t="n">
-        <v>43.55492097253444</v>
+        <v>43.55492493684502</v>
       </c>
       <c r="F76" t="n">
         <v>1012691</v>
@@ -1952,16 +1952,16 @@
         <v>44264</v>
       </c>
       <c r="B77" t="n">
-        <v>43.50685882568359</v>
+        <v>43.50686264038086</v>
       </c>
       <c r="C77" t="n">
-        <v>43.50685882568359</v>
+        <v>43.50686264038086</v>
       </c>
       <c r="D77" t="n">
-        <v>39.89249844113039</v>
+        <v>39.89250193891922</v>
       </c>
       <c r="E77" t="n">
-        <v>42.29566117843103</v>
+        <v>42.29566488693005</v>
       </c>
       <c r="F77" t="n">
         <v>563525</v>
@@ -1972,16 +1972,16 @@
         <v>44265</v>
       </c>
       <c r="B78" t="n">
-        <v>44.69882965087891</v>
+        <v>44.69882583618164</v>
       </c>
       <c r="C78" t="n">
-        <v>44.89108404365759</v>
+        <v>44.89108021255291</v>
       </c>
       <c r="D78" t="n">
-        <v>43.38189774093629</v>
+        <v>43.38189403862891</v>
       </c>
       <c r="E78" t="n">
-        <v>43.83369425231464</v>
+        <v>43.83369051144994</v>
       </c>
       <c r="F78" t="n">
         <v>425454</v>
@@ -2012,16 +2012,16 @@
         <v>44267</v>
       </c>
       <c r="B80" t="n">
-        <v>45.66009140014648</v>
+        <v>45.66009521484375</v>
       </c>
       <c r="C80" t="n">
-        <v>49.01490590711195</v>
+        <v>49.01491000208902</v>
       </c>
       <c r="D80" t="n">
-        <v>45.18906989096082</v>
+        <v>45.18907366630634</v>
       </c>
       <c r="E80" t="n">
-        <v>47.15005242731743</v>
+        <v>47.15005636649431</v>
       </c>
       <c r="F80" t="n">
         <v>954539</v>
@@ -2052,16 +2052,16 @@
         <v>44271</v>
       </c>
       <c r="B82" t="n">
-        <v>42.7570686340332</v>
+        <v>42.75707244873047</v>
       </c>
       <c r="C82" t="n">
-        <v>45.18906887745489</v>
+        <v>45.18907290913018</v>
       </c>
       <c r="D82" t="n">
-        <v>42.7570686340332</v>
+        <v>42.75707244873047</v>
       </c>
       <c r="E82" t="n">
-        <v>44.5065717038056</v>
+        <v>44.50657567458991</v>
       </c>
       <c r="F82" t="n">
         <v>561175</v>
@@ -2092,16 +2092,16 @@
         <v>44273</v>
       </c>
       <c r="B84" t="n">
-        <v>40.89221572875977</v>
+        <v>40.89221954345703</v>
       </c>
       <c r="C84" t="n">
-        <v>45.02565269480871</v>
+        <v>45.0256568951004</v>
       </c>
       <c r="D84" t="n">
-        <v>40.57499846451049</v>
+        <v>40.57500224961562</v>
       </c>
       <c r="E84" t="n">
-        <v>44.01632571721106</v>
+        <v>44.01632982334604</v>
       </c>
       <c r="F84" t="n">
         <v>572621</v>
@@ -2112,16 +2112,16 @@
         <v>44274</v>
       </c>
       <c r="B85" t="n">
-        <v>42.2956657409668</v>
+        <v>42.29566192626953</v>
       </c>
       <c r="C85" t="n">
-        <v>44.17013572642225</v>
+        <v>44.17013174266427</v>
       </c>
       <c r="D85" t="n">
-        <v>41.45936795627186</v>
+        <v>41.4593642170013</v>
       </c>
       <c r="E85" t="n">
-        <v>41.45936795627186</v>
+        <v>41.4593642170013</v>
       </c>
       <c r="F85" t="n">
         <v>639255</v>
@@ -2212,16 +2212,16 @@
         <v>44281</v>
       </c>
       <c r="B90" t="n">
-        <v>37.87384796142578</v>
+        <v>37.87384414672852</v>
       </c>
       <c r="C90" t="n">
-        <v>40.94989565175231</v>
+        <v>40.949891527232</v>
       </c>
       <c r="D90" t="n">
-        <v>37.56624319239313</v>
+        <v>37.56623940867817</v>
       </c>
       <c r="E90" t="n">
-        <v>39.95979362121066</v>
+        <v>39.95978959641457</v>
       </c>
       <c r="F90" t="n">
         <v>840076</v>
@@ -2312,16 +2312,16 @@
         <v>44291</v>
       </c>
       <c r="B95" t="n">
-        <v>35.68216323852539</v>
+        <v>35.68215942382812</v>
       </c>
       <c r="C95" t="n">
-        <v>37.01832012039754</v>
+        <v>37.01831616285484</v>
       </c>
       <c r="D95" t="n">
-        <v>35.09579131613852</v>
+        <v>35.09578756412892</v>
       </c>
       <c r="E95" t="n">
-        <v>37.01832012039754</v>
+        <v>37.01831616285484</v>
       </c>
       <c r="F95" t="n">
         <v>1091895</v>
@@ -2512,16 +2512,16 @@
         <v>44305</v>
       </c>
       <c r="B105" t="n">
-        <v>41.33440017700195</v>
+        <v>41.33439636230469</v>
       </c>
       <c r="C105" t="n">
-        <v>42.23798940934727</v>
+        <v>42.23798551125894</v>
       </c>
       <c r="D105" t="n">
-        <v>40.2097189655786</v>
+        <v>40.20971525467667</v>
       </c>
       <c r="E105" t="n">
-        <v>40.38274828563441</v>
+        <v>40.38274455876383</v>
       </c>
       <c r="F105" t="n">
         <v>1793083</v>
@@ -2552,16 +2552,16 @@
         <v>44308</v>
       </c>
       <c r="B107" t="n">
-        <v>42.37256622314453</v>
+        <v>42.3725700378418</v>
       </c>
       <c r="C107" t="n">
-        <v>42.77629628383934</v>
+        <v>42.77630013488342</v>
       </c>
       <c r="D107" t="n">
-        <v>41.0460181707321</v>
+        <v>41.04602186600353</v>
       </c>
       <c r="E107" t="n">
-        <v>42.58404191096891</v>
+        <v>42.58404574470481</v>
       </c>
       <c r="F107" t="n">
         <v>1175903</v>
@@ -2572,16 +2572,16 @@
         <v>44309</v>
       </c>
       <c r="B108" t="n">
-        <v>44.09323120117188</v>
+        <v>44.09323501586914</v>
       </c>
       <c r="C108" t="n">
-        <v>44.3143194172334</v>
+        <v>44.31432325105797</v>
       </c>
       <c r="D108" t="n">
-        <v>42.38217817402538</v>
+        <v>42.38218184069201</v>
       </c>
       <c r="E108" t="n">
-        <v>42.82435835372392</v>
+        <v>42.82436205864548</v>
       </c>
       <c r="F108" t="n">
         <v>1899574</v>
@@ -2612,16 +2612,16 @@
         <v>44313</v>
       </c>
       <c r="B110" t="n">
-        <v>43.73756408691406</v>
+        <v>43.7375602722168</v>
       </c>
       <c r="C110" t="n">
-        <v>44.31432350323168</v>
+        <v>44.31431963823069</v>
       </c>
       <c r="D110" t="n">
-        <v>43.04545428636325</v>
+        <v>43.04545053203033</v>
       </c>
       <c r="E110" t="n">
-        <v>43.40112171865809</v>
+        <v>43.40111793330461</v>
       </c>
       <c r="F110" t="n">
         <v>1146163</v>
@@ -2732,16 +2732,16 @@
         <v>44321</v>
       </c>
       <c r="B116" t="n">
-        <v>39.74831008911133</v>
+        <v>39.74831390380859</v>
       </c>
       <c r="C116" t="n">
-        <v>40.6422867086336</v>
+        <v>40.64229060912697</v>
       </c>
       <c r="D116" t="n">
-        <v>39.07542542863015</v>
+        <v>39.0754291787498</v>
       </c>
       <c r="E116" t="n">
-        <v>39.89249805311069</v>
+        <v>39.89250188164586</v>
       </c>
       <c r="F116" t="n">
         <v>3650961</v>
@@ -2772,16 +2772,16 @@
         <v>44323</v>
       </c>
       <c r="B118" t="n">
-        <v>38.83511352539062</v>
+        <v>38.83510971069336</v>
       </c>
       <c r="C118" t="n">
-        <v>39.99824491189721</v>
+        <v>39.99824098294782</v>
       </c>
       <c r="D118" t="n">
-        <v>37.51818162368365</v>
+        <v>37.51817793834604</v>
       </c>
       <c r="E118" t="n">
-        <v>39.66180253732045</v>
+        <v>39.66179864141913</v>
       </c>
       <c r="F118" t="n">
         <v>2227429</v>
@@ -2832,16 +2832,16 @@
         <v>44328</v>
       </c>
       <c r="B121" t="n">
-        <v>37.05676651000977</v>
+        <v>37.05677032470703</v>
       </c>
       <c r="C121" t="n">
-        <v>38.70052798471127</v>
+        <v>38.70053196862062</v>
       </c>
       <c r="D121" t="n">
-        <v>37.05676651000977</v>
+        <v>37.05677032470703</v>
       </c>
       <c r="E121" t="n">
-        <v>37.81616767208757</v>
+        <v>37.8161715649591</v>
       </c>
       <c r="F121" t="n">
         <v>783049</v>
@@ -2892,16 +2892,16 @@
         <v>44333</v>
       </c>
       <c r="B124" t="n">
-        <v>36.43194961547852</v>
+        <v>36.43194580078125</v>
       </c>
       <c r="C124" t="n">
-        <v>37.13367194429578</v>
+        <v>37.13366805612294</v>
       </c>
       <c r="D124" t="n">
-        <v>35.93209045798972</v>
+        <v>35.93208669563144</v>
       </c>
       <c r="E124" t="n">
-        <v>36.52807493515874</v>
+        <v>36.52807111039643</v>
       </c>
       <c r="F124" t="n">
         <v>946466</v>
@@ -2912,16 +2912,16 @@
         <v>44334</v>
       </c>
       <c r="B125" t="n">
-        <v>35.14385223388672</v>
+        <v>35.14385604858398</v>
       </c>
       <c r="C125" t="n">
-        <v>36.91258044505902</v>
+        <v>36.91258445174329</v>
       </c>
       <c r="D125" t="n">
-        <v>34.59593046500746</v>
+        <v>34.59593422023043</v>
       </c>
       <c r="E125" t="n">
-        <v>36.52807170518645</v>
+        <v>36.52807567013412</v>
       </c>
       <c r="F125" t="n">
         <v>2070451</v>
@@ -2952,16 +2952,16 @@
         <v>44336</v>
       </c>
       <c r="B127" t="n">
-        <v>34.63438034057617</v>
+        <v>34.63438415527344</v>
       </c>
       <c r="C127" t="n">
-        <v>35.26881488495837</v>
+        <v>35.26881876953347</v>
       </c>
       <c r="D127" t="n">
-        <v>34.51902996798866</v>
+        <v>34.51903376998102</v>
       </c>
       <c r="E127" t="n">
-        <v>34.51902996798866</v>
+        <v>34.51903376998102</v>
       </c>
       <c r="F127" t="n">
         <v>943604</v>
@@ -3012,16 +3012,16 @@
         <v>44341</v>
       </c>
       <c r="B130" t="n">
-        <v>37.29708480834961</v>
+        <v>37.29708862304688</v>
       </c>
       <c r="C130" t="n">
-        <v>38.78704584439543</v>
+        <v>38.78704981148397</v>
       </c>
       <c r="D130" t="n">
-        <v>37.22979709165812</v>
+        <v>37.22980089947328</v>
       </c>
       <c r="E130" t="n">
-        <v>37.52778929886728</v>
+        <v>37.52779313716071</v>
       </c>
       <c r="F130" t="n">
         <v>1731150</v>
@@ -3092,16 +3092,16 @@
         <v>44347</v>
       </c>
       <c r="B134" t="n">
-        <v>39.38302993774414</v>
+        <v>39.38303375244141</v>
       </c>
       <c r="C134" t="n">
-        <v>40.11358977958957</v>
+        <v>40.11359366504992</v>
       </c>
       <c r="D134" t="n">
-        <v>39.02736254769899</v>
+        <v>39.02736632794579</v>
       </c>
       <c r="E134" t="n">
-        <v>39.3926424686217</v>
+        <v>39.39264628425005</v>
       </c>
       <c r="F134" t="n">
         <v>715598</v>
@@ -3192,16 +3192,16 @@
         <v>44355</v>
       </c>
       <c r="B139" t="n">
-        <v>38.46022033691406</v>
+        <v>38.4602165222168</v>
       </c>
       <c r="C139" t="n">
-        <v>38.85433789767048</v>
+        <v>38.85433404388245</v>
       </c>
       <c r="D139" t="n">
-        <v>37.72004412796937</v>
+        <v>37.72004038668688</v>
       </c>
       <c r="E139" t="n">
-        <v>38.43138274082768</v>
+        <v>38.43137892899068</v>
       </c>
       <c r="F139" t="n">
         <v>978352</v>
@@ -3212,16 +3212,16 @@
         <v>44356</v>
       </c>
       <c r="B140" t="n">
-        <v>38.01803207397461</v>
+        <v>38.01803588867188</v>
       </c>
       <c r="C140" t="n">
-        <v>38.66207914230487</v>
+        <v>38.66208302162527</v>
       </c>
       <c r="D140" t="n">
-        <v>37.29708475810054</v>
+        <v>37.29708850045856</v>
       </c>
       <c r="E140" t="n">
-        <v>38.48905358533129</v>
+        <v>38.48905744729046</v>
       </c>
       <c r="F140" t="n">
         <v>837521</v>
@@ -3332,16 +3332,16 @@
         <v>44364</v>
       </c>
       <c r="B146" t="n">
-        <v>42.48791885375977</v>
+        <v>42.4879150390625</v>
       </c>
       <c r="C146" t="n">
-        <v>44.00671761209134</v>
+        <v>44.0067136610316</v>
       </c>
       <c r="D146" t="n">
-        <v>41.62277975128091</v>
+        <v>41.62277601425852</v>
       </c>
       <c r="E146" t="n">
-        <v>42.95894040588714</v>
+        <v>42.95893654890009</v>
       </c>
       <c r="F146" t="n">
         <v>1582144</v>
@@ -3372,16 +3372,16 @@
         <v>44368</v>
       </c>
       <c r="B148" t="n">
-        <v>46.96741104125977</v>
+        <v>46.96741485595703</v>
       </c>
       <c r="C148" t="n">
-        <v>47.24617818755916</v>
+        <v>47.24618202489792</v>
       </c>
       <c r="D148" t="n">
-        <v>43.53569625432814</v>
+        <v>43.53569979030122</v>
       </c>
       <c r="E148" t="n">
-        <v>43.73755940512824</v>
+        <v>43.73756295749668</v>
       </c>
       <c r="F148" t="n">
         <v>2655439</v>
@@ -3452,16 +3452,16 @@
         <v>44372</v>
       </c>
       <c r="B152" t="n">
-        <v>44.45851516723633</v>
+        <v>44.45851135253906</v>
       </c>
       <c r="C152" t="n">
-        <v>44.9872081751215</v>
+        <v>44.98720431506052</v>
       </c>
       <c r="D152" t="n">
-        <v>43.97788107180344</v>
+        <v>43.97787729834627</v>
       </c>
       <c r="E152" t="n">
-        <v>44.9872081751215</v>
+        <v>44.98720431506052</v>
       </c>
       <c r="F152" t="n">
         <v>1347904</v>
@@ -3472,16 +3472,16 @@
         <v>44375</v>
       </c>
       <c r="B153" t="n">
-        <v>44.53541564941406</v>
+        <v>44.5354118347168</v>
       </c>
       <c r="C153" t="n">
-        <v>44.64115350201283</v>
+        <v>44.64114967825854</v>
       </c>
       <c r="D153" t="n">
-        <v>43.20886748802305</v>
+        <v>43.20886378695175</v>
       </c>
       <c r="E153" t="n">
-        <v>44.13168555555202</v>
+        <v>44.13168177543641</v>
       </c>
       <c r="F153" t="n">
         <v>1110393</v>
@@ -3512,16 +3512,16 @@
         <v>44377</v>
       </c>
       <c r="B155" t="n">
-        <v>43.58375930786133</v>
+        <v>43.58376312255859</v>
       </c>
       <c r="C155" t="n">
-        <v>44.45851087872119</v>
+        <v>44.45851476998166</v>
       </c>
       <c r="D155" t="n">
-        <v>43.50685905923421</v>
+        <v>43.50686286720073</v>
       </c>
       <c r="E155" t="n">
-        <v>44.21819385418598</v>
+        <v>44.21819772441255</v>
       </c>
       <c r="F155" t="n">
         <v>1274116</v>
@@ -3572,16 +3572,16 @@
         <v>44382</v>
       </c>
       <c r="B158" t="n">
-        <v>45.04488754272461</v>
+        <v>45.04488372802734</v>
       </c>
       <c r="C158" t="n">
-        <v>46.21763144885693</v>
+        <v>46.21762753484401</v>
       </c>
       <c r="D158" t="n">
-        <v>44.42967424579171</v>
+        <v>44.42967048319475</v>
       </c>
       <c r="E158" t="n">
-        <v>44.98720860256699</v>
+        <v>44.98720479275436</v>
       </c>
       <c r="F158" t="n">
         <v>3391068</v>
@@ -3592,16 +3592,16 @@
         <v>44383</v>
       </c>
       <c r="B159" t="n">
-        <v>44.37199783325195</v>
+        <v>44.37199401855469</v>
       </c>
       <c r="C159" t="n">
-        <v>45.94847553926477</v>
+        <v>45.94847158903642</v>
       </c>
       <c r="D159" t="n">
-        <v>43.75678830080941</v>
+        <v>43.75678453900221</v>
       </c>
       <c r="E159" t="n">
-        <v>45.78505875053358</v>
+        <v>45.7850548143543</v>
       </c>
       <c r="F159" t="n">
         <v>1563442</v>
@@ -3652,16 +3652,16 @@
         <v>44389</v>
       </c>
       <c r="B162" t="n">
-        <v>44.72766494750977</v>
+        <v>44.72766876220703</v>
       </c>
       <c r="C162" t="n">
-        <v>45.75621700299953</v>
+        <v>45.75622090541913</v>
       </c>
       <c r="D162" t="n">
-        <v>44.08361413043626</v>
+        <v>44.08361789020423</v>
       </c>
       <c r="E162" t="n">
-        <v>45.75621700299953</v>
+        <v>45.75622090541913</v>
       </c>
       <c r="F162" t="n">
         <v>1597780</v>
@@ -3732,16 +3732,16 @@
         <v>44393</v>
       </c>
       <c r="B166" t="n">
-        <v>41.70929336547852</v>
+        <v>41.70928955078125</v>
       </c>
       <c r="C166" t="n">
-        <v>41.91116028433812</v>
+        <v>41.91115645117827</v>
       </c>
       <c r="D166" t="n">
-        <v>40.45003668764308</v>
+        <v>40.45003298811638</v>
       </c>
       <c r="E166" t="n">
-        <v>41.62278057778546</v>
+        <v>41.62277677100059</v>
       </c>
       <c r="F166" t="n">
         <v>1471156</v>
@@ -3752,16 +3752,16 @@
         <v>44396</v>
       </c>
       <c r="B167" t="n">
-        <v>40.22894668579102</v>
+        <v>40.22894287109375</v>
       </c>
       <c r="C167" t="n">
-        <v>41.05563189370605</v>
+        <v>41.05562800061862</v>
       </c>
       <c r="D167" t="n">
-        <v>39.50799557728174</v>
+        <v>39.50799183094843</v>
       </c>
       <c r="E167" t="n">
-        <v>40.46925997438512</v>
+        <v>40.46925613690023</v>
       </c>
       <c r="F167" t="n">
         <v>1632835</v>
@@ -3792,16 +3792,16 @@
         <v>44398</v>
       </c>
       <c r="B169" t="n">
-        <v>40.45964813232422</v>
+        <v>40.45964431762695</v>
       </c>
       <c r="C169" t="n">
-        <v>41.40169122996932</v>
+        <v>41.40168732645247</v>
       </c>
       <c r="D169" t="n">
-        <v>40.22894737134245</v>
+        <v>40.22894357839657</v>
       </c>
       <c r="E169" t="n">
-        <v>40.37313534695605</v>
+        <v>40.37313154041556</v>
       </c>
       <c r="F169" t="n">
         <v>985812</v>
@@ -3812,16 +3812,16 @@
         <v>44399</v>
       </c>
       <c r="B170" t="n">
-        <v>40.89221572875977</v>
+        <v>40.89221954345703</v>
       </c>
       <c r="C170" t="n">
-        <v>41.15175780815924</v>
+        <v>41.15176164706832</v>
       </c>
       <c r="D170" t="n">
-        <v>40.39235663157741</v>
+        <v>40.3923603996445</v>
       </c>
       <c r="E170" t="n">
-        <v>41.08446634492577</v>
+        <v>41.08447017755746</v>
       </c>
       <c r="F170" t="n">
         <v>757704</v>
@@ -3832,16 +3832,16 @@
         <v>44400</v>
       </c>
       <c r="B171" t="n">
-        <v>40.56539154052734</v>
+        <v>40.56538772583008</v>
       </c>
       <c r="C171" t="n">
-        <v>40.8633837843476</v>
+        <v>40.86337994162768</v>
       </c>
       <c r="D171" t="n">
-        <v>40.20010782417279</v>
+        <v>40.20010404382616</v>
       </c>
       <c r="E171" t="n">
-        <v>40.62306673334884</v>
+        <v>40.6230629132279</v>
       </c>
       <c r="F171" t="n">
         <v>715496</v>
@@ -3872,16 +3872,16 @@
         <v>44404</v>
       </c>
       <c r="B173" t="n">
-        <v>38.54673385620117</v>
+        <v>38.54673004150391</v>
       </c>
       <c r="C173" t="n">
-        <v>40.84415903525979</v>
+        <v>40.84415499320262</v>
       </c>
       <c r="D173" t="n">
-        <v>38.32564186777011</v>
+        <v>38.32563807495276</v>
       </c>
       <c r="E173" t="n">
-        <v>40.62306704682872</v>
+        <v>40.62306302665147</v>
       </c>
       <c r="F173" t="n">
         <v>1543819</v>
@@ -3932,16 +3932,16 @@
         <v>44407</v>
       </c>
       <c r="B176" t="n">
-        <v>37.21057510375977</v>
+        <v>37.2105712890625</v>
       </c>
       <c r="C176" t="n">
-        <v>38.26796483899034</v>
+        <v>38.26796091589321</v>
       </c>
       <c r="D176" t="n">
-        <v>36.33582347177977</v>
+        <v>36.33581974675896</v>
       </c>
       <c r="E176" t="n">
-        <v>37.56624252608663</v>
+        <v>37.5662386749276</v>
       </c>
       <c r="F176" t="n">
         <v>1168442</v>
@@ -3952,16 +3952,16 @@
         <v>44410</v>
       </c>
       <c r="B177" t="n">
-        <v>39.04659271240234</v>
+        <v>39.04658889770508</v>
       </c>
       <c r="C177" t="n">
-        <v>40.34429954077027</v>
+        <v>40.3442955992922</v>
       </c>
       <c r="D177" t="n">
-        <v>38.19106610976557</v>
+        <v>38.19106237864987</v>
       </c>
       <c r="E177" t="n">
-        <v>39.17155563014188</v>
+        <v>39.17155180323623</v>
       </c>
       <c r="F177" t="n">
         <v>3352028</v>
@@ -4052,16 +4052,16 @@
         <v>44417</v>
       </c>
       <c r="B182" t="n">
-        <v>37.10483551025391</v>
+        <v>37.10483169555664</v>
       </c>
       <c r="C182" t="n">
-        <v>37.44127788724551</v>
+        <v>37.44127403795907</v>
       </c>
       <c r="D182" t="n">
-        <v>35.94170411539885</v>
+        <v>35.94170042028153</v>
       </c>
       <c r="E182" t="n">
-        <v>36.11473344381713</v>
+        <v>36.1147297309109</v>
       </c>
       <c r="F182" t="n">
         <v>1206460</v>
@@ -4092,16 +4092,16 @@
         <v>44419</v>
       </c>
       <c r="B184" t="n">
-        <v>36.43194961547852</v>
+        <v>36.43194580078125</v>
       </c>
       <c r="C184" t="n">
-        <v>36.74916691799907</v>
+        <v>36.74916307008678</v>
       </c>
       <c r="D184" t="n">
-        <v>36.09550724902192</v>
+        <v>36.09550346955268</v>
       </c>
       <c r="E184" t="n">
-        <v>36.4703997433506</v>
+        <v>36.47039592462733</v>
       </c>
       <c r="F184" t="n">
         <v>786524</v>
@@ -4112,16 +4112,16 @@
         <v>44420</v>
       </c>
       <c r="B185" t="n">
-        <v>36.12434005737305</v>
+        <v>36.12434387207031</v>
       </c>
       <c r="C185" t="n">
-        <v>36.95102893978947</v>
+        <v>36.95103284178433</v>
       </c>
       <c r="D185" t="n">
-        <v>35.47068047502529</v>
+        <v>35.4706842206967</v>
       </c>
       <c r="E185" t="n">
-        <v>36.19162777223157</v>
+        <v>36.19163159403436</v>
       </c>
       <c r="F185" t="n">
         <v>689639</v>
@@ -4132,16 +4132,16 @@
         <v>44421</v>
       </c>
       <c r="B186" t="n">
-        <v>34.75934600830078</v>
+        <v>34.75934219360352</v>
       </c>
       <c r="C186" t="n">
-        <v>35.97054000708643</v>
+        <v>35.97053605946554</v>
       </c>
       <c r="D186" t="n">
-        <v>34.59593296747376</v>
+        <v>34.59592917071041</v>
       </c>
       <c r="E186" t="n">
-        <v>35.69177658449917</v>
+        <v>35.69177266747142</v>
       </c>
       <c r="F186" t="n">
         <v>915908</v>
@@ -4252,16 +4252,16 @@
         <v>44431</v>
       </c>
       <c r="B192" t="n">
-        <v>33.16364669799805</v>
+        <v>33.16364288330078</v>
       </c>
       <c r="C192" t="n">
-        <v>34.42290334478545</v>
+        <v>34.42289938524034</v>
       </c>
       <c r="D192" t="n">
-        <v>32.77914168126674</v>
+        <v>32.77913791079774</v>
       </c>
       <c r="E192" t="n">
-        <v>33.74040609688286</v>
+        <v>33.740402215843</v>
       </c>
       <c r="F192" t="n">
         <v>2084044</v>
@@ -4272,16 +4272,16 @@
         <v>44432</v>
       </c>
       <c r="B193" t="n">
-        <v>35.43223190307617</v>
+        <v>35.43223571777344</v>
       </c>
       <c r="C193" t="n">
-        <v>35.43223190307617</v>
+        <v>35.43223571777344</v>
       </c>
       <c r="D193" t="n">
-        <v>33.47124932262768</v>
+        <v>33.47125292620207</v>
       </c>
       <c r="E193" t="n">
-        <v>33.93265831128927</v>
+        <v>33.93266196453976</v>
       </c>
       <c r="F193" t="n">
         <v>1429663</v>
@@ -4332,16 +4332,16 @@
         <v>44435</v>
       </c>
       <c r="B196" t="n">
-        <v>36.43194961547852</v>
+        <v>36.43194580078125</v>
       </c>
       <c r="C196" t="n">
-        <v>36.66265413028687</v>
+        <v>36.66265029143312</v>
       </c>
       <c r="D196" t="n">
-        <v>35.02850121026817</v>
+        <v>35.02849754252244</v>
       </c>
       <c r="E196" t="n">
-        <v>35.75906488256532</v>
+        <v>35.75906113832411</v>
       </c>
       <c r="F196" t="n">
         <v>2701327</v>
@@ -4392,16 +4392,16 @@
         <v>44440</v>
       </c>
       <c r="B199" t="n">
-        <v>36.00899505615234</v>
+        <v>36.00899124145508</v>
       </c>
       <c r="C199" t="n">
-        <v>37.2298016265613</v>
+        <v>37.22979768253502</v>
       </c>
       <c r="D199" t="n">
-        <v>35.47068576189898</v>
+        <v>35.47068200422877</v>
       </c>
       <c r="E199" t="n">
-        <v>37.10483496133683</v>
+        <v>37.10483103054919</v>
       </c>
       <c r="F199" t="n">
         <v>1150659</v>
@@ -4712,16 +4712,16 @@
         <v>44463</v>
       </c>
       <c r="B215" t="n">
-        <v>34.54787063598633</v>
+        <v>34.54786682128906</v>
       </c>
       <c r="C215" t="n">
-        <v>35.65332304773112</v>
+        <v>35.65331911097231</v>
       </c>
       <c r="D215" t="n">
-        <v>33.88459469184851</v>
+        <v>33.88459095038866</v>
       </c>
       <c r="E215" t="n">
-        <v>34.46135784884584</v>
+        <v>34.46135404370111</v>
       </c>
       <c r="F215" t="n">
         <v>2639905</v>
@@ -4852,16 +4852,16 @@
         <v>44474</v>
       </c>
       <c r="B222" t="n">
-        <v>41.2382698059082</v>
+        <v>41.23827362060547</v>
       </c>
       <c r="C222" t="n">
-        <v>43.07428564103963</v>
+        <v>43.07428962557536</v>
       </c>
       <c r="D222" t="n">
-        <v>40.94989013953506</v>
+        <v>40.9498939275561</v>
       </c>
       <c r="E222" t="n">
-        <v>41.82464166928109</v>
+        <v>41.82464553821999</v>
       </c>
       <c r="F222" t="n">
         <v>3033780</v>
@@ -4952,16 +4952,16 @@
         <v>44482</v>
       </c>
       <c r="B227" t="n">
-        <v>39.66180038452148</v>
+        <v>39.66179656982422</v>
       </c>
       <c r="C227" t="n">
-        <v>40.05591793090613</v>
+        <v>40.05591407830239</v>
       </c>
       <c r="D227" t="n">
-        <v>38.88317407585477</v>
+        <v>38.88317033604628</v>
       </c>
       <c r="E227" t="n">
-        <v>39.43109587666738</v>
+        <v>39.43109208415942</v>
       </c>
       <c r="F227" t="n">
         <v>1130628</v>
@@ -5012,16 +5012,16 @@
         <v>44487</v>
       </c>
       <c r="B230" t="n">
-        <v>39.87327575683594</v>
+        <v>39.87327194213867</v>
       </c>
       <c r="C230" t="n">
-        <v>41.44975342469183</v>
+        <v>41.44974945917212</v>
       </c>
       <c r="D230" t="n">
-        <v>39.18116598648377</v>
+        <v>39.18116223800101</v>
       </c>
       <c r="E230" t="n">
-        <v>39.72908778283576</v>
+        <v>39.72908398193304</v>
       </c>
       <c r="F230" t="n">
         <v>2573169</v>
@@ -5032,16 +5032,16 @@
         <v>44488</v>
       </c>
       <c r="B231" t="n">
-        <v>37.58546829223633</v>
+        <v>37.58546447753906</v>
       </c>
       <c r="C231" t="n">
-        <v>40.08475657457366</v>
+        <v>40.08475250621378</v>
       </c>
       <c r="D231" t="n">
-        <v>36.86452090235465</v>
+        <v>36.86451716082918</v>
       </c>
       <c r="E231" t="n">
-        <v>39.57528488714614</v>
+        <v>39.57528087049455</v>
       </c>
       <c r="F231" t="n">
         <v>2915331</v>
@@ -5072,16 +5072,16 @@
         <v>44490</v>
       </c>
       <c r="B233" t="n">
-        <v>34.41329193115234</v>
+        <v>34.41328811645508</v>
       </c>
       <c r="C233" t="n">
-        <v>36.09550752381791</v>
+        <v>36.09550352264783</v>
       </c>
       <c r="D233" t="n">
-        <v>33.48086508042814</v>
+        <v>33.48086136908995</v>
       </c>
       <c r="E233" t="n">
-        <v>35.62448595864728</v>
+        <v>35.62448200968972</v>
       </c>
       <c r="F233" t="n">
         <v>3113087</v>
@@ -5092,16 +5092,16 @@
         <v>44491</v>
       </c>
       <c r="B234" t="n">
-        <v>32.63495254516602</v>
+        <v>32.63494873046875</v>
       </c>
       <c r="C234" t="n">
-        <v>34.06723862420559</v>
+        <v>34.06723464208851</v>
       </c>
       <c r="D234" t="n">
-        <v>31.04886594627039</v>
+        <v>31.04886231697067</v>
       </c>
       <c r="E234" t="n">
-        <v>33.63467091453443</v>
+        <v>33.63466698298016</v>
       </c>
       <c r="F234" t="n">
         <v>4894520</v>
@@ -5112,16 +5112,16 @@
         <v>44494</v>
       </c>
       <c r="B235" t="n">
-        <v>36.84706115722656</v>
+        <v>36.8470573425293</v>
       </c>
       <c r="C235" t="n">
-        <v>37.31127712193275</v>
+        <v>37.3112732591762</v>
       </c>
       <c r="D235" t="n">
-        <v>32.95926229019877</v>
+        <v>32.95925887799699</v>
       </c>
       <c r="E235" t="n">
-        <v>32.95926229019877</v>
+        <v>32.95925887799699</v>
       </c>
       <c r="F235" t="n">
         <v>3449995</v>
@@ -5152,16 +5152,16 @@
         <v>44496</v>
       </c>
       <c r="B237" t="n">
-        <v>35.29000473022461</v>
+        <v>35.29000854492188</v>
       </c>
       <c r="C237" t="n">
-        <v>36.07336794668348</v>
+        <v>36.07337184605893</v>
       </c>
       <c r="D237" t="n">
-        <v>34.47762778370612</v>
+        <v>34.47763151058894</v>
       </c>
       <c r="E237" t="n">
-        <v>36.07336794668348</v>
+        <v>36.07337184605893</v>
       </c>
       <c r="F237" t="n">
         <v>2270538</v>
@@ -5272,16 +5272,16 @@
         <v>44505</v>
       </c>
       <c r="B243" t="n">
-        <v>34.33256149291992</v>
+        <v>34.33255767822266</v>
       </c>
       <c r="C243" t="n">
-        <v>35.80257809171644</v>
+        <v>35.80257411368536</v>
       </c>
       <c r="D243" t="n">
-        <v>31.73102433433615</v>
+        <v>31.73102080869616</v>
       </c>
       <c r="E243" t="n">
-        <v>33.17202720107906</v>
+        <v>33.17202351532898</v>
       </c>
       <c r="F243" t="n">
         <v>9166770</v>
@@ -5312,16 +5312,16 @@
         <v>44509</v>
       </c>
       <c r="B245" t="n">
-        <v>34.50664520263672</v>
+        <v>34.50664138793945</v>
       </c>
       <c r="C245" t="n">
-        <v>35.10625735786877</v>
+        <v>35.1062534768846</v>
       </c>
       <c r="D245" t="n">
-        <v>32.63044377861175</v>
+        <v>32.63044017132788</v>
       </c>
       <c r="E245" t="n">
-        <v>33.89736430140155</v>
+        <v>33.89736055406007</v>
       </c>
       <c r="F245" t="n">
         <v>7032350</v>
@@ -5372,16 +5372,16 @@
         <v>44512</v>
       </c>
       <c r="B248" t="n">
-        <v>30.94766235351562</v>
+        <v>30.94766044616699</v>
       </c>
       <c r="C248" t="n">
-        <v>33.11399911175717</v>
+        <v>33.11399707089411</v>
       </c>
       <c r="D248" t="n">
-        <v>30.69621126299056</v>
+        <v>30.69620937113922</v>
       </c>
       <c r="E248" t="n">
-        <v>32.10819849723269</v>
+        <v>32.10819651835855</v>
       </c>
       <c r="F248" t="n">
         <v>3403064</v>
@@ -5552,16 +5552,16 @@
         <v>44526</v>
       </c>
       <c r="B257" t="n">
-        <v>26.69235992431641</v>
+        <v>26.69235801696777</v>
       </c>
       <c r="C257" t="n">
-        <v>27.61111748815896</v>
+        <v>27.61111551515892</v>
       </c>
       <c r="D257" t="n">
-        <v>25.85096918966023</v>
+        <v>25.85096734243463</v>
       </c>
       <c r="E257" t="n">
-        <v>26.59564810870458</v>
+        <v>26.59564620826666</v>
       </c>
       <c r="F257" t="n">
         <v>3664026</v>
@@ -5592,16 +5592,16 @@
         <v>44530</v>
       </c>
       <c r="B259" t="n">
-        <v>26.71170043945312</v>
+        <v>26.71169853210449</v>
       </c>
       <c r="C259" t="n">
-        <v>26.71170043945312</v>
+        <v>26.71169853210449</v>
       </c>
       <c r="D259" t="n">
-        <v>25.48346622320262</v>
+        <v>25.48346440355603</v>
       </c>
       <c r="E259" t="n">
-        <v>26.53761992558345</v>
+        <v>26.53761803066504</v>
       </c>
       <c r="F259" t="n">
         <v>4757647</v>
@@ -5612,16 +5612,16 @@
         <v>44531</v>
       </c>
       <c r="B260" t="n">
-        <v>26.69235992431641</v>
+        <v>26.69235801696777</v>
       </c>
       <c r="C260" t="n">
-        <v>28.01730598945588</v>
+        <v>28.01730398743094</v>
       </c>
       <c r="D260" t="n">
-        <v>26.32485577450663</v>
+        <v>26.32485389341864</v>
       </c>
       <c r="E260" t="n">
-        <v>27.17591712858762</v>
+        <v>27.17591518668557</v>
       </c>
       <c r="F260" t="n">
         <v>3467467</v>
@@ -5752,16 +5752,16 @@
         <v>44540</v>
       </c>
       <c r="B267" t="n">
-        <v>29.43896102905273</v>
+        <v>29.43896293640137</v>
       </c>
       <c r="C267" t="n">
-        <v>29.76778079564096</v>
+        <v>29.76778272429381</v>
       </c>
       <c r="D267" t="n">
-        <v>28.76198025889329</v>
+        <v>28.76198212238038</v>
       </c>
       <c r="E267" t="n">
-        <v>29.57435718308462</v>
+        <v>29.57435909920557</v>
       </c>
       <c r="F267" t="n">
         <v>1281952</v>
@@ -5832,16 +5832,16 @@
         <v>44546</v>
       </c>
       <c r="B271" t="n">
-        <v>30.62851524353027</v>
+        <v>30.62851333618164</v>
       </c>
       <c r="C271" t="n">
-        <v>30.86062322322113</v>
+        <v>30.86062130141829</v>
       </c>
       <c r="D271" t="n">
-        <v>29.25521235155887</v>
+        <v>29.25521052973079</v>
       </c>
       <c r="E271" t="n">
-        <v>29.49699095054871</v>
+        <v>29.4969891136642</v>
       </c>
       <c r="F271" t="n">
         <v>3477726</v>
@@ -5952,16 +5952,16 @@
         <v>44557</v>
       </c>
       <c r="B277" t="n">
-        <v>30.7252254486084</v>
+        <v>30.72522354125977</v>
       </c>
       <c r="C277" t="n">
-        <v>31.01536089416671</v>
+        <v>31.01535896880716</v>
       </c>
       <c r="D277" t="n">
-        <v>29.98054840663</v>
+        <v>29.98054654550914</v>
       </c>
       <c r="E277" t="n">
-        <v>29.98054840663</v>
+        <v>29.98054654550914</v>
       </c>
       <c r="F277" t="n">
         <v>1273927</v>
@@ -6132,16 +6132,16 @@
         <v>44571</v>
       </c>
       <c r="B286" t="n">
-        <v>33.37511825561523</v>
+        <v>33.37511444091797</v>
       </c>
       <c r="C286" t="n">
-        <v>33.89736166431392</v>
+        <v>33.89735778992546</v>
       </c>
       <c r="D286" t="n">
-        <v>32.24359399308115</v>
+        <v>32.24359030771443</v>
       </c>
       <c r="E286" t="n">
-        <v>32.3789901547752</v>
+        <v>32.37898645393302</v>
       </c>
       <c r="F286" t="n">
         <v>2829132</v>
@@ -6152,16 +6152,16 @@
         <v>44572</v>
       </c>
       <c r="B287" t="n">
-        <v>35.10625076293945</v>
+        <v>35.10625457763672</v>
       </c>
       <c r="C287" t="n">
-        <v>35.63816285834681</v>
+        <v>35.63816673084244</v>
       </c>
       <c r="D287" t="n">
-        <v>33.18169098013564</v>
+        <v>33.18169458570739</v>
       </c>
       <c r="E287" t="n">
-        <v>33.55886569280182</v>
+        <v>33.55886933935793</v>
       </c>
       <c r="F287" t="n">
         <v>3953735</v>
@@ -6172,16 +6172,16 @@
         <v>44573</v>
       </c>
       <c r="B288" t="n">
-        <v>34.89348602294922</v>
+        <v>34.89348983764648</v>
       </c>
       <c r="C288" t="n">
-        <v>35.98632394454952</v>
+        <v>35.98632787872025</v>
       </c>
       <c r="D288" t="n">
-        <v>34.13913659549451</v>
+        <v>34.13914032772324</v>
       </c>
       <c r="E288" t="n">
-        <v>35.34802942826484</v>
+        <v>35.34803329265463</v>
       </c>
       <c r="F288" t="n">
         <v>3302601</v>
@@ -6292,16 +6292,16 @@
         <v>44581</v>
       </c>
       <c r="B294" t="n">
-        <v>35.2996711730957</v>
+        <v>35.29967498779297</v>
       </c>
       <c r="C294" t="n">
-        <v>36.17007552296929</v>
+        <v>36.17007943172774</v>
       </c>
       <c r="D294" t="n">
-        <v>34.98052391082881</v>
+        <v>34.98052769103708</v>
       </c>
       <c r="E294" t="n">
-        <v>35.8702694969556</v>
+        <v>35.87027337331519</v>
       </c>
       <c r="F294" t="n">
         <v>3650414</v>
@@ -6332,16 +6332,16 @@
         <v>44585</v>
       </c>
       <c r="B296" t="n">
-        <v>34.35190582275391</v>
+        <v>34.35190200805664</v>
       </c>
       <c r="C296" t="n">
-        <v>35.31902021252021</v>
+        <v>35.3190162904272</v>
       </c>
       <c r="D296" t="n">
-        <v>34.05209976231423</v>
+        <v>34.05209598090971</v>
       </c>
       <c r="E296" t="n">
-        <v>34.2358508967577</v>
+        <v>34.23584709494806</v>
       </c>
       <c r="F296" t="n">
         <v>2113697</v>
@@ -6392,16 +6392,16 @@
         <v>44588</v>
       </c>
       <c r="B299" t="n">
-        <v>36.09270858764648</v>
+        <v>36.09271240234375</v>
       </c>
       <c r="C299" t="n">
-        <v>37.10817788022283</v>
+        <v>37.1081818022467</v>
       </c>
       <c r="D299" t="n">
-        <v>35.68652012110085</v>
+        <v>35.68652389286739</v>
       </c>
       <c r="E299" t="n">
-        <v>35.87994373577622</v>
+        <v>35.87994752798603</v>
       </c>
       <c r="F299" t="n">
         <v>3171460</v>
@@ -6492,16 +6492,16 @@
         <v>44595</v>
       </c>
       <c r="B304" t="n">
-        <v>35.2996711730957</v>
+        <v>35.29967498779297</v>
       </c>
       <c r="C304" t="n">
-        <v>35.58980845477045</v>
+        <v>35.58981230082171</v>
       </c>
       <c r="D304" t="n">
-        <v>33.84899975502328</v>
+        <v>33.84900341295216</v>
       </c>
       <c r="E304" t="n">
-        <v>34.98052391082881</v>
+        <v>34.98052769103708</v>
       </c>
       <c r="F304" t="n">
         <v>4177823</v>
@@ -6592,16 +6592,16 @@
         <v>44602</v>
       </c>
       <c r="B309" t="n">
-        <v>37.28226089477539</v>
+        <v>37.28226470947266</v>
       </c>
       <c r="C309" t="n">
-        <v>38.38477139493146</v>
+        <v>38.3847753224369</v>
       </c>
       <c r="D309" t="n">
-        <v>36.33448778997354</v>
+        <v>36.33449150769526</v>
       </c>
       <c r="E309" t="n">
-        <v>36.3635015200494</v>
+        <v>36.36350524073979</v>
       </c>
       <c r="F309" t="n">
         <v>7025951</v>
@@ -6612,16 +6612,16 @@
         <v>44603</v>
       </c>
       <c r="B310" t="n">
-        <v>38.07529449462891</v>
+        <v>38.07529067993164</v>
       </c>
       <c r="C310" t="n">
-        <v>38.49115547855604</v>
+        <v>38.49115162219439</v>
       </c>
       <c r="D310" t="n">
-        <v>37.37897243800389</v>
+        <v>37.37896869306991</v>
       </c>
       <c r="E310" t="n">
-        <v>37.78516092896444</v>
+        <v>37.78515714333515</v>
       </c>
       <c r="F310" t="n">
         <v>5486491</v>
@@ -6632,16 +6632,16 @@
         <v>44606</v>
       </c>
       <c r="B311" t="n">
-        <v>37.57239532470703</v>
+        <v>37.57239151000977</v>
       </c>
       <c r="C311" t="n">
-        <v>38.84898823510746</v>
+        <v>38.84898429079868</v>
       </c>
       <c r="D311" t="n">
-        <v>36.95344198127135</v>
+        <v>36.95343822941596</v>
       </c>
       <c r="E311" t="n">
-        <v>38.2977310983781</v>
+        <v>38.29772721003804</v>
       </c>
       <c r="F311" t="n">
         <v>3902640</v>
@@ -6652,16 +6652,16 @@
         <v>44607</v>
       </c>
       <c r="B312" t="n">
-        <v>35.79290390014648</v>
+        <v>35.79290008544922</v>
       </c>
       <c r="C312" t="n">
-        <v>36.65363583255173</v>
+        <v>36.65363192612031</v>
       </c>
       <c r="D312" t="n">
-        <v>35.63816650158672</v>
+        <v>35.63816270338088</v>
       </c>
       <c r="E312" t="n">
-        <v>36.55692589534578</v>
+        <v>36.55692199922141</v>
       </c>
       <c r="F312" t="n">
         <v>3810709</v>
@@ -6672,16 +6672,16 @@
         <v>44608</v>
       </c>
       <c r="B313" t="n">
-        <v>35.92829895019531</v>
+        <v>35.92830276489258</v>
       </c>
       <c r="C313" t="n">
-        <v>36.80837209332255</v>
+        <v>36.80837600146183</v>
       </c>
       <c r="D313" t="n">
-        <v>35.69619285953032</v>
+        <v>35.69619664958365</v>
       </c>
       <c r="E313" t="n">
-        <v>36.4408698462091</v>
+        <v>36.44087371532872</v>
       </c>
       <c r="F313" t="n">
         <v>4244663</v>
@@ -6692,16 +6692,16 @@
         <v>44609</v>
       </c>
       <c r="B314" t="n">
-        <v>35.2996711730957</v>
+        <v>35.29967498779297</v>
       </c>
       <c r="C314" t="n">
-        <v>35.89928322512308</v>
+        <v>35.89928710461807</v>
       </c>
       <c r="D314" t="n">
-        <v>34.41959807888318</v>
+        <v>34.41960179847439</v>
       </c>
       <c r="E314" t="n">
-        <v>35.68651838361181</v>
+        <v>35.68652224011414</v>
       </c>
       <c r="F314" t="n">
         <v>4430658</v>
@@ -6712,16 +6712,16 @@
         <v>44610</v>
       </c>
       <c r="B315" t="n">
-        <v>34.48729705810547</v>
+        <v>34.48730087280273</v>
       </c>
       <c r="C315" t="n">
-        <v>35.41572509065163</v>
+        <v>35.41572900804387</v>
       </c>
       <c r="D315" t="n">
-        <v>33.80064384086931</v>
+        <v>33.80064757961473</v>
       </c>
       <c r="E315" t="n">
-        <v>34.83545803875718</v>
+        <v>34.83546189196511</v>
       </c>
       <c r="F315" t="n">
         <v>4069741</v>
@@ -6852,16 +6852,16 @@
         <v>44623</v>
       </c>
       <c r="B322" t="n">
-        <v>37.34028244018555</v>
+        <v>37.34028625488281</v>
       </c>
       <c r="C322" t="n">
-        <v>37.88187078764361</v>
+        <v>37.88187465766974</v>
       </c>
       <c r="D322" t="n">
-        <v>36.31514444477941</v>
+        <v>36.31514815474819</v>
       </c>
       <c r="E322" t="n">
-        <v>37.12751759702811</v>
+        <v>37.12752138998924</v>
       </c>
       <c r="F322" t="n">
         <v>9786414</v>
@@ -6892,16 +6892,16 @@
         <v>44627</v>
       </c>
       <c r="B324" t="n">
-        <v>37.04048538208008</v>
+        <v>37.04048156738281</v>
       </c>
       <c r="C324" t="n">
-        <v>39.28418904358112</v>
+        <v>39.28418499781101</v>
       </c>
       <c r="D324" t="n">
-        <v>36.65363811402602</v>
+        <v>36.65363433916909</v>
       </c>
       <c r="E324" t="n">
-        <v>38.17200970618351</v>
+        <v>38.17200577495368</v>
       </c>
       <c r="F324" t="n">
         <v>5025922</v>
@@ -6952,16 +6952,16 @@
         <v>44630</v>
       </c>
       <c r="B327" t="n">
-        <v>35.72520446777344</v>
+        <v>35.7252082824707</v>
       </c>
       <c r="C327" t="n">
-        <v>37.22423084456335</v>
+        <v>37.22423481932497</v>
       </c>
       <c r="D327" t="n">
-        <v>35.51243962707166</v>
+        <v>35.51244341905014</v>
       </c>
       <c r="E327" t="n">
-        <v>36.75034245134777</v>
+        <v>36.75034637550812</v>
       </c>
       <c r="F327" t="n">
         <v>4502679</v>
@@ -7032,16 +7032,16 @@
         <v>44636</v>
       </c>
       <c r="B331" t="n">
-        <v>32.84320831298828</v>
+        <v>32.84320449829102</v>
       </c>
       <c r="C331" t="n">
-        <v>34.44861737575539</v>
+        <v>34.44861337459189</v>
       </c>
       <c r="D331" t="n">
-        <v>32.34030985608281</v>
+        <v>32.34030609979657</v>
       </c>
       <c r="E331" t="n">
-        <v>34.10045632903992</v>
+        <v>34.10045236831488</v>
       </c>
       <c r="F331" t="n">
         <v>3899288</v>
@@ -7092,16 +7092,16 @@
         <v>44641</v>
       </c>
       <c r="B334" t="n">
-        <v>36.61495208740234</v>
+        <v>36.61494827270508</v>
       </c>
       <c r="C334" t="n">
-        <v>36.86640318776314</v>
+        <v>36.86639934686866</v>
       </c>
       <c r="D334" t="n">
-        <v>35.88961626653654</v>
+        <v>35.88961252740777</v>
       </c>
       <c r="E334" t="n">
-        <v>35.97665746445866</v>
+        <v>35.97665371626157</v>
       </c>
       <c r="F334" t="n">
         <v>3600944</v>
@@ -7212,16 +7212,16 @@
         <v>44649</v>
       </c>
       <c r="B340" t="n">
-        <v>40.11590576171875</v>
+        <v>40.11590194702148</v>
       </c>
       <c r="C340" t="n">
-        <v>40.60913544747385</v>
+        <v>40.60913158587444</v>
       </c>
       <c r="D340" t="n">
-        <v>37.8141747233464</v>
+        <v>37.81417112752509</v>
       </c>
       <c r="E340" t="n">
-        <v>38.00759834997051</v>
+        <v>38.00759473575618</v>
       </c>
       <c r="F340" t="n">
         <v>6952609</v>
@@ -7252,16 +7252,16 @@
         <v>44651</v>
       </c>
       <c r="B342" t="n">
-        <v>40.47373580932617</v>
+        <v>40.47373962402344</v>
       </c>
       <c r="C342" t="n">
-        <v>41.13137533388116</v>
+        <v>41.13137921056172</v>
       </c>
       <c r="D342" t="n">
-        <v>39.6710313879373</v>
+        <v>39.67103512697872</v>
       </c>
       <c r="E342" t="n">
-        <v>40.13524730247168</v>
+        <v>40.135251085266</v>
       </c>
       <c r="F342" t="n">
         <v>3810811</v>
@@ -7312,16 +7312,16 @@
         <v>44656</v>
       </c>
       <c r="B345" t="n">
-        <v>41.9727668762207</v>
+        <v>41.97276306152344</v>
       </c>
       <c r="C345" t="n">
-        <v>43.03659497534015</v>
+        <v>43.03659106395681</v>
       </c>
       <c r="D345" t="n">
-        <v>41.5762508676977</v>
+        <v>41.57624708903781</v>
       </c>
       <c r="E345" t="n">
-        <v>42.30158667490721</v>
+        <v>42.30158283032514</v>
       </c>
       <c r="F345" t="n">
         <v>5903074</v>
@@ -7432,16 +7432,16 @@
         <v>44664</v>
       </c>
       <c r="B351" t="n">
-        <v>43.62653350830078</v>
+        <v>43.62652969360352</v>
       </c>
       <c r="C351" t="n">
-        <v>43.71357095479976</v>
+        <v>43.71356713249195</v>
       </c>
       <c r="D351" t="n">
-        <v>42.8431702567798</v>
+        <v>42.8431665105797</v>
       </c>
       <c r="E351" t="n">
-        <v>43.30738621093589</v>
+        <v>43.30738242414481</v>
       </c>
       <c r="F351" t="n">
         <v>3238402</v>
@@ -7452,16 +7452,16 @@
         <v>44665</v>
       </c>
       <c r="B352" t="n">
-        <v>42.93987655639648</v>
+        <v>42.93988037109375</v>
       </c>
       <c r="C352" t="n">
-        <v>43.62652981023535</v>
+        <v>43.62653368593358</v>
       </c>
       <c r="D352" t="n">
-        <v>42.2242133212342</v>
+        <v>42.2242170723533</v>
       </c>
       <c r="E352" t="n">
-        <v>43.62652981023535</v>
+        <v>43.62653368593358</v>
       </c>
       <c r="F352" t="n">
         <v>2345809</v>
@@ -7552,16 +7552,16 @@
         <v>44676</v>
       </c>
       <c r="B357" t="n">
-        <v>41.94374847412109</v>
+        <v>41.94375228881836</v>
       </c>
       <c r="C357" t="n">
-        <v>42.40796438837074</v>
+        <v>42.40796824528748</v>
       </c>
       <c r="D357" t="n">
-        <v>40.64781815768625</v>
+        <v>40.64782185452133</v>
       </c>
       <c r="E357" t="n">
-        <v>40.75420058099602</v>
+        <v>40.75420428750637</v>
       </c>
       <c r="F357" t="n">
         <v>3287465</v>
@@ -7592,16 +7592,16 @@
         <v>44678</v>
       </c>
       <c r="B359" t="n">
-        <v>42.16619110107422</v>
+        <v>42.16618728637695</v>
       </c>
       <c r="C359" t="n">
-        <v>43.58784900340616</v>
+        <v>43.58784506009413</v>
       </c>
       <c r="D359" t="n">
-        <v>41.46986901615963</v>
+        <v>41.46986526445734</v>
       </c>
       <c r="E359" t="n">
-        <v>43.52015279261696</v>
+        <v>43.52014885542929</v>
       </c>
       <c r="F359" t="n">
         <v>3779727</v>
@@ -7672,16 +7672,16 @@
         <v>44684</v>
       </c>
       <c r="B363" t="n">
-        <v>42.12749862670898</v>
+        <v>42.12750244140625</v>
       </c>
       <c r="C363" t="n">
-        <v>42.54335956584936</v>
+        <v>42.54336341820335</v>
       </c>
       <c r="D363" t="n">
-        <v>41.25709802345466</v>
+        <v>41.25710175933607</v>
       </c>
       <c r="E363" t="n">
-        <v>42.54335956584936</v>
+        <v>42.54336341820335</v>
       </c>
       <c r="F363" t="n">
         <v>4458389</v>
@@ -7692,16 +7692,16 @@
         <v>44685</v>
       </c>
       <c r="B364" t="n">
-        <v>44.10041809082031</v>
+        <v>44.10041427612305</v>
       </c>
       <c r="C364" t="n">
-        <v>44.32285544811791</v>
+        <v>44.32285161417975</v>
       </c>
       <c r="D364" t="n">
-        <v>42.16618932580826</v>
+        <v>42.16618567842227</v>
       </c>
       <c r="E364" t="n">
-        <v>43.04626251447057</v>
+        <v>43.04625879095802</v>
       </c>
       <c r="F364" t="n">
         <v>5759540</v>
@@ -7712,16 +7712,16 @@
         <v>44686</v>
       </c>
       <c r="B365" t="n">
-        <v>42.92053604125977</v>
+        <v>42.92053985595703</v>
       </c>
       <c r="C365" t="n">
-        <v>44.57429987842104</v>
+        <v>44.57430384010176</v>
       </c>
       <c r="D365" t="n">
-        <v>42.01144918067956</v>
+        <v>42.01145291457887</v>
       </c>
       <c r="E365" t="n">
-        <v>44.09074271874429</v>
+        <v>44.09074663744735</v>
       </c>
       <c r="F365" t="n">
         <v>4814532</v>
@@ -7732,16 +7732,16 @@
         <v>44687</v>
       </c>
       <c r="B366" t="n">
-        <v>42.55303192138672</v>
+        <v>42.55303573608398</v>
       </c>
       <c r="C366" t="n">
-        <v>43.90698966019007</v>
+        <v>43.90699359626386</v>
       </c>
       <c r="D366" t="n">
-        <v>41.82769621387857</v>
+        <v>41.82769996355259</v>
       </c>
       <c r="E366" t="n">
-        <v>43.33639133753226</v>
+        <v>43.33639522245434</v>
       </c>
       <c r="F366" t="n">
         <v>4093307</v>
@@ -7892,16 +7892,16 @@
         <v>44699</v>
       </c>
       <c r="B374" t="n">
-        <v>39.99985122680664</v>
+        <v>39.99985504150391</v>
       </c>
       <c r="C374" t="n">
-        <v>42.2242133773643</v>
+        <v>42.22421740419406</v>
       </c>
       <c r="D374" t="n">
-        <v>39.72905892177436</v>
+        <v>39.72906271064676</v>
       </c>
       <c r="E374" t="n">
-        <v>42.13717219055205</v>
+        <v>42.13717620908088</v>
       </c>
       <c r="F374" t="n">
         <v>1865839</v>
@@ -7952,16 +7952,16 @@
         <v>44704</v>
       </c>
       <c r="B377" t="n">
-        <v>42.28224182128906</v>
+        <v>42.28224563598633</v>
       </c>
       <c r="C377" t="n">
-        <v>42.7948127143697</v>
+        <v>42.79481657531103</v>
       </c>
       <c r="D377" t="n">
-        <v>41.3538099687909</v>
+        <v>41.35381369972519</v>
       </c>
       <c r="E377" t="n">
-        <v>41.42150992041549</v>
+        <v>41.42151365745766</v>
       </c>
       <c r="F377" t="n">
         <v>3400119</v>
@@ -8012,16 +8012,16 @@
         <v>44707</v>
       </c>
       <c r="B380" t="n">
-        <v>46.59557342529297</v>
+        <v>46.5955696105957</v>
       </c>
       <c r="C380" t="n">
-        <v>47.16617181868395</v>
+        <v>47.1661679572728</v>
       </c>
       <c r="D380" t="n">
-        <v>45.10621935322675</v>
+        <v>45.10621566046026</v>
       </c>
       <c r="E380" t="n">
-        <v>45.25128426416589</v>
+        <v>45.2512805595232</v>
       </c>
       <c r="F380" t="n">
         <v>4582217</v>
@@ -8072,16 +8072,16 @@
         <v>44712</v>
       </c>
       <c r="B383" t="n">
-        <v>47.14683151245117</v>
+        <v>47.14682769775391</v>
       </c>
       <c r="C383" t="n">
-        <v>49.54527256510714</v>
+        <v>49.5452685563496</v>
       </c>
       <c r="D383" t="n">
-        <v>47.11781778017441</v>
+        <v>47.11781396782467</v>
       </c>
       <c r="E383" t="n">
-        <v>48.22032836396376</v>
+        <v>48.22032446240879</v>
       </c>
       <c r="F383" t="n">
         <v>6322705</v>
@@ -8152,16 +8152,16 @@
         <v>44718</v>
       </c>
       <c r="B387" t="n">
-        <v>45.31898498535156</v>
+        <v>45.3189811706543</v>
       </c>
       <c r="C387" t="n">
-        <v>47.45630618888874</v>
+        <v>47.4563021942838</v>
       </c>
       <c r="D387" t="n">
-        <v>45.13523009894016</v>
+        <v>45.13522629971035</v>
       </c>
       <c r="E387" t="n">
-        <v>47.156500121283</v>
+        <v>47.15649615191405</v>
       </c>
       <c r="F387" t="n">
         <v>1711233</v>
@@ -8172,16 +8172,16 @@
         <v>44719</v>
       </c>
       <c r="B388" t="n">
-        <v>45.31898498535156</v>
+        <v>45.3189811706543</v>
       </c>
       <c r="C388" t="n">
-        <v>45.84122466966569</v>
+        <v>45.84122081100923</v>
       </c>
       <c r="D388" t="n">
-        <v>44.73871408907649</v>
+        <v>44.73871032322317</v>
       </c>
       <c r="E388" t="n">
-        <v>44.98049269229714</v>
+        <v>44.98048890609225</v>
       </c>
       <c r="F388" t="n">
         <v>1887578</v>
@@ -8192,16 +8192,16 @@
         <v>44720</v>
       </c>
       <c r="B389" t="n">
-        <v>45.25128173828125</v>
+        <v>45.25128555297852</v>
       </c>
       <c r="C389" t="n">
-        <v>46.00563122530019</v>
+        <v>46.00563510358936</v>
       </c>
       <c r="D389" t="n">
-        <v>44.9224619623857</v>
+        <v>44.92246574936335</v>
       </c>
       <c r="E389" t="n">
-        <v>45.31898169100119</v>
+        <v>45.31898551140559</v>
       </c>
       <c r="F389" t="n">
         <v>1920490</v>
@@ -8212,16 +8212,16 @@
         <v>44721</v>
       </c>
       <c r="B390" t="n">
-        <v>44.50660705566406</v>
+        <v>44.5066032409668</v>
       </c>
       <c r="C390" t="n">
-        <v>45.59944512032232</v>
+        <v>45.59944121195702</v>
       </c>
       <c r="D390" t="n">
-        <v>44.32285592064108</v>
+        <v>44.32285212169327</v>
       </c>
       <c r="E390" t="n">
-        <v>45.2222703572209</v>
+        <v>45.22226648118356</v>
       </c>
       <c r="F390" t="n">
         <v>1644697</v>
@@ -8472,16 +8472,16 @@
         <v>44741</v>
       </c>
       <c r="B403" t="n">
-        <v>34.71940994262695</v>
+        <v>34.71940612792969</v>
       </c>
       <c r="C403" t="n">
-        <v>35.41573204057546</v>
+        <v>35.41572814937177</v>
       </c>
       <c r="D403" t="n">
-        <v>34.0907840567348</v>
+        <v>34.09078031110602</v>
       </c>
       <c r="E403" t="n">
-        <v>35.29967710839206</v>
+        <v>35.29967322993957</v>
       </c>
       <c r="F403" t="n">
         <v>2690880</v>
@@ -8532,16 +8532,16 @@
         <v>44746</v>
       </c>
       <c r="B406" t="n">
-        <v>35.08690643310547</v>
+        <v>35.08691024780273</v>
       </c>
       <c r="C406" t="n">
-        <v>35.60914979405575</v>
+        <v>35.60915366553204</v>
       </c>
       <c r="D406" t="n">
-        <v>34.19716459197961</v>
+        <v>34.1971683099429</v>
       </c>
       <c r="E406" t="n">
-        <v>34.57433556409744</v>
+        <v>34.57433932306729</v>
       </c>
       <c r="F406" t="n">
         <v>2359523</v>
@@ -8612,16 +8612,16 @@
         <v>44750</v>
       </c>
       <c r="B410" t="n">
-        <v>31.81806564331055</v>
+        <v>31.81806373596191</v>
       </c>
       <c r="C410" t="n">
-        <v>32.48537398775778</v>
+        <v>32.48537204040704</v>
       </c>
       <c r="D410" t="n">
-        <v>31.19911226993215</v>
+        <v>31.19911039968697</v>
       </c>
       <c r="E410" t="n">
-        <v>31.31516719855805</v>
+        <v>31.3151653213559</v>
       </c>
       <c r="F410" t="n">
         <v>4375906</v>
@@ -8712,16 +8712,16 @@
         <v>44757</v>
       </c>
       <c r="B415" t="n">
-        <v>27.79486656188965</v>
+        <v>27.79486846923828</v>
       </c>
       <c r="C415" t="n">
-        <v>29.07145943509457</v>
+        <v>29.07146143004599</v>
       </c>
       <c r="D415" t="n">
-        <v>27.79486656188965</v>
+        <v>27.79486846923828</v>
       </c>
       <c r="E415" t="n">
-        <v>29.06178694260021</v>
+        <v>29.06178893688788</v>
       </c>
       <c r="F415" t="n">
         <v>4618481</v>
@@ -8752,16 +8752,16 @@
         <v>44761</v>
       </c>
       <c r="B417" t="n">
-        <v>29.43896102905273</v>
+        <v>29.43896293640137</v>
       </c>
       <c r="C417" t="n">
-        <v>29.5356728353309</v>
+        <v>29.53567474894549</v>
       </c>
       <c r="D417" t="n">
-        <v>28.11401509178381</v>
+        <v>28.11401691328927</v>
       </c>
       <c r="E417" t="n">
-        <v>28.14302882104603</v>
+        <v>28.14303064443129</v>
       </c>
       <c r="F417" t="n">
         <v>4570230</v>
@@ -8772,16 +8772,16 @@
         <v>44762</v>
       </c>
       <c r="B418" t="n">
-        <v>30.5994987487793</v>
+        <v>30.59950065612793</v>
       </c>
       <c r="C418" t="n">
-        <v>30.97667347904845</v>
+        <v>30.97667540990739</v>
       </c>
       <c r="D418" t="n">
-        <v>29.21652536238831</v>
+        <v>29.21652718353251</v>
       </c>
       <c r="E418" t="n">
-        <v>29.21652536238831</v>
+        <v>29.21652718353251</v>
       </c>
       <c r="F418" t="n">
         <v>5027446</v>
@@ -8792,16 +8792,16 @@
         <v>44763</v>
       </c>
       <c r="B419" t="n">
-        <v>29.44863319396973</v>
+        <v>29.44863510131836</v>
       </c>
       <c r="C419" t="n">
-        <v>29.86449039614633</v>
+        <v>29.86449233042948</v>
       </c>
       <c r="D419" t="n">
-        <v>28.83935050759925</v>
+        <v>28.83935237548546</v>
       </c>
       <c r="E419" t="n">
-        <v>29.86449039614633</v>
+        <v>29.86449233042948</v>
       </c>
       <c r="F419" t="n">
         <v>5437325</v>
@@ -8832,16 +8832,16 @@
         <v>44767</v>
       </c>
       <c r="B421" t="n">
-        <v>29.26488304138184</v>
+        <v>29.2648811340332</v>
       </c>
       <c r="C421" t="n">
-        <v>29.71942650877206</v>
+        <v>29.7194245717984</v>
       </c>
       <c r="D421" t="n">
-        <v>28.43316480875549</v>
+        <v>28.43316295561438</v>
       </c>
       <c r="E421" t="n">
-        <v>28.87803765682343</v>
+        <v>28.87803577468757</v>
       </c>
       <c r="F421" t="n">
         <v>3521914</v>
@@ -8852,16 +8852,16 @@
         <v>44768</v>
       </c>
       <c r="B422" t="n">
-        <v>28.95540618896484</v>
+        <v>28.95540428161621</v>
       </c>
       <c r="C422" t="n">
-        <v>30.15462856046375</v>
+        <v>30.15462657412001</v>
       </c>
       <c r="D422" t="n">
-        <v>28.81033940483069</v>
+        <v>28.81033750703789</v>
       </c>
       <c r="E422" t="n">
-        <v>29.88383623072646</v>
+        <v>29.88383426222034</v>
       </c>
       <c r="F422" t="n">
         <v>2984449</v>
@@ -8872,16 +8872,16 @@
         <v>44769</v>
       </c>
       <c r="B423" t="n">
-        <v>29.66139793395996</v>
+        <v>29.66139984130859</v>
       </c>
       <c r="C423" t="n">
-        <v>29.76778035716261</v>
+        <v>29.76778227135207</v>
       </c>
       <c r="D423" t="n">
-        <v>28.6169130648438</v>
+        <v>28.61691490502781</v>
       </c>
       <c r="E423" t="n">
-        <v>28.95540344493757</v>
+        <v>28.95540530688788</v>
       </c>
       <c r="F423" t="n">
         <v>2554762</v>
@@ -8892,16 +8892,16 @@
         <v>44770</v>
       </c>
       <c r="B424" t="n">
-        <v>30.78325080871582</v>
+        <v>30.78325271606445</v>
       </c>
       <c r="C424" t="n">
-        <v>30.88963323601387</v>
+        <v>30.88963514995402</v>
       </c>
       <c r="D424" t="n">
-        <v>29.53567353730325</v>
+        <v>29.53567536735125</v>
       </c>
       <c r="E424" t="n">
-        <v>29.96120324649545</v>
+        <v>29.96120510290952</v>
       </c>
       <c r="F424" t="n">
         <v>4208906</v>
@@ -8952,16 +8952,16 @@
         <v>44775</v>
       </c>
       <c r="B427" t="n">
-        <v>31.85675048828125</v>
+        <v>31.85674858093262</v>
       </c>
       <c r="C427" t="n">
-        <v>32.07918409507452</v>
+        <v>32.0791821744082</v>
       </c>
       <c r="D427" t="n">
-        <v>30.94766170651904</v>
+        <v>30.94765985359998</v>
       </c>
       <c r="E427" t="n">
-        <v>31.32483646063348</v>
+        <v>31.32483458513196</v>
       </c>
       <c r="F427" t="n">
         <v>3020206</v>
@@ -9072,16 +9072,16 @@
         <v>44783</v>
       </c>
       <c r="B433" t="n">
-        <v>33.26873779296875</v>
+        <v>33.26873397827148</v>
       </c>
       <c r="C433" t="n">
-        <v>33.97473237410905</v>
+        <v>33.97472847846024</v>
       </c>
       <c r="D433" t="n">
-        <v>32.87222177725572</v>
+        <v>32.87221800802422</v>
       </c>
       <c r="E433" t="n">
-        <v>33.62657133023831</v>
+        <v>33.62656747451073</v>
       </c>
       <c r="F433" t="n">
         <v>3325457</v>
@@ -9152,16 +9152,16 @@
         <v>44789</v>
       </c>
       <c r="B437" t="n">
-        <v>32.27260971069336</v>
+        <v>32.27260589599609</v>
       </c>
       <c r="C437" t="n">
-        <v>32.61110200955398</v>
+        <v>32.61109815484615</v>
       </c>
       <c r="D437" t="n">
-        <v>31.73102503057709</v>
+        <v>31.73102127989639</v>
       </c>
       <c r="E437" t="n">
-        <v>32.39833338730038</v>
+        <v>32.39832955774229</v>
       </c>
       <c r="F437" t="n">
         <v>2684074</v>
@@ -9172,16 +9172,16 @@
         <v>44790</v>
       </c>
       <c r="B438" t="n">
-        <v>32.53372573852539</v>
+        <v>32.53372955322266</v>
       </c>
       <c r="C438" t="n">
-        <v>32.93024545622303</v>
+        <v>32.93024931741367</v>
       </c>
       <c r="D438" t="n">
-        <v>31.80839000156146</v>
+        <v>31.80839373121048</v>
       </c>
       <c r="E438" t="n">
-        <v>31.81806249384815</v>
+        <v>31.8180662246313</v>
       </c>
       <c r="F438" t="n">
         <v>3057587</v>
@@ -9252,16 +9252,16 @@
         <v>44796</v>
       </c>
       <c r="B442" t="n">
-        <v>35.11592483520508</v>
+        <v>35.11592102050781</v>
       </c>
       <c r="C442" t="n">
-        <v>35.54145457609587</v>
+        <v>35.54145071517264</v>
       </c>
       <c r="D442" t="n">
-        <v>33.43314711052539</v>
+        <v>33.43314347863087</v>
       </c>
       <c r="E442" t="n">
-        <v>33.46216084263848</v>
+        <v>33.46215720759215</v>
       </c>
       <c r="F442" t="n">
         <v>5706007</v>
@@ -9292,16 +9292,16 @@
         <v>44798</v>
       </c>
       <c r="B444" t="n">
-        <v>35.73487854003906</v>
+        <v>35.7348747253418</v>
       </c>
       <c r="C444" t="n">
-        <v>36.56659679067325</v>
+        <v>36.56659288719009</v>
       </c>
       <c r="D444" t="n">
-        <v>35.39638999233915</v>
+        <v>35.39638621377552</v>
       </c>
       <c r="E444" t="n">
-        <v>35.86060596289047</v>
+        <v>35.8606021347718</v>
       </c>
       <c r="F444" t="n">
         <v>2850362</v>
@@ -9372,16 +9372,16 @@
         <v>44804</v>
       </c>
       <c r="B448" t="n">
-        <v>36.16040802001953</v>
+        <v>36.16040420532227</v>
       </c>
       <c r="C448" t="n">
-        <v>36.46021408739674</v>
+        <v>36.46021024107181</v>
       </c>
       <c r="D448" t="n">
-        <v>35.22230734004456</v>
+        <v>35.22230362431106</v>
       </c>
       <c r="E448" t="n">
-        <v>35.91862941698318</v>
+        <v>35.91862562779205</v>
       </c>
       <c r="F448" t="n">
         <v>3394125</v>
@@ -9392,16 +9392,16 @@
         <v>44805</v>
       </c>
       <c r="B449" t="n">
-        <v>35.58013916015625</v>
+        <v>35.58013534545898</v>
       </c>
       <c r="C449" t="n">
-        <v>36.22810623483188</v>
+        <v>36.22810235066332</v>
       </c>
       <c r="D449" t="n">
-        <v>35.00954078502128</v>
+        <v>35.00953703150028</v>
       </c>
       <c r="E449" t="n">
-        <v>35.84125898955293</v>
+        <v>35.8412551468599</v>
       </c>
       <c r="F449" t="n">
         <v>3340084</v>
@@ -9492,16 +9492,16 @@
         <v>44813</v>
       </c>
       <c r="B454" t="n">
-        <v>35.92829895019531</v>
+        <v>35.92830276489258</v>
       </c>
       <c r="C454" t="n">
-        <v>36.3731698941971</v>
+        <v>36.37317375612866</v>
       </c>
       <c r="D454" t="n">
-        <v>35.60915167019012</v>
+        <v>35.60915545100184</v>
       </c>
       <c r="E454" t="n">
-        <v>35.79290279374685</v>
+        <v>35.79290659406839</v>
       </c>
       <c r="F454" t="n">
         <v>3544465</v>
@@ -9552,16 +9552,16 @@
         <v>44818</v>
       </c>
       <c r="B457" t="n">
-        <v>37.25325012207031</v>
+        <v>37.25324630737305</v>
       </c>
       <c r="C457" t="n">
-        <v>37.57239743066493</v>
+        <v>37.57239358328728</v>
       </c>
       <c r="D457" t="n">
-        <v>35.96698839437353</v>
+        <v>35.96698471138824</v>
       </c>
       <c r="E457" t="n">
-        <v>36.05402584393507</v>
+        <v>36.05402215203722</v>
       </c>
       <c r="F457" t="n">
         <v>4057043</v>
@@ -9592,16 +9592,16 @@
         <v>44820</v>
       </c>
       <c r="B459" t="n">
-        <v>36.7987060546875</v>
+        <v>36.79870223999023</v>
       </c>
       <c r="C459" t="n">
-        <v>36.7987060546875</v>
+        <v>36.79870223999023</v>
       </c>
       <c r="D459" t="n">
-        <v>35.7832329328566</v>
+        <v>35.78322922342723</v>
       </c>
       <c r="E459" t="n">
-        <v>36.14106646140942</v>
+        <v>36.14106271488564</v>
       </c>
       <c r="F459" t="n">
         <v>2974596</v>
@@ -9612,16 +9612,16 @@
         <v>44823</v>
       </c>
       <c r="B460" t="n">
-        <v>36.84706115722656</v>
+        <v>36.8470573425293</v>
       </c>
       <c r="C460" t="n">
-        <v>37.39831831798563</v>
+        <v>37.3983144462179</v>
       </c>
       <c r="D460" t="n">
-        <v>35.79290555412169</v>
+        <v>35.7929018485589</v>
       </c>
       <c r="E460" t="n">
-        <v>35.79290555412169</v>
+        <v>35.7929018485589</v>
       </c>
       <c r="F460" t="n">
         <v>3461677</v>
@@ -9652,16 +9652,16 @@
         <v>44825</v>
       </c>
       <c r="B462" t="n">
-        <v>38.03661346435547</v>
+        <v>38.0366096496582</v>
       </c>
       <c r="C462" t="n">
-        <v>38.79096301231463</v>
+        <v>38.79095912196355</v>
       </c>
       <c r="D462" t="n">
-        <v>37.62075246461414</v>
+        <v>37.62074869162363</v>
       </c>
       <c r="E462" t="n">
-        <v>37.93989977373904</v>
+        <v>37.9398959687412</v>
       </c>
       <c r="F462" t="n">
         <v>4689181</v>
@@ -9732,16 +9732,16 @@
         <v>44831</v>
       </c>
       <c r="B466" t="n">
-        <v>33.61689376831055</v>
+        <v>33.61689758300781</v>
       </c>
       <c r="C466" t="n">
-        <v>34.44861190035511</v>
+        <v>34.44861580943209</v>
       </c>
       <c r="D466" t="n">
-        <v>33.3267602334253</v>
+        <v>33.32676401519949</v>
       </c>
       <c r="E466" t="n">
-        <v>34.44861190035511</v>
+        <v>34.44861580943209</v>
       </c>
       <c r="F466" t="n">
         <v>5480701</v>
@@ -9752,16 +9752,16 @@
         <v>44832</v>
       </c>
       <c r="B467" t="n">
-        <v>34.57433700561523</v>
+        <v>34.5743408203125</v>
       </c>
       <c r="C467" t="n">
-        <v>34.99987045518622</v>
+        <v>34.99987431683395</v>
       </c>
       <c r="D467" t="n">
-        <v>33.19136547412988</v>
+        <v>33.19136913623947</v>
       </c>
       <c r="E467" t="n">
-        <v>33.66525014270204</v>
+        <v>33.66525385709685</v>
       </c>
       <c r="F467" t="n">
         <v>4399676</v>
@@ -9772,16 +9772,16 @@
         <v>44833</v>
       </c>
       <c r="B468" t="n">
-        <v>33.90703201293945</v>
+        <v>33.90702819824219</v>
       </c>
       <c r="C468" t="n">
-        <v>34.69039528924284</v>
+        <v>34.69039138641359</v>
       </c>
       <c r="D468" t="n">
-        <v>33.09465875193581</v>
+        <v>33.09465502863428</v>
       </c>
       <c r="E468" t="n">
-        <v>34.61302658569848</v>
+        <v>34.61302269157358</v>
       </c>
       <c r="F468" t="n">
         <v>4499631</v>
@@ -9812,16 +9812,16 @@
         <v>44837</v>
       </c>
       <c r="B470" t="n">
-        <v>36.7987060546875</v>
+        <v>36.79870223999023</v>
       </c>
       <c r="C470" t="n">
-        <v>36.91476098234264</v>
+        <v>36.91475715561467</v>
       </c>
       <c r="D470" t="n">
-        <v>35.52211309320833</v>
+        <v>35.52210941084767</v>
       </c>
       <c r="E470" t="n">
-        <v>36.26679013465196</v>
+        <v>36.26678637509517</v>
       </c>
       <c r="F470" t="n">
         <v>4419789</v>
@@ -9852,16 +9852,16 @@
         <v>44839</v>
       </c>
       <c r="B472" t="n">
-        <v>41.63427734375</v>
+        <v>41.63427352905273</v>
       </c>
       <c r="C472" t="n">
-        <v>42.48533680478608</v>
+        <v>42.48533291211138</v>
       </c>
       <c r="D472" t="n">
-        <v>40.55110803146717</v>
+        <v>40.55110431601417</v>
       </c>
       <c r="E472" t="n">
-        <v>40.61880798727272</v>
+        <v>40.61880426561678</v>
       </c>
       <c r="F472" t="n">
         <v>6927519</v>
@@ -9892,16 +9892,16 @@
         <v>44841</v>
       </c>
       <c r="B474" t="n">
-        <v>41.47953796386719</v>
+        <v>41.47954177856445</v>
       </c>
       <c r="C474" t="n">
-        <v>42.45632104937901</v>
+        <v>42.45632495390688</v>
       </c>
       <c r="D474" t="n">
-        <v>41.22808688619578</v>
+        <v>41.22809067776815</v>
       </c>
       <c r="E474" t="n">
-        <v>41.59558913638236</v>
+        <v>41.59559296175236</v>
       </c>
       <c r="F474" t="n">
         <v>3503020</v>
@@ -10072,16 +10072,16 @@
         <v>44855</v>
       </c>
       <c r="B483" t="n">
-        <v>44.22614288330078</v>
+        <v>44.22613906860352</v>
       </c>
       <c r="C483" t="n">
-        <v>44.68068635480393</v>
+        <v>44.68068250090031</v>
       </c>
       <c r="D483" t="n">
-        <v>42.41764149048589</v>
+        <v>42.41763783177974</v>
       </c>
       <c r="E483" t="n">
-        <v>42.9688949036628</v>
+        <v>42.96889119740864</v>
       </c>
       <c r="F483" t="n">
         <v>5360835</v>
@@ -10112,16 +10112,16 @@
         <v>44859</v>
       </c>
       <c r="B485" t="n">
-        <v>42.69810104370117</v>
+        <v>42.69809722900391</v>
       </c>
       <c r="C485" t="n">
-        <v>44.71937098158734</v>
+        <v>44.7193669863075</v>
       </c>
       <c r="D485" t="n">
-        <v>42.52402240539543</v>
+        <v>42.52401860625056</v>
       </c>
       <c r="E485" t="n">
-        <v>43.43310931590769</v>
+        <v>43.43310543554394</v>
       </c>
       <c r="F485" t="n">
         <v>3364870</v>
@@ -10232,16 +10232,16 @@
         <v>44868</v>
       </c>
       <c r="B491" t="n">
-        <v>46.30543899536133</v>
+        <v>46.30543518066406</v>
       </c>
       <c r="C491" t="n">
-        <v>46.43116266535413</v>
+        <v>46.4311588402996</v>
       </c>
       <c r="D491" t="n">
-        <v>44.51627889399545</v>
+        <v>44.51627522669133</v>
       </c>
       <c r="E491" t="n">
-        <v>44.98049109746535</v>
+        <v>44.98048739191887</v>
       </c>
       <c r="F491" t="n">
         <v>3262984</v>
@@ -10312,16 +10312,16 @@
         <v>44874</v>
       </c>
       <c r="B495" t="n">
-        <v>44.69035720825195</v>
+        <v>44.69035339355469</v>
       </c>
       <c r="C495" t="n">
-        <v>46.49886228228617</v>
+        <v>46.49885831321781</v>
       </c>
       <c r="D495" t="n">
-        <v>44.23581375342662</v>
+        <v>44.23580997752845</v>
       </c>
       <c r="E495" t="n">
-        <v>45.35766552501359</v>
+        <v>45.35766165335595</v>
       </c>
       <c r="F495" t="n">
         <v>4884014</v>
@@ -10332,16 +10332,16 @@
         <v>44875</v>
       </c>
       <c r="B496" t="n">
-        <v>42.05980682373047</v>
+        <v>42.0598030090332</v>
       </c>
       <c r="C496" t="n">
-        <v>44.68068514703247</v>
+        <v>44.68068109462947</v>
       </c>
       <c r="D496" t="n">
-        <v>41.6439458411077</v>
+        <v>41.64394206412777</v>
       </c>
       <c r="E496" t="n">
-        <v>43.65554705124352</v>
+        <v>43.65554309181744</v>
       </c>
       <c r="F496" t="n">
         <v>5453172</v>
@@ -10472,16 +10472,16 @@
         <v>44887</v>
       </c>
       <c r="B503" t="n">
-        <v>35.72520446777344</v>
+        <v>35.7252082824707</v>
       </c>
       <c r="C503" t="n">
-        <v>38.01726275125628</v>
+        <v>38.01726681069696</v>
       </c>
       <c r="D503" t="n">
-        <v>35.41572595102293</v>
+        <v>35.41572973267442</v>
       </c>
       <c r="E503" t="n">
-        <v>37.37896822915095</v>
+        <v>37.37897222043525</v>
       </c>
       <c r="F503" t="n">
         <v>4879239</v>
@@ -10492,16 +10492,16 @@
         <v>44888</v>
       </c>
       <c r="B504" t="n">
-        <v>34.29388046264648</v>
+        <v>34.29387664794922</v>
       </c>
       <c r="C504" t="n">
-        <v>35.59948346985989</v>
+        <v>35.59947950993321</v>
       </c>
       <c r="D504" t="n">
-        <v>33.84900571743197</v>
+        <v>33.84900195222058</v>
       </c>
       <c r="E504" t="n">
-        <v>35.37704984482862</v>
+        <v>35.37704590964446</v>
       </c>
       <c r="F504" t="n">
         <v>5644348</v>
@@ -10532,16 +10532,16 @@
         <v>44890</v>
       </c>
       <c r="B506" t="n">
-        <v>34.23584747314453</v>
+        <v>34.2358512878418</v>
       </c>
       <c r="C506" t="n">
-        <v>36.49889581830917</v>
+        <v>36.49889988516448</v>
       </c>
       <c r="D506" t="n">
-        <v>34.11012381427162</v>
+        <v>34.11012761496025</v>
       </c>
       <c r="E506" t="n">
-        <v>36.17007605925269</v>
+        <v>36.17008008946956</v>
       </c>
       <c r="F506" t="n">
         <v>4398253</v>
@@ -10552,16 +10552,16 @@
         <v>44893</v>
       </c>
       <c r="B507" t="n">
-        <v>33.64590835571289</v>
+        <v>33.64591217041016</v>
       </c>
       <c r="C507" t="n">
-        <v>34.11012427192836</v>
+        <v>34.11012813925738</v>
       </c>
       <c r="D507" t="n">
-        <v>32.92057262619048</v>
+        <v>32.92057635865081</v>
       </c>
       <c r="E507" t="n">
-        <v>33.36544355803103</v>
+        <v>33.36544734092983</v>
       </c>
       <c r="F507" t="n">
         <v>4077054</v>
@@ -10652,16 +10652,16 @@
         <v>44900</v>
       </c>
       <c r="B512" t="n">
-        <v>34.04242324829102</v>
+        <v>34.04242706298828</v>
       </c>
       <c r="C512" t="n">
-        <v>35.87994187083461</v>
+        <v>35.879945891439</v>
       </c>
       <c r="D512" t="n">
-        <v>33.77163095133564</v>
+        <v>33.77163473568869</v>
       </c>
       <c r="E512" t="n">
-        <v>35.57046335392476</v>
+        <v>35.57046733984986</v>
       </c>
       <c r="F512" t="n">
         <v>5158181</v>
@@ -10732,16 +10732,16 @@
         <v>44904</v>
       </c>
       <c r="B516" t="n">
-        <v>31.69234085083008</v>
+        <v>31.69233894348145</v>
       </c>
       <c r="C516" t="n">
-        <v>32.74649642178647</v>
+        <v>32.74649445099531</v>
       </c>
       <c r="D516" t="n">
-        <v>31.4892447329005</v>
+        <v>31.48924283777486</v>
       </c>
       <c r="E516" t="n">
-        <v>32.22425300897184</v>
+        <v>32.22425106961099</v>
       </c>
       <c r="F516" t="n">
         <v>2885712</v>
@@ -10752,16 +10752,16 @@
         <v>44907</v>
       </c>
       <c r="B517" t="n">
-        <v>32.23392486572266</v>
+        <v>32.23392105102539</v>
       </c>
       <c r="C517" t="n">
-        <v>32.41767599422015</v>
+        <v>32.41767215777701</v>
       </c>
       <c r="D517" t="n">
-        <v>31.06371439332975</v>
+        <v>31.06371071712008</v>
       </c>
       <c r="E517" t="n">
-        <v>31.59562654097396</v>
+        <v>31.59562280181559</v>
       </c>
       <c r="F517" t="n">
         <v>3445728</v>
@@ -10772,16 +10772,16 @@
         <v>44908</v>
       </c>
       <c r="B518" t="n">
-        <v>32.5240592956543</v>
+        <v>32.52405548095703</v>
       </c>
       <c r="C518" t="n">
-        <v>33.41380497900949</v>
+        <v>33.41380105995531</v>
       </c>
       <c r="D518" t="n">
-        <v>31.98247464077933</v>
+        <v>31.9824708896037</v>
       </c>
       <c r="E518" t="n">
-        <v>32.39833187733107</v>
+        <v>32.39832807738018</v>
       </c>
       <c r="F518" t="n">
         <v>3369136</v>
@@ -10872,16 +10872,16 @@
         <v>44915</v>
       </c>
       <c r="B523" t="n">
-        <v>31.63431167602539</v>
+        <v>31.63431358337402</v>
       </c>
       <c r="C523" t="n">
-        <v>31.83740403538475</v>
+        <v>31.83740595497857</v>
       </c>
       <c r="D523" t="n">
-        <v>30.62851300266902</v>
+        <v>30.62851484937437</v>
       </c>
       <c r="E523" t="n">
-        <v>30.76390915810044</v>
+        <v>30.76391101296931</v>
       </c>
       <c r="F523" t="n">
         <v>3472546</v>
@@ -10892,16 +10892,16 @@
         <v>44916</v>
       </c>
       <c r="B524" t="n">
-        <v>32.19523620605469</v>
+        <v>32.19524002075195</v>
       </c>
       <c r="C524" t="n">
-        <v>32.50471472608491</v>
+        <v>32.50471857745117</v>
       </c>
       <c r="D524" t="n">
-        <v>31.22812192077017</v>
+        <v>31.22812562087756</v>
       </c>
       <c r="E524" t="n">
-        <v>32.34997359228213</v>
+        <v>32.34997742531367</v>
       </c>
       <c r="F524" t="n">
         <v>3938295</v>
@@ -10912,16 +10912,16 @@
         <v>44917</v>
       </c>
       <c r="B525" t="n">
-        <v>32.01148986816406</v>
+        <v>32.0114860534668</v>
       </c>
       <c r="C525" t="n">
-        <v>32.78518066232546</v>
+        <v>32.78517675543017</v>
       </c>
       <c r="D525" t="n">
-        <v>31.53760514678948</v>
+        <v>31.5376013885634</v>
       </c>
       <c r="E525" t="n">
-        <v>32.41767837830338</v>
+        <v>32.41767451520204</v>
       </c>
       <c r="F525" t="n">
         <v>3822391</v>
@@ -10932,16 +10932,16 @@
         <v>44918</v>
       </c>
       <c r="B526" t="n">
-        <v>34.68072128295898</v>
+        <v>34.68072509765625</v>
       </c>
       <c r="C526" t="n">
-        <v>34.88381363050969</v>
+        <v>34.88381746754605</v>
       </c>
       <c r="D526" t="n">
-        <v>32.68846528926745</v>
+        <v>32.68846888482701</v>
       </c>
       <c r="E526" t="n">
-        <v>33.17202242375276</v>
+        <v>33.17202607250107</v>
       </c>
       <c r="F526" t="n">
         <v>6955860</v>
@@ -11012,16 +11012,16 @@
         <v>44924</v>
       </c>
       <c r="B530" t="n">
-        <v>36.50856781005859</v>
+        <v>36.50856399536133</v>
       </c>
       <c r="C530" t="n">
-        <v>37.23390359436439</v>
+        <v>37.23389970387844</v>
       </c>
       <c r="D530" t="n">
-        <v>35.61882587917678</v>
+        <v>35.61882215744662</v>
       </c>
       <c r="E530" t="n">
-        <v>35.87994571220566</v>
+        <v>35.87994196319169</v>
       </c>
       <c r="F530" t="n">
         <v>4887264</v>
@@ -11032,16 +11032,16 @@
         <v>44928</v>
       </c>
       <c r="B531" t="n">
-        <v>35.2126350402832</v>
+        <v>35.21263885498047</v>
       </c>
       <c r="C531" t="n">
-        <v>36.68264774905137</v>
+        <v>36.68265172299981</v>
       </c>
       <c r="D531" t="n">
-        <v>34.78710534150101</v>
+        <v>34.78710911009928</v>
       </c>
       <c r="E531" t="n">
-        <v>36.01533947163607</v>
+        <v>36.01534337329287</v>
       </c>
       <c r="F531" t="n">
         <v>2924313</v>
@@ -11152,16 +11152,16 @@
         <v>44936</v>
       </c>
       <c r="B537" t="n">
-        <v>37.79483032226562</v>
+        <v>37.79483413696289</v>
       </c>
       <c r="C537" t="n">
-        <v>38.07529137196207</v>
+        <v>38.07529521496675</v>
       </c>
       <c r="D537" t="n">
-        <v>36.49889625466188</v>
+        <v>36.49889993855829</v>
       </c>
       <c r="E537" t="n">
-        <v>37.0985045751726</v>
+        <v>37.09850831958851</v>
       </c>
       <c r="F537" t="n">
         <v>3183751</v>
@@ -11192,16 +11192,16 @@
         <v>44938</v>
       </c>
       <c r="B539" t="n">
-        <v>43.42343902587891</v>
+        <v>43.42343521118164</v>
       </c>
       <c r="C539" t="n">
-        <v>44.7290457434945</v>
+        <v>44.72904181410123</v>
       </c>
       <c r="D539" t="n">
-        <v>43.19133291383822</v>
+        <v>43.19132911953119</v>
       </c>
       <c r="E539" t="n">
-        <v>43.40409778676949</v>
+        <v>43.40409397377132</v>
       </c>
       <c r="F539" t="n">
         <v>7341055</v>
@@ -11212,16 +11212,16 @@
         <v>44939</v>
       </c>
       <c r="B540" t="n">
-        <v>42.75612640380859</v>
+        <v>42.75613021850586</v>
       </c>
       <c r="C540" t="n">
-        <v>43.50080338468374</v>
+        <v>43.50080726582102</v>
       </c>
       <c r="D540" t="n">
-        <v>42.35961043000531</v>
+        <v>42.35961420932546</v>
       </c>
       <c r="E540" t="n">
-        <v>43.42343468839838</v>
+        <v>43.42343856263282</v>
       </c>
       <c r="F540" t="n">
         <v>4249336</v>
@@ -11272,16 +11272,16 @@
         <v>44944</v>
       </c>
       <c r="B543" t="n">
-        <v>44.53561782836914</v>
+        <v>44.53562164306641</v>
       </c>
       <c r="C543" t="n">
-        <v>45.241612337541</v>
+        <v>45.24161621271021</v>
       </c>
       <c r="D543" t="n">
-        <v>43.220342491427</v>
+        <v>43.22034619346439</v>
       </c>
       <c r="E543" t="n">
-        <v>43.42343485149192</v>
+        <v>43.42343857092518</v>
       </c>
       <c r="F543" t="n">
         <v>6730959</v>
@@ -11332,16 +11332,16 @@
         <v>44949</v>
       </c>
       <c r="B546" t="n">
-        <v>46.45050430297852</v>
+        <v>46.45050811767578</v>
       </c>
       <c r="C546" t="n">
-        <v>48.53947031074529</v>
+        <v>48.53947429699662</v>
       </c>
       <c r="D546" t="n">
-        <v>45.88957845353607</v>
+        <v>45.88958222216792</v>
       </c>
       <c r="E546" t="n">
-        <v>47.67873842593739</v>
+        <v>47.67874234150205</v>
       </c>
       <c r="F546" t="n">
         <v>5971946</v>
@@ -11392,16 +11392,16 @@
         <v>44952</v>
       </c>
       <c r="B549" t="n">
-        <v>45.26095199584961</v>
+        <v>45.26095581054688</v>
       </c>
       <c r="C549" t="n">
-        <v>46.77931963988798</v>
+        <v>46.77932358255676</v>
       </c>
       <c r="D549" t="n">
-        <v>45.24161075927422</v>
+        <v>45.24161457234137</v>
       </c>
       <c r="E549" t="n">
-        <v>45.92826025966649</v>
+        <v>45.92826413060603</v>
       </c>
       <c r="F549" t="n">
         <v>3327082</v>
@@ -11412,16 +11412,16 @@
         <v>44953</v>
       </c>
       <c r="B550" t="n">
-        <v>44.50660705566406</v>
+        <v>44.5066032409668</v>
       </c>
       <c r="C550" t="n">
-        <v>46.34412590104548</v>
+        <v>46.34412192885299</v>
       </c>
       <c r="D550" t="n">
-        <v>44.16811476963287</v>
+        <v>44.16811098394805</v>
       </c>
       <c r="E550" t="n">
-        <v>46.20872973614816</v>
+        <v>46.20872577556058</v>
       </c>
       <c r="F550" t="n">
         <v>4035914</v>
@@ -11432,16 +11432,16 @@
         <v>44956</v>
       </c>
       <c r="B551" t="n">
-        <v>43.79093933105469</v>
+        <v>43.79094314575195</v>
       </c>
       <c r="C551" t="n">
-        <v>44.43890261092821</v>
+        <v>44.43890648207057</v>
       </c>
       <c r="D551" t="n">
-        <v>43.13329981152729</v>
+        <v>43.13330356893655</v>
       </c>
       <c r="E551" t="n">
-        <v>44.3131789517849</v>
+        <v>44.31318281197527</v>
       </c>
       <c r="F551" t="n">
         <v>3870439</v>
@@ -11572,16 +11572,16 @@
         <v>44965</v>
       </c>
       <c r="B558" t="n">
-        <v>43.12363052368164</v>
+        <v>43.12362670898438</v>
       </c>
       <c r="C558" t="n">
-        <v>43.13330301647882</v>
+        <v>43.13329920092593</v>
       </c>
       <c r="D558" t="n">
-        <v>42.08881994983436</v>
+        <v>42.08881622667597</v>
       </c>
       <c r="E558" t="n">
-        <v>42.57237713333137</v>
+        <v>42.57237336739773</v>
       </c>
       <c r="F558" t="n">
         <v>2757212</v>
@@ -11672,16 +11672,16 @@
         <v>44972</v>
       </c>
       <c r="B563" t="n">
-        <v>40.0482063293457</v>
+        <v>40.04821014404297</v>
       </c>
       <c r="C563" t="n">
-        <v>40.52209099098364</v>
+        <v>40.52209485081966</v>
       </c>
       <c r="D563" t="n">
-        <v>38.90700964744255</v>
+        <v>38.90701335343782</v>
       </c>
       <c r="E563" t="n">
-        <v>38.92635463185054</v>
+        <v>38.92635833968847</v>
       </c>
       <c r="F563" t="n">
         <v>3495706</v>
@@ -11752,16 +11752,16 @@
         <v>44980</v>
       </c>
       <c r="B567" t="n">
-        <v>38.00759506225586</v>
+        <v>38.00759887695312</v>
       </c>
       <c r="C567" t="n">
-        <v>39.07141929530241</v>
+        <v>39.07142321677222</v>
       </c>
       <c r="D567" t="n">
-        <v>37.7368027579212</v>
+        <v>37.73680654543994</v>
       </c>
       <c r="E567" t="n">
-        <v>37.95924009667655</v>
+        <v>37.95924390652058</v>
       </c>
       <c r="F567" t="n">
         <v>3548732</v>
@@ -11812,16 +11812,16 @@
         <v>44985</v>
       </c>
       <c r="B570" t="n">
-        <v>35.2126350402832</v>
+        <v>35.21263885498047</v>
       </c>
       <c r="C570" t="n">
-        <v>38.49115271645117</v>
+        <v>38.49115688632073</v>
       </c>
       <c r="D570" t="n">
-        <v>35.2126350402832</v>
+        <v>35.21263885498047</v>
       </c>
       <c r="E570" t="n">
-        <v>37.13719117707558</v>
+        <v>37.13719520026616</v>
       </c>
       <c r="F570" t="n">
         <v>11036876</v>
@@ -11832,16 +11832,16 @@
         <v>44986</v>
       </c>
       <c r="B571" t="n">
-        <v>31.52792930603027</v>
+        <v>31.52793121337891</v>
       </c>
       <c r="C571" t="n">
-        <v>35.21263549119504</v>
+        <v>35.21263762145776</v>
       </c>
       <c r="D571" t="n">
-        <v>29.89350481936535</v>
+        <v>29.89350662783602</v>
       </c>
       <c r="E571" t="n">
-        <v>35.10625306513723</v>
+        <v>35.10625518896411</v>
       </c>
       <c r="F571" t="n">
         <v>24633899</v>
@@ -11872,16 +11872,16 @@
         <v>44988</v>
       </c>
       <c r="B573" t="n">
-        <v>31.74069404602051</v>
+        <v>31.74069595336914</v>
       </c>
       <c r="C573" t="n">
-        <v>31.93411766023568</v>
+        <v>31.93411957920744</v>
       </c>
       <c r="D573" t="n">
-        <v>30.40607560502645</v>
+        <v>30.40607743217574</v>
       </c>
       <c r="E573" t="n">
-        <v>30.47377368262298</v>
+        <v>30.47377551384036</v>
       </c>
       <c r="F573" t="n">
         <v>7573675</v>
@@ -11892,16 +11892,16 @@
         <v>44991</v>
       </c>
       <c r="B574" t="n">
-        <v>31.86641883850098</v>
+        <v>31.86642074584961</v>
       </c>
       <c r="C574" t="n">
-        <v>32.34997601739302</v>
+        <v>32.34997795368473</v>
       </c>
       <c r="D574" t="n">
-        <v>30.94766132287878</v>
+        <v>30.94766317523564</v>
       </c>
       <c r="E574" t="n">
-        <v>31.74069517121325</v>
+        <v>31.74069707103675</v>
       </c>
       <c r="F574" t="n">
         <v>5963007</v>
@@ -11992,16 +11992,16 @@
         <v>44998</v>
       </c>
       <c r="B579" t="n">
-        <v>26.4505786895752</v>
+        <v>26.45058059692383</v>
       </c>
       <c r="C579" t="n">
-        <v>27.32098119587531</v>
+        <v>27.32098316598858</v>
       </c>
       <c r="D579" t="n">
-        <v>25.76392542920967</v>
+        <v>25.76392728704381</v>
       </c>
       <c r="E579" t="n">
-        <v>26.59564546166059</v>
+        <v>26.59564737946998</v>
       </c>
       <c r="F579" t="n">
         <v>13860726</v>
@@ -12032,16 +12032,16 @@
         <v>45000</v>
       </c>
       <c r="B581" t="n">
-        <v>26.28617095947266</v>
+        <v>26.28616905212402</v>
       </c>
       <c r="C581" t="n">
-        <v>26.82775374453002</v>
+        <v>26.82775179788365</v>
       </c>
       <c r="D581" t="n">
-        <v>25.62853324821252</v>
+        <v>25.62853138858268</v>
       </c>
       <c r="E581" t="n">
-        <v>26.58597514665809</v>
+        <v>26.58597321755539</v>
       </c>
       <c r="F581" t="n">
         <v>12174787</v>
@@ -12072,16 +12072,16 @@
         <v>45002</v>
       </c>
       <c r="B583" t="n">
-        <v>30.70588111877441</v>
+        <v>30.70588302612305</v>
       </c>
       <c r="C583" t="n">
-        <v>30.8896322374788</v>
+        <v>30.88963415624145</v>
       </c>
       <c r="D583" t="n">
-        <v>27.73684012155175</v>
+        <v>27.73684184447329</v>
       </c>
       <c r="E583" t="n">
-        <v>30.45443004984579</v>
+        <v>30.45443194157511</v>
       </c>
       <c r="F583" t="n">
         <v>23193684</v>
@@ -12092,16 +12092,16 @@
         <v>45005</v>
       </c>
       <c r="B584" t="n">
-        <v>29.79679679870605</v>
+        <v>29.79679489135742</v>
       </c>
       <c r="C584" t="n">
-        <v>31.20878403151084</v>
+        <v>31.20878203377826</v>
       </c>
       <c r="D584" t="n">
-        <v>29.32291022343201</v>
+        <v>29.32290834641774</v>
       </c>
       <c r="E584" t="n">
-        <v>30.70588372476053</v>
+        <v>30.70588175921954</v>
       </c>
       <c r="F584" t="n">
         <v>7729094</v>
@@ -12252,16 +12252,16 @@
         <v>45015</v>
       </c>
       <c r="B592" t="n">
-        <v>29.38093566894531</v>
+        <v>29.38093376159668</v>
       </c>
       <c r="C592" t="n">
-        <v>30.51245994826028</v>
+        <v>30.51245796745546</v>
       </c>
       <c r="D592" t="n">
-        <v>29.27455323657771</v>
+        <v>29.2745513361352</v>
       </c>
       <c r="E592" t="n">
-        <v>29.95153405508782</v>
+        <v>29.95153211069714</v>
       </c>
       <c r="F592" t="n">
         <v>5560645</v>
@@ -12312,16 +12312,16 @@
         <v>45020</v>
       </c>
       <c r="B595" t="n">
-        <v>27.92059326171875</v>
+        <v>27.92059135437012</v>
       </c>
       <c r="C595" t="n">
-        <v>29.70975523383049</v>
+        <v>29.70975320425825</v>
       </c>
       <c r="D595" t="n">
-        <v>27.91092264260987</v>
+        <v>27.91092073592187</v>
       </c>
       <c r="E595" t="n">
-        <v>29.57435907115471</v>
+        <v>29.57435705083184</v>
       </c>
       <c r="F595" t="n">
         <v>7552242</v>
@@ -12332,16 +12332,16 @@
         <v>45021</v>
       </c>
       <c r="B596" t="n">
-        <v>26.76972579956055</v>
+        <v>26.76972770690918</v>
       </c>
       <c r="C596" t="n">
-        <v>27.85289314814766</v>
+        <v>27.8528951326722</v>
       </c>
       <c r="D596" t="n">
-        <v>26.23781180677641</v>
+        <v>26.23781367622606</v>
       </c>
       <c r="E596" t="n">
-        <v>27.65947141114338</v>
+        <v>27.65947338188658</v>
       </c>
       <c r="F596" t="n">
         <v>12382825</v>
@@ -12372,16 +12372,16 @@
         <v>45026</v>
       </c>
       <c r="B598" t="n">
-        <v>29.65172576904297</v>
+        <v>29.6517276763916</v>
       </c>
       <c r="C598" t="n">
-        <v>29.8354768886412</v>
+        <v>29.83547880780963</v>
       </c>
       <c r="D598" t="n">
-        <v>28.19138368313743</v>
+        <v>28.19138549654949</v>
       </c>
       <c r="E598" t="n">
-        <v>28.33645045512486</v>
+        <v>28.33645227786835</v>
       </c>
       <c r="F598" t="n">
         <v>8774363</v>
@@ -12552,16 +12552,16 @@
         <v>45040</v>
       </c>
       <c r="B607" t="n">
-        <v>26.96700286865234</v>
+        <v>26.96700477600098</v>
       </c>
       <c r="C607" t="n">
-        <v>27.07506608384296</v>
+        <v>27.07506799883479</v>
       </c>
       <c r="D607" t="n">
-        <v>26.23019953206389</v>
+        <v>26.23020138729918</v>
       </c>
       <c r="E607" t="n">
-        <v>26.86876204901633</v>
+        <v>26.86876394941649</v>
       </c>
       <c r="F607" t="n">
         <v>6680100</v>
@@ -12572,16 +12572,16 @@
         <v>45041</v>
       </c>
       <c r="B608" t="n">
-        <v>27.21260452270508</v>
+        <v>27.21260261535645</v>
       </c>
       <c r="C608" t="n">
-        <v>27.45820563979163</v>
+        <v>27.45820371522866</v>
       </c>
       <c r="D608" t="n">
-        <v>26.42667982375542</v>
+        <v>26.42667797149275</v>
       </c>
       <c r="E608" t="n">
-        <v>26.79999457104816</v>
+        <v>26.79999269261962</v>
       </c>
       <c r="F608" t="n">
         <v>5323000</v>
@@ -12612,16 +12612,16 @@
         <v>45043</v>
       </c>
       <c r="B610" t="n">
-        <v>29.90439224243164</v>
+        <v>29.90439414978027</v>
       </c>
       <c r="C610" t="n">
-        <v>30.267880842768</v>
+        <v>30.26788277330051</v>
       </c>
       <c r="D610" t="n">
-        <v>26.73122441728851</v>
+        <v>26.73122612224756</v>
       </c>
       <c r="E610" t="n">
-        <v>26.73122441728851</v>
+        <v>26.73122612224756</v>
       </c>
       <c r="F610" t="n">
         <v>20933600</v>
@@ -12672,16 +12672,16 @@
         <v>45049</v>
       </c>
       <c r="B613" t="n">
-        <v>29.14793968200684</v>
+        <v>29.14794158935547</v>
       </c>
       <c r="C613" t="n">
-        <v>29.61949336143113</v>
+        <v>29.61949529963673</v>
       </c>
       <c r="D613" t="n">
-        <v>28.33254407533193</v>
+        <v>28.33254592932366</v>
       </c>
       <c r="E613" t="n">
-        <v>29.26582903875679</v>
+        <v>29.26583095381972</v>
       </c>
       <c r="F613" t="n">
         <v>9250000</v>
@@ -12692,16 +12692,16 @@
         <v>45050</v>
       </c>
       <c r="B614" t="n">
-        <v>29.2756519317627</v>
+        <v>29.27565383911133</v>
       </c>
       <c r="C614" t="n">
-        <v>29.95351152857367</v>
+        <v>29.95351348008578</v>
       </c>
       <c r="D614" t="n">
-        <v>29.17741298555374</v>
+        <v>29.17741488650197</v>
       </c>
       <c r="E614" t="n">
-        <v>29.47213357175619</v>
+        <v>29.47213549190587</v>
       </c>
       <c r="F614" t="n">
         <v>6670900</v>
@@ -12792,16 +12792,16 @@
         <v>45057</v>
       </c>
       <c r="B619" t="n">
-        <v>31.66289520263672</v>
+        <v>31.66289710998535</v>
       </c>
       <c r="C619" t="n">
-        <v>31.81025737023202</v>
+        <v>31.81025928645763</v>
       </c>
       <c r="D619" t="n">
-        <v>31.10292496189554</v>
+        <v>31.10292683551199</v>
       </c>
       <c r="E619" t="n">
-        <v>31.71201467597662</v>
+        <v>31.71201658628417</v>
       </c>
       <c r="F619" t="n">
         <v>4858000</v>
@@ -12812,16 +12812,16 @@
         <v>45058</v>
       </c>
       <c r="B620" t="n">
-        <v>32.49794006347656</v>
+        <v>32.49794387817383</v>
       </c>
       <c r="C620" t="n">
-        <v>32.64529847816273</v>
+        <v>32.64530231015733</v>
       </c>
       <c r="D620" t="n">
-        <v>31.46641242279611</v>
+        <v>31.46641611640984</v>
       </c>
       <c r="E620" t="n">
-        <v>31.554828970638</v>
+        <v>31.55483267463029</v>
       </c>
       <c r="F620" t="n">
         <v>5317000</v>
@@ -12852,16 +12852,16 @@
         <v>45062</v>
       </c>
       <c r="B622" t="n">
-        <v>29.90439224243164</v>
+        <v>29.90439414978027</v>
       </c>
       <c r="C622" t="n">
-        <v>32.08532946581322</v>
+        <v>32.08533151226543</v>
       </c>
       <c r="D622" t="n">
-        <v>29.70791060120974</v>
+        <v>29.70791249602647</v>
       </c>
       <c r="E622" t="n">
-        <v>31.86919928571158</v>
+        <v>31.86920131837866</v>
       </c>
       <c r="F622" t="n">
         <v>13269700</v>
@@ -12912,16 +12912,16 @@
         <v>45065</v>
       </c>
       <c r="B625" t="n">
-        <v>32.49794006347656</v>
+        <v>32.49794387817383</v>
       </c>
       <c r="C625" t="n">
-        <v>34.87535696477425</v>
+        <v>34.87536105853923</v>
       </c>
       <c r="D625" t="n">
-        <v>31.04398009551434</v>
+        <v>31.0439837395418</v>
       </c>
       <c r="E625" t="n">
-        <v>31.8691980857257</v>
+        <v>31.86920182661951</v>
       </c>
       <c r="F625" t="n">
         <v>19443700</v>
@@ -12972,16 +12972,16 @@
         <v>45070</v>
       </c>
       <c r="B628" t="n">
-        <v>31.48606300354004</v>
+        <v>31.48606109619141</v>
       </c>
       <c r="C628" t="n">
-        <v>31.86920015318507</v>
+        <v>31.86919822262693</v>
       </c>
       <c r="D628" t="n">
-        <v>30.464363313224</v>
+        <v>30.46436146776744</v>
       </c>
       <c r="E628" t="n">
-        <v>31.04398210943912</v>
+        <v>31.04398022887067</v>
       </c>
       <c r="F628" t="n">
         <v>7685200</v>
@@ -13212,16 +13212,16 @@
         <v>45089</v>
       </c>
       <c r="B640" t="n">
-        <v>31.26010894775391</v>
+        <v>31.26011085510254</v>
       </c>
       <c r="C640" t="n">
-        <v>31.86919865058509</v>
+        <v>31.86920059509758</v>
       </c>
       <c r="D640" t="n">
-        <v>30.47418614610471</v>
+        <v>30.47418800549994</v>
       </c>
       <c r="E640" t="n">
-        <v>31.61377514538992</v>
+        <v>31.61377707431765</v>
       </c>
       <c r="F640" t="n">
         <v>7223600</v>
@@ -13252,16 +13252,16 @@
         <v>45091</v>
       </c>
       <c r="B642" t="n">
-        <v>31.1422233581543</v>
+        <v>31.14222145080566</v>
       </c>
       <c r="C642" t="n">
-        <v>31.71201601865814</v>
+        <v>31.71201407641177</v>
       </c>
       <c r="D642" t="n">
-        <v>30.57242882386257</v>
+        <v>30.5724269514118</v>
       </c>
       <c r="E642" t="n">
-        <v>31.33870313362062</v>
+        <v>31.33870121423831</v>
       </c>
       <c r="F642" t="n">
         <v>8288400</v>
@@ -13292,16 +13292,16 @@
         <v>45093</v>
       </c>
       <c r="B644" t="n">
-        <v>31.91832160949707</v>
+        <v>31.9183235168457</v>
       </c>
       <c r="C644" t="n">
-        <v>31.91832160949707</v>
+        <v>31.9183235168457</v>
       </c>
       <c r="D644" t="n">
-        <v>31.19134068168367</v>
+        <v>31.19134254558997</v>
       </c>
       <c r="E644" t="n">
-        <v>31.42711752024974</v>
+        <v>31.4271193982454</v>
       </c>
       <c r="F644" t="n">
         <v>5722800</v>
@@ -13332,16 +13332,16 @@
         <v>45097</v>
       </c>
       <c r="B646" t="n">
-        <v>32.16392135620117</v>
+        <v>32.16392517089844</v>
       </c>
       <c r="C646" t="n">
-        <v>32.29163122856222</v>
+        <v>32.2916350584061</v>
       </c>
       <c r="D646" t="n">
-        <v>31.48605992910253</v>
+        <v>31.48606366340425</v>
       </c>
       <c r="E646" t="n">
-        <v>32.12462428120915</v>
+        <v>32.12462809124572</v>
       </c>
       <c r="F646" t="n">
         <v>4954700</v>
@@ -13352,16 +13352,16 @@
         <v>45098</v>
       </c>
       <c r="B647" t="n">
-        <v>32.06568145751953</v>
+        <v>32.06567764282227</v>
       </c>
       <c r="C647" t="n">
-        <v>32.36040205044127</v>
+        <v>32.36039820068254</v>
       </c>
       <c r="D647" t="n">
-        <v>31.48606266749066</v>
+        <v>31.4860589217478</v>
       </c>
       <c r="E647" t="n">
-        <v>32.12462707513414</v>
+        <v>32.1246232534244</v>
       </c>
       <c r="F647" t="n">
         <v>4670300</v>
@@ -13412,16 +13412,16 @@
         <v>45103</v>
       </c>
       <c r="B650" t="n">
-        <v>30.53313064575195</v>
+        <v>30.53312873840332</v>
       </c>
       <c r="C650" t="n">
-        <v>30.83767550472773</v>
+        <v>30.83767357835474</v>
       </c>
       <c r="D650" t="n">
-        <v>30.30717806889212</v>
+        <v>30.30717617565832</v>
       </c>
       <c r="E650" t="n">
-        <v>30.58225011940398</v>
+        <v>30.58224820898695</v>
       </c>
       <c r="F650" t="n">
         <v>2874500</v>
@@ -13452,16 +13452,16 @@
         <v>45105</v>
       </c>
       <c r="B652" t="n">
-        <v>29.37389183044434</v>
+        <v>29.37389373779297</v>
       </c>
       <c r="C652" t="n">
-        <v>30.06157567506449</v>
+        <v>30.06157762706682</v>
       </c>
       <c r="D652" t="n">
-        <v>29.30512382073987</v>
+        <v>29.30512572362315</v>
       </c>
       <c r="E652" t="n">
-        <v>29.75703082903567</v>
+        <v>29.75703276126285</v>
       </c>
       <c r="F652" t="n">
         <v>4532500</v>
@@ -13532,16 +13532,16 @@
         <v>45111</v>
       </c>
       <c r="B656" t="n">
-        <v>29.80615234375</v>
+        <v>29.80615043640137</v>
       </c>
       <c r="C656" t="n">
-        <v>30.15981855937348</v>
+        <v>30.15981662939312</v>
       </c>
       <c r="D656" t="n">
-        <v>29.57037549126363</v>
+        <v>29.57037359900278</v>
       </c>
       <c r="E656" t="n">
-        <v>29.80615234375</v>
+        <v>29.80615043640137</v>
       </c>
       <c r="F656" t="n">
         <v>2514900</v>
@@ -13552,16 +13552,16 @@
         <v>45112</v>
       </c>
       <c r="B657" t="n">
-        <v>30.40542030334473</v>
+        <v>30.40541839599609</v>
       </c>
       <c r="C657" t="n">
-        <v>30.70996517647691</v>
+        <v>30.70996325002402</v>
       </c>
       <c r="D657" t="n">
-        <v>29.34442350856649</v>
+        <v>29.34442166777476</v>
       </c>
       <c r="E657" t="n">
-        <v>29.60967130192012</v>
+        <v>29.60966944448926</v>
       </c>
       <c r="F657" t="n">
         <v>5394800</v>
@@ -13612,16 +13612,16 @@
         <v>45117</v>
       </c>
       <c r="B660" t="n">
-        <v>31.07345390319824</v>
+        <v>31.07345199584961</v>
       </c>
       <c r="C660" t="n">
-        <v>31.93796904965617</v>
+        <v>31.93796708924193</v>
       </c>
       <c r="D660" t="n">
-        <v>30.84750131505205</v>
+        <v>30.84749942157282</v>
       </c>
       <c r="E660" t="n">
-        <v>31.56465803319331</v>
+        <v>31.56465609569361</v>
       </c>
       <c r="F660" t="n">
         <v>7339200</v>
@@ -13652,16 +13652,16 @@
         <v>45119</v>
       </c>
       <c r="B662" t="n">
-        <v>31.07345390319824</v>
+        <v>31.07345199584961</v>
       </c>
       <c r="C662" t="n">
-        <v>32.08533122554864</v>
+        <v>32.08532925608902</v>
       </c>
       <c r="D662" t="n">
-        <v>31.04398296705007</v>
+        <v>31.04398106151042</v>
       </c>
       <c r="E662" t="n">
-        <v>31.77096208138212</v>
+        <v>31.77096013121909</v>
       </c>
       <c r="F662" t="n">
         <v>4503800</v>
@@ -13732,16 +13732,16 @@
         <v>45125</v>
       </c>
       <c r="B666" t="n">
-        <v>32.91054916381836</v>
+        <v>32.91055297851562</v>
       </c>
       <c r="C666" t="n">
-        <v>33.03826279198419</v>
+        <v>33.03826662148488</v>
       </c>
       <c r="D666" t="n">
-        <v>32.0362098005708</v>
+        <v>32.03621351392245</v>
       </c>
       <c r="E666" t="n">
-        <v>32.18356821992315</v>
+        <v>32.18357195035527</v>
       </c>
       <c r="F666" t="n">
         <v>4775600</v>
@@ -13752,16 +13752,16 @@
         <v>45126</v>
       </c>
       <c r="B667" t="n">
-        <v>33.64735412597656</v>
+        <v>33.6473503112793</v>
       </c>
       <c r="C667" t="n">
-        <v>34.04031742501827</v>
+        <v>34.04031356576963</v>
       </c>
       <c r="D667" t="n">
-        <v>33.04808678134705</v>
+        <v>33.04808303459044</v>
       </c>
       <c r="E667" t="n">
-        <v>33.04808678134705</v>
+        <v>33.04808303459044</v>
       </c>
       <c r="F667" t="n">
         <v>7484200</v>
@@ -13772,16 +13772,16 @@
         <v>45127</v>
       </c>
       <c r="B668" t="n">
-        <v>33.92242431640625</v>
+        <v>33.92242813110352</v>
       </c>
       <c r="C668" t="n">
-        <v>34.11890595509385</v>
+        <v>34.11890979188617</v>
       </c>
       <c r="D668" t="n">
-        <v>33.64735227078894</v>
+        <v>33.64735605455338</v>
       </c>
       <c r="E668" t="n">
-        <v>33.91260192088087</v>
+        <v>33.91260573447357</v>
       </c>
       <c r="F668" t="n">
         <v>3587900</v>
@@ -13952,16 +13952,16 @@
         <v>45140</v>
       </c>
       <c r="B677" t="n">
-        <v>34.44309997558594</v>
+        <v>34.4431037902832</v>
       </c>
       <c r="C677" t="n">
-        <v>34.58063599342123</v>
+        <v>34.5806398233511</v>
       </c>
       <c r="D677" t="n">
-        <v>33.71611906300245</v>
+        <v>33.71612279718397</v>
       </c>
       <c r="E677" t="n">
-        <v>34.38415436183849</v>
+        <v>34.38415817000732</v>
       </c>
       <c r="F677" t="n">
         <v>3408800</v>
@@ -14012,16 +14012,16 @@
         <v>45145</v>
       </c>
       <c r="B680" t="n">
-        <v>35.68093109130859</v>
+        <v>35.68092727661133</v>
       </c>
       <c r="C680" t="n">
-        <v>36.15248480095344</v>
+        <v>36.15248093584172</v>
       </c>
       <c r="D680" t="n">
-        <v>35.09148989114647</v>
+        <v>35.09148613946717</v>
       </c>
       <c r="E680" t="n">
-        <v>36.05424585011833</v>
+        <v>36.05424199550948</v>
       </c>
       <c r="F680" t="n">
         <v>3820600</v>
@@ -14032,16 +14032,16 @@
         <v>45146</v>
       </c>
       <c r="B681" t="n">
-        <v>36.34896850585938</v>
+        <v>36.34896469116211</v>
       </c>
       <c r="C681" t="n">
-        <v>36.51597548123902</v>
+        <v>36.51597164901496</v>
       </c>
       <c r="D681" t="n">
-        <v>34.30556523426109</v>
+        <v>34.30556163401185</v>
       </c>
       <c r="E681" t="n">
-        <v>34.76729657396523</v>
+        <v>34.76729292525891</v>
       </c>
       <c r="F681" t="n">
         <v>5274900</v>
@@ -14172,16 +14172,16 @@
         <v>45155</v>
       </c>
       <c r="B688" t="n">
-        <v>31.26993560791016</v>
+        <v>31.26993370056152</v>
       </c>
       <c r="C688" t="n">
-        <v>31.74149119874277</v>
+        <v>31.74148926263102</v>
       </c>
       <c r="D688" t="n">
-        <v>30.96539073320894</v>
+        <v>30.9653888444364</v>
       </c>
       <c r="E688" t="n">
-        <v>31.4664153864515</v>
+        <v>31.46641346711834</v>
       </c>
       <c r="F688" t="n">
         <v>4529600</v>
@@ -14252,16 +14252,16 @@
         <v>45161</v>
       </c>
       <c r="B692" t="n">
-        <v>31.05380439758301</v>
+        <v>31.05380630493164</v>
       </c>
       <c r="C692" t="n">
-        <v>31.24045988874735</v>
+        <v>31.2404618075605</v>
       </c>
       <c r="D692" t="n">
-        <v>30.68048966767887</v>
+        <v>30.68049155209822</v>
       </c>
       <c r="E692" t="n">
-        <v>31.09309960011686</v>
+        <v>31.09310150987904</v>
       </c>
       <c r="F692" t="n">
         <v>4847400</v>
@@ -14272,16 +14272,16 @@
         <v>45162</v>
       </c>
       <c r="B693" t="n">
-        <v>30.91626739501953</v>
+        <v>30.91626930236816</v>
       </c>
       <c r="C693" t="n">
-        <v>31.30923067440671</v>
+        <v>31.30923260599883</v>
       </c>
       <c r="D693" t="n">
-        <v>30.56260306687397</v>
+        <v>30.56260495240363</v>
       </c>
       <c r="E693" t="n">
-        <v>31.05380529232016</v>
+        <v>31.05380720815405</v>
       </c>
       <c r="F693" t="n">
         <v>3471700</v>
@@ -14332,16 +14332,16 @@
         <v>45167</v>
       </c>
       <c r="B696" t="n">
-        <v>31.29940605163574</v>
+        <v>31.29940795898438</v>
       </c>
       <c r="C696" t="n">
-        <v>31.55482955705047</v>
+        <v>31.55483147996431</v>
       </c>
       <c r="D696" t="n">
-        <v>30.63137073276579</v>
+        <v>30.63137259940515</v>
       </c>
       <c r="E696" t="n">
-        <v>31.06362921093831</v>
+        <v>31.06363110391898</v>
       </c>
       <c r="F696" t="n">
         <v>3743200</v>
@@ -14352,16 +14352,16 @@
         <v>45168</v>
       </c>
       <c r="B697" t="n">
-        <v>31.63342475891113</v>
+        <v>31.6334228515625</v>
       </c>
       <c r="C697" t="n">
-        <v>31.70219277216898</v>
+        <v>31.70219086067396</v>
       </c>
       <c r="D697" t="n">
-        <v>30.96538941791287</v>
+        <v>30.96538755084366</v>
       </c>
       <c r="E697" t="n">
-        <v>31.49588873239543</v>
+        <v>31.49588683333958</v>
       </c>
       <c r="F697" t="n">
         <v>3276100</v>
@@ -14412,16 +14412,16 @@
         <v>45173</v>
       </c>
       <c r="B700" t="n">
-        <v>32.27198791503906</v>
+        <v>32.2719841003418</v>
       </c>
       <c r="C700" t="n">
-        <v>32.55688613348561</v>
+        <v>32.55688228511206</v>
       </c>
       <c r="D700" t="n">
-        <v>32.06568385929886</v>
+        <v>32.06568006898767</v>
       </c>
       <c r="E700" t="n">
-        <v>32.22286843713558</v>
+        <v>32.22286462824446</v>
       </c>
       <c r="F700" t="n">
         <v>2652900</v>
@@ -14432,16 +14432,16 @@
         <v>45174</v>
       </c>
       <c r="B701" t="n">
-        <v>32.63547897338867</v>
+        <v>32.63547515869141</v>
       </c>
       <c r="C701" t="n">
-        <v>32.93019957643972</v>
+        <v>32.93019572729314</v>
       </c>
       <c r="D701" t="n">
-        <v>32.07550870331895</v>
+        <v>32.07550495407551</v>
       </c>
       <c r="E701" t="n">
-        <v>32.27198660696912</v>
+        <v>32.27198283475976</v>
       </c>
       <c r="F701" t="n">
         <v>6036900</v>
@@ -14452,16 +14452,16 @@
         <v>45175</v>
       </c>
       <c r="B702" t="n">
-        <v>32.00673675537109</v>
+        <v>32.00674057006836</v>
       </c>
       <c r="C702" t="n">
-        <v>32.71406536628031</v>
+        <v>32.71406926527997</v>
       </c>
       <c r="D702" t="n">
-        <v>31.928142605506</v>
+        <v>31.92814641083608</v>
       </c>
       <c r="E702" t="n">
-        <v>32.65512350145682</v>
+        <v>32.65512739343153</v>
       </c>
       <c r="F702" t="n">
         <v>4505300</v>
@@ -14512,16 +14512,16 @@
         <v>45181</v>
       </c>
       <c r="B705" t="n">
-        <v>32.33092880249023</v>
+        <v>32.3309326171875</v>
       </c>
       <c r="C705" t="n">
-        <v>32.64529791212711</v>
+        <v>32.6453017639165</v>
       </c>
       <c r="D705" t="n">
-        <v>31.76113619661418</v>
+        <v>31.76113994408213</v>
       </c>
       <c r="E705" t="n">
-        <v>31.97726261725491</v>
+        <v>31.97726639022342</v>
       </c>
       <c r="F705" t="n">
         <v>3620500</v>
@@ -14532,16 +14532,16 @@
         <v>45182</v>
       </c>
       <c r="B706" t="n">
-        <v>31.63342475891113</v>
+        <v>31.6334228515625</v>
       </c>
       <c r="C706" t="n">
-        <v>32.1148008517161</v>
+        <v>32.11479891534272</v>
       </c>
       <c r="D706" t="n">
-        <v>31.44676551071783</v>
+        <v>31.44676361462388</v>
       </c>
       <c r="E706" t="n">
-        <v>31.60395007638945</v>
+        <v>31.60394817081799</v>
       </c>
       <c r="F706" t="n">
         <v>7302700</v>
@@ -14552,16 +14552,16 @@
         <v>45183</v>
       </c>
       <c r="B707" t="n">
-        <v>32.31128311157227</v>
+        <v>32.311279296875</v>
       </c>
       <c r="C707" t="n">
-        <v>32.31128311157227</v>
+        <v>32.311279296875</v>
       </c>
       <c r="D707" t="n">
-        <v>31.74149045549294</v>
+        <v>31.74148670806588</v>
       </c>
       <c r="E707" t="n">
-        <v>31.83972940556933</v>
+        <v>31.83972564654409</v>
       </c>
       <c r="F707" t="n">
         <v>4362300</v>
@@ -14592,16 +14592,16 @@
         <v>45187</v>
       </c>
       <c r="B709" t="n">
-        <v>31.98709106445312</v>
+        <v>31.98709297180176</v>
       </c>
       <c r="C709" t="n">
-        <v>32.7140682775227</v>
+        <v>32.71407022822005</v>
       </c>
       <c r="D709" t="n">
-        <v>31.75131234145109</v>
+        <v>31.75131423474054</v>
       </c>
       <c r="E709" t="n">
-        <v>32.5568837113799</v>
+        <v>32.55688565270453</v>
       </c>
       <c r="F709" t="n">
         <v>5099000</v>
@@ -14692,16 +14692,16 @@
         <v>45194</v>
       </c>
       <c r="B714" t="n">
-        <v>30.95556449890137</v>
+        <v>30.95556640625</v>
       </c>
       <c r="C714" t="n">
-        <v>31.20116561183414</v>
+        <v>31.20116753431566</v>
       </c>
       <c r="D714" t="n">
-        <v>29.99280858591396</v>
+        <v>29.99281043394172</v>
       </c>
       <c r="E714" t="n">
-        <v>30.45453800366397</v>
+        <v>30.45453988014151</v>
       </c>
       <c r="F714" t="n">
         <v>6350700</v>
@@ -14712,16 +14712,16 @@
         <v>45195</v>
       </c>
       <c r="B715" t="n">
-        <v>30.32682609558105</v>
+        <v>30.32682800292969</v>
       </c>
       <c r="C715" t="n">
-        <v>30.83767498381136</v>
+        <v>30.83767692328888</v>
       </c>
       <c r="D715" t="n">
-        <v>30.19911246818264</v>
+        <v>30.19911436749897</v>
       </c>
       <c r="E715" t="n">
-        <v>30.75908270302303</v>
+        <v>30.75908463755763</v>
       </c>
       <c r="F715" t="n">
         <v>3433500</v>
@@ -14732,16 +14732,16 @@
         <v>45196</v>
       </c>
       <c r="B716" t="n">
-        <v>30.86714935302734</v>
+        <v>30.86714744567871</v>
       </c>
       <c r="C716" t="n">
-        <v>31.0734533978611</v>
+        <v>31.07345147776449</v>
       </c>
       <c r="D716" t="n">
-        <v>30.42506658011519</v>
+        <v>30.42506470008381</v>
       </c>
       <c r="E716" t="n">
-        <v>30.65102103837466</v>
+        <v>30.65101914438107</v>
       </c>
       <c r="F716" t="n">
         <v>4307600</v>
@@ -14752,16 +14752,16 @@
         <v>45197</v>
       </c>
       <c r="B717" t="n">
-        <v>30.58224868774414</v>
+        <v>30.58225059509277</v>
       </c>
       <c r="C717" t="n">
-        <v>31.21098878902595</v>
+        <v>31.21099073558775</v>
       </c>
       <c r="D717" t="n">
-        <v>30.41523986184255</v>
+        <v>30.41524175877521</v>
       </c>
       <c r="E717" t="n">
-        <v>30.82784979208249</v>
+        <v>30.82785171474873</v>
       </c>
       <c r="F717" t="n">
         <v>4298000</v>
@@ -14772,16 +14772,16 @@
         <v>45198</v>
       </c>
       <c r="B718" t="n">
-        <v>31.02433395385742</v>
+        <v>31.02433204650879</v>
       </c>
       <c r="C718" t="n">
-        <v>31.60395088345571</v>
+        <v>31.60394894047274</v>
       </c>
       <c r="D718" t="n">
-        <v>30.47418795995777</v>
+        <v>30.47418608643163</v>
       </c>
       <c r="E718" t="n">
-        <v>30.86714938417181</v>
+        <v>30.86714748648674</v>
       </c>
       <c r="F718" t="n">
         <v>5846000</v>
@@ -14852,16 +14852,16 @@
         <v>45204</v>
       </c>
       <c r="B722" t="n">
-        <v>28.03782272338867</v>
+        <v>28.0378246307373</v>
       </c>
       <c r="C722" t="n">
-        <v>28.78444842505877</v>
+        <v>28.78445038319864</v>
       </c>
       <c r="D722" t="n">
-        <v>27.72345173862667</v>
+        <v>27.72345362458937</v>
       </c>
       <c r="E722" t="n">
-        <v>28.62726386957162</v>
+        <v>28.62726581701858</v>
       </c>
       <c r="F722" t="n">
         <v>8409300</v>
@@ -14912,16 +14912,16 @@
         <v>45209</v>
       </c>
       <c r="B725" t="n">
-        <v>30.27770614624023</v>
+        <v>30.2777042388916</v>
       </c>
       <c r="C725" t="n">
-        <v>30.40541977953243</v>
+        <v>30.40541786413846</v>
       </c>
       <c r="D725" t="n">
-        <v>29.43283768343539</v>
+        <v>29.43283582930937</v>
       </c>
       <c r="E725" t="n">
-        <v>29.75703296465965</v>
+        <v>29.7570310901109</v>
       </c>
       <c r="F725" t="n">
         <v>7018100</v>
@@ -14972,16 +14972,16 @@
         <v>45215</v>
       </c>
       <c r="B728" t="n">
-        <v>31.67271995544434</v>
+        <v>31.67272186279297</v>
       </c>
       <c r="C728" t="n">
-        <v>32.01656000130495</v>
+        <v>32.01656192935982</v>
       </c>
       <c r="D728" t="n">
-        <v>31.32887616200829</v>
+        <v>31.32887804865046</v>
       </c>
       <c r="E728" t="n">
-        <v>31.91832105893775</v>
+        <v>31.91832298107662</v>
       </c>
       <c r="F728" t="n">
         <v>3741500</v>
@@ -15012,16 +15012,16 @@
         <v>45217</v>
       </c>
       <c r="B730" t="n">
-        <v>32.06568145751953</v>
+        <v>32.06567764282227</v>
       </c>
       <c r="C730" t="n">
-        <v>33.06773447151397</v>
+        <v>33.06773053760736</v>
       </c>
       <c r="D730" t="n">
-        <v>31.63342483773936</v>
+        <v>31.63342107446555</v>
       </c>
       <c r="E730" t="n">
-        <v>32.52741275989484</v>
+        <v>32.52740889026767</v>
       </c>
       <c r="F730" t="n">
         <v>7439800</v>
@@ -15132,16 +15132,16 @@
         <v>45225</v>
       </c>
       <c r="B736" t="n">
-        <v>31.98709106445312</v>
+        <v>31.98709297180176</v>
       </c>
       <c r="C736" t="n">
-        <v>32.12462709138111</v>
+        <v>32.12462900693085</v>
       </c>
       <c r="D736" t="n">
-        <v>31.19134209034388</v>
+        <v>31.19134395024304</v>
       </c>
       <c r="E736" t="n">
-        <v>31.57447923609348</v>
+        <v>31.57448111883861</v>
       </c>
       <c r="F736" t="n">
         <v>2923500</v>
@@ -15152,16 +15152,16 @@
         <v>45226</v>
       </c>
       <c r="B737" t="n">
-        <v>31.52535820007324</v>
+        <v>31.52536010742188</v>
       </c>
       <c r="C737" t="n">
-        <v>32.556882098507</v>
+        <v>32.55688406826494</v>
       </c>
       <c r="D737" t="n">
-        <v>31.24046001693592</v>
+        <v>31.24046190704763</v>
       </c>
       <c r="E737" t="n">
-        <v>32.32110713476096</v>
+        <v>32.32110909025403</v>
       </c>
       <c r="F737" t="n">
         <v>3378100</v>
@@ -15172,16 +15172,16 @@
         <v>45229</v>
       </c>
       <c r="B738" t="n">
-        <v>31.07345390319824</v>
+        <v>31.07345199584961</v>
       </c>
       <c r="C738" t="n">
-        <v>32.11480216169681</v>
+        <v>32.11480019042821</v>
       </c>
       <c r="D738" t="n">
-        <v>30.98503922096583</v>
+        <v>30.98503731904426</v>
       </c>
       <c r="E738" t="n">
-        <v>31.54500949323592</v>
+        <v>31.5450075569423</v>
       </c>
       <c r="F738" t="n">
         <v>3227500</v>
@@ -15192,16 +15192,16 @@
         <v>45230</v>
       </c>
       <c r="B739" t="n">
-        <v>31.86919784545898</v>
+        <v>31.86919975280762</v>
       </c>
       <c r="C739" t="n">
-        <v>32.10497655378492</v>
+        <v>32.10497847524474</v>
       </c>
       <c r="D739" t="n">
-        <v>31.20116441782789</v>
+        <v>31.2011662851952</v>
       </c>
       <c r="E739" t="n">
-        <v>31.20116441782789</v>
+        <v>31.2011662851952</v>
       </c>
       <c r="F739" t="n">
         <v>3372100</v>
@@ -15212,16 +15212,16 @@
         <v>45231</v>
       </c>
       <c r="B740" t="n">
-        <v>32.06568145751953</v>
+        <v>32.06567764282227</v>
       </c>
       <c r="C740" t="n">
-        <v>32.74354294357276</v>
+        <v>32.74353904823363</v>
       </c>
       <c r="D740" t="n">
-        <v>31.94779396986597</v>
+        <v>31.9477901691932</v>
       </c>
       <c r="E740" t="n">
-        <v>32.0755076009098</v>
+        <v>32.07550378504357</v>
       </c>
       <c r="F740" t="n">
         <v>4282500</v>
@@ -15232,16 +15232,16 @@
         <v>45233</v>
       </c>
       <c r="B741" t="n">
-        <v>32.69441604614258</v>
+        <v>32.69441986083984</v>
       </c>
       <c r="C741" t="n">
-        <v>32.94984327951414</v>
+        <v>32.94984712401398</v>
       </c>
       <c r="D741" t="n">
-        <v>32.4684634920525</v>
+        <v>32.46846728038622</v>
       </c>
       <c r="E741" t="n">
-        <v>32.7337131201344</v>
+        <v>32.73371693941674</v>
       </c>
       <c r="F741" t="n">
         <v>3190300</v>
@@ -15272,16 +15272,16 @@
         <v>45237</v>
       </c>
       <c r="B743" t="n">
-        <v>32.48811340332031</v>
+        <v>32.48811721801758</v>
       </c>
       <c r="C743" t="n">
-        <v>32.63547556323554</v>
+        <v>32.63547939523581</v>
       </c>
       <c r="D743" t="n">
-        <v>31.81025571237618</v>
+        <v>31.81025944748058</v>
       </c>
       <c r="E743" t="n">
-        <v>31.87902372098318</v>
+        <v>31.8790274641622</v>
       </c>
       <c r="F743" t="n">
         <v>3324000</v>
@@ -15312,16 +15312,16 @@
         <v>45239</v>
       </c>
       <c r="B745" t="n">
-        <v>30.81802940368652</v>
+        <v>30.81802749633789</v>
       </c>
       <c r="C745" t="n">
-        <v>33.77506711733456</v>
+        <v>33.77506502697286</v>
       </c>
       <c r="D745" t="n">
-        <v>30.67066723245724</v>
+        <v>30.67066533422895</v>
       </c>
       <c r="E745" t="n">
-        <v>33.41157476098916</v>
+        <v>33.41157269312426</v>
       </c>
       <c r="F745" t="n">
         <v>15431300</v>
@@ -15332,16 +15332,16 @@
         <v>45240</v>
       </c>
       <c r="B746" t="n">
-        <v>31.25028419494629</v>
+        <v>31.25028610229492</v>
       </c>
       <c r="C746" t="n">
-        <v>32.06567979171039</v>
+        <v>32.06568174882637</v>
       </c>
       <c r="D746" t="n">
-        <v>31.04398016537612</v>
+        <v>31.04398206013306</v>
       </c>
       <c r="E746" t="n">
-        <v>31.05380443446818</v>
+        <v>31.05380632982475</v>
       </c>
       <c r="F746" t="n">
         <v>4738300</v>
@@ -15352,16 +15352,16 @@
         <v>45243</v>
       </c>
       <c r="B747" t="n">
-        <v>30.94574165344238</v>
+        <v>30.94573974609375</v>
       </c>
       <c r="C747" t="n">
-        <v>31.41729536226194</v>
+        <v>31.41729342584897</v>
       </c>
       <c r="D747" t="n">
-        <v>30.67066771973704</v>
+        <v>30.67066582934266</v>
       </c>
       <c r="E747" t="n">
-        <v>31.21099131732383</v>
+        <v>31.21098939362647</v>
       </c>
       <c r="F747" t="n">
         <v>3172300</v>
@@ -15392,16 +15392,16 @@
         <v>45246</v>
       </c>
       <c r="B749" t="n">
-        <v>31.13239669799805</v>
+        <v>31.13239860534668</v>
       </c>
       <c r="C749" t="n">
-        <v>32.13444778565191</v>
+        <v>32.13444975439192</v>
       </c>
       <c r="D749" t="n">
-        <v>30.68048968892551</v>
+        <v>30.68049156858774</v>
       </c>
       <c r="E749" t="n">
-        <v>31.78078159366364</v>
+        <v>31.78078354073604</v>
       </c>
       <c r="F749" t="n">
         <v>5148500</v>
@@ -15492,16 +15492,16 @@
         <v>45253</v>
       </c>
       <c r="B754" t="n">
-        <v>31.81025886535645</v>
+        <v>31.81025505065918</v>
       </c>
       <c r="C754" t="n">
-        <v>32.00674051552654</v>
+        <v>32.00673667726713</v>
       </c>
       <c r="D754" t="n">
-        <v>31.58430627931235</v>
+        <v>31.5843024917114</v>
       </c>
       <c r="E754" t="n">
-        <v>31.82990740513103</v>
+        <v>31.82990358807751</v>
       </c>
       <c r="F754" t="n">
         <v>2086300</v>
@@ -15552,16 +15552,16 @@
         <v>45258</v>
       </c>
       <c r="B757" t="n">
-        <v>29.80615234375</v>
+        <v>29.80615043640137</v>
       </c>
       <c r="C757" t="n">
-        <v>30.21876230404811</v>
+        <v>30.21876037029583</v>
       </c>
       <c r="D757" t="n">
-        <v>29.63914350568201</v>
+        <v>29.63914160902057</v>
       </c>
       <c r="E757" t="n">
-        <v>30.17946522507312</v>
+        <v>30.17946329383553</v>
       </c>
       <c r="F757" t="n">
         <v>5777500</v>
@@ -15592,16 +15592,16 @@
         <v>45260</v>
       </c>
       <c r="B759" t="n">
-        <v>29.45248413085938</v>
+        <v>29.45248603820801</v>
       </c>
       <c r="C759" t="n">
-        <v>29.83562312973222</v>
+        <v>29.83562506189301</v>
       </c>
       <c r="D759" t="n">
-        <v>29.17741209183939</v>
+        <v>29.1774139813743</v>
       </c>
       <c r="E759" t="n">
-        <v>29.66861430298963</v>
+        <v>29.66861622433489</v>
       </c>
       <c r="F759" t="n">
         <v>4483800</v>
@@ -15732,16 +15732,16 @@
         <v>45271</v>
       </c>
       <c r="B766" t="n">
-        <v>26.91788291931152</v>
+        <v>26.91788101196289</v>
       </c>
       <c r="C766" t="n">
-        <v>27.08489175922624</v>
+        <v>27.08488984004369</v>
       </c>
       <c r="D766" t="n">
-        <v>26.48562441474616</v>
+        <v>26.48562253802652</v>
       </c>
       <c r="E766" t="n">
-        <v>26.96700426857343</v>
+        <v>26.96700235774415</v>
       </c>
       <c r="F766" t="n">
         <v>6627000</v>
@@ -15792,16 +15792,16 @@
         <v>45274</v>
       </c>
       <c r="B769" t="n">
-        <v>27.00629806518555</v>
+        <v>27.00629997253418</v>
       </c>
       <c r="C769" t="n">
-        <v>27.2027797044063</v>
+        <v>27.20278162563166</v>
       </c>
       <c r="D769" t="n">
-        <v>26.49544730224182</v>
+        <v>26.49544917351107</v>
       </c>
       <c r="E769" t="n">
-        <v>26.82946496464443</v>
+        <v>26.82946685950403</v>
       </c>
       <c r="F769" t="n">
         <v>14011300</v>
@@ -15812,16 +15812,16 @@
         <v>45275</v>
       </c>
       <c r="B770" t="n">
-        <v>25.88635635375977</v>
+        <v>25.8863582611084</v>
       </c>
       <c r="C770" t="n">
-        <v>27.21260267051552</v>
+        <v>27.21260467558413</v>
       </c>
       <c r="D770" t="n">
-        <v>25.88635635375977</v>
+        <v>25.8863582611084</v>
       </c>
       <c r="E770" t="n">
-        <v>27.1634813261689</v>
+        <v>27.16348332761816</v>
       </c>
       <c r="F770" t="n">
         <v>11924000</v>
@@ -15832,16 +15832,16 @@
         <v>45278</v>
       </c>
       <c r="B771" t="n">
-        <v>26.21055030822754</v>
+        <v>26.21055221557617</v>
       </c>
       <c r="C771" t="n">
-        <v>26.76069626050536</v>
+        <v>26.76069820788825</v>
       </c>
       <c r="D771" t="n">
-        <v>25.94530066428034</v>
+        <v>25.94530255232668</v>
       </c>
       <c r="E771" t="n">
-        <v>26.12213376024514</v>
+        <v>26.12213566115967</v>
       </c>
       <c r="F771" t="n">
         <v>4958200</v>
@@ -15852,16 +15852,16 @@
         <v>45279</v>
       </c>
       <c r="B772" t="n">
-        <v>26.32843971252441</v>
+        <v>26.32843780517578</v>
       </c>
       <c r="C772" t="n">
-        <v>26.52492136101001</v>
+        <v>26.52491943942738</v>
       </c>
       <c r="D772" t="n">
-        <v>26.13195993782669</v>
+        <v>26.13195804471192</v>
       </c>
       <c r="E772" t="n">
-        <v>26.30879304670615</v>
+        <v>26.30879114078081</v>
       </c>
       <c r="F772" t="n">
         <v>3900900</v>
@@ -15872,16 +15872,16 @@
         <v>45280</v>
       </c>
       <c r="B773" t="n">
-        <v>25.85688591003418</v>
+        <v>25.85688400268555</v>
       </c>
       <c r="C773" t="n">
-        <v>26.54456980342805</v>
+        <v>26.54456784535201</v>
       </c>
       <c r="D773" t="n">
-        <v>25.68987707156926</v>
+        <v>25.68987517654013</v>
       </c>
       <c r="E773" t="n">
-        <v>26.54456980342805</v>
+        <v>26.54456784535201</v>
       </c>
       <c r="F773" t="n">
         <v>6168300</v>
@@ -15912,16 +15912,16 @@
         <v>45282</v>
       </c>
       <c r="B775" t="n">
-        <v>25.95512580871582</v>
+        <v>25.95512771606445</v>
       </c>
       <c r="C775" t="n">
-        <v>26.2203754616087</v>
+        <v>26.22037738844958</v>
       </c>
       <c r="D775" t="n">
-        <v>25.79794124562103</v>
+        <v>25.79794314141873</v>
       </c>
       <c r="E775" t="n">
-        <v>26.03371809026321</v>
+        <v>26.03372000338731</v>
       </c>
       <c r="F775" t="n">
         <v>3644200</v>
@@ -16012,16 +16012,16 @@
         <v>45294</v>
       </c>
       <c r="B780" t="n">
-        <v>25.88635635375977</v>
+        <v>25.8863582611084</v>
       </c>
       <c r="C780" t="n">
-        <v>26.28914200846361</v>
+        <v>26.28914394549015</v>
       </c>
       <c r="D780" t="n">
-        <v>25.35585707754239</v>
+        <v>25.35585894580298</v>
       </c>
       <c r="E780" t="n">
-        <v>25.64075525338972</v>
+        <v>25.64075714264207</v>
       </c>
       <c r="F780" t="n">
         <v>5734800</v>
@@ -16052,16 +16052,16 @@
         <v>45296</v>
       </c>
       <c r="B782" t="n">
-        <v>25.68987464904785</v>
+        <v>25.68987655639648</v>
       </c>
       <c r="C782" t="n">
-        <v>25.97477282406455</v>
+        <v>25.97477475256549</v>
       </c>
       <c r="D782" t="n">
-        <v>25.21832098742127</v>
+        <v>25.21832285975933</v>
       </c>
       <c r="E782" t="n">
-        <v>25.36568127245611</v>
+        <v>25.36568315573496</v>
       </c>
       <c r="F782" t="n">
         <v>3417300</v>
@@ -16092,16 +16092,16 @@
         <v>45300</v>
       </c>
       <c r="B784" t="n">
-        <v>28.01817512512207</v>
+        <v>28.0181770324707</v>
       </c>
       <c r="C784" t="n">
-        <v>28.24412769698892</v>
+        <v>28.24412961971936</v>
       </c>
       <c r="D784" t="n">
-        <v>26.79999384234995</v>
+        <v>26.7999956667704</v>
       </c>
       <c r="E784" t="n">
-        <v>27.01612214494592</v>
+        <v>27.01612398407939</v>
       </c>
       <c r="F784" t="n">
         <v>10290300</v>
@@ -16152,16 +16152,16 @@
         <v>45303</v>
       </c>
       <c r="B787" t="n">
-        <v>28.20483207702637</v>
+        <v>28.20483016967773</v>
       </c>
       <c r="C787" t="n">
-        <v>28.86304316187749</v>
+        <v>28.86304121001741</v>
       </c>
       <c r="D787" t="n">
-        <v>27.82169492460737</v>
+        <v>27.82169304316834</v>
       </c>
       <c r="E787" t="n">
-        <v>28.63709057833746</v>
+        <v>28.63708864175739</v>
       </c>
       <c r="F787" t="n">
         <v>5067700</v>
@@ -16172,16 +16172,16 @@
         <v>45306</v>
       </c>
       <c r="B788" t="n">
-        <v>28.52902793884277</v>
+        <v>28.52902603149414</v>
       </c>
       <c r="C788" t="n">
-        <v>28.68621251092004</v>
+        <v>28.68621059306261</v>
       </c>
       <c r="D788" t="n">
-        <v>27.9002877767458</v>
+        <v>27.90028591143248</v>
       </c>
       <c r="E788" t="n">
-        <v>28.06729661880138</v>
+        <v>28.06729474232245</v>
       </c>
       <c r="F788" t="n">
         <v>3859400</v>
@@ -16252,16 +16252,16 @@
         <v>45310</v>
       </c>
       <c r="B792" t="n">
-        <v>29.03005027770996</v>
+        <v>29.03005218505859</v>
       </c>
       <c r="C792" t="n">
-        <v>29.197059106456</v>
+        <v>29.19706102477754</v>
       </c>
       <c r="D792" t="n">
-        <v>28.0574701128199</v>
+        <v>28.05747195626752</v>
       </c>
       <c r="E792" t="n">
-        <v>28.73532969699943</v>
+        <v>28.73533158498416</v>
       </c>
       <c r="F792" t="n">
         <v>7851200</v>
@@ -16312,16 +16312,16 @@
         <v>45315</v>
       </c>
       <c r="B795" t="n">
-        <v>27.86099243164062</v>
+        <v>27.86099052429199</v>
       </c>
       <c r="C795" t="n">
-        <v>28.52902779653059</v>
+        <v>28.52902584344861</v>
       </c>
       <c r="D795" t="n">
-        <v>27.63503797084227</v>
+        <v>27.63503607896236</v>
       </c>
       <c r="E795" t="n">
-        <v>28.04764793893384</v>
+        <v>28.04764601880687</v>
       </c>
       <c r="F795" t="n">
         <v>4070600</v>
@@ -16352,16 +16352,16 @@
         <v>45317</v>
       </c>
       <c r="B797" t="n">
-        <v>28.24412727355957</v>
+        <v>28.2441291809082</v>
       </c>
       <c r="C797" t="n">
-        <v>28.24412727355957</v>
+        <v>28.2441291809082</v>
       </c>
       <c r="D797" t="n">
-        <v>27.50732395337975</v>
+        <v>27.50732581097147</v>
       </c>
       <c r="E797" t="n">
-        <v>27.65468424265817</v>
+        <v>27.65468611020124</v>
       </c>
       <c r="F797" t="n">
         <v>2761100</v>
@@ -16392,16 +16392,16 @@
         <v>45321</v>
       </c>
       <c r="B799" t="n">
-        <v>27.2420768737793</v>
+        <v>27.24207496643066</v>
       </c>
       <c r="C799" t="n">
-        <v>27.54662362392648</v>
+        <v>27.54662169525507</v>
       </c>
       <c r="D799" t="n">
-        <v>26.97682720382707</v>
+        <v>26.97682531504984</v>
       </c>
       <c r="E799" t="n">
-        <v>27.369790510625</v>
+        <v>27.36978859433452</v>
       </c>
       <c r="F799" t="n">
         <v>2184900</v>
@@ -16432,16 +16432,16 @@
         <v>45323</v>
       </c>
       <c r="B801" t="n">
-        <v>26.24002265930176</v>
+        <v>26.24002075195312</v>
       </c>
       <c r="C801" t="n">
-        <v>27.40908451061442</v>
+        <v>27.4090825182884</v>
       </c>
       <c r="D801" t="n">
-        <v>26.10248663224892</v>
+        <v>26.10248473489757</v>
       </c>
       <c r="E801" t="n">
-        <v>27.31084368823903</v>
+        <v>27.31084170305399</v>
       </c>
       <c r="F801" t="n">
         <v>7611700</v>
@@ -16532,16 +16532,16 @@
         <v>45330</v>
       </c>
       <c r="B806" t="n">
-        <v>28.79427528381348</v>
+        <v>28.79427337646484</v>
       </c>
       <c r="C806" t="n">
-        <v>28.81392382346353</v>
+        <v>28.81392191481336</v>
       </c>
       <c r="D806" t="n">
-        <v>27.39926082305394</v>
+        <v>27.39925900811183</v>
       </c>
       <c r="E806" t="n">
-        <v>28.71568299900116</v>
+        <v>28.71568109685852</v>
       </c>
       <c r="F806" t="n">
         <v>6908300</v>
@@ -16552,16 +16552,16 @@
         <v>45331</v>
       </c>
       <c r="B807" t="n">
-        <v>27.6939811706543</v>
+        <v>27.69398307800293</v>
       </c>
       <c r="C807" t="n">
-        <v>28.9121624286317</v>
+        <v>28.9121644198793</v>
       </c>
       <c r="D807" t="n">
-        <v>27.52697234402422</v>
+        <v>27.52697423987057</v>
       </c>
       <c r="E807" t="n">
-        <v>28.83357014985212</v>
+        <v>28.83357213568689</v>
       </c>
       <c r="F807" t="n">
         <v>5513900</v>
@@ -16592,16 +16592,16 @@
         <v>45337</v>
       </c>
       <c r="B809" t="n">
-        <v>28.00835227966309</v>
+        <v>28.00835037231445</v>
       </c>
       <c r="C809" t="n">
-        <v>28.26377767232718</v>
+        <v>28.26377574758426</v>
       </c>
       <c r="D809" t="n">
-        <v>27.28137318075199</v>
+        <v>27.28137132291011</v>
       </c>
       <c r="E809" t="n">
-        <v>27.40908494019011</v>
+        <v>27.40908307365115</v>
       </c>
       <c r="F809" t="n">
         <v>2788300</v>
@@ -16632,16 +16632,16 @@
         <v>45341</v>
       </c>
       <c r="B811" t="n">
-        <v>28.67638778686523</v>
+        <v>28.6763858795166</v>
       </c>
       <c r="C811" t="n">
-        <v>28.76480434148215</v>
+        <v>28.76480242825268</v>
       </c>
       <c r="D811" t="n">
-        <v>28.23430501378064</v>
+        <v>28.2343031358362</v>
       </c>
       <c r="E811" t="n">
-        <v>28.74515580183664</v>
+        <v>28.74515388991405</v>
       </c>
       <c r="F811" t="n">
         <v>1698200</v>
@@ -16672,16 +16672,16 @@
         <v>45343</v>
       </c>
       <c r="B813" t="n">
-        <v>28.92198944091797</v>
+        <v>28.92198753356934</v>
       </c>
       <c r="C813" t="n">
-        <v>28.98093318714647</v>
+        <v>28.98093127591061</v>
       </c>
       <c r="D813" t="n">
-        <v>28.36201916727748</v>
+        <v>28.36201729685779</v>
       </c>
       <c r="E813" t="n">
-        <v>28.6370912322024</v>
+        <v>28.63708934364225</v>
       </c>
       <c r="F813" t="n">
         <v>2751400</v>
@@ -16792,16 +16792,16 @@
         <v>45351</v>
       </c>
       <c r="B819" t="n">
-        <v>27.45820617675781</v>
+        <v>27.45820426940918</v>
       </c>
       <c r="C819" t="n">
-        <v>28.14588819377561</v>
+        <v>28.14588623865804</v>
       </c>
       <c r="D819" t="n">
-        <v>27.45820617675781</v>
+        <v>27.45820426940918</v>
       </c>
       <c r="E819" t="n">
-        <v>27.98870362566938</v>
+        <v>27.98870168147043</v>
       </c>
       <c r="F819" t="n">
         <v>2784300</v>
@@ -16972,16 +16972,16 @@
         <v>45364</v>
       </c>
       <c r="B828" t="n">
-        <v>29.13811683654785</v>
+        <v>29.13811492919922</v>
       </c>
       <c r="C828" t="n">
-        <v>29.36406941808906</v>
+        <v>29.36406749594983</v>
       </c>
       <c r="D828" t="n">
-        <v>28.98093226905937</v>
+        <v>28.98093037199986</v>
       </c>
       <c r="E828" t="n">
-        <v>28.98093226905937</v>
+        <v>28.98093037199986</v>
       </c>
       <c r="F828" t="n">
         <v>2596400</v>
@@ -17032,16 +17032,16 @@
         <v>45369</v>
       </c>
       <c r="B831" t="n">
-        <v>28.98093032836914</v>
+        <v>28.98093223571777</v>
       </c>
       <c r="C831" t="n">
-        <v>29.28547517326093</v>
+        <v>29.28547710065286</v>
       </c>
       <c r="D831" t="n">
-        <v>28.61743986927554</v>
+        <v>28.61744175270144</v>
       </c>
       <c r="E831" t="n">
-        <v>28.77462630002598</v>
+        <v>28.77462819379693</v>
       </c>
       <c r="F831" t="n">
         <v>4710300</v>
@@ -17112,16 +17112,16 @@
         <v>45373</v>
       </c>
       <c r="B835" t="n">
-        <v>29.71773338317871</v>
+        <v>29.71773529052734</v>
       </c>
       <c r="C835" t="n">
-        <v>30.00263156131158</v>
+        <v>30.0026334869456</v>
       </c>
       <c r="D835" t="n">
-        <v>29.28547491839919</v>
+        <v>29.28547679800454</v>
       </c>
       <c r="E835" t="n">
-        <v>29.88474220772164</v>
+        <v>29.88474412578926</v>
       </c>
       <c r="F835" t="n">
         <v>3854000</v>
@@ -17152,16 +17152,16 @@
         <v>45377</v>
       </c>
       <c r="B837" t="n">
-        <v>30.81802940368652</v>
+        <v>30.81802749633789</v>
       </c>
       <c r="C837" t="n">
-        <v>31.22081509112746</v>
+        <v>31.22081315885015</v>
       </c>
       <c r="D837" t="n">
-        <v>30.51348266534799</v>
+        <v>30.51348077684796</v>
       </c>
       <c r="E837" t="n">
-        <v>30.61172348823823</v>
+        <v>30.61172159365801</v>
       </c>
       <c r="F837" t="n">
         <v>3327200</v>
@@ -17172,16 +17172,16 @@
         <v>45378</v>
       </c>
       <c r="B838" t="n">
-        <v>31.48606300354004</v>
+        <v>31.48606109619141</v>
       </c>
       <c r="C838" t="n">
-        <v>31.91832337550937</v>
+        <v>31.91832144197546</v>
       </c>
       <c r="D838" t="n">
-        <v>30.38577102935353</v>
+        <v>30.3857691886579</v>
       </c>
       <c r="E838" t="n">
-        <v>30.6510206900868</v>
+        <v>30.65101883332299</v>
       </c>
       <c r="F838" t="n">
         <v>9071000</v>
@@ -17372,16 +17372,16 @@
         <v>45393</v>
       </c>
       <c r="B848" t="n">
-        <v>35.62198257446289</v>
+        <v>35.62198638916016</v>
       </c>
       <c r="C848" t="n">
-        <v>35.91670689814429</v>
+        <v>35.91671074440308</v>
       </c>
       <c r="D848" t="n">
-        <v>34.59045868430435</v>
+        <v>34.59046238853748</v>
       </c>
       <c r="E848" t="n">
-        <v>34.74764324139922</v>
+        <v>34.74764696246498</v>
       </c>
       <c r="F848" t="n">
         <v>5960900</v>
@@ -17412,16 +17412,16 @@
         <v>45397</v>
       </c>
       <c r="B850" t="n">
-        <v>34.06978988647461</v>
+        <v>34.06978607177734</v>
       </c>
       <c r="C850" t="n">
-        <v>34.52169507730631</v>
+        <v>34.52169121201051</v>
       </c>
       <c r="D850" t="n">
-        <v>33.83401114697602</v>
+        <v>33.83400735867823</v>
       </c>
       <c r="E850" t="n">
-        <v>34.43327851844133</v>
+        <v>34.43327466304528</v>
       </c>
       <c r="F850" t="n">
         <v>4151100</v>
@@ -17472,16 +17472,16 @@
         <v>45400</v>
       </c>
       <c r="B853" t="n">
-        <v>32.33092880249023</v>
+        <v>32.3309326171875</v>
       </c>
       <c r="C853" t="n">
-        <v>33.28386227408815</v>
+        <v>33.28386620122118</v>
       </c>
       <c r="D853" t="n">
-        <v>31.93796554165645</v>
+        <v>31.93796930998834</v>
       </c>
       <c r="E853" t="n">
-        <v>33.00878649247434</v>
+        <v>33.00879038715143</v>
       </c>
       <c r="F853" t="n">
         <v>4478700</v>
@@ -17632,16 +17632,16 @@
         <v>45412</v>
       </c>
       <c r="B861" t="n">
-        <v>32.58635330200195</v>
+        <v>32.58635711669922</v>
       </c>
       <c r="C861" t="n">
-        <v>33.66700042877825</v>
+        <v>33.66700436998067</v>
       </c>
       <c r="D861" t="n">
-        <v>32.43899488533395</v>
+        <v>32.43899868278081</v>
       </c>
       <c r="E861" t="n">
-        <v>33.60805481356574</v>
+        <v>33.60805874786774</v>
       </c>
       <c r="F861" t="n">
         <v>6661700</v>
@@ -29832,19 +29832,39 @@
         <v>46303</v>
       </c>
       <c r="B1471" t="n">
-        <v>20.57</v>
+        <v>20.56999969482422</v>
       </c>
       <c r="C1471" t="n">
-        <v>20.84</v>
+        <v>20.84000015258789</v>
       </c>
       <c r="D1471" t="n">
-        <v>20.05</v>
+        <v>20.04999923706055</v>
       </c>
       <c r="E1471" t="n">
-        <v>20.1</v>
+        <v>20.10000038146973</v>
       </c>
       <c r="F1471" t="n">
         <v>5536900</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1472" t="n">
+        <v>20.57</v>
+      </c>
+      <c r="C1472" t="n">
+        <v>21</v>
+      </c>
+      <c r="D1472" t="n">
+        <v>20.36</v>
+      </c>
+      <c r="E1472" t="n">
+        <v>20.62</v>
+      </c>
+      <c r="F1472" t="n">
+        <v>6335300</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -29852,16 +29852,16 @@
         <v>46304</v>
       </c>
       <c r="B1472" t="n">
-        <v>20.57</v>
+        <v>20.56999969482422</v>
       </c>
       <c r="C1472" t="n">
         <v>21</v>
       </c>
       <c r="D1472" t="n">
-        <v>20.36</v>
+        <v>20.36000061035156</v>
       </c>
       <c r="E1472" t="n">
-        <v>20.62</v>
+        <v>20.6200008392334</v>
       </c>
       <c r="F1472" t="n">
         <v>6335300</v>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1472"/>
+  <dimension ref="A1:F1473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,16 +512,16 @@
         <v>44152</v>
       </c>
       <c r="B5" t="n">
-        <v>20.17695426940918</v>
+        <v>20.17695617675781</v>
       </c>
       <c r="C5" t="n">
-        <v>20.17695426940918</v>
+        <v>20.17695617675781</v>
       </c>
       <c r="D5" t="n">
-        <v>19.85012445790661</v>
+        <v>19.85012633435968</v>
       </c>
       <c r="E5" t="n">
-        <v>20.12888973916155</v>
+        <v>20.12889164196659</v>
       </c>
       <c r="F5" t="n">
         <v>262242</v>
@@ -572,16 +572,16 @@
         <v>44158</v>
       </c>
       <c r="B8" t="n">
-        <v>20.20579147338867</v>
+        <v>20.2057933807373</v>
       </c>
       <c r="C8" t="n">
-        <v>20.52300874747816</v>
+        <v>20.52301068477087</v>
       </c>
       <c r="D8" t="n">
-        <v>20.14811628674976</v>
+        <v>20.14811818865408</v>
       </c>
       <c r="E8" t="n">
-        <v>20.14811628674976</v>
+        <v>20.14811818865408</v>
       </c>
       <c r="F8" t="n">
         <v>79408</v>
@@ -632,16 +632,16 @@
         <v>44161</v>
       </c>
       <c r="B11" t="n">
-        <v>22.87810897827148</v>
+        <v>22.87811088562012</v>
       </c>
       <c r="C11" t="n">
-        <v>22.87810897827148</v>
+        <v>22.87811088562012</v>
       </c>
       <c r="D11" t="n">
-        <v>22.31096214463751</v>
+        <v>22.3109640047031</v>
       </c>
       <c r="E11" t="n">
-        <v>22.31096214463751</v>
+        <v>22.3109640047031</v>
       </c>
       <c r="F11" t="n">
         <v>72970</v>
@@ -652,16 +652,16 @@
         <v>44162</v>
       </c>
       <c r="B12" t="n">
-        <v>23.07036399841309</v>
+        <v>23.07036209106445</v>
       </c>
       <c r="C12" t="n">
-        <v>23.55099623037812</v>
+        <v>23.55099428329309</v>
       </c>
       <c r="D12" t="n">
-        <v>22.10909953448302</v>
+        <v>22.10909770660719</v>
       </c>
       <c r="E12" t="n">
-        <v>23.07036399841309</v>
+        <v>23.07036209106445</v>
       </c>
       <c r="F12" t="n">
         <v>72050</v>
@@ -692,16 +692,16 @@
         <v>44166</v>
       </c>
       <c r="B14" t="n">
-        <v>23.07036399841309</v>
+        <v>23.07036209106445</v>
       </c>
       <c r="C14" t="n">
-        <v>23.16649119432127</v>
+        <v>23.1664892790253</v>
       </c>
       <c r="D14" t="n">
-        <v>23.03191386956499</v>
+        <v>23.03191196539523</v>
       </c>
       <c r="E14" t="n">
-        <v>23.12803919168523</v>
+        <v>23.12803727956828</v>
       </c>
       <c r="F14" t="n">
         <v>93512</v>
@@ -792,16 +792,16 @@
         <v>44173</v>
       </c>
       <c r="B19" t="n">
-        <v>26.33866310119629</v>
+        <v>26.33866500854492</v>
       </c>
       <c r="C19" t="n">
-        <v>26.57898012603766</v>
+        <v>26.57898205078916</v>
       </c>
       <c r="D19" t="n">
-        <v>25.56965124500673</v>
+        <v>25.56965309666637</v>
       </c>
       <c r="E19" t="n">
-        <v>25.56965124500673</v>
+        <v>25.56965309666637</v>
       </c>
       <c r="F19" t="n">
         <v>126420</v>
@@ -812,16 +812,16 @@
         <v>44174</v>
       </c>
       <c r="B20" t="n">
-        <v>26.83852195739746</v>
+        <v>26.83852005004883</v>
       </c>
       <c r="C20" t="n">
-        <v>27.77095064592048</v>
+        <v>27.77094867230641</v>
       </c>
       <c r="D20" t="n">
-        <v>26.27137696749292</v>
+        <v>26.27137510044991</v>
       </c>
       <c r="E20" t="n">
-        <v>26.49246706969505</v>
+        <v>26.4924651869397</v>
       </c>
       <c r="F20" t="n">
         <v>212880</v>
@@ -892,16 +892,16 @@
         <v>44180</v>
       </c>
       <c r="B24" t="n">
-        <v>33.00984573364258</v>
+        <v>33.00984191894531</v>
       </c>
       <c r="C24" t="n">
-        <v>33.98072266755544</v>
+        <v>33.9807187406613</v>
       </c>
       <c r="D24" t="n">
-        <v>30.76048335959674</v>
+        <v>30.7604798048412</v>
       </c>
       <c r="E24" t="n">
-        <v>30.76048335959674</v>
+        <v>30.7604798048412</v>
       </c>
       <c r="F24" t="n">
         <v>887803</v>
@@ -912,16 +912,16 @@
         <v>44181</v>
       </c>
       <c r="B25" t="n">
-        <v>32.68301391601562</v>
+        <v>32.68301773071289</v>
       </c>
       <c r="C25" t="n">
-        <v>34.45173835953219</v>
+        <v>34.4517423806715</v>
       </c>
       <c r="D25" t="n">
-        <v>32.10625456033017</v>
+        <v>32.10625830770921</v>
       </c>
       <c r="E25" t="n">
-        <v>33.62505319761509</v>
+        <v>33.62505712226533</v>
       </c>
       <c r="F25" t="n">
         <v>376808</v>
@@ -932,16 +932,16 @@
         <v>44182</v>
       </c>
       <c r="B26" t="n">
-        <v>32.10625839233398</v>
+        <v>32.10625457763672</v>
       </c>
       <c r="C26" t="n">
-        <v>33.64428227520571</v>
+        <v>33.64427827776851</v>
       </c>
       <c r="D26" t="n">
-        <v>31.64484935368452</v>
+        <v>31.64484559380946</v>
       </c>
       <c r="E26" t="n">
-        <v>33.6250572108933</v>
+        <v>33.62505321574033</v>
       </c>
       <c r="F26" t="n">
         <v>258257</v>
@@ -972,16 +972,16 @@
         <v>44186</v>
       </c>
       <c r="B28" t="n">
-        <v>32.18315887451172</v>
+        <v>32.18315505981445</v>
       </c>
       <c r="C28" t="n">
-        <v>33.33667773162143</v>
+        <v>33.33667378019659</v>
       </c>
       <c r="D28" t="n">
-        <v>29.12633427792858</v>
+        <v>29.12633082555934</v>
       </c>
       <c r="E28" t="n">
-        <v>31.86594156356414</v>
+        <v>31.86593778646691</v>
       </c>
       <c r="F28" t="n">
         <v>236079</v>
@@ -992,16 +992,16 @@
         <v>44187</v>
       </c>
       <c r="B29" t="n">
-        <v>33.16364288330078</v>
+        <v>33.16364669799805</v>
       </c>
       <c r="C29" t="n">
-        <v>33.47124761081827</v>
+        <v>33.47125146089823</v>
       </c>
       <c r="D29" t="n">
-        <v>32.59649608138177</v>
+        <v>32.59649983084212</v>
       </c>
       <c r="E29" t="n">
-        <v>33.21170553641675</v>
+        <v>33.21170935664249</v>
       </c>
       <c r="F29" t="n">
         <v>167504</v>
@@ -1032,16 +1032,16 @@
         <v>44193</v>
       </c>
       <c r="B31" t="n">
-        <v>36.21085739135742</v>
+        <v>36.21085357666016</v>
       </c>
       <c r="C31" t="n">
-        <v>36.66265388599569</v>
+        <v>36.66265002370312</v>
       </c>
       <c r="D31" t="n">
-        <v>35.56681025863972</v>
+        <v>35.56680651179074</v>
       </c>
       <c r="E31" t="n">
-        <v>35.56681025863972</v>
+        <v>35.56680651179074</v>
       </c>
       <c r="F31" t="n">
         <v>451822</v>
@@ -1052,16 +1052,16 @@
         <v>44194</v>
       </c>
       <c r="B32" t="n">
-        <v>36.09550476074219</v>
+        <v>36.09550857543945</v>
       </c>
       <c r="C32" t="n">
-        <v>37.06638166531152</v>
+        <v>37.06638558261441</v>
       </c>
       <c r="D32" t="n">
-        <v>35.95131304358604</v>
+        <v>35.95131684304462</v>
       </c>
       <c r="E32" t="n">
-        <v>36.52807241705953</v>
+        <v>36.52807627747203</v>
       </c>
       <c r="F32" t="n">
         <v>337154</v>
@@ -1092,16 +1092,16 @@
         <v>44200</v>
       </c>
       <c r="B34" t="n">
-        <v>34.99966049194336</v>
+        <v>34.99966430664062</v>
       </c>
       <c r="C34" t="n">
-        <v>36.62420073506411</v>
+        <v>36.62420472682393</v>
       </c>
       <c r="D34" t="n">
-        <v>34.98043542972244</v>
+        <v>34.98043924232432</v>
       </c>
       <c r="E34" t="n">
-        <v>36.52807167638402</v>
+        <v>36.52807565766651</v>
       </c>
       <c r="F34" t="n">
         <v>331840</v>
@@ -1112,16 +1112,16 @@
         <v>44201</v>
       </c>
       <c r="B35" t="n">
-        <v>36.13395690917969</v>
+        <v>36.13395309448242</v>
       </c>
       <c r="C35" t="n">
-        <v>36.32621129362743</v>
+        <v>36.32620745863368</v>
       </c>
       <c r="D35" t="n">
-        <v>34.60554560816865</v>
+        <v>34.60554195482727</v>
       </c>
       <c r="E35" t="n">
-        <v>35.45145965313264</v>
+        <v>35.45145591048728</v>
       </c>
       <c r="F35" t="n">
         <v>328059</v>
@@ -1172,16 +1172,16 @@
         <v>44204</v>
       </c>
       <c r="B38" t="n">
-        <v>34.13452529907227</v>
+        <v>34.134521484375</v>
       </c>
       <c r="C38" t="n">
-        <v>35.75906572541368</v>
+        <v>35.75906172916622</v>
       </c>
       <c r="D38" t="n">
-        <v>34.13452529907227</v>
+        <v>34.134521484375</v>
       </c>
       <c r="E38" t="n">
-        <v>35.16308123419719</v>
+        <v>35.16307730455386</v>
       </c>
       <c r="F38" t="n">
         <v>367201</v>
@@ -1272,16 +1272,16 @@
         <v>44211</v>
       </c>
       <c r="B43" t="n">
-        <v>33.94226837158203</v>
+        <v>33.9422721862793</v>
       </c>
       <c r="C43" t="n">
-        <v>35.04772061203977</v>
+        <v>35.0477245509764</v>
       </c>
       <c r="D43" t="n">
-        <v>33.16364216523639</v>
+        <v>33.16364589242556</v>
       </c>
       <c r="E43" t="n">
-        <v>34.60554046537172</v>
+        <v>34.60554435461268</v>
       </c>
       <c r="F43" t="n">
         <v>319883</v>
@@ -1292,16 +1292,16 @@
         <v>44214</v>
       </c>
       <c r="B44" t="n">
-        <v>34.04801177978516</v>
+        <v>34.04800796508789</v>
       </c>
       <c r="C44" t="n">
-        <v>34.5094208103909</v>
+        <v>34.50941694399793</v>
       </c>
       <c r="D44" t="n">
-        <v>33.27900172554335</v>
+        <v>33.27899799700501</v>
       </c>
       <c r="E44" t="n">
-        <v>34.11529950370554</v>
+        <v>34.11529568146945</v>
       </c>
       <c r="F44" t="n">
         <v>117631</v>
@@ -1332,16 +1332,16 @@
         <v>44216</v>
       </c>
       <c r="B46" t="n">
-        <v>34.12490844726562</v>
+        <v>34.12491226196289</v>
       </c>
       <c r="C46" t="n">
-        <v>35.28803968588292</v>
+        <v>35.28804363060232</v>
       </c>
       <c r="D46" t="n">
-        <v>33.66350321275509</v>
+        <v>33.66350697587357</v>
       </c>
       <c r="E46" t="n">
-        <v>34.60554249130722</v>
+        <v>34.60554635973278</v>
       </c>
       <c r="F46" t="n">
         <v>359332</v>
@@ -1372,16 +1372,16 @@
         <v>44218</v>
       </c>
       <c r="B48" t="n">
-        <v>32.95216369628906</v>
+        <v>32.95216751098633</v>
       </c>
       <c r="C48" t="n">
-        <v>33.45202278739948</v>
+        <v>33.45202665996278</v>
       </c>
       <c r="D48" t="n">
-        <v>32.53882112897777</v>
+        <v>32.53882489582456</v>
       </c>
       <c r="E48" t="n">
-        <v>33.19248071115274</v>
+        <v>33.19248455367023</v>
       </c>
       <c r="F48" t="n">
         <v>220341</v>
@@ -1472,16 +1472,16 @@
         <v>44228</v>
       </c>
       <c r="B53" t="n">
-        <v>31.7794246673584</v>
+        <v>31.77942657470703</v>
       </c>
       <c r="C53" t="n">
-        <v>33.1155814640686</v>
+        <v>33.11558345161116</v>
       </c>
       <c r="D53" t="n">
-        <v>31.66407054800669</v>
+        <v>31.66407244843196</v>
       </c>
       <c r="E53" t="n">
-        <v>32.68301382233215</v>
+        <v>32.68301578391271</v>
       </c>
       <c r="F53" t="n">
         <v>610435</v>
@@ -1492,16 +1492,16 @@
         <v>44229</v>
       </c>
       <c r="B54" t="n">
-        <v>32.63494873046875</v>
+        <v>32.63495254516602</v>
       </c>
       <c r="C54" t="n">
-        <v>33.65389204571495</v>
+        <v>33.65389597951643</v>
       </c>
       <c r="D54" t="n">
-        <v>31.97167657096734</v>
+        <v>31.97168030813476</v>
       </c>
       <c r="E54" t="n">
-        <v>33.64427951434755</v>
+        <v>33.64428344702543</v>
       </c>
       <c r="F54" t="n">
         <v>582228</v>
@@ -1532,16 +1532,16 @@
         <v>44231</v>
       </c>
       <c r="B56" t="n">
-        <v>32.68301391601562</v>
+        <v>32.68301773071289</v>
       </c>
       <c r="C56" t="n">
-        <v>34.11529602664492</v>
+        <v>34.11530000851534</v>
       </c>
       <c r="D56" t="n">
-        <v>32.44269689321744</v>
+        <v>32.44270067986538</v>
       </c>
       <c r="E56" t="n">
-        <v>33.06751890394745</v>
+        <v>33.06752276352339</v>
       </c>
       <c r="F56" t="n">
         <v>466743</v>
@@ -1612,16 +1612,16 @@
         <v>44237</v>
       </c>
       <c r="B60" t="n">
-        <v>34.83624649047852</v>
+        <v>34.83625030517578</v>
       </c>
       <c r="C60" t="n">
-        <v>35.33610184184258</v>
+        <v>35.33610571127585</v>
       </c>
       <c r="D60" t="n">
-        <v>34.23064955227608</v>
+        <v>34.23065330065825</v>
       </c>
       <c r="E60" t="n">
-        <v>34.43251269995998</v>
+        <v>34.43251647044691</v>
       </c>
       <c r="F60" t="n">
         <v>186206</v>
@@ -1652,16 +1652,16 @@
         <v>44239</v>
       </c>
       <c r="B62" t="n">
-        <v>34.40367889404297</v>
+        <v>34.4036750793457</v>
       </c>
       <c r="C62" t="n">
-        <v>34.52864555631986</v>
+        <v>34.52864172776623</v>
       </c>
       <c r="D62" t="n">
-        <v>32.673400666573</v>
+        <v>32.67339704372985</v>
       </c>
       <c r="E62" t="n">
-        <v>33.67311897448496</v>
+        <v>33.67311524079254</v>
       </c>
       <c r="F62" t="n">
         <v>218195</v>
@@ -1692,16 +1692,16 @@
         <v>44245</v>
       </c>
       <c r="B64" t="n">
-        <v>37.00870895385742</v>
+        <v>37.00870513916016</v>
       </c>
       <c r="C64" t="n">
-        <v>37.38360144742785</v>
+        <v>37.38359759408829</v>
       </c>
       <c r="D64" t="n">
-        <v>35.71100215049589</v>
+        <v>35.71099846956061</v>
       </c>
       <c r="E64" t="n">
-        <v>36.37427435009953</v>
+        <v>36.37427060079703</v>
       </c>
       <c r="F64" t="n">
         <v>661534</v>
@@ -1812,16 +1812,16 @@
         <v>44253</v>
       </c>
       <c r="B70" t="n">
-        <v>34.57670593261719</v>
+        <v>34.57670974731445</v>
       </c>
       <c r="C70" t="n">
-        <v>37.21057322750037</v>
+        <v>37.21057733278074</v>
       </c>
       <c r="D70" t="n">
-        <v>33.75001700107128</v>
+        <v>33.75002072456356</v>
       </c>
       <c r="E70" t="n">
-        <v>36.5376847961999</v>
+        <v>36.53768882724342</v>
       </c>
       <c r="F70" t="n">
         <v>410022</v>
@@ -1932,16 +1932,16 @@
         <v>44263</v>
       </c>
       <c r="B76" t="n">
-        <v>41.91115951538086</v>
+        <v>41.91115570068359</v>
       </c>
       <c r="C76" t="n">
-        <v>44.60270214463106</v>
+        <v>44.60269808495321</v>
       </c>
       <c r="D76" t="n">
-        <v>40.70957805138659</v>
+        <v>40.70957434605565</v>
       </c>
       <c r="E76" t="n">
-        <v>43.55492493684502</v>
+        <v>43.55492097253444</v>
       </c>
       <c r="F76" t="n">
         <v>1012691</v>
@@ -1952,16 +1952,16 @@
         <v>44264</v>
       </c>
       <c r="B77" t="n">
-        <v>43.50686264038086</v>
+        <v>43.50685882568359</v>
       </c>
       <c r="C77" t="n">
-        <v>43.50686264038086</v>
+        <v>43.50685882568359</v>
       </c>
       <c r="D77" t="n">
-        <v>39.89250193891922</v>
+        <v>39.89249844113039</v>
       </c>
       <c r="E77" t="n">
-        <v>42.29566488693005</v>
+        <v>42.29566117843103</v>
       </c>
       <c r="F77" t="n">
         <v>563525</v>
@@ -1972,16 +1972,16 @@
         <v>44265</v>
       </c>
       <c r="B78" t="n">
-        <v>44.69882583618164</v>
+        <v>44.69882965087891</v>
       </c>
       <c r="C78" t="n">
-        <v>44.89108021255291</v>
+        <v>44.89108404365759</v>
       </c>
       <c r="D78" t="n">
-        <v>43.38189403862891</v>
+        <v>43.38189774093629</v>
       </c>
       <c r="E78" t="n">
-        <v>43.83369051144994</v>
+        <v>43.83369425231464</v>
       </c>
       <c r="F78" t="n">
         <v>425454</v>
@@ -2012,16 +2012,16 @@
         <v>44267</v>
       </c>
       <c r="B80" t="n">
-        <v>45.66009521484375</v>
+        <v>45.66009140014648</v>
       </c>
       <c r="C80" t="n">
-        <v>49.01491000208902</v>
+        <v>49.01490590711195</v>
       </c>
       <c r="D80" t="n">
-        <v>45.18907366630634</v>
+        <v>45.18906989096082</v>
       </c>
       <c r="E80" t="n">
-        <v>47.15005636649431</v>
+        <v>47.15005242731743</v>
       </c>
       <c r="F80" t="n">
         <v>954539</v>
@@ -2052,16 +2052,16 @@
         <v>44271</v>
       </c>
       <c r="B82" t="n">
-        <v>42.75707244873047</v>
+        <v>42.7570686340332</v>
       </c>
       <c r="C82" t="n">
-        <v>45.18907290913018</v>
+        <v>45.18906887745489</v>
       </c>
       <c r="D82" t="n">
-        <v>42.75707244873047</v>
+        <v>42.7570686340332</v>
       </c>
       <c r="E82" t="n">
-        <v>44.50657567458991</v>
+        <v>44.5065717038056</v>
       </c>
       <c r="F82" t="n">
         <v>561175</v>
@@ -2092,16 +2092,16 @@
         <v>44273</v>
       </c>
       <c r="B84" t="n">
-        <v>40.89221954345703</v>
+        <v>40.89221572875977</v>
       </c>
       <c r="C84" t="n">
-        <v>45.0256568951004</v>
+        <v>45.02565269480871</v>
       </c>
       <c r="D84" t="n">
-        <v>40.57500224961562</v>
+        <v>40.57499846451049</v>
       </c>
       <c r="E84" t="n">
-        <v>44.01632982334604</v>
+        <v>44.01632571721106</v>
       </c>
       <c r="F84" t="n">
         <v>572621</v>
@@ -2112,16 +2112,16 @@
         <v>44274</v>
       </c>
       <c r="B85" t="n">
-        <v>42.29566192626953</v>
+        <v>42.2956657409668</v>
       </c>
       <c r="C85" t="n">
-        <v>44.17013174266427</v>
+        <v>44.17013572642225</v>
       </c>
       <c r="D85" t="n">
-        <v>41.4593642170013</v>
+        <v>41.45936795627186</v>
       </c>
       <c r="E85" t="n">
-        <v>41.4593642170013</v>
+        <v>41.45936795627186</v>
       </c>
       <c r="F85" t="n">
         <v>639255</v>
@@ -2212,16 +2212,16 @@
         <v>44281</v>
       </c>
       <c r="B90" t="n">
-        <v>37.87384414672852</v>
+        <v>37.87384796142578</v>
       </c>
       <c r="C90" t="n">
-        <v>40.949891527232</v>
+        <v>40.94989565175231</v>
       </c>
       <c r="D90" t="n">
-        <v>37.56623940867817</v>
+        <v>37.56624319239313</v>
       </c>
       <c r="E90" t="n">
-        <v>39.95978959641457</v>
+        <v>39.95979362121066</v>
       </c>
       <c r="F90" t="n">
         <v>840076</v>
@@ -2312,16 +2312,16 @@
         <v>44291</v>
       </c>
       <c r="B95" t="n">
-        <v>35.68215942382812</v>
+        <v>35.68216323852539</v>
       </c>
       <c r="C95" t="n">
-        <v>37.01831616285484</v>
+        <v>37.01832012039754</v>
       </c>
       <c r="D95" t="n">
-        <v>35.09578756412892</v>
+        <v>35.09579131613852</v>
       </c>
       <c r="E95" t="n">
-        <v>37.01831616285484</v>
+        <v>37.01832012039754</v>
       </c>
       <c r="F95" t="n">
         <v>1091895</v>
@@ -2512,16 +2512,16 @@
         <v>44305</v>
       </c>
       <c r="B105" t="n">
-        <v>41.33439636230469</v>
+        <v>41.33440017700195</v>
       </c>
       <c r="C105" t="n">
-        <v>42.23798551125894</v>
+        <v>42.23798940934727</v>
       </c>
       <c r="D105" t="n">
-        <v>40.20971525467667</v>
+        <v>40.2097189655786</v>
       </c>
       <c r="E105" t="n">
-        <v>40.38274455876383</v>
+        <v>40.38274828563441</v>
       </c>
       <c r="F105" t="n">
         <v>1793083</v>
@@ -2552,16 +2552,16 @@
         <v>44308</v>
       </c>
       <c r="B107" t="n">
-        <v>42.3725700378418</v>
+        <v>42.37256622314453</v>
       </c>
       <c r="C107" t="n">
-        <v>42.77630013488342</v>
+        <v>42.77629628383934</v>
       </c>
       <c r="D107" t="n">
-        <v>41.04602186600353</v>
+        <v>41.0460181707321</v>
       </c>
       <c r="E107" t="n">
-        <v>42.58404574470481</v>
+        <v>42.58404191096891</v>
       </c>
       <c r="F107" t="n">
         <v>1175903</v>
@@ -2572,16 +2572,16 @@
         <v>44309</v>
       </c>
       <c r="B108" t="n">
-        <v>44.09323501586914</v>
+        <v>44.09323120117188</v>
       </c>
       <c r="C108" t="n">
-        <v>44.31432325105797</v>
+        <v>44.3143194172334</v>
       </c>
       <c r="D108" t="n">
-        <v>42.38218184069201</v>
+        <v>42.38217817402538</v>
       </c>
       <c r="E108" t="n">
-        <v>42.82436205864548</v>
+        <v>42.82435835372392</v>
       </c>
       <c r="F108" t="n">
         <v>1899574</v>
@@ -2612,16 +2612,16 @@
         <v>44313</v>
       </c>
       <c r="B110" t="n">
-        <v>43.7375602722168</v>
+        <v>43.73756408691406</v>
       </c>
       <c r="C110" t="n">
-        <v>44.31431963823069</v>
+        <v>44.31432350323168</v>
       </c>
       <c r="D110" t="n">
-        <v>43.04545053203033</v>
+        <v>43.04545428636325</v>
       </c>
       <c r="E110" t="n">
-        <v>43.40111793330461</v>
+        <v>43.40112171865809</v>
       </c>
       <c r="F110" t="n">
         <v>1146163</v>
@@ -2732,16 +2732,16 @@
         <v>44321</v>
       </c>
       <c r="B116" t="n">
-        <v>39.74831390380859</v>
+        <v>39.74831008911133</v>
       </c>
       <c r="C116" t="n">
-        <v>40.64229060912697</v>
+        <v>40.6422867086336</v>
       </c>
       <c r="D116" t="n">
-        <v>39.0754291787498</v>
+        <v>39.07542542863015</v>
       </c>
       <c r="E116" t="n">
-        <v>39.89250188164586</v>
+        <v>39.89249805311069</v>
       </c>
       <c r="F116" t="n">
         <v>3650961</v>
@@ -2772,16 +2772,16 @@
         <v>44323</v>
       </c>
       <c r="B118" t="n">
-        <v>38.83510971069336</v>
+        <v>38.83511352539062</v>
       </c>
       <c r="C118" t="n">
-        <v>39.99824098294782</v>
+        <v>39.99824491189721</v>
       </c>
       <c r="D118" t="n">
-        <v>37.51817793834604</v>
+        <v>37.51818162368365</v>
       </c>
       <c r="E118" t="n">
-        <v>39.66179864141913</v>
+        <v>39.66180253732045</v>
       </c>
       <c r="F118" t="n">
         <v>2227429</v>
@@ -2832,16 +2832,16 @@
         <v>44328</v>
       </c>
       <c r="B121" t="n">
-        <v>37.05677032470703</v>
+        <v>37.05676651000977</v>
       </c>
       <c r="C121" t="n">
-        <v>38.70053196862062</v>
+        <v>38.70052798471127</v>
       </c>
       <c r="D121" t="n">
-        <v>37.05677032470703</v>
+        <v>37.05676651000977</v>
       </c>
       <c r="E121" t="n">
-        <v>37.8161715649591</v>
+        <v>37.81616767208757</v>
       </c>
       <c r="F121" t="n">
         <v>783049</v>
@@ -2892,16 +2892,16 @@
         <v>44333</v>
       </c>
       <c r="B124" t="n">
-        <v>36.43194580078125</v>
+        <v>36.43194961547852</v>
       </c>
       <c r="C124" t="n">
-        <v>37.13366805612294</v>
+        <v>37.13367194429578</v>
       </c>
       <c r="D124" t="n">
-        <v>35.93208669563144</v>
+        <v>35.93209045798972</v>
       </c>
       <c r="E124" t="n">
-        <v>36.52807111039643</v>
+        <v>36.52807493515874</v>
       </c>
       <c r="F124" t="n">
         <v>946466</v>
@@ -2912,16 +2912,16 @@
         <v>44334</v>
       </c>
       <c r="B125" t="n">
-        <v>35.14385604858398</v>
+        <v>35.14385223388672</v>
       </c>
       <c r="C125" t="n">
-        <v>36.91258445174329</v>
+        <v>36.91258044505902</v>
       </c>
       <c r="D125" t="n">
-        <v>34.59593422023043</v>
+        <v>34.59593046500746</v>
       </c>
       <c r="E125" t="n">
-        <v>36.52807567013412</v>
+        <v>36.52807170518645</v>
       </c>
       <c r="F125" t="n">
         <v>2070451</v>
@@ -2952,16 +2952,16 @@
         <v>44336</v>
       </c>
       <c r="B127" t="n">
-        <v>34.63438415527344</v>
+        <v>34.63438034057617</v>
       </c>
       <c r="C127" t="n">
-        <v>35.26881876953347</v>
+        <v>35.26881488495837</v>
       </c>
       <c r="D127" t="n">
-        <v>34.51903376998102</v>
+        <v>34.51902996798866</v>
       </c>
       <c r="E127" t="n">
-        <v>34.51903376998102</v>
+        <v>34.51902996798866</v>
       </c>
       <c r="F127" t="n">
         <v>943604</v>
@@ -3012,16 +3012,16 @@
         <v>44341</v>
       </c>
       <c r="B130" t="n">
-        <v>37.29708862304688</v>
+        <v>37.29708480834961</v>
       </c>
       <c r="C130" t="n">
-        <v>38.78704981148397</v>
+        <v>38.78704584439543</v>
       </c>
       <c r="D130" t="n">
-        <v>37.22980089947328</v>
+        <v>37.22979709165812</v>
       </c>
       <c r="E130" t="n">
-        <v>37.52779313716071</v>
+        <v>37.52778929886728</v>
       </c>
       <c r="F130" t="n">
         <v>1731150</v>
@@ -3092,16 +3092,16 @@
         <v>44347</v>
       </c>
       <c r="B134" t="n">
-        <v>39.38303375244141</v>
+        <v>39.38302993774414</v>
       </c>
       <c r="C134" t="n">
-        <v>40.11359366504992</v>
+        <v>40.11358977958957</v>
       </c>
       <c r="D134" t="n">
-        <v>39.02736632794579</v>
+        <v>39.02736254769899</v>
       </c>
       <c r="E134" t="n">
-        <v>39.39264628425005</v>
+        <v>39.3926424686217</v>
       </c>
       <c r="F134" t="n">
         <v>715598</v>
@@ -3192,16 +3192,16 @@
         <v>44355</v>
       </c>
       <c r="B139" t="n">
-        <v>38.4602165222168</v>
+        <v>38.46022033691406</v>
       </c>
       <c r="C139" t="n">
-        <v>38.85433404388245</v>
+        <v>38.85433789767048</v>
       </c>
       <c r="D139" t="n">
-        <v>37.72004038668688</v>
+        <v>37.72004412796937</v>
       </c>
       <c r="E139" t="n">
-        <v>38.43137892899068</v>
+        <v>38.43138274082768</v>
       </c>
       <c r="F139" t="n">
         <v>978352</v>
@@ -3212,16 +3212,16 @@
         <v>44356</v>
       </c>
       <c r="B140" t="n">
-        <v>38.01803588867188</v>
+        <v>38.01803207397461</v>
       </c>
       <c r="C140" t="n">
-        <v>38.66208302162527</v>
+        <v>38.66207914230487</v>
       </c>
       <c r="D140" t="n">
-        <v>37.29708850045856</v>
+        <v>37.29708475810054</v>
       </c>
       <c r="E140" t="n">
-        <v>38.48905744729046</v>
+        <v>38.48905358533129</v>
       </c>
       <c r="F140" t="n">
         <v>837521</v>
@@ -3332,16 +3332,16 @@
         <v>44364</v>
       </c>
       <c r="B146" t="n">
-        <v>42.4879150390625</v>
+        <v>42.48791885375977</v>
       </c>
       <c r="C146" t="n">
-        <v>44.0067136610316</v>
+        <v>44.00671761209134</v>
       </c>
       <c r="D146" t="n">
-        <v>41.62277601425852</v>
+        <v>41.62277975128091</v>
       </c>
       <c r="E146" t="n">
-        <v>42.95893654890009</v>
+        <v>42.95894040588714</v>
       </c>
       <c r="F146" t="n">
         <v>1582144</v>
@@ -3372,16 +3372,16 @@
         <v>44368</v>
       </c>
       <c r="B148" t="n">
-        <v>46.96741485595703</v>
+        <v>46.96741104125977</v>
       </c>
       <c r="C148" t="n">
-        <v>47.24618202489792</v>
+        <v>47.24617818755916</v>
       </c>
       <c r="D148" t="n">
-        <v>43.53569979030122</v>
+        <v>43.53569625432814</v>
       </c>
       <c r="E148" t="n">
-        <v>43.73756295749668</v>
+        <v>43.73755940512824</v>
       </c>
       <c r="F148" t="n">
         <v>2655439</v>
@@ -3452,16 +3452,16 @@
         <v>44372</v>
       </c>
       <c r="B152" t="n">
-        <v>44.45851135253906</v>
+        <v>44.45851516723633</v>
       </c>
       <c r="C152" t="n">
-        <v>44.98720431506052</v>
+        <v>44.9872081751215</v>
       </c>
       <c r="D152" t="n">
-        <v>43.97787729834627</v>
+        <v>43.97788107180344</v>
       </c>
       <c r="E152" t="n">
-        <v>44.98720431506052</v>
+        <v>44.9872081751215</v>
       </c>
       <c r="F152" t="n">
         <v>1347904</v>
@@ -3472,16 +3472,16 @@
         <v>44375</v>
       </c>
       <c r="B153" t="n">
-        <v>44.5354118347168</v>
+        <v>44.53541564941406</v>
       </c>
       <c r="C153" t="n">
-        <v>44.64114967825854</v>
+        <v>44.64115350201283</v>
       </c>
       <c r="D153" t="n">
-        <v>43.20886378695175</v>
+        <v>43.20886748802305</v>
       </c>
       <c r="E153" t="n">
-        <v>44.13168177543641</v>
+        <v>44.13168555555202</v>
       </c>
       <c r="F153" t="n">
         <v>1110393</v>
@@ -3512,16 +3512,16 @@
         <v>44377</v>
       </c>
       <c r="B155" t="n">
-        <v>43.58376312255859</v>
+        <v>43.58375930786133</v>
       </c>
       <c r="C155" t="n">
-        <v>44.45851476998166</v>
+        <v>44.45851087872119</v>
       </c>
       <c r="D155" t="n">
-        <v>43.50686286720073</v>
+        <v>43.50685905923421</v>
       </c>
       <c r="E155" t="n">
-        <v>44.21819772441255</v>
+        <v>44.21819385418598</v>
       </c>
       <c r="F155" t="n">
         <v>1274116</v>
@@ -3572,16 +3572,16 @@
         <v>44382</v>
       </c>
       <c r="B158" t="n">
-        <v>45.04488372802734</v>
+        <v>45.04488754272461</v>
       </c>
       <c r="C158" t="n">
-        <v>46.21762753484401</v>
+        <v>46.21763144885693</v>
       </c>
       <c r="D158" t="n">
-        <v>44.42967048319475</v>
+        <v>44.42967424579171</v>
       </c>
       <c r="E158" t="n">
-        <v>44.98720479275436</v>
+        <v>44.98720860256699</v>
       </c>
       <c r="F158" t="n">
         <v>3391068</v>
@@ -3592,16 +3592,16 @@
         <v>44383</v>
       </c>
       <c r="B159" t="n">
-        <v>44.37199401855469</v>
+        <v>44.37199783325195</v>
       </c>
       <c r="C159" t="n">
-        <v>45.94847158903642</v>
+        <v>45.94847553926477</v>
       </c>
       <c r="D159" t="n">
-        <v>43.75678453900221</v>
+        <v>43.75678830080941</v>
       </c>
       <c r="E159" t="n">
-        <v>45.7850548143543</v>
+        <v>45.78505875053358</v>
       </c>
       <c r="F159" t="n">
         <v>1563442</v>
@@ -3652,16 +3652,16 @@
         <v>44389</v>
       </c>
       <c r="B162" t="n">
-        <v>44.72766876220703</v>
+        <v>44.72766494750977</v>
       </c>
       <c r="C162" t="n">
-        <v>45.75622090541913</v>
+        <v>45.75621700299953</v>
       </c>
       <c r="D162" t="n">
-        <v>44.08361789020423</v>
+        <v>44.08361413043626</v>
       </c>
       <c r="E162" t="n">
-        <v>45.75622090541913</v>
+        <v>45.75621700299953</v>
       </c>
       <c r="F162" t="n">
         <v>1597780</v>
@@ -3732,16 +3732,16 @@
         <v>44393</v>
       </c>
       <c r="B166" t="n">
-        <v>41.70928955078125</v>
+        <v>41.70929336547852</v>
       </c>
       <c r="C166" t="n">
-        <v>41.91115645117827</v>
+        <v>41.91116028433812</v>
       </c>
       <c r="D166" t="n">
-        <v>40.45003298811638</v>
+        <v>40.45003668764308</v>
       </c>
       <c r="E166" t="n">
-        <v>41.62277677100059</v>
+        <v>41.62278057778546</v>
       </c>
       <c r="F166" t="n">
         <v>1471156</v>
@@ -3752,16 +3752,16 @@
         <v>44396</v>
       </c>
       <c r="B167" t="n">
-        <v>40.22894287109375</v>
+        <v>40.22894668579102</v>
       </c>
       <c r="C167" t="n">
-        <v>41.05562800061862</v>
+        <v>41.05563189370605</v>
       </c>
       <c r="D167" t="n">
-        <v>39.50799183094843</v>
+        <v>39.50799557728174</v>
       </c>
       <c r="E167" t="n">
-        <v>40.46925613690023</v>
+        <v>40.46925997438512</v>
       </c>
       <c r="F167" t="n">
         <v>1632835</v>
@@ -3792,16 +3792,16 @@
         <v>44398</v>
       </c>
       <c r="B169" t="n">
-        <v>40.45964431762695</v>
+        <v>40.45964813232422</v>
       </c>
       <c r="C169" t="n">
-        <v>41.40168732645247</v>
+        <v>41.40169122996932</v>
       </c>
       <c r="D169" t="n">
-        <v>40.22894357839657</v>
+        <v>40.22894737134245</v>
       </c>
       <c r="E169" t="n">
-        <v>40.37313154041556</v>
+        <v>40.37313534695605</v>
       </c>
       <c r="F169" t="n">
         <v>985812</v>
@@ -3812,16 +3812,16 @@
         <v>44399</v>
       </c>
       <c r="B170" t="n">
-        <v>40.89221954345703</v>
+        <v>40.89221572875977</v>
       </c>
       <c r="C170" t="n">
-        <v>41.15176164706832</v>
+        <v>41.15175780815924</v>
       </c>
       <c r="D170" t="n">
-        <v>40.3923603996445</v>
+        <v>40.39235663157741</v>
       </c>
       <c r="E170" t="n">
-        <v>41.08447017755746</v>
+        <v>41.08446634492577</v>
       </c>
       <c r="F170" t="n">
         <v>757704</v>
@@ -3832,16 +3832,16 @@
         <v>44400</v>
       </c>
       <c r="B171" t="n">
-        <v>40.56538772583008</v>
+        <v>40.56539154052734</v>
       </c>
       <c r="C171" t="n">
-        <v>40.86337994162768</v>
+        <v>40.8633837843476</v>
       </c>
       <c r="D171" t="n">
-        <v>40.20010404382616</v>
+        <v>40.20010782417279</v>
       </c>
       <c r="E171" t="n">
-        <v>40.6230629132279</v>
+        <v>40.62306673334884</v>
       </c>
       <c r="F171" t="n">
         <v>715496</v>
@@ -3872,16 +3872,16 @@
         <v>44404</v>
       </c>
       <c r="B173" t="n">
-        <v>38.54673004150391</v>
+        <v>38.54673385620117</v>
       </c>
       <c r="C173" t="n">
-        <v>40.84415499320262</v>
+        <v>40.84415903525979</v>
       </c>
       <c r="D173" t="n">
-        <v>38.32563807495276</v>
+        <v>38.32564186777011</v>
       </c>
       <c r="E173" t="n">
-        <v>40.62306302665147</v>
+        <v>40.62306704682872</v>
       </c>
       <c r="F173" t="n">
         <v>1543819</v>
@@ -3932,16 +3932,16 @@
         <v>44407</v>
       </c>
       <c r="B176" t="n">
-        <v>37.2105712890625</v>
+        <v>37.21057510375977</v>
       </c>
       <c r="C176" t="n">
-        <v>38.26796091589321</v>
+        <v>38.26796483899034</v>
       </c>
       <c r="D176" t="n">
-        <v>36.33581974675896</v>
+        <v>36.33582347177977</v>
       </c>
       <c r="E176" t="n">
-        <v>37.5662386749276</v>
+        <v>37.56624252608663</v>
       </c>
       <c r="F176" t="n">
         <v>1168442</v>
@@ -3952,16 +3952,16 @@
         <v>44410</v>
       </c>
       <c r="B177" t="n">
-        <v>39.04658889770508</v>
+        <v>39.04659271240234</v>
       </c>
       <c r="C177" t="n">
-        <v>40.3442955992922</v>
+        <v>40.34429954077027</v>
       </c>
       <c r="D177" t="n">
-        <v>38.19106237864987</v>
+        <v>38.19106610976557</v>
       </c>
       <c r="E177" t="n">
-        <v>39.17155180323623</v>
+        <v>39.17155563014188</v>
       </c>
       <c r="F177" t="n">
         <v>3352028</v>
@@ -4052,16 +4052,16 @@
         <v>44417</v>
       </c>
       <c r="B182" t="n">
-        <v>37.10483169555664</v>
+        <v>37.10483551025391</v>
       </c>
       <c r="C182" t="n">
-        <v>37.44127403795907</v>
+        <v>37.44127788724551</v>
       </c>
       <c r="D182" t="n">
-        <v>35.94170042028153</v>
+        <v>35.94170411539885</v>
       </c>
       <c r="E182" t="n">
-        <v>36.1147297309109</v>
+        <v>36.11473344381713</v>
       </c>
       <c r="F182" t="n">
         <v>1206460</v>
@@ -4092,16 +4092,16 @@
         <v>44419</v>
       </c>
       <c r="B184" t="n">
-        <v>36.43194580078125</v>
+        <v>36.43194961547852</v>
       </c>
       <c r="C184" t="n">
-        <v>36.74916307008678</v>
+        <v>36.74916691799907</v>
       </c>
       <c r="D184" t="n">
-        <v>36.09550346955268</v>
+        <v>36.09550724902192</v>
       </c>
       <c r="E184" t="n">
-        <v>36.47039592462733</v>
+        <v>36.4703997433506</v>
       </c>
       <c r="F184" t="n">
         <v>786524</v>
@@ -4112,16 +4112,16 @@
         <v>44420</v>
       </c>
       <c r="B185" t="n">
-        <v>36.12434387207031</v>
+        <v>36.12434005737305</v>
       </c>
       <c r="C185" t="n">
-        <v>36.95103284178433</v>
+        <v>36.95102893978947</v>
       </c>
       <c r="D185" t="n">
-        <v>35.4706842206967</v>
+        <v>35.47068047502529</v>
       </c>
       <c r="E185" t="n">
-        <v>36.19163159403436</v>
+        <v>36.19162777223157</v>
       </c>
       <c r="F185" t="n">
         <v>689639</v>
@@ -4132,16 +4132,16 @@
         <v>44421</v>
       </c>
       <c r="B186" t="n">
-        <v>34.75934219360352</v>
+        <v>34.75934600830078</v>
       </c>
       <c r="C186" t="n">
-        <v>35.97053605946554</v>
+        <v>35.97054000708643</v>
       </c>
       <c r="D186" t="n">
-        <v>34.59592917071041</v>
+        <v>34.59593296747376</v>
       </c>
       <c r="E186" t="n">
-        <v>35.69177266747142</v>
+        <v>35.69177658449917</v>
       </c>
       <c r="F186" t="n">
         <v>915908</v>
@@ -4252,16 +4252,16 @@
         <v>44431</v>
       </c>
       <c r="B192" t="n">
-        <v>33.16364288330078</v>
+        <v>33.16364669799805</v>
       </c>
       <c r="C192" t="n">
-        <v>34.42289938524034</v>
+        <v>34.42290334478545</v>
       </c>
       <c r="D192" t="n">
-        <v>32.77913791079774</v>
+        <v>32.77914168126674</v>
       </c>
       <c r="E192" t="n">
-        <v>33.740402215843</v>
+        <v>33.74040609688286</v>
       </c>
       <c r="F192" t="n">
         <v>2084044</v>
@@ -4272,16 +4272,16 @@
         <v>44432</v>
       </c>
       <c r="B193" t="n">
-        <v>35.43223571777344</v>
+        <v>35.43223190307617</v>
       </c>
       <c r="C193" t="n">
-        <v>35.43223571777344</v>
+        <v>35.43223190307617</v>
       </c>
       <c r="D193" t="n">
-        <v>33.47125292620207</v>
+        <v>33.47124932262768</v>
       </c>
       <c r="E193" t="n">
-        <v>33.93266196453976</v>
+        <v>33.93265831128927</v>
       </c>
       <c r="F193" t="n">
         <v>1429663</v>
@@ -4332,16 +4332,16 @@
         <v>44435</v>
       </c>
       <c r="B196" t="n">
-        <v>36.43194580078125</v>
+        <v>36.43194961547852</v>
       </c>
       <c r="C196" t="n">
-        <v>36.66265029143312</v>
+        <v>36.66265413028687</v>
       </c>
       <c r="D196" t="n">
-        <v>35.02849754252244</v>
+        <v>35.02850121026817</v>
       </c>
       <c r="E196" t="n">
-        <v>35.75906113832411</v>
+        <v>35.75906488256532</v>
       </c>
       <c r="F196" t="n">
         <v>2701327</v>
@@ -4392,16 +4392,16 @@
         <v>44440</v>
       </c>
       <c r="B199" t="n">
-        <v>36.00899124145508</v>
+        <v>36.00899505615234</v>
       </c>
       <c r="C199" t="n">
-        <v>37.22979768253502</v>
+        <v>37.2298016265613</v>
       </c>
       <c r="D199" t="n">
-        <v>35.47068200422877</v>
+        <v>35.47068576189898</v>
       </c>
       <c r="E199" t="n">
-        <v>37.10483103054919</v>
+        <v>37.10483496133683</v>
       </c>
       <c r="F199" t="n">
         <v>1150659</v>
@@ -4712,16 +4712,16 @@
         <v>44463</v>
       </c>
       <c r="B215" t="n">
-        <v>34.54786682128906</v>
+        <v>34.54787063598633</v>
       </c>
       <c r="C215" t="n">
-        <v>35.65331911097231</v>
+        <v>35.65332304773112</v>
       </c>
       <c r="D215" t="n">
-        <v>33.88459095038866</v>
+        <v>33.88459469184851</v>
       </c>
       <c r="E215" t="n">
-        <v>34.46135404370111</v>
+        <v>34.46135784884584</v>
       </c>
       <c r="F215" t="n">
         <v>2639905</v>
@@ -4852,16 +4852,16 @@
         <v>44474</v>
       </c>
       <c r="B222" t="n">
-        <v>41.23827362060547</v>
+        <v>41.2382698059082</v>
       </c>
       <c r="C222" t="n">
-        <v>43.07428962557536</v>
+        <v>43.07428564103963</v>
       </c>
       <c r="D222" t="n">
-        <v>40.9498939275561</v>
+        <v>40.94989013953506</v>
       </c>
       <c r="E222" t="n">
-        <v>41.82464553821999</v>
+        <v>41.82464166928109</v>
       </c>
       <c r="F222" t="n">
         <v>3033780</v>
@@ -4952,16 +4952,16 @@
         <v>44482</v>
       </c>
       <c r="B227" t="n">
-        <v>39.66179656982422</v>
+        <v>39.66180038452148</v>
       </c>
       <c r="C227" t="n">
-        <v>40.05591407830239</v>
+        <v>40.05591793090613</v>
       </c>
       <c r="D227" t="n">
-        <v>38.88317033604628</v>
+        <v>38.88317407585477</v>
       </c>
       <c r="E227" t="n">
-        <v>39.43109208415942</v>
+        <v>39.43109587666738</v>
       </c>
       <c r="F227" t="n">
         <v>1130628</v>
@@ -5012,16 +5012,16 @@
         <v>44487</v>
       </c>
       <c r="B230" t="n">
-        <v>39.87327194213867</v>
+        <v>39.87327575683594</v>
       </c>
       <c r="C230" t="n">
-        <v>41.44974945917212</v>
+        <v>41.44975342469183</v>
       </c>
       <c r="D230" t="n">
-        <v>39.18116223800101</v>
+        <v>39.18116598648377</v>
       </c>
       <c r="E230" t="n">
-        <v>39.72908398193304</v>
+        <v>39.72908778283576</v>
       </c>
       <c r="F230" t="n">
         <v>2573169</v>
@@ -5032,16 +5032,16 @@
         <v>44488</v>
       </c>
       <c r="B231" t="n">
-        <v>37.58546447753906</v>
+        <v>37.58546829223633</v>
       </c>
       <c r="C231" t="n">
-        <v>40.08475250621378</v>
+        <v>40.08475657457366</v>
       </c>
       <c r="D231" t="n">
-        <v>36.86451716082918</v>
+        <v>36.86452090235465</v>
       </c>
       <c r="E231" t="n">
-        <v>39.57528087049455</v>
+        <v>39.57528488714614</v>
       </c>
       <c r="F231" t="n">
         <v>2915331</v>
@@ -5072,16 +5072,16 @@
         <v>44490</v>
       </c>
       <c r="B233" t="n">
-        <v>34.41328811645508</v>
+        <v>34.41329193115234</v>
       </c>
       <c r="C233" t="n">
-        <v>36.09550352264783</v>
+        <v>36.09550752381791</v>
       </c>
       <c r="D233" t="n">
-        <v>33.48086136908995</v>
+        <v>33.48086508042814</v>
       </c>
       <c r="E233" t="n">
-        <v>35.62448200968972</v>
+        <v>35.62448595864728</v>
       </c>
       <c r="F233" t="n">
         <v>3113087</v>
@@ -5092,16 +5092,16 @@
         <v>44491</v>
       </c>
       <c r="B234" t="n">
-        <v>32.63494873046875</v>
+        <v>32.63495254516602</v>
       </c>
       <c r="C234" t="n">
-        <v>34.06723464208851</v>
+        <v>34.06723862420559</v>
       </c>
       <c r="D234" t="n">
-        <v>31.04886231697067</v>
+        <v>31.04886594627039</v>
       </c>
       <c r="E234" t="n">
-        <v>33.63466698298016</v>
+        <v>33.63467091453443</v>
       </c>
       <c r="F234" t="n">
         <v>4894520</v>
@@ -5112,16 +5112,16 @@
         <v>44494</v>
       </c>
       <c r="B235" t="n">
-        <v>36.8470573425293</v>
+        <v>36.84706115722656</v>
       </c>
       <c r="C235" t="n">
-        <v>37.3112732591762</v>
+        <v>37.31127712193275</v>
       </c>
       <c r="D235" t="n">
-        <v>32.95925887799699</v>
+        <v>32.95926229019877</v>
       </c>
       <c r="E235" t="n">
-        <v>32.95925887799699</v>
+        <v>32.95926229019877</v>
       </c>
       <c r="F235" t="n">
         <v>3449995</v>
@@ -5152,16 +5152,16 @@
         <v>44496</v>
       </c>
       <c r="B237" t="n">
-        <v>35.29000854492188</v>
+        <v>35.29000473022461</v>
       </c>
       <c r="C237" t="n">
-        <v>36.07337184605893</v>
+        <v>36.07336794668348</v>
       </c>
       <c r="D237" t="n">
-        <v>34.47763151058894</v>
+        <v>34.47762778370612</v>
       </c>
       <c r="E237" t="n">
-        <v>36.07337184605893</v>
+        <v>36.07336794668348</v>
       </c>
       <c r="F237" t="n">
         <v>2270538</v>
@@ -5272,16 +5272,16 @@
         <v>44505</v>
       </c>
       <c r="B243" t="n">
-        <v>34.33255767822266</v>
+        <v>34.33256149291992</v>
       </c>
       <c r="C243" t="n">
-        <v>35.80257411368536</v>
+        <v>35.80257809171644</v>
       </c>
       <c r="D243" t="n">
-        <v>31.73102080869616</v>
+        <v>31.73102433433615</v>
       </c>
       <c r="E243" t="n">
-        <v>33.17202351532898</v>
+        <v>33.17202720107906</v>
       </c>
       <c r="F243" t="n">
         <v>9166770</v>
@@ -5312,16 +5312,16 @@
         <v>44509</v>
       </c>
       <c r="B245" t="n">
-        <v>34.50664138793945</v>
+        <v>34.50664520263672</v>
       </c>
       <c r="C245" t="n">
-        <v>35.1062534768846</v>
+        <v>35.10625735786877</v>
       </c>
       <c r="D245" t="n">
-        <v>32.63044017132788</v>
+        <v>32.63044377861175</v>
       </c>
       <c r="E245" t="n">
-        <v>33.89736055406007</v>
+        <v>33.89736430140155</v>
       </c>
       <c r="F245" t="n">
         <v>7032350</v>
@@ -5372,16 +5372,16 @@
         <v>44512</v>
       </c>
       <c r="B248" t="n">
-        <v>30.94766044616699</v>
+        <v>30.94766235351562</v>
       </c>
       <c r="C248" t="n">
-        <v>33.11399707089411</v>
+        <v>33.11399911175717</v>
       </c>
       <c r="D248" t="n">
-        <v>30.69620937113922</v>
+        <v>30.69621126299056</v>
       </c>
       <c r="E248" t="n">
-        <v>32.10819651835855</v>
+        <v>32.10819849723269</v>
       </c>
       <c r="F248" t="n">
         <v>3403064</v>
@@ -5552,16 +5552,16 @@
         <v>44526</v>
       </c>
       <c r="B257" t="n">
-        <v>26.69235801696777</v>
+        <v>26.69235992431641</v>
       </c>
       <c r="C257" t="n">
-        <v>27.61111551515892</v>
+        <v>27.61111748815896</v>
       </c>
       <c r="D257" t="n">
-        <v>25.85096734243463</v>
+        <v>25.85096918966023</v>
       </c>
       <c r="E257" t="n">
-        <v>26.59564620826666</v>
+        <v>26.59564810870458</v>
       </c>
       <c r="F257" t="n">
         <v>3664026</v>
@@ -5592,16 +5592,16 @@
         <v>44530</v>
       </c>
       <c r="B259" t="n">
-        <v>26.71169853210449</v>
+        <v>26.71170043945312</v>
       </c>
       <c r="C259" t="n">
-        <v>26.71169853210449</v>
+        <v>26.71170043945312</v>
       </c>
       <c r="D259" t="n">
-        <v>25.48346440355603</v>
+        <v>25.48346622320262</v>
       </c>
       <c r="E259" t="n">
-        <v>26.53761803066504</v>
+        <v>26.53761992558345</v>
       </c>
       <c r="F259" t="n">
         <v>4757647</v>
@@ -5612,16 +5612,16 @@
         <v>44531</v>
       </c>
       <c r="B260" t="n">
-        <v>26.69235801696777</v>
+        <v>26.69235992431641</v>
       </c>
       <c r="C260" t="n">
-        <v>28.01730398743094</v>
+        <v>28.01730598945588</v>
       </c>
       <c r="D260" t="n">
-        <v>26.32485389341864</v>
+        <v>26.32485577450663</v>
       </c>
       <c r="E260" t="n">
-        <v>27.17591518668557</v>
+        <v>27.17591712858762</v>
       </c>
       <c r="F260" t="n">
         <v>3467467</v>
@@ -5752,16 +5752,16 @@
         <v>44540</v>
       </c>
       <c r="B267" t="n">
-        <v>29.43896293640137</v>
+        <v>29.43896102905273</v>
       </c>
       <c r="C267" t="n">
-        <v>29.76778272429381</v>
+        <v>29.76778079564096</v>
       </c>
       <c r="D267" t="n">
-        <v>28.76198212238038</v>
+        <v>28.76198025889329</v>
       </c>
       <c r="E267" t="n">
-        <v>29.57435909920557</v>
+        <v>29.57435718308462</v>
       </c>
       <c r="F267" t="n">
         <v>1281952</v>
@@ -5832,16 +5832,16 @@
         <v>44546</v>
       </c>
       <c r="B271" t="n">
-        <v>30.62851333618164</v>
+        <v>30.62851524353027</v>
       </c>
       <c r="C271" t="n">
-        <v>30.86062130141829</v>
+        <v>30.86062322322113</v>
       </c>
       <c r="D271" t="n">
-        <v>29.25521052973079</v>
+        <v>29.25521235155887</v>
       </c>
       <c r="E271" t="n">
-        <v>29.4969891136642</v>
+        <v>29.49699095054871</v>
       </c>
       <c r="F271" t="n">
         <v>3477726</v>
@@ -5952,16 +5952,16 @@
         <v>44557</v>
       </c>
       <c r="B277" t="n">
-        <v>30.72522354125977</v>
+        <v>30.7252254486084</v>
       </c>
       <c r="C277" t="n">
-        <v>31.01535896880716</v>
+        <v>31.01536089416671</v>
       </c>
       <c r="D277" t="n">
-        <v>29.98054654550914</v>
+        <v>29.98054840663</v>
       </c>
       <c r="E277" t="n">
-        <v>29.98054654550914</v>
+        <v>29.98054840663</v>
       </c>
       <c r="F277" t="n">
         <v>1273927</v>
@@ -6132,16 +6132,16 @@
         <v>44571</v>
       </c>
       <c r="B286" t="n">
-        <v>33.37511444091797</v>
+        <v>33.37511825561523</v>
       </c>
       <c r="C286" t="n">
-        <v>33.89735778992546</v>
+        <v>33.89736166431392</v>
       </c>
       <c r="D286" t="n">
-        <v>32.24359030771443</v>
+        <v>32.24359399308115</v>
       </c>
       <c r="E286" t="n">
-        <v>32.37898645393302</v>
+        <v>32.3789901547752</v>
       </c>
       <c r="F286" t="n">
         <v>2829132</v>
@@ -6152,16 +6152,16 @@
         <v>44572</v>
       </c>
       <c r="B287" t="n">
-        <v>35.10625457763672</v>
+        <v>35.10625076293945</v>
       </c>
       <c r="C287" t="n">
-        <v>35.63816673084244</v>
+        <v>35.63816285834681</v>
       </c>
       <c r="D287" t="n">
-        <v>33.18169458570739</v>
+        <v>33.18169098013564</v>
       </c>
       <c r="E287" t="n">
-        <v>33.55886933935793</v>
+        <v>33.55886569280182</v>
       </c>
       <c r="F287" t="n">
         <v>3953735</v>
@@ -6172,16 +6172,16 @@
         <v>44573</v>
       </c>
       <c r="B288" t="n">
-        <v>34.89348983764648</v>
+        <v>34.89348602294922</v>
       </c>
       <c r="C288" t="n">
-        <v>35.98632787872025</v>
+        <v>35.98632394454952</v>
       </c>
       <c r="D288" t="n">
-        <v>34.13914032772324</v>
+        <v>34.13913659549451</v>
       </c>
       <c r="E288" t="n">
-        <v>35.34803329265463</v>
+        <v>35.34802942826484</v>
       </c>
       <c r="F288" t="n">
         <v>3302601</v>
@@ -6292,16 +6292,16 @@
         <v>44581</v>
       </c>
       <c r="B294" t="n">
-        <v>35.29967498779297</v>
+        <v>35.2996711730957</v>
       </c>
       <c r="C294" t="n">
-        <v>36.17007943172774</v>
+        <v>36.17007552296929</v>
       </c>
       <c r="D294" t="n">
-        <v>34.98052769103708</v>
+        <v>34.98052391082881</v>
       </c>
       <c r="E294" t="n">
-        <v>35.87027337331519</v>
+        <v>35.8702694969556</v>
       </c>
       <c r="F294" t="n">
         <v>3650414</v>
@@ -6332,16 +6332,16 @@
         <v>44585</v>
       </c>
       <c r="B296" t="n">
-        <v>34.35190200805664</v>
+        <v>34.35190582275391</v>
       </c>
       <c r="C296" t="n">
-        <v>35.3190162904272</v>
+        <v>35.31902021252021</v>
       </c>
       <c r="D296" t="n">
-        <v>34.05209598090971</v>
+        <v>34.05209976231423</v>
       </c>
       <c r="E296" t="n">
-        <v>34.23584709494806</v>
+        <v>34.2358508967577</v>
       </c>
       <c r="F296" t="n">
         <v>2113697</v>
@@ -6392,16 +6392,16 @@
         <v>44588</v>
       </c>
       <c r="B299" t="n">
-        <v>36.09271240234375</v>
+        <v>36.09270858764648</v>
       </c>
       <c r="C299" t="n">
-        <v>37.1081818022467</v>
+        <v>37.10817788022283</v>
       </c>
       <c r="D299" t="n">
-        <v>35.68652389286739</v>
+        <v>35.68652012110085</v>
       </c>
       <c r="E299" t="n">
-        <v>35.87994752798603</v>
+        <v>35.87994373577622</v>
       </c>
       <c r="F299" t="n">
         <v>3171460</v>
@@ -6492,16 +6492,16 @@
         <v>44595</v>
       </c>
       <c r="B304" t="n">
-        <v>35.29967498779297</v>
+        <v>35.2996711730957</v>
       </c>
       <c r="C304" t="n">
-        <v>35.58981230082171</v>
+        <v>35.58980845477045</v>
       </c>
       <c r="D304" t="n">
-        <v>33.84900341295216</v>
+        <v>33.84899975502328</v>
       </c>
       <c r="E304" t="n">
-        <v>34.98052769103708</v>
+        <v>34.98052391082881</v>
       </c>
       <c r="F304" t="n">
         <v>4177823</v>
@@ -6592,16 +6592,16 @@
         <v>44602</v>
       </c>
       <c r="B309" t="n">
-        <v>37.28226470947266</v>
+        <v>37.28226089477539</v>
       </c>
       <c r="C309" t="n">
-        <v>38.3847753224369</v>
+        <v>38.38477139493146</v>
       </c>
       <c r="D309" t="n">
-        <v>36.33449150769526</v>
+        <v>36.33448778997354</v>
       </c>
       <c r="E309" t="n">
-        <v>36.36350524073979</v>
+        <v>36.3635015200494</v>
       </c>
       <c r="F309" t="n">
         <v>7025951</v>
@@ -6612,16 +6612,16 @@
         <v>44603</v>
       </c>
       <c r="B310" t="n">
-        <v>38.07529067993164</v>
+        <v>38.07529449462891</v>
       </c>
       <c r="C310" t="n">
-        <v>38.49115162219439</v>
+        <v>38.49115547855604</v>
       </c>
       <c r="D310" t="n">
-        <v>37.37896869306991</v>
+        <v>37.37897243800389</v>
       </c>
       <c r="E310" t="n">
-        <v>37.78515714333515</v>
+        <v>37.78516092896444</v>
       </c>
       <c r="F310" t="n">
         <v>5486491</v>
@@ -6632,16 +6632,16 @@
         <v>44606</v>
       </c>
       <c r="B311" t="n">
-        <v>37.57239151000977</v>
+        <v>37.57239532470703</v>
       </c>
       <c r="C311" t="n">
-        <v>38.84898429079868</v>
+        <v>38.84898823510746</v>
       </c>
       <c r="D311" t="n">
-        <v>36.95343822941596</v>
+        <v>36.95344198127135</v>
       </c>
       <c r="E311" t="n">
-        <v>38.29772721003804</v>
+        <v>38.2977310983781</v>
       </c>
       <c r="F311" t="n">
         <v>3902640</v>
@@ -6652,16 +6652,16 @@
         <v>44607</v>
       </c>
       <c r="B312" t="n">
-        <v>35.79290008544922</v>
+        <v>35.79290390014648</v>
       </c>
       <c r="C312" t="n">
-        <v>36.65363192612031</v>
+        <v>36.65363583255173</v>
       </c>
       <c r="D312" t="n">
-        <v>35.63816270338088</v>
+        <v>35.63816650158672</v>
       </c>
       <c r="E312" t="n">
-        <v>36.55692199922141</v>
+        <v>36.55692589534578</v>
       </c>
       <c r="F312" t="n">
         <v>3810709</v>
@@ -6672,16 +6672,16 @@
         <v>44608</v>
       </c>
       <c r="B313" t="n">
-        <v>35.92830276489258</v>
+        <v>35.92829895019531</v>
       </c>
       <c r="C313" t="n">
-        <v>36.80837600146183</v>
+        <v>36.80837209332255</v>
       </c>
       <c r="D313" t="n">
-        <v>35.69619664958365</v>
+        <v>35.69619285953032</v>
       </c>
       <c r="E313" t="n">
-        <v>36.44087371532872</v>
+        <v>36.4408698462091</v>
       </c>
       <c r="F313" t="n">
         <v>4244663</v>
@@ -6692,16 +6692,16 @@
         <v>44609</v>
       </c>
       <c r="B314" t="n">
-        <v>35.29967498779297</v>
+        <v>35.2996711730957</v>
       </c>
       <c r="C314" t="n">
-        <v>35.89928710461807</v>
+        <v>35.89928322512308</v>
       </c>
       <c r="D314" t="n">
-        <v>34.41960179847439</v>
+        <v>34.41959807888318</v>
       </c>
       <c r="E314" t="n">
-        <v>35.68652224011414</v>
+        <v>35.68651838361181</v>
       </c>
       <c r="F314" t="n">
         <v>4430658</v>
@@ -6712,16 +6712,16 @@
         <v>44610</v>
       </c>
       <c r="B315" t="n">
-        <v>34.48730087280273</v>
+        <v>34.48729705810547</v>
       </c>
       <c r="C315" t="n">
-        <v>35.41572900804387</v>
+        <v>35.41572509065163</v>
       </c>
       <c r="D315" t="n">
-        <v>33.80064757961473</v>
+        <v>33.80064384086931</v>
       </c>
       <c r="E315" t="n">
-        <v>34.83546189196511</v>
+        <v>34.83545803875718</v>
       </c>
       <c r="F315" t="n">
         <v>4069741</v>
@@ -6852,16 +6852,16 @@
         <v>44623</v>
       </c>
       <c r="B322" t="n">
-        <v>37.34028625488281</v>
+        <v>37.34028244018555</v>
       </c>
       <c r="C322" t="n">
-        <v>37.88187465766974</v>
+        <v>37.88187078764361</v>
       </c>
       <c r="D322" t="n">
-        <v>36.31514815474819</v>
+        <v>36.31514444477941</v>
       </c>
       <c r="E322" t="n">
-        <v>37.12752138998924</v>
+        <v>37.12751759702811</v>
       </c>
       <c r="F322" t="n">
         <v>9786414</v>
@@ -6892,16 +6892,16 @@
         <v>44627</v>
       </c>
       <c r="B324" t="n">
-        <v>37.04048156738281</v>
+        <v>37.04048538208008</v>
       </c>
       <c r="C324" t="n">
-        <v>39.28418499781101</v>
+        <v>39.28418904358112</v>
       </c>
       <c r="D324" t="n">
-        <v>36.65363433916909</v>
+        <v>36.65363811402602</v>
       </c>
       <c r="E324" t="n">
-        <v>38.17200577495368</v>
+        <v>38.17200970618351</v>
       </c>
       <c r="F324" t="n">
         <v>5025922</v>
@@ -6952,16 +6952,16 @@
         <v>44630</v>
       </c>
       <c r="B327" t="n">
-        <v>35.7252082824707</v>
+        <v>35.72520446777344</v>
       </c>
       <c r="C327" t="n">
-        <v>37.22423481932497</v>
+        <v>37.22423084456335</v>
       </c>
       <c r="D327" t="n">
-        <v>35.51244341905014</v>
+        <v>35.51243962707166</v>
       </c>
       <c r="E327" t="n">
-        <v>36.75034637550812</v>
+        <v>36.75034245134777</v>
       </c>
       <c r="F327" t="n">
         <v>4502679</v>
@@ -7032,16 +7032,16 @@
         <v>44636</v>
       </c>
       <c r="B331" t="n">
-        <v>32.84320449829102</v>
+        <v>32.84320831298828</v>
       </c>
       <c r="C331" t="n">
-        <v>34.44861337459189</v>
+        <v>34.44861737575539</v>
       </c>
       <c r="D331" t="n">
-        <v>32.34030609979657</v>
+        <v>32.34030985608281</v>
       </c>
       <c r="E331" t="n">
-        <v>34.10045236831488</v>
+        <v>34.10045632903992</v>
       </c>
       <c r="F331" t="n">
         <v>3899288</v>
@@ -7092,16 +7092,16 @@
         <v>44641</v>
       </c>
       <c r="B334" t="n">
-        <v>36.61494827270508</v>
+        <v>36.61495208740234</v>
       </c>
       <c r="C334" t="n">
-        <v>36.86639934686866</v>
+        <v>36.86640318776314</v>
       </c>
       <c r="D334" t="n">
-        <v>35.88961252740777</v>
+        <v>35.88961626653654</v>
       </c>
       <c r="E334" t="n">
-        <v>35.97665371626157</v>
+        <v>35.97665746445866</v>
       </c>
       <c r="F334" t="n">
         <v>3600944</v>
@@ -7212,16 +7212,16 @@
         <v>44649</v>
       </c>
       <c r="B340" t="n">
-        <v>40.11590194702148</v>
+        <v>40.11590576171875</v>
       </c>
       <c r="C340" t="n">
-        <v>40.60913158587444</v>
+        <v>40.60913544747385</v>
       </c>
       <c r="D340" t="n">
-        <v>37.81417112752509</v>
+        <v>37.8141747233464</v>
       </c>
       <c r="E340" t="n">
-        <v>38.00759473575618</v>
+        <v>38.00759834997051</v>
       </c>
       <c r="F340" t="n">
         <v>6952609</v>
@@ -7252,16 +7252,16 @@
         <v>44651</v>
       </c>
       <c r="B342" t="n">
-        <v>40.47373962402344</v>
+        <v>40.47373580932617</v>
       </c>
       <c r="C342" t="n">
-        <v>41.13137921056172</v>
+        <v>41.13137533388116</v>
       </c>
       <c r="D342" t="n">
-        <v>39.67103512697872</v>
+        <v>39.6710313879373</v>
       </c>
       <c r="E342" t="n">
-        <v>40.135251085266</v>
+        <v>40.13524730247168</v>
       </c>
       <c r="F342" t="n">
         <v>3810811</v>
@@ -7312,16 +7312,16 @@
         <v>44656</v>
       </c>
       <c r="B345" t="n">
-        <v>41.97276306152344</v>
+        <v>41.9727668762207</v>
       </c>
       <c r="C345" t="n">
-        <v>43.03659106395681</v>
+        <v>43.03659497534015</v>
       </c>
       <c r="D345" t="n">
-        <v>41.57624708903781</v>
+        <v>41.5762508676977</v>
       </c>
       <c r="E345" t="n">
-        <v>42.30158283032514</v>
+        <v>42.30158667490721</v>
       </c>
       <c r="F345" t="n">
         <v>5903074</v>
@@ -7432,16 +7432,16 @@
         <v>44664</v>
       </c>
       <c r="B351" t="n">
-        <v>43.62652969360352</v>
+        <v>43.62653350830078</v>
       </c>
       <c r="C351" t="n">
-        <v>43.71356713249195</v>
+        <v>43.71357095479976</v>
       </c>
       <c r="D351" t="n">
-        <v>42.8431665105797</v>
+        <v>42.8431702567798</v>
       </c>
       <c r="E351" t="n">
-        <v>43.30738242414481</v>
+        <v>43.30738621093589</v>
       </c>
       <c r="F351" t="n">
         <v>3238402</v>
@@ -7452,16 +7452,16 @@
         <v>44665</v>
       </c>
       <c r="B352" t="n">
-        <v>42.93988037109375</v>
+        <v>42.93987655639648</v>
       </c>
       <c r="C352" t="n">
-        <v>43.62653368593358</v>
+        <v>43.62652981023535</v>
       </c>
       <c r="D352" t="n">
-        <v>42.2242170723533</v>
+        <v>42.2242133212342</v>
       </c>
       <c r="E352" t="n">
-        <v>43.62653368593358</v>
+        <v>43.62652981023535</v>
       </c>
       <c r="F352" t="n">
         <v>2345809</v>
@@ -7552,16 +7552,16 @@
         <v>44676</v>
       </c>
       <c r="B357" t="n">
-        <v>41.94375228881836</v>
+        <v>41.94374847412109</v>
       </c>
       <c r="C357" t="n">
-        <v>42.40796824528748</v>
+        <v>42.40796438837074</v>
       </c>
       <c r="D357" t="n">
-        <v>40.64782185452133</v>
+        <v>40.64781815768625</v>
       </c>
       <c r="E357" t="n">
-        <v>40.75420428750637</v>
+        <v>40.75420058099602</v>
       </c>
       <c r="F357" t="n">
         <v>3287465</v>
@@ -7592,16 +7592,16 @@
         <v>44678</v>
       </c>
       <c r="B359" t="n">
-        <v>42.16618728637695</v>
+        <v>42.16619110107422</v>
       </c>
       <c r="C359" t="n">
-        <v>43.58784506009413</v>
+        <v>43.58784900340616</v>
       </c>
       <c r="D359" t="n">
-        <v>41.46986526445734</v>
+        <v>41.46986901615963</v>
       </c>
       <c r="E359" t="n">
-        <v>43.52014885542929</v>
+        <v>43.52015279261696</v>
       </c>
       <c r="F359" t="n">
         <v>3779727</v>
@@ -7672,16 +7672,16 @@
         <v>44684</v>
       </c>
       <c r="B363" t="n">
-        <v>42.12750244140625</v>
+        <v>42.12749862670898</v>
       </c>
       <c r="C363" t="n">
-        <v>42.54336341820335</v>
+        <v>42.54335956584936</v>
       </c>
       <c r="D363" t="n">
-        <v>41.25710175933607</v>
+        <v>41.25709802345466</v>
       </c>
       <c r="E363" t="n">
-        <v>42.54336341820335</v>
+        <v>42.54335956584936</v>
       </c>
       <c r="F363" t="n">
         <v>4458389</v>
@@ -7692,16 +7692,16 @@
         <v>44685</v>
       </c>
       <c r="B364" t="n">
-        <v>44.10041427612305</v>
+        <v>44.10041809082031</v>
       </c>
       <c r="C364" t="n">
-        <v>44.32285161417975</v>
+        <v>44.32285544811791</v>
       </c>
       <c r="D364" t="n">
-        <v>42.16618567842227</v>
+        <v>42.16618932580826</v>
       </c>
       <c r="E364" t="n">
-        <v>43.04625879095802</v>
+        <v>43.04626251447057</v>
       </c>
       <c r="F364" t="n">
         <v>5759540</v>
@@ -7712,16 +7712,16 @@
         <v>44686</v>
       </c>
       <c r="B365" t="n">
-        <v>42.92053985595703</v>
+        <v>42.92053604125977</v>
       </c>
       <c r="C365" t="n">
-        <v>44.57430384010176</v>
+        <v>44.57429987842104</v>
       </c>
       <c r="D365" t="n">
-        <v>42.01145291457887</v>
+        <v>42.01144918067956</v>
       </c>
       <c r="E365" t="n">
-        <v>44.09074663744735</v>
+        <v>44.09074271874429</v>
       </c>
       <c r="F365" t="n">
         <v>4814532</v>
@@ -7732,16 +7732,16 @@
         <v>44687</v>
       </c>
       <c r="B366" t="n">
-        <v>42.55303573608398</v>
+        <v>42.55303192138672</v>
       </c>
       <c r="C366" t="n">
-        <v>43.90699359626386</v>
+        <v>43.90698966019007</v>
       </c>
       <c r="D366" t="n">
-        <v>41.82769996355259</v>
+        <v>41.82769621387857</v>
       </c>
       <c r="E366" t="n">
-        <v>43.33639522245434</v>
+        <v>43.33639133753226</v>
       </c>
       <c r="F366" t="n">
         <v>4093307</v>
@@ -7892,16 +7892,16 @@
         <v>44699</v>
       </c>
       <c r="B374" t="n">
-        <v>39.99985504150391</v>
+        <v>39.99985122680664</v>
       </c>
       <c r="C374" t="n">
-        <v>42.22421740419406</v>
+        <v>42.2242133773643</v>
       </c>
       <c r="D374" t="n">
-        <v>39.72906271064676</v>
+        <v>39.72905892177436</v>
       </c>
       <c r="E374" t="n">
-        <v>42.13717620908088</v>
+        <v>42.13717219055205</v>
       </c>
       <c r="F374" t="n">
         <v>1865839</v>
@@ -7952,16 +7952,16 @@
         <v>44704</v>
       </c>
       <c r="B377" t="n">
-        <v>42.28224563598633</v>
+        <v>42.28224182128906</v>
       </c>
       <c r="C377" t="n">
-        <v>42.79481657531103</v>
+        <v>42.7948127143697</v>
       </c>
       <c r="D377" t="n">
-        <v>41.35381369972519</v>
+        <v>41.3538099687909</v>
       </c>
       <c r="E377" t="n">
-        <v>41.42151365745766</v>
+        <v>41.42150992041549</v>
       </c>
       <c r="F377" t="n">
         <v>3400119</v>
@@ -8012,16 +8012,16 @@
         <v>44707</v>
       </c>
       <c r="B380" t="n">
-        <v>46.5955696105957</v>
+        <v>46.59557342529297</v>
       </c>
       <c r="C380" t="n">
-        <v>47.1661679572728</v>
+        <v>47.16617181868395</v>
       </c>
       <c r="D380" t="n">
-        <v>45.10621566046026</v>
+        <v>45.10621935322675</v>
       </c>
       <c r="E380" t="n">
-        <v>45.2512805595232</v>
+        <v>45.25128426416589</v>
       </c>
       <c r="F380" t="n">
         <v>4582217</v>
@@ -8072,16 +8072,16 @@
         <v>44712</v>
       </c>
       <c r="B383" t="n">
-        <v>47.14682769775391</v>
+        <v>47.14683151245117</v>
       </c>
       <c r="C383" t="n">
-        <v>49.5452685563496</v>
+        <v>49.54527256510714</v>
       </c>
       <c r="D383" t="n">
-        <v>47.11781396782467</v>
+        <v>47.11781778017441</v>
       </c>
       <c r="E383" t="n">
-        <v>48.22032446240879</v>
+        <v>48.22032836396376</v>
       </c>
       <c r="F383" t="n">
         <v>6322705</v>
@@ -8152,16 +8152,16 @@
         <v>44718</v>
       </c>
       <c r="B387" t="n">
-        <v>45.3189811706543</v>
+        <v>45.31898498535156</v>
       </c>
       <c r="C387" t="n">
-        <v>47.4563021942838</v>
+        <v>47.45630618888874</v>
       </c>
       <c r="D387" t="n">
-        <v>45.13522629971035</v>
+        <v>45.13523009894016</v>
       </c>
       <c r="E387" t="n">
-        <v>47.15649615191405</v>
+        <v>47.156500121283</v>
       </c>
       <c r="F387" t="n">
         <v>1711233</v>
@@ -8172,16 +8172,16 @@
         <v>44719</v>
       </c>
       <c r="B388" t="n">
-        <v>45.3189811706543</v>
+        <v>45.31898498535156</v>
       </c>
       <c r="C388" t="n">
-        <v>45.84122081100923</v>
+        <v>45.84122466966569</v>
       </c>
       <c r="D388" t="n">
-        <v>44.73871032322317</v>
+        <v>44.73871408907649</v>
       </c>
       <c r="E388" t="n">
-        <v>44.98048890609225</v>
+        <v>44.98049269229714</v>
       </c>
       <c r="F388" t="n">
         <v>1887578</v>
@@ -8192,16 +8192,16 @@
         <v>44720</v>
       </c>
       <c r="B389" t="n">
-        <v>45.25128555297852</v>
+        <v>45.25128173828125</v>
       </c>
       <c r="C389" t="n">
-        <v>46.00563510358936</v>
+        <v>46.00563122530019</v>
       </c>
       <c r="D389" t="n">
-        <v>44.92246574936335</v>
+        <v>44.9224619623857</v>
       </c>
       <c r="E389" t="n">
-        <v>45.31898551140559</v>
+        <v>45.31898169100119</v>
       </c>
       <c r="F389" t="n">
         <v>1920490</v>
@@ -8212,16 +8212,16 @@
         <v>44721</v>
       </c>
       <c r="B390" t="n">
-        <v>44.5066032409668</v>
+        <v>44.50660705566406</v>
       </c>
       <c r="C390" t="n">
-        <v>45.59944121195702</v>
+        <v>45.59944512032232</v>
       </c>
       <c r="D390" t="n">
-        <v>44.32285212169327</v>
+        <v>44.32285592064108</v>
       </c>
       <c r="E390" t="n">
-        <v>45.22226648118356</v>
+        <v>45.2222703572209</v>
       </c>
       <c r="F390" t="n">
         <v>1644697</v>
@@ -8472,16 +8472,16 @@
         <v>44741</v>
       </c>
       <c r="B403" t="n">
-        <v>34.71940612792969</v>
+        <v>34.71940994262695</v>
       </c>
       <c r="C403" t="n">
-        <v>35.41572814937177</v>
+        <v>35.41573204057546</v>
       </c>
       <c r="D403" t="n">
-        <v>34.09078031110602</v>
+        <v>34.0907840567348</v>
       </c>
       <c r="E403" t="n">
-        <v>35.29967322993957</v>
+        <v>35.29967710839206</v>
       </c>
       <c r="F403" t="n">
         <v>2690880</v>
@@ -8532,16 +8532,16 @@
         <v>44746</v>
       </c>
       <c r="B406" t="n">
-        <v>35.08691024780273</v>
+        <v>35.08690643310547</v>
       </c>
       <c r="C406" t="n">
-        <v>35.60915366553204</v>
+        <v>35.60914979405575</v>
       </c>
       <c r="D406" t="n">
-        <v>34.1971683099429</v>
+        <v>34.19716459197961</v>
       </c>
       <c r="E406" t="n">
-        <v>34.57433932306729</v>
+        <v>34.57433556409744</v>
       </c>
       <c r="F406" t="n">
         <v>2359523</v>
@@ -8612,16 +8612,16 @@
         <v>44750</v>
       </c>
       <c r="B410" t="n">
-        <v>31.81806373596191</v>
+        <v>31.81806564331055</v>
       </c>
       <c r="C410" t="n">
-        <v>32.48537204040704</v>
+        <v>32.48537398775778</v>
       </c>
       <c r="D410" t="n">
-        <v>31.19911039968697</v>
+        <v>31.19911226993215</v>
       </c>
       <c r="E410" t="n">
-        <v>31.3151653213559</v>
+        <v>31.31516719855805</v>
       </c>
       <c r="F410" t="n">
         <v>4375906</v>
@@ -8712,16 +8712,16 @@
         <v>44757</v>
       </c>
       <c r="B415" t="n">
-        <v>27.79486846923828</v>
+        <v>27.79486656188965</v>
       </c>
       <c r="C415" t="n">
-        <v>29.07146143004599</v>
+        <v>29.07145943509457</v>
       </c>
       <c r="D415" t="n">
-        <v>27.79486846923828</v>
+        <v>27.79486656188965</v>
       </c>
       <c r="E415" t="n">
-        <v>29.06178893688788</v>
+        <v>29.06178694260021</v>
       </c>
       <c r="F415" t="n">
         <v>4618481</v>
@@ -8752,16 +8752,16 @@
         <v>44761</v>
       </c>
       <c r="B417" t="n">
-        <v>29.43896293640137</v>
+        <v>29.43896102905273</v>
       </c>
       <c r="C417" t="n">
-        <v>29.53567474894549</v>
+        <v>29.5356728353309</v>
       </c>
       <c r="D417" t="n">
-        <v>28.11401691328927</v>
+        <v>28.11401509178381</v>
       </c>
       <c r="E417" t="n">
-        <v>28.14303064443129</v>
+        <v>28.14302882104603</v>
       </c>
       <c r="F417" t="n">
         <v>4570230</v>
@@ -8772,16 +8772,16 @@
         <v>44762</v>
       </c>
       <c r="B418" t="n">
-        <v>30.59950065612793</v>
+        <v>30.5994987487793</v>
       </c>
       <c r="C418" t="n">
-        <v>30.97667540990739</v>
+        <v>30.97667347904845</v>
       </c>
       <c r="D418" t="n">
-        <v>29.21652718353251</v>
+        <v>29.21652536238831</v>
       </c>
       <c r="E418" t="n">
-        <v>29.21652718353251</v>
+        <v>29.21652536238831</v>
       </c>
       <c r="F418" t="n">
         <v>5027446</v>
@@ -8792,16 +8792,16 @@
         <v>44763</v>
       </c>
       <c r="B419" t="n">
-        <v>29.44863510131836</v>
+        <v>29.44863319396973</v>
       </c>
       <c r="C419" t="n">
-        <v>29.86449233042948</v>
+        <v>29.86449039614633</v>
       </c>
       <c r="D419" t="n">
-        <v>28.83935237548546</v>
+        <v>28.83935050759925</v>
       </c>
       <c r="E419" t="n">
-        <v>29.86449233042948</v>
+        <v>29.86449039614633</v>
       </c>
       <c r="F419" t="n">
         <v>5437325</v>
@@ -8832,16 +8832,16 @@
         <v>44767</v>
       </c>
       <c r="B421" t="n">
-        <v>29.2648811340332</v>
+        <v>29.26488304138184</v>
       </c>
       <c r="C421" t="n">
-        <v>29.7194245717984</v>
+        <v>29.71942650877206</v>
       </c>
       <c r="D421" t="n">
-        <v>28.43316295561438</v>
+        <v>28.43316480875549</v>
       </c>
       <c r="E421" t="n">
-        <v>28.87803577468757</v>
+        <v>28.87803765682343</v>
       </c>
       <c r="F421" t="n">
         <v>3521914</v>
@@ -8852,16 +8852,16 @@
         <v>44768</v>
       </c>
       <c r="B422" t="n">
-        <v>28.95540428161621</v>
+        <v>28.95540618896484</v>
       </c>
       <c r="C422" t="n">
-        <v>30.15462657412001</v>
+        <v>30.15462856046375</v>
       </c>
       <c r="D422" t="n">
-        <v>28.81033750703789</v>
+        <v>28.81033940483069</v>
       </c>
       <c r="E422" t="n">
-        <v>29.88383426222034</v>
+        <v>29.88383623072646</v>
       </c>
       <c r="F422" t="n">
         <v>2984449</v>
@@ -8872,16 +8872,16 @@
         <v>44769</v>
       </c>
       <c r="B423" t="n">
-        <v>29.66139984130859</v>
+        <v>29.66139793395996</v>
       </c>
       <c r="C423" t="n">
-        <v>29.76778227135207</v>
+        <v>29.76778035716261</v>
       </c>
       <c r="D423" t="n">
-        <v>28.61691490502781</v>
+        <v>28.6169130648438</v>
       </c>
       <c r="E423" t="n">
-        <v>28.95540530688788</v>
+        <v>28.95540344493757</v>
       </c>
       <c r="F423" t="n">
         <v>2554762</v>
@@ -8892,16 +8892,16 @@
         <v>44770</v>
       </c>
       <c r="B424" t="n">
-        <v>30.78325271606445</v>
+        <v>30.78325080871582</v>
       </c>
       <c r="C424" t="n">
-        <v>30.88963514995402</v>
+        <v>30.88963323601387</v>
       </c>
       <c r="D424" t="n">
-        <v>29.53567536735125</v>
+        <v>29.53567353730325</v>
       </c>
       <c r="E424" t="n">
-        <v>29.96120510290952</v>
+        <v>29.96120324649545</v>
       </c>
       <c r="F424" t="n">
         <v>4208906</v>
@@ -8952,16 +8952,16 @@
         <v>44775</v>
       </c>
       <c r="B427" t="n">
-        <v>31.85674858093262</v>
+        <v>31.85675048828125</v>
       </c>
       <c r="C427" t="n">
-        <v>32.0791821744082</v>
+        <v>32.07918409507452</v>
       </c>
       <c r="D427" t="n">
-        <v>30.94765985359998</v>
+        <v>30.94766170651904</v>
       </c>
       <c r="E427" t="n">
-        <v>31.32483458513196</v>
+        <v>31.32483646063348</v>
       </c>
       <c r="F427" t="n">
         <v>3020206</v>
@@ -9072,16 +9072,16 @@
         <v>44783</v>
       </c>
       <c r="B433" t="n">
-        <v>33.26873397827148</v>
+        <v>33.26873779296875</v>
       </c>
       <c r="C433" t="n">
-        <v>33.97472847846024</v>
+        <v>33.97473237410905</v>
       </c>
       <c r="D433" t="n">
-        <v>32.87221800802422</v>
+        <v>32.87222177725572</v>
       </c>
       <c r="E433" t="n">
-        <v>33.62656747451073</v>
+        <v>33.62657133023831</v>
       </c>
       <c r="F433" t="n">
         <v>3325457</v>
@@ -9152,16 +9152,16 @@
         <v>44789</v>
       </c>
       <c r="B437" t="n">
-        <v>32.27260589599609</v>
+        <v>32.27260971069336</v>
       </c>
       <c r="C437" t="n">
-        <v>32.61109815484615</v>
+        <v>32.61110200955398</v>
       </c>
       <c r="D437" t="n">
-        <v>31.73102127989639</v>
+        <v>31.73102503057709</v>
       </c>
       <c r="E437" t="n">
-        <v>32.39832955774229</v>
+        <v>32.39833338730038</v>
       </c>
       <c r="F437" t="n">
         <v>2684074</v>
@@ -9172,16 +9172,16 @@
         <v>44790</v>
       </c>
       <c r="B438" t="n">
-        <v>32.53372955322266</v>
+        <v>32.53372573852539</v>
       </c>
       <c r="C438" t="n">
-        <v>32.93024931741367</v>
+        <v>32.93024545622303</v>
       </c>
       <c r="D438" t="n">
-        <v>31.80839373121048</v>
+        <v>31.80839000156146</v>
       </c>
       <c r="E438" t="n">
-        <v>31.8180662246313</v>
+        <v>31.81806249384815</v>
       </c>
       <c r="F438" t="n">
         <v>3057587</v>
@@ -9252,16 +9252,16 @@
         <v>44796</v>
       </c>
       <c r="B442" t="n">
-        <v>35.11592102050781</v>
+        <v>35.11592483520508</v>
       </c>
       <c r="C442" t="n">
-        <v>35.54145071517264</v>
+        <v>35.54145457609587</v>
       </c>
       <c r="D442" t="n">
-        <v>33.43314347863087</v>
+        <v>33.43314711052539</v>
       </c>
       <c r="E442" t="n">
-        <v>33.46215720759215</v>
+        <v>33.46216084263848</v>
       </c>
       <c r="F442" t="n">
         <v>5706007</v>
@@ -9292,16 +9292,16 @@
         <v>44798</v>
       </c>
       <c r="B444" t="n">
-        <v>35.7348747253418</v>
+        <v>35.73487854003906</v>
       </c>
       <c r="C444" t="n">
-        <v>36.56659288719009</v>
+        <v>36.56659679067325</v>
       </c>
       <c r="D444" t="n">
-        <v>35.39638621377552</v>
+        <v>35.39638999233915</v>
       </c>
       <c r="E444" t="n">
-        <v>35.8606021347718</v>
+        <v>35.86060596289047</v>
       </c>
       <c r="F444" t="n">
         <v>2850362</v>
@@ -9372,16 +9372,16 @@
         <v>44804</v>
       </c>
       <c r="B448" t="n">
-        <v>36.16040420532227</v>
+        <v>36.16040802001953</v>
       </c>
       <c r="C448" t="n">
-        <v>36.46021024107181</v>
+        <v>36.46021408739674</v>
       </c>
       <c r="D448" t="n">
-        <v>35.22230362431106</v>
+        <v>35.22230734004456</v>
       </c>
       <c r="E448" t="n">
-        <v>35.91862562779205</v>
+        <v>35.91862941698318</v>
       </c>
       <c r="F448" t="n">
         <v>3394125</v>
@@ -9392,16 +9392,16 @@
         <v>44805</v>
       </c>
       <c r="B449" t="n">
-        <v>35.58013534545898</v>
+        <v>35.58013916015625</v>
       </c>
       <c r="C449" t="n">
-        <v>36.22810235066332</v>
+        <v>36.22810623483188</v>
       </c>
       <c r="D449" t="n">
-        <v>35.00953703150028</v>
+        <v>35.00954078502128</v>
       </c>
       <c r="E449" t="n">
-        <v>35.8412551468599</v>
+        <v>35.84125898955293</v>
       </c>
       <c r="F449" t="n">
         <v>3340084</v>
@@ -9492,16 +9492,16 @@
         <v>44813</v>
       </c>
       <c r="B454" t="n">
-        <v>35.92830276489258</v>
+        <v>35.92829895019531</v>
       </c>
       <c r="C454" t="n">
-        <v>36.37317375612866</v>
+        <v>36.3731698941971</v>
       </c>
       <c r="D454" t="n">
-        <v>35.60915545100184</v>
+        <v>35.60915167019012</v>
       </c>
       <c r="E454" t="n">
-        <v>35.79290659406839</v>
+        <v>35.79290279374685</v>
       </c>
       <c r="F454" t="n">
         <v>3544465</v>
@@ -9552,16 +9552,16 @@
         <v>44818</v>
       </c>
       <c r="B457" t="n">
-        <v>37.25324630737305</v>
+        <v>37.25325012207031</v>
       </c>
       <c r="C457" t="n">
-        <v>37.57239358328728</v>
+        <v>37.57239743066493</v>
       </c>
       <c r="D457" t="n">
-        <v>35.96698471138824</v>
+        <v>35.96698839437353</v>
       </c>
       <c r="E457" t="n">
-        <v>36.05402215203722</v>
+        <v>36.05402584393507</v>
       </c>
       <c r="F457" t="n">
         <v>4057043</v>
@@ -9592,16 +9592,16 @@
         <v>44820</v>
       </c>
       <c r="B459" t="n">
-        <v>36.79870223999023</v>
+        <v>36.7987060546875</v>
       </c>
       <c r="C459" t="n">
-        <v>36.79870223999023</v>
+        <v>36.7987060546875</v>
       </c>
       <c r="D459" t="n">
-        <v>35.78322922342723</v>
+        <v>35.7832329328566</v>
       </c>
       <c r="E459" t="n">
-        <v>36.14106271488564</v>
+        <v>36.14106646140942</v>
       </c>
       <c r="F459" t="n">
         <v>2974596</v>
@@ -9612,16 +9612,16 @@
         <v>44823</v>
       </c>
       <c r="B460" t="n">
-        <v>36.8470573425293</v>
+        <v>36.84706115722656</v>
       </c>
       <c r="C460" t="n">
-        <v>37.3983144462179</v>
+        <v>37.39831831798563</v>
       </c>
       <c r="D460" t="n">
-        <v>35.7929018485589</v>
+        <v>35.79290555412169</v>
       </c>
       <c r="E460" t="n">
-        <v>35.7929018485589</v>
+        <v>35.79290555412169</v>
       </c>
       <c r="F460" t="n">
         <v>3461677</v>
@@ -9652,16 +9652,16 @@
         <v>44825</v>
       </c>
       <c r="B462" t="n">
-        <v>38.0366096496582</v>
+        <v>38.03661346435547</v>
       </c>
       <c r="C462" t="n">
-        <v>38.79095912196355</v>
+        <v>38.79096301231463</v>
       </c>
       <c r="D462" t="n">
-        <v>37.62074869162363</v>
+        <v>37.62075246461414</v>
       </c>
       <c r="E462" t="n">
-        <v>37.9398959687412</v>
+        <v>37.93989977373904</v>
       </c>
       <c r="F462" t="n">
         <v>4689181</v>
@@ -9732,16 +9732,16 @@
         <v>44831</v>
       </c>
       <c r="B466" t="n">
-        <v>33.61689758300781</v>
+        <v>33.61689376831055</v>
       </c>
       <c r="C466" t="n">
-        <v>34.44861580943209</v>
+        <v>34.44861190035511</v>
       </c>
       <c r="D466" t="n">
-        <v>33.32676401519949</v>
+        <v>33.3267602334253</v>
       </c>
       <c r="E466" t="n">
-        <v>34.44861580943209</v>
+        <v>34.44861190035511</v>
       </c>
       <c r="F466" t="n">
         <v>5480701</v>
@@ -9752,16 +9752,16 @@
         <v>44832</v>
       </c>
       <c r="B467" t="n">
-        <v>34.5743408203125</v>
+        <v>34.57433700561523</v>
       </c>
       <c r="C467" t="n">
-        <v>34.99987431683395</v>
+        <v>34.99987045518622</v>
       </c>
       <c r="D467" t="n">
-        <v>33.19136913623947</v>
+        <v>33.19136547412988</v>
       </c>
       <c r="E467" t="n">
-        <v>33.66525385709685</v>
+        <v>33.66525014270204</v>
       </c>
       <c r="F467" t="n">
         <v>4399676</v>
@@ -9772,16 +9772,16 @@
         <v>44833</v>
       </c>
       <c r="B468" t="n">
-        <v>33.90702819824219</v>
+        <v>33.90703201293945</v>
       </c>
       <c r="C468" t="n">
-        <v>34.69039138641359</v>
+        <v>34.69039528924284</v>
       </c>
       <c r="D468" t="n">
-        <v>33.09465502863428</v>
+        <v>33.09465875193581</v>
       </c>
       <c r="E468" t="n">
-        <v>34.61302269157358</v>
+        <v>34.61302658569848</v>
       </c>
       <c r="F468" t="n">
         <v>4499631</v>
@@ -9812,16 +9812,16 @@
         <v>44837</v>
       </c>
       <c r="B470" t="n">
-        <v>36.79870223999023</v>
+        <v>36.7987060546875</v>
       </c>
       <c r="C470" t="n">
-        <v>36.91475715561467</v>
+        <v>36.91476098234264</v>
       </c>
       <c r="D470" t="n">
-        <v>35.52210941084767</v>
+        <v>35.52211309320833</v>
       </c>
       <c r="E470" t="n">
-        <v>36.26678637509517</v>
+        <v>36.26679013465196</v>
       </c>
       <c r="F470" t="n">
         <v>4419789</v>
@@ -9852,16 +9852,16 @@
         <v>44839</v>
       </c>
       <c r="B472" t="n">
-        <v>41.63427352905273</v>
+        <v>41.63427734375</v>
       </c>
       <c r="C472" t="n">
-        <v>42.48533291211138</v>
+        <v>42.48533680478608</v>
       </c>
       <c r="D472" t="n">
-        <v>40.55110431601417</v>
+        <v>40.55110803146717</v>
       </c>
       <c r="E472" t="n">
-        <v>40.61880426561678</v>
+        <v>40.61880798727272</v>
       </c>
       <c r="F472" t="n">
         <v>6927519</v>
@@ -9892,16 +9892,16 @@
         <v>44841</v>
       </c>
       <c r="B474" t="n">
-        <v>41.47954177856445</v>
+        <v>41.47953796386719</v>
       </c>
       <c r="C474" t="n">
-        <v>42.45632495390688</v>
+        <v>42.45632104937901</v>
       </c>
       <c r="D474" t="n">
-        <v>41.22809067776815</v>
+        <v>41.22808688619578</v>
       </c>
       <c r="E474" t="n">
-        <v>41.59559296175236</v>
+        <v>41.59558913638236</v>
       </c>
       <c r="F474" t="n">
         <v>3503020</v>
@@ -10072,16 +10072,16 @@
         <v>44855</v>
       </c>
       <c r="B483" t="n">
-        <v>44.22613906860352</v>
+        <v>44.22614288330078</v>
       </c>
       <c r="C483" t="n">
-        <v>44.68068250090031</v>
+        <v>44.68068635480393</v>
       </c>
       <c r="D483" t="n">
-        <v>42.41763783177974</v>
+        <v>42.41764149048589</v>
       </c>
       <c r="E483" t="n">
-        <v>42.96889119740864</v>
+        <v>42.9688949036628</v>
       </c>
       <c r="F483" t="n">
         <v>5360835</v>
@@ -10112,16 +10112,16 @@
         <v>44859</v>
       </c>
       <c r="B485" t="n">
-        <v>42.69809722900391</v>
+        <v>42.69810104370117</v>
       </c>
       <c r="C485" t="n">
-        <v>44.7193669863075</v>
+        <v>44.71937098158734</v>
       </c>
       <c r="D485" t="n">
-        <v>42.52401860625056</v>
+        <v>42.52402240539543</v>
       </c>
       <c r="E485" t="n">
-        <v>43.43310543554394</v>
+        <v>43.43310931590769</v>
       </c>
       <c r="F485" t="n">
         <v>3364870</v>
@@ -10232,16 +10232,16 @@
         <v>44868</v>
       </c>
       <c r="B491" t="n">
-        <v>46.30543518066406</v>
+        <v>46.30543899536133</v>
       </c>
       <c r="C491" t="n">
-        <v>46.4311588402996</v>
+        <v>46.43116266535413</v>
       </c>
       <c r="D491" t="n">
-        <v>44.51627522669133</v>
+        <v>44.51627889399545</v>
       </c>
       <c r="E491" t="n">
-        <v>44.98048739191887</v>
+        <v>44.98049109746535</v>
       </c>
       <c r="F491" t="n">
         <v>3262984</v>
@@ -10312,16 +10312,16 @@
         <v>44874</v>
       </c>
       <c r="B495" t="n">
-        <v>44.69035339355469</v>
+        <v>44.69035720825195</v>
       </c>
       <c r="C495" t="n">
-        <v>46.49885831321781</v>
+        <v>46.49886228228617</v>
       </c>
       <c r="D495" t="n">
-        <v>44.23580997752845</v>
+        <v>44.23581375342662</v>
       </c>
       <c r="E495" t="n">
-        <v>45.35766165335595</v>
+        <v>45.35766552501359</v>
       </c>
       <c r="F495" t="n">
         <v>4884014</v>
@@ -10332,16 +10332,16 @@
         <v>44875</v>
       </c>
       <c r="B496" t="n">
-        <v>42.0598030090332</v>
+        <v>42.05980682373047</v>
       </c>
       <c r="C496" t="n">
-        <v>44.68068109462947</v>
+        <v>44.68068514703247</v>
       </c>
       <c r="D496" t="n">
-        <v>41.64394206412777</v>
+        <v>41.6439458411077</v>
       </c>
       <c r="E496" t="n">
-        <v>43.65554309181744</v>
+        <v>43.65554705124352</v>
       </c>
       <c r="F496" t="n">
         <v>5453172</v>
@@ -10472,16 +10472,16 @@
         <v>44887</v>
       </c>
       <c r="B503" t="n">
-        <v>35.7252082824707</v>
+        <v>35.72520446777344</v>
       </c>
       <c r="C503" t="n">
-        <v>38.01726681069696</v>
+        <v>38.01726275125628</v>
       </c>
       <c r="D503" t="n">
-        <v>35.41572973267442</v>
+        <v>35.41572595102293</v>
       </c>
       <c r="E503" t="n">
-        <v>37.37897222043525</v>
+        <v>37.37896822915095</v>
       </c>
       <c r="F503" t="n">
         <v>4879239</v>
@@ -10492,16 +10492,16 @@
         <v>44888</v>
       </c>
       <c r="B504" t="n">
-        <v>34.29387664794922</v>
+        <v>34.29388046264648</v>
       </c>
       <c r="C504" t="n">
-        <v>35.59947950993321</v>
+        <v>35.59948346985989</v>
       </c>
       <c r="D504" t="n">
-        <v>33.84900195222058</v>
+        <v>33.84900571743197</v>
       </c>
       <c r="E504" t="n">
-        <v>35.37704590964446</v>
+        <v>35.37704984482862</v>
       </c>
       <c r="F504" t="n">
         <v>5644348</v>
@@ -10532,16 +10532,16 @@
         <v>44890</v>
       </c>
       <c r="B506" t="n">
-        <v>34.2358512878418</v>
+        <v>34.23584747314453</v>
       </c>
       <c r="C506" t="n">
-        <v>36.49889988516448</v>
+        <v>36.49889581830917</v>
       </c>
       <c r="D506" t="n">
-        <v>34.11012761496025</v>
+        <v>34.11012381427162</v>
       </c>
       <c r="E506" t="n">
-        <v>36.17008008946956</v>
+        <v>36.17007605925269</v>
       </c>
       <c r="F506" t="n">
         <v>4398253</v>
@@ -10552,16 +10552,16 @@
         <v>44893</v>
       </c>
       <c r="B507" t="n">
-        <v>33.64591217041016</v>
+        <v>33.64590835571289</v>
       </c>
       <c r="C507" t="n">
-        <v>34.11012813925738</v>
+        <v>34.11012427192836</v>
       </c>
       <c r="D507" t="n">
-        <v>32.92057635865081</v>
+        <v>32.92057262619048</v>
       </c>
       <c r="E507" t="n">
-        <v>33.36544734092983</v>
+        <v>33.36544355803103</v>
       </c>
       <c r="F507" t="n">
         <v>4077054</v>
@@ -10652,16 +10652,16 @@
         <v>44900</v>
       </c>
       <c r="B512" t="n">
-        <v>34.04242706298828</v>
+        <v>34.04242324829102</v>
       </c>
       <c r="C512" t="n">
-        <v>35.879945891439</v>
+        <v>35.87994187083461</v>
       </c>
       <c r="D512" t="n">
-        <v>33.77163473568869</v>
+        <v>33.77163095133564</v>
       </c>
       <c r="E512" t="n">
-        <v>35.57046733984986</v>
+        <v>35.57046335392476</v>
       </c>
       <c r="F512" t="n">
         <v>5158181</v>
@@ -10732,16 +10732,16 @@
         <v>44904</v>
       </c>
       <c r="B516" t="n">
-        <v>31.69233894348145</v>
+        <v>31.69234085083008</v>
       </c>
       <c r="C516" t="n">
-        <v>32.74649445099531</v>
+        <v>32.74649642178647</v>
       </c>
       <c r="D516" t="n">
-        <v>31.48924283777486</v>
+        <v>31.4892447329005</v>
       </c>
       <c r="E516" t="n">
-        <v>32.22425106961099</v>
+        <v>32.22425300897184</v>
       </c>
       <c r="F516" t="n">
         <v>2885712</v>
@@ -10752,16 +10752,16 @@
         <v>44907</v>
       </c>
       <c r="B517" t="n">
-        <v>32.23392105102539</v>
+        <v>32.23392486572266</v>
       </c>
       <c r="C517" t="n">
-        <v>32.41767215777701</v>
+        <v>32.41767599422015</v>
       </c>
       <c r="D517" t="n">
-        <v>31.06371071712008</v>
+        <v>31.06371439332975</v>
       </c>
       <c r="E517" t="n">
-        <v>31.59562280181559</v>
+        <v>31.59562654097396</v>
       </c>
       <c r="F517" t="n">
         <v>3445728</v>
@@ -10772,16 +10772,16 @@
         <v>44908</v>
       </c>
       <c r="B518" t="n">
-        <v>32.52405548095703</v>
+        <v>32.5240592956543</v>
       </c>
       <c r="C518" t="n">
-        <v>33.41380105995531</v>
+        <v>33.41380497900949</v>
       </c>
       <c r="D518" t="n">
-        <v>31.9824708896037</v>
+        <v>31.98247464077933</v>
       </c>
       <c r="E518" t="n">
-        <v>32.39832807738018</v>
+        <v>32.39833187733107</v>
       </c>
       <c r="F518" t="n">
         <v>3369136</v>
@@ -10872,16 +10872,16 @@
         <v>44915</v>
       </c>
       <c r="B523" t="n">
-        <v>31.63431358337402</v>
+        <v>31.63431167602539</v>
       </c>
       <c r="C523" t="n">
-        <v>31.83740595497857</v>
+        <v>31.83740403538475</v>
       </c>
       <c r="D523" t="n">
-        <v>30.62851484937437</v>
+        <v>30.62851300266902</v>
       </c>
       <c r="E523" t="n">
-        <v>30.76391101296931</v>
+        <v>30.76390915810044</v>
       </c>
       <c r="F523" t="n">
         <v>3472546</v>
@@ -10892,16 +10892,16 @@
         <v>44916</v>
       </c>
       <c r="B524" t="n">
-        <v>32.19524002075195</v>
+        <v>32.19523620605469</v>
       </c>
       <c r="C524" t="n">
-        <v>32.50471857745117</v>
+        <v>32.50471472608491</v>
       </c>
       <c r="D524" t="n">
-        <v>31.22812562087756</v>
+        <v>31.22812192077017</v>
       </c>
       <c r="E524" t="n">
-        <v>32.34997742531367</v>
+        <v>32.34997359228213</v>
       </c>
       <c r="F524" t="n">
         <v>3938295</v>
@@ -10912,16 +10912,16 @@
         <v>44917</v>
       </c>
       <c r="B525" t="n">
-        <v>32.0114860534668</v>
+        <v>32.01148986816406</v>
       </c>
       <c r="C525" t="n">
-        <v>32.78517675543017</v>
+        <v>32.78518066232546</v>
       </c>
       <c r="D525" t="n">
-        <v>31.5376013885634</v>
+        <v>31.53760514678948</v>
       </c>
       <c r="E525" t="n">
-        <v>32.41767451520204</v>
+        <v>32.41767837830338</v>
       </c>
       <c r="F525" t="n">
         <v>3822391</v>
@@ -10932,16 +10932,16 @@
         <v>44918</v>
       </c>
       <c r="B526" t="n">
-        <v>34.68072509765625</v>
+        <v>34.68072128295898</v>
       </c>
       <c r="C526" t="n">
-        <v>34.88381746754605</v>
+        <v>34.88381363050969</v>
       </c>
       <c r="D526" t="n">
-        <v>32.68846888482701</v>
+        <v>32.68846528926745</v>
       </c>
       <c r="E526" t="n">
-        <v>33.17202607250107</v>
+        <v>33.17202242375276</v>
       </c>
       <c r="F526" t="n">
         <v>6955860</v>
@@ -11012,16 +11012,16 @@
         <v>44924</v>
       </c>
       <c r="B530" t="n">
-        <v>36.50856399536133</v>
+        <v>36.50856781005859</v>
       </c>
       <c r="C530" t="n">
-        <v>37.23389970387844</v>
+        <v>37.23390359436439</v>
       </c>
       <c r="D530" t="n">
-        <v>35.61882215744662</v>
+        <v>35.61882587917678</v>
       </c>
       <c r="E530" t="n">
-        <v>35.87994196319169</v>
+        <v>35.87994571220566</v>
       </c>
       <c r="F530" t="n">
         <v>4887264</v>
@@ -11032,16 +11032,16 @@
         <v>44928</v>
       </c>
       <c r="B531" t="n">
-        <v>35.21263885498047</v>
+        <v>35.2126350402832</v>
       </c>
       <c r="C531" t="n">
-        <v>36.68265172299981</v>
+        <v>36.68264774905137</v>
       </c>
       <c r="D531" t="n">
-        <v>34.78710911009928</v>
+        <v>34.78710534150101</v>
       </c>
       <c r="E531" t="n">
-        <v>36.01534337329287</v>
+        <v>36.01533947163607</v>
       </c>
       <c r="F531" t="n">
         <v>2924313</v>
@@ -11152,16 +11152,16 @@
         <v>44936</v>
       </c>
       <c r="B537" t="n">
-        <v>37.79483413696289</v>
+        <v>37.79483032226562</v>
       </c>
       <c r="C537" t="n">
-        <v>38.07529521496675</v>
+        <v>38.07529137196207</v>
       </c>
       <c r="D537" t="n">
-        <v>36.49889993855829</v>
+        <v>36.49889625466188</v>
       </c>
       <c r="E537" t="n">
-        <v>37.09850831958851</v>
+        <v>37.0985045751726</v>
       </c>
       <c r="F537" t="n">
         <v>3183751</v>
@@ -11192,16 +11192,16 @@
         <v>44938</v>
       </c>
       <c r="B539" t="n">
-        <v>43.42343521118164</v>
+        <v>43.42343902587891</v>
       </c>
       <c r="C539" t="n">
-        <v>44.72904181410123</v>
+        <v>44.7290457434945</v>
       </c>
       <c r="D539" t="n">
-        <v>43.19132911953119</v>
+        <v>43.19133291383822</v>
       </c>
       <c r="E539" t="n">
-        <v>43.40409397377132</v>
+        <v>43.40409778676949</v>
       </c>
       <c r="F539" t="n">
         <v>7341055</v>
@@ -11212,16 +11212,16 @@
         <v>44939</v>
       </c>
       <c r="B540" t="n">
-        <v>42.75613021850586</v>
+        <v>42.75612640380859</v>
       </c>
       <c r="C540" t="n">
-        <v>43.50080726582102</v>
+        <v>43.50080338468374</v>
       </c>
       <c r="D540" t="n">
-        <v>42.35961420932546</v>
+        <v>42.35961043000531</v>
       </c>
       <c r="E540" t="n">
-        <v>43.42343856263282</v>
+        <v>43.42343468839838</v>
       </c>
       <c r="F540" t="n">
         <v>4249336</v>
@@ -11272,16 +11272,16 @@
         <v>44944</v>
       </c>
       <c r="B543" t="n">
-        <v>44.53562164306641</v>
+        <v>44.53561782836914</v>
       </c>
       <c r="C543" t="n">
-        <v>45.24161621271021</v>
+        <v>45.241612337541</v>
       </c>
       <c r="D543" t="n">
-        <v>43.22034619346439</v>
+        <v>43.220342491427</v>
       </c>
       <c r="E543" t="n">
-        <v>43.42343857092518</v>
+        <v>43.42343485149192</v>
       </c>
       <c r="F543" t="n">
         <v>6730959</v>
@@ -11332,16 +11332,16 @@
         <v>44949</v>
       </c>
       <c r="B546" t="n">
-        <v>46.45050811767578</v>
+        <v>46.45050430297852</v>
       </c>
       <c r="C546" t="n">
-        <v>48.53947429699662</v>
+        <v>48.53947031074529</v>
       </c>
       <c r="D546" t="n">
-        <v>45.88958222216792</v>
+        <v>45.88957845353607</v>
       </c>
       <c r="E546" t="n">
-        <v>47.67874234150205</v>
+        <v>47.67873842593739</v>
       </c>
       <c r="F546" t="n">
         <v>5971946</v>
@@ -11392,16 +11392,16 @@
         <v>44952</v>
       </c>
       <c r="B549" t="n">
-        <v>45.26095581054688</v>
+        <v>45.26095199584961</v>
       </c>
       <c r="C549" t="n">
-        <v>46.77932358255676</v>
+        <v>46.77931963988798</v>
       </c>
       <c r="D549" t="n">
-        <v>45.24161457234137</v>
+        <v>45.24161075927422</v>
       </c>
       <c r="E549" t="n">
-        <v>45.92826413060603</v>
+        <v>45.92826025966649</v>
       </c>
       <c r="F549" t="n">
         <v>3327082</v>
@@ -11412,16 +11412,16 @@
         <v>44953</v>
       </c>
       <c r="B550" t="n">
-        <v>44.5066032409668</v>
+        <v>44.50660705566406</v>
       </c>
       <c r="C550" t="n">
-        <v>46.34412192885299</v>
+        <v>46.34412590104548</v>
       </c>
       <c r="D550" t="n">
-        <v>44.16811098394805</v>
+        <v>44.16811476963287</v>
       </c>
       <c r="E550" t="n">
-        <v>46.20872577556058</v>
+        <v>46.20872973614816</v>
       </c>
       <c r="F550" t="n">
         <v>4035914</v>
@@ -11432,16 +11432,16 @@
         <v>44956</v>
       </c>
       <c r="B551" t="n">
-        <v>43.79094314575195</v>
+        <v>43.79093933105469</v>
       </c>
       <c r="C551" t="n">
-        <v>44.43890648207057</v>
+        <v>44.43890261092821</v>
       </c>
       <c r="D551" t="n">
-        <v>43.13330356893655</v>
+        <v>43.13329981152729</v>
       </c>
       <c r="E551" t="n">
-        <v>44.31318281197527</v>
+        <v>44.3131789517849</v>
       </c>
       <c r="F551" t="n">
         <v>3870439</v>
@@ -11572,16 +11572,16 @@
         <v>44965</v>
       </c>
       <c r="B558" t="n">
-        <v>43.12362670898438</v>
+        <v>43.12363052368164</v>
       </c>
       <c r="C558" t="n">
-        <v>43.13329920092593</v>
+        <v>43.13330301647882</v>
       </c>
       <c r="D558" t="n">
-        <v>42.08881622667597</v>
+        <v>42.08881994983436</v>
       </c>
       <c r="E558" t="n">
-        <v>42.57237336739773</v>
+        <v>42.57237713333137</v>
       </c>
       <c r="F558" t="n">
         <v>2757212</v>
@@ -11672,16 +11672,16 @@
         <v>44972</v>
       </c>
       <c r="B563" t="n">
-        <v>40.04821014404297</v>
+        <v>40.0482063293457</v>
       </c>
       <c r="C563" t="n">
-        <v>40.52209485081966</v>
+        <v>40.52209099098364</v>
       </c>
       <c r="D563" t="n">
-        <v>38.90701335343782</v>
+        <v>38.90700964744255</v>
       </c>
       <c r="E563" t="n">
-        <v>38.92635833968847</v>
+        <v>38.92635463185054</v>
       </c>
       <c r="F563" t="n">
         <v>3495706</v>
@@ -11752,16 +11752,16 @@
         <v>44980</v>
       </c>
       <c r="B567" t="n">
-        <v>38.00759887695312</v>
+        <v>38.00759506225586</v>
       </c>
       <c r="C567" t="n">
-        <v>39.07142321677222</v>
+        <v>39.07141929530241</v>
       </c>
       <c r="D567" t="n">
-        <v>37.73680654543994</v>
+        <v>37.7368027579212</v>
       </c>
       <c r="E567" t="n">
-        <v>37.95924390652058</v>
+        <v>37.95924009667655</v>
       </c>
       <c r="F567" t="n">
         <v>3548732</v>
@@ -11812,16 +11812,16 @@
         <v>44985</v>
       </c>
       <c r="B570" t="n">
-        <v>35.21263885498047</v>
+        <v>35.2126350402832</v>
       </c>
       <c r="C570" t="n">
-        <v>38.49115688632073</v>
+        <v>38.49115271645117</v>
       </c>
       <c r="D570" t="n">
-        <v>35.21263885498047</v>
+        <v>35.2126350402832</v>
       </c>
       <c r="E570" t="n">
-        <v>37.13719520026616</v>
+        <v>37.13719117707558</v>
       </c>
       <c r="F570" t="n">
         <v>11036876</v>
@@ -11832,16 +11832,16 @@
         <v>44986</v>
       </c>
       <c r="B571" t="n">
-        <v>31.52793121337891</v>
+        <v>31.52792930603027</v>
       </c>
       <c r="C571" t="n">
-        <v>35.21263762145776</v>
+        <v>35.21263549119504</v>
       </c>
       <c r="D571" t="n">
-        <v>29.89350662783602</v>
+        <v>29.89350481936535</v>
       </c>
       <c r="E571" t="n">
-        <v>35.10625518896411</v>
+        <v>35.10625306513723</v>
       </c>
       <c r="F571" t="n">
         <v>24633899</v>
@@ -11872,16 +11872,16 @@
         <v>44988</v>
       </c>
       <c r="B573" t="n">
-        <v>31.74069595336914</v>
+        <v>31.74069404602051</v>
       </c>
       <c r="C573" t="n">
-        <v>31.93411957920744</v>
+        <v>31.93411766023568</v>
       </c>
       <c r="D573" t="n">
-        <v>30.40607743217574</v>
+        <v>30.40607560502645</v>
       </c>
       <c r="E573" t="n">
-        <v>30.47377551384036</v>
+        <v>30.47377368262298</v>
       </c>
       <c r="F573" t="n">
         <v>7573675</v>
@@ -11892,16 +11892,16 @@
         <v>44991</v>
       </c>
       <c r="B574" t="n">
-        <v>31.86642074584961</v>
+        <v>31.86641883850098</v>
       </c>
       <c r="C574" t="n">
-        <v>32.34997795368473</v>
+        <v>32.34997601739302</v>
       </c>
       <c r="D574" t="n">
-        <v>30.94766317523564</v>
+        <v>30.94766132287878</v>
       </c>
       <c r="E574" t="n">
-        <v>31.74069707103675</v>
+        <v>31.74069517121325</v>
       </c>
       <c r="F574" t="n">
         <v>5963007</v>
@@ -11992,16 +11992,16 @@
         <v>44998</v>
       </c>
       <c r="B579" t="n">
-        <v>26.45058059692383</v>
+        <v>26.4505786895752</v>
       </c>
       <c r="C579" t="n">
-        <v>27.32098316598858</v>
+        <v>27.32098119587531</v>
       </c>
       <c r="D579" t="n">
-        <v>25.76392728704381</v>
+        <v>25.76392542920967</v>
       </c>
       <c r="E579" t="n">
-        <v>26.59564737946998</v>
+        <v>26.59564546166059</v>
       </c>
       <c r="F579" t="n">
         <v>13860726</v>
@@ -12032,16 +12032,16 @@
         <v>45000</v>
       </c>
       <c r="B581" t="n">
-        <v>26.28616905212402</v>
+        <v>26.28617095947266</v>
       </c>
       <c r="C581" t="n">
-        <v>26.82775179788365</v>
+        <v>26.82775374453002</v>
       </c>
       <c r="D581" t="n">
-        <v>25.62853138858268</v>
+        <v>25.62853324821252</v>
       </c>
       <c r="E581" t="n">
-        <v>26.58597321755539</v>
+        <v>26.58597514665809</v>
       </c>
       <c r="F581" t="n">
         <v>12174787</v>
@@ -12072,16 +12072,16 @@
         <v>45002</v>
       </c>
       <c r="B583" t="n">
-        <v>30.70588302612305</v>
+        <v>30.70588111877441</v>
       </c>
       <c r="C583" t="n">
-        <v>30.88963415624145</v>
+        <v>30.8896322374788</v>
       </c>
       <c r="D583" t="n">
-        <v>27.73684184447329</v>
+        <v>27.73684012155175</v>
       </c>
       <c r="E583" t="n">
-        <v>30.45443194157511</v>
+        <v>30.45443004984579</v>
       </c>
       <c r="F583" t="n">
         <v>23193684</v>
@@ -12092,16 +12092,16 @@
         <v>45005</v>
       </c>
       <c r="B584" t="n">
-        <v>29.79679489135742</v>
+        <v>29.79679679870605</v>
       </c>
       <c r="C584" t="n">
-        <v>31.20878203377826</v>
+        <v>31.20878403151084</v>
       </c>
       <c r="D584" t="n">
-        <v>29.32290834641774</v>
+        <v>29.32291022343201</v>
       </c>
       <c r="E584" t="n">
-        <v>30.70588175921954</v>
+        <v>30.70588372476053</v>
       </c>
       <c r="F584" t="n">
         <v>7729094</v>
@@ -12252,16 +12252,16 @@
         <v>45015</v>
       </c>
       <c r="B592" t="n">
-        <v>29.38093376159668</v>
+        <v>29.38093566894531</v>
       </c>
       <c r="C592" t="n">
-        <v>30.51245796745546</v>
+        <v>30.51245994826028</v>
       </c>
       <c r="D592" t="n">
-        <v>29.2745513361352</v>
+        <v>29.27455323657771</v>
       </c>
       <c r="E592" t="n">
-        <v>29.95153211069714</v>
+        <v>29.95153405508782</v>
       </c>
       <c r="F592" t="n">
         <v>5560645</v>
@@ -12312,16 +12312,16 @@
         <v>45020</v>
       </c>
       <c r="B595" t="n">
-        <v>27.92059135437012</v>
+        <v>27.92059326171875</v>
       </c>
       <c r="C595" t="n">
-        <v>29.70975320425825</v>
+        <v>29.70975523383049</v>
       </c>
       <c r="D595" t="n">
-        <v>27.91092073592187</v>
+        <v>27.91092264260987</v>
       </c>
       <c r="E595" t="n">
-        <v>29.57435705083184</v>
+        <v>29.57435907115471</v>
       </c>
       <c r="F595" t="n">
         <v>7552242</v>
@@ -12332,16 +12332,16 @@
         <v>45021</v>
       </c>
       <c r="B596" t="n">
-        <v>26.76972770690918</v>
+        <v>26.76972579956055</v>
       </c>
       <c r="C596" t="n">
-        <v>27.8528951326722</v>
+        <v>27.85289314814766</v>
       </c>
       <c r="D596" t="n">
-        <v>26.23781367622606</v>
+        <v>26.23781180677641</v>
       </c>
       <c r="E596" t="n">
-        <v>27.65947338188658</v>
+        <v>27.65947141114338</v>
       </c>
       <c r="F596" t="n">
         <v>12382825</v>
@@ -12372,16 +12372,16 @@
         <v>45026</v>
       </c>
       <c r="B598" t="n">
-        <v>29.6517276763916</v>
+        <v>29.65172576904297</v>
       </c>
       <c r="C598" t="n">
-        <v>29.83547880780963</v>
+        <v>29.8354768886412</v>
       </c>
       <c r="D598" t="n">
-        <v>28.19138549654949</v>
+        <v>28.19138368313743</v>
       </c>
       <c r="E598" t="n">
-        <v>28.33645227786835</v>
+        <v>28.33645045512486</v>
       </c>
       <c r="F598" t="n">
         <v>8774363</v>
@@ -12552,16 +12552,16 @@
         <v>45040</v>
       </c>
       <c r="B607" t="n">
-        <v>26.96700477600098</v>
+        <v>26.96700286865234</v>
       </c>
       <c r="C607" t="n">
-        <v>27.07506799883479</v>
+        <v>27.07506608384296</v>
       </c>
       <c r="D607" t="n">
-        <v>26.23020138729918</v>
+        <v>26.23019953206389</v>
       </c>
       <c r="E607" t="n">
-        <v>26.86876394941649</v>
+        <v>26.86876204901633</v>
       </c>
       <c r="F607" t="n">
         <v>6680100</v>
@@ -12572,16 +12572,16 @@
         <v>45041</v>
       </c>
       <c r="B608" t="n">
-        <v>27.21260261535645</v>
+        <v>27.21260452270508</v>
       </c>
       <c r="C608" t="n">
-        <v>27.45820371522866</v>
+        <v>27.45820563979163</v>
       </c>
       <c r="D608" t="n">
-        <v>26.42667797149275</v>
+        <v>26.42667982375542</v>
       </c>
       <c r="E608" t="n">
-        <v>26.79999269261962</v>
+        <v>26.79999457104816</v>
       </c>
       <c r="F608" t="n">
         <v>5323000</v>
@@ -12612,16 +12612,16 @@
         <v>45043</v>
       </c>
       <c r="B610" t="n">
-        <v>29.90439414978027</v>
+        <v>29.90439224243164</v>
       </c>
       <c r="C610" t="n">
-        <v>30.26788277330051</v>
+        <v>30.267880842768</v>
       </c>
       <c r="D610" t="n">
-        <v>26.73122612224756</v>
+        <v>26.73122441728851</v>
       </c>
       <c r="E610" t="n">
-        <v>26.73122612224756</v>
+        <v>26.73122441728851</v>
       </c>
       <c r="F610" t="n">
         <v>20933600</v>
@@ -12672,16 +12672,16 @@
         <v>45049</v>
       </c>
       <c r="B613" t="n">
-        <v>29.14794158935547</v>
+        <v>29.14793968200684</v>
       </c>
       <c r="C613" t="n">
-        <v>29.61949529963673</v>
+        <v>29.61949336143113</v>
       </c>
       <c r="D613" t="n">
-        <v>28.33254592932366</v>
+        <v>28.33254407533193</v>
       </c>
       <c r="E613" t="n">
-        <v>29.26583095381972</v>
+        <v>29.26582903875679</v>
       </c>
       <c r="F613" t="n">
         <v>9250000</v>
@@ -12692,16 +12692,16 @@
         <v>45050</v>
       </c>
       <c r="B614" t="n">
-        <v>29.27565383911133</v>
+        <v>29.2756519317627</v>
       </c>
       <c r="C614" t="n">
-        <v>29.95351348008578</v>
+        <v>29.95351152857367</v>
       </c>
       <c r="D614" t="n">
-        <v>29.17741488650197</v>
+        <v>29.17741298555374</v>
       </c>
       <c r="E614" t="n">
-        <v>29.47213549190587</v>
+        <v>29.47213357175619</v>
       </c>
       <c r="F614" t="n">
         <v>6670900</v>
@@ -12792,16 +12792,16 @@
         <v>45057</v>
       </c>
       <c r="B619" t="n">
-        <v>31.66289710998535</v>
+        <v>31.66289520263672</v>
       </c>
       <c r="C619" t="n">
-        <v>31.81025928645763</v>
+        <v>31.81025737023202</v>
       </c>
       <c r="D619" t="n">
-        <v>31.10292683551199</v>
+        <v>31.10292496189554</v>
       </c>
       <c r="E619" t="n">
-        <v>31.71201658628417</v>
+        <v>31.71201467597662</v>
       </c>
       <c r="F619" t="n">
         <v>4858000</v>
@@ -12812,16 +12812,16 @@
         <v>45058</v>
       </c>
       <c r="B620" t="n">
-        <v>32.49794387817383</v>
+        <v>32.49794006347656</v>
       </c>
       <c r="C620" t="n">
-        <v>32.64530231015733</v>
+        <v>32.64529847816273</v>
       </c>
       <c r="D620" t="n">
-        <v>31.46641611640984</v>
+        <v>31.46641242279611</v>
       </c>
       <c r="E620" t="n">
-        <v>31.55483267463029</v>
+        <v>31.554828970638</v>
       </c>
       <c r="F620" t="n">
         <v>5317000</v>
@@ -12852,16 +12852,16 @@
         <v>45062</v>
       </c>
       <c r="B622" t="n">
-        <v>29.90439414978027</v>
+        <v>29.90439224243164</v>
       </c>
       <c r="C622" t="n">
-        <v>32.08533151226543</v>
+        <v>32.08532946581322</v>
       </c>
       <c r="D622" t="n">
-        <v>29.70791249602647</v>
+        <v>29.70791060120974</v>
       </c>
       <c r="E622" t="n">
-        <v>31.86920131837866</v>
+        <v>31.86919928571158</v>
       </c>
       <c r="F622" t="n">
         <v>13269700</v>
@@ -12912,16 +12912,16 @@
         <v>45065</v>
       </c>
       <c r="B625" t="n">
-        <v>32.49794387817383</v>
+        <v>32.49794006347656</v>
       </c>
       <c r="C625" t="n">
-        <v>34.87536105853923</v>
+        <v>34.87535696477425</v>
       </c>
       <c r="D625" t="n">
-        <v>31.0439837395418</v>
+        <v>31.04398009551434</v>
       </c>
       <c r="E625" t="n">
-        <v>31.86920182661951</v>
+        <v>31.8691980857257</v>
       </c>
       <c r="F625" t="n">
         <v>19443700</v>
@@ -12972,16 +12972,16 @@
         <v>45070</v>
       </c>
       <c r="B628" t="n">
-        <v>31.48606109619141</v>
+        <v>31.48606300354004</v>
       </c>
       <c r="C628" t="n">
-        <v>31.86919822262693</v>
+        <v>31.86920015318507</v>
       </c>
       <c r="D628" t="n">
-        <v>30.46436146776744</v>
+        <v>30.464363313224</v>
       </c>
       <c r="E628" t="n">
-        <v>31.04398022887067</v>
+        <v>31.04398210943912</v>
       </c>
       <c r="F628" t="n">
         <v>7685200</v>
@@ -13212,16 +13212,16 @@
         <v>45089</v>
       </c>
       <c r="B640" t="n">
-        <v>31.26011085510254</v>
+        <v>31.26010894775391</v>
       </c>
       <c r="C640" t="n">
-        <v>31.86920059509758</v>
+        <v>31.86919865058509</v>
       </c>
       <c r="D640" t="n">
-        <v>30.47418800549994</v>
+        <v>30.47418614610471</v>
       </c>
       <c r="E640" t="n">
-        <v>31.61377707431765</v>
+        <v>31.61377514538992</v>
       </c>
       <c r="F640" t="n">
         <v>7223600</v>
@@ -13252,16 +13252,16 @@
         <v>45091</v>
       </c>
       <c r="B642" t="n">
-        <v>31.14222145080566</v>
+        <v>31.1422233581543</v>
       </c>
       <c r="C642" t="n">
-        <v>31.71201407641177</v>
+        <v>31.71201601865814</v>
       </c>
       <c r="D642" t="n">
-        <v>30.5724269514118</v>
+        <v>30.57242882386257</v>
       </c>
       <c r="E642" t="n">
-        <v>31.33870121423831</v>
+        <v>31.33870313362062</v>
       </c>
       <c r="F642" t="n">
         <v>8288400</v>
@@ -13292,16 +13292,16 @@
         <v>45093</v>
       </c>
       <c r="B644" t="n">
-        <v>31.9183235168457</v>
+        <v>31.91832160949707</v>
       </c>
       <c r="C644" t="n">
-        <v>31.9183235168457</v>
+        <v>31.91832160949707</v>
       </c>
       <c r="D644" t="n">
-        <v>31.19134254558997</v>
+        <v>31.19134068168367</v>
       </c>
       <c r="E644" t="n">
-        <v>31.4271193982454</v>
+        <v>31.42711752024974</v>
       </c>
       <c r="F644" t="n">
         <v>5722800</v>
@@ -13332,16 +13332,16 @@
         <v>45097</v>
       </c>
       <c r="B646" t="n">
-        <v>32.16392517089844</v>
+        <v>32.16392135620117</v>
       </c>
       <c r="C646" t="n">
-        <v>32.2916350584061</v>
+        <v>32.29163122856222</v>
       </c>
       <c r="D646" t="n">
-        <v>31.48606366340425</v>
+        <v>31.48605992910253</v>
       </c>
       <c r="E646" t="n">
-        <v>32.12462809124572</v>
+        <v>32.12462428120915</v>
       </c>
       <c r="F646" t="n">
         <v>4954700</v>
@@ -13352,16 +13352,16 @@
         <v>45098</v>
       </c>
       <c r="B647" t="n">
-        <v>32.06567764282227</v>
+        <v>32.06568145751953</v>
       </c>
       <c r="C647" t="n">
-        <v>32.36039820068254</v>
+        <v>32.36040205044127</v>
       </c>
       <c r="D647" t="n">
-        <v>31.4860589217478</v>
+        <v>31.48606266749066</v>
       </c>
       <c r="E647" t="n">
-        <v>32.1246232534244</v>
+        <v>32.12462707513414</v>
       </c>
       <c r="F647" t="n">
         <v>4670300</v>
@@ -13412,16 +13412,16 @@
         <v>45103</v>
       </c>
       <c r="B650" t="n">
-        <v>30.53312873840332</v>
+        <v>30.53313064575195</v>
       </c>
       <c r="C650" t="n">
-        <v>30.83767357835474</v>
+        <v>30.83767550472773</v>
       </c>
       <c r="D650" t="n">
-        <v>30.30717617565832</v>
+        <v>30.30717806889212</v>
       </c>
       <c r="E650" t="n">
-        <v>30.58224820898695</v>
+        <v>30.58225011940398</v>
       </c>
       <c r="F650" t="n">
         <v>2874500</v>
@@ -13452,16 +13452,16 @@
         <v>45105</v>
       </c>
       <c r="B652" t="n">
-        <v>29.37389373779297</v>
+        <v>29.37389183044434</v>
       </c>
       <c r="C652" t="n">
-        <v>30.06157762706682</v>
+        <v>30.06157567506449</v>
       </c>
       <c r="D652" t="n">
-        <v>29.30512572362315</v>
+        <v>29.30512382073987</v>
       </c>
       <c r="E652" t="n">
-        <v>29.75703276126285</v>
+        <v>29.75703082903567</v>
       </c>
       <c r="F652" t="n">
         <v>4532500</v>
@@ -13532,16 +13532,16 @@
         <v>45111</v>
       </c>
       <c r="B656" t="n">
-        <v>29.80615043640137</v>
+        <v>29.80615234375</v>
       </c>
       <c r="C656" t="n">
-        <v>30.15981662939312</v>
+        <v>30.15981855937348</v>
       </c>
       <c r="D656" t="n">
-        <v>29.57037359900278</v>
+        <v>29.57037549126363</v>
       </c>
       <c r="E656" t="n">
-        <v>29.80615043640137</v>
+        <v>29.80615234375</v>
       </c>
       <c r="F656" t="n">
         <v>2514900</v>
@@ -13552,16 +13552,16 @@
         <v>45112</v>
       </c>
       <c r="B657" t="n">
-        <v>30.40541839599609</v>
+        <v>30.40542030334473</v>
       </c>
       <c r="C657" t="n">
-        <v>30.70996325002402</v>
+        <v>30.70996517647691</v>
       </c>
       <c r="D657" t="n">
-        <v>29.34442166777476</v>
+        <v>29.34442350856649</v>
       </c>
       <c r="E657" t="n">
-        <v>29.60966944448926</v>
+        <v>29.60967130192012</v>
       </c>
       <c r="F657" t="n">
         <v>5394800</v>
@@ -13612,16 +13612,16 @@
         <v>45117</v>
       </c>
       <c r="B660" t="n">
-        <v>31.07345199584961</v>
+        <v>31.07345390319824</v>
       </c>
       <c r="C660" t="n">
-        <v>31.93796708924193</v>
+        <v>31.93796904965617</v>
       </c>
       <c r="D660" t="n">
-        <v>30.84749942157282</v>
+        <v>30.84750131505205</v>
       </c>
       <c r="E660" t="n">
-        <v>31.56465609569361</v>
+        <v>31.56465803319331</v>
       </c>
       <c r="F660" t="n">
         <v>7339200</v>
@@ -13652,16 +13652,16 @@
         <v>45119</v>
       </c>
       <c r="B662" t="n">
-        <v>31.07345199584961</v>
+        <v>31.07345390319824</v>
       </c>
       <c r="C662" t="n">
-        <v>32.08532925608902</v>
+        <v>32.08533122554864</v>
       </c>
       <c r="D662" t="n">
-        <v>31.04398106151042</v>
+        <v>31.04398296705007</v>
       </c>
       <c r="E662" t="n">
-        <v>31.77096013121909</v>
+        <v>31.77096208138212</v>
       </c>
       <c r="F662" t="n">
         <v>4503800</v>
@@ -13732,16 +13732,16 @@
         <v>45125</v>
       </c>
       <c r="B666" t="n">
-        <v>32.91055297851562</v>
+        <v>32.91054916381836</v>
       </c>
       <c r="C666" t="n">
-        <v>33.03826662148488</v>
+        <v>33.03826279198419</v>
       </c>
       <c r="D666" t="n">
-        <v>32.03621351392245</v>
+        <v>32.0362098005708</v>
       </c>
       <c r="E666" t="n">
-        <v>32.18357195035527</v>
+        <v>32.18356821992315</v>
       </c>
       <c r="F666" t="n">
         <v>4775600</v>
@@ -13752,16 +13752,16 @@
         <v>45126</v>
       </c>
       <c r="B667" t="n">
-        <v>33.6473503112793</v>
+        <v>33.64735412597656</v>
       </c>
       <c r="C667" t="n">
-        <v>34.04031356576963</v>
+        <v>34.04031742501827</v>
       </c>
       <c r="D667" t="n">
-        <v>33.04808303459044</v>
+        <v>33.04808678134705</v>
       </c>
       <c r="E667" t="n">
-        <v>33.04808303459044</v>
+        <v>33.04808678134705</v>
       </c>
       <c r="F667" t="n">
         <v>7484200</v>
@@ -13772,16 +13772,16 @@
         <v>45127</v>
       </c>
       <c r="B668" t="n">
-        <v>33.92242813110352</v>
+        <v>33.92242431640625</v>
       </c>
       <c r="C668" t="n">
-        <v>34.11890979188617</v>
+        <v>34.11890595509385</v>
       </c>
       <c r="D668" t="n">
-        <v>33.64735605455338</v>
+        <v>33.64735227078894</v>
       </c>
       <c r="E668" t="n">
-        <v>33.91260573447357</v>
+        <v>33.91260192088087</v>
       </c>
       <c r="F668" t="n">
         <v>3587900</v>
@@ -13952,16 +13952,16 @@
         <v>45140</v>
       </c>
       <c r="B677" t="n">
-        <v>34.4431037902832</v>
+        <v>34.44309997558594</v>
       </c>
       <c r="C677" t="n">
-        <v>34.5806398233511</v>
+        <v>34.58063599342123</v>
       </c>
       <c r="D677" t="n">
-        <v>33.71612279718397</v>
+        <v>33.71611906300245</v>
       </c>
       <c r="E677" t="n">
-        <v>34.38415817000732</v>
+        <v>34.38415436183849</v>
       </c>
       <c r="F677" t="n">
         <v>3408800</v>
@@ -14012,16 +14012,16 @@
         <v>45145</v>
       </c>
       <c r="B680" t="n">
-        <v>35.68092727661133</v>
+        <v>35.68093109130859</v>
       </c>
       <c r="C680" t="n">
-        <v>36.15248093584172</v>
+        <v>36.15248480095344</v>
       </c>
       <c r="D680" t="n">
-        <v>35.09148613946717</v>
+        <v>35.09148989114647</v>
       </c>
       <c r="E680" t="n">
-        <v>36.05424199550948</v>
+        <v>36.05424585011833</v>
       </c>
       <c r="F680" t="n">
         <v>3820600</v>
@@ -14032,16 +14032,16 @@
         <v>45146</v>
       </c>
       <c r="B681" t="n">
-        <v>36.34896469116211</v>
+        <v>36.34896850585938</v>
       </c>
       <c r="C681" t="n">
-        <v>36.51597164901496</v>
+        <v>36.51597548123902</v>
       </c>
       <c r="D681" t="n">
-        <v>34.30556163401185</v>
+        <v>34.30556523426109</v>
       </c>
       <c r="E681" t="n">
-        <v>34.76729292525891</v>
+        <v>34.76729657396523</v>
       </c>
       <c r="F681" t="n">
         <v>5274900</v>
@@ -14172,16 +14172,16 @@
         <v>45155</v>
       </c>
       <c r="B688" t="n">
-        <v>31.26993370056152</v>
+        <v>31.26993560791016</v>
       </c>
       <c r="C688" t="n">
-        <v>31.74148926263102</v>
+        <v>31.74149119874277</v>
       </c>
       <c r="D688" t="n">
-        <v>30.9653888444364</v>
+        <v>30.96539073320894</v>
       </c>
       <c r="E688" t="n">
-        <v>31.46641346711834</v>
+        <v>31.4664153864515</v>
       </c>
       <c r="F688" t="n">
         <v>4529600</v>
@@ -14252,16 +14252,16 @@
         <v>45161</v>
       </c>
       <c r="B692" t="n">
-        <v>31.05380630493164</v>
+        <v>31.05380439758301</v>
       </c>
       <c r="C692" t="n">
-        <v>31.2404618075605</v>
+        <v>31.24045988874735</v>
       </c>
       <c r="D692" t="n">
-        <v>30.68049155209822</v>
+        <v>30.68048966767887</v>
       </c>
       <c r="E692" t="n">
-        <v>31.09310150987904</v>
+        <v>31.09309960011686</v>
       </c>
       <c r="F692" t="n">
         <v>4847400</v>
@@ -14272,16 +14272,16 @@
         <v>45162</v>
       </c>
       <c r="B693" t="n">
-        <v>30.91626930236816</v>
+        <v>30.91626739501953</v>
       </c>
       <c r="C693" t="n">
-        <v>31.30923260599883</v>
+        <v>31.30923067440671</v>
       </c>
       <c r="D693" t="n">
-        <v>30.56260495240363</v>
+        <v>30.56260306687397</v>
       </c>
       <c r="E693" t="n">
-        <v>31.05380720815405</v>
+        <v>31.05380529232016</v>
       </c>
       <c r="F693" t="n">
         <v>3471700</v>
@@ -14332,16 +14332,16 @@
         <v>45167</v>
       </c>
       <c r="B696" t="n">
-        <v>31.29940795898438</v>
+        <v>31.29940605163574</v>
       </c>
       <c r="C696" t="n">
-        <v>31.55483147996431</v>
+        <v>31.55482955705047</v>
       </c>
       <c r="D696" t="n">
-        <v>30.63137259940515</v>
+        <v>30.63137073276579</v>
       </c>
       <c r="E696" t="n">
-        <v>31.06363110391898</v>
+        <v>31.06362921093831</v>
       </c>
       <c r="F696" t="n">
         <v>3743200</v>
@@ -14352,16 +14352,16 @@
         <v>45168</v>
       </c>
       <c r="B697" t="n">
-        <v>31.6334228515625</v>
+        <v>31.63342475891113</v>
       </c>
       <c r="C697" t="n">
-        <v>31.70219086067396</v>
+        <v>31.70219277216898</v>
       </c>
       <c r="D697" t="n">
-        <v>30.96538755084366</v>
+        <v>30.96538941791287</v>
       </c>
       <c r="E697" t="n">
-        <v>31.49588683333958</v>
+        <v>31.49588873239543</v>
       </c>
       <c r="F697" t="n">
         <v>3276100</v>
@@ -14412,16 +14412,16 @@
         <v>45173</v>
       </c>
       <c r="B700" t="n">
-        <v>32.2719841003418</v>
+        <v>32.27198791503906</v>
       </c>
       <c r="C700" t="n">
-        <v>32.55688228511206</v>
+        <v>32.55688613348561</v>
       </c>
       <c r="D700" t="n">
-        <v>32.06568006898767</v>
+        <v>32.06568385929886</v>
       </c>
       <c r="E700" t="n">
-        <v>32.22286462824446</v>
+        <v>32.22286843713558</v>
       </c>
       <c r="F700" t="n">
         <v>2652900</v>
@@ -14432,16 +14432,16 @@
         <v>45174</v>
       </c>
       <c r="B701" t="n">
-        <v>32.63547515869141</v>
+        <v>32.63547897338867</v>
       </c>
       <c r="C701" t="n">
-        <v>32.93019572729314</v>
+        <v>32.93019957643972</v>
       </c>
       <c r="D701" t="n">
-        <v>32.07550495407551</v>
+        <v>32.07550870331895</v>
       </c>
       <c r="E701" t="n">
-        <v>32.27198283475976</v>
+        <v>32.27198660696912</v>
       </c>
       <c r="F701" t="n">
         <v>6036900</v>
@@ -14452,16 +14452,16 @@
         <v>45175</v>
       </c>
       <c r="B702" t="n">
-        <v>32.00674057006836</v>
+        <v>32.00673675537109</v>
       </c>
       <c r="C702" t="n">
-        <v>32.71406926527997</v>
+        <v>32.71406536628031</v>
       </c>
       <c r="D702" t="n">
-        <v>31.92814641083608</v>
+        <v>31.928142605506</v>
       </c>
       <c r="E702" t="n">
-        <v>32.65512739343153</v>
+        <v>32.65512350145682</v>
       </c>
       <c r="F702" t="n">
         <v>4505300</v>
@@ -14512,16 +14512,16 @@
         <v>45181</v>
       </c>
       <c r="B705" t="n">
-        <v>32.3309326171875</v>
+        <v>32.33092880249023</v>
       </c>
       <c r="C705" t="n">
-        <v>32.6453017639165</v>
+        <v>32.64529791212711</v>
       </c>
       <c r="D705" t="n">
-        <v>31.76113994408213</v>
+        <v>31.76113619661418</v>
       </c>
       <c r="E705" t="n">
-        <v>31.97726639022342</v>
+        <v>31.97726261725491</v>
       </c>
       <c r="F705" t="n">
         <v>3620500</v>
@@ -14532,16 +14532,16 @@
         <v>45182</v>
       </c>
       <c r="B706" t="n">
-        <v>31.6334228515625</v>
+        <v>31.63342475891113</v>
       </c>
       <c r="C706" t="n">
-        <v>32.11479891534272</v>
+        <v>32.1148008517161</v>
       </c>
       <c r="D706" t="n">
-        <v>31.44676361462388</v>
+        <v>31.44676551071783</v>
       </c>
       <c r="E706" t="n">
-        <v>31.60394817081799</v>
+        <v>31.60395007638945</v>
       </c>
       <c r="F706" t="n">
         <v>7302700</v>
@@ -14552,16 +14552,16 @@
         <v>45183</v>
       </c>
       <c r="B707" t="n">
-        <v>32.311279296875</v>
+        <v>32.31128311157227</v>
       </c>
       <c r="C707" t="n">
-        <v>32.311279296875</v>
+        <v>32.31128311157227</v>
       </c>
       <c r="D707" t="n">
-        <v>31.74148670806588</v>
+        <v>31.74149045549294</v>
       </c>
       <c r="E707" t="n">
-        <v>31.83972564654409</v>
+        <v>31.83972940556933</v>
       </c>
       <c r="F707" t="n">
         <v>4362300</v>
@@ -14592,16 +14592,16 @@
         <v>45187</v>
       </c>
       <c r="B709" t="n">
-        <v>31.98709297180176</v>
+        <v>31.98709106445312</v>
       </c>
       <c r="C709" t="n">
-        <v>32.71407022822005</v>
+        <v>32.7140682775227</v>
       </c>
       <c r="D709" t="n">
-        <v>31.75131423474054</v>
+        <v>31.75131234145109</v>
       </c>
       <c r="E709" t="n">
-        <v>32.55688565270453</v>
+        <v>32.5568837113799</v>
       </c>
       <c r="F709" t="n">
         <v>5099000</v>
@@ -14692,16 +14692,16 @@
         <v>45194</v>
       </c>
       <c r="B714" t="n">
-        <v>30.95556640625</v>
+        <v>30.95556449890137</v>
       </c>
       <c r="C714" t="n">
-        <v>31.20116753431566</v>
+        <v>31.20116561183414</v>
       </c>
       <c r="D714" t="n">
-        <v>29.99281043394172</v>
+        <v>29.99280858591396</v>
       </c>
       <c r="E714" t="n">
-        <v>30.45453988014151</v>
+        <v>30.45453800366397</v>
       </c>
       <c r="F714" t="n">
         <v>6350700</v>
@@ -14712,16 +14712,16 @@
         <v>45195</v>
       </c>
       <c r="B715" t="n">
-        <v>30.32682800292969</v>
+        <v>30.32682609558105</v>
       </c>
       <c r="C715" t="n">
-        <v>30.83767692328888</v>
+        <v>30.83767498381136</v>
       </c>
       <c r="D715" t="n">
-        <v>30.19911436749897</v>
+        <v>30.19911246818264</v>
       </c>
       <c r="E715" t="n">
-        <v>30.75908463755763</v>
+        <v>30.75908270302303</v>
       </c>
       <c r="F715" t="n">
         <v>3433500</v>
@@ -14732,16 +14732,16 @@
         <v>45196</v>
       </c>
       <c r="B716" t="n">
-        <v>30.86714744567871</v>
+        <v>30.86714935302734</v>
       </c>
       <c r="C716" t="n">
-        <v>31.07345147776449</v>
+        <v>31.0734533978611</v>
       </c>
       <c r="D716" t="n">
-        <v>30.42506470008381</v>
+        <v>30.42506658011519</v>
       </c>
       <c r="E716" t="n">
-        <v>30.65101914438107</v>
+        <v>30.65102103837466</v>
       </c>
       <c r="F716" t="n">
         <v>4307600</v>
@@ -14752,16 +14752,16 @@
         <v>45197</v>
       </c>
       <c r="B717" t="n">
-        <v>30.58225059509277</v>
+        <v>30.58224868774414</v>
       </c>
       <c r="C717" t="n">
-        <v>31.21099073558775</v>
+        <v>31.21098878902595</v>
       </c>
       <c r="D717" t="n">
-        <v>30.41524175877521</v>
+        <v>30.41523986184255</v>
       </c>
       <c r="E717" t="n">
-        <v>30.82785171474873</v>
+        <v>30.82784979208249</v>
       </c>
       <c r="F717" t="n">
         <v>4298000</v>
@@ -14772,16 +14772,16 @@
         <v>45198</v>
       </c>
       <c r="B718" t="n">
-        <v>31.02433204650879</v>
+        <v>31.02433395385742</v>
       </c>
       <c r="C718" t="n">
-        <v>31.60394894047274</v>
+        <v>31.60395088345571</v>
       </c>
       <c r="D718" t="n">
-        <v>30.47418608643163</v>
+        <v>30.47418795995777</v>
       </c>
       <c r="E718" t="n">
-        <v>30.86714748648674</v>
+        <v>30.86714938417181</v>
       </c>
       <c r="F718" t="n">
         <v>5846000</v>
@@ -14852,16 +14852,16 @@
         <v>45204</v>
       </c>
       <c r="B722" t="n">
-        <v>28.0378246307373</v>
+        <v>28.03782272338867</v>
       </c>
       <c r="C722" t="n">
-        <v>28.78445038319864</v>
+        <v>28.78444842505877</v>
       </c>
       <c r="D722" t="n">
-        <v>27.72345362458937</v>
+        <v>27.72345173862667</v>
       </c>
       <c r="E722" t="n">
-        <v>28.62726581701858</v>
+        <v>28.62726386957162</v>
       </c>
       <c r="F722" t="n">
         <v>8409300</v>
@@ -14912,16 +14912,16 @@
         <v>45209</v>
       </c>
       <c r="B725" t="n">
-        <v>30.2777042388916</v>
+        <v>30.27770614624023</v>
       </c>
       <c r="C725" t="n">
-        <v>30.40541786413846</v>
+        <v>30.40541977953243</v>
       </c>
       <c r="D725" t="n">
-        <v>29.43283582930937</v>
+        <v>29.43283768343539</v>
       </c>
       <c r="E725" t="n">
-        <v>29.7570310901109</v>
+        <v>29.75703296465965</v>
       </c>
       <c r="F725" t="n">
         <v>7018100</v>
@@ -14972,16 +14972,16 @@
         <v>45215</v>
       </c>
       <c r="B728" t="n">
-        <v>31.67272186279297</v>
+        <v>31.67271995544434</v>
       </c>
       <c r="C728" t="n">
-        <v>32.01656192935982</v>
+        <v>32.01656000130495</v>
       </c>
       <c r="D728" t="n">
-        <v>31.32887804865046</v>
+        <v>31.32887616200829</v>
       </c>
       <c r="E728" t="n">
-        <v>31.91832298107662</v>
+        <v>31.91832105893775</v>
       </c>
       <c r="F728" t="n">
         <v>3741500</v>
@@ -15012,16 +15012,16 @@
         <v>45217</v>
       </c>
       <c r="B730" t="n">
-        <v>32.06567764282227</v>
+        <v>32.06568145751953</v>
       </c>
       <c r="C730" t="n">
-        <v>33.06773053760736</v>
+        <v>33.06773447151397</v>
       </c>
       <c r="D730" t="n">
-        <v>31.63342107446555</v>
+        <v>31.63342483773936</v>
       </c>
       <c r="E730" t="n">
-        <v>32.52740889026767</v>
+        <v>32.52741275989484</v>
       </c>
       <c r="F730" t="n">
         <v>7439800</v>
@@ -15132,16 +15132,16 @@
         <v>45225</v>
       </c>
       <c r="B736" t="n">
-        <v>31.98709297180176</v>
+        <v>31.98709106445312</v>
       </c>
       <c r="C736" t="n">
-        <v>32.12462900693085</v>
+        <v>32.12462709138111</v>
       </c>
       <c r="D736" t="n">
-        <v>31.19134395024304</v>
+        <v>31.19134209034388</v>
       </c>
       <c r="E736" t="n">
-        <v>31.57448111883861</v>
+        <v>31.57447923609348</v>
       </c>
       <c r="F736" t="n">
         <v>2923500</v>
@@ -15152,16 +15152,16 @@
         <v>45226</v>
       </c>
       <c r="B737" t="n">
-        <v>31.52536010742188</v>
+        <v>31.52535820007324</v>
       </c>
       <c r="C737" t="n">
-        <v>32.55688406826494</v>
+        <v>32.556882098507</v>
       </c>
       <c r="D737" t="n">
-        <v>31.24046190704763</v>
+        <v>31.24046001693592</v>
       </c>
       <c r="E737" t="n">
-        <v>32.32110909025403</v>
+        <v>32.32110713476096</v>
       </c>
       <c r="F737" t="n">
         <v>3378100</v>
@@ -15172,16 +15172,16 @@
         <v>45229</v>
       </c>
       <c r="B738" t="n">
-        <v>31.07345199584961</v>
+        <v>31.07345390319824</v>
       </c>
       <c r="C738" t="n">
-        <v>32.11480019042821</v>
+        <v>32.11480216169681</v>
       </c>
       <c r="D738" t="n">
-        <v>30.98503731904426</v>
+        <v>30.98503922096583</v>
       </c>
       <c r="E738" t="n">
-        <v>31.5450075569423</v>
+        <v>31.54500949323592</v>
       </c>
       <c r="F738" t="n">
         <v>3227500</v>
@@ -15192,16 +15192,16 @@
         <v>45230</v>
       </c>
       <c r="B739" t="n">
-        <v>31.86919975280762</v>
+        <v>31.86919784545898</v>
       </c>
       <c r="C739" t="n">
-        <v>32.10497847524474</v>
+        <v>32.10497655378492</v>
       </c>
       <c r="D739" t="n">
-        <v>31.2011662851952</v>
+        <v>31.20116441782789</v>
       </c>
       <c r="E739" t="n">
-        <v>31.2011662851952</v>
+        <v>31.20116441782789</v>
       </c>
       <c r="F739" t="n">
         <v>3372100</v>
@@ -15212,16 +15212,16 @@
         <v>45231</v>
       </c>
       <c r="B740" t="n">
-        <v>32.06567764282227</v>
+        <v>32.06568145751953</v>
       </c>
       <c r="C740" t="n">
-        <v>32.74353904823363</v>
+        <v>32.74354294357276</v>
       </c>
       <c r="D740" t="n">
-        <v>31.9477901691932</v>
+        <v>31.94779396986597</v>
       </c>
       <c r="E740" t="n">
-        <v>32.07550378504357</v>
+        <v>32.0755076009098</v>
       </c>
       <c r="F740" t="n">
         <v>4282500</v>
@@ -15232,16 +15232,16 @@
         <v>45233</v>
       </c>
       <c r="B741" t="n">
-        <v>32.69441986083984</v>
+        <v>32.69441604614258</v>
       </c>
       <c r="C741" t="n">
-        <v>32.94984712401398</v>
+        <v>32.94984327951414</v>
       </c>
       <c r="D741" t="n">
-        <v>32.46846728038622</v>
+        <v>32.4684634920525</v>
       </c>
       <c r="E741" t="n">
-        <v>32.73371693941674</v>
+        <v>32.7337131201344</v>
       </c>
       <c r="F741" t="n">
         <v>3190300</v>
@@ -15272,16 +15272,16 @@
         <v>45237</v>
       </c>
       <c r="B743" t="n">
-        <v>32.48811721801758</v>
+        <v>32.48811340332031</v>
       </c>
       <c r="C743" t="n">
-        <v>32.63547939523581</v>
+        <v>32.63547556323554</v>
       </c>
       <c r="D743" t="n">
-        <v>31.81025944748058</v>
+        <v>31.81025571237618</v>
       </c>
       <c r="E743" t="n">
-        <v>31.8790274641622</v>
+        <v>31.87902372098318</v>
       </c>
       <c r="F743" t="n">
         <v>3324000</v>
@@ -15312,16 +15312,16 @@
         <v>45239</v>
       </c>
       <c r="B745" t="n">
-        <v>30.81802749633789</v>
+        <v>30.81802940368652</v>
       </c>
       <c r="C745" t="n">
-        <v>33.77506502697286</v>
+        <v>33.77506711733456</v>
       </c>
       <c r="D745" t="n">
-        <v>30.67066533422895</v>
+        <v>30.67066723245724</v>
       </c>
       <c r="E745" t="n">
-        <v>33.41157269312426</v>
+        <v>33.41157476098916</v>
       </c>
       <c r="F745" t="n">
         <v>15431300</v>
@@ -15332,16 +15332,16 @@
         <v>45240</v>
       </c>
       <c r="B746" t="n">
-        <v>31.25028610229492</v>
+        <v>31.25028419494629</v>
       </c>
       <c r="C746" t="n">
-        <v>32.06568174882637</v>
+        <v>32.06567979171039</v>
       </c>
       <c r="D746" t="n">
-        <v>31.04398206013306</v>
+        <v>31.04398016537612</v>
       </c>
       <c r="E746" t="n">
-        <v>31.05380632982475</v>
+        <v>31.05380443446818</v>
       </c>
       <c r="F746" t="n">
         <v>4738300</v>
@@ -15352,16 +15352,16 @@
         <v>45243</v>
       </c>
       <c r="B747" t="n">
-        <v>30.94573974609375</v>
+        <v>30.94574165344238</v>
       </c>
       <c r="C747" t="n">
-        <v>31.41729342584897</v>
+        <v>31.41729536226194</v>
       </c>
       <c r="D747" t="n">
-        <v>30.67066582934266</v>
+        <v>30.67066771973704</v>
       </c>
       <c r="E747" t="n">
-        <v>31.21098939362647</v>
+        <v>31.21099131732383</v>
       </c>
       <c r="F747" t="n">
         <v>3172300</v>
@@ -15392,16 +15392,16 @@
         <v>45246</v>
       </c>
       <c r="B749" t="n">
-        <v>31.13239860534668</v>
+        <v>31.13239669799805</v>
       </c>
       <c r="C749" t="n">
-        <v>32.13444975439192</v>
+        <v>32.13444778565191</v>
       </c>
       <c r="D749" t="n">
-        <v>30.68049156858774</v>
+        <v>30.68048968892551</v>
       </c>
       <c r="E749" t="n">
-        <v>31.78078354073604</v>
+        <v>31.78078159366364</v>
       </c>
       <c r="F749" t="n">
         <v>5148500</v>
@@ -15492,16 +15492,16 @@
         <v>45253</v>
       </c>
       <c r="B754" t="n">
-        <v>31.81025505065918</v>
+        <v>31.81025886535645</v>
       </c>
       <c r="C754" t="n">
-        <v>32.00673667726713</v>
+        <v>32.00674051552654</v>
       </c>
       <c r="D754" t="n">
-        <v>31.5843024917114</v>
+        <v>31.58430627931235</v>
       </c>
       <c r="E754" t="n">
-        <v>31.82990358807751</v>
+        <v>31.82990740513103</v>
       </c>
       <c r="F754" t="n">
         <v>2086300</v>
@@ -15552,16 +15552,16 @@
         <v>45258</v>
       </c>
       <c r="B757" t="n">
-        <v>29.80615043640137</v>
+        <v>29.80615234375</v>
       </c>
       <c r="C757" t="n">
-        <v>30.21876037029583</v>
+        <v>30.21876230404811</v>
       </c>
       <c r="D757" t="n">
-        <v>29.63914160902057</v>
+        <v>29.63914350568201</v>
       </c>
       <c r="E757" t="n">
-        <v>30.17946329383553</v>
+        <v>30.17946522507312</v>
       </c>
       <c r="F757" t="n">
         <v>5777500</v>
@@ -15592,16 +15592,16 @@
         <v>45260</v>
       </c>
       <c r="B759" t="n">
-        <v>29.45248603820801</v>
+        <v>29.45248413085938</v>
       </c>
       <c r="C759" t="n">
-        <v>29.83562506189301</v>
+        <v>29.83562312973222</v>
       </c>
       <c r="D759" t="n">
-        <v>29.1774139813743</v>
+        <v>29.17741209183939</v>
       </c>
       <c r="E759" t="n">
-        <v>29.66861622433489</v>
+        <v>29.66861430298963</v>
       </c>
       <c r="F759" t="n">
         <v>4483800</v>
@@ -15732,16 +15732,16 @@
         <v>45271</v>
       </c>
       <c r="B766" t="n">
-        <v>26.91788101196289</v>
+        <v>26.91788291931152</v>
       </c>
       <c r="C766" t="n">
-        <v>27.08488984004369</v>
+        <v>27.08489175922624</v>
       </c>
       <c r="D766" t="n">
-        <v>26.48562253802652</v>
+        <v>26.48562441474616</v>
       </c>
       <c r="E766" t="n">
-        <v>26.96700235774415</v>
+        <v>26.96700426857343</v>
       </c>
       <c r="F766" t="n">
         <v>6627000</v>
@@ -15792,16 +15792,16 @@
         <v>45274</v>
       </c>
       <c r="B769" t="n">
-        <v>27.00629997253418</v>
+        <v>27.00629806518555</v>
       </c>
       <c r="C769" t="n">
-        <v>27.20278162563166</v>
+        <v>27.2027797044063</v>
       </c>
       <c r="D769" t="n">
-        <v>26.49544917351107</v>
+        <v>26.49544730224182</v>
       </c>
       <c r="E769" t="n">
-        <v>26.82946685950403</v>
+        <v>26.82946496464443</v>
       </c>
       <c r="F769" t="n">
         <v>14011300</v>
@@ -15812,16 +15812,16 @@
         <v>45275</v>
       </c>
       <c r="B770" t="n">
-        <v>25.8863582611084</v>
+        <v>25.88635635375977</v>
       </c>
       <c r="C770" t="n">
-        <v>27.21260467558413</v>
+        <v>27.21260267051552</v>
       </c>
       <c r="D770" t="n">
-        <v>25.8863582611084</v>
+        <v>25.88635635375977</v>
       </c>
       <c r="E770" t="n">
-        <v>27.16348332761816</v>
+        <v>27.1634813261689</v>
       </c>
       <c r="F770" t="n">
         <v>11924000</v>
@@ -15832,16 +15832,16 @@
         <v>45278</v>
       </c>
       <c r="B771" t="n">
-        <v>26.21055221557617</v>
+        <v>26.21055030822754</v>
       </c>
       <c r="C771" t="n">
-        <v>26.76069820788825</v>
+        <v>26.76069626050536</v>
       </c>
       <c r="D771" t="n">
-        <v>25.94530255232668</v>
+        <v>25.94530066428034</v>
       </c>
       <c r="E771" t="n">
-        <v>26.12213566115967</v>
+        <v>26.12213376024514</v>
       </c>
       <c r="F771" t="n">
         <v>4958200</v>
@@ -15852,16 +15852,16 @@
         <v>45279</v>
       </c>
       <c r="B772" t="n">
-        <v>26.32843780517578</v>
+        <v>26.32843971252441</v>
       </c>
       <c r="C772" t="n">
-        <v>26.52491943942738</v>
+        <v>26.52492136101001</v>
       </c>
       <c r="D772" t="n">
-        <v>26.13195804471192</v>
+        <v>26.13195993782669</v>
       </c>
       <c r="E772" t="n">
-        <v>26.30879114078081</v>
+        <v>26.30879304670615</v>
       </c>
       <c r="F772" t="n">
         <v>3900900</v>
@@ -15872,16 +15872,16 @@
         <v>45280</v>
       </c>
       <c r="B773" t="n">
-        <v>25.85688400268555</v>
+        <v>25.85688591003418</v>
       </c>
       <c r="C773" t="n">
-        <v>26.54456784535201</v>
+        <v>26.54456980342805</v>
       </c>
       <c r="D773" t="n">
-        <v>25.68987517654013</v>
+        <v>25.68987707156926</v>
       </c>
       <c r="E773" t="n">
-        <v>26.54456784535201</v>
+        <v>26.54456980342805</v>
       </c>
       <c r="F773" t="n">
         <v>6168300</v>
@@ -15912,16 +15912,16 @@
         <v>45282</v>
       </c>
       <c r="B775" t="n">
-        <v>25.95512771606445</v>
+        <v>25.95512580871582</v>
       </c>
       <c r="C775" t="n">
-        <v>26.22037738844958</v>
+        <v>26.2203754616087</v>
       </c>
       <c r="D775" t="n">
-        <v>25.79794314141873</v>
+        <v>25.79794124562103</v>
       </c>
       <c r="E775" t="n">
-        <v>26.03372000338731</v>
+        <v>26.03371809026321</v>
       </c>
       <c r="F775" t="n">
         <v>3644200</v>
@@ -16012,16 +16012,16 @@
         <v>45294</v>
       </c>
       <c r="B780" t="n">
-        <v>25.8863582611084</v>
+        <v>25.88635635375977</v>
       </c>
       <c r="C780" t="n">
-        <v>26.28914394549015</v>
+        <v>26.28914200846361</v>
       </c>
       <c r="D780" t="n">
-        <v>25.35585894580298</v>
+        <v>25.35585707754239</v>
       </c>
       <c r="E780" t="n">
-        <v>25.64075714264207</v>
+        <v>25.64075525338972</v>
       </c>
       <c r="F780" t="n">
         <v>5734800</v>
@@ -16052,16 +16052,16 @@
         <v>45296</v>
       </c>
       <c r="B782" t="n">
-        <v>25.68987655639648</v>
+        <v>25.68987464904785</v>
       </c>
       <c r="C782" t="n">
-        <v>25.97477475256549</v>
+        <v>25.97477282406455</v>
       </c>
       <c r="D782" t="n">
-        <v>25.21832285975933</v>
+        <v>25.21832098742127</v>
       </c>
       <c r="E782" t="n">
-        <v>25.36568315573496</v>
+        <v>25.36568127245611</v>
       </c>
       <c r="F782" t="n">
         <v>3417300</v>
@@ -16092,16 +16092,16 @@
         <v>45300</v>
       </c>
       <c r="B784" t="n">
-        <v>28.0181770324707</v>
+        <v>28.01817512512207</v>
       </c>
       <c r="C784" t="n">
-        <v>28.24412961971936</v>
+        <v>28.24412769698892</v>
       </c>
       <c r="D784" t="n">
-        <v>26.7999956667704</v>
+        <v>26.79999384234995</v>
       </c>
       <c r="E784" t="n">
-        <v>27.01612398407939</v>
+        <v>27.01612214494592</v>
       </c>
       <c r="F784" t="n">
         <v>10290300</v>
@@ -16152,16 +16152,16 @@
         <v>45303</v>
       </c>
       <c r="B787" t="n">
-        <v>28.20483016967773</v>
+        <v>28.20483207702637</v>
       </c>
       <c r="C787" t="n">
-        <v>28.86304121001741</v>
+        <v>28.86304316187749</v>
       </c>
       <c r="D787" t="n">
-        <v>27.82169304316834</v>
+        <v>27.82169492460737</v>
       </c>
       <c r="E787" t="n">
-        <v>28.63708864175739</v>
+        <v>28.63709057833746</v>
       </c>
       <c r="F787" t="n">
         <v>5067700</v>
@@ -16172,16 +16172,16 @@
         <v>45306</v>
       </c>
       <c r="B788" t="n">
-        <v>28.52902603149414</v>
+        <v>28.52902793884277</v>
       </c>
       <c r="C788" t="n">
-        <v>28.68621059306261</v>
+        <v>28.68621251092004</v>
       </c>
       <c r="D788" t="n">
-        <v>27.90028591143248</v>
+        <v>27.9002877767458</v>
       </c>
       <c r="E788" t="n">
-        <v>28.06729474232245</v>
+        <v>28.06729661880138</v>
       </c>
       <c r="F788" t="n">
         <v>3859400</v>
@@ -16252,16 +16252,16 @@
         <v>45310</v>
       </c>
       <c r="B792" t="n">
-        <v>29.03005218505859</v>
+        <v>29.03005027770996</v>
       </c>
       <c r="C792" t="n">
-        <v>29.19706102477754</v>
+        <v>29.197059106456</v>
       </c>
       <c r="D792" t="n">
-        <v>28.05747195626752</v>
+        <v>28.0574701128199</v>
       </c>
       <c r="E792" t="n">
-        <v>28.73533158498416</v>
+        <v>28.73532969699943</v>
       </c>
       <c r="F792" t="n">
         <v>7851200</v>
@@ -16312,16 +16312,16 @@
         <v>45315</v>
       </c>
       <c r="B795" t="n">
-        <v>27.86099052429199</v>
+        <v>27.86099243164062</v>
       </c>
       <c r="C795" t="n">
-        <v>28.52902584344861</v>
+        <v>28.52902779653059</v>
       </c>
       <c r="D795" t="n">
-        <v>27.63503607896236</v>
+        <v>27.63503797084227</v>
       </c>
       <c r="E795" t="n">
-        <v>28.04764601880687</v>
+        <v>28.04764793893384</v>
       </c>
       <c r="F795" t="n">
         <v>4070600</v>
@@ -16352,16 +16352,16 @@
         <v>45317</v>
       </c>
       <c r="B797" t="n">
-        <v>28.2441291809082</v>
+        <v>28.24412727355957</v>
       </c>
       <c r="C797" t="n">
-        <v>28.2441291809082</v>
+        <v>28.24412727355957</v>
       </c>
       <c r="D797" t="n">
-        <v>27.50732581097147</v>
+        <v>27.50732395337975</v>
       </c>
       <c r="E797" t="n">
-        <v>27.65468611020124</v>
+        <v>27.65468424265817</v>
       </c>
       <c r="F797" t="n">
         <v>2761100</v>
@@ -16392,16 +16392,16 @@
         <v>45321</v>
       </c>
       <c r="B799" t="n">
-        <v>27.24207496643066</v>
+        <v>27.2420768737793</v>
       </c>
       <c r="C799" t="n">
-        <v>27.54662169525507</v>
+        <v>27.54662362392648</v>
       </c>
       <c r="D799" t="n">
-        <v>26.97682531504984</v>
+        <v>26.97682720382707</v>
       </c>
       <c r="E799" t="n">
-        <v>27.36978859433452</v>
+        <v>27.369790510625</v>
       </c>
       <c r="F799" t="n">
         <v>2184900</v>
@@ -16432,16 +16432,16 @@
         <v>45323</v>
       </c>
       <c r="B801" t="n">
-        <v>26.24002075195312</v>
+        <v>26.24002265930176</v>
       </c>
       <c r="C801" t="n">
-        <v>27.4090825182884</v>
+        <v>27.40908451061442</v>
       </c>
       <c r="D801" t="n">
-        <v>26.10248473489757</v>
+        <v>26.10248663224892</v>
       </c>
       <c r="E801" t="n">
-        <v>27.31084170305399</v>
+        <v>27.31084368823903</v>
       </c>
       <c r="F801" t="n">
         <v>7611700</v>
@@ -16532,16 +16532,16 @@
         <v>45330</v>
       </c>
       <c r="B806" t="n">
-        <v>28.79427337646484</v>
+        <v>28.79427528381348</v>
       </c>
       <c r="C806" t="n">
-        <v>28.81392191481336</v>
+        <v>28.81392382346353</v>
       </c>
       <c r="D806" t="n">
-        <v>27.39925900811183</v>
+        <v>27.39926082305394</v>
       </c>
       <c r="E806" t="n">
-        <v>28.71568109685852</v>
+        <v>28.71568299900116</v>
       </c>
       <c r="F806" t="n">
         <v>6908300</v>
@@ -16552,16 +16552,16 @@
         <v>45331</v>
       </c>
       <c r="B807" t="n">
-        <v>27.69398307800293</v>
+        <v>27.6939811706543</v>
       </c>
       <c r="C807" t="n">
-        <v>28.9121644198793</v>
+        <v>28.9121624286317</v>
       </c>
       <c r="D807" t="n">
-        <v>27.52697423987057</v>
+        <v>27.52697234402422</v>
       </c>
       <c r="E807" t="n">
-        <v>28.83357213568689</v>
+        <v>28.83357014985212</v>
       </c>
       <c r="F807" t="n">
         <v>5513900</v>
@@ -16592,16 +16592,16 @@
         <v>45337</v>
       </c>
       <c r="B809" t="n">
-        <v>28.00835037231445</v>
+        <v>28.00835227966309</v>
       </c>
       <c r="C809" t="n">
-        <v>28.26377574758426</v>
+        <v>28.26377767232718</v>
       </c>
       <c r="D809" t="n">
-        <v>27.28137132291011</v>
+        <v>27.28137318075199</v>
       </c>
       <c r="E809" t="n">
-        <v>27.40908307365115</v>
+        <v>27.40908494019011</v>
       </c>
       <c r="F809" t="n">
         <v>2788300</v>
@@ -16632,16 +16632,16 @@
         <v>45341</v>
       </c>
       <c r="B811" t="n">
-        <v>28.6763858795166</v>
+        <v>28.67638778686523</v>
       </c>
       <c r="C811" t="n">
-        <v>28.76480242825268</v>
+        <v>28.76480434148215</v>
       </c>
       <c r="D811" t="n">
-        <v>28.2343031358362</v>
+        <v>28.23430501378064</v>
       </c>
       <c r="E811" t="n">
-        <v>28.74515388991405</v>
+        <v>28.74515580183664</v>
       </c>
       <c r="F811" t="n">
         <v>1698200</v>
@@ -16672,16 +16672,16 @@
         <v>45343</v>
       </c>
       <c r="B813" t="n">
-        <v>28.92198753356934</v>
+        <v>28.92198944091797</v>
       </c>
       <c r="C813" t="n">
-        <v>28.98093127591061</v>
+        <v>28.98093318714647</v>
       </c>
       <c r="D813" t="n">
-        <v>28.36201729685779</v>
+        <v>28.36201916727748</v>
       </c>
       <c r="E813" t="n">
-        <v>28.63708934364225</v>
+        <v>28.6370912322024</v>
       </c>
       <c r="F813" t="n">
         <v>2751400</v>
@@ -16792,16 +16792,16 @@
         <v>45351</v>
       </c>
       <c r="B819" t="n">
-        <v>27.45820426940918</v>
+        <v>27.45820617675781</v>
       </c>
       <c r="C819" t="n">
-        <v>28.14588623865804</v>
+        <v>28.14588819377561</v>
       </c>
       <c r="D819" t="n">
-        <v>27.45820426940918</v>
+        <v>27.45820617675781</v>
       </c>
       <c r="E819" t="n">
-        <v>27.98870168147043</v>
+        <v>27.98870362566938</v>
       </c>
       <c r="F819" t="n">
         <v>2784300</v>
@@ -16972,16 +16972,16 @@
         <v>45364</v>
       </c>
       <c r="B828" t="n">
-        <v>29.13811492919922</v>
+        <v>29.13811683654785</v>
       </c>
       <c r="C828" t="n">
-        <v>29.36406749594983</v>
+        <v>29.36406941808906</v>
       </c>
       <c r="D828" t="n">
-        <v>28.98093037199986</v>
+        <v>28.98093226905937</v>
       </c>
       <c r="E828" t="n">
-        <v>28.98093037199986</v>
+        <v>28.98093226905937</v>
       </c>
       <c r="F828" t="n">
         <v>2596400</v>
@@ -17032,16 +17032,16 @@
         <v>45369</v>
       </c>
       <c r="B831" t="n">
-        <v>28.98093223571777</v>
+        <v>28.98093032836914</v>
       </c>
       <c r="C831" t="n">
-        <v>29.28547710065286</v>
+        <v>29.28547517326093</v>
       </c>
       <c r="D831" t="n">
-        <v>28.61744175270144</v>
+        <v>28.61743986927554</v>
       </c>
       <c r="E831" t="n">
-        <v>28.77462819379693</v>
+        <v>28.77462630002598</v>
       </c>
       <c r="F831" t="n">
         <v>4710300</v>
@@ -17112,16 +17112,16 @@
         <v>45373</v>
       </c>
       <c r="B835" t="n">
-        <v>29.71773529052734</v>
+        <v>29.71773338317871</v>
       </c>
       <c r="C835" t="n">
-        <v>30.0026334869456</v>
+        <v>30.00263156131158</v>
       </c>
       <c r="D835" t="n">
-        <v>29.28547679800454</v>
+        <v>29.28547491839919</v>
       </c>
       <c r="E835" t="n">
-        <v>29.88474412578926</v>
+        <v>29.88474220772164</v>
       </c>
       <c r="F835" t="n">
         <v>3854000</v>
@@ -17152,16 +17152,16 @@
         <v>45377</v>
       </c>
       <c r="B837" t="n">
-        <v>30.81802749633789</v>
+        <v>30.81802940368652</v>
       </c>
       <c r="C837" t="n">
-        <v>31.22081315885015</v>
+        <v>31.22081509112746</v>
       </c>
       <c r="D837" t="n">
-        <v>30.51348077684796</v>
+        <v>30.51348266534799</v>
       </c>
       <c r="E837" t="n">
-        <v>30.61172159365801</v>
+        <v>30.61172348823823</v>
       </c>
       <c r="F837" t="n">
         <v>3327200</v>
@@ -17172,16 +17172,16 @@
         <v>45378</v>
       </c>
       <c r="B838" t="n">
-        <v>31.48606109619141</v>
+        <v>31.48606300354004</v>
       </c>
       <c r="C838" t="n">
-        <v>31.91832144197546</v>
+        <v>31.91832337550937</v>
       </c>
       <c r="D838" t="n">
-        <v>30.3857691886579</v>
+        <v>30.38577102935353</v>
       </c>
       <c r="E838" t="n">
-        <v>30.65101883332299</v>
+        <v>30.6510206900868</v>
       </c>
       <c r="F838" t="n">
         <v>9071000</v>
@@ -17372,16 +17372,16 @@
         <v>45393</v>
       </c>
       <c r="B848" t="n">
-        <v>35.62198638916016</v>
+        <v>35.62198257446289</v>
       </c>
       <c r="C848" t="n">
-        <v>35.91671074440308</v>
+        <v>35.91670689814429</v>
       </c>
       <c r="D848" t="n">
-        <v>34.59046238853748</v>
+        <v>34.59045868430435</v>
       </c>
       <c r="E848" t="n">
-        <v>34.74764696246498</v>
+        <v>34.74764324139922</v>
       </c>
       <c r="F848" t="n">
         <v>5960900</v>
@@ -17412,16 +17412,16 @@
         <v>45397</v>
       </c>
       <c r="B850" t="n">
-        <v>34.06978607177734</v>
+        <v>34.06978988647461</v>
       </c>
       <c r="C850" t="n">
-        <v>34.52169121201051</v>
+        <v>34.52169507730631</v>
       </c>
       <c r="D850" t="n">
-        <v>33.83400735867823</v>
+        <v>33.83401114697602</v>
       </c>
       <c r="E850" t="n">
-        <v>34.43327466304528</v>
+        <v>34.43327851844133</v>
       </c>
       <c r="F850" t="n">
         <v>4151100</v>
@@ -17472,16 +17472,16 @@
         <v>45400</v>
       </c>
       <c r="B853" t="n">
-        <v>32.3309326171875</v>
+        <v>32.33092880249023</v>
       </c>
       <c r="C853" t="n">
-        <v>33.28386620122118</v>
+        <v>33.28386227408815</v>
       </c>
       <c r="D853" t="n">
-        <v>31.93796930998834</v>
+        <v>31.93796554165645</v>
       </c>
       <c r="E853" t="n">
-        <v>33.00879038715143</v>
+        <v>33.00878649247434</v>
       </c>
       <c r="F853" t="n">
         <v>4478700</v>
@@ -17632,16 +17632,16 @@
         <v>45412</v>
       </c>
       <c r="B861" t="n">
-        <v>32.58635711669922</v>
+        <v>32.58635330200195</v>
       </c>
       <c r="C861" t="n">
-        <v>33.66700436998067</v>
+        <v>33.66700042877825</v>
       </c>
       <c r="D861" t="n">
-        <v>32.43899868278081</v>
+        <v>32.43899488533395</v>
       </c>
       <c r="E861" t="n">
-        <v>33.60805874786774</v>
+        <v>33.60805481356574</v>
       </c>
       <c r="F861" t="n">
         <v>6661700</v>
@@ -29865,6 +29865,26 @@
       </c>
       <c r="F1472" t="n">
         <v>6335300</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1473" t="n">
+        <v>20.91</v>
+      </c>
+      <c r="C1473" t="n">
+        <v>21.08</v>
+      </c>
+      <c r="D1473" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1473" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F1473" t="n">
+        <v>4828200</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1473"/>
+  <dimension ref="A1:F1474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29872,10 +29872,10 @@
         <v>46308</v>
       </c>
       <c r="B1473" t="n">
-        <v>20.91</v>
+        <v>20.90999984741211</v>
       </c>
       <c r="C1473" t="n">
-        <v>21.08</v>
+        <v>21.07999992370605</v>
       </c>
       <c r="D1473" t="n">
         <v>20</v>
@@ -29885,6 +29885,26 @@
       </c>
       <c r="F1473" t="n">
         <v>4828200</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1474" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="C1474" t="n">
+        <v>20.92</v>
+      </c>
+      <c r="D1474" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="E1474" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F1474" t="n">
+        <v>4186100</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1474"/>
+  <dimension ref="A1:F1475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29892,19 +29892,39 @@
         <v>46309</v>
       </c>
       <c r="B1474" t="n">
-        <v>20.55</v>
+        <v>20.54999923706055</v>
       </c>
       <c r="C1474" t="n">
-        <v>20.92</v>
+        <v>20.92000007629395</v>
       </c>
       <c r="D1474" t="n">
-        <v>20.4</v>
+        <v>20.39999961853027</v>
       </c>
       <c r="E1474" t="n">
-        <v>20.8</v>
+        <v>20.79999923706055</v>
       </c>
       <c r="F1474" t="n">
         <v>4186100</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1475" t="n">
+        <v>20.69</v>
+      </c>
+      <c r="C1475" t="n">
+        <v>20.78</v>
+      </c>
+      <c r="D1475" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="E1475" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F1475" t="n">
+        <v>2715100</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1475"/>
+  <dimension ref="A1:F1476"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29912,19 +29912,39 @@
         <v>46310</v>
       </c>
       <c r="B1475" t="n">
-        <v>20.69</v>
+        <v>20.69000053405762</v>
       </c>
       <c r="C1475" t="n">
-        <v>20.78</v>
+        <v>20.78000068664551</v>
       </c>
       <c r="D1475" t="n">
-        <v>20.15</v>
+        <v>20.14999961853027</v>
       </c>
       <c r="E1475" t="n">
-        <v>20.2</v>
+        <v>20.20000076293945</v>
       </c>
       <c r="F1475" t="n">
         <v>2715100</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1476" t="n">
+        <v>21</v>
+      </c>
+      <c r="C1476" t="n">
+        <v>21.57</v>
+      </c>
+      <c r="D1476" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="E1476" t="n">
+        <v>20.89</v>
+      </c>
+      <c r="F1476" t="n">
+        <v>5036200</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1476"/>
+  <dimension ref="A1:F1477"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,16 +512,16 @@
         <v>44152</v>
       </c>
       <c r="B5" t="n">
-        <v>20.17695617675781</v>
+        <v>20.17695426940918</v>
       </c>
       <c r="C5" t="n">
-        <v>20.17695617675781</v>
+        <v>20.17695426940918</v>
       </c>
       <c r="D5" t="n">
-        <v>19.85012633435968</v>
+        <v>19.85012445790661</v>
       </c>
       <c r="E5" t="n">
-        <v>20.12889164196659</v>
+        <v>20.12888973916155</v>
       </c>
       <c r="F5" t="n">
         <v>262242</v>
@@ -572,16 +572,16 @@
         <v>44158</v>
       </c>
       <c r="B8" t="n">
-        <v>20.2057933807373</v>
+        <v>20.20579147338867</v>
       </c>
       <c r="C8" t="n">
-        <v>20.52301068477087</v>
+        <v>20.52300874747816</v>
       </c>
       <c r="D8" t="n">
-        <v>20.14811818865408</v>
+        <v>20.14811628674976</v>
       </c>
       <c r="E8" t="n">
-        <v>20.14811818865408</v>
+        <v>20.14811628674976</v>
       </c>
       <c r="F8" t="n">
         <v>79408</v>
@@ -632,16 +632,16 @@
         <v>44161</v>
       </c>
       <c r="B11" t="n">
-        <v>22.87811088562012</v>
+        <v>22.87810897827148</v>
       </c>
       <c r="C11" t="n">
-        <v>22.87811088562012</v>
+        <v>22.87810897827148</v>
       </c>
       <c r="D11" t="n">
-        <v>22.3109640047031</v>
+        <v>22.31096214463751</v>
       </c>
       <c r="E11" t="n">
-        <v>22.3109640047031</v>
+        <v>22.31096214463751</v>
       </c>
       <c r="F11" t="n">
         <v>72970</v>
@@ -652,16 +652,16 @@
         <v>44162</v>
       </c>
       <c r="B12" t="n">
-        <v>23.07036209106445</v>
+        <v>23.07036399841309</v>
       </c>
       <c r="C12" t="n">
-        <v>23.55099428329309</v>
+        <v>23.55099623037812</v>
       </c>
       <c r="D12" t="n">
-        <v>22.10909770660719</v>
+        <v>22.10909953448302</v>
       </c>
       <c r="E12" t="n">
-        <v>23.07036209106445</v>
+        <v>23.07036399841309</v>
       </c>
       <c r="F12" t="n">
         <v>72050</v>
@@ -692,16 +692,16 @@
         <v>44166</v>
       </c>
       <c r="B14" t="n">
-        <v>23.07036209106445</v>
+        <v>23.07036399841309</v>
       </c>
       <c r="C14" t="n">
-        <v>23.1664892790253</v>
+        <v>23.16649119432127</v>
       </c>
       <c r="D14" t="n">
-        <v>23.03191196539523</v>
+        <v>23.03191386956499</v>
       </c>
       <c r="E14" t="n">
-        <v>23.12803727956828</v>
+        <v>23.12803919168523</v>
       </c>
       <c r="F14" t="n">
         <v>93512</v>
@@ -792,16 +792,16 @@
         <v>44173</v>
       </c>
       <c r="B19" t="n">
-        <v>26.33866500854492</v>
+        <v>26.33866310119629</v>
       </c>
       <c r="C19" t="n">
-        <v>26.57898205078916</v>
+        <v>26.57898012603766</v>
       </c>
       <c r="D19" t="n">
-        <v>25.56965309666637</v>
+        <v>25.56965124500673</v>
       </c>
       <c r="E19" t="n">
-        <v>25.56965309666637</v>
+        <v>25.56965124500673</v>
       </c>
       <c r="F19" t="n">
         <v>126420</v>
@@ -812,16 +812,16 @@
         <v>44174</v>
       </c>
       <c r="B20" t="n">
-        <v>26.83852005004883</v>
+        <v>26.83852195739746</v>
       </c>
       <c r="C20" t="n">
-        <v>27.77094867230641</v>
+        <v>27.77095064592048</v>
       </c>
       <c r="D20" t="n">
-        <v>26.27137510044991</v>
+        <v>26.27137696749292</v>
       </c>
       <c r="E20" t="n">
-        <v>26.4924651869397</v>
+        <v>26.49246706969505</v>
       </c>
       <c r="F20" t="n">
         <v>212880</v>
@@ -892,16 +892,16 @@
         <v>44180</v>
       </c>
       <c r="B24" t="n">
-        <v>33.00984191894531</v>
+        <v>33.00984573364258</v>
       </c>
       <c r="C24" t="n">
-        <v>33.9807187406613</v>
+        <v>33.98072266755544</v>
       </c>
       <c r="D24" t="n">
-        <v>30.7604798048412</v>
+        <v>30.76048335959674</v>
       </c>
       <c r="E24" t="n">
-        <v>30.7604798048412</v>
+        <v>30.76048335959674</v>
       </c>
       <c r="F24" t="n">
         <v>887803</v>
@@ -912,16 +912,16 @@
         <v>44181</v>
       </c>
       <c r="B25" t="n">
-        <v>32.68301773071289</v>
+        <v>32.68301391601562</v>
       </c>
       <c r="C25" t="n">
-        <v>34.4517423806715</v>
+        <v>34.45173835953219</v>
       </c>
       <c r="D25" t="n">
-        <v>32.10625830770921</v>
+        <v>32.10625456033017</v>
       </c>
       <c r="E25" t="n">
-        <v>33.62505712226533</v>
+        <v>33.62505319761509</v>
       </c>
       <c r="F25" t="n">
         <v>376808</v>
@@ -932,16 +932,16 @@
         <v>44182</v>
       </c>
       <c r="B26" t="n">
-        <v>32.10625457763672</v>
+        <v>32.10625839233398</v>
       </c>
       <c r="C26" t="n">
-        <v>33.64427827776851</v>
+        <v>33.64428227520571</v>
       </c>
       <c r="D26" t="n">
-        <v>31.64484559380946</v>
+        <v>31.64484935368452</v>
       </c>
       <c r="E26" t="n">
-        <v>33.62505321574033</v>
+        <v>33.6250572108933</v>
       </c>
       <c r="F26" t="n">
         <v>258257</v>
@@ -972,16 +972,16 @@
         <v>44186</v>
       </c>
       <c r="B28" t="n">
-        <v>32.18315505981445</v>
+        <v>32.18315887451172</v>
       </c>
       <c r="C28" t="n">
-        <v>33.33667378019659</v>
+        <v>33.33667773162143</v>
       </c>
       <c r="D28" t="n">
-        <v>29.12633082555934</v>
+        <v>29.12633427792858</v>
       </c>
       <c r="E28" t="n">
-        <v>31.86593778646691</v>
+        <v>31.86594156356414</v>
       </c>
       <c r="F28" t="n">
         <v>236079</v>
@@ -992,16 +992,16 @@
         <v>44187</v>
       </c>
       <c r="B29" t="n">
-        <v>33.16364669799805</v>
+        <v>33.16364288330078</v>
       </c>
       <c r="C29" t="n">
-        <v>33.47125146089823</v>
+        <v>33.47124761081827</v>
       </c>
       <c r="D29" t="n">
-        <v>32.59649983084212</v>
+        <v>32.59649608138177</v>
       </c>
       <c r="E29" t="n">
-        <v>33.21170935664249</v>
+        <v>33.21170553641675</v>
       </c>
       <c r="F29" t="n">
         <v>167504</v>
@@ -1032,16 +1032,16 @@
         <v>44193</v>
       </c>
       <c r="B31" t="n">
-        <v>36.21085357666016</v>
+        <v>36.21085739135742</v>
       </c>
       <c r="C31" t="n">
-        <v>36.66265002370312</v>
+        <v>36.66265388599569</v>
       </c>
       <c r="D31" t="n">
-        <v>35.56680651179074</v>
+        <v>35.56681025863972</v>
       </c>
       <c r="E31" t="n">
-        <v>35.56680651179074</v>
+        <v>35.56681025863972</v>
       </c>
       <c r="F31" t="n">
         <v>451822</v>
@@ -1052,16 +1052,16 @@
         <v>44194</v>
       </c>
       <c r="B32" t="n">
-        <v>36.09550857543945</v>
+        <v>36.09550476074219</v>
       </c>
       <c r="C32" t="n">
-        <v>37.06638558261441</v>
+        <v>37.06638166531152</v>
       </c>
       <c r="D32" t="n">
-        <v>35.95131684304462</v>
+        <v>35.95131304358604</v>
       </c>
       <c r="E32" t="n">
-        <v>36.52807627747203</v>
+        <v>36.52807241705953</v>
       </c>
       <c r="F32" t="n">
         <v>337154</v>
@@ -1092,16 +1092,16 @@
         <v>44200</v>
       </c>
       <c r="B34" t="n">
-        <v>34.99966430664062</v>
+        <v>34.99966049194336</v>
       </c>
       <c r="C34" t="n">
-        <v>36.62420472682393</v>
+        <v>36.62420073506411</v>
       </c>
       <c r="D34" t="n">
-        <v>34.98043924232432</v>
+        <v>34.98043542972244</v>
       </c>
       <c r="E34" t="n">
-        <v>36.52807565766651</v>
+        <v>36.52807167638402</v>
       </c>
       <c r="F34" t="n">
         <v>331840</v>
@@ -1112,16 +1112,16 @@
         <v>44201</v>
       </c>
       <c r="B35" t="n">
-        <v>36.13395309448242</v>
+        <v>36.13395690917969</v>
       </c>
       <c r="C35" t="n">
-        <v>36.32620745863368</v>
+        <v>36.32621129362743</v>
       </c>
       <c r="D35" t="n">
-        <v>34.60554195482727</v>
+        <v>34.60554560816865</v>
       </c>
       <c r="E35" t="n">
-        <v>35.45145591048728</v>
+        <v>35.45145965313264</v>
       </c>
       <c r="F35" t="n">
         <v>328059</v>
@@ -1172,16 +1172,16 @@
         <v>44204</v>
       </c>
       <c r="B38" t="n">
-        <v>34.134521484375</v>
+        <v>34.13452529907227</v>
       </c>
       <c r="C38" t="n">
-        <v>35.75906172916622</v>
+        <v>35.75906572541368</v>
       </c>
       <c r="D38" t="n">
-        <v>34.134521484375</v>
+        <v>34.13452529907227</v>
       </c>
       <c r="E38" t="n">
-        <v>35.16307730455386</v>
+        <v>35.16308123419719</v>
       </c>
       <c r="F38" t="n">
         <v>367201</v>
@@ -1272,16 +1272,16 @@
         <v>44211</v>
       </c>
       <c r="B43" t="n">
-        <v>33.9422721862793</v>
+        <v>33.94226837158203</v>
       </c>
       <c r="C43" t="n">
-        <v>35.0477245509764</v>
+        <v>35.04772061203977</v>
       </c>
       <c r="D43" t="n">
-        <v>33.16364589242556</v>
+        <v>33.16364216523639</v>
       </c>
       <c r="E43" t="n">
-        <v>34.60554435461268</v>
+        <v>34.60554046537172</v>
       </c>
       <c r="F43" t="n">
         <v>319883</v>
@@ -1292,16 +1292,16 @@
         <v>44214</v>
       </c>
       <c r="B44" t="n">
-        <v>34.04800796508789</v>
+        <v>34.04801177978516</v>
       </c>
       <c r="C44" t="n">
-        <v>34.50941694399793</v>
+        <v>34.5094208103909</v>
       </c>
       <c r="D44" t="n">
-        <v>33.27899799700501</v>
+        <v>33.27900172554335</v>
       </c>
       <c r="E44" t="n">
-        <v>34.11529568146945</v>
+        <v>34.11529950370554</v>
       </c>
       <c r="F44" t="n">
         <v>117631</v>
@@ -1332,16 +1332,16 @@
         <v>44216</v>
       </c>
       <c r="B46" t="n">
-        <v>34.12491226196289</v>
+        <v>34.12490844726562</v>
       </c>
       <c r="C46" t="n">
-        <v>35.28804363060232</v>
+        <v>35.28803968588292</v>
       </c>
       <c r="D46" t="n">
-        <v>33.66350697587357</v>
+        <v>33.66350321275509</v>
       </c>
       <c r="E46" t="n">
-        <v>34.60554635973278</v>
+        <v>34.60554249130722</v>
       </c>
       <c r="F46" t="n">
         <v>359332</v>
@@ -1372,16 +1372,16 @@
         <v>44218</v>
       </c>
       <c r="B48" t="n">
-        <v>32.95216751098633</v>
+        <v>32.95216369628906</v>
       </c>
       <c r="C48" t="n">
-        <v>33.45202665996278</v>
+        <v>33.45202278739948</v>
       </c>
       <c r="D48" t="n">
-        <v>32.53882489582456</v>
+        <v>32.53882112897777</v>
       </c>
       <c r="E48" t="n">
-        <v>33.19248455367023</v>
+        <v>33.19248071115274</v>
       </c>
       <c r="F48" t="n">
         <v>220341</v>
@@ -1472,16 +1472,16 @@
         <v>44228</v>
       </c>
       <c r="B53" t="n">
-        <v>31.77942657470703</v>
+        <v>31.7794246673584</v>
       </c>
       <c r="C53" t="n">
-        <v>33.11558345161116</v>
+        <v>33.1155814640686</v>
       </c>
       <c r="D53" t="n">
-        <v>31.66407244843196</v>
+        <v>31.66407054800669</v>
       </c>
       <c r="E53" t="n">
-        <v>32.68301578391271</v>
+        <v>32.68301382233215</v>
       </c>
       <c r="F53" t="n">
         <v>610435</v>
@@ -1492,16 +1492,16 @@
         <v>44229</v>
       </c>
       <c r="B54" t="n">
-        <v>32.63495254516602</v>
+        <v>32.63494873046875</v>
       </c>
       <c r="C54" t="n">
-        <v>33.65389597951643</v>
+        <v>33.65389204571495</v>
       </c>
       <c r="D54" t="n">
-        <v>31.97168030813476</v>
+        <v>31.97167657096734</v>
       </c>
       <c r="E54" t="n">
-        <v>33.64428344702543</v>
+        <v>33.64427951434755</v>
       </c>
       <c r="F54" t="n">
         <v>582228</v>
@@ -1532,16 +1532,16 @@
         <v>44231</v>
       </c>
       <c r="B56" t="n">
-        <v>32.68301773071289</v>
+        <v>32.68301391601562</v>
       </c>
       <c r="C56" t="n">
-        <v>34.11530000851534</v>
+        <v>34.11529602664492</v>
       </c>
       <c r="D56" t="n">
-        <v>32.44270067986538</v>
+        <v>32.44269689321744</v>
       </c>
       <c r="E56" t="n">
-        <v>33.06752276352339</v>
+        <v>33.06751890394745</v>
       </c>
       <c r="F56" t="n">
         <v>466743</v>
@@ -1612,16 +1612,16 @@
         <v>44237</v>
       </c>
       <c r="B60" t="n">
-        <v>34.83625030517578</v>
+        <v>34.83624649047852</v>
       </c>
       <c r="C60" t="n">
-        <v>35.33610571127585</v>
+        <v>35.33610184184258</v>
       </c>
       <c r="D60" t="n">
-        <v>34.23065330065825</v>
+        <v>34.23064955227608</v>
       </c>
       <c r="E60" t="n">
-        <v>34.43251647044691</v>
+        <v>34.43251269995998</v>
       </c>
       <c r="F60" t="n">
         <v>186206</v>
@@ -1652,16 +1652,16 @@
         <v>44239</v>
       </c>
       <c r="B62" t="n">
-        <v>34.4036750793457</v>
+        <v>34.40367889404297</v>
       </c>
       <c r="C62" t="n">
-        <v>34.52864172776623</v>
+        <v>34.52864555631986</v>
       </c>
       <c r="D62" t="n">
-        <v>32.67339704372985</v>
+        <v>32.673400666573</v>
       </c>
       <c r="E62" t="n">
-        <v>33.67311524079254</v>
+        <v>33.67311897448496</v>
       </c>
       <c r="F62" t="n">
         <v>218195</v>
@@ -1692,16 +1692,16 @@
         <v>44245</v>
       </c>
       <c r="B64" t="n">
-        <v>37.00870513916016</v>
+        <v>37.00870895385742</v>
       </c>
       <c r="C64" t="n">
-        <v>37.38359759408829</v>
+        <v>37.38360144742785</v>
       </c>
       <c r="D64" t="n">
-        <v>35.71099846956061</v>
+        <v>35.71100215049589</v>
       </c>
       <c r="E64" t="n">
-        <v>36.37427060079703</v>
+        <v>36.37427435009953</v>
       </c>
       <c r="F64" t="n">
         <v>661534</v>
@@ -1812,16 +1812,16 @@
         <v>44253</v>
       </c>
       <c r="B70" t="n">
-        <v>34.57670974731445</v>
+        <v>34.57670593261719</v>
       </c>
       <c r="C70" t="n">
-        <v>37.21057733278074</v>
+        <v>37.21057322750037</v>
       </c>
       <c r="D70" t="n">
-        <v>33.75002072456356</v>
+        <v>33.75001700107128</v>
       </c>
       <c r="E70" t="n">
-        <v>36.53768882724342</v>
+        <v>36.5376847961999</v>
       </c>
       <c r="F70" t="n">
         <v>410022</v>
@@ -1932,16 +1932,16 @@
         <v>44263</v>
       </c>
       <c r="B76" t="n">
-        <v>41.91115570068359</v>
+        <v>41.91115951538086</v>
       </c>
       <c r="C76" t="n">
-        <v>44.60269808495321</v>
+        <v>44.60270214463106</v>
       </c>
       <c r="D76" t="n">
-        <v>40.70957434605565</v>
+        <v>40.70957805138659</v>
       </c>
       <c r="E76" t="n">
-        <v>43.55492097253444</v>
+        <v>43.55492493684502</v>
       </c>
       <c r="F76" t="n">
         <v>1012691</v>
@@ -1952,16 +1952,16 @@
         <v>44264</v>
       </c>
       <c r="B77" t="n">
-        <v>43.50685882568359</v>
+        <v>43.50686264038086</v>
       </c>
       <c r="C77" t="n">
-        <v>43.50685882568359</v>
+        <v>43.50686264038086</v>
       </c>
       <c r="D77" t="n">
-        <v>39.89249844113039</v>
+        <v>39.89250193891922</v>
       </c>
       <c r="E77" t="n">
-        <v>42.29566117843103</v>
+        <v>42.29566488693005</v>
       </c>
       <c r="F77" t="n">
         <v>563525</v>
@@ -1972,16 +1972,16 @@
         <v>44265</v>
       </c>
       <c r="B78" t="n">
-        <v>44.69882965087891</v>
+        <v>44.69882583618164</v>
       </c>
       <c r="C78" t="n">
-        <v>44.89108404365759</v>
+        <v>44.89108021255291</v>
       </c>
       <c r="D78" t="n">
-        <v>43.38189774093629</v>
+        <v>43.38189403862891</v>
       </c>
       <c r="E78" t="n">
-        <v>43.83369425231464</v>
+        <v>43.83369051144994</v>
       </c>
       <c r="F78" t="n">
         <v>425454</v>
@@ -2012,16 +2012,16 @@
         <v>44267</v>
       </c>
       <c r="B80" t="n">
-        <v>45.66009140014648</v>
+        <v>45.66009521484375</v>
       </c>
       <c r="C80" t="n">
-        <v>49.01490590711195</v>
+        <v>49.01491000208902</v>
       </c>
       <c r="D80" t="n">
-        <v>45.18906989096082</v>
+        <v>45.18907366630634</v>
       </c>
       <c r="E80" t="n">
-        <v>47.15005242731743</v>
+        <v>47.15005636649431</v>
       </c>
       <c r="F80" t="n">
         <v>954539</v>
@@ -2052,16 +2052,16 @@
         <v>44271</v>
       </c>
       <c r="B82" t="n">
-        <v>42.7570686340332</v>
+        <v>42.75707244873047</v>
       </c>
       <c r="C82" t="n">
-        <v>45.18906887745489</v>
+        <v>45.18907290913018</v>
       </c>
       <c r="D82" t="n">
-        <v>42.7570686340332</v>
+        <v>42.75707244873047</v>
       </c>
       <c r="E82" t="n">
-        <v>44.5065717038056</v>
+        <v>44.50657567458991</v>
       </c>
       <c r="F82" t="n">
         <v>561175</v>
@@ -2092,16 +2092,16 @@
         <v>44273</v>
       </c>
       <c r="B84" t="n">
-        <v>40.89221572875977</v>
+        <v>40.89221954345703</v>
       </c>
       <c r="C84" t="n">
-        <v>45.02565269480871</v>
+        <v>45.0256568951004</v>
       </c>
       <c r="D84" t="n">
-        <v>40.57499846451049</v>
+        <v>40.57500224961562</v>
       </c>
       <c r="E84" t="n">
-        <v>44.01632571721106</v>
+        <v>44.01632982334604</v>
       </c>
       <c r="F84" t="n">
         <v>572621</v>
@@ -2112,16 +2112,16 @@
         <v>44274</v>
       </c>
       <c r="B85" t="n">
-        <v>42.2956657409668</v>
+        <v>42.29566192626953</v>
       </c>
       <c r="C85" t="n">
-        <v>44.17013572642225</v>
+        <v>44.17013174266427</v>
       </c>
       <c r="D85" t="n">
-        <v>41.45936795627186</v>
+        <v>41.4593642170013</v>
       </c>
       <c r="E85" t="n">
-        <v>41.45936795627186</v>
+        <v>41.4593642170013</v>
       </c>
       <c r="F85" t="n">
         <v>639255</v>
@@ -2212,16 +2212,16 @@
         <v>44281</v>
       </c>
       <c r="B90" t="n">
-        <v>37.87384796142578</v>
+        <v>37.87384414672852</v>
       </c>
       <c r="C90" t="n">
-        <v>40.94989565175231</v>
+        <v>40.949891527232</v>
       </c>
       <c r="D90" t="n">
-        <v>37.56624319239313</v>
+        <v>37.56623940867817</v>
       </c>
       <c r="E90" t="n">
-        <v>39.95979362121066</v>
+        <v>39.95978959641457</v>
       </c>
       <c r="F90" t="n">
         <v>840076</v>
@@ -2312,16 +2312,16 @@
         <v>44291</v>
       </c>
       <c r="B95" t="n">
-        <v>35.68216323852539</v>
+        <v>35.68215942382812</v>
       </c>
       <c r="C95" t="n">
-        <v>37.01832012039754</v>
+        <v>37.01831616285484</v>
       </c>
       <c r="D95" t="n">
-        <v>35.09579131613852</v>
+        <v>35.09578756412892</v>
       </c>
       <c r="E95" t="n">
-        <v>37.01832012039754</v>
+        <v>37.01831616285484</v>
       </c>
       <c r="F95" t="n">
         <v>1091895</v>
@@ -2512,16 +2512,16 @@
         <v>44305</v>
       </c>
       <c r="B105" t="n">
-        <v>41.33440017700195</v>
+        <v>41.33439636230469</v>
       </c>
       <c r="C105" t="n">
-        <v>42.23798940934727</v>
+        <v>42.23798551125894</v>
       </c>
       <c r="D105" t="n">
-        <v>40.2097189655786</v>
+        <v>40.20971525467667</v>
       </c>
       <c r="E105" t="n">
-        <v>40.38274828563441</v>
+        <v>40.38274455876383</v>
       </c>
       <c r="F105" t="n">
         <v>1793083</v>
@@ -2552,16 +2552,16 @@
         <v>44308</v>
       </c>
       <c r="B107" t="n">
-        <v>42.37256622314453</v>
+        <v>42.3725700378418</v>
       </c>
       <c r="C107" t="n">
-        <v>42.77629628383934</v>
+        <v>42.77630013488342</v>
       </c>
       <c r="D107" t="n">
-        <v>41.0460181707321</v>
+        <v>41.04602186600353</v>
       </c>
       <c r="E107" t="n">
-        <v>42.58404191096891</v>
+        <v>42.58404574470481</v>
       </c>
       <c r="F107" t="n">
         <v>1175903</v>
@@ -2572,16 +2572,16 @@
         <v>44309</v>
       </c>
       <c r="B108" t="n">
-        <v>44.09323120117188</v>
+        <v>44.09323501586914</v>
       </c>
       <c r="C108" t="n">
-        <v>44.3143194172334</v>
+        <v>44.31432325105797</v>
       </c>
       <c r="D108" t="n">
-        <v>42.38217817402538</v>
+        <v>42.38218184069201</v>
       </c>
       <c r="E108" t="n">
-        <v>42.82435835372392</v>
+        <v>42.82436205864548</v>
       </c>
       <c r="F108" t="n">
         <v>1899574</v>
@@ -2612,16 +2612,16 @@
         <v>44313</v>
       </c>
       <c r="B110" t="n">
-        <v>43.73756408691406</v>
+        <v>43.7375602722168</v>
       </c>
       <c r="C110" t="n">
-        <v>44.31432350323168</v>
+        <v>44.31431963823069</v>
       </c>
       <c r="D110" t="n">
-        <v>43.04545428636325</v>
+        <v>43.04545053203033</v>
       </c>
       <c r="E110" t="n">
-        <v>43.40112171865809</v>
+        <v>43.40111793330461</v>
       </c>
       <c r="F110" t="n">
         <v>1146163</v>
@@ -2732,16 +2732,16 @@
         <v>44321</v>
       </c>
       <c r="B116" t="n">
-        <v>39.74831008911133</v>
+        <v>39.74831390380859</v>
       </c>
       <c r="C116" t="n">
-        <v>40.6422867086336</v>
+        <v>40.64229060912697</v>
       </c>
       <c r="D116" t="n">
-        <v>39.07542542863015</v>
+        <v>39.0754291787498</v>
       </c>
       <c r="E116" t="n">
-        <v>39.89249805311069</v>
+        <v>39.89250188164586</v>
       </c>
       <c r="F116" t="n">
         <v>3650961</v>
@@ -2772,16 +2772,16 @@
         <v>44323</v>
       </c>
       <c r="B118" t="n">
-        <v>38.83511352539062</v>
+        <v>38.83510971069336</v>
       </c>
       <c r="C118" t="n">
-        <v>39.99824491189721</v>
+        <v>39.99824098294782</v>
       </c>
       <c r="D118" t="n">
-        <v>37.51818162368365</v>
+        <v>37.51817793834604</v>
       </c>
       <c r="E118" t="n">
-        <v>39.66180253732045</v>
+        <v>39.66179864141913</v>
       </c>
       <c r="F118" t="n">
         <v>2227429</v>
@@ -2832,16 +2832,16 @@
         <v>44328</v>
       </c>
       <c r="B121" t="n">
-        <v>37.05676651000977</v>
+        <v>37.05677032470703</v>
       </c>
       <c r="C121" t="n">
-        <v>38.70052798471127</v>
+        <v>38.70053196862062</v>
       </c>
       <c r="D121" t="n">
-        <v>37.05676651000977</v>
+        <v>37.05677032470703</v>
       </c>
       <c r="E121" t="n">
-        <v>37.81616767208757</v>
+        <v>37.8161715649591</v>
       </c>
       <c r="F121" t="n">
         <v>783049</v>
@@ -2892,16 +2892,16 @@
         <v>44333</v>
       </c>
       <c r="B124" t="n">
-        <v>36.43194961547852</v>
+        <v>36.43194580078125</v>
       </c>
       <c r="C124" t="n">
-        <v>37.13367194429578</v>
+        <v>37.13366805612294</v>
       </c>
       <c r="D124" t="n">
-        <v>35.93209045798972</v>
+        <v>35.93208669563144</v>
       </c>
       <c r="E124" t="n">
-        <v>36.52807493515874</v>
+        <v>36.52807111039643</v>
       </c>
       <c r="F124" t="n">
         <v>946466</v>
@@ -2912,16 +2912,16 @@
         <v>44334</v>
       </c>
       <c r="B125" t="n">
-        <v>35.14385223388672</v>
+        <v>35.14385604858398</v>
       </c>
       <c r="C125" t="n">
-        <v>36.91258044505902</v>
+        <v>36.91258445174329</v>
       </c>
       <c r="D125" t="n">
-        <v>34.59593046500746</v>
+        <v>34.59593422023043</v>
       </c>
       <c r="E125" t="n">
-        <v>36.52807170518645</v>
+        <v>36.52807567013412</v>
       </c>
       <c r="F125" t="n">
         <v>2070451</v>
@@ -2952,16 +2952,16 @@
         <v>44336</v>
       </c>
       <c r="B127" t="n">
-        <v>34.63438034057617</v>
+        <v>34.63438415527344</v>
       </c>
       <c r="C127" t="n">
-        <v>35.26881488495837</v>
+        <v>35.26881876953347</v>
       </c>
       <c r="D127" t="n">
-        <v>34.51902996798866</v>
+        <v>34.51903376998102</v>
       </c>
       <c r="E127" t="n">
-        <v>34.51902996798866</v>
+        <v>34.51903376998102</v>
       </c>
       <c r="F127" t="n">
         <v>943604</v>
@@ -3012,16 +3012,16 @@
         <v>44341</v>
       </c>
       <c r="B130" t="n">
-        <v>37.29708480834961</v>
+        <v>37.29708862304688</v>
       </c>
       <c r="C130" t="n">
-        <v>38.78704584439543</v>
+        <v>38.78704981148397</v>
       </c>
       <c r="D130" t="n">
-        <v>37.22979709165812</v>
+        <v>37.22980089947328</v>
       </c>
       <c r="E130" t="n">
-        <v>37.52778929886728</v>
+        <v>37.52779313716071</v>
       </c>
       <c r="F130" t="n">
         <v>1731150</v>
@@ -3092,16 +3092,16 @@
         <v>44347</v>
       </c>
       <c r="B134" t="n">
-        <v>39.38302993774414</v>
+        <v>39.38303375244141</v>
       </c>
       <c r="C134" t="n">
-        <v>40.11358977958957</v>
+        <v>40.11359366504992</v>
       </c>
       <c r="D134" t="n">
-        <v>39.02736254769899</v>
+        <v>39.02736632794579</v>
       </c>
       <c r="E134" t="n">
-        <v>39.3926424686217</v>
+        <v>39.39264628425005</v>
       </c>
       <c r="F134" t="n">
         <v>715598</v>
@@ -3192,16 +3192,16 @@
         <v>44355</v>
       </c>
       <c r="B139" t="n">
-        <v>38.46022033691406</v>
+        <v>38.4602165222168</v>
       </c>
       <c r="C139" t="n">
-        <v>38.85433789767048</v>
+        <v>38.85433404388245</v>
       </c>
       <c r="D139" t="n">
-        <v>37.72004412796937</v>
+        <v>37.72004038668688</v>
       </c>
       <c r="E139" t="n">
-        <v>38.43138274082768</v>
+        <v>38.43137892899068</v>
       </c>
       <c r="F139" t="n">
         <v>978352</v>
@@ -3212,16 +3212,16 @@
         <v>44356</v>
       </c>
       <c r="B140" t="n">
-        <v>38.01803207397461</v>
+        <v>38.01803588867188</v>
       </c>
       <c r="C140" t="n">
-        <v>38.66207914230487</v>
+        <v>38.66208302162527</v>
       </c>
       <c r="D140" t="n">
-        <v>37.29708475810054</v>
+        <v>37.29708850045856</v>
       </c>
       <c r="E140" t="n">
-        <v>38.48905358533129</v>
+        <v>38.48905744729046</v>
       </c>
       <c r="F140" t="n">
         <v>837521</v>
@@ -3332,16 +3332,16 @@
         <v>44364</v>
       </c>
       <c r="B146" t="n">
-        <v>42.48791885375977</v>
+        <v>42.4879150390625</v>
       </c>
       <c r="C146" t="n">
-        <v>44.00671761209134</v>
+        <v>44.0067136610316</v>
       </c>
       <c r="D146" t="n">
-        <v>41.62277975128091</v>
+        <v>41.62277601425852</v>
       </c>
       <c r="E146" t="n">
-        <v>42.95894040588714</v>
+        <v>42.95893654890009</v>
       </c>
       <c r="F146" t="n">
         <v>1582144</v>
@@ -3372,16 +3372,16 @@
         <v>44368</v>
       </c>
       <c r="B148" t="n">
-        <v>46.96741104125977</v>
+        <v>46.96741485595703</v>
       </c>
       <c r="C148" t="n">
-        <v>47.24617818755916</v>
+        <v>47.24618202489792</v>
       </c>
       <c r="D148" t="n">
-        <v>43.53569625432814</v>
+        <v>43.53569979030122</v>
       </c>
       <c r="E148" t="n">
-        <v>43.73755940512824</v>
+        <v>43.73756295749668</v>
       </c>
       <c r="F148" t="n">
         <v>2655439</v>
@@ -3452,16 +3452,16 @@
         <v>44372</v>
       </c>
       <c r="B152" t="n">
-        <v>44.45851516723633</v>
+        <v>44.45851135253906</v>
       </c>
       <c r="C152" t="n">
-        <v>44.9872081751215</v>
+        <v>44.98720431506052</v>
       </c>
       <c r="D152" t="n">
-        <v>43.97788107180344</v>
+        <v>43.97787729834627</v>
       </c>
       <c r="E152" t="n">
-        <v>44.9872081751215</v>
+        <v>44.98720431506052</v>
       </c>
       <c r="F152" t="n">
         <v>1347904</v>
@@ -3472,16 +3472,16 @@
         <v>44375</v>
       </c>
       <c r="B153" t="n">
-        <v>44.53541564941406</v>
+        <v>44.5354118347168</v>
       </c>
       <c r="C153" t="n">
-        <v>44.64115350201283</v>
+        <v>44.64114967825854</v>
       </c>
       <c r="D153" t="n">
-        <v>43.20886748802305</v>
+        <v>43.20886378695175</v>
       </c>
       <c r="E153" t="n">
-        <v>44.13168555555202</v>
+        <v>44.13168177543641</v>
       </c>
       <c r="F153" t="n">
         <v>1110393</v>
@@ -3512,16 +3512,16 @@
         <v>44377</v>
       </c>
       <c r="B155" t="n">
-        <v>43.58375930786133</v>
+        <v>43.58376312255859</v>
       </c>
       <c r="C155" t="n">
-        <v>44.45851087872119</v>
+        <v>44.45851476998166</v>
       </c>
       <c r="D155" t="n">
-        <v>43.50685905923421</v>
+        <v>43.50686286720073</v>
       </c>
       <c r="E155" t="n">
-        <v>44.21819385418598</v>
+        <v>44.21819772441255</v>
       </c>
       <c r="F155" t="n">
         <v>1274116</v>
@@ -3572,16 +3572,16 @@
         <v>44382</v>
       </c>
       <c r="B158" t="n">
-        <v>45.04488754272461</v>
+        <v>45.04488372802734</v>
       </c>
       <c r="C158" t="n">
-        <v>46.21763144885693</v>
+        <v>46.21762753484401</v>
       </c>
       <c r="D158" t="n">
-        <v>44.42967424579171</v>
+        <v>44.42967048319475</v>
       </c>
       <c r="E158" t="n">
-        <v>44.98720860256699</v>
+        <v>44.98720479275436</v>
       </c>
       <c r="F158" t="n">
         <v>3391068</v>
@@ -3592,16 +3592,16 @@
         <v>44383</v>
       </c>
       <c r="B159" t="n">
-        <v>44.37199783325195</v>
+        <v>44.37199401855469</v>
       </c>
       <c r="C159" t="n">
-        <v>45.94847553926477</v>
+        <v>45.94847158903642</v>
       </c>
       <c r="D159" t="n">
-        <v>43.75678830080941</v>
+        <v>43.75678453900221</v>
       </c>
       <c r="E159" t="n">
-        <v>45.78505875053358</v>
+        <v>45.7850548143543</v>
       </c>
       <c r="F159" t="n">
         <v>1563442</v>
@@ -3652,16 +3652,16 @@
         <v>44389</v>
       </c>
       <c r="B162" t="n">
-        <v>44.72766494750977</v>
+        <v>44.72766876220703</v>
       </c>
       <c r="C162" t="n">
-        <v>45.75621700299953</v>
+        <v>45.75622090541913</v>
       </c>
       <c r="D162" t="n">
-        <v>44.08361413043626</v>
+        <v>44.08361789020423</v>
       </c>
       <c r="E162" t="n">
-        <v>45.75621700299953</v>
+        <v>45.75622090541913</v>
       </c>
       <c r="F162" t="n">
         <v>1597780</v>
@@ -3732,16 +3732,16 @@
         <v>44393</v>
       </c>
       <c r="B166" t="n">
-        <v>41.70929336547852</v>
+        <v>41.70928955078125</v>
       </c>
       <c r="C166" t="n">
-        <v>41.91116028433812</v>
+        <v>41.91115645117827</v>
       </c>
       <c r="D166" t="n">
-        <v>40.45003668764308</v>
+        <v>40.45003298811638</v>
       </c>
       <c r="E166" t="n">
-        <v>41.62278057778546</v>
+        <v>41.62277677100059</v>
       </c>
       <c r="F166" t="n">
         <v>1471156</v>
@@ -3752,16 +3752,16 @@
         <v>44396</v>
       </c>
       <c r="B167" t="n">
-        <v>40.22894668579102</v>
+        <v>40.22894287109375</v>
       </c>
       <c r="C167" t="n">
-        <v>41.05563189370605</v>
+        <v>41.05562800061862</v>
       </c>
       <c r="D167" t="n">
-        <v>39.50799557728174</v>
+        <v>39.50799183094843</v>
       </c>
       <c r="E167" t="n">
-        <v>40.46925997438512</v>
+        <v>40.46925613690023</v>
       </c>
       <c r="F167" t="n">
         <v>1632835</v>
@@ -3792,16 +3792,16 @@
         <v>44398</v>
       </c>
       <c r="B169" t="n">
-        <v>40.45964813232422</v>
+        <v>40.45964431762695</v>
       </c>
       <c r="C169" t="n">
-        <v>41.40169122996932</v>
+        <v>41.40168732645247</v>
       </c>
       <c r="D169" t="n">
-        <v>40.22894737134245</v>
+        <v>40.22894357839657</v>
       </c>
       <c r="E169" t="n">
-        <v>40.37313534695605</v>
+        <v>40.37313154041556</v>
       </c>
       <c r="F169" t="n">
         <v>985812</v>
@@ -3812,16 +3812,16 @@
         <v>44399</v>
       </c>
       <c r="B170" t="n">
-        <v>40.89221572875977</v>
+        <v>40.89221954345703</v>
       </c>
       <c r="C170" t="n">
-        <v>41.15175780815924</v>
+        <v>41.15176164706832</v>
       </c>
       <c r="D170" t="n">
-        <v>40.39235663157741</v>
+        <v>40.3923603996445</v>
       </c>
       <c r="E170" t="n">
-        <v>41.08446634492577</v>
+        <v>41.08447017755746</v>
       </c>
       <c r="F170" t="n">
         <v>757704</v>
@@ -3832,16 +3832,16 @@
         <v>44400</v>
       </c>
       <c r="B171" t="n">
-        <v>40.56539154052734</v>
+        <v>40.56538772583008</v>
       </c>
       <c r="C171" t="n">
-        <v>40.8633837843476</v>
+        <v>40.86337994162768</v>
       </c>
       <c r="D171" t="n">
-        <v>40.20010782417279</v>
+        <v>40.20010404382616</v>
       </c>
       <c r="E171" t="n">
-        <v>40.62306673334884</v>
+        <v>40.6230629132279</v>
       </c>
       <c r="F171" t="n">
         <v>715496</v>
@@ -3872,16 +3872,16 @@
         <v>44404</v>
       </c>
       <c r="B173" t="n">
-        <v>38.54673385620117</v>
+        <v>38.54673004150391</v>
       </c>
       <c r="C173" t="n">
-        <v>40.84415903525979</v>
+        <v>40.84415499320262</v>
       </c>
       <c r="D173" t="n">
-        <v>38.32564186777011</v>
+        <v>38.32563807495276</v>
       </c>
       <c r="E173" t="n">
-        <v>40.62306704682872</v>
+        <v>40.62306302665147</v>
       </c>
       <c r="F173" t="n">
         <v>1543819</v>
@@ -3932,16 +3932,16 @@
         <v>44407</v>
       </c>
       <c r="B176" t="n">
-        <v>37.21057510375977</v>
+        <v>37.2105712890625</v>
       </c>
       <c r="C176" t="n">
-        <v>38.26796483899034</v>
+        <v>38.26796091589321</v>
       </c>
       <c r="D176" t="n">
-        <v>36.33582347177977</v>
+        <v>36.33581974675896</v>
       </c>
       <c r="E176" t="n">
-        <v>37.56624252608663</v>
+        <v>37.5662386749276</v>
       </c>
       <c r="F176" t="n">
         <v>1168442</v>
@@ -3952,16 +3952,16 @@
         <v>44410</v>
       </c>
       <c r="B177" t="n">
-        <v>39.04659271240234</v>
+        <v>39.04658889770508</v>
       </c>
       <c r="C177" t="n">
-        <v>40.34429954077027</v>
+        <v>40.3442955992922</v>
       </c>
       <c r="D177" t="n">
-        <v>38.19106610976557</v>
+        <v>38.19106237864987</v>
       </c>
       <c r="E177" t="n">
-        <v>39.17155563014188</v>
+        <v>39.17155180323623</v>
       </c>
       <c r="F177" t="n">
         <v>3352028</v>
@@ -4052,16 +4052,16 @@
         <v>44417</v>
       </c>
       <c r="B182" t="n">
-        <v>37.10483551025391</v>
+        <v>37.10483169555664</v>
       </c>
       <c r="C182" t="n">
-        <v>37.44127788724551</v>
+        <v>37.44127403795907</v>
       </c>
       <c r="D182" t="n">
-        <v>35.94170411539885</v>
+        <v>35.94170042028153</v>
       </c>
       <c r="E182" t="n">
-        <v>36.11473344381713</v>
+        <v>36.1147297309109</v>
       </c>
       <c r="F182" t="n">
         <v>1206460</v>
@@ -4092,16 +4092,16 @@
         <v>44419</v>
       </c>
       <c r="B184" t="n">
-        <v>36.43194961547852</v>
+        <v>36.43194580078125</v>
       </c>
       <c r="C184" t="n">
-        <v>36.74916691799907</v>
+        <v>36.74916307008678</v>
       </c>
       <c r="D184" t="n">
-        <v>36.09550724902192</v>
+        <v>36.09550346955268</v>
       </c>
       <c r="E184" t="n">
-        <v>36.4703997433506</v>
+        <v>36.47039592462733</v>
       </c>
       <c r="F184" t="n">
         <v>786524</v>
@@ -4112,16 +4112,16 @@
         <v>44420</v>
       </c>
       <c r="B185" t="n">
-        <v>36.12434005737305</v>
+        <v>36.12434387207031</v>
       </c>
       <c r="C185" t="n">
-        <v>36.95102893978947</v>
+        <v>36.95103284178433</v>
       </c>
       <c r="D185" t="n">
-        <v>35.47068047502529</v>
+        <v>35.4706842206967</v>
       </c>
       <c r="E185" t="n">
-        <v>36.19162777223157</v>
+        <v>36.19163159403436</v>
       </c>
       <c r="F185" t="n">
         <v>689639</v>
@@ -4132,16 +4132,16 @@
         <v>44421</v>
       </c>
       <c r="B186" t="n">
-        <v>34.75934600830078</v>
+        <v>34.75934219360352</v>
       </c>
       <c r="C186" t="n">
-        <v>35.97054000708643</v>
+        <v>35.97053605946554</v>
       </c>
       <c r="D186" t="n">
-        <v>34.59593296747376</v>
+        <v>34.59592917071041</v>
       </c>
       <c r="E186" t="n">
-        <v>35.69177658449917</v>
+        <v>35.69177266747142</v>
       </c>
       <c r="F186" t="n">
         <v>915908</v>
@@ -4252,16 +4252,16 @@
         <v>44431</v>
       </c>
       <c r="B192" t="n">
-        <v>33.16364669799805</v>
+        <v>33.16364288330078</v>
       </c>
       <c r="C192" t="n">
-        <v>34.42290334478545</v>
+        <v>34.42289938524034</v>
       </c>
       <c r="D192" t="n">
-        <v>32.77914168126674</v>
+        <v>32.77913791079774</v>
       </c>
       <c r="E192" t="n">
-        <v>33.74040609688286</v>
+        <v>33.740402215843</v>
       </c>
       <c r="F192" t="n">
         <v>2084044</v>
@@ -4272,16 +4272,16 @@
         <v>44432</v>
       </c>
       <c r="B193" t="n">
-        <v>35.43223190307617</v>
+        <v>35.43223571777344</v>
       </c>
       <c r="C193" t="n">
-        <v>35.43223190307617</v>
+        <v>35.43223571777344</v>
       </c>
       <c r="D193" t="n">
-        <v>33.47124932262768</v>
+        <v>33.47125292620207</v>
       </c>
       <c r="E193" t="n">
-        <v>33.93265831128927</v>
+        <v>33.93266196453976</v>
       </c>
       <c r="F193" t="n">
         <v>1429663</v>
@@ -4332,16 +4332,16 @@
         <v>44435</v>
       </c>
       <c r="B196" t="n">
-        <v>36.43194961547852</v>
+        <v>36.43194580078125</v>
       </c>
       <c r="C196" t="n">
-        <v>36.66265413028687</v>
+        <v>36.66265029143312</v>
       </c>
       <c r="D196" t="n">
-        <v>35.02850121026817</v>
+        <v>35.02849754252244</v>
       </c>
       <c r="E196" t="n">
-        <v>35.75906488256532</v>
+        <v>35.75906113832411</v>
       </c>
       <c r="F196" t="n">
         <v>2701327</v>
@@ -4392,16 +4392,16 @@
         <v>44440</v>
       </c>
       <c r="B199" t="n">
-        <v>36.00899505615234</v>
+        <v>36.00899124145508</v>
       </c>
       <c r="C199" t="n">
-        <v>37.2298016265613</v>
+        <v>37.22979768253502</v>
       </c>
       <c r="D199" t="n">
-        <v>35.47068576189898</v>
+        <v>35.47068200422877</v>
       </c>
       <c r="E199" t="n">
-        <v>37.10483496133683</v>
+        <v>37.10483103054919</v>
       </c>
       <c r="F199" t="n">
         <v>1150659</v>
@@ -4712,16 +4712,16 @@
         <v>44463</v>
       </c>
       <c r="B215" t="n">
-        <v>34.54787063598633</v>
+        <v>34.54786682128906</v>
       </c>
       <c r="C215" t="n">
-        <v>35.65332304773112</v>
+        <v>35.65331911097231</v>
       </c>
       <c r="D215" t="n">
-        <v>33.88459469184851</v>
+        <v>33.88459095038866</v>
       </c>
       <c r="E215" t="n">
-        <v>34.46135784884584</v>
+        <v>34.46135404370111</v>
       </c>
       <c r="F215" t="n">
         <v>2639905</v>
@@ -4852,16 +4852,16 @@
         <v>44474</v>
       </c>
       <c r="B222" t="n">
-        <v>41.2382698059082</v>
+        <v>41.23827362060547</v>
       </c>
       <c r="C222" t="n">
-        <v>43.07428564103963</v>
+        <v>43.07428962557536</v>
       </c>
       <c r="D222" t="n">
-        <v>40.94989013953506</v>
+        <v>40.9498939275561</v>
       </c>
       <c r="E222" t="n">
-        <v>41.82464166928109</v>
+        <v>41.82464553821999</v>
       </c>
       <c r="F222" t="n">
         <v>3033780</v>
@@ -4952,16 +4952,16 @@
         <v>44482</v>
       </c>
       <c r="B227" t="n">
-        <v>39.66180038452148</v>
+        <v>39.66179656982422</v>
       </c>
       <c r="C227" t="n">
-        <v>40.05591793090613</v>
+        <v>40.05591407830239</v>
       </c>
       <c r="D227" t="n">
-        <v>38.88317407585477</v>
+        <v>38.88317033604628</v>
       </c>
       <c r="E227" t="n">
-        <v>39.43109587666738</v>
+        <v>39.43109208415942</v>
       </c>
       <c r="F227" t="n">
         <v>1130628</v>
@@ -5012,16 +5012,16 @@
         <v>44487</v>
       </c>
       <c r="B230" t="n">
-        <v>39.87327575683594</v>
+        <v>39.87327194213867</v>
       </c>
       <c r="C230" t="n">
-        <v>41.44975342469183</v>
+        <v>41.44974945917212</v>
       </c>
       <c r="D230" t="n">
-        <v>39.18116598648377</v>
+        <v>39.18116223800101</v>
       </c>
       <c r="E230" t="n">
-        <v>39.72908778283576</v>
+        <v>39.72908398193304</v>
       </c>
       <c r="F230" t="n">
         <v>2573169</v>
@@ -5032,16 +5032,16 @@
         <v>44488</v>
       </c>
       <c r="B231" t="n">
-        <v>37.58546829223633</v>
+        <v>37.58546447753906</v>
       </c>
       <c r="C231" t="n">
-        <v>40.08475657457366</v>
+        <v>40.08475250621378</v>
       </c>
       <c r="D231" t="n">
-        <v>36.86452090235465</v>
+        <v>36.86451716082918</v>
       </c>
       <c r="E231" t="n">
-        <v>39.57528488714614</v>
+        <v>39.57528087049455</v>
       </c>
       <c r="F231" t="n">
         <v>2915331</v>
@@ -5072,16 +5072,16 @@
         <v>44490</v>
       </c>
       <c r="B233" t="n">
-        <v>34.41329193115234</v>
+        <v>34.41328811645508</v>
       </c>
       <c r="C233" t="n">
-        <v>36.09550752381791</v>
+        <v>36.09550352264783</v>
       </c>
       <c r="D233" t="n">
-        <v>33.48086508042814</v>
+        <v>33.48086136908995</v>
       </c>
       <c r="E233" t="n">
-        <v>35.62448595864728</v>
+        <v>35.62448200968972</v>
       </c>
       <c r="F233" t="n">
         <v>3113087</v>
@@ -5092,16 +5092,16 @@
         <v>44491</v>
       </c>
       <c r="B234" t="n">
-        <v>32.63495254516602</v>
+        <v>32.63494873046875</v>
       </c>
       <c r="C234" t="n">
-        <v>34.06723862420559</v>
+        <v>34.06723464208851</v>
       </c>
       <c r="D234" t="n">
-        <v>31.04886594627039</v>
+        <v>31.04886231697067</v>
       </c>
       <c r="E234" t="n">
-        <v>33.63467091453443</v>
+        <v>33.63466698298016</v>
       </c>
       <c r="F234" t="n">
         <v>4894520</v>
@@ -5112,16 +5112,16 @@
         <v>44494</v>
       </c>
       <c r="B235" t="n">
-        <v>36.84706115722656</v>
+        <v>36.8470573425293</v>
       </c>
       <c r="C235" t="n">
-        <v>37.31127712193275</v>
+        <v>37.3112732591762</v>
       </c>
       <c r="D235" t="n">
-        <v>32.95926229019877</v>
+        <v>32.95925887799699</v>
       </c>
       <c r="E235" t="n">
-        <v>32.95926229019877</v>
+        <v>32.95925887799699</v>
       </c>
       <c r="F235" t="n">
         <v>3449995</v>
@@ -5152,16 +5152,16 @@
         <v>44496</v>
       </c>
       <c r="B237" t="n">
-        <v>35.29000473022461</v>
+        <v>35.29000854492188</v>
       </c>
       <c r="C237" t="n">
-        <v>36.07336794668348</v>
+        <v>36.07337184605893</v>
       </c>
       <c r="D237" t="n">
-        <v>34.47762778370612</v>
+        <v>34.47763151058894</v>
       </c>
       <c r="E237" t="n">
-        <v>36.07336794668348</v>
+        <v>36.07337184605893</v>
       </c>
       <c r="F237" t="n">
         <v>2270538</v>
@@ -5272,16 +5272,16 @@
         <v>44505</v>
       </c>
       <c r="B243" t="n">
-        <v>34.33256149291992</v>
+        <v>34.33255767822266</v>
       </c>
       <c r="C243" t="n">
-        <v>35.80257809171644</v>
+        <v>35.80257411368536</v>
       </c>
       <c r="D243" t="n">
-        <v>31.73102433433615</v>
+        <v>31.73102080869616</v>
       </c>
       <c r="E243" t="n">
-        <v>33.17202720107906</v>
+        <v>33.17202351532898</v>
       </c>
       <c r="F243" t="n">
         <v>9166770</v>
@@ -5312,16 +5312,16 @@
         <v>44509</v>
       </c>
       <c r="B245" t="n">
-        <v>34.50664520263672</v>
+        <v>34.50664138793945</v>
       </c>
       <c r="C245" t="n">
-        <v>35.10625735786877</v>
+        <v>35.1062534768846</v>
       </c>
       <c r="D245" t="n">
-        <v>32.63044377861175</v>
+        <v>32.63044017132788</v>
       </c>
       <c r="E245" t="n">
-        <v>33.89736430140155</v>
+        <v>33.89736055406007</v>
       </c>
       <c r="F245" t="n">
         <v>7032350</v>
@@ -5372,16 +5372,16 @@
         <v>44512</v>
       </c>
       <c r="B248" t="n">
-        <v>30.94766235351562</v>
+        <v>30.94766044616699</v>
       </c>
       <c r="C248" t="n">
-        <v>33.11399911175717</v>
+        <v>33.11399707089411</v>
       </c>
       <c r="D248" t="n">
-        <v>30.69621126299056</v>
+        <v>30.69620937113922</v>
       </c>
       <c r="E248" t="n">
-        <v>32.10819849723269</v>
+        <v>32.10819651835855</v>
       </c>
       <c r="F248" t="n">
         <v>3403064</v>
@@ -5552,16 +5552,16 @@
         <v>44526</v>
       </c>
       <c r="B257" t="n">
-        <v>26.69235992431641</v>
+        <v>26.69235801696777</v>
       </c>
       <c r="C257" t="n">
-        <v>27.61111748815896</v>
+        <v>27.61111551515892</v>
       </c>
       <c r="D257" t="n">
-        <v>25.85096918966023</v>
+        <v>25.85096734243463</v>
       </c>
       <c r="E257" t="n">
-        <v>26.59564810870458</v>
+        <v>26.59564620826666</v>
       </c>
       <c r="F257" t="n">
         <v>3664026</v>
@@ -5592,16 +5592,16 @@
         <v>44530</v>
       </c>
       <c r="B259" t="n">
-        <v>26.71170043945312</v>
+        <v>26.71169853210449</v>
       </c>
       <c r="C259" t="n">
-        <v>26.71170043945312</v>
+        <v>26.71169853210449</v>
       </c>
       <c r="D259" t="n">
-        <v>25.48346622320262</v>
+        <v>25.48346440355603</v>
       </c>
       <c r="E259" t="n">
-        <v>26.53761992558345</v>
+        <v>26.53761803066504</v>
       </c>
       <c r="F259" t="n">
         <v>4757647</v>
@@ -5612,16 +5612,16 @@
         <v>44531</v>
       </c>
       <c r="B260" t="n">
-        <v>26.69235992431641</v>
+        <v>26.69235801696777</v>
       </c>
       <c r="C260" t="n">
-        <v>28.01730598945588</v>
+        <v>28.01730398743094</v>
       </c>
       <c r="D260" t="n">
-        <v>26.32485577450663</v>
+        <v>26.32485389341864</v>
       </c>
       <c r="E260" t="n">
-        <v>27.17591712858762</v>
+        <v>27.17591518668557</v>
       </c>
       <c r="F260" t="n">
         <v>3467467</v>
@@ -5752,16 +5752,16 @@
         <v>44540</v>
       </c>
       <c r="B267" t="n">
-        <v>29.43896102905273</v>
+        <v>29.43896293640137</v>
       </c>
       <c r="C267" t="n">
-        <v>29.76778079564096</v>
+        <v>29.76778272429381</v>
       </c>
       <c r="D267" t="n">
-        <v>28.76198025889329</v>
+        <v>28.76198212238038</v>
       </c>
       <c r="E267" t="n">
-        <v>29.57435718308462</v>
+        <v>29.57435909920557</v>
       </c>
       <c r="F267" t="n">
         <v>1281952</v>
@@ -5832,16 +5832,16 @@
         <v>44546</v>
       </c>
       <c r="B271" t="n">
-        <v>30.62851524353027</v>
+        <v>30.62851333618164</v>
       </c>
       <c r="C271" t="n">
-        <v>30.86062322322113</v>
+        <v>30.86062130141829</v>
       </c>
       <c r="D271" t="n">
-        <v>29.25521235155887</v>
+        <v>29.25521052973079</v>
       </c>
       <c r="E271" t="n">
-        <v>29.49699095054871</v>
+        <v>29.4969891136642</v>
       </c>
       <c r="F271" t="n">
         <v>3477726</v>
@@ -5952,16 +5952,16 @@
         <v>44557</v>
       </c>
       <c r="B277" t="n">
-        <v>30.7252254486084</v>
+        <v>30.72522354125977</v>
       </c>
       <c r="C277" t="n">
-        <v>31.01536089416671</v>
+        <v>31.01535896880716</v>
       </c>
       <c r="D277" t="n">
-        <v>29.98054840663</v>
+        <v>29.98054654550914</v>
       </c>
       <c r="E277" t="n">
-        <v>29.98054840663</v>
+        <v>29.98054654550914</v>
       </c>
       <c r="F277" t="n">
         <v>1273927</v>
@@ -6132,16 +6132,16 @@
         <v>44571</v>
       </c>
       <c r="B286" t="n">
-        <v>33.37511825561523</v>
+        <v>33.37511444091797</v>
       </c>
       <c r="C286" t="n">
-        <v>33.89736166431392</v>
+        <v>33.89735778992546</v>
       </c>
       <c r="D286" t="n">
-        <v>32.24359399308115</v>
+        <v>32.24359030771443</v>
       </c>
       <c r="E286" t="n">
-        <v>32.3789901547752</v>
+        <v>32.37898645393302</v>
       </c>
       <c r="F286" t="n">
         <v>2829132</v>
@@ -6152,16 +6152,16 @@
         <v>44572</v>
       </c>
       <c r="B287" t="n">
-        <v>35.10625076293945</v>
+        <v>35.10625457763672</v>
       </c>
       <c r="C287" t="n">
-        <v>35.63816285834681</v>
+        <v>35.63816673084244</v>
       </c>
       <c r="D287" t="n">
-        <v>33.18169098013564</v>
+        <v>33.18169458570739</v>
       </c>
       <c r="E287" t="n">
-        <v>33.55886569280182</v>
+        <v>33.55886933935793</v>
       </c>
       <c r="F287" t="n">
         <v>3953735</v>
@@ -6172,16 +6172,16 @@
         <v>44573</v>
       </c>
       <c r="B288" t="n">
-        <v>34.89348602294922</v>
+        <v>34.89348983764648</v>
       </c>
       <c r="C288" t="n">
-        <v>35.98632394454952</v>
+        <v>35.98632787872025</v>
       </c>
       <c r="D288" t="n">
-        <v>34.13913659549451</v>
+        <v>34.13914032772324</v>
       </c>
       <c r="E288" t="n">
-        <v>35.34802942826484</v>
+        <v>35.34803329265463</v>
       </c>
       <c r="F288" t="n">
         <v>3302601</v>
@@ -6292,16 +6292,16 @@
         <v>44581</v>
       </c>
       <c r="B294" t="n">
-        <v>35.2996711730957</v>
+        <v>35.29967498779297</v>
       </c>
       <c r="C294" t="n">
-        <v>36.17007552296929</v>
+        <v>36.17007943172774</v>
       </c>
       <c r="D294" t="n">
-        <v>34.98052391082881</v>
+        <v>34.98052769103708</v>
       </c>
       <c r="E294" t="n">
-        <v>35.8702694969556</v>
+        <v>35.87027337331519</v>
       </c>
       <c r="F294" t="n">
         <v>3650414</v>
@@ -6332,16 +6332,16 @@
         <v>44585</v>
       </c>
       <c r="B296" t="n">
-        <v>34.35190582275391</v>
+        <v>34.35190200805664</v>
       </c>
       <c r="C296" t="n">
-        <v>35.31902021252021</v>
+        <v>35.3190162904272</v>
       </c>
       <c r="D296" t="n">
-        <v>34.05209976231423</v>
+        <v>34.05209598090971</v>
       </c>
       <c r="E296" t="n">
-        <v>34.2358508967577</v>
+        <v>34.23584709494806</v>
       </c>
       <c r="F296" t="n">
         <v>2113697</v>
@@ -6392,16 +6392,16 @@
         <v>44588</v>
       </c>
       <c r="B299" t="n">
-        <v>36.09270858764648</v>
+        <v>36.09271240234375</v>
       </c>
       <c r="C299" t="n">
-        <v>37.10817788022283</v>
+        <v>37.1081818022467</v>
       </c>
       <c r="D299" t="n">
-        <v>35.68652012110085</v>
+        <v>35.68652389286739</v>
       </c>
       <c r="E299" t="n">
-        <v>35.87994373577622</v>
+        <v>35.87994752798603</v>
       </c>
       <c r="F299" t="n">
         <v>3171460</v>
@@ -6492,16 +6492,16 @@
         <v>44595</v>
       </c>
       <c r="B304" t="n">
-        <v>35.2996711730957</v>
+        <v>35.29967498779297</v>
       </c>
       <c r="C304" t="n">
-        <v>35.58980845477045</v>
+        <v>35.58981230082171</v>
       </c>
       <c r="D304" t="n">
-        <v>33.84899975502328</v>
+        <v>33.84900341295216</v>
       </c>
       <c r="E304" t="n">
-        <v>34.98052391082881</v>
+        <v>34.98052769103708</v>
       </c>
       <c r="F304" t="n">
         <v>4177823</v>
@@ -6592,16 +6592,16 @@
         <v>44602</v>
       </c>
       <c r="B309" t="n">
-        <v>37.28226089477539</v>
+        <v>37.28226470947266</v>
       </c>
       <c r="C309" t="n">
-        <v>38.38477139493146</v>
+        <v>38.3847753224369</v>
       </c>
       <c r="D309" t="n">
-        <v>36.33448778997354</v>
+        <v>36.33449150769526</v>
       </c>
       <c r="E309" t="n">
-        <v>36.3635015200494</v>
+        <v>36.36350524073979</v>
       </c>
       <c r="F309" t="n">
         <v>7025951</v>
@@ -6612,16 +6612,16 @@
         <v>44603</v>
       </c>
       <c r="B310" t="n">
-        <v>38.07529449462891</v>
+        <v>38.07529067993164</v>
       </c>
       <c r="C310" t="n">
-        <v>38.49115547855604</v>
+        <v>38.49115162219439</v>
       </c>
       <c r="D310" t="n">
-        <v>37.37897243800389</v>
+        <v>37.37896869306991</v>
       </c>
       <c r="E310" t="n">
-        <v>37.78516092896444</v>
+        <v>37.78515714333515</v>
       </c>
       <c r="F310" t="n">
         <v>5486491</v>
@@ -6632,16 +6632,16 @@
         <v>44606</v>
       </c>
       <c r="B311" t="n">
-        <v>37.57239532470703</v>
+        <v>37.57239151000977</v>
       </c>
       <c r="C311" t="n">
-        <v>38.84898823510746</v>
+        <v>38.84898429079868</v>
       </c>
       <c r="D311" t="n">
-        <v>36.95344198127135</v>
+        <v>36.95343822941596</v>
       </c>
       <c r="E311" t="n">
-        <v>38.2977310983781</v>
+        <v>38.29772721003804</v>
       </c>
       <c r="F311" t="n">
         <v>3902640</v>
@@ -6652,16 +6652,16 @@
         <v>44607</v>
       </c>
       <c r="B312" t="n">
-        <v>35.79290390014648</v>
+        <v>35.79290008544922</v>
       </c>
       <c r="C312" t="n">
-        <v>36.65363583255173</v>
+        <v>36.65363192612031</v>
       </c>
       <c r="D312" t="n">
-        <v>35.63816650158672</v>
+        <v>35.63816270338088</v>
       </c>
       <c r="E312" t="n">
-        <v>36.55692589534578</v>
+        <v>36.55692199922141</v>
       </c>
       <c r="F312" t="n">
         <v>3810709</v>
@@ -6672,16 +6672,16 @@
         <v>44608</v>
       </c>
       <c r="B313" t="n">
-        <v>35.92829895019531</v>
+        <v>35.92830276489258</v>
       </c>
       <c r="C313" t="n">
-        <v>36.80837209332255</v>
+        <v>36.80837600146183</v>
       </c>
       <c r="D313" t="n">
-        <v>35.69619285953032</v>
+        <v>35.69619664958365</v>
       </c>
       <c r="E313" t="n">
-        <v>36.4408698462091</v>
+        <v>36.44087371532872</v>
       </c>
       <c r="F313" t="n">
         <v>4244663</v>
@@ -6692,16 +6692,16 @@
         <v>44609</v>
       </c>
       <c r="B314" t="n">
-        <v>35.2996711730957</v>
+        <v>35.29967498779297</v>
       </c>
       <c r="C314" t="n">
-        <v>35.89928322512308</v>
+        <v>35.89928710461807</v>
       </c>
       <c r="D314" t="n">
-        <v>34.41959807888318</v>
+        <v>34.41960179847439</v>
       </c>
       <c r="E314" t="n">
-        <v>35.68651838361181</v>
+        <v>35.68652224011414</v>
       </c>
       <c r="F314" t="n">
         <v>4430658</v>
@@ -6712,16 +6712,16 @@
         <v>44610</v>
       </c>
       <c r="B315" t="n">
-        <v>34.48729705810547</v>
+        <v>34.48730087280273</v>
       </c>
       <c r="C315" t="n">
-        <v>35.41572509065163</v>
+        <v>35.41572900804387</v>
       </c>
       <c r="D315" t="n">
-        <v>33.80064384086931</v>
+        <v>33.80064757961473</v>
       </c>
       <c r="E315" t="n">
-        <v>34.83545803875718</v>
+        <v>34.83546189196511</v>
       </c>
       <c r="F315" t="n">
         <v>4069741</v>
@@ -6852,16 +6852,16 @@
         <v>44623</v>
       </c>
       <c r="B322" t="n">
-        <v>37.34028244018555</v>
+        <v>37.34028625488281</v>
       </c>
       <c r="C322" t="n">
-        <v>37.88187078764361</v>
+        <v>37.88187465766974</v>
       </c>
       <c r="D322" t="n">
-        <v>36.31514444477941</v>
+        <v>36.31514815474819</v>
       </c>
       <c r="E322" t="n">
-        <v>37.12751759702811</v>
+        <v>37.12752138998924</v>
       </c>
       <c r="F322" t="n">
         <v>9786414</v>
@@ -6892,16 +6892,16 @@
         <v>44627</v>
       </c>
       <c r="B324" t="n">
-        <v>37.04048538208008</v>
+        <v>37.04048156738281</v>
       </c>
       <c r="C324" t="n">
-        <v>39.28418904358112</v>
+        <v>39.28418499781101</v>
       </c>
       <c r="D324" t="n">
-        <v>36.65363811402602</v>
+        <v>36.65363433916909</v>
       </c>
       <c r="E324" t="n">
-        <v>38.17200970618351</v>
+        <v>38.17200577495368</v>
       </c>
       <c r="F324" t="n">
         <v>5025922</v>
@@ -6952,16 +6952,16 @@
         <v>44630</v>
       </c>
       <c r="B327" t="n">
-        <v>35.72520446777344</v>
+        <v>35.7252082824707</v>
       </c>
       <c r="C327" t="n">
-        <v>37.22423084456335</v>
+        <v>37.22423481932497</v>
       </c>
       <c r="D327" t="n">
-        <v>35.51243962707166</v>
+        <v>35.51244341905014</v>
       </c>
       <c r="E327" t="n">
-        <v>36.75034245134777</v>
+        <v>36.75034637550812</v>
       </c>
       <c r="F327" t="n">
         <v>4502679</v>
@@ -7032,16 +7032,16 @@
         <v>44636</v>
       </c>
       <c r="B331" t="n">
-        <v>32.84320831298828</v>
+        <v>32.84320449829102</v>
       </c>
       <c r="C331" t="n">
-        <v>34.44861737575539</v>
+        <v>34.44861337459189</v>
       </c>
       <c r="D331" t="n">
-        <v>32.34030985608281</v>
+        <v>32.34030609979657</v>
       </c>
       <c r="E331" t="n">
-        <v>34.10045632903992</v>
+        <v>34.10045236831488</v>
       </c>
       <c r="F331" t="n">
         <v>3899288</v>
@@ -7092,16 +7092,16 @@
         <v>44641</v>
       </c>
       <c r="B334" t="n">
-        <v>36.61495208740234</v>
+        <v>36.61494827270508</v>
       </c>
       <c r="C334" t="n">
-        <v>36.86640318776314</v>
+        <v>36.86639934686866</v>
       </c>
       <c r="D334" t="n">
-        <v>35.88961626653654</v>
+        <v>35.88961252740777</v>
       </c>
       <c r="E334" t="n">
-        <v>35.97665746445866</v>
+        <v>35.97665371626157</v>
       </c>
       <c r="F334" t="n">
         <v>3600944</v>
@@ -7212,16 +7212,16 @@
         <v>44649</v>
       </c>
       <c r="B340" t="n">
-        <v>40.11590576171875</v>
+        <v>40.11590194702148</v>
       </c>
       <c r="C340" t="n">
-        <v>40.60913544747385</v>
+        <v>40.60913158587444</v>
       </c>
       <c r="D340" t="n">
-        <v>37.8141747233464</v>
+        <v>37.81417112752509</v>
       </c>
       <c r="E340" t="n">
-        <v>38.00759834997051</v>
+        <v>38.00759473575618</v>
       </c>
       <c r="F340" t="n">
         <v>6952609</v>
@@ -7252,16 +7252,16 @@
         <v>44651</v>
       </c>
       <c r="B342" t="n">
-        <v>40.47373580932617</v>
+        <v>40.47373962402344</v>
       </c>
       <c r="C342" t="n">
-        <v>41.13137533388116</v>
+        <v>41.13137921056172</v>
       </c>
       <c r="D342" t="n">
-        <v>39.6710313879373</v>
+        <v>39.67103512697872</v>
       </c>
       <c r="E342" t="n">
-        <v>40.13524730247168</v>
+        <v>40.135251085266</v>
       </c>
       <c r="F342" t="n">
         <v>3810811</v>
@@ -7312,16 +7312,16 @@
         <v>44656</v>
       </c>
       <c r="B345" t="n">
-        <v>41.9727668762207</v>
+        <v>41.97276306152344</v>
       </c>
       <c r="C345" t="n">
-        <v>43.03659497534015</v>
+        <v>43.03659106395681</v>
       </c>
       <c r="D345" t="n">
-        <v>41.5762508676977</v>
+        <v>41.57624708903781</v>
       </c>
       <c r="E345" t="n">
-        <v>42.30158667490721</v>
+        <v>42.30158283032514</v>
       </c>
       <c r="F345" t="n">
         <v>5903074</v>
@@ -7432,16 +7432,16 @@
         <v>44664</v>
       </c>
       <c r="B351" t="n">
-        <v>43.62653350830078</v>
+        <v>43.62652969360352</v>
       </c>
       <c r="C351" t="n">
-        <v>43.71357095479976</v>
+        <v>43.71356713249195</v>
       </c>
       <c r="D351" t="n">
-        <v>42.8431702567798</v>
+        <v>42.8431665105797</v>
       </c>
       <c r="E351" t="n">
-        <v>43.30738621093589</v>
+        <v>43.30738242414481</v>
       </c>
       <c r="F351" t="n">
         <v>3238402</v>
@@ -7452,16 +7452,16 @@
         <v>44665</v>
       </c>
       <c r="B352" t="n">
-        <v>42.93987655639648</v>
+        <v>42.93988037109375</v>
       </c>
       <c r="C352" t="n">
-        <v>43.62652981023535</v>
+        <v>43.62653368593358</v>
       </c>
       <c r="D352" t="n">
-        <v>42.2242133212342</v>
+        <v>42.2242170723533</v>
       </c>
       <c r="E352" t="n">
-        <v>43.62652981023535</v>
+        <v>43.62653368593358</v>
       </c>
       <c r="F352" t="n">
         <v>2345809</v>
@@ -7552,16 +7552,16 @@
         <v>44676</v>
       </c>
       <c r="B357" t="n">
-        <v>41.94374847412109</v>
+        <v>41.94375228881836</v>
       </c>
       <c r="C357" t="n">
-        <v>42.40796438837074</v>
+        <v>42.40796824528748</v>
       </c>
       <c r="D357" t="n">
-        <v>40.64781815768625</v>
+        <v>40.64782185452133</v>
       </c>
       <c r="E357" t="n">
-        <v>40.75420058099602</v>
+        <v>40.75420428750637</v>
       </c>
       <c r="F357" t="n">
         <v>3287465</v>
@@ -7592,16 +7592,16 @@
         <v>44678</v>
       </c>
       <c r="B359" t="n">
-        <v>42.16619110107422</v>
+        <v>42.16618728637695</v>
       </c>
       <c r="C359" t="n">
-        <v>43.58784900340616</v>
+        <v>43.58784506009413</v>
       </c>
       <c r="D359" t="n">
-        <v>41.46986901615963</v>
+        <v>41.46986526445734</v>
       </c>
       <c r="E359" t="n">
-        <v>43.52015279261696</v>
+        <v>43.52014885542929</v>
       </c>
       <c r="F359" t="n">
         <v>3779727</v>
@@ -7672,16 +7672,16 @@
         <v>44684</v>
       </c>
       <c r="B363" t="n">
-        <v>42.12749862670898</v>
+        <v>42.12750244140625</v>
       </c>
       <c r="C363" t="n">
-        <v>42.54335956584936</v>
+        <v>42.54336341820335</v>
       </c>
       <c r="D363" t="n">
-        <v>41.25709802345466</v>
+        <v>41.25710175933607</v>
       </c>
       <c r="E363" t="n">
-        <v>42.54335956584936</v>
+        <v>42.54336341820335</v>
       </c>
       <c r="F363" t="n">
         <v>4458389</v>
@@ -7692,16 +7692,16 @@
         <v>44685</v>
       </c>
       <c r="B364" t="n">
-        <v>44.10041809082031</v>
+        <v>44.10041427612305</v>
       </c>
       <c r="C364" t="n">
-        <v>44.32285544811791</v>
+        <v>44.32285161417975</v>
       </c>
       <c r="D364" t="n">
-        <v>42.16618932580826</v>
+        <v>42.16618567842227</v>
       </c>
       <c r="E364" t="n">
-        <v>43.04626251447057</v>
+        <v>43.04625879095802</v>
       </c>
       <c r="F364" t="n">
         <v>5759540</v>
@@ -7712,16 +7712,16 @@
         <v>44686</v>
       </c>
       <c r="B365" t="n">
-        <v>42.92053604125977</v>
+        <v>42.92053985595703</v>
       </c>
       <c r="C365" t="n">
-        <v>44.57429987842104</v>
+        <v>44.57430384010176</v>
       </c>
       <c r="D365" t="n">
-        <v>42.01144918067956</v>
+        <v>42.01145291457887</v>
       </c>
       <c r="E365" t="n">
-        <v>44.09074271874429</v>
+        <v>44.09074663744735</v>
       </c>
       <c r="F365" t="n">
         <v>4814532</v>
@@ -7732,16 +7732,16 @@
         <v>44687</v>
       </c>
       <c r="B366" t="n">
-        <v>42.55303192138672</v>
+        <v>42.55303573608398</v>
       </c>
       <c r="C366" t="n">
-        <v>43.90698966019007</v>
+        <v>43.90699359626386</v>
       </c>
       <c r="D366" t="n">
-        <v>41.82769621387857</v>
+        <v>41.82769996355259</v>
       </c>
       <c r="E366" t="n">
-        <v>43.33639133753226</v>
+        <v>43.33639522245434</v>
       </c>
       <c r="F366" t="n">
         <v>4093307</v>
@@ -7892,16 +7892,16 @@
         <v>44699</v>
       </c>
       <c r="B374" t="n">
-        <v>39.99985122680664</v>
+        <v>39.99985504150391</v>
       </c>
       <c r="C374" t="n">
-        <v>42.2242133773643</v>
+        <v>42.22421740419406</v>
       </c>
       <c r="D374" t="n">
-        <v>39.72905892177436</v>
+        <v>39.72906271064676</v>
       </c>
       <c r="E374" t="n">
-        <v>42.13717219055205</v>
+        <v>42.13717620908088</v>
       </c>
       <c r="F374" t="n">
         <v>1865839</v>
@@ -7952,16 +7952,16 @@
         <v>44704</v>
       </c>
       <c r="B377" t="n">
-        <v>42.28224182128906</v>
+        <v>42.28224563598633</v>
       </c>
       <c r="C377" t="n">
-        <v>42.7948127143697</v>
+        <v>42.79481657531103</v>
       </c>
       <c r="D377" t="n">
-        <v>41.3538099687909</v>
+        <v>41.35381369972519</v>
       </c>
       <c r="E377" t="n">
-        <v>41.42150992041549</v>
+        <v>41.42151365745766</v>
       </c>
       <c r="F377" t="n">
         <v>3400119</v>
@@ -8012,16 +8012,16 @@
         <v>44707</v>
       </c>
       <c r="B380" t="n">
-        <v>46.59557342529297</v>
+        <v>46.5955696105957</v>
       </c>
       <c r="C380" t="n">
-        <v>47.16617181868395</v>
+        <v>47.1661679572728</v>
       </c>
       <c r="D380" t="n">
-        <v>45.10621935322675</v>
+        <v>45.10621566046026</v>
       </c>
       <c r="E380" t="n">
-        <v>45.25128426416589</v>
+        <v>45.2512805595232</v>
       </c>
       <c r="F380" t="n">
         <v>4582217</v>
@@ -8072,16 +8072,16 @@
         <v>44712</v>
       </c>
       <c r="B383" t="n">
-        <v>47.14683151245117</v>
+        <v>47.14682769775391</v>
       </c>
       <c r="C383" t="n">
-        <v>49.54527256510714</v>
+        <v>49.5452685563496</v>
       </c>
       <c r="D383" t="n">
-        <v>47.11781778017441</v>
+        <v>47.11781396782467</v>
       </c>
       <c r="E383" t="n">
-        <v>48.22032836396376</v>
+        <v>48.22032446240879</v>
       </c>
       <c r="F383" t="n">
         <v>6322705</v>
@@ -8152,16 +8152,16 @@
         <v>44718</v>
       </c>
       <c r="B387" t="n">
-        <v>45.31898498535156</v>
+        <v>45.3189811706543</v>
       </c>
       <c r="C387" t="n">
-        <v>47.45630618888874</v>
+        <v>47.4563021942838</v>
       </c>
       <c r="D387" t="n">
-        <v>45.13523009894016</v>
+        <v>45.13522629971035</v>
       </c>
       <c r="E387" t="n">
-        <v>47.156500121283</v>
+        <v>47.15649615191405</v>
       </c>
       <c r="F387" t="n">
         <v>1711233</v>
@@ -8172,16 +8172,16 @@
         <v>44719</v>
       </c>
       <c r="B388" t="n">
-        <v>45.31898498535156</v>
+        <v>45.3189811706543</v>
       </c>
       <c r="C388" t="n">
-        <v>45.84122466966569</v>
+        <v>45.84122081100923</v>
       </c>
       <c r="D388" t="n">
-        <v>44.73871408907649</v>
+        <v>44.73871032322317</v>
       </c>
       <c r="E388" t="n">
-        <v>44.98049269229714</v>
+        <v>44.98048890609225</v>
       </c>
       <c r="F388" t="n">
         <v>1887578</v>
@@ -8192,16 +8192,16 @@
         <v>44720</v>
       </c>
       <c r="B389" t="n">
-        <v>45.25128173828125</v>
+        <v>45.25128555297852</v>
       </c>
       <c r="C389" t="n">
-        <v>46.00563122530019</v>
+        <v>46.00563510358936</v>
       </c>
       <c r="D389" t="n">
-        <v>44.9224619623857</v>
+        <v>44.92246574936335</v>
       </c>
       <c r="E389" t="n">
-        <v>45.31898169100119</v>
+        <v>45.31898551140559</v>
       </c>
       <c r="F389" t="n">
         <v>1920490</v>
@@ -8212,16 +8212,16 @@
         <v>44721</v>
       </c>
       <c r="B390" t="n">
-        <v>44.50660705566406</v>
+        <v>44.5066032409668</v>
       </c>
       <c r="C390" t="n">
-        <v>45.59944512032232</v>
+        <v>45.59944121195702</v>
       </c>
       <c r="D390" t="n">
-        <v>44.32285592064108</v>
+        <v>44.32285212169327</v>
       </c>
       <c r="E390" t="n">
-        <v>45.2222703572209</v>
+        <v>45.22226648118356</v>
       </c>
       <c r="F390" t="n">
         <v>1644697</v>
@@ -8472,16 +8472,16 @@
         <v>44741</v>
       </c>
       <c r="B403" t="n">
-        <v>34.71940994262695</v>
+        <v>34.71940612792969</v>
       </c>
       <c r="C403" t="n">
-        <v>35.41573204057546</v>
+        <v>35.41572814937177</v>
       </c>
       <c r="D403" t="n">
-        <v>34.0907840567348</v>
+        <v>34.09078031110602</v>
       </c>
       <c r="E403" t="n">
-        <v>35.29967710839206</v>
+        <v>35.29967322993957</v>
       </c>
       <c r="F403" t="n">
         <v>2690880</v>
@@ -8532,16 +8532,16 @@
         <v>44746</v>
       </c>
       <c r="B406" t="n">
-        <v>35.08690643310547</v>
+        <v>35.08691024780273</v>
       </c>
       <c r="C406" t="n">
-        <v>35.60914979405575</v>
+        <v>35.60915366553204</v>
       </c>
       <c r="D406" t="n">
-        <v>34.19716459197961</v>
+        <v>34.1971683099429</v>
       </c>
       <c r="E406" t="n">
-        <v>34.57433556409744</v>
+        <v>34.57433932306729</v>
       </c>
       <c r="F406" t="n">
         <v>2359523</v>
@@ -8612,16 +8612,16 @@
         <v>44750</v>
       </c>
       <c r="B410" t="n">
-        <v>31.81806564331055</v>
+        <v>31.81806373596191</v>
       </c>
       <c r="C410" t="n">
-        <v>32.48537398775778</v>
+        <v>32.48537204040704</v>
       </c>
       <c r="D410" t="n">
-        <v>31.19911226993215</v>
+        <v>31.19911039968697</v>
       </c>
       <c r="E410" t="n">
-        <v>31.31516719855805</v>
+        <v>31.3151653213559</v>
       </c>
       <c r="F410" t="n">
         <v>4375906</v>
@@ -8712,16 +8712,16 @@
         <v>44757</v>
       </c>
       <c r="B415" t="n">
-        <v>27.79486656188965</v>
+        <v>27.79486846923828</v>
       </c>
       <c r="C415" t="n">
-        <v>29.07145943509457</v>
+        <v>29.07146143004599</v>
       </c>
       <c r="D415" t="n">
-        <v>27.79486656188965</v>
+        <v>27.79486846923828</v>
       </c>
       <c r="E415" t="n">
-        <v>29.06178694260021</v>
+        <v>29.06178893688788</v>
       </c>
       <c r="F415" t="n">
         <v>4618481</v>
@@ -8752,16 +8752,16 @@
         <v>44761</v>
       </c>
       <c r="B417" t="n">
-        <v>29.43896102905273</v>
+        <v>29.43896293640137</v>
       </c>
       <c r="C417" t="n">
-        <v>29.5356728353309</v>
+        <v>29.53567474894549</v>
       </c>
       <c r="D417" t="n">
-        <v>28.11401509178381</v>
+        <v>28.11401691328927</v>
       </c>
       <c r="E417" t="n">
-        <v>28.14302882104603</v>
+        <v>28.14303064443129</v>
       </c>
       <c r="F417" t="n">
         <v>4570230</v>
@@ -8772,16 +8772,16 @@
         <v>44762</v>
       </c>
       <c r="B418" t="n">
-        <v>30.5994987487793</v>
+        <v>30.59950065612793</v>
       </c>
       <c r="C418" t="n">
-        <v>30.97667347904845</v>
+        <v>30.97667540990739</v>
       </c>
       <c r="D418" t="n">
-        <v>29.21652536238831</v>
+        <v>29.21652718353251</v>
       </c>
       <c r="E418" t="n">
-        <v>29.21652536238831</v>
+        <v>29.21652718353251</v>
       </c>
       <c r="F418" t="n">
         <v>5027446</v>
@@ -8792,16 +8792,16 @@
         <v>44763</v>
       </c>
       <c r="B419" t="n">
-        <v>29.44863319396973</v>
+        <v>29.44863510131836</v>
       </c>
       <c r="C419" t="n">
-        <v>29.86449039614633</v>
+        <v>29.86449233042948</v>
       </c>
       <c r="D419" t="n">
-        <v>28.83935050759925</v>
+        <v>28.83935237548546</v>
       </c>
       <c r="E419" t="n">
-        <v>29.86449039614633</v>
+        <v>29.86449233042948</v>
       </c>
       <c r="F419" t="n">
         <v>5437325</v>
@@ -8832,16 +8832,16 @@
         <v>44767</v>
       </c>
       <c r="B421" t="n">
-        <v>29.26488304138184</v>
+        <v>29.2648811340332</v>
       </c>
       <c r="C421" t="n">
-        <v>29.71942650877206</v>
+        <v>29.7194245717984</v>
       </c>
       <c r="D421" t="n">
-        <v>28.43316480875549</v>
+        <v>28.43316295561438</v>
       </c>
       <c r="E421" t="n">
-        <v>28.87803765682343</v>
+        <v>28.87803577468757</v>
       </c>
       <c r="F421" t="n">
         <v>3521914</v>
@@ -8852,16 +8852,16 @@
         <v>44768</v>
       </c>
       <c r="B422" t="n">
-        <v>28.95540618896484</v>
+        <v>28.95540428161621</v>
       </c>
       <c r="C422" t="n">
-        <v>30.15462856046375</v>
+        <v>30.15462657412001</v>
       </c>
       <c r="D422" t="n">
-        <v>28.81033940483069</v>
+        <v>28.81033750703789</v>
       </c>
       <c r="E422" t="n">
-        <v>29.88383623072646</v>
+        <v>29.88383426222034</v>
       </c>
       <c r="F422" t="n">
         <v>2984449</v>
@@ -8872,16 +8872,16 @@
         <v>44769</v>
       </c>
       <c r="B423" t="n">
-        <v>29.66139793395996</v>
+        <v>29.66139984130859</v>
       </c>
       <c r="C423" t="n">
-        <v>29.76778035716261</v>
+        <v>29.76778227135207</v>
       </c>
       <c r="D423" t="n">
-        <v>28.6169130648438</v>
+        <v>28.61691490502781</v>
       </c>
       <c r="E423" t="n">
-        <v>28.95540344493757</v>
+        <v>28.95540530688788</v>
       </c>
       <c r="F423" t="n">
         <v>2554762</v>
@@ -8892,16 +8892,16 @@
         <v>44770</v>
       </c>
       <c r="B424" t="n">
-        <v>30.78325080871582</v>
+        <v>30.78325271606445</v>
       </c>
       <c r="C424" t="n">
-        <v>30.88963323601387</v>
+        <v>30.88963514995402</v>
       </c>
       <c r="D424" t="n">
-        <v>29.53567353730325</v>
+        <v>29.53567536735125</v>
       </c>
       <c r="E424" t="n">
-        <v>29.96120324649545</v>
+        <v>29.96120510290952</v>
       </c>
       <c r="F424" t="n">
         <v>4208906</v>
@@ -8952,16 +8952,16 @@
         <v>44775</v>
       </c>
       <c r="B427" t="n">
-        <v>31.85675048828125</v>
+        <v>31.85674858093262</v>
       </c>
       <c r="C427" t="n">
-        <v>32.07918409507452</v>
+        <v>32.0791821744082</v>
       </c>
       <c r="D427" t="n">
-        <v>30.94766170651904</v>
+        <v>30.94765985359998</v>
       </c>
       <c r="E427" t="n">
-        <v>31.32483646063348</v>
+        <v>31.32483458513196</v>
       </c>
       <c r="F427" t="n">
         <v>3020206</v>
@@ -9072,16 +9072,16 @@
         <v>44783</v>
       </c>
       <c r="B433" t="n">
-        <v>33.26873779296875</v>
+        <v>33.26873397827148</v>
       </c>
       <c r="C433" t="n">
-        <v>33.97473237410905</v>
+        <v>33.97472847846024</v>
       </c>
       <c r="D433" t="n">
-        <v>32.87222177725572</v>
+        <v>32.87221800802422</v>
       </c>
       <c r="E433" t="n">
-        <v>33.62657133023831</v>
+        <v>33.62656747451073</v>
       </c>
       <c r="F433" t="n">
         <v>3325457</v>
@@ -9152,16 +9152,16 @@
         <v>44789</v>
       </c>
       <c r="B437" t="n">
-        <v>32.27260971069336</v>
+        <v>32.27260589599609</v>
       </c>
       <c r="C437" t="n">
-        <v>32.61110200955398</v>
+        <v>32.61109815484615</v>
       </c>
       <c r="D437" t="n">
-        <v>31.73102503057709</v>
+        <v>31.73102127989639</v>
       </c>
       <c r="E437" t="n">
-        <v>32.39833338730038</v>
+        <v>32.39832955774229</v>
       </c>
       <c r="F437" t="n">
         <v>2684074</v>
@@ -9172,16 +9172,16 @@
         <v>44790</v>
       </c>
       <c r="B438" t="n">
-        <v>32.53372573852539</v>
+        <v>32.53372955322266</v>
       </c>
       <c r="C438" t="n">
-        <v>32.93024545622303</v>
+        <v>32.93024931741367</v>
       </c>
       <c r="D438" t="n">
-        <v>31.80839000156146</v>
+        <v>31.80839373121048</v>
       </c>
       <c r="E438" t="n">
-        <v>31.81806249384815</v>
+        <v>31.8180662246313</v>
       </c>
       <c r="F438" t="n">
         <v>3057587</v>
@@ -9252,16 +9252,16 @@
         <v>44796</v>
       </c>
       <c r="B442" t="n">
-        <v>35.11592483520508</v>
+        <v>35.11592102050781</v>
       </c>
       <c r="C442" t="n">
-        <v>35.54145457609587</v>
+        <v>35.54145071517264</v>
       </c>
       <c r="D442" t="n">
-        <v>33.43314711052539</v>
+        <v>33.43314347863087</v>
       </c>
       <c r="E442" t="n">
-        <v>33.46216084263848</v>
+        <v>33.46215720759215</v>
       </c>
       <c r="F442" t="n">
         <v>5706007</v>
@@ -9292,16 +9292,16 @@
         <v>44798</v>
       </c>
       <c r="B444" t="n">
-        <v>35.73487854003906</v>
+        <v>35.7348747253418</v>
       </c>
       <c r="C444" t="n">
-        <v>36.56659679067325</v>
+        <v>36.56659288719009</v>
       </c>
       <c r="D444" t="n">
-        <v>35.39638999233915</v>
+        <v>35.39638621377552</v>
       </c>
       <c r="E444" t="n">
-        <v>35.86060596289047</v>
+        <v>35.8606021347718</v>
       </c>
       <c r="F444" t="n">
         <v>2850362</v>
@@ -9372,16 +9372,16 @@
         <v>44804</v>
       </c>
       <c r="B448" t="n">
-        <v>36.16040802001953</v>
+        <v>36.16040420532227</v>
       </c>
       <c r="C448" t="n">
-        <v>36.46021408739674</v>
+        <v>36.46021024107181</v>
       </c>
       <c r="D448" t="n">
-        <v>35.22230734004456</v>
+        <v>35.22230362431106</v>
       </c>
       <c r="E448" t="n">
-        <v>35.91862941698318</v>
+        <v>35.91862562779205</v>
       </c>
       <c r="F448" t="n">
         <v>3394125</v>
@@ -9392,16 +9392,16 @@
         <v>44805</v>
       </c>
       <c r="B449" t="n">
-        <v>35.58013916015625</v>
+        <v>35.58013534545898</v>
       </c>
       <c r="C449" t="n">
-        <v>36.22810623483188</v>
+        <v>36.22810235066332</v>
       </c>
       <c r="D449" t="n">
-        <v>35.00954078502128</v>
+        <v>35.00953703150028</v>
       </c>
       <c r="E449" t="n">
-        <v>35.84125898955293</v>
+        <v>35.8412551468599</v>
       </c>
       <c r="F449" t="n">
         <v>3340084</v>
@@ -9492,16 +9492,16 @@
         <v>44813</v>
       </c>
       <c r="B454" t="n">
-        <v>35.92829895019531</v>
+        <v>35.92830276489258</v>
       </c>
       <c r="C454" t="n">
-        <v>36.3731698941971</v>
+        <v>36.37317375612866</v>
       </c>
       <c r="D454" t="n">
-        <v>35.60915167019012</v>
+        <v>35.60915545100184</v>
       </c>
       <c r="E454" t="n">
-        <v>35.79290279374685</v>
+        <v>35.79290659406839</v>
       </c>
       <c r="F454" t="n">
         <v>3544465</v>
@@ -9552,16 +9552,16 @@
         <v>44818</v>
       </c>
       <c r="B457" t="n">
-        <v>37.25325012207031</v>
+        <v>37.25324630737305</v>
       </c>
       <c r="C457" t="n">
-        <v>37.57239743066493</v>
+        <v>37.57239358328728</v>
       </c>
       <c r="D457" t="n">
-        <v>35.96698839437353</v>
+        <v>35.96698471138824</v>
       </c>
       <c r="E457" t="n">
-        <v>36.05402584393507</v>
+        <v>36.05402215203722</v>
       </c>
       <c r="F457" t="n">
         <v>4057043</v>
@@ -9592,16 +9592,16 @@
         <v>44820</v>
       </c>
       <c r="B459" t="n">
-        <v>36.7987060546875</v>
+        <v>36.79870223999023</v>
       </c>
       <c r="C459" t="n">
-        <v>36.7987060546875</v>
+        <v>36.79870223999023</v>
       </c>
       <c r="D459" t="n">
-        <v>35.7832329328566</v>
+        <v>35.78322922342723</v>
       </c>
       <c r="E459" t="n">
-        <v>36.14106646140942</v>
+        <v>36.14106271488564</v>
       </c>
       <c r="F459" t="n">
         <v>2974596</v>
@@ -9612,16 +9612,16 @@
         <v>44823</v>
       </c>
       <c r="B460" t="n">
-        <v>36.84706115722656</v>
+        <v>36.8470573425293</v>
       </c>
       <c r="C460" t="n">
-        <v>37.39831831798563</v>
+        <v>37.3983144462179</v>
       </c>
       <c r="D460" t="n">
-        <v>35.79290555412169</v>
+        <v>35.7929018485589</v>
       </c>
       <c r="E460" t="n">
-        <v>35.79290555412169</v>
+        <v>35.7929018485589</v>
       </c>
       <c r="F460" t="n">
         <v>3461677</v>
@@ -9652,16 +9652,16 @@
         <v>44825</v>
       </c>
       <c r="B462" t="n">
-        <v>38.03661346435547</v>
+        <v>38.0366096496582</v>
       </c>
       <c r="C462" t="n">
-        <v>38.79096301231463</v>
+        <v>38.79095912196355</v>
       </c>
       <c r="D462" t="n">
-        <v>37.62075246461414</v>
+        <v>37.62074869162363</v>
       </c>
       <c r="E462" t="n">
-        <v>37.93989977373904</v>
+        <v>37.9398959687412</v>
       </c>
       <c r="F462" t="n">
         <v>4689181</v>
@@ -9732,16 +9732,16 @@
         <v>44831</v>
       </c>
       <c r="B466" t="n">
-        <v>33.61689376831055</v>
+        <v>33.61689758300781</v>
       </c>
       <c r="C466" t="n">
-        <v>34.44861190035511</v>
+        <v>34.44861580943209</v>
       </c>
       <c r="D466" t="n">
-        <v>33.3267602334253</v>
+        <v>33.32676401519949</v>
       </c>
       <c r="E466" t="n">
-        <v>34.44861190035511</v>
+        <v>34.44861580943209</v>
       </c>
       <c r="F466" t="n">
         <v>5480701</v>
@@ -9752,16 +9752,16 @@
         <v>44832</v>
       </c>
       <c r="B467" t="n">
-        <v>34.57433700561523</v>
+        <v>34.5743408203125</v>
       </c>
       <c r="C467" t="n">
-        <v>34.99987045518622</v>
+        <v>34.99987431683395</v>
       </c>
       <c r="D467" t="n">
-        <v>33.19136547412988</v>
+        <v>33.19136913623947</v>
       </c>
       <c r="E467" t="n">
-        <v>33.66525014270204</v>
+        <v>33.66525385709685</v>
       </c>
       <c r="F467" t="n">
         <v>4399676</v>
@@ -9772,16 +9772,16 @@
         <v>44833</v>
       </c>
       <c r="B468" t="n">
-        <v>33.90703201293945</v>
+        <v>33.90702819824219</v>
       </c>
       <c r="C468" t="n">
-        <v>34.69039528924284</v>
+        <v>34.69039138641359</v>
       </c>
       <c r="D468" t="n">
-        <v>33.09465875193581</v>
+        <v>33.09465502863428</v>
       </c>
       <c r="E468" t="n">
-        <v>34.61302658569848</v>
+        <v>34.61302269157358</v>
       </c>
       <c r="F468" t="n">
         <v>4499631</v>
@@ -9812,16 +9812,16 @@
         <v>44837</v>
       </c>
       <c r="B470" t="n">
-        <v>36.7987060546875</v>
+        <v>36.79870223999023</v>
       </c>
       <c r="C470" t="n">
-        <v>36.91476098234264</v>
+        <v>36.91475715561467</v>
       </c>
       <c r="D470" t="n">
-        <v>35.52211309320833</v>
+        <v>35.52210941084767</v>
       </c>
       <c r="E470" t="n">
-        <v>36.26679013465196</v>
+        <v>36.26678637509517</v>
       </c>
       <c r="F470" t="n">
         <v>4419789</v>
@@ -9852,16 +9852,16 @@
         <v>44839</v>
       </c>
       <c r="B472" t="n">
-        <v>41.63427734375</v>
+        <v>41.63427352905273</v>
       </c>
       <c r="C472" t="n">
-        <v>42.48533680478608</v>
+        <v>42.48533291211138</v>
       </c>
       <c r="D472" t="n">
-        <v>40.55110803146717</v>
+        <v>40.55110431601417</v>
       </c>
       <c r="E472" t="n">
-        <v>40.61880798727272</v>
+        <v>40.61880426561678</v>
       </c>
       <c r="F472" t="n">
         <v>6927519</v>
@@ -9892,16 +9892,16 @@
         <v>44841</v>
       </c>
       <c r="B474" t="n">
-        <v>41.47953796386719</v>
+        <v>41.47954177856445</v>
       </c>
       <c r="C474" t="n">
-        <v>42.45632104937901</v>
+        <v>42.45632495390688</v>
       </c>
       <c r="D474" t="n">
-        <v>41.22808688619578</v>
+        <v>41.22809067776815</v>
       </c>
       <c r="E474" t="n">
-        <v>41.59558913638236</v>
+        <v>41.59559296175236</v>
       </c>
       <c r="F474" t="n">
         <v>3503020</v>
@@ -10072,16 +10072,16 @@
         <v>44855</v>
       </c>
       <c r="B483" t="n">
-        <v>44.22614288330078</v>
+        <v>44.22613906860352</v>
       </c>
       <c r="C483" t="n">
-        <v>44.68068635480393</v>
+        <v>44.68068250090031</v>
       </c>
       <c r="D483" t="n">
-        <v>42.41764149048589</v>
+        <v>42.41763783177974</v>
       </c>
       <c r="E483" t="n">
-        <v>42.9688949036628</v>
+        <v>42.96889119740864</v>
       </c>
       <c r="F483" t="n">
         <v>5360835</v>
@@ -10112,16 +10112,16 @@
         <v>44859</v>
       </c>
       <c r="B485" t="n">
-        <v>42.69810104370117</v>
+        <v>42.69809722900391</v>
       </c>
       <c r="C485" t="n">
-        <v>44.71937098158734</v>
+        <v>44.7193669863075</v>
       </c>
       <c r="D485" t="n">
-        <v>42.52402240539543</v>
+        <v>42.52401860625056</v>
       </c>
       <c r="E485" t="n">
-        <v>43.43310931590769</v>
+        <v>43.43310543554394</v>
       </c>
       <c r="F485" t="n">
         <v>3364870</v>
@@ -10232,16 +10232,16 @@
         <v>44868</v>
       </c>
       <c r="B491" t="n">
-        <v>46.30543899536133</v>
+        <v>46.30543518066406</v>
       </c>
       <c r="C491" t="n">
-        <v>46.43116266535413</v>
+        <v>46.4311588402996</v>
       </c>
       <c r="D491" t="n">
-        <v>44.51627889399545</v>
+        <v>44.51627522669133</v>
       </c>
       <c r="E491" t="n">
-        <v>44.98049109746535</v>
+        <v>44.98048739191887</v>
       </c>
       <c r="F491" t="n">
         <v>3262984</v>
@@ -10312,16 +10312,16 @@
         <v>44874</v>
       </c>
       <c r="B495" t="n">
-        <v>44.69035720825195</v>
+        <v>44.69035339355469</v>
       </c>
       <c r="C495" t="n">
-        <v>46.49886228228617</v>
+        <v>46.49885831321781</v>
       </c>
       <c r="D495" t="n">
-        <v>44.23581375342662</v>
+        <v>44.23580997752845</v>
       </c>
       <c r="E495" t="n">
-        <v>45.35766552501359</v>
+        <v>45.35766165335595</v>
       </c>
       <c r="F495" t="n">
         <v>4884014</v>
@@ -10332,16 +10332,16 @@
         <v>44875</v>
       </c>
       <c r="B496" t="n">
-        <v>42.05980682373047</v>
+        <v>42.0598030090332</v>
       </c>
       <c r="C496" t="n">
-        <v>44.68068514703247</v>
+        <v>44.68068109462947</v>
       </c>
       <c r="D496" t="n">
-        <v>41.6439458411077</v>
+        <v>41.64394206412777</v>
       </c>
       <c r="E496" t="n">
-        <v>43.65554705124352</v>
+        <v>43.65554309181744</v>
       </c>
       <c r="F496" t="n">
         <v>5453172</v>
@@ -10472,16 +10472,16 @@
         <v>44887</v>
       </c>
       <c r="B503" t="n">
-        <v>35.72520446777344</v>
+        <v>35.7252082824707</v>
       </c>
       <c r="C503" t="n">
-        <v>38.01726275125628</v>
+        <v>38.01726681069696</v>
       </c>
       <c r="D503" t="n">
-        <v>35.41572595102293</v>
+        <v>35.41572973267442</v>
       </c>
       <c r="E503" t="n">
-        <v>37.37896822915095</v>
+        <v>37.37897222043525</v>
       </c>
       <c r="F503" t="n">
         <v>4879239</v>
@@ -10492,16 +10492,16 @@
         <v>44888</v>
       </c>
       <c r="B504" t="n">
-        <v>34.29388046264648</v>
+        <v>34.29387664794922</v>
       </c>
       <c r="C504" t="n">
-        <v>35.59948346985989</v>
+        <v>35.59947950993321</v>
       </c>
       <c r="D504" t="n">
-        <v>33.84900571743197</v>
+        <v>33.84900195222058</v>
       </c>
       <c r="E504" t="n">
-        <v>35.37704984482862</v>
+        <v>35.37704590964446</v>
       </c>
       <c r="F504" t="n">
         <v>5644348</v>
@@ -10532,16 +10532,16 @@
         <v>44890</v>
       </c>
       <c r="B506" t="n">
-        <v>34.23584747314453</v>
+        <v>34.2358512878418</v>
       </c>
       <c r="C506" t="n">
-        <v>36.49889581830917</v>
+        <v>36.49889988516448</v>
       </c>
       <c r="D506" t="n">
-        <v>34.11012381427162</v>
+        <v>34.11012761496025</v>
       </c>
       <c r="E506" t="n">
-        <v>36.17007605925269</v>
+        <v>36.17008008946956</v>
       </c>
       <c r="F506" t="n">
         <v>4398253</v>
@@ -10552,16 +10552,16 @@
         <v>44893</v>
       </c>
       <c r="B507" t="n">
-        <v>33.64590835571289</v>
+        <v>33.64591217041016</v>
       </c>
       <c r="C507" t="n">
-        <v>34.11012427192836</v>
+        <v>34.11012813925738</v>
       </c>
       <c r="D507" t="n">
-        <v>32.92057262619048</v>
+        <v>32.92057635865081</v>
       </c>
       <c r="E507" t="n">
-        <v>33.36544355803103</v>
+        <v>33.36544734092983</v>
       </c>
       <c r="F507" t="n">
         <v>4077054</v>
@@ -10652,16 +10652,16 @@
         <v>44900</v>
       </c>
       <c r="B512" t="n">
-        <v>34.04242324829102</v>
+        <v>34.04242706298828</v>
       </c>
       <c r="C512" t="n">
-        <v>35.87994187083461</v>
+        <v>35.879945891439</v>
       </c>
       <c r="D512" t="n">
-        <v>33.77163095133564</v>
+        <v>33.77163473568869</v>
       </c>
       <c r="E512" t="n">
-        <v>35.57046335392476</v>
+        <v>35.57046733984986</v>
       </c>
       <c r="F512" t="n">
         <v>5158181</v>
@@ -10732,16 +10732,16 @@
         <v>44904</v>
       </c>
       <c r="B516" t="n">
-        <v>31.69234085083008</v>
+        <v>31.69233894348145</v>
       </c>
       <c r="C516" t="n">
-        <v>32.74649642178647</v>
+        <v>32.74649445099531</v>
       </c>
       <c r="D516" t="n">
-        <v>31.4892447329005</v>
+        <v>31.48924283777486</v>
       </c>
       <c r="E516" t="n">
-        <v>32.22425300897184</v>
+        <v>32.22425106961099</v>
       </c>
       <c r="F516" t="n">
         <v>2885712</v>
@@ -10752,16 +10752,16 @@
         <v>44907</v>
       </c>
       <c r="B517" t="n">
-        <v>32.23392486572266</v>
+        <v>32.23392105102539</v>
       </c>
       <c r="C517" t="n">
-        <v>32.41767599422015</v>
+        <v>32.41767215777701</v>
       </c>
       <c r="D517" t="n">
-        <v>31.06371439332975</v>
+        <v>31.06371071712008</v>
       </c>
       <c r="E517" t="n">
-        <v>31.59562654097396</v>
+        <v>31.59562280181559</v>
       </c>
       <c r="F517" t="n">
         <v>3445728</v>
@@ -10772,16 +10772,16 @@
         <v>44908</v>
       </c>
       <c r="B518" t="n">
-        <v>32.5240592956543</v>
+        <v>32.52405548095703</v>
       </c>
       <c r="C518" t="n">
-        <v>33.41380497900949</v>
+        <v>33.41380105995531</v>
       </c>
       <c r="D518" t="n">
-        <v>31.98247464077933</v>
+        <v>31.9824708896037</v>
       </c>
       <c r="E518" t="n">
-        <v>32.39833187733107</v>
+        <v>32.39832807738018</v>
       </c>
       <c r="F518" t="n">
         <v>3369136</v>
@@ -10872,16 +10872,16 @@
         <v>44915</v>
       </c>
       <c r="B523" t="n">
-        <v>31.63431167602539</v>
+        <v>31.63431358337402</v>
       </c>
       <c r="C523" t="n">
-        <v>31.83740403538475</v>
+        <v>31.83740595497857</v>
       </c>
       <c r="D523" t="n">
-        <v>30.62851300266902</v>
+        <v>30.62851484937437</v>
       </c>
       <c r="E523" t="n">
-        <v>30.76390915810044</v>
+        <v>30.76391101296931</v>
       </c>
       <c r="F523" t="n">
         <v>3472546</v>
@@ -10892,16 +10892,16 @@
         <v>44916</v>
       </c>
       <c r="B524" t="n">
-        <v>32.19523620605469</v>
+        <v>32.19524002075195</v>
       </c>
       <c r="C524" t="n">
-        <v>32.50471472608491</v>
+        <v>32.50471857745117</v>
       </c>
       <c r="D524" t="n">
-        <v>31.22812192077017</v>
+        <v>31.22812562087756</v>
       </c>
       <c r="E524" t="n">
-        <v>32.34997359228213</v>
+        <v>32.34997742531367</v>
       </c>
       <c r="F524" t="n">
         <v>3938295</v>
@@ -10912,16 +10912,16 @@
         <v>44917</v>
       </c>
       <c r="B525" t="n">
-        <v>32.01148986816406</v>
+        <v>32.0114860534668</v>
       </c>
       <c r="C525" t="n">
-        <v>32.78518066232546</v>
+        <v>32.78517675543017</v>
       </c>
       <c r="D525" t="n">
-        <v>31.53760514678948</v>
+        <v>31.5376013885634</v>
       </c>
       <c r="E525" t="n">
-        <v>32.41767837830338</v>
+        <v>32.41767451520204</v>
       </c>
       <c r="F525" t="n">
         <v>3822391</v>
@@ -10932,16 +10932,16 @@
         <v>44918</v>
       </c>
       <c r="B526" t="n">
-        <v>34.68072128295898</v>
+        <v>34.68072509765625</v>
       </c>
       <c r="C526" t="n">
-        <v>34.88381363050969</v>
+        <v>34.88381746754605</v>
       </c>
       <c r="D526" t="n">
-        <v>32.68846528926745</v>
+        <v>32.68846888482701</v>
       </c>
       <c r="E526" t="n">
-        <v>33.17202242375276</v>
+        <v>33.17202607250107</v>
       </c>
       <c r="F526" t="n">
         <v>6955860</v>
@@ -11012,16 +11012,16 @@
         <v>44924</v>
       </c>
       <c r="B530" t="n">
-        <v>36.50856781005859</v>
+        <v>36.50856399536133</v>
       </c>
       <c r="C530" t="n">
-        <v>37.23390359436439</v>
+        <v>37.23389970387844</v>
       </c>
       <c r="D530" t="n">
-        <v>35.61882587917678</v>
+        <v>35.61882215744662</v>
       </c>
       <c r="E530" t="n">
-        <v>35.87994571220566</v>
+        <v>35.87994196319169</v>
       </c>
       <c r="F530" t="n">
         <v>4887264</v>
@@ -11032,16 +11032,16 @@
         <v>44928</v>
       </c>
       <c r="B531" t="n">
-        <v>35.2126350402832</v>
+        <v>35.21263885498047</v>
       </c>
       <c r="C531" t="n">
-        <v>36.68264774905137</v>
+        <v>36.68265172299981</v>
       </c>
       <c r="D531" t="n">
-        <v>34.78710534150101</v>
+        <v>34.78710911009928</v>
       </c>
       <c r="E531" t="n">
-        <v>36.01533947163607</v>
+        <v>36.01534337329287</v>
       </c>
       <c r="F531" t="n">
         <v>2924313</v>
@@ -11152,16 +11152,16 @@
         <v>44936</v>
       </c>
       <c r="B537" t="n">
-        <v>37.79483032226562</v>
+        <v>37.79483413696289</v>
       </c>
       <c r="C537" t="n">
-        <v>38.07529137196207</v>
+        <v>38.07529521496675</v>
       </c>
       <c r="D537" t="n">
-        <v>36.49889625466188</v>
+        <v>36.49889993855829</v>
       </c>
       <c r="E537" t="n">
-        <v>37.0985045751726</v>
+        <v>37.09850831958851</v>
       </c>
       <c r="F537" t="n">
         <v>3183751</v>
@@ -11192,16 +11192,16 @@
         <v>44938</v>
       </c>
       <c r="B539" t="n">
-        <v>43.42343902587891</v>
+        <v>43.42343521118164</v>
       </c>
       <c r="C539" t="n">
-        <v>44.7290457434945</v>
+        <v>44.72904181410123</v>
       </c>
       <c r="D539" t="n">
-        <v>43.19133291383822</v>
+        <v>43.19132911953119</v>
       </c>
       <c r="E539" t="n">
-        <v>43.40409778676949</v>
+        <v>43.40409397377132</v>
       </c>
       <c r="F539" t="n">
         <v>7341055</v>
@@ -11212,16 +11212,16 @@
         <v>44939</v>
       </c>
       <c r="B540" t="n">
-        <v>42.75612640380859</v>
+        <v>42.75613021850586</v>
       </c>
       <c r="C540" t="n">
-        <v>43.50080338468374</v>
+        <v>43.50080726582102</v>
       </c>
       <c r="D540" t="n">
-        <v>42.35961043000531</v>
+        <v>42.35961420932546</v>
       </c>
       <c r="E540" t="n">
-        <v>43.42343468839838</v>
+        <v>43.42343856263282</v>
       </c>
       <c r="F540" t="n">
         <v>4249336</v>
@@ -11272,16 +11272,16 @@
         <v>44944</v>
       </c>
       <c r="B543" t="n">
-        <v>44.53561782836914</v>
+        <v>44.53562164306641</v>
       </c>
       <c r="C543" t="n">
-        <v>45.241612337541</v>
+        <v>45.24161621271021</v>
       </c>
       <c r="D543" t="n">
-        <v>43.220342491427</v>
+        <v>43.22034619346439</v>
       </c>
       <c r="E543" t="n">
-        <v>43.42343485149192</v>
+        <v>43.42343857092518</v>
       </c>
       <c r="F543" t="n">
         <v>6730959</v>
@@ -11332,16 +11332,16 @@
         <v>44949</v>
       </c>
       <c r="B546" t="n">
-        <v>46.45050430297852</v>
+        <v>46.45050811767578</v>
       </c>
       <c r="C546" t="n">
-        <v>48.53947031074529</v>
+        <v>48.53947429699662</v>
       </c>
       <c r="D546" t="n">
-        <v>45.88957845353607</v>
+        <v>45.88958222216792</v>
       </c>
       <c r="E546" t="n">
-        <v>47.67873842593739</v>
+        <v>47.67874234150205</v>
       </c>
       <c r="F546" t="n">
         <v>5971946</v>
@@ -11392,16 +11392,16 @@
         <v>44952</v>
       </c>
       <c r="B549" t="n">
-        <v>45.26095199584961</v>
+        <v>45.26095581054688</v>
       </c>
       <c r="C549" t="n">
-        <v>46.77931963988798</v>
+        <v>46.77932358255676</v>
       </c>
       <c r="D549" t="n">
-        <v>45.24161075927422</v>
+        <v>45.24161457234137</v>
       </c>
       <c r="E549" t="n">
-        <v>45.92826025966649</v>
+        <v>45.92826413060603</v>
       </c>
       <c r="F549" t="n">
         <v>3327082</v>
@@ -11412,16 +11412,16 @@
         <v>44953</v>
       </c>
       <c r="B550" t="n">
-        <v>44.50660705566406</v>
+        <v>44.5066032409668</v>
       </c>
       <c r="C550" t="n">
-        <v>46.34412590104548</v>
+        <v>46.34412192885299</v>
       </c>
       <c r="D550" t="n">
-        <v>44.16811476963287</v>
+        <v>44.16811098394805</v>
       </c>
       <c r="E550" t="n">
-        <v>46.20872973614816</v>
+        <v>46.20872577556058</v>
       </c>
       <c r="F550" t="n">
         <v>4035914</v>
@@ -11432,16 +11432,16 @@
         <v>44956</v>
       </c>
       <c r="B551" t="n">
-        <v>43.79093933105469</v>
+        <v>43.79094314575195</v>
       </c>
       <c r="C551" t="n">
-        <v>44.43890261092821</v>
+        <v>44.43890648207057</v>
       </c>
       <c r="D551" t="n">
-        <v>43.13329981152729</v>
+        <v>43.13330356893655</v>
       </c>
       <c r="E551" t="n">
-        <v>44.3131789517849</v>
+        <v>44.31318281197527</v>
       </c>
       <c r="F551" t="n">
         <v>3870439</v>
@@ -11572,16 +11572,16 @@
         <v>44965</v>
       </c>
       <c r="B558" t="n">
-        <v>43.12363052368164</v>
+        <v>43.12362670898438</v>
       </c>
       <c r="C558" t="n">
-        <v>43.13330301647882</v>
+        <v>43.13329920092593</v>
       </c>
       <c r="D558" t="n">
-        <v>42.08881994983436</v>
+        <v>42.08881622667597</v>
       </c>
       <c r="E558" t="n">
-        <v>42.57237713333137</v>
+        <v>42.57237336739773</v>
       </c>
       <c r="F558" t="n">
         <v>2757212</v>
@@ -11672,16 +11672,16 @@
         <v>44972</v>
       </c>
       <c r="B563" t="n">
-        <v>40.0482063293457</v>
+        <v>40.04821014404297</v>
       </c>
       <c r="C563" t="n">
-        <v>40.52209099098364</v>
+        <v>40.52209485081966</v>
       </c>
       <c r="D563" t="n">
-        <v>38.90700964744255</v>
+        <v>38.90701335343782</v>
       </c>
       <c r="E563" t="n">
-        <v>38.92635463185054</v>
+        <v>38.92635833968847</v>
       </c>
       <c r="F563" t="n">
         <v>3495706</v>
@@ -11752,16 +11752,16 @@
         <v>44980</v>
       </c>
       <c r="B567" t="n">
-        <v>38.00759506225586</v>
+        <v>38.00759887695312</v>
       </c>
       <c r="C567" t="n">
-        <v>39.07141929530241</v>
+        <v>39.07142321677222</v>
       </c>
       <c r="D567" t="n">
-        <v>37.7368027579212</v>
+        <v>37.73680654543994</v>
       </c>
       <c r="E567" t="n">
-        <v>37.95924009667655</v>
+        <v>37.95924390652058</v>
       </c>
       <c r="F567" t="n">
         <v>3548732</v>
@@ -11812,16 +11812,16 @@
         <v>44985</v>
       </c>
       <c r="B570" t="n">
-        <v>35.2126350402832</v>
+        <v>35.21263885498047</v>
       </c>
       <c r="C570" t="n">
-        <v>38.49115271645117</v>
+        <v>38.49115688632073</v>
       </c>
       <c r="D570" t="n">
-        <v>35.2126350402832</v>
+        <v>35.21263885498047</v>
       </c>
       <c r="E570" t="n">
-        <v>37.13719117707558</v>
+        <v>37.13719520026616</v>
       </c>
       <c r="F570" t="n">
         <v>11036876</v>
@@ -11832,16 +11832,16 @@
         <v>44986</v>
       </c>
       <c r="B571" t="n">
-        <v>31.52792930603027</v>
+        <v>31.52793121337891</v>
       </c>
       <c r="C571" t="n">
-        <v>35.21263549119504</v>
+        <v>35.21263762145776</v>
       </c>
       <c r="D571" t="n">
-        <v>29.89350481936535</v>
+        <v>29.89350662783602</v>
       </c>
       <c r="E571" t="n">
-        <v>35.10625306513723</v>
+        <v>35.10625518896411</v>
       </c>
       <c r="F571" t="n">
         <v>24633899</v>
@@ -11872,16 +11872,16 @@
         <v>44988</v>
       </c>
       <c r="B573" t="n">
-        <v>31.74069404602051</v>
+        <v>31.74069595336914</v>
       </c>
       <c r="C573" t="n">
-        <v>31.93411766023568</v>
+        <v>31.93411957920744</v>
       </c>
       <c r="D573" t="n">
-        <v>30.40607560502645</v>
+        <v>30.40607743217574</v>
       </c>
       <c r="E573" t="n">
-        <v>30.47377368262298</v>
+        <v>30.47377551384036</v>
       </c>
       <c r="F573" t="n">
         <v>7573675</v>
@@ -11892,16 +11892,16 @@
         <v>44991</v>
       </c>
       <c r="B574" t="n">
-        <v>31.86641883850098</v>
+        <v>31.86642074584961</v>
       </c>
       <c r="C574" t="n">
-        <v>32.34997601739302</v>
+        <v>32.34997795368473</v>
       </c>
       <c r="D574" t="n">
-        <v>30.94766132287878</v>
+        <v>30.94766317523564</v>
       </c>
       <c r="E574" t="n">
-        <v>31.74069517121325</v>
+        <v>31.74069707103675</v>
       </c>
       <c r="F574" t="n">
         <v>5963007</v>
@@ -11992,16 +11992,16 @@
         <v>44998</v>
       </c>
       <c r="B579" t="n">
-        <v>26.4505786895752</v>
+        <v>26.45058059692383</v>
       </c>
       <c r="C579" t="n">
-        <v>27.32098119587531</v>
+        <v>27.32098316598858</v>
       </c>
       <c r="D579" t="n">
-        <v>25.76392542920967</v>
+        <v>25.76392728704381</v>
       </c>
       <c r="E579" t="n">
-        <v>26.59564546166059</v>
+        <v>26.59564737946998</v>
       </c>
       <c r="F579" t="n">
         <v>13860726</v>
@@ -12032,16 +12032,16 @@
         <v>45000</v>
       </c>
       <c r="B581" t="n">
-        <v>26.28617095947266</v>
+        <v>26.28616905212402</v>
       </c>
       <c r="C581" t="n">
-        <v>26.82775374453002</v>
+        <v>26.82775179788365</v>
       </c>
       <c r="D581" t="n">
-        <v>25.62853324821252</v>
+        <v>25.62853138858268</v>
       </c>
       <c r="E581" t="n">
-        <v>26.58597514665809</v>
+        <v>26.58597321755539</v>
       </c>
       <c r="F581" t="n">
         <v>12174787</v>
@@ -12072,16 +12072,16 @@
         <v>45002</v>
       </c>
       <c r="B583" t="n">
-        <v>30.70588111877441</v>
+        <v>30.70588302612305</v>
       </c>
       <c r="C583" t="n">
-        <v>30.8896322374788</v>
+        <v>30.88963415624145</v>
       </c>
       <c r="D583" t="n">
-        <v>27.73684012155175</v>
+        <v>27.73684184447329</v>
       </c>
       <c r="E583" t="n">
-        <v>30.45443004984579</v>
+        <v>30.45443194157511</v>
       </c>
       <c r="F583" t="n">
         <v>23193684</v>
@@ -12092,16 +12092,16 @@
         <v>45005</v>
       </c>
       <c r="B584" t="n">
-        <v>29.79679679870605</v>
+        <v>29.79679489135742</v>
       </c>
       <c r="C584" t="n">
-        <v>31.20878403151084</v>
+        <v>31.20878203377826</v>
       </c>
       <c r="D584" t="n">
-        <v>29.32291022343201</v>
+        <v>29.32290834641774</v>
       </c>
       <c r="E584" t="n">
-        <v>30.70588372476053</v>
+        <v>30.70588175921954</v>
       </c>
       <c r="F584" t="n">
         <v>7729094</v>
@@ -12252,16 +12252,16 @@
         <v>45015</v>
       </c>
       <c r="B592" t="n">
-        <v>29.38093566894531</v>
+        <v>29.38093376159668</v>
       </c>
       <c r="C592" t="n">
-        <v>30.51245994826028</v>
+        <v>30.51245796745546</v>
       </c>
       <c r="D592" t="n">
-        <v>29.27455323657771</v>
+        <v>29.2745513361352</v>
       </c>
       <c r="E592" t="n">
-        <v>29.95153405508782</v>
+        <v>29.95153211069714</v>
       </c>
       <c r="F592" t="n">
         <v>5560645</v>
@@ -12312,16 +12312,16 @@
         <v>45020</v>
       </c>
       <c r="B595" t="n">
-        <v>27.92059326171875</v>
+        <v>27.92059135437012</v>
       </c>
       <c r="C595" t="n">
-        <v>29.70975523383049</v>
+        <v>29.70975320425825</v>
       </c>
       <c r="D595" t="n">
-        <v>27.91092264260987</v>
+        <v>27.91092073592187</v>
       </c>
       <c r="E595" t="n">
-        <v>29.57435907115471</v>
+        <v>29.57435705083184</v>
       </c>
       <c r="F595" t="n">
         <v>7552242</v>
@@ -12332,16 +12332,16 @@
         <v>45021</v>
       </c>
       <c r="B596" t="n">
-        <v>26.76972579956055</v>
+        <v>26.76972770690918</v>
       </c>
       <c r="C596" t="n">
-        <v>27.85289314814766</v>
+        <v>27.8528951326722</v>
       </c>
       <c r="D596" t="n">
-        <v>26.23781180677641</v>
+        <v>26.23781367622606</v>
       </c>
       <c r="E596" t="n">
-        <v>27.65947141114338</v>
+        <v>27.65947338188658</v>
       </c>
       <c r="F596" t="n">
         <v>12382825</v>
@@ -12372,16 +12372,16 @@
         <v>45026</v>
       </c>
       <c r="B598" t="n">
-        <v>29.65172576904297</v>
+        <v>29.6517276763916</v>
       </c>
       <c r="C598" t="n">
-        <v>29.8354768886412</v>
+        <v>29.83547880780963</v>
       </c>
       <c r="D598" t="n">
-        <v>28.19138368313743</v>
+        <v>28.19138549654949</v>
       </c>
       <c r="E598" t="n">
-        <v>28.33645045512486</v>
+        <v>28.33645227786835</v>
       </c>
       <c r="F598" t="n">
         <v>8774363</v>
@@ -12552,16 +12552,16 @@
         <v>45040</v>
       </c>
       <c r="B607" t="n">
-        <v>26.96700286865234</v>
+        <v>26.96700477600098</v>
       </c>
       <c r="C607" t="n">
-        <v>27.07506608384296</v>
+        <v>27.07506799883479</v>
       </c>
       <c r="D607" t="n">
-        <v>26.23019953206389</v>
+        <v>26.23020138729918</v>
       </c>
       <c r="E607" t="n">
-        <v>26.86876204901633</v>
+        <v>26.86876394941649</v>
       </c>
       <c r="F607" t="n">
         <v>6680100</v>
@@ -12572,16 +12572,16 @@
         <v>45041</v>
       </c>
       <c r="B608" t="n">
-        <v>27.21260452270508</v>
+        <v>27.21260261535645</v>
       </c>
       <c r="C608" t="n">
-        <v>27.45820563979163</v>
+        <v>27.45820371522866</v>
       </c>
       <c r="D608" t="n">
-        <v>26.42667982375542</v>
+        <v>26.42667797149275</v>
       </c>
       <c r="E608" t="n">
-        <v>26.79999457104816</v>
+        <v>26.79999269261962</v>
       </c>
       <c r="F608" t="n">
         <v>5323000</v>
@@ -12612,16 +12612,16 @@
         <v>45043</v>
       </c>
       <c r="B610" t="n">
-        <v>29.90439224243164</v>
+        <v>29.90439414978027</v>
       </c>
       <c r="C610" t="n">
-        <v>30.267880842768</v>
+        <v>30.26788277330051</v>
       </c>
       <c r="D610" t="n">
-        <v>26.73122441728851</v>
+        <v>26.73122612224756</v>
       </c>
       <c r="E610" t="n">
-        <v>26.73122441728851</v>
+        <v>26.73122612224756</v>
       </c>
       <c r="F610" t="n">
         <v>20933600</v>
@@ -12672,16 +12672,16 @@
         <v>45049</v>
       </c>
       <c r="B613" t="n">
-        <v>29.14793968200684</v>
+        <v>29.14794158935547</v>
       </c>
       <c r="C613" t="n">
-        <v>29.61949336143113</v>
+        <v>29.61949529963673</v>
       </c>
       <c r="D613" t="n">
-        <v>28.33254407533193</v>
+        <v>28.33254592932366</v>
       </c>
       <c r="E613" t="n">
-        <v>29.26582903875679</v>
+        <v>29.26583095381972</v>
       </c>
       <c r="F613" t="n">
         <v>9250000</v>
@@ -12692,16 +12692,16 @@
         <v>45050</v>
       </c>
       <c r="B614" t="n">
-        <v>29.2756519317627</v>
+        <v>29.27565383911133</v>
       </c>
       <c r="C614" t="n">
-        <v>29.95351152857367</v>
+        <v>29.95351348008578</v>
       </c>
       <c r="D614" t="n">
-        <v>29.17741298555374</v>
+        <v>29.17741488650197</v>
       </c>
       <c r="E614" t="n">
-        <v>29.47213357175619</v>
+        <v>29.47213549190587</v>
       </c>
       <c r="F614" t="n">
         <v>6670900</v>
@@ -12792,16 +12792,16 @@
         <v>45057</v>
       </c>
       <c r="B619" t="n">
-        <v>31.66289520263672</v>
+        <v>31.66289710998535</v>
       </c>
       <c r="C619" t="n">
-        <v>31.81025737023202</v>
+        <v>31.81025928645763</v>
       </c>
       <c r="D619" t="n">
-        <v>31.10292496189554</v>
+        <v>31.10292683551199</v>
       </c>
       <c r="E619" t="n">
-        <v>31.71201467597662</v>
+        <v>31.71201658628417</v>
       </c>
       <c r="F619" t="n">
         <v>4858000</v>
@@ -12812,16 +12812,16 @@
         <v>45058</v>
       </c>
       <c r="B620" t="n">
-        <v>32.49794006347656</v>
+        <v>32.49794387817383</v>
       </c>
       <c r="C620" t="n">
-        <v>32.64529847816273</v>
+        <v>32.64530231015733</v>
       </c>
       <c r="D620" t="n">
-        <v>31.46641242279611</v>
+        <v>31.46641611640984</v>
       </c>
       <c r="E620" t="n">
-        <v>31.554828970638</v>
+        <v>31.55483267463029</v>
       </c>
       <c r="F620" t="n">
         <v>5317000</v>
@@ -12852,16 +12852,16 @@
         <v>45062</v>
       </c>
       <c r="B622" t="n">
-        <v>29.90439224243164</v>
+        <v>29.90439414978027</v>
       </c>
       <c r="C622" t="n">
-        <v>32.08532946581322</v>
+        <v>32.08533151226543</v>
       </c>
       <c r="D622" t="n">
-        <v>29.70791060120974</v>
+        <v>29.70791249602647</v>
       </c>
       <c r="E622" t="n">
-        <v>31.86919928571158</v>
+        <v>31.86920131837866</v>
       </c>
       <c r="F622" t="n">
         <v>13269700</v>
@@ -12912,16 +12912,16 @@
         <v>45065</v>
       </c>
       <c r="B625" t="n">
-        <v>32.49794006347656</v>
+        <v>32.49794387817383</v>
       </c>
       <c r="C625" t="n">
-        <v>34.87535696477425</v>
+        <v>34.87536105853923</v>
       </c>
       <c r="D625" t="n">
-        <v>31.04398009551434</v>
+        <v>31.0439837395418</v>
       </c>
       <c r="E625" t="n">
-        <v>31.8691980857257</v>
+        <v>31.86920182661951</v>
       </c>
       <c r="F625" t="n">
         <v>19443700</v>
@@ -12972,16 +12972,16 @@
         <v>45070</v>
       </c>
       <c r="B628" t="n">
-        <v>31.48606300354004</v>
+        <v>31.48606109619141</v>
       </c>
       <c r="C628" t="n">
-        <v>31.86920015318507</v>
+        <v>31.86919822262693</v>
       </c>
       <c r="D628" t="n">
-        <v>30.464363313224</v>
+        <v>30.46436146776744</v>
       </c>
       <c r="E628" t="n">
-        <v>31.04398210943912</v>
+        <v>31.04398022887067</v>
       </c>
       <c r="F628" t="n">
         <v>7685200</v>
@@ -13212,16 +13212,16 @@
         <v>45089</v>
       </c>
       <c r="B640" t="n">
-        <v>31.26010894775391</v>
+        <v>31.26011085510254</v>
       </c>
       <c r="C640" t="n">
-        <v>31.86919865058509</v>
+        <v>31.86920059509758</v>
       </c>
       <c r="D640" t="n">
-        <v>30.47418614610471</v>
+        <v>30.47418800549994</v>
       </c>
       <c r="E640" t="n">
-        <v>31.61377514538992</v>
+        <v>31.61377707431765</v>
       </c>
       <c r="F640" t="n">
         <v>7223600</v>
@@ -13252,16 +13252,16 @@
         <v>45091</v>
       </c>
       <c r="B642" t="n">
-        <v>31.1422233581543</v>
+        <v>31.14222145080566</v>
       </c>
       <c r="C642" t="n">
-        <v>31.71201601865814</v>
+        <v>31.71201407641177</v>
       </c>
       <c r="D642" t="n">
-        <v>30.57242882386257</v>
+        <v>30.5724269514118</v>
       </c>
       <c r="E642" t="n">
-        <v>31.33870313362062</v>
+        <v>31.33870121423831</v>
       </c>
       <c r="F642" t="n">
         <v>8288400</v>
@@ -13292,16 +13292,16 @@
         <v>45093</v>
       </c>
       <c r="B644" t="n">
-        <v>31.91832160949707</v>
+        <v>31.9183235168457</v>
       </c>
       <c r="C644" t="n">
-        <v>31.91832160949707</v>
+        <v>31.9183235168457</v>
       </c>
       <c r="D644" t="n">
-        <v>31.19134068168367</v>
+        <v>31.19134254558997</v>
       </c>
       <c r="E644" t="n">
-        <v>31.42711752024974</v>
+        <v>31.4271193982454</v>
       </c>
       <c r="F644" t="n">
         <v>5722800</v>
@@ -13332,16 +13332,16 @@
         <v>45097</v>
       </c>
       <c r="B646" t="n">
-        <v>32.16392135620117</v>
+        <v>32.16392517089844</v>
       </c>
       <c r="C646" t="n">
-        <v>32.29163122856222</v>
+        <v>32.2916350584061</v>
       </c>
       <c r="D646" t="n">
-        <v>31.48605992910253</v>
+        <v>31.48606366340425</v>
       </c>
       <c r="E646" t="n">
-        <v>32.12462428120915</v>
+        <v>32.12462809124572</v>
       </c>
       <c r="F646" t="n">
         <v>4954700</v>
@@ -13352,16 +13352,16 @@
         <v>45098</v>
       </c>
       <c r="B647" t="n">
-        <v>32.06568145751953</v>
+        <v>32.06567764282227</v>
       </c>
       <c r="C647" t="n">
-        <v>32.36040205044127</v>
+        <v>32.36039820068254</v>
       </c>
       <c r="D647" t="n">
-        <v>31.48606266749066</v>
+        <v>31.4860589217478</v>
       </c>
       <c r="E647" t="n">
-        <v>32.12462707513414</v>
+        <v>32.1246232534244</v>
       </c>
       <c r="F647" t="n">
         <v>4670300</v>
@@ -13412,16 +13412,16 @@
         <v>45103</v>
       </c>
       <c r="B650" t="n">
-        <v>30.53313064575195</v>
+        <v>30.53312873840332</v>
       </c>
       <c r="C650" t="n">
-        <v>30.83767550472773</v>
+        <v>30.83767357835474</v>
       </c>
       <c r="D650" t="n">
-        <v>30.30717806889212</v>
+        <v>30.30717617565832</v>
       </c>
       <c r="E650" t="n">
-        <v>30.58225011940398</v>
+        <v>30.58224820898695</v>
       </c>
       <c r="F650" t="n">
         <v>2874500</v>
@@ -13452,16 +13452,16 @@
         <v>45105</v>
       </c>
       <c r="B652" t="n">
-        <v>29.37389183044434</v>
+        <v>29.37389373779297</v>
       </c>
       <c r="C652" t="n">
-        <v>30.06157567506449</v>
+        <v>30.06157762706682</v>
       </c>
       <c r="D652" t="n">
-        <v>29.30512382073987</v>
+        <v>29.30512572362315</v>
       </c>
       <c r="E652" t="n">
-        <v>29.75703082903567</v>
+        <v>29.75703276126285</v>
       </c>
       <c r="F652" t="n">
         <v>4532500</v>
@@ -13532,16 +13532,16 @@
         <v>45111</v>
       </c>
       <c r="B656" t="n">
-        <v>29.80615234375</v>
+        <v>29.80615043640137</v>
       </c>
       <c r="C656" t="n">
-        <v>30.15981855937348</v>
+        <v>30.15981662939312</v>
       </c>
       <c r="D656" t="n">
-        <v>29.57037549126363</v>
+        <v>29.57037359900278</v>
       </c>
       <c r="E656" t="n">
-        <v>29.80615234375</v>
+        <v>29.80615043640137</v>
       </c>
       <c r="F656" t="n">
         <v>2514900</v>
@@ -13552,16 +13552,16 @@
         <v>45112</v>
       </c>
       <c r="B657" t="n">
-        <v>30.40542030334473</v>
+        <v>30.40541839599609</v>
       </c>
       <c r="C657" t="n">
-        <v>30.70996517647691</v>
+        <v>30.70996325002402</v>
       </c>
       <c r="D657" t="n">
-        <v>29.34442350856649</v>
+        <v>29.34442166777476</v>
       </c>
       <c r="E657" t="n">
-        <v>29.60967130192012</v>
+        <v>29.60966944448926</v>
       </c>
       <c r="F657" t="n">
         <v>5394800</v>
@@ -13612,16 +13612,16 @@
         <v>45117</v>
       </c>
       <c r="B660" t="n">
-        <v>31.07345390319824</v>
+        <v>31.07345199584961</v>
       </c>
       <c r="C660" t="n">
-        <v>31.93796904965617</v>
+        <v>31.93796708924193</v>
       </c>
       <c r="D660" t="n">
-        <v>30.84750131505205</v>
+        <v>30.84749942157282</v>
       </c>
       <c r="E660" t="n">
-        <v>31.56465803319331</v>
+        <v>31.56465609569361</v>
       </c>
       <c r="F660" t="n">
         <v>7339200</v>
@@ -13652,16 +13652,16 @@
         <v>45119</v>
       </c>
       <c r="B662" t="n">
-        <v>31.07345390319824</v>
+        <v>31.07345199584961</v>
       </c>
       <c r="C662" t="n">
-        <v>32.08533122554864</v>
+        <v>32.08532925608902</v>
       </c>
       <c r="D662" t="n">
-        <v>31.04398296705007</v>
+        <v>31.04398106151042</v>
       </c>
       <c r="E662" t="n">
-        <v>31.77096208138212</v>
+        <v>31.77096013121909</v>
       </c>
       <c r="F662" t="n">
         <v>4503800</v>
@@ -13732,16 +13732,16 @@
         <v>45125</v>
       </c>
       <c r="B666" t="n">
-        <v>32.91054916381836</v>
+        <v>32.91055297851562</v>
       </c>
       <c r="C666" t="n">
-        <v>33.03826279198419</v>
+        <v>33.03826662148488</v>
       </c>
       <c r="D666" t="n">
-        <v>32.0362098005708</v>
+        <v>32.03621351392245</v>
       </c>
       <c r="E666" t="n">
-        <v>32.18356821992315</v>
+        <v>32.18357195035527</v>
       </c>
       <c r="F666" t="n">
         <v>4775600</v>
@@ -13752,16 +13752,16 @@
         <v>45126</v>
       </c>
       <c r="B667" t="n">
-        <v>33.64735412597656</v>
+        <v>33.6473503112793</v>
       </c>
       <c r="C667" t="n">
-        <v>34.04031742501827</v>
+        <v>34.04031356576963</v>
       </c>
       <c r="D667" t="n">
-        <v>33.04808678134705</v>
+        <v>33.04808303459044</v>
       </c>
       <c r="E667" t="n">
-        <v>33.04808678134705</v>
+        <v>33.04808303459044</v>
       </c>
       <c r="F667" t="n">
         <v>7484200</v>
@@ -13772,16 +13772,16 @@
         <v>45127</v>
       </c>
       <c r="B668" t="n">
-        <v>33.92242431640625</v>
+        <v>33.92242813110352</v>
       </c>
       <c r="C668" t="n">
-        <v>34.11890595509385</v>
+        <v>34.11890979188617</v>
       </c>
       <c r="D668" t="n">
-        <v>33.64735227078894</v>
+        <v>33.64735605455338</v>
       </c>
       <c r="E668" t="n">
-        <v>33.91260192088087</v>
+        <v>33.91260573447357</v>
       </c>
       <c r="F668" t="n">
         <v>3587900</v>
@@ -13952,16 +13952,16 @@
         <v>45140</v>
       </c>
       <c r="B677" t="n">
-        <v>34.44309997558594</v>
+        <v>34.4431037902832</v>
       </c>
       <c r="C677" t="n">
-        <v>34.58063599342123</v>
+        <v>34.5806398233511</v>
       </c>
       <c r="D677" t="n">
-        <v>33.71611906300245</v>
+        <v>33.71612279718397</v>
       </c>
       <c r="E677" t="n">
-        <v>34.38415436183849</v>
+        <v>34.38415817000732</v>
       </c>
       <c r="F677" t="n">
         <v>3408800</v>
@@ -14012,16 +14012,16 @@
         <v>45145</v>
       </c>
       <c r="B680" t="n">
-        <v>35.68093109130859</v>
+        <v>35.68092727661133</v>
       </c>
       <c r="C680" t="n">
-        <v>36.15248480095344</v>
+        <v>36.15248093584172</v>
       </c>
       <c r="D680" t="n">
-        <v>35.09148989114647</v>
+        <v>35.09148613946717</v>
       </c>
       <c r="E680" t="n">
-        <v>36.05424585011833</v>
+        <v>36.05424199550948</v>
       </c>
       <c r="F680" t="n">
         <v>3820600</v>
@@ -14032,16 +14032,16 @@
         <v>45146</v>
       </c>
       <c r="B681" t="n">
-        <v>36.34896850585938</v>
+        <v>36.34896469116211</v>
       </c>
       <c r="C681" t="n">
-        <v>36.51597548123902</v>
+        <v>36.51597164901496</v>
       </c>
       <c r="D681" t="n">
-        <v>34.30556523426109</v>
+        <v>34.30556163401185</v>
       </c>
       <c r="E681" t="n">
-        <v>34.76729657396523</v>
+        <v>34.76729292525891</v>
       </c>
       <c r="F681" t="n">
         <v>5274900</v>
@@ -14172,16 +14172,16 @@
         <v>45155</v>
       </c>
       <c r="B688" t="n">
-        <v>31.26993560791016</v>
+        <v>31.26993370056152</v>
       </c>
       <c r="C688" t="n">
-        <v>31.74149119874277</v>
+        <v>31.74148926263102</v>
       </c>
       <c r="D688" t="n">
-        <v>30.96539073320894</v>
+        <v>30.9653888444364</v>
       </c>
       <c r="E688" t="n">
-        <v>31.4664153864515</v>
+        <v>31.46641346711834</v>
       </c>
       <c r="F688" t="n">
         <v>4529600</v>
@@ -14252,16 +14252,16 @@
         <v>45161</v>
       </c>
       <c r="B692" t="n">
-        <v>31.05380439758301</v>
+        <v>31.05380630493164</v>
       </c>
       <c r="C692" t="n">
-        <v>31.24045988874735</v>
+        <v>31.2404618075605</v>
       </c>
       <c r="D692" t="n">
-        <v>30.68048966767887</v>
+        <v>30.68049155209822</v>
       </c>
       <c r="E692" t="n">
-        <v>31.09309960011686</v>
+        <v>31.09310150987904</v>
       </c>
       <c r="F692" t="n">
         <v>4847400</v>
@@ -14272,16 +14272,16 @@
         <v>45162</v>
       </c>
       <c r="B693" t="n">
-        <v>30.91626739501953</v>
+        <v>30.91626930236816</v>
       </c>
       <c r="C693" t="n">
-        <v>31.30923067440671</v>
+        <v>31.30923260599883</v>
       </c>
       <c r="D693" t="n">
-        <v>30.56260306687397</v>
+        <v>30.56260495240363</v>
       </c>
       <c r="E693" t="n">
-        <v>31.05380529232016</v>
+        <v>31.05380720815405</v>
       </c>
       <c r="F693" t="n">
         <v>3471700</v>
@@ -14332,16 +14332,16 @@
         <v>45167</v>
       </c>
       <c r="B696" t="n">
-        <v>31.29940605163574</v>
+        <v>31.29940795898438</v>
       </c>
       <c r="C696" t="n">
-        <v>31.55482955705047</v>
+        <v>31.55483147996431</v>
       </c>
       <c r="D696" t="n">
-        <v>30.63137073276579</v>
+        <v>30.63137259940515</v>
       </c>
       <c r="E696" t="n">
-        <v>31.06362921093831</v>
+        <v>31.06363110391898</v>
       </c>
       <c r="F696" t="n">
         <v>3743200</v>
@@ -14352,16 +14352,16 @@
         <v>45168</v>
       </c>
       <c r="B697" t="n">
-        <v>31.63342475891113</v>
+        <v>31.6334228515625</v>
       </c>
       <c r="C697" t="n">
-        <v>31.70219277216898</v>
+        <v>31.70219086067396</v>
       </c>
       <c r="D697" t="n">
-        <v>30.96538941791287</v>
+        <v>30.96538755084366</v>
       </c>
       <c r="E697" t="n">
-        <v>31.49588873239543</v>
+        <v>31.49588683333958</v>
       </c>
       <c r="F697" t="n">
         <v>3276100</v>
@@ -14412,16 +14412,16 @@
         <v>45173</v>
       </c>
       <c r="B700" t="n">
-        <v>32.27198791503906</v>
+        <v>32.2719841003418</v>
       </c>
       <c r="C700" t="n">
-        <v>32.55688613348561</v>
+        <v>32.55688228511206</v>
       </c>
       <c r="D700" t="n">
-        <v>32.06568385929886</v>
+        <v>32.06568006898767</v>
       </c>
       <c r="E700" t="n">
-        <v>32.22286843713558</v>
+        <v>32.22286462824446</v>
       </c>
       <c r="F700" t="n">
         <v>2652900</v>
@@ -14432,16 +14432,16 @@
         <v>45174</v>
       </c>
       <c r="B701" t="n">
-        <v>32.63547897338867</v>
+        <v>32.63547515869141</v>
       </c>
       <c r="C701" t="n">
-        <v>32.93019957643972</v>
+        <v>32.93019572729314</v>
       </c>
       <c r="D701" t="n">
-        <v>32.07550870331895</v>
+        <v>32.07550495407551</v>
       </c>
       <c r="E701" t="n">
-        <v>32.27198660696912</v>
+        <v>32.27198283475976</v>
       </c>
       <c r="F701" t="n">
         <v>6036900</v>
@@ -14452,16 +14452,16 @@
         <v>45175</v>
       </c>
       <c r="B702" t="n">
-        <v>32.00673675537109</v>
+        <v>32.00674057006836</v>
       </c>
       <c r="C702" t="n">
-        <v>32.71406536628031</v>
+        <v>32.71406926527997</v>
       </c>
       <c r="D702" t="n">
-        <v>31.928142605506</v>
+        <v>31.92814641083608</v>
       </c>
       <c r="E702" t="n">
-        <v>32.65512350145682</v>
+        <v>32.65512739343153</v>
       </c>
       <c r="F702" t="n">
         <v>4505300</v>
@@ -14512,16 +14512,16 @@
         <v>45181</v>
       </c>
       <c r="B705" t="n">
-        <v>32.33092880249023</v>
+        <v>32.3309326171875</v>
       </c>
       <c r="C705" t="n">
-        <v>32.64529791212711</v>
+        <v>32.6453017639165</v>
       </c>
       <c r="D705" t="n">
-        <v>31.76113619661418</v>
+        <v>31.76113994408213</v>
       </c>
       <c r="E705" t="n">
-        <v>31.97726261725491</v>
+        <v>31.97726639022342</v>
       </c>
       <c r="F705" t="n">
         <v>3620500</v>
@@ -14532,16 +14532,16 @@
         <v>45182</v>
       </c>
       <c r="B706" t="n">
-        <v>31.63342475891113</v>
+        <v>31.6334228515625</v>
       </c>
       <c r="C706" t="n">
-        <v>32.1148008517161</v>
+        <v>32.11479891534272</v>
       </c>
       <c r="D706" t="n">
-        <v>31.44676551071783</v>
+        <v>31.44676361462388</v>
       </c>
       <c r="E706" t="n">
-        <v>31.60395007638945</v>
+        <v>31.60394817081799</v>
       </c>
       <c r="F706" t="n">
         <v>7302700</v>
@@ -14552,16 +14552,16 @@
         <v>45183</v>
       </c>
       <c r="B707" t="n">
-        <v>32.31128311157227</v>
+        <v>32.311279296875</v>
       </c>
       <c r="C707" t="n">
-        <v>32.31128311157227</v>
+        <v>32.311279296875</v>
       </c>
       <c r="D707" t="n">
-        <v>31.74149045549294</v>
+        <v>31.74148670806588</v>
       </c>
       <c r="E707" t="n">
-        <v>31.83972940556933</v>
+        <v>31.83972564654409</v>
       </c>
       <c r="F707" t="n">
         <v>4362300</v>
@@ -14592,16 +14592,16 @@
         <v>45187</v>
       </c>
       <c r="B709" t="n">
-        <v>31.98709106445312</v>
+        <v>31.98709297180176</v>
       </c>
       <c r="C709" t="n">
-        <v>32.7140682775227</v>
+        <v>32.71407022822005</v>
       </c>
       <c r="D709" t="n">
-        <v>31.75131234145109</v>
+        <v>31.75131423474054</v>
       </c>
       <c r="E709" t="n">
-        <v>32.5568837113799</v>
+        <v>32.55688565270453</v>
       </c>
       <c r="F709" t="n">
         <v>5099000</v>
@@ -14692,16 +14692,16 @@
         <v>45194</v>
       </c>
       <c r="B714" t="n">
-        <v>30.95556449890137</v>
+        <v>30.95556640625</v>
       </c>
       <c r="C714" t="n">
-        <v>31.20116561183414</v>
+        <v>31.20116753431566</v>
       </c>
       <c r="D714" t="n">
-        <v>29.99280858591396</v>
+        <v>29.99281043394172</v>
       </c>
       <c r="E714" t="n">
-        <v>30.45453800366397</v>
+        <v>30.45453988014151</v>
       </c>
       <c r="F714" t="n">
         <v>6350700</v>
@@ -14712,16 +14712,16 @@
         <v>45195</v>
       </c>
       <c r="B715" t="n">
-        <v>30.32682609558105</v>
+        <v>30.32682800292969</v>
       </c>
       <c r="C715" t="n">
-        <v>30.83767498381136</v>
+        <v>30.83767692328888</v>
       </c>
       <c r="D715" t="n">
-        <v>30.19911246818264</v>
+        <v>30.19911436749897</v>
       </c>
       <c r="E715" t="n">
-        <v>30.75908270302303</v>
+        <v>30.75908463755763</v>
       </c>
       <c r="F715" t="n">
         <v>3433500</v>
@@ -14732,16 +14732,16 @@
         <v>45196</v>
       </c>
       <c r="B716" t="n">
-        <v>30.86714935302734</v>
+        <v>30.86714744567871</v>
       </c>
       <c r="C716" t="n">
-        <v>31.0734533978611</v>
+        <v>31.07345147776449</v>
       </c>
       <c r="D716" t="n">
-        <v>30.42506658011519</v>
+        <v>30.42506470008381</v>
       </c>
       <c r="E716" t="n">
-        <v>30.65102103837466</v>
+        <v>30.65101914438107</v>
       </c>
       <c r="F716" t="n">
         <v>4307600</v>
@@ -14752,16 +14752,16 @@
         <v>45197</v>
       </c>
       <c r="B717" t="n">
-        <v>30.58224868774414</v>
+        <v>30.58225059509277</v>
       </c>
       <c r="C717" t="n">
-        <v>31.21098878902595</v>
+        <v>31.21099073558775</v>
       </c>
       <c r="D717" t="n">
-        <v>30.41523986184255</v>
+        <v>30.41524175877521</v>
       </c>
       <c r="E717" t="n">
-        <v>30.82784979208249</v>
+        <v>30.82785171474873</v>
       </c>
       <c r="F717" t="n">
         <v>4298000</v>
@@ -14772,16 +14772,16 @@
         <v>45198</v>
       </c>
       <c r="B718" t="n">
-        <v>31.02433395385742</v>
+        <v>31.02433204650879</v>
       </c>
       <c r="C718" t="n">
-        <v>31.60395088345571</v>
+        <v>31.60394894047274</v>
       </c>
       <c r="D718" t="n">
-        <v>30.47418795995777</v>
+        <v>30.47418608643163</v>
       </c>
       <c r="E718" t="n">
-        <v>30.86714938417181</v>
+        <v>30.86714748648674</v>
       </c>
       <c r="F718" t="n">
         <v>5846000</v>
@@ -14852,16 +14852,16 @@
         <v>45204</v>
       </c>
       <c r="B722" t="n">
-        <v>28.03782272338867</v>
+        <v>28.0378246307373</v>
       </c>
       <c r="C722" t="n">
-        <v>28.78444842505877</v>
+        <v>28.78445038319864</v>
       </c>
       <c r="D722" t="n">
-        <v>27.72345173862667</v>
+        <v>27.72345362458937</v>
       </c>
       <c r="E722" t="n">
-        <v>28.62726386957162</v>
+        <v>28.62726581701858</v>
       </c>
       <c r="F722" t="n">
         <v>8409300</v>
@@ -14912,16 +14912,16 @@
         <v>45209</v>
       </c>
       <c r="B725" t="n">
-        <v>30.27770614624023</v>
+        <v>30.2777042388916</v>
       </c>
       <c r="C725" t="n">
-        <v>30.40541977953243</v>
+        <v>30.40541786413846</v>
       </c>
       <c r="D725" t="n">
-        <v>29.43283768343539</v>
+        <v>29.43283582930937</v>
       </c>
       <c r="E725" t="n">
-        <v>29.75703296465965</v>
+        <v>29.7570310901109</v>
       </c>
       <c r="F725" t="n">
         <v>7018100</v>
@@ -14972,16 +14972,16 @@
         <v>45215</v>
       </c>
       <c r="B728" t="n">
-        <v>31.67271995544434</v>
+        <v>31.67272186279297</v>
       </c>
       <c r="C728" t="n">
-        <v>32.01656000130495</v>
+        <v>32.01656192935982</v>
       </c>
       <c r="D728" t="n">
-        <v>31.32887616200829</v>
+        <v>31.32887804865046</v>
       </c>
       <c r="E728" t="n">
-        <v>31.91832105893775</v>
+        <v>31.91832298107662</v>
       </c>
       <c r="F728" t="n">
         <v>3741500</v>
@@ -15012,16 +15012,16 @@
         <v>45217</v>
       </c>
       <c r="B730" t="n">
-        <v>32.06568145751953</v>
+        <v>32.06567764282227</v>
       </c>
       <c r="C730" t="n">
-        <v>33.06773447151397</v>
+        <v>33.06773053760736</v>
       </c>
       <c r="D730" t="n">
-        <v>31.63342483773936</v>
+        <v>31.63342107446555</v>
       </c>
       <c r="E730" t="n">
-        <v>32.52741275989484</v>
+        <v>32.52740889026767</v>
       </c>
       <c r="F730" t="n">
         <v>7439800</v>
@@ -15132,16 +15132,16 @@
         <v>45225</v>
       </c>
       <c r="B736" t="n">
-        <v>31.98709106445312</v>
+        <v>31.98709297180176</v>
       </c>
       <c r="C736" t="n">
-        <v>32.12462709138111</v>
+        <v>32.12462900693085</v>
       </c>
       <c r="D736" t="n">
-        <v>31.19134209034388</v>
+        <v>31.19134395024304</v>
       </c>
       <c r="E736" t="n">
-        <v>31.57447923609348</v>
+        <v>31.57448111883861</v>
       </c>
       <c r="F736" t="n">
         <v>2923500</v>
@@ -15152,16 +15152,16 @@
         <v>45226</v>
       </c>
       <c r="B737" t="n">
-        <v>31.52535820007324</v>
+        <v>31.52536010742188</v>
       </c>
       <c r="C737" t="n">
-        <v>32.556882098507</v>
+        <v>32.55688406826494</v>
       </c>
       <c r="D737" t="n">
-        <v>31.24046001693592</v>
+        <v>31.24046190704763</v>
       </c>
       <c r="E737" t="n">
-        <v>32.32110713476096</v>
+        <v>32.32110909025403</v>
       </c>
       <c r="F737" t="n">
         <v>3378100</v>
@@ -15172,16 +15172,16 @@
         <v>45229</v>
       </c>
       <c r="B738" t="n">
-        <v>31.07345390319824</v>
+        <v>31.07345199584961</v>
       </c>
       <c r="C738" t="n">
-        <v>32.11480216169681</v>
+        <v>32.11480019042821</v>
       </c>
       <c r="D738" t="n">
-        <v>30.98503922096583</v>
+        <v>30.98503731904426</v>
       </c>
       <c r="E738" t="n">
-        <v>31.54500949323592</v>
+        <v>31.5450075569423</v>
       </c>
       <c r="F738" t="n">
         <v>3227500</v>
@@ -15192,16 +15192,16 @@
         <v>45230</v>
       </c>
       <c r="B739" t="n">
-        <v>31.86919784545898</v>
+        <v>31.86919975280762</v>
       </c>
       <c r="C739" t="n">
-        <v>32.10497655378492</v>
+        <v>32.10497847524474</v>
       </c>
       <c r="D739" t="n">
-        <v>31.20116441782789</v>
+        <v>31.2011662851952</v>
       </c>
       <c r="E739" t="n">
-        <v>31.20116441782789</v>
+        <v>31.2011662851952</v>
       </c>
       <c r="F739" t="n">
         <v>3372100</v>
@@ -15212,16 +15212,16 @@
         <v>45231</v>
       </c>
       <c r="B740" t="n">
-        <v>32.06568145751953</v>
+        <v>32.06567764282227</v>
       </c>
       <c r="C740" t="n">
-        <v>32.74354294357276</v>
+        <v>32.74353904823363</v>
       </c>
       <c r="D740" t="n">
-        <v>31.94779396986597</v>
+        <v>31.9477901691932</v>
       </c>
       <c r="E740" t="n">
-        <v>32.0755076009098</v>
+        <v>32.07550378504357</v>
       </c>
       <c r="F740" t="n">
         <v>4282500</v>
@@ -15232,16 +15232,16 @@
         <v>45233</v>
       </c>
       <c r="B741" t="n">
-        <v>32.69441604614258</v>
+        <v>32.69441986083984</v>
       </c>
       <c r="C741" t="n">
-        <v>32.94984327951414</v>
+        <v>32.94984712401398</v>
       </c>
       <c r="D741" t="n">
-        <v>32.4684634920525</v>
+        <v>32.46846728038622</v>
       </c>
       <c r="E741" t="n">
-        <v>32.7337131201344</v>
+        <v>32.73371693941674</v>
       </c>
       <c r="F741" t="n">
         <v>3190300</v>
@@ -15272,16 +15272,16 @@
         <v>45237</v>
       </c>
       <c r="B743" t="n">
-        <v>32.48811340332031</v>
+        <v>32.48811721801758</v>
       </c>
       <c r="C743" t="n">
-        <v>32.63547556323554</v>
+        <v>32.63547939523581</v>
       </c>
       <c r="D743" t="n">
-        <v>31.81025571237618</v>
+        <v>31.81025944748058</v>
       </c>
       <c r="E743" t="n">
-        <v>31.87902372098318</v>
+        <v>31.8790274641622</v>
       </c>
       <c r="F743" t="n">
         <v>3324000</v>
@@ -15312,16 +15312,16 @@
         <v>45239</v>
       </c>
       <c r="B745" t="n">
-        <v>30.81802940368652</v>
+        <v>30.81802749633789</v>
       </c>
       <c r="C745" t="n">
-        <v>33.77506711733456</v>
+        <v>33.77506502697286</v>
       </c>
       <c r="D745" t="n">
-        <v>30.67066723245724</v>
+        <v>30.67066533422895</v>
       </c>
       <c r="E745" t="n">
-        <v>33.41157476098916</v>
+        <v>33.41157269312426</v>
       </c>
       <c r="F745" t="n">
         <v>15431300</v>
@@ -15332,16 +15332,16 @@
         <v>45240</v>
       </c>
       <c r="B746" t="n">
-        <v>31.25028419494629</v>
+        <v>31.25028610229492</v>
       </c>
       <c r="C746" t="n">
-        <v>32.06567979171039</v>
+        <v>32.06568174882637</v>
       </c>
       <c r="D746" t="n">
-        <v>31.04398016537612</v>
+        <v>31.04398206013306</v>
       </c>
       <c r="E746" t="n">
-        <v>31.05380443446818</v>
+        <v>31.05380632982475</v>
       </c>
       <c r="F746" t="n">
         <v>4738300</v>
@@ -15352,16 +15352,16 @@
         <v>45243</v>
       </c>
       <c r="B747" t="n">
-        <v>30.94574165344238</v>
+        <v>30.94573974609375</v>
       </c>
       <c r="C747" t="n">
-        <v>31.41729536226194</v>
+        <v>31.41729342584897</v>
       </c>
       <c r="D747" t="n">
-        <v>30.67066771973704</v>
+        <v>30.67066582934266</v>
       </c>
       <c r="E747" t="n">
-        <v>31.21099131732383</v>
+        <v>31.21098939362647</v>
       </c>
       <c r="F747" t="n">
         <v>3172300</v>
@@ -15392,16 +15392,16 @@
         <v>45246</v>
       </c>
       <c r="B749" t="n">
-        <v>31.13239669799805</v>
+        <v>31.13239860534668</v>
       </c>
       <c r="C749" t="n">
-        <v>32.13444778565191</v>
+        <v>32.13444975439192</v>
       </c>
       <c r="D749" t="n">
-        <v>30.68048968892551</v>
+        <v>30.68049156858774</v>
       </c>
       <c r="E749" t="n">
-        <v>31.78078159366364</v>
+        <v>31.78078354073604</v>
       </c>
       <c r="F749" t="n">
         <v>5148500</v>
@@ -15492,16 +15492,16 @@
         <v>45253</v>
       </c>
       <c r="B754" t="n">
-        <v>31.81025886535645</v>
+        <v>31.81025505065918</v>
       </c>
       <c r="C754" t="n">
-        <v>32.00674051552654</v>
+        <v>32.00673667726713</v>
       </c>
       <c r="D754" t="n">
-        <v>31.58430627931235</v>
+        <v>31.5843024917114</v>
       </c>
       <c r="E754" t="n">
-        <v>31.82990740513103</v>
+        <v>31.82990358807751</v>
       </c>
       <c r="F754" t="n">
         <v>2086300</v>
@@ -15552,16 +15552,16 @@
         <v>45258</v>
       </c>
       <c r="B757" t="n">
-        <v>29.80615234375</v>
+        <v>29.80615043640137</v>
       </c>
       <c r="C757" t="n">
-        <v>30.21876230404811</v>
+        <v>30.21876037029583</v>
       </c>
       <c r="D757" t="n">
-        <v>29.63914350568201</v>
+        <v>29.63914160902057</v>
       </c>
       <c r="E757" t="n">
-        <v>30.17946522507312</v>
+        <v>30.17946329383553</v>
       </c>
       <c r="F757" t="n">
         <v>5777500</v>
@@ -15592,16 +15592,16 @@
         <v>45260</v>
       </c>
       <c r="B759" t="n">
-        <v>29.45248413085938</v>
+        <v>29.45248603820801</v>
       </c>
       <c r="C759" t="n">
-        <v>29.83562312973222</v>
+        <v>29.83562506189301</v>
       </c>
       <c r="D759" t="n">
-        <v>29.17741209183939</v>
+        <v>29.1774139813743</v>
       </c>
       <c r="E759" t="n">
-        <v>29.66861430298963</v>
+        <v>29.66861622433489</v>
       </c>
       <c r="F759" t="n">
         <v>4483800</v>
@@ -15732,16 +15732,16 @@
         <v>45271</v>
       </c>
       <c r="B766" t="n">
-        <v>26.91788291931152</v>
+        <v>26.91788101196289</v>
       </c>
       <c r="C766" t="n">
-        <v>27.08489175922624</v>
+        <v>27.08488984004369</v>
       </c>
       <c r="D766" t="n">
-        <v>26.48562441474616</v>
+        <v>26.48562253802652</v>
       </c>
       <c r="E766" t="n">
-        <v>26.96700426857343</v>
+        <v>26.96700235774415</v>
       </c>
       <c r="F766" t="n">
         <v>6627000</v>
@@ -15792,16 +15792,16 @@
         <v>45274</v>
       </c>
       <c r="B769" t="n">
-        <v>27.00629806518555</v>
+        <v>27.00629997253418</v>
       </c>
       <c r="C769" t="n">
-        <v>27.2027797044063</v>
+        <v>27.20278162563166</v>
       </c>
       <c r="D769" t="n">
-        <v>26.49544730224182</v>
+        <v>26.49544917351107</v>
       </c>
       <c r="E769" t="n">
-        <v>26.82946496464443</v>
+        <v>26.82946685950403</v>
       </c>
       <c r="F769" t="n">
         <v>14011300</v>
@@ -15812,16 +15812,16 @@
         <v>45275</v>
       </c>
       <c r="B770" t="n">
-        <v>25.88635635375977</v>
+        <v>25.8863582611084</v>
       </c>
       <c r="C770" t="n">
-        <v>27.21260267051552</v>
+        <v>27.21260467558413</v>
       </c>
       <c r="D770" t="n">
-        <v>25.88635635375977</v>
+        <v>25.8863582611084</v>
       </c>
       <c r="E770" t="n">
-        <v>27.1634813261689</v>
+        <v>27.16348332761816</v>
       </c>
       <c r="F770" t="n">
         <v>11924000</v>
@@ -15832,16 +15832,16 @@
         <v>45278</v>
       </c>
       <c r="B771" t="n">
-        <v>26.21055030822754</v>
+        <v>26.21055221557617</v>
       </c>
       <c r="C771" t="n">
-        <v>26.76069626050536</v>
+        <v>26.76069820788825</v>
       </c>
       <c r="D771" t="n">
-        <v>25.94530066428034</v>
+        <v>25.94530255232668</v>
       </c>
       <c r="E771" t="n">
-        <v>26.12213376024514</v>
+        <v>26.12213566115967</v>
       </c>
       <c r="F771" t="n">
         <v>4958200</v>
@@ -15852,16 +15852,16 @@
         <v>45279</v>
       </c>
       <c r="B772" t="n">
-        <v>26.32843971252441</v>
+        <v>26.32843780517578</v>
       </c>
       <c r="C772" t="n">
-        <v>26.52492136101001</v>
+        <v>26.52491943942738</v>
       </c>
       <c r="D772" t="n">
-        <v>26.13195993782669</v>
+        <v>26.13195804471192</v>
       </c>
       <c r="E772" t="n">
-        <v>26.30879304670615</v>
+        <v>26.30879114078081</v>
       </c>
       <c r="F772" t="n">
         <v>3900900</v>
@@ -15872,16 +15872,16 @@
         <v>45280</v>
       </c>
       <c r="B773" t="n">
-        <v>25.85688591003418</v>
+        <v>25.85688400268555</v>
       </c>
       <c r="C773" t="n">
-        <v>26.54456980342805</v>
+        <v>26.54456784535201</v>
       </c>
       <c r="D773" t="n">
-        <v>25.68987707156926</v>
+        <v>25.68987517654013</v>
       </c>
       <c r="E773" t="n">
-        <v>26.54456980342805</v>
+        <v>26.54456784535201</v>
       </c>
       <c r="F773" t="n">
         <v>6168300</v>
@@ -15912,16 +15912,16 @@
         <v>45282</v>
       </c>
       <c r="B775" t="n">
-        <v>25.95512580871582</v>
+        <v>25.95512771606445</v>
       </c>
       <c r="C775" t="n">
-        <v>26.2203754616087</v>
+        <v>26.22037738844958</v>
       </c>
       <c r="D775" t="n">
-        <v>25.79794124562103</v>
+        <v>25.79794314141873</v>
       </c>
       <c r="E775" t="n">
-        <v>26.03371809026321</v>
+        <v>26.03372000338731</v>
       </c>
       <c r="F775" t="n">
         <v>3644200</v>
@@ -16012,16 +16012,16 @@
         <v>45294</v>
       </c>
       <c r="B780" t="n">
-        <v>25.88635635375977</v>
+        <v>25.8863582611084</v>
       </c>
       <c r="C780" t="n">
-        <v>26.28914200846361</v>
+        <v>26.28914394549015</v>
       </c>
       <c r="D780" t="n">
-        <v>25.35585707754239</v>
+        <v>25.35585894580298</v>
       </c>
       <c r="E780" t="n">
-        <v>25.64075525338972</v>
+        <v>25.64075714264207</v>
       </c>
       <c r="F780" t="n">
         <v>5734800</v>
@@ -16052,16 +16052,16 @@
         <v>45296</v>
       </c>
       <c r="B782" t="n">
-        <v>25.68987464904785</v>
+        <v>25.68987655639648</v>
       </c>
       <c r="C782" t="n">
-        <v>25.97477282406455</v>
+        <v>25.97477475256549</v>
       </c>
       <c r="D782" t="n">
-        <v>25.21832098742127</v>
+        <v>25.21832285975933</v>
       </c>
       <c r="E782" t="n">
-        <v>25.36568127245611</v>
+        <v>25.36568315573496</v>
       </c>
       <c r="F782" t="n">
         <v>3417300</v>
@@ -16092,16 +16092,16 @@
         <v>45300</v>
       </c>
       <c r="B784" t="n">
-        <v>28.01817512512207</v>
+        <v>28.0181770324707</v>
       </c>
       <c r="C784" t="n">
-        <v>28.24412769698892</v>
+        <v>28.24412961971936</v>
       </c>
       <c r="D784" t="n">
-        <v>26.79999384234995</v>
+        <v>26.7999956667704</v>
       </c>
       <c r="E784" t="n">
-        <v>27.01612214494592</v>
+        <v>27.01612398407939</v>
       </c>
       <c r="F784" t="n">
         <v>10290300</v>
@@ -16152,16 +16152,16 @@
         <v>45303</v>
       </c>
       <c r="B787" t="n">
-        <v>28.20483207702637</v>
+        <v>28.20483016967773</v>
       </c>
       <c r="C787" t="n">
-        <v>28.86304316187749</v>
+        <v>28.86304121001741</v>
       </c>
       <c r="D787" t="n">
-        <v>27.82169492460737</v>
+        <v>27.82169304316834</v>
       </c>
       <c r="E787" t="n">
-        <v>28.63709057833746</v>
+        <v>28.63708864175739</v>
       </c>
       <c r="F787" t="n">
         <v>5067700</v>
@@ -16172,16 +16172,16 @@
         <v>45306</v>
       </c>
       <c r="B788" t="n">
-        <v>28.52902793884277</v>
+        <v>28.52902603149414</v>
       </c>
       <c r="C788" t="n">
-        <v>28.68621251092004</v>
+        <v>28.68621059306261</v>
       </c>
       <c r="D788" t="n">
-        <v>27.9002877767458</v>
+        <v>27.90028591143248</v>
       </c>
       <c r="E788" t="n">
-        <v>28.06729661880138</v>
+        <v>28.06729474232245</v>
       </c>
       <c r="F788" t="n">
         <v>3859400</v>
@@ -16252,16 +16252,16 @@
         <v>45310</v>
       </c>
       <c r="B792" t="n">
-        <v>29.03005027770996</v>
+        <v>29.03005218505859</v>
       </c>
       <c r="C792" t="n">
-        <v>29.197059106456</v>
+        <v>29.19706102477754</v>
       </c>
       <c r="D792" t="n">
-        <v>28.0574701128199</v>
+        <v>28.05747195626752</v>
       </c>
       <c r="E792" t="n">
-        <v>28.73532969699943</v>
+        <v>28.73533158498416</v>
       </c>
       <c r="F792" t="n">
         <v>7851200</v>
@@ -16312,16 +16312,16 @@
         <v>45315</v>
       </c>
       <c r="B795" t="n">
-        <v>27.86099243164062</v>
+        <v>27.86099052429199</v>
       </c>
       <c r="C795" t="n">
-        <v>28.52902779653059</v>
+        <v>28.52902584344861</v>
       </c>
       <c r="D795" t="n">
-        <v>27.63503797084227</v>
+        <v>27.63503607896236</v>
       </c>
       <c r="E795" t="n">
-        <v>28.04764793893384</v>
+        <v>28.04764601880687</v>
       </c>
       <c r="F795" t="n">
         <v>4070600</v>
@@ -16352,16 +16352,16 @@
         <v>45317</v>
       </c>
       <c r="B797" t="n">
-        <v>28.24412727355957</v>
+        <v>28.2441291809082</v>
       </c>
       <c r="C797" t="n">
-        <v>28.24412727355957</v>
+        <v>28.2441291809082</v>
       </c>
       <c r="D797" t="n">
-        <v>27.50732395337975</v>
+        <v>27.50732581097147</v>
       </c>
       <c r="E797" t="n">
-        <v>27.65468424265817</v>
+        <v>27.65468611020124</v>
       </c>
       <c r="F797" t="n">
         <v>2761100</v>
@@ -16392,16 +16392,16 @@
         <v>45321</v>
       </c>
       <c r="B799" t="n">
-        <v>27.2420768737793</v>
+        <v>27.24207496643066</v>
       </c>
       <c r="C799" t="n">
-        <v>27.54662362392648</v>
+        <v>27.54662169525507</v>
       </c>
       <c r="D799" t="n">
-        <v>26.97682720382707</v>
+        <v>26.97682531504984</v>
       </c>
       <c r="E799" t="n">
-        <v>27.369790510625</v>
+        <v>27.36978859433452</v>
       </c>
       <c r="F799" t="n">
         <v>2184900</v>
@@ -16432,16 +16432,16 @@
         <v>45323</v>
       </c>
       <c r="B801" t="n">
-        <v>26.24002265930176</v>
+        <v>26.24002075195312</v>
       </c>
       <c r="C801" t="n">
-        <v>27.40908451061442</v>
+        <v>27.4090825182884</v>
       </c>
       <c r="D801" t="n">
-        <v>26.10248663224892</v>
+        <v>26.10248473489757</v>
       </c>
       <c r="E801" t="n">
-        <v>27.31084368823903</v>
+        <v>27.31084170305399</v>
       </c>
       <c r="F801" t="n">
         <v>7611700</v>
@@ -16532,16 +16532,16 @@
         <v>45330</v>
       </c>
       <c r="B806" t="n">
-        <v>28.79427528381348</v>
+        <v>28.79427337646484</v>
       </c>
       <c r="C806" t="n">
-        <v>28.81392382346353</v>
+        <v>28.81392191481336</v>
       </c>
       <c r="D806" t="n">
-        <v>27.39926082305394</v>
+        <v>27.39925900811183</v>
       </c>
       <c r="E806" t="n">
-        <v>28.71568299900116</v>
+        <v>28.71568109685852</v>
       </c>
       <c r="F806" t="n">
         <v>6908300</v>
@@ -16552,16 +16552,16 @@
         <v>45331</v>
       </c>
       <c r="B807" t="n">
-        <v>27.6939811706543</v>
+        <v>27.69398307800293</v>
       </c>
       <c r="C807" t="n">
-        <v>28.9121624286317</v>
+        <v>28.9121644198793</v>
       </c>
       <c r="D807" t="n">
-        <v>27.52697234402422</v>
+        <v>27.52697423987057</v>
       </c>
       <c r="E807" t="n">
-        <v>28.83357014985212</v>
+        <v>28.83357213568689</v>
       </c>
       <c r="F807" t="n">
         <v>5513900</v>
@@ -16592,16 +16592,16 @@
         <v>45337</v>
       </c>
       <c r="B809" t="n">
-        <v>28.00835227966309</v>
+        <v>28.00835037231445</v>
       </c>
       <c r="C809" t="n">
-        <v>28.26377767232718</v>
+        <v>28.26377574758426</v>
       </c>
       <c r="D809" t="n">
-        <v>27.28137318075199</v>
+        <v>27.28137132291011</v>
       </c>
       <c r="E809" t="n">
-        <v>27.40908494019011</v>
+        <v>27.40908307365115</v>
       </c>
       <c r="F809" t="n">
         <v>2788300</v>
@@ -16632,16 +16632,16 @@
         <v>45341</v>
       </c>
       <c r="B811" t="n">
-        <v>28.67638778686523</v>
+        <v>28.6763858795166</v>
       </c>
       <c r="C811" t="n">
-        <v>28.76480434148215</v>
+        <v>28.76480242825268</v>
       </c>
       <c r="D811" t="n">
-        <v>28.23430501378064</v>
+        <v>28.2343031358362</v>
       </c>
       <c r="E811" t="n">
-        <v>28.74515580183664</v>
+        <v>28.74515388991405</v>
       </c>
       <c r="F811" t="n">
         <v>1698200</v>
@@ -16672,16 +16672,16 @@
         <v>45343</v>
       </c>
       <c r="B813" t="n">
-        <v>28.92198944091797</v>
+        <v>28.92198753356934</v>
       </c>
       <c r="C813" t="n">
-        <v>28.98093318714647</v>
+        <v>28.98093127591061</v>
       </c>
       <c r="D813" t="n">
-        <v>28.36201916727748</v>
+        <v>28.36201729685779</v>
       </c>
       <c r="E813" t="n">
-        <v>28.6370912322024</v>
+        <v>28.63708934364225</v>
       </c>
       <c r="F813" t="n">
         <v>2751400</v>
@@ -16792,16 +16792,16 @@
         <v>45351</v>
       </c>
       <c r="B819" t="n">
-        <v>27.45820617675781</v>
+        <v>27.45820426940918</v>
       </c>
       <c r="C819" t="n">
-        <v>28.14588819377561</v>
+        <v>28.14588623865804</v>
       </c>
       <c r="D819" t="n">
-        <v>27.45820617675781</v>
+        <v>27.45820426940918</v>
       </c>
       <c r="E819" t="n">
-        <v>27.98870362566938</v>
+        <v>27.98870168147043</v>
       </c>
       <c r="F819" t="n">
         <v>2784300</v>
@@ -16972,16 +16972,16 @@
         <v>45364</v>
       </c>
       <c r="B828" t="n">
-        <v>29.13811683654785</v>
+        <v>29.13811492919922</v>
       </c>
       <c r="C828" t="n">
-        <v>29.36406941808906</v>
+        <v>29.36406749594983</v>
       </c>
       <c r="D828" t="n">
-        <v>28.98093226905937</v>
+        <v>28.98093037199986</v>
       </c>
       <c r="E828" t="n">
-        <v>28.98093226905937</v>
+        <v>28.98093037199986</v>
       </c>
       <c r="F828" t="n">
         <v>2596400</v>
@@ -17032,16 +17032,16 @@
         <v>45369</v>
       </c>
       <c r="B831" t="n">
-        <v>28.98093032836914</v>
+        <v>28.98093223571777</v>
       </c>
       <c r="C831" t="n">
-        <v>29.28547517326093</v>
+        <v>29.28547710065286</v>
       </c>
       <c r="D831" t="n">
-        <v>28.61743986927554</v>
+        <v>28.61744175270144</v>
       </c>
       <c r="E831" t="n">
-        <v>28.77462630002598</v>
+        <v>28.77462819379693</v>
       </c>
       <c r="F831" t="n">
         <v>4710300</v>
@@ -17112,16 +17112,16 @@
         <v>45373</v>
       </c>
       <c r="B835" t="n">
-        <v>29.71773338317871</v>
+        <v>29.71773529052734</v>
       </c>
       <c r="C835" t="n">
-        <v>30.00263156131158</v>
+        <v>30.0026334869456</v>
       </c>
       <c r="D835" t="n">
-        <v>29.28547491839919</v>
+        <v>29.28547679800454</v>
       </c>
       <c r="E835" t="n">
-        <v>29.88474220772164</v>
+        <v>29.88474412578926</v>
       </c>
       <c r="F835" t="n">
         <v>3854000</v>
@@ -17152,16 +17152,16 @@
         <v>45377</v>
       </c>
       <c r="B837" t="n">
-        <v>30.81802940368652</v>
+        <v>30.81802749633789</v>
       </c>
       <c r="C837" t="n">
-        <v>31.22081509112746</v>
+        <v>31.22081315885015</v>
       </c>
       <c r="D837" t="n">
-        <v>30.51348266534799</v>
+        <v>30.51348077684796</v>
       </c>
       <c r="E837" t="n">
-        <v>30.61172348823823</v>
+        <v>30.61172159365801</v>
       </c>
       <c r="F837" t="n">
         <v>3327200</v>
@@ -17172,16 +17172,16 @@
         <v>45378</v>
       </c>
       <c r="B838" t="n">
-        <v>31.48606300354004</v>
+        <v>31.48606109619141</v>
       </c>
       <c r="C838" t="n">
-        <v>31.91832337550937</v>
+        <v>31.91832144197546</v>
       </c>
       <c r="D838" t="n">
-        <v>30.38577102935353</v>
+        <v>30.3857691886579</v>
       </c>
       <c r="E838" t="n">
-        <v>30.6510206900868</v>
+        <v>30.65101883332299</v>
       </c>
       <c r="F838" t="n">
         <v>9071000</v>
@@ -17372,16 +17372,16 @@
         <v>45393</v>
       </c>
       <c r="B848" t="n">
-        <v>35.62198257446289</v>
+        <v>35.62198638916016</v>
       </c>
       <c r="C848" t="n">
-        <v>35.91670689814429</v>
+        <v>35.91671074440308</v>
       </c>
       <c r="D848" t="n">
-        <v>34.59045868430435</v>
+        <v>34.59046238853748</v>
       </c>
       <c r="E848" t="n">
-        <v>34.74764324139922</v>
+        <v>34.74764696246498</v>
       </c>
       <c r="F848" t="n">
         <v>5960900</v>
@@ -17412,16 +17412,16 @@
         <v>45397</v>
       </c>
       <c r="B850" t="n">
-        <v>34.06978988647461</v>
+        <v>34.06978607177734</v>
       </c>
       <c r="C850" t="n">
-        <v>34.52169507730631</v>
+        <v>34.52169121201051</v>
       </c>
       <c r="D850" t="n">
-        <v>33.83401114697602</v>
+        <v>33.83400735867823</v>
       </c>
       <c r="E850" t="n">
-        <v>34.43327851844133</v>
+        <v>34.43327466304528</v>
       </c>
       <c r="F850" t="n">
         <v>4151100</v>
@@ -17472,16 +17472,16 @@
         <v>45400</v>
       </c>
       <c r="B853" t="n">
-        <v>32.33092880249023</v>
+        <v>32.3309326171875</v>
       </c>
       <c r="C853" t="n">
-        <v>33.28386227408815</v>
+        <v>33.28386620122118</v>
       </c>
       <c r="D853" t="n">
-        <v>31.93796554165645</v>
+        <v>31.93796930998834</v>
       </c>
       <c r="E853" t="n">
-        <v>33.00878649247434</v>
+        <v>33.00879038715143</v>
       </c>
       <c r="F853" t="n">
         <v>4478700</v>
@@ -17632,16 +17632,16 @@
         <v>45412</v>
       </c>
       <c r="B861" t="n">
-        <v>32.58635330200195</v>
+        <v>32.58635711669922</v>
       </c>
       <c r="C861" t="n">
-        <v>33.66700042877825</v>
+        <v>33.66700436998067</v>
       </c>
       <c r="D861" t="n">
-        <v>32.43899488533395</v>
+        <v>32.43899868278081</v>
       </c>
       <c r="E861" t="n">
-        <v>33.60805481356574</v>
+        <v>33.60805874786774</v>
       </c>
       <c r="F861" t="n">
         <v>6661700</v>
@@ -29935,16 +29935,36 @@
         <v>21</v>
       </c>
       <c r="C1476" t="n">
-        <v>21.57</v>
+        <v>21.56999969482422</v>
       </c>
       <c r="D1476" t="n">
-        <v>20.83</v>
+        <v>20.82999992370605</v>
       </c>
       <c r="E1476" t="n">
-        <v>20.89</v>
+        <v>20.88999938964844</v>
       </c>
       <c r="F1476" t="n">
-        <v>5036200</v>
+        <v>5015500</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1477" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="C1477" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="D1477" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="E1477" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F1477" t="n">
+        <v>2558200</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1477"/>
+  <dimension ref="A1:F1478"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29952,19 +29952,39 @@
         <v>46314</v>
       </c>
       <c r="B1477" t="n">
-        <v>20.96</v>
+        <v>20.95999908447266</v>
       </c>
       <c r="C1477" t="n">
-        <v>21.11</v>
+        <v>21.11000061035156</v>
       </c>
       <c r="D1477" t="n">
-        <v>20.79</v>
+        <v>20.79000091552734</v>
       </c>
       <c r="E1477" t="n">
-        <v>20.8</v>
+        <v>20.79999923706055</v>
       </c>
       <c r="F1477" t="n">
         <v>2558200</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1478" t="n">
+        <v>20.97</v>
+      </c>
+      <c r="C1478" t="n">
+        <v>21.39</v>
+      </c>
+      <c r="D1478" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="E1478" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="F1478" t="n">
+        <v>4376200</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRAV3.xlsx
+++ b/database/BRAV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1478"/>
+  <dimension ref="A1:F1479"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,16 +512,16 @@
         <v>44152</v>
       </c>
       <c r="B5" t="n">
-        <v>20.17695426940918</v>
+        <v>20.17695617675781</v>
       </c>
       <c r="C5" t="n">
-        <v>20.17695426940918</v>
+        <v>20.17695617675781</v>
       </c>
       <c r="D5" t="n">
-        <v>19.85012445790661</v>
+        <v>19.85012633435968</v>
       </c>
       <c r="E5" t="n">
-        <v>20.12888973916155</v>
+        <v>20.12889164196659</v>
       </c>
       <c r="F5" t="n">
         <v>262242</v>
@@ -572,16 +572,16 @@
         <v>44158</v>
       </c>
       <c r="B8" t="n">
-        <v>20.20579147338867</v>
+        <v>20.2057933807373</v>
       </c>
       <c r="C8" t="n">
-        <v>20.52300874747816</v>
+        <v>20.52301068477087</v>
       </c>
       <c r="D8" t="n">
-        <v>20.14811628674976</v>
+        <v>20.14811818865408</v>
       </c>
       <c r="E8" t="n">
-        <v>20.14811628674976</v>
+        <v>20.14811818865408</v>
       </c>
       <c r="F8" t="n">
         <v>79408</v>
@@ -632,16 +632,16 @@
         <v>44161</v>
       </c>
       <c r="B11" t="n">
-        <v>22.87810897827148</v>
+        <v>22.87811088562012</v>
       </c>
       <c r="C11" t="n">
-        <v>22.87810897827148</v>
+        <v>22.87811088562012</v>
       </c>
       <c r="D11" t="n">
-        <v>22.31096214463751</v>
+        <v>22.3109640047031</v>
       </c>
       <c r="E11" t="n">
-        <v>22.31096214463751</v>
+        <v>22.3109640047031</v>
       </c>
       <c r="F11" t="n">
         <v>72970</v>
@@ -652,16 +652,16 @@
         <v>44162</v>
       </c>
       <c r="B12" t="n">
-        <v>23.07036399841309</v>
+        <v>23.07036209106445</v>
       </c>
       <c r="C12" t="n">
-        <v>23.55099623037812</v>
+        <v>23.55099428329309</v>
       </c>
       <c r="D12" t="n">
-        <v>22.10909953448302</v>
+        <v>22.10909770660719</v>
       </c>
       <c r="E12" t="n">
-        <v>23.07036399841309</v>
+        <v>23.07036209106445</v>
       </c>
       <c r="F12" t="n">
         <v>72050</v>
@@ -692,16 +692,16 @@
         <v>44166</v>
       </c>
       <c r="B14" t="n">
-        <v>23.07036399841309</v>
+        <v>23.07036209106445</v>
       </c>
       <c r="C14" t="n">
-        <v>23.16649119432127</v>
+        <v>23.1664892790253</v>
       </c>
       <c r="D14" t="n">
-        <v>23.03191386956499</v>
+        <v>23.03191196539523</v>
       </c>
       <c r="E14" t="n">
-        <v>23.12803919168523</v>
+        <v>23.12803727956828</v>
       </c>
       <c r="F14" t="n">
         <v>93512</v>
@@ -792,16 +792,16 @@
         <v>44173</v>
       </c>
       <c r="B19" t="n">
-        <v>26.33866310119629</v>
+        <v>26.33866500854492</v>
       </c>
       <c r="C19" t="n">
-        <v>26.57898012603766</v>
+        <v>26.57898205078916</v>
       </c>
       <c r="D19" t="n">
-        <v>25.56965124500673</v>
+        <v>25.56965309666637</v>
       </c>
       <c r="E19" t="n">
-        <v>25.56965124500673</v>
+        <v>25.56965309666637</v>
       </c>
       <c r="F19" t="n">
         <v>126420</v>
@@ -812,16 +812,16 @@
         <v>44174</v>
       </c>
       <c r="B20" t="n">
-        <v>26.83852195739746</v>
+        <v>26.83852005004883</v>
       </c>
       <c r="C20" t="n">
-        <v>27.77095064592048</v>
+        <v>27.77094867230641</v>
       </c>
       <c r="D20" t="n">
-        <v>26.27137696749292</v>
+        <v>26.27137510044991</v>
       </c>
       <c r="E20" t="n">
-        <v>26.49246706969505</v>
+        <v>26.4924651869397</v>
       </c>
       <c r="F20" t="n">
         <v>212880</v>
@@ -892,16 +892,16 @@
         <v>44180</v>
       </c>
       <c r="B24" t="n">
-        <v>33.00984573364258</v>
+        <v>33.00984191894531</v>
       </c>
       <c r="C24" t="n">
-        <v>33.98072266755544</v>
+        <v>33.9807187406613</v>
       </c>
       <c r="D24" t="n">
-        <v>30.76048335959674</v>
+        <v>30.7604798048412</v>
       </c>
       <c r="E24" t="n">
-        <v>30.76048335959674</v>
+        <v>30.7604798048412</v>
       </c>
       <c r="F24" t="n">
         <v>887803</v>
@@ -912,16 +912,16 @@
         <v>44181</v>
       </c>
       <c r="B25" t="n">
-        <v>32.68301391601562</v>
+        <v>32.68301773071289</v>
       </c>
       <c r="C25" t="n">
-        <v>34.45173835953219</v>
+        <v>34.4517423806715</v>
       </c>
       <c r="D25" t="n">
-        <v>32.10625456033017</v>
+        <v>32.10625830770921</v>
       </c>
       <c r="E25" t="n">
-        <v>33.62505319761509</v>
+        <v>33.62505712226533</v>
       </c>
       <c r="F25" t="n">
         <v>376808</v>
@@ -932,16 +932,16 @@
         <v>44182</v>
       </c>
       <c r="B26" t="n">
-        <v>32.10625839233398</v>
+        <v>32.10625457763672</v>
       </c>
       <c r="C26" t="n">
-        <v>33.64428227520571</v>
+        <v>33.64427827776851</v>
       </c>
       <c r="D26" t="n">
-        <v>31.64484935368452</v>
+        <v>31.64484559380946</v>
       </c>
       <c r="E26" t="n">
-        <v>33.6250572108933</v>
+        <v>33.62505321574033</v>
       </c>
       <c r="F26" t="n">
         <v>258257</v>
@@ -972,16 +972,16 @@
         <v>44186</v>
       </c>
       <c r="B28" t="n">
-        <v>32.18315887451172</v>
+        <v>32.18315505981445</v>
       </c>
       <c r="C28" t="n">
-        <v>33.33667773162143</v>
+        <v>33.33667378019659</v>
       </c>
       <c r="D28" t="n">
-        <v>29.12633427792858</v>
+        <v>29.12633082555934</v>
       </c>
       <c r="E28" t="n">
-        <v>31.86594156356414</v>
+        <v>31.86593778646691</v>
       </c>
       <c r="F28" t="n">
         <v>236079</v>
@@ -992,16 +992,16 @@
         <v>44187</v>
       </c>
       <c r="B29" t="n">
-        <v>33.16364288330078</v>
+        <v>33.16364669799805</v>
       </c>
       <c r="C29" t="n">
-        <v>33.47124761081827</v>
+        <v>33.47125146089823</v>
       </c>
       <c r="D29" t="n">
-        <v>32.59649608138177</v>
+        <v>32.59649983084212</v>
       </c>
       <c r="E29" t="n">
-        <v>33.21170553641675</v>
+        <v>33.21170935664249</v>
       </c>
       <c r="F29" t="n">
         <v>167504</v>
@@ -1032,16 +1032,16 @@
         <v>44193</v>
       </c>
       <c r="B31" t="n">
-        <v>36.21085739135742</v>
+        <v>36.21085357666016</v>
       </c>
       <c r="C31" t="n">
-        <v>36.66265388599569</v>
+        <v>36.66265002370312</v>
       </c>
       <c r="D31" t="n">
-        <v>35.56681025863972</v>
+        <v>35.56680651179074</v>
       </c>
       <c r="E31" t="n">
-        <v>35.56681025863972</v>
+        <v>35.56680651179074</v>
       </c>
       <c r="F31" t="n">
         <v>451822</v>
@@ -1052,16 +1052,16 @@
         <v>44194</v>
       </c>
       <c r="B32" t="n">
-        <v>36.09550476074219</v>
+        <v>36.09550857543945</v>
       </c>
       <c r="C32" t="n">
-        <v>37.06638166531152</v>
+        <v>37.06638558261441</v>
       </c>
       <c r="D32" t="n">
-        <v>35.95131304358604</v>
+        <v>35.95131684304462</v>
       </c>
       <c r="E32" t="n">
-        <v>36.52807241705953</v>
+        <v>36.52807627747203</v>
       </c>
       <c r="F32" t="n">
         <v>337154</v>
@@ -1092,16 +1092,16 @@
         <v>44200</v>
       </c>
       <c r="B34" t="n">
-        <v>34.99966049194336</v>
+        <v>34.99966430664062</v>
       </c>
       <c r="C34" t="n">
-        <v>36.62420073506411</v>
+        <v>36.62420472682393</v>
       </c>
       <c r="D34" t="n">
-        <v>34.98043542972244</v>
+        <v>34.98043924232432</v>
       </c>
       <c r="E34" t="n">
-        <v>36.52807167638402</v>
+        <v>36.52807565766651</v>
       </c>
       <c r="F34" t="n">
         <v>331840</v>
@@ -1112,16 +1112,16 @@
         <v>44201</v>
       </c>
       <c r="B35" t="n">
-        <v>36.13395690917969</v>
+        <v>36.13395309448242</v>
       </c>
       <c r="C35" t="n">
-        <v>36.32621129362743</v>
+        <v>36.32620745863368</v>
       </c>
       <c r="D35" t="n">
-        <v>34.60554560816865</v>
+        <v>34.60554195482727</v>
       </c>
       <c r="E35" t="n">
-        <v>35.45145965313264</v>
+        <v>35.45145591048728</v>
       </c>
       <c r="F35" t="n">
         <v>328059</v>
@@ -1172,16 +1172,16 @@
         <v>44204</v>
       </c>
       <c r="B38" t="n">
-        <v>34.13452529907227</v>
+        <v>34.134521484375</v>
       </c>
       <c r="C38" t="n">
-        <v>35.75906572541368</v>
+        <v>35.75906172916622</v>
       </c>
       <c r="D38" t="n">
-        <v>34.13452529907227</v>
+        <v>34.134521484375</v>
       </c>
       <c r="E38" t="n">
-        <v>35.16308123419719</v>
+        <v>35.16307730455386</v>
       </c>
       <c r="F38" t="n">
         <v>367201</v>
@@ -1272,16 +1272,16 @@
         <v>44211</v>
       </c>
       <c r="B43" t="n">
-        <v>33.94226837158203</v>
+        <v>33.9422721862793</v>
       </c>
       <c r="C43" t="n">
-        <v>35.04772061203977</v>
+        <v>35.0477245509764</v>
       </c>
       <c r="D43" t="n">
-        <v>33.16364216523639</v>
+        <v>33.16364589242556</v>
       </c>
       <c r="E43" t="n">
-        <v>34.60554046537172</v>
+        <v>34.60554435461268</v>
       </c>
       <c r="F43" t="n">
         <v>319883</v>
@@ -1292,16 +1292,16 @@
         <v>44214</v>
       </c>
       <c r="B44" t="n">
-        <v>34.04801177978516</v>
+        <v>34.04800796508789</v>
       </c>
       <c r="C44" t="n">
-        <v>34.5094208103909</v>
+        <v>34.50941694399793</v>
       </c>
       <c r="D44" t="n">
-        <v>33.27900172554335</v>
+        <v>33.27899799700501</v>
       </c>
       <c r="E44" t="n">
-        <v>34.11529950370554</v>
+        <v>34.11529568146945</v>
       </c>
       <c r="F44" t="n">
         <v>117631</v>
@@ -1332,16 +1332,16 @@
         <v>44216</v>
       </c>
       <c r="B46" t="n">
-        <v>34.12490844726562</v>
+        <v>34.12491226196289</v>
       </c>
       <c r="C46" t="n">
-        <v>35.28803968588292</v>
+        <v>35.28804363060232</v>
       </c>
       <c r="D46" t="n">
-        <v>33.66350321275509</v>
+        <v>33.66350697587357</v>
       </c>
       <c r="E46" t="n">
-        <v>34.60554249130722</v>
+        <v>34.60554635973278</v>
       </c>
       <c r="F46" t="n">
         <v>359332</v>
@@ -1372,16 +1372,16 @@
         <v>44218</v>
       </c>
       <c r="B48" t="n">
-        <v>32.95216369628906</v>
+        <v>32.95216751098633</v>
       </c>
       <c r="C48" t="n">
-        <v>33.45202278739948</v>
+        <v>33.45202665996278</v>
       </c>
       <c r="D48" t="n">
-        <v>32.53882112897777</v>
+        <v>32.53882489582456</v>
       </c>
       <c r="E48" t="n">
-        <v>33.19248071115274</v>
+        <v>33.19248455367023</v>
       </c>
       <c r="F48" t="n">
         <v>220341</v>
@@ -1472,16 +1472,16 @@
         <v>44228</v>
       </c>
       <c r="B53" t="n">
-        <v>31.7794246673584</v>
+        <v>31.77942657470703</v>
       </c>
       <c r="C53" t="n">
-        <v>33.1155814640686</v>
+        <v>33.11558345161116</v>
       </c>
       <c r="D53" t="n">
-        <v>31.66407054800669</v>
+        <v>31.66407244843196</v>
       </c>
       <c r="E53" t="n">
-        <v>32.68301382233215</v>
+        <v>32.68301578391271</v>
       </c>
       <c r="F53" t="n">
         <v>610435</v>
@@ -1492,16 +1492,16 @@
         <v>44229</v>
       </c>
       <c r="B54" t="n">
-        <v>32.63494873046875</v>
+        <v>32.63495254516602</v>
       </c>
       <c r="C54" t="n">
-        <v>33.65389204571495</v>
+        <v>33.65389597951643</v>
       </c>
       <c r="D54" t="n">
-        <v>31.97167657096734</v>
+        <v>31.97168030813476</v>
       </c>
       <c r="E54" t="n">
-        <v>33.64427951434755</v>
+        <v>33.64428344702543</v>
       </c>
       <c r="F54" t="n">
         <v>582228</v>
@@ -1532,16 +1532,16 @@
         <v>44231</v>
       </c>
       <c r="B56" t="n">
-        <v>32.68301391601562</v>
+        <v>32.68301773071289</v>
       </c>
       <c r="C56" t="n">
-        <v>34.11529602664492</v>
+        <v>34.11530000851534</v>
       </c>
       <c r="D56" t="n">
-        <v>32.44269689321744</v>
+        <v>32.44270067986538</v>
       </c>
       <c r="E56" t="n">
-        <v>33.06751890394745</v>
+        <v>33.06752276352339</v>
       </c>
       <c r="F56" t="n">
         <v>466743</v>
@@ -1612,16 +1612,16 @@
         <v>44237</v>
       </c>
       <c r="B60" t="n">
-        <v>34.83624649047852</v>
+        <v>34.83625030517578</v>
       </c>
       <c r="C60" t="n">
-        <v>35.33610184184258</v>
+        <v>35.33610571127585</v>
       </c>
       <c r="D60" t="n">
-        <v>34.23064955227608</v>
+        <v>34.23065330065825</v>
       </c>
       <c r="E60" t="n">
-        <v>34.43251269995998</v>
+        <v>34.43251647044691</v>
       </c>
       <c r="F60" t="n">
         <v>186206</v>
@@ -1652,16 +1652,16 @@
         <v>44239</v>
       </c>
       <c r="B62" t="n">
-        <v>34.40367889404297</v>
+        <v>34.4036750793457</v>
       </c>
       <c r="C62" t="n">
-        <v>34.52864555631986</v>
+        <v>34.52864172776623</v>
       </c>
       <c r="D62" t="n">
-        <v>32.673400666573</v>
+        <v>32.67339704372985</v>
       </c>
       <c r="E62" t="n">
-        <v>33.67311897448496</v>
+        <v>33.67311524079254</v>
       </c>
       <c r="F62" t="n">
         <v>218195</v>
@@ -1692,16 +1692,16 @@
         <v>44245</v>
       </c>
       <c r="B64" t="n">
-        <v>37.00870895385742</v>
+        <v>37.00870513916016</v>
       </c>
       <c r="C64" t="n">
-        <v>37.38360144742785</v>
+        <v>37.38359759408829</v>
       </c>
       <c r="D64" t="n">
-        <v>35.71100215049589</v>
+        <v>35.71099846956061</v>
       </c>
       <c r="E64" t="n">
-        <v>36.37427435009953</v>
+        <v>36.37427060079703</v>
       </c>
       <c r="F64" t="n">
         <v>661534</v>
@@ -1812,16 +1812,16 @@
         <v>44253</v>
       </c>
       <c r="B70" t="n">
-        <v>34.57670593261719</v>
+        <v>34.57670974731445</v>
       </c>
       <c r="C70" t="n">
-        <v>37.21057322750037</v>
+        <v>37.21057733278074</v>
       </c>
       <c r="D70" t="n">
-        <v>33.75001700107128</v>
+        <v>33.75002072456356</v>
       </c>
       <c r="E70" t="n">
-        <v>36.5376847961999</v>
+        <v>36.53768882724342</v>
       </c>
       <c r="F70" t="n">
         <v>410022</v>
@@ -1932,16 +1932,16 @@
         <v>44263</v>
       </c>
       <c r="B76" t="n">
-        <v>41.91115951538086</v>
+        <v>41.91115570068359</v>
       </c>
       <c r="C76" t="n">
-        <v>44.60270214463106</v>
+        <v>44.60269808495321</v>
       </c>
       <c r="D76" t="n">
-        <v>40.70957805138659</v>
+        <v>40.70957434605565</v>
       </c>
       <c r="E76" t="n">
-        <v>43.55492493684502</v>
+        <v>43.55492097253444</v>
       </c>
       <c r="F76" t="n">
         <v>1012691</v>
@@ -1952,16 +1952,16 @@
         <v>44264</v>
       </c>
       <c r="B77" t="n">
-        <v>43.50686264038086</v>
+        <v>43.50685882568359</v>
       </c>
       <c r="C77" t="n">
-        <v>43.50686264038086</v>
+        <v>43.50685882568359</v>
       </c>
       <c r="D77" t="n">
-        <v>39.89250193891922</v>
+        <v>39.89249844113039</v>
       </c>
       <c r="E77" t="n">
-        <v>42.29566488693005</v>
+        <v>42.29566117843103</v>
       </c>
       <c r="F77" t="n">
         <v>563525</v>
@@ -1972,16 +1972,16 @@
         <v>44265</v>
       </c>
       <c r="B78" t="n">
-        <v>44.69882583618164</v>
+        <v>44.69882965087891</v>
       </c>
       <c r="C78" t="n">
-        <v>44.89108021255291</v>
+        <v>44.89108404365759</v>
       </c>
       <c r="D78" t="n">
-        <v>43.38189403862891</v>
+        <v>43.38189774093629</v>
       </c>
       <c r="E78" t="n">
-        <v>43.83369051144994</v>
+        <v>43.83369425231464</v>
       </c>
       <c r="F78" t="n">
         <v>425454</v>
@@ -2012,16 +2012,16 @@
         <v>44267</v>
       </c>
       <c r="B80" t="n">
-        <v>45.66009521484375</v>
+        <v>45.66009140014648</v>
       </c>
       <c r="C80" t="n">
-        <v>49.01491000208902</v>
+        <v>49.01490590711195</v>
       </c>
       <c r="D80" t="n">
-        <v>45.18907366630634</v>
+        <v>45.18906989096082</v>
       </c>
       <c r="E80" t="n">
-        <v>47.15005636649431</v>
+        <v>47.15005242731743</v>
       </c>
       <c r="F80" t="n">
         <v>954539</v>
@@ -2052,16 +2052,16 @@
         <v>44271</v>
       </c>
       <c r="B82" t="n">
-        <v>42.75707244873047</v>
+        <v>42.7570686340332</v>
       </c>
       <c r="C82" t="n">
-        <v>45.18907290913018</v>
+        <v>45.18906887745489</v>
       </c>
       <c r="D82" t="n">
-        <v>42.75707244873047</v>
+        <v>42.7570686340332</v>
       </c>
       <c r="E82" t="n">
-        <v>44.50657567458991</v>
+        <v>44.5065717038056</v>
       </c>
       <c r="F82" t="n">
         <v>561175</v>
@@ -2092,16 +2092,16 @@
         <v>44273</v>
       </c>
       <c r="B84" t="n">
-        <v>40.89221954345703</v>
+        <v>40.89221572875977</v>
       </c>
       <c r="C84" t="n">
-        <v>45.0256568951004</v>
+        <v>45.02565269480871</v>
       </c>
       <c r="D84" t="n">
-        <v>40.57500224961562</v>
+        <v>40.57499846451049</v>
       </c>
       <c r="E84" t="n">
-        <v>44.01632982334604</v>
+        <v>44.01632571721106</v>
       </c>
       <c r="F84" t="n">
         <v>572621</v>
@@ -2112,16 +2112,16 @@
         <v>44274</v>
       </c>
       <c r="B85" t="n">
-        <v>42.29566192626953</v>
+        <v>42.2956657409668</v>
       </c>
       <c r="C85" t="n">
-        <v>44.17013174266427</v>
+        <v>44.17013572642225</v>
       </c>
       <c r="D85" t="n">
-        <v>41.4593642170013</v>
+        <v>41.45936795627186</v>
       </c>
       <c r="E85" t="n">
-        <v>41.4593642170013</v>
+        <v>41.45936795627186</v>
       </c>
       <c r="F85" t="n">
         <v>639255</v>
@@ -2212,16 +2212,16 @@
         <v>44281</v>
       </c>
       <c r="B90" t="n">
-        <v>37.87384414672852</v>
+        <v>37.87384796142578</v>
       </c>
       <c r="C90" t="n">
-        <v>40.949891527232</v>
+        <v>40.94989565175231</v>
       </c>
       <c r="D90" t="n">
-        <v>37.56623940867817</v>
+        <v>37.56624319239313</v>
       </c>
       <c r="E90" t="n">
-        <v>39.95978959641457</v>
+        <v>39.95979362121066</v>
       </c>
       <c r="F90" t="n">
         <v>840076</v>
@@ -2312,16 +2312,16 @@
         <v>44291</v>
       </c>
       <c r="B95" t="n">
-        <v>35.68215942382812</v>
+        <v>35.68216323852539</v>
       </c>
       <c r="C95" t="n">
-        <v>37.01831616285484</v>
+        <v>37.01832012039754</v>
       </c>
       <c r="D95" t="n">
-        <v>35.09578756412892</v>
+        <v>35.09579131613852</v>
       </c>
       <c r="E95" t="n">
-        <v>37.01831616285484</v>
+        <v>37.01832012039754</v>
       </c>
       <c r="F95" t="n">
         <v>1091895</v>
@@ -2512,16 +2512,16 @@
         <v>44305</v>
       </c>
       <c r="B105" t="n">
-        <v>41.33439636230469</v>
+        <v>41.33440017700195</v>
       </c>
       <c r="C105" t="n">
-        <v>42.23798551125894</v>
+        <v>42.23798940934727</v>
       </c>
       <c r="D105" t="n">
-        <v>40.20971525467667</v>
+        <v>40.2097189655786</v>
       </c>
       <c r="E105" t="n">
-        <v>40.38274455876383</v>
+        <v>40.38274828563441</v>
       </c>
       <c r="F105" t="n">
         <v>1793083</v>
@@ -2552,16 +2552,16 @@
         <v>44308</v>
       </c>
       <c r="B107" t="n">
-        <v>42.3725700378418</v>
+        <v>42.37256622314453</v>
       </c>
       <c r="C107" t="n">
-        <v>42.77630013488342</v>
+        <v>42.77629628383934</v>
       </c>
       <c r="D107" t="n">
-        <v>41.04602186600353</v>
+        <v>41.0460181707321</v>
       </c>
       <c r="E107" t="n">
-        <v>42.58404574470481</v>
+        <v>42.58404191096891</v>
       </c>
       <c r="F107" t="n">
         <v>1175903</v>
@@ -2572,16 +2572,16 @@
         <v>44309</v>
       </c>
       <c r="B108" t="n">
-        <v>44.09323501586914</v>
+        <v>44.09323120117188</v>
       </c>
       <c r="C108" t="n">
-        <v>44.31432325105797</v>
+        <v>44.3143194172334</v>
       </c>
       <c r="D108" t="n">
-        <v>42.38218184069201</v>
+        <v>42.38217817402538</v>
       </c>
       <c r="E108" t="n">
-        <v>42.82436205864548</v>
+        <v>42.82435835372392</v>
       </c>
       <c r="F108" t="n">
         <v>1899574</v>
@@ -2612,16 +2612,16 @@
         <v>44313</v>
       </c>
       <c r="B110" t="n">
-        <v>43.7375602722168</v>
+        <v>43.73756408691406</v>
       </c>
       <c r="C110" t="n">
-        <v>44.31431963823069</v>
+        <v>44.31432350323168</v>
       </c>
       <c r="D110" t="n">
-        <v>43.04545053203033</v>
+        <v>43.04545428636325</v>
       </c>
       <c r="E110" t="n">
-        <v>43.40111793330461</v>
+        <v>43.40112171865809</v>
       </c>
       <c r="F110" t="n">
         <v>1146163</v>
@@ -2732,16 +2732,16 @@
         <v>44321</v>
       </c>
       <c r="B116" t="n">
-        <v>39.74831390380859</v>
+        <v>39.74831008911133</v>
       </c>
       <c r="C116" t="n">
-        <v>40.64229060912697</v>
+        <v>40.6422867086336</v>
       </c>
       <c r="D116" t="n">
-        <v>39.0754291787498</v>
+        <v>39.07542542863015</v>
       </c>
       <c r="E116" t="n">
-        <v>39.89250188164586</v>
+        <v>39.89249805311069</v>
       </c>
       <c r="F116" t="n">
         <v>3650961</v>
@@ -2772,16 +2772,16 @@
         <v>44323</v>
       </c>
       <c r="B118" t="n">
-        <v>38.83510971069336</v>
+        <v>38.83511352539062</v>
       </c>
       <c r="C118" t="n">
-        <v>39.99824098294782</v>
+        <v>39.99824491189721</v>
       </c>
       <c r="D118" t="n">
-        <v>37.51817793834604</v>
+        <v>37.51818162368365</v>
       </c>
       <c r="E118" t="n">
-        <v>39.66179864141913</v>
+        <v>39.66180253732045</v>
       </c>
       <c r="F118" t="n">
         <v>2227429</v>
@@ -2832,16 +2832,16 @@
         <v>44328</v>
       </c>
       <c r="B121" t="n">
-        <v>37.05677032470703</v>
+        <v>37.05676651000977</v>
       </c>
       <c r="C121" t="n">
-        <v>38.70053196862062</v>
+        <v>38.70052798471127</v>
       </c>
       <c r="D121" t="n">
-        <v>37.05677032470703</v>
+        <v>37.05676651000977</v>
       </c>
       <c r="E121" t="n">
-        <v>37.8161715649591</v>
+        <v>37.81616767208757</v>
       </c>
       <c r="F121" t="n">
         <v>783049</v>
@@ -2892,16 +2892,16 @@
         <v>44333</v>
       </c>
       <c r="B124" t="n">
-        <v>36.43194580078125</v>
+        <v>36.43194961547852</v>
       </c>
       <c r="C124" t="n">
-        <v>37.13366805612294</v>
+        <v>37.13367194429578</v>
       </c>
       <c r="D124" t="n">
-        <v>35.93208669563144</v>
+        <v>35.93209045798972</v>
       </c>
       <c r="E124" t="n">
-        <v>36.52807111039643</v>
+        <v>36.52807493515874</v>
       </c>
       <c r="F124" t="n">
         <v>946466</v>
@@ -2912,16 +2912,16 @@
         <v>44334</v>
       </c>
       <c r="B125" t="n">
-        <v>35.14385604858398</v>
+        <v>35.14385223388672</v>
       </c>
       <c r="C125" t="n">
-        <v>36.91258445174329</v>
+        <v>36.91258044505902</v>
       </c>
       <c r="D125" t="n">
-        <v>34.59593422023043</v>
+        <v>34.59593046500746</v>
       </c>
       <c r="E125" t="n">
-        <v>36.52807567013412</v>
+        <v>36.52807170518645</v>
       </c>
       <c r="F125" t="n">
         <v>2070451</v>
@@ -2952,16 +2952,16 @@
         <v>44336</v>
       </c>
       <c r="B127" t="n">
-        <v>34.63438415527344</v>
+        <v>34.63438034057617</v>
       </c>
       <c r="C127" t="n">
-        <v>35.26881876953347</v>
+        <v>35.26881488495837</v>
       </c>
       <c r="D127" t="n">
-        <v>34.51903376998102</v>
+        <v>34.51902996798866</v>
       </c>
       <c r="E127" t="n">
-        <v>34.51903376998102</v>
+        <v>34.51902996798866</v>
       </c>
       <c r="F127" t="n">
         <v>943604</v>
@@ -3012,16 +3012,16 @@
         <v>44341</v>
       </c>
       <c r="B130" t="n">
-        <v>37.29708862304688</v>
+        <v>37.29708480834961</v>
       </c>
       <c r="C130" t="n">
-        <v>38.78704981148397</v>
+        <v>38.78704584439543</v>
       </c>
       <c r="D130" t="n">
-        <v>37.22980089947328</v>
+        <v>37.22979709165812</v>
       </c>
       <c r="E130" t="n">
-        <v>37.52779313716071</v>
+        <v>37.52778929886728</v>
       </c>
       <c r="F130" t="n">
         <v>1731150</v>
@@ -3092,16 +3092,16 @@
         <v>44347</v>
       </c>
       <c r="B134" t="n">
-        <v>39.38303375244141</v>
+        <v>39.38302993774414</v>
       </c>
       <c r="C134" t="n">
-        <v>40.11359366504992</v>
+        <v>40.11358977958957</v>
       </c>
       <c r="D134" t="n">
-        <v>39.02736632794579</v>
+        <v>39.02736254769899</v>
       </c>
       <c r="E134" t="n">
-        <v>39.39264628425005</v>
+        <v>39.3926424686217</v>
       </c>
       <c r="F134" t="n">
         <v>715598</v>
@@ -3192,16 +3192,16 @@
         <v>44355</v>
       </c>
       <c r="B139" t="n">
-        <v>38.4602165222168</v>
+        <v>38.46022033691406</v>
       </c>
       <c r="C139" t="n">
-        <v>38.85433404388245</v>
+        <v>38.85433789767048</v>
       </c>
       <c r="D139" t="n">
-        <v>37.72004038668688</v>
+        <v>37.72004412796937</v>
       </c>
       <c r="E139" t="n">
-        <v>38.43137892899068</v>
+        <v>38.43138274082768</v>
       </c>
       <c r="F139" t="n">
         <v>978352</v>
@@ -3212,16 +3212,16 @@
         <v>44356</v>
       </c>
       <c r="B140" t="n">
-        <v>38.01803588867188</v>
+        <v>38.01803207397461</v>
       </c>
       <c r="C140" t="n">
-        <v>38.66208302162527</v>
+        <v>38.66207914230487</v>
       </c>
       <c r="D140" t="n">
-        <v>37.29708850045856</v>
+        <v>37.29708475810054</v>
       </c>
       <c r="E140" t="n">
-        <v>38.48905744729046</v>
+        <v>38.48905358533129</v>
       </c>
       <c r="F140" t="n">
         <v>837521</v>
@@ -3332,16 +3332,16 @@
         <v>44364</v>
       </c>
       <c r="B146" t="n">
-        <v>42.4879150390625</v>
+        <v>42.48791885375977</v>
       </c>
       <c r="C146" t="n">
-        <v>44.0067136610316</v>
+        <v>44.00671761209134</v>
       </c>
       <c r="D146" t="n">
-        <v>41.62277601425852</v>
+        <v>41.62277975128091</v>
       </c>
       <c r="E146" t="n">
-        <v>42.95893654890009</v>
+        <v>42.95894040588714</v>
       </c>
       <c r="F146" t="n">
         <v>1582144</v>
@@ -3372,16 +3372,16 @@
         <v>44368</v>
       </c>
       <c r="B148" t="n">
-        <v>46.96741485595703</v>
+        <v>46.96741104125977</v>
       </c>
       <c r="C148" t="n">
-        <v>47.24618202489792</v>
+        <v>47.24617818755916</v>
       </c>
       <c r="D148" t="n">
-        <v>43.53569979030122</v>
+        <v>43.53569625432814</v>
       </c>
       <c r="E148" t="n">
-        <v>43.73756295749668</v>
+        <v>43.73755940512824</v>
       </c>
       <c r="F148" t="n">
         <v>2655439</v>
@@ -3452,16 +3452,16 @@
         <v>44372</v>
       </c>
       <c r="B152" t="n">
-        <v>44.45851135253906</v>
+        <v>44.45851516723633</v>
       </c>
       <c r="C152" t="n">
-        <v>44.98720431506052</v>
+        <v>44.9872081751215</v>
       </c>
       <c r="D152" t="n">
-        <v>43.97787729834627</v>
+        <v>43.97788107180344</v>
       </c>
       <c r="E152" t="n">
-        <v>44.98720431506052</v>
+        <v>44.9872081751215</v>
       </c>
       <c r="F152" t="n">
         <v>1347904</v>
@@ -3472,16 +3472,16 @@
         <v>44375</v>
       </c>
       <c r="B153" t="n">
-        <v>44.5354118347168</v>
+        <v>44.53541564941406</v>
       </c>
       <c r="C153" t="n">
-        <v>44.64114967825854</v>
+        <v>44.64115350201283</v>
       </c>
       <c r="D153" t="n">
-        <v>43.20886378695175</v>
+        <v>43.20886748802305</v>
       </c>
       <c r="E153" t="n">
-        <v>44.13168177543641</v>
+        <v>44.13168555555202</v>
       </c>
       <c r="F153" t="n">
         <v>1110393</v>
@@ -3512,16 +3512,16 @@
         <v>44377</v>
       </c>
       <c r="B155" t="n">
-        <v>43.58376312255859</v>
+        <v>43.58375930786133</v>
       </c>
       <c r="C155" t="n">
-        <v>44.45851476998166</v>
+        <v>44.45851087872119</v>
       </c>
       <c r="D155" t="n">
-        <v>43.50686286720073</v>
+        <v>43.50685905923421</v>
       </c>
       <c r="E155" t="n">
-        <v>44.21819772441255</v>
+        <v>44.21819385418598</v>
       </c>
       <c r="F155" t="n">
         <v>1274116</v>
@@ -3572,16 +3572,16 @@
         <v>44382</v>
       </c>
       <c r="B158" t="n">
-        <v>45.04488372802734</v>
+        <v>45.04488754272461</v>
       </c>
       <c r="C158" t="n">
-        <v>46.21762753484401</v>
+        <v>46.21763144885693</v>
       </c>
       <c r="D158" t="n">
-        <v>44.42967048319475</v>
+        <v>44.42967424579171</v>
       </c>
       <c r="E158" t="n">
-        <v>44.98720479275436</v>
+        <v>44.98720860256699</v>
       </c>
       <c r="F158" t="n">
         <v>3391068</v>
@@ -3592,16 +3592,16 @@
         <v>44383</v>
       </c>
       <c r="B159" t="n">
-        <v>44.37199401855469</v>
+        <v>44.37199783325195</v>
       </c>
       <c r="C159" t="n">
-        <v>45.94847158903642</v>
+        <v>45.94847553926477</v>
       </c>
       <c r="D159" t="n">
-        <v>43.75678453900221</v>
+        <v>43.75678830080941</v>
       </c>
       <c r="E159" t="n">
-        <v>45.7850548143543</v>
+        <v>45.78505875053358</v>
       </c>
       <c r="F159" t="n">
         <v>1563442</v>
@@ -3652,16 +3652,16 @@
         <v>44389</v>
       </c>
       <c r="B162" t="n">
-        <v>44.72766876220703</v>
+        <v>44.72766494750977</v>
       </c>
       <c r="C162" t="n">
-        <v>45.75622090541913</v>
+        <v>45.75621700299953</v>
       </c>
       <c r="D162" t="n">
-        <v>44.08361789020423</v>
+        <v>44.08361413043626</v>
       </c>
       <c r="E162" t="n">
-        <v>45.75622090541913</v>
+        <v>45.75621700299953</v>
       </c>
       <c r="F162" t="n">
         <v>1597780</v>
@@ -3732,16 +3732,16 @@
         <v>44393</v>
       </c>
       <c r="B166" t="n">
-        <v>41.70928955078125</v>
+        <v>41.70929336547852</v>
       </c>
       <c r="C166" t="n">
-        <v>41.91115645117827</v>
+        <v>41.91116028433812</v>
       </c>
       <c r="D166" t="n">
-        <v>40.45003298811638</v>
+        <v>40.45003668764308</v>
       </c>
       <c r="E166" t="n">
-        <v>41.62277677100059</v>
+        <v>41.62278057778546</v>
       </c>
       <c r="F166" t="n">
         <v>1471156</v>
@@ -3752,16 +3752,16 @@
         <v>44396</v>
       </c>
       <c r="B167" t="n">
-        <v>40.22894287109375</v>
+        <v>40.22894668579102</v>
       </c>
       <c r="C167" t="n">
-        <v>41.05562800061862</v>
+        <v>41.05563189370605</v>
       </c>
       <c r="D167" t="n">
-        <v>39.50799183094843</v>
+        <v>39.50799557728174</v>
       </c>
       <c r="E167" t="n">
-        <v>40.46925613690023</v>
+        <v>40.46925997438512</v>
       </c>
       <c r="F167" t="n">
         <v>1632835</v>
@@ -3792,16 +3792,16 @@
         <v>44398</v>
       </c>
       <c r="B169" t="n">
-        <v>40.45964431762695</v>
+        <v>40.45964813232422</v>
       </c>
       <c r="C169" t="n">
-        <v>41.40168732645247</v>
+        <v>41.40169122996932</v>
       </c>
       <c r="D169" t="n">
-        <v>40.22894357839657</v>
+        <v>40.22894737134245</v>
       </c>
       <c r="E169" t="n">
-        <v>40.37313154041556</v>
+        <v>40.37313534695605</v>
       </c>
       <c r="F169" t="n">
         <v>985812</v>
@@ -3812,16 +3812,16 @@
         <v>44399</v>
       </c>
       <c r="B170" t="n">
-        <v>40.89221954345703</v>
+        <v>40.89221572875977</v>
       </c>
       <c r="C170" t="n">
-        <v>41.15176164706832</v>
+        <v>41.15175780815924</v>
       </c>
       <c r="D170" t="n">
-        <v>40.3923603996445</v>
+        <v>40.39235663157741</v>
       </c>
       <c r="E170" t="n">
-        <v>41.08447017755746</v>
+        <v>41.08446634492577</v>
       </c>
       <c r="F170" t="n">
         <v>757704</v>
@@ -3832,16 +3832,16 @@
         <v>44400</v>
       </c>
       <c r="B171" t="n">
-        <v>40.56538772583008</v>
+        <v>40.56539154052734</v>
       </c>
       <c r="C171" t="n">
-        <v>40.86337994162768</v>
+        <v>40.8633837843476</v>
       </c>
       <c r="D171" t="n">
-        <v>40.20010404382616</v>
+        <v>40.20010782417279</v>
       </c>
       <c r="E171" t="n">
-        <v>40.6230629132279</v>
+        <v>40.62306673334884</v>
       </c>
       <c r="F171" t="n">
         <v>715496</v>
@@ -3872,16 +3872,16 @@
         <v>44404</v>
       </c>
       <c r="B173" t="n">
-        <v>38.54673004150391</v>
+        <v>38.54673385620117</v>
       </c>
       <c r="C173" t="n">
-        <v>40.84415499320262</v>
+        <v>40.84415903525979</v>
       </c>
       <c r="D173" t="n">
-        <v>38.32563807495276</v>
+        <v>38.32564186777011</v>
       </c>
       <c r="E173" t="n">
-        <v>40.62306302665147</v>
+        <v>40.62306704682872</v>
       </c>
       <c r="F173" t="n">
         <v>1543819</v>
@@ -3932,16 +3932,16 @@
         <v>44407</v>
       </c>
       <c r="B176" t="n">
-        <v>37.2105712890625</v>
+        <v>37.21057510375977</v>
       </c>
       <c r="C176" t="n">
-        <v>38.26796091589321</v>
+        <v>38.26796483899034</v>
       </c>
       <c r="D176" t="n">
-        <v>36.33581974675896</v>
+        <v>36.33582347177977</v>
       </c>
       <c r="E176" t="n">
-        <v>37.5662386749276</v>
+        <v>37.56624252608663</v>
       </c>
       <c r="F176" t="n">
         <v>1168442</v>
@@ -3952,16 +3952,16 @@
         <v>44410</v>
       </c>
       <c r="B177" t="n">
-        <v>39.04658889770508</v>
+        <v>39.04659271240234</v>
       </c>
       <c r="C177" t="n">
-        <v>40.3442955992922</v>
+        <v>40.34429954077027</v>
       </c>
       <c r="D177" t="n">
-        <v>38.19106237864987</v>
+        <v>38.19106610976557</v>
       </c>
       <c r="E177" t="n">
-        <v>39.17155180323623</v>
+        <v>39.17155563014188</v>
       </c>
       <c r="F177" t="n">
         <v>3352028</v>
@@ -4052,16 +4052,16 @@
         <v>44417</v>
       </c>
       <c r="B182" t="n">
-        <v>37.10483169555664</v>
+        <v>37.10483551025391</v>
       </c>
       <c r="C182" t="n">
-        <v>37.44127403795907</v>
+        <v>37.44127788724551</v>
       </c>
       <c r="D182" t="n">
-        <v>35.94170042028153</v>
+        <v>35.94170411539885</v>
       </c>
       <c r="E182" t="n">
-        <v>36.1147297309109</v>
+        <v>36.11473344381713</v>
       </c>
       <c r="F182" t="n">
         <v>1206460</v>
@@ -4092,16 +4092,16 @@
         <v>44419</v>
       </c>
       <c r="B184" t="n">
-        <v>36.43194580078125</v>
+        <v>36.43194961547852</v>
       </c>
       <c r="C184" t="n">
-        <v>36.74916307008678</v>
+        <v>36.74916691799907</v>
       </c>
       <c r="D184" t="n">
-        <v>36.09550346955268</v>
+        <v>36.09550724902192</v>
       </c>
       <c r="E184" t="n">
-        <v>36.47039592462733</v>
+        <v>36.4703997433506</v>
       </c>
       <c r="F184" t="n">
         <v>786524</v>
@@ -4112,16 +4112,16 @@
         <v>44420</v>
       </c>
       <c r="B185" t="n">
-        <v>36.12434387207031</v>
+        <v>36.12434005737305</v>
       </c>
       <c r="C185" t="n">
-        <v>36.95103284178433</v>
+        <v>36.95102893978947</v>
       </c>
       <c r="D185" t="n">
-        <v>35.4706842206967</v>
+        <v>35.47068047502529</v>
       </c>
       <c r="E185" t="n">
-        <v>36.19163159403436</v>
+        <v>36.19162777223157</v>
       </c>
       <c r="F185" t="n">
         <v>689639</v>
@@ -4132,16 +4132,16 @@
         <v>44421</v>
       </c>
       <c r="B186" t="n">
-        <v>34.75934219360352</v>
+        <v>34.75934600830078</v>
       </c>
       <c r="C186" t="n">
-        <v>35.97053605946554</v>
+        <v>35.97054000708643</v>
       </c>
       <c r="D186" t="n">
-        <v>34.59592917071041</v>
+        <v>34.59593296747376</v>
       </c>
       <c r="E186" t="n">
-        <v>35.69177266747142</v>
+        <v>35.69177658449917</v>
       </c>
       <c r="F186" t="n">
         <v>915908</v>
@@ -4252,16 +4252,16 @@
         <v>44431</v>
       </c>
       <c r="B192" t="n">
-        <v>33.16364288330078</v>
+        <v>33.16364669799805</v>
       </c>
       <c r="C192" t="n">
-        <v>34.42289938524034</v>
+        <v>34.42290334478545</v>
       </c>
       <c r="D192" t="n">
-        <v>32.77913791079774</v>
+        <v>32.77914168126674</v>
       </c>
       <c r="E192" t="n">
-        <v>33.740402215843</v>
+        <v>33.74040609688286</v>
       </c>
       <c r="F192" t="n">
         <v>2084044</v>
@@ -4272,16 +4272,16 @@
         <v>44432</v>
       </c>
       <c r="B193" t="n">
-        <v>35.43223571777344</v>
+        <v>35.43223190307617</v>
       </c>
       <c r="C193" t="n">
-        <v>35.43223571777344</v>
+        <v>35.43223190307617</v>
       </c>
       <c r="D193" t="n">
-        <v>33.47125292620207</v>
+        <v>33.47124932262768</v>
       </c>
       <c r="E193" t="n">
-        <v>33.93266196453976</v>
+        <v>33.93265831128927</v>
       </c>
       <c r="F193" t="n">
         <v>1429663</v>
@@ -4332,16 +4332,16 @@
         <v>44435</v>
       </c>
       <c r="B196" t="n">
-        <v>36.43194580078125</v>
+        <v>36.43194961547852</v>
       </c>
       <c r="C196" t="n">
-        <v>36.66265029143312</v>
+        <v>36.66265413028687</v>
       </c>
       <c r="D196" t="n">
-        <v>35.02849754252244</v>
+        <v>35.02850121026817</v>
       </c>
       <c r="E196" t="n">
-        <v>35.75906113832411</v>
+        <v>35.75906488256532</v>
       </c>
       <c r="F196" t="n">
         <v>2701327</v>
@@ -4392,16 +4392,16 @@
         <v>44440</v>
       </c>
       <c r="B199" t="n">
-        <v>36.00899124145508</v>
+        <v>36.00899505615234</v>
       </c>
       <c r="C199" t="n">
-        <v>37.22979768253502</v>
+        <v>37.2298016265613</v>
       </c>
       <c r="D199" t="n">
-        <v>35.47068200422877</v>
+        <v>35.47068576189898</v>
       </c>
       <c r="E199" t="n">
-        <v>37.10483103054919</v>
+        <v>37.10483496133683</v>
       </c>
       <c r="F199" t="n">
         <v>1150659</v>
@@ -4712,16 +4712,16 @@
         <v>44463</v>
       </c>
       <c r="B215" t="n">
-        <v>34.54786682128906</v>
+        <v>34.54787063598633</v>
       </c>
       <c r="C215" t="n">
-        <v>35.65331911097231</v>
+        <v>35.65332304773112</v>
       </c>
       <c r="D215" t="n">
-        <v>33.88459095038866</v>
+        <v>33.88459469184851</v>
       </c>
       <c r="E215" t="n">
-        <v>34.46135404370111</v>
+        <v>34.46135784884584</v>
       </c>
       <c r="F215" t="n">
         <v>2639905</v>
@@ -4852,16 +4852,16 @@
         <v>44474</v>
       </c>
       <c r="B222" t="n">
-        <v>41.23827362060547</v>
+        <v>41.2382698059082</v>
       </c>
       <c r="C222" t="n">
-        <v>43.07428962557536</v>
+        <v>43.07428564103963</v>
       </c>
       <c r="D222" t="n">
-        <v>40.9498939275561</v>
+        <v>40.94989013953506</v>
       </c>
       <c r="E222" t="n">
-        <v>41.82464553821999</v>
+        <v>41.82464166928109</v>
       </c>
       <c r="F222" t="n">
         <v>3033780</v>
@@ -4952,16 +4952,16 @@
         <v>44482</v>
       </c>
       <c r="B227" t="n">
-        <v>39.66179656982422</v>
+        <v>39.66180038452148</v>
       </c>
       <c r="C227" t="n">
-        <v>40.05591407830239</v>
+        <v>40.05591793090613</v>
       </c>
       <c r="D227" t="n">
-        <v>38.88317033604628</v>
+        <v>38.88317407585477</v>
       </c>
       <c r="E227" t="n">
-        <v>39.43109208415942</v>
+        <v>39.43109587666738</v>
       </c>
       <c r="F227" t="n">
         <v>1130628</v>
@@ -5012,16 +5012,16 @@
         <v>44487</v>
       </c>
       <c r="B230" t="n">
-        <v>39.87327194213867</v>
+        <v>39.87327575683594</v>
       </c>
       <c r="C230" t="n">
-        <v>41.44974945917212</v>
+        <v>41.44975342469183</v>
       </c>
       <c r="D230" t="n">
-        <v>39.18116223800101</v>
+        <v>39.18116598648377</v>
       </c>
       <c r="E230" t="n">
-        <v>39.72908398193304</v>
+        <v>39.72908778283576</v>
       </c>
       <c r="F230" t="n">
         <v>2573169</v>
@@ -5032,16 +5032,16 @@
         <v>44488</v>
       </c>
       <c r="B231" t="n">
-        <v>37.58546447753906</v>
+        <v>37.58546829223633</v>
       </c>
       <c r="C231" t="n">
-        <v>40.08475250621378</v>
+        <v>40.08475657457366</v>
       </c>
       <c r="D231" t="n">
-        <v>36.86451716082918</v>
+        <v>36.86452090235465</v>
       </c>
       <c r="E231" t="n">
-        <v>39.57528087049455</v>
+        <v>39.57528488714614</v>
       </c>
       <c r="F231" t="n">
         <v>2915331</v>
@@ -5072,16 +5072,16 @@
         <v>44490</v>
       </c>
       <c r="B233" t="n">
-        <v>34.41328811645508</v>
+        <v>34.41329193115234</v>
       </c>
       <c r="C233" t="n">
-        <v>36.09550352264783</v>
+        <v>36.09550752381791</v>
       </c>
       <c r="D233" t="n">
-        <v>33.48086136908995</v>
+        <v>33.48086508042814</v>
       </c>
       <c r="E233" t="n">
-        <v>35.62448200968972</v>
+        <v>35.62448595864728</v>
       </c>
       <c r="F233" t="n">
         <v>3113087</v>
@@ -5092,16 +5092,16 @@
         <v>44491</v>
       </c>
       <c r="B234" t="n">
-        <v>32.63494873046875</v>
+        <v>32.63495254516602</v>
       </c>
       <c r="C234" t="n">
-        <v>34.06723464208851</v>
+        <v>34.06723862420559</v>
       </c>
       <c r="D234" t="n">
-        <v>31.04886231697067</v>
+        <v>31.04886594627039</v>
       </c>
       <c r="E234" t="n">
-        <v>33.63466698298016</v>
+        <v>33.63467091453443</v>
       </c>
       <c r="F234" t="n">
         <v>4894520</v>
@@ -5112,16 +5112,16 @@
         <v>44494</v>
       </c>
       <c r="B235" t="n">
-        <v>36.8470573425293</v>
+        <v>36.84706115722656</v>
       </c>
       <c r="C235" t="n">
-        <v>37.3112732591762</v>
+        <v>37.31127712193275</v>
       </c>
       <c r="D235" t="n">
-        <v>32.95925887799699</v>
+        <v>32.95926229019877</v>
       </c>
       <c r="E235" t="n">
-        <v>32.95925887799699</v>
+        <v>32.95926229019877</v>
       </c>
       <c r="F235" t="n">
         <v>3449995</v>
@@ -5152,16 +5152,16 @@
         <v>44496</v>
       </c>
       <c r="B237" t="n">
-        <v>35.29000854492188</v>
+        <v>35.29000473022461</v>
       </c>
       <c r="C237" t="n">
-        <v>36.07337184605893</v>
+        <v>36.07336794668348</v>
       </c>
       <c r="D237" t="n">
-        <v>34.47763151058894</v>
+        <v>34.47762778370612</v>
       </c>
       <c r="E237" t="n">
-        <v>36.07337184605893</v>
+        <v>36.07336794668348</v>
       </c>
       <c r="F237" t="n">
         <v>2270538</v>
@@ -5272,16 +5272,16 @@
         <v>44505</v>
       </c>
       <c r="B243" t="n">
-        <v>34.33255767822266</v>
+        <v>34.33256149291992</v>
       </c>
       <c r="C243" t="n">
-        <v>35.80257411368536</v>
+        <v>35.80257809171644</v>
       </c>
       <c r="D243" t="n">
-        <v>31.73102080869616</v>
+        <v>31.73102433433615</v>
       </c>
       <c r="E243" t="n">
-        <v>33.17202351532898</v>
+        <v>33.17202720107906</v>
       </c>
       <c r="F243" t="n">
         <v>9166770</v>
@@ -5312,16 +5312,16 @@
         <v>44509</v>
       </c>
       <c r="B245" t="n">
-        <v>34.50664138793945</v>
+        <v>34.50664520263672</v>
       </c>
       <c r="C245" t="n">
-        <v>35.1062534768846</v>
+        <v>35.10625735786877</v>
       </c>
       <c r="D245" t="n">
-        <v>32.63044017132788</v>
+        <v>32.63044377861175</v>
       </c>
       <c r="E245" t="n">
-        <v>33.89736055406007</v>
+        <v>33.89736430140155</v>
       </c>
       <c r="F245" t="n">
         <v>7032350</v>
@@ -5372,16 +5372,16 @@
         <v>44512</v>
       </c>
       <c r="B248" t="n">
-        <v>30.94766044616699</v>
+        <v>30.94766235351562</v>
       </c>
       <c r="C248" t="n">
-        <v>33.11399707089411</v>
+        <v>33.11399911175717</v>
       </c>
       <c r="D248" t="n">
-        <v>30.69620937113922</v>
+        <v>30.69621126299056</v>
       </c>
       <c r="E248" t="n">
-        <v>32.10819651835855</v>
+        <v>32.10819849723269</v>
       </c>
       <c r="F248" t="n">
         <v>3403064</v>
@@ -5552,16 +5552,16 @@
         <v>44526</v>
       </c>
       <c r="B257" t="n">
-        <v>26.69235801696777</v>
+        <v>26.69235992431641</v>
       </c>
       <c r="C257" t="n">
-        <v>27.61111551515892</v>
+        <v>27.61111748815896</v>
       </c>
       <c r="D257" t="n">
-        <v>25.85096734243463</v>
+        <v>25.85096918966023</v>
       </c>
       <c r="E257" t="n">
-        <v>26.59564620826666</v>
+        <v>26.59564810870458</v>
       </c>
       <c r="F257" t="n">
         <v>3664026</v>
@@ -5592,16 +5592,16 @@
         <v>44530</v>
       </c>
       <c r="B259" t="n">
-        <v>26.71169853210449</v>
+        <v>26.71170043945312</v>
       </c>
       <c r="C259" t="n">
-        <v>26.71169853210449</v>
+        <v>26.71170043945312</v>
       </c>
       <c r="D259" t="n">
-        <v>25.48346440355603</v>
+        <v>25.48346622320262</v>
       </c>
       <c r="E259" t="n">
-        <v>26.53761803066504</v>
+        <v>26.53761992558345</v>
       </c>
       <c r="F259" t="n">
         <v>4757647</v>
@@ -5612,16 +5612,16 @@
         <v>44531</v>
       </c>
       <c r="B260" t="n">
-        <v>26.69235801696777</v>
+        <v>26.69235992431641</v>
       </c>
       <c r="C260" t="n">
-        <v>28.01730398743094</v>
+        <v>28.01730598945588</v>
       </c>
       <c r="D260" t="n">
-        <v>26.32485389341864</v>
+        <v>26.32485577450663</v>
       </c>
       <c r="E260" t="n">
-        <v>27.17591518668557</v>
+        <v>27.17591712858762</v>
       </c>
       <c r="F260" t="n">
         <v>3467467</v>
@@ -5752,16 +5752,16 @@
         <v>44540</v>
       </c>
       <c r="B267" t="n">
-        <v>29.43896293640137</v>
+        <v>29.43896102905273</v>
       </c>
       <c r="C267" t="n">
-        <v>29.76778272429381</v>
+        <v>29.76778079564096</v>
       </c>
       <c r="D267" t="n">
-        <v>28.76198212238038</v>
+        <v>28.76198025889329</v>
       </c>
       <c r="E267" t="n">
-        <v>29.57435909920557</v>
+        <v>29.57435718308462</v>
       </c>
       <c r="F267" t="n">
         <v>1281952</v>
@@ -5832,16 +5832,16 @@
         <v>44546</v>
       </c>
       <c r="B271" t="n">
-        <v>30.62851333618164</v>
+        <v>30.62851524353027</v>
       </c>
       <c r="C271" t="n">
-        <v>30.86062130141829</v>
+        <v>30.86062322322113</v>
       </c>
       <c r="D271" t="n">
-        <v>29.25521052973079</v>
+        <v>29.25521235155887</v>
       </c>
       <c r="E271" t="n">
-        <v>29.4969891136642</v>
+        <v>29.49699095054871</v>
       </c>
       <c r="F271" t="n">
         <v>3477726</v>
@@ -5952,16 +5952,16 @@
         <v>44557</v>
       </c>
       <c r="B277" t="n">
-        <v>30.72522354125977</v>
+        <v>30.7252254486084</v>
       </c>
       <c r="C277" t="n">
-        <v>31.01535896880716</v>
+        <v>31.01536089416671</v>
       </c>
       <c r="D277" t="n">
-        <v>29.98054654550914</v>
+        <v>29.98054840663</v>
       </c>
       <c r="E277" t="n">
-        <v>29.98054654550914</v>
+        <v>29.98054840663</v>
       </c>
       <c r="F277" t="n">
         <v>1273927</v>
@@ -6132,16 +6132,16 @@
         <v>44571</v>
       </c>
       <c r="B286" t="n">
-        <v>33.37511444091797</v>
+        <v>33.37511825561523</v>
       </c>
       <c r="C286" t="n">
-        <v>33.89735778992546</v>
+        <v>33.89736166431392</v>
       </c>
       <c r="D286" t="n">
-        <v>32.24359030771443</v>
+        <v>32.24359399308115</v>
       </c>
       <c r="E286" t="n">
-        <v>32.37898645393302</v>
+        <v>32.3789901547752</v>
       </c>
       <c r="F286" t="n">
         <v>2829132</v>
@@ -6152,16 +6152,16 @@
         <v>44572</v>
       </c>
       <c r="B287" t="n">
-        <v>35.10625457763672</v>
+        <v>35.10625076293945</v>
       </c>
       <c r="C287" t="n">
-        <v>35.63816673084244</v>
+        <v>35.63816285834681</v>
       </c>
       <c r="D287" t="n">
-        <v>33.18169458570739</v>
+        <v>33.18169098013564</v>
       </c>
       <c r="E287" t="n">
-        <v>33.55886933935793</v>
+        <v>33.55886569280182</v>
       </c>
       <c r="F287" t="n">
         <v>3953735</v>
@@ -6172,16 +6172,16 @@
         <v>44573</v>
       </c>
       <c r="B288" t="n">
-        <v>34.89348983764648</v>
+        <v>34.89348602294922</v>
       </c>
       <c r="C288" t="n">
-        <v>35.98632787872025</v>
+        <v>35.98632394454952</v>
       </c>
       <c r="D288" t="n">
-        <v>34.13914032772324</v>
+        <v>34.13913659549451</v>
       </c>
       <c r="E288" t="n">
-        <v>35.34803329265463</v>
+        <v>35.34802942826484</v>
       </c>
       <c r="F288" t="n">
         <v>3302601</v>
@@ -6292,16 +6292,16 @@
         <v>44581</v>
       </c>
       <c r="B294" t="n">
-        <v>35.29967498779297</v>
+        <v>35.2996711730957</v>
       </c>
       <c r="C294" t="n">
-        <v>36.17007943172774</v>
+        <v>36.17007552296929</v>
       </c>
       <c r="D294" t="n">
-        <v>34.98052769103708</v>
+        <v>34.98052391082881</v>
       </c>
       <c r="E294" t="n">
-        <v>35.87027337331519</v>
+        <v>35.8702694969556</v>
       </c>
       <c r="F294" t="n">
         <v>3650414</v>
@@ -6332,16 +6332,16 @@
         <v>44585</v>
       </c>
       <c r="B296" t="n">
-        <v>34.35190200805664</v>
+        <v>34.35190582275391</v>
       </c>
       <c r="C296" t="n">
-        <v>35.3190162904272</v>
+        <v>35.31902021252021</v>
       </c>
       <c r="D296" t="n">
-        <v>34.05209598090971</v>
+        <v>34.05209976231423</v>
       </c>
       <c r="E296" t="n">
-        <v>34.23584709494806</v>
+        <v>34.2358508967577</v>
       </c>
       <c r="F296" t="n">
         <v>2113697</v>
@@ -6392,16 +6392,16 @@
         <v>44588</v>
       </c>
       <c r="B299" t="n">
-        <v>36.09271240234375</v>
+        <v>36.09270858764648</v>
       </c>
       <c r="C299" t="n">
-        <v>37.1081818022467</v>
+        <v>37.10817788022283</v>
       </c>
       <c r="D299" t="n">
-        <v>35.68652389286739</v>
+        <v>35.68652012110085</v>
       </c>
       <c r="E299" t="n">
-        <v>35.87994752798603</v>
+        <v>35.87994373577622</v>
       </c>
       <c r="F299" t="n">
         <v>3171460</v>
@@ -6492,16 +6492,16 @@
         <v>44595</v>
       </c>
       <c r="B304" t="n">
-        <v>35.29967498779297</v>
+        <v>35.2996711730957</v>
       </c>
       <c r="C304" t="n">
-        <v>35.58981230082171</v>
+        <v>35.58980845477045</v>
       </c>
       <c r="D304" t="n">
-        <v>33.84900341295216</v>
+        <v>33.84899975502328</v>
       </c>
       <c r="E304" t="n">
-        <v>34.98052769103708</v>
+        <v>34.98052391082881</v>
       </c>
       <c r="F304" t="n">
         <v>4177823</v>
@@ -6592,16 +6592,16 @@
         <v>44602</v>
       </c>
       <c r="B309" t="n">
-        <v>37.28226470947266</v>
+        <v>37.28226089477539</v>
       </c>
       <c r="C309" t="n">
-        <v>38.3847753224369</v>
+        <v>38.38477139493146</v>
       </c>
       <c r="D309" t="n">
-        <v>36.33449150769526</v>
+        <v>36.33448778997354</v>
       </c>
       <c r="E309" t="n">
-        <v>36.36350524073979</v>
+        <v>36.3635015200494</v>
       </c>
       <c r="F309" t="n">
         <v>7025951</v>
@@ -6612,16 +6612,16 @@
         <v>44603</v>
       </c>
       <c r="B310" t="n">
-        <v>38.07529067993164</v>
+        <v>38.07529449462891</v>
       </c>
       <c r="C310" t="n">
-        <v>38.49115162219439</v>
+        <v>38.49115547855604</v>
       </c>
       <c r="D310" t="n">
-        <v>37.37896869306991</v>
+        <v>37.37897243800389</v>
       </c>
       <c r="E310" t="n">
-        <v>37.78515714333515</v>
+        <v>37.78516092896444</v>
       </c>
       <c r="F310" t="n">
         <v>5486491</v>
@@ -6632,16 +6632,16 @@
         <v>44606</v>
       </c>
       <c r="B311" t="n">
-        <v>37.57239151000977</v>
+        <v>37.57239532470703</v>
       </c>
       <c r="C311" t="n">
-        <v>38.84898429079868</v>
+        <v>38.84898823510746</v>
       </c>
       <c r="D311" t="n">
-        <v>36.95343822941596</v>
+        <v>36.95344198127135</v>
       </c>
       <c r="E311" t="n">
-        <v>38.29772721003804</v>
+        <v>38.2977310983781</v>
       </c>
       <c r="F311" t="n">
         <v>3902640</v>
@@ -6652,16 +6652,16 @@
         <v>44607</v>
       </c>
       <c r="B312" t="n">
-        <v>35.79290008544922</v>
+        <v>35.79290390014648</v>
       </c>
       <c r="C312" t="n">
-        <v>36.65363192612031</v>
+        <v>36.65363583255173</v>
       </c>
       <c r="D312" t="n">
-        <v>35.63816270338088</v>
+        <v>35.63816650158672</v>
       </c>
       <c r="E312" t="n">
-        <v>36.55692199922141</v>
+        <v>36.55692589534578</v>
       </c>
       <c r="F312" t="n">
         <v>3810709</v>
@@ -6672,16 +6672,16 @@
         <v>44608</v>
       </c>
       <c r="B313" t="n">
-        <v>35.92830276489258</v>
+        <v>35.92829895019531</v>
       </c>
       <c r="C313" t="n">
-        <v>36.80837600146183</v>
+        <v>36.80837209332255</v>
       </c>
       <c r="D313" t="n">
-        <v>35.69619664958365</v>
+        <v>35.69619285953032</v>
       </c>
       <c r="E313" t="n">
-        <v>36.44087371532872</v>
+        <v>36.4408698462091</v>
       </c>
       <c r="F313" t="n">
         <v>4244663</v>
@@ -6692,16 +6692,16 @@
         <v>44609</v>
       </c>
       <c r="B314" t="n">
-        <v>35.29967498779297</v>
+        <v>35.2996711730957</v>
       </c>
       <c r="C314" t="n">
-        <v>35.89928710461807</v>
+        <v>35.89928322512308</v>
       </c>
       <c r="D314" t="n">
-        <v>34.41960179847439</v>
+        <v>34.41959807888318</v>
       </c>
       <c r="E314" t="n">
-        <v>35.68652224011414</v>
+        <v>35.68651838361181</v>
       </c>
       <c r="F314" t="n">
         <v>4430658</v>
@@ -6712,16 +6712,16 @@
         <v>44610</v>
       </c>
       <c r="B315" t="n">
-        <v>34.48730087280273</v>
+        <v>34.48729705810547</v>
       </c>
       <c r="C315" t="n">
-        <v>35.41572900804387</v>
+        <v>35.41572509065163</v>
       </c>
       <c r="D315" t="n">
-        <v>33.80064757961473</v>
+        <v>33.80064384086931</v>
       </c>
       <c r="E315" t="n">
-        <v>34.83546189196511</v>
+        <v>34.83545803875718</v>
       </c>
       <c r="F315" t="n">
         <v>4069741</v>
@@ -6852,16 +6852,16 @@
         <v>44623</v>
       </c>
       <c r="B322" t="n">
-        <v>37.34028625488281</v>
+        <v>37.34028244018555</v>
       </c>
       <c r="C322" t="n">
-        <v>37.88187465766974</v>
+        <v>37.88187078764361</v>
       </c>
       <c r="D322" t="n">
-        <v>36.31514815474819</v>
+        <v>36.31514444477941</v>
       </c>
       <c r="E322" t="n">
-        <v>37.12752138998924</v>
+        <v>37.12751759702811</v>
       </c>
       <c r="F322" t="n">
         <v>9786414</v>
@@ -6892,16 +6892,16 @@
         <v>44627</v>
       </c>
       <c r="B324" t="n">
-        <v>37.04048156738281</v>
+        <v>37.04048538208008</v>
       </c>
       <c r="C324" t="n">
-        <v>39.28418499781101</v>
+        <v>39.28418904358112</v>
       </c>
       <c r="D324" t="n">
-        <v>36.65363433916909</v>
+        <v>36.65363811402602</v>
       </c>
       <c r="E324" t="n">
-        <v>38.17200577495368</v>
+        <v>38.17200970618351</v>
       </c>
       <c r="F324" t="n">
         <v>5025922</v>
@@ -6952,16 +6952,16 @@
         <v>44630</v>
       </c>
       <c r="B327" t="n">
-        <v>35.7252082824707</v>
+        <v>35.72520446777344</v>
       </c>
       <c r="C327" t="n">
-        <v>37.22423481932497</v>
+        <v>37.22423084456335</v>
       </c>
       <c r="D327" t="n">
-        <v>35.51244341905014</v>
+        <v>35.51243962707166</v>
       </c>
       <c r="E327" t="n">
-        <v>36.75034637550812</v>
+        <v>36.75034245134777</v>
       </c>
       <c r="F327" t="n">
         <v>4502679</v>
@@ -7032,16 +7032,16 @@
         <v>44636</v>
       </c>
       <c r="B331" t="n">
-        <v>32.84320449829102</v>
+        <v>32.84320831298828</v>
       </c>
       <c r="C331" t="n">
-        <v>34.44861337459189</v>
+        <v>34.44861737575539</v>
       </c>
       <c r="D331" t="n">
-        <v>32.34030609979657</v>
+        <v>32.34030985608281</v>
       </c>
       <c r="E331" t="n">
-        <v>34.10045236831488</v>
+        <v>34.10045632903992</v>
       </c>
       <c r="F331" t="n">
         <v>3899288</v>
@@ -7092,16 +7092,16 @@
         <v>44641</v>
       </c>
       <c r="B334" t="n">
-        <v>36.61494827270508</v>
+        <v>36.61495208740234</v>
       </c>
       <c r="C334" t="n">
-        <v>36.86639934686866</v>
+        <v>36.86640318776314</v>
       </c>
       <c r="D334" t="n">
-        <v>35.88961252740777</v>
+        <v>35.88961626653654</v>
       </c>
       <c r="E334" t="n">
-        <v>35.97665371626157</v>
+        <v>35.97665746445866</v>
       </c>
       <c r="F334" t="n">
         <v>3600944</v>
@@ -7212,16 +7212,16 @@
         <v>44649</v>
       </c>
       <c r="B340" t="n">
-        <v>40.11590194702148</v>
+        <v>40.11590576171875</v>
       </c>
       <c r="C340" t="n">
-        <v>40.60913158587444</v>
+        <v>40.60913544747385</v>
       </c>
       <c r="D340" t="n">
-        <v>37.81417112752509</v>
+        <v>37.8141747233464</v>
       </c>
       <c r="E340" t="n">
-        <v>38.00759473575618</v>
+        <v>38.00759834997051</v>
       </c>
       <c r="F340" t="n">
         <v>6952609</v>
@@ -7252,16 +7252,16 @@
         <v>44651</v>
       </c>
       <c r="B342" t="n">
-        <v>40.47373962402344</v>
+        <v>40.47373580932617</v>
       </c>
       <c r="C342" t="n">
-        <v>41.13137921056172</v>
+        <v>41.13137533388116</v>
       </c>
       <c r="D342" t="n">
-        <v>39.67103512697872</v>
+        <v>39.6710313879373</v>
       </c>
       <c r="E342" t="n">
-        <v>40.135251085266</v>
+        <v>40.13524730247168</v>
       </c>
       <c r="F342" t="n">
         <v>3810811</v>
@@ -7312,16 +7312,16 @@
         <v>44656</v>
       </c>
       <c r="B345" t="n">
-        <v>41.97276306152344</v>
+        <v>41.9727668762207</v>
       </c>
       <c r="C345" t="n">
-        <v>43.03659106395681</v>
+        <v>43.03659497534015</v>
       </c>
       <c r="D345" t="n">
-        <v>41.57624708903781</v>
+        <v>41.5762508676977</v>
       </c>
       <c r="E345" t="n">
-        <v>42.30158283032514</v>
+        <v>42.30158667490721</v>
       </c>
       <c r="F345" t="n">
         <v>5903074</v>
@@ -7432,16 +7432,16 @@
         <v>44664</v>
       </c>
       <c r="B351" t="n">
-        <v>43.62652969360352</v>
+        <v>43.62653350830078</v>
       </c>
       <c r="C351" t="n">
-        <v>43.71356713249195</v>
+        <v>43.71357095479976</v>
       </c>
       <c r="D351" t="n">
-        <v>42.8431665105797</v>
+        <v>42.8431702567798</v>
       </c>
       <c r="E351" t="n">
-        <v>43.30738242414481</v>
+        <v>43.30738621093589</v>
       </c>
       <c r="F351" t="n">
         <v>3238402</v>
@@ -7452,16 +7452,16 @@
         <v>44665</v>
       </c>
       <c r="B352" t="n">
-        <v>42.93988037109375</v>
+        <v>42.93987655639648</v>
       </c>
       <c r="C352" t="n">
-        <v>43.62653368593358</v>
+        <v>43.62652981023535</v>
       </c>
       <c r="D352" t="n">
-        <v>42.2242170723533</v>
+        <v>42.2242133212342</v>
       </c>
       <c r="E352" t="n">
-        <v>43.62653368593358</v>
+        <v>43.62652981023535</v>
       </c>
       <c r="F352" t="n">
         <v>2345809</v>
@@ -7552,16 +7552,16 @@
         <v>44676</v>
       </c>
       <c r="B357" t="n">
-        <v>41.94375228881836</v>
+        <v>41.94374847412109</v>
       </c>
       <c r="C357" t="n">
-        <v>42.40796824528748</v>
+        <v>42.40796438837074</v>
       </c>
       <c r="D357" t="n">
-        <v>40.64782185452133</v>
+        <v>40.64781815768625</v>
       </c>
       <c r="E357" t="n">
-        <v>40.75420428750637</v>
+        <v>40.75420058099602</v>
       </c>
       <c r="F357" t="n">
         <v>3287465</v>
@@ -7592,16 +7592,16 @@
         <v>44678</v>
       </c>
       <c r="B359" t="n">
-        <v>42.16618728637695</v>
+        <v>42.16619110107422</v>
       </c>
       <c r="C359" t="n">
-        <v>43.58784506009413</v>
+        <v>43.58784900340616</v>
       </c>
       <c r="D359" t="n">
-        <v>41.46986526445734</v>
+        <v>41.46986901615963</v>
       </c>
       <c r="E359" t="n">
-        <v>43.52014885542929</v>
+        <v>43.52015279261696</v>
       </c>
       <c r="F359" t="n">
         <v>3779727</v>
@@ -7672,16 +7672,16 @@
         <v>44684</v>
       </c>
       <c r="B363" t="n">
-        <v>42.12750244140625</v>
+        <v>42.12749862670898</v>
       </c>
       <c r="C363" t="n">
-        <v>42.54336341820335</v>
+        <v>42.54335956584936</v>
       </c>
       <c r="D363" t="n">
-        <v>41.25710175933607</v>
+        <v>41.25709802345466</v>
       </c>
       <c r="E363" t="n">
-        <v>42.54336341820335</v>
+        <v>42.54335956584936</v>
       </c>
       <c r="F363" t="n">
         <v>4458389</v>
@@ -7692,16 +7692,16 @@
         <v>44685</v>
       </c>
       <c r="B364" t="n">
-        <v>44.10041427612305</v>
+        <v>44.10041809082031</v>
       </c>
       <c r="C364" t="n">
-        <v>44.32285161417975</v>
+        <v>44.32285544811791</v>
       </c>
       <c r="D364" t="n">
-        <v>42.16618567842227</v>
+        <v>42.16618932580826</v>
       </c>
       <c r="E364" t="n">
-        <v>43.04625879095802</v>
+        <v>43.04626251447057</v>
       </c>
       <c r="F364" t="n">
         <v>5759540</v>
@@ -7712,16 +7712,16 @@
         <v>44686</v>
       </c>
       <c r="B365" t="n">
-        <v>42.92053985595703</v>
+        <v>42.92053604125977</v>
       </c>
       <c r="C365" t="n">
-        <v>44.57430384010176</v>
+        <v>44.57429987842104</v>
       </c>
       <c r="D365" t="n">
-        <v>42.01145291457887</v>
+        <v>42.01144918067956</v>
       </c>
       <c r="E365" t="n">
-        <v>44.09074663744735</v>
+        <v>44.09074271874429</v>
       </c>
       <c r="F365" t="n">
         <v>4814532</v>
@@ -7732,16 +7732,16 @@
         <v>44687</v>
       </c>
       <c r="B366" t="n">
-        <v>42.55303573608398</v>
+        <v>42.55303192138672</v>
       </c>
       <c r="C366" t="n">
-        <v>43.90699359626386</v>
+        <v>43.90698966019007</v>
       </c>
       <c r="D366" t="n">
-        <v>41.82769996355259</v>
+        <v>41.82769621387857</v>
       </c>
       <c r="E366" t="n">
-        <v>43.33639522245434</v>
+        <v>43.33639133753226</v>
       </c>
       <c r="F366" t="n">
         <v>4093307</v>
@@ -7892,16 +7892,16 @@
         <v>44699</v>
       </c>
       <c r="B374" t="n">
-        <v>39.99985504150391</v>
+        <v>39.99985122680664</v>
       </c>
       <c r="C374" t="n">
-        <v>42.22421740419406</v>
+        <v>42.2242133773643</v>
       </c>
       <c r="D374" t="n">
-        <v>39.72906271064676</v>
+        <v>39.72905892177436</v>
       </c>
       <c r="E374" t="n">
-        <v>42.13717620908088</v>
+        <v>42.13717219055205</v>
       </c>
       <c r="F374" t="n">
         <v>1865839</v>
@@ -7952,16 +7952,16 @@
         <v>44704</v>
       </c>
       <c r="B377" t="n">
-        <v>42.28224563598633</v>
+        <v>42.28224182128906</v>
       </c>
       <c r="C377" t="n">
-        <v>42.79481657531103</v>
+        <v>42.7948127143697</v>
       </c>
       <c r="D377" t="n">
-        <v>41.35381369972519</v>
+        <v>41.3538099687909</v>
       </c>
       <c r="E377" t="n">
-        <v>41.42151365745766</v>
+        <v>41.42150992041549</v>
       </c>
       <c r="F377" t="n">
         <v>3400119</v>
@@ -8012,16 +8012,16 @@
         <v>44707</v>
       </c>
       <c r="B380" t="n">
-        <v>46.5955696105957</v>
+        <v>46.59557342529297</v>
       </c>
       <c r="C380" t="n">
-        <v>47.1661679572728</v>
+        <v>47.16617181868395</v>
       </c>
       <c r="D380" t="n">
-        <v>45.10621566046026</v>
+        <v>45.10621935322675</v>
       </c>
       <c r="E380" t="n">
-        <v>45.2512805595232</v>
+        <v>45.25128426416589</v>
       </c>
       <c r="F380" t="n">
         <v>4582217</v>
@@ -8072,16 +8072,16 @@
         <v>44712</v>
       </c>
       <c r="B383" t="n">
-        <v>47.14682769775391</v>
+        <v>47.14683151245117</v>
       </c>
       <c r="C383" t="n">
-        <v>49.5452685563496</v>
+        <v>49.54527256510714</v>
       </c>
       <c r="D383" t="n">
-        <v>47.11781396782467</v>
+        <v>47.11781778017441</v>
       </c>
       <c r="E383" t="n">
-        <v>48.22032446240879</v>
+        <v>48.22032836396376</v>
       </c>
       <c r="F383" t="n">
         <v>6322705</v>
@@ -8152,16 +8152,16 @@
         <v>44718</v>
       </c>
       <c r="B387" t="n">
-        <v>45.3189811706543</v>
+        <v>45.31898498535156</v>
       </c>
       <c r="C387" t="n">
-        <v>47.4563021942838</v>
+        <v>47.45630618888874</v>
       </c>
       <c r="D387" t="n">
-        <v>45.13522629971035</v>
+        <v>45.13523009894016</v>
       </c>
       <c r="E387" t="n">
-        <v>47.15649615191405</v>
+        <v>47.156500121283</v>
       </c>
       <c r="F387" t="n">
         <v>1711233</v>
@@ -8172,16 +8172,16 @@
         <v>44719</v>
       </c>
       <c r="B388" t="n">
-        <v>45.3189811706543</v>
+        <v>45.31898498535156</v>
       </c>
       <c r="C388" t="n">
-        <v>45.84122081100923</v>
+        <v>45.84122466966569</v>
       </c>
       <c r="D388" t="n">
-        <v>44.73871032322317</v>
+        <v>44.73871408907649</v>
       </c>
       <c r="E388" t="n">
-        <v>44.98048890609225</v>
+        <v>44.98049269229714</v>
       </c>
       <c r="F388" t="n">
         <v>1887578</v>
@@ -8192,16 +8192,16 @@
         <v>44720</v>
       </c>
       <c r="B389" t="n">
-        <v>45.25128555297852</v>
+        <v>45.25128173828125</v>
       </c>
       <c r="C389" t="n">
-        <v>46.00563510358936</v>
+        <v>46.00563122530019</v>
       </c>
       <c r="D389" t="n">
-        <v>44.92246574936335</v>
+        <v>44.9224619623857</v>
       </c>
       <c r="E389" t="n">
-        <v>45.31898551140559</v>
+        <v>45.31898169100119</v>
       </c>
       <c r="F389" t="n">
         <v>1920490</v>
@@ -8212,16 +8212,16 @@
         <v>44721</v>
       </c>
       <c r="B390" t="n">
-        <v>44.5066032409668</v>
+        <v>44.50660705566406</v>
       </c>
       <c r="C390" t="n">
-        <v>45.59944121195702</v>
+        <v>45.59944512032232</v>
       </c>
       <c r="D390" t="n">
-        <v>44.32285212169327</v>
+        <v>44.32285592064108</v>
       </c>
       <c r="E390" t="n">
-        <v>45.22226648118356</v>
+        <v>45.2222703572209</v>
       </c>
       <c r="F390" t="n">
         <v>1644697</v>
@@ -8472,16 +8472,16 @@
         <v>44741</v>
       </c>
       <c r="B403" t="n">
-        <v>34.71940612792969</v>
+        <v>34.71940994262695</v>
       </c>
       <c r="C403" t="n">
-        <v>35.41572814937177</v>
+        <v>35.41573204057546</v>
       </c>
       <c r="D403" t="n">
-        <v>34.09078031110602</v>
+        <v>34.0907840567348</v>
       </c>
       <c r="E403" t="n">
-        <v>35.29967322993957</v>
+        <v>35.29967710839206</v>
       </c>
       <c r="F403" t="n">
         <v>2690880</v>
@@ -8532,16 +8532,16 @@
         <v>44746</v>
       </c>
       <c r="B406" t="n">
-        <v>35.08691024780273</v>
+        <v>35.08690643310547</v>
       </c>
       <c r="C406" t="n">
-        <v>35.60915366553204</v>
+        <v>35.60914979405575</v>
       </c>
       <c r="D406" t="n">
-        <v>34.1971683099429</v>
+        <v>34.19716459197961</v>
       </c>
       <c r="E406" t="n">
-        <v>34.57433932306729</v>
+        <v>34.57433556409744</v>
       </c>
       <c r="F406" t="n">
         <v>2359523</v>
@@ -8612,16 +8612,16 @@
         <v>44750</v>
       </c>
       <c r="B410" t="n">
-        <v>31.81806373596191</v>
+        <v>31.81806564331055</v>
       </c>
       <c r="C410" t="n">
-        <v>32.48537204040704</v>
+        <v>32.48537398775778</v>
       </c>
       <c r="D410" t="n">
-        <v>31.19911039968697</v>
+        <v>31.19911226993215</v>
       </c>
       <c r="E410" t="n">
-        <v>31.3151653213559</v>
+        <v>31.31516719855805</v>
       </c>
       <c r="F410" t="n">
         <v>4375906</v>
@@ -8712,16 +8712,16 @@
         <v>44757</v>
       </c>
       <c r="B415" t="n">
-        <v>27.79486846923828</v>
+        <v>27.79486656188965</v>
       </c>
       <c r="C415" t="n">
-        <v>29.07146143004599</v>
+        <v>29.07145943509457</v>
       </c>
       <c r="D415" t="n">
-        <v>27.79486846923828</v>
+        <v>27.79486656188965</v>
       </c>
       <c r="E415" t="n">
-        <v>29.06178893688788</v>
+        <v>29.06178694260021</v>
       </c>
       <c r="F415" t="n">
         <v>4618481</v>
@@ -8752,16 +8752,16 @@
         <v>44761</v>
       </c>
       <c r="B417" t="n">
-        <v>29.43896293640137</v>
+        <v>29.43896102905273</v>
       </c>
       <c r="C417" t="n">
-        <v>29.53567474894549</v>
+        <v>29.5356728353309</v>
       </c>
       <c r="D417" t="n">
-        <v>28.11401691328927</v>
+        <v>28.11401509178381</v>
       </c>
       <c r="E417" t="n">
-        <v>28.14303064443129</v>
+        <v>28.14302882104603</v>
       </c>
       <c r="F417" t="n">
         <v>4570230</v>
@@ -8772,16 +8772,16 @@
         <v>44762</v>
       </c>
       <c r="B418" t="n">
-        <v>30.59950065612793</v>
+        <v>30.5994987487793</v>
       </c>
       <c r="C418" t="n">
-        <v>30.97667540990739</v>
+        <v>30.97667347904845</v>
       </c>
       <c r="D418" t="n">
-        <v>29.21652718353251</v>
+        <v>29.21652536238831</v>
       </c>
       <c r="E418" t="n">
-        <v>29.21652718353251</v>
+        <v>29.21652536238831</v>
       </c>
       <c r="F418" t="n">
         <v>5027446</v>
@@ -8792,16 +8792,16 @@
         <v>44763</v>
       </c>
       <c r="B419" t="n">
-        <v>29.44863510131836</v>
+        <v>29.44863319396973</v>
       </c>
       <c r="C419" t="n">
-        <v>29.86449233042948</v>
+        <v>29.86449039614633</v>
       </c>
       <c r="D419" t="n">
-        <v>28.83935237548546</v>
+        <v>28.83935050759925</v>
       </c>
       <c r="E419" t="n">
-        <v>29.86449233042948</v>
+        <v>29.86449039614633</v>
       </c>
       <c r="F419" t="n">
         <v>5437325</v>
@@ -8832,16 +8832,16 @@
         <v>44767</v>
       </c>
       <c r="B421" t="n">
-        <v>29.2648811340332</v>
+        <v>29.26488304138184</v>
       </c>
       <c r="C421" t="n">
-        <v>29.7194245717984</v>
+        <v>29.71942650877206</v>
       </c>
       <c r="D421" t="n">
-        <v>28.43316295561438</v>
+        <v>28.43316480875549</v>
       </c>
       <c r="E421" t="n">
-        <v>28.87803577468757</v>
+        <v>28.87803765682343</v>
       </c>
       <c r="F421" t="n">
         <v>3521914</v>
@@ -8852,16 +8852,16 @@
         <v>44768</v>
       </c>
       <c r="B422" t="n">
-        <v>28.95540428161621</v>
+        <v>28.95540618896484</v>
       </c>
       <c r="C422" t="n">
-        <v>30.15462657412001</v>
+        <v>30.15462856046375</v>
       </c>
       <c r="D422" t="n">
-        <v>28.81033750703789</v>
+        <v>28.81033940483069</v>
       </c>
       <c r="E422" t="n">
-        <v>29.88383426222034</v>
+        <v>29.88383623072646</v>
       <